--- a/posts.xlsx
+++ b/posts.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C811"/>
+  <dimension ref="A1:C810"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -12704,28 +12704,6 @@
     <row r="585">
       <c r="A585" t="inlineStr">
         <is>
-          <t xml:space="preserve">「あまり考えるな。疲れるよ」
-لا تفكر كثيرا. ستتعب كثيرا
-[laa tu-fakkir kaThiiran. sa-ta-t*abu kaThiiran]
-⁦「考えるな」[laa tu-fakkir]：「くたびれた」( تعب )[ta*iba]⁩
-考える（かんがえる）・疲れる（つかれる）
-2109 WORDSBEFORELEAVING tumblr </t>
-        </is>
-      </c>
-      <c r="B585" t="inlineStr">
-        <is>
-          <t>images/「あまり考えるな。疲れるよ」_img1.jpg</t>
-        </is>
-      </c>
-      <c r="C585" t="inlineStr">
-        <is>
-          <t>健康 ,気楽</t>
-        </is>
-      </c>
-    </row>
-    <row r="586">
-      <c r="A586" t="inlineStr">
-        <is>
           <t xml:space="preserve">「美しい時は作るもの。待つものではない」
 اصنع اللحظات الجميلة. لا تنتظرها
 [i_sna*i ^laHa_Dhaati l-jamiila. laa ta-nta_Dhir-haa]
@@ -12733,19 +12711,19 @@
 2308 abojamal.tumblr com </t>
         </is>
       </c>
-      <c r="B586" t="inlineStr">
+      <c r="B585" t="inlineStr">
         <is>
           <t>images/「美しい時は作るもの。待つものではない_img1.jpg</t>
         </is>
       </c>
-      <c r="C586" t="inlineStr">
+      <c r="C585" t="inlineStr">
         <is>
           <t>おうち時間</t>
         </is>
       </c>
     </row>
-    <row r="587">
-      <c r="A587" t="inlineStr">
+    <row r="586">
+      <c r="A586" t="inlineStr">
         <is>
           <t xml:space="preserve">「大切な時間を大切じゃないことに使わないこと」
 لا تضيع الوقت المهم في شيء غير مهم
@@ -12754,19 +12732,19 @@
 2308 Anwar_122_ </t>
         </is>
       </c>
-      <c r="B587" t="inlineStr">
+      <c r="B586" t="inlineStr">
         <is>
           <t>images/「大切な時間を大切じゃないことに使わな_img1.jpg</t>
         </is>
       </c>
-      <c r="C587" t="inlineStr">
+      <c r="C586" t="inlineStr">
         <is>
           <t>時間 ,貴重</t>
         </is>
       </c>
     </row>
-    <row r="588">
-      <c r="A588" t="inlineStr">
+    <row r="587">
+      <c r="A587" t="inlineStr">
         <is>
           <t xml:space="preserve">「このイノセントな目に騙されるな…」
 لا تنخدع بهذه العيون البريئة
@@ -12776,19 +12754,19 @@
 2201 https://twitter.com/NatGeoMagArab/status/1475715760202797056 </t>
         </is>
       </c>
-      <c r="B588" t="inlineStr">
+      <c r="B587" t="inlineStr">
         <is>
           <t>images/「このイノセントな目に騙されるな…」.png</t>
         </is>
       </c>
-      <c r="C588" t="inlineStr">
+      <c r="C587" t="inlineStr">
         <is>
           <t>がうがう ,カワイイ</t>
         </is>
       </c>
     </row>
-    <row r="589">
-      <c r="A589" t="inlineStr">
+    <row r="588">
+      <c r="A588" t="inlineStr">
         <is>
           <t xml:space="preserve">⁦「カメラを止めろ！」⁩
 أوقفوا التّصوير
@@ -12798,19 +12776,19 @@
 2509 alsalwabooks com </t>
         </is>
       </c>
-      <c r="B589" t="inlineStr">
+      <c r="B588" t="inlineStr">
         <is>
           <t>images/⁦「カメラを止めろ！」⁩_img1.jpg</t>
         </is>
       </c>
-      <c r="C589" t="inlineStr">
+      <c r="C588" t="inlineStr">
         <is>
           <t>絵本 ,撮影</t>
         </is>
       </c>
     </row>
-    <row r="590">
-      <c r="A590" t="inlineStr">
+    <row r="589">
+      <c r="A589" t="inlineStr">
         <is>
           <t xml:space="preserve">「話す前に考えなさい」
 فكر قبل ان تتكلم
@@ -12820,19 +12798,19 @@
 2308 Islamuna YouTube </t>
         </is>
       </c>
-      <c r="B590" t="inlineStr">
+      <c r="B589" t="inlineStr">
         <is>
           <t>images/「話す前に考えなさい」_img1.jpg</t>
         </is>
       </c>
-      <c r="C590" t="inlineStr">
+      <c r="C589" t="inlineStr">
         <is>
           <t>失言 ,発言</t>
         </is>
       </c>
     </row>
-    <row r="591">
-      <c r="A591" t="inlineStr">
+    <row r="590">
+      <c r="A590" t="inlineStr">
         <is>
           <t xml:space="preserve">「ツイッターでフォローして下さい」
 تابعونا على تويتر
@@ -12842,19 +12820,19 @@
 2109 出典不明 </t>
         </is>
       </c>
-      <c r="B591" t="inlineStr">
+      <c r="B590" t="inlineStr">
         <is>
           <t>images/「ツイッターでフォローして下さい」_img1.jpg</t>
         </is>
       </c>
-      <c r="C591" t="inlineStr">
+      <c r="C590" t="inlineStr">
         <is>
           <t>FollowUs ,バナー</t>
         </is>
       </c>
     </row>
-    <row r="592">
-      <c r="A592" t="inlineStr">
+    <row r="591">
+      <c r="A591" t="inlineStr">
         <is>
           <t xml:space="preserve">「敵を倒せ」دمّر العدو
 ダンミリ_ルアドゥーウ [dammiri l-*aduuw]
@@ -12863,19 +12841,19 @@
 2308 apkpure com </t>
         </is>
       </c>
-      <c r="B592" t="inlineStr">
+      <c r="B591" t="inlineStr">
         <is>
           <t>images/「敵を倒せ」_img1.jpg</t>
         </is>
       </c>
-      <c r="C592" t="inlineStr">
+      <c r="C591" t="inlineStr">
         <is>
           <t>ゲーム ,パンダ</t>
         </is>
       </c>
     </row>
-    <row r="593">
-      <c r="A593" t="inlineStr">
+    <row r="592">
+      <c r="A592" t="inlineStr">
         <is>
           <t xml:space="preserve">「咲け。蒔かれたらどこであろうと」
 أزهر أيْنمَا زرعت
@@ -12884,19 +12862,19 @@
 2407 Ahmed Madyan </t>
         </is>
       </c>
-      <c r="B593" t="inlineStr">
+      <c r="B592" t="inlineStr">
         <is>
           <t>images/「咲け。蒔かれたらどこであろうと」_img1.jpg</t>
         </is>
       </c>
-      <c r="C593" t="inlineStr">
+      <c r="C592" t="inlineStr">
         <is>
           <t>環境のせいにしない ,花</t>
         </is>
       </c>
     </row>
-    <row r="594">
-      <c r="A594" t="inlineStr">
+    <row r="593">
+      <c r="A593" t="inlineStr">
         <is>
           <t xml:space="preserve">「頭を働かせろ」شغل مخك
 シャッギル・ムッハク [Sha^Ghil mu^Kha-k]
@@ -12905,19 +12883,19 @@
 2103 facebook elpage </t>
         </is>
       </c>
-      <c r="B594" t="inlineStr">
+      <c r="B593" t="inlineStr">
         <is>
           <t>images/「頭を働かせろ」_img1.jpg</t>
         </is>
       </c>
-      <c r="C594" t="inlineStr">
+      <c r="C593" t="inlineStr">
         <is>
           <t>電源 ,頭脳</t>
         </is>
       </c>
     </row>
-    <row r="595">
-      <c r="A595" t="inlineStr">
+    <row r="594">
+      <c r="A594" t="inlineStr">
         <is>
           <t xml:space="preserve">「傷跡は星にかえなさい」
 حوّل نُدوبكَ إلى نُجومْ
@@ -12927,19 +12905,19 @@
 2107 saramj1992 Instagram </t>
         </is>
       </c>
-      <c r="B595" t="inlineStr">
+      <c r="B594" t="inlineStr">
         <is>
           <t>images/「傷跡は星にかえなさい」_img1.jpg</t>
         </is>
       </c>
-      <c r="C595" t="inlineStr">
+      <c r="C594" t="inlineStr">
         <is>
           <t>勲章 ,証</t>
         </is>
       </c>
     </row>
-    <row r="596">
-      <c r="A596" t="inlineStr">
+    <row r="595">
+      <c r="A595" t="inlineStr">
         <is>
           <t xml:space="preserve">「あなたの主の栄光を誉め称え、また（御赦しを請え。本当にかれは、度々赦される御方である）」
 فسَبِّح بحمد ربك و
@@ -12948,19 +12926,19 @@
 2109 出典不明 </t>
         </is>
       </c>
-      <c r="B596" t="inlineStr">
+      <c r="B595" t="inlineStr">
         <is>
           <t>images/「あなたの主の栄光を誉め称え、また（御_img1.jpg</t>
         </is>
       </c>
-      <c r="C596" t="inlineStr">
+      <c r="C595" t="inlineStr">
         <is>
           <t>イスラム教 ,カリグラフィー</t>
         </is>
       </c>
     </row>
-    <row r="597">
-      <c r="A597" t="inlineStr">
+    <row r="596">
+      <c r="A596" t="inlineStr">
         <is>
           <t xml:space="preserve">「誰かを幸福にしなさい」
 أسْعِد أحدهم
@@ -12970,19 +12948,19 @@
 1810 in4sser.tumblr </t>
         </is>
       </c>
-      <c r="B597" t="inlineStr">
+      <c r="B596" t="inlineStr">
         <is>
           <t>images/「誰かを幸福にしなさい」_img1.jpg</t>
         </is>
       </c>
-      <c r="C597" t="inlineStr">
+      <c r="C596" t="inlineStr">
         <is>
           <t>人生 ,happy</t>
         </is>
       </c>
     </row>
-    <row r="598">
-      <c r="A598" t="inlineStr">
+    <row r="597">
+      <c r="A597" t="inlineStr">
         <is>
           <t xml:space="preserve">「見よ」أبْصِرْ
 アブスィル ['ab_sir]
@@ -12991,19 +12969,19 @@
 1811 Ruh Al-Alam, via Behance </t>
         </is>
       </c>
-      <c r="B598" t="inlineStr">
+      <c r="B597" t="inlineStr">
         <is>
           <t>images/「見よ」_img1.jpg</t>
         </is>
       </c>
-      <c r="C598" t="inlineStr">
+      <c r="C597" t="inlineStr">
         <is>
           <t>目 ,瞳</t>
         </is>
       </c>
     </row>
-    <row r="599">
-      <c r="A599" t="inlineStr">
+    <row r="598">
+      <c r="A598" t="inlineStr">
         <is>
           <t xml:space="preserve">「言葉は口から出す前に味わいなさい」
 ‪تذوق كلماتك قبل أن تنطقها‬
@@ -13013,19 +12991,19 @@
 2109 Reham-des </t>
         </is>
       </c>
-      <c r="B599" t="inlineStr">
+      <c r="B598" t="inlineStr">
         <is>
           <t>images/「言葉は口から出す前に味わいなさい」_img1.jpg</t>
         </is>
       </c>
-      <c r="C599" t="inlineStr">
+      <c r="C598" t="inlineStr">
         <is>
           <t>言葉</t>
         </is>
       </c>
     </row>
-    <row r="600">
-      <c r="A600" t="inlineStr">
+    <row r="599">
+      <c r="A599" t="inlineStr">
         <is>
           <t xml:space="preserve">「テレビを観るのをやめて下さい」
 توقفي عن مشاهدة التلفاز
@@ -13035,19 +13013,19 @@
 1809 </t>
         </is>
       </c>
-      <c r="B600" t="inlineStr">
+      <c r="B599" t="inlineStr">
         <is>
           <t>images/「テレビを観るのをやめて下さい」_img1.jpg</t>
         </is>
       </c>
-      <c r="C600" t="inlineStr">
+      <c r="C599" t="inlineStr">
         <is>
           <t>あらびあや</t>
         </is>
       </c>
     </row>
-    <row r="601">
-      <c r="A601" t="inlineStr">
+    <row r="600">
+      <c r="A600" t="inlineStr">
         <is>
           <t xml:space="preserve">「言わぬが花」
 انْطِقْ جَمَالاً أو تجَمَّلْ بالسّكُوت
@@ -13057,19 +13035,19 @@
 2411 Ahmed Madyan </t>
         </is>
       </c>
-      <c r="B601" t="inlineStr">
+      <c r="B600" t="inlineStr">
         <is>
           <t>images/「言わぬが花」_img1.jpg</t>
         </is>
       </c>
-      <c r="C601" t="inlineStr">
+      <c r="C600" t="inlineStr">
         <is>
           <t>ことわざ ,デザイン</t>
         </is>
       </c>
     </row>
-    <row r="602">
-      <c r="A602" t="inlineStr">
+    <row r="601">
+      <c r="A601" t="inlineStr">
         <is>
           <t xml:space="preserve">「たくさん考えて、少し話すこと」
 فكّر كثيرا. تكلم قليلا
@@ -13079,19 +13057,19 @@
 2105 In49r </t>
         </is>
       </c>
-      <c r="B602" t="inlineStr">
+      <c r="B601" t="inlineStr">
         <is>
           <t>images/「たくさん考えて、少し話すこと」_img1.jpg</t>
         </is>
       </c>
-      <c r="C602" t="inlineStr">
+      <c r="C601" t="inlineStr">
         <is>
           <t>思慮 ,会話</t>
         </is>
       </c>
     </row>
-    <row r="603">
-      <c r="A603" t="inlineStr">
+    <row r="602">
+      <c r="A602" t="inlineStr">
         <is>
           <t xml:space="preserve">「子供たちよ、いつでも思い出すんだよ」
 تذكروا دوما يا أطفال
@@ -13101,19 +13079,19 @@
 1809 </t>
         </is>
       </c>
-      <c r="B603" t="inlineStr">
+      <c r="B602" t="inlineStr">
         <is>
           <t>images/「子供たちよ、いつでも思い出すんだよ」_img1.jpg</t>
         </is>
       </c>
-      <c r="C603" t="inlineStr">
+      <c r="C602" t="inlineStr">
         <is>
           <t>オープニング ,ハム太郎</t>
         </is>
       </c>
     </row>
-    <row r="604">
-      <c r="A604" t="inlineStr">
+    <row r="603">
+      <c r="A603" t="inlineStr">
         <is>
           <t xml:space="preserve">「分かってから話しなさい」
 تعلَّم ثمَّ تكلَّم
@@ -13123,19 +13101,19 @@
 1903 Hashem Al Shareef, Pinterest </t>
         </is>
       </c>
-      <c r="B604" t="inlineStr">
+      <c r="B603" t="inlineStr">
         <is>
           <t>images/「分かってから話しなさい」_img1.jpg</t>
         </is>
       </c>
-      <c r="C604" t="inlineStr">
+      <c r="C603" t="inlineStr">
         <is>
           <t>教訓 ,トーク</t>
         </is>
       </c>
     </row>
-    <row r="605">
-      <c r="A605" t="inlineStr">
+    <row r="604">
+      <c r="A604" t="inlineStr">
         <is>
           <t xml:space="preserve">「蟻に学べ」تعلم من النملة
 タアッラム・ミナ_ンナムラ [ta*allam mina ^namla]
@@ -13144,19 +13122,19 @@
 2308 fatakat com </t>
         </is>
       </c>
-      <c r="B605" t="inlineStr">
+      <c r="B604" t="inlineStr">
         <is>
           <t>images/「蟻に学べ」_img1.jpg</t>
         </is>
       </c>
-      <c r="C605" t="inlineStr">
+      <c r="C604" t="inlineStr">
         <is>
           <t>教訓 ,問題解決</t>
         </is>
       </c>
     </row>
-    <row r="606">
-      <c r="A606" t="inlineStr">
+    <row r="605">
+      <c r="A605" t="inlineStr">
         <is>
           <t xml:space="preserve">「自分と仲直りしよう、一杯の珈琲で！」
 تصالح مع نفسك بكوب قهوة
@@ -13166,19 +13144,19 @@
 2308 asm95_ </t>
         </is>
       </c>
-      <c r="B606" t="inlineStr">
+      <c r="B605" t="inlineStr">
         <is>
           <t>images/「自分と仲直りしよう、一杯の珈琲で！」_img1.jpg</t>
         </is>
       </c>
-      <c r="C606" t="inlineStr">
+      <c r="C605" t="inlineStr">
         <is>
           <t>一服 ,リラックス</t>
         </is>
       </c>
     </row>
-    <row r="607">
-      <c r="A607" t="inlineStr">
+    <row r="606">
+      <c r="A606" t="inlineStr">
         <is>
           <t xml:space="preserve">「気をつけて　ジュード」
 انتبهي يا جود
@@ -13188,19 +13166,19 @@
 2109 سلسلة الحلزونة </t>
         </is>
       </c>
-      <c r="B607" t="inlineStr">
+      <c r="B606" t="inlineStr">
         <is>
           <t>images/「気をつけて　ジュード」_img1.jpg</t>
         </is>
       </c>
-      <c r="C607" t="inlineStr">
+      <c r="C606" t="inlineStr">
         <is>
           <t>絵本 ,わんぱく</t>
         </is>
       </c>
     </row>
-    <row r="608">
-      <c r="A608" t="inlineStr">
+    <row r="607">
+      <c r="A607" t="inlineStr">
         <is>
           <t xml:space="preserve">「coming soon」
 انتظرونا قريبا
@@ -13209,19 +13187,19 @@
 2307 出典不明 </t>
         </is>
       </c>
-      <c r="B608" t="inlineStr">
+      <c r="B607" t="inlineStr">
         <is>
           <t>images/「coming soon」_img1.jpg</t>
         </is>
       </c>
-      <c r="C608" t="inlineStr">
+      <c r="C607" t="inlineStr">
         <is>
           <t>フレーズ ,カミングスーン</t>
         </is>
       </c>
     </row>
-    <row r="609">
-      <c r="A609" t="inlineStr">
+    <row r="608">
+      <c r="A608" t="inlineStr">
         <is>
           <t xml:space="preserve">「自分の胸に聞きなさい。それが全て知っています」
 استمع لقلبك.. إنه يعرف كل شيء
@@ -13230,19 +13208,19 @@
 1811 </t>
         </is>
       </c>
-      <c r="B609" t="inlineStr">
+      <c r="B608" t="inlineStr">
         <is>
           <t>images/「自分の胸に聞きなさい。それが全て知っ_img1.jpg</t>
         </is>
       </c>
-      <c r="C609" t="inlineStr">
+      <c r="C608" t="inlineStr">
         <is>
           <t>あらびあや</t>
         </is>
       </c>
     </row>
-    <row r="610">
-      <c r="A610" t="inlineStr">
+    <row r="609">
+      <c r="A609" t="inlineStr">
         <is>
           <t xml:space="preserve">「笑ってくれ、絶望を癒すのは君の笑みだから」
 ابتسمي فإن دواء اليأس بسمتك
@@ -13251,19 +13229,19 @@
 2308 arab-quotes tumblr </t>
         </is>
       </c>
-      <c r="B610" t="inlineStr">
+      <c r="B609" t="inlineStr">
         <is>
           <t>images/「笑ってくれ、絶望を癒すのは君の笑みだ_img1.jpg</t>
         </is>
       </c>
-      <c r="C610" t="inlineStr">
+      <c r="C609" t="inlineStr">
         <is>
           <t>癒し ,スマイル</t>
         </is>
       </c>
     </row>
-    <row r="611">
-      <c r="A611" t="inlineStr">
+    <row r="610">
+      <c r="A610" t="inlineStr">
         <is>
           <t xml:space="preserve">「自分を頼りなさい。宇宙で最も確かな物が自分だと思って。」
 استند على نفسك وكأنك أكثر الأشياء ثباتًا بهذا الكون
@@ -13271,19 +13249,19 @@
 2308 x_nourh.15 </t>
         </is>
       </c>
-      <c r="B611" t="inlineStr">
+      <c r="B610" t="inlineStr">
         <is>
           <t>images/「自分を頼りなさい。宇宙で最も確かな物_img1.jpg</t>
         </is>
       </c>
-      <c r="C611" t="inlineStr">
+      <c r="C610" t="inlineStr">
         <is>
           <t>自我 ,宇宙</t>
         </is>
       </c>
     </row>
-    <row r="612">
-      <c r="A612" t="inlineStr">
+    <row r="611">
+      <c r="A611" t="inlineStr">
         <is>
           <t xml:space="preserve">「古いデバイスを交換して新品をゲットしよう」
 استبدل جهازك القديم واحصل على واحد جديد
@@ -13292,19 +13270,19 @@
 2406 stc </t>
         </is>
       </c>
-      <c r="B612" t="inlineStr">
+      <c r="B611" t="inlineStr">
         <is>
           <t>images/「古いデバイスを交換して新品をゲットし_img1.jpg</t>
         </is>
       </c>
-      <c r="C612" t="inlineStr">
+      <c r="C611" t="inlineStr">
         <is>
           <t>キャンペーン ,下取り</t>
         </is>
       </c>
     </row>
-    <row r="613">
-      <c r="A613" t="inlineStr">
+    <row r="612">
+      <c r="A612" t="inlineStr">
         <is>
           <t xml:space="preserve">「あなたの声を聞かせてください。私の心を彩ってください」
 هات صوتك، لوّن قلبي
@@ -13313,19 +13291,19 @@
 2105 3a2esha_ Instagram </t>
         </is>
       </c>
-      <c r="B613" t="inlineStr">
+      <c r="B612" t="inlineStr">
         <is>
           <t>images/「あなたの声を聞かせてください。私の心_img1.jpg</t>
         </is>
       </c>
-      <c r="C613" t="inlineStr">
+      <c r="C612" t="inlineStr">
         <is>
           <t>電話 ,肉声</t>
         </is>
       </c>
     </row>
-    <row r="614">
-      <c r="A614" t="inlineStr">
+    <row r="613">
+      <c r="A613" t="inlineStr">
         <is>
           <t xml:space="preserve">「この子カンガルーは抱っこが好き」
 يُحب صغير الكنغر هذا أن يؤخذ في الأحضان
@@ -13333,19 +13311,19 @@
 2308 NatGeoMagArab </t>
         </is>
       </c>
-      <c r="B614" t="inlineStr">
+      <c r="B613" t="inlineStr">
         <is>
           <t>images/「この子カンガルーは抱っこが好き」.png</t>
         </is>
       </c>
-      <c r="C614" t="inlineStr">
+      <c r="C613" t="inlineStr">
         <is>
           <t>カンガルー ,人肌</t>
         </is>
       </c>
     </row>
-    <row r="615">
-      <c r="A615" t="inlineStr">
+    <row r="614">
+      <c r="A614" t="inlineStr">
         <is>
           <t xml:space="preserve">「カタールが好き」أحب قطر
 ウヒッブ・カタル ['u-Hibb qa_tar]
@@ -13354,19 +13332,19 @@
 1810 出典不明 </t>
         </is>
       </c>
-      <c r="B615" t="inlineStr">
+      <c r="B614" t="inlineStr">
         <is>
           <t>images/「カタールが好き」_img1.jpg</t>
         </is>
       </c>
-      <c r="C615" t="inlineStr">
+      <c r="C614" t="inlineStr">
         <is>
           <t>カタール</t>
         </is>
       </c>
     </row>
-    <row r="616">
-      <c r="A616" t="inlineStr">
+    <row r="615">
+      <c r="A615" t="inlineStr">
         <is>
           <t xml:space="preserve">「一緒に読むのが好き」
 أُحبُّ أن نَقْرَأَ مَعاً
@@ -13376,19 +13354,19 @@
 2509 www.neelwafurat com,  id=lbb212750-185765 </t>
         </is>
       </c>
-      <c r="B616" t="inlineStr">
+      <c r="B615" t="inlineStr">
         <is>
           <t>images/「一緒に読むのが好き」_img1.jpg</t>
         </is>
       </c>
-      <c r="C616" t="inlineStr">
+      <c r="C615" t="inlineStr">
         <is>
           <t>好き ,本</t>
         </is>
       </c>
     </row>
-    <row r="617">
-      <c r="A617" t="inlineStr">
+    <row r="616">
+      <c r="A616" t="inlineStr">
         <is>
           <t xml:space="preserve">「病院に行きたくない」
 لا أريد أن أذهب إلى المشفى
@@ -13398,19 +13376,19 @@
 2508 Tony Ross https://education.hachette-antoine.com/ar/component/%D9%84%D8%A7-%D8%A3%D8%B1%D9%8A%D8%AF-%D8%A3%D9%86-%D8%A3%D8%B0%D9%87%D8%A8-%D8%A5%D9%84%D9%89-%D8%A7%D9%84%D9%85%D8%B4%D9%81%D9%89/ </t>
         </is>
       </c>
-      <c r="B617" t="inlineStr">
+      <c r="B616" t="inlineStr">
         <is>
           <t>images/「病院に行きたくない」_img1.jpg</t>
         </is>
       </c>
-      <c r="C617" t="inlineStr">
+      <c r="C616" t="inlineStr">
         <is>
           <t>絵本 ,子供</t>
         </is>
       </c>
     </row>
-    <row r="618">
-      <c r="A618" t="inlineStr">
+    <row r="617">
+      <c r="A617" t="inlineStr">
         <is>
           <t xml:space="preserve">「男性はいくら？」「女性はいくら？」
 كم يساوى الرجل؟ ..وكم تساوى المرأة؟
@@ -13419,19 +13397,19 @@
 2308 Pinterest, Masr Elmahrousa, Farah Noweir </t>
         </is>
       </c>
-      <c r="B618" t="inlineStr">
+      <c r="B617" t="inlineStr">
         <is>
           <t>images/「男性はいくら？」「女性はいくら？」_img1.jpg,images/「男性はいくら？」「女性はいくら？」_img2.jpg</t>
         </is>
       </c>
-      <c r="C618" t="inlineStr">
+      <c r="C617" t="inlineStr">
         <is>
           <t xml:space="preserve">全身コーデ ,相場 </t>
         </is>
       </c>
     </row>
-    <row r="619">
-      <c r="A619" t="inlineStr">
+    <row r="618">
+      <c r="A618" t="inlineStr">
         <is>
           <t xml:space="preserve">「黙ってもらえます？」
 ممكن تعيرنا سكوتك؟
@@ -13441,19 +13419,19 @@
 2308 Basel26 </t>
         </is>
       </c>
-      <c r="B619" t="inlineStr">
+      <c r="B618" t="inlineStr">
         <is>
           <t>images/「黙ってもらえます？」_img1.jpg</t>
         </is>
       </c>
-      <c r="C619" t="inlineStr">
+      <c r="C618" t="inlineStr">
         <is>
           <t>音量 ,ボリューム</t>
         </is>
       </c>
     </row>
-    <row r="620">
-      <c r="A620" t="inlineStr">
+    <row r="619">
+      <c r="A619" t="inlineStr">
         <is>
           <t xml:space="preserve">「眠りたいです」
 أُريدُ أَن أَنام
@@ -13463,19 +13441,19 @@
 2109 goodreads com </t>
         </is>
       </c>
-      <c r="B620" t="inlineStr">
+      <c r="B619" t="inlineStr">
         <is>
           <t>images/「眠りたいです」_img1.jpg</t>
         </is>
       </c>
-      <c r="C620" t="inlineStr">
+      <c r="C619" t="inlineStr">
         <is>
           <t>絵本</t>
         </is>
       </c>
     </row>
-    <row r="621">
-      <c r="A621" t="inlineStr">
+    <row r="620">
+      <c r="A620" t="inlineStr">
         <is>
           <t xml:space="preserve">「飛びたい！」أُريد أن أطير
 ウリードゥ・アン・アティール ['u-riidu 'an 'a-_tiir]
@@ -13484,19 +13462,19 @@
 2308 出典不明 </t>
         </is>
       </c>
-      <c r="B621" t="inlineStr">
+      <c r="B620" t="inlineStr">
         <is>
           <t>images/「飛びたい！」_img1.jpg</t>
         </is>
       </c>
-      <c r="C621" t="inlineStr">
+      <c r="C620" t="inlineStr">
         <is>
           <t>鳥 ,希望</t>
         </is>
       </c>
     </row>
-    <row r="622">
-      <c r="A622" t="inlineStr">
+    <row r="621">
+      <c r="A621" t="inlineStr">
         <is>
           <t xml:space="preserve">「うちゅうへとびたい」
 أُريدُ أَنْ أَطيرَ إلى الفَضاء
@@ -13505,19 +13483,19 @@
 2308 mybookshelf co </t>
         </is>
       </c>
-      <c r="B622" t="inlineStr">
+      <c r="B621" t="inlineStr">
         <is>
           <t>images/「うちゅうへとびたい」_img1.jpg</t>
         </is>
       </c>
-      <c r="C622" t="inlineStr">
+      <c r="C621" t="inlineStr">
         <is>
           <t>絵本 ,宇宙</t>
         </is>
       </c>
     </row>
-    <row r="623">
-      <c r="A623" t="inlineStr">
+    <row r="622">
+      <c r="A622" t="inlineStr">
         <is>
           <t xml:space="preserve">「とても愛しています」
 أُحِبّك جِدّاً
@@ -13527,19 +13505,19 @@
 2308 hobe cc </t>
         </is>
       </c>
-      <c r="B623" t="inlineStr">
+      <c r="B622" t="inlineStr">
         <is>
           <t>images/「とても愛しています」_img1.jpg</t>
         </is>
       </c>
-      <c r="C623" t="inlineStr">
+      <c r="C622" t="inlineStr">
         <is>
           <t>恋 ,love</t>
         </is>
       </c>
     </row>
-    <row r="624">
-      <c r="A624" t="inlineStr">
+    <row r="623">
+      <c r="A623" t="inlineStr">
         <is>
           <t xml:space="preserve">「あす日が昇るだろう。私は朝が大好きだ」
 غدا ستشرق الشمس وأحب الصباح كثيرا
@@ -13548,19 +13526,19 @@
 2105 warag-3nb.tumblr com </t>
         </is>
       </c>
-      <c r="B624" t="inlineStr">
+      <c r="B623" t="inlineStr">
         <is>
           <t>images/「あす日が昇るだろう。私は朝が大好きだ_img1.jpg,images/ 「あす日が昇るだろう。私は朝が大好きだ_img2.jpg</t>
         </is>
       </c>
-      <c r="C624" t="inlineStr">
+      <c r="C623" t="inlineStr">
         <is>
           <t>おやすみ ,壁</t>
         </is>
       </c>
     </row>
-    <row r="625">
-      <c r="A625" t="inlineStr">
+    <row r="624">
+      <c r="A624" t="inlineStr">
         <is>
           <t xml:space="preserve">「きみは何をえらぶ？」
 ماذا تختار؟
@@ -13570,19 +13548,19 @@
 2109 embadomjp org </t>
         </is>
       </c>
-      <c r="B625" t="inlineStr">
+      <c r="B624" t="inlineStr">
         <is>
           <t>images/「きみは何をえらぶ？」_img1.jpg</t>
         </is>
       </c>
-      <c r="C625" t="inlineStr">
+      <c r="C624" t="inlineStr">
         <is>
           <t>優柔不断 ,絵本</t>
         </is>
       </c>
     </row>
-    <row r="626">
-      <c r="A626" t="inlineStr">
+    <row r="625">
+      <c r="A625" t="inlineStr">
         <is>
           <t xml:space="preserve">「ちょっと静けさが必要な時もある」
 في بعض الأوقات نحتاج لشوية هدوء
@@ -13592,19 +13570,19 @@
 2308 IN49r </t>
         </is>
       </c>
-      <c r="B626" t="inlineStr">
+      <c r="B625" t="inlineStr">
         <is>
           <t>images/「ちょっと静けさが必要な時もある」_img1.jpg</t>
         </is>
       </c>
-      <c r="C626" t="inlineStr">
+      <c r="C625" t="inlineStr">
         <is>
           <t>ミュート ,精神</t>
         </is>
       </c>
     </row>
-    <row r="627">
-      <c r="A627" t="inlineStr">
+    <row r="626">
+      <c r="A626" t="inlineStr">
         <is>
           <t xml:space="preserve">「逃げるな。全力でぶつかれ」
 لا تهرب اصطدم بكل قوتك
@@ -13614,19 +13592,19 @@
 2308 https://risingvibes.tumblr.com/post/189545775129 </t>
         </is>
       </c>
-      <c r="B627" t="inlineStr">
+      <c r="B626" t="inlineStr">
         <is>
           <t>images/「逃げるな。全力でぶつかれ」_img1.jpg</t>
         </is>
       </c>
-      <c r="C627" t="inlineStr">
+      <c r="C626" t="inlineStr">
         <is>
           <t>応援 ,力</t>
         </is>
       </c>
     </row>
-    <row r="628">
-      <c r="A628" t="inlineStr">
+    <row r="627">
+      <c r="A627" t="inlineStr">
         <is>
           <t xml:space="preserve">「着るのだいすき」
 أُحِبُ أَن أَرتَدِيَ
@@ -13636,19 +13614,19 @@
 2308 https://kitab.firmabikes.ru/epub-_hb_n_rtdy_5187.html </t>
         </is>
       </c>
-      <c r="B628" t="inlineStr">
+      <c r="B627" t="inlineStr">
         <is>
           <t>images/「着るのだいすき」_img1.jpg</t>
         </is>
       </c>
-      <c r="C628" t="inlineStr">
+      <c r="C627" t="inlineStr">
         <is>
           <t xml:space="preserve">絵本 ,ファッション </t>
         </is>
       </c>
     </row>
-    <row r="629">
-      <c r="A629" t="inlineStr">
+    <row r="628">
+      <c r="A628" t="inlineStr">
         <is>
           <t xml:space="preserve">「車のバッテリーが要る！」
 نحتاج بطارية سيارة
@@ -13658,19 +13636,19 @@
 2308 instagram roaa_27 </t>
         </is>
       </c>
-      <c r="B629" t="inlineStr">
+      <c r="B628" t="inlineStr">
         <is>
           <t>images/「車のバッテリーが要る！」_img1.jpg</t>
         </is>
       </c>
-      <c r="C629" t="inlineStr">
+      <c r="C628" t="inlineStr">
         <is>
           <t>スマホ ,充電</t>
         </is>
       </c>
     </row>
-    <row r="630">
-      <c r="A630" t="inlineStr">
+    <row r="629">
+      <c r="A629" t="inlineStr">
         <is>
           <t xml:space="preserve">「今日は幸せでいることにしました」
 اخترت أن أكون سعيدا اليوم
@@ -13680,19 +13658,19 @@
 2109 awaasha tumblr </t>
         </is>
       </c>
-      <c r="B630" t="inlineStr">
+      <c r="B629" t="inlineStr">
         <is>
           <t>images/「今日は幸せでいることにしました」_img1.jpg</t>
         </is>
       </c>
-      <c r="C630" t="inlineStr">
+      <c r="C629" t="inlineStr">
         <is>
           <t>心構え ,happy</t>
         </is>
       </c>
     </row>
-    <row r="631">
-      <c r="A631" t="inlineStr">
+    <row r="630">
+      <c r="A630" t="inlineStr">
         <is>
           <t xml:space="preserve">「理想的なスイカの選び方」
 كيف تختار البطيخة المُثلى؟
@@ -13702,19 +13680,19 @@
 2308 bit ly/octmel </t>
         </is>
       </c>
-      <c r="B631" t="inlineStr">
+      <c r="B630" t="inlineStr">
         <is>
           <t>images/「理想的なスイカの選び方」_img1.jpg</t>
         </is>
       </c>
-      <c r="C631" t="inlineStr">
+      <c r="C630" t="inlineStr">
         <is>
           <t>八百屋 ,西瓜</t>
         </is>
       </c>
     </row>
-    <row r="632">
-      <c r="A632" t="inlineStr">
+    <row r="631">
+      <c r="A631" t="inlineStr">
         <is>
           <t xml:space="preserve">「お問い合わせください」
 اتصل بنا
@@ -13724,19 +13702,19 @@
 2308 mtawir.blogspot com </t>
         </is>
       </c>
-      <c r="B632" t="inlineStr">
+      <c r="B631" t="inlineStr">
         <is>
           <t>images/「お問い合わせください」_img1.jpg</t>
         </is>
       </c>
-      <c r="C632" t="inlineStr">
+      <c r="C631" t="inlineStr">
         <is>
           <t>広告 ,電話</t>
         </is>
       </c>
     </row>
-    <row r="633">
-      <c r="A633" t="inlineStr">
+    <row r="632">
+      <c r="A632" t="inlineStr">
         <is>
           <t xml:space="preserve">「両方の動物が海岸の火山岩の亀裂の中に定住している」
 يحتل كلا الحيوانين شقوقًا في صخور الساحل البركانية
@@ -13744,19 +13722,19 @@
 2507 https://x.com/NatGeoMagArab/status/1925167200056521151 </t>
         </is>
       </c>
-      <c r="B633" t="inlineStr">
+      <c r="B632" t="inlineStr">
         <is>
           <t>images/「両方の動物が海岸の火山岩の亀裂の中に_img1.jpg,images/「両方の動物が海岸の火山岩の亀裂の中に_img2.jpg</t>
         </is>
       </c>
-      <c r="C633" t="inlineStr">
+      <c r="C632" t="inlineStr">
         <is>
           <t>手書き語学 ,アラビア語 ,イグアナ</t>
         </is>
       </c>
     </row>
-    <row r="634">
-      <c r="A634" t="inlineStr">
+    <row r="633">
+      <c r="A633" t="inlineStr">
         <is>
           <t xml:space="preserve">「命じられたように正しき道を辿れ」
 واستقم كما أمرت
@@ -13766,19 +13744,19 @@
 2308 Ahmed Madyan </t>
         </is>
       </c>
-      <c r="B634" t="inlineStr">
+      <c r="B633" t="inlineStr">
         <is>
           <t>images/「命じられたように正しき道を辿れ」_img1.jpg</t>
         </is>
       </c>
-      <c r="C634" t="inlineStr">
+      <c r="C633" t="inlineStr">
         <is>
           <t>書道 ,アート</t>
         </is>
       </c>
     </row>
-    <row r="635">
-      <c r="A635" t="inlineStr">
+    <row r="634">
+      <c r="A634" t="inlineStr">
         <is>
           <t xml:space="preserve">「くつろぎなさい」استكن
 イスタキンナ [istakinna]
@@ -13786,19 +13764,19 @@
 2603 m2ff tumblr com </t>
         </is>
       </c>
-      <c r="B635" t="inlineStr">
+      <c r="B634" t="inlineStr">
         <is>
           <t>images/「くつろぎなさい」.jpeg</t>
         </is>
       </c>
-      <c r="C635" t="inlineStr">
+      <c r="C634" t="inlineStr">
         <is>
           <t>relax ,コーヒー</t>
         </is>
       </c>
     </row>
-    <row r="636">
-      <c r="A636" t="inlineStr">
+    <row r="635">
+      <c r="A635" t="inlineStr">
         <is>
           <t xml:space="preserve">「彼は応えるだろう」سيستجيب 
 サヤスタジーブ [sa-ya-stajiibu]
@@ -13807,19 +13785,19 @@
 1811 kareem mrghani </t>
         </is>
       </c>
-      <c r="B636" t="inlineStr">
+      <c r="B635" t="inlineStr">
         <is>
           <t>images/「彼は応えるだろう」_img1.jpg</t>
         </is>
       </c>
-      <c r="C636" t="inlineStr">
+      <c r="C635" t="inlineStr">
         <is>
           <t>縦書き ,現代アート</t>
         </is>
       </c>
     </row>
-    <row r="637">
-      <c r="A637" t="inlineStr">
+    <row r="636">
+      <c r="A636" t="inlineStr">
         <is>
           <t xml:space="preserve">「アラビア語が好き」
 أنا أُحبّ لُغتي
@@ -13829,19 +13807,19 @@
 2308 出典不明 </t>
         </is>
       </c>
-      <c r="B637" t="inlineStr">
+      <c r="B636" t="inlineStr">
         <is>
           <t>images/「アラビア語が好き」_img1.jpg</t>
         </is>
       </c>
-      <c r="C637" t="inlineStr">
+      <c r="C636" t="inlineStr">
         <is>
           <t>和訳 ,こども</t>
         </is>
       </c>
     </row>
-    <row r="638">
-      <c r="A638" t="inlineStr">
+    <row r="637">
+      <c r="A637" t="inlineStr">
         <is>
           <t xml:space="preserve">「私はサッカーが好きです」
 أنا أُحِبُّ كُرةَ القَدَم
@@ -13851,19 +13829,19 @@
 2109 Arabic With Nadia </t>
         </is>
       </c>
-      <c r="B638" t="inlineStr">
+      <c r="B637" t="inlineStr">
         <is>
           <t>images/「私はサッカーが好きです」_img1.jpg</t>
         </is>
       </c>
-      <c r="C638" t="inlineStr">
+      <c r="C637" t="inlineStr">
         <is>
           <t>自由時間 ,例文</t>
         </is>
       </c>
     </row>
-    <row r="639">
-      <c r="A639" t="inlineStr">
+    <row r="638">
+      <c r="A638" t="inlineStr">
         <is>
           <t xml:space="preserve">「これ、私の眼鏡じゃありません」
 هٰذِهِ لَيْسَتْ نَظَّارَاتِي
@@ -13873,19 +13851,19 @@
 2509 </t>
         </is>
       </c>
-      <c r="B639" t="inlineStr">
+      <c r="B638" t="inlineStr">
         <is>
           <t>images/「これ、私の眼鏡じゃありません」_img1.jpg</t>
         </is>
       </c>
-      <c r="C639" t="inlineStr">
+      <c r="C638" t="inlineStr">
         <is>
           <t>あらびあや</t>
         </is>
       </c>
     </row>
-    <row r="640">
-      <c r="A640" t="inlineStr">
+    <row r="639">
+      <c r="A639" t="inlineStr">
         <is>
           <t xml:space="preserve">「我らも米を食います」
 نحن أيضاً نأكل الأرز
@@ -13895,19 +13873,19 @@
 1809 </t>
         </is>
       </c>
-      <c r="B640" t="inlineStr">
+      <c r="B639" t="inlineStr">
         <is>
           <t>images/「我らも米を食います」_img1.jpg</t>
         </is>
       </c>
-      <c r="C640" t="inlineStr">
+      <c r="C639" t="inlineStr">
         <is>
           <t>あらびあや</t>
         </is>
       </c>
     </row>
-    <row r="641">
-      <c r="A641" t="inlineStr">
+    <row r="640">
+      <c r="A640" t="inlineStr">
         <is>
           <t xml:space="preserve">「ひとりでできるもん！」
 أنا أستطيع أن أفعله وحدي
@@ -13916,19 +13894,19 @@
 2105 </t>
         </is>
       </c>
-      <c r="B641" t="inlineStr">
+      <c r="B640" t="inlineStr">
         <is>
           <t>images/「ひとりでできるもん！」_img1.jpg</t>
         </is>
       </c>
-      <c r="C641" t="inlineStr">
+      <c r="C640" t="inlineStr">
         <is>
           <t>あらびあや</t>
         </is>
       </c>
     </row>
-    <row r="642">
-      <c r="A642" t="inlineStr">
+    <row r="641">
+      <c r="A641" t="inlineStr">
         <is>
           <t xml:space="preserve">「恋しくないと言っている時は恋しい」
 أُريدُك حينَ أَقُولُ أَنا لا أُريدُك
@@ -13938,19 +13916,19 @@
 2308 DARWISHISM </t>
         </is>
       </c>
-      <c r="B642" t="inlineStr">
+      <c r="B641" t="inlineStr">
         <is>
           <t>images/「恋しくないと言っている時は恋しい」_img1.jpg</t>
         </is>
       </c>
-      <c r="C642" t="inlineStr">
+      <c r="C641" t="inlineStr">
         <is>
           <t>本音 ,恋愛</t>
         </is>
       </c>
     </row>
-    <row r="643">
-      <c r="A643" t="inlineStr">
+    <row r="642">
+      <c r="A642" t="inlineStr">
         <is>
           <t xml:space="preserve">「私は〜する」
 ⁦「着る」：( أنا ألبس )['ana 'a-lbas]⁩
@@ -13961,19 +13939,19 @@
 2109 RABIE </t>
         </is>
       </c>
-      <c r="B643" t="inlineStr">
+      <c r="B642" t="inlineStr">
         <is>
           <t>images/「私は〜する」_img1.jpg,images/「私は〜する」_img2.jpg,images/「私は〜する」_img3.jpg,images/「私は〜する」_img4.jpg</t>
         </is>
       </c>
-      <c r="C643" t="inlineStr">
+      <c r="C642" t="inlineStr">
         <is>
           <t>動詞 ,絵本</t>
         </is>
       </c>
     </row>
-    <row r="644">
-      <c r="A644" t="inlineStr">
+    <row r="643">
+      <c r="A643" t="inlineStr">
         <is>
           <t xml:space="preserve">「彼は完璧ではない。私は彼の欠点については目をつむった」
 هو ليس كامل. أنا أعميت نفسي عن سيئاته
@@ -13982,19 +13960,19 @@
 2308 _NOHA </t>
         </is>
       </c>
-      <c r="B644" t="inlineStr">
+      <c r="B643" t="inlineStr">
         <is>
           <t>images/「彼は完璧ではない。私は彼の欠点につい_img1.jpg</t>
         </is>
       </c>
-      <c r="C644" t="inlineStr">
+      <c r="C643" t="inlineStr">
         <is>
           <t>愛 ,寛容</t>
         </is>
       </c>
     </row>
-    <row r="645">
-      <c r="A645" t="inlineStr">
+    <row r="644">
+      <c r="A644" t="inlineStr">
         <is>
           <t xml:space="preserve">「この子トラは検疫期間中に生まれた」
 صغير النمر هذا ولد في زمن الحجر الصحي
@@ -14003,19 +13981,19 @@
 2310 https://www.akhbaralaan.net/?p=434924 </t>
         </is>
       </c>
-      <c r="B645" t="inlineStr">
+      <c r="B644" t="inlineStr">
         <is>
           <t>images/「この子トラは検疫期間中に生まれた」_img1.jpg</t>
         </is>
       </c>
-      <c r="C645" t="inlineStr">
+      <c r="C644" t="inlineStr">
         <is>
           <t>Covid ,メキシコ</t>
         </is>
       </c>
     </row>
-    <row r="646">
-      <c r="A646" t="inlineStr">
+    <row r="645">
+      <c r="A645" t="inlineStr">
         <is>
           <t xml:space="preserve">「睡眠の素晴らしさに匹敵するものは無い！」
 وجمال النوم ليس له مثيل
@@ -14024,19 +14002,19 @@
 2308 arabzy tumblr </t>
         </is>
       </c>
-      <c r="B646" t="inlineStr">
+      <c r="B645" t="inlineStr">
         <is>
           <t>images/「睡眠の素晴らしさに匹敵するものは無い_img1.jpg</t>
         </is>
       </c>
-      <c r="C646" t="inlineStr">
+      <c r="C645" t="inlineStr">
         <is>
           <t>オフトゥン ,おやすみ</t>
         </is>
       </c>
     </row>
-    <row r="647">
-      <c r="A647" t="inlineStr">
+    <row r="646">
+      <c r="A646" t="inlineStr">
         <is>
           <t xml:space="preserve">「大器晩成」
 الأشياء العظيمة تأخذ وقت
@@ -14046,19 +14024,19 @@
 2109 出典不明 </t>
         </is>
       </c>
-      <c r="B647" t="inlineStr">
+      <c r="B646" t="inlineStr">
         <is>
           <t>images/「大器晩成」_img1.jpg</t>
         </is>
       </c>
-      <c r="C647" t="inlineStr">
+      <c r="C646" t="inlineStr">
         <is>
           <t>ことわざ ,和訳</t>
         </is>
       </c>
     </row>
-    <row r="648">
-      <c r="A648" t="inlineStr">
+    <row r="647">
+      <c r="A647" t="inlineStr">
         <is>
           <t xml:space="preserve">「コーヒーは急には飲まれない」
 القهْوة لا تشرَب عَلى عَجلْ
@@ -14069,19 +14047,19 @@
 2012 Ahmed Madyan </t>
         </is>
       </c>
-      <c r="B648" t="inlineStr">
+      <c r="B647" t="inlineStr">
         <is>
           <t>images/「コーヒーは急には飲まれない」_img1.jpg</t>
         </is>
       </c>
-      <c r="C648" t="inlineStr">
+      <c r="C647" t="inlineStr">
         <is>
           <t>名言</t>
         </is>
       </c>
     </row>
-    <row r="649">
-      <c r="A649" t="inlineStr">
+    <row r="648">
+      <c r="A648" t="inlineStr">
         <is>
           <t xml:space="preserve">「成功者は情報共有している」
 الناجحون يشاركون المعلومة
@@ -14091,19 +14069,19 @@
 2109 出典不明 </t>
         </is>
       </c>
-      <c r="B649" t="inlineStr">
+      <c r="B648" t="inlineStr">
         <is>
           <t>images/「成功者は情報共有している」_img1.jpg</t>
         </is>
       </c>
-      <c r="C649" t="inlineStr">
+      <c r="C648" t="inlineStr">
         <is>
           <t>鳥 ,シェア</t>
         </is>
       </c>
     </row>
-    <row r="650">
-      <c r="A650" t="inlineStr">
+    <row r="649">
+      <c r="A649" t="inlineStr">
         <is>
           <t xml:space="preserve">「間違いで賢くなる、痛みで強くなる」
 الأخطاء تجعلك حكيمًا، والألم يجعلك قويًا
@@ -14112,19 +14090,19 @@
 2111 https://alaminin.blogspot.com/2020/03/blog-post_6.html </t>
         </is>
       </c>
-      <c r="B650" t="inlineStr">
+      <c r="B649" t="inlineStr">
         <is>
           <t>images/「間違いで賢くなる、痛みで強くなる」_img1.jpg</t>
         </is>
       </c>
-      <c r="C650" t="inlineStr">
+      <c r="C649" t="inlineStr">
         <is>
           <t>名言</t>
         </is>
       </c>
     </row>
-    <row r="651">
-      <c r="A651" t="inlineStr">
+    <row r="650">
+      <c r="A650" t="inlineStr">
         <is>
           <t xml:space="preserve">「何事も永遠には続かない」
 لا شيء يبقى للأبد
@@ -14134,19 +14112,19 @@
 2308 KiTeLetZ </t>
         </is>
       </c>
-      <c r="B651" t="inlineStr">
+      <c r="B650" t="inlineStr">
         <is>
           <t>images/「何事も永遠には続かない」_img1.jpg</t>
         </is>
       </c>
-      <c r="C651" t="inlineStr">
+      <c r="C650" t="inlineStr">
         <is>
           <t>変化 ,名言</t>
         </is>
       </c>
     </row>
-    <row r="652">
-      <c r="A652" t="inlineStr">
+    <row r="651">
+      <c r="A651" t="inlineStr">
         <is>
           <t xml:space="preserve">「惑星地球はあなた方を歓迎します」
 كوكب الارض يرحّب بكم
@@ -14156,19 +14134,19 @@
 1811 iN49R </t>
         </is>
       </c>
-      <c r="B652" t="inlineStr">
+      <c r="B651" t="inlineStr">
         <is>
           <t>images/「惑星地球はあなた方を歓迎します」_img1.jpg</t>
         </is>
       </c>
-      <c r="C652" t="inlineStr">
+      <c r="C651" t="inlineStr">
         <is>
           <t>宇宙 ,人類</t>
         </is>
       </c>
     </row>
-    <row r="653">
-      <c r="A653" t="inlineStr">
+    <row r="652">
+      <c r="A652" t="inlineStr">
         <is>
           <t xml:space="preserve">「自分を信じなさい。人の言うことは尽きないのだから」
 ثق بنفسك فكلام الناس لا ينتهي
@@ -14177,19 +14155,19 @@
 2105 出典不明 </t>
         </is>
       </c>
-      <c r="B653" t="inlineStr">
+      <c r="B652" t="inlineStr">
         <is>
           <t>images/「自分を信じなさい。人の言うことは尽き_img1.jpg</t>
         </is>
       </c>
-      <c r="C653" t="inlineStr">
+      <c r="C652" t="inlineStr">
         <is>
           <t>自信 ,無視</t>
         </is>
       </c>
     </row>
-    <row r="654">
-      <c r="A654" t="inlineStr">
+    <row r="653">
+      <c r="A653" t="inlineStr">
         <is>
           <t xml:space="preserve">「弟が歩くぞ」أخي الصغير يمشي
 アキ_ッサギール・ヤムシー ['aKh-i ^_saGhiiru ya-mShii]
@@ -14198,19 +14176,19 @@
 2308 gulfkids com http://www.gulfkids.com/ar/book48-1909.htm </t>
         </is>
       </c>
-      <c r="B654" t="inlineStr">
+      <c r="B653" t="inlineStr">
         <is>
           <t>images/「弟が歩くぞ」_img1.jpg</t>
         </is>
       </c>
-      <c r="C654" t="inlineStr">
+      <c r="C653" t="inlineStr">
         <is>
           <t>兄弟 ,絵本</t>
         </is>
       </c>
     </row>
-    <row r="655">
-      <c r="A655" t="inlineStr">
+    <row r="654">
+      <c r="A654" t="inlineStr">
         <is>
           <t xml:space="preserve">花より団子おおお（違う）
 「誰もふさわしくない」[laa 'aHada ya-staHiqqu]
@@ -14218,19 +14196,19 @@
 2308 https://twitter.com/NatGeoMagArab/status/1370041991317233664 </t>
         </is>
       </c>
-      <c r="B655" t="inlineStr">
+      <c r="B654" t="inlineStr">
         <is>
           <t>images/花より団子おおお（違う）_img1.jpg</t>
         </is>
       </c>
-      <c r="C655" t="inlineStr">
+      <c r="C654" t="inlineStr">
         <is>
           <t>手書き語学 ,アラビア語 ,キノボリカンガルー</t>
         </is>
       </c>
     </row>
-    <row r="656">
-      <c r="A656" t="inlineStr">
+    <row r="655">
+      <c r="A655" t="inlineStr">
         <is>
           <t xml:space="preserve">「諸行無常」كلّ شيءٍ يتغيّر
 クッル・シャイイン・ヤタガイヤル [kullu Shay'in ya-taGhayyaru]
@@ -14240,19 +14218,19 @@
 د. ماجد عبدالله </t>
         </is>
       </c>
-      <c r="B656" t="inlineStr">
+      <c r="B655" t="inlineStr">
         <is>
           <t>images/「諸行無常」_img1.jpg</t>
         </is>
       </c>
-      <c r="C656" t="inlineStr">
+      <c r="C655" t="inlineStr">
         <is>
           <t>表紙 ,タイトル</t>
         </is>
       </c>
     </row>
-    <row r="657">
-      <c r="A657" t="inlineStr">
+    <row r="656">
+      <c r="A656" t="inlineStr">
         <is>
           <t xml:space="preserve">「幸せな人生には弱い記憶力が必要」
 الحياة السعيدة تتطلب ذاكرة ضعيفة
@@ -14261,19 +14239,19 @@
 2012 出典不明 </t>
         </is>
       </c>
-      <c r="B657" t="inlineStr">
+      <c r="B656" t="inlineStr">
         <is>
           <t>images/「幸せな人生には弱い記憶力が必要」_img1.jpg</t>
         </is>
       </c>
-      <c r="C657" t="inlineStr">
+      <c r="C656" t="inlineStr">
         <is>
           <t>前向き</t>
         </is>
       </c>
     </row>
-    <row r="658">
-      <c r="A658" t="inlineStr">
+    <row r="657">
+      <c r="A657" t="inlineStr">
         <is>
           <t xml:space="preserve">「このパンダは私たちに、幸せは単純なことの中に隠れているのだと教えている」
 دب "الباندا" هذا يؤكد لنا أن السعادة تكمن في أبسط الأشياء
@@ -14281,19 +14259,19 @@
 2308 https://twitter.com/NatGeoMagArab/status/1309938472065486848 </t>
         </is>
       </c>
-      <c r="B658" t="inlineStr">
+      <c r="B657" t="inlineStr">
         <is>
           <t>images/「このパンダは私たちに、幸せは単純なこ.png</t>
         </is>
       </c>
-      <c r="C658" t="inlineStr">
+      <c r="C657" t="inlineStr">
         <is>
           <t>パンダ ,雪</t>
         </is>
       </c>
     </row>
-    <row r="659">
-      <c r="A659" t="inlineStr">
+    <row r="658">
+      <c r="A658" t="inlineStr">
         <is>
           <t xml:space="preserve">「良い時間は速く過ぎる」
 الأوقات الجميلة تمر بسرعة
@@ -14303,19 +14281,19 @@
 1810 Nasser.Tumblr </t>
         </is>
       </c>
-      <c r="B659" t="inlineStr">
+      <c r="B658" t="inlineStr">
         <is>
           <t>images/「良い時間は速く過ぎる」_img1.jpg</t>
         </is>
       </c>
-      <c r="C659" t="inlineStr">
+      <c r="C658" t="inlineStr">
         <is>
           <t>相対論 ,心理学</t>
         </is>
       </c>
     </row>
-    <row r="660">
-      <c r="A660" t="inlineStr">
+    <row r="659">
+      <c r="A659" t="inlineStr">
         <is>
           <t xml:space="preserve">「今日が始まりかもしれない」
 كل يوم ممكن يكون بداية
@@ -14325,19 +14303,19 @@
 2308 Ahmed Madyan </t>
         </is>
       </c>
-      <c r="B660" t="inlineStr">
+      <c r="B659" t="inlineStr">
         <is>
           <t>images/「今日が始まりかもしれない」_img1.jpg</t>
         </is>
       </c>
-      <c r="C660" t="inlineStr">
+      <c r="C659" t="inlineStr">
         <is>
           <t>吉日 ,開始</t>
         </is>
       </c>
     </row>
-    <row r="661">
-      <c r="A661" t="inlineStr">
+    <row r="660">
+      <c r="A660" t="inlineStr">
         <is>
           <t xml:space="preserve">「ヌール、歯医者さんに行く」
 نور تذهب إلى طبيب الأسنان
@@ -14347,19 +14325,19 @@
 2109 RABIE </t>
         </is>
       </c>
-      <c r="B661" t="inlineStr">
+      <c r="B660" t="inlineStr">
         <is>
           <t>images/「ヌール、歯医者さんに行く」_img1.jpg</t>
         </is>
       </c>
-      <c r="C661" t="inlineStr">
+      <c r="C660" t="inlineStr">
         <is>
           <t>絵本 ,歯科</t>
         </is>
       </c>
     </row>
-    <row r="662">
-      <c r="A662" t="inlineStr">
+    <row r="661">
+      <c r="A661" t="inlineStr">
         <is>
           <t xml:space="preserve">「ラヤンはねむれない」
 لَيان لا تَسْتَطيعُ أَنْ تَنام
@@ -14368,19 +14346,19 @@
 2308 出典不明 </t>
         </is>
       </c>
-      <c r="B662" t="inlineStr">
+      <c r="B661" t="inlineStr">
         <is>
           <t>images/「ラヤンはねむれない」_img1.jpg</t>
         </is>
       </c>
-      <c r="C662" t="inlineStr">
+      <c r="C661" t="inlineStr">
         <is>
           <t>絵本 ,不眠症</t>
         </is>
       </c>
     </row>
-    <row r="663">
-      <c r="A663" t="inlineStr">
+    <row r="662">
+      <c r="A662" t="inlineStr">
         <is>
           <t xml:space="preserve">「クネイトラ県、蜂の巣を約60%失う」
 القنيطرة تفقد حوالي 60 % من خلايا نحلها
@@ -14388,19 +14366,19 @@
 2403 nabd com/t/101679025-fb119f </t>
         </is>
       </c>
-      <c r="B663" t="inlineStr">
+      <c r="B662" t="inlineStr">
         <is>
           <t>images/「クネイトラ県、蜂の巣を約60%失う」_img1.jpg</t>
         </is>
       </c>
-      <c r="C663" t="inlineStr">
+      <c r="C662" t="inlineStr">
         <is>
           <t>蜂の巣 ,パーセント</t>
         </is>
       </c>
     </row>
-    <row r="664">
-      <c r="A664" t="inlineStr">
+    <row r="663">
+      <c r="A663" t="inlineStr">
         <is>
           <t xml:space="preserve">「結ばれしター」ة
 ⁦( تاء مربوطة )[taa' marbuu_ta]：ت「ター」( تاء )[taa']・「結ばれている」( مربوط )[marbuu_t]：( ربط )【結】⁩
@@ -14408,19 +14386,19 @@
 2308 出典不明 </t>
         </is>
       </c>
-      <c r="B664" t="inlineStr">
+      <c r="B663" t="inlineStr">
         <is>
           <t>images/「結ばれしター」_img1.jpg</t>
         </is>
       </c>
-      <c r="C664" t="inlineStr">
+      <c r="C663" t="inlineStr">
         <is>
           <t>アラビア文字 ,顔</t>
         </is>
       </c>
     </row>
-    <row r="665">
-      <c r="A665" t="inlineStr">
+    <row r="664">
+      <c r="A664" t="inlineStr">
         <is>
           <t xml:space="preserve">「忙しい」مشغول
 マシュグール [maShGhuul]
@@ -14429,19 +14407,19 @@
 1811 skyshinichi.instagram </t>
         </is>
       </c>
-      <c r="B665" t="inlineStr">
+      <c r="B664" t="inlineStr">
         <is>
           <t>images/「忙しい」_img1.jpg</t>
         </is>
       </c>
-      <c r="C665" t="inlineStr">
+      <c r="C664" t="inlineStr">
         <is>
           <t>スティッチ ,残業</t>
         </is>
       </c>
     </row>
-    <row r="666">
-      <c r="A666" t="inlineStr">
+    <row r="665">
+      <c r="A665" t="inlineStr">
         <is>
           <t xml:space="preserve">「駐車禁止」ممنوع الوقوف
 マムヌーア・アルウクーフ [mamnuu* al-wuquuf]
@@ -14450,19 +14428,19 @@
 2106 出典不明 </t>
         </is>
       </c>
-      <c r="B666" t="inlineStr">
+      <c r="B665" t="inlineStr">
         <is>
           <t>images/「駐車禁止」_img1.jpg</t>
         </is>
       </c>
-      <c r="C666" t="inlineStr">
+      <c r="C665" t="inlineStr">
         <is>
           <t>標識 ,ジョーク</t>
         </is>
       </c>
     </row>
-    <row r="667">
-      <c r="A667" t="inlineStr">
+    <row r="666">
+      <c r="A666" t="inlineStr">
         <is>
           <t xml:space="preserve">「一人ひとりが責任を」
 كُلنا مسؤول
@@ -14472,19 +14450,19 @@
 2308 covid19awareness sa </t>
         </is>
       </c>
-      <c r="B667" t="inlineStr">
+      <c r="B666" t="inlineStr">
         <is>
           <t>images/「一人ひとりが責任を」_img1.jpg</t>
         </is>
       </c>
-      <c r="C667" t="inlineStr">
+      <c r="C666" t="inlineStr">
         <is>
           <t>Covid ,感染拡大防止</t>
         </is>
       </c>
     </row>
-    <row r="668">
-      <c r="A668" t="inlineStr">
+    <row r="667">
+      <c r="A667" t="inlineStr">
         <is>
           <t xml:space="preserve">「おめでとうございます」مبروك
 マブルーク [mabruuk]
@@ -14493,19 +14471,19 @@
 2308 </t>
         </is>
       </c>
-      <c r="B668" t="inlineStr">
+      <c r="B667" t="inlineStr">
         <is>
           <t>images/「おめでとうございます」_img1.jpg</t>
         </is>
       </c>
-      <c r="C668" t="inlineStr">
+      <c r="C667" t="inlineStr">
         <is>
           <t>詐欺 ,広告</t>
         </is>
       </c>
     </row>
-    <row r="669">
-      <c r="A669" t="inlineStr">
+    <row r="668">
+      <c r="A668" t="inlineStr">
         <is>
           <t xml:space="preserve">「手書きフォント」
 خط مكتوب باليد
@@ -14515,19 +14493,19 @@
 1809 FahdAlFraikh Behance </t>
         </is>
       </c>
-      <c r="B669" t="inlineStr">
+      <c r="B668" t="inlineStr">
         <is>
           <t>images/「手書きフォント」_img1.jpg</t>
         </is>
       </c>
-      <c r="C669" t="inlineStr">
+      <c r="C668" t="inlineStr">
         <is>
           <t>可愛いフォント ,筆跡</t>
         </is>
       </c>
     </row>
-    <row r="670">
-      <c r="A670" t="inlineStr">
+    <row r="669">
+      <c r="A669" t="inlineStr">
         <is>
           <t xml:space="preserve">「開かれたターと結ばれたター」
 التاء المفتوحة والمربوطة
@@ -14537,19 +14515,19 @@
 2109 slideshare.net </t>
         </is>
       </c>
-      <c r="B670" t="inlineStr">
+      <c r="B669" t="inlineStr">
         <is>
           <t>images/「開かれたターと結ばれたター」_img1.jpg</t>
         </is>
       </c>
-      <c r="C670" t="inlineStr">
+      <c r="C669" t="inlineStr">
         <is>
           <t>アラビア文字 ,スマイリー</t>
         </is>
       </c>
     </row>
-    <row r="671">
-      <c r="A671" t="inlineStr">
+    <row r="670">
+      <c r="A670" t="inlineStr">
         <is>
           <t xml:space="preserve">「このラマは誇らしげにして立っている」
 تقف هذه اللاما مزهوة بنفسها
@@ -14557,19 +14535,19 @@
 2410 https://twitter.com/NatGeoMagArab/status/1597485552965935104 </t>
         </is>
       </c>
-      <c r="B671" t="inlineStr">
+      <c r="B670" t="inlineStr">
         <is>
           <t>images/「このラマは誇らしげにして立っている」_img1.jpg</t>
         </is>
       </c>
-      <c r="C671" t="inlineStr">
+      <c r="C670" t="inlineStr">
         <is>
           <t>手書き語学 ,アラビア語 ,マチュピチュ遺跡</t>
         </is>
       </c>
     </row>
-    <row r="672">
-      <c r="A672" t="inlineStr">
+    <row r="671">
+      <c r="A671" t="inlineStr">
         <is>
           <t xml:space="preserve">「小さな生き物にしては危険な名前だ」
 اسم خطير لمخلوق صغير
@@ -14578,19 +14556,19 @@
 2308 https://twitter.com/NatGeoMagArab/status/1495035772071669760 </t>
         </is>
       </c>
-      <c r="B672" t="inlineStr">
+      <c r="B671" t="inlineStr">
         <is>
           <t>images/「小さな生き物にしては危険な名前だ」_img1.jpg</t>
         </is>
       </c>
-      <c r="C672" t="inlineStr">
+      <c r="C671" t="inlineStr">
         <is>
           <t>有袋類 ,タスマニアデビル</t>
         </is>
       </c>
     </row>
-    <row r="673">
-      <c r="A673" t="inlineStr">
+    <row r="672">
+      <c r="A672" t="inlineStr">
         <is>
           <t xml:space="preserve">「こわれている」مكسر
 ムカッサル [mukassar]
@@ -14598,19 +14576,19 @@
 2105 behance Written-Visuals </t>
         </is>
       </c>
-      <c r="B673" t="inlineStr">
+      <c r="B672" t="inlineStr">
         <is>
           <t>images/「こわれている」_img1.jpg</t>
         </is>
       </c>
-      <c r="C673" t="inlineStr">
+      <c r="C672" t="inlineStr">
         <is>
           <t>バラバラ ,デザイン</t>
         </is>
       </c>
     </row>
-    <row r="674">
-      <c r="A674" t="inlineStr">
+    <row r="673">
+      <c r="A673" t="inlineStr">
         <is>
           <t xml:space="preserve">「早起きする方法」
 كيف تنهض مُبكّرًا
@@ -14620,19 +14598,19 @@
 2308 Funders and Founders </t>
         </is>
       </c>
-      <c r="B674" t="inlineStr">
+      <c r="B673" t="inlineStr">
         <is>
           <t>images/「早起きする方法」_img1.jpg</t>
         </is>
       </c>
-      <c r="C674" t="inlineStr">
+      <c r="C673" t="inlineStr">
         <is>
           <t>オフトゥン ,寝起き</t>
         </is>
       </c>
     </row>
-    <row r="675">
-      <c r="A675" t="inlineStr">
+    <row r="674">
+      <c r="A674" t="inlineStr">
         <is>
           <t xml:space="preserve">「アラブ・デザイン文字展覧会」
 معرض لتخطيط الحرف العربي
@@ -14642,38 +14620,38 @@
 2109 arabic lettering exhibition </t>
         </is>
       </c>
-      <c r="B675" t="inlineStr">
+      <c r="B674" t="inlineStr">
         <is>
           <t>images/「アラブ・デザイン文字展覧会」_img1.jpg</t>
         </is>
       </c>
-      <c r="C675" t="inlineStr">
+      <c r="C674" t="inlineStr">
         <is>
           <t>ポスター</t>
         </is>
       </c>
     </row>
-    <row r="676">
-      <c r="A676" t="inlineStr">
+    <row r="675">
+      <c r="A675" t="inlineStr">
         <is>
           <t xml:space="preserve">「お気に入りのおもちゃには触らせない」
 ⁦「彼は〜を許さない」[laa ya-smaHu bi-]：「彼は許す」( يسمح )[ya-smaH(u)]：「許した」( سمح )[samaHa]：( سَ )[sa]・( مَ )[ma]・( حَ )[Ha]⁩
 2209 https://pic.twitter.com/qWcIPB3fz2 </t>
         </is>
       </c>
-      <c r="B676" t="inlineStr">
+      <c r="B675" t="inlineStr">
         <is>
           <t>images/「お気に入りのおもちゃには触らせない」_img1.jpg</t>
         </is>
       </c>
-      <c r="C676" t="inlineStr">
+      <c r="C675" t="inlineStr">
         <is>
           <t>パンダ ,ボール</t>
         </is>
       </c>
     </row>
-    <row r="677">
-      <c r="A677" t="inlineStr">
+    <row r="676">
+      <c r="A676" t="inlineStr">
         <is>
           <t xml:space="preserve">「名探偵コナン」المحقق كونان
 アルムハッキク・コナン [al-muHaqqiq Conan]
@@ -14682,19 +14660,19 @@
 1809 wikipedia </t>
         </is>
       </c>
-      <c r="B677" t="inlineStr">
+      <c r="B676" t="inlineStr">
         <is>
           <t>images/「名探偵コナン」_img1.jpg</t>
         </is>
       </c>
-      <c r="C677" t="inlineStr">
+      <c r="C676" t="inlineStr">
         <is>
           <t>江戸川コナン ,ロゴ</t>
         </is>
       </c>
     </row>
-    <row r="678">
-      <c r="A678" t="inlineStr">
+    <row r="677">
+      <c r="A677" t="inlineStr">
         <is>
           <t xml:space="preserve">「イードおめでとう」عيد مبارك
 イード・ムバーラク [*iid mubaarak]
@@ -14702,19 +14680,19 @@
 2308 出典不明 </t>
         </is>
       </c>
-      <c r="B678" t="inlineStr">
+      <c r="B677" t="inlineStr">
         <is>
           <t>images/「イードおめでとう」_img1.jpg</t>
         </is>
       </c>
-      <c r="C678" t="inlineStr">
+      <c r="C677" t="inlineStr">
         <is>
           <t>عيد ,アラビア語</t>
         </is>
       </c>
     </row>
-    <row r="679">
-      <c r="A679" t="inlineStr">
+    <row r="678">
+      <c r="A678" t="inlineStr">
         <is>
           <t xml:space="preserve">「戦士」محارب
 ムハーリブ [muHaarib]
@@ -14723,19 +14701,19 @@
 1809 abudinges.tumblr </t>
         </is>
       </c>
-      <c r="B679" t="inlineStr">
+      <c r="B678" t="inlineStr">
         <is>
           <t>images/「戦士」_img1.jpg</t>
         </is>
       </c>
-      <c r="C679" t="inlineStr">
+      <c r="C678" t="inlineStr">
         <is>
           <t>ロゴ ,赤</t>
         </is>
       </c>
     </row>
-    <row r="680">
-      <c r="A680" t="inlineStr">
+    <row r="679">
+      <c r="A679" t="inlineStr">
         <is>
           <t xml:space="preserve">「ライブ」بث مباشر
 バッス・ムバーシル [ba^Th(un) mubaaShir(un)]
@@ -14744,19 +14722,19 @@
 2308 beIN SPORTS </t>
         </is>
       </c>
-      <c r="B680" t="inlineStr">
+      <c r="B679" t="inlineStr">
         <is>
           <t>images/「ライブ」_img1.jpg</t>
         </is>
       </c>
-      <c r="C680" t="inlineStr">
+      <c r="C679" t="inlineStr">
         <is>
           <t xml:space="preserve">生放送 ,試合 </t>
         </is>
       </c>
     </row>
-    <row r="681">
-      <c r="A681" t="inlineStr">
+    <row r="680">
+      <c r="A680" t="inlineStr">
         <is>
           <t xml:space="preserve">「信者」مُؤْمِنٌ
 ムッミン [mu'min(un)]
@@ -14765,19 +14743,19 @@
 2106 出典不明 </t>
         </is>
       </c>
-      <c r="B681" t="inlineStr">
+      <c r="B680" t="inlineStr">
         <is>
           <t>images/「信者」_img1.jpg</t>
         </is>
       </c>
-      <c r="C681" t="inlineStr">
+      <c r="C680" t="inlineStr">
         <is>
           <t>明暗 ,信仰</t>
         </is>
       </c>
     </row>
-    <row r="682">
-      <c r="A682" t="inlineStr">
+    <row r="681">
+      <c r="A681" t="inlineStr">
         <is>
           <t xml:space="preserve">「開⇔閉」
 مفتوح
@@ -14788,19 +14766,19 @@
 2312 Hussein Safina, behance </t>
         </is>
       </c>
-      <c r="B682" t="inlineStr">
+      <c r="B681" t="inlineStr">
         <is>
           <t>images/「開⇔閉」_img1.jpg</t>
         </is>
       </c>
-      <c r="C682" t="inlineStr">
+      <c r="C681" t="inlineStr">
         <is>
           <t>オープンマインド ,トグル</t>
         </is>
       </c>
     </row>
-    <row r="683">
-      <c r="A683" t="inlineStr">
+    <row r="682">
+      <c r="A682" t="inlineStr">
         <is>
           <t xml:space="preserve">「予想外な結末！」
 نهاية غير متوقعة
@@ -14808,19 +14786,19 @@
 2308 https://twitter.com/NatGeoMagArab/status/1159011433444593665 </t>
         </is>
       </c>
-      <c r="B683" t="inlineStr">
+      <c r="B682" t="inlineStr">
         <is>
           <t>images/「予想外な結末！」_img1.jpg</t>
         </is>
       </c>
-      <c r="C683" t="inlineStr">
+      <c r="C682" t="inlineStr">
         <is>
           <t>手書き語学 ,アラビア語 ,ウサギ</t>
         </is>
       </c>
     </row>
-    <row r="684">
-      <c r="A684" t="inlineStr">
+    <row r="683">
+      <c r="A683" t="inlineStr">
         <is>
           <t xml:space="preserve">「ベイルート・アニメイテッド」
 بیروت متحرّکة
@@ -14830,19 +14808,19 @@
 2308 arabic_script Instagram </t>
         </is>
       </c>
-      <c r="B684" t="inlineStr">
+      <c r="B683" t="inlineStr">
         <is>
           <t>images/「ベイルート・アニメイテッド」_img1.jpg</t>
         </is>
       </c>
-      <c r="C684" t="inlineStr">
+      <c r="C683" t="inlineStr">
         <is>
           <t>アニメ ,レバノン</t>
         </is>
       </c>
     </row>
-    <row r="685">
-      <c r="A685" t="inlineStr">
+    <row r="684">
+      <c r="A684" t="inlineStr">
         <is>
           <t xml:space="preserve">「夢みれば叶う」
 كُلُّ مُتَوَقَّعٍ آتٍ
@@ -14852,19 +14830,19 @@
 2108 Ahmed Madyan </t>
         </is>
       </c>
-      <c r="B685" t="inlineStr">
+      <c r="B684" t="inlineStr">
         <is>
           <t>images/「夢みれば叶う」_img1.jpg</t>
         </is>
       </c>
-      <c r="C685" t="inlineStr">
+      <c r="C684" t="inlineStr">
         <is>
           <t>希望 ,ドリカム</t>
         </is>
       </c>
     </row>
-    <row r="686">
-      <c r="A686" t="inlineStr">
+    <row r="685">
+      <c r="A685" t="inlineStr">
         <is>
           <t xml:space="preserve">「もし両者が人間のように鎧で武装して戦いに突入したら」
 لو خاضا معاركهما متسلحين بالدروع على غرار البش
@@ -14872,19 +14850,19 @@
 2404 https://x.com/NatGeoMagArab/status/1759284149456945464 </t>
         </is>
       </c>
-      <c r="B686" t="inlineStr">
+      <c r="B685" t="inlineStr">
         <is>
           <t>images/「もし両者が人間のように鎧で武装して戦_img1.jpg,images/「もし両者が人間のように鎧で武装して戦_img2.jpg</t>
         </is>
       </c>
-      <c r="C686" t="inlineStr">
+      <c r="C685" t="inlineStr">
         <is>
           <t>手書き語学 ,アラビア語 ,猫</t>
         </is>
       </c>
     </row>
-    <row r="687">
-      <c r="A687" t="inlineStr">
+    <row r="686">
+      <c r="A686" t="inlineStr">
         <is>
           <t xml:space="preserve">「全ては結びついている」
 كل شيء مترابط
@@ -14894,19 +14872,19 @@
 2308 Ahmed Madyan https://twitter.com/madyco22/status/1451990828298166273 </t>
         </is>
       </c>
-      <c r="B687" t="inlineStr">
+      <c r="B686" t="inlineStr">
         <is>
           <t>images/「全ては結びついている」_img1.jpg</t>
         </is>
       </c>
-      <c r="C687" t="inlineStr">
+      <c r="C686" t="inlineStr">
         <is>
           <t>一筆書き ,デザイン</t>
         </is>
       </c>
     </row>
-    <row r="688">
-      <c r="A688" t="inlineStr">
+    <row r="687">
+      <c r="A687" t="inlineStr">
         <is>
           <t xml:space="preserve">「初心者のためのスケッチトレーニング」
 تعليم الرسم للمبتدئين
@@ -14916,19 +14894,19 @@
 2308 free-bookspdf com </t>
         </is>
       </c>
-      <c r="B688" t="inlineStr">
+      <c r="B687" t="inlineStr">
         <is>
           <t>images/「初心者のためのスケッチトレーニング」_img1.jpg</t>
         </is>
       </c>
-      <c r="C688" t="inlineStr">
+      <c r="C687" t="inlineStr">
         <is>
           <t>イラスト ,絵</t>
         </is>
       </c>
     </row>
-    <row r="689">
-      <c r="A689" t="inlineStr">
+    <row r="688">
+      <c r="A688" t="inlineStr">
         <is>
           <t xml:space="preserve">「初心者のためのスルス体書道トレーニング」
 تعليم خط الثلث للمبتدئين
@@ -14938,19 +14916,19 @@
 2308 出典不明 </t>
         </is>
       </c>
-      <c r="B689" t="inlineStr">
+      <c r="B688" t="inlineStr">
         <is>
           <t>images/「初心者のためのスルス体書道トレーニン_img1.jpg</t>
         </is>
       </c>
-      <c r="C689" t="inlineStr">
+      <c r="C688" t="inlineStr">
         <is>
           <t>書道</t>
         </is>
       </c>
     </row>
-    <row r="690">
-      <c r="A690" t="inlineStr">
+    <row r="689">
+      <c r="A689" t="inlineStr">
         <is>
           <t xml:space="preserve">「笑顔でいなさい」خليك مبتسم
 カッリーク・ムブタスィム [Khallii-k mubtasim]
@@ -14959,19 +14937,19 @@
 2308 https://tmblr.co/Zj9tguYLXBvC </t>
         </is>
       </c>
-      <c r="B690" t="inlineStr">
+      <c r="B689" t="inlineStr">
         <is>
           <t>images/「笑顔でいなさい」_img1.jpg</t>
         </is>
       </c>
-      <c r="C690" t="inlineStr">
+      <c r="C689" t="inlineStr">
         <is>
           <t>スマイル ,名言</t>
         </is>
       </c>
     </row>
-    <row r="691">
-      <c r="A691" t="inlineStr">
+    <row r="690">
+      <c r="A690" t="inlineStr">
         <is>
           <t xml:space="preserve">自動車メーカー
 ⁦・「TOYOTA」( تويوتا )⁩
@@ -14983,19 +14961,19 @@
 2308 syarah com </t>
         </is>
       </c>
-      <c r="B691" t="inlineStr">
+      <c r="B690" t="inlineStr">
         <is>
           <t>images/自動車メーカー_img1.jpg,images/自動車メーカー_img2.jpg,images/自動車メーカー_img3.jpg,images/自動車メーカー_img4.jpg</t>
         </is>
       </c>
-      <c r="C691" t="inlineStr">
+      <c r="C690" t="inlineStr">
         <is>
           <t>日本車 ,韓国車</t>
         </is>
       </c>
     </row>
-    <row r="692">
-      <c r="A692" t="inlineStr">
+    <row r="691">
+      <c r="A691" t="inlineStr">
         <is>
           <t xml:space="preserve">「僕たちは協力して不可能を達成するよ」
 بالتعاون نحقق المحال
@@ -15005,19 +14983,19 @@
 2109 </t>
         </is>
       </c>
-      <c r="B692" t="inlineStr">
+      <c r="B691" t="inlineStr">
         <is>
           <t>images/「僕たちは協力して不可能を達成するよ」_img1.jpg</t>
         </is>
       </c>
-      <c r="C692" t="inlineStr">
+      <c r="C691" t="inlineStr">
         <is>
           <t>無理 ,ハム太郎</t>
         </is>
       </c>
     </row>
-    <row r="693">
-      <c r="A693" t="inlineStr">
+    <row r="692">
+      <c r="A692" t="inlineStr">
         <is>
           <t xml:space="preserve">「幸せは伝染性。喜びを広めよう」
 السعادة معدية فأشع الفرح
@@ -15027,19 +15005,19 @@
 2511 instagram　com/p/fVEfxEo7Va/ </t>
         </is>
       </c>
-      <c r="B693" t="inlineStr">
+      <c r="B692" t="inlineStr">
         <is>
           <t>images/「幸せは伝染性。喜びを広めよう」_img1.jpg</t>
         </is>
       </c>
-      <c r="C693" t="inlineStr">
+      <c r="C692" t="inlineStr">
         <is>
           <t>拡散希望</t>
         </is>
       </c>
     </row>
-    <row r="694">
-      <c r="A694" t="inlineStr">
+    <row r="693">
+      <c r="A693" t="inlineStr">
         <is>
           <t xml:space="preserve">「ストレスは人間だけのものではない」
 الشعور بالتوتر ليس حكرًا على البشر
@@ -15047,19 +15025,19 @@
 2408 https://x.com/NatGeoMagArab/status/1736755816911487420 </t>
         </is>
       </c>
-      <c r="B694" t="inlineStr">
+      <c r="B693" t="inlineStr">
         <is>
           <t>images/「ストレスは人間だけのものではない」_img1.jpg</t>
         </is>
       </c>
-      <c r="C694" t="inlineStr">
+      <c r="C693" t="inlineStr">
         <is>
           <t>手書き語学 ,アラビア語 ,ストレス</t>
         </is>
       </c>
     </row>
-    <row r="695">
-      <c r="A695" t="inlineStr">
+    <row r="694">
+      <c r="A694" t="inlineStr">
         <is>
           <t xml:space="preserve">「私達は出来ます！」
 نستطيع فعلها
@@ -15069,19 +15047,19 @@
 2308 NAHARBAHIJ com </t>
         </is>
       </c>
-      <c r="B695" t="inlineStr">
+      <c r="B694" t="inlineStr">
         <is>
           <t>images/「私達は出来ます！」_img1.jpg</t>
         </is>
       </c>
-      <c r="C695" t="inlineStr">
+      <c r="C694" t="inlineStr">
         <is>
           <t>女性 ,パロディ</t>
         </is>
       </c>
     </row>
-    <row r="696">
-      <c r="A696" t="inlineStr">
+    <row r="695">
+      <c r="A695" t="inlineStr">
         <is>
           <t xml:space="preserve">「全然分からん」ولا فاهم إشي
 ウラー・ファーヒム・イシ [w-laa faahim 'iShy]
@@ -15091,19 +15069,19 @@
 2209 出典不明 </t>
         </is>
       </c>
-      <c r="B696" t="inlineStr">
+      <c r="B695" t="inlineStr">
         <is>
           <t>images/「全然分からん」_img1.jpg</t>
         </is>
       </c>
-      <c r="C696" t="inlineStr">
+      <c r="C695" t="inlineStr">
         <is>
           <t>アラビア語</t>
         </is>
       </c>
     </row>
-    <row r="697">
-      <c r="A697" t="inlineStr">
+    <row r="696">
+      <c r="A696" t="inlineStr">
         <is>
           <t xml:space="preserve">「人間は一人ひとり、特別な才がある。だから自分を他人と比べるのはやめよう」
 لكل إنسان مواهبه الخاصة 
@@ -15112,19 +15090,19 @@
 1812 Gwid3 </t>
         </is>
       </c>
-      <c r="B697" t="inlineStr">
+      <c r="B696" t="inlineStr">
         <is>
           <t>images/「人間は一人ひとり、特別な才がある。だ_img1.jpg</t>
         </is>
       </c>
-      <c r="C697" t="inlineStr">
+      <c r="C696" t="inlineStr">
         <is>
           <t>自尊 ,プライド</t>
         </is>
       </c>
     </row>
-    <row r="698">
-      <c r="A698" t="inlineStr">
+    <row r="697">
+      <c r="A697" t="inlineStr">
         <is>
           <t xml:space="preserve">「デザイン」تَصْمِيمٌ
 タスミーム [ta_smiim(un)]
@@ -15132,19 +15110,19 @@
 1903 arabictypography com </t>
         </is>
       </c>
-      <c r="B698" t="inlineStr">
+      <c r="B697" t="inlineStr">
         <is>
           <t>images/「デザイン」_img1.jpg</t>
         </is>
       </c>
-      <c r="C698" t="inlineStr">
+      <c r="C697" t="inlineStr">
         <is>
           <t>文字 ,タイポグラフィー</t>
         </is>
       </c>
     </row>
-    <row r="699">
-      <c r="A699" t="inlineStr">
+    <row r="698">
+      <c r="A698" t="inlineStr">
         <is>
           <t xml:space="preserve">「この猫は食事をシェアするのが嫌い！」
 هذه القطة لا تحب مشاركة الطعام
@@ -15153,19 +15131,19 @@
 2605 facebook com/alahram/videos/2154923608133231/ </t>
         </is>
       </c>
-      <c r="B699" t="inlineStr">
+      <c r="B698" t="inlineStr">
         <is>
           <t>images/「この猫は食事をシェアするのが嫌い！」_img1.jpg</t>
         </is>
       </c>
-      <c r="C699" t="inlineStr">
+      <c r="C698" t="inlineStr">
         <is>
           <t>猫 ,ネコ</t>
         </is>
       </c>
     </row>
-    <row r="700">
-      <c r="A700" t="inlineStr">
+    <row r="699">
+      <c r="A699" t="inlineStr">
         <is>
           <t xml:space="preserve">「怪獣との戦いでは自分が怪獣化せぬよう警戒しなさい」
 احذر عند محاربة الوحوش ألا تصبح واحدا منهم
@@ -15175,19 +15153,19 @@
 2108 warag-3nb.tumblr </t>
         </is>
       </c>
-      <c r="B700" t="inlineStr">
+      <c r="B699" t="inlineStr">
         <is>
           <t>images/「怪獣との戦いでは自分が怪獣化せぬよう_img1.jpg,images/ 「怪獣との戦いでは自分が怪獣化せぬよう_img2.jpg</t>
         </is>
       </c>
-      <c r="C700" t="inlineStr">
+      <c r="C699" t="inlineStr">
         <is>
           <t>正気 ,モンスター</t>
         </is>
       </c>
     </row>
-    <row r="701">
-      <c r="A701" t="inlineStr">
+    <row r="700">
+      <c r="A700" t="inlineStr">
         <is>
           <t xml:space="preserve">「錯視アート」فن الخداع البصري
 ファンヌ_ルヒダーイ_ルバサリーイ [fannu l-Khidaa*i l-ba_sariyy]
@@ -15196,19 +15174,19 @@
 2409 https://online.pubhtml5.com/idtb/neft/ </t>
         </is>
       </c>
-      <c r="B701" t="inlineStr">
+      <c r="B700" t="inlineStr">
         <is>
           <t>images/「錯視アート」_img1.jpg</t>
         </is>
       </c>
-      <c r="C701" t="inlineStr">
+      <c r="C700" t="inlineStr">
         <is>
           <t>トリックアート</t>
         </is>
       </c>
     </row>
-    <row r="702">
-      <c r="A702" t="inlineStr">
+    <row r="701">
+      <c r="A701" t="inlineStr">
         <is>
           <t xml:space="preserve">「自然界の消防士の訓練」
 تدريبات رجال الإطفاء في الطبيعة
@@ -15216,19 +15194,19 @@
 2308 https://twitter.com/NatGeoMagArab/status/1462420543890608129 </t>
         </is>
       </c>
-      <c r="B702" t="inlineStr">
+      <c r="B701" t="inlineStr">
         <is>
           <t>images/「自然界の消防士の訓練」_img1.jpg,images/ 「自然界の消防士の訓練」_img2.jpg</t>
         </is>
       </c>
-      <c r="C702" t="inlineStr">
+      <c r="C701" t="inlineStr">
         <is>
           <t>手書き語学 ,アラビア語 ,ヒグマ</t>
         </is>
       </c>
     </row>
-    <row r="703">
-      <c r="A703" t="inlineStr">
+    <row r="702">
+      <c r="A702" t="inlineStr">
         <is>
           <t xml:space="preserve">「救助」إسعاف
 イスアーフ ['is*aaf]
@@ -15237,19 +15215,19 @@
 2109 ambulance gov ae </t>
         </is>
       </c>
-      <c r="B703" t="inlineStr">
+      <c r="B702" t="inlineStr">
         <is>
           <t>images/「救助」_img1.jpg</t>
         </is>
       </c>
-      <c r="C703" t="inlineStr">
+      <c r="C702" t="inlineStr">
         <is>
           <t>救急車 ,はたらくくるま</t>
         </is>
       </c>
     </row>
-    <row r="704">
-      <c r="A704" t="inlineStr">
+    <row r="703">
+      <c r="A703" t="inlineStr">
         <is>
           <t xml:space="preserve">「感情／感覚」الإحْسَاسْ
 アルイヒサース [al-'iHsaas]
@@ -15258,19 +15236,19 @@
 2308 iN49R </t>
         </is>
       </c>
-      <c r="B704" t="inlineStr">
+      <c r="B703" t="inlineStr">
         <is>
           <t>images/「感情／感覚」_img1.jpg</t>
         </is>
       </c>
-      <c r="C704" t="inlineStr">
+      <c r="C703" t="inlineStr">
         <is>
           <t>オフ ,一休み</t>
         </is>
       </c>
     </row>
-    <row r="705">
-      <c r="A705" t="inlineStr">
+    <row r="704">
+      <c r="A704" t="inlineStr">
         <is>
           <t xml:space="preserve">「ひらめき」إلهام
 イルハーム ['lhaam]
@@ -15282,19 +15260,19 @@
 2103 出典不明 </t>
         </is>
       </c>
-      <c r="B705" t="inlineStr">
+      <c r="B704" t="inlineStr">
         <is>
           <t>images/「ひらめき」_img1.jpg</t>
         </is>
       </c>
-      <c r="C705" t="inlineStr">
+      <c r="C704" t="inlineStr">
         <is>
           <t>アラビア語</t>
         </is>
       </c>
     </row>
-    <row r="706">
-      <c r="A706" t="inlineStr">
+    <row r="705">
+      <c r="A705" t="inlineStr">
         <is>
           <t xml:space="preserve">「Ibdaa／クリエイティビティ」
 إبداع
@@ -15303,19 +15281,19 @@
 2308 Ibdaa Design &amp; Decoration Office </t>
         </is>
       </c>
-      <c r="B706" t="inlineStr">
+      <c r="B705" t="inlineStr">
         <is>
           <t>images/「Ibdaa／クリエイティビティ」_img1.jpg</t>
         </is>
       </c>
-      <c r="C706" t="inlineStr">
+      <c r="C705" t="inlineStr">
         <is>
           <t>創造性 ,独自性</t>
         </is>
       </c>
     </row>
-    <row r="707">
-      <c r="A707" t="inlineStr">
+    <row r="706">
+      <c r="A706" t="inlineStr">
         <is>
           <t xml:space="preserve">「奮闘なくして進歩なし」
 بدون كفاح لايوجد تقدم
@@ -15325,19 +15303,19 @@
 2105 ROUYMS TUMBLR COM </t>
         </is>
       </c>
-      <c r="B707" t="inlineStr">
+      <c r="B706" t="inlineStr">
         <is>
           <t>images/「奮闘なくして進歩なし」_img1.jpg</t>
         </is>
       </c>
-      <c r="C707" t="inlineStr">
+      <c r="C706" t="inlineStr">
         <is>
           <t>努力 ,三角形</t>
         </is>
       </c>
     </row>
-    <row r="708">
-      <c r="A708" t="inlineStr">
+    <row r="707">
+      <c r="A707" t="inlineStr">
         <is>
           <t xml:space="preserve">「木に登れば熊の危険を避けられるとお考えなら、考え直しましょう！」 
 إن اعتقدت أنك بمنأى عن خطر الدب عند تسلق الأشجار.. راجع حساباتك
@@ -15345,19 +15323,19 @@
 2202 NatGeoMagArab </t>
         </is>
       </c>
-      <c r="B708" t="inlineStr">
+      <c r="B707" t="inlineStr">
         <is>
           <t>images/「木に登れば熊の危険を避けられるとお考.jpeg</t>
         </is>
       </c>
-      <c r="C708" t="inlineStr">
+      <c r="C707" t="inlineStr">
         <is>
           <t>クマ</t>
         </is>
       </c>
     </row>
-    <row r="709">
-      <c r="A709" t="inlineStr">
+    <row r="708">
+      <c r="A708" t="inlineStr">
         <is>
           <t xml:space="preserve">「卒業おめでとう」مبروك التخرج
 マブルーク・タカッルジ [mabruuk a^taKharruj]
@@ -15366,19 +15344,19 @@
 2308 https://instagram.com/fatoomworld </t>
         </is>
       </c>
-      <c r="B709" t="inlineStr">
+      <c r="B708" t="inlineStr">
         <is>
           <t>images/「卒業おめでとう」_img1.jpg</t>
         </is>
       </c>
-      <c r="C709" t="inlineStr">
+      <c r="C708" t="inlineStr">
         <is>
           <t>卒業 ,イラスト</t>
         </is>
       </c>
     </row>
-    <row r="710">
-      <c r="A710" t="inlineStr">
+    <row r="709">
+      <c r="A709" t="inlineStr">
         <is>
           <t xml:space="preserve">「停止距離の計算」
 حساب مسافة التوقف
@@ -15388,19 +15366,19 @@
 2109 assurance-auto-info </t>
         </is>
       </c>
-      <c r="B710" t="inlineStr">
+      <c r="B709" t="inlineStr">
         <is>
           <t>images/「停止距離の計算」_img1.jpg</t>
         </is>
       </c>
-      <c r="C710" t="inlineStr">
+      <c r="C709" t="inlineStr">
         <is>
           <t>保険 ,自動車</t>
         </is>
       </c>
     </row>
-    <row r="711">
-      <c r="A711" t="inlineStr">
+    <row r="710">
+      <c r="A710" t="inlineStr">
         <is>
           <t xml:space="preserve">「教師要らず：10日でフランス語会話」
 بدون معلم
@@ -15410,19 +15388,19 @@
 2308 englais-best com </t>
         </is>
       </c>
-      <c r="B711" t="inlineStr">
+      <c r="B710" t="inlineStr">
         <is>
           <t>images/「教師要らず：10日でフランス語会話」_img1.jpg</t>
         </is>
       </c>
-      <c r="C711" t="inlineStr">
+      <c r="C710" t="inlineStr">
         <is>
           <t>教師なし学習</t>
         </is>
       </c>
     </row>
-    <row r="712">
-      <c r="A712" t="inlineStr">
+    <row r="711">
+      <c r="A711" t="inlineStr">
         <is>
           <t xml:space="preserve">「衝突」تصادم
 タサードゥム [ta_saadum]
@@ -15431,19 +15409,19 @@
 1810 </t>
         </is>
       </c>
-      <c r="B712" t="inlineStr">
+      <c r="B711" t="inlineStr">
         <is>
           <t>images/「衝突」_img1.jpg</t>
         </is>
       </c>
-      <c r="C712" t="inlineStr">
+      <c r="C711" t="inlineStr">
         <is>
           <t>あらびあや</t>
         </is>
       </c>
     </row>
-    <row r="713">
-      <c r="A713" t="inlineStr">
+    <row r="712">
+      <c r="A712" t="inlineStr">
         <is>
           <t xml:space="preserve">「楽観主義」تَفَاؤُلٌ
 タファーウル [tafaa'ul(un)]
@@ -15452,19 +15430,19 @@
 1904 arabictypography com </t>
         </is>
       </c>
-      <c r="B713" t="inlineStr">
+      <c r="B712" t="inlineStr">
         <is>
           <t>images/「楽観主義」_img1.jpg</t>
         </is>
       </c>
-      <c r="C713" t="inlineStr">
+      <c r="C712" t="inlineStr">
         <is>
           <t>やわらか ,緑</t>
         </is>
       </c>
     </row>
-    <row r="714">
-      <c r="A714" t="inlineStr">
+    <row r="713">
+      <c r="A713" t="inlineStr">
         <is>
           <t xml:space="preserve">「シベリアジャコウジカは、絶滅の危機にあると見なされている」
 يعد "أيل المسك السيبيري" مهددًا بالانقراض
@@ -15472,19 +15450,19 @@
 2308 https://twitter.com/NatGeoMagArab/status/1320666649045790720 </t>
         </is>
       </c>
-      <c r="B714" t="inlineStr">
+      <c r="B713" t="inlineStr">
         <is>
           <t>images/「シベリアジャコウジカは、絶滅の危機に_img1.jpg,images/「シベリアジャコウジカは、絶滅の危機に_img2.jpg</t>
         </is>
       </c>
-      <c r="C714" t="inlineStr">
+      <c r="C713" t="inlineStr">
         <is>
           <t>手書き語学 ,シベリア</t>
         </is>
       </c>
     </row>
-    <row r="715">
-      <c r="A715" t="inlineStr">
+    <row r="714">
+      <c r="A714" t="inlineStr">
         <is>
           <t xml:space="preserve">「融合／折衷／フュージョン」
 انصهار
@@ -15493,38 +15471,38 @@
 1811 elmahdyart Instagram </t>
         </is>
       </c>
-      <c r="B715" t="inlineStr">
+      <c r="B714" t="inlineStr">
         <is>
           <t>images/「融合／折衷／フュージョン」_img1.jpg</t>
         </is>
       </c>
-      <c r="C715" t="inlineStr">
+      <c r="C714" t="inlineStr">
         <is>
           <t>カリグラフィー ,書道</t>
         </is>
       </c>
     </row>
-    <row r="716">
-      <c r="A716" t="inlineStr">
+    <row r="715">
+      <c r="A715" t="inlineStr">
         <is>
           <t xml:space="preserve">「この子供は、昼寝をしようとする母親を邪魔しているようだ」
 「場所はインドのトラ保護区、バンダウガル公園。トラは生態ピラミッドのトップの捕食動物だが、最もリスクの高い絶滅危惧種のひとつである」
 2308 https://twitter.com/natgeomagarab/status/1553681890665586689 </t>
         </is>
       </c>
-      <c r="B716" t="inlineStr">
+      <c r="B715" t="inlineStr">
         <is>
           <t>images/「この子供は、昼寝をしようとする母親を_img1.jpg,images/「この子供は、昼寝をしようとする母親を_img2.jpg</t>
         </is>
       </c>
-      <c r="C716" t="inlineStr">
+      <c r="C715" t="inlineStr">
         <is>
           <t>手書き語学 ,アラビア語 ,トラ</t>
         </is>
       </c>
     </row>
-    <row r="717">
-      <c r="A717" t="inlineStr">
+    <row r="716">
+      <c r="A716" t="inlineStr">
         <is>
           <t xml:space="preserve">「もし敬意が落ちたら、それと一緒に全部落ちるのだ」
 إن سقط الإحترام سقط معه كل شيء
@@ -15533,19 +15511,19 @@
 2109 出典不明 </t>
         </is>
       </c>
-      <c r="B717" t="inlineStr">
+      <c r="B716" t="inlineStr">
         <is>
           <t>images/「もし敬意が落ちたら、それと一緒に全部_img1.jpg</t>
         </is>
       </c>
-      <c r="C717" t="inlineStr">
+      <c r="C716" t="inlineStr">
         <is>
           <t>リスペクト ,落書き</t>
         </is>
       </c>
     </row>
-    <row r="718">
-      <c r="A718" t="inlineStr">
+    <row r="717">
+      <c r="A717" t="inlineStr">
         <is>
           <t xml:space="preserve">「エジプト特許庁」
 مكتب براءات الاختراع المصرى
@@ -15555,19 +15533,19 @@
 2312 </t>
         </is>
       </c>
-      <c r="B718" t="inlineStr">
+      <c r="B717" t="inlineStr">
         <is>
           <t>images/「エジプト特許庁」_img1.jpg</t>
         </is>
       </c>
-      <c r="C718" t="inlineStr">
+      <c r="C717" t="inlineStr">
         <is>
           <t>patent</t>
         </is>
       </c>
     </row>
-    <row r="719">
-      <c r="A719" t="inlineStr">
+    <row r="718">
+      <c r="A718" t="inlineStr">
         <is>
           <t xml:space="preserve">「選挙」إنتخابات
 インティカーバート [intiKhaabaat]
@@ -15576,19 +15554,19 @@
 2311 nna-leb gov lb </t>
         </is>
       </c>
-      <c r="B719" t="inlineStr">
+      <c r="B718" t="inlineStr">
         <is>
           <t>images/「選挙」_img1.jpg</t>
         </is>
       </c>
-      <c r="C719" t="inlineStr">
+      <c r="C718" t="inlineStr">
         <is>
           <t>選挙 ,投票</t>
         </is>
       </c>
     </row>
-    <row r="720">
-      <c r="A720" t="inlineStr">
+    <row r="719">
+      <c r="A719" t="inlineStr">
         <is>
           <t xml:space="preserve">「待ちぼうけ」إنتظار
 インティザール [inti_Dhaar]
@@ -15597,19 +15575,19 @@
 1809 in4sser.tumblr </t>
         </is>
       </c>
-      <c r="B720" t="inlineStr">
+      <c r="B719" t="inlineStr">
         <is>
           <t>images/「待ちぼうけ」_img1.jpg</t>
         </is>
       </c>
-      <c r="C720" t="inlineStr">
+      <c r="C719" t="inlineStr">
         <is>
           <t>遅すぎ ,辛抱</t>
         </is>
       </c>
     </row>
-    <row r="721">
-      <c r="A721" t="inlineStr">
+    <row r="720">
+      <c r="A720" t="inlineStr">
         <is>
           <t xml:space="preserve">「試験」إختبار
 イクティバール [iKhtibaar]
@@ -15618,19 +15596,19 @@
 2109 出典不明 </t>
         </is>
       </c>
-      <c r="B721" t="inlineStr">
+      <c r="B720" t="inlineStr">
         <is>
           <t>images/「試験」_img1.jpg</t>
         </is>
       </c>
-      <c r="C721" t="inlineStr">
+      <c r="C720" t="inlineStr">
         <is>
           <t>テスト ,考査</t>
         </is>
       </c>
     </row>
-    <row r="722">
-      <c r="A722" t="inlineStr">
+    <row r="721">
+      <c r="A721" t="inlineStr">
         <is>
           <t xml:space="preserve">「チャンネル登録」اشتراك
 イシティラーク [iShtiraak]
@@ -15639,19 +15617,19 @@
 2308 </t>
         </is>
       </c>
-      <c r="B722" t="inlineStr">
+      <c r="B721" t="inlineStr">
         <is>
           <t>images/「チャンネル登録」_img1.jpg</t>
         </is>
       </c>
-      <c r="C722" t="inlineStr">
+      <c r="C721" t="inlineStr">
         <is>
           <t>Subscribe ,YouTube</t>
         </is>
       </c>
     </row>
-    <row r="723">
-      <c r="A723" t="inlineStr">
+    <row r="722">
+      <c r="A722" t="inlineStr">
         <is>
           <t xml:space="preserve">「スマイル」ابتسام
 イブティサーム [ibtisaam]
@@ -15659,37 +15637,37 @@
 1903 behance Written-Visuals </t>
         </is>
       </c>
+      <c r="B722" t="inlineStr">
+        <is>
+          <t>images/「スマイル」_img1.jpg</t>
+        </is>
+      </c>
+      <c r="C722" t="inlineStr">
+        <is>
+          <t>スマイリー ,ツ</t>
+        </is>
+      </c>
+    </row>
+    <row r="723">
+      <c r="A723" t="inlineStr">
+        <is>
+          <t xml:space="preserve">「身体の一部として…」
+2308 https://twitter.com/NatGeoMagArab/status/1528292080337813504 </t>
+        </is>
+      </c>
       <c r="B723" t="inlineStr">
         <is>
-          <t>images/「スマイル」_img1.jpg</t>
+          <t>images/「身体の一部として…」_img1.jpg</t>
         </is>
       </c>
       <c r="C723" t="inlineStr">
         <is>
-          <t>スマイリー ,ツ</t>
+          <t>手書き語学 ,カンガルー</t>
         </is>
       </c>
     </row>
     <row r="724">
       <c r="A724" t="inlineStr">
-        <is>
-          <t xml:space="preserve">「身体の一部として…」
-2308 https://twitter.com/NatGeoMagArab/status/1528292080337813504 </t>
-        </is>
-      </c>
-      <c r="B724" t="inlineStr">
-        <is>
-          <t>images/「身体の一部として…」_img1.jpg</t>
-        </is>
-      </c>
-      <c r="C724" t="inlineStr">
-        <is>
-          <t>手書き語学 ,カンガルー</t>
-        </is>
-      </c>
-    </row>
-    <row r="725">
-      <c r="A725" t="inlineStr">
         <is>
           <t xml:space="preserve">「ディスカバリー」إكتشاف
 イクティシャーフ [iktiShaaf]
@@ -15697,19 +15675,19 @@
 2308 tephanegabrielli com </t>
         </is>
       </c>
-      <c r="B725" t="inlineStr">
+      <c r="B724" t="inlineStr">
         <is>
           <t>images/「ディスカバリー」_img1.jpg</t>
         </is>
       </c>
-      <c r="C725" t="inlineStr">
+      <c r="C724" t="inlineStr">
         <is>
           <t>discovery ,デザイン</t>
         </is>
       </c>
     </row>
-    <row r="726">
-      <c r="A726" t="inlineStr">
+    <row r="725">
+      <c r="A725" t="inlineStr">
         <is>
           <t xml:space="preserve">「重力波の発見は新しい窓を開いた」
 فتَح اكتشاف موجات الجاذبية نافذة جديدة
@@ -15717,19 +15695,19 @@
 2308 https://twitter.com/SciTalk2U/status/1454891943440289793 </t>
         </is>
       </c>
-      <c r="B726" t="inlineStr">
+      <c r="B725" t="inlineStr">
         <is>
           <t>images/「重力波の発見は新しい窓を開いた」_img1.jpg</t>
         </is>
       </c>
-      <c r="C726" t="inlineStr">
+      <c r="C725" t="inlineStr">
         <is>
           <t>手書き語学 ,アラビア語 ,重力波</t>
         </is>
       </c>
     </row>
-    <row r="727">
-      <c r="A727" t="inlineStr">
+    <row r="726">
+      <c r="A726" t="inlineStr">
         <is>
           <t xml:space="preserve">「微笑みに微笑み。先にした人の方が美しい」
 الإبتسامة بالإبتسامة والبادئ أجمل
@@ -15738,19 +15716,19 @@
 2104 出典不明 </t>
         </is>
       </c>
-      <c r="B727" t="inlineStr">
+      <c r="B726" t="inlineStr">
         <is>
           <t>images/「微笑みに微笑み。先にした人の方が美し_img1.jpg,images/「微笑みに微笑み。先にした人の方が美し_img2.jpg</t>
         </is>
       </c>
-      <c r="C727" t="inlineStr">
+      <c r="C726" t="inlineStr">
         <is>
           <t>スマイル ,名言</t>
         </is>
       </c>
     </row>
-    <row r="728">
-      <c r="A728" t="inlineStr">
+    <row r="727">
+      <c r="A727" t="inlineStr">
         <is>
           <t xml:space="preserve">「笑顔」ابتسامة
 イブティサーマ [ibtisaama(tun)]
@@ -15759,19 +15737,19 @@
 2308 satokomatsu, minne </t>
         </is>
       </c>
-      <c r="B728" t="inlineStr">
+      <c r="B727" t="inlineStr">
         <is>
           <t>images/「笑顔」_img1.jpg</t>
         </is>
       </c>
-      <c r="C728" t="inlineStr">
+      <c r="C727" t="inlineStr">
         <is>
           <t>スマイル ,ツ</t>
         </is>
       </c>
     </row>
-    <row r="729">
-      <c r="A729" t="inlineStr">
+    <row r="728">
+      <c r="A728" t="inlineStr">
         <is>
           <t xml:space="preserve">「信仰」ايمان
 イーマーン ['iimaan]
@@ -15780,19 +15758,19 @@
 2506 instagram com/p/6ST-WHOOkJ/ </t>
         </is>
       </c>
-      <c r="B729" t="inlineStr">
+      <c r="B728" t="inlineStr">
         <is>
           <t>images/「信仰」_img1.jpg</t>
         </is>
       </c>
-      <c r="C729" t="inlineStr">
+      <c r="C728" t="inlineStr">
         <is>
           <t>宗教 ,信念</t>
         </is>
       </c>
     </row>
-    <row r="730">
-      <c r="A730" t="inlineStr">
+    <row r="729">
+      <c r="A729" t="inlineStr">
         <is>
           <t xml:space="preserve">「放送」إذاعة
 イザーア ['iDhaa*a]
@@ -15801,19 +15779,19 @@
 2404 heemades, Instagram </t>
         </is>
       </c>
-      <c r="B730" t="inlineStr">
+      <c r="B729" t="inlineStr">
         <is>
           <t>images/「放送」_img1.jpg</t>
         </is>
       </c>
-      <c r="C730" t="inlineStr">
+      <c r="C729" t="inlineStr">
         <is>
           <t>デザイン ,ラジオ</t>
         </is>
       </c>
     </row>
-    <row r="731">
-      <c r="A731" t="inlineStr">
+    <row r="730">
+      <c r="A730" t="inlineStr">
         <is>
           <t xml:space="preserve">「かきとりのちから」
 مهاراتي الإملائية
@@ -15822,19 +15800,19 @@
 2308 iqrawaoktoub.wordpress com </t>
         </is>
       </c>
-      <c r="B731" t="inlineStr">
+      <c r="B730" t="inlineStr">
         <is>
           <t>images/「かきとりのちから」_img1.jpg</t>
         </is>
       </c>
-      <c r="C731" t="inlineStr">
+      <c r="C730" t="inlineStr">
         <is>
           <t>国語 ,教材</t>
         </is>
       </c>
     </row>
-    <row r="732">
-      <c r="A732" t="inlineStr">
+    <row r="731">
+      <c r="A731" t="inlineStr">
         <is>
           <t xml:space="preserve">「歴史を作った男たち」
 رجال صنعوا التاريخ
@@ -15844,38 +15822,38 @@
 2410 https://x.gd/Wl5rJ </t>
         </is>
       </c>
-      <c r="B732" t="inlineStr">
+      <c r="B731" t="inlineStr">
         <is>
           <t>images/「歴史を作った男たち」_img1.jpg</t>
         </is>
       </c>
-      <c r="C732" t="inlineStr">
+      <c r="C731" t="inlineStr">
         <is>
           <t>偉人</t>
         </is>
       </c>
     </row>
-    <row r="733">
-      <c r="A733" t="inlineStr">
+    <row r="732">
+      <c r="A732" t="inlineStr">
         <is>
           <t xml:space="preserve">「無限の宇宙を旅した光」
 「何百年もの末にジェイムズ・ウェッブ望遠鏡のレンズの上に落ち、我々に遠い宇宙の美しさを見せてくれる。最も純粋な形と最も素晴らしい姿で」
 2308 https://twitter.com/NatGeoMagArab/status/1557811592636485632 </t>
         </is>
       </c>
-      <c r="B733" t="inlineStr">
+      <c r="B732" t="inlineStr">
         <is>
           <t>images/「無限の宇宙を旅した光」_img1.jpg</t>
         </is>
       </c>
-      <c r="C733" t="inlineStr">
+      <c r="C732" t="inlineStr">
         <is>
           <t>手書き語学 ,宇宙</t>
         </is>
       </c>
     </row>
-    <row r="734">
-      <c r="A734" t="inlineStr">
+    <row r="733">
+      <c r="A733" t="inlineStr">
         <is>
           <t xml:space="preserve">「日本好きになり行きたくなる20項」
 عشرون شيئا يجعلك تحب اليابان وترغب في زيارتها
@@ -15884,19 +15862,19 @@
 2308 wattpad </t>
         </is>
       </c>
-      <c r="B734" t="inlineStr">
+      <c r="B733" t="inlineStr">
         <is>
           <t>images/「日本好きになり行きたくなる20項」_img1.jpg</t>
         </is>
       </c>
-      <c r="C734" t="inlineStr">
+      <c r="C733" t="inlineStr">
         <is>
           <t>اليابان ,Japan</t>
         </is>
       </c>
     </row>
-    <row r="735">
-      <c r="A735" t="inlineStr">
+    <row r="734">
+      <c r="A734" t="inlineStr">
         <is>
           <t xml:space="preserve">「ピッタリの瞬間に撮影され、ドラゴンが火を噴いているように見える」
 التُقطت في اللحظة المناسبة لتبدو مثل تنين ينفث اللهب
@@ -15904,19 +15882,19 @@
 2509 https://twitter.com/NatGeoMagArab/status/1588780660269150208 </t>
         </is>
       </c>
-      <c r="B735" t="inlineStr">
+      <c r="B734" t="inlineStr">
         <is>
           <t>images/「ピッタリの瞬間に撮影され、ドラゴンが_img1.jpg,images/ 「ピッタリの瞬間に撮影され、ドラゴンが_img2.jpg</t>
         </is>
       </c>
-      <c r="C735" t="inlineStr">
+      <c r="C734" t="inlineStr">
         <is>
           <t xml:space="preserve">ドラゴン </t>
         </is>
       </c>
     </row>
-    <row r="736">
-      <c r="A736" t="inlineStr">
+    <row r="735">
+      <c r="A735" t="inlineStr">
         <is>
           <t xml:space="preserve">「満足は不滅の宝である」
 القَناعَةُ كنز لا يَفنَى
@@ -15926,55 +15904,55 @@
 2308 kareem mrghani </t>
         </is>
       </c>
+      <c r="B735" t="inlineStr">
+        <is>
+          <t>images/「満足は不滅の宝である」_img1.jpg</t>
+        </is>
+      </c>
+      <c r="C735" t="inlineStr">
+        <is>
+          <t>幸福度</t>
+        </is>
+      </c>
+    </row>
+    <row r="736">
+      <c r="A736" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ゴシキセイガイインコ。
+2409 https://twitter.com/NatGeoMagArab/status/1600022262014676992 </t>
+        </is>
+      </c>
       <c r="B736" t="inlineStr">
         <is>
-          <t>images/「満足は不滅の宝である」_img1.jpg</t>
+          <t>images/ゴシキセイガイインコ。_img1.jpg</t>
         </is>
       </c>
       <c r="C736" t="inlineStr">
         <is>
-          <t>幸福度</t>
+          <t>手書き語学 ,アラビア語,オウム</t>
         </is>
       </c>
     </row>
     <row r="737">
       <c r="A737" t="inlineStr">
         <is>
-          <t xml:space="preserve">ゴシキセイガイインコ。
-2409 https://twitter.com/NatGeoMagArab/status/1600022262014676992 </t>
+          <t xml:space="preserve">モモンガ。
+2403 https://twitter.com/NatGeoMagArab/status/1552541872966344704 </t>
         </is>
       </c>
       <c r="B737" t="inlineStr">
         <is>
-          <t>images/ゴシキセイガイインコ。_img1.jpg</t>
+          <t>images/モモンガ。_img1.jpg,images/ モモンガ。_img2.jpg</t>
         </is>
       </c>
       <c r="C737" t="inlineStr">
         <is>
-          <t>手書き語学 ,アラビア語,オウム</t>
+          <t>手書き語学 ,アラビア語 ,モモンガ</t>
         </is>
       </c>
     </row>
     <row r="738">
       <c r="A738" t="inlineStr">
-        <is>
-          <t xml:space="preserve">モモンガ。
-2403 https://twitter.com/NatGeoMagArab/status/1552541872966344704 </t>
-        </is>
-      </c>
-      <c r="B738" t="inlineStr">
-        <is>
-          <t>images/モモンガ。_img1.jpg,images/ モモンガ。_img2.jpg</t>
-        </is>
-      </c>
-      <c r="C738" t="inlineStr">
-        <is>
-          <t>手書き語学 ,アラビア語 ,モモンガ</t>
-        </is>
-      </c>
-    </row>
-    <row r="739">
-      <c r="A739" t="inlineStr">
         <is>
           <t xml:space="preserve">「象の群れ。ドローンの音から逃げている」
 قطيع من الفيلة يفر هاربًا من صوت الدرون
@@ -15986,56 +15964,56 @@
 2009 https://twitter.com/NatGeoMagArab/status/1302970033627258881 </t>
         </is>
       </c>
+      <c r="B738" t="inlineStr">
+        <is>
+          <t>images/「象の群れ。ドローンの音から逃げている.jpg</t>
+        </is>
+      </c>
+      <c r="C738" t="inlineStr">
+        <is>
+          <t>ゾウ ,ドローン</t>
+        </is>
+      </c>
+    </row>
+    <row r="739">
+      <c r="A739" t="inlineStr">
+        <is>
+          <t xml:space="preserve">カルマン線。
+2308 https://twitter.com/NatGeoMagArab/status/1536436999522881536 </t>
+        </is>
+      </c>
       <c r="B739" t="inlineStr">
         <is>
-          <t>images/「象の群れ。ドローンの音から逃げている.jpg</t>
+          <t>images/カルマン線。_img1.jpg</t>
         </is>
       </c>
       <c r="C739" t="inlineStr">
         <is>
-          <t>ゾウ ,ドローン</t>
+          <t xml:space="preserve">手書き語学 ,アラビア語 ,宇宙 </t>
         </is>
       </c>
     </row>
     <row r="740">
       <c r="A740" t="inlineStr">
-        <is>
-          <t xml:space="preserve">カルマン線。
-2308 https://twitter.com/NatGeoMagArab/status/1536436999522881536 </t>
-        </is>
-      </c>
-      <c r="B740" t="inlineStr">
-        <is>
-          <t>images/カルマン線。_img1.jpg</t>
-        </is>
-      </c>
-      <c r="C740" t="inlineStr">
-        <is>
-          <t xml:space="preserve">手書き語学 ,アラビア語 ,宇宙 </t>
-        </is>
-      </c>
-    </row>
-    <row r="741">
-      <c r="A741" t="inlineStr">
         <is>
           <t xml:space="preserve">「恥ずかしがり屋のマヌルネコと暖かい朝の太陽光線」
 ⁦「二つの美しいもの」[Shay'-ayni jamiil-ayni] 属格：「物」( شيء )[Shay']・「美しい」( جميل )[jamiil]⁩
 2309 https://twitter.com/NatGeoMagArab/status/1697512148820504912 </t>
         </is>
       </c>
-      <c r="B741" t="inlineStr">
+      <c r="B740" t="inlineStr">
         <is>
           <t>images/「恥ずかしがり屋のマヌルネコと暖かい朝_img1.jpg</t>
         </is>
       </c>
-      <c r="C741" t="inlineStr">
+      <c r="C740" t="inlineStr">
         <is>
           <t>手書き語学 ,アラビア語 ,マヌルネコ</t>
         </is>
       </c>
     </row>
-    <row r="742">
-      <c r="A742" t="inlineStr">
+    <row r="741">
+      <c r="A741" t="inlineStr">
         <is>
           <t xml:space="preserve">「二回失敗しているペンギン」
 بطريق يفشل مرتين
@@ -16045,19 +16023,19 @@
 2308 https://twitter.com/NatGeoMagArab/status/1479483133766426626 </t>
         </is>
       </c>
-      <c r="B742" t="inlineStr">
+      <c r="B741" t="inlineStr">
         <is>
           <t>images/「二回失敗しているペンギン」_img1.jpg</t>
         </is>
       </c>
-      <c r="C742" t="inlineStr">
+      <c r="C741" t="inlineStr">
         <is>
           <t>ペンギン ,動物</t>
         </is>
       </c>
     </row>
-    <row r="743">
-      <c r="A743" t="inlineStr">
+    <row r="742">
+      <c r="A742" t="inlineStr">
         <is>
           <t xml:space="preserve">「2億光年の彼方できらめく炎と光」
 وهج ووميض يتلألأ على بعد 200 مليون سنة ضوئية
@@ -16068,15 +16046,15 @@
 2010 https://twitter.com/NatGeoMagArab/status/1303415502673342464 </t>
         </is>
       </c>
-      <c r="B743" t="inlineStr"/>
-      <c r="C743" t="inlineStr">
+      <c r="B742" t="inlineStr"/>
+      <c r="C742" t="inlineStr">
         <is>
           <t>宇宙 ,銀河</t>
         </is>
       </c>
     </row>
-    <row r="744">
-      <c r="A744" t="inlineStr">
+    <row r="743">
+      <c r="A743" t="inlineStr">
         <is>
           <t xml:space="preserve">「さまよう黒猫」قطة سوداء تجوب
 キッタトゥン・サウダーウ・タジューブ [qi^_tatun sawdaa'u ta-juub]
@@ -16085,19 +16063,19 @@
 2308 https://twitter.com/NatGeoMagArab/status/1532973177453760512 </t>
         </is>
       </c>
-      <c r="B744" t="inlineStr">
+      <c r="B743" t="inlineStr">
         <is>
           <t>images/「さまよう黒猫」_img1.jpg,images/ 「さまよう黒猫」_img2.jpg</t>
         </is>
       </c>
-      <c r="C744" t="inlineStr">
+      <c r="C743" t="inlineStr">
         <is>
           <t xml:space="preserve">手書き語学 ,モロッコ </t>
         </is>
       </c>
     </row>
-    <row r="745">
-      <c r="A745" t="inlineStr">
+    <row r="744">
+      <c r="A744" t="inlineStr">
         <is>
           <t xml:space="preserve">「サイのざらざらした皮を利用して自分の体を掻くネコ」
 قطة تستغل جلد الكركدن الخشن لحك جسدها
@@ -16106,19 +16084,19 @@
 2308 https://twitter.com/NatGeoMagArab/status/1476855740929216517 </t>
         </is>
       </c>
-      <c r="B745" t="inlineStr">
+      <c r="B744" t="inlineStr">
         <is>
           <t>images/「サイのざらざらした皮を利用して自分の_img1.jpg</t>
         </is>
       </c>
-      <c r="C745" t="inlineStr">
+      <c r="C744" t="inlineStr">
         <is>
           <t>サイ ,チェコ</t>
         </is>
       </c>
     </row>
-    <row r="746">
-      <c r="A746" t="inlineStr">
+    <row r="745">
+      <c r="A745" t="inlineStr">
         <is>
           <t xml:space="preserve">「沈まぬ太陽」شمس لا تغيب
 シャムス・ラー・タギーブ [Shams laa ta-Ghiib]
@@ -16127,19 +16105,19 @@
 2308 AHMED ELASSAL </t>
         </is>
       </c>
-      <c r="B746" t="inlineStr">
+      <c r="B745" t="inlineStr">
         <is>
           <t>images/「沈まぬ太陽」_img1.jpg</t>
         </is>
       </c>
-      <c r="C746" t="inlineStr">
+      <c r="C745" t="inlineStr">
         <is>
           <t>帝国 ,白夜</t>
         </is>
       </c>
     </row>
-    <row r="747">
-      <c r="A747" t="inlineStr">
+    <row r="746">
+      <c r="A746" t="inlineStr">
         <is>
           <t xml:space="preserve">「子供に食べさせている忍耐強い母親」
 أم صبورة تطعم صغيرها
@@ -16148,19 +16126,19 @@
 2308 https://twitter.com/natgeomagarab/status/1585572054509957120 </t>
         </is>
       </c>
-      <c r="B747" t="inlineStr">
+      <c r="B746" t="inlineStr">
         <is>
           <t>images/「子供に食べさせている忍耐強い母親」_img1.jpg</t>
         </is>
       </c>
-      <c r="C747" t="inlineStr">
+      <c r="C746" t="inlineStr">
         <is>
           <t>手書き語学 ,アラビア語 ,ミヤコドリ</t>
         </is>
       </c>
     </row>
-    <row r="748">
-      <c r="A748" t="inlineStr">
+    <row r="747">
+      <c r="A747" t="inlineStr">
         <is>
           <t xml:space="preserve">「コーヒーは繰り返さない恋物語」
 القهوة قصة عشق لن تتكرر
@@ -16170,19 +16148,19 @@
 2403 pin it/7tvd8Wc </t>
         </is>
       </c>
-      <c r="B748" t="inlineStr">
+      <c r="B747" t="inlineStr">
         <is>
           <t>images/「コーヒーは繰り返さない恋物語」_img1.jpg</t>
         </is>
       </c>
-      <c r="C748" t="inlineStr">
+      <c r="C747" t="inlineStr">
         <is>
           <t>コーヒー ,名言</t>
         </is>
       </c>
     </row>
-    <row r="749">
-      <c r="A749" t="inlineStr">
+    <row r="748">
+      <c r="A748" t="inlineStr">
         <is>
           <t xml:space="preserve">「星々で飾られた空。魅惑的な色合いで黄昏の美を満たしている」
 سماء مرصعة بالنجوم تضفي لمسة سحرية على جمال الشفق
@@ -16190,19 +16168,19 @@
 2010 https://twitter.com/NatGeoMagArab/status/1303777701975584768 </t>
         </is>
       </c>
-      <c r="B749" t="inlineStr">
+      <c r="B748" t="inlineStr">
         <is>
           <t>images/「星々で飾られた空。魅惑的な色合いで黄.png</t>
         </is>
       </c>
-      <c r="C749" t="inlineStr">
+      <c r="C748" t="inlineStr">
         <is>
           <t>星空 ,宇宙</t>
         </is>
       </c>
     </row>
-    <row r="750">
-      <c r="A750" t="inlineStr">
+    <row r="749">
+      <c r="A749" t="inlineStr">
         <is>
           <t xml:space="preserve">「国際宇宙ステーションからの写真。巨大な台風『ハイシェン（海神）』を映している」
 لقطات من محطة الفضاء الدولية تظهر إعصار "هايشن" الهائل
@@ -16210,19 +16188,19 @@
 2403 https://twitter.com/NatGeoMagArab/status/1302871968522235904 </t>
         </is>
       </c>
-      <c r="B750" t="inlineStr">
+      <c r="B749" t="inlineStr">
         <is>
           <t>images/「国際宇宙ステーションからの写真。巨大.png</t>
         </is>
       </c>
-      <c r="C750" t="inlineStr">
+      <c r="C749" t="inlineStr">
         <is>
           <t>台風</t>
         </is>
       </c>
     </row>
-    <row r="751">
-      <c r="A751" t="inlineStr">
+    <row r="750">
+      <c r="A750" t="inlineStr">
         <is>
           <t xml:space="preserve">「草を食む幸運な子羊たち」
 خراف محظوظة ترعى
@@ -16232,19 +16210,19 @@
 2308 https://twitter.com/NatGeoMagArab/status/1490211393554972676 </t>
         </is>
       </c>
-      <c r="B751" t="inlineStr">
+      <c r="B750" t="inlineStr">
         <is>
           <t>images/「草を食む幸運な子羊たち」_img1.jpg,images/ 「草を食む幸運な子羊たち」_img2.jpg</t>
         </is>
       </c>
-      <c r="C751" t="inlineStr">
+      <c r="C750" t="inlineStr">
         <is>
           <t>羊 ,アイルランド</t>
         </is>
       </c>
     </row>
-    <row r="752">
-      <c r="A752" t="inlineStr">
+    <row r="751">
+      <c r="A751" t="inlineStr">
         <is>
           <t xml:space="preserve">「お金で買えぬ10のもの」
 ١٠ أشياء لا تشترى بالمال
@@ -16254,19 +16232,19 @@
 2308 ayb124 </t>
         </is>
       </c>
-      <c r="B752" t="inlineStr">
+      <c r="B751" t="inlineStr">
         <is>
           <t>images/「お金で買えぬ10のもの」_img1.jpg</t>
         </is>
       </c>
-      <c r="C752" t="inlineStr">
+      <c r="C751" t="inlineStr">
         <is>
           <t>価値 ,購買</t>
         </is>
       </c>
     </row>
-    <row r="753">
-      <c r="A753" t="inlineStr">
+    <row r="752">
+      <c r="A752" t="inlineStr">
         <is>
           <t xml:space="preserve">「お金では買えないよ」
 هي أشْيَاءٌ لا تُشْتَرَى
@@ -16276,19 +16254,19 @@
 1906 mardy_zaawely, Instagram </t>
         </is>
       </c>
-      <c r="B753" t="inlineStr">
+      <c r="B752" t="inlineStr">
         <is>
           <t>images/「お金では買えないよ」_img1.jpg</t>
         </is>
       </c>
-      <c r="C753" t="inlineStr">
+      <c r="C752" t="inlineStr">
         <is>
           <t>マスターカード ,価値</t>
         </is>
       </c>
     </row>
-    <row r="754">
-      <c r="A754" t="inlineStr">
+    <row r="753">
+      <c r="A753" t="inlineStr">
         <is>
           <t xml:space="preserve">「好奇心旺盛なホッキョクギツネ」
 ثعلب قطبي يملؤه الفضول
@@ -16298,15 +16276,15 @@
 2308 https://twitter.com/natgeomagarab/status/1157592172968808449 </t>
         </is>
       </c>
-      <c r="B754" t="inlineStr"/>
-      <c r="C754" t="inlineStr">
+      <c r="B753" t="inlineStr"/>
+      <c r="C753" t="inlineStr">
         <is>
           <t>ファーストコンタクト ,キツネ</t>
         </is>
       </c>
     </row>
-    <row r="755">
-      <c r="A755" t="inlineStr">
+    <row r="754">
+      <c r="A754" t="inlineStr">
         <is>
           <t xml:space="preserve">「グレンダイザーのいる国は死にません」
 لنْ يَموتَ شَعبٌ لدَيهِ غرندايزر
@@ -16315,56 +16293,56 @@
 2308 https://www.aljarida.com/articles/1462241741574732100/ </t>
         </is>
       </c>
+      <c r="B754" t="inlineStr">
+        <is>
+          <t>images/「グレンダイザーのいる国は死にません」_img1.jpg</t>
+        </is>
+      </c>
+      <c r="C754" t="inlineStr">
+        <is>
+          <t>UFOロボ ,アニメ</t>
+        </is>
+      </c>
+    </row>
+    <row r="755">
+      <c r="A755" t="inlineStr">
+        <is>
+          <t xml:space="preserve">「凍結路面を運転中、彼女は嫌な場面に居合わせた」
+2408 https://twitter.com/NatGeoMagArab/status/1610305209657626625 </t>
+        </is>
+      </c>
       <c r="B755" t="inlineStr">
         <is>
-          <t>images/「グレンダイザーのいる国は死にません」_img1.jpg</t>
+          <t>images/「凍結路面を運転中、彼女は嫌な場面に居_img1.jpg</t>
         </is>
       </c>
       <c r="C755" t="inlineStr">
         <is>
-          <t>UFOロボ ,アニメ</t>
+          <t>手書き語学 ,アラビア語 ,路面凍結</t>
         </is>
       </c>
     </row>
     <row r="756">
       <c r="A756" t="inlineStr">
-        <is>
-          <t xml:space="preserve">「凍結路面を運転中、彼女は嫌な場面に居合わせた」
-2408 https://twitter.com/NatGeoMagArab/status/1610305209657626625 </t>
-        </is>
-      </c>
-      <c r="B756" t="inlineStr">
-        <is>
-          <t>images/「凍結路面を運転中、彼女は嫌な場面に居_img1.jpg</t>
-        </is>
-      </c>
-      <c r="C756" t="inlineStr">
-        <is>
-          <t>手書き語学 ,アラビア語 ,路面凍結</t>
-        </is>
-      </c>
-    </row>
-    <row r="757">
-      <c r="A757" t="inlineStr">
         <is>
           <t xml:space="preserve">「虹が美しさを加えている、アルパカという動物の美しいショット」
 ⁦「美しいショット」[laq_tatun jamiilatun]：「ショット」( لقطة )[laq_ta]：( ـلٌ )[-lun]・( ـقٌ )[-qun]・( ـطٌ )[-_tun]・( ـةٌ )[-tun]⁩
 2308 https://twitter.com/natgeomagarab/status/1155115655928004608 </t>
         </is>
       </c>
-      <c r="B757" t="inlineStr">
+      <c r="B756" t="inlineStr">
         <is>
           <t>images/「虹が美しさを加えている、アルパカとい_img1.jpg</t>
         </is>
       </c>
-      <c r="C757" t="inlineStr">
+      <c r="C756" t="inlineStr">
         <is>
           <t>モフモフ ,アルパカ</t>
         </is>
       </c>
     </row>
-    <row r="758">
-      <c r="A758" t="inlineStr">
+    <row r="757">
+      <c r="A757" t="inlineStr">
         <is>
           <t xml:space="preserve">「幸せは…全然思いもよらない所からやって来る」
 السعادة تأتينا من أماكن لم نكن نتوقعها أبداً
@@ -16373,19 +16351,19 @@
 2109 出典不明 </t>
         </is>
       </c>
-      <c r="B758" t="inlineStr">
+      <c r="B757" t="inlineStr">
         <is>
           <t>images/「幸せは…全然思いもよらない所からやっ_img1.jpg,images/ 「幸せは…全然思いもよらない所からやっ_img2.jpg</t>
         </is>
       </c>
-      <c r="C758" t="inlineStr">
+      <c r="C757" t="inlineStr">
         <is>
           <t>訪れ ,予想</t>
         </is>
       </c>
     </row>
-    <row r="759">
-      <c r="A759" t="inlineStr">
+    <row r="758">
+      <c r="A758" t="inlineStr">
         <is>
           <t xml:space="preserve">「あらゆる問題は、食べ物が解決してくれる」
 كل مشكلة ولها أكلة تحلها
@@ -16394,19 +16372,19 @@
 1909 ALQA AN 878 </t>
         </is>
       </c>
-      <c r="B759" t="inlineStr">
+      <c r="B758" t="inlineStr">
         <is>
           <t>images/「あらゆる問題は、食べ物が解決してくれ_img1.jpg</t>
         </is>
       </c>
-      <c r="C759" t="inlineStr">
+      <c r="C758" t="inlineStr">
         <is>
           <t>ストレス ,精神</t>
         </is>
       </c>
     </row>
-    <row r="760">
-      <c r="A760" t="inlineStr">
+    <row r="759">
+      <c r="A759" t="inlineStr">
         <is>
           <t xml:space="preserve">「冬で私が好きな物」
 أشياء أحبها بالشتاء
@@ -16416,19 +16394,19 @@
 2109 出典不明 </t>
         </is>
       </c>
-      <c r="B760" t="inlineStr">
+      <c r="B759" t="inlineStr">
         <is>
           <t>images/「冬で私が好きな物」_img1.jpg</t>
         </is>
       </c>
-      <c r="C760" t="inlineStr">
+      <c r="C759" t="inlineStr">
         <is>
           <t>季節 ,冬</t>
         </is>
       </c>
     </row>
-    <row r="761">
-      <c r="A761" t="inlineStr">
+    <row r="760">
+      <c r="A760" t="inlineStr">
         <is>
           <t xml:space="preserve">「お金で買うことの出来ない物」
 أشياء لا تستطيع شراءها بالمال
@@ -16438,19 +16416,19 @@
 2409 https://x.com/akhbarak/status/1038402708414373888 </t>
         </is>
       </c>
-      <c r="B761" t="inlineStr">
+      <c r="B760" t="inlineStr">
         <is>
           <t>images/「お金で買うことの出来ない物」_img1.jpg,images/ 「お金で買うことの出来ない物」_img2.jpg</t>
         </is>
       </c>
-      <c r="C761" t="inlineStr">
+      <c r="C760" t="inlineStr">
         <is>
           <t>ショッピング ,価値</t>
         </is>
       </c>
     </row>
-    <row r="762">
-      <c r="A762" t="inlineStr">
+    <row r="761">
+      <c r="A761" t="inlineStr">
         <is>
           <t xml:space="preserve">「私たちが愛する言葉」
 كلماتٌ نُحبّها
@@ -16460,19 +16438,19 @@
 2109 جليل خزعل </t>
         </is>
       </c>
-      <c r="B762" t="inlineStr">
+      <c r="B761" t="inlineStr">
         <is>
           <t>images/「私たちが愛する言葉」_img1.jpg</t>
         </is>
       </c>
-      <c r="C762" t="inlineStr">
+      <c r="C761" t="inlineStr">
         <is>
           <t>花 ,贈り物</t>
         </is>
       </c>
     </row>
-    <row r="763">
-      <c r="A763" t="inlineStr">
+    <row r="762">
+      <c r="A762" t="inlineStr">
         <is>
           <t xml:space="preserve">「お茶についてあなたが知らない10の事実」
 عشر معلومات لا تعرفها عن الشاي
@@ -16481,19 +16459,19 @@
 2012 http://ara.tv/6syq2 </t>
         </is>
       </c>
-      <c r="B763" t="inlineStr">
+      <c r="B762" t="inlineStr">
         <is>
           <t>images/「お茶についてあなたが知らない10の事_img1.jpg</t>
         </is>
       </c>
-      <c r="C763" t="inlineStr">
+      <c r="C762" t="inlineStr">
         <is>
           <t>神農</t>
         </is>
       </c>
     </row>
-    <row r="764">
-      <c r="A764" t="inlineStr">
+    <row r="763">
+      <c r="A763" t="inlineStr">
         <is>
           <t xml:space="preserve">「大きくなったウソ」
 الكذبة الّتي كبرت
@@ -16503,19 +16481,19 @@
 2509 سلسلة الحلزونة </t>
         </is>
       </c>
-      <c r="B764" t="inlineStr">
+      <c r="B763" t="inlineStr">
         <is>
           <t>images/「大きくなったウソ」_img1.jpg</t>
         </is>
       </c>
-      <c r="C764" t="inlineStr">
+      <c r="C763" t="inlineStr">
         <is>
           <t>絵本</t>
         </is>
       </c>
     </row>
-    <row r="765">
-      <c r="A765" t="inlineStr">
+    <row r="764">
+      <c r="A764" t="inlineStr">
         <is>
           <t xml:space="preserve">「自分に合った掃除機を買うには？」
 كيف تشتري المكنسة الكهربائية التي تناسبك؟
@@ -16524,19 +16502,19 @@
 2106 ts3a com </t>
         </is>
       </c>
-      <c r="B765" t="inlineStr">
+      <c r="B764" t="inlineStr">
         <is>
           <t>images/「自分に合った掃除機を買うには？」_img1.jpg</t>
         </is>
       </c>
-      <c r="C765" t="inlineStr">
+      <c r="C764" t="inlineStr">
         <is>
           <t>家電 ,掃除</t>
         </is>
       </c>
     </row>
-    <row r="766">
-      <c r="A766" t="inlineStr">
+    <row r="765">
+      <c r="A765" t="inlineStr">
         <is>
           <t xml:space="preserve">「仮にこれが批判の数としよう」
 لنفرض ان عدد الذين ينتقدونك
@@ -16547,19 +16525,19 @@
 2504 出典不明 </t>
         </is>
       </c>
-      <c r="B766" t="inlineStr">
+      <c r="B765" t="inlineStr">
         <is>
           <t>images/「仮にこれが批判の数としよう」_img1.jpg</t>
         </is>
       </c>
-      <c r="C766" t="inlineStr">
+      <c r="C765" t="inlineStr">
         <is>
           <t>アンチ</t>
         </is>
       </c>
     </row>
-    <row r="767">
-      <c r="A767" t="inlineStr">
+    <row r="766">
+      <c r="A766" t="inlineStr">
         <is>
           <t xml:space="preserve">「ここに見えるのは何？」
 ما الذي تراه هنا؟
@@ -16569,15 +16547,15 @@
 2204 https://twitter.com/NatGeoMagArab/status/1506933850617700352 </t>
         </is>
       </c>
-      <c r="B767" t="inlineStr"/>
-      <c r="C767" t="inlineStr">
+      <c r="B766" t="inlineStr"/>
+      <c r="C766" t="inlineStr">
         <is>
           <t xml:space="preserve">ペンギン </t>
         </is>
       </c>
     </row>
-    <row r="768">
-      <c r="A768" t="inlineStr">
+    <row r="767">
+      <c r="A767" t="inlineStr">
         <is>
           <t xml:space="preserve">「今日辛いこと、明日は平気だろう」
 ما يؤلم اليوم سيهون غدًا
@@ -16587,19 +16565,19 @@
 2308 basmahjeff </t>
         </is>
       </c>
-      <c r="B768" t="inlineStr">
+      <c r="B767" t="inlineStr">
         <is>
           <t>images/「今日辛いこと、明日は平気だろう」_img1.jpg</t>
         </is>
       </c>
-      <c r="C768" t="inlineStr">
+      <c r="C767" t="inlineStr">
         <is>
           <t>悩み ,達観</t>
         </is>
       </c>
     </row>
-    <row r="769">
-      <c r="A769" t="inlineStr">
+    <row r="768">
+      <c r="A768" t="inlineStr">
         <is>
           <t xml:space="preserve">「自分のすることを好きでなきゃ」
 عليك أن تحب ما تفعل
@@ -16608,19 +16586,19 @@
 1810 Ahmed Elhakeem </t>
         </is>
       </c>
-      <c r="B769" t="inlineStr">
+      <c r="B768" t="inlineStr">
         <is>
           <t>images/「自分のすることを好きでなきゃ」_img1.jpg</t>
         </is>
       </c>
-      <c r="C769" t="inlineStr">
+      <c r="C768" t="inlineStr">
         <is>
           <t>転職 ,かわいい</t>
         </is>
       </c>
     </row>
-    <row r="770">
-      <c r="A770" t="inlineStr">
+    <row r="769">
+      <c r="A769" t="inlineStr">
         <is>
           <t xml:space="preserve">「この地上に生き甲斐あり」
 على هذه الأرض ما يستحق الحياة
@@ -16630,19 +16608,19 @@
 2308 Mahmoud Gafar </t>
         </is>
       </c>
-      <c r="B770" t="inlineStr">
+      <c r="B769" t="inlineStr">
         <is>
           <t>images/「この地上に生き甲斐あり」_img1.jpg</t>
         </is>
       </c>
-      <c r="C770" t="inlineStr">
+      <c r="C769" t="inlineStr">
         <is>
           <t>詩</t>
         </is>
       </c>
     </row>
-    <row r="771">
-      <c r="A771" t="inlineStr">
+    <row r="770">
+      <c r="A770" t="inlineStr">
         <is>
           <t xml:space="preserve">「おそらく、あなたの求めるものはあるだろう」
 لعلَّ ما تَرجوهُ سيَكونُ
@@ -16652,19 +16630,19 @@
 2308 PIXEL Instagram </t>
         </is>
       </c>
-      <c r="B771" t="inlineStr">
+      <c r="B770" t="inlineStr">
         <is>
           <t>images/「おそらく、あなたの求めるものはあるだ_img1.jpg</t>
         </is>
       </c>
-      <c r="C771" t="inlineStr">
+      <c r="C770" t="inlineStr">
         <is>
           <t>願い ,信仰</t>
         </is>
       </c>
     </row>
-    <row r="772">
-      <c r="A772" t="inlineStr">
+    <row r="771">
+      <c r="A771" t="inlineStr">
         <is>
           <t xml:space="preserve">「オレンジの効能が何か知っていますか？」
 هل تعرف ما هي فوائد البرتقال؟
@@ -16674,19 +16652,19 @@
 2308 sadahadhramowt com </t>
         </is>
       </c>
-      <c r="B772" t="inlineStr">
+      <c r="B771" t="inlineStr">
         <is>
           <t>images/「オレンジの効能が何か知っていますか？_img1.jpg</t>
         </is>
       </c>
-      <c r="C772" t="inlineStr">
+      <c r="C771" t="inlineStr">
         <is>
           <t>オレンジ ,フルーツ</t>
         </is>
       </c>
     </row>
-    <row r="773">
-      <c r="A773" t="inlineStr">
+    <row r="772">
+      <c r="A772" t="inlineStr">
         <is>
           <t xml:space="preserve">「遊ぶパンダの光景より可愛いものがありますか？」
 هل هناك ما هو ألطف من مشاهدة الباندا وهي تلعب؟
@@ -16694,19 +16672,19 @@
 2308 https://twitter.com/NatGeoMagArab/status/1494612797858074626 </t>
         </is>
       </c>
-      <c r="B773" t="inlineStr">
+      <c r="B772" t="inlineStr">
         <is>
           <t>images/「遊ぶパンダの光景より可愛いものがあり_img1.jpg</t>
         </is>
       </c>
-      <c r="C773" t="inlineStr">
+      <c r="C772" t="inlineStr">
         <is>
           <t>パンダ ,モコモコ</t>
         </is>
       </c>
     </row>
-    <row r="774">
-      <c r="A774" t="inlineStr">
+    <row r="773">
+      <c r="A773" t="inlineStr">
         <is>
           <t xml:space="preserve">「大事なのは何者だったかじゃない。何者になるかだ」
 ليسَ المُهم ما كُنتَ بل مَا ستكون
@@ -16715,19 +16693,19 @@
 2308 出典不明 </t>
         </is>
       </c>
-      <c r="B774" t="inlineStr">
+      <c r="B773" t="inlineStr">
         <is>
           <t>images/「大事なのは何者だったかじゃない。何者_img1.jpg</t>
         </is>
       </c>
-      <c r="C774" t="inlineStr">
+      <c r="C773" t="inlineStr">
         <is>
           <t>自己実現 ,存在価値</t>
         </is>
       </c>
     </row>
-    <row r="775">
-      <c r="A775" t="inlineStr">
+    <row r="774">
+      <c r="A774" t="inlineStr">
         <is>
           <t xml:space="preserve">「あなたであれ。ありのままが美しいから」
 كُنْ أَنْتَ لأنك جميل كما أنت
@@ -16736,19 +16714,19 @@
 2308 IDREES DESIGN </t>
         </is>
       </c>
-      <c r="B775" t="inlineStr">
+      <c r="B774" t="inlineStr">
         <is>
           <t>images/「あなたであれ。ありのままが美しいから_img1.jpg</t>
         </is>
       </c>
-      <c r="C775" t="inlineStr">
+      <c r="C774" t="inlineStr">
         <is>
           <t>自己肯定 ,BeYourself</t>
         </is>
       </c>
     </row>
-    <row r="776">
-      <c r="A776" t="inlineStr">
+    <row r="775">
+      <c r="A775" t="inlineStr">
         <is>
           <t xml:space="preserve">「恐れの中に生きる者は決して自由になれない」
 من يعش في خوف لن يكون حرا أبدا
@@ -16757,19 +16735,19 @@
 2111 rjeem com </t>
         </is>
       </c>
-      <c r="B776" t="inlineStr">
+      <c r="B775" t="inlineStr">
         <is>
           <t>images/「恐れの中に生きる者は決して自由になれ_img1.jpg,images/ 「恐れの中に生きる者は決して自由になれ_img2.jpg</t>
         </is>
       </c>
-      <c r="C776" t="inlineStr">
+      <c r="C775" t="inlineStr">
         <is>
           <t>勇気 ,壁</t>
         </is>
       </c>
     </row>
-    <row r="777">
-      <c r="A777" t="inlineStr">
+    <row r="776">
+      <c r="A776" t="inlineStr">
         <is>
           <t xml:space="preserve">「己の翼を信じる者は己の重さを案じない」
 من يثق في جناحيه لن يهتم لوزنه
@@ -16778,19 +16756,19 @@
 2308 kmrghani </t>
         </is>
       </c>
-      <c r="B777" t="inlineStr">
+      <c r="B776" t="inlineStr">
         <is>
           <t>images/「己の翼を信じる者は己の重さを案じない_img1.jpg</t>
         </is>
       </c>
-      <c r="C777" t="inlineStr">
+      <c r="C776" t="inlineStr">
         <is>
           <t>自信</t>
         </is>
       </c>
     </row>
-    <row r="778">
-      <c r="A778" t="inlineStr">
+    <row r="777">
+      <c r="A777" t="inlineStr">
         <is>
           <t xml:space="preserve">「珈琲で一番大事な事！誰と飲むか？」
 الأهم من القهوة!! من ستشربها معه؟
@@ -16799,19 +16777,19 @@
 1812 gwid3.tumblr </t>
         </is>
       </c>
-      <c r="B778" t="inlineStr">
+      <c r="B777" t="inlineStr">
         <is>
           <t>images/「珈琲で一番大事な事！誰と飲むか？」_img1.jpg</t>
         </is>
       </c>
-      <c r="C778" t="inlineStr">
+      <c r="C777" t="inlineStr">
         <is>
           <t>コーヒー ,名言</t>
         </is>
       </c>
     </row>
-    <row r="779">
-      <c r="A779" t="inlineStr">
+    <row r="778">
+      <c r="A778" t="inlineStr">
         <is>
           <t xml:space="preserve">「人生は美しい、そう望んだ者には。」
 الحياة جَميلَة .. لمن أراد ذلك
@@ -16821,19 +16799,19 @@
 2109 出典不明 </t>
         </is>
       </c>
-      <c r="B779" t="inlineStr">
+      <c r="B778" t="inlineStr">
         <is>
           <t>images/「人生は美しい、そう望んだ者には。」_img1.jpg</t>
         </is>
       </c>
-      <c r="C779" t="inlineStr">
+      <c r="C778" t="inlineStr">
         <is>
           <t>名言 ,アート</t>
         </is>
       </c>
     </row>
-    <row r="780">
-      <c r="A780" t="inlineStr">
+    <row r="779">
+      <c r="A779" t="inlineStr">
         <is>
           <t xml:space="preserve">「ハム太郎って子を知ってるかい」
 هل تعرفون من هو هامتارو
@@ -16843,19 +16821,19 @@
 2109 </t>
         </is>
       </c>
-      <c r="B780" t="inlineStr">
+      <c r="B779" t="inlineStr">
         <is>
           <t>images/「ハム太郎って子を知ってるかい」_img1.jpg</t>
         </is>
       </c>
-      <c r="C780" t="inlineStr">
+      <c r="C779" t="inlineStr">
         <is>
           <t>オープニング ,ハム太郎</t>
         </is>
       </c>
     </row>
-    <row r="781">
-      <c r="A781" t="inlineStr">
+    <row r="780">
+      <c r="A780" t="inlineStr">
         <is>
           <t xml:space="preserve">「幸せを求める人もいれば、作る人もいる」
 هناك من يبحث عن السعادة وهناك من يصنعها
@@ -16864,19 +16842,19 @@
 2308 hindah tumblr </t>
         </is>
       </c>
-      <c r="B781" t="inlineStr">
+      <c r="B780" t="inlineStr">
         <is>
           <t>images/「幸せを求める人もいれば、作る人もいる_img1.jpg</t>
         </is>
       </c>
-      <c r="C781" t="inlineStr">
+      <c r="C780" t="inlineStr">
         <is>
           <t>幸せ ,名言 ,教訓</t>
         </is>
       </c>
     </row>
-    <row r="782">
-      <c r="A782" t="inlineStr">
+    <row r="781">
+      <c r="A781" t="inlineStr">
         <is>
           <t xml:space="preserve">「明白なるアラブの言葉によって」
 بلسان عربي مبين
@@ -16886,19 +16864,19 @@
 2109 Abdullah Barakat behance </t>
         </is>
       </c>
-      <c r="B782" t="inlineStr">
+      <c r="B781" t="inlineStr">
         <is>
           <t>images/「明白なるアラブの言葉によって」_img1.jpg</t>
         </is>
       </c>
-      <c r="C782" t="inlineStr">
+      <c r="C781" t="inlineStr">
         <is>
           <t>イスラム教 ,神聖</t>
         </is>
       </c>
     </row>
-    <row r="783">
-      <c r="A783" t="inlineStr">
+    <row r="782">
+      <c r="A782" t="inlineStr">
         <is>
           <t xml:space="preserve">「結婚前、結婚後」
 قبل الزواج، بعد الزواج
@@ -16908,19 +16886,19 @@
 2308 出典不明 </t>
         </is>
       </c>
-      <c r="B783" t="inlineStr">
+      <c r="B782" t="inlineStr">
         <is>
           <t>images/「結婚前、結婚後」_img1.jpg</t>
         </is>
       </c>
-      <c r="C783" t="inlineStr">
+      <c r="C782" t="inlineStr">
         <is>
           <t>BeforeAfter ,幸せ太り</t>
         </is>
       </c>
     </row>
-    <row r="784">
-      <c r="A784" t="inlineStr">
+    <row r="783">
+      <c r="A783" t="inlineStr">
         <is>
           <t xml:space="preserve">「驚きの価格で」بسعر رائع
 ビスィアル・ラーイア [bi-si*r raa'i*]
@@ -16929,19 +16907,19 @@
 2109 Jarir Bookstore </t>
         </is>
       </c>
-      <c r="B784" t="inlineStr">
+      <c r="B783" t="inlineStr">
         <is>
           <t>images/「驚きの価格で」_img1.jpg</t>
         </is>
       </c>
-      <c r="C784" t="inlineStr">
+      <c r="C783" t="inlineStr">
         <is>
           <t>広告 ,安値</t>
         </is>
       </c>
     </row>
-    <row r="785">
-      <c r="A785" t="inlineStr">
+    <row r="784">
+      <c r="A784" t="inlineStr">
         <is>
           <t xml:space="preserve">「我が魂と共に」مع نفسي
 マア・ナフスィ [ma*a nafs-iy]
@@ -16950,19 +16928,19 @@
 2110 出典不明 </t>
         </is>
       </c>
-      <c r="B785" t="inlineStr">
+      <c r="B784" t="inlineStr">
         <is>
           <t>images/「我が魂と共に」_img1.jpg</t>
         </is>
       </c>
-      <c r="C785" t="inlineStr">
+      <c r="C784" t="inlineStr">
         <is>
           <t>ソウル ,soul</t>
         </is>
       </c>
     </row>
-    <row r="786">
-      <c r="A786" t="inlineStr">
+    <row r="785">
+      <c r="A785" t="inlineStr">
         <is>
           <t xml:space="preserve">「暗い夜に」في ليلة مظلمة
  [fiy layla(tin) mu_Dhlima(tin)]
@@ -16971,19 +16949,19 @@
 2109 سلسلة الحلزونة </t>
         </is>
       </c>
-      <c r="B786" t="inlineStr">
+      <c r="B785" t="inlineStr">
         <is>
           <t>images/「暗い夜に」_img1.jpg</t>
         </is>
       </c>
-      <c r="C786" t="inlineStr">
+      <c r="C785" t="inlineStr">
         <is>
           <t>絵本</t>
         </is>
       </c>
     </row>
-    <row r="787">
-      <c r="A787" t="inlineStr">
+    <row r="786">
+      <c r="A786" t="inlineStr">
         <is>
           <t xml:space="preserve">「ゆっくりと」بشويش
 ビシワェーシ [bi-ShwySh]
@@ -16991,19 +16969,19 @@
 2109 出典不明 </t>
         </is>
       </c>
-      <c r="B787" t="inlineStr">
+      <c r="B786" t="inlineStr">
         <is>
           <t>images/「ゆっくりと」_img1.jpg</t>
         </is>
       </c>
-      <c r="C787" t="inlineStr">
+      <c r="C786" t="inlineStr">
         <is>
           <t>丸 ,円</t>
         </is>
       </c>
     </row>
-    <row r="788">
-      <c r="A788" t="inlineStr">
+    <row r="787">
+      <c r="A787" t="inlineStr">
         <is>
           <t xml:space="preserve">「この広い宇宙に…」
 في الكون الفسيح
@@ -17012,19 +16990,19 @@
 2308 wattpad </t>
         </is>
       </c>
-      <c r="B788" t="inlineStr">
+      <c r="B787" t="inlineStr">
         <is>
           <t>images/「この広い宇宙に…」_img1.jpg</t>
         </is>
       </c>
-      <c r="C788" t="inlineStr">
+      <c r="C787" t="inlineStr">
         <is>
           <t>アニメ ,宇宙</t>
         </is>
       </c>
     </row>
-    <row r="789">
-      <c r="A789" t="inlineStr">
+    <row r="788">
+      <c r="A788" t="inlineStr">
         <is>
           <t xml:space="preserve">「がんばって！」بالتوفيق
 ビッタウフィーク [bi^tawfiiq]
@@ -17032,19 +17010,19 @@
 2111 https://sites.google.com/site/mathmatic1905/ </t>
         </is>
       </c>
-      <c r="B789" t="inlineStr">
+      <c r="B788" t="inlineStr">
         <is>
           <t>images/「がんばって！」_img1.jpg</t>
         </is>
       </c>
-      <c r="C789" t="inlineStr">
+      <c r="C788" t="inlineStr">
         <is>
           <t>アラビア語</t>
         </is>
       </c>
     </row>
-    <row r="790">
-      <c r="A790" t="inlineStr">
+    <row r="789">
+      <c r="A789" t="inlineStr">
         <is>
           <t xml:space="preserve">「インターステラー」بين النجوم
 バイナ_ンヌジューム [bayna ^nujuum]
@@ -17052,19 +17030,19 @@
 2308 kmrghani </t>
         </is>
       </c>
-      <c r="B790" t="inlineStr">
+      <c r="B789" t="inlineStr">
         <is>
           <t>images/「インターステラー」_img1.jpg</t>
         </is>
       </c>
-      <c r="C790" t="inlineStr">
+      <c r="C789" t="inlineStr">
         <is>
           <t>映画 ,宇宙</t>
         </is>
       </c>
     </row>
-    <row r="791">
-      <c r="A791" t="inlineStr">
+    <row r="790">
+      <c r="A790" t="inlineStr">
         <is>
           <t xml:space="preserve">「アラビア語で」بالعربية
 ビ_ルアラビーヤ [bi-l-*arabiyya]
@@ -17073,19 +17051,19 @@
 1811 </t>
         </is>
       </c>
-      <c r="B791" t="inlineStr">
+      <c r="B790" t="inlineStr">
         <is>
           <t>images/「アラビア語で」_img1.jpg</t>
         </is>
       </c>
-      <c r="C791" t="inlineStr">
+      <c r="C790" t="inlineStr">
         <is>
           <t>ニュース ,CNN</t>
         </is>
       </c>
     </row>
-    <row r="792">
-      <c r="A792" t="inlineStr">
+    <row r="791">
+      <c r="A791" t="inlineStr">
         <is>
           <t xml:space="preserve">「17世紀に発明されて以来…」
 منذ اختراعه بالقرن السابع عشر
@@ -17093,19 +17071,19 @@
 2308 https://twitter.com/SciTalk2U/status/1450888395815854080 </t>
         </is>
       </c>
-      <c r="B792" t="inlineStr">
+      <c r="B791" t="inlineStr">
         <is>
           <t>images/「17世紀に発明されて以来…」_img1.jpg</t>
         </is>
       </c>
-      <c r="C792" t="inlineStr">
+      <c r="C791" t="inlineStr">
         <is>
           <t>手書き語学 ,アラビア語 ,望遠鏡</t>
         </is>
       </c>
     </row>
-    <row r="793">
-      <c r="A793" t="inlineStr">
+    <row r="792">
+      <c r="A792" t="inlineStr">
         <is>
           <t xml:space="preserve">「私できるよ」إنّني أستطيع
 インナニー・アスタティーウ ['inna-niy 'a-sta_tii*u]
@@ -17114,19 +17092,19 @@
 2412 سلسلة الحلزونة </t>
         </is>
       </c>
-      <c r="B793" t="inlineStr">
+      <c r="B792" t="inlineStr">
         <is>
           <t>images/「私できるよ」_img1.jpg</t>
         </is>
       </c>
-      <c r="C793" t="inlineStr">
+      <c r="C792" t="inlineStr">
         <is>
           <t>絵本 ,こども</t>
         </is>
       </c>
     </row>
-    <row r="794">
-      <c r="A794" t="inlineStr">
+    <row r="793">
+      <c r="A793" t="inlineStr">
         <is>
           <t xml:space="preserve">「問題なし」مافيش مشكلة
 マフィーシムシュキラ [ma-fy-Sh muShkila]
@@ -17135,19 +17113,19 @@
 2109 tanzerin.theshop </t>
         </is>
       </c>
-      <c r="B794" t="inlineStr">
+      <c r="B793" t="inlineStr">
         <is>
           <t>images/「問題なし」_img1.jpg</t>
         </is>
       </c>
-      <c r="C794" t="inlineStr">
+      <c r="C793" t="inlineStr">
         <is>
           <t>シャツ ,キッズ</t>
         </is>
       </c>
     </row>
-    <row r="795">
-      <c r="A795" t="inlineStr">
+    <row r="794">
+      <c r="A794" t="inlineStr">
         <is>
           <t xml:space="preserve">「不可能はない」مفيش مستحيل
 マフィーシ・ムスタヒール [ma-fy-Sh mustaHiil]
@@ -17156,19 +17134,19 @@
 2109 أموج </t>
         </is>
       </c>
-      <c r="B795" t="inlineStr">
+      <c r="B794" t="inlineStr">
         <is>
           <t>images/「不可能はない」_img1.jpg</t>
         </is>
       </c>
-      <c r="C795" t="inlineStr">
+      <c r="C794" t="inlineStr">
         <is>
           <t>ポジティブ ,挑戦</t>
         </is>
       </c>
     </row>
-    <row r="796">
-      <c r="A796" t="inlineStr">
+    <row r="795">
+      <c r="A795" t="inlineStr">
         <is>
           <t xml:space="preserve">「等々」إلخ
 イラク ['ilaKh]
@@ -17177,19 +17155,19 @@
 2201 出典不明 </t>
         </is>
       </c>
-      <c r="B796" t="inlineStr">
+      <c r="B795" t="inlineStr">
         <is>
           <t>images/「等々」_img1.jpg</t>
         </is>
       </c>
-      <c r="C796" t="inlineStr">
+      <c r="C795" t="inlineStr">
         <is>
           <t>etc ,とんち</t>
         </is>
       </c>
     </row>
-    <row r="797">
-      <c r="A797" t="inlineStr">
+    <row r="796">
+      <c r="A796" t="inlineStr">
         <is>
           <t xml:space="preserve">⁦「調子どう？」⁩شلونَك؟
 シュローナク？ [Sh-loon-ak?]
@@ -17198,19 +17176,19 @@
 2202 Jozoor Team. </t>
         </is>
       </c>
-      <c r="B797" t="inlineStr">
+      <c r="B796" t="inlineStr">
         <is>
           <t>images/⁦「調子どう？」⁩_img1.jpg</t>
         </is>
       </c>
-      <c r="C797" t="inlineStr">
+      <c r="C796" t="inlineStr">
         <is>
           <t>洒落 ,ルービックキューブ</t>
         </is>
       </c>
     </row>
-    <row r="798">
-      <c r="A798" t="inlineStr">
+    <row r="797">
+      <c r="A797" t="inlineStr">
         <is>
           <t xml:space="preserve">「行くな」ماتروحش
 マトロホシ [ma-troH-Sh]
@@ -17219,19 +17197,19 @@
 2411 triiq tumblr </t>
         </is>
       </c>
-      <c r="B798" t="inlineStr">
+      <c r="B797" t="inlineStr">
         <is>
           <t>images/「行くな」_img1.jpg</t>
         </is>
       </c>
-      <c r="C798" t="inlineStr">
+      <c r="C797" t="inlineStr">
         <is>
           <t>ロゴ ,デザイン ,嵐</t>
         </is>
       </c>
     </row>
-    <row r="799">
-      <c r="A799" t="inlineStr">
+    <row r="798">
+      <c r="A798" t="inlineStr">
         <is>
           <t xml:space="preserve">⁦「元気？」⁩شلونَك؟
 シュローナク？ [Sh-loon-ak?]
@@ -17242,19 +17220,19 @@
 2202 出典不明 </t>
         </is>
       </c>
-      <c r="B799" t="inlineStr">
+      <c r="B798" t="inlineStr">
         <is>
           <t>images/⁦「元気？」⁩_img1.jpg</t>
         </is>
       </c>
-      <c r="C799" t="inlineStr">
+      <c r="C798" t="inlineStr">
         <is>
           <t>洒落 ,挨拶</t>
         </is>
       </c>
     </row>
-    <row r="800">
-      <c r="A800" t="inlineStr">
+    <row r="799">
+      <c r="A799" t="inlineStr">
         <is>
           <t xml:space="preserve">「気分が良いぞう」I فيل GOOD
 アイ・フィール・グッド [ai fiyl gud]
@@ -17263,19 +17241,19 @@
 2308 出典不明 </t>
         </is>
       </c>
-      <c r="B800" t="inlineStr">
+      <c r="B799" t="inlineStr">
         <is>
           <t>images/「気分が良いぞう」_img1.jpg</t>
         </is>
       </c>
-      <c r="C800" t="inlineStr">
+      <c r="C799" t="inlineStr">
         <is>
           <t>洒落 ,和訳</t>
         </is>
       </c>
     </row>
-    <row r="801">
-      <c r="A801" t="inlineStr">
+    <row r="800">
+      <c r="A800" t="inlineStr">
         <is>
           <t xml:space="preserve">「レットイットゴー／let it go」
 ليت اِت غو
@@ -17284,19 +17262,19 @@
 2109 出典不明 </t>
         </is>
       </c>
-      <c r="B801" t="inlineStr">
+      <c r="B800" t="inlineStr">
         <is>
           <t>images/「レットイットゴー／let it go_img1.jpg</t>
         </is>
       </c>
-      <c r="C801" t="inlineStr">
+      <c r="C800" t="inlineStr">
         <is>
           <t>折衷 ,アナ雪</t>
         </is>
       </c>
     </row>
-    <row r="802">
-      <c r="A802" t="inlineStr">
+    <row r="801">
+      <c r="A801" t="inlineStr">
         <is>
           <t xml:space="preserve">「ようこそ」اهلا وسهلا
 アハラン・ワサハラン ['ahlan wa-sahlan]
@@ -17304,19 +17282,19 @@
 2106 behance Anwar Al Eissa </t>
         </is>
       </c>
-      <c r="B802" t="inlineStr">
+      <c r="B801" t="inlineStr">
         <is>
           <t>images/「ようこそ」_img1.jpg</t>
         </is>
       </c>
-      <c r="C802" t="inlineStr">
+      <c r="C801" t="inlineStr">
         <is>
           <t>アラビア語</t>
         </is>
       </c>
     </row>
-    <row r="803">
-      <c r="A803" t="inlineStr">
+    <row r="802">
+      <c r="A802" t="inlineStr">
         <is>
           <t xml:space="preserve">「まぁ何というサプライズでしょう」
 يا لها من مفاجأة
@@ -17327,19 +17305,19 @@
 2108 neelwafurat com </t>
         </is>
       </c>
-      <c r="B803" t="inlineStr">
+      <c r="B802" t="inlineStr">
         <is>
           <t>images/「まぁ何というサプライズでしょう」_img1.jpg</t>
         </is>
       </c>
-      <c r="C803" t="inlineStr">
+      <c r="C802" t="inlineStr">
         <is>
           <t>中国語 ,学習</t>
         </is>
       </c>
     </row>
-    <row r="804">
-      <c r="A804" t="inlineStr">
+    <row r="803">
+      <c r="A803" t="inlineStr">
         <is>
           <t xml:space="preserve">「ハックション」اتشوو
 アチュー！ ['aatShuu]
@@ -17347,19 +17325,19 @@
 1811 </t>
         </is>
       </c>
-      <c r="B804" t="inlineStr">
+      <c r="B803" t="inlineStr">
         <is>
           <t>images/「ハックション」_img1.jpg</t>
         </is>
       </c>
-      <c r="C804" t="inlineStr">
+      <c r="C803" t="inlineStr">
         <is>
           <t>あらびあや</t>
         </is>
       </c>
     </row>
-    <row r="805">
-      <c r="A805" t="inlineStr">
+    <row r="804">
+      <c r="A804" t="inlineStr">
         <is>
           <t xml:space="preserve">「スブハーナッラー」「アルハムドゥリッラー」「アッラーアクバル」
 سبحان الله
@@ -17370,19 +17348,19 @@
 2308 dribbble com </t>
         </is>
       </c>
-      <c r="B805" t="inlineStr">
+      <c r="B804" t="inlineStr">
         <is>
           <t>images/「スブハーナッラー」「アルハムドゥリッ_img1.jpg</t>
         </is>
       </c>
-      <c r="C805" t="inlineStr">
+      <c r="C804" t="inlineStr">
         <is>
           <t>四角 ,コンパクト</t>
         </is>
       </c>
     </row>
-    <row r="806">
-      <c r="A806" t="inlineStr">
+    <row r="805">
+      <c r="A805" t="inlineStr">
         <is>
           <t xml:space="preserve">「すごく美味しい！」لذيذ جدًا
 ラズィーズ・ジッダン [laDhiiDh jiddan]
@@ -17391,19 +17369,19 @@
 2109 goodreads com </t>
         </is>
       </c>
-      <c r="B806" t="inlineStr">
+      <c r="B805" t="inlineStr">
         <is>
           <t>images/「すごく美味しい！」_img1.jpg</t>
         </is>
       </c>
-      <c r="C806" t="inlineStr">
+      <c r="C805" t="inlineStr">
         <is>
           <t>フレーズ ,感想</t>
         </is>
       </c>
     </row>
-    <row r="807">
-      <c r="A807" t="inlineStr">
+    <row r="806">
+      <c r="A806" t="inlineStr">
         <is>
           <t xml:space="preserve">「しとしと、雨」تك تك يا مطر
 ティクティク [tik tik yaa ma_tar]
@@ -17412,19 +17390,19 @@
 2308 出典不明 </t>
         </is>
       </c>
-      <c r="B807" t="inlineStr">
+      <c r="B806" t="inlineStr">
         <is>
           <t>images/「しとしと、雨」_img1.jpg</t>
         </is>
       </c>
-      <c r="C807" t="inlineStr">
+      <c r="C806" t="inlineStr">
         <is>
           <t>天気 ,梅雨</t>
         </is>
       </c>
     </row>
-    <row r="808">
-      <c r="A808" t="inlineStr">
+    <row r="807">
+      <c r="A807" t="inlineStr">
         <is>
           <t xml:space="preserve">「さかさま」رأساً على عقب
 ラッアサン・アラー・アケブ [ra'san *alaa *aqib]
@@ -17432,19 +17410,19 @@
 2109 出典不明 </t>
         </is>
       </c>
-      <c r="B808" t="inlineStr">
+      <c r="B807" t="inlineStr">
         <is>
           <t>images/「さかさま」_img1.jpg</t>
         </is>
       </c>
-      <c r="C808" t="inlineStr">
+      <c r="C807" t="inlineStr">
         <is>
           <t>壁 ,上下</t>
         </is>
       </c>
     </row>
-    <row r="809">
-      <c r="A809" t="inlineStr">
+    <row r="808">
+      <c r="A808" t="inlineStr">
         <is>
           <t xml:space="preserve">「エジプトよどこへ行った」
 فينك يا مصر؟
@@ -17454,19 +17432,19 @@
 1809 shehabfawzy1.tumblr </t>
         </is>
       </c>
-      <c r="B809" t="inlineStr">
+      <c r="B808" t="inlineStr">
         <is>
           <t>images/「エジプトよどこへ行った」_img1.jpg</t>
         </is>
       </c>
-      <c r="C809" t="inlineStr">
+      <c r="C808" t="inlineStr">
         <is>
           <t>ピラミッド ,歴史</t>
         </is>
       </c>
     </row>
-    <row r="810">
-      <c r="A810" t="inlineStr">
+    <row r="809">
+      <c r="A809" t="inlineStr">
         <is>
           <t xml:space="preserve">「ありがとう」شكراً
 シュクラン [Shukran]
@@ -17474,19 +17452,19 @@
 2109 出典不明 </t>
         </is>
       </c>
-      <c r="B810" t="inlineStr">
+      <c r="B809" t="inlineStr">
         <is>
           <t>images/「ありがとう」_img1.jpg</t>
         </is>
       </c>
-      <c r="C810" t="inlineStr">
+      <c r="C809" t="inlineStr">
         <is>
           <t>挨拶 ,文字</t>
         </is>
       </c>
     </row>
-    <row r="811">
-      <c r="A811" t="inlineStr">
+    <row r="810">
+      <c r="A810" t="inlineStr">
         <is>
           <t xml:space="preserve">「昼寝の時間だ」
 إنه وقت القيلولة
@@ -17495,12 +17473,12 @@
 2501 https://x.com/NatGeoMagArab/status/1858049951579910486 </t>
         </is>
       </c>
-      <c r="B811" t="inlineStr">
+      <c r="B810" t="inlineStr">
         <is>
           <t>images/「昼寝の時間だ」_img1.jpg</t>
         </is>
       </c>
-      <c r="C811" t="inlineStr">
+      <c r="C810" t="inlineStr">
         <is>
           <t>手書き語学 ,アラビア語 ,ペンギン</t>
         </is>

--- a/posts.xlsx
+++ b/posts.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C810"/>
+  <dimension ref="A1:C809"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -10674,46 +10674,25 @@
     <row r="489">
       <c r="A489" t="inlineStr">
         <is>
-          <t xml:space="preserve">「鼓動する」ينبض
-ヤンビド [ya-nbi_d]
-⁦「鼓動／脈動した」ナバダ ( نبض )[naba_da]：( ـنـ )[-n-]・( ـبـ )[-b-]：( ن )[n]・( ب )[b]・( ض )[_d]⁩
-鼓動（コドウ）
-2308 出典不明 </t>
-        </is>
-      </c>
-      <c r="B489" t="inlineStr">
-        <is>
-          <t>images/「鼓動する」_img1.jpg</t>
-        </is>
-      </c>
-      <c r="C489" t="inlineStr">
-        <is>
-          <t>心臓</t>
-        </is>
-      </c>
-    </row>
-    <row r="490">
-      <c r="A490" t="inlineStr">
-        <is>
           <t xml:space="preserve">「お母さんがこの方法で僕を運ぶ時、暴れる余地はない」
 حين تحملني أمي بهذه الطريقة، فلا مجال للشغب
 [Hiyna ta-Hmilu-niy 'umm-iy bi-haaDhihi ^_tariiqati, fa-laa majaala li^ShaGhab]
 2412 https://twitter.com/NatGeoMagArab/status/1540945459396546562 </t>
         </is>
       </c>
-      <c r="B490" t="inlineStr">
+      <c r="B489" t="inlineStr">
         <is>
           <t>images/「お母さんがこの方法で僕を運ぶ時、暴れ_img1.jpg,images/ 「お母さんがこの方法で僕を運ぶ時、暴れ_img2.jpg</t>
         </is>
       </c>
-      <c r="C490" t="inlineStr">
+      <c r="C489" t="inlineStr">
         <is>
           <t xml:space="preserve">手書き語学 ,アラビア語 ,ピューマ </t>
         </is>
       </c>
     </row>
-    <row r="491">
-      <c r="A491" t="inlineStr">
+    <row r="490">
+      <c r="A490" t="inlineStr">
         <is>
           <t xml:space="preserve">「これには小さいスナネコが写っている」
 يظهر من خلالها قط رمال صغير
@@ -10722,19 +10701,19 @@
 2604 https://x.com/NatGeoMagArab/status/1934317490534019202 </t>
         </is>
       </c>
-      <c r="B491" t="inlineStr">
+      <c r="B490" t="inlineStr">
         <is>
           <t>images/「これには小さいスナネコが写っている」_img1.jpg,images/ 「これには小さいスナネコが写っている」_img2.jpg</t>
         </is>
       </c>
-      <c r="C491" t="inlineStr">
+      <c r="C490" t="inlineStr">
         <is>
           <t>手書き語学 ,アラビア語 ,スナネコ</t>
         </is>
       </c>
     </row>
-    <row r="492">
-      <c r="A492" t="inlineStr">
+    <row r="491">
+      <c r="A491" t="inlineStr">
         <is>
           <t xml:space="preserve">「アイデアを手に入れる方法」
 كيف تحصل على أفكار
@@ -10744,19 +10723,19 @@
 2312 ibtesamah com </t>
         </is>
       </c>
-      <c r="B492" t="inlineStr">
+      <c r="B491" t="inlineStr">
         <is>
           <t>images/「アイデアを手に入れる方法」_img1.jpg</t>
         </is>
       </c>
-      <c r="C492" t="inlineStr">
+      <c r="C491" t="inlineStr">
         <is>
           <t>電球 ,魚</t>
         </is>
       </c>
     </row>
-    <row r="493">
-      <c r="A493" t="inlineStr">
+    <row r="492">
+      <c r="A492" t="inlineStr">
         <is>
           <t xml:space="preserve">「仕事で成功するでしょう」
 ستنجح في عملك
@@ -10766,19 +10745,19 @@
 2105 </t>
         </is>
       </c>
-      <c r="B493" t="inlineStr">
+      <c r="B492" t="inlineStr">
         <is>
           <t>images/「仕事で成功するでしょう」_img1.jpg</t>
         </is>
       </c>
-      <c r="C493" t="inlineStr">
+      <c r="C492" t="inlineStr">
         <is>
           <t>手相 ,あらびあや</t>
         </is>
       </c>
     </row>
-    <row r="494">
-      <c r="A494" t="inlineStr">
+    <row r="493">
+      <c r="A493" t="inlineStr">
         <is>
           <t xml:space="preserve">「わかりません」لا أَعْرِفُ
 ラー・アアリフ [laa 'a-*rifu]
@@ -10786,19 +10765,19 @@
 1809 </t>
         </is>
       </c>
-      <c r="B494" t="inlineStr">
+      <c r="B493" t="inlineStr">
         <is>
           <t>images/「わかりません」_img1.jpg</t>
         </is>
       </c>
-      <c r="C494" t="inlineStr">
+      <c r="C493" t="inlineStr">
         <is>
           <t>あらびあや</t>
         </is>
       </c>
     </row>
-    <row r="495">
-      <c r="A495" t="inlineStr">
+    <row r="494">
+      <c r="A494" t="inlineStr">
         <is>
           <t xml:space="preserve">「母リスは、子供たちが心配じゃないのだろうか」
 ألا تشعر أم السناجب بالقلق على صغارها
@@ -10807,19 +10786,19 @@
 2109 NatGeoMagArab </t>
         </is>
       </c>
-      <c r="B495" t="inlineStr">
+      <c r="B494" t="inlineStr">
         <is>
           <t>images/「母リスは、子供たちが心配じゃないのだ.png</t>
         </is>
       </c>
-      <c r="C495" t="inlineStr">
+      <c r="C494" t="inlineStr">
         <is>
           <t>リス ,元気</t>
         </is>
       </c>
     </row>
-    <row r="496">
-      <c r="A496" t="inlineStr">
+    <row r="495">
+      <c r="A495" t="inlineStr">
         <is>
           <t xml:space="preserve">「分かりません」لا أفهم
 ラー・アフハム [laa 'a-fham]
@@ -10828,19 +10807,19 @@
 2303 https://www.vogue.fr/fashion-culture/fashion-exhibitions/diaporama/middle-east-art-scene/12755/amp </t>
         </is>
       </c>
-      <c r="B496" t="inlineStr">
+      <c r="B495" t="inlineStr">
         <is>
           <t>images/「分かりません」_img1.jpg</t>
         </is>
       </c>
-      <c r="C496" t="inlineStr">
+      <c r="C495" t="inlineStr">
         <is>
           <t>イミフ ,否定</t>
         </is>
       </c>
     </row>
-    <row r="497">
-      <c r="A497" t="inlineStr">
+    <row r="496">
+      <c r="A496" t="inlineStr">
         <is>
           <t xml:space="preserve">「クイズ ミリオネア／100万を獲るのは誰だ」
 من سيربح المليون
@@ -10850,19 +10829,19 @@
 2308 MBC 1 </t>
         </is>
       </c>
-      <c r="B497" t="inlineStr">
+      <c r="B496" t="inlineStr">
         <is>
           <t>images/「クイズ ミリオネア／100万を獲るの_img1.jpg</t>
         </is>
       </c>
-      <c r="C497" t="inlineStr">
+      <c r="C496" t="inlineStr">
         <is>
           <t>テレビ ,みのもんた</t>
         </is>
       </c>
     </row>
-    <row r="498">
-      <c r="A498" t="inlineStr">
+    <row r="497">
+      <c r="A497" t="inlineStr">
         <is>
           <t xml:space="preserve">「知っていますか？」هل تعلم؟
 ハル・タアラム？ [hal ta-*lam?]
@@ -10871,19 +10850,19 @@
 2103 el-ma3lomaa com </t>
         </is>
       </c>
-      <c r="B498" t="inlineStr">
+      <c r="B497" t="inlineStr">
         <is>
           <t>images/「知っていますか？」_img1.jpg</t>
         </is>
       </c>
-      <c r="C498" t="inlineStr">
+      <c r="C497" t="inlineStr">
         <is>
           <t>知識 ,クイズ</t>
         </is>
       </c>
     </row>
-    <row r="499">
-      <c r="A499" t="inlineStr">
+    <row r="498">
+      <c r="A498" t="inlineStr">
         <is>
           <t xml:space="preserve">「貴女はどこに住んでいますか」
 أين تسكنين؟
@@ -10893,19 +10872,19 @@
 1811 </t>
         </is>
       </c>
-      <c r="B499" t="inlineStr">
+      <c r="B498" t="inlineStr">
         <is>
           <t>images/「貴女はどこに住んでいますか」_img1.jpg</t>
         </is>
       </c>
-      <c r="C499" t="inlineStr">
+      <c r="C498" t="inlineStr">
         <is>
           <t>あらびあや</t>
         </is>
       </c>
     </row>
-    <row r="500">
-      <c r="A500" t="inlineStr">
+    <row r="499">
+      <c r="A499" t="inlineStr">
         <is>
           <t xml:space="preserve">「きょうりゅうはどうやってがっこうにいくの？」
 كَيْفَ تَذْهَبُ الدِّيناصوراتُ إلى الْمَدْرَسَةِ؟
@@ -10914,19 +10893,19 @@
 2308 sanabilbooks.com </t>
         </is>
       </c>
-      <c r="B500" t="inlineStr">
+      <c r="B499" t="inlineStr">
         <is>
           <t>images/「きょうりゅうはどうやってがっこうにい_img1.jpg</t>
         </is>
       </c>
-      <c r="C500" t="inlineStr">
+      <c r="C499" t="inlineStr">
         <is>
           <t>絵本 ,恐竜</t>
         </is>
       </c>
     </row>
-    <row r="501">
-      <c r="A501" t="inlineStr">
+    <row r="500">
+      <c r="A500" t="inlineStr">
         <is>
           <t xml:space="preserve">「私たちにはどれだけの時間があるのか？」
 كم من الوقت نملك؟
@@ -10936,19 +10915,19 @@
 2308 Founders and Founders </t>
         </is>
       </c>
-      <c r="B501" t="inlineStr">
+      <c r="B500" t="inlineStr">
         <is>
           <t>images/「私たちにはどれだけの時間があるのか？_img1.jpg</t>
         </is>
       </c>
-      <c r="C501" t="inlineStr">
+      <c r="C500" t="inlineStr">
         <is>
           <t>チャート</t>
         </is>
       </c>
     </row>
-    <row r="502">
-      <c r="A502" t="inlineStr">
+    <row r="501">
+      <c r="A501" t="inlineStr">
         <is>
           <t xml:space="preserve">「あなたのスマホの着信音にいかが？」
 هل يصلح صوتها نغمة رنين لهاتفك؟
@@ -10957,19 +10936,19 @@
 2507 https://twitter.com/NatGeoMagArab/status/1752232696435339325 </t>
         </is>
       </c>
-      <c r="B502" t="inlineStr">
+      <c r="B501" t="inlineStr">
         <is>
           <t>images/「あなたのスマホの着信音にいかが？」_img1.jpg</t>
         </is>
       </c>
-      <c r="C502" t="inlineStr">
+      <c r="C501" t="inlineStr">
         <is>
           <t>手書き語学 ,アラビア語 ,フクロウ</t>
         </is>
       </c>
     </row>
-    <row r="503">
-      <c r="A503" t="inlineStr">
+    <row r="502">
+      <c r="A502" t="inlineStr">
         <is>
           <t xml:space="preserve">「コーヒーが冷めないうちに」
 قبل أن تبرد القهوة
@@ -10979,19 +10958,19 @@
 2403 https://a.co d/7jizZfE </t>
         </is>
       </c>
-      <c r="B503" t="inlineStr">
+      <c r="B502" t="inlineStr">
         <is>
           <t>images/「コーヒーが冷めないうちに」_img1.jpg</t>
         </is>
       </c>
-      <c r="C503" t="inlineStr">
+      <c r="C502" t="inlineStr">
         <is>
           <t>小説 ,表紙</t>
         </is>
       </c>
     </row>
-    <row r="504">
-      <c r="A504" t="inlineStr">
+    <row r="503">
+      <c r="A503" t="inlineStr">
         <is>
           <t xml:space="preserve">「悲しむな」Don't be sad
 لا تحزَنْ
@@ -11001,15 +10980,15 @@
 2402 MADYAN </t>
         </is>
       </c>
-      <c r="B504" t="inlineStr">
+      <c r="B503" t="inlineStr">
         <is>
           <t>images/「悲しむな」Don't be sad_img1.jpg</t>
         </is>
       </c>
-      <c r="C504" t="inlineStr"/>
-    </row>
-    <row r="505">
-      <c r="A505" t="inlineStr">
+      <c r="C503" t="inlineStr"/>
+    </row>
+    <row r="504">
+      <c r="A504" t="inlineStr">
         <is>
           <t xml:space="preserve">「悲しむな」لا تحزن
 ラー・タハザン [laa ta-Hzan]
@@ -11018,19 +10997,19 @@
 1903 fadli7 deviantart com </t>
         </is>
       </c>
-      <c r="B505" t="inlineStr">
+      <c r="B504" t="inlineStr">
         <is>
           <t>images/「悲しむな」_img1.jpg</t>
         </is>
       </c>
-      <c r="C505" t="inlineStr">
+      <c r="C504" t="inlineStr">
         <is>
           <t>書道 ,カリグラフィー</t>
         </is>
       </c>
     </row>
-    <row r="506">
-      <c r="A506" t="inlineStr">
+    <row r="505">
+      <c r="A505" t="inlineStr">
         <is>
           <t xml:space="preserve">「心配しないで、パパ」
 لا تقلق يا بابا
@@ -11040,19 +11019,19 @@
 2308 alsalwabooks </t>
         </is>
       </c>
-      <c r="B506" t="inlineStr">
+      <c r="B505" t="inlineStr">
         <is>
           <t>images/「心配しないで、パパ」_img1.jpg</t>
         </is>
       </c>
-      <c r="C506" t="inlineStr">
+      <c r="C505" t="inlineStr">
         <is>
           <t>絵本 ,親子</t>
         </is>
       </c>
     </row>
-    <row r="507">
-      <c r="A507" t="inlineStr">
+    <row r="506">
+      <c r="A506" t="inlineStr">
         <is>
           <t xml:space="preserve">「時は剣のごとし。あなたが割かなければあなたが割かれる」
 الوقت كالسيف إن لم تقطعه قطعك
@@ -11061,19 +11040,19 @@
 2308 sultanart </t>
         </is>
       </c>
-      <c r="B507" t="inlineStr">
+      <c r="B506" t="inlineStr">
         <is>
           <t>images/「時は剣のごとし。あなたが割かなければ_img1.jpg</t>
         </is>
       </c>
-      <c r="C507" t="inlineStr">
+      <c r="C506" t="inlineStr">
         <is>
           <t>ことわざ</t>
         </is>
       </c>
     </row>
-    <row r="508">
-      <c r="A508" t="inlineStr">
+    <row r="507">
+      <c r="A507" t="inlineStr">
         <is>
           <t xml:space="preserve">「そんな風に私を見ないで」
 لا تنظر إلي هكذا
@@ -11083,19 +11062,19 @@
 1810 </t>
         </is>
       </c>
-      <c r="B508" t="inlineStr">
+      <c r="B507" t="inlineStr">
         <is>
           <t>images/「そんな風に私を見ないで」_img1.jpg</t>
         </is>
       </c>
-      <c r="C508" t="inlineStr">
+      <c r="C507" t="inlineStr">
         <is>
           <t>あらびあや</t>
         </is>
       </c>
     </row>
-    <row r="509">
-      <c r="A509" t="inlineStr">
+    <row r="508">
+      <c r="A508" t="inlineStr">
         <is>
           <t xml:space="preserve">「必要以上に勉強するな」
 لا تدرس أكثر من اللازم
@@ -11105,19 +11084,19 @@
 2109 出典不明 </t>
         </is>
       </c>
-      <c r="B509" t="inlineStr">
+      <c r="B508" t="inlineStr">
         <is>
           <t>images/「必要以上に勉強するな」_img1.jpg</t>
         </is>
       </c>
-      <c r="C509" t="inlineStr">
+      <c r="C508" t="inlineStr">
         <is>
           <t>徹夜 ,計画</t>
         </is>
       </c>
     </row>
-    <row r="510">
-      <c r="A510" t="inlineStr">
+    <row r="509">
+      <c r="A509" t="inlineStr">
         <is>
           <t xml:space="preserve">「翼を広げなさい」
 افْرِدْ جَنَاحَكَ
@@ -11127,19 +11106,19 @@
 2308 Librairie SANA </t>
         </is>
       </c>
-      <c r="B510" t="inlineStr">
+      <c r="B509" t="inlineStr">
         <is>
           <t>images/「翼を広げなさい」_img1.jpg</t>
         </is>
       </c>
-      <c r="C510" t="inlineStr">
+      <c r="C509" t="inlineStr">
         <is>
           <t>絵本 ,鳥</t>
         </is>
       </c>
     </row>
-    <row r="511">
-      <c r="A511" t="inlineStr">
+    <row r="510">
+      <c r="A510" t="inlineStr">
         <is>
           <t xml:space="preserve">「作ろう。自分の幸せは自分で」
 اصنع سعادتك بنفسك
@@ -11149,19 +11128,19 @@
 1812 fado1997 tumblr </t>
         </is>
       </c>
-      <c r="B511" t="inlineStr">
+      <c r="B510" t="inlineStr">
         <is>
           <t>images/「作ろう。自分の幸せは自分で」_img1.jpg</t>
         </is>
       </c>
-      <c r="C511" t="inlineStr">
+      <c r="C510" t="inlineStr">
         <is>
           <t>ポジティブ</t>
         </is>
       </c>
     </row>
-    <row r="512">
-      <c r="A512" t="inlineStr">
+    <row r="511">
+      <c r="A511" t="inlineStr">
         <is>
           <t xml:space="preserve">「あなたの栄光を作れ」
 اصنَع مجدَك
@@ -11171,19 +11150,19 @@
 1811 Ahmed Madyan </t>
         </is>
       </c>
-      <c r="B512" t="inlineStr">
+      <c r="B511" t="inlineStr">
         <is>
           <t>images/「あなたの栄光を作れ」_img1.jpg</t>
         </is>
       </c>
-      <c r="C512" t="inlineStr">
+      <c r="C511" t="inlineStr">
         <is>
           <t>ヒーロー ,自分</t>
         </is>
       </c>
     </row>
-    <row r="513">
-      <c r="A513" t="inlineStr">
+    <row r="512">
+      <c r="A512" t="inlineStr">
         <is>
           <t xml:space="preserve">「声を上げろ」إرفع صوتك
 イルファア・サウタク [irfa* _sawta-k]
@@ -11192,19 +11171,19 @@
 2109 ALHURRA </t>
         </is>
       </c>
-      <c r="B513" t="inlineStr">
+      <c r="B512" t="inlineStr">
         <is>
           <t>images/「声を上げろ」_img1.jpg</t>
         </is>
       </c>
-      <c r="C513" t="inlineStr">
+      <c r="C512" t="inlineStr">
         <is>
           <t>発言 ,言論</t>
         </is>
       </c>
     </row>
-    <row r="514">
-      <c r="A514" t="inlineStr">
+    <row r="513">
+      <c r="A513" t="inlineStr">
         <is>
           <t xml:space="preserve">「口を開く前に、心を開きなさい」
 افتح عقلك قبل أن تفتح فمك
@@ -11214,19 +11193,19 @@
 2308 出典不明 </t>
         </is>
       </c>
-      <c r="B514" t="inlineStr">
+      <c r="B513" t="inlineStr">
         <is>
           <t>images/「口を開く前に、心を開きなさい」_img1.jpg</t>
         </is>
       </c>
-      <c r="C514" t="inlineStr">
+      <c r="C513" t="inlineStr">
         <is>
           <t>教訓 ,名言</t>
         </is>
       </c>
     </row>
-    <row r="515">
-      <c r="A515" t="inlineStr">
+    <row r="514">
+      <c r="A514" t="inlineStr">
         <is>
           <t xml:space="preserve">「読んでちょうだい、読んであげるよ」
 اِقرأ لي، أقرأ لك
@@ -11236,19 +11215,19 @@
 2308 archive org </t>
         </is>
       </c>
-      <c r="B515" t="inlineStr">
+      <c r="B514" t="inlineStr">
         <is>
           <t>images/「読んでちょうだい、読んであげるよ」_img1.jpg,images/「読んでちょうだい、読んであげるよ」_img2.jpg</t>
         </is>
       </c>
-      <c r="C515" t="inlineStr">
+      <c r="C514" t="inlineStr">
         <is>
           <t xml:space="preserve">絵本 ,読み聞かせ </t>
         </is>
       </c>
     </row>
-    <row r="516">
-      <c r="A516" t="inlineStr">
+    <row r="515">
+      <c r="A515" t="inlineStr">
         <is>
           <t xml:space="preserve">「がんばれ」ابذل جهدك
 ウブズル・ジャハダク [ubDhul jahda-k]
@@ -11256,19 +11235,19 @@
 2308 https://twitter.com/Ishaiookh/status/1469579864915288068 </t>
         </is>
       </c>
-      <c r="B516" t="inlineStr">
+      <c r="B515" t="inlineStr">
         <is>
           <t>images/「がんばれ」_img1.jpg</t>
         </is>
       </c>
-      <c r="C516" t="inlineStr">
+      <c r="C515" t="inlineStr">
         <is>
           <t>文字 ,下办つ_ぺ中ヵ可</t>
         </is>
       </c>
     </row>
-    <row r="517">
-      <c r="A517" t="inlineStr">
+    <row r="516">
+      <c r="A516" t="inlineStr">
         <is>
           <t xml:space="preserve">「窓を開けよ。そこに光がある」
 افتح النافذة ثمة ضوء
@@ -11278,19 +11257,19 @@
 2308 الدكتور خالد المنيف </t>
         </is>
       </c>
-      <c r="B517" t="inlineStr">
+      <c r="B516" t="inlineStr">
         <is>
           <t>images/「窓を開けよ。そこに光がある」_img1.jpg</t>
         </is>
       </c>
-      <c r="C517" t="inlineStr">
+      <c r="C516" t="inlineStr">
         <is>
           <t>換気 ,ウインドウズ</t>
         </is>
       </c>
     </row>
-    <row r="518">
-      <c r="A518" t="inlineStr">
+    <row r="517">
+      <c r="A517" t="inlineStr">
         <is>
           <t xml:space="preserve">「笑えよ」اضحك
 イドハク [i_dHak]
@@ -11299,19 +11278,19 @@
 1809 </t>
         </is>
       </c>
-      <c r="B518" t="inlineStr">
+      <c r="B517" t="inlineStr">
         <is>
           <t>images/「笑えよ」_img1.jpg</t>
         </is>
       </c>
-      <c r="C518" t="inlineStr">
+      <c r="C517" t="inlineStr">
         <is>
           <t>あらびあや</t>
         </is>
       </c>
     </row>
-    <row r="519">
-      <c r="A519" t="inlineStr">
+    <row r="518">
+      <c r="A518" t="inlineStr">
         <is>
           <t xml:space="preserve">「よろこべ」افرح
 イフラハ [ifraH]
@@ -11319,19 +11298,19 @@
 2308 https://samia-khalil.blogspot.jp/2014/08/blog-post.html?m=1 </t>
         </is>
       </c>
-      <c r="B519" t="inlineStr">
+      <c r="B518" t="inlineStr">
         <is>
           <t>images/「よろこべ」_img1.jpg</t>
         </is>
       </c>
-      <c r="C519" t="inlineStr">
+      <c r="C518" t="inlineStr">
         <is>
           <t>子供 ,笑顔</t>
         </is>
       </c>
     </row>
-    <row r="520">
-      <c r="A520" t="inlineStr">
+    <row r="519">
+      <c r="A519" t="inlineStr">
         <is>
           <t xml:space="preserve">「いつでも正しいことをしなさい」
 دائما افعل الشيء الصحيح
@@ -11341,19 +11320,19 @@
 2508 instagram com/p/zNNDYAsNaG/ </t>
         </is>
       </c>
-      <c r="B520" t="inlineStr">
+      <c r="B519" t="inlineStr">
         <is>
           <t>images/「いつでも正しいことをしなさい」_img1.jpg</t>
         </is>
       </c>
-      <c r="C520" t="inlineStr">
+      <c r="C519" t="inlineStr">
         <is>
           <t>教訓 ,正義</t>
         </is>
       </c>
     </row>
-    <row r="521">
-      <c r="A521" t="inlineStr">
+    <row r="520">
+      <c r="A520" t="inlineStr">
         <is>
           <t xml:space="preserve">「コンフォートゾーンから、出よう」
 اخرج من منطقة الراحة
@@ -11363,37 +11342,37 @@
 2010 kareem mrghani </t>
         </is>
       </c>
+      <c r="B520" t="inlineStr">
+        <is>
+          <t>images/「コンフォートゾーンから、出よう」_img1.jpg</t>
+        </is>
+      </c>
+      <c r="C520" t="inlineStr">
+        <is>
+          <t>鳥 ,勇気</t>
+        </is>
+      </c>
+    </row>
+    <row r="521">
+      <c r="A521" t="inlineStr">
+        <is>
+          <t xml:space="preserve">オットセイ。
+2308 https://twitter.com/NatGeoMagArab/status/1602604286109970432 </t>
+        </is>
+      </c>
       <c r="B521" t="inlineStr">
         <is>
-          <t>images/「コンフォートゾーンから、出よう」_img1.jpg</t>
+          <t>images/オットセイ。_img1.jpg,images/オットセイ。_img2.jpg</t>
         </is>
       </c>
       <c r="C521" t="inlineStr">
         <is>
-          <t>鳥 ,勇気</t>
+          <t>手書き語学 ,アラビア語 ,オットセイ</t>
         </is>
       </c>
     </row>
     <row r="522">
       <c r="A522" t="inlineStr">
-        <is>
-          <t xml:space="preserve">オットセイ。
-2308 https://twitter.com/NatGeoMagArab/status/1602604286109970432 </t>
-        </is>
-      </c>
-      <c r="B522" t="inlineStr">
-        <is>
-          <t>images/オットセイ。_img1.jpg,images/オットセイ。_img2.jpg</t>
-        </is>
-      </c>
-      <c r="C522" t="inlineStr">
-        <is>
-          <t>手書き語学 ,アラビア語 ,オットセイ</t>
-        </is>
-      </c>
-    </row>
-    <row r="523">
-      <c r="A523" t="inlineStr">
         <is>
           <t xml:space="preserve">「かわいい家に住む」
 يعيش في بيت لطيف
@@ -11403,19 +11382,19 @@
 2607 </t>
         </is>
       </c>
-      <c r="B523" t="inlineStr">
+      <c r="B522" t="inlineStr">
         <is>
           <t>images/「かわいい家に住む」_img1.jpg</t>
         </is>
       </c>
-      <c r="C523" t="inlineStr">
+      <c r="C522" t="inlineStr">
         <is>
           <t>アニメ ,ハム太郎</t>
         </is>
       </c>
     </row>
-    <row r="524">
-      <c r="A524" t="inlineStr">
+    <row r="523">
+      <c r="A523" t="inlineStr">
         <is>
           <t xml:space="preserve">「私の美しい町で大きい家に住んでいます」
 أعيش في بيت كبير في مدينتي الجميلة
@@ -11424,15 +11403,15 @@
 2410 Arabic With Nadia youtu be ocbg19GPCWE </t>
         </is>
       </c>
-      <c r="B524" t="inlineStr">
+      <c r="B523" t="inlineStr">
         <is>
           <t>images/「私の美しい町で大きい家に住んでいます_img1.jpg</t>
         </is>
       </c>
-      <c r="C524" t="inlineStr"/>
-    </row>
-    <row r="525">
-      <c r="A525" t="inlineStr">
+      <c r="C523" t="inlineStr"/>
+    </row>
+    <row r="524">
+      <c r="A524" t="inlineStr">
         <is>
           <t xml:space="preserve">「どうして早く寝るのかな」
 لماذا أنام باكراً؟
@@ -11442,19 +11421,19 @@
 2511 سلسلة الحلزونة </t>
         </is>
       </c>
-      <c r="B525" t="inlineStr">
+      <c r="B524" t="inlineStr">
         <is>
           <t>images/「どうして早く寝るのかな」_img1.jpg</t>
         </is>
       </c>
-      <c r="C525" t="inlineStr">
+      <c r="C524" t="inlineStr">
         <is>
           <t>絵本 ,ホルモン</t>
         </is>
       </c>
     </row>
-    <row r="526">
-      <c r="A526" t="inlineStr">
+    <row r="525">
+      <c r="A525" t="inlineStr">
         <is>
           <t xml:space="preserve">⁦「この絵文字はどんな意味？」⁩
 ماذا يعني هذا الايموجي؟؟
@@ -11464,19 +11443,19 @@
 2407 YouTube Smail Tech </t>
         </is>
       </c>
-      <c r="B526" t="inlineStr">
+      <c r="B525" t="inlineStr">
         <is>
           <t>images/⁦「この絵文字はどんな意味？」⁩_img1.jpg</t>
         </is>
       </c>
-      <c r="C526" t="inlineStr">
+      <c r="C525" t="inlineStr">
         <is>
           <t>顔 ,絵文字</t>
         </is>
       </c>
     </row>
-    <row r="527">
-      <c r="A527" t="inlineStr">
+    <row r="526">
+      <c r="A526" t="inlineStr">
         <is>
           <t xml:space="preserve">「回し車の中で回る」
 يدور في دولاب خفيف
@@ -11486,19 +11465,19 @@
 2109 </t>
         </is>
       </c>
-      <c r="B527" t="inlineStr">
+      <c r="B526" t="inlineStr">
         <is>
           <t>images/「回し車の中で回る」_img1.jpg</t>
         </is>
       </c>
-      <c r="C527" t="inlineStr">
+      <c r="C526" t="inlineStr">
         <is>
           <t>ハムスター  ,ハム太郎</t>
         </is>
       </c>
     </row>
-    <row r="528">
-      <c r="A528" t="inlineStr">
+    <row r="527">
+      <c r="A527" t="inlineStr">
         <is>
           <t xml:space="preserve">「自信を持つには？」
 كيف تثق بنفسك؟
@@ -11508,19 +11487,19 @@
 2411 Gwid3, tumblr </t>
         </is>
       </c>
-      <c r="B528" t="inlineStr">
+      <c r="B527" t="inlineStr">
         <is>
           <t>images/「自信を持つには？」_img1.jpg</t>
         </is>
       </c>
-      <c r="C528" t="inlineStr">
+      <c r="C527" t="inlineStr">
         <is>
           <t>イラスト ,自信</t>
         </is>
       </c>
     </row>
-    <row r="529">
-      <c r="A529" t="inlineStr">
+    <row r="528">
+      <c r="A528" t="inlineStr">
         <is>
           <t xml:space="preserve">「幸せな眠り…。この子ライオンは深い眠りに落ちている」
 نوم هانئ.. يغط هذا الشبل في نوم عميق
@@ -11531,19 +11510,19 @@
 2105 https://twitter.com/NatGeoMagArab/status/1305084013141319682 </t>
         </is>
       </c>
-      <c r="B529" t="inlineStr">
+      <c r="B528" t="inlineStr">
         <is>
           <t>images/「幸せな眠り…。この子ライオンは深い眠.jpeg</t>
         </is>
       </c>
-      <c r="C529" t="inlineStr">
+      <c r="C528" t="inlineStr">
         <is>
           <t>お昼寝 ,ｽﾔｧ</t>
         </is>
       </c>
     </row>
-    <row r="530">
-      <c r="A530" t="inlineStr">
+    <row r="529">
+      <c r="A529" t="inlineStr">
         <is>
           <t xml:space="preserve">「いつ思いつきますか？」
 متى تأتي الأفكار؟
@@ -11553,19 +11532,19 @@
 2103 alyaum com </t>
         </is>
       </c>
-      <c r="B530" t="inlineStr">
+      <c r="B529" t="inlineStr">
         <is>
           <t>images/「いつ思いつきますか？」_img1.jpg</t>
         </is>
       </c>
-      <c r="C530" t="inlineStr">
+      <c r="C529" t="inlineStr">
         <is>
           <t>ひらめき ,メモ</t>
         </is>
       </c>
     </row>
-    <row r="531">
-      <c r="A531" t="inlineStr">
+    <row r="530">
+      <c r="A530" t="inlineStr">
         <is>
           <t xml:space="preserve">「美しくありなさい。世界が美しく見えますよ」
 كن جميلا ترىٰ الوجود جميلا
@@ -11575,19 +11554,19 @@
 2111 https://iiislam.tumblr.com/post/90505498218 </t>
         </is>
       </c>
-      <c r="B531" t="inlineStr">
+      <c r="B530" t="inlineStr">
         <is>
           <t>images/「美しくありなさい。世界が美しく見えま_img1.jpg</t>
         </is>
       </c>
-      <c r="C531" t="inlineStr">
+      <c r="C530" t="inlineStr">
         <is>
           <t>壁 ,宇宙</t>
         </is>
       </c>
     </row>
-    <row r="532">
-      <c r="A532" t="inlineStr">
+    <row r="531">
+      <c r="A531" t="inlineStr">
         <is>
           <t xml:space="preserve">「まもなくNASAがジェイムズ・ウェッブ宇宙望遠鏡の打ち上げを行う」
 بعد ساعات قليلة ستقوم وكالة ناسا بإطلاق تلسكوب جيمس ويب
@@ -11595,19 +11574,19 @@
 2308 https://twitter.com/scitalk2u/status/1474643899603947524 </t>
         </is>
       </c>
-      <c r="B532" t="inlineStr">
+      <c r="B531" t="inlineStr">
         <is>
           <t>images/「まもなくNASAがジェイムズ・ウェッ_img1.jpg</t>
         </is>
       </c>
-      <c r="C532" t="inlineStr">
+      <c r="C531" t="inlineStr">
         <is>
           <t>NASA ,望遠鏡</t>
         </is>
       </c>
     </row>
-    <row r="533">
-      <c r="A533" t="inlineStr">
+    <row r="532">
+      <c r="A532" t="inlineStr">
         <is>
           <t xml:space="preserve">「お疲れ様です」يعطيك العافية
 ヤーアティーキルアーフィエ [ya-*_tiy-k el-*aafyeh]
@@ -11616,15 +11595,15 @@
 2109 محمد و ديمة بشار </t>
         </is>
       </c>
-      <c r="B533" t="inlineStr"/>
-      <c r="C533" t="inlineStr">
+      <c r="B532" t="inlineStr"/>
+      <c r="C532" t="inlineStr">
         <is>
           <t>歌 ,労い</t>
         </is>
       </c>
     </row>
-    <row r="534">
-      <c r="A534" t="inlineStr">
+    <row r="533">
+      <c r="A533" t="inlineStr">
         <is>
           <t xml:space="preserve">「まるでこのペンギンは大声で叫んでいるかのようだ」
 يبدو هذا البطريق وكأنه يصيح بعلو صوته
@@ -11632,19 +11611,19 @@
 2308 https://twitter.com/NatGeoMagArab/status/1492023331846967296 </t>
         </is>
       </c>
-      <c r="B534" t="inlineStr">
+      <c r="B533" t="inlineStr">
         <is>
           <t>images/「まるでこのペンギンは大声で叫んでいる_img1.jpg</t>
         </is>
       </c>
-      <c r="C534" t="inlineStr">
+      <c r="C533" t="inlineStr">
         <is>
           <t>手書き語学 ,ペンギン</t>
         </is>
       </c>
     </row>
-    <row r="535">
-      <c r="A535" t="inlineStr">
+    <row r="534">
+      <c r="A534" t="inlineStr">
         <is>
           <t xml:space="preserve">「Reteti Elephant Sanctuaryではゾウの孤児たちが良質な世話を受けている」
 تحظى الفيلة اليتيمة في "ملاذ ريتِيتِي لرعاية الفِيَلة" برعاية فائقة
@@ -11652,19 +11631,19 @@
 2209 https://twitter.com/NatGeoMagArab/status/1568683277845942273 </t>
         </is>
       </c>
-      <c r="B535" t="inlineStr">
+      <c r="B534" t="inlineStr">
         <is>
           <t>images/「Reteti Elephant Sa.jpg</t>
         </is>
       </c>
-      <c r="C535" t="inlineStr">
+      <c r="C534" t="inlineStr">
         <is>
           <t>ケニア</t>
         </is>
       </c>
     </row>
-    <row r="536">
-      <c r="A536" t="inlineStr">
+    <row r="535">
+      <c r="A535" t="inlineStr">
         <is>
           <t xml:space="preserve">「すぐ戻ります」سنعود بعد قليل
 サナウード・バアド・カリール [sa-na-*uud ba*d qaliil]
@@ -11673,19 +11652,19 @@
 2308 Clacket Media </t>
         </is>
       </c>
-      <c r="B536" t="inlineStr">
+      <c r="B535" t="inlineStr">
         <is>
           <t>images/「すぐ戻ります」_img1.jpg</t>
         </is>
       </c>
-      <c r="C536" t="inlineStr">
+      <c r="C535" t="inlineStr">
         <is>
           <t>プレート ,ドラマ</t>
         </is>
       </c>
     </row>
-    <row r="537">
-      <c r="A537" t="inlineStr">
+    <row r="536">
+      <c r="A536" t="inlineStr">
         <is>
           <t xml:space="preserve">「いつの日か、私は飛ぶんだ」
 يوم من الأيام سأطير
@@ -11695,19 +11674,19 @@
 2105 a-d-a-y-d-r-e-a-m-e-r.tumblr com </t>
         </is>
       </c>
-      <c r="B537" t="inlineStr">
+      <c r="B536" t="inlineStr">
         <is>
           <t>images/「いつの日か、私は飛ぶんだ」_img1.jpg</t>
         </is>
       </c>
-      <c r="C537" t="inlineStr">
+      <c r="C536" t="inlineStr">
         <is>
           <t>希望 ,未来</t>
         </is>
       </c>
     </row>
-    <row r="538">
-      <c r="A538" t="inlineStr">
+    <row r="537">
+      <c r="A537" t="inlineStr">
         <is>
           <t xml:space="preserve">「彼の声がこんなふうだと想像しましたか？」
 هل تخيلت أن يكون صوته هكذا؟
@@ -11715,19 +11694,19 @@
 2504 https://twitter.com/NatGeoMagArab/status/1567543266954067970 </t>
         </is>
       </c>
-      <c r="B538" t="inlineStr">
+      <c r="B537" t="inlineStr">
         <is>
           <t>images/「彼の声がこんなふうだと想像しましたか_img1.jpg</t>
         </is>
       </c>
-      <c r="C538" t="inlineStr">
+      <c r="C537" t="inlineStr">
         <is>
           <t>手書き語学 ,アラビア語 ,齧歯類</t>
         </is>
       </c>
     </row>
-    <row r="539">
-      <c r="A539" t="inlineStr">
+    <row r="538">
+      <c r="A538" t="inlineStr">
         <is>
           <t xml:space="preserve">「幸せでいるための10の科学的方法」
 عشر طرق علمية لتكون سعيدا
@@ -11736,19 +11715,19 @@
 2308 Founders and Founders </t>
         </is>
       </c>
-      <c r="B539" t="inlineStr">
+      <c r="B538" t="inlineStr">
         <is>
           <t>images/「幸せでいるための10の科学的方法」_img1.jpg</t>
         </is>
       </c>
-      <c r="C539" t="inlineStr">
+      <c r="C538" t="inlineStr">
         <is>
           <t>happy ,コツ</t>
         </is>
       </c>
     </row>
-    <row r="540">
-      <c r="A540" t="inlineStr">
+    <row r="539">
+      <c r="A539" t="inlineStr">
         <is>
           <t xml:space="preserve">「何事も難しい。簡単になる前は」
 كل شيء صعب قبل أن يصير سهل
@@ -11757,19 +11736,19 @@
 1809 nihad me </t>
         </is>
       </c>
-      <c r="B540" t="inlineStr">
+      <c r="B539" t="inlineStr">
         <is>
           <t>images/「何事も難しい。簡単になる前は」_img1.jpg</t>
         </is>
       </c>
-      <c r="C540" t="inlineStr">
+      <c r="C539" t="inlineStr">
         <is>
           <t>初心者 ,教訓</t>
         </is>
       </c>
     </row>
-    <row r="541">
-      <c r="A541" t="inlineStr">
+    <row r="540">
+      <c r="A540" t="inlineStr">
         <is>
           <t xml:space="preserve">「私は戻らない」لن اعود
 ラン・アウード [lan 'a-*uud(a)]
@@ -11778,19 +11757,19 @@
 2109 elcinema com </t>
         </is>
       </c>
-      <c r="B541" t="inlineStr">
+      <c r="B540" t="inlineStr">
         <is>
           <t>images/「私は戻らない」_img1.jpg</t>
         </is>
       </c>
-      <c r="C541" t="inlineStr">
+      <c r="C540" t="inlineStr">
         <is>
           <t>タイトル ,なんちゅう顔しとる</t>
         </is>
       </c>
     </row>
-    <row r="542">
-      <c r="A542" t="inlineStr">
+    <row r="541">
+      <c r="A541" t="inlineStr">
         <is>
           <t xml:space="preserve">「私は作家になるのが夢です」
 أحلُمُ أن أكونَ كاتبة
@@ -11800,19 +11779,19 @@
 2308 Maktabatee com </t>
         </is>
       </c>
-      <c r="B542" t="inlineStr">
+      <c r="B541" t="inlineStr">
         <is>
           <t>images/「私は作家になるのが夢です」_img1.jpg</t>
         </is>
       </c>
-      <c r="C542" t="inlineStr">
+      <c r="C541" t="inlineStr">
         <is>
           <t>作家志望 ,ライター</t>
         </is>
       </c>
     </row>
-    <row r="543">
-      <c r="A543" t="inlineStr">
+    <row r="542">
+      <c r="A542" t="inlineStr">
         <is>
           <t xml:space="preserve">「あなたが去った後も波は止みません」
 لن يقف الموج بعد رحيلك
@@ -11822,19 +11801,19 @@
 2308 ريم الشاوش https://ar.arabwomanmag.com/%D9%84%D9%86-%D9%8A%D9%82%D9%81-%D8%A7%D9%84%D9%85%D9%88%D8%AC-%D8%A8%D8%B9%D8%AF-%D8%B1%D8%AD%D9%8A%D9%84%D9%83-%D8%A8%D8%B9%D8%AF-%D8%B1%D8%AD%D9%8A%D9%84%D9%83/ </t>
         </is>
       </c>
-      <c r="B543" t="inlineStr">
+      <c r="B542" t="inlineStr">
         <is>
           <t>images/「あなたが去った後も波は止みません」_img1.jpg</t>
         </is>
       </c>
-      <c r="C543" t="inlineStr">
+      <c r="C542" t="inlineStr">
         <is>
           <t>海 ,哲学</t>
         </is>
       </c>
     </row>
-    <row r="544">
-      <c r="A544" t="inlineStr">
+    <row r="543">
+      <c r="A543" t="inlineStr">
         <is>
           <t xml:space="preserve">「彼の尖った牙を心配するな」
 لا تدع أنيابه المدببة تقلقك
@@ -11843,19 +11822,19 @@
 2308 https://twitter.com/NatGeoMagArab/status/1524691046818406400 </t>
         </is>
       </c>
-      <c r="B544" t="inlineStr">
+      <c r="B543" t="inlineStr">
         <is>
           <t>images/「彼の尖った牙を心配するな」_img1.jpg,images/「彼の尖った牙を心配するな」_img2.jpg,images/「彼の尖った牙を心配するな」_img3.jpg</t>
         </is>
       </c>
-      <c r="C544" t="inlineStr">
+      <c r="C543" t="inlineStr">
         <is>
           <t xml:space="preserve">手書き語学 ,アラビア語 ,キバノロ </t>
         </is>
       </c>
     </row>
-    <row r="545">
-      <c r="A545" t="inlineStr">
+    <row r="544">
+      <c r="A544" t="inlineStr">
         <is>
           <t xml:space="preserve">「恐れるな」لا تخف
 ラー・タカフ [laa ta-Khaf]
@@ -11864,19 +11843,19 @@
 2308 KiTeLetZ </t>
         </is>
       </c>
-      <c r="B545" t="inlineStr">
+      <c r="B544" t="inlineStr">
         <is>
           <t>images/「恐れるな」_img1.jpg</t>
         </is>
       </c>
-      <c r="C545" t="inlineStr">
+      <c r="C544" t="inlineStr">
         <is>
           <t>カリグラフィー ,緑</t>
         </is>
       </c>
     </row>
-    <row r="546">
-      <c r="A546" t="inlineStr">
+    <row r="545">
+      <c r="A545" t="inlineStr">
         <is>
           <t xml:space="preserve">「立ち上がれ。遅すぎることはない」
 انهض. لم يفت الأوان بعد
@@ -11886,19 +11865,19 @@
 2308 typo_g </t>
         </is>
       </c>
-      <c r="B546" t="inlineStr">
+      <c r="B545" t="inlineStr">
         <is>
           <t>images/「立ち上がれ。遅すぎることはない」_img1.jpg</t>
         </is>
       </c>
-      <c r="C546" t="inlineStr">
+      <c r="C545" t="inlineStr">
         <is>
           <t>出発</t>
         </is>
       </c>
     </row>
-    <row r="547">
-      <c r="A547" t="inlineStr">
+    <row r="546">
+      <c r="A546" t="inlineStr">
         <is>
           <t xml:space="preserve">「泣かないで」لا تَبْكِ
 ラー・タブキ [laa ta-bki]
@@ -11907,19 +11886,19 @@
 2203 arwa </t>
         </is>
       </c>
-      <c r="B547" t="inlineStr">
+      <c r="B546" t="inlineStr">
         <is>
           <t>images/「泣かないで」_img1.jpg</t>
         </is>
       </c>
-      <c r="C547" t="inlineStr">
+      <c r="C546" t="inlineStr">
         <is>
           <t>傘 ,虹</t>
         </is>
       </c>
     </row>
-    <row r="548">
-      <c r="A548" t="inlineStr">
+    <row r="547">
+      <c r="A547" t="inlineStr">
         <is>
           <t xml:space="preserve">「強くあるしかない」
 لا تكنْ الا قوِيا
@@ -11929,19 +11908,19 @@
 2401 AHMED ELASSAL </t>
         </is>
       </c>
-      <c r="B548" t="inlineStr">
+      <c r="B547" t="inlineStr">
         <is>
           <t>images/「強くあるしかない」_img1.jpg</t>
         </is>
       </c>
-      <c r="C548" t="inlineStr">
+      <c r="C547" t="inlineStr">
         <is>
           <t>二重否定 ,心構え</t>
         </is>
       </c>
     </row>
-    <row r="549">
-      <c r="A549" t="inlineStr">
+    <row r="548">
+      <c r="A548" t="inlineStr">
         <is>
           <t xml:space="preserve">「止まりなさい」قف
 キフ [qif]
@@ -11951,19 +11930,19 @@
 2308 出典不明（英語版：同内容。中国語版：「今日も可愛いね」） </t>
         </is>
       </c>
-      <c r="B549" t="inlineStr">
+      <c r="B548" t="inlineStr">
         <is>
           <t>images/「止まりなさい」_img1.jpg,images/「止まりなさい」_img2.jpg,images/「止まりなさい」_img3.jpg,images/「止まりなさい」_img4.jpg</t>
         </is>
       </c>
-      <c r="C549" t="inlineStr">
+      <c r="C548" t="inlineStr">
         <is>
           <t>かわいい ,職質</t>
         </is>
       </c>
     </row>
-    <row r="550">
-      <c r="A550" t="inlineStr">
+    <row r="549">
+      <c r="A549" t="inlineStr">
         <is>
           <t xml:space="preserve">「自分の人生を生きろ」عش حياتك
 イシ・ハヤータク [*iSh Hayaata-k]
@@ -11972,19 +11951,19 @@
 2607 Pinterest, hus2013asr </t>
         </is>
       </c>
-      <c r="B550" t="inlineStr">
+      <c r="B549" t="inlineStr">
         <is>
           <t>images/「自分の人生を生きろ」_img1.jpg</t>
         </is>
       </c>
-      <c r="C550" t="inlineStr">
+      <c r="C549" t="inlineStr">
         <is>
           <t>iPhone ,壁紙</t>
         </is>
       </c>
     </row>
-    <row r="551">
-      <c r="A551" t="inlineStr">
+    <row r="550">
+      <c r="A550" t="inlineStr">
         <is>
           <t xml:space="preserve">「おやすみザイナ」نامي يا زينة
 ナーミー・ヤー・ザイナ [naam-ii yaa zayna]
@@ -11993,19 +11972,19 @@
 2511 Dar Alsalwa </t>
         </is>
       </c>
-      <c r="B551" t="inlineStr">
+      <c r="B550" t="inlineStr">
         <is>
           <t>images/「おやすみザイナ」_img1.jpg</t>
         </is>
       </c>
-      <c r="C551" t="inlineStr">
+      <c r="C550" t="inlineStr">
         <is>
           <t>絵本 ,ベッド</t>
         </is>
       </c>
     </row>
-    <row r="552">
-      <c r="A552" t="inlineStr">
+    <row r="551">
+      <c r="A551" t="inlineStr">
         <is>
           <t xml:space="preserve">「強くありなさい」كُن قَوياً
 クン・カウィーヤン [kun qawiiyan]
@@ -12014,19 +11993,19 @@
 2109 MJCODEZ </t>
         </is>
       </c>
-      <c r="B552" t="inlineStr">
+      <c r="B551" t="inlineStr">
         <is>
           <t>images/「強くありなさい」_img1.jpg</t>
         </is>
       </c>
-      <c r="C552" t="inlineStr">
+      <c r="C551" t="inlineStr">
         <is>
           <t>名言 ,強い</t>
         </is>
       </c>
     </row>
-    <row r="553">
-      <c r="A553" t="inlineStr">
+    <row r="552">
+      <c r="A552" t="inlineStr">
         <is>
           <t xml:space="preserve">「強くありなさい、自分のために」
 كُن قويًا لأجلك
@@ -12036,19 +12015,19 @@
 1809 gwid3.tumblr </t>
         </is>
       </c>
-      <c r="B553" t="inlineStr">
+      <c r="B552" t="inlineStr">
         <is>
           <t>images/「強くありなさい、自分のために」_img1.jpg</t>
         </is>
       </c>
-      <c r="C553" t="inlineStr">
+      <c r="C552" t="inlineStr">
         <is>
           <t>名言 ,強い</t>
         </is>
       </c>
     </row>
-    <row r="554">
-      <c r="A554" t="inlineStr">
+    <row r="553">
+      <c r="A553" t="inlineStr">
         <is>
           <t xml:space="preserve">「賢くバカであれ」
 كن غبياً بطريقة ذكية
@@ -12058,19 +12037,19 @@
 2110 ALADMIRAL jony </t>
         </is>
       </c>
-      <c r="B554" t="inlineStr">
+      <c r="B553" t="inlineStr">
         <is>
           <t>images/「賢くバカであれ」_img1.jpg</t>
         </is>
       </c>
-      <c r="C554" t="inlineStr">
+      <c r="C553" t="inlineStr">
         <is>
           <t>逆説的 ,キツネ</t>
         </is>
       </c>
     </row>
-    <row r="555">
-      <c r="A555" t="inlineStr">
+    <row r="554">
+      <c r="A554" t="inlineStr">
         <is>
           <t xml:space="preserve">「どこでも自分でありなさい」
 كن أنت أينما كنت
@@ -12080,19 +12059,19 @@
 2605 souqfann com/r/15987  </t>
         </is>
       </c>
-      <c r="B555" t="inlineStr">
+      <c r="B554" t="inlineStr">
         <is>
           <t>images/「どこでも自分でありなさい」_img1.jpg</t>
         </is>
       </c>
-      <c r="C555" t="inlineStr">
+      <c r="C554" t="inlineStr">
         <is>
           <t>デザイン ,アート</t>
         </is>
       </c>
     </row>
-    <row r="556">
-      <c r="A556" t="inlineStr">
+    <row r="555">
+      <c r="A555" t="inlineStr">
         <is>
           <t xml:space="preserve">「止まれ。検問中」قف للتفتيش
 キフ。リッタフティーシ [qif li^taftiiSh]
@@ -12101,19 +12080,19 @@
 2109 Marcel Musil flickr </t>
         </is>
       </c>
-      <c r="B556" t="inlineStr">
+      <c r="B555" t="inlineStr">
         <is>
           <t>images/「止まれ。検問中」_img1.jpg</t>
         </is>
       </c>
-      <c r="C556" t="inlineStr">
+      <c r="C555" t="inlineStr">
         <is>
           <t>標識</t>
         </is>
       </c>
     </row>
-    <row r="557">
-      <c r="A557" t="inlineStr">
+    <row r="556">
+      <c r="A556" t="inlineStr">
         <is>
           <t xml:space="preserve">「さあおやすみ」هَيّا نَمْ
 ハイヤー・ナム [hayyaa nam]
@@ -12121,19 +12100,19 @@
 2308 Maktabatee com </t>
         </is>
       </c>
-      <c r="B557" t="inlineStr">
+      <c r="B556" t="inlineStr">
         <is>
           <t>images/「さあおやすみ」_img1.jpg</t>
         </is>
       </c>
-      <c r="C557" t="inlineStr">
+      <c r="C556" t="inlineStr">
         <is>
           <t>就寝 ,絵本</t>
         </is>
       </c>
     </row>
-    <row r="558">
-      <c r="A558" t="inlineStr">
+    <row r="557">
+      <c r="A557" t="inlineStr">
         <is>
           <t xml:space="preserve">「あなたであれ」كن أنت
 クン・アンタ [ku 'anta]
@@ -12141,19 +12120,19 @@
 1809 madyan22.tumblr </t>
         </is>
       </c>
-      <c r="B558" t="inlineStr">
+      <c r="B557" t="inlineStr">
         <is>
           <t>images/「あなたであれ」_img1.jpg</t>
         </is>
       </c>
-      <c r="C558" t="inlineStr">
+      <c r="C557" t="inlineStr">
         <is>
           <t>個性 ,自尊心</t>
         </is>
       </c>
     </row>
-    <row r="559">
-      <c r="A559" t="inlineStr">
+    <row r="558">
+      <c r="A558" t="inlineStr">
         <is>
           <t xml:space="preserve">「過去を忘れろ。だが教訓は忘れるな」
 إنسَ الماضي ولكن لاتنسَ الدرس
@@ -12163,19 +12142,19 @@
 2308 https://www.instagram.com/emanalyafai </t>
         </is>
       </c>
-      <c r="B559" t="inlineStr">
+      <c r="B558" t="inlineStr">
         <is>
           <t>images/「過去を忘れろ。だが教訓は忘れるな」_img1.jpg</t>
         </is>
       </c>
-      <c r="C559" t="inlineStr">
+      <c r="C558" t="inlineStr">
         <is>
           <t>名言 ,未来</t>
         </is>
       </c>
     </row>
-    <row r="560">
-      <c r="A560" t="inlineStr">
+    <row r="559">
+      <c r="A559" t="inlineStr">
         <is>
           <t xml:space="preserve">「この世界で君も何かを持っている。だから立ち上がれ！」
 لَكْ شيءٌ في هَذَا العَالَم… فَقُمْ
@@ -12183,19 +12162,19 @@
 2511 mjdal7arbi tumblr, Ghassan Kanafani </t>
         </is>
       </c>
-      <c r="B560" t="inlineStr">
+      <c r="B559" t="inlineStr">
         <is>
           <t>images/「この世界で君も何かを持っている。だか.jpg</t>
         </is>
       </c>
-      <c r="C560" t="inlineStr">
+      <c r="C559" t="inlineStr">
         <is>
           <t>鼓舞 ,ハンカチ王子</t>
         </is>
       </c>
     </row>
-    <row r="561">
-      <c r="A561" t="inlineStr">
+    <row r="560">
+      <c r="A560" t="inlineStr">
         <is>
           <t xml:space="preserve">「かぞえてかずをかきましょう」
 عد واكتب العدد
@@ -12204,19 +12183,19 @@
 2604 facebook Qsre alawani </t>
         </is>
       </c>
-      <c r="B561" t="inlineStr">
+      <c r="B560" t="inlineStr">
         <is>
           <t>images/「かぞえてかずをかきましょう」.JPG</t>
         </is>
       </c>
-      <c r="C561" t="inlineStr">
+      <c r="C560" t="inlineStr">
         <is>
           <t>算数 ,さんすう</t>
         </is>
       </c>
     </row>
-    <row r="562">
-      <c r="A562" t="inlineStr">
+    <row r="561">
+      <c r="A561" t="inlineStr">
         <is>
           <t xml:space="preserve">「いつも人助けしなさい」
 كن عونا للناس دوما
@@ -12226,19 +12205,19 @@
 2109 Muhammad ElMahdy </t>
         </is>
       </c>
-      <c r="B562" t="inlineStr">
+      <c r="B561" t="inlineStr">
         <is>
           <t>images/「いつも人助けしなさい」_img1.jpg</t>
         </is>
       </c>
-      <c r="C562" t="inlineStr">
+      <c r="C561" t="inlineStr">
         <is>
           <t>教訓 ,助っ人</t>
         </is>
       </c>
     </row>
-    <row r="563">
-      <c r="A563" t="inlineStr">
+    <row r="562">
+      <c r="A562" t="inlineStr">
         <is>
           <t xml:space="preserve">「毎年、ノーベル賞が授けられる」
 في كل عام تُمنح جوائز نوبل
@@ -12246,19 +12225,19 @@
 2404 https://twitter.com/SciTalk2U/status/1462482447627661319 </t>
         </is>
       </c>
-      <c r="B563" t="inlineStr">
+      <c r="B562" t="inlineStr">
         <is>
           <t>images/「毎年、ノーベル賞が授けられる」_img1.jpg</t>
         </is>
       </c>
-      <c r="C563" t="inlineStr">
+      <c r="C562" t="inlineStr">
         <is>
           <t>手書き語学 ,アラビア語 ,ノーベル賞</t>
         </is>
       </c>
     </row>
-    <row r="564">
-      <c r="A564" t="inlineStr">
+    <row r="563">
+      <c r="A563" t="inlineStr">
         <is>
           <t xml:space="preserve">「あなたはアラビア語を話しますか」
 هل تتكلم العربية؟
@@ -12268,19 +12247,19 @@
 2109 al3arabiya com </t>
         </is>
       </c>
-      <c r="B564" t="inlineStr">
+      <c r="B563" t="inlineStr">
         <is>
           <t>images/「あなたはアラビア語を話しますか」_img1.jpg</t>
         </is>
       </c>
-      <c r="C564" t="inlineStr">
+      <c r="C563" t="inlineStr">
         <is>
           <t>教科書 ,テキスト</t>
         </is>
       </c>
     </row>
-    <row r="565">
-      <c r="A565" t="inlineStr">
+    <row r="564">
+      <c r="A564" t="inlineStr">
         <is>
           <t xml:space="preserve">「このインコは亜熱帯が起源である」
 يتحدر هذا الباراكيت من المناطق شبه الاستوائية
@@ -12288,19 +12267,19 @@
 2402 https://x.com/NatGeoMagArab/status/1690626751578439680 </t>
         </is>
       </c>
-      <c r="B565" t="inlineStr">
+      <c r="B564" t="inlineStr">
         <is>
           <t>images/「このインコは亜熱帯が起源である」_img1.jpg,images/「このインコは亜熱帯が起源である」_img2.jpg</t>
         </is>
       </c>
-      <c r="C565" t="inlineStr">
+      <c r="C564" t="inlineStr">
         <is>
           <t>手書き語学 ,アラビア語 ,オナガミドリインコ</t>
         </is>
       </c>
     </row>
-    <row r="566">
-      <c r="A566" t="inlineStr">
+    <row r="565">
+      <c r="A565" t="inlineStr">
         <is>
           <t xml:space="preserve">「彼を覚えていますか」
 هل تتذكرونه؟
@@ -12310,19 +12289,19 @@
 2308 http://newsfacetruth.blogspot.com/2017/07/blog-post_11.html </t>
         </is>
       </c>
-      <c r="B566" t="inlineStr">
+      <c r="B565" t="inlineStr">
         <is>
           <t>images/「彼を覚えていますか」_img1.jpg</t>
         </is>
       </c>
-      <c r="C566" t="inlineStr">
+      <c r="C565" t="inlineStr">
         <is>
           <t>グレンダイザー ,UFOロボ</t>
         </is>
       </c>
     </row>
-    <row r="567">
-      <c r="A567" t="inlineStr">
+    <row r="566">
+      <c r="A566" t="inlineStr">
         <is>
           <t xml:space="preserve">「内面が変われば周りが変わる」
 عندما تتغير الأشياء داخلك، تتغير الأشياء من حولك
@@ -12331,19 +12310,19 @@
 2501 Facebook, Cairo Mockingbird </t>
         </is>
       </c>
-      <c r="B567" t="inlineStr">
+      <c r="B566" t="inlineStr">
         <is>
           <t>images/「内面が変われば周りが変わる」_img1.jpg</t>
         </is>
       </c>
-      <c r="C567" t="inlineStr">
+      <c r="C566" t="inlineStr">
         <is>
           <t>ポジティブ</t>
         </is>
       </c>
     </row>
-    <row r="568">
-      <c r="A568" t="inlineStr">
+    <row r="567">
+      <c r="A567" t="inlineStr">
         <is>
           <t xml:space="preserve">「天才になるには？」
 كيف تصبح عبقريا؟
@@ -12352,19 +12331,19 @@
 2109 Infographics Samah Faris </t>
         </is>
       </c>
-      <c r="B568" t="inlineStr">
+      <c r="B567" t="inlineStr">
         <is>
           <t>images/「天才になるには？」_img1.jpg</t>
         </is>
       </c>
-      <c r="C568" t="inlineStr">
+      <c r="C567" t="inlineStr">
         <is>
           <t>秘訣 ,コツ</t>
         </is>
       </c>
     </row>
-    <row r="569">
-      <c r="A569" t="inlineStr">
+    <row r="568">
+      <c r="A568" t="inlineStr">
         <is>
           <t xml:space="preserve">「クリエイティブになるには？」
 كيف تصبح مبدعًا؟
@@ -12373,19 +12352,19 @@
 2308 Gwid3 </t>
         </is>
       </c>
-      <c r="B569" t="inlineStr">
+      <c r="B568" t="inlineStr">
         <is>
           <t>images/「クリエイティブになるには？」_img1.jpg</t>
         </is>
       </c>
-      <c r="C569" t="inlineStr">
+      <c r="C568" t="inlineStr">
         <is>
           <t>心得 ,Tips</t>
         </is>
       </c>
     </row>
-    <row r="570">
-      <c r="A570" t="inlineStr">
+    <row r="569">
+      <c r="A569" t="inlineStr">
         <is>
           <t xml:space="preserve">「彼らと友情を交わすよハム太郎」
 وبالإخاء يبادلهم هامتارو
@@ -12395,19 +12374,19 @@
 2109 </t>
         </is>
       </c>
-      <c r="B570" t="inlineStr">
+      <c r="B569" t="inlineStr">
         <is>
           <t>images/「彼らと友情を交わすよハム太郎」_img1.jpg</t>
         </is>
       </c>
-      <c r="C570" t="inlineStr">
+      <c r="C569" t="inlineStr">
         <is>
           <t>アニメ ,ハム太郎</t>
         </is>
       </c>
     </row>
-    <row r="571">
-      <c r="A571" t="inlineStr">
+    <row r="570">
+      <c r="A570" t="inlineStr">
         <is>
           <t xml:space="preserve">「誰がニワトリを助ける？」
 من يساعد الدّجاجة؟
@@ -12417,19 +12396,19 @@
 2109 alnqsh com </t>
         </is>
       </c>
-      <c r="B571" t="inlineStr">
+      <c r="B570" t="inlineStr">
         <is>
           <t>images/「誰がニワトリを助ける？」_img1.jpg</t>
         </is>
       </c>
-      <c r="C571" t="inlineStr">
+      <c r="C570" t="inlineStr">
         <is>
           <t>絵本 ,チキン</t>
         </is>
       </c>
     </row>
-    <row r="572">
-      <c r="A572" t="inlineStr">
+    <row r="571">
+      <c r="A571" t="inlineStr">
         <is>
           <t xml:space="preserve">「心臓病を避けるには？」
 كيف تتجنب أمراض القلب؟
@@ -12439,37 +12418,37 @@
 2608 lanamedical_sa </t>
         </is>
       </c>
+      <c r="B571" t="inlineStr">
+        <is>
+          <t>images/「心臓病を避けるには？」.jpg</t>
+        </is>
+      </c>
+      <c r="C571" t="inlineStr">
+        <is>
+          <t>生活習慣病 ,心臓</t>
+        </is>
+      </c>
+    </row>
+    <row r="572">
+      <c r="A572" t="inlineStr">
+        <is>
+          <t xml:space="preserve">「どうやらこの好奇心旺盛なペンギンは…」
+2308 https://twitter.com/NatGeoMagArab/status/1591460860207443968 </t>
+        </is>
+      </c>
       <c r="B572" t="inlineStr">
         <is>
-          <t>images/「心臓病を避けるには？」.jpg</t>
+          <t>images/「どうやらこの好奇心旺盛なペンギンは…_img1.jpg,images/ 「どうやらこの好奇心旺盛なペンギンは…_img2.jpg</t>
         </is>
       </c>
       <c r="C572" t="inlineStr">
         <is>
-          <t>生活習慣病 ,心臓</t>
+          <t>手書き語学 ,アラビア語 ,オウサマペンギン</t>
         </is>
       </c>
     </row>
     <row r="573">
       <c r="A573" t="inlineStr">
-        <is>
-          <t xml:space="preserve">「どうやらこの好奇心旺盛なペンギンは…」
-2308 https://twitter.com/NatGeoMagArab/status/1591460860207443968 </t>
-        </is>
-      </c>
-      <c r="B573" t="inlineStr">
-        <is>
-          <t>images/「どうやらこの好奇心旺盛なペンギンは…_img1.jpg,images/ 「どうやらこの好奇心旺盛なペンギンは…_img2.jpg</t>
-        </is>
-      </c>
-      <c r="C573" t="inlineStr">
-        <is>
-          <t>手書き語学 ,アラビア語 ,オウサマペンギン</t>
-        </is>
-      </c>
-    </row>
-    <row r="574">
-      <c r="A574" t="inlineStr">
         <is>
           <t xml:space="preserve">「この生き物を見分けられますか？」
 هل تُميز هذا الكائن؟
@@ -12478,19 +12457,19 @@
 2308 https://twitter.com/NatGeoMagArab/status/1455121397827600388 </t>
         </is>
       </c>
-      <c r="B574" t="inlineStr">
+      <c r="B573" t="inlineStr">
         <is>
           <t>images/「この生き物を見分けられますか？」_img1.jpg</t>
         </is>
       </c>
-      <c r="C574" t="inlineStr">
+      <c r="C573" t="inlineStr">
         <is>
           <t xml:space="preserve">手書き語学 ,カバ </t>
         </is>
       </c>
     </row>
-    <row r="575">
-      <c r="A575" t="inlineStr">
+    <row r="574">
+      <c r="A574" t="inlineStr">
         <is>
           <t xml:space="preserve">「ひとを幸せにするには？」
 كيف تسعد غيرك؟
@@ -12500,19 +12479,19 @@
 2308 Gwid3 </t>
         </is>
       </c>
-      <c r="B575" t="inlineStr">
+      <c r="B574" t="inlineStr">
         <is>
           <t>images/「ひとを幸せにするには？」_img1.jpg</t>
         </is>
       </c>
-      <c r="C575" t="inlineStr">
+      <c r="C574" t="inlineStr">
         <is>
           <t>思いやり ,心</t>
         </is>
       </c>
     </row>
-    <row r="576">
-      <c r="A576" t="inlineStr">
+    <row r="575">
+      <c r="A575" t="inlineStr">
         <is>
           <t xml:space="preserve">「ラマダン月に口臭をおさえる方法は？」
 كيف تتجنب رائحة الفم في رمضان
@@ -12521,19 +12500,19 @@
 2109 AlArabiya </t>
         </is>
       </c>
-      <c r="B576" t="inlineStr">
+      <c r="B575" t="inlineStr">
         <is>
           <t>images/「ラマダン月に口臭をおさえる方法は？」_img1.jpg</t>
         </is>
       </c>
-      <c r="C576" t="inlineStr">
+      <c r="C575" t="inlineStr">
         <is>
           <t>イスラム教 ,ブレスケア</t>
         </is>
       </c>
     </row>
-    <row r="577">
-      <c r="A577" t="inlineStr">
+    <row r="576">
+      <c r="A576" t="inlineStr">
         <is>
           <t xml:space="preserve">「ヨユウなきユウヨ」
 يمهل ولا يهمل
@@ -12543,19 +12522,19 @@
 2512 instagram com/p/CK4CLqeJ3dy/ </t>
         </is>
       </c>
-      <c r="B577" t="inlineStr">
+      <c r="B576" t="inlineStr">
         <is>
           <t>images/「ヨユウなきユウヨ」_img1.jpg</t>
         </is>
       </c>
-      <c r="C577" t="inlineStr">
+      <c r="C576" t="inlineStr">
         <is>
           <t>時計 ,からくり</t>
         </is>
       </c>
     </row>
-    <row r="578">
-      <c r="A578" t="inlineStr">
+    <row r="577">
+      <c r="A577" t="inlineStr">
         <is>
           <t xml:space="preserve">「どうして？　動物は絶滅する」
 لماذا؟ تنقرض الحيوانات
@@ -12565,19 +12544,19 @@
 2308 goodreads com </t>
         </is>
       </c>
-      <c r="B578" t="inlineStr">
+      <c r="B577" t="inlineStr">
         <is>
           <t>images/「どうして？　動物は絶滅する」_img1.jpg</t>
         </is>
       </c>
-      <c r="C578" t="inlineStr">
+      <c r="C577" t="inlineStr">
         <is>
           <t>動物 ,子供用</t>
         </is>
       </c>
     </row>
-    <row r="579">
-      <c r="A579" t="inlineStr">
+    <row r="578">
+      <c r="A578" t="inlineStr">
         <is>
           <t xml:space="preserve">「私たちは異なる。だから調和する」
 نختلف.. لنأتلف
@@ -12587,19 +12566,19 @@
 2103 Nawal Saed </t>
         </is>
       </c>
-      <c r="B579" t="inlineStr">
+      <c r="B578" t="inlineStr">
         <is>
           <t>images/「私たちは異なる。だから調和する」_img1.jpg</t>
         </is>
       </c>
-      <c r="C579" t="inlineStr">
+      <c r="C578" t="inlineStr">
         <is>
           <t>異符号 ,ハーモニー</t>
         </is>
       </c>
     </row>
-    <row r="580">
-      <c r="A580" t="inlineStr">
+    <row r="579">
+      <c r="A579" t="inlineStr">
         <is>
           <t xml:space="preserve">「私の肺には蝶々が住んでいて、呼吸の度に羽ばたく」
 تسكن رئتيّ فراشة ترفرف كلما أتنفس
@@ -12608,19 +12587,19 @@
 2109 出典不明 </t>
         </is>
       </c>
-      <c r="B580" t="inlineStr">
+      <c r="B579" t="inlineStr">
         <is>
           <t>images/「私の肺には蝶々が住んでいて、呼吸の度_img1.jpg</t>
         </is>
       </c>
-      <c r="C580" t="inlineStr">
+      <c r="C579" t="inlineStr">
         <is>
           <t>人体 ,昆虫</t>
         </is>
       </c>
     </row>
-    <row r="581">
-      <c r="A581" t="inlineStr">
+    <row r="580">
+      <c r="A580" t="inlineStr">
         <is>
           <t xml:space="preserve">「安らぎを感じますか？」
 هل تستشعر السكينة؟
@@ -12629,19 +12608,19 @@
 2404 https://twitter.com/NatGeoMagArab/status/1541421154950209536 </t>
         </is>
       </c>
-      <c r="B581" t="inlineStr">
+      <c r="B580" t="inlineStr">
         <is>
           <t>images/「安らぎを感じますか？」_img1.jpg</t>
         </is>
       </c>
-      <c r="C581" t="inlineStr">
+      <c r="C580" t="inlineStr">
         <is>
           <t>手書き語学 ,アラビア語 ,エイ</t>
         </is>
       </c>
     </row>
-    <row r="582">
-      <c r="A582" t="inlineStr">
+    <row r="581">
+      <c r="A581" t="inlineStr">
         <is>
           <t xml:space="preserve">「たとえあなたの使うブラウザがChromeだろうとSafariだろうと」
 سواء كنت تستخدم متصفح كروم أو سفاري
@@ -12649,19 +12628,19 @@
 2308 https://twitter.com/ShaayTech/status/1536235333972635649 </t>
         </is>
       </c>
-      <c r="B582" t="inlineStr">
+      <c r="B581" t="inlineStr">
         <is>
           <t>images/「たとえあなたの使うブラウザがChro_img1.jpg</t>
         </is>
       </c>
-      <c r="C582" t="inlineStr">
+      <c r="C581" t="inlineStr">
         <is>
           <t xml:space="preserve">手書き語学 ,アラビア語 ,iPhone </t>
         </is>
       </c>
     </row>
-    <row r="583">
-      <c r="A583" t="inlineStr">
+    <row r="582">
+      <c r="A582" t="inlineStr">
         <is>
           <t xml:space="preserve">「このミドリモリヤツガシラは気づいて欲しい」
 يحرص "هدهد الخشب الأخضر" هذا على أن يدرك
@@ -12670,19 +12649,19 @@
 2308 https://twitter.com/NatGeoMagArab/status/1531161022928539648 </t>
         </is>
       </c>
-      <c r="B583" t="inlineStr">
+      <c r="B582" t="inlineStr">
         <is>
           <t>images/「このミドリモリヤツガシラは気づいて欲_img1.jpg</t>
         </is>
       </c>
-      <c r="C583" t="inlineStr">
+      <c r="C582" t="inlineStr">
         <is>
           <t xml:space="preserve">手書き語学 ,アラビア語 ,鳥 </t>
         </is>
       </c>
     </row>
-    <row r="584">
-      <c r="A584" t="inlineStr">
+    <row r="583">
+      <c r="A583" t="inlineStr">
         <is>
           <t xml:space="preserve">「あなたの怖いものは何ですか」
 ماهي مخاوفك؟
@@ -12694,15 +12673,15 @@
 2308 1112kok </t>
         </is>
       </c>
-      <c r="B584" t="inlineStr">
+      <c r="B583" t="inlineStr">
         <is>
           <t>images/「あなたの怖いものは何ですか」_img1.jpg</t>
         </is>
       </c>
-      <c r="C584" t="inlineStr"/>
-    </row>
-    <row r="585">
-      <c r="A585" t="inlineStr">
+      <c r="C583" t="inlineStr"/>
+    </row>
+    <row r="584">
+      <c r="A584" t="inlineStr">
         <is>
           <t xml:space="preserve">「美しい時は作るもの。待つものではない」
 اصنع اللحظات الجميلة. لا تنتظرها
@@ -12711,19 +12690,19 @@
 2308 abojamal.tumblr com </t>
         </is>
       </c>
-      <c r="B585" t="inlineStr">
+      <c r="B584" t="inlineStr">
         <is>
           <t>images/「美しい時は作るもの。待つものではない_img1.jpg</t>
         </is>
       </c>
-      <c r="C585" t="inlineStr">
+      <c r="C584" t="inlineStr">
         <is>
           <t>おうち時間</t>
         </is>
       </c>
     </row>
-    <row r="586">
-      <c r="A586" t="inlineStr">
+    <row r="585">
+      <c r="A585" t="inlineStr">
         <is>
           <t xml:space="preserve">「大切な時間を大切じゃないことに使わないこと」
 لا تضيع الوقت المهم في شيء غير مهم
@@ -12732,19 +12711,19 @@
 2308 Anwar_122_ </t>
         </is>
       </c>
-      <c r="B586" t="inlineStr">
+      <c r="B585" t="inlineStr">
         <is>
           <t>images/「大切な時間を大切じゃないことに使わな_img1.jpg</t>
         </is>
       </c>
-      <c r="C586" t="inlineStr">
+      <c r="C585" t="inlineStr">
         <is>
           <t>時間 ,貴重</t>
         </is>
       </c>
     </row>
-    <row r="587">
-      <c r="A587" t="inlineStr">
+    <row r="586">
+      <c r="A586" t="inlineStr">
         <is>
           <t xml:space="preserve">「このイノセントな目に騙されるな…」
 لا تنخدع بهذه العيون البريئة
@@ -12754,19 +12733,19 @@
 2201 https://twitter.com/NatGeoMagArab/status/1475715760202797056 </t>
         </is>
       </c>
-      <c r="B587" t="inlineStr">
+      <c r="B586" t="inlineStr">
         <is>
           <t>images/「このイノセントな目に騙されるな…」.png</t>
         </is>
       </c>
-      <c r="C587" t="inlineStr">
+      <c r="C586" t="inlineStr">
         <is>
           <t>がうがう ,カワイイ</t>
         </is>
       </c>
     </row>
-    <row r="588">
-      <c r="A588" t="inlineStr">
+    <row r="587">
+      <c r="A587" t="inlineStr">
         <is>
           <t xml:space="preserve">⁦「カメラを止めろ！」⁩
 أوقفوا التّصوير
@@ -12776,19 +12755,19 @@
 2509 alsalwabooks com </t>
         </is>
       </c>
-      <c r="B588" t="inlineStr">
+      <c r="B587" t="inlineStr">
         <is>
           <t>images/⁦「カメラを止めろ！」⁩_img1.jpg</t>
         </is>
       </c>
-      <c r="C588" t="inlineStr">
+      <c r="C587" t="inlineStr">
         <is>
           <t>絵本 ,撮影</t>
         </is>
       </c>
     </row>
-    <row r="589">
-      <c r="A589" t="inlineStr">
+    <row r="588">
+      <c r="A588" t="inlineStr">
         <is>
           <t xml:space="preserve">「話す前に考えなさい」
 فكر قبل ان تتكلم
@@ -12798,19 +12777,19 @@
 2308 Islamuna YouTube </t>
         </is>
       </c>
-      <c r="B589" t="inlineStr">
+      <c r="B588" t="inlineStr">
         <is>
           <t>images/「話す前に考えなさい」_img1.jpg</t>
         </is>
       </c>
-      <c r="C589" t="inlineStr">
+      <c r="C588" t="inlineStr">
         <is>
           <t>失言 ,発言</t>
         </is>
       </c>
     </row>
-    <row r="590">
-      <c r="A590" t="inlineStr">
+    <row r="589">
+      <c r="A589" t="inlineStr">
         <is>
           <t xml:space="preserve">「ツイッターでフォローして下さい」
 تابعونا على تويتر
@@ -12820,19 +12799,19 @@
 2109 出典不明 </t>
         </is>
       </c>
-      <c r="B590" t="inlineStr">
+      <c r="B589" t="inlineStr">
         <is>
           <t>images/「ツイッターでフォローして下さい」_img1.jpg</t>
         </is>
       </c>
-      <c r="C590" t="inlineStr">
+      <c r="C589" t="inlineStr">
         <is>
           <t>FollowUs ,バナー</t>
         </is>
       </c>
     </row>
-    <row r="591">
-      <c r="A591" t="inlineStr">
+    <row r="590">
+      <c r="A590" t="inlineStr">
         <is>
           <t xml:space="preserve">「敵を倒せ」دمّر العدو
 ダンミリ_ルアドゥーウ [dammiri l-*aduuw]
@@ -12841,19 +12820,19 @@
 2308 apkpure com </t>
         </is>
       </c>
-      <c r="B591" t="inlineStr">
+      <c r="B590" t="inlineStr">
         <is>
           <t>images/「敵を倒せ」_img1.jpg</t>
         </is>
       </c>
-      <c r="C591" t="inlineStr">
+      <c r="C590" t="inlineStr">
         <is>
           <t>ゲーム ,パンダ</t>
         </is>
       </c>
     </row>
-    <row r="592">
-      <c r="A592" t="inlineStr">
+    <row r="591">
+      <c r="A591" t="inlineStr">
         <is>
           <t xml:space="preserve">「咲け。蒔かれたらどこであろうと」
 أزهر أيْنمَا زرعت
@@ -12862,19 +12841,19 @@
 2407 Ahmed Madyan </t>
         </is>
       </c>
-      <c r="B592" t="inlineStr">
+      <c r="B591" t="inlineStr">
         <is>
           <t>images/「咲け。蒔かれたらどこであろうと」_img1.jpg</t>
         </is>
       </c>
-      <c r="C592" t="inlineStr">
+      <c r="C591" t="inlineStr">
         <is>
           <t>環境のせいにしない ,花</t>
         </is>
       </c>
     </row>
-    <row r="593">
-      <c r="A593" t="inlineStr">
+    <row r="592">
+      <c r="A592" t="inlineStr">
         <is>
           <t xml:space="preserve">「頭を働かせろ」شغل مخك
 シャッギル・ムッハク [Sha^Ghil mu^Kha-k]
@@ -12883,19 +12862,19 @@
 2103 facebook elpage </t>
         </is>
       </c>
-      <c r="B593" t="inlineStr">
+      <c r="B592" t="inlineStr">
         <is>
           <t>images/「頭を働かせろ」_img1.jpg</t>
         </is>
       </c>
-      <c r="C593" t="inlineStr">
+      <c r="C592" t="inlineStr">
         <is>
           <t>電源 ,頭脳</t>
         </is>
       </c>
     </row>
-    <row r="594">
-      <c r="A594" t="inlineStr">
+    <row r="593">
+      <c r="A593" t="inlineStr">
         <is>
           <t xml:space="preserve">「傷跡は星にかえなさい」
 حوّل نُدوبكَ إلى نُجومْ
@@ -12905,19 +12884,19 @@
 2107 saramj1992 Instagram </t>
         </is>
       </c>
-      <c r="B594" t="inlineStr">
+      <c r="B593" t="inlineStr">
         <is>
           <t>images/「傷跡は星にかえなさい」_img1.jpg</t>
         </is>
       </c>
-      <c r="C594" t="inlineStr">
+      <c r="C593" t="inlineStr">
         <is>
           <t>勲章 ,証</t>
         </is>
       </c>
     </row>
-    <row r="595">
-      <c r="A595" t="inlineStr">
+    <row r="594">
+      <c r="A594" t="inlineStr">
         <is>
           <t xml:space="preserve">「あなたの主の栄光を誉め称え、また（御赦しを請え。本当にかれは、度々赦される御方である）」
 فسَبِّح بحمد ربك و
@@ -12926,19 +12905,19 @@
 2109 出典不明 </t>
         </is>
       </c>
-      <c r="B595" t="inlineStr">
+      <c r="B594" t="inlineStr">
         <is>
           <t>images/「あなたの主の栄光を誉め称え、また（御_img1.jpg</t>
         </is>
       </c>
-      <c r="C595" t="inlineStr">
+      <c r="C594" t="inlineStr">
         <is>
           <t>イスラム教 ,カリグラフィー</t>
         </is>
       </c>
     </row>
-    <row r="596">
-      <c r="A596" t="inlineStr">
+    <row r="595">
+      <c r="A595" t="inlineStr">
         <is>
           <t xml:space="preserve">「誰かを幸福にしなさい」
 أسْعِد أحدهم
@@ -12948,19 +12927,19 @@
 1810 in4sser.tumblr </t>
         </is>
       </c>
-      <c r="B596" t="inlineStr">
+      <c r="B595" t="inlineStr">
         <is>
           <t>images/「誰かを幸福にしなさい」_img1.jpg</t>
         </is>
       </c>
-      <c r="C596" t="inlineStr">
+      <c r="C595" t="inlineStr">
         <is>
           <t>人生 ,happy</t>
         </is>
       </c>
     </row>
-    <row r="597">
-      <c r="A597" t="inlineStr">
+    <row r="596">
+      <c r="A596" t="inlineStr">
         <is>
           <t xml:space="preserve">「見よ」أبْصِرْ
 アブスィル ['ab_sir]
@@ -12969,19 +12948,19 @@
 1811 Ruh Al-Alam, via Behance </t>
         </is>
       </c>
-      <c r="B597" t="inlineStr">
+      <c r="B596" t="inlineStr">
         <is>
           <t>images/「見よ」_img1.jpg</t>
         </is>
       </c>
-      <c r="C597" t="inlineStr">
+      <c r="C596" t="inlineStr">
         <is>
           <t>目 ,瞳</t>
         </is>
       </c>
     </row>
-    <row r="598">
-      <c r="A598" t="inlineStr">
+    <row r="597">
+      <c r="A597" t="inlineStr">
         <is>
           <t xml:space="preserve">「言葉は口から出す前に味わいなさい」
 ‪تذوق كلماتك قبل أن تنطقها‬
@@ -12991,19 +12970,19 @@
 2109 Reham-des </t>
         </is>
       </c>
-      <c r="B598" t="inlineStr">
+      <c r="B597" t="inlineStr">
         <is>
           <t>images/「言葉は口から出す前に味わいなさい」_img1.jpg</t>
         </is>
       </c>
-      <c r="C598" t="inlineStr">
+      <c r="C597" t="inlineStr">
         <is>
           <t>言葉</t>
         </is>
       </c>
     </row>
-    <row r="599">
-      <c r="A599" t="inlineStr">
+    <row r="598">
+      <c r="A598" t="inlineStr">
         <is>
           <t xml:space="preserve">「テレビを観るのをやめて下さい」
 توقفي عن مشاهدة التلفاز
@@ -13013,19 +12992,19 @@
 1809 </t>
         </is>
       </c>
-      <c r="B599" t="inlineStr">
+      <c r="B598" t="inlineStr">
         <is>
           <t>images/「テレビを観るのをやめて下さい」_img1.jpg</t>
         </is>
       </c>
-      <c r="C599" t="inlineStr">
+      <c r="C598" t="inlineStr">
         <is>
           <t>あらびあや</t>
         </is>
       </c>
     </row>
-    <row r="600">
-      <c r="A600" t="inlineStr">
+    <row r="599">
+      <c r="A599" t="inlineStr">
         <is>
           <t xml:space="preserve">「言わぬが花」
 انْطِقْ جَمَالاً أو تجَمَّلْ بالسّكُوت
@@ -13035,19 +13014,19 @@
 2411 Ahmed Madyan </t>
         </is>
       </c>
-      <c r="B600" t="inlineStr">
+      <c r="B599" t="inlineStr">
         <is>
           <t>images/「言わぬが花」_img1.jpg</t>
         </is>
       </c>
-      <c r="C600" t="inlineStr">
+      <c r="C599" t="inlineStr">
         <is>
           <t>ことわざ ,デザイン</t>
         </is>
       </c>
     </row>
-    <row r="601">
-      <c r="A601" t="inlineStr">
+    <row r="600">
+      <c r="A600" t="inlineStr">
         <is>
           <t xml:space="preserve">「たくさん考えて、少し話すこと」
 فكّر كثيرا. تكلم قليلا
@@ -13057,19 +13036,19 @@
 2105 In49r </t>
         </is>
       </c>
-      <c r="B601" t="inlineStr">
+      <c r="B600" t="inlineStr">
         <is>
           <t>images/「たくさん考えて、少し話すこと」_img1.jpg</t>
         </is>
       </c>
-      <c r="C601" t="inlineStr">
+      <c r="C600" t="inlineStr">
         <is>
           <t>思慮 ,会話</t>
         </is>
       </c>
     </row>
-    <row r="602">
-      <c r="A602" t="inlineStr">
+    <row r="601">
+      <c r="A601" t="inlineStr">
         <is>
           <t xml:space="preserve">「子供たちよ、いつでも思い出すんだよ」
 تذكروا دوما يا أطفال
@@ -13079,19 +13058,19 @@
 1809 </t>
         </is>
       </c>
-      <c r="B602" t="inlineStr">
+      <c r="B601" t="inlineStr">
         <is>
           <t>images/「子供たちよ、いつでも思い出すんだよ」_img1.jpg</t>
         </is>
       </c>
-      <c r="C602" t="inlineStr">
+      <c r="C601" t="inlineStr">
         <is>
           <t>オープニング ,ハム太郎</t>
         </is>
       </c>
     </row>
-    <row r="603">
-      <c r="A603" t="inlineStr">
+    <row r="602">
+      <c r="A602" t="inlineStr">
         <is>
           <t xml:space="preserve">「分かってから話しなさい」
 تعلَّم ثمَّ تكلَّم
@@ -13101,19 +13080,19 @@
 1903 Hashem Al Shareef, Pinterest </t>
         </is>
       </c>
-      <c r="B603" t="inlineStr">
+      <c r="B602" t="inlineStr">
         <is>
           <t>images/「分かってから話しなさい」_img1.jpg</t>
         </is>
       </c>
-      <c r="C603" t="inlineStr">
+      <c r="C602" t="inlineStr">
         <is>
           <t>教訓 ,トーク</t>
         </is>
       </c>
     </row>
-    <row r="604">
-      <c r="A604" t="inlineStr">
+    <row r="603">
+      <c r="A603" t="inlineStr">
         <is>
           <t xml:space="preserve">「蟻に学べ」تعلم من النملة
 タアッラム・ミナ_ンナムラ [ta*allam mina ^namla]
@@ -13122,19 +13101,19 @@
 2308 fatakat com </t>
         </is>
       </c>
-      <c r="B604" t="inlineStr">
+      <c r="B603" t="inlineStr">
         <is>
           <t>images/「蟻に学べ」_img1.jpg</t>
         </is>
       </c>
-      <c r="C604" t="inlineStr">
+      <c r="C603" t="inlineStr">
         <is>
           <t>教訓 ,問題解決</t>
         </is>
       </c>
     </row>
-    <row r="605">
-      <c r="A605" t="inlineStr">
+    <row r="604">
+      <c r="A604" t="inlineStr">
         <is>
           <t xml:space="preserve">「自分と仲直りしよう、一杯の珈琲で！」
 تصالح مع نفسك بكوب قهوة
@@ -13144,19 +13123,19 @@
 2308 asm95_ </t>
         </is>
       </c>
-      <c r="B605" t="inlineStr">
+      <c r="B604" t="inlineStr">
         <is>
           <t>images/「自分と仲直りしよう、一杯の珈琲で！」_img1.jpg</t>
         </is>
       </c>
-      <c r="C605" t="inlineStr">
+      <c r="C604" t="inlineStr">
         <is>
           <t>一服 ,リラックス</t>
         </is>
       </c>
     </row>
-    <row r="606">
-      <c r="A606" t="inlineStr">
+    <row r="605">
+      <c r="A605" t="inlineStr">
         <is>
           <t xml:space="preserve">「気をつけて　ジュード」
 انتبهي يا جود
@@ -13166,19 +13145,19 @@
 2109 سلسلة الحلزونة </t>
         </is>
       </c>
-      <c r="B606" t="inlineStr">
+      <c r="B605" t="inlineStr">
         <is>
           <t>images/「気をつけて　ジュード」_img1.jpg</t>
         </is>
       </c>
-      <c r="C606" t="inlineStr">
+      <c r="C605" t="inlineStr">
         <is>
           <t>絵本 ,わんぱく</t>
         </is>
       </c>
     </row>
-    <row r="607">
-      <c r="A607" t="inlineStr">
+    <row r="606">
+      <c r="A606" t="inlineStr">
         <is>
           <t xml:space="preserve">「coming soon」
 انتظرونا قريبا
@@ -13187,19 +13166,19 @@
 2307 出典不明 </t>
         </is>
       </c>
-      <c r="B607" t="inlineStr">
+      <c r="B606" t="inlineStr">
         <is>
           <t>images/「coming soon」_img1.jpg</t>
         </is>
       </c>
-      <c r="C607" t="inlineStr">
+      <c r="C606" t="inlineStr">
         <is>
           <t>フレーズ ,カミングスーン</t>
         </is>
       </c>
     </row>
-    <row r="608">
-      <c r="A608" t="inlineStr">
+    <row r="607">
+      <c r="A607" t="inlineStr">
         <is>
           <t xml:space="preserve">「自分の胸に聞きなさい。それが全て知っています」
 استمع لقلبك.. إنه يعرف كل شيء
@@ -13208,19 +13187,19 @@
 1811 </t>
         </is>
       </c>
-      <c r="B608" t="inlineStr">
+      <c r="B607" t="inlineStr">
         <is>
           <t>images/「自分の胸に聞きなさい。それが全て知っ_img1.jpg</t>
         </is>
       </c>
-      <c r="C608" t="inlineStr">
+      <c r="C607" t="inlineStr">
         <is>
           <t>あらびあや</t>
         </is>
       </c>
     </row>
-    <row r="609">
-      <c r="A609" t="inlineStr">
+    <row r="608">
+      <c r="A608" t="inlineStr">
         <is>
           <t xml:space="preserve">「笑ってくれ、絶望を癒すのは君の笑みだから」
 ابتسمي فإن دواء اليأس بسمتك
@@ -13229,19 +13208,19 @@
 2308 arab-quotes tumblr </t>
         </is>
       </c>
-      <c r="B609" t="inlineStr">
+      <c r="B608" t="inlineStr">
         <is>
           <t>images/「笑ってくれ、絶望を癒すのは君の笑みだ_img1.jpg</t>
         </is>
       </c>
-      <c r="C609" t="inlineStr">
+      <c r="C608" t="inlineStr">
         <is>
           <t>癒し ,スマイル</t>
         </is>
       </c>
     </row>
-    <row r="610">
-      <c r="A610" t="inlineStr">
+    <row r="609">
+      <c r="A609" t="inlineStr">
         <is>
           <t xml:space="preserve">「自分を頼りなさい。宇宙で最も確かな物が自分だと思って。」
 استند على نفسك وكأنك أكثر الأشياء ثباتًا بهذا الكون
@@ -13249,19 +13228,19 @@
 2308 x_nourh.15 </t>
         </is>
       </c>
-      <c r="B610" t="inlineStr">
+      <c r="B609" t="inlineStr">
         <is>
           <t>images/「自分を頼りなさい。宇宙で最も確かな物_img1.jpg</t>
         </is>
       </c>
-      <c r="C610" t="inlineStr">
+      <c r="C609" t="inlineStr">
         <is>
           <t>自我 ,宇宙</t>
         </is>
       </c>
     </row>
-    <row r="611">
-      <c r="A611" t="inlineStr">
+    <row r="610">
+      <c r="A610" t="inlineStr">
         <is>
           <t xml:space="preserve">「古いデバイスを交換して新品をゲットしよう」
 استبدل جهازك القديم واحصل على واحد جديد
@@ -13270,19 +13249,19 @@
 2406 stc </t>
         </is>
       </c>
-      <c r="B611" t="inlineStr">
+      <c r="B610" t="inlineStr">
         <is>
           <t>images/「古いデバイスを交換して新品をゲットし_img1.jpg</t>
         </is>
       </c>
-      <c r="C611" t="inlineStr">
+      <c r="C610" t="inlineStr">
         <is>
           <t>キャンペーン ,下取り</t>
         </is>
       </c>
     </row>
-    <row r="612">
-      <c r="A612" t="inlineStr">
+    <row r="611">
+      <c r="A611" t="inlineStr">
         <is>
           <t xml:space="preserve">「あなたの声を聞かせてください。私の心を彩ってください」
 هات صوتك، لوّن قلبي
@@ -13291,19 +13270,19 @@
 2105 3a2esha_ Instagram </t>
         </is>
       </c>
-      <c r="B612" t="inlineStr">
+      <c r="B611" t="inlineStr">
         <is>
           <t>images/「あなたの声を聞かせてください。私の心_img1.jpg</t>
         </is>
       </c>
-      <c r="C612" t="inlineStr">
+      <c r="C611" t="inlineStr">
         <is>
           <t>電話 ,肉声</t>
         </is>
       </c>
     </row>
-    <row r="613">
-      <c r="A613" t="inlineStr">
+    <row r="612">
+      <c r="A612" t="inlineStr">
         <is>
           <t xml:space="preserve">「この子カンガルーは抱っこが好き」
 يُحب صغير الكنغر هذا أن يؤخذ في الأحضان
@@ -13311,19 +13290,19 @@
 2308 NatGeoMagArab </t>
         </is>
       </c>
-      <c r="B613" t="inlineStr">
+      <c r="B612" t="inlineStr">
         <is>
           <t>images/「この子カンガルーは抱っこが好き」.png</t>
         </is>
       </c>
-      <c r="C613" t="inlineStr">
+      <c r="C612" t="inlineStr">
         <is>
           <t>カンガルー ,人肌</t>
         </is>
       </c>
     </row>
-    <row r="614">
-      <c r="A614" t="inlineStr">
+    <row r="613">
+      <c r="A613" t="inlineStr">
         <is>
           <t xml:space="preserve">「カタールが好き」أحب قطر
 ウヒッブ・カタル ['u-Hibb qa_tar]
@@ -13332,19 +13311,19 @@
 1810 出典不明 </t>
         </is>
       </c>
-      <c r="B614" t="inlineStr">
+      <c r="B613" t="inlineStr">
         <is>
           <t>images/「カタールが好き」_img1.jpg</t>
         </is>
       </c>
-      <c r="C614" t="inlineStr">
+      <c r="C613" t="inlineStr">
         <is>
           <t>カタール</t>
         </is>
       </c>
     </row>
-    <row r="615">
-      <c r="A615" t="inlineStr">
+    <row r="614">
+      <c r="A614" t="inlineStr">
         <is>
           <t xml:space="preserve">「一緒に読むのが好き」
 أُحبُّ أن نَقْرَأَ مَعاً
@@ -13354,19 +13333,19 @@
 2509 www.neelwafurat com,  id=lbb212750-185765 </t>
         </is>
       </c>
-      <c r="B615" t="inlineStr">
+      <c r="B614" t="inlineStr">
         <is>
           <t>images/「一緒に読むのが好き」_img1.jpg</t>
         </is>
       </c>
-      <c r="C615" t="inlineStr">
+      <c r="C614" t="inlineStr">
         <is>
           <t>好き ,本</t>
         </is>
       </c>
     </row>
-    <row r="616">
-      <c r="A616" t="inlineStr">
+    <row r="615">
+      <c r="A615" t="inlineStr">
         <is>
           <t xml:space="preserve">「病院に行きたくない」
 لا أريد أن أذهب إلى المشفى
@@ -13376,19 +13355,19 @@
 2508 Tony Ross https://education.hachette-antoine.com/ar/component/%D9%84%D8%A7-%D8%A3%D8%B1%D9%8A%D8%AF-%D8%A3%D9%86-%D8%A3%D8%B0%D9%87%D8%A8-%D8%A5%D9%84%D9%89-%D8%A7%D9%84%D9%85%D8%B4%D9%81%D9%89/ </t>
         </is>
       </c>
-      <c r="B616" t="inlineStr">
+      <c r="B615" t="inlineStr">
         <is>
           <t>images/「病院に行きたくない」_img1.jpg</t>
         </is>
       </c>
-      <c r="C616" t="inlineStr">
+      <c r="C615" t="inlineStr">
         <is>
           <t>絵本 ,子供</t>
         </is>
       </c>
     </row>
-    <row r="617">
-      <c r="A617" t="inlineStr">
+    <row r="616">
+      <c r="A616" t="inlineStr">
         <is>
           <t xml:space="preserve">「男性はいくら？」「女性はいくら？」
 كم يساوى الرجل؟ ..وكم تساوى المرأة؟
@@ -13397,19 +13376,19 @@
 2308 Pinterest, Masr Elmahrousa, Farah Noweir </t>
         </is>
       </c>
-      <c r="B617" t="inlineStr">
+      <c r="B616" t="inlineStr">
         <is>
           <t>images/「男性はいくら？」「女性はいくら？」_img1.jpg,images/「男性はいくら？」「女性はいくら？」_img2.jpg</t>
         </is>
       </c>
-      <c r="C617" t="inlineStr">
+      <c r="C616" t="inlineStr">
         <is>
           <t xml:space="preserve">全身コーデ ,相場 </t>
         </is>
       </c>
     </row>
-    <row r="618">
-      <c r="A618" t="inlineStr">
+    <row r="617">
+      <c r="A617" t="inlineStr">
         <is>
           <t xml:space="preserve">「黙ってもらえます？」
 ممكن تعيرنا سكوتك؟
@@ -13419,19 +13398,19 @@
 2308 Basel26 </t>
         </is>
       </c>
-      <c r="B618" t="inlineStr">
+      <c r="B617" t="inlineStr">
         <is>
           <t>images/「黙ってもらえます？」_img1.jpg</t>
         </is>
       </c>
-      <c r="C618" t="inlineStr">
+      <c r="C617" t="inlineStr">
         <is>
           <t>音量 ,ボリューム</t>
         </is>
       </c>
     </row>
-    <row r="619">
-      <c r="A619" t="inlineStr">
+    <row r="618">
+      <c r="A618" t="inlineStr">
         <is>
           <t xml:space="preserve">「眠りたいです」
 أُريدُ أَن أَنام
@@ -13441,19 +13420,19 @@
 2109 goodreads com </t>
         </is>
       </c>
-      <c r="B619" t="inlineStr">
+      <c r="B618" t="inlineStr">
         <is>
           <t>images/「眠りたいです」_img1.jpg</t>
         </is>
       </c>
-      <c r="C619" t="inlineStr">
+      <c r="C618" t="inlineStr">
         <is>
           <t>絵本</t>
         </is>
       </c>
     </row>
-    <row r="620">
-      <c r="A620" t="inlineStr">
+    <row r="619">
+      <c r="A619" t="inlineStr">
         <is>
           <t xml:space="preserve">「飛びたい！」أُريد أن أطير
 ウリードゥ・アン・アティール ['u-riidu 'an 'a-_tiir]
@@ -13462,19 +13441,19 @@
 2308 出典不明 </t>
         </is>
       </c>
-      <c r="B620" t="inlineStr">
+      <c r="B619" t="inlineStr">
         <is>
           <t>images/「飛びたい！」_img1.jpg</t>
         </is>
       </c>
-      <c r="C620" t="inlineStr">
+      <c r="C619" t="inlineStr">
         <is>
           <t>鳥 ,希望</t>
         </is>
       </c>
     </row>
-    <row r="621">
-      <c r="A621" t="inlineStr">
+    <row r="620">
+      <c r="A620" t="inlineStr">
         <is>
           <t xml:space="preserve">「うちゅうへとびたい」
 أُريدُ أَنْ أَطيرَ إلى الفَضاء
@@ -13483,19 +13462,19 @@
 2308 mybookshelf co </t>
         </is>
       </c>
-      <c r="B621" t="inlineStr">
+      <c r="B620" t="inlineStr">
         <is>
           <t>images/「うちゅうへとびたい」_img1.jpg</t>
         </is>
       </c>
-      <c r="C621" t="inlineStr">
+      <c r="C620" t="inlineStr">
         <is>
           <t>絵本 ,宇宙</t>
         </is>
       </c>
     </row>
-    <row r="622">
-      <c r="A622" t="inlineStr">
+    <row r="621">
+      <c r="A621" t="inlineStr">
         <is>
           <t xml:space="preserve">「とても愛しています」
 أُحِبّك جِدّاً
@@ -13505,19 +13484,19 @@
 2308 hobe cc </t>
         </is>
       </c>
-      <c r="B622" t="inlineStr">
+      <c r="B621" t="inlineStr">
         <is>
           <t>images/「とても愛しています」_img1.jpg</t>
         </is>
       </c>
-      <c r="C622" t="inlineStr">
+      <c r="C621" t="inlineStr">
         <is>
           <t>恋 ,love</t>
         </is>
       </c>
     </row>
-    <row r="623">
-      <c r="A623" t="inlineStr">
+    <row r="622">
+      <c r="A622" t="inlineStr">
         <is>
           <t xml:space="preserve">「あす日が昇るだろう。私は朝が大好きだ」
 غدا ستشرق الشمس وأحب الصباح كثيرا
@@ -13526,19 +13505,19 @@
 2105 warag-3nb.tumblr com </t>
         </is>
       </c>
-      <c r="B623" t="inlineStr">
+      <c r="B622" t="inlineStr">
         <is>
           <t>images/「あす日が昇るだろう。私は朝が大好きだ_img1.jpg,images/ 「あす日が昇るだろう。私は朝が大好きだ_img2.jpg</t>
         </is>
       </c>
-      <c r="C623" t="inlineStr">
+      <c r="C622" t="inlineStr">
         <is>
           <t>おやすみ ,壁</t>
         </is>
       </c>
     </row>
-    <row r="624">
-      <c r="A624" t="inlineStr">
+    <row r="623">
+      <c r="A623" t="inlineStr">
         <is>
           <t xml:space="preserve">「きみは何をえらぶ？」
 ماذا تختار؟
@@ -13548,19 +13527,19 @@
 2109 embadomjp org </t>
         </is>
       </c>
-      <c r="B624" t="inlineStr">
+      <c r="B623" t="inlineStr">
         <is>
           <t>images/「きみは何をえらぶ？」_img1.jpg</t>
         </is>
       </c>
-      <c r="C624" t="inlineStr">
+      <c r="C623" t="inlineStr">
         <is>
           <t>優柔不断 ,絵本</t>
         </is>
       </c>
     </row>
-    <row r="625">
-      <c r="A625" t="inlineStr">
+    <row r="624">
+      <c r="A624" t="inlineStr">
         <is>
           <t xml:space="preserve">「ちょっと静けさが必要な時もある」
 في بعض الأوقات نحتاج لشوية هدوء
@@ -13570,19 +13549,19 @@
 2308 IN49r </t>
         </is>
       </c>
-      <c r="B625" t="inlineStr">
+      <c r="B624" t="inlineStr">
         <is>
           <t>images/「ちょっと静けさが必要な時もある」_img1.jpg</t>
         </is>
       </c>
-      <c r="C625" t="inlineStr">
+      <c r="C624" t="inlineStr">
         <is>
           <t>ミュート ,精神</t>
         </is>
       </c>
     </row>
-    <row r="626">
-      <c r="A626" t="inlineStr">
+    <row r="625">
+      <c r="A625" t="inlineStr">
         <is>
           <t xml:space="preserve">「逃げるな。全力でぶつかれ」
 لا تهرب اصطدم بكل قوتك
@@ -13592,19 +13571,19 @@
 2308 https://risingvibes.tumblr.com/post/189545775129 </t>
         </is>
       </c>
-      <c r="B626" t="inlineStr">
+      <c r="B625" t="inlineStr">
         <is>
           <t>images/「逃げるな。全力でぶつかれ」_img1.jpg</t>
         </is>
       </c>
-      <c r="C626" t="inlineStr">
+      <c r="C625" t="inlineStr">
         <is>
           <t>応援 ,力</t>
         </is>
       </c>
     </row>
-    <row r="627">
-      <c r="A627" t="inlineStr">
+    <row r="626">
+      <c r="A626" t="inlineStr">
         <is>
           <t xml:space="preserve">「着るのだいすき」
 أُحِبُ أَن أَرتَدِيَ
@@ -13614,19 +13593,19 @@
 2308 https://kitab.firmabikes.ru/epub-_hb_n_rtdy_5187.html </t>
         </is>
       </c>
-      <c r="B627" t="inlineStr">
+      <c r="B626" t="inlineStr">
         <is>
           <t>images/「着るのだいすき」_img1.jpg</t>
         </is>
       </c>
-      <c r="C627" t="inlineStr">
+      <c r="C626" t="inlineStr">
         <is>
           <t xml:space="preserve">絵本 ,ファッション </t>
         </is>
       </c>
     </row>
-    <row r="628">
-      <c r="A628" t="inlineStr">
+    <row r="627">
+      <c r="A627" t="inlineStr">
         <is>
           <t xml:space="preserve">「車のバッテリーが要る！」
 نحتاج بطارية سيارة
@@ -13636,19 +13615,19 @@
 2308 instagram roaa_27 </t>
         </is>
       </c>
-      <c r="B628" t="inlineStr">
+      <c r="B627" t="inlineStr">
         <is>
           <t>images/「車のバッテリーが要る！」_img1.jpg</t>
         </is>
       </c>
-      <c r="C628" t="inlineStr">
+      <c r="C627" t="inlineStr">
         <is>
           <t>スマホ ,充電</t>
         </is>
       </c>
     </row>
-    <row r="629">
-      <c r="A629" t="inlineStr">
+    <row r="628">
+      <c r="A628" t="inlineStr">
         <is>
           <t xml:space="preserve">「今日は幸せでいることにしました」
 اخترت أن أكون سعيدا اليوم
@@ -13658,19 +13637,19 @@
 2109 awaasha tumblr </t>
         </is>
       </c>
-      <c r="B629" t="inlineStr">
+      <c r="B628" t="inlineStr">
         <is>
           <t>images/「今日は幸せでいることにしました」_img1.jpg</t>
         </is>
       </c>
-      <c r="C629" t="inlineStr">
+      <c r="C628" t="inlineStr">
         <is>
           <t>心構え ,happy</t>
         </is>
       </c>
     </row>
-    <row r="630">
-      <c r="A630" t="inlineStr">
+    <row r="629">
+      <c r="A629" t="inlineStr">
         <is>
           <t xml:space="preserve">「理想的なスイカの選び方」
 كيف تختار البطيخة المُثلى؟
@@ -13680,19 +13659,19 @@
 2308 bit ly/octmel </t>
         </is>
       </c>
-      <c r="B630" t="inlineStr">
+      <c r="B629" t="inlineStr">
         <is>
           <t>images/「理想的なスイカの選び方」_img1.jpg</t>
         </is>
       </c>
-      <c r="C630" t="inlineStr">
+      <c r="C629" t="inlineStr">
         <is>
           <t>八百屋 ,西瓜</t>
         </is>
       </c>
     </row>
-    <row r="631">
-      <c r="A631" t="inlineStr">
+    <row r="630">
+      <c r="A630" t="inlineStr">
         <is>
           <t xml:space="preserve">「お問い合わせください」
 اتصل بنا
@@ -13702,19 +13681,19 @@
 2308 mtawir.blogspot com </t>
         </is>
       </c>
-      <c r="B631" t="inlineStr">
+      <c r="B630" t="inlineStr">
         <is>
           <t>images/「お問い合わせください」_img1.jpg</t>
         </is>
       </c>
-      <c r="C631" t="inlineStr">
+      <c r="C630" t="inlineStr">
         <is>
           <t>広告 ,電話</t>
         </is>
       </c>
     </row>
-    <row r="632">
-      <c r="A632" t="inlineStr">
+    <row r="631">
+      <c r="A631" t="inlineStr">
         <is>
           <t xml:space="preserve">「両方の動物が海岸の火山岩の亀裂の中に定住している」
 يحتل كلا الحيوانين شقوقًا في صخور الساحل البركانية
@@ -13722,19 +13701,19 @@
 2507 https://x.com/NatGeoMagArab/status/1925167200056521151 </t>
         </is>
       </c>
-      <c r="B632" t="inlineStr">
+      <c r="B631" t="inlineStr">
         <is>
           <t>images/「両方の動物が海岸の火山岩の亀裂の中に_img1.jpg,images/「両方の動物が海岸の火山岩の亀裂の中に_img2.jpg</t>
         </is>
       </c>
-      <c r="C632" t="inlineStr">
+      <c r="C631" t="inlineStr">
         <is>
           <t>手書き語学 ,アラビア語 ,イグアナ</t>
         </is>
       </c>
     </row>
-    <row r="633">
-      <c r="A633" t="inlineStr">
+    <row r="632">
+      <c r="A632" t="inlineStr">
         <is>
           <t xml:space="preserve">「命じられたように正しき道を辿れ」
 واستقم كما أمرت
@@ -13744,19 +13723,19 @@
 2308 Ahmed Madyan </t>
         </is>
       </c>
-      <c r="B633" t="inlineStr">
+      <c r="B632" t="inlineStr">
         <is>
           <t>images/「命じられたように正しき道を辿れ」_img1.jpg</t>
         </is>
       </c>
-      <c r="C633" t="inlineStr">
+      <c r="C632" t="inlineStr">
         <is>
           <t>書道 ,アート</t>
         </is>
       </c>
     </row>
-    <row r="634">
-      <c r="A634" t="inlineStr">
+    <row r="633">
+      <c r="A633" t="inlineStr">
         <is>
           <t xml:space="preserve">「くつろぎなさい」استكن
 イスタキンナ [istakinna]
@@ -13764,19 +13743,19 @@
 2603 m2ff tumblr com </t>
         </is>
       </c>
-      <c r="B634" t="inlineStr">
+      <c r="B633" t="inlineStr">
         <is>
           <t>images/「くつろぎなさい」.jpeg</t>
         </is>
       </c>
-      <c r="C634" t="inlineStr">
+      <c r="C633" t="inlineStr">
         <is>
           <t>relax ,コーヒー</t>
         </is>
       </c>
     </row>
-    <row r="635">
-      <c r="A635" t="inlineStr">
+    <row r="634">
+      <c r="A634" t="inlineStr">
         <is>
           <t xml:space="preserve">「彼は応えるだろう」سيستجيب 
 サヤスタジーブ [sa-ya-stajiibu]
@@ -13785,19 +13764,19 @@
 1811 kareem mrghani </t>
         </is>
       </c>
-      <c r="B635" t="inlineStr">
+      <c r="B634" t="inlineStr">
         <is>
           <t>images/「彼は応えるだろう」_img1.jpg</t>
         </is>
       </c>
-      <c r="C635" t="inlineStr">
+      <c r="C634" t="inlineStr">
         <is>
           <t>縦書き ,現代アート</t>
         </is>
       </c>
     </row>
-    <row r="636">
-      <c r="A636" t="inlineStr">
+    <row r="635">
+      <c r="A635" t="inlineStr">
         <is>
           <t xml:space="preserve">「アラビア語が好き」
 أنا أُحبّ لُغتي
@@ -13807,19 +13786,19 @@
 2308 出典不明 </t>
         </is>
       </c>
-      <c r="B636" t="inlineStr">
+      <c r="B635" t="inlineStr">
         <is>
           <t>images/「アラビア語が好き」_img1.jpg</t>
         </is>
       </c>
-      <c r="C636" t="inlineStr">
+      <c r="C635" t="inlineStr">
         <is>
           <t>和訳 ,こども</t>
         </is>
       </c>
     </row>
-    <row r="637">
-      <c r="A637" t="inlineStr">
+    <row r="636">
+      <c r="A636" t="inlineStr">
         <is>
           <t xml:space="preserve">「私はサッカーが好きです」
 أنا أُحِبُّ كُرةَ القَدَم
@@ -13829,19 +13808,19 @@
 2109 Arabic With Nadia </t>
         </is>
       </c>
-      <c r="B637" t="inlineStr">
+      <c r="B636" t="inlineStr">
         <is>
           <t>images/「私はサッカーが好きです」_img1.jpg</t>
         </is>
       </c>
-      <c r="C637" t="inlineStr">
+      <c r="C636" t="inlineStr">
         <is>
           <t>自由時間 ,例文</t>
         </is>
       </c>
     </row>
-    <row r="638">
-      <c r="A638" t="inlineStr">
+    <row r="637">
+      <c r="A637" t="inlineStr">
         <is>
           <t xml:space="preserve">「これ、私の眼鏡じゃありません」
 هٰذِهِ لَيْسَتْ نَظَّارَاتِي
@@ -13851,19 +13830,19 @@
 2509 </t>
         </is>
       </c>
-      <c r="B638" t="inlineStr">
+      <c r="B637" t="inlineStr">
         <is>
           <t>images/「これ、私の眼鏡じゃありません」_img1.jpg</t>
         </is>
       </c>
-      <c r="C638" t="inlineStr">
+      <c r="C637" t="inlineStr">
         <is>
           <t>あらびあや</t>
         </is>
       </c>
     </row>
-    <row r="639">
-      <c r="A639" t="inlineStr">
+    <row r="638">
+      <c r="A638" t="inlineStr">
         <is>
           <t xml:space="preserve">「我らも米を食います」
 نحن أيضاً نأكل الأرز
@@ -13873,19 +13852,19 @@
 1809 </t>
         </is>
       </c>
-      <c r="B639" t="inlineStr">
+      <c r="B638" t="inlineStr">
         <is>
           <t>images/「我らも米を食います」_img1.jpg</t>
         </is>
       </c>
-      <c r="C639" t="inlineStr">
+      <c r="C638" t="inlineStr">
         <is>
           <t>あらびあや</t>
         </is>
       </c>
     </row>
-    <row r="640">
-      <c r="A640" t="inlineStr">
+    <row r="639">
+      <c r="A639" t="inlineStr">
         <is>
           <t xml:space="preserve">「ひとりでできるもん！」
 أنا أستطيع أن أفعله وحدي
@@ -13894,19 +13873,19 @@
 2105 </t>
         </is>
       </c>
-      <c r="B640" t="inlineStr">
+      <c r="B639" t="inlineStr">
         <is>
           <t>images/「ひとりでできるもん！」_img1.jpg</t>
         </is>
       </c>
-      <c r="C640" t="inlineStr">
+      <c r="C639" t="inlineStr">
         <is>
           <t>あらびあや</t>
         </is>
       </c>
     </row>
-    <row r="641">
-      <c r="A641" t="inlineStr">
+    <row r="640">
+      <c r="A640" t="inlineStr">
         <is>
           <t xml:space="preserve">「恋しくないと言っている時は恋しい」
 أُريدُك حينَ أَقُولُ أَنا لا أُريدُك
@@ -13916,19 +13895,19 @@
 2308 DARWISHISM </t>
         </is>
       </c>
-      <c r="B641" t="inlineStr">
+      <c r="B640" t="inlineStr">
         <is>
           <t>images/「恋しくないと言っている時は恋しい」_img1.jpg</t>
         </is>
       </c>
-      <c r="C641" t="inlineStr">
+      <c r="C640" t="inlineStr">
         <is>
           <t>本音 ,恋愛</t>
         </is>
       </c>
     </row>
-    <row r="642">
-      <c r="A642" t="inlineStr">
+    <row r="641">
+      <c r="A641" t="inlineStr">
         <is>
           <t xml:space="preserve">「私は〜する」
 ⁦「着る」：( أنا ألبس )['ana 'a-lbas]⁩
@@ -13939,19 +13918,19 @@
 2109 RABIE </t>
         </is>
       </c>
-      <c r="B642" t="inlineStr">
+      <c r="B641" t="inlineStr">
         <is>
           <t>images/「私は〜する」_img1.jpg,images/「私は〜する」_img2.jpg,images/「私は〜する」_img3.jpg,images/「私は〜する」_img4.jpg</t>
         </is>
       </c>
-      <c r="C642" t="inlineStr">
+      <c r="C641" t="inlineStr">
         <is>
           <t>動詞 ,絵本</t>
         </is>
       </c>
     </row>
-    <row r="643">
-      <c r="A643" t="inlineStr">
+    <row r="642">
+      <c r="A642" t="inlineStr">
         <is>
           <t xml:space="preserve">「彼は完璧ではない。私は彼の欠点については目をつむった」
 هو ليس كامل. أنا أعميت نفسي عن سيئاته
@@ -13960,19 +13939,19 @@
 2308 _NOHA </t>
         </is>
       </c>
-      <c r="B643" t="inlineStr">
+      <c r="B642" t="inlineStr">
         <is>
           <t>images/「彼は完璧ではない。私は彼の欠点につい_img1.jpg</t>
         </is>
       </c>
-      <c r="C643" t="inlineStr">
+      <c r="C642" t="inlineStr">
         <is>
           <t>愛 ,寛容</t>
         </is>
       </c>
     </row>
-    <row r="644">
-      <c r="A644" t="inlineStr">
+    <row r="643">
+      <c r="A643" t="inlineStr">
         <is>
           <t xml:space="preserve">「この子トラは検疫期間中に生まれた」
 صغير النمر هذا ولد في زمن الحجر الصحي
@@ -13981,19 +13960,19 @@
 2310 https://www.akhbaralaan.net/?p=434924 </t>
         </is>
       </c>
-      <c r="B644" t="inlineStr">
+      <c r="B643" t="inlineStr">
         <is>
           <t>images/「この子トラは検疫期間中に生まれた」_img1.jpg</t>
         </is>
       </c>
-      <c r="C644" t="inlineStr">
+      <c r="C643" t="inlineStr">
         <is>
           <t>Covid ,メキシコ</t>
         </is>
       </c>
     </row>
-    <row r="645">
-      <c r="A645" t="inlineStr">
+    <row r="644">
+      <c r="A644" t="inlineStr">
         <is>
           <t xml:space="preserve">「睡眠の素晴らしさに匹敵するものは無い！」
 وجمال النوم ليس له مثيل
@@ -14002,19 +13981,19 @@
 2308 arabzy tumblr </t>
         </is>
       </c>
-      <c r="B645" t="inlineStr">
+      <c r="B644" t="inlineStr">
         <is>
           <t>images/「睡眠の素晴らしさに匹敵するものは無い_img1.jpg</t>
         </is>
       </c>
-      <c r="C645" t="inlineStr">
+      <c r="C644" t="inlineStr">
         <is>
           <t>オフトゥン ,おやすみ</t>
         </is>
       </c>
     </row>
-    <row r="646">
-      <c r="A646" t="inlineStr">
+    <row r="645">
+      <c r="A645" t="inlineStr">
         <is>
           <t xml:space="preserve">「大器晩成」
 الأشياء العظيمة تأخذ وقت
@@ -14024,19 +14003,19 @@
 2109 出典不明 </t>
         </is>
       </c>
-      <c r="B646" t="inlineStr">
+      <c r="B645" t="inlineStr">
         <is>
           <t>images/「大器晩成」_img1.jpg</t>
         </is>
       </c>
-      <c r="C646" t="inlineStr">
+      <c r="C645" t="inlineStr">
         <is>
           <t>ことわざ ,和訳</t>
         </is>
       </c>
     </row>
-    <row r="647">
-      <c r="A647" t="inlineStr">
+    <row r="646">
+      <c r="A646" t="inlineStr">
         <is>
           <t xml:space="preserve">「コーヒーは急には飲まれない」
 القهْوة لا تشرَب عَلى عَجلْ
@@ -14047,19 +14026,19 @@
 2012 Ahmed Madyan </t>
         </is>
       </c>
-      <c r="B647" t="inlineStr">
+      <c r="B646" t="inlineStr">
         <is>
           <t>images/「コーヒーは急には飲まれない」_img1.jpg</t>
         </is>
       </c>
-      <c r="C647" t="inlineStr">
+      <c r="C646" t="inlineStr">
         <is>
           <t>名言</t>
         </is>
       </c>
     </row>
-    <row r="648">
-      <c r="A648" t="inlineStr">
+    <row r="647">
+      <c r="A647" t="inlineStr">
         <is>
           <t xml:space="preserve">「成功者は情報共有している」
 الناجحون يشاركون المعلومة
@@ -14069,19 +14048,19 @@
 2109 出典不明 </t>
         </is>
       </c>
-      <c r="B648" t="inlineStr">
+      <c r="B647" t="inlineStr">
         <is>
           <t>images/「成功者は情報共有している」_img1.jpg</t>
         </is>
       </c>
-      <c r="C648" t="inlineStr">
+      <c r="C647" t="inlineStr">
         <is>
           <t>鳥 ,シェア</t>
         </is>
       </c>
     </row>
-    <row r="649">
-      <c r="A649" t="inlineStr">
+    <row r="648">
+      <c r="A648" t="inlineStr">
         <is>
           <t xml:space="preserve">「間違いで賢くなる、痛みで強くなる」
 الأخطاء تجعلك حكيمًا، والألم يجعلك قويًا
@@ -14090,19 +14069,19 @@
 2111 https://alaminin.blogspot.com/2020/03/blog-post_6.html </t>
         </is>
       </c>
-      <c r="B649" t="inlineStr">
+      <c r="B648" t="inlineStr">
         <is>
           <t>images/「間違いで賢くなる、痛みで強くなる」_img1.jpg</t>
         </is>
       </c>
-      <c r="C649" t="inlineStr">
+      <c r="C648" t="inlineStr">
         <is>
           <t>名言</t>
         </is>
       </c>
     </row>
-    <row r="650">
-      <c r="A650" t="inlineStr">
+    <row r="649">
+      <c r="A649" t="inlineStr">
         <is>
           <t xml:space="preserve">「何事も永遠には続かない」
 لا شيء يبقى للأبد
@@ -14112,19 +14091,19 @@
 2308 KiTeLetZ </t>
         </is>
       </c>
-      <c r="B650" t="inlineStr">
+      <c r="B649" t="inlineStr">
         <is>
           <t>images/「何事も永遠には続かない」_img1.jpg</t>
         </is>
       </c>
-      <c r="C650" t="inlineStr">
+      <c r="C649" t="inlineStr">
         <is>
           <t>変化 ,名言</t>
         </is>
       </c>
     </row>
-    <row r="651">
-      <c r="A651" t="inlineStr">
+    <row r="650">
+      <c r="A650" t="inlineStr">
         <is>
           <t xml:space="preserve">「惑星地球はあなた方を歓迎します」
 كوكب الارض يرحّب بكم
@@ -14134,19 +14113,19 @@
 1811 iN49R </t>
         </is>
       </c>
-      <c r="B651" t="inlineStr">
+      <c r="B650" t="inlineStr">
         <is>
           <t>images/「惑星地球はあなた方を歓迎します」_img1.jpg</t>
         </is>
       </c>
-      <c r="C651" t="inlineStr">
+      <c r="C650" t="inlineStr">
         <is>
           <t>宇宙 ,人類</t>
         </is>
       </c>
     </row>
-    <row r="652">
-      <c r="A652" t="inlineStr">
+    <row r="651">
+      <c r="A651" t="inlineStr">
         <is>
           <t xml:space="preserve">「自分を信じなさい。人の言うことは尽きないのだから」
 ثق بنفسك فكلام الناس لا ينتهي
@@ -14155,19 +14134,19 @@
 2105 出典不明 </t>
         </is>
       </c>
-      <c r="B652" t="inlineStr">
+      <c r="B651" t="inlineStr">
         <is>
           <t>images/「自分を信じなさい。人の言うことは尽き_img1.jpg</t>
         </is>
       </c>
-      <c r="C652" t="inlineStr">
+      <c r="C651" t="inlineStr">
         <is>
           <t>自信 ,無視</t>
         </is>
       </c>
     </row>
-    <row r="653">
-      <c r="A653" t="inlineStr">
+    <row r="652">
+      <c r="A652" t="inlineStr">
         <is>
           <t xml:space="preserve">「弟が歩くぞ」أخي الصغير يمشي
 アキ_ッサギール・ヤムシー ['aKh-i ^_saGhiiru ya-mShii]
@@ -14176,19 +14155,19 @@
 2308 gulfkids com http://www.gulfkids.com/ar/book48-1909.htm </t>
         </is>
       </c>
-      <c r="B653" t="inlineStr">
+      <c r="B652" t="inlineStr">
         <is>
           <t>images/「弟が歩くぞ」_img1.jpg</t>
         </is>
       </c>
-      <c r="C653" t="inlineStr">
+      <c r="C652" t="inlineStr">
         <is>
           <t>兄弟 ,絵本</t>
         </is>
       </c>
     </row>
-    <row r="654">
-      <c r="A654" t="inlineStr">
+    <row r="653">
+      <c r="A653" t="inlineStr">
         <is>
           <t xml:space="preserve">花より団子おおお（違う）
 「誰もふさわしくない」[laa 'aHada ya-staHiqqu]
@@ -14196,19 +14175,19 @@
 2308 https://twitter.com/NatGeoMagArab/status/1370041991317233664 </t>
         </is>
       </c>
-      <c r="B654" t="inlineStr">
+      <c r="B653" t="inlineStr">
         <is>
           <t>images/花より団子おおお（違う）_img1.jpg</t>
         </is>
       </c>
-      <c r="C654" t="inlineStr">
+      <c r="C653" t="inlineStr">
         <is>
           <t>手書き語学 ,アラビア語 ,キノボリカンガルー</t>
         </is>
       </c>
     </row>
-    <row r="655">
-      <c r="A655" t="inlineStr">
+    <row r="654">
+      <c r="A654" t="inlineStr">
         <is>
           <t xml:space="preserve">「諸行無常」كلّ شيءٍ يتغيّر
 クッル・シャイイン・ヤタガイヤル [kullu Shay'in ya-taGhayyaru]
@@ -14218,19 +14197,19 @@
 د. ماجد عبدالله </t>
         </is>
       </c>
-      <c r="B655" t="inlineStr">
+      <c r="B654" t="inlineStr">
         <is>
           <t>images/「諸行無常」_img1.jpg</t>
         </is>
       </c>
-      <c r="C655" t="inlineStr">
+      <c r="C654" t="inlineStr">
         <is>
           <t>表紙 ,タイトル</t>
         </is>
       </c>
     </row>
-    <row r="656">
-      <c r="A656" t="inlineStr">
+    <row r="655">
+      <c r="A655" t="inlineStr">
         <is>
           <t xml:space="preserve">「幸せな人生には弱い記憶力が必要」
 الحياة السعيدة تتطلب ذاكرة ضعيفة
@@ -14239,19 +14218,19 @@
 2012 出典不明 </t>
         </is>
       </c>
-      <c r="B656" t="inlineStr">
+      <c r="B655" t="inlineStr">
         <is>
           <t>images/「幸せな人生には弱い記憶力が必要」_img1.jpg</t>
         </is>
       </c>
-      <c r="C656" t="inlineStr">
+      <c r="C655" t="inlineStr">
         <is>
           <t>前向き</t>
         </is>
       </c>
     </row>
-    <row r="657">
-      <c r="A657" t="inlineStr">
+    <row r="656">
+      <c r="A656" t="inlineStr">
         <is>
           <t xml:space="preserve">「このパンダは私たちに、幸せは単純なことの中に隠れているのだと教えている」
 دب "الباندا" هذا يؤكد لنا أن السعادة تكمن في أبسط الأشياء
@@ -14259,19 +14238,19 @@
 2308 https://twitter.com/NatGeoMagArab/status/1309938472065486848 </t>
         </is>
       </c>
-      <c r="B657" t="inlineStr">
+      <c r="B656" t="inlineStr">
         <is>
           <t>images/「このパンダは私たちに、幸せは単純なこ.png</t>
         </is>
       </c>
-      <c r="C657" t="inlineStr">
+      <c r="C656" t="inlineStr">
         <is>
           <t>パンダ ,雪</t>
         </is>
       </c>
     </row>
-    <row r="658">
-      <c r="A658" t="inlineStr">
+    <row r="657">
+      <c r="A657" t="inlineStr">
         <is>
           <t xml:space="preserve">「良い時間は速く過ぎる」
 الأوقات الجميلة تمر بسرعة
@@ -14281,19 +14260,19 @@
 1810 Nasser.Tumblr </t>
         </is>
       </c>
-      <c r="B658" t="inlineStr">
+      <c r="B657" t="inlineStr">
         <is>
           <t>images/「良い時間は速く過ぎる」_img1.jpg</t>
         </is>
       </c>
-      <c r="C658" t="inlineStr">
+      <c r="C657" t="inlineStr">
         <is>
           <t>相対論 ,心理学</t>
         </is>
       </c>
     </row>
-    <row r="659">
-      <c r="A659" t="inlineStr">
+    <row r="658">
+      <c r="A658" t="inlineStr">
         <is>
           <t xml:space="preserve">「今日が始まりかもしれない」
 كل يوم ممكن يكون بداية
@@ -14303,19 +14282,19 @@
 2308 Ahmed Madyan </t>
         </is>
       </c>
-      <c r="B659" t="inlineStr">
+      <c r="B658" t="inlineStr">
         <is>
           <t>images/「今日が始まりかもしれない」_img1.jpg</t>
         </is>
       </c>
-      <c r="C659" t="inlineStr">
+      <c r="C658" t="inlineStr">
         <is>
           <t>吉日 ,開始</t>
         </is>
       </c>
     </row>
-    <row r="660">
-      <c r="A660" t="inlineStr">
+    <row r="659">
+      <c r="A659" t="inlineStr">
         <is>
           <t xml:space="preserve">「ヌール、歯医者さんに行く」
 نور تذهب إلى طبيب الأسنان
@@ -14325,19 +14304,19 @@
 2109 RABIE </t>
         </is>
       </c>
-      <c r="B660" t="inlineStr">
+      <c r="B659" t="inlineStr">
         <is>
           <t>images/「ヌール、歯医者さんに行く」_img1.jpg</t>
         </is>
       </c>
-      <c r="C660" t="inlineStr">
+      <c r="C659" t="inlineStr">
         <is>
           <t>絵本 ,歯科</t>
         </is>
       </c>
     </row>
-    <row r="661">
-      <c r="A661" t="inlineStr">
+    <row r="660">
+      <c r="A660" t="inlineStr">
         <is>
           <t xml:space="preserve">「ラヤンはねむれない」
 لَيان لا تَسْتَطيعُ أَنْ تَنام
@@ -14346,19 +14325,19 @@
 2308 出典不明 </t>
         </is>
       </c>
-      <c r="B661" t="inlineStr">
+      <c r="B660" t="inlineStr">
         <is>
           <t>images/「ラヤンはねむれない」_img1.jpg</t>
         </is>
       </c>
-      <c r="C661" t="inlineStr">
+      <c r="C660" t="inlineStr">
         <is>
           <t>絵本 ,不眠症</t>
         </is>
       </c>
     </row>
-    <row r="662">
-      <c r="A662" t="inlineStr">
+    <row r="661">
+      <c r="A661" t="inlineStr">
         <is>
           <t xml:space="preserve">「クネイトラ県、蜂の巣を約60%失う」
 القنيطرة تفقد حوالي 60 % من خلايا نحلها
@@ -14366,19 +14345,19 @@
 2403 nabd com/t/101679025-fb119f </t>
         </is>
       </c>
-      <c r="B662" t="inlineStr">
+      <c r="B661" t="inlineStr">
         <is>
           <t>images/「クネイトラ県、蜂の巣を約60%失う」_img1.jpg</t>
         </is>
       </c>
-      <c r="C662" t="inlineStr">
+      <c r="C661" t="inlineStr">
         <is>
           <t>蜂の巣 ,パーセント</t>
         </is>
       </c>
     </row>
-    <row r="663">
-      <c r="A663" t="inlineStr">
+    <row r="662">
+      <c r="A662" t="inlineStr">
         <is>
           <t xml:space="preserve">「結ばれしター」ة
 ⁦( تاء مربوطة )[taa' marbuu_ta]：ت「ター」( تاء )[taa']・「結ばれている」( مربوط )[marbuu_t]：( ربط )【結】⁩
@@ -14386,19 +14365,19 @@
 2308 出典不明 </t>
         </is>
       </c>
-      <c r="B663" t="inlineStr">
+      <c r="B662" t="inlineStr">
         <is>
           <t>images/「結ばれしター」_img1.jpg</t>
         </is>
       </c>
-      <c r="C663" t="inlineStr">
+      <c r="C662" t="inlineStr">
         <is>
           <t>アラビア文字 ,顔</t>
         </is>
       </c>
     </row>
-    <row r="664">
-      <c r="A664" t="inlineStr">
+    <row r="663">
+      <c r="A663" t="inlineStr">
         <is>
           <t xml:space="preserve">「忙しい」مشغول
 マシュグール [maShGhuul]
@@ -14407,19 +14386,19 @@
 1811 skyshinichi.instagram </t>
         </is>
       </c>
-      <c r="B664" t="inlineStr">
+      <c r="B663" t="inlineStr">
         <is>
           <t>images/「忙しい」_img1.jpg</t>
         </is>
       </c>
-      <c r="C664" t="inlineStr">
+      <c r="C663" t="inlineStr">
         <is>
           <t>スティッチ ,残業</t>
         </is>
       </c>
     </row>
-    <row r="665">
-      <c r="A665" t="inlineStr">
+    <row r="664">
+      <c r="A664" t="inlineStr">
         <is>
           <t xml:space="preserve">「駐車禁止」ممنوع الوقوف
 マムヌーア・アルウクーフ [mamnuu* al-wuquuf]
@@ -14428,19 +14407,19 @@
 2106 出典不明 </t>
         </is>
       </c>
-      <c r="B665" t="inlineStr">
+      <c r="B664" t="inlineStr">
         <is>
           <t>images/「駐車禁止」_img1.jpg</t>
         </is>
       </c>
-      <c r="C665" t="inlineStr">
+      <c r="C664" t="inlineStr">
         <is>
           <t>標識 ,ジョーク</t>
         </is>
       </c>
     </row>
-    <row r="666">
-      <c r="A666" t="inlineStr">
+    <row r="665">
+      <c r="A665" t="inlineStr">
         <is>
           <t xml:space="preserve">「一人ひとりが責任を」
 كُلنا مسؤول
@@ -14450,19 +14429,19 @@
 2308 covid19awareness sa </t>
         </is>
       </c>
-      <c r="B666" t="inlineStr">
+      <c r="B665" t="inlineStr">
         <is>
           <t>images/「一人ひとりが責任を」_img1.jpg</t>
         </is>
       </c>
-      <c r="C666" t="inlineStr">
+      <c r="C665" t="inlineStr">
         <is>
           <t>Covid ,感染拡大防止</t>
         </is>
       </c>
     </row>
-    <row r="667">
-      <c r="A667" t="inlineStr">
+    <row r="666">
+      <c r="A666" t="inlineStr">
         <is>
           <t xml:space="preserve">「おめでとうございます」مبروك
 マブルーク [mabruuk]
@@ -14471,19 +14450,19 @@
 2308 </t>
         </is>
       </c>
-      <c r="B667" t="inlineStr">
+      <c r="B666" t="inlineStr">
         <is>
           <t>images/「おめでとうございます」_img1.jpg</t>
         </is>
       </c>
-      <c r="C667" t="inlineStr">
+      <c r="C666" t="inlineStr">
         <is>
           <t>詐欺 ,広告</t>
         </is>
       </c>
     </row>
-    <row r="668">
-      <c r="A668" t="inlineStr">
+    <row r="667">
+      <c r="A667" t="inlineStr">
         <is>
           <t xml:space="preserve">「手書きフォント」
 خط مكتوب باليد
@@ -14493,19 +14472,19 @@
 1809 FahdAlFraikh Behance </t>
         </is>
       </c>
-      <c r="B668" t="inlineStr">
+      <c r="B667" t="inlineStr">
         <is>
           <t>images/「手書きフォント」_img1.jpg</t>
         </is>
       </c>
-      <c r="C668" t="inlineStr">
+      <c r="C667" t="inlineStr">
         <is>
           <t>可愛いフォント ,筆跡</t>
         </is>
       </c>
     </row>
-    <row r="669">
-      <c r="A669" t="inlineStr">
+    <row r="668">
+      <c r="A668" t="inlineStr">
         <is>
           <t xml:space="preserve">「開かれたターと結ばれたター」
 التاء المفتوحة والمربوطة
@@ -14515,19 +14494,19 @@
 2109 slideshare.net </t>
         </is>
       </c>
-      <c r="B669" t="inlineStr">
+      <c r="B668" t="inlineStr">
         <is>
           <t>images/「開かれたターと結ばれたター」_img1.jpg</t>
         </is>
       </c>
-      <c r="C669" t="inlineStr">
+      <c r="C668" t="inlineStr">
         <is>
           <t>アラビア文字 ,スマイリー</t>
         </is>
       </c>
     </row>
-    <row r="670">
-      <c r="A670" t="inlineStr">
+    <row r="669">
+      <c r="A669" t="inlineStr">
         <is>
           <t xml:space="preserve">「このラマは誇らしげにして立っている」
 تقف هذه اللاما مزهوة بنفسها
@@ -14535,19 +14514,19 @@
 2410 https://twitter.com/NatGeoMagArab/status/1597485552965935104 </t>
         </is>
       </c>
-      <c r="B670" t="inlineStr">
+      <c r="B669" t="inlineStr">
         <is>
           <t>images/「このラマは誇らしげにして立っている」_img1.jpg</t>
         </is>
       </c>
-      <c r="C670" t="inlineStr">
+      <c r="C669" t="inlineStr">
         <is>
           <t>手書き語学 ,アラビア語 ,マチュピチュ遺跡</t>
         </is>
       </c>
     </row>
-    <row r="671">
-      <c r="A671" t="inlineStr">
+    <row r="670">
+      <c r="A670" t="inlineStr">
         <is>
           <t xml:space="preserve">「小さな生き物にしては危険な名前だ」
 اسم خطير لمخلوق صغير
@@ -14556,19 +14535,19 @@
 2308 https://twitter.com/NatGeoMagArab/status/1495035772071669760 </t>
         </is>
       </c>
-      <c r="B671" t="inlineStr">
+      <c r="B670" t="inlineStr">
         <is>
           <t>images/「小さな生き物にしては危険な名前だ」_img1.jpg</t>
         </is>
       </c>
-      <c r="C671" t="inlineStr">
+      <c r="C670" t="inlineStr">
         <is>
           <t>有袋類 ,タスマニアデビル</t>
         </is>
       </c>
     </row>
-    <row r="672">
-      <c r="A672" t="inlineStr">
+    <row r="671">
+      <c r="A671" t="inlineStr">
         <is>
           <t xml:space="preserve">「こわれている」مكسر
 ムカッサル [mukassar]
@@ -14576,19 +14555,19 @@
 2105 behance Written-Visuals </t>
         </is>
       </c>
-      <c r="B672" t="inlineStr">
+      <c r="B671" t="inlineStr">
         <is>
           <t>images/「こわれている」_img1.jpg</t>
         </is>
       </c>
-      <c r="C672" t="inlineStr">
+      <c r="C671" t="inlineStr">
         <is>
           <t>バラバラ ,デザイン</t>
         </is>
       </c>
     </row>
-    <row r="673">
-      <c r="A673" t="inlineStr">
+    <row r="672">
+      <c r="A672" t="inlineStr">
         <is>
           <t xml:space="preserve">「早起きする方法」
 كيف تنهض مُبكّرًا
@@ -14598,19 +14577,19 @@
 2308 Funders and Founders </t>
         </is>
       </c>
-      <c r="B673" t="inlineStr">
+      <c r="B672" t="inlineStr">
         <is>
           <t>images/「早起きする方法」_img1.jpg</t>
         </is>
       </c>
-      <c r="C673" t="inlineStr">
+      <c r="C672" t="inlineStr">
         <is>
           <t>オフトゥン ,寝起き</t>
         </is>
       </c>
     </row>
-    <row r="674">
-      <c r="A674" t="inlineStr">
+    <row r="673">
+      <c r="A673" t="inlineStr">
         <is>
           <t xml:space="preserve">「アラブ・デザイン文字展覧会」
 معرض لتخطيط الحرف العربي
@@ -14620,38 +14599,38 @@
 2109 arabic lettering exhibition </t>
         </is>
       </c>
-      <c r="B674" t="inlineStr">
+      <c r="B673" t="inlineStr">
         <is>
           <t>images/「アラブ・デザイン文字展覧会」_img1.jpg</t>
         </is>
       </c>
-      <c r="C674" t="inlineStr">
+      <c r="C673" t="inlineStr">
         <is>
           <t>ポスター</t>
         </is>
       </c>
     </row>
-    <row r="675">
-      <c r="A675" t="inlineStr">
+    <row r="674">
+      <c r="A674" t="inlineStr">
         <is>
           <t xml:space="preserve">「お気に入りのおもちゃには触らせない」
 ⁦「彼は〜を許さない」[laa ya-smaHu bi-]：「彼は許す」( يسمح )[ya-smaH(u)]：「許した」( سمح )[samaHa]：( سَ )[sa]・( مَ )[ma]・( حَ )[Ha]⁩
 2209 https://pic.twitter.com/qWcIPB3fz2 </t>
         </is>
       </c>
-      <c r="B675" t="inlineStr">
+      <c r="B674" t="inlineStr">
         <is>
           <t>images/「お気に入りのおもちゃには触らせない」_img1.jpg</t>
         </is>
       </c>
-      <c r="C675" t="inlineStr">
+      <c r="C674" t="inlineStr">
         <is>
           <t>パンダ ,ボール</t>
         </is>
       </c>
     </row>
-    <row r="676">
-      <c r="A676" t="inlineStr">
+    <row r="675">
+      <c r="A675" t="inlineStr">
         <is>
           <t xml:space="preserve">「名探偵コナン」المحقق كونان
 アルムハッキク・コナン [al-muHaqqiq Conan]
@@ -14660,19 +14639,19 @@
 1809 wikipedia </t>
         </is>
       </c>
-      <c r="B676" t="inlineStr">
+      <c r="B675" t="inlineStr">
         <is>
           <t>images/「名探偵コナン」_img1.jpg</t>
         </is>
       </c>
-      <c r="C676" t="inlineStr">
+      <c r="C675" t="inlineStr">
         <is>
           <t>江戸川コナン ,ロゴ</t>
         </is>
       </c>
     </row>
-    <row r="677">
-      <c r="A677" t="inlineStr">
+    <row r="676">
+      <c r="A676" t="inlineStr">
         <is>
           <t xml:space="preserve">「イードおめでとう」عيد مبارك
 イード・ムバーラク [*iid mubaarak]
@@ -14680,19 +14659,19 @@
 2308 出典不明 </t>
         </is>
       </c>
-      <c r="B677" t="inlineStr">
+      <c r="B676" t="inlineStr">
         <is>
           <t>images/「イードおめでとう」_img1.jpg</t>
         </is>
       </c>
-      <c r="C677" t="inlineStr">
+      <c r="C676" t="inlineStr">
         <is>
           <t>عيد ,アラビア語</t>
         </is>
       </c>
     </row>
-    <row r="678">
-      <c r="A678" t="inlineStr">
+    <row r="677">
+      <c r="A677" t="inlineStr">
         <is>
           <t xml:space="preserve">「戦士」محارب
 ムハーリブ [muHaarib]
@@ -14701,19 +14680,19 @@
 1809 abudinges.tumblr </t>
         </is>
       </c>
-      <c r="B678" t="inlineStr">
+      <c r="B677" t="inlineStr">
         <is>
           <t>images/「戦士」_img1.jpg</t>
         </is>
       </c>
-      <c r="C678" t="inlineStr">
+      <c r="C677" t="inlineStr">
         <is>
           <t>ロゴ ,赤</t>
         </is>
       </c>
     </row>
-    <row r="679">
-      <c r="A679" t="inlineStr">
+    <row r="678">
+      <c r="A678" t="inlineStr">
         <is>
           <t xml:space="preserve">「ライブ」بث مباشر
 バッス・ムバーシル [ba^Th(un) mubaaShir(un)]
@@ -14722,19 +14701,19 @@
 2308 beIN SPORTS </t>
         </is>
       </c>
-      <c r="B679" t="inlineStr">
+      <c r="B678" t="inlineStr">
         <is>
           <t>images/「ライブ」_img1.jpg</t>
         </is>
       </c>
-      <c r="C679" t="inlineStr">
+      <c r="C678" t="inlineStr">
         <is>
           <t xml:space="preserve">生放送 ,試合 </t>
         </is>
       </c>
     </row>
-    <row r="680">
-      <c r="A680" t="inlineStr">
+    <row r="679">
+      <c r="A679" t="inlineStr">
         <is>
           <t xml:space="preserve">「信者」مُؤْمِنٌ
 ムッミン [mu'min(un)]
@@ -14743,19 +14722,19 @@
 2106 出典不明 </t>
         </is>
       </c>
-      <c r="B680" t="inlineStr">
+      <c r="B679" t="inlineStr">
         <is>
           <t>images/「信者」_img1.jpg</t>
         </is>
       </c>
-      <c r="C680" t="inlineStr">
+      <c r="C679" t="inlineStr">
         <is>
           <t>明暗 ,信仰</t>
         </is>
       </c>
     </row>
-    <row r="681">
-      <c r="A681" t="inlineStr">
+    <row r="680">
+      <c r="A680" t="inlineStr">
         <is>
           <t xml:space="preserve">「開⇔閉」
 مفتوح
@@ -14766,19 +14745,19 @@
 2312 Hussein Safina, behance </t>
         </is>
       </c>
-      <c r="B681" t="inlineStr">
+      <c r="B680" t="inlineStr">
         <is>
           <t>images/「開⇔閉」_img1.jpg</t>
         </is>
       </c>
-      <c r="C681" t="inlineStr">
+      <c r="C680" t="inlineStr">
         <is>
           <t>オープンマインド ,トグル</t>
         </is>
       </c>
     </row>
-    <row r="682">
-      <c r="A682" t="inlineStr">
+    <row r="681">
+      <c r="A681" t="inlineStr">
         <is>
           <t xml:space="preserve">「予想外な結末！」
 نهاية غير متوقعة
@@ -14786,19 +14765,19 @@
 2308 https://twitter.com/NatGeoMagArab/status/1159011433444593665 </t>
         </is>
       </c>
-      <c r="B682" t="inlineStr">
+      <c r="B681" t="inlineStr">
         <is>
           <t>images/「予想外な結末！」_img1.jpg</t>
         </is>
       </c>
-      <c r="C682" t="inlineStr">
+      <c r="C681" t="inlineStr">
         <is>
           <t>手書き語学 ,アラビア語 ,ウサギ</t>
         </is>
       </c>
     </row>
-    <row r="683">
-      <c r="A683" t="inlineStr">
+    <row r="682">
+      <c r="A682" t="inlineStr">
         <is>
           <t xml:space="preserve">「ベイルート・アニメイテッド」
 بیروت متحرّکة
@@ -14808,19 +14787,19 @@
 2308 arabic_script Instagram </t>
         </is>
       </c>
-      <c r="B683" t="inlineStr">
+      <c r="B682" t="inlineStr">
         <is>
           <t>images/「ベイルート・アニメイテッド」_img1.jpg</t>
         </is>
       </c>
-      <c r="C683" t="inlineStr">
+      <c r="C682" t="inlineStr">
         <is>
           <t>アニメ ,レバノン</t>
         </is>
       </c>
     </row>
-    <row r="684">
-      <c r="A684" t="inlineStr">
+    <row r="683">
+      <c r="A683" t="inlineStr">
         <is>
           <t xml:space="preserve">「夢みれば叶う」
 كُلُّ مُتَوَقَّعٍ آتٍ
@@ -14830,19 +14809,19 @@
 2108 Ahmed Madyan </t>
         </is>
       </c>
-      <c r="B684" t="inlineStr">
+      <c r="B683" t="inlineStr">
         <is>
           <t>images/「夢みれば叶う」_img1.jpg</t>
         </is>
       </c>
-      <c r="C684" t="inlineStr">
+      <c r="C683" t="inlineStr">
         <is>
           <t>希望 ,ドリカム</t>
         </is>
       </c>
     </row>
-    <row r="685">
-      <c r="A685" t="inlineStr">
+    <row r="684">
+      <c r="A684" t="inlineStr">
         <is>
           <t xml:space="preserve">「もし両者が人間のように鎧で武装して戦いに突入したら」
 لو خاضا معاركهما متسلحين بالدروع على غرار البش
@@ -14850,19 +14829,19 @@
 2404 https://x.com/NatGeoMagArab/status/1759284149456945464 </t>
         </is>
       </c>
-      <c r="B685" t="inlineStr">
+      <c r="B684" t="inlineStr">
         <is>
           <t>images/「もし両者が人間のように鎧で武装して戦_img1.jpg,images/「もし両者が人間のように鎧で武装して戦_img2.jpg</t>
         </is>
       </c>
-      <c r="C685" t="inlineStr">
+      <c r="C684" t="inlineStr">
         <is>
           <t>手書き語学 ,アラビア語 ,猫</t>
         </is>
       </c>
     </row>
-    <row r="686">
-      <c r="A686" t="inlineStr">
+    <row r="685">
+      <c r="A685" t="inlineStr">
         <is>
           <t xml:space="preserve">「全ては結びついている」
 كل شيء مترابط
@@ -14872,19 +14851,19 @@
 2308 Ahmed Madyan https://twitter.com/madyco22/status/1451990828298166273 </t>
         </is>
       </c>
-      <c r="B686" t="inlineStr">
+      <c r="B685" t="inlineStr">
         <is>
           <t>images/「全ては結びついている」_img1.jpg</t>
         </is>
       </c>
-      <c r="C686" t="inlineStr">
+      <c r="C685" t="inlineStr">
         <is>
           <t>一筆書き ,デザイン</t>
         </is>
       </c>
     </row>
-    <row r="687">
-      <c r="A687" t="inlineStr">
+    <row r="686">
+      <c r="A686" t="inlineStr">
         <is>
           <t xml:space="preserve">「初心者のためのスケッチトレーニング」
 تعليم الرسم للمبتدئين
@@ -14894,19 +14873,19 @@
 2308 free-bookspdf com </t>
         </is>
       </c>
-      <c r="B687" t="inlineStr">
+      <c r="B686" t="inlineStr">
         <is>
           <t>images/「初心者のためのスケッチトレーニング」_img1.jpg</t>
         </is>
       </c>
-      <c r="C687" t="inlineStr">
+      <c r="C686" t="inlineStr">
         <is>
           <t>イラスト ,絵</t>
         </is>
       </c>
     </row>
-    <row r="688">
-      <c r="A688" t="inlineStr">
+    <row r="687">
+      <c r="A687" t="inlineStr">
         <is>
           <t xml:space="preserve">「初心者のためのスルス体書道トレーニング」
 تعليم خط الثلث للمبتدئين
@@ -14916,19 +14895,19 @@
 2308 出典不明 </t>
         </is>
       </c>
-      <c r="B688" t="inlineStr">
+      <c r="B687" t="inlineStr">
         <is>
           <t>images/「初心者のためのスルス体書道トレーニン_img1.jpg</t>
         </is>
       </c>
-      <c r="C688" t="inlineStr">
+      <c r="C687" t="inlineStr">
         <is>
           <t>書道</t>
         </is>
       </c>
     </row>
-    <row r="689">
-      <c r="A689" t="inlineStr">
+    <row r="688">
+      <c r="A688" t="inlineStr">
         <is>
           <t xml:space="preserve">「笑顔でいなさい」خليك مبتسم
 カッリーク・ムブタスィム [Khallii-k mubtasim]
@@ -14937,19 +14916,19 @@
 2308 https://tmblr.co/Zj9tguYLXBvC </t>
         </is>
       </c>
-      <c r="B689" t="inlineStr">
+      <c r="B688" t="inlineStr">
         <is>
           <t>images/「笑顔でいなさい」_img1.jpg</t>
         </is>
       </c>
-      <c r="C689" t="inlineStr">
+      <c r="C688" t="inlineStr">
         <is>
           <t>スマイル ,名言</t>
         </is>
       </c>
     </row>
-    <row r="690">
-      <c r="A690" t="inlineStr">
+    <row r="689">
+      <c r="A689" t="inlineStr">
         <is>
           <t xml:space="preserve">自動車メーカー
 ⁦・「TOYOTA」( تويوتا )⁩
@@ -14961,19 +14940,19 @@
 2308 syarah com </t>
         </is>
       </c>
-      <c r="B690" t="inlineStr">
+      <c r="B689" t="inlineStr">
         <is>
           <t>images/自動車メーカー_img1.jpg,images/自動車メーカー_img2.jpg,images/自動車メーカー_img3.jpg,images/自動車メーカー_img4.jpg</t>
         </is>
       </c>
-      <c r="C690" t="inlineStr">
+      <c r="C689" t="inlineStr">
         <is>
           <t>日本車 ,韓国車</t>
         </is>
       </c>
     </row>
-    <row r="691">
-      <c r="A691" t="inlineStr">
+    <row r="690">
+      <c r="A690" t="inlineStr">
         <is>
           <t xml:space="preserve">「僕たちは協力して不可能を達成するよ」
 بالتعاون نحقق المحال
@@ -14983,19 +14962,19 @@
 2109 </t>
         </is>
       </c>
-      <c r="B691" t="inlineStr">
+      <c r="B690" t="inlineStr">
         <is>
           <t>images/「僕たちは協力して不可能を達成するよ」_img1.jpg</t>
         </is>
       </c>
-      <c r="C691" t="inlineStr">
+      <c r="C690" t="inlineStr">
         <is>
           <t>無理 ,ハム太郎</t>
         </is>
       </c>
     </row>
-    <row r="692">
-      <c r="A692" t="inlineStr">
+    <row r="691">
+      <c r="A691" t="inlineStr">
         <is>
           <t xml:space="preserve">「幸せは伝染性。喜びを広めよう」
 السعادة معدية فأشع الفرح
@@ -15005,19 +14984,19 @@
 2511 instagram　com/p/fVEfxEo7Va/ </t>
         </is>
       </c>
-      <c r="B692" t="inlineStr">
+      <c r="B691" t="inlineStr">
         <is>
           <t>images/「幸せは伝染性。喜びを広めよう」_img1.jpg</t>
         </is>
       </c>
-      <c r="C692" t="inlineStr">
+      <c r="C691" t="inlineStr">
         <is>
           <t>拡散希望</t>
         </is>
       </c>
     </row>
-    <row r="693">
-      <c r="A693" t="inlineStr">
+    <row r="692">
+      <c r="A692" t="inlineStr">
         <is>
           <t xml:space="preserve">「ストレスは人間だけのものではない」
 الشعور بالتوتر ليس حكرًا على البشر
@@ -15025,19 +15004,19 @@
 2408 https://x.com/NatGeoMagArab/status/1736755816911487420 </t>
         </is>
       </c>
-      <c r="B693" t="inlineStr">
+      <c r="B692" t="inlineStr">
         <is>
           <t>images/「ストレスは人間だけのものではない」_img1.jpg</t>
         </is>
       </c>
-      <c r="C693" t="inlineStr">
+      <c r="C692" t="inlineStr">
         <is>
           <t>手書き語学 ,アラビア語 ,ストレス</t>
         </is>
       </c>
     </row>
-    <row r="694">
-      <c r="A694" t="inlineStr">
+    <row r="693">
+      <c r="A693" t="inlineStr">
         <is>
           <t xml:space="preserve">「私達は出来ます！」
 نستطيع فعلها
@@ -15047,19 +15026,19 @@
 2308 NAHARBAHIJ com </t>
         </is>
       </c>
-      <c r="B694" t="inlineStr">
+      <c r="B693" t="inlineStr">
         <is>
           <t>images/「私達は出来ます！」_img1.jpg</t>
         </is>
       </c>
-      <c r="C694" t="inlineStr">
+      <c r="C693" t="inlineStr">
         <is>
           <t>女性 ,パロディ</t>
         </is>
       </c>
     </row>
-    <row r="695">
-      <c r="A695" t="inlineStr">
+    <row r="694">
+      <c r="A694" t="inlineStr">
         <is>
           <t xml:space="preserve">「全然分からん」ولا فاهم إشي
 ウラー・ファーヒム・イシ [w-laa faahim 'iShy]
@@ -15069,19 +15048,19 @@
 2209 出典不明 </t>
         </is>
       </c>
-      <c r="B695" t="inlineStr">
+      <c r="B694" t="inlineStr">
         <is>
           <t>images/「全然分からん」_img1.jpg</t>
         </is>
       </c>
-      <c r="C695" t="inlineStr">
+      <c r="C694" t="inlineStr">
         <is>
           <t>アラビア語</t>
         </is>
       </c>
     </row>
-    <row r="696">
-      <c r="A696" t="inlineStr">
+    <row r="695">
+      <c r="A695" t="inlineStr">
         <is>
           <t xml:space="preserve">「人間は一人ひとり、特別な才がある。だから自分を他人と比べるのはやめよう」
 لكل إنسان مواهبه الخاصة 
@@ -15090,19 +15069,19 @@
 1812 Gwid3 </t>
         </is>
       </c>
-      <c r="B696" t="inlineStr">
+      <c r="B695" t="inlineStr">
         <is>
           <t>images/「人間は一人ひとり、特別な才がある。だ_img1.jpg</t>
         </is>
       </c>
-      <c r="C696" t="inlineStr">
+      <c r="C695" t="inlineStr">
         <is>
           <t>自尊 ,プライド</t>
         </is>
       </c>
     </row>
-    <row r="697">
-      <c r="A697" t="inlineStr">
+    <row r="696">
+      <c r="A696" t="inlineStr">
         <is>
           <t xml:space="preserve">「デザイン」تَصْمِيمٌ
 タスミーム [ta_smiim(un)]
@@ -15110,19 +15089,19 @@
 1903 arabictypography com </t>
         </is>
       </c>
-      <c r="B697" t="inlineStr">
+      <c r="B696" t="inlineStr">
         <is>
           <t>images/「デザイン」_img1.jpg</t>
         </is>
       </c>
-      <c r="C697" t="inlineStr">
+      <c r="C696" t="inlineStr">
         <is>
           <t>文字 ,タイポグラフィー</t>
         </is>
       </c>
     </row>
-    <row r="698">
-      <c r="A698" t="inlineStr">
+    <row r="697">
+      <c r="A697" t="inlineStr">
         <is>
           <t xml:space="preserve">「この猫は食事をシェアするのが嫌い！」
 هذه القطة لا تحب مشاركة الطعام
@@ -15131,19 +15110,19 @@
 2605 facebook com/alahram/videos/2154923608133231/ </t>
         </is>
       </c>
-      <c r="B698" t="inlineStr">
+      <c r="B697" t="inlineStr">
         <is>
           <t>images/「この猫は食事をシェアするのが嫌い！」_img1.jpg</t>
         </is>
       </c>
-      <c r="C698" t="inlineStr">
+      <c r="C697" t="inlineStr">
         <is>
           <t>猫 ,ネコ</t>
         </is>
       </c>
     </row>
-    <row r="699">
-      <c r="A699" t="inlineStr">
+    <row r="698">
+      <c r="A698" t="inlineStr">
         <is>
           <t xml:space="preserve">「怪獣との戦いでは自分が怪獣化せぬよう警戒しなさい」
 احذر عند محاربة الوحوش ألا تصبح واحدا منهم
@@ -15153,19 +15132,19 @@
 2108 warag-3nb.tumblr </t>
         </is>
       </c>
-      <c r="B699" t="inlineStr">
+      <c r="B698" t="inlineStr">
         <is>
           <t>images/「怪獣との戦いでは自分が怪獣化せぬよう_img1.jpg,images/ 「怪獣との戦いでは自分が怪獣化せぬよう_img2.jpg</t>
         </is>
       </c>
-      <c r="C699" t="inlineStr">
+      <c r="C698" t="inlineStr">
         <is>
           <t>正気 ,モンスター</t>
         </is>
       </c>
     </row>
-    <row r="700">
-      <c r="A700" t="inlineStr">
+    <row r="699">
+      <c r="A699" t="inlineStr">
         <is>
           <t xml:space="preserve">「錯視アート」فن الخداع البصري
 ファンヌ_ルヒダーイ_ルバサリーイ [fannu l-Khidaa*i l-ba_sariyy]
@@ -15174,19 +15153,19 @@
 2409 https://online.pubhtml5.com/idtb/neft/ </t>
         </is>
       </c>
-      <c r="B700" t="inlineStr">
+      <c r="B699" t="inlineStr">
         <is>
           <t>images/「錯視アート」_img1.jpg</t>
         </is>
       </c>
-      <c r="C700" t="inlineStr">
+      <c r="C699" t="inlineStr">
         <is>
           <t>トリックアート</t>
         </is>
       </c>
     </row>
-    <row r="701">
-      <c r="A701" t="inlineStr">
+    <row r="700">
+      <c r="A700" t="inlineStr">
         <is>
           <t xml:space="preserve">「自然界の消防士の訓練」
 تدريبات رجال الإطفاء في الطبيعة
@@ -15194,19 +15173,19 @@
 2308 https://twitter.com/NatGeoMagArab/status/1462420543890608129 </t>
         </is>
       </c>
-      <c r="B701" t="inlineStr">
+      <c r="B700" t="inlineStr">
         <is>
           <t>images/「自然界の消防士の訓練」_img1.jpg,images/ 「自然界の消防士の訓練」_img2.jpg</t>
         </is>
       </c>
-      <c r="C701" t="inlineStr">
+      <c r="C700" t="inlineStr">
         <is>
           <t>手書き語学 ,アラビア語 ,ヒグマ</t>
         </is>
       </c>
     </row>
-    <row r="702">
-      <c r="A702" t="inlineStr">
+    <row r="701">
+      <c r="A701" t="inlineStr">
         <is>
           <t xml:space="preserve">「救助」إسعاف
 イスアーフ ['is*aaf]
@@ -15215,19 +15194,19 @@
 2109 ambulance gov ae </t>
         </is>
       </c>
-      <c r="B702" t="inlineStr">
+      <c r="B701" t="inlineStr">
         <is>
           <t>images/「救助」_img1.jpg</t>
         </is>
       </c>
-      <c r="C702" t="inlineStr">
+      <c r="C701" t="inlineStr">
         <is>
           <t>救急車 ,はたらくくるま</t>
         </is>
       </c>
     </row>
-    <row r="703">
-      <c r="A703" t="inlineStr">
+    <row r="702">
+      <c r="A702" t="inlineStr">
         <is>
           <t xml:space="preserve">「感情／感覚」الإحْسَاسْ
 アルイヒサース [al-'iHsaas]
@@ -15236,19 +15215,19 @@
 2308 iN49R </t>
         </is>
       </c>
-      <c r="B703" t="inlineStr">
+      <c r="B702" t="inlineStr">
         <is>
           <t>images/「感情／感覚」_img1.jpg</t>
         </is>
       </c>
-      <c r="C703" t="inlineStr">
+      <c r="C702" t="inlineStr">
         <is>
           <t>オフ ,一休み</t>
         </is>
       </c>
     </row>
-    <row r="704">
-      <c r="A704" t="inlineStr">
+    <row r="703">
+      <c r="A703" t="inlineStr">
         <is>
           <t xml:space="preserve">「ひらめき」إلهام
 イルハーム ['lhaam]
@@ -15260,19 +15239,19 @@
 2103 出典不明 </t>
         </is>
       </c>
-      <c r="B704" t="inlineStr">
+      <c r="B703" t="inlineStr">
         <is>
           <t>images/「ひらめき」_img1.jpg</t>
         </is>
       </c>
-      <c r="C704" t="inlineStr">
+      <c r="C703" t="inlineStr">
         <is>
           <t>アラビア語</t>
         </is>
       </c>
     </row>
-    <row r="705">
-      <c r="A705" t="inlineStr">
+    <row r="704">
+      <c r="A704" t="inlineStr">
         <is>
           <t xml:space="preserve">「Ibdaa／クリエイティビティ」
 إبداع
@@ -15281,19 +15260,19 @@
 2308 Ibdaa Design &amp; Decoration Office </t>
         </is>
       </c>
-      <c r="B705" t="inlineStr">
+      <c r="B704" t="inlineStr">
         <is>
           <t>images/「Ibdaa／クリエイティビティ」_img1.jpg</t>
         </is>
       </c>
-      <c r="C705" t="inlineStr">
+      <c r="C704" t="inlineStr">
         <is>
           <t>創造性 ,独自性</t>
         </is>
       </c>
     </row>
-    <row r="706">
-      <c r="A706" t="inlineStr">
+    <row r="705">
+      <c r="A705" t="inlineStr">
         <is>
           <t xml:space="preserve">「奮闘なくして進歩なし」
 بدون كفاح لايوجد تقدم
@@ -15303,19 +15282,19 @@
 2105 ROUYMS TUMBLR COM </t>
         </is>
       </c>
-      <c r="B706" t="inlineStr">
+      <c r="B705" t="inlineStr">
         <is>
           <t>images/「奮闘なくして進歩なし」_img1.jpg</t>
         </is>
       </c>
-      <c r="C706" t="inlineStr">
+      <c r="C705" t="inlineStr">
         <is>
           <t>努力 ,三角形</t>
         </is>
       </c>
     </row>
-    <row r="707">
-      <c r="A707" t="inlineStr">
+    <row r="706">
+      <c r="A706" t="inlineStr">
         <is>
           <t xml:space="preserve">「木に登れば熊の危険を避けられるとお考えなら、考え直しましょう！」 
 إن اعتقدت أنك بمنأى عن خطر الدب عند تسلق الأشجار.. راجع حساباتك
@@ -15323,19 +15302,19 @@
 2202 NatGeoMagArab </t>
         </is>
       </c>
-      <c r="B707" t="inlineStr">
+      <c r="B706" t="inlineStr">
         <is>
           <t>images/「木に登れば熊の危険を避けられるとお考.jpeg</t>
         </is>
       </c>
-      <c r="C707" t="inlineStr">
+      <c r="C706" t="inlineStr">
         <is>
           <t>クマ</t>
         </is>
       </c>
     </row>
-    <row r="708">
-      <c r="A708" t="inlineStr">
+    <row r="707">
+      <c r="A707" t="inlineStr">
         <is>
           <t xml:space="preserve">「卒業おめでとう」مبروك التخرج
 マブルーク・タカッルジ [mabruuk a^taKharruj]
@@ -15344,19 +15323,19 @@
 2308 https://instagram.com/fatoomworld </t>
         </is>
       </c>
-      <c r="B708" t="inlineStr">
+      <c r="B707" t="inlineStr">
         <is>
           <t>images/「卒業おめでとう」_img1.jpg</t>
         </is>
       </c>
-      <c r="C708" t="inlineStr">
+      <c r="C707" t="inlineStr">
         <is>
           <t>卒業 ,イラスト</t>
         </is>
       </c>
     </row>
-    <row r="709">
-      <c r="A709" t="inlineStr">
+    <row r="708">
+      <c r="A708" t="inlineStr">
         <is>
           <t xml:space="preserve">「停止距離の計算」
 حساب مسافة التوقف
@@ -15366,19 +15345,19 @@
 2109 assurance-auto-info </t>
         </is>
       </c>
-      <c r="B709" t="inlineStr">
+      <c r="B708" t="inlineStr">
         <is>
           <t>images/「停止距離の計算」_img1.jpg</t>
         </is>
       </c>
-      <c r="C709" t="inlineStr">
+      <c r="C708" t="inlineStr">
         <is>
           <t>保険 ,自動車</t>
         </is>
       </c>
     </row>
-    <row r="710">
-      <c r="A710" t="inlineStr">
+    <row r="709">
+      <c r="A709" t="inlineStr">
         <is>
           <t xml:space="preserve">「教師要らず：10日でフランス語会話」
 بدون معلم
@@ -15388,19 +15367,19 @@
 2308 englais-best com </t>
         </is>
       </c>
-      <c r="B710" t="inlineStr">
+      <c r="B709" t="inlineStr">
         <is>
           <t>images/「教師要らず：10日でフランス語会話」_img1.jpg</t>
         </is>
       </c>
-      <c r="C710" t="inlineStr">
+      <c r="C709" t="inlineStr">
         <is>
           <t>教師なし学習</t>
         </is>
       </c>
     </row>
-    <row r="711">
-      <c r="A711" t="inlineStr">
+    <row r="710">
+      <c r="A710" t="inlineStr">
         <is>
           <t xml:space="preserve">「衝突」تصادم
 タサードゥム [ta_saadum]
@@ -15409,19 +15388,19 @@
 1810 </t>
         </is>
       </c>
-      <c r="B711" t="inlineStr">
+      <c r="B710" t="inlineStr">
         <is>
           <t>images/「衝突」_img1.jpg</t>
         </is>
       </c>
-      <c r="C711" t="inlineStr">
+      <c r="C710" t="inlineStr">
         <is>
           <t>あらびあや</t>
         </is>
       </c>
     </row>
-    <row r="712">
-      <c r="A712" t="inlineStr">
+    <row r="711">
+      <c r="A711" t="inlineStr">
         <is>
           <t xml:space="preserve">「楽観主義」تَفَاؤُلٌ
 タファーウル [tafaa'ul(un)]
@@ -15430,19 +15409,19 @@
 1904 arabictypography com </t>
         </is>
       </c>
-      <c r="B712" t="inlineStr">
+      <c r="B711" t="inlineStr">
         <is>
           <t>images/「楽観主義」_img1.jpg</t>
         </is>
       </c>
-      <c r="C712" t="inlineStr">
+      <c r="C711" t="inlineStr">
         <is>
           <t>やわらか ,緑</t>
         </is>
       </c>
     </row>
-    <row r="713">
-      <c r="A713" t="inlineStr">
+    <row r="712">
+      <c r="A712" t="inlineStr">
         <is>
           <t xml:space="preserve">「シベリアジャコウジカは、絶滅の危機にあると見なされている」
 يعد "أيل المسك السيبيري" مهددًا بالانقراض
@@ -15450,19 +15429,19 @@
 2308 https://twitter.com/NatGeoMagArab/status/1320666649045790720 </t>
         </is>
       </c>
-      <c r="B713" t="inlineStr">
+      <c r="B712" t="inlineStr">
         <is>
           <t>images/「シベリアジャコウジカは、絶滅の危機に_img1.jpg,images/「シベリアジャコウジカは、絶滅の危機に_img2.jpg</t>
         </is>
       </c>
-      <c r="C713" t="inlineStr">
+      <c r="C712" t="inlineStr">
         <is>
           <t>手書き語学 ,シベリア</t>
         </is>
       </c>
     </row>
-    <row r="714">
-      <c r="A714" t="inlineStr">
+    <row r="713">
+      <c r="A713" t="inlineStr">
         <is>
           <t xml:space="preserve">「融合／折衷／フュージョン」
 انصهار
@@ -15471,38 +15450,38 @@
 1811 elmahdyart Instagram </t>
         </is>
       </c>
-      <c r="B714" t="inlineStr">
+      <c r="B713" t="inlineStr">
         <is>
           <t>images/「融合／折衷／フュージョン」_img1.jpg</t>
         </is>
       </c>
-      <c r="C714" t="inlineStr">
+      <c r="C713" t="inlineStr">
         <is>
           <t>カリグラフィー ,書道</t>
         </is>
       </c>
     </row>
-    <row r="715">
-      <c r="A715" t="inlineStr">
+    <row r="714">
+      <c r="A714" t="inlineStr">
         <is>
           <t xml:space="preserve">「この子供は、昼寝をしようとする母親を邪魔しているようだ」
 「場所はインドのトラ保護区、バンダウガル公園。トラは生態ピラミッドのトップの捕食動物だが、最もリスクの高い絶滅危惧種のひとつである」
 2308 https://twitter.com/natgeomagarab/status/1553681890665586689 </t>
         </is>
       </c>
-      <c r="B715" t="inlineStr">
+      <c r="B714" t="inlineStr">
         <is>
           <t>images/「この子供は、昼寝をしようとする母親を_img1.jpg,images/「この子供は、昼寝をしようとする母親を_img2.jpg</t>
         </is>
       </c>
-      <c r="C715" t="inlineStr">
+      <c r="C714" t="inlineStr">
         <is>
           <t>手書き語学 ,アラビア語 ,トラ</t>
         </is>
       </c>
     </row>
-    <row r="716">
-      <c r="A716" t="inlineStr">
+    <row r="715">
+      <c r="A715" t="inlineStr">
         <is>
           <t xml:space="preserve">「もし敬意が落ちたら、それと一緒に全部落ちるのだ」
 إن سقط الإحترام سقط معه كل شيء
@@ -15511,19 +15490,19 @@
 2109 出典不明 </t>
         </is>
       </c>
-      <c r="B716" t="inlineStr">
+      <c r="B715" t="inlineStr">
         <is>
           <t>images/「もし敬意が落ちたら、それと一緒に全部_img1.jpg</t>
         </is>
       </c>
-      <c r="C716" t="inlineStr">
+      <c r="C715" t="inlineStr">
         <is>
           <t>リスペクト ,落書き</t>
         </is>
       </c>
     </row>
-    <row r="717">
-      <c r="A717" t="inlineStr">
+    <row r="716">
+      <c r="A716" t="inlineStr">
         <is>
           <t xml:space="preserve">「エジプト特許庁」
 مكتب براءات الاختراع المصرى
@@ -15533,19 +15512,19 @@
 2312 </t>
         </is>
       </c>
-      <c r="B717" t="inlineStr">
+      <c r="B716" t="inlineStr">
         <is>
           <t>images/「エジプト特許庁」_img1.jpg</t>
         </is>
       </c>
-      <c r="C717" t="inlineStr">
+      <c r="C716" t="inlineStr">
         <is>
           <t>patent</t>
         </is>
       </c>
     </row>
-    <row r="718">
-      <c r="A718" t="inlineStr">
+    <row r="717">
+      <c r="A717" t="inlineStr">
         <is>
           <t xml:space="preserve">「選挙」إنتخابات
 インティカーバート [intiKhaabaat]
@@ -15554,19 +15533,19 @@
 2311 nna-leb gov lb </t>
         </is>
       </c>
-      <c r="B718" t="inlineStr">
+      <c r="B717" t="inlineStr">
         <is>
           <t>images/「選挙」_img1.jpg</t>
         </is>
       </c>
-      <c r="C718" t="inlineStr">
+      <c r="C717" t="inlineStr">
         <is>
           <t>選挙 ,投票</t>
         </is>
       </c>
     </row>
-    <row r="719">
-      <c r="A719" t="inlineStr">
+    <row r="718">
+      <c r="A718" t="inlineStr">
         <is>
           <t xml:space="preserve">「待ちぼうけ」إنتظار
 インティザール [inti_Dhaar]
@@ -15575,19 +15554,19 @@
 1809 in4sser.tumblr </t>
         </is>
       </c>
-      <c r="B719" t="inlineStr">
+      <c r="B718" t="inlineStr">
         <is>
           <t>images/「待ちぼうけ」_img1.jpg</t>
         </is>
       </c>
-      <c r="C719" t="inlineStr">
+      <c r="C718" t="inlineStr">
         <is>
           <t>遅すぎ ,辛抱</t>
         </is>
       </c>
     </row>
-    <row r="720">
-      <c r="A720" t="inlineStr">
+    <row r="719">
+      <c r="A719" t="inlineStr">
         <is>
           <t xml:space="preserve">「試験」إختبار
 イクティバール [iKhtibaar]
@@ -15596,19 +15575,19 @@
 2109 出典不明 </t>
         </is>
       </c>
-      <c r="B720" t="inlineStr">
+      <c r="B719" t="inlineStr">
         <is>
           <t>images/「試験」_img1.jpg</t>
         </is>
       </c>
-      <c r="C720" t="inlineStr">
+      <c r="C719" t="inlineStr">
         <is>
           <t>テスト ,考査</t>
         </is>
       </c>
     </row>
-    <row r="721">
-      <c r="A721" t="inlineStr">
+    <row r="720">
+      <c r="A720" t="inlineStr">
         <is>
           <t xml:space="preserve">「チャンネル登録」اشتراك
 イシティラーク [iShtiraak]
@@ -15617,19 +15596,19 @@
 2308 </t>
         </is>
       </c>
-      <c r="B721" t="inlineStr">
+      <c r="B720" t="inlineStr">
         <is>
           <t>images/「チャンネル登録」_img1.jpg</t>
         </is>
       </c>
-      <c r="C721" t="inlineStr">
+      <c r="C720" t="inlineStr">
         <is>
           <t>Subscribe ,YouTube</t>
         </is>
       </c>
     </row>
-    <row r="722">
-      <c r="A722" t="inlineStr">
+    <row r="721">
+      <c r="A721" t="inlineStr">
         <is>
           <t xml:space="preserve">「スマイル」ابتسام
 イブティサーム [ibtisaam]
@@ -15637,37 +15616,37 @@
 1903 behance Written-Visuals </t>
         </is>
       </c>
+      <c r="B721" t="inlineStr">
+        <is>
+          <t>images/「スマイル」_img1.jpg</t>
+        </is>
+      </c>
+      <c r="C721" t="inlineStr">
+        <is>
+          <t>スマイリー ,ツ</t>
+        </is>
+      </c>
+    </row>
+    <row r="722">
+      <c r="A722" t="inlineStr">
+        <is>
+          <t xml:space="preserve">「身体の一部として…」
+2308 https://twitter.com/NatGeoMagArab/status/1528292080337813504 </t>
+        </is>
+      </c>
       <c r="B722" t="inlineStr">
         <is>
-          <t>images/「スマイル」_img1.jpg</t>
+          <t>images/「身体の一部として…」_img1.jpg</t>
         </is>
       </c>
       <c r="C722" t="inlineStr">
         <is>
-          <t>スマイリー ,ツ</t>
+          <t>手書き語学 ,カンガルー</t>
         </is>
       </c>
     </row>
     <row r="723">
       <c r="A723" t="inlineStr">
-        <is>
-          <t xml:space="preserve">「身体の一部として…」
-2308 https://twitter.com/NatGeoMagArab/status/1528292080337813504 </t>
-        </is>
-      </c>
-      <c r="B723" t="inlineStr">
-        <is>
-          <t>images/「身体の一部として…」_img1.jpg</t>
-        </is>
-      </c>
-      <c r="C723" t="inlineStr">
-        <is>
-          <t>手書き語学 ,カンガルー</t>
-        </is>
-      </c>
-    </row>
-    <row r="724">
-      <c r="A724" t="inlineStr">
         <is>
           <t xml:space="preserve">「ディスカバリー」إكتشاف
 イクティシャーフ [iktiShaaf]
@@ -15675,19 +15654,19 @@
 2308 tephanegabrielli com </t>
         </is>
       </c>
-      <c r="B724" t="inlineStr">
+      <c r="B723" t="inlineStr">
         <is>
           <t>images/「ディスカバリー」_img1.jpg</t>
         </is>
       </c>
-      <c r="C724" t="inlineStr">
+      <c r="C723" t="inlineStr">
         <is>
           <t>discovery ,デザイン</t>
         </is>
       </c>
     </row>
-    <row r="725">
-      <c r="A725" t="inlineStr">
+    <row r="724">
+      <c r="A724" t="inlineStr">
         <is>
           <t xml:space="preserve">「重力波の発見は新しい窓を開いた」
 فتَح اكتشاف موجات الجاذبية نافذة جديدة
@@ -15695,19 +15674,19 @@
 2308 https://twitter.com/SciTalk2U/status/1454891943440289793 </t>
         </is>
       </c>
-      <c r="B725" t="inlineStr">
+      <c r="B724" t="inlineStr">
         <is>
           <t>images/「重力波の発見は新しい窓を開いた」_img1.jpg</t>
         </is>
       </c>
-      <c r="C725" t="inlineStr">
+      <c r="C724" t="inlineStr">
         <is>
           <t>手書き語学 ,アラビア語 ,重力波</t>
         </is>
       </c>
     </row>
-    <row r="726">
-      <c r="A726" t="inlineStr">
+    <row r="725">
+      <c r="A725" t="inlineStr">
         <is>
           <t xml:space="preserve">「微笑みに微笑み。先にした人の方が美しい」
 الإبتسامة بالإبتسامة والبادئ أجمل
@@ -15716,19 +15695,19 @@
 2104 出典不明 </t>
         </is>
       </c>
-      <c r="B726" t="inlineStr">
+      <c r="B725" t="inlineStr">
         <is>
           <t>images/「微笑みに微笑み。先にした人の方が美し_img1.jpg,images/「微笑みに微笑み。先にした人の方が美し_img2.jpg</t>
         </is>
       </c>
-      <c r="C726" t="inlineStr">
+      <c r="C725" t="inlineStr">
         <is>
           <t>スマイル ,名言</t>
         </is>
       </c>
     </row>
-    <row r="727">
-      <c r="A727" t="inlineStr">
+    <row r="726">
+      <c r="A726" t="inlineStr">
         <is>
           <t xml:space="preserve">「笑顔」ابتسامة
 イブティサーマ [ibtisaama(tun)]
@@ -15737,19 +15716,19 @@
 2308 satokomatsu, minne </t>
         </is>
       </c>
-      <c r="B727" t="inlineStr">
+      <c r="B726" t="inlineStr">
         <is>
           <t>images/「笑顔」_img1.jpg</t>
         </is>
       </c>
-      <c r="C727" t="inlineStr">
+      <c r="C726" t="inlineStr">
         <is>
           <t>スマイル ,ツ</t>
         </is>
       </c>
     </row>
-    <row r="728">
-      <c r="A728" t="inlineStr">
+    <row r="727">
+      <c r="A727" t="inlineStr">
         <is>
           <t xml:space="preserve">「信仰」ايمان
 イーマーン ['iimaan]
@@ -15758,19 +15737,19 @@
 2506 instagram com/p/6ST-WHOOkJ/ </t>
         </is>
       </c>
-      <c r="B728" t="inlineStr">
+      <c r="B727" t="inlineStr">
         <is>
           <t>images/「信仰」_img1.jpg</t>
         </is>
       </c>
-      <c r="C728" t="inlineStr">
+      <c r="C727" t="inlineStr">
         <is>
           <t>宗教 ,信念</t>
         </is>
       </c>
     </row>
-    <row r="729">
-      <c r="A729" t="inlineStr">
+    <row r="728">
+      <c r="A728" t="inlineStr">
         <is>
           <t xml:space="preserve">「放送」إذاعة
 イザーア ['iDhaa*a]
@@ -15779,19 +15758,19 @@
 2404 heemades, Instagram </t>
         </is>
       </c>
-      <c r="B729" t="inlineStr">
+      <c r="B728" t="inlineStr">
         <is>
           <t>images/「放送」_img1.jpg</t>
         </is>
       </c>
-      <c r="C729" t="inlineStr">
+      <c r="C728" t="inlineStr">
         <is>
           <t>デザイン ,ラジオ</t>
         </is>
       </c>
     </row>
-    <row r="730">
-      <c r="A730" t="inlineStr">
+    <row r="729">
+      <c r="A729" t="inlineStr">
         <is>
           <t xml:space="preserve">「かきとりのちから」
 مهاراتي الإملائية
@@ -15800,19 +15779,19 @@
 2308 iqrawaoktoub.wordpress com </t>
         </is>
       </c>
-      <c r="B730" t="inlineStr">
+      <c r="B729" t="inlineStr">
         <is>
           <t>images/「かきとりのちから」_img1.jpg</t>
         </is>
       </c>
-      <c r="C730" t="inlineStr">
+      <c r="C729" t="inlineStr">
         <is>
           <t>国語 ,教材</t>
         </is>
       </c>
     </row>
-    <row r="731">
-      <c r="A731" t="inlineStr">
+    <row r="730">
+      <c r="A730" t="inlineStr">
         <is>
           <t xml:space="preserve">「歴史を作った男たち」
 رجال صنعوا التاريخ
@@ -15822,38 +15801,38 @@
 2410 https://x.gd/Wl5rJ </t>
         </is>
       </c>
-      <c r="B731" t="inlineStr">
+      <c r="B730" t="inlineStr">
         <is>
           <t>images/「歴史を作った男たち」_img1.jpg</t>
         </is>
       </c>
-      <c r="C731" t="inlineStr">
+      <c r="C730" t="inlineStr">
         <is>
           <t>偉人</t>
         </is>
       </c>
     </row>
-    <row r="732">
-      <c r="A732" t="inlineStr">
+    <row r="731">
+      <c r="A731" t="inlineStr">
         <is>
           <t xml:space="preserve">「無限の宇宙を旅した光」
 「何百年もの末にジェイムズ・ウェッブ望遠鏡のレンズの上に落ち、我々に遠い宇宙の美しさを見せてくれる。最も純粋な形と最も素晴らしい姿で」
 2308 https://twitter.com/NatGeoMagArab/status/1557811592636485632 </t>
         </is>
       </c>
-      <c r="B732" t="inlineStr">
+      <c r="B731" t="inlineStr">
         <is>
           <t>images/「無限の宇宙を旅した光」_img1.jpg</t>
         </is>
       </c>
-      <c r="C732" t="inlineStr">
+      <c r="C731" t="inlineStr">
         <is>
           <t>手書き語学 ,宇宙</t>
         </is>
       </c>
     </row>
-    <row r="733">
-      <c r="A733" t="inlineStr">
+    <row r="732">
+      <c r="A732" t="inlineStr">
         <is>
           <t xml:space="preserve">「日本好きになり行きたくなる20項」
 عشرون شيئا يجعلك تحب اليابان وترغب في زيارتها
@@ -15862,19 +15841,19 @@
 2308 wattpad </t>
         </is>
       </c>
-      <c r="B733" t="inlineStr">
+      <c r="B732" t="inlineStr">
         <is>
           <t>images/「日本好きになり行きたくなる20項」_img1.jpg</t>
         </is>
       </c>
-      <c r="C733" t="inlineStr">
+      <c r="C732" t="inlineStr">
         <is>
           <t>اليابان ,Japan</t>
         </is>
       </c>
     </row>
-    <row r="734">
-      <c r="A734" t="inlineStr">
+    <row r="733">
+      <c r="A733" t="inlineStr">
         <is>
           <t xml:space="preserve">「ピッタリの瞬間に撮影され、ドラゴンが火を噴いているように見える」
 التُقطت في اللحظة المناسبة لتبدو مثل تنين ينفث اللهب
@@ -15882,19 +15861,19 @@
 2509 https://twitter.com/NatGeoMagArab/status/1588780660269150208 </t>
         </is>
       </c>
-      <c r="B734" t="inlineStr">
+      <c r="B733" t="inlineStr">
         <is>
           <t>images/「ピッタリの瞬間に撮影され、ドラゴンが_img1.jpg,images/ 「ピッタリの瞬間に撮影され、ドラゴンが_img2.jpg</t>
         </is>
       </c>
-      <c r="C734" t="inlineStr">
+      <c r="C733" t="inlineStr">
         <is>
           <t xml:space="preserve">ドラゴン </t>
         </is>
       </c>
     </row>
-    <row r="735">
-      <c r="A735" t="inlineStr">
+    <row r="734">
+      <c r="A734" t="inlineStr">
         <is>
           <t xml:space="preserve">「満足は不滅の宝である」
 القَناعَةُ كنز لا يَفنَى
@@ -15904,55 +15883,55 @@
 2308 kareem mrghani </t>
         </is>
       </c>
+      <c r="B734" t="inlineStr">
+        <is>
+          <t>images/「満足は不滅の宝である」_img1.jpg</t>
+        </is>
+      </c>
+      <c r="C734" t="inlineStr">
+        <is>
+          <t>幸福度</t>
+        </is>
+      </c>
+    </row>
+    <row r="735">
+      <c r="A735" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ゴシキセイガイインコ。
+2409 https://twitter.com/NatGeoMagArab/status/1600022262014676992 </t>
+        </is>
+      </c>
       <c r="B735" t="inlineStr">
         <is>
-          <t>images/「満足は不滅の宝である」_img1.jpg</t>
+          <t>images/ゴシキセイガイインコ。_img1.jpg</t>
         </is>
       </c>
       <c r="C735" t="inlineStr">
         <is>
-          <t>幸福度</t>
+          <t>手書き語学 ,アラビア語,オウム</t>
         </is>
       </c>
     </row>
     <row r="736">
       <c r="A736" t="inlineStr">
         <is>
-          <t xml:space="preserve">ゴシキセイガイインコ。
-2409 https://twitter.com/NatGeoMagArab/status/1600022262014676992 </t>
+          <t xml:space="preserve">モモンガ。
+2403 https://twitter.com/NatGeoMagArab/status/1552541872966344704 </t>
         </is>
       </c>
       <c r="B736" t="inlineStr">
         <is>
-          <t>images/ゴシキセイガイインコ。_img1.jpg</t>
+          <t>images/モモンガ。_img1.jpg,images/ モモンガ。_img2.jpg</t>
         </is>
       </c>
       <c r="C736" t="inlineStr">
         <is>
-          <t>手書き語学 ,アラビア語,オウム</t>
+          <t>手書き語学 ,アラビア語 ,モモンガ</t>
         </is>
       </c>
     </row>
     <row r="737">
       <c r="A737" t="inlineStr">
-        <is>
-          <t xml:space="preserve">モモンガ。
-2403 https://twitter.com/NatGeoMagArab/status/1552541872966344704 </t>
-        </is>
-      </c>
-      <c r="B737" t="inlineStr">
-        <is>
-          <t>images/モモンガ。_img1.jpg,images/ モモンガ。_img2.jpg</t>
-        </is>
-      </c>
-      <c r="C737" t="inlineStr">
-        <is>
-          <t>手書き語学 ,アラビア語 ,モモンガ</t>
-        </is>
-      </c>
-    </row>
-    <row r="738">
-      <c r="A738" t="inlineStr">
         <is>
           <t xml:space="preserve">「象の群れ。ドローンの音から逃げている」
 قطيع من الفيلة يفر هاربًا من صوت الدرون
@@ -15964,56 +15943,56 @@
 2009 https://twitter.com/NatGeoMagArab/status/1302970033627258881 </t>
         </is>
       </c>
+      <c r="B737" t="inlineStr">
+        <is>
+          <t>images/「象の群れ。ドローンの音から逃げている.jpg</t>
+        </is>
+      </c>
+      <c r="C737" t="inlineStr">
+        <is>
+          <t>ゾウ ,ドローン</t>
+        </is>
+      </c>
+    </row>
+    <row r="738">
+      <c r="A738" t="inlineStr">
+        <is>
+          <t xml:space="preserve">カルマン線。
+2308 https://twitter.com/NatGeoMagArab/status/1536436999522881536 </t>
+        </is>
+      </c>
       <c r="B738" t="inlineStr">
         <is>
-          <t>images/「象の群れ。ドローンの音から逃げている.jpg</t>
+          <t>images/カルマン線。_img1.jpg</t>
         </is>
       </c>
       <c r="C738" t="inlineStr">
         <is>
-          <t>ゾウ ,ドローン</t>
+          <t xml:space="preserve">手書き語学 ,アラビア語 ,宇宙 </t>
         </is>
       </c>
     </row>
     <row r="739">
       <c r="A739" t="inlineStr">
-        <is>
-          <t xml:space="preserve">カルマン線。
-2308 https://twitter.com/NatGeoMagArab/status/1536436999522881536 </t>
-        </is>
-      </c>
-      <c r="B739" t="inlineStr">
-        <is>
-          <t>images/カルマン線。_img1.jpg</t>
-        </is>
-      </c>
-      <c r="C739" t="inlineStr">
-        <is>
-          <t xml:space="preserve">手書き語学 ,アラビア語 ,宇宙 </t>
-        </is>
-      </c>
-    </row>
-    <row r="740">
-      <c r="A740" t="inlineStr">
         <is>
           <t xml:space="preserve">「恥ずかしがり屋のマヌルネコと暖かい朝の太陽光線」
 ⁦「二つの美しいもの」[Shay'-ayni jamiil-ayni] 属格：「物」( شيء )[Shay']・「美しい」( جميل )[jamiil]⁩
 2309 https://twitter.com/NatGeoMagArab/status/1697512148820504912 </t>
         </is>
       </c>
-      <c r="B740" t="inlineStr">
+      <c r="B739" t="inlineStr">
         <is>
           <t>images/「恥ずかしがり屋のマヌルネコと暖かい朝_img1.jpg</t>
         </is>
       </c>
-      <c r="C740" t="inlineStr">
+      <c r="C739" t="inlineStr">
         <is>
           <t>手書き語学 ,アラビア語 ,マヌルネコ</t>
         </is>
       </c>
     </row>
-    <row r="741">
-      <c r="A741" t="inlineStr">
+    <row r="740">
+      <c r="A740" t="inlineStr">
         <is>
           <t xml:space="preserve">「二回失敗しているペンギン」
 بطريق يفشل مرتين
@@ -16023,19 +16002,19 @@
 2308 https://twitter.com/NatGeoMagArab/status/1479483133766426626 </t>
         </is>
       </c>
-      <c r="B741" t="inlineStr">
+      <c r="B740" t="inlineStr">
         <is>
           <t>images/「二回失敗しているペンギン」_img1.jpg</t>
         </is>
       </c>
-      <c r="C741" t="inlineStr">
+      <c r="C740" t="inlineStr">
         <is>
           <t>ペンギン ,動物</t>
         </is>
       </c>
     </row>
-    <row r="742">
-      <c r="A742" t="inlineStr">
+    <row r="741">
+      <c r="A741" t="inlineStr">
         <is>
           <t xml:space="preserve">「2億光年の彼方できらめく炎と光」
 وهج ووميض يتلألأ على بعد 200 مليون سنة ضوئية
@@ -16046,15 +16025,15 @@
 2010 https://twitter.com/NatGeoMagArab/status/1303415502673342464 </t>
         </is>
       </c>
-      <c r="B742" t="inlineStr"/>
-      <c r="C742" t="inlineStr">
+      <c r="B741" t="inlineStr"/>
+      <c r="C741" t="inlineStr">
         <is>
           <t>宇宙 ,銀河</t>
         </is>
       </c>
     </row>
-    <row r="743">
-      <c r="A743" t="inlineStr">
+    <row r="742">
+      <c r="A742" t="inlineStr">
         <is>
           <t xml:space="preserve">「さまよう黒猫」قطة سوداء تجوب
 キッタトゥン・サウダーウ・タジューブ [qi^_tatun sawdaa'u ta-juub]
@@ -16063,19 +16042,19 @@
 2308 https://twitter.com/NatGeoMagArab/status/1532973177453760512 </t>
         </is>
       </c>
-      <c r="B743" t="inlineStr">
+      <c r="B742" t="inlineStr">
         <is>
           <t>images/「さまよう黒猫」_img1.jpg,images/ 「さまよう黒猫」_img2.jpg</t>
         </is>
       </c>
-      <c r="C743" t="inlineStr">
+      <c r="C742" t="inlineStr">
         <is>
           <t xml:space="preserve">手書き語学 ,モロッコ </t>
         </is>
       </c>
     </row>
-    <row r="744">
-      <c r="A744" t="inlineStr">
+    <row r="743">
+      <c r="A743" t="inlineStr">
         <is>
           <t xml:space="preserve">「サイのざらざらした皮を利用して自分の体を掻くネコ」
 قطة تستغل جلد الكركدن الخشن لحك جسدها
@@ -16084,19 +16063,19 @@
 2308 https://twitter.com/NatGeoMagArab/status/1476855740929216517 </t>
         </is>
       </c>
-      <c r="B744" t="inlineStr">
+      <c r="B743" t="inlineStr">
         <is>
           <t>images/「サイのざらざらした皮を利用して自分の_img1.jpg</t>
         </is>
       </c>
-      <c r="C744" t="inlineStr">
+      <c r="C743" t="inlineStr">
         <is>
           <t>サイ ,チェコ</t>
         </is>
       </c>
     </row>
-    <row r="745">
-      <c r="A745" t="inlineStr">
+    <row r="744">
+      <c r="A744" t="inlineStr">
         <is>
           <t xml:space="preserve">「沈まぬ太陽」شمس لا تغيب
 シャムス・ラー・タギーブ [Shams laa ta-Ghiib]
@@ -16105,19 +16084,19 @@
 2308 AHMED ELASSAL </t>
         </is>
       </c>
-      <c r="B745" t="inlineStr">
+      <c r="B744" t="inlineStr">
         <is>
           <t>images/「沈まぬ太陽」_img1.jpg</t>
         </is>
       </c>
-      <c r="C745" t="inlineStr">
+      <c r="C744" t="inlineStr">
         <is>
           <t>帝国 ,白夜</t>
         </is>
       </c>
     </row>
-    <row r="746">
-      <c r="A746" t="inlineStr">
+    <row r="745">
+      <c r="A745" t="inlineStr">
         <is>
           <t xml:space="preserve">「子供に食べさせている忍耐強い母親」
 أم صبورة تطعم صغيرها
@@ -16126,19 +16105,19 @@
 2308 https://twitter.com/natgeomagarab/status/1585572054509957120 </t>
         </is>
       </c>
-      <c r="B746" t="inlineStr">
+      <c r="B745" t="inlineStr">
         <is>
           <t>images/「子供に食べさせている忍耐強い母親」_img1.jpg</t>
         </is>
       </c>
-      <c r="C746" t="inlineStr">
+      <c r="C745" t="inlineStr">
         <is>
           <t>手書き語学 ,アラビア語 ,ミヤコドリ</t>
         </is>
       </c>
     </row>
-    <row r="747">
-      <c r="A747" t="inlineStr">
+    <row r="746">
+      <c r="A746" t="inlineStr">
         <is>
           <t xml:space="preserve">「コーヒーは繰り返さない恋物語」
 القهوة قصة عشق لن تتكرر
@@ -16148,19 +16127,19 @@
 2403 pin it/7tvd8Wc </t>
         </is>
       </c>
-      <c r="B747" t="inlineStr">
+      <c r="B746" t="inlineStr">
         <is>
           <t>images/「コーヒーは繰り返さない恋物語」_img1.jpg</t>
         </is>
       </c>
-      <c r="C747" t="inlineStr">
+      <c r="C746" t="inlineStr">
         <is>
           <t>コーヒー ,名言</t>
         </is>
       </c>
     </row>
-    <row r="748">
-      <c r="A748" t="inlineStr">
+    <row r="747">
+      <c r="A747" t="inlineStr">
         <is>
           <t xml:space="preserve">「星々で飾られた空。魅惑的な色合いで黄昏の美を満たしている」
 سماء مرصعة بالنجوم تضفي لمسة سحرية على جمال الشفق
@@ -16168,19 +16147,19 @@
 2010 https://twitter.com/NatGeoMagArab/status/1303777701975584768 </t>
         </is>
       </c>
-      <c r="B748" t="inlineStr">
+      <c r="B747" t="inlineStr">
         <is>
           <t>images/「星々で飾られた空。魅惑的な色合いで黄.png</t>
         </is>
       </c>
-      <c r="C748" t="inlineStr">
+      <c r="C747" t="inlineStr">
         <is>
           <t>星空 ,宇宙</t>
         </is>
       </c>
     </row>
-    <row r="749">
-      <c r="A749" t="inlineStr">
+    <row r="748">
+      <c r="A748" t="inlineStr">
         <is>
           <t xml:space="preserve">「国際宇宙ステーションからの写真。巨大な台風『ハイシェン（海神）』を映している」
 لقطات من محطة الفضاء الدولية تظهر إعصار "هايشن" الهائل
@@ -16188,19 +16167,19 @@
 2403 https://twitter.com/NatGeoMagArab/status/1302871968522235904 </t>
         </is>
       </c>
-      <c r="B749" t="inlineStr">
+      <c r="B748" t="inlineStr">
         <is>
           <t>images/「国際宇宙ステーションからの写真。巨大.png</t>
         </is>
       </c>
-      <c r="C749" t="inlineStr">
+      <c r="C748" t="inlineStr">
         <is>
           <t>台風</t>
         </is>
       </c>
     </row>
-    <row r="750">
-      <c r="A750" t="inlineStr">
+    <row r="749">
+      <c r="A749" t="inlineStr">
         <is>
           <t xml:space="preserve">「草を食む幸運な子羊たち」
 خراف محظوظة ترعى
@@ -16210,19 +16189,19 @@
 2308 https://twitter.com/NatGeoMagArab/status/1490211393554972676 </t>
         </is>
       </c>
-      <c r="B750" t="inlineStr">
+      <c r="B749" t="inlineStr">
         <is>
           <t>images/「草を食む幸運な子羊たち」_img1.jpg,images/ 「草を食む幸運な子羊たち」_img2.jpg</t>
         </is>
       </c>
-      <c r="C750" t="inlineStr">
+      <c r="C749" t="inlineStr">
         <is>
           <t>羊 ,アイルランド</t>
         </is>
       </c>
     </row>
-    <row r="751">
-      <c r="A751" t="inlineStr">
+    <row r="750">
+      <c r="A750" t="inlineStr">
         <is>
           <t xml:space="preserve">「お金で買えぬ10のもの」
 ١٠ أشياء لا تشترى بالمال
@@ -16232,19 +16211,19 @@
 2308 ayb124 </t>
         </is>
       </c>
-      <c r="B751" t="inlineStr">
+      <c r="B750" t="inlineStr">
         <is>
           <t>images/「お金で買えぬ10のもの」_img1.jpg</t>
         </is>
       </c>
-      <c r="C751" t="inlineStr">
+      <c r="C750" t="inlineStr">
         <is>
           <t>価値 ,購買</t>
         </is>
       </c>
     </row>
-    <row r="752">
-      <c r="A752" t="inlineStr">
+    <row r="751">
+      <c r="A751" t="inlineStr">
         <is>
           <t xml:space="preserve">「お金では買えないよ」
 هي أشْيَاءٌ لا تُشْتَرَى
@@ -16254,19 +16233,19 @@
 1906 mardy_zaawely, Instagram </t>
         </is>
       </c>
-      <c r="B752" t="inlineStr">
+      <c r="B751" t="inlineStr">
         <is>
           <t>images/「お金では買えないよ」_img1.jpg</t>
         </is>
       </c>
-      <c r="C752" t="inlineStr">
+      <c r="C751" t="inlineStr">
         <is>
           <t>マスターカード ,価値</t>
         </is>
       </c>
     </row>
-    <row r="753">
-      <c r="A753" t="inlineStr">
+    <row r="752">
+      <c r="A752" t="inlineStr">
         <is>
           <t xml:space="preserve">「好奇心旺盛なホッキョクギツネ」
 ثعلب قطبي يملؤه الفضول
@@ -16276,15 +16255,15 @@
 2308 https://twitter.com/natgeomagarab/status/1157592172968808449 </t>
         </is>
       </c>
-      <c r="B753" t="inlineStr"/>
-      <c r="C753" t="inlineStr">
+      <c r="B752" t="inlineStr"/>
+      <c r="C752" t="inlineStr">
         <is>
           <t>ファーストコンタクト ,キツネ</t>
         </is>
       </c>
     </row>
-    <row r="754">
-      <c r="A754" t="inlineStr">
+    <row r="753">
+      <c r="A753" t="inlineStr">
         <is>
           <t xml:space="preserve">「グレンダイザーのいる国は死にません」
 لنْ يَموتَ شَعبٌ لدَيهِ غرندايزر
@@ -16293,56 +16272,56 @@
 2308 https://www.aljarida.com/articles/1462241741574732100/ </t>
         </is>
       </c>
+      <c r="B753" t="inlineStr">
+        <is>
+          <t>images/「グレンダイザーのいる国は死にません」_img1.jpg</t>
+        </is>
+      </c>
+      <c r="C753" t="inlineStr">
+        <is>
+          <t>UFOロボ ,アニメ</t>
+        </is>
+      </c>
+    </row>
+    <row r="754">
+      <c r="A754" t="inlineStr">
+        <is>
+          <t xml:space="preserve">「凍結路面を運転中、彼女は嫌な場面に居合わせた」
+2408 https://twitter.com/NatGeoMagArab/status/1610305209657626625 </t>
+        </is>
+      </c>
       <c r="B754" t="inlineStr">
         <is>
-          <t>images/「グレンダイザーのいる国は死にません」_img1.jpg</t>
+          <t>images/「凍結路面を運転中、彼女は嫌な場面に居_img1.jpg</t>
         </is>
       </c>
       <c r="C754" t="inlineStr">
         <is>
-          <t>UFOロボ ,アニメ</t>
+          <t>手書き語学 ,アラビア語 ,路面凍結</t>
         </is>
       </c>
     </row>
     <row r="755">
       <c r="A755" t="inlineStr">
-        <is>
-          <t xml:space="preserve">「凍結路面を運転中、彼女は嫌な場面に居合わせた」
-2408 https://twitter.com/NatGeoMagArab/status/1610305209657626625 </t>
-        </is>
-      </c>
-      <c r="B755" t="inlineStr">
-        <is>
-          <t>images/「凍結路面を運転中、彼女は嫌な場面に居_img1.jpg</t>
-        </is>
-      </c>
-      <c r="C755" t="inlineStr">
-        <is>
-          <t>手書き語学 ,アラビア語 ,路面凍結</t>
-        </is>
-      </c>
-    </row>
-    <row r="756">
-      <c r="A756" t="inlineStr">
         <is>
           <t xml:space="preserve">「虹が美しさを加えている、アルパカという動物の美しいショット」
 ⁦「美しいショット」[laq_tatun jamiilatun]：「ショット」( لقطة )[laq_ta]：( ـلٌ )[-lun]・( ـقٌ )[-qun]・( ـطٌ )[-_tun]・( ـةٌ )[-tun]⁩
 2308 https://twitter.com/natgeomagarab/status/1155115655928004608 </t>
         </is>
       </c>
-      <c r="B756" t="inlineStr">
+      <c r="B755" t="inlineStr">
         <is>
           <t>images/「虹が美しさを加えている、アルパカとい_img1.jpg</t>
         </is>
       </c>
-      <c r="C756" t="inlineStr">
+      <c r="C755" t="inlineStr">
         <is>
           <t>モフモフ ,アルパカ</t>
         </is>
       </c>
     </row>
-    <row r="757">
-      <c r="A757" t="inlineStr">
+    <row r="756">
+      <c r="A756" t="inlineStr">
         <is>
           <t xml:space="preserve">「幸せは…全然思いもよらない所からやって来る」
 السعادة تأتينا من أماكن لم نكن نتوقعها أبداً
@@ -16351,19 +16330,19 @@
 2109 出典不明 </t>
         </is>
       </c>
-      <c r="B757" t="inlineStr">
+      <c r="B756" t="inlineStr">
         <is>
           <t>images/「幸せは…全然思いもよらない所からやっ_img1.jpg,images/ 「幸せは…全然思いもよらない所からやっ_img2.jpg</t>
         </is>
       </c>
-      <c r="C757" t="inlineStr">
+      <c r="C756" t="inlineStr">
         <is>
           <t>訪れ ,予想</t>
         </is>
       </c>
     </row>
-    <row r="758">
-      <c r="A758" t="inlineStr">
+    <row r="757">
+      <c r="A757" t="inlineStr">
         <is>
           <t xml:space="preserve">「あらゆる問題は、食べ物が解決してくれる」
 كل مشكلة ولها أكلة تحلها
@@ -16372,19 +16351,19 @@
 1909 ALQA AN 878 </t>
         </is>
       </c>
-      <c r="B758" t="inlineStr">
+      <c r="B757" t="inlineStr">
         <is>
           <t>images/「あらゆる問題は、食べ物が解決してくれ_img1.jpg</t>
         </is>
       </c>
-      <c r="C758" t="inlineStr">
+      <c r="C757" t="inlineStr">
         <is>
           <t>ストレス ,精神</t>
         </is>
       </c>
     </row>
-    <row r="759">
-      <c r="A759" t="inlineStr">
+    <row r="758">
+      <c r="A758" t="inlineStr">
         <is>
           <t xml:space="preserve">「冬で私が好きな物」
 أشياء أحبها بالشتاء
@@ -16394,19 +16373,19 @@
 2109 出典不明 </t>
         </is>
       </c>
-      <c r="B759" t="inlineStr">
+      <c r="B758" t="inlineStr">
         <is>
           <t>images/「冬で私が好きな物」_img1.jpg</t>
         </is>
       </c>
-      <c r="C759" t="inlineStr">
+      <c r="C758" t="inlineStr">
         <is>
           <t>季節 ,冬</t>
         </is>
       </c>
     </row>
-    <row r="760">
-      <c r="A760" t="inlineStr">
+    <row r="759">
+      <c r="A759" t="inlineStr">
         <is>
           <t xml:space="preserve">「お金で買うことの出来ない物」
 أشياء لا تستطيع شراءها بالمال
@@ -16416,19 +16395,19 @@
 2409 https://x.com/akhbarak/status/1038402708414373888 </t>
         </is>
       </c>
-      <c r="B760" t="inlineStr">
+      <c r="B759" t="inlineStr">
         <is>
           <t>images/「お金で買うことの出来ない物」_img1.jpg,images/ 「お金で買うことの出来ない物」_img2.jpg</t>
         </is>
       </c>
-      <c r="C760" t="inlineStr">
+      <c r="C759" t="inlineStr">
         <is>
           <t>ショッピング ,価値</t>
         </is>
       </c>
     </row>
-    <row r="761">
-      <c r="A761" t="inlineStr">
+    <row r="760">
+      <c r="A760" t="inlineStr">
         <is>
           <t xml:space="preserve">「私たちが愛する言葉」
 كلماتٌ نُحبّها
@@ -16438,19 +16417,19 @@
 2109 جليل خزعل </t>
         </is>
       </c>
-      <c r="B761" t="inlineStr">
+      <c r="B760" t="inlineStr">
         <is>
           <t>images/「私たちが愛する言葉」_img1.jpg</t>
         </is>
       </c>
-      <c r="C761" t="inlineStr">
+      <c r="C760" t="inlineStr">
         <is>
           <t>花 ,贈り物</t>
         </is>
       </c>
     </row>
-    <row r="762">
-      <c r="A762" t="inlineStr">
+    <row r="761">
+      <c r="A761" t="inlineStr">
         <is>
           <t xml:space="preserve">「お茶についてあなたが知らない10の事実」
 عشر معلومات لا تعرفها عن الشاي
@@ -16459,19 +16438,19 @@
 2012 http://ara.tv/6syq2 </t>
         </is>
       </c>
-      <c r="B762" t="inlineStr">
+      <c r="B761" t="inlineStr">
         <is>
           <t>images/「お茶についてあなたが知らない10の事_img1.jpg</t>
         </is>
       </c>
-      <c r="C762" t="inlineStr">
+      <c r="C761" t="inlineStr">
         <is>
           <t>神農</t>
         </is>
       </c>
     </row>
-    <row r="763">
-      <c r="A763" t="inlineStr">
+    <row r="762">
+      <c r="A762" t="inlineStr">
         <is>
           <t xml:space="preserve">「大きくなったウソ」
 الكذبة الّتي كبرت
@@ -16481,19 +16460,19 @@
 2509 سلسلة الحلزونة </t>
         </is>
       </c>
-      <c r="B763" t="inlineStr">
+      <c r="B762" t="inlineStr">
         <is>
           <t>images/「大きくなったウソ」_img1.jpg</t>
         </is>
       </c>
-      <c r="C763" t="inlineStr">
+      <c r="C762" t="inlineStr">
         <is>
           <t>絵本</t>
         </is>
       </c>
     </row>
-    <row r="764">
-      <c r="A764" t="inlineStr">
+    <row r="763">
+      <c r="A763" t="inlineStr">
         <is>
           <t xml:space="preserve">「自分に合った掃除機を買うには？」
 كيف تشتري المكنسة الكهربائية التي تناسبك؟
@@ -16502,19 +16481,19 @@
 2106 ts3a com </t>
         </is>
       </c>
-      <c r="B764" t="inlineStr">
+      <c r="B763" t="inlineStr">
         <is>
           <t>images/「自分に合った掃除機を買うには？」_img1.jpg</t>
         </is>
       </c>
-      <c r="C764" t="inlineStr">
+      <c r="C763" t="inlineStr">
         <is>
           <t>家電 ,掃除</t>
         </is>
       </c>
     </row>
-    <row r="765">
-      <c r="A765" t="inlineStr">
+    <row r="764">
+      <c r="A764" t="inlineStr">
         <is>
           <t xml:space="preserve">「仮にこれが批判の数としよう」
 لنفرض ان عدد الذين ينتقدونك
@@ -16525,19 +16504,19 @@
 2504 出典不明 </t>
         </is>
       </c>
-      <c r="B765" t="inlineStr">
+      <c r="B764" t="inlineStr">
         <is>
           <t>images/「仮にこれが批判の数としよう」_img1.jpg</t>
         </is>
       </c>
-      <c r="C765" t="inlineStr">
+      <c r="C764" t="inlineStr">
         <is>
           <t>アンチ</t>
         </is>
       </c>
     </row>
-    <row r="766">
-      <c r="A766" t="inlineStr">
+    <row r="765">
+      <c r="A765" t="inlineStr">
         <is>
           <t xml:space="preserve">「ここに見えるのは何？」
 ما الذي تراه هنا؟
@@ -16547,15 +16526,15 @@
 2204 https://twitter.com/NatGeoMagArab/status/1506933850617700352 </t>
         </is>
       </c>
-      <c r="B766" t="inlineStr"/>
-      <c r="C766" t="inlineStr">
+      <c r="B765" t="inlineStr"/>
+      <c r="C765" t="inlineStr">
         <is>
           <t xml:space="preserve">ペンギン </t>
         </is>
       </c>
     </row>
-    <row r="767">
-      <c r="A767" t="inlineStr">
+    <row r="766">
+      <c r="A766" t="inlineStr">
         <is>
           <t xml:space="preserve">「今日辛いこと、明日は平気だろう」
 ما يؤلم اليوم سيهون غدًا
@@ -16565,19 +16544,19 @@
 2308 basmahjeff </t>
         </is>
       </c>
-      <c r="B767" t="inlineStr">
+      <c r="B766" t="inlineStr">
         <is>
           <t>images/「今日辛いこと、明日は平気だろう」_img1.jpg</t>
         </is>
       </c>
-      <c r="C767" t="inlineStr">
+      <c r="C766" t="inlineStr">
         <is>
           <t>悩み ,達観</t>
         </is>
       </c>
     </row>
-    <row r="768">
-      <c r="A768" t="inlineStr">
+    <row r="767">
+      <c r="A767" t="inlineStr">
         <is>
           <t xml:space="preserve">「自分のすることを好きでなきゃ」
 عليك أن تحب ما تفعل
@@ -16586,19 +16565,19 @@
 1810 Ahmed Elhakeem </t>
         </is>
       </c>
-      <c r="B768" t="inlineStr">
+      <c r="B767" t="inlineStr">
         <is>
           <t>images/「自分のすることを好きでなきゃ」_img1.jpg</t>
         </is>
       </c>
-      <c r="C768" t="inlineStr">
+      <c r="C767" t="inlineStr">
         <is>
           <t>転職 ,かわいい</t>
         </is>
       </c>
     </row>
-    <row r="769">
-      <c r="A769" t="inlineStr">
+    <row r="768">
+      <c r="A768" t="inlineStr">
         <is>
           <t xml:space="preserve">「この地上に生き甲斐あり」
 على هذه الأرض ما يستحق الحياة
@@ -16608,19 +16587,19 @@
 2308 Mahmoud Gafar </t>
         </is>
       </c>
-      <c r="B769" t="inlineStr">
+      <c r="B768" t="inlineStr">
         <is>
           <t>images/「この地上に生き甲斐あり」_img1.jpg</t>
         </is>
       </c>
-      <c r="C769" t="inlineStr">
+      <c r="C768" t="inlineStr">
         <is>
           <t>詩</t>
         </is>
       </c>
     </row>
-    <row r="770">
-      <c r="A770" t="inlineStr">
+    <row r="769">
+      <c r="A769" t="inlineStr">
         <is>
           <t xml:space="preserve">「おそらく、あなたの求めるものはあるだろう」
 لعلَّ ما تَرجوهُ سيَكونُ
@@ -16630,19 +16609,19 @@
 2308 PIXEL Instagram </t>
         </is>
       </c>
-      <c r="B770" t="inlineStr">
+      <c r="B769" t="inlineStr">
         <is>
           <t>images/「おそらく、あなたの求めるものはあるだ_img1.jpg</t>
         </is>
       </c>
-      <c r="C770" t="inlineStr">
+      <c r="C769" t="inlineStr">
         <is>
           <t>願い ,信仰</t>
         </is>
       </c>
     </row>
-    <row r="771">
-      <c r="A771" t="inlineStr">
+    <row r="770">
+      <c r="A770" t="inlineStr">
         <is>
           <t xml:space="preserve">「オレンジの効能が何か知っていますか？」
 هل تعرف ما هي فوائد البرتقال؟
@@ -16652,19 +16631,19 @@
 2308 sadahadhramowt com </t>
         </is>
       </c>
-      <c r="B771" t="inlineStr">
+      <c r="B770" t="inlineStr">
         <is>
           <t>images/「オレンジの効能が何か知っていますか？_img1.jpg</t>
         </is>
       </c>
-      <c r="C771" t="inlineStr">
+      <c r="C770" t="inlineStr">
         <is>
           <t>オレンジ ,フルーツ</t>
         </is>
       </c>
     </row>
-    <row r="772">
-      <c r="A772" t="inlineStr">
+    <row r="771">
+      <c r="A771" t="inlineStr">
         <is>
           <t xml:space="preserve">「遊ぶパンダの光景より可愛いものがありますか？」
 هل هناك ما هو ألطف من مشاهدة الباندا وهي تلعب؟
@@ -16672,19 +16651,19 @@
 2308 https://twitter.com/NatGeoMagArab/status/1494612797858074626 </t>
         </is>
       </c>
-      <c r="B772" t="inlineStr">
+      <c r="B771" t="inlineStr">
         <is>
           <t>images/「遊ぶパンダの光景より可愛いものがあり_img1.jpg</t>
         </is>
       </c>
-      <c r="C772" t="inlineStr">
+      <c r="C771" t="inlineStr">
         <is>
           <t>パンダ ,モコモコ</t>
         </is>
       </c>
     </row>
-    <row r="773">
-      <c r="A773" t="inlineStr">
+    <row r="772">
+      <c r="A772" t="inlineStr">
         <is>
           <t xml:space="preserve">「大事なのは何者だったかじゃない。何者になるかだ」
 ليسَ المُهم ما كُنتَ بل مَا ستكون
@@ -16693,19 +16672,19 @@
 2308 出典不明 </t>
         </is>
       </c>
-      <c r="B773" t="inlineStr">
+      <c r="B772" t="inlineStr">
         <is>
           <t>images/「大事なのは何者だったかじゃない。何者_img1.jpg</t>
         </is>
       </c>
-      <c r="C773" t="inlineStr">
+      <c r="C772" t="inlineStr">
         <is>
           <t>自己実現 ,存在価値</t>
         </is>
       </c>
     </row>
-    <row r="774">
-      <c r="A774" t="inlineStr">
+    <row r="773">
+      <c r="A773" t="inlineStr">
         <is>
           <t xml:space="preserve">「あなたであれ。ありのままが美しいから」
 كُنْ أَنْتَ لأنك جميل كما أنت
@@ -16714,19 +16693,19 @@
 2308 IDREES DESIGN </t>
         </is>
       </c>
-      <c r="B774" t="inlineStr">
+      <c r="B773" t="inlineStr">
         <is>
           <t>images/「あなたであれ。ありのままが美しいから_img1.jpg</t>
         </is>
       </c>
-      <c r="C774" t="inlineStr">
+      <c r="C773" t="inlineStr">
         <is>
           <t>自己肯定 ,BeYourself</t>
         </is>
       </c>
     </row>
-    <row r="775">
-      <c r="A775" t="inlineStr">
+    <row r="774">
+      <c r="A774" t="inlineStr">
         <is>
           <t xml:space="preserve">「恐れの中に生きる者は決して自由になれない」
 من يعش في خوف لن يكون حرا أبدا
@@ -16735,19 +16714,19 @@
 2111 rjeem com </t>
         </is>
       </c>
-      <c r="B775" t="inlineStr">
+      <c r="B774" t="inlineStr">
         <is>
           <t>images/「恐れの中に生きる者は決して自由になれ_img1.jpg,images/ 「恐れの中に生きる者は決して自由になれ_img2.jpg</t>
         </is>
       </c>
-      <c r="C775" t="inlineStr">
+      <c r="C774" t="inlineStr">
         <is>
           <t>勇気 ,壁</t>
         </is>
       </c>
     </row>
-    <row r="776">
-      <c r="A776" t="inlineStr">
+    <row r="775">
+      <c r="A775" t="inlineStr">
         <is>
           <t xml:space="preserve">「己の翼を信じる者は己の重さを案じない」
 من يثق في جناحيه لن يهتم لوزنه
@@ -16756,19 +16735,19 @@
 2308 kmrghani </t>
         </is>
       </c>
-      <c r="B776" t="inlineStr">
+      <c r="B775" t="inlineStr">
         <is>
           <t>images/「己の翼を信じる者は己の重さを案じない_img1.jpg</t>
         </is>
       </c>
-      <c r="C776" t="inlineStr">
+      <c r="C775" t="inlineStr">
         <is>
           <t>自信</t>
         </is>
       </c>
     </row>
-    <row r="777">
-      <c r="A777" t="inlineStr">
+    <row r="776">
+      <c r="A776" t="inlineStr">
         <is>
           <t xml:space="preserve">「珈琲で一番大事な事！誰と飲むか？」
 الأهم من القهوة!! من ستشربها معه؟
@@ -16777,19 +16756,19 @@
 1812 gwid3.tumblr </t>
         </is>
       </c>
-      <c r="B777" t="inlineStr">
+      <c r="B776" t="inlineStr">
         <is>
           <t>images/「珈琲で一番大事な事！誰と飲むか？」_img1.jpg</t>
         </is>
       </c>
-      <c r="C777" t="inlineStr">
+      <c r="C776" t="inlineStr">
         <is>
           <t>コーヒー ,名言</t>
         </is>
       </c>
     </row>
-    <row r="778">
-      <c r="A778" t="inlineStr">
+    <row r="777">
+      <c r="A777" t="inlineStr">
         <is>
           <t xml:space="preserve">「人生は美しい、そう望んだ者には。」
 الحياة جَميلَة .. لمن أراد ذلك
@@ -16799,19 +16778,19 @@
 2109 出典不明 </t>
         </is>
       </c>
-      <c r="B778" t="inlineStr">
+      <c r="B777" t="inlineStr">
         <is>
           <t>images/「人生は美しい、そう望んだ者には。」_img1.jpg</t>
         </is>
       </c>
-      <c r="C778" t="inlineStr">
+      <c r="C777" t="inlineStr">
         <is>
           <t>名言 ,アート</t>
         </is>
       </c>
     </row>
-    <row r="779">
-      <c r="A779" t="inlineStr">
+    <row r="778">
+      <c r="A778" t="inlineStr">
         <is>
           <t xml:space="preserve">「ハム太郎って子を知ってるかい」
 هل تعرفون من هو هامتارو
@@ -16821,19 +16800,19 @@
 2109 </t>
         </is>
       </c>
-      <c r="B779" t="inlineStr">
+      <c r="B778" t="inlineStr">
         <is>
           <t>images/「ハム太郎って子を知ってるかい」_img1.jpg</t>
         </is>
       </c>
-      <c r="C779" t="inlineStr">
+      <c r="C778" t="inlineStr">
         <is>
           <t>オープニング ,ハム太郎</t>
         </is>
       </c>
     </row>
-    <row r="780">
-      <c r="A780" t="inlineStr">
+    <row r="779">
+      <c r="A779" t="inlineStr">
         <is>
           <t xml:space="preserve">「幸せを求める人もいれば、作る人もいる」
 هناك من يبحث عن السعادة وهناك من يصنعها
@@ -16842,19 +16821,19 @@
 2308 hindah tumblr </t>
         </is>
       </c>
-      <c r="B780" t="inlineStr">
+      <c r="B779" t="inlineStr">
         <is>
           <t>images/「幸せを求める人もいれば、作る人もいる_img1.jpg</t>
         </is>
       </c>
-      <c r="C780" t="inlineStr">
+      <c r="C779" t="inlineStr">
         <is>
           <t>幸せ ,名言 ,教訓</t>
         </is>
       </c>
     </row>
-    <row r="781">
-      <c r="A781" t="inlineStr">
+    <row r="780">
+      <c r="A780" t="inlineStr">
         <is>
           <t xml:space="preserve">「明白なるアラブの言葉によって」
 بلسان عربي مبين
@@ -16864,19 +16843,19 @@
 2109 Abdullah Barakat behance </t>
         </is>
       </c>
-      <c r="B781" t="inlineStr">
+      <c r="B780" t="inlineStr">
         <is>
           <t>images/「明白なるアラブの言葉によって」_img1.jpg</t>
         </is>
       </c>
-      <c r="C781" t="inlineStr">
+      <c r="C780" t="inlineStr">
         <is>
           <t>イスラム教 ,神聖</t>
         </is>
       </c>
     </row>
-    <row r="782">
-      <c r="A782" t="inlineStr">
+    <row r="781">
+      <c r="A781" t="inlineStr">
         <is>
           <t xml:space="preserve">「結婚前、結婚後」
 قبل الزواج، بعد الزواج
@@ -16886,19 +16865,19 @@
 2308 出典不明 </t>
         </is>
       </c>
-      <c r="B782" t="inlineStr">
+      <c r="B781" t="inlineStr">
         <is>
           <t>images/「結婚前、結婚後」_img1.jpg</t>
         </is>
       </c>
-      <c r="C782" t="inlineStr">
+      <c r="C781" t="inlineStr">
         <is>
           <t>BeforeAfter ,幸せ太り</t>
         </is>
       </c>
     </row>
-    <row r="783">
-      <c r="A783" t="inlineStr">
+    <row r="782">
+      <c r="A782" t="inlineStr">
         <is>
           <t xml:space="preserve">「驚きの価格で」بسعر رائع
 ビスィアル・ラーイア [bi-si*r raa'i*]
@@ -16907,19 +16886,19 @@
 2109 Jarir Bookstore </t>
         </is>
       </c>
-      <c r="B783" t="inlineStr">
+      <c r="B782" t="inlineStr">
         <is>
           <t>images/「驚きの価格で」_img1.jpg</t>
         </is>
       </c>
-      <c r="C783" t="inlineStr">
+      <c r="C782" t="inlineStr">
         <is>
           <t>広告 ,安値</t>
         </is>
       </c>
     </row>
-    <row r="784">
-      <c r="A784" t="inlineStr">
+    <row r="783">
+      <c r="A783" t="inlineStr">
         <is>
           <t xml:space="preserve">「我が魂と共に」مع نفسي
 マア・ナフスィ [ma*a nafs-iy]
@@ -16928,19 +16907,19 @@
 2110 出典不明 </t>
         </is>
       </c>
-      <c r="B784" t="inlineStr">
+      <c r="B783" t="inlineStr">
         <is>
           <t>images/「我が魂と共に」_img1.jpg</t>
         </is>
       </c>
-      <c r="C784" t="inlineStr">
+      <c r="C783" t="inlineStr">
         <is>
           <t>ソウル ,soul</t>
         </is>
       </c>
     </row>
-    <row r="785">
-      <c r="A785" t="inlineStr">
+    <row r="784">
+      <c r="A784" t="inlineStr">
         <is>
           <t xml:space="preserve">「暗い夜に」في ليلة مظلمة
  [fiy layla(tin) mu_Dhlima(tin)]
@@ -16949,19 +16928,19 @@
 2109 سلسلة الحلزونة </t>
         </is>
       </c>
-      <c r="B785" t="inlineStr">
+      <c r="B784" t="inlineStr">
         <is>
           <t>images/「暗い夜に」_img1.jpg</t>
         </is>
       </c>
-      <c r="C785" t="inlineStr">
+      <c r="C784" t="inlineStr">
         <is>
           <t>絵本</t>
         </is>
       </c>
     </row>
-    <row r="786">
-      <c r="A786" t="inlineStr">
+    <row r="785">
+      <c r="A785" t="inlineStr">
         <is>
           <t xml:space="preserve">「ゆっくりと」بشويش
 ビシワェーシ [bi-ShwySh]
@@ -16969,19 +16948,19 @@
 2109 出典不明 </t>
         </is>
       </c>
-      <c r="B786" t="inlineStr">
+      <c r="B785" t="inlineStr">
         <is>
           <t>images/「ゆっくりと」_img1.jpg</t>
         </is>
       </c>
-      <c r="C786" t="inlineStr">
+      <c r="C785" t="inlineStr">
         <is>
           <t>丸 ,円</t>
         </is>
       </c>
     </row>
-    <row r="787">
-      <c r="A787" t="inlineStr">
+    <row r="786">
+      <c r="A786" t="inlineStr">
         <is>
           <t xml:space="preserve">「この広い宇宙に…」
 في الكون الفسيح
@@ -16990,19 +16969,19 @@
 2308 wattpad </t>
         </is>
       </c>
-      <c r="B787" t="inlineStr">
+      <c r="B786" t="inlineStr">
         <is>
           <t>images/「この広い宇宙に…」_img1.jpg</t>
         </is>
       </c>
-      <c r="C787" t="inlineStr">
+      <c r="C786" t="inlineStr">
         <is>
           <t>アニメ ,宇宙</t>
         </is>
       </c>
     </row>
-    <row r="788">
-      <c r="A788" t="inlineStr">
+    <row r="787">
+      <c r="A787" t="inlineStr">
         <is>
           <t xml:space="preserve">「がんばって！」بالتوفيق
 ビッタウフィーク [bi^tawfiiq]
@@ -17010,19 +16989,19 @@
 2111 https://sites.google.com/site/mathmatic1905/ </t>
         </is>
       </c>
-      <c r="B788" t="inlineStr">
+      <c r="B787" t="inlineStr">
         <is>
           <t>images/「がんばって！」_img1.jpg</t>
         </is>
       </c>
-      <c r="C788" t="inlineStr">
+      <c r="C787" t="inlineStr">
         <is>
           <t>アラビア語</t>
         </is>
       </c>
     </row>
-    <row r="789">
-      <c r="A789" t="inlineStr">
+    <row r="788">
+      <c r="A788" t="inlineStr">
         <is>
           <t xml:space="preserve">「インターステラー」بين النجوم
 バイナ_ンヌジューム [bayna ^nujuum]
@@ -17030,19 +17009,19 @@
 2308 kmrghani </t>
         </is>
       </c>
-      <c r="B789" t="inlineStr">
+      <c r="B788" t="inlineStr">
         <is>
           <t>images/「インターステラー」_img1.jpg</t>
         </is>
       </c>
-      <c r="C789" t="inlineStr">
+      <c r="C788" t="inlineStr">
         <is>
           <t>映画 ,宇宙</t>
         </is>
       </c>
     </row>
-    <row r="790">
-      <c r="A790" t="inlineStr">
+    <row r="789">
+      <c r="A789" t="inlineStr">
         <is>
           <t xml:space="preserve">「アラビア語で」بالعربية
 ビ_ルアラビーヤ [bi-l-*arabiyya]
@@ -17051,19 +17030,19 @@
 1811 </t>
         </is>
       </c>
-      <c r="B790" t="inlineStr">
+      <c r="B789" t="inlineStr">
         <is>
           <t>images/「アラビア語で」_img1.jpg</t>
         </is>
       </c>
-      <c r="C790" t="inlineStr">
+      <c r="C789" t="inlineStr">
         <is>
           <t>ニュース ,CNN</t>
         </is>
       </c>
     </row>
-    <row r="791">
-      <c r="A791" t="inlineStr">
+    <row r="790">
+      <c r="A790" t="inlineStr">
         <is>
           <t xml:space="preserve">「17世紀に発明されて以来…」
 منذ اختراعه بالقرن السابع عشر
@@ -17071,19 +17050,19 @@
 2308 https://twitter.com/SciTalk2U/status/1450888395815854080 </t>
         </is>
       </c>
-      <c r="B791" t="inlineStr">
+      <c r="B790" t="inlineStr">
         <is>
           <t>images/「17世紀に発明されて以来…」_img1.jpg</t>
         </is>
       </c>
-      <c r="C791" t="inlineStr">
+      <c r="C790" t="inlineStr">
         <is>
           <t>手書き語学 ,アラビア語 ,望遠鏡</t>
         </is>
       </c>
     </row>
-    <row r="792">
-      <c r="A792" t="inlineStr">
+    <row r="791">
+      <c r="A791" t="inlineStr">
         <is>
           <t xml:space="preserve">「私できるよ」إنّني أستطيع
 インナニー・アスタティーウ ['inna-niy 'a-sta_tii*u]
@@ -17092,19 +17071,19 @@
 2412 سلسلة الحلزونة </t>
         </is>
       </c>
-      <c r="B792" t="inlineStr">
+      <c r="B791" t="inlineStr">
         <is>
           <t>images/「私できるよ」_img1.jpg</t>
         </is>
       </c>
-      <c r="C792" t="inlineStr">
+      <c r="C791" t="inlineStr">
         <is>
           <t>絵本 ,こども</t>
         </is>
       </c>
     </row>
-    <row r="793">
-      <c r="A793" t="inlineStr">
+    <row r="792">
+      <c r="A792" t="inlineStr">
         <is>
           <t xml:space="preserve">「問題なし」مافيش مشكلة
 マフィーシムシュキラ [ma-fy-Sh muShkila]
@@ -17113,19 +17092,19 @@
 2109 tanzerin.theshop </t>
         </is>
       </c>
-      <c r="B793" t="inlineStr">
+      <c r="B792" t="inlineStr">
         <is>
           <t>images/「問題なし」_img1.jpg</t>
         </is>
       </c>
-      <c r="C793" t="inlineStr">
+      <c r="C792" t="inlineStr">
         <is>
           <t>シャツ ,キッズ</t>
         </is>
       </c>
     </row>
-    <row r="794">
-      <c r="A794" t="inlineStr">
+    <row r="793">
+      <c r="A793" t="inlineStr">
         <is>
           <t xml:space="preserve">「不可能はない」مفيش مستحيل
 マフィーシ・ムスタヒール [ma-fy-Sh mustaHiil]
@@ -17134,19 +17113,19 @@
 2109 أموج </t>
         </is>
       </c>
-      <c r="B794" t="inlineStr">
+      <c r="B793" t="inlineStr">
         <is>
           <t>images/「不可能はない」_img1.jpg</t>
         </is>
       </c>
-      <c r="C794" t="inlineStr">
+      <c r="C793" t="inlineStr">
         <is>
           <t>ポジティブ ,挑戦</t>
         </is>
       </c>
     </row>
-    <row r="795">
-      <c r="A795" t="inlineStr">
+    <row r="794">
+      <c r="A794" t="inlineStr">
         <is>
           <t xml:space="preserve">「等々」إلخ
 イラク ['ilaKh]
@@ -17155,19 +17134,19 @@
 2201 出典不明 </t>
         </is>
       </c>
-      <c r="B795" t="inlineStr">
+      <c r="B794" t="inlineStr">
         <is>
           <t>images/「等々」_img1.jpg</t>
         </is>
       </c>
-      <c r="C795" t="inlineStr">
+      <c r="C794" t="inlineStr">
         <is>
           <t>etc ,とんち</t>
         </is>
       </c>
     </row>
-    <row r="796">
-      <c r="A796" t="inlineStr">
+    <row r="795">
+      <c r="A795" t="inlineStr">
         <is>
           <t xml:space="preserve">⁦「調子どう？」⁩شلونَك؟
 シュローナク？ [Sh-loon-ak?]
@@ -17176,19 +17155,19 @@
 2202 Jozoor Team. </t>
         </is>
       </c>
-      <c r="B796" t="inlineStr">
+      <c r="B795" t="inlineStr">
         <is>
           <t>images/⁦「調子どう？」⁩_img1.jpg</t>
         </is>
       </c>
-      <c r="C796" t="inlineStr">
+      <c r="C795" t="inlineStr">
         <is>
           <t>洒落 ,ルービックキューブ</t>
         </is>
       </c>
     </row>
-    <row r="797">
-      <c r="A797" t="inlineStr">
+    <row r="796">
+      <c r="A796" t="inlineStr">
         <is>
           <t xml:space="preserve">「行くな」ماتروحش
 マトロホシ [ma-troH-Sh]
@@ -17197,19 +17176,19 @@
 2411 triiq tumblr </t>
         </is>
       </c>
-      <c r="B797" t="inlineStr">
+      <c r="B796" t="inlineStr">
         <is>
           <t>images/「行くな」_img1.jpg</t>
         </is>
       </c>
-      <c r="C797" t="inlineStr">
+      <c r="C796" t="inlineStr">
         <is>
           <t>ロゴ ,デザイン ,嵐</t>
         </is>
       </c>
     </row>
-    <row r="798">
-      <c r="A798" t="inlineStr">
+    <row r="797">
+      <c r="A797" t="inlineStr">
         <is>
           <t xml:space="preserve">⁦「元気？」⁩شلونَك؟
 シュローナク？ [Sh-loon-ak?]
@@ -17220,19 +17199,19 @@
 2202 出典不明 </t>
         </is>
       </c>
-      <c r="B798" t="inlineStr">
+      <c r="B797" t="inlineStr">
         <is>
           <t>images/⁦「元気？」⁩_img1.jpg</t>
         </is>
       </c>
-      <c r="C798" t="inlineStr">
+      <c r="C797" t="inlineStr">
         <is>
           <t>洒落 ,挨拶</t>
         </is>
       </c>
     </row>
-    <row r="799">
-      <c r="A799" t="inlineStr">
+    <row r="798">
+      <c r="A798" t="inlineStr">
         <is>
           <t xml:space="preserve">「気分が良いぞう」I فيل GOOD
 アイ・フィール・グッド [ai fiyl gud]
@@ -17241,19 +17220,19 @@
 2308 出典不明 </t>
         </is>
       </c>
-      <c r="B799" t="inlineStr">
+      <c r="B798" t="inlineStr">
         <is>
           <t>images/「気分が良いぞう」_img1.jpg</t>
         </is>
       </c>
-      <c r="C799" t="inlineStr">
+      <c r="C798" t="inlineStr">
         <is>
           <t>洒落 ,和訳</t>
         </is>
       </c>
     </row>
-    <row r="800">
-      <c r="A800" t="inlineStr">
+    <row r="799">
+      <c r="A799" t="inlineStr">
         <is>
           <t xml:space="preserve">「レットイットゴー／let it go」
 ليت اِت غو
@@ -17262,19 +17241,19 @@
 2109 出典不明 </t>
         </is>
       </c>
-      <c r="B800" t="inlineStr">
+      <c r="B799" t="inlineStr">
         <is>
           <t>images/「レットイットゴー／let it go_img1.jpg</t>
         </is>
       </c>
-      <c r="C800" t="inlineStr">
+      <c r="C799" t="inlineStr">
         <is>
           <t>折衷 ,アナ雪</t>
         </is>
       </c>
     </row>
-    <row r="801">
-      <c r="A801" t="inlineStr">
+    <row r="800">
+      <c r="A800" t="inlineStr">
         <is>
           <t xml:space="preserve">「ようこそ」اهلا وسهلا
 アハラン・ワサハラン ['ahlan wa-sahlan]
@@ -17282,19 +17261,19 @@
 2106 behance Anwar Al Eissa </t>
         </is>
       </c>
-      <c r="B801" t="inlineStr">
+      <c r="B800" t="inlineStr">
         <is>
           <t>images/「ようこそ」_img1.jpg</t>
         </is>
       </c>
-      <c r="C801" t="inlineStr">
+      <c r="C800" t="inlineStr">
         <is>
           <t>アラビア語</t>
         </is>
       </c>
     </row>
-    <row r="802">
-      <c r="A802" t="inlineStr">
+    <row r="801">
+      <c r="A801" t="inlineStr">
         <is>
           <t xml:space="preserve">「まぁ何というサプライズでしょう」
 يا لها من مفاجأة
@@ -17305,19 +17284,19 @@
 2108 neelwafurat com </t>
         </is>
       </c>
-      <c r="B802" t="inlineStr">
+      <c r="B801" t="inlineStr">
         <is>
           <t>images/「まぁ何というサプライズでしょう」_img1.jpg</t>
         </is>
       </c>
-      <c r="C802" t="inlineStr">
+      <c r="C801" t="inlineStr">
         <is>
           <t>中国語 ,学習</t>
         </is>
       </c>
     </row>
-    <row r="803">
-      <c r="A803" t="inlineStr">
+    <row r="802">
+      <c r="A802" t="inlineStr">
         <is>
           <t xml:space="preserve">「ハックション」اتشوو
 アチュー！ ['aatShuu]
@@ -17325,19 +17304,19 @@
 1811 </t>
         </is>
       </c>
-      <c r="B803" t="inlineStr">
+      <c r="B802" t="inlineStr">
         <is>
           <t>images/「ハックション」_img1.jpg</t>
         </is>
       </c>
-      <c r="C803" t="inlineStr">
+      <c r="C802" t="inlineStr">
         <is>
           <t>あらびあや</t>
         </is>
       </c>
     </row>
-    <row r="804">
-      <c r="A804" t="inlineStr">
+    <row r="803">
+      <c r="A803" t="inlineStr">
         <is>
           <t xml:space="preserve">「スブハーナッラー」「アルハムドゥリッラー」「アッラーアクバル」
 سبحان الله
@@ -17348,19 +17327,19 @@
 2308 dribbble com </t>
         </is>
       </c>
-      <c r="B804" t="inlineStr">
+      <c r="B803" t="inlineStr">
         <is>
           <t>images/「スブハーナッラー」「アルハムドゥリッ_img1.jpg</t>
         </is>
       </c>
-      <c r="C804" t="inlineStr">
+      <c r="C803" t="inlineStr">
         <is>
           <t>四角 ,コンパクト</t>
         </is>
       </c>
     </row>
-    <row r="805">
-      <c r="A805" t="inlineStr">
+    <row r="804">
+      <c r="A804" t="inlineStr">
         <is>
           <t xml:space="preserve">「すごく美味しい！」لذيذ جدًا
 ラズィーズ・ジッダン [laDhiiDh jiddan]
@@ -17369,19 +17348,19 @@
 2109 goodreads com </t>
         </is>
       </c>
-      <c r="B805" t="inlineStr">
+      <c r="B804" t="inlineStr">
         <is>
           <t>images/「すごく美味しい！」_img1.jpg</t>
         </is>
       </c>
-      <c r="C805" t="inlineStr">
+      <c r="C804" t="inlineStr">
         <is>
           <t>フレーズ ,感想</t>
         </is>
       </c>
     </row>
-    <row r="806">
-      <c r="A806" t="inlineStr">
+    <row r="805">
+      <c r="A805" t="inlineStr">
         <is>
           <t xml:space="preserve">「しとしと、雨」تك تك يا مطر
 ティクティク [tik tik yaa ma_tar]
@@ -17390,19 +17369,19 @@
 2308 出典不明 </t>
         </is>
       </c>
-      <c r="B806" t="inlineStr">
+      <c r="B805" t="inlineStr">
         <is>
           <t>images/「しとしと、雨」_img1.jpg</t>
         </is>
       </c>
-      <c r="C806" t="inlineStr">
+      <c r="C805" t="inlineStr">
         <is>
           <t>天気 ,梅雨</t>
         </is>
       </c>
     </row>
-    <row r="807">
-      <c r="A807" t="inlineStr">
+    <row r="806">
+      <c r="A806" t="inlineStr">
         <is>
           <t xml:space="preserve">「さかさま」رأساً على عقب
 ラッアサン・アラー・アケブ [ra'san *alaa *aqib]
@@ -17410,19 +17389,19 @@
 2109 出典不明 </t>
         </is>
       </c>
-      <c r="B807" t="inlineStr">
+      <c r="B806" t="inlineStr">
         <is>
           <t>images/「さかさま」_img1.jpg</t>
         </is>
       </c>
-      <c r="C807" t="inlineStr">
+      <c r="C806" t="inlineStr">
         <is>
           <t>壁 ,上下</t>
         </is>
       </c>
     </row>
-    <row r="808">
-      <c r="A808" t="inlineStr">
+    <row r="807">
+      <c r="A807" t="inlineStr">
         <is>
           <t xml:space="preserve">「エジプトよどこへ行った」
 فينك يا مصر؟
@@ -17432,19 +17411,19 @@
 1809 shehabfawzy1.tumblr </t>
         </is>
       </c>
-      <c r="B808" t="inlineStr">
+      <c r="B807" t="inlineStr">
         <is>
           <t>images/「エジプトよどこへ行った」_img1.jpg</t>
         </is>
       </c>
-      <c r="C808" t="inlineStr">
+      <c r="C807" t="inlineStr">
         <is>
           <t>ピラミッド ,歴史</t>
         </is>
       </c>
     </row>
-    <row r="809">
-      <c r="A809" t="inlineStr">
+    <row r="808">
+      <c r="A808" t="inlineStr">
         <is>
           <t xml:space="preserve">「ありがとう」شكراً
 シュクラン [Shukran]
@@ -17452,19 +17431,19 @@
 2109 出典不明 </t>
         </is>
       </c>
-      <c r="B809" t="inlineStr">
+      <c r="B808" t="inlineStr">
         <is>
           <t>images/「ありがとう」_img1.jpg</t>
         </is>
       </c>
-      <c r="C809" t="inlineStr">
+      <c r="C808" t="inlineStr">
         <is>
           <t>挨拶 ,文字</t>
         </is>
       </c>
     </row>
-    <row r="810">
-      <c r="A810" t="inlineStr">
+    <row r="809">
+      <c r="A809" t="inlineStr">
         <is>
           <t xml:space="preserve">「昼寝の時間だ」
 إنه وقت القيلولة
@@ -17473,12 +17452,12 @@
 2501 https://x.com/NatGeoMagArab/status/1858049951579910486 </t>
         </is>
       </c>
-      <c r="B810" t="inlineStr">
+      <c r="B809" t="inlineStr">
         <is>
           <t>images/「昼寝の時間だ」_img1.jpg</t>
         </is>
       </c>
-      <c r="C810" t="inlineStr">
+      <c r="C809" t="inlineStr">
         <is>
           <t>手書き語学 ,アラビア語 ,ペンギン</t>
         </is>

--- a/posts.xlsx
+++ b/posts.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C809"/>
+  <dimension ref="A1:C808"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -14189,28 +14189,6 @@
     <row r="654">
       <c r="A654" t="inlineStr">
         <is>
-          <t xml:space="preserve">「諸行無常」كلّ شيءٍ يتغيّر
-クッル・シャイイン・ヤタガイヤル [kullu Shay'in ya-taGhayyaru]
-「あらゆる物は」[kullu Shay'in]・「それは変わる」[ya-taGhayyaru] 
-諸行無常（ショギョウ・ムジョウ）
-2510 
-د. ماجد عبدالله </t>
-        </is>
-      </c>
-      <c r="B654" t="inlineStr">
-        <is>
-          <t>images/「諸行無常」_img1.jpg</t>
-        </is>
-      </c>
-      <c r="C654" t="inlineStr">
-        <is>
-          <t>表紙 ,タイトル</t>
-        </is>
-      </c>
-    </row>
-    <row r="655">
-      <c r="A655" t="inlineStr">
-        <is>
           <t xml:space="preserve">「幸せな人生には弱い記憶力が必要」
 الحياة السعيدة تتطلب ذاكرة ضعيفة
 [al-Hayaatu ^sa*iidatu ta-ta_tallabu Dhaakiratan _da*iifatan]
@@ -14218,19 +14196,19 @@
 2012 出典不明 </t>
         </is>
       </c>
-      <c r="B655" t="inlineStr">
+      <c r="B654" t="inlineStr">
         <is>
           <t>images/「幸せな人生には弱い記憶力が必要」_img1.jpg</t>
         </is>
       </c>
-      <c r="C655" t="inlineStr">
+      <c r="C654" t="inlineStr">
         <is>
           <t>前向き</t>
         </is>
       </c>
     </row>
-    <row r="656">
-      <c r="A656" t="inlineStr">
+    <row r="655">
+      <c r="A655" t="inlineStr">
         <is>
           <t xml:space="preserve">「このパンダは私たちに、幸せは単純なことの中に隠れているのだと教えている」
 دب "الباندا" هذا يؤكد لنا أن السعادة تكمن في أبسط الأشياء
@@ -14238,19 +14216,19 @@
 2308 https://twitter.com/NatGeoMagArab/status/1309938472065486848 </t>
         </is>
       </c>
-      <c r="B656" t="inlineStr">
+      <c r="B655" t="inlineStr">
         <is>
           <t>images/「このパンダは私たちに、幸せは単純なこ.png</t>
         </is>
       </c>
-      <c r="C656" t="inlineStr">
+      <c r="C655" t="inlineStr">
         <is>
           <t>パンダ ,雪</t>
         </is>
       </c>
     </row>
-    <row r="657">
-      <c r="A657" t="inlineStr">
+    <row r="656">
+      <c r="A656" t="inlineStr">
         <is>
           <t xml:space="preserve">「良い時間は速く過ぎる」
 الأوقات الجميلة تمر بسرعة
@@ -14260,19 +14238,19 @@
 1810 Nasser.Tumblr </t>
         </is>
       </c>
-      <c r="B657" t="inlineStr">
+      <c r="B656" t="inlineStr">
         <is>
           <t>images/「良い時間は速く過ぎる」_img1.jpg</t>
         </is>
       </c>
-      <c r="C657" t="inlineStr">
+      <c r="C656" t="inlineStr">
         <is>
           <t>相対論 ,心理学</t>
         </is>
       </c>
     </row>
-    <row r="658">
-      <c r="A658" t="inlineStr">
+    <row r="657">
+      <c r="A657" t="inlineStr">
         <is>
           <t xml:space="preserve">「今日が始まりかもしれない」
 كل يوم ممكن يكون بداية
@@ -14282,19 +14260,19 @@
 2308 Ahmed Madyan </t>
         </is>
       </c>
-      <c r="B658" t="inlineStr">
+      <c r="B657" t="inlineStr">
         <is>
           <t>images/「今日が始まりかもしれない」_img1.jpg</t>
         </is>
       </c>
-      <c r="C658" t="inlineStr">
+      <c r="C657" t="inlineStr">
         <is>
           <t>吉日 ,開始</t>
         </is>
       </c>
     </row>
-    <row r="659">
-      <c r="A659" t="inlineStr">
+    <row r="658">
+      <c r="A658" t="inlineStr">
         <is>
           <t xml:space="preserve">「ヌール、歯医者さんに行く」
 نور تذهب إلى طبيب الأسنان
@@ -14304,19 +14282,19 @@
 2109 RABIE </t>
         </is>
       </c>
-      <c r="B659" t="inlineStr">
+      <c r="B658" t="inlineStr">
         <is>
           <t>images/「ヌール、歯医者さんに行く」_img1.jpg</t>
         </is>
       </c>
-      <c r="C659" t="inlineStr">
+      <c r="C658" t="inlineStr">
         <is>
           <t>絵本 ,歯科</t>
         </is>
       </c>
     </row>
-    <row r="660">
-      <c r="A660" t="inlineStr">
+    <row r="659">
+      <c r="A659" t="inlineStr">
         <is>
           <t xml:space="preserve">「ラヤンはねむれない」
 لَيان لا تَسْتَطيعُ أَنْ تَنام
@@ -14325,19 +14303,19 @@
 2308 出典不明 </t>
         </is>
       </c>
-      <c r="B660" t="inlineStr">
+      <c r="B659" t="inlineStr">
         <is>
           <t>images/「ラヤンはねむれない」_img1.jpg</t>
         </is>
       </c>
-      <c r="C660" t="inlineStr">
+      <c r="C659" t="inlineStr">
         <is>
           <t>絵本 ,不眠症</t>
         </is>
       </c>
     </row>
-    <row r="661">
-      <c r="A661" t="inlineStr">
+    <row r="660">
+      <c r="A660" t="inlineStr">
         <is>
           <t xml:space="preserve">「クネイトラ県、蜂の巣を約60%失う」
 القنيطرة تفقد حوالي 60 % من خلايا نحلها
@@ -14345,19 +14323,19 @@
 2403 nabd com/t/101679025-fb119f </t>
         </is>
       </c>
-      <c r="B661" t="inlineStr">
+      <c r="B660" t="inlineStr">
         <is>
           <t>images/「クネイトラ県、蜂の巣を約60%失う」_img1.jpg</t>
         </is>
       </c>
-      <c r="C661" t="inlineStr">
+      <c r="C660" t="inlineStr">
         <is>
           <t>蜂の巣 ,パーセント</t>
         </is>
       </c>
     </row>
-    <row r="662">
-      <c r="A662" t="inlineStr">
+    <row r="661">
+      <c r="A661" t="inlineStr">
         <is>
           <t xml:space="preserve">「結ばれしター」ة
 ⁦( تاء مربوطة )[taa' marbuu_ta]：ت「ター」( تاء )[taa']・「結ばれている」( مربوط )[marbuu_t]：( ربط )【結】⁩
@@ -14365,19 +14343,19 @@
 2308 出典不明 </t>
         </is>
       </c>
-      <c r="B662" t="inlineStr">
+      <c r="B661" t="inlineStr">
         <is>
           <t>images/「結ばれしター」_img1.jpg</t>
         </is>
       </c>
-      <c r="C662" t="inlineStr">
+      <c r="C661" t="inlineStr">
         <is>
           <t>アラビア文字 ,顔</t>
         </is>
       </c>
     </row>
-    <row r="663">
-      <c r="A663" t="inlineStr">
+    <row r="662">
+      <c r="A662" t="inlineStr">
         <is>
           <t xml:space="preserve">「忙しい」مشغول
 マシュグール [maShGhuul]
@@ -14386,19 +14364,19 @@
 1811 skyshinichi.instagram </t>
         </is>
       </c>
-      <c r="B663" t="inlineStr">
+      <c r="B662" t="inlineStr">
         <is>
           <t>images/「忙しい」_img1.jpg</t>
         </is>
       </c>
-      <c r="C663" t="inlineStr">
+      <c r="C662" t="inlineStr">
         <is>
           <t>スティッチ ,残業</t>
         </is>
       </c>
     </row>
-    <row r="664">
-      <c r="A664" t="inlineStr">
+    <row r="663">
+      <c r="A663" t="inlineStr">
         <is>
           <t xml:space="preserve">「駐車禁止」ممنوع الوقوف
 マムヌーア・アルウクーフ [mamnuu* al-wuquuf]
@@ -14407,19 +14385,19 @@
 2106 出典不明 </t>
         </is>
       </c>
-      <c r="B664" t="inlineStr">
+      <c r="B663" t="inlineStr">
         <is>
           <t>images/「駐車禁止」_img1.jpg</t>
         </is>
       </c>
-      <c r="C664" t="inlineStr">
+      <c r="C663" t="inlineStr">
         <is>
           <t>標識 ,ジョーク</t>
         </is>
       </c>
     </row>
-    <row r="665">
-      <c r="A665" t="inlineStr">
+    <row r="664">
+      <c r="A664" t="inlineStr">
         <is>
           <t xml:space="preserve">「一人ひとりが責任を」
 كُلنا مسؤول
@@ -14429,19 +14407,19 @@
 2308 covid19awareness sa </t>
         </is>
       </c>
-      <c r="B665" t="inlineStr">
+      <c r="B664" t="inlineStr">
         <is>
           <t>images/「一人ひとりが責任を」_img1.jpg</t>
         </is>
       </c>
-      <c r="C665" t="inlineStr">
+      <c r="C664" t="inlineStr">
         <is>
           <t>Covid ,感染拡大防止</t>
         </is>
       </c>
     </row>
-    <row r="666">
-      <c r="A666" t="inlineStr">
+    <row r="665">
+      <c r="A665" t="inlineStr">
         <is>
           <t xml:space="preserve">「おめでとうございます」مبروك
 マブルーク [mabruuk]
@@ -14450,19 +14428,19 @@
 2308 </t>
         </is>
       </c>
-      <c r="B666" t="inlineStr">
+      <c r="B665" t="inlineStr">
         <is>
           <t>images/「おめでとうございます」_img1.jpg</t>
         </is>
       </c>
-      <c r="C666" t="inlineStr">
+      <c r="C665" t="inlineStr">
         <is>
           <t>詐欺 ,広告</t>
         </is>
       </c>
     </row>
-    <row r="667">
-      <c r="A667" t="inlineStr">
+    <row r="666">
+      <c r="A666" t="inlineStr">
         <is>
           <t xml:space="preserve">「手書きフォント」
 خط مكتوب باليد
@@ -14472,19 +14450,19 @@
 1809 FahdAlFraikh Behance </t>
         </is>
       </c>
-      <c r="B667" t="inlineStr">
+      <c r="B666" t="inlineStr">
         <is>
           <t>images/「手書きフォント」_img1.jpg</t>
         </is>
       </c>
-      <c r="C667" t="inlineStr">
+      <c r="C666" t="inlineStr">
         <is>
           <t>可愛いフォント ,筆跡</t>
         </is>
       </c>
     </row>
-    <row r="668">
-      <c r="A668" t="inlineStr">
+    <row r="667">
+      <c r="A667" t="inlineStr">
         <is>
           <t xml:space="preserve">「開かれたターと結ばれたター」
 التاء المفتوحة والمربوطة
@@ -14494,19 +14472,19 @@
 2109 slideshare.net </t>
         </is>
       </c>
-      <c r="B668" t="inlineStr">
+      <c r="B667" t="inlineStr">
         <is>
           <t>images/「開かれたターと結ばれたター」_img1.jpg</t>
         </is>
       </c>
-      <c r="C668" t="inlineStr">
+      <c r="C667" t="inlineStr">
         <is>
           <t>アラビア文字 ,スマイリー</t>
         </is>
       </c>
     </row>
-    <row r="669">
-      <c r="A669" t="inlineStr">
+    <row r="668">
+      <c r="A668" t="inlineStr">
         <is>
           <t xml:space="preserve">「このラマは誇らしげにして立っている」
 تقف هذه اللاما مزهوة بنفسها
@@ -14514,19 +14492,19 @@
 2410 https://twitter.com/NatGeoMagArab/status/1597485552965935104 </t>
         </is>
       </c>
-      <c r="B669" t="inlineStr">
+      <c r="B668" t="inlineStr">
         <is>
           <t>images/「このラマは誇らしげにして立っている」_img1.jpg</t>
         </is>
       </c>
-      <c r="C669" t="inlineStr">
+      <c r="C668" t="inlineStr">
         <is>
           <t>手書き語学 ,アラビア語 ,マチュピチュ遺跡</t>
         </is>
       </c>
     </row>
-    <row r="670">
-      <c r="A670" t="inlineStr">
+    <row r="669">
+      <c r="A669" t="inlineStr">
         <is>
           <t xml:space="preserve">「小さな生き物にしては危険な名前だ」
 اسم خطير لمخلوق صغير
@@ -14535,19 +14513,19 @@
 2308 https://twitter.com/NatGeoMagArab/status/1495035772071669760 </t>
         </is>
       </c>
-      <c r="B670" t="inlineStr">
+      <c r="B669" t="inlineStr">
         <is>
           <t>images/「小さな生き物にしては危険な名前だ」_img1.jpg</t>
         </is>
       </c>
-      <c r="C670" t="inlineStr">
+      <c r="C669" t="inlineStr">
         <is>
           <t>有袋類 ,タスマニアデビル</t>
         </is>
       </c>
     </row>
-    <row r="671">
-      <c r="A671" t="inlineStr">
+    <row r="670">
+      <c r="A670" t="inlineStr">
         <is>
           <t xml:space="preserve">「こわれている」مكسر
 ムカッサル [mukassar]
@@ -14555,19 +14533,19 @@
 2105 behance Written-Visuals </t>
         </is>
       </c>
-      <c r="B671" t="inlineStr">
+      <c r="B670" t="inlineStr">
         <is>
           <t>images/「こわれている」_img1.jpg</t>
         </is>
       </c>
-      <c r="C671" t="inlineStr">
+      <c r="C670" t="inlineStr">
         <is>
           <t>バラバラ ,デザイン</t>
         </is>
       </c>
     </row>
-    <row r="672">
-      <c r="A672" t="inlineStr">
+    <row r="671">
+      <c r="A671" t="inlineStr">
         <is>
           <t xml:space="preserve">「早起きする方法」
 كيف تنهض مُبكّرًا
@@ -14577,19 +14555,19 @@
 2308 Funders and Founders </t>
         </is>
       </c>
-      <c r="B672" t="inlineStr">
+      <c r="B671" t="inlineStr">
         <is>
           <t>images/「早起きする方法」_img1.jpg</t>
         </is>
       </c>
-      <c r="C672" t="inlineStr">
+      <c r="C671" t="inlineStr">
         <is>
           <t>オフトゥン ,寝起き</t>
         </is>
       </c>
     </row>
-    <row r="673">
-      <c r="A673" t="inlineStr">
+    <row r="672">
+      <c r="A672" t="inlineStr">
         <is>
           <t xml:space="preserve">「アラブ・デザイン文字展覧会」
 معرض لتخطيط الحرف العربي
@@ -14599,38 +14577,38 @@
 2109 arabic lettering exhibition </t>
         </is>
       </c>
-      <c r="B673" t="inlineStr">
+      <c r="B672" t="inlineStr">
         <is>
           <t>images/「アラブ・デザイン文字展覧会」_img1.jpg</t>
         </is>
       </c>
-      <c r="C673" t="inlineStr">
+      <c r="C672" t="inlineStr">
         <is>
           <t>ポスター</t>
         </is>
       </c>
     </row>
-    <row r="674">
-      <c r="A674" t="inlineStr">
+    <row r="673">
+      <c r="A673" t="inlineStr">
         <is>
           <t xml:space="preserve">「お気に入りのおもちゃには触らせない」
 ⁦「彼は〜を許さない」[laa ya-smaHu bi-]：「彼は許す」( يسمح )[ya-smaH(u)]：「許した」( سمح )[samaHa]：( سَ )[sa]・( مَ )[ma]・( حَ )[Ha]⁩
 2209 https://pic.twitter.com/qWcIPB3fz2 </t>
         </is>
       </c>
-      <c r="B674" t="inlineStr">
+      <c r="B673" t="inlineStr">
         <is>
           <t>images/「お気に入りのおもちゃには触らせない」_img1.jpg</t>
         </is>
       </c>
-      <c r="C674" t="inlineStr">
+      <c r="C673" t="inlineStr">
         <is>
           <t>パンダ ,ボール</t>
         </is>
       </c>
     </row>
-    <row r="675">
-      <c r="A675" t="inlineStr">
+    <row r="674">
+      <c r="A674" t="inlineStr">
         <is>
           <t xml:space="preserve">「名探偵コナン」المحقق كونان
 アルムハッキク・コナン [al-muHaqqiq Conan]
@@ -14639,19 +14617,19 @@
 1809 wikipedia </t>
         </is>
       </c>
-      <c r="B675" t="inlineStr">
+      <c r="B674" t="inlineStr">
         <is>
           <t>images/「名探偵コナン」_img1.jpg</t>
         </is>
       </c>
-      <c r="C675" t="inlineStr">
+      <c r="C674" t="inlineStr">
         <is>
           <t>江戸川コナン ,ロゴ</t>
         </is>
       </c>
     </row>
-    <row r="676">
-      <c r="A676" t="inlineStr">
+    <row r="675">
+      <c r="A675" t="inlineStr">
         <is>
           <t xml:space="preserve">「イードおめでとう」عيد مبارك
 イード・ムバーラク [*iid mubaarak]
@@ -14659,19 +14637,19 @@
 2308 出典不明 </t>
         </is>
       </c>
-      <c r="B676" t="inlineStr">
+      <c r="B675" t="inlineStr">
         <is>
           <t>images/「イードおめでとう」_img1.jpg</t>
         </is>
       </c>
-      <c r="C676" t="inlineStr">
+      <c r="C675" t="inlineStr">
         <is>
           <t>عيد ,アラビア語</t>
         </is>
       </c>
     </row>
-    <row r="677">
-      <c r="A677" t="inlineStr">
+    <row r="676">
+      <c r="A676" t="inlineStr">
         <is>
           <t xml:space="preserve">「戦士」محارب
 ムハーリブ [muHaarib]
@@ -14680,19 +14658,19 @@
 1809 abudinges.tumblr </t>
         </is>
       </c>
-      <c r="B677" t="inlineStr">
+      <c r="B676" t="inlineStr">
         <is>
           <t>images/「戦士」_img1.jpg</t>
         </is>
       </c>
-      <c r="C677" t="inlineStr">
+      <c r="C676" t="inlineStr">
         <is>
           <t>ロゴ ,赤</t>
         </is>
       </c>
     </row>
-    <row r="678">
-      <c r="A678" t="inlineStr">
+    <row r="677">
+      <c r="A677" t="inlineStr">
         <is>
           <t xml:space="preserve">「ライブ」بث مباشر
 バッス・ムバーシル [ba^Th(un) mubaaShir(un)]
@@ -14701,19 +14679,19 @@
 2308 beIN SPORTS </t>
         </is>
       </c>
-      <c r="B678" t="inlineStr">
+      <c r="B677" t="inlineStr">
         <is>
           <t>images/「ライブ」_img1.jpg</t>
         </is>
       </c>
-      <c r="C678" t="inlineStr">
+      <c r="C677" t="inlineStr">
         <is>
           <t xml:space="preserve">生放送 ,試合 </t>
         </is>
       </c>
     </row>
-    <row r="679">
-      <c r="A679" t="inlineStr">
+    <row r="678">
+      <c r="A678" t="inlineStr">
         <is>
           <t xml:space="preserve">「信者」مُؤْمِنٌ
 ムッミン [mu'min(un)]
@@ -14722,19 +14700,19 @@
 2106 出典不明 </t>
         </is>
       </c>
-      <c r="B679" t="inlineStr">
+      <c r="B678" t="inlineStr">
         <is>
           <t>images/「信者」_img1.jpg</t>
         </is>
       </c>
-      <c r="C679" t="inlineStr">
+      <c r="C678" t="inlineStr">
         <is>
           <t>明暗 ,信仰</t>
         </is>
       </c>
     </row>
-    <row r="680">
-      <c r="A680" t="inlineStr">
+    <row r="679">
+      <c r="A679" t="inlineStr">
         <is>
           <t xml:space="preserve">「開⇔閉」
 مفتوح
@@ -14745,19 +14723,19 @@
 2312 Hussein Safina, behance </t>
         </is>
       </c>
-      <c r="B680" t="inlineStr">
+      <c r="B679" t="inlineStr">
         <is>
           <t>images/「開⇔閉」_img1.jpg</t>
         </is>
       </c>
-      <c r="C680" t="inlineStr">
+      <c r="C679" t="inlineStr">
         <is>
           <t>オープンマインド ,トグル</t>
         </is>
       </c>
     </row>
-    <row r="681">
-      <c r="A681" t="inlineStr">
+    <row r="680">
+      <c r="A680" t="inlineStr">
         <is>
           <t xml:space="preserve">「予想外な結末！」
 نهاية غير متوقعة
@@ -14765,19 +14743,19 @@
 2308 https://twitter.com/NatGeoMagArab/status/1159011433444593665 </t>
         </is>
       </c>
-      <c r="B681" t="inlineStr">
+      <c r="B680" t="inlineStr">
         <is>
           <t>images/「予想外な結末！」_img1.jpg</t>
         </is>
       </c>
-      <c r="C681" t="inlineStr">
+      <c r="C680" t="inlineStr">
         <is>
           <t>手書き語学 ,アラビア語 ,ウサギ</t>
         </is>
       </c>
     </row>
-    <row r="682">
-      <c r="A682" t="inlineStr">
+    <row r="681">
+      <c r="A681" t="inlineStr">
         <is>
           <t xml:space="preserve">「ベイルート・アニメイテッド」
 بیروت متحرّکة
@@ -14787,19 +14765,19 @@
 2308 arabic_script Instagram </t>
         </is>
       </c>
-      <c r="B682" t="inlineStr">
+      <c r="B681" t="inlineStr">
         <is>
           <t>images/「ベイルート・アニメイテッド」_img1.jpg</t>
         </is>
       </c>
-      <c r="C682" t="inlineStr">
+      <c r="C681" t="inlineStr">
         <is>
           <t>アニメ ,レバノン</t>
         </is>
       </c>
     </row>
-    <row r="683">
-      <c r="A683" t="inlineStr">
+    <row r="682">
+      <c r="A682" t="inlineStr">
         <is>
           <t xml:space="preserve">「夢みれば叶う」
 كُلُّ مُتَوَقَّعٍ آتٍ
@@ -14809,19 +14787,19 @@
 2108 Ahmed Madyan </t>
         </is>
       </c>
-      <c r="B683" t="inlineStr">
+      <c r="B682" t="inlineStr">
         <is>
           <t>images/「夢みれば叶う」_img1.jpg</t>
         </is>
       </c>
-      <c r="C683" t="inlineStr">
+      <c r="C682" t="inlineStr">
         <is>
           <t>希望 ,ドリカム</t>
         </is>
       </c>
     </row>
-    <row r="684">
-      <c r="A684" t="inlineStr">
+    <row r="683">
+      <c r="A683" t="inlineStr">
         <is>
           <t xml:space="preserve">「もし両者が人間のように鎧で武装して戦いに突入したら」
 لو خاضا معاركهما متسلحين بالدروع على غرار البش
@@ -14829,19 +14807,19 @@
 2404 https://x.com/NatGeoMagArab/status/1759284149456945464 </t>
         </is>
       </c>
-      <c r="B684" t="inlineStr">
+      <c r="B683" t="inlineStr">
         <is>
           <t>images/「もし両者が人間のように鎧で武装して戦_img1.jpg,images/「もし両者が人間のように鎧で武装して戦_img2.jpg</t>
         </is>
       </c>
-      <c r="C684" t="inlineStr">
+      <c r="C683" t="inlineStr">
         <is>
           <t>手書き語学 ,アラビア語 ,猫</t>
         </is>
       </c>
     </row>
-    <row r="685">
-      <c r="A685" t="inlineStr">
+    <row r="684">
+      <c r="A684" t="inlineStr">
         <is>
           <t xml:space="preserve">「全ては結びついている」
 كل شيء مترابط
@@ -14851,19 +14829,19 @@
 2308 Ahmed Madyan https://twitter.com/madyco22/status/1451990828298166273 </t>
         </is>
       </c>
-      <c r="B685" t="inlineStr">
+      <c r="B684" t="inlineStr">
         <is>
           <t>images/「全ては結びついている」_img1.jpg</t>
         </is>
       </c>
-      <c r="C685" t="inlineStr">
+      <c r="C684" t="inlineStr">
         <is>
           <t>一筆書き ,デザイン</t>
         </is>
       </c>
     </row>
-    <row r="686">
-      <c r="A686" t="inlineStr">
+    <row r="685">
+      <c r="A685" t="inlineStr">
         <is>
           <t xml:space="preserve">「初心者のためのスケッチトレーニング」
 تعليم الرسم للمبتدئين
@@ -14873,19 +14851,19 @@
 2308 free-bookspdf com </t>
         </is>
       </c>
-      <c r="B686" t="inlineStr">
+      <c r="B685" t="inlineStr">
         <is>
           <t>images/「初心者のためのスケッチトレーニング」_img1.jpg</t>
         </is>
       </c>
-      <c r="C686" t="inlineStr">
+      <c r="C685" t="inlineStr">
         <is>
           <t>イラスト ,絵</t>
         </is>
       </c>
     </row>
-    <row r="687">
-      <c r="A687" t="inlineStr">
+    <row r="686">
+      <c r="A686" t="inlineStr">
         <is>
           <t xml:space="preserve">「初心者のためのスルス体書道トレーニング」
 تعليم خط الثلث للمبتدئين
@@ -14895,19 +14873,19 @@
 2308 出典不明 </t>
         </is>
       </c>
-      <c r="B687" t="inlineStr">
+      <c r="B686" t="inlineStr">
         <is>
           <t>images/「初心者のためのスルス体書道トレーニン_img1.jpg</t>
         </is>
       </c>
-      <c r="C687" t="inlineStr">
+      <c r="C686" t="inlineStr">
         <is>
           <t>書道</t>
         </is>
       </c>
     </row>
-    <row r="688">
-      <c r="A688" t="inlineStr">
+    <row r="687">
+      <c r="A687" t="inlineStr">
         <is>
           <t xml:space="preserve">「笑顔でいなさい」خليك مبتسم
 カッリーク・ムブタスィム [Khallii-k mubtasim]
@@ -14916,19 +14894,19 @@
 2308 https://tmblr.co/Zj9tguYLXBvC </t>
         </is>
       </c>
-      <c r="B688" t="inlineStr">
+      <c r="B687" t="inlineStr">
         <is>
           <t>images/「笑顔でいなさい」_img1.jpg</t>
         </is>
       </c>
-      <c r="C688" t="inlineStr">
+      <c r="C687" t="inlineStr">
         <is>
           <t>スマイル ,名言</t>
         </is>
       </c>
     </row>
-    <row r="689">
-      <c r="A689" t="inlineStr">
+    <row r="688">
+      <c r="A688" t="inlineStr">
         <is>
           <t xml:space="preserve">自動車メーカー
 ⁦・「TOYOTA」( تويوتا )⁩
@@ -14940,19 +14918,19 @@
 2308 syarah com </t>
         </is>
       </c>
-      <c r="B689" t="inlineStr">
+      <c r="B688" t="inlineStr">
         <is>
           <t>images/自動車メーカー_img1.jpg,images/自動車メーカー_img2.jpg,images/自動車メーカー_img3.jpg,images/自動車メーカー_img4.jpg</t>
         </is>
       </c>
-      <c r="C689" t="inlineStr">
+      <c r="C688" t="inlineStr">
         <is>
           <t>日本車 ,韓国車</t>
         </is>
       </c>
     </row>
-    <row r="690">
-      <c r="A690" t="inlineStr">
+    <row r="689">
+      <c r="A689" t="inlineStr">
         <is>
           <t xml:space="preserve">「僕たちは協力して不可能を達成するよ」
 بالتعاون نحقق المحال
@@ -14962,19 +14940,19 @@
 2109 </t>
         </is>
       </c>
-      <c r="B690" t="inlineStr">
+      <c r="B689" t="inlineStr">
         <is>
           <t>images/「僕たちは協力して不可能を達成するよ」_img1.jpg</t>
         </is>
       </c>
-      <c r="C690" t="inlineStr">
+      <c r="C689" t="inlineStr">
         <is>
           <t>無理 ,ハム太郎</t>
         </is>
       </c>
     </row>
-    <row r="691">
-      <c r="A691" t="inlineStr">
+    <row r="690">
+      <c r="A690" t="inlineStr">
         <is>
           <t xml:space="preserve">「幸せは伝染性。喜びを広めよう」
 السعادة معدية فأشع الفرح
@@ -14984,19 +14962,19 @@
 2511 instagram　com/p/fVEfxEo7Va/ </t>
         </is>
       </c>
-      <c r="B691" t="inlineStr">
+      <c r="B690" t="inlineStr">
         <is>
           <t>images/「幸せは伝染性。喜びを広めよう」_img1.jpg</t>
         </is>
       </c>
-      <c r="C691" t="inlineStr">
+      <c r="C690" t="inlineStr">
         <is>
           <t>拡散希望</t>
         </is>
       </c>
     </row>
-    <row r="692">
-      <c r="A692" t="inlineStr">
+    <row r="691">
+      <c r="A691" t="inlineStr">
         <is>
           <t xml:space="preserve">「ストレスは人間だけのものではない」
 الشعور بالتوتر ليس حكرًا على البشر
@@ -15004,19 +14982,19 @@
 2408 https://x.com/NatGeoMagArab/status/1736755816911487420 </t>
         </is>
       </c>
-      <c r="B692" t="inlineStr">
+      <c r="B691" t="inlineStr">
         <is>
           <t>images/「ストレスは人間だけのものではない」_img1.jpg</t>
         </is>
       </c>
-      <c r="C692" t="inlineStr">
+      <c r="C691" t="inlineStr">
         <is>
           <t>手書き語学 ,アラビア語 ,ストレス</t>
         </is>
       </c>
     </row>
-    <row r="693">
-      <c r="A693" t="inlineStr">
+    <row r="692">
+      <c r="A692" t="inlineStr">
         <is>
           <t xml:space="preserve">「私達は出来ます！」
 نستطيع فعلها
@@ -15026,19 +15004,19 @@
 2308 NAHARBAHIJ com </t>
         </is>
       </c>
-      <c r="B693" t="inlineStr">
+      <c r="B692" t="inlineStr">
         <is>
           <t>images/「私達は出来ます！」_img1.jpg</t>
         </is>
       </c>
-      <c r="C693" t="inlineStr">
+      <c r="C692" t="inlineStr">
         <is>
           <t>女性 ,パロディ</t>
         </is>
       </c>
     </row>
-    <row r="694">
-      <c r="A694" t="inlineStr">
+    <row r="693">
+      <c r="A693" t="inlineStr">
         <is>
           <t xml:space="preserve">「全然分からん」ولا فاهم إشي
 ウラー・ファーヒム・イシ [w-laa faahim 'iShy]
@@ -15048,19 +15026,19 @@
 2209 出典不明 </t>
         </is>
       </c>
-      <c r="B694" t="inlineStr">
+      <c r="B693" t="inlineStr">
         <is>
           <t>images/「全然分からん」_img1.jpg</t>
         </is>
       </c>
-      <c r="C694" t="inlineStr">
+      <c r="C693" t="inlineStr">
         <is>
           <t>アラビア語</t>
         </is>
       </c>
     </row>
-    <row r="695">
-      <c r="A695" t="inlineStr">
+    <row r="694">
+      <c r="A694" t="inlineStr">
         <is>
           <t xml:space="preserve">「人間は一人ひとり、特別な才がある。だから自分を他人と比べるのはやめよう」
 لكل إنسان مواهبه الخاصة 
@@ -15069,19 +15047,19 @@
 1812 Gwid3 </t>
         </is>
       </c>
-      <c r="B695" t="inlineStr">
+      <c r="B694" t="inlineStr">
         <is>
           <t>images/「人間は一人ひとり、特別な才がある。だ_img1.jpg</t>
         </is>
       </c>
-      <c r="C695" t="inlineStr">
+      <c r="C694" t="inlineStr">
         <is>
           <t>自尊 ,プライド</t>
         </is>
       </c>
     </row>
-    <row r="696">
-      <c r="A696" t="inlineStr">
+    <row r="695">
+      <c r="A695" t="inlineStr">
         <is>
           <t xml:space="preserve">「デザイン」تَصْمِيمٌ
 タスミーム [ta_smiim(un)]
@@ -15089,19 +15067,19 @@
 1903 arabictypography com </t>
         </is>
       </c>
-      <c r="B696" t="inlineStr">
+      <c r="B695" t="inlineStr">
         <is>
           <t>images/「デザイン」_img1.jpg</t>
         </is>
       </c>
-      <c r="C696" t="inlineStr">
+      <c r="C695" t="inlineStr">
         <is>
           <t>文字 ,タイポグラフィー</t>
         </is>
       </c>
     </row>
-    <row r="697">
-      <c r="A697" t="inlineStr">
+    <row r="696">
+      <c r="A696" t="inlineStr">
         <is>
           <t xml:space="preserve">「この猫は食事をシェアするのが嫌い！」
 هذه القطة لا تحب مشاركة الطعام
@@ -15110,19 +15088,19 @@
 2605 facebook com/alahram/videos/2154923608133231/ </t>
         </is>
       </c>
-      <c r="B697" t="inlineStr">
+      <c r="B696" t="inlineStr">
         <is>
           <t>images/「この猫は食事をシェアするのが嫌い！」_img1.jpg</t>
         </is>
       </c>
-      <c r="C697" t="inlineStr">
+      <c r="C696" t="inlineStr">
         <is>
           <t>猫 ,ネコ</t>
         </is>
       </c>
     </row>
-    <row r="698">
-      <c r="A698" t="inlineStr">
+    <row r="697">
+      <c r="A697" t="inlineStr">
         <is>
           <t xml:space="preserve">「怪獣との戦いでは自分が怪獣化せぬよう警戒しなさい」
 احذر عند محاربة الوحوش ألا تصبح واحدا منهم
@@ -15132,19 +15110,19 @@
 2108 warag-3nb.tumblr </t>
         </is>
       </c>
-      <c r="B698" t="inlineStr">
+      <c r="B697" t="inlineStr">
         <is>
           <t>images/「怪獣との戦いでは自分が怪獣化せぬよう_img1.jpg,images/ 「怪獣との戦いでは自分が怪獣化せぬよう_img2.jpg</t>
         </is>
       </c>
-      <c r="C698" t="inlineStr">
+      <c r="C697" t="inlineStr">
         <is>
           <t>正気 ,モンスター</t>
         </is>
       </c>
     </row>
-    <row r="699">
-      <c r="A699" t="inlineStr">
+    <row r="698">
+      <c r="A698" t="inlineStr">
         <is>
           <t xml:space="preserve">「錯視アート」فن الخداع البصري
 ファンヌ_ルヒダーイ_ルバサリーイ [fannu l-Khidaa*i l-ba_sariyy]
@@ -15153,19 +15131,19 @@
 2409 https://online.pubhtml5.com/idtb/neft/ </t>
         </is>
       </c>
-      <c r="B699" t="inlineStr">
+      <c r="B698" t="inlineStr">
         <is>
           <t>images/「錯視アート」_img1.jpg</t>
         </is>
       </c>
-      <c r="C699" t="inlineStr">
+      <c r="C698" t="inlineStr">
         <is>
           <t>トリックアート</t>
         </is>
       </c>
     </row>
-    <row r="700">
-      <c r="A700" t="inlineStr">
+    <row r="699">
+      <c r="A699" t="inlineStr">
         <is>
           <t xml:space="preserve">「自然界の消防士の訓練」
 تدريبات رجال الإطفاء في الطبيعة
@@ -15173,19 +15151,19 @@
 2308 https://twitter.com/NatGeoMagArab/status/1462420543890608129 </t>
         </is>
       </c>
-      <c r="B700" t="inlineStr">
+      <c r="B699" t="inlineStr">
         <is>
           <t>images/「自然界の消防士の訓練」_img1.jpg,images/ 「自然界の消防士の訓練」_img2.jpg</t>
         </is>
       </c>
-      <c r="C700" t="inlineStr">
+      <c r="C699" t="inlineStr">
         <is>
           <t>手書き語学 ,アラビア語 ,ヒグマ</t>
         </is>
       </c>
     </row>
-    <row r="701">
-      <c r="A701" t="inlineStr">
+    <row r="700">
+      <c r="A700" t="inlineStr">
         <is>
           <t xml:space="preserve">「救助」إسعاف
 イスアーフ ['is*aaf]
@@ -15194,19 +15172,19 @@
 2109 ambulance gov ae </t>
         </is>
       </c>
-      <c r="B701" t="inlineStr">
+      <c r="B700" t="inlineStr">
         <is>
           <t>images/「救助」_img1.jpg</t>
         </is>
       </c>
-      <c r="C701" t="inlineStr">
+      <c r="C700" t="inlineStr">
         <is>
           <t>救急車 ,はたらくくるま</t>
         </is>
       </c>
     </row>
-    <row r="702">
-      <c r="A702" t="inlineStr">
+    <row r="701">
+      <c r="A701" t="inlineStr">
         <is>
           <t xml:space="preserve">「感情／感覚」الإحْسَاسْ
 アルイヒサース [al-'iHsaas]
@@ -15215,19 +15193,19 @@
 2308 iN49R </t>
         </is>
       </c>
-      <c r="B702" t="inlineStr">
+      <c r="B701" t="inlineStr">
         <is>
           <t>images/「感情／感覚」_img1.jpg</t>
         </is>
       </c>
-      <c r="C702" t="inlineStr">
+      <c r="C701" t="inlineStr">
         <is>
           <t>オフ ,一休み</t>
         </is>
       </c>
     </row>
-    <row r="703">
-      <c r="A703" t="inlineStr">
+    <row r="702">
+      <c r="A702" t="inlineStr">
         <is>
           <t xml:space="preserve">「ひらめき」إلهام
 イルハーム ['lhaam]
@@ -15239,19 +15217,19 @@
 2103 出典不明 </t>
         </is>
       </c>
-      <c r="B703" t="inlineStr">
+      <c r="B702" t="inlineStr">
         <is>
           <t>images/「ひらめき」_img1.jpg</t>
         </is>
       </c>
-      <c r="C703" t="inlineStr">
+      <c r="C702" t="inlineStr">
         <is>
           <t>アラビア語</t>
         </is>
       </c>
     </row>
-    <row r="704">
-      <c r="A704" t="inlineStr">
+    <row r="703">
+      <c r="A703" t="inlineStr">
         <is>
           <t xml:space="preserve">「Ibdaa／クリエイティビティ」
 إبداع
@@ -15260,19 +15238,19 @@
 2308 Ibdaa Design &amp; Decoration Office </t>
         </is>
       </c>
-      <c r="B704" t="inlineStr">
+      <c r="B703" t="inlineStr">
         <is>
           <t>images/「Ibdaa／クリエイティビティ」_img1.jpg</t>
         </is>
       </c>
-      <c r="C704" t="inlineStr">
+      <c r="C703" t="inlineStr">
         <is>
           <t>創造性 ,独自性</t>
         </is>
       </c>
     </row>
-    <row r="705">
-      <c r="A705" t="inlineStr">
+    <row r="704">
+      <c r="A704" t="inlineStr">
         <is>
           <t xml:space="preserve">「奮闘なくして進歩なし」
 بدون كفاح لايوجد تقدم
@@ -15282,19 +15260,19 @@
 2105 ROUYMS TUMBLR COM </t>
         </is>
       </c>
-      <c r="B705" t="inlineStr">
+      <c r="B704" t="inlineStr">
         <is>
           <t>images/「奮闘なくして進歩なし」_img1.jpg</t>
         </is>
       </c>
-      <c r="C705" t="inlineStr">
+      <c r="C704" t="inlineStr">
         <is>
           <t>努力 ,三角形</t>
         </is>
       </c>
     </row>
-    <row r="706">
-      <c r="A706" t="inlineStr">
+    <row r="705">
+      <c r="A705" t="inlineStr">
         <is>
           <t xml:space="preserve">「木に登れば熊の危険を避けられるとお考えなら、考え直しましょう！」 
 إن اعتقدت أنك بمنأى عن خطر الدب عند تسلق الأشجار.. راجع حساباتك
@@ -15302,19 +15280,19 @@
 2202 NatGeoMagArab </t>
         </is>
       </c>
-      <c r="B706" t="inlineStr">
+      <c r="B705" t="inlineStr">
         <is>
           <t>images/「木に登れば熊の危険を避けられるとお考.jpeg</t>
         </is>
       </c>
-      <c r="C706" t="inlineStr">
+      <c r="C705" t="inlineStr">
         <is>
           <t>クマ</t>
         </is>
       </c>
     </row>
-    <row r="707">
-      <c r="A707" t="inlineStr">
+    <row r="706">
+      <c r="A706" t="inlineStr">
         <is>
           <t xml:space="preserve">「卒業おめでとう」مبروك التخرج
 マブルーク・タカッルジ [mabruuk a^taKharruj]
@@ -15323,19 +15301,19 @@
 2308 https://instagram.com/fatoomworld </t>
         </is>
       </c>
-      <c r="B707" t="inlineStr">
+      <c r="B706" t="inlineStr">
         <is>
           <t>images/「卒業おめでとう」_img1.jpg</t>
         </is>
       </c>
-      <c r="C707" t="inlineStr">
+      <c r="C706" t="inlineStr">
         <is>
           <t>卒業 ,イラスト</t>
         </is>
       </c>
     </row>
-    <row r="708">
-      <c r="A708" t="inlineStr">
+    <row r="707">
+      <c r="A707" t="inlineStr">
         <is>
           <t xml:space="preserve">「停止距離の計算」
 حساب مسافة التوقف
@@ -15345,19 +15323,19 @@
 2109 assurance-auto-info </t>
         </is>
       </c>
-      <c r="B708" t="inlineStr">
+      <c r="B707" t="inlineStr">
         <is>
           <t>images/「停止距離の計算」_img1.jpg</t>
         </is>
       </c>
-      <c r="C708" t="inlineStr">
+      <c r="C707" t="inlineStr">
         <is>
           <t>保険 ,自動車</t>
         </is>
       </c>
     </row>
-    <row r="709">
-      <c r="A709" t="inlineStr">
+    <row r="708">
+      <c r="A708" t="inlineStr">
         <is>
           <t xml:space="preserve">「教師要らず：10日でフランス語会話」
 بدون معلم
@@ -15367,19 +15345,19 @@
 2308 englais-best com </t>
         </is>
       </c>
-      <c r="B709" t="inlineStr">
+      <c r="B708" t="inlineStr">
         <is>
           <t>images/「教師要らず：10日でフランス語会話」_img1.jpg</t>
         </is>
       </c>
-      <c r="C709" t="inlineStr">
+      <c r="C708" t="inlineStr">
         <is>
           <t>教師なし学習</t>
         </is>
       </c>
     </row>
-    <row r="710">
-      <c r="A710" t="inlineStr">
+    <row r="709">
+      <c r="A709" t="inlineStr">
         <is>
           <t xml:space="preserve">「衝突」تصادم
 タサードゥム [ta_saadum]
@@ -15388,19 +15366,19 @@
 1810 </t>
         </is>
       </c>
-      <c r="B710" t="inlineStr">
+      <c r="B709" t="inlineStr">
         <is>
           <t>images/「衝突」_img1.jpg</t>
         </is>
       </c>
-      <c r="C710" t="inlineStr">
+      <c r="C709" t="inlineStr">
         <is>
           <t>あらびあや</t>
         </is>
       </c>
     </row>
-    <row r="711">
-      <c r="A711" t="inlineStr">
+    <row r="710">
+      <c r="A710" t="inlineStr">
         <is>
           <t xml:space="preserve">「楽観主義」تَفَاؤُلٌ
 タファーウル [tafaa'ul(un)]
@@ -15409,19 +15387,19 @@
 1904 arabictypography com </t>
         </is>
       </c>
-      <c r="B711" t="inlineStr">
+      <c r="B710" t="inlineStr">
         <is>
           <t>images/「楽観主義」_img1.jpg</t>
         </is>
       </c>
-      <c r="C711" t="inlineStr">
+      <c r="C710" t="inlineStr">
         <is>
           <t>やわらか ,緑</t>
         </is>
       </c>
     </row>
-    <row r="712">
-      <c r="A712" t="inlineStr">
+    <row r="711">
+      <c r="A711" t="inlineStr">
         <is>
           <t xml:space="preserve">「シベリアジャコウジカは、絶滅の危機にあると見なされている」
 يعد "أيل المسك السيبيري" مهددًا بالانقراض
@@ -15429,19 +15407,19 @@
 2308 https://twitter.com/NatGeoMagArab/status/1320666649045790720 </t>
         </is>
       </c>
-      <c r="B712" t="inlineStr">
+      <c r="B711" t="inlineStr">
         <is>
           <t>images/「シベリアジャコウジカは、絶滅の危機に_img1.jpg,images/「シベリアジャコウジカは、絶滅の危機に_img2.jpg</t>
         </is>
       </c>
-      <c r="C712" t="inlineStr">
+      <c r="C711" t="inlineStr">
         <is>
           <t>手書き語学 ,シベリア</t>
         </is>
       </c>
     </row>
-    <row r="713">
-      <c r="A713" t="inlineStr">
+    <row r="712">
+      <c r="A712" t="inlineStr">
         <is>
           <t xml:space="preserve">「融合／折衷／フュージョン」
 انصهار
@@ -15450,38 +15428,38 @@
 1811 elmahdyart Instagram </t>
         </is>
       </c>
-      <c r="B713" t="inlineStr">
+      <c r="B712" t="inlineStr">
         <is>
           <t>images/「融合／折衷／フュージョン」_img1.jpg</t>
         </is>
       </c>
-      <c r="C713" t="inlineStr">
+      <c r="C712" t="inlineStr">
         <is>
           <t>カリグラフィー ,書道</t>
         </is>
       </c>
     </row>
-    <row r="714">
-      <c r="A714" t="inlineStr">
+    <row r="713">
+      <c r="A713" t="inlineStr">
         <is>
           <t xml:space="preserve">「この子供は、昼寝をしようとする母親を邪魔しているようだ」
 「場所はインドのトラ保護区、バンダウガル公園。トラは生態ピラミッドのトップの捕食動物だが、最もリスクの高い絶滅危惧種のひとつである」
 2308 https://twitter.com/natgeomagarab/status/1553681890665586689 </t>
         </is>
       </c>
-      <c r="B714" t="inlineStr">
+      <c r="B713" t="inlineStr">
         <is>
           <t>images/「この子供は、昼寝をしようとする母親を_img1.jpg,images/「この子供は、昼寝をしようとする母親を_img2.jpg</t>
         </is>
       </c>
-      <c r="C714" t="inlineStr">
+      <c r="C713" t="inlineStr">
         <is>
           <t>手書き語学 ,アラビア語 ,トラ</t>
         </is>
       </c>
     </row>
-    <row r="715">
-      <c r="A715" t="inlineStr">
+    <row r="714">
+      <c r="A714" t="inlineStr">
         <is>
           <t xml:space="preserve">「もし敬意が落ちたら、それと一緒に全部落ちるのだ」
 إن سقط الإحترام سقط معه كل شيء
@@ -15490,19 +15468,19 @@
 2109 出典不明 </t>
         </is>
       </c>
-      <c r="B715" t="inlineStr">
+      <c r="B714" t="inlineStr">
         <is>
           <t>images/「もし敬意が落ちたら、それと一緒に全部_img1.jpg</t>
         </is>
       </c>
-      <c r="C715" t="inlineStr">
+      <c r="C714" t="inlineStr">
         <is>
           <t>リスペクト ,落書き</t>
         </is>
       </c>
     </row>
-    <row r="716">
-      <c r="A716" t="inlineStr">
+    <row r="715">
+      <c r="A715" t="inlineStr">
         <is>
           <t xml:space="preserve">「エジプト特許庁」
 مكتب براءات الاختراع المصرى
@@ -15512,19 +15490,19 @@
 2312 </t>
         </is>
       </c>
-      <c r="B716" t="inlineStr">
+      <c r="B715" t="inlineStr">
         <is>
           <t>images/「エジプト特許庁」_img1.jpg</t>
         </is>
       </c>
-      <c r="C716" t="inlineStr">
+      <c r="C715" t="inlineStr">
         <is>
           <t>patent</t>
         </is>
       </c>
     </row>
-    <row r="717">
-      <c r="A717" t="inlineStr">
+    <row r="716">
+      <c r="A716" t="inlineStr">
         <is>
           <t xml:space="preserve">「選挙」إنتخابات
 インティカーバート [intiKhaabaat]
@@ -15533,19 +15511,19 @@
 2311 nna-leb gov lb </t>
         </is>
       </c>
-      <c r="B717" t="inlineStr">
+      <c r="B716" t="inlineStr">
         <is>
           <t>images/「選挙」_img1.jpg</t>
         </is>
       </c>
-      <c r="C717" t="inlineStr">
+      <c r="C716" t="inlineStr">
         <is>
           <t>選挙 ,投票</t>
         </is>
       </c>
     </row>
-    <row r="718">
-      <c r="A718" t="inlineStr">
+    <row r="717">
+      <c r="A717" t="inlineStr">
         <is>
           <t xml:space="preserve">「待ちぼうけ」إنتظار
 インティザール [inti_Dhaar]
@@ -15554,19 +15532,19 @@
 1809 in4sser.tumblr </t>
         </is>
       </c>
-      <c r="B718" t="inlineStr">
+      <c r="B717" t="inlineStr">
         <is>
           <t>images/「待ちぼうけ」_img1.jpg</t>
         </is>
       </c>
-      <c r="C718" t="inlineStr">
+      <c r="C717" t="inlineStr">
         <is>
           <t>遅すぎ ,辛抱</t>
         </is>
       </c>
     </row>
-    <row r="719">
-      <c r="A719" t="inlineStr">
+    <row r="718">
+      <c r="A718" t="inlineStr">
         <is>
           <t xml:space="preserve">「試験」إختبار
 イクティバール [iKhtibaar]
@@ -15575,19 +15553,19 @@
 2109 出典不明 </t>
         </is>
       </c>
-      <c r="B719" t="inlineStr">
+      <c r="B718" t="inlineStr">
         <is>
           <t>images/「試験」_img1.jpg</t>
         </is>
       </c>
-      <c r="C719" t="inlineStr">
+      <c r="C718" t="inlineStr">
         <is>
           <t>テスト ,考査</t>
         </is>
       </c>
     </row>
-    <row r="720">
-      <c r="A720" t="inlineStr">
+    <row r="719">
+      <c r="A719" t="inlineStr">
         <is>
           <t xml:space="preserve">「チャンネル登録」اشتراك
 イシティラーク [iShtiraak]
@@ -15596,19 +15574,19 @@
 2308 </t>
         </is>
       </c>
-      <c r="B720" t="inlineStr">
+      <c r="B719" t="inlineStr">
         <is>
           <t>images/「チャンネル登録」_img1.jpg</t>
         </is>
       </c>
-      <c r="C720" t="inlineStr">
+      <c r="C719" t="inlineStr">
         <is>
           <t>Subscribe ,YouTube</t>
         </is>
       </c>
     </row>
-    <row r="721">
-      <c r="A721" t="inlineStr">
+    <row r="720">
+      <c r="A720" t="inlineStr">
         <is>
           <t xml:space="preserve">「スマイル」ابتسام
 イブティサーム [ibtisaam]
@@ -15616,37 +15594,37 @@
 1903 behance Written-Visuals </t>
         </is>
       </c>
+      <c r="B720" t="inlineStr">
+        <is>
+          <t>images/「スマイル」_img1.jpg</t>
+        </is>
+      </c>
+      <c r="C720" t="inlineStr">
+        <is>
+          <t>スマイリー ,ツ</t>
+        </is>
+      </c>
+    </row>
+    <row r="721">
+      <c r="A721" t="inlineStr">
+        <is>
+          <t xml:space="preserve">「身体の一部として…」
+2308 https://twitter.com/NatGeoMagArab/status/1528292080337813504 </t>
+        </is>
+      </c>
       <c r="B721" t="inlineStr">
         <is>
-          <t>images/「スマイル」_img1.jpg</t>
+          <t>images/「身体の一部として…」_img1.jpg</t>
         </is>
       </c>
       <c r="C721" t="inlineStr">
         <is>
-          <t>スマイリー ,ツ</t>
+          <t>手書き語学 ,カンガルー</t>
         </is>
       </c>
     </row>
     <row r="722">
       <c r="A722" t="inlineStr">
-        <is>
-          <t xml:space="preserve">「身体の一部として…」
-2308 https://twitter.com/NatGeoMagArab/status/1528292080337813504 </t>
-        </is>
-      </c>
-      <c r="B722" t="inlineStr">
-        <is>
-          <t>images/「身体の一部として…」_img1.jpg</t>
-        </is>
-      </c>
-      <c r="C722" t="inlineStr">
-        <is>
-          <t>手書き語学 ,カンガルー</t>
-        </is>
-      </c>
-    </row>
-    <row r="723">
-      <c r="A723" t="inlineStr">
         <is>
           <t xml:space="preserve">「ディスカバリー」إكتشاف
 イクティシャーフ [iktiShaaf]
@@ -15654,19 +15632,19 @@
 2308 tephanegabrielli com </t>
         </is>
       </c>
-      <c r="B723" t="inlineStr">
+      <c r="B722" t="inlineStr">
         <is>
           <t>images/「ディスカバリー」_img1.jpg</t>
         </is>
       </c>
-      <c r="C723" t="inlineStr">
+      <c r="C722" t="inlineStr">
         <is>
           <t>discovery ,デザイン</t>
         </is>
       </c>
     </row>
-    <row r="724">
-      <c r="A724" t="inlineStr">
+    <row r="723">
+      <c r="A723" t="inlineStr">
         <is>
           <t xml:space="preserve">「重力波の発見は新しい窓を開いた」
 فتَح اكتشاف موجات الجاذبية نافذة جديدة
@@ -15674,19 +15652,19 @@
 2308 https://twitter.com/SciTalk2U/status/1454891943440289793 </t>
         </is>
       </c>
-      <c r="B724" t="inlineStr">
+      <c r="B723" t="inlineStr">
         <is>
           <t>images/「重力波の発見は新しい窓を開いた」_img1.jpg</t>
         </is>
       </c>
-      <c r="C724" t="inlineStr">
+      <c r="C723" t="inlineStr">
         <is>
           <t>手書き語学 ,アラビア語 ,重力波</t>
         </is>
       </c>
     </row>
-    <row r="725">
-      <c r="A725" t="inlineStr">
+    <row r="724">
+      <c r="A724" t="inlineStr">
         <is>
           <t xml:space="preserve">「微笑みに微笑み。先にした人の方が美しい」
 الإبتسامة بالإبتسامة والبادئ أجمل
@@ -15695,19 +15673,19 @@
 2104 出典不明 </t>
         </is>
       </c>
-      <c r="B725" t="inlineStr">
+      <c r="B724" t="inlineStr">
         <is>
           <t>images/「微笑みに微笑み。先にした人の方が美し_img1.jpg,images/「微笑みに微笑み。先にした人の方が美し_img2.jpg</t>
         </is>
       </c>
-      <c r="C725" t="inlineStr">
+      <c r="C724" t="inlineStr">
         <is>
           <t>スマイル ,名言</t>
         </is>
       </c>
     </row>
-    <row r="726">
-      <c r="A726" t="inlineStr">
+    <row r="725">
+      <c r="A725" t="inlineStr">
         <is>
           <t xml:space="preserve">「笑顔」ابتسامة
 イブティサーマ [ibtisaama(tun)]
@@ -15716,19 +15694,19 @@
 2308 satokomatsu, minne </t>
         </is>
       </c>
-      <c r="B726" t="inlineStr">
+      <c r="B725" t="inlineStr">
         <is>
           <t>images/「笑顔」_img1.jpg</t>
         </is>
       </c>
-      <c r="C726" t="inlineStr">
+      <c r="C725" t="inlineStr">
         <is>
           <t>スマイル ,ツ</t>
         </is>
       </c>
     </row>
-    <row r="727">
-      <c r="A727" t="inlineStr">
+    <row r="726">
+      <c r="A726" t="inlineStr">
         <is>
           <t xml:space="preserve">「信仰」ايمان
 イーマーン ['iimaan]
@@ -15737,19 +15715,19 @@
 2506 instagram com/p/6ST-WHOOkJ/ </t>
         </is>
       </c>
-      <c r="B727" t="inlineStr">
+      <c r="B726" t="inlineStr">
         <is>
           <t>images/「信仰」_img1.jpg</t>
         </is>
       </c>
-      <c r="C727" t="inlineStr">
+      <c r="C726" t="inlineStr">
         <is>
           <t>宗教 ,信念</t>
         </is>
       </c>
     </row>
-    <row r="728">
-      <c r="A728" t="inlineStr">
+    <row r="727">
+      <c r="A727" t="inlineStr">
         <is>
           <t xml:space="preserve">「放送」إذاعة
 イザーア ['iDhaa*a]
@@ -15758,19 +15736,19 @@
 2404 heemades, Instagram </t>
         </is>
       </c>
-      <c r="B728" t="inlineStr">
+      <c r="B727" t="inlineStr">
         <is>
           <t>images/「放送」_img1.jpg</t>
         </is>
       </c>
-      <c r="C728" t="inlineStr">
+      <c r="C727" t="inlineStr">
         <is>
           <t>デザイン ,ラジオ</t>
         </is>
       </c>
     </row>
-    <row r="729">
-      <c r="A729" t="inlineStr">
+    <row r="728">
+      <c r="A728" t="inlineStr">
         <is>
           <t xml:space="preserve">「かきとりのちから」
 مهاراتي الإملائية
@@ -15779,19 +15757,19 @@
 2308 iqrawaoktoub.wordpress com </t>
         </is>
       </c>
-      <c r="B729" t="inlineStr">
+      <c r="B728" t="inlineStr">
         <is>
           <t>images/「かきとりのちから」_img1.jpg</t>
         </is>
       </c>
-      <c r="C729" t="inlineStr">
+      <c r="C728" t="inlineStr">
         <is>
           <t>国語 ,教材</t>
         </is>
       </c>
     </row>
-    <row r="730">
-      <c r="A730" t="inlineStr">
+    <row r="729">
+      <c r="A729" t="inlineStr">
         <is>
           <t xml:space="preserve">「歴史を作った男たち」
 رجال صنعوا التاريخ
@@ -15801,38 +15779,38 @@
 2410 https://x.gd/Wl5rJ </t>
         </is>
       </c>
-      <c r="B730" t="inlineStr">
+      <c r="B729" t="inlineStr">
         <is>
           <t>images/「歴史を作った男たち」_img1.jpg</t>
         </is>
       </c>
-      <c r="C730" t="inlineStr">
+      <c r="C729" t="inlineStr">
         <is>
           <t>偉人</t>
         </is>
       </c>
     </row>
-    <row r="731">
-      <c r="A731" t="inlineStr">
+    <row r="730">
+      <c r="A730" t="inlineStr">
         <is>
           <t xml:space="preserve">「無限の宇宙を旅した光」
 「何百年もの末にジェイムズ・ウェッブ望遠鏡のレンズの上に落ち、我々に遠い宇宙の美しさを見せてくれる。最も純粋な形と最も素晴らしい姿で」
 2308 https://twitter.com/NatGeoMagArab/status/1557811592636485632 </t>
         </is>
       </c>
-      <c r="B731" t="inlineStr">
+      <c r="B730" t="inlineStr">
         <is>
           <t>images/「無限の宇宙を旅した光」_img1.jpg</t>
         </is>
       </c>
-      <c r="C731" t="inlineStr">
+      <c r="C730" t="inlineStr">
         <is>
           <t>手書き語学 ,宇宙</t>
         </is>
       </c>
     </row>
-    <row r="732">
-      <c r="A732" t="inlineStr">
+    <row r="731">
+      <c r="A731" t="inlineStr">
         <is>
           <t xml:space="preserve">「日本好きになり行きたくなる20項」
 عشرون شيئا يجعلك تحب اليابان وترغب في زيارتها
@@ -15841,19 +15819,19 @@
 2308 wattpad </t>
         </is>
       </c>
-      <c r="B732" t="inlineStr">
+      <c r="B731" t="inlineStr">
         <is>
           <t>images/「日本好きになり行きたくなる20項」_img1.jpg</t>
         </is>
       </c>
-      <c r="C732" t="inlineStr">
+      <c r="C731" t="inlineStr">
         <is>
           <t>اليابان ,Japan</t>
         </is>
       </c>
     </row>
-    <row r="733">
-      <c r="A733" t="inlineStr">
+    <row r="732">
+      <c r="A732" t="inlineStr">
         <is>
           <t xml:space="preserve">「ピッタリの瞬間に撮影され、ドラゴンが火を噴いているように見える」
 التُقطت في اللحظة المناسبة لتبدو مثل تنين ينفث اللهب
@@ -15861,19 +15839,19 @@
 2509 https://twitter.com/NatGeoMagArab/status/1588780660269150208 </t>
         </is>
       </c>
-      <c r="B733" t="inlineStr">
+      <c r="B732" t="inlineStr">
         <is>
           <t>images/「ピッタリの瞬間に撮影され、ドラゴンが_img1.jpg,images/ 「ピッタリの瞬間に撮影され、ドラゴンが_img2.jpg</t>
         </is>
       </c>
-      <c r="C733" t="inlineStr">
+      <c r="C732" t="inlineStr">
         <is>
           <t xml:space="preserve">ドラゴン </t>
         </is>
       </c>
     </row>
-    <row r="734">
-      <c r="A734" t="inlineStr">
+    <row r="733">
+      <c r="A733" t="inlineStr">
         <is>
           <t xml:space="preserve">「満足は不滅の宝である」
 القَناعَةُ كنز لا يَفنَى
@@ -15883,55 +15861,55 @@
 2308 kareem mrghani </t>
         </is>
       </c>
+      <c r="B733" t="inlineStr">
+        <is>
+          <t>images/「満足は不滅の宝である」_img1.jpg</t>
+        </is>
+      </c>
+      <c r="C733" t="inlineStr">
+        <is>
+          <t>幸福度</t>
+        </is>
+      </c>
+    </row>
+    <row r="734">
+      <c r="A734" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ゴシキセイガイインコ。
+2409 https://twitter.com/NatGeoMagArab/status/1600022262014676992 </t>
+        </is>
+      </c>
       <c r="B734" t="inlineStr">
         <is>
-          <t>images/「満足は不滅の宝である」_img1.jpg</t>
+          <t>images/ゴシキセイガイインコ。_img1.jpg</t>
         </is>
       </c>
       <c r="C734" t="inlineStr">
         <is>
-          <t>幸福度</t>
+          <t>手書き語学 ,アラビア語,オウム</t>
         </is>
       </c>
     </row>
     <row r="735">
       <c r="A735" t="inlineStr">
         <is>
-          <t xml:space="preserve">ゴシキセイガイインコ。
-2409 https://twitter.com/NatGeoMagArab/status/1600022262014676992 </t>
+          <t xml:space="preserve">モモンガ。
+2403 https://twitter.com/NatGeoMagArab/status/1552541872966344704 </t>
         </is>
       </c>
       <c r="B735" t="inlineStr">
         <is>
-          <t>images/ゴシキセイガイインコ。_img1.jpg</t>
+          <t>images/モモンガ。_img1.jpg,images/ モモンガ。_img2.jpg</t>
         </is>
       </c>
       <c r="C735" t="inlineStr">
         <is>
-          <t>手書き語学 ,アラビア語,オウム</t>
+          <t>手書き語学 ,アラビア語 ,モモンガ</t>
         </is>
       </c>
     </row>
     <row r="736">
       <c r="A736" t="inlineStr">
-        <is>
-          <t xml:space="preserve">モモンガ。
-2403 https://twitter.com/NatGeoMagArab/status/1552541872966344704 </t>
-        </is>
-      </c>
-      <c r="B736" t="inlineStr">
-        <is>
-          <t>images/モモンガ。_img1.jpg,images/ モモンガ。_img2.jpg</t>
-        </is>
-      </c>
-      <c r="C736" t="inlineStr">
-        <is>
-          <t>手書き語学 ,アラビア語 ,モモンガ</t>
-        </is>
-      </c>
-    </row>
-    <row r="737">
-      <c r="A737" t="inlineStr">
         <is>
           <t xml:space="preserve">「象の群れ。ドローンの音から逃げている」
 قطيع من الفيلة يفر هاربًا من صوت الدرون
@@ -15943,56 +15921,56 @@
 2009 https://twitter.com/NatGeoMagArab/status/1302970033627258881 </t>
         </is>
       </c>
+      <c r="B736" t="inlineStr">
+        <is>
+          <t>images/「象の群れ。ドローンの音から逃げている.jpg</t>
+        </is>
+      </c>
+      <c r="C736" t="inlineStr">
+        <is>
+          <t>ゾウ ,ドローン</t>
+        </is>
+      </c>
+    </row>
+    <row r="737">
+      <c r="A737" t="inlineStr">
+        <is>
+          <t xml:space="preserve">カルマン線。
+2308 https://twitter.com/NatGeoMagArab/status/1536436999522881536 </t>
+        </is>
+      </c>
       <c r="B737" t="inlineStr">
         <is>
-          <t>images/「象の群れ。ドローンの音から逃げている.jpg</t>
+          <t>images/カルマン線。_img1.jpg</t>
         </is>
       </c>
       <c r="C737" t="inlineStr">
         <is>
-          <t>ゾウ ,ドローン</t>
+          <t xml:space="preserve">手書き語学 ,アラビア語 ,宇宙 </t>
         </is>
       </c>
     </row>
     <row r="738">
       <c r="A738" t="inlineStr">
-        <is>
-          <t xml:space="preserve">カルマン線。
-2308 https://twitter.com/NatGeoMagArab/status/1536436999522881536 </t>
-        </is>
-      </c>
-      <c r="B738" t="inlineStr">
-        <is>
-          <t>images/カルマン線。_img1.jpg</t>
-        </is>
-      </c>
-      <c r="C738" t="inlineStr">
-        <is>
-          <t xml:space="preserve">手書き語学 ,アラビア語 ,宇宙 </t>
-        </is>
-      </c>
-    </row>
-    <row r="739">
-      <c r="A739" t="inlineStr">
         <is>
           <t xml:space="preserve">「恥ずかしがり屋のマヌルネコと暖かい朝の太陽光線」
 ⁦「二つの美しいもの」[Shay'-ayni jamiil-ayni] 属格：「物」( شيء )[Shay']・「美しい」( جميل )[jamiil]⁩
 2309 https://twitter.com/NatGeoMagArab/status/1697512148820504912 </t>
         </is>
       </c>
-      <c r="B739" t="inlineStr">
+      <c r="B738" t="inlineStr">
         <is>
           <t>images/「恥ずかしがり屋のマヌルネコと暖かい朝_img1.jpg</t>
         </is>
       </c>
-      <c r="C739" t="inlineStr">
+      <c r="C738" t="inlineStr">
         <is>
           <t>手書き語学 ,アラビア語 ,マヌルネコ</t>
         </is>
       </c>
     </row>
-    <row r="740">
-      <c r="A740" t="inlineStr">
+    <row r="739">
+      <c r="A739" t="inlineStr">
         <is>
           <t xml:space="preserve">「二回失敗しているペンギン」
 بطريق يفشل مرتين
@@ -16002,19 +15980,19 @@
 2308 https://twitter.com/NatGeoMagArab/status/1479483133766426626 </t>
         </is>
       </c>
-      <c r="B740" t="inlineStr">
+      <c r="B739" t="inlineStr">
         <is>
           <t>images/「二回失敗しているペンギン」_img1.jpg</t>
         </is>
       </c>
-      <c r="C740" t="inlineStr">
+      <c r="C739" t="inlineStr">
         <is>
           <t>ペンギン ,動物</t>
         </is>
       </c>
     </row>
-    <row r="741">
-      <c r="A741" t="inlineStr">
+    <row r="740">
+      <c r="A740" t="inlineStr">
         <is>
           <t xml:space="preserve">「2億光年の彼方できらめく炎と光」
 وهج ووميض يتلألأ على بعد 200 مليون سنة ضوئية
@@ -16025,15 +16003,15 @@
 2010 https://twitter.com/NatGeoMagArab/status/1303415502673342464 </t>
         </is>
       </c>
-      <c r="B741" t="inlineStr"/>
-      <c r="C741" t="inlineStr">
+      <c r="B740" t="inlineStr"/>
+      <c r="C740" t="inlineStr">
         <is>
           <t>宇宙 ,銀河</t>
         </is>
       </c>
     </row>
-    <row r="742">
-      <c r="A742" t="inlineStr">
+    <row r="741">
+      <c r="A741" t="inlineStr">
         <is>
           <t xml:space="preserve">「さまよう黒猫」قطة سوداء تجوب
 キッタトゥン・サウダーウ・タジューブ [qi^_tatun sawdaa'u ta-juub]
@@ -16042,19 +16020,19 @@
 2308 https://twitter.com/NatGeoMagArab/status/1532973177453760512 </t>
         </is>
       </c>
-      <c r="B742" t="inlineStr">
+      <c r="B741" t="inlineStr">
         <is>
           <t>images/「さまよう黒猫」_img1.jpg,images/ 「さまよう黒猫」_img2.jpg</t>
         </is>
       </c>
-      <c r="C742" t="inlineStr">
+      <c r="C741" t="inlineStr">
         <is>
           <t xml:space="preserve">手書き語学 ,モロッコ </t>
         </is>
       </c>
     </row>
-    <row r="743">
-      <c r="A743" t="inlineStr">
+    <row r="742">
+      <c r="A742" t="inlineStr">
         <is>
           <t xml:space="preserve">「サイのざらざらした皮を利用して自分の体を掻くネコ」
 قطة تستغل جلد الكركدن الخشن لحك جسدها
@@ -16063,19 +16041,19 @@
 2308 https://twitter.com/NatGeoMagArab/status/1476855740929216517 </t>
         </is>
       </c>
-      <c r="B743" t="inlineStr">
+      <c r="B742" t="inlineStr">
         <is>
           <t>images/「サイのざらざらした皮を利用して自分の_img1.jpg</t>
         </is>
       </c>
-      <c r="C743" t="inlineStr">
+      <c r="C742" t="inlineStr">
         <is>
           <t>サイ ,チェコ</t>
         </is>
       </c>
     </row>
-    <row r="744">
-      <c r="A744" t="inlineStr">
+    <row r="743">
+      <c r="A743" t="inlineStr">
         <is>
           <t xml:space="preserve">「沈まぬ太陽」شمس لا تغيب
 シャムス・ラー・タギーブ [Shams laa ta-Ghiib]
@@ -16084,19 +16062,19 @@
 2308 AHMED ELASSAL </t>
         </is>
       </c>
-      <c r="B744" t="inlineStr">
+      <c r="B743" t="inlineStr">
         <is>
           <t>images/「沈まぬ太陽」_img1.jpg</t>
         </is>
       </c>
-      <c r="C744" t="inlineStr">
+      <c r="C743" t="inlineStr">
         <is>
           <t>帝国 ,白夜</t>
         </is>
       </c>
     </row>
-    <row r="745">
-      <c r="A745" t="inlineStr">
+    <row r="744">
+      <c r="A744" t="inlineStr">
         <is>
           <t xml:space="preserve">「子供に食べさせている忍耐強い母親」
 أم صبورة تطعم صغيرها
@@ -16105,19 +16083,19 @@
 2308 https://twitter.com/natgeomagarab/status/1585572054509957120 </t>
         </is>
       </c>
-      <c r="B745" t="inlineStr">
+      <c r="B744" t="inlineStr">
         <is>
           <t>images/「子供に食べさせている忍耐強い母親」_img1.jpg</t>
         </is>
       </c>
-      <c r="C745" t="inlineStr">
+      <c r="C744" t="inlineStr">
         <is>
           <t>手書き語学 ,アラビア語 ,ミヤコドリ</t>
         </is>
       </c>
     </row>
-    <row r="746">
-      <c r="A746" t="inlineStr">
+    <row r="745">
+      <c r="A745" t="inlineStr">
         <is>
           <t xml:space="preserve">「コーヒーは繰り返さない恋物語」
 القهوة قصة عشق لن تتكرر
@@ -16127,19 +16105,19 @@
 2403 pin it/7tvd8Wc </t>
         </is>
       </c>
-      <c r="B746" t="inlineStr">
+      <c r="B745" t="inlineStr">
         <is>
           <t>images/「コーヒーは繰り返さない恋物語」_img1.jpg</t>
         </is>
       </c>
-      <c r="C746" t="inlineStr">
+      <c r="C745" t="inlineStr">
         <is>
           <t>コーヒー ,名言</t>
         </is>
       </c>
     </row>
-    <row r="747">
-      <c r="A747" t="inlineStr">
+    <row r="746">
+      <c r="A746" t="inlineStr">
         <is>
           <t xml:space="preserve">「星々で飾られた空。魅惑的な色合いで黄昏の美を満たしている」
 سماء مرصعة بالنجوم تضفي لمسة سحرية على جمال الشفق
@@ -16147,19 +16125,19 @@
 2010 https://twitter.com/NatGeoMagArab/status/1303777701975584768 </t>
         </is>
       </c>
-      <c r="B747" t="inlineStr">
+      <c r="B746" t="inlineStr">
         <is>
           <t>images/「星々で飾られた空。魅惑的な色合いで黄.png</t>
         </is>
       </c>
-      <c r="C747" t="inlineStr">
+      <c r="C746" t="inlineStr">
         <is>
           <t>星空 ,宇宙</t>
         </is>
       </c>
     </row>
-    <row r="748">
-      <c r="A748" t="inlineStr">
+    <row r="747">
+      <c r="A747" t="inlineStr">
         <is>
           <t xml:space="preserve">「国際宇宙ステーションからの写真。巨大な台風『ハイシェン（海神）』を映している」
 لقطات من محطة الفضاء الدولية تظهر إعصار "هايشن" الهائل
@@ -16167,19 +16145,19 @@
 2403 https://twitter.com/NatGeoMagArab/status/1302871968522235904 </t>
         </is>
       </c>
-      <c r="B748" t="inlineStr">
+      <c r="B747" t="inlineStr">
         <is>
           <t>images/「国際宇宙ステーションからの写真。巨大.png</t>
         </is>
       </c>
-      <c r="C748" t="inlineStr">
+      <c r="C747" t="inlineStr">
         <is>
           <t>台風</t>
         </is>
       </c>
     </row>
-    <row r="749">
-      <c r="A749" t="inlineStr">
+    <row r="748">
+      <c r="A748" t="inlineStr">
         <is>
           <t xml:space="preserve">「草を食む幸運な子羊たち」
 خراف محظوظة ترعى
@@ -16189,19 +16167,19 @@
 2308 https://twitter.com/NatGeoMagArab/status/1490211393554972676 </t>
         </is>
       </c>
-      <c r="B749" t="inlineStr">
+      <c r="B748" t="inlineStr">
         <is>
           <t>images/「草を食む幸運な子羊たち」_img1.jpg,images/ 「草を食む幸運な子羊たち」_img2.jpg</t>
         </is>
       </c>
-      <c r="C749" t="inlineStr">
+      <c r="C748" t="inlineStr">
         <is>
           <t>羊 ,アイルランド</t>
         </is>
       </c>
     </row>
-    <row r="750">
-      <c r="A750" t="inlineStr">
+    <row r="749">
+      <c r="A749" t="inlineStr">
         <is>
           <t xml:space="preserve">「お金で買えぬ10のもの」
 ١٠ أشياء لا تشترى بالمال
@@ -16211,19 +16189,19 @@
 2308 ayb124 </t>
         </is>
       </c>
-      <c r="B750" t="inlineStr">
+      <c r="B749" t="inlineStr">
         <is>
           <t>images/「お金で買えぬ10のもの」_img1.jpg</t>
         </is>
       </c>
-      <c r="C750" t="inlineStr">
+      <c r="C749" t="inlineStr">
         <is>
           <t>価値 ,購買</t>
         </is>
       </c>
     </row>
-    <row r="751">
-      <c r="A751" t="inlineStr">
+    <row r="750">
+      <c r="A750" t="inlineStr">
         <is>
           <t xml:space="preserve">「お金では買えないよ」
 هي أشْيَاءٌ لا تُشْتَرَى
@@ -16233,19 +16211,19 @@
 1906 mardy_zaawely, Instagram </t>
         </is>
       </c>
-      <c r="B751" t="inlineStr">
+      <c r="B750" t="inlineStr">
         <is>
           <t>images/「お金では買えないよ」_img1.jpg</t>
         </is>
       </c>
-      <c r="C751" t="inlineStr">
+      <c r="C750" t="inlineStr">
         <is>
           <t>マスターカード ,価値</t>
         </is>
       </c>
     </row>
-    <row r="752">
-      <c r="A752" t="inlineStr">
+    <row r="751">
+      <c r="A751" t="inlineStr">
         <is>
           <t xml:space="preserve">「好奇心旺盛なホッキョクギツネ」
 ثعلب قطبي يملؤه الفضول
@@ -16255,15 +16233,15 @@
 2308 https://twitter.com/natgeomagarab/status/1157592172968808449 </t>
         </is>
       </c>
-      <c r="B752" t="inlineStr"/>
-      <c r="C752" t="inlineStr">
+      <c r="B751" t="inlineStr"/>
+      <c r="C751" t="inlineStr">
         <is>
           <t>ファーストコンタクト ,キツネ</t>
         </is>
       </c>
     </row>
-    <row r="753">
-      <c r="A753" t="inlineStr">
+    <row r="752">
+      <c r="A752" t="inlineStr">
         <is>
           <t xml:space="preserve">「グレンダイザーのいる国は死にません」
 لنْ يَموتَ شَعبٌ لدَيهِ غرندايزر
@@ -16272,56 +16250,56 @@
 2308 https://www.aljarida.com/articles/1462241741574732100/ </t>
         </is>
       </c>
+      <c r="B752" t="inlineStr">
+        <is>
+          <t>images/「グレンダイザーのいる国は死にません」_img1.jpg</t>
+        </is>
+      </c>
+      <c r="C752" t="inlineStr">
+        <is>
+          <t>UFOロボ ,アニメ</t>
+        </is>
+      </c>
+    </row>
+    <row r="753">
+      <c r="A753" t="inlineStr">
+        <is>
+          <t xml:space="preserve">「凍結路面を運転中、彼女は嫌な場面に居合わせた」
+2408 https://twitter.com/NatGeoMagArab/status/1610305209657626625 </t>
+        </is>
+      </c>
       <c r="B753" t="inlineStr">
         <is>
-          <t>images/「グレンダイザーのいる国は死にません」_img1.jpg</t>
+          <t>images/「凍結路面を運転中、彼女は嫌な場面に居_img1.jpg</t>
         </is>
       </c>
       <c r="C753" t="inlineStr">
         <is>
-          <t>UFOロボ ,アニメ</t>
+          <t>手書き語学 ,アラビア語 ,路面凍結</t>
         </is>
       </c>
     </row>
     <row r="754">
       <c r="A754" t="inlineStr">
-        <is>
-          <t xml:space="preserve">「凍結路面を運転中、彼女は嫌な場面に居合わせた」
-2408 https://twitter.com/NatGeoMagArab/status/1610305209657626625 </t>
-        </is>
-      </c>
-      <c r="B754" t="inlineStr">
-        <is>
-          <t>images/「凍結路面を運転中、彼女は嫌な場面に居_img1.jpg</t>
-        </is>
-      </c>
-      <c r="C754" t="inlineStr">
-        <is>
-          <t>手書き語学 ,アラビア語 ,路面凍結</t>
-        </is>
-      </c>
-    </row>
-    <row r="755">
-      <c r="A755" t="inlineStr">
         <is>
           <t xml:space="preserve">「虹が美しさを加えている、アルパカという動物の美しいショット」
 ⁦「美しいショット」[laq_tatun jamiilatun]：「ショット」( لقطة )[laq_ta]：( ـلٌ )[-lun]・( ـقٌ )[-qun]・( ـطٌ )[-_tun]・( ـةٌ )[-tun]⁩
 2308 https://twitter.com/natgeomagarab/status/1155115655928004608 </t>
         </is>
       </c>
-      <c r="B755" t="inlineStr">
+      <c r="B754" t="inlineStr">
         <is>
           <t>images/「虹が美しさを加えている、アルパカとい_img1.jpg</t>
         </is>
       </c>
-      <c r="C755" t="inlineStr">
+      <c r="C754" t="inlineStr">
         <is>
           <t>モフモフ ,アルパカ</t>
         </is>
       </c>
     </row>
-    <row r="756">
-      <c r="A756" t="inlineStr">
+    <row r="755">
+      <c r="A755" t="inlineStr">
         <is>
           <t xml:space="preserve">「幸せは…全然思いもよらない所からやって来る」
 السعادة تأتينا من أماكن لم نكن نتوقعها أبداً
@@ -16330,19 +16308,19 @@
 2109 出典不明 </t>
         </is>
       </c>
-      <c r="B756" t="inlineStr">
+      <c r="B755" t="inlineStr">
         <is>
           <t>images/「幸せは…全然思いもよらない所からやっ_img1.jpg,images/ 「幸せは…全然思いもよらない所からやっ_img2.jpg</t>
         </is>
       </c>
-      <c r="C756" t="inlineStr">
+      <c r="C755" t="inlineStr">
         <is>
           <t>訪れ ,予想</t>
         </is>
       </c>
     </row>
-    <row r="757">
-      <c r="A757" t="inlineStr">
+    <row r="756">
+      <c r="A756" t="inlineStr">
         <is>
           <t xml:space="preserve">「あらゆる問題は、食べ物が解決してくれる」
 كل مشكلة ولها أكلة تحلها
@@ -16351,19 +16329,19 @@
 1909 ALQA AN 878 </t>
         </is>
       </c>
-      <c r="B757" t="inlineStr">
+      <c r="B756" t="inlineStr">
         <is>
           <t>images/「あらゆる問題は、食べ物が解決してくれ_img1.jpg</t>
         </is>
       </c>
-      <c r="C757" t="inlineStr">
+      <c r="C756" t="inlineStr">
         <is>
           <t>ストレス ,精神</t>
         </is>
       </c>
     </row>
-    <row r="758">
-      <c r="A758" t="inlineStr">
+    <row r="757">
+      <c r="A757" t="inlineStr">
         <is>
           <t xml:space="preserve">「冬で私が好きな物」
 أشياء أحبها بالشتاء
@@ -16373,19 +16351,19 @@
 2109 出典不明 </t>
         </is>
       </c>
-      <c r="B758" t="inlineStr">
+      <c r="B757" t="inlineStr">
         <is>
           <t>images/「冬で私が好きな物」_img1.jpg</t>
         </is>
       </c>
-      <c r="C758" t="inlineStr">
+      <c r="C757" t="inlineStr">
         <is>
           <t>季節 ,冬</t>
         </is>
       </c>
     </row>
-    <row r="759">
-      <c r="A759" t="inlineStr">
+    <row r="758">
+      <c r="A758" t="inlineStr">
         <is>
           <t xml:space="preserve">「お金で買うことの出来ない物」
 أشياء لا تستطيع شراءها بالمال
@@ -16395,19 +16373,19 @@
 2409 https://x.com/akhbarak/status/1038402708414373888 </t>
         </is>
       </c>
-      <c r="B759" t="inlineStr">
+      <c r="B758" t="inlineStr">
         <is>
           <t>images/「お金で買うことの出来ない物」_img1.jpg,images/ 「お金で買うことの出来ない物」_img2.jpg</t>
         </is>
       </c>
-      <c r="C759" t="inlineStr">
+      <c r="C758" t="inlineStr">
         <is>
           <t>ショッピング ,価値</t>
         </is>
       </c>
     </row>
-    <row r="760">
-      <c r="A760" t="inlineStr">
+    <row r="759">
+      <c r="A759" t="inlineStr">
         <is>
           <t xml:space="preserve">「私たちが愛する言葉」
 كلماتٌ نُحبّها
@@ -16417,19 +16395,19 @@
 2109 جليل خزعل </t>
         </is>
       </c>
-      <c r="B760" t="inlineStr">
+      <c r="B759" t="inlineStr">
         <is>
           <t>images/「私たちが愛する言葉」_img1.jpg</t>
         </is>
       </c>
-      <c r="C760" t="inlineStr">
+      <c r="C759" t="inlineStr">
         <is>
           <t>花 ,贈り物</t>
         </is>
       </c>
     </row>
-    <row r="761">
-      <c r="A761" t="inlineStr">
+    <row r="760">
+      <c r="A760" t="inlineStr">
         <is>
           <t xml:space="preserve">「お茶についてあなたが知らない10の事実」
 عشر معلومات لا تعرفها عن الشاي
@@ -16438,19 +16416,19 @@
 2012 http://ara.tv/6syq2 </t>
         </is>
       </c>
-      <c r="B761" t="inlineStr">
+      <c r="B760" t="inlineStr">
         <is>
           <t>images/「お茶についてあなたが知らない10の事_img1.jpg</t>
         </is>
       </c>
-      <c r="C761" t="inlineStr">
+      <c r="C760" t="inlineStr">
         <is>
           <t>神農</t>
         </is>
       </c>
     </row>
-    <row r="762">
-      <c r="A762" t="inlineStr">
+    <row r="761">
+      <c r="A761" t="inlineStr">
         <is>
           <t xml:space="preserve">「大きくなったウソ」
 الكذبة الّتي كبرت
@@ -16460,19 +16438,19 @@
 2509 سلسلة الحلزونة </t>
         </is>
       </c>
-      <c r="B762" t="inlineStr">
+      <c r="B761" t="inlineStr">
         <is>
           <t>images/「大きくなったウソ」_img1.jpg</t>
         </is>
       </c>
-      <c r="C762" t="inlineStr">
+      <c r="C761" t="inlineStr">
         <is>
           <t>絵本</t>
         </is>
       </c>
     </row>
-    <row r="763">
-      <c r="A763" t="inlineStr">
+    <row r="762">
+      <c r="A762" t="inlineStr">
         <is>
           <t xml:space="preserve">「自分に合った掃除機を買うには？」
 كيف تشتري المكنسة الكهربائية التي تناسبك؟
@@ -16481,19 +16459,19 @@
 2106 ts3a com </t>
         </is>
       </c>
-      <c r="B763" t="inlineStr">
+      <c r="B762" t="inlineStr">
         <is>
           <t>images/「自分に合った掃除機を買うには？」_img1.jpg</t>
         </is>
       </c>
-      <c r="C763" t="inlineStr">
+      <c r="C762" t="inlineStr">
         <is>
           <t>家電 ,掃除</t>
         </is>
       </c>
     </row>
-    <row r="764">
-      <c r="A764" t="inlineStr">
+    <row r="763">
+      <c r="A763" t="inlineStr">
         <is>
           <t xml:space="preserve">「仮にこれが批判の数としよう」
 لنفرض ان عدد الذين ينتقدونك
@@ -16504,19 +16482,19 @@
 2504 出典不明 </t>
         </is>
       </c>
-      <c r="B764" t="inlineStr">
+      <c r="B763" t="inlineStr">
         <is>
           <t>images/「仮にこれが批判の数としよう」_img1.jpg</t>
         </is>
       </c>
-      <c r="C764" t="inlineStr">
+      <c r="C763" t="inlineStr">
         <is>
           <t>アンチ</t>
         </is>
       </c>
     </row>
-    <row r="765">
-      <c r="A765" t="inlineStr">
+    <row r="764">
+      <c r="A764" t="inlineStr">
         <is>
           <t xml:space="preserve">「ここに見えるのは何？」
 ما الذي تراه هنا؟
@@ -16526,15 +16504,15 @@
 2204 https://twitter.com/NatGeoMagArab/status/1506933850617700352 </t>
         </is>
       </c>
-      <c r="B765" t="inlineStr"/>
-      <c r="C765" t="inlineStr">
+      <c r="B764" t="inlineStr"/>
+      <c r="C764" t="inlineStr">
         <is>
           <t xml:space="preserve">ペンギン </t>
         </is>
       </c>
     </row>
-    <row r="766">
-      <c r="A766" t="inlineStr">
+    <row r="765">
+      <c r="A765" t="inlineStr">
         <is>
           <t xml:space="preserve">「今日辛いこと、明日は平気だろう」
 ما يؤلم اليوم سيهون غدًا
@@ -16544,19 +16522,19 @@
 2308 basmahjeff </t>
         </is>
       </c>
-      <c r="B766" t="inlineStr">
+      <c r="B765" t="inlineStr">
         <is>
           <t>images/「今日辛いこと、明日は平気だろう」_img1.jpg</t>
         </is>
       </c>
-      <c r="C766" t="inlineStr">
+      <c r="C765" t="inlineStr">
         <is>
           <t>悩み ,達観</t>
         </is>
       </c>
     </row>
-    <row r="767">
-      <c r="A767" t="inlineStr">
+    <row r="766">
+      <c r="A766" t="inlineStr">
         <is>
           <t xml:space="preserve">「自分のすることを好きでなきゃ」
 عليك أن تحب ما تفعل
@@ -16565,19 +16543,19 @@
 1810 Ahmed Elhakeem </t>
         </is>
       </c>
-      <c r="B767" t="inlineStr">
+      <c r="B766" t="inlineStr">
         <is>
           <t>images/「自分のすることを好きでなきゃ」_img1.jpg</t>
         </is>
       </c>
-      <c r="C767" t="inlineStr">
+      <c r="C766" t="inlineStr">
         <is>
           <t>転職 ,かわいい</t>
         </is>
       </c>
     </row>
-    <row r="768">
-      <c r="A768" t="inlineStr">
+    <row r="767">
+      <c r="A767" t="inlineStr">
         <is>
           <t xml:space="preserve">「この地上に生き甲斐あり」
 على هذه الأرض ما يستحق الحياة
@@ -16587,19 +16565,19 @@
 2308 Mahmoud Gafar </t>
         </is>
       </c>
-      <c r="B768" t="inlineStr">
+      <c r="B767" t="inlineStr">
         <is>
           <t>images/「この地上に生き甲斐あり」_img1.jpg</t>
         </is>
       </c>
-      <c r="C768" t="inlineStr">
+      <c r="C767" t="inlineStr">
         <is>
           <t>詩</t>
         </is>
       </c>
     </row>
-    <row r="769">
-      <c r="A769" t="inlineStr">
+    <row r="768">
+      <c r="A768" t="inlineStr">
         <is>
           <t xml:space="preserve">「おそらく、あなたの求めるものはあるだろう」
 لعلَّ ما تَرجوهُ سيَكونُ
@@ -16609,19 +16587,19 @@
 2308 PIXEL Instagram </t>
         </is>
       </c>
-      <c r="B769" t="inlineStr">
+      <c r="B768" t="inlineStr">
         <is>
           <t>images/「おそらく、あなたの求めるものはあるだ_img1.jpg</t>
         </is>
       </c>
-      <c r="C769" t="inlineStr">
+      <c r="C768" t="inlineStr">
         <is>
           <t>願い ,信仰</t>
         </is>
       </c>
     </row>
-    <row r="770">
-      <c r="A770" t="inlineStr">
+    <row r="769">
+      <c r="A769" t="inlineStr">
         <is>
           <t xml:space="preserve">「オレンジの効能が何か知っていますか？」
 هل تعرف ما هي فوائد البرتقال؟
@@ -16631,19 +16609,19 @@
 2308 sadahadhramowt com </t>
         </is>
       </c>
-      <c r="B770" t="inlineStr">
+      <c r="B769" t="inlineStr">
         <is>
           <t>images/「オレンジの効能が何か知っていますか？_img1.jpg</t>
         </is>
       </c>
-      <c r="C770" t="inlineStr">
+      <c r="C769" t="inlineStr">
         <is>
           <t>オレンジ ,フルーツ</t>
         </is>
       </c>
     </row>
-    <row r="771">
-      <c r="A771" t="inlineStr">
+    <row r="770">
+      <c r="A770" t="inlineStr">
         <is>
           <t xml:space="preserve">「遊ぶパンダの光景より可愛いものがありますか？」
 هل هناك ما هو ألطف من مشاهدة الباندا وهي تلعب؟
@@ -16651,19 +16629,19 @@
 2308 https://twitter.com/NatGeoMagArab/status/1494612797858074626 </t>
         </is>
       </c>
-      <c r="B771" t="inlineStr">
+      <c r="B770" t="inlineStr">
         <is>
           <t>images/「遊ぶパンダの光景より可愛いものがあり_img1.jpg</t>
         </is>
       </c>
-      <c r="C771" t="inlineStr">
+      <c r="C770" t="inlineStr">
         <is>
           <t>パンダ ,モコモコ</t>
         </is>
       </c>
     </row>
-    <row r="772">
-      <c r="A772" t="inlineStr">
+    <row r="771">
+      <c r="A771" t="inlineStr">
         <is>
           <t xml:space="preserve">「大事なのは何者だったかじゃない。何者になるかだ」
 ليسَ المُهم ما كُنتَ بل مَا ستكون
@@ -16672,19 +16650,19 @@
 2308 出典不明 </t>
         </is>
       </c>
-      <c r="B772" t="inlineStr">
+      <c r="B771" t="inlineStr">
         <is>
           <t>images/「大事なのは何者だったかじゃない。何者_img1.jpg</t>
         </is>
       </c>
-      <c r="C772" t="inlineStr">
+      <c r="C771" t="inlineStr">
         <is>
           <t>自己実現 ,存在価値</t>
         </is>
       </c>
     </row>
-    <row r="773">
-      <c r="A773" t="inlineStr">
+    <row r="772">
+      <c r="A772" t="inlineStr">
         <is>
           <t xml:space="preserve">「あなたであれ。ありのままが美しいから」
 كُنْ أَنْتَ لأنك جميل كما أنت
@@ -16693,19 +16671,19 @@
 2308 IDREES DESIGN </t>
         </is>
       </c>
-      <c r="B773" t="inlineStr">
+      <c r="B772" t="inlineStr">
         <is>
           <t>images/「あなたであれ。ありのままが美しいから_img1.jpg</t>
         </is>
       </c>
-      <c r="C773" t="inlineStr">
+      <c r="C772" t="inlineStr">
         <is>
           <t>自己肯定 ,BeYourself</t>
         </is>
       </c>
     </row>
-    <row r="774">
-      <c r="A774" t="inlineStr">
+    <row r="773">
+      <c r="A773" t="inlineStr">
         <is>
           <t xml:space="preserve">「恐れの中に生きる者は決して自由になれない」
 من يعش في خوف لن يكون حرا أبدا
@@ -16714,19 +16692,19 @@
 2111 rjeem com </t>
         </is>
       </c>
-      <c r="B774" t="inlineStr">
+      <c r="B773" t="inlineStr">
         <is>
           <t>images/「恐れの中に生きる者は決して自由になれ_img1.jpg,images/ 「恐れの中に生きる者は決して自由になれ_img2.jpg</t>
         </is>
       </c>
-      <c r="C774" t="inlineStr">
+      <c r="C773" t="inlineStr">
         <is>
           <t>勇気 ,壁</t>
         </is>
       </c>
     </row>
-    <row r="775">
-      <c r="A775" t="inlineStr">
+    <row r="774">
+      <c r="A774" t="inlineStr">
         <is>
           <t xml:space="preserve">「己の翼を信じる者は己の重さを案じない」
 من يثق في جناحيه لن يهتم لوزنه
@@ -16735,19 +16713,19 @@
 2308 kmrghani </t>
         </is>
       </c>
-      <c r="B775" t="inlineStr">
+      <c r="B774" t="inlineStr">
         <is>
           <t>images/「己の翼を信じる者は己の重さを案じない_img1.jpg</t>
         </is>
       </c>
-      <c r="C775" t="inlineStr">
+      <c r="C774" t="inlineStr">
         <is>
           <t>自信</t>
         </is>
       </c>
     </row>
-    <row r="776">
-      <c r="A776" t="inlineStr">
+    <row r="775">
+      <c r="A775" t="inlineStr">
         <is>
           <t xml:space="preserve">「珈琲で一番大事な事！誰と飲むか？」
 الأهم من القهوة!! من ستشربها معه؟
@@ -16756,19 +16734,19 @@
 1812 gwid3.tumblr </t>
         </is>
       </c>
-      <c r="B776" t="inlineStr">
+      <c r="B775" t="inlineStr">
         <is>
           <t>images/「珈琲で一番大事な事！誰と飲むか？」_img1.jpg</t>
         </is>
       </c>
-      <c r="C776" t="inlineStr">
+      <c r="C775" t="inlineStr">
         <is>
           <t>コーヒー ,名言</t>
         </is>
       </c>
     </row>
-    <row r="777">
-      <c r="A777" t="inlineStr">
+    <row r="776">
+      <c r="A776" t="inlineStr">
         <is>
           <t xml:space="preserve">「人生は美しい、そう望んだ者には。」
 الحياة جَميلَة .. لمن أراد ذلك
@@ -16778,19 +16756,19 @@
 2109 出典不明 </t>
         </is>
       </c>
-      <c r="B777" t="inlineStr">
+      <c r="B776" t="inlineStr">
         <is>
           <t>images/「人生は美しい、そう望んだ者には。」_img1.jpg</t>
         </is>
       </c>
-      <c r="C777" t="inlineStr">
+      <c r="C776" t="inlineStr">
         <is>
           <t>名言 ,アート</t>
         </is>
       </c>
     </row>
-    <row r="778">
-      <c r="A778" t="inlineStr">
+    <row r="777">
+      <c r="A777" t="inlineStr">
         <is>
           <t xml:space="preserve">「ハム太郎って子を知ってるかい」
 هل تعرفون من هو هامتارو
@@ -16800,19 +16778,19 @@
 2109 </t>
         </is>
       </c>
-      <c r="B778" t="inlineStr">
+      <c r="B777" t="inlineStr">
         <is>
           <t>images/「ハム太郎って子を知ってるかい」_img1.jpg</t>
         </is>
       </c>
-      <c r="C778" t="inlineStr">
+      <c r="C777" t="inlineStr">
         <is>
           <t>オープニング ,ハム太郎</t>
         </is>
       </c>
     </row>
-    <row r="779">
-      <c r="A779" t="inlineStr">
+    <row r="778">
+      <c r="A778" t="inlineStr">
         <is>
           <t xml:space="preserve">「幸せを求める人もいれば、作る人もいる」
 هناك من يبحث عن السعادة وهناك من يصنعها
@@ -16821,19 +16799,19 @@
 2308 hindah tumblr </t>
         </is>
       </c>
-      <c r="B779" t="inlineStr">
+      <c r="B778" t="inlineStr">
         <is>
           <t>images/「幸せを求める人もいれば、作る人もいる_img1.jpg</t>
         </is>
       </c>
-      <c r="C779" t="inlineStr">
+      <c r="C778" t="inlineStr">
         <is>
           <t>幸せ ,名言 ,教訓</t>
         </is>
       </c>
     </row>
-    <row r="780">
-      <c r="A780" t="inlineStr">
+    <row r="779">
+      <c r="A779" t="inlineStr">
         <is>
           <t xml:space="preserve">「明白なるアラブの言葉によって」
 بلسان عربي مبين
@@ -16843,19 +16821,19 @@
 2109 Abdullah Barakat behance </t>
         </is>
       </c>
-      <c r="B780" t="inlineStr">
+      <c r="B779" t="inlineStr">
         <is>
           <t>images/「明白なるアラブの言葉によって」_img1.jpg</t>
         </is>
       </c>
-      <c r="C780" t="inlineStr">
+      <c r="C779" t="inlineStr">
         <is>
           <t>イスラム教 ,神聖</t>
         </is>
       </c>
     </row>
-    <row r="781">
-      <c r="A781" t="inlineStr">
+    <row r="780">
+      <c r="A780" t="inlineStr">
         <is>
           <t xml:space="preserve">「結婚前、結婚後」
 قبل الزواج، بعد الزواج
@@ -16865,19 +16843,19 @@
 2308 出典不明 </t>
         </is>
       </c>
-      <c r="B781" t="inlineStr">
+      <c r="B780" t="inlineStr">
         <is>
           <t>images/「結婚前、結婚後」_img1.jpg</t>
         </is>
       </c>
-      <c r="C781" t="inlineStr">
+      <c r="C780" t="inlineStr">
         <is>
           <t>BeforeAfter ,幸せ太り</t>
         </is>
       </c>
     </row>
-    <row r="782">
-      <c r="A782" t="inlineStr">
+    <row r="781">
+      <c r="A781" t="inlineStr">
         <is>
           <t xml:space="preserve">「驚きの価格で」بسعر رائع
 ビスィアル・ラーイア [bi-si*r raa'i*]
@@ -16886,19 +16864,19 @@
 2109 Jarir Bookstore </t>
         </is>
       </c>
-      <c r="B782" t="inlineStr">
+      <c r="B781" t="inlineStr">
         <is>
           <t>images/「驚きの価格で」_img1.jpg</t>
         </is>
       </c>
-      <c r="C782" t="inlineStr">
+      <c r="C781" t="inlineStr">
         <is>
           <t>広告 ,安値</t>
         </is>
       </c>
     </row>
-    <row r="783">
-      <c r="A783" t="inlineStr">
+    <row r="782">
+      <c r="A782" t="inlineStr">
         <is>
           <t xml:space="preserve">「我が魂と共に」مع نفسي
 マア・ナフスィ [ma*a nafs-iy]
@@ -16907,19 +16885,19 @@
 2110 出典不明 </t>
         </is>
       </c>
-      <c r="B783" t="inlineStr">
+      <c r="B782" t="inlineStr">
         <is>
           <t>images/「我が魂と共に」_img1.jpg</t>
         </is>
       </c>
-      <c r="C783" t="inlineStr">
+      <c r="C782" t="inlineStr">
         <is>
           <t>ソウル ,soul</t>
         </is>
       </c>
     </row>
-    <row r="784">
-      <c r="A784" t="inlineStr">
+    <row r="783">
+      <c r="A783" t="inlineStr">
         <is>
           <t xml:space="preserve">「暗い夜に」في ليلة مظلمة
  [fiy layla(tin) mu_Dhlima(tin)]
@@ -16928,19 +16906,19 @@
 2109 سلسلة الحلزونة </t>
         </is>
       </c>
-      <c r="B784" t="inlineStr">
+      <c r="B783" t="inlineStr">
         <is>
           <t>images/「暗い夜に」_img1.jpg</t>
         </is>
       </c>
-      <c r="C784" t="inlineStr">
+      <c r="C783" t="inlineStr">
         <is>
           <t>絵本</t>
         </is>
       </c>
     </row>
-    <row r="785">
-      <c r="A785" t="inlineStr">
+    <row r="784">
+      <c r="A784" t="inlineStr">
         <is>
           <t xml:space="preserve">「ゆっくりと」بشويش
 ビシワェーシ [bi-ShwySh]
@@ -16948,19 +16926,19 @@
 2109 出典不明 </t>
         </is>
       </c>
-      <c r="B785" t="inlineStr">
+      <c r="B784" t="inlineStr">
         <is>
           <t>images/「ゆっくりと」_img1.jpg</t>
         </is>
       </c>
-      <c r="C785" t="inlineStr">
+      <c r="C784" t="inlineStr">
         <is>
           <t>丸 ,円</t>
         </is>
       </c>
     </row>
-    <row r="786">
-      <c r="A786" t="inlineStr">
+    <row r="785">
+      <c r="A785" t="inlineStr">
         <is>
           <t xml:space="preserve">「この広い宇宙に…」
 في الكون الفسيح
@@ -16969,19 +16947,19 @@
 2308 wattpad </t>
         </is>
       </c>
-      <c r="B786" t="inlineStr">
+      <c r="B785" t="inlineStr">
         <is>
           <t>images/「この広い宇宙に…」_img1.jpg</t>
         </is>
       </c>
-      <c r="C786" t="inlineStr">
+      <c r="C785" t="inlineStr">
         <is>
           <t>アニメ ,宇宙</t>
         </is>
       </c>
     </row>
-    <row r="787">
-      <c r="A787" t="inlineStr">
+    <row r="786">
+      <c r="A786" t="inlineStr">
         <is>
           <t xml:space="preserve">「がんばって！」بالتوفيق
 ビッタウフィーク [bi^tawfiiq]
@@ -16989,19 +16967,19 @@
 2111 https://sites.google.com/site/mathmatic1905/ </t>
         </is>
       </c>
-      <c r="B787" t="inlineStr">
+      <c r="B786" t="inlineStr">
         <is>
           <t>images/「がんばって！」_img1.jpg</t>
         </is>
       </c>
-      <c r="C787" t="inlineStr">
+      <c r="C786" t="inlineStr">
         <is>
           <t>アラビア語</t>
         </is>
       </c>
     </row>
-    <row r="788">
-      <c r="A788" t="inlineStr">
+    <row r="787">
+      <c r="A787" t="inlineStr">
         <is>
           <t xml:space="preserve">「インターステラー」بين النجوم
 バイナ_ンヌジューム [bayna ^nujuum]
@@ -17009,19 +16987,19 @@
 2308 kmrghani </t>
         </is>
       </c>
-      <c r="B788" t="inlineStr">
+      <c r="B787" t="inlineStr">
         <is>
           <t>images/「インターステラー」_img1.jpg</t>
         </is>
       </c>
-      <c r="C788" t="inlineStr">
+      <c r="C787" t="inlineStr">
         <is>
           <t>映画 ,宇宙</t>
         </is>
       </c>
     </row>
-    <row r="789">
-      <c r="A789" t="inlineStr">
+    <row r="788">
+      <c r="A788" t="inlineStr">
         <is>
           <t xml:space="preserve">「アラビア語で」بالعربية
 ビ_ルアラビーヤ [bi-l-*arabiyya]
@@ -17030,19 +17008,19 @@
 1811 </t>
         </is>
       </c>
-      <c r="B789" t="inlineStr">
+      <c r="B788" t="inlineStr">
         <is>
           <t>images/「アラビア語で」_img1.jpg</t>
         </is>
       </c>
-      <c r="C789" t="inlineStr">
+      <c r="C788" t="inlineStr">
         <is>
           <t>ニュース ,CNN</t>
         </is>
       </c>
     </row>
-    <row r="790">
-      <c r="A790" t="inlineStr">
+    <row r="789">
+      <c r="A789" t="inlineStr">
         <is>
           <t xml:space="preserve">「17世紀に発明されて以来…」
 منذ اختراعه بالقرن السابع عشر
@@ -17050,19 +17028,19 @@
 2308 https://twitter.com/SciTalk2U/status/1450888395815854080 </t>
         </is>
       </c>
-      <c r="B790" t="inlineStr">
+      <c r="B789" t="inlineStr">
         <is>
           <t>images/「17世紀に発明されて以来…」_img1.jpg</t>
         </is>
       </c>
-      <c r="C790" t="inlineStr">
+      <c r="C789" t="inlineStr">
         <is>
           <t>手書き語学 ,アラビア語 ,望遠鏡</t>
         </is>
       </c>
     </row>
-    <row r="791">
-      <c r="A791" t="inlineStr">
+    <row r="790">
+      <c r="A790" t="inlineStr">
         <is>
           <t xml:space="preserve">「私できるよ」إنّني أستطيع
 インナニー・アスタティーウ ['inna-niy 'a-sta_tii*u]
@@ -17071,19 +17049,19 @@
 2412 سلسلة الحلزونة </t>
         </is>
       </c>
-      <c r="B791" t="inlineStr">
+      <c r="B790" t="inlineStr">
         <is>
           <t>images/「私できるよ」_img1.jpg</t>
         </is>
       </c>
-      <c r="C791" t="inlineStr">
+      <c r="C790" t="inlineStr">
         <is>
           <t>絵本 ,こども</t>
         </is>
       </c>
     </row>
-    <row r="792">
-      <c r="A792" t="inlineStr">
+    <row r="791">
+      <c r="A791" t="inlineStr">
         <is>
           <t xml:space="preserve">「問題なし」مافيش مشكلة
 マフィーシムシュキラ [ma-fy-Sh muShkila]
@@ -17092,19 +17070,19 @@
 2109 tanzerin.theshop </t>
         </is>
       </c>
-      <c r="B792" t="inlineStr">
+      <c r="B791" t="inlineStr">
         <is>
           <t>images/「問題なし」_img1.jpg</t>
         </is>
       </c>
-      <c r="C792" t="inlineStr">
+      <c r="C791" t="inlineStr">
         <is>
           <t>シャツ ,キッズ</t>
         </is>
       </c>
     </row>
-    <row r="793">
-      <c r="A793" t="inlineStr">
+    <row r="792">
+      <c r="A792" t="inlineStr">
         <is>
           <t xml:space="preserve">「不可能はない」مفيش مستحيل
 マフィーシ・ムスタヒール [ma-fy-Sh mustaHiil]
@@ -17113,19 +17091,19 @@
 2109 أموج </t>
         </is>
       </c>
-      <c r="B793" t="inlineStr">
+      <c r="B792" t="inlineStr">
         <is>
           <t>images/「不可能はない」_img1.jpg</t>
         </is>
       </c>
-      <c r="C793" t="inlineStr">
+      <c r="C792" t="inlineStr">
         <is>
           <t>ポジティブ ,挑戦</t>
         </is>
       </c>
     </row>
-    <row r="794">
-      <c r="A794" t="inlineStr">
+    <row r="793">
+      <c r="A793" t="inlineStr">
         <is>
           <t xml:space="preserve">「等々」إلخ
 イラク ['ilaKh]
@@ -17134,19 +17112,19 @@
 2201 出典不明 </t>
         </is>
       </c>
-      <c r="B794" t="inlineStr">
+      <c r="B793" t="inlineStr">
         <is>
           <t>images/「等々」_img1.jpg</t>
         </is>
       </c>
-      <c r="C794" t="inlineStr">
+      <c r="C793" t="inlineStr">
         <is>
           <t>etc ,とんち</t>
         </is>
       </c>
     </row>
-    <row r="795">
-      <c r="A795" t="inlineStr">
+    <row r="794">
+      <c r="A794" t="inlineStr">
         <is>
           <t xml:space="preserve">⁦「調子どう？」⁩شلونَك؟
 シュローナク？ [Sh-loon-ak?]
@@ -17155,19 +17133,19 @@
 2202 Jozoor Team. </t>
         </is>
       </c>
-      <c r="B795" t="inlineStr">
+      <c r="B794" t="inlineStr">
         <is>
           <t>images/⁦「調子どう？」⁩_img1.jpg</t>
         </is>
       </c>
-      <c r="C795" t="inlineStr">
+      <c r="C794" t="inlineStr">
         <is>
           <t>洒落 ,ルービックキューブ</t>
         </is>
       </c>
     </row>
-    <row r="796">
-      <c r="A796" t="inlineStr">
+    <row r="795">
+      <c r="A795" t="inlineStr">
         <is>
           <t xml:space="preserve">「行くな」ماتروحش
 マトロホシ [ma-troH-Sh]
@@ -17176,19 +17154,19 @@
 2411 triiq tumblr </t>
         </is>
       </c>
-      <c r="B796" t="inlineStr">
+      <c r="B795" t="inlineStr">
         <is>
           <t>images/「行くな」_img1.jpg</t>
         </is>
       </c>
-      <c r="C796" t="inlineStr">
+      <c r="C795" t="inlineStr">
         <is>
           <t>ロゴ ,デザイン ,嵐</t>
         </is>
       </c>
     </row>
-    <row r="797">
-      <c r="A797" t="inlineStr">
+    <row r="796">
+      <c r="A796" t="inlineStr">
         <is>
           <t xml:space="preserve">⁦「元気？」⁩شلونَك؟
 シュローナク？ [Sh-loon-ak?]
@@ -17199,19 +17177,19 @@
 2202 出典不明 </t>
         </is>
       </c>
-      <c r="B797" t="inlineStr">
+      <c r="B796" t="inlineStr">
         <is>
           <t>images/⁦「元気？」⁩_img1.jpg</t>
         </is>
       </c>
-      <c r="C797" t="inlineStr">
+      <c r="C796" t="inlineStr">
         <is>
           <t>洒落 ,挨拶</t>
         </is>
       </c>
     </row>
-    <row r="798">
-      <c r="A798" t="inlineStr">
+    <row r="797">
+      <c r="A797" t="inlineStr">
         <is>
           <t xml:space="preserve">「気分が良いぞう」I فيل GOOD
 アイ・フィール・グッド [ai fiyl gud]
@@ -17220,19 +17198,19 @@
 2308 出典不明 </t>
         </is>
       </c>
-      <c r="B798" t="inlineStr">
+      <c r="B797" t="inlineStr">
         <is>
           <t>images/「気分が良いぞう」_img1.jpg</t>
         </is>
       </c>
-      <c r="C798" t="inlineStr">
+      <c r="C797" t="inlineStr">
         <is>
           <t>洒落 ,和訳</t>
         </is>
       </c>
     </row>
-    <row r="799">
-      <c r="A799" t="inlineStr">
+    <row r="798">
+      <c r="A798" t="inlineStr">
         <is>
           <t xml:space="preserve">「レットイットゴー／let it go」
 ليت اِت غو
@@ -17241,19 +17219,19 @@
 2109 出典不明 </t>
         </is>
       </c>
-      <c r="B799" t="inlineStr">
+      <c r="B798" t="inlineStr">
         <is>
           <t>images/「レットイットゴー／let it go_img1.jpg</t>
         </is>
       </c>
-      <c r="C799" t="inlineStr">
+      <c r="C798" t="inlineStr">
         <is>
           <t>折衷 ,アナ雪</t>
         </is>
       </c>
     </row>
-    <row r="800">
-      <c r="A800" t="inlineStr">
+    <row r="799">
+      <c r="A799" t="inlineStr">
         <is>
           <t xml:space="preserve">「ようこそ」اهلا وسهلا
 アハラン・ワサハラン ['ahlan wa-sahlan]
@@ -17261,19 +17239,19 @@
 2106 behance Anwar Al Eissa </t>
         </is>
       </c>
-      <c r="B800" t="inlineStr">
+      <c r="B799" t="inlineStr">
         <is>
           <t>images/「ようこそ」_img1.jpg</t>
         </is>
       </c>
-      <c r="C800" t="inlineStr">
+      <c r="C799" t="inlineStr">
         <is>
           <t>アラビア語</t>
         </is>
       </c>
     </row>
-    <row r="801">
-      <c r="A801" t="inlineStr">
+    <row r="800">
+      <c r="A800" t="inlineStr">
         <is>
           <t xml:space="preserve">「まぁ何というサプライズでしょう」
 يا لها من مفاجأة
@@ -17284,19 +17262,19 @@
 2108 neelwafurat com </t>
         </is>
       </c>
-      <c r="B801" t="inlineStr">
+      <c r="B800" t="inlineStr">
         <is>
           <t>images/「まぁ何というサプライズでしょう」_img1.jpg</t>
         </is>
       </c>
-      <c r="C801" t="inlineStr">
+      <c r="C800" t="inlineStr">
         <is>
           <t>中国語 ,学習</t>
         </is>
       </c>
     </row>
-    <row r="802">
-      <c r="A802" t="inlineStr">
+    <row r="801">
+      <c r="A801" t="inlineStr">
         <is>
           <t xml:space="preserve">「ハックション」اتشوو
 アチュー！ ['aatShuu]
@@ -17304,19 +17282,19 @@
 1811 </t>
         </is>
       </c>
-      <c r="B802" t="inlineStr">
+      <c r="B801" t="inlineStr">
         <is>
           <t>images/「ハックション」_img1.jpg</t>
         </is>
       </c>
-      <c r="C802" t="inlineStr">
+      <c r="C801" t="inlineStr">
         <is>
           <t>あらびあや</t>
         </is>
       </c>
     </row>
-    <row r="803">
-      <c r="A803" t="inlineStr">
+    <row r="802">
+      <c r="A802" t="inlineStr">
         <is>
           <t xml:space="preserve">「スブハーナッラー」「アルハムドゥリッラー」「アッラーアクバル」
 سبحان الله
@@ -17327,19 +17305,19 @@
 2308 dribbble com </t>
         </is>
       </c>
-      <c r="B803" t="inlineStr">
+      <c r="B802" t="inlineStr">
         <is>
           <t>images/「スブハーナッラー」「アルハムドゥリッ_img1.jpg</t>
         </is>
       </c>
-      <c r="C803" t="inlineStr">
+      <c r="C802" t="inlineStr">
         <is>
           <t>四角 ,コンパクト</t>
         </is>
       </c>
     </row>
-    <row r="804">
-      <c r="A804" t="inlineStr">
+    <row r="803">
+      <c r="A803" t="inlineStr">
         <is>
           <t xml:space="preserve">「すごく美味しい！」لذيذ جدًا
 ラズィーズ・ジッダン [laDhiiDh jiddan]
@@ -17348,19 +17326,19 @@
 2109 goodreads com </t>
         </is>
       </c>
-      <c r="B804" t="inlineStr">
+      <c r="B803" t="inlineStr">
         <is>
           <t>images/「すごく美味しい！」_img1.jpg</t>
         </is>
       </c>
-      <c r="C804" t="inlineStr">
+      <c r="C803" t="inlineStr">
         <is>
           <t>フレーズ ,感想</t>
         </is>
       </c>
     </row>
-    <row r="805">
-      <c r="A805" t="inlineStr">
+    <row r="804">
+      <c r="A804" t="inlineStr">
         <is>
           <t xml:space="preserve">「しとしと、雨」تك تك يا مطر
 ティクティク [tik tik yaa ma_tar]
@@ -17369,19 +17347,19 @@
 2308 出典不明 </t>
         </is>
       </c>
-      <c r="B805" t="inlineStr">
+      <c r="B804" t="inlineStr">
         <is>
           <t>images/「しとしと、雨」_img1.jpg</t>
         </is>
       </c>
-      <c r="C805" t="inlineStr">
+      <c r="C804" t="inlineStr">
         <is>
           <t>天気 ,梅雨</t>
         </is>
       </c>
     </row>
-    <row r="806">
-      <c r="A806" t="inlineStr">
+    <row r="805">
+      <c r="A805" t="inlineStr">
         <is>
           <t xml:space="preserve">「さかさま」رأساً على عقب
 ラッアサン・アラー・アケブ [ra'san *alaa *aqib]
@@ -17389,19 +17367,19 @@
 2109 出典不明 </t>
         </is>
       </c>
-      <c r="B806" t="inlineStr">
+      <c r="B805" t="inlineStr">
         <is>
           <t>images/「さかさま」_img1.jpg</t>
         </is>
       </c>
-      <c r="C806" t="inlineStr">
+      <c r="C805" t="inlineStr">
         <is>
           <t>壁 ,上下</t>
         </is>
       </c>
     </row>
-    <row r="807">
-      <c r="A807" t="inlineStr">
+    <row r="806">
+      <c r="A806" t="inlineStr">
         <is>
           <t xml:space="preserve">「エジプトよどこへ行った」
 فينك يا مصر؟
@@ -17411,19 +17389,19 @@
 1809 shehabfawzy1.tumblr </t>
         </is>
       </c>
-      <c r="B807" t="inlineStr">
+      <c r="B806" t="inlineStr">
         <is>
           <t>images/「エジプトよどこへ行った」_img1.jpg</t>
         </is>
       </c>
-      <c r="C807" t="inlineStr">
+      <c r="C806" t="inlineStr">
         <is>
           <t>ピラミッド ,歴史</t>
         </is>
       </c>
     </row>
-    <row r="808">
-      <c r="A808" t="inlineStr">
+    <row r="807">
+      <c r="A807" t="inlineStr">
         <is>
           <t xml:space="preserve">「ありがとう」شكراً
 シュクラン [Shukran]
@@ -17431,19 +17409,19 @@
 2109 出典不明 </t>
         </is>
       </c>
-      <c r="B808" t="inlineStr">
+      <c r="B807" t="inlineStr">
         <is>
           <t>images/「ありがとう」_img1.jpg</t>
         </is>
       </c>
-      <c r="C808" t="inlineStr">
+      <c r="C807" t="inlineStr">
         <is>
           <t>挨拶 ,文字</t>
         </is>
       </c>
     </row>
-    <row r="809">
-      <c r="A809" t="inlineStr">
+    <row r="808">
+      <c r="A808" t="inlineStr">
         <is>
           <t xml:space="preserve">「昼寝の時間だ」
 إنه وقت القيلولة
@@ -17452,12 +17430,12 @@
 2501 https://x.com/NatGeoMagArab/status/1858049951579910486 </t>
         </is>
       </c>
-      <c r="B809" t="inlineStr">
+      <c r="B808" t="inlineStr">
         <is>
           <t>images/「昼寝の時間だ」_img1.jpg</t>
         </is>
       </c>
-      <c r="C809" t="inlineStr">
+      <c r="C808" t="inlineStr">
         <is>
           <t>手書き語学 ,アラビア語 ,ペンギン</t>
         </is>

--- a/posts.xlsx
+++ b/posts.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C808"/>
+  <dimension ref="A1:C807"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -10929,27 +10929,6 @@
     <row r="501">
       <c r="A501" t="inlineStr">
         <is>
-          <t xml:space="preserve">「あなたのスマホの着信音にいかが？」
-هل يصلح صوتها نغمة رنين لهاتفك؟
-[hal ya-_sluHu _sawtu-haa naGhmata raniinin li-haatifi-k?]
-「それはメロディーとして相応しくある」[ya-_sluHu naGhmatan]
-2507 https://twitter.com/NatGeoMagArab/status/1752232696435339325 </t>
-        </is>
-      </c>
-      <c r="B501" t="inlineStr">
-        <is>
-          <t>images/「あなたのスマホの着信音にいかが？」_img1.jpg</t>
-        </is>
-      </c>
-      <c r="C501" t="inlineStr">
-        <is>
-          <t>手書き語学 ,アラビア語 ,フクロウ</t>
-        </is>
-      </c>
-    </row>
-    <row r="502">
-      <c r="A502" t="inlineStr">
-        <is>
           <t xml:space="preserve">「コーヒーが冷めないうちに」
 قبل أن تبرد القهوة
 [qabla 'an ta-bruda l-qahwa]
@@ -10958,19 +10937,19 @@
 2403 https://a.co d/7jizZfE </t>
         </is>
       </c>
-      <c r="B502" t="inlineStr">
+      <c r="B501" t="inlineStr">
         <is>
           <t>images/「コーヒーが冷めないうちに」_img1.jpg</t>
         </is>
       </c>
-      <c r="C502" t="inlineStr">
+      <c r="C501" t="inlineStr">
         <is>
           <t>小説 ,表紙</t>
         </is>
       </c>
     </row>
-    <row r="503">
-      <c r="A503" t="inlineStr">
+    <row r="502">
+      <c r="A502" t="inlineStr">
         <is>
           <t xml:space="preserve">「悲しむな」Don't be sad
 لا تحزَنْ
@@ -10980,15 +10959,15 @@
 2402 MADYAN </t>
         </is>
       </c>
-      <c r="B503" t="inlineStr">
+      <c r="B502" t="inlineStr">
         <is>
           <t>images/「悲しむな」Don't be sad_img1.jpg</t>
         </is>
       </c>
-      <c r="C503" t="inlineStr"/>
-    </row>
-    <row r="504">
-      <c r="A504" t="inlineStr">
+      <c r="C502" t="inlineStr"/>
+    </row>
+    <row r="503">
+      <c r="A503" t="inlineStr">
         <is>
           <t xml:space="preserve">「悲しむな」لا تحزن
 ラー・タハザン [laa ta-Hzan]
@@ -10997,19 +10976,19 @@
 1903 fadli7 deviantart com </t>
         </is>
       </c>
-      <c r="B504" t="inlineStr">
+      <c r="B503" t="inlineStr">
         <is>
           <t>images/「悲しむな」_img1.jpg</t>
         </is>
       </c>
-      <c r="C504" t="inlineStr">
+      <c r="C503" t="inlineStr">
         <is>
           <t>書道 ,カリグラフィー</t>
         </is>
       </c>
     </row>
-    <row r="505">
-      <c r="A505" t="inlineStr">
+    <row r="504">
+      <c r="A504" t="inlineStr">
         <is>
           <t xml:space="preserve">「心配しないで、パパ」
 لا تقلق يا بابا
@@ -11019,19 +10998,19 @@
 2308 alsalwabooks </t>
         </is>
       </c>
-      <c r="B505" t="inlineStr">
+      <c r="B504" t="inlineStr">
         <is>
           <t>images/「心配しないで、パパ」_img1.jpg</t>
         </is>
       </c>
-      <c r="C505" t="inlineStr">
+      <c r="C504" t="inlineStr">
         <is>
           <t>絵本 ,親子</t>
         </is>
       </c>
     </row>
-    <row r="506">
-      <c r="A506" t="inlineStr">
+    <row r="505">
+      <c r="A505" t="inlineStr">
         <is>
           <t xml:space="preserve">「時は剣のごとし。あなたが割かなければあなたが割かれる」
 الوقت كالسيف إن لم تقطعه قطعك
@@ -11040,19 +11019,19 @@
 2308 sultanart </t>
         </is>
       </c>
-      <c r="B506" t="inlineStr">
+      <c r="B505" t="inlineStr">
         <is>
           <t>images/「時は剣のごとし。あなたが割かなければ_img1.jpg</t>
         </is>
       </c>
-      <c r="C506" t="inlineStr">
+      <c r="C505" t="inlineStr">
         <is>
           <t>ことわざ</t>
         </is>
       </c>
     </row>
-    <row r="507">
-      <c r="A507" t="inlineStr">
+    <row r="506">
+      <c r="A506" t="inlineStr">
         <is>
           <t xml:space="preserve">「そんな風に私を見ないで」
 لا تنظر إلي هكذا
@@ -11062,19 +11041,19 @@
 1810 </t>
         </is>
       </c>
-      <c r="B507" t="inlineStr">
+      <c r="B506" t="inlineStr">
         <is>
           <t>images/「そんな風に私を見ないで」_img1.jpg</t>
         </is>
       </c>
-      <c r="C507" t="inlineStr">
+      <c r="C506" t="inlineStr">
         <is>
           <t>あらびあや</t>
         </is>
       </c>
     </row>
-    <row r="508">
-      <c r="A508" t="inlineStr">
+    <row r="507">
+      <c r="A507" t="inlineStr">
         <is>
           <t xml:space="preserve">「必要以上に勉強するな」
 لا تدرس أكثر من اللازم
@@ -11084,19 +11063,19 @@
 2109 出典不明 </t>
         </is>
       </c>
-      <c r="B508" t="inlineStr">
+      <c r="B507" t="inlineStr">
         <is>
           <t>images/「必要以上に勉強するな」_img1.jpg</t>
         </is>
       </c>
-      <c r="C508" t="inlineStr">
+      <c r="C507" t="inlineStr">
         <is>
           <t>徹夜 ,計画</t>
         </is>
       </c>
     </row>
-    <row r="509">
-      <c r="A509" t="inlineStr">
+    <row r="508">
+      <c r="A508" t="inlineStr">
         <is>
           <t xml:space="preserve">「翼を広げなさい」
 افْرِدْ جَنَاحَكَ
@@ -11106,19 +11085,19 @@
 2308 Librairie SANA </t>
         </is>
       </c>
-      <c r="B509" t="inlineStr">
+      <c r="B508" t="inlineStr">
         <is>
           <t>images/「翼を広げなさい」_img1.jpg</t>
         </is>
       </c>
-      <c r="C509" t="inlineStr">
+      <c r="C508" t="inlineStr">
         <is>
           <t>絵本 ,鳥</t>
         </is>
       </c>
     </row>
-    <row r="510">
-      <c r="A510" t="inlineStr">
+    <row r="509">
+      <c r="A509" t="inlineStr">
         <is>
           <t xml:space="preserve">「作ろう。自分の幸せは自分で」
 اصنع سعادتك بنفسك
@@ -11128,19 +11107,19 @@
 1812 fado1997 tumblr </t>
         </is>
       </c>
-      <c r="B510" t="inlineStr">
+      <c r="B509" t="inlineStr">
         <is>
           <t>images/「作ろう。自分の幸せは自分で」_img1.jpg</t>
         </is>
       </c>
-      <c r="C510" t="inlineStr">
+      <c r="C509" t="inlineStr">
         <is>
           <t>ポジティブ</t>
         </is>
       </c>
     </row>
-    <row r="511">
-      <c r="A511" t="inlineStr">
+    <row r="510">
+      <c r="A510" t="inlineStr">
         <is>
           <t xml:space="preserve">「あなたの栄光を作れ」
 اصنَع مجدَك
@@ -11150,19 +11129,19 @@
 1811 Ahmed Madyan </t>
         </is>
       </c>
-      <c r="B511" t="inlineStr">
+      <c r="B510" t="inlineStr">
         <is>
           <t>images/「あなたの栄光を作れ」_img1.jpg</t>
         </is>
       </c>
-      <c r="C511" t="inlineStr">
+      <c r="C510" t="inlineStr">
         <is>
           <t>ヒーロー ,自分</t>
         </is>
       </c>
     </row>
-    <row r="512">
-      <c r="A512" t="inlineStr">
+    <row r="511">
+      <c r="A511" t="inlineStr">
         <is>
           <t xml:space="preserve">「声を上げろ」إرفع صوتك
 イルファア・サウタク [irfa* _sawta-k]
@@ -11171,19 +11150,19 @@
 2109 ALHURRA </t>
         </is>
       </c>
-      <c r="B512" t="inlineStr">
+      <c r="B511" t="inlineStr">
         <is>
           <t>images/「声を上げろ」_img1.jpg</t>
         </is>
       </c>
-      <c r="C512" t="inlineStr">
+      <c r="C511" t="inlineStr">
         <is>
           <t>発言 ,言論</t>
         </is>
       </c>
     </row>
-    <row r="513">
-      <c r="A513" t="inlineStr">
+    <row r="512">
+      <c r="A512" t="inlineStr">
         <is>
           <t xml:space="preserve">「口を開く前に、心を開きなさい」
 افتح عقلك قبل أن تفتح فمك
@@ -11193,19 +11172,19 @@
 2308 出典不明 </t>
         </is>
       </c>
-      <c r="B513" t="inlineStr">
+      <c r="B512" t="inlineStr">
         <is>
           <t>images/「口を開く前に、心を開きなさい」_img1.jpg</t>
         </is>
       </c>
-      <c r="C513" t="inlineStr">
+      <c r="C512" t="inlineStr">
         <is>
           <t>教訓 ,名言</t>
         </is>
       </c>
     </row>
-    <row r="514">
-      <c r="A514" t="inlineStr">
+    <row r="513">
+      <c r="A513" t="inlineStr">
         <is>
           <t xml:space="preserve">「読んでちょうだい、読んであげるよ」
 اِقرأ لي، أقرأ لك
@@ -11215,19 +11194,19 @@
 2308 archive org </t>
         </is>
       </c>
-      <c r="B514" t="inlineStr">
+      <c r="B513" t="inlineStr">
         <is>
           <t>images/「読んでちょうだい、読んであげるよ」_img1.jpg,images/「読んでちょうだい、読んであげるよ」_img2.jpg</t>
         </is>
       </c>
-      <c r="C514" t="inlineStr">
+      <c r="C513" t="inlineStr">
         <is>
           <t xml:space="preserve">絵本 ,読み聞かせ </t>
         </is>
       </c>
     </row>
-    <row r="515">
-      <c r="A515" t="inlineStr">
+    <row r="514">
+      <c r="A514" t="inlineStr">
         <is>
           <t xml:space="preserve">「がんばれ」ابذل جهدك
 ウブズル・ジャハダク [ubDhul jahda-k]
@@ -11235,19 +11214,19 @@
 2308 https://twitter.com/Ishaiookh/status/1469579864915288068 </t>
         </is>
       </c>
-      <c r="B515" t="inlineStr">
+      <c r="B514" t="inlineStr">
         <is>
           <t>images/「がんばれ」_img1.jpg</t>
         </is>
       </c>
-      <c r="C515" t="inlineStr">
+      <c r="C514" t="inlineStr">
         <is>
           <t>文字 ,下办つ_ぺ中ヵ可</t>
         </is>
       </c>
     </row>
-    <row r="516">
-      <c r="A516" t="inlineStr">
+    <row r="515">
+      <c r="A515" t="inlineStr">
         <is>
           <t xml:space="preserve">「窓を開けよ。そこに光がある」
 افتح النافذة ثمة ضوء
@@ -11257,19 +11236,19 @@
 2308 الدكتور خالد المنيف </t>
         </is>
       </c>
-      <c r="B516" t="inlineStr">
+      <c r="B515" t="inlineStr">
         <is>
           <t>images/「窓を開けよ。そこに光がある」_img1.jpg</t>
         </is>
       </c>
-      <c r="C516" t="inlineStr">
+      <c r="C515" t="inlineStr">
         <is>
           <t>換気 ,ウインドウズ</t>
         </is>
       </c>
     </row>
-    <row r="517">
-      <c r="A517" t="inlineStr">
+    <row r="516">
+      <c r="A516" t="inlineStr">
         <is>
           <t xml:space="preserve">「笑えよ」اضحك
 イドハク [i_dHak]
@@ -11278,19 +11257,19 @@
 1809 </t>
         </is>
       </c>
-      <c r="B517" t="inlineStr">
+      <c r="B516" t="inlineStr">
         <is>
           <t>images/「笑えよ」_img1.jpg</t>
         </is>
       </c>
-      <c r="C517" t="inlineStr">
+      <c r="C516" t="inlineStr">
         <is>
           <t>あらびあや</t>
         </is>
       </c>
     </row>
-    <row r="518">
-      <c r="A518" t="inlineStr">
+    <row r="517">
+      <c r="A517" t="inlineStr">
         <is>
           <t xml:space="preserve">「よろこべ」افرح
 イフラハ [ifraH]
@@ -11298,19 +11277,19 @@
 2308 https://samia-khalil.blogspot.jp/2014/08/blog-post.html?m=1 </t>
         </is>
       </c>
-      <c r="B518" t="inlineStr">
+      <c r="B517" t="inlineStr">
         <is>
           <t>images/「よろこべ」_img1.jpg</t>
         </is>
       </c>
-      <c r="C518" t="inlineStr">
+      <c r="C517" t="inlineStr">
         <is>
           <t>子供 ,笑顔</t>
         </is>
       </c>
     </row>
-    <row r="519">
-      <c r="A519" t="inlineStr">
+    <row r="518">
+      <c r="A518" t="inlineStr">
         <is>
           <t xml:space="preserve">「いつでも正しいことをしなさい」
 دائما افعل الشيء الصحيح
@@ -11320,19 +11299,19 @@
 2508 instagram com/p/zNNDYAsNaG/ </t>
         </is>
       </c>
-      <c r="B519" t="inlineStr">
+      <c r="B518" t="inlineStr">
         <is>
           <t>images/「いつでも正しいことをしなさい」_img1.jpg</t>
         </is>
       </c>
-      <c r="C519" t="inlineStr">
+      <c r="C518" t="inlineStr">
         <is>
           <t>教訓 ,正義</t>
         </is>
       </c>
     </row>
-    <row r="520">
-      <c r="A520" t="inlineStr">
+    <row r="519">
+      <c r="A519" t="inlineStr">
         <is>
           <t xml:space="preserve">「コンフォートゾーンから、出よう」
 اخرج من منطقة الراحة
@@ -11342,37 +11321,37 @@
 2010 kareem mrghani </t>
         </is>
       </c>
+      <c r="B519" t="inlineStr">
+        <is>
+          <t>images/「コンフォートゾーンから、出よう」_img1.jpg</t>
+        </is>
+      </c>
+      <c r="C519" t="inlineStr">
+        <is>
+          <t>鳥 ,勇気</t>
+        </is>
+      </c>
+    </row>
+    <row r="520">
+      <c r="A520" t="inlineStr">
+        <is>
+          <t xml:space="preserve">オットセイ。
+2308 https://twitter.com/NatGeoMagArab/status/1602604286109970432 </t>
+        </is>
+      </c>
       <c r="B520" t="inlineStr">
         <is>
-          <t>images/「コンフォートゾーンから、出よう」_img1.jpg</t>
+          <t>images/オットセイ。_img1.jpg,images/オットセイ。_img2.jpg</t>
         </is>
       </c>
       <c r="C520" t="inlineStr">
         <is>
-          <t>鳥 ,勇気</t>
+          <t>手書き語学 ,アラビア語 ,オットセイ</t>
         </is>
       </c>
     </row>
     <row r="521">
       <c r="A521" t="inlineStr">
-        <is>
-          <t xml:space="preserve">オットセイ。
-2308 https://twitter.com/NatGeoMagArab/status/1602604286109970432 </t>
-        </is>
-      </c>
-      <c r="B521" t="inlineStr">
-        <is>
-          <t>images/オットセイ。_img1.jpg,images/オットセイ。_img2.jpg</t>
-        </is>
-      </c>
-      <c r="C521" t="inlineStr">
-        <is>
-          <t>手書き語学 ,アラビア語 ,オットセイ</t>
-        </is>
-      </c>
-    </row>
-    <row r="522">
-      <c r="A522" t="inlineStr">
         <is>
           <t xml:space="preserve">「かわいい家に住む」
 يعيش في بيت لطيف
@@ -11382,19 +11361,19 @@
 2607 </t>
         </is>
       </c>
-      <c r="B522" t="inlineStr">
+      <c r="B521" t="inlineStr">
         <is>
           <t>images/「かわいい家に住む」_img1.jpg</t>
         </is>
       </c>
-      <c r="C522" t="inlineStr">
+      <c r="C521" t="inlineStr">
         <is>
           <t>アニメ ,ハム太郎</t>
         </is>
       </c>
     </row>
-    <row r="523">
-      <c r="A523" t="inlineStr">
+    <row r="522">
+      <c r="A522" t="inlineStr">
         <is>
           <t xml:space="preserve">「私の美しい町で大きい家に住んでいます」
 أعيش في بيت كبير في مدينتي الجميلة
@@ -11403,15 +11382,15 @@
 2410 Arabic With Nadia youtu be ocbg19GPCWE </t>
         </is>
       </c>
-      <c r="B523" t="inlineStr">
+      <c r="B522" t="inlineStr">
         <is>
           <t>images/「私の美しい町で大きい家に住んでいます_img1.jpg</t>
         </is>
       </c>
-      <c r="C523" t="inlineStr"/>
-    </row>
-    <row r="524">
-      <c r="A524" t="inlineStr">
+      <c r="C522" t="inlineStr"/>
+    </row>
+    <row r="523">
+      <c r="A523" t="inlineStr">
         <is>
           <t xml:space="preserve">「どうして早く寝るのかな」
 لماذا أنام باكراً؟
@@ -11421,19 +11400,19 @@
 2511 سلسلة الحلزونة </t>
         </is>
       </c>
-      <c r="B524" t="inlineStr">
+      <c r="B523" t="inlineStr">
         <is>
           <t>images/「どうして早く寝るのかな」_img1.jpg</t>
         </is>
       </c>
-      <c r="C524" t="inlineStr">
+      <c r="C523" t="inlineStr">
         <is>
           <t>絵本 ,ホルモン</t>
         </is>
       </c>
     </row>
-    <row r="525">
-      <c r="A525" t="inlineStr">
+    <row r="524">
+      <c r="A524" t="inlineStr">
         <is>
           <t xml:space="preserve">⁦「この絵文字はどんな意味？」⁩
 ماذا يعني هذا الايموجي؟؟
@@ -11443,19 +11422,19 @@
 2407 YouTube Smail Tech </t>
         </is>
       </c>
-      <c r="B525" t="inlineStr">
+      <c r="B524" t="inlineStr">
         <is>
           <t>images/⁦「この絵文字はどんな意味？」⁩_img1.jpg</t>
         </is>
       </c>
-      <c r="C525" t="inlineStr">
+      <c r="C524" t="inlineStr">
         <is>
           <t>顔 ,絵文字</t>
         </is>
       </c>
     </row>
-    <row r="526">
-      <c r="A526" t="inlineStr">
+    <row r="525">
+      <c r="A525" t="inlineStr">
         <is>
           <t xml:space="preserve">「回し車の中で回る」
 يدور في دولاب خفيف
@@ -11465,19 +11444,19 @@
 2109 </t>
         </is>
       </c>
-      <c r="B526" t="inlineStr">
+      <c r="B525" t="inlineStr">
         <is>
           <t>images/「回し車の中で回る」_img1.jpg</t>
         </is>
       </c>
-      <c r="C526" t="inlineStr">
+      <c r="C525" t="inlineStr">
         <is>
           <t>ハムスター  ,ハム太郎</t>
         </is>
       </c>
     </row>
-    <row r="527">
-      <c r="A527" t="inlineStr">
+    <row r="526">
+      <c r="A526" t="inlineStr">
         <is>
           <t xml:space="preserve">「自信を持つには？」
 كيف تثق بنفسك؟
@@ -11487,19 +11466,19 @@
 2411 Gwid3, tumblr </t>
         </is>
       </c>
-      <c r="B527" t="inlineStr">
+      <c r="B526" t="inlineStr">
         <is>
           <t>images/「自信を持つには？」_img1.jpg</t>
         </is>
       </c>
-      <c r="C527" t="inlineStr">
+      <c r="C526" t="inlineStr">
         <is>
           <t>イラスト ,自信</t>
         </is>
       </c>
     </row>
-    <row r="528">
-      <c r="A528" t="inlineStr">
+    <row r="527">
+      <c r="A527" t="inlineStr">
         <is>
           <t xml:space="preserve">「幸せな眠り…。この子ライオンは深い眠りに落ちている」
 نوم هانئ.. يغط هذا الشبل في نوم عميق
@@ -11510,19 +11489,19 @@
 2105 https://twitter.com/NatGeoMagArab/status/1305084013141319682 </t>
         </is>
       </c>
-      <c r="B528" t="inlineStr">
+      <c r="B527" t="inlineStr">
         <is>
           <t>images/「幸せな眠り…。この子ライオンは深い眠.jpeg</t>
         </is>
       </c>
-      <c r="C528" t="inlineStr">
+      <c r="C527" t="inlineStr">
         <is>
           <t>お昼寝 ,ｽﾔｧ</t>
         </is>
       </c>
     </row>
-    <row r="529">
-      <c r="A529" t="inlineStr">
+    <row r="528">
+      <c r="A528" t="inlineStr">
         <is>
           <t xml:space="preserve">「いつ思いつきますか？」
 متى تأتي الأفكار؟
@@ -11532,19 +11511,19 @@
 2103 alyaum com </t>
         </is>
       </c>
-      <c r="B529" t="inlineStr">
+      <c r="B528" t="inlineStr">
         <is>
           <t>images/「いつ思いつきますか？」_img1.jpg</t>
         </is>
       </c>
-      <c r="C529" t="inlineStr">
+      <c r="C528" t="inlineStr">
         <is>
           <t>ひらめき ,メモ</t>
         </is>
       </c>
     </row>
-    <row r="530">
-      <c r="A530" t="inlineStr">
+    <row r="529">
+      <c r="A529" t="inlineStr">
         <is>
           <t xml:space="preserve">「美しくありなさい。世界が美しく見えますよ」
 كن جميلا ترىٰ الوجود جميلا
@@ -11554,19 +11533,19 @@
 2111 https://iiislam.tumblr.com/post/90505498218 </t>
         </is>
       </c>
-      <c r="B530" t="inlineStr">
+      <c r="B529" t="inlineStr">
         <is>
           <t>images/「美しくありなさい。世界が美しく見えま_img1.jpg</t>
         </is>
       </c>
-      <c r="C530" t="inlineStr">
+      <c r="C529" t="inlineStr">
         <is>
           <t>壁 ,宇宙</t>
         </is>
       </c>
     </row>
-    <row r="531">
-      <c r="A531" t="inlineStr">
+    <row r="530">
+      <c r="A530" t="inlineStr">
         <is>
           <t xml:space="preserve">「まもなくNASAがジェイムズ・ウェッブ宇宙望遠鏡の打ち上げを行う」
 بعد ساعات قليلة ستقوم وكالة ناسا بإطلاق تلسكوب جيمس ويب
@@ -11574,19 +11553,19 @@
 2308 https://twitter.com/scitalk2u/status/1474643899603947524 </t>
         </is>
       </c>
-      <c r="B531" t="inlineStr">
+      <c r="B530" t="inlineStr">
         <is>
           <t>images/「まもなくNASAがジェイムズ・ウェッ_img1.jpg</t>
         </is>
       </c>
-      <c r="C531" t="inlineStr">
+      <c r="C530" t="inlineStr">
         <is>
           <t>NASA ,望遠鏡</t>
         </is>
       </c>
     </row>
-    <row r="532">
-      <c r="A532" t="inlineStr">
+    <row r="531">
+      <c r="A531" t="inlineStr">
         <is>
           <t xml:space="preserve">「お疲れ様です」يعطيك العافية
 ヤーアティーキルアーフィエ [ya-*_tiy-k el-*aafyeh]
@@ -11595,15 +11574,15 @@
 2109 محمد و ديمة بشار </t>
         </is>
       </c>
-      <c r="B532" t="inlineStr"/>
-      <c r="C532" t="inlineStr">
+      <c r="B531" t="inlineStr"/>
+      <c r="C531" t="inlineStr">
         <is>
           <t>歌 ,労い</t>
         </is>
       </c>
     </row>
-    <row r="533">
-      <c r="A533" t="inlineStr">
+    <row r="532">
+      <c r="A532" t="inlineStr">
         <is>
           <t xml:space="preserve">「まるでこのペンギンは大声で叫んでいるかのようだ」
 يبدو هذا البطريق وكأنه يصيح بعلو صوته
@@ -11611,19 +11590,19 @@
 2308 https://twitter.com/NatGeoMagArab/status/1492023331846967296 </t>
         </is>
       </c>
-      <c r="B533" t="inlineStr">
+      <c r="B532" t="inlineStr">
         <is>
           <t>images/「まるでこのペンギンは大声で叫んでいる_img1.jpg</t>
         </is>
       </c>
-      <c r="C533" t="inlineStr">
+      <c r="C532" t="inlineStr">
         <is>
           <t>手書き語学 ,ペンギン</t>
         </is>
       </c>
     </row>
-    <row r="534">
-      <c r="A534" t="inlineStr">
+    <row r="533">
+      <c r="A533" t="inlineStr">
         <is>
           <t xml:space="preserve">「Reteti Elephant Sanctuaryではゾウの孤児たちが良質な世話を受けている」
 تحظى الفيلة اليتيمة في "ملاذ ريتِيتِي لرعاية الفِيَلة" برعاية فائقة
@@ -11631,19 +11610,19 @@
 2209 https://twitter.com/NatGeoMagArab/status/1568683277845942273 </t>
         </is>
       </c>
-      <c r="B534" t="inlineStr">
+      <c r="B533" t="inlineStr">
         <is>
           <t>images/「Reteti Elephant Sa.jpg</t>
         </is>
       </c>
-      <c r="C534" t="inlineStr">
+      <c r="C533" t="inlineStr">
         <is>
           <t>ケニア</t>
         </is>
       </c>
     </row>
-    <row r="535">
-      <c r="A535" t="inlineStr">
+    <row r="534">
+      <c r="A534" t="inlineStr">
         <is>
           <t xml:space="preserve">「すぐ戻ります」سنعود بعد قليل
 サナウード・バアド・カリール [sa-na-*uud ba*d qaliil]
@@ -11652,19 +11631,19 @@
 2308 Clacket Media </t>
         </is>
       </c>
-      <c r="B535" t="inlineStr">
+      <c r="B534" t="inlineStr">
         <is>
           <t>images/「すぐ戻ります」_img1.jpg</t>
         </is>
       </c>
-      <c r="C535" t="inlineStr">
+      <c r="C534" t="inlineStr">
         <is>
           <t>プレート ,ドラマ</t>
         </is>
       </c>
     </row>
-    <row r="536">
-      <c r="A536" t="inlineStr">
+    <row r="535">
+      <c r="A535" t="inlineStr">
         <is>
           <t xml:space="preserve">「いつの日か、私は飛ぶんだ」
 يوم من الأيام سأطير
@@ -11674,19 +11653,19 @@
 2105 a-d-a-y-d-r-e-a-m-e-r.tumblr com </t>
         </is>
       </c>
-      <c r="B536" t="inlineStr">
+      <c r="B535" t="inlineStr">
         <is>
           <t>images/「いつの日か、私は飛ぶんだ」_img1.jpg</t>
         </is>
       </c>
-      <c r="C536" t="inlineStr">
+      <c r="C535" t="inlineStr">
         <is>
           <t>希望 ,未来</t>
         </is>
       </c>
     </row>
-    <row r="537">
-      <c r="A537" t="inlineStr">
+    <row r="536">
+      <c r="A536" t="inlineStr">
         <is>
           <t xml:space="preserve">「彼の声がこんなふうだと想像しましたか？」
 هل تخيلت أن يكون صوته هكذا؟
@@ -11694,19 +11673,19 @@
 2504 https://twitter.com/NatGeoMagArab/status/1567543266954067970 </t>
         </is>
       </c>
-      <c r="B537" t="inlineStr">
+      <c r="B536" t="inlineStr">
         <is>
           <t>images/「彼の声がこんなふうだと想像しましたか_img1.jpg</t>
         </is>
       </c>
-      <c r="C537" t="inlineStr">
+      <c r="C536" t="inlineStr">
         <is>
           <t>手書き語学 ,アラビア語 ,齧歯類</t>
         </is>
       </c>
     </row>
-    <row r="538">
-      <c r="A538" t="inlineStr">
+    <row r="537">
+      <c r="A537" t="inlineStr">
         <is>
           <t xml:space="preserve">「幸せでいるための10の科学的方法」
 عشر طرق علمية لتكون سعيدا
@@ -11715,19 +11694,19 @@
 2308 Founders and Founders </t>
         </is>
       </c>
-      <c r="B538" t="inlineStr">
+      <c r="B537" t="inlineStr">
         <is>
           <t>images/「幸せでいるための10の科学的方法」_img1.jpg</t>
         </is>
       </c>
-      <c r="C538" t="inlineStr">
+      <c r="C537" t="inlineStr">
         <is>
           <t>happy ,コツ</t>
         </is>
       </c>
     </row>
-    <row r="539">
-      <c r="A539" t="inlineStr">
+    <row r="538">
+      <c r="A538" t="inlineStr">
         <is>
           <t xml:space="preserve">「何事も難しい。簡単になる前は」
 كل شيء صعب قبل أن يصير سهل
@@ -11736,19 +11715,19 @@
 1809 nihad me </t>
         </is>
       </c>
-      <c r="B539" t="inlineStr">
+      <c r="B538" t="inlineStr">
         <is>
           <t>images/「何事も難しい。簡単になる前は」_img1.jpg</t>
         </is>
       </c>
-      <c r="C539" t="inlineStr">
+      <c r="C538" t="inlineStr">
         <is>
           <t>初心者 ,教訓</t>
         </is>
       </c>
     </row>
-    <row r="540">
-      <c r="A540" t="inlineStr">
+    <row r="539">
+      <c r="A539" t="inlineStr">
         <is>
           <t xml:space="preserve">「私は戻らない」لن اعود
 ラン・アウード [lan 'a-*uud(a)]
@@ -11757,19 +11736,19 @@
 2109 elcinema com </t>
         </is>
       </c>
-      <c r="B540" t="inlineStr">
+      <c r="B539" t="inlineStr">
         <is>
           <t>images/「私は戻らない」_img1.jpg</t>
         </is>
       </c>
-      <c r="C540" t="inlineStr">
+      <c r="C539" t="inlineStr">
         <is>
           <t>タイトル ,なんちゅう顔しとる</t>
         </is>
       </c>
     </row>
-    <row r="541">
-      <c r="A541" t="inlineStr">
+    <row r="540">
+      <c r="A540" t="inlineStr">
         <is>
           <t xml:space="preserve">「私は作家になるのが夢です」
 أحلُمُ أن أكونَ كاتبة
@@ -11779,19 +11758,19 @@
 2308 Maktabatee com </t>
         </is>
       </c>
-      <c r="B541" t="inlineStr">
+      <c r="B540" t="inlineStr">
         <is>
           <t>images/「私は作家になるのが夢です」_img1.jpg</t>
         </is>
       </c>
-      <c r="C541" t="inlineStr">
+      <c r="C540" t="inlineStr">
         <is>
           <t>作家志望 ,ライター</t>
         </is>
       </c>
     </row>
-    <row r="542">
-      <c r="A542" t="inlineStr">
+    <row r="541">
+      <c r="A541" t="inlineStr">
         <is>
           <t xml:space="preserve">「あなたが去った後も波は止みません」
 لن يقف الموج بعد رحيلك
@@ -11801,19 +11780,19 @@
 2308 ريم الشاوش https://ar.arabwomanmag.com/%D9%84%D9%86-%D9%8A%D9%82%D9%81-%D8%A7%D9%84%D9%85%D9%88%D8%AC-%D8%A8%D8%B9%D8%AF-%D8%B1%D8%AD%D9%8A%D9%84%D9%83-%D8%A8%D8%B9%D8%AF-%D8%B1%D8%AD%D9%8A%D9%84%D9%83/ </t>
         </is>
       </c>
-      <c r="B542" t="inlineStr">
+      <c r="B541" t="inlineStr">
         <is>
           <t>images/「あなたが去った後も波は止みません」_img1.jpg</t>
         </is>
       </c>
-      <c r="C542" t="inlineStr">
+      <c r="C541" t="inlineStr">
         <is>
           <t>海 ,哲学</t>
         </is>
       </c>
     </row>
-    <row r="543">
-      <c r="A543" t="inlineStr">
+    <row r="542">
+      <c r="A542" t="inlineStr">
         <is>
           <t xml:space="preserve">「彼の尖った牙を心配するな」
 لا تدع أنيابه المدببة تقلقك
@@ -11822,19 +11801,19 @@
 2308 https://twitter.com/NatGeoMagArab/status/1524691046818406400 </t>
         </is>
       </c>
-      <c r="B543" t="inlineStr">
+      <c r="B542" t="inlineStr">
         <is>
           <t>images/「彼の尖った牙を心配するな」_img1.jpg,images/「彼の尖った牙を心配するな」_img2.jpg,images/「彼の尖った牙を心配するな」_img3.jpg</t>
         </is>
       </c>
-      <c r="C543" t="inlineStr">
+      <c r="C542" t="inlineStr">
         <is>
           <t xml:space="preserve">手書き語学 ,アラビア語 ,キバノロ </t>
         </is>
       </c>
     </row>
-    <row r="544">
-      <c r="A544" t="inlineStr">
+    <row r="543">
+      <c r="A543" t="inlineStr">
         <is>
           <t xml:space="preserve">「恐れるな」لا تخف
 ラー・タカフ [laa ta-Khaf]
@@ -11843,19 +11822,19 @@
 2308 KiTeLetZ </t>
         </is>
       </c>
-      <c r="B544" t="inlineStr">
+      <c r="B543" t="inlineStr">
         <is>
           <t>images/「恐れるな」_img1.jpg</t>
         </is>
       </c>
-      <c r="C544" t="inlineStr">
+      <c r="C543" t="inlineStr">
         <is>
           <t>カリグラフィー ,緑</t>
         </is>
       </c>
     </row>
-    <row r="545">
-      <c r="A545" t="inlineStr">
+    <row r="544">
+      <c r="A544" t="inlineStr">
         <is>
           <t xml:space="preserve">「立ち上がれ。遅すぎることはない」
 انهض. لم يفت الأوان بعد
@@ -11865,19 +11844,19 @@
 2308 typo_g </t>
         </is>
       </c>
-      <c r="B545" t="inlineStr">
+      <c r="B544" t="inlineStr">
         <is>
           <t>images/「立ち上がれ。遅すぎることはない」_img1.jpg</t>
         </is>
       </c>
-      <c r="C545" t="inlineStr">
+      <c r="C544" t="inlineStr">
         <is>
           <t>出発</t>
         </is>
       </c>
     </row>
-    <row r="546">
-      <c r="A546" t="inlineStr">
+    <row r="545">
+      <c r="A545" t="inlineStr">
         <is>
           <t xml:space="preserve">「泣かないで」لا تَبْكِ
 ラー・タブキ [laa ta-bki]
@@ -11886,19 +11865,19 @@
 2203 arwa </t>
         </is>
       </c>
-      <c r="B546" t="inlineStr">
+      <c r="B545" t="inlineStr">
         <is>
           <t>images/「泣かないで」_img1.jpg</t>
         </is>
       </c>
-      <c r="C546" t="inlineStr">
+      <c r="C545" t="inlineStr">
         <is>
           <t>傘 ,虹</t>
         </is>
       </c>
     </row>
-    <row r="547">
-      <c r="A547" t="inlineStr">
+    <row r="546">
+      <c r="A546" t="inlineStr">
         <is>
           <t xml:space="preserve">「強くあるしかない」
 لا تكنْ الا قوِيا
@@ -11908,19 +11887,19 @@
 2401 AHMED ELASSAL </t>
         </is>
       </c>
-      <c r="B547" t="inlineStr">
+      <c r="B546" t="inlineStr">
         <is>
           <t>images/「強くあるしかない」_img1.jpg</t>
         </is>
       </c>
-      <c r="C547" t="inlineStr">
+      <c r="C546" t="inlineStr">
         <is>
           <t>二重否定 ,心構え</t>
         </is>
       </c>
     </row>
-    <row r="548">
-      <c r="A548" t="inlineStr">
+    <row r="547">
+      <c r="A547" t="inlineStr">
         <is>
           <t xml:space="preserve">「止まりなさい」قف
 キフ [qif]
@@ -11930,19 +11909,19 @@
 2308 出典不明（英語版：同内容。中国語版：「今日も可愛いね」） </t>
         </is>
       </c>
-      <c r="B548" t="inlineStr">
+      <c r="B547" t="inlineStr">
         <is>
           <t>images/「止まりなさい」_img1.jpg,images/「止まりなさい」_img2.jpg,images/「止まりなさい」_img3.jpg,images/「止まりなさい」_img4.jpg</t>
         </is>
       </c>
-      <c r="C548" t="inlineStr">
+      <c r="C547" t="inlineStr">
         <is>
           <t>かわいい ,職質</t>
         </is>
       </c>
     </row>
-    <row r="549">
-      <c r="A549" t="inlineStr">
+    <row r="548">
+      <c r="A548" t="inlineStr">
         <is>
           <t xml:space="preserve">「自分の人生を生きろ」عش حياتك
 イシ・ハヤータク [*iSh Hayaata-k]
@@ -11951,19 +11930,19 @@
 2607 Pinterest, hus2013asr </t>
         </is>
       </c>
-      <c r="B549" t="inlineStr">
+      <c r="B548" t="inlineStr">
         <is>
           <t>images/「自分の人生を生きろ」_img1.jpg</t>
         </is>
       </c>
-      <c r="C549" t="inlineStr">
+      <c r="C548" t="inlineStr">
         <is>
           <t>iPhone ,壁紙</t>
         </is>
       </c>
     </row>
-    <row r="550">
-      <c r="A550" t="inlineStr">
+    <row r="549">
+      <c r="A549" t="inlineStr">
         <is>
           <t xml:space="preserve">「おやすみザイナ」نامي يا زينة
 ナーミー・ヤー・ザイナ [naam-ii yaa zayna]
@@ -11972,19 +11951,19 @@
 2511 Dar Alsalwa </t>
         </is>
       </c>
-      <c r="B550" t="inlineStr">
+      <c r="B549" t="inlineStr">
         <is>
           <t>images/「おやすみザイナ」_img1.jpg</t>
         </is>
       </c>
-      <c r="C550" t="inlineStr">
+      <c r="C549" t="inlineStr">
         <is>
           <t>絵本 ,ベッド</t>
         </is>
       </c>
     </row>
-    <row r="551">
-      <c r="A551" t="inlineStr">
+    <row r="550">
+      <c r="A550" t="inlineStr">
         <is>
           <t xml:space="preserve">「強くありなさい」كُن قَوياً
 クン・カウィーヤン [kun qawiiyan]
@@ -11993,19 +11972,19 @@
 2109 MJCODEZ </t>
         </is>
       </c>
-      <c r="B551" t="inlineStr">
+      <c r="B550" t="inlineStr">
         <is>
           <t>images/「強くありなさい」_img1.jpg</t>
         </is>
       </c>
-      <c r="C551" t="inlineStr">
+      <c r="C550" t="inlineStr">
         <is>
           <t>名言 ,強い</t>
         </is>
       </c>
     </row>
-    <row r="552">
-      <c r="A552" t="inlineStr">
+    <row r="551">
+      <c r="A551" t="inlineStr">
         <is>
           <t xml:space="preserve">「強くありなさい、自分のために」
 كُن قويًا لأجلك
@@ -12015,19 +11994,19 @@
 1809 gwid3.tumblr </t>
         </is>
       </c>
-      <c r="B552" t="inlineStr">
+      <c r="B551" t="inlineStr">
         <is>
           <t>images/「強くありなさい、自分のために」_img1.jpg</t>
         </is>
       </c>
-      <c r="C552" t="inlineStr">
+      <c r="C551" t="inlineStr">
         <is>
           <t>名言 ,強い</t>
         </is>
       </c>
     </row>
-    <row r="553">
-      <c r="A553" t="inlineStr">
+    <row r="552">
+      <c r="A552" t="inlineStr">
         <is>
           <t xml:space="preserve">「賢くバカであれ」
 كن غبياً بطريقة ذكية
@@ -12037,19 +12016,19 @@
 2110 ALADMIRAL jony </t>
         </is>
       </c>
-      <c r="B553" t="inlineStr">
+      <c r="B552" t="inlineStr">
         <is>
           <t>images/「賢くバカであれ」_img1.jpg</t>
         </is>
       </c>
-      <c r="C553" t="inlineStr">
+      <c r="C552" t="inlineStr">
         <is>
           <t>逆説的 ,キツネ</t>
         </is>
       </c>
     </row>
-    <row r="554">
-      <c r="A554" t="inlineStr">
+    <row r="553">
+      <c r="A553" t="inlineStr">
         <is>
           <t xml:space="preserve">「どこでも自分でありなさい」
 كن أنت أينما كنت
@@ -12059,19 +12038,19 @@
 2605 souqfann com/r/15987  </t>
         </is>
       </c>
-      <c r="B554" t="inlineStr">
+      <c r="B553" t="inlineStr">
         <is>
           <t>images/「どこでも自分でありなさい」_img1.jpg</t>
         </is>
       </c>
-      <c r="C554" t="inlineStr">
+      <c r="C553" t="inlineStr">
         <is>
           <t>デザイン ,アート</t>
         </is>
       </c>
     </row>
-    <row r="555">
-      <c r="A555" t="inlineStr">
+    <row r="554">
+      <c r="A554" t="inlineStr">
         <is>
           <t xml:space="preserve">「止まれ。検問中」قف للتفتيش
 キフ。リッタフティーシ [qif li^taftiiSh]
@@ -12080,19 +12059,19 @@
 2109 Marcel Musil flickr </t>
         </is>
       </c>
-      <c r="B555" t="inlineStr">
+      <c r="B554" t="inlineStr">
         <is>
           <t>images/「止まれ。検問中」_img1.jpg</t>
         </is>
       </c>
-      <c r="C555" t="inlineStr">
+      <c r="C554" t="inlineStr">
         <is>
           <t>標識</t>
         </is>
       </c>
     </row>
-    <row r="556">
-      <c r="A556" t="inlineStr">
+    <row r="555">
+      <c r="A555" t="inlineStr">
         <is>
           <t xml:space="preserve">「さあおやすみ」هَيّا نَمْ
 ハイヤー・ナム [hayyaa nam]
@@ -12100,19 +12079,19 @@
 2308 Maktabatee com </t>
         </is>
       </c>
-      <c r="B556" t="inlineStr">
+      <c r="B555" t="inlineStr">
         <is>
           <t>images/「さあおやすみ」_img1.jpg</t>
         </is>
       </c>
-      <c r="C556" t="inlineStr">
+      <c r="C555" t="inlineStr">
         <is>
           <t>就寝 ,絵本</t>
         </is>
       </c>
     </row>
-    <row r="557">
-      <c r="A557" t="inlineStr">
+    <row r="556">
+      <c r="A556" t="inlineStr">
         <is>
           <t xml:space="preserve">「あなたであれ」كن أنت
 クン・アンタ [ku 'anta]
@@ -12120,19 +12099,19 @@
 1809 madyan22.tumblr </t>
         </is>
       </c>
-      <c r="B557" t="inlineStr">
+      <c r="B556" t="inlineStr">
         <is>
           <t>images/「あなたであれ」_img1.jpg</t>
         </is>
       </c>
-      <c r="C557" t="inlineStr">
+      <c r="C556" t="inlineStr">
         <is>
           <t>個性 ,自尊心</t>
         </is>
       </c>
     </row>
-    <row r="558">
-      <c r="A558" t="inlineStr">
+    <row r="557">
+      <c r="A557" t="inlineStr">
         <is>
           <t xml:space="preserve">「過去を忘れろ。だが教訓は忘れるな」
 إنسَ الماضي ولكن لاتنسَ الدرس
@@ -12142,19 +12121,19 @@
 2308 https://www.instagram.com/emanalyafai </t>
         </is>
       </c>
-      <c r="B558" t="inlineStr">
+      <c r="B557" t="inlineStr">
         <is>
           <t>images/「過去を忘れろ。だが教訓は忘れるな」_img1.jpg</t>
         </is>
       </c>
-      <c r="C558" t="inlineStr">
+      <c r="C557" t="inlineStr">
         <is>
           <t>名言 ,未来</t>
         </is>
       </c>
     </row>
-    <row r="559">
-      <c r="A559" t="inlineStr">
+    <row r="558">
+      <c r="A558" t="inlineStr">
         <is>
           <t xml:space="preserve">「この世界で君も何かを持っている。だから立ち上がれ！」
 لَكْ شيءٌ في هَذَا العَالَم… فَقُمْ
@@ -12162,19 +12141,19 @@
 2511 mjdal7arbi tumblr, Ghassan Kanafani </t>
         </is>
       </c>
-      <c r="B559" t="inlineStr">
+      <c r="B558" t="inlineStr">
         <is>
           <t>images/「この世界で君も何かを持っている。だか.jpg</t>
         </is>
       </c>
-      <c r="C559" t="inlineStr">
+      <c r="C558" t="inlineStr">
         <is>
           <t>鼓舞 ,ハンカチ王子</t>
         </is>
       </c>
     </row>
-    <row r="560">
-      <c r="A560" t="inlineStr">
+    <row r="559">
+      <c r="A559" t="inlineStr">
         <is>
           <t xml:space="preserve">「かぞえてかずをかきましょう」
 عد واكتب العدد
@@ -12183,19 +12162,19 @@
 2604 facebook Qsre alawani </t>
         </is>
       </c>
-      <c r="B560" t="inlineStr">
+      <c r="B559" t="inlineStr">
         <is>
           <t>images/「かぞえてかずをかきましょう」.JPG</t>
         </is>
       </c>
-      <c r="C560" t="inlineStr">
+      <c r="C559" t="inlineStr">
         <is>
           <t>算数 ,さんすう</t>
         </is>
       </c>
     </row>
-    <row r="561">
-      <c r="A561" t="inlineStr">
+    <row r="560">
+      <c r="A560" t="inlineStr">
         <is>
           <t xml:space="preserve">「いつも人助けしなさい」
 كن عونا للناس دوما
@@ -12205,19 +12184,19 @@
 2109 Muhammad ElMahdy </t>
         </is>
       </c>
-      <c r="B561" t="inlineStr">
+      <c r="B560" t="inlineStr">
         <is>
           <t>images/「いつも人助けしなさい」_img1.jpg</t>
         </is>
       </c>
-      <c r="C561" t="inlineStr">
+      <c r="C560" t="inlineStr">
         <is>
           <t>教訓 ,助っ人</t>
         </is>
       </c>
     </row>
-    <row r="562">
-      <c r="A562" t="inlineStr">
+    <row r="561">
+      <c r="A561" t="inlineStr">
         <is>
           <t xml:space="preserve">「毎年、ノーベル賞が授けられる」
 في كل عام تُمنح جوائز نوبل
@@ -12225,19 +12204,19 @@
 2404 https://twitter.com/SciTalk2U/status/1462482447627661319 </t>
         </is>
       </c>
-      <c r="B562" t="inlineStr">
+      <c r="B561" t="inlineStr">
         <is>
           <t>images/「毎年、ノーベル賞が授けられる」_img1.jpg</t>
         </is>
       </c>
-      <c r="C562" t="inlineStr">
+      <c r="C561" t="inlineStr">
         <is>
           <t>手書き語学 ,アラビア語 ,ノーベル賞</t>
         </is>
       </c>
     </row>
-    <row r="563">
-      <c r="A563" t="inlineStr">
+    <row r="562">
+      <c r="A562" t="inlineStr">
         <is>
           <t xml:space="preserve">「あなたはアラビア語を話しますか」
 هل تتكلم العربية؟
@@ -12247,19 +12226,19 @@
 2109 al3arabiya com </t>
         </is>
       </c>
-      <c r="B563" t="inlineStr">
+      <c r="B562" t="inlineStr">
         <is>
           <t>images/「あなたはアラビア語を話しますか」_img1.jpg</t>
         </is>
       </c>
-      <c r="C563" t="inlineStr">
+      <c r="C562" t="inlineStr">
         <is>
           <t>教科書 ,テキスト</t>
         </is>
       </c>
     </row>
-    <row r="564">
-      <c r="A564" t="inlineStr">
+    <row r="563">
+      <c r="A563" t="inlineStr">
         <is>
           <t xml:space="preserve">「このインコは亜熱帯が起源である」
 يتحدر هذا الباراكيت من المناطق شبه الاستوائية
@@ -12267,19 +12246,19 @@
 2402 https://x.com/NatGeoMagArab/status/1690626751578439680 </t>
         </is>
       </c>
-      <c r="B564" t="inlineStr">
+      <c r="B563" t="inlineStr">
         <is>
           <t>images/「このインコは亜熱帯が起源である」_img1.jpg,images/「このインコは亜熱帯が起源である」_img2.jpg</t>
         </is>
       </c>
-      <c r="C564" t="inlineStr">
+      <c r="C563" t="inlineStr">
         <is>
           <t>手書き語学 ,アラビア語 ,オナガミドリインコ</t>
         </is>
       </c>
     </row>
-    <row r="565">
-      <c r="A565" t="inlineStr">
+    <row r="564">
+      <c r="A564" t="inlineStr">
         <is>
           <t xml:space="preserve">「彼を覚えていますか」
 هل تتذكرونه؟
@@ -12289,19 +12268,19 @@
 2308 http://newsfacetruth.blogspot.com/2017/07/blog-post_11.html </t>
         </is>
       </c>
-      <c r="B565" t="inlineStr">
+      <c r="B564" t="inlineStr">
         <is>
           <t>images/「彼を覚えていますか」_img1.jpg</t>
         </is>
       </c>
-      <c r="C565" t="inlineStr">
+      <c r="C564" t="inlineStr">
         <is>
           <t>グレンダイザー ,UFOロボ</t>
         </is>
       </c>
     </row>
-    <row r="566">
-      <c r="A566" t="inlineStr">
+    <row r="565">
+      <c r="A565" t="inlineStr">
         <is>
           <t xml:space="preserve">「内面が変われば周りが変わる」
 عندما تتغير الأشياء داخلك، تتغير الأشياء من حولك
@@ -12310,19 +12289,19 @@
 2501 Facebook, Cairo Mockingbird </t>
         </is>
       </c>
-      <c r="B566" t="inlineStr">
+      <c r="B565" t="inlineStr">
         <is>
           <t>images/「内面が変われば周りが変わる」_img1.jpg</t>
         </is>
       </c>
-      <c r="C566" t="inlineStr">
+      <c r="C565" t="inlineStr">
         <is>
           <t>ポジティブ</t>
         </is>
       </c>
     </row>
-    <row r="567">
-      <c r="A567" t="inlineStr">
+    <row r="566">
+      <c r="A566" t="inlineStr">
         <is>
           <t xml:space="preserve">「天才になるには？」
 كيف تصبح عبقريا؟
@@ -12331,19 +12310,19 @@
 2109 Infographics Samah Faris </t>
         </is>
       </c>
-      <c r="B567" t="inlineStr">
+      <c r="B566" t="inlineStr">
         <is>
           <t>images/「天才になるには？」_img1.jpg</t>
         </is>
       </c>
-      <c r="C567" t="inlineStr">
+      <c r="C566" t="inlineStr">
         <is>
           <t>秘訣 ,コツ</t>
         </is>
       </c>
     </row>
-    <row r="568">
-      <c r="A568" t="inlineStr">
+    <row r="567">
+      <c r="A567" t="inlineStr">
         <is>
           <t xml:space="preserve">「クリエイティブになるには？」
 كيف تصبح مبدعًا؟
@@ -12352,19 +12331,19 @@
 2308 Gwid3 </t>
         </is>
       </c>
-      <c r="B568" t="inlineStr">
+      <c r="B567" t="inlineStr">
         <is>
           <t>images/「クリエイティブになるには？」_img1.jpg</t>
         </is>
       </c>
-      <c r="C568" t="inlineStr">
+      <c r="C567" t="inlineStr">
         <is>
           <t>心得 ,Tips</t>
         </is>
       </c>
     </row>
-    <row r="569">
-      <c r="A569" t="inlineStr">
+    <row r="568">
+      <c r="A568" t="inlineStr">
         <is>
           <t xml:space="preserve">「彼らと友情を交わすよハム太郎」
 وبالإخاء يبادلهم هامتارو
@@ -12374,19 +12353,19 @@
 2109 </t>
         </is>
       </c>
-      <c r="B569" t="inlineStr">
+      <c r="B568" t="inlineStr">
         <is>
           <t>images/「彼らと友情を交わすよハム太郎」_img1.jpg</t>
         </is>
       </c>
-      <c r="C569" t="inlineStr">
+      <c r="C568" t="inlineStr">
         <is>
           <t>アニメ ,ハム太郎</t>
         </is>
       </c>
     </row>
-    <row r="570">
-      <c r="A570" t="inlineStr">
+    <row r="569">
+      <c r="A569" t="inlineStr">
         <is>
           <t xml:space="preserve">「誰がニワトリを助ける？」
 من يساعد الدّجاجة؟
@@ -12396,19 +12375,19 @@
 2109 alnqsh com </t>
         </is>
       </c>
-      <c r="B570" t="inlineStr">
+      <c r="B569" t="inlineStr">
         <is>
           <t>images/「誰がニワトリを助ける？」_img1.jpg</t>
         </is>
       </c>
-      <c r="C570" t="inlineStr">
+      <c r="C569" t="inlineStr">
         <is>
           <t>絵本 ,チキン</t>
         </is>
       </c>
     </row>
-    <row r="571">
-      <c r="A571" t="inlineStr">
+    <row r="570">
+      <c r="A570" t="inlineStr">
         <is>
           <t xml:space="preserve">「心臓病を避けるには？」
 كيف تتجنب أمراض القلب؟
@@ -12418,37 +12397,37 @@
 2608 lanamedical_sa </t>
         </is>
       </c>
+      <c r="B570" t="inlineStr">
+        <is>
+          <t>images/「心臓病を避けるには？」.jpg</t>
+        </is>
+      </c>
+      <c r="C570" t="inlineStr">
+        <is>
+          <t>生活習慣病 ,心臓</t>
+        </is>
+      </c>
+    </row>
+    <row r="571">
+      <c r="A571" t="inlineStr">
+        <is>
+          <t xml:space="preserve">「どうやらこの好奇心旺盛なペンギンは…」
+2308 https://twitter.com/NatGeoMagArab/status/1591460860207443968 </t>
+        </is>
+      </c>
       <c r="B571" t="inlineStr">
         <is>
-          <t>images/「心臓病を避けるには？」.jpg</t>
+          <t>images/「どうやらこの好奇心旺盛なペンギンは…_img1.jpg,images/ 「どうやらこの好奇心旺盛なペンギンは…_img2.jpg</t>
         </is>
       </c>
       <c r="C571" t="inlineStr">
         <is>
-          <t>生活習慣病 ,心臓</t>
+          <t>手書き語学 ,アラビア語 ,オウサマペンギン</t>
         </is>
       </c>
     </row>
     <row r="572">
       <c r="A572" t="inlineStr">
-        <is>
-          <t xml:space="preserve">「どうやらこの好奇心旺盛なペンギンは…」
-2308 https://twitter.com/NatGeoMagArab/status/1591460860207443968 </t>
-        </is>
-      </c>
-      <c r="B572" t="inlineStr">
-        <is>
-          <t>images/「どうやらこの好奇心旺盛なペンギンは…_img1.jpg,images/ 「どうやらこの好奇心旺盛なペンギンは…_img2.jpg</t>
-        </is>
-      </c>
-      <c r="C572" t="inlineStr">
-        <is>
-          <t>手書き語学 ,アラビア語 ,オウサマペンギン</t>
-        </is>
-      </c>
-    </row>
-    <row r="573">
-      <c r="A573" t="inlineStr">
         <is>
           <t xml:space="preserve">「この生き物を見分けられますか？」
 هل تُميز هذا الكائن؟
@@ -12457,19 +12436,19 @@
 2308 https://twitter.com/NatGeoMagArab/status/1455121397827600388 </t>
         </is>
       </c>
-      <c r="B573" t="inlineStr">
+      <c r="B572" t="inlineStr">
         <is>
           <t>images/「この生き物を見分けられますか？」_img1.jpg</t>
         </is>
       </c>
-      <c r="C573" t="inlineStr">
+      <c r="C572" t="inlineStr">
         <is>
           <t xml:space="preserve">手書き語学 ,カバ </t>
         </is>
       </c>
     </row>
-    <row r="574">
-      <c r="A574" t="inlineStr">
+    <row r="573">
+      <c r="A573" t="inlineStr">
         <is>
           <t xml:space="preserve">「ひとを幸せにするには？」
 كيف تسعد غيرك؟
@@ -12479,19 +12458,19 @@
 2308 Gwid3 </t>
         </is>
       </c>
-      <c r="B574" t="inlineStr">
+      <c r="B573" t="inlineStr">
         <is>
           <t>images/「ひとを幸せにするには？」_img1.jpg</t>
         </is>
       </c>
-      <c r="C574" t="inlineStr">
+      <c r="C573" t="inlineStr">
         <is>
           <t>思いやり ,心</t>
         </is>
       </c>
     </row>
-    <row r="575">
-      <c r="A575" t="inlineStr">
+    <row r="574">
+      <c r="A574" t="inlineStr">
         <is>
           <t xml:space="preserve">「ラマダン月に口臭をおさえる方法は？」
 كيف تتجنب رائحة الفم في رمضان
@@ -12500,19 +12479,19 @@
 2109 AlArabiya </t>
         </is>
       </c>
-      <c r="B575" t="inlineStr">
+      <c r="B574" t="inlineStr">
         <is>
           <t>images/「ラマダン月に口臭をおさえる方法は？」_img1.jpg</t>
         </is>
       </c>
-      <c r="C575" t="inlineStr">
+      <c r="C574" t="inlineStr">
         <is>
           <t>イスラム教 ,ブレスケア</t>
         </is>
       </c>
     </row>
-    <row r="576">
-      <c r="A576" t="inlineStr">
+    <row r="575">
+      <c r="A575" t="inlineStr">
         <is>
           <t xml:space="preserve">「ヨユウなきユウヨ」
 يمهل ولا يهمل
@@ -12522,19 +12501,19 @@
 2512 instagram com/p/CK4CLqeJ3dy/ </t>
         </is>
       </c>
-      <c r="B576" t="inlineStr">
+      <c r="B575" t="inlineStr">
         <is>
           <t>images/「ヨユウなきユウヨ」_img1.jpg</t>
         </is>
       </c>
-      <c r="C576" t="inlineStr">
+      <c r="C575" t="inlineStr">
         <is>
           <t>時計 ,からくり</t>
         </is>
       </c>
     </row>
-    <row r="577">
-      <c r="A577" t="inlineStr">
+    <row r="576">
+      <c r="A576" t="inlineStr">
         <is>
           <t xml:space="preserve">「どうして？　動物は絶滅する」
 لماذا؟ تنقرض الحيوانات
@@ -12544,19 +12523,19 @@
 2308 goodreads com </t>
         </is>
       </c>
-      <c r="B577" t="inlineStr">
+      <c r="B576" t="inlineStr">
         <is>
           <t>images/「どうして？　動物は絶滅する」_img1.jpg</t>
         </is>
       </c>
-      <c r="C577" t="inlineStr">
+      <c r="C576" t="inlineStr">
         <is>
           <t>動物 ,子供用</t>
         </is>
       </c>
     </row>
-    <row r="578">
-      <c r="A578" t="inlineStr">
+    <row r="577">
+      <c r="A577" t="inlineStr">
         <is>
           <t xml:space="preserve">「私たちは異なる。だから調和する」
 نختلف.. لنأتلف
@@ -12566,19 +12545,19 @@
 2103 Nawal Saed </t>
         </is>
       </c>
-      <c r="B578" t="inlineStr">
+      <c r="B577" t="inlineStr">
         <is>
           <t>images/「私たちは異なる。だから調和する」_img1.jpg</t>
         </is>
       </c>
-      <c r="C578" t="inlineStr">
+      <c r="C577" t="inlineStr">
         <is>
           <t>異符号 ,ハーモニー</t>
         </is>
       </c>
     </row>
-    <row r="579">
-      <c r="A579" t="inlineStr">
+    <row r="578">
+      <c r="A578" t="inlineStr">
         <is>
           <t xml:space="preserve">「私の肺には蝶々が住んでいて、呼吸の度に羽ばたく」
 تسكن رئتيّ فراشة ترفرف كلما أتنفس
@@ -12587,19 +12566,19 @@
 2109 出典不明 </t>
         </is>
       </c>
-      <c r="B579" t="inlineStr">
+      <c r="B578" t="inlineStr">
         <is>
           <t>images/「私の肺には蝶々が住んでいて、呼吸の度_img1.jpg</t>
         </is>
       </c>
-      <c r="C579" t="inlineStr">
+      <c r="C578" t="inlineStr">
         <is>
           <t>人体 ,昆虫</t>
         </is>
       </c>
     </row>
-    <row r="580">
-      <c r="A580" t="inlineStr">
+    <row r="579">
+      <c r="A579" t="inlineStr">
         <is>
           <t xml:space="preserve">「安らぎを感じますか？」
 هل تستشعر السكينة؟
@@ -12608,19 +12587,19 @@
 2404 https://twitter.com/NatGeoMagArab/status/1541421154950209536 </t>
         </is>
       </c>
-      <c r="B580" t="inlineStr">
+      <c r="B579" t="inlineStr">
         <is>
           <t>images/「安らぎを感じますか？」_img1.jpg</t>
         </is>
       </c>
-      <c r="C580" t="inlineStr">
+      <c r="C579" t="inlineStr">
         <is>
           <t>手書き語学 ,アラビア語 ,エイ</t>
         </is>
       </c>
     </row>
-    <row r="581">
-      <c r="A581" t="inlineStr">
+    <row r="580">
+      <c r="A580" t="inlineStr">
         <is>
           <t xml:space="preserve">「たとえあなたの使うブラウザがChromeだろうとSafariだろうと」
 سواء كنت تستخدم متصفح كروم أو سفاري
@@ -12628,19 +12607,19 @@
 2308 https://twitter.com/ShaayTech/status/1536235333972635649 </t>
         </is>
       </c>
-      <c r="B581" t="inlineStr">
+      <c r="B580" t="inlineStr">
         <is>
           <t>images/「たとえあなたの使うブラウザがChro_img1.jpg</t>
         </is>
       </c>
-      <c r="C581" t="inlineStr">
+      <c r="C580" t="inlineStr">
         <is>
           <t xml:space="preserve">手書き語学 ,アラビア語 ,iPhone </t>
         </is>
       </c>
     </row>
-    <row r="582">
-      <c r="A582" t="inlineStr">
+    <row r="581">
+      <c r="A581" t="inlineStr">
         <is>
           <t xml:space="preserve">「このミドリモリヤツガシラは気づいて欲しい」
 يحرص "هدهد الخشب الأخضر" هذا على أن يدرك
@@ -12649,19 +12628,19 @@
 2308 https://twitter.com/NatGeoMagArab/status/1531161022928539648 </t>
         </is>
       </c>
-      <c r="B582" t="inlineStr">
+      <c r="B581" t="inlineStr">
         <is>
           <t>images/「このミドリモリヤツガシラは気づいて欲_img1.jpg</t>
         </is>
       </c>
-      <c r="C582" t="inlineStr">
+      <c r="C581" t="inlineStr">
         <is>
           <t xml:space="preserve">手書き語学 ,アラビア語 ,鳥 </t>
         </is>
       </c>
     </row>
-    <row r="583">
-      <c r="A583" t="inlineStr">
+    <row r="582">
+      <c r="A582" t="inlineStr">
         <is>
           <t xml:space="preserve">「あなたの怖いものは何ですか」
 ماهي مخاوفك؟
@@ -12673,15 +12652,15 @@
 2308 1112kok </t>
         </is>
       </c>
-      <c r="B583" t="inlineStr">
+      <c r="B582" t="inlineStr">
         <is>
           <t>images/「あなたの怖いものは何ですか」_img1.jpg</t>
         </is>
       </c>
-      <c r="C583" t="inlineStr"/>
-    </row>
-    <row r="584">
-      <c r="A584" t="inlineStr">
+      <c r="C582" t="inlineStr"/>
+    </row>
+    <row r="583">
+      <c r="A583" t="inlineStr">
         <is>
           <t xml:space="preserve">「美しい時は作るもの。待つものではない」
 اصنع اللحظات الجميلة. لا تنتظرها
@@ -12690,19 +12669,19 @@
 2308 abojamal.tumblr com </t>
         </is>
       </c>
-      <c r="B584" t="inlineStr">
+      <c r="B583" t="inlineStr">
         <is>
           <t>images/「美しい時は作るもの。待つものではない_img1.jpg</t>
         </is>
       </c>
-      <c r="C584" t="inlineStr">
+      <c r="C583" t="inlineStr">
         <is>
           <t>おうち時間</t>
         </is>
       </c>
     </row>
-    <row r="585">
-      <c r="A585" t="inlineStr">
+    <row r="584">
+      <c r="A584" t="inlineStr">
         <is>
           <t xml:space="preserve">「大切な時間を大切じゃないことに使わないこと」
 لا تضيع الوقت المهم في شيء غير مهم
@@ -12711,19 +12690,19 @@
 2308 Anwar_122_ </t>
         </is>
       </c>
-      <c r="B585" t="inlineStr">
+      <c r="B584" t="inlineStr">
         <is>
           <t>images/「大切な時間を大切じゃないことに使わな_img1.jpg</t>
         </is>
       </c>
-      <c r="C585" t="inlineStr">
+      <c r="C584" t="inlineStr">
         <is>
           <t>時間 ,貴重</t>
         </is>
       </c>
     </row>
-    <row r="586">
-      <c r="A586" t="inlineStr">
+    <row r="585">
+      <c r="A585" t="inlineStr">
         <is>
           <t xml:space="preserve">「このイノセントな目に騙されるな…」
 لا تنخدع بهذه العيون البريئة
@@ -12733,19 +12712,19 @@
 2201 https://twitter.com/NatGeoMagArab/status/1475715760202797056 </t>
         </is>
       </c>
-      <c r="B586" t="inlineStr">
+      <c r="B585" t="inlineStr">
         <is>
           <t>images/「このイノセントな目に騙されるな…」.png</t>
         </is>
       </c>
-      <c r="C586" t="inlineStr">
+      <c r="C585" t="inlineStr">
         <is>
           <t>がうがう ,カワイイ</t>
         </is>
       </c>
     </row>
-    <row r="587">
-      <c r="A587" t="inlineStr">
+    <row r="586">
+      <c r="A586" t="inlineStr">
         <is>
           <t xml:space="preserve">⁦「カメラを止めろ！」⁩
 أوقفوا التّصوير
@@ -12755,19 +12734,19 @@
 2509 alsalwabooks com </t>
         </is>
       </c>
-      <c r="B587" t="inlineStr">
+      <c r="B586" t="inlineStr">
         <is>
           <t>images/⁦「カメラを止めろ！」⁩_img1.jpg</t>
         </is>
       </c>
-      <c r="C587" t="inlineStr">
+      <c r="C586" t="inlineStr">
         <is>
           <t>絵本 ,撮影</t>
         </is>
       </c>
     </row>
-    <row r="588">
-      <c r="A588" t="inlineStr">
+    <row r="587">
+      <c r="A587" t="inlineStr">
         <is>
           <t xml:space="preserve">「話す前に考えなさい」
 فكر قبل ان تتكلم
@@ -12777,19 +12756,19 @@
 2308 Islamuna YouTube </t>
         </is>
       </c>
-      <c r="B588" t="inlineStr">
+      <c r="B587" t="inlineStr">
         <is>
           <t>images/「話す前に考えなさい」_img1.jpg</t>
         </is>
       </c>
-      <c r="C588" t="inlineStr">
+      <c r="C587" t="inlineStr">
         <is>
           <t>失言 ,発言</t>
         </is>
       </c>
     </row>
-    <row r="589">
-      <c r="A589" t="inlineStr">
+    <row r="588">
+      <c r="A588" t="inlineStr">
         <is>
           <t xml:space="preserve">「ツイッターでフォローして下さい」
 تابعونا على تويتر
@@ -12799,19 +12778,19 @@
 2109 出典不明 </t>
         </is>
       </c>
-      <c r="B589" t="inlineStr">
+      <c r="B588" t="inlineStr">
         <is>
           <t>images/「ツイッターでフォローして下さい」_img1.jpg</t>
         </is>
       </c>
-      <c r="C589" t="inlineStr">
+      <c r="C588" t="inlineStr">
         <is>
           <t>FollowUs ,バナー</t>
         </is>
       </c>
     </row>
-    <row r="590">
-      <c r="A590" t="inlineStr">
+    <row r="589">
+      <c r="A589" t="inlineStr">
         <is>
           <t xml:space="preserve">「敵を倒せ」دمّر العدو
 ダンミリ_ルアドゥーウ [dammiri l-*aduuw]
@@ -12820,19 +12799,19 @@
 2308 apkpure com </t>
         </is>
       </c>
-      <c r="B590" t="inlineStr">
+      <c r="B589" t="inlineStr">
         <is>
           <t>images/「敵を倒せ」_img1.jpg</t>
         </is>
       </c>
-      <c r="C590" t="inlineStr">
+      <c r="C589" t="inlineStr">
         <is>
           <t>ゲーム ,パンダ</t>
         </is>
       </c>
     </row>
-    <row r="591">
-      <c r="A591" t="inlineStr">
+    <row r="590">
+      <c r="A590" t="inlineStr">
         <is>
           <t xml:space="preserve">「咲け。蒔かれたらどこであろうと」
 أزهر أيْنمَا زرعت
@@ -12841,19 +12820,19 @@
 2407 Ahmed Madyan </t>
         </is>
       </c>
-      <c r="B591" t="inlineStr">
+      <c r="B590" t="inlineStr">
         <is>
           <t>images/「咲け。蒔かれたらどこであろうと」_img1.jpg</t>
         </is>
       </c>
-      <c r="C591" t="inlineStr">
+      <c r="C590" t="inlineStr">
         <is>
           <t>環境のせいにしない ,花</t>
         </is>
       </c>
     </row>
-    <row r="592">
-      <c r="A592" t="inlineStr">
+    <row r="591">
+      <c r="A591" t="inlineStr">
         <is>
           <t xml:space="preserve">「頭を働かせろ」شغل مخك
 シャッギル・ムッハク [Sha^Ghil mu^Kha-k]
@@ -12862,19 +12841,19 @@
 2103 facebook elpage </t>
         </is>
       </c>
-      <c r="B592" t="inlineStr">
+      <c r="B591" t="inlineStr">
         <is>
           <t>images/「頭を働かせろ」_img1.jpg</t>
         </is>
       </c>
-      <c r="C592" t="inlineStr">
+      <c r="C591" t="inlineStr">
         <is>
           <t>電源 ,頭脳</t>
         </is>
       </c>
     </row>
-    <row r="593">
-      <c r="A593" t="inlineStr">
+    <row r="592">
+      <c r="A592" t="inlineStr">
         <is>
           <t xml:space="preserve">「傷跡は星にかえなさい」
 حوّل نُدوبكَ إلى نُجومْ
@@ -12884,19 +12863,19 @@
 2107 saramj1992 Instagram </t>
         </is>
       </c>
-      <c r="B593" t="inlineStr">
+      <c r="B592" t="inlineStr">
         <is>
           <t>images/「傷跡は星にかえなさい」_img1.jpg</t>
         </is>
       </c>
-      <c r="C593" t="inlineStr">
+      <c r="C592" t="inlineStr">
         <is>
           <t>勲章 ,証</t>
         </is>
       </c>
     </row>
-    <row r="594">
-      <c r="A594" t="inlineStr">
+    <row r="593">
+      <c r="A593" t="inlineStr">
         <is>
           <t xml:space="preserve">「あなたの主の栄光を誉め称え、また（御赦しを請え。本当にかれは、度々赦される御方である）」
 فسَبِّح بحمد ربك و
@@ -12905,19 +12884,19 @@
 2109 出典不明 </t>
         </is>
       </c>
-      <c r="B594" t="inlineStr">
+      <c r="B593" t="inlineStr">
         <is>
           <t>images/「あなたの主の栄光を誉め称え、また（御_img1.jpg</t>
         </is>
       </c>
-      <c r="C594" t="inlineStr">
+      <c r="C593" t="inlineStr">
         <is>
           <t>イスラム教 ,カリグラフィー</t>
         </is>
       </c>
     </row>
-    <row r="595">
-      <c r="A595" t="inlineStr">
+    <row r="594">
+      <c r="A594" t="inlineStr">
         <is>
           <t xml:space="preserve">「誰かを幸福にしなさい」
 أسْعِد أحدهم
@@ -12927,19 +12906,19 @@
 1810 in4sser.tumblr </t>
         </is>
       </c>
-      <c r="B595" t="inlineStr">
+      <c r="B594" t="inlineStr">
         <is>
           <t>images/「誰かを幸福にしなさい」_img1.jpg</t>
         </is>
       </c>
-      <c r="C595" t="inlineStr">
+      <c r="C594" t="inlineStr">
         <is>
           <t>人生 ,happy</t>
         </is>
       </c>
     </row>
-    <row r="596">
-      <c r="A596" t="inlineStr">
+    <row r="595">
+      <c r="A595" t="inlineStr">
         <is>
           <t xml:space="preserve">「見よ」أبْصِرْ
 アブスィル ['ab_sir]
@@ -12948,19 +12927,19 @@
 1811 Ruh Al-Alam, via Behance </t>
         </is>
       </c>
-      <c r="B596" t="inlineStr">
+      <c r="B595" t="inlineStr">
         <is>
           <t>images/「見よ」_img1.jpg</t>
         </is>
       </c>
-      <c r="C596" t="inlineStr">
+      <c r="C595" t="inlineStr">
         <is>
           <t>目 ,瞳</t>
         </is>
       </c>
     </row>
-    <row r="597">
-      <c r="A597" t="inlineStr">
+    <row r="596">
+      <c r="A596" t="inlineStr">
         <is>
           <t xml:space="preserve">「言葉は口から出す前に味わいなさい」
 ‪تذوق كلماتك قبل أن تنطقها‬
@@ -12970,19 +12949,19 @@
 2109 Reham-des </t>
         </is>
       </c>
-      <c r="B597" t="inlineStr">
+      <c r="B596" t="inlineStr">
         <is>
           <t>images/「言葉は口から出す前に味わいなさい」_img1.jpg</t>
         </is>
       </c>
-      <c r="C597" t="inlineStr">
+      <c r="C596" t="inlineStr">
         <is>
           <t>言葉</t>
         </is>
       </c>
     </row>
-    <row r="598">
-      <c r="A598" t="inlineStr">
+    <row r="597">
+      <c r="A597" t="inlineStr">
         <is>
           <t xml:space="preserve">「テレビを観るのをやめて下さい」
 توقفي عن مشاهدة التلفاز
@@ -12992,19 +12971,19 @@
 1809 </t>
         </is>
       </c>
-      <c r="B598" t="inlineStr">
+      <c r="B597" t="inlineStr">
         <is>
           <t>images/「テレビを観るのをやめて下さい」_img1.jpg</t>
         </is>
       </c>
-      <c r="C598" t="inlineStr">
+      <c r="C597" t="inlineStr">
         <is>
           <t>あらびあや</t>
         </is>
       </c>
     </row>
-    <row r="599">
-      <c r="A599" t="inlineStr">
+    <row r="598">
+      <c r="A598" t="inlineStr">
         <is>
           <t xml:space="preserve">「言わぬが花」
 انْطِقْ جَمَالاً أو تجَمَّلْ بالسّكُوت
@@ -13014,19 +12993,19 @@
 2411 Ahmed Madyan </t>
         </is>
       </c>
-      <c r="B599" t="inlineStr">
+      <c r="B598" t="inlineStr">
         <is>
           <t>images/「言わぬが花」_img1.jpg</t>
         </is>
       </c>
-      <c r="C599" t="inlineStr">
+      <c r="C598" t="inlineStr">
         <is>
           <t>ことわざ ,デザイン</t>
         </is>
       </c>
     </row>
-    <row r="600">
-      <c r="A600" t="inlineStr">
+    <row r="599">
+      <c r="A599" t="inlineStr">
         <is>
           <t xml:space="preserve">「たくさん考えて、少し話すこと」
 فكّر كثيرا. تكلم قليلا
@@ -13036,19 +13015,19 @@
 2105 In49r </t>
         </is>
       </c>
-      <c r="B600" t="inlineStr">
+      <c r="B599" t="inlineStr">
         <is>
           <t>images/「たくさん考えて、少し話すこと」_img1.jpg</t>
         </is>
       </c>
-      <c r="C600" t="inlineStr">
+      <c r="C599" t="inlineStr">
         <is>
           <t>思慮 ,会話</t>
         </is>
       </c>
     </row>
-    <row r="601">
-      <c r="A601" t="inlineStr">
+    <row r="600">
+      <c r="A600" t="inlineStr">
         <is>
           <t xml:space="preserve">「子供たちよ、いつでも思い出すんだよ」
 تذكروا دوما يا أطفال
@@ -13058,19 +13037,19 @@
 1809 </t>
         </is>
       </c>
-      <c r="B601" t="inlineStr">
+      <c r="B600" t="inlineStr">
         <is>
           <t>images/「子供たちよ、いつでも思い出すんだよ」_img1.jpg</t>
         </is>
       </c>
-      <c r="C601" t="inlineStr">
+      <c r="C600" t="inlineStr">
         <is>
           <t>オープニング ,ハム太郎</t>
         </is>
       </c>
     </row>
-    <row r="602">
-      <c r="A602" t="inlineStr">
+    <row r="601">
+      <c r="A601" t="inlineStr">
         <is>
           <t xml:space="preserve">「分かってから話しなさい」
 تعلَّم ثمَّ تكلَّم
@@ -13080,19 +13059,19 @@
 1903 Hashem Al Shareef, Pinterest </t>
         </is>
       </c>
-      <c r="B602" t="inlineStr">
+      <c r="B601" t="inlineStr">
         <is>
           <t>images/「分かってから話しなさい」_img1.jpg</t>
         </is>
       </c>
-      <c r="C602" t="inlineStr">
+      <c r="C601" t="inlineStr">
         <is>
           <t>教訓 ,トーク</t>
         </is>
       </c>
     </row>
-    <row r="603">
-      <c r="A603" t="inlineStr">
+    <row r="602">
+      <c r="A602" t="inlineStr">
         <is>
           <t xml:space="preserve">「蟻に学べ」تعلم من النملة
 タアッラム・ミナ_ンナムラ [ta*allam mina ^namla]
@@ -13101,19 +13080,19 @@
 2308 fatakat com </t>
         </is>
       </c>
-      <c r="B603" t="inlineStr">
+      <c r="B602" t="inlineStr">
         <is>
           <t>images/「蟻に学べ」_img1.jpg</t>
         </is>
       </c>
-      <c r="C603" t="inlineStr">
+      <c r="C602" t="inlineStr">
         <is>
           <t>教訓 ,問題解決</t>
         </is>
       </c>
     </row>
-    <row r="604">
-      <c r="A604" t="inlineStr">
+    <row r="603">
+      <c r="A603" t="inlineStr">
         <is>
           <t xml:space="preserve">「自分と仲直りしよう、一杯の珈琲で！」
 تصالح مع نفسك بكوب قهوة
@@ -13123,19 +13102,19 @@
 2308 asm95_ </t>
         </is>
       </c>
-      <c r="B604" t="inlineStr">
+      <c r="B603" t="inlineStr">
         <is>
           <t>images/「自分と仲直りしよう、一杯の珈琲で！」_img1.jpg</t>
         </is>
       </c>
-      <c r="C604" t="inlineStr">
+      <c r="C603" t="inlineStr">
         <is>
           <t>一服 ,リラックス</t>
         </is>
       </c>
     </row>
-    <row r="605">
-      <c r="A605" t="inlineStr">
+    <row r="604">
+      <c r="A604" t="inlineStr">
         <is>
           <t xml:space="preserve">「気をつけて　ジュード」
 انتبهي يا جود
@@ -13145,19 +13124,19 @@
 2109 سلسلة الحلزونة </t>
         </is>
       </c>
-      <c r="B605" t="inlineStr">
+      <c r="B604" t="inlineStr">
         <is>
           <t>images/「気をつけて　ジュード」_img1.jpg</t>
         </is>
       </c>
-      <c r="C605" t="inlineStr">
+      <c r="C604" t="inlineStr">
         <is>
           <t>絵本 ,わんぱく</t>
         </is>
       </c>
     </row>
-    <row r="606">
-      <c r="A606" t="inlineStr">
+    <row r="605">
+      <c r="A605" t="inlineStr">
         <is>
           <t xml:space="preserve">「coming soon」
 انتظرونا قريبا
@@ -13166,19 +13145,19 @@
 2307 出典不明 </t>
         </is>
       </c>
-      <c r="B606" t="inlineStr">
+      <c r="B605" t="inlineStr">
         <is>
           <t>images/「coming soon」_img1.jpg</t>
         </is>
       </c>
-      <c r="C606" t="inlineStr">
+      <c r="C605" t="inlineStr">
         <is>
           <t>フレーズ ,カミングスーン</t>
         </is>
       </c>
     </row>
-    <row r="607">
-      <c r="A607" t="inlineStr">
+    <row r="606">
+      <c r="A606" t="inlineStr">
         <is>
           <t xml:space="preserve">「自分の胸に聞きなさい。それが全て知っています」
 استمع لقلبك.. إنه يعرف كل شيء
@@ -13187,19 +13166,19 @@
 1811 </t>
         </is>
       </c>
-      <c r="B607" t="inlineStr">
+      <c r="B606" t="inlineStr">
         <is>
           <t>images/「自分の胸に聞きなさい。それが全て知っ_img1.jpg</t>
         </is>
       </c>
-      <c r="C607" t="inlineStr">
+      <c r="C606" t="inlineStr">
         <is>
           <t>あらびあや</t>
         </is>
       </c>
     </row>
-    <row r="608">
-      <c r="A608" t="inlineStr">
+    <row r="607">
+      <c r="A607" t="inlineStr">
         <is>
           <t xml:space="preserve">「笑ってくれ、絶望を癒すのは君の笑みだから」
 ابتسمي فإن دواء اليأس بسمتك
@@ -13208,19 +13187,19 @@
 2308 arab-quotes tumblr </t>
         </is>
       </c>
-      <c r="B608" t="inlineStr">
+      <c r="B607" t="inlineStr">
         <is>
           <t>images/「笑ってくれ、絶望を癒すのは君の笑みだ_img1.jpg</t>
         </is>
       </c>
-      <c r="C608" t="inlineStr">
+      <c r="C607" t="inlineStr">
         <is>
           <t>癒し ,スマイル</t>
         </is>
       </c>
     </row>
-    <row r="609">
-      <c r="A609" t="inlineStr">
+    <row r="608">
+      <c r="A608" t="inlineStr">
         <is>
           <t xml:space="preserve">「自分を頼りなさい。宇宙で最も確かな物が自分だと思って。」
 استند على نفسك وكأنك أكثر الأشياء ثباتًا بهذا الكون
@@ -13228,19 +13207,19 @@
 2308 x_nourh.15 </t>
         </is>
       </c>
-      <c r="B609" t="inlineStr">
+      <c r="B608" t="inlineStr">
         <is>
           <t>images/「自分を頼りなさい。宇宙で最も確かな物_img1.jpg</t>
         </is>
       </c>
-      <c r="C609" t="inlineStr">
+      <c r="C608" t="inlineStr">
         <is>
           <t>自我 ,宇宙</t>
         </is>
       </c>
     </row>
-    <row r="610">
-      <c r="A610" t="inlineStr">
+    <row r="609">
+      <c r="A609" t="inlineStr">
         <is>
           <t xml:space="preserve">「古いデバイスを交換して新品をゲットしよう」
 استبدل جهازك القديم واحصل على واحد جديد
@@ -13249,19 +13228,19 @@
 2406 stc </t>
         </is>
       </c>
-      <c r="B610" t="inlineStr">
+      <c r="B609" t="inlineStr">
         <is>
           <t>images/「古いデバイスを交換して新品をゲットし_img1.jpg</t>
         </is>
       </c>
-      <c r="C610" t="inlineStr">
+      <c r="C609" t="inlineStr">
         <is>
           <t>キャンペーン ,下取り</t>
         </is>
       </c>
     </row>
-    <row r="611">
-      <c r="A611" t="inlineStr">
+    <row r="610">
+      <c r="A610" t="inlineStr">
         <is>
           <t xml:space="preserve">「あなたの声を聞かせてください。私の心を彩ってください」
 هات صوتك، لوّن قلبي
@@ -13270,19 +13249,19 @@
 2105 3a2esha_ Instagram </t>
         </is>
       </c>
-      <c r="B611" t="inlineStr">
+      <c r="B610" t="inlineStr">
         <is>
           <t>images/「あなたの声を聞かせてください。私の心_img1.jpg</t>
         </is>
       </c>
-      <c r="C611" t="inlineStr">
+      <c r="C610" t="inlineStr">
         <is>
           <t>電話 ,肉声</t>
         </is>
       </c>
     </row>
-    <row r="612">
-      <c r="A612" t="inlineStr">
+    <row r="611">
+      <c r="A611" t="inlineStr">
         <is>
           <t xml:space="preserve">「この子カンガルーは抱っこが好き」
 يُحب صغير الكنغر هذا أن يؤخذ في الأحضان
@@ -13290,19 +13269,19 @@
 2308 NatGeoMagArab </t>
         </is>
       </c>
-      <c r="B612" t="inlineStr">
+      <c r="B611" t="inlineStr">
         <is>
           <t>images/「この子カンガルーは抱っこが好き」.png</t>
         </is>
       </c>
-      <c r="C612" t="inlineStr">
+      <c r="C611" t="inlineStr">
         <is>
           <t>カンガルー ,人肌</t>
         </is>
       </c>
     </row>
-    <row r="613">
-      <c r="A613" t="inlineStr">
+    <row r="612">
+      <c r="A612" t="inlineStr">
         <is>
           <t xml:space="preserve">「カタールが好き」أحب قطر
 ウヒッブ・カタル ['u-Hibb qa_tar]
@@ -13311,19 +13290,19 @@
 1810 出典不明 </t>
         </is>
       </c>
-      <c r="B613" t="inlineStr">
+      <c r="B612" t="inlineStr">
         <is>
           <t>images/「カタールが好き」_img1.jpg</t>
         </is>
       </c>
-      <c r="C613" t="inlineStr">
+      <c r="C612" t="inlineStr">
         <is>
           <t>カタール</t>
         </is>
       </c>
     </row>
-    <row r="614">
-      <c r="A614" t="inlineStr">
+    <row r="613">
+      <c r="A613" t="inlineStr">
         <is>
           <t xml:space="preserve">「一緒に読むのが好き」
 أُحبُّ أن نَقْرَأَ مَعاً
@@ -13333,19 +13312,19 @@
 2509 www.neelwafurat com,  id=lbb212750-185765 </t>
         </is>
       </c>
-      <c r="B614" t="inlineStr">
+      <c r="B613" t="inlineStr">
         <is>
           <t>images/「一緒に読むのが好き」_img1.jpg</t>
         </is>
       </c>
-      <c r="C614" t="inlineStr">
+      <c r="C613" t="inlineStr">
         <is>
           <t>好き ,本</t>
         </is>
       </c>
     </row>
-    <row r="615">
-      <c r="A615" t="inlineStr">
+    <row r="614">
+      <c r="A614" t="inlineStr">
         <is>
           <t xml:space="preserve">「病院に行きたくない」
 لا أريد أن أذهب إلى المشفى
@@ -13355,19 +13334,19 @@
 2508 Tony Ross https://education.hachette-antoine.com/ar/component/%D9%84%D8%A7-%D8%A3%D8%B1%D9%8A%D8%AF-%D8%A3%D9%86-%D8%A3%D8%B0%D9%87%D8%A8-%D8%A5%D9%84%D9%89-%D8%A7%D9%84%D9%85%D8%B4%D9%81%D9%89/ </t>
         </is>
       </c>
-      <c r="B615" t="inlineStr">
+      <c r="B614" t="inlineStr">
         <is>
           <t>images/「病院に行きたくない」_img1.jpg</t>
         </is>
       </c>
-      <c r="C615" t="inlineStr">
+      <c r="C614" t="inlineStr">
         <is>
           <t>絵本 ,子供</t>
         </is>
       </c>
     </row>
-    <row r="616">
-      <c r="A616" t="inlineStr">
+    <row r="615">
+      <c r="A615" t="inlineStr">
         <is>
           <t xml:space="preserve">「男性はいくら？」「女性はいくら？」
 كم يساوى الرجل؟ ..وكم تساوى المرأة؟
@@ -13376,19 +13355,19 @@
 2308 Pinterest, Masr Elmahrousa, Farah Noweir </t>
         </is>
       </c>
-      <c r="B616" t="inlineStr">
+      <c r="B615" t="inlineStr">
         <is>
           <t>images/「男性はいくら？」「女性はいくら？」_img1.jpg,images/「男性はいくら？」「女性はいくら？」_img2.jpg</t>
         </is>
       </c>
-      <c r="C616" t="inlineStr">
+      <c r="C615" t="inlineStr">
         <is>
           <t xml:space="preserve">全身コーデ ,相場 </t>
         </is>
       </c>
     </row>
-    <row r="617">
-      <c r="A617" t="inlineStr">
+    <row r="616">
+      <c r="A616" t="inlineStr">
         <is>
           <t xml:space="preserve">「黙ってもらえます？」
 ممكن تعيرنا سكوتك؟
@@ -13398,19 +13377,19 @@
 2308 Basel26 </t>
         </is>
       </c>
-      <c r="B617" t="inlineStr">
+      <c r="B616" t="inlineStr">
         <is>
           <t>images/「黙ってもらえます？」_img1.jpg</t>
         </is>
       </c>
-      <c r="C617" t="inlineStr">
+      <c r="C616" t="inlineStr">
         <is>
           <t>音量 ,ボリューム</t>
         </is>
       </c>
     </row>
-    <row r="618">
-      <c r="A618" t="inlineStr">
+    <row r="617">
+      <c r="A617" t="inlineStr">
         <is>
           <t xml:space="preserve">「眠りたいです」
 أُريدُ أَن أَنام
@@ -13420,19 +13399,19 @@
 2109 goodreads com </t>
         </is>
       </c>
-      <c r="B618" t="inlineStr">
+      <c r="B617" t="inlineStr">
         <is>
           <t>images/「眠りたいです」_img1.jpg</t>
         </is>
       </c>
-      <c r="C618" t="inlineStr">
+      <c r="C617" t="inlineStr">
         <is>
           <t>絵本</t>
         </is>
       </c>
     </row>
-    <row r="619">
-      <c r="A619" t="inlineStr">
+    <row r="618">
+      <c r="A618" t="inlineStr">
         <is>
           <t xml:space="preserve">「飛びたい！」أُريد أن أطير
 ウリードゥ・アン・アティール ['u-riidu 'an 'a-_tiir]
@@ -13441,19 +13420,19 @@
 2308 出典不明 </t>
         </is>
       </c>
-      <c r="B619" t="inlineStr">
+      <c r="B618" t="inlineStr">
         <is>
           <t>images/「飛びたい！」_img1.jpg</t>
         </is>
       </c>
-      <c r="C619" t="inlineStr">
+      <c r="C618" t="inlineStr">
         <is>
           <t>鳥 ,希望</t>
         </is>
       </c>
     </row>
-    <row r="620">
-      <c r="A620" t="inlineStr">
+    <row r="619">
+      <c r="A619" t="inlineStr">
         <is>
           <t xml:space="preserve">「うちゅうへとびたい」
 أُريدُ أَنْ أَطيرَ إلى الفَضاء
@@ -13462,19 +13441,19 @@
 2308 mybookshelf co </t>
         </is>
       </c>
-      <c r="B620" t="inlineStr">
+      <c r="B619" t="inlineStr">
         <is>
           <t>images/「うちゅうへとびたい」_img1.jpg</t>
         </is>
       </c>
-      <c r="C620" t="inlineStr">
+      <c r="C619" t="inlineStr">
         <is>
           <t>絵本 ,宇宙</t>
         </is>
       </c>
     </row>
-    <row r="621">
-      <c r="A621" t="inlineStr">
+    <row r="620">
+      <c r="A620" t="inlineStr">
         <is>
           <t xml:space="preserve">「とても愛しています」
 أُحِبّك جِدّاً
@@ -13484,19 +13463,19 @@
 2308 hobe cc </t>
         </is>
       </c>
-      <c r="B621" t="inlineStr">
+      <c r="B620" t="inlineStr">
         <is>
           <t>images/「とても愛しています」_img1.jpg</t>
         </is>
       </c>
-      <c r="C621" t="inlineStr">
+      <c r="C620" t="inlineStr">
         <is>
           <t>恋 ,love</t>
         </is>
       </c>
     </row>
-    <row r="622">
-      <c r="A622" t="inlineStr">
+    <row r="621">
+      <c r="A621" t="inlineStr">
         <is>
           <t xml:space="preserve">「あす日が昇るだろう。私は朝が大好きだ」
 غدا ستشرق الشمس وأحب الصباح كثيرا
@@ -13505,19 +13484,19 @@
 2105 warag-3nb.tumblr com </t>
         </is>
       </c>
-      <c r="B622" t="inlineStr">
+      <c r="B621" t="inlineStr">
         <is>
           <t>images/「あす日が昇るだろう。私は朝が大好きだ_img1.jpg,images/ 「あす日が昇るだろう。私は朝が大好きだ_img2.jpg</t>
         </is>
       </c>
-      <c r="C622" t="inlineStr">
+      <c r="C621" t="inlineStr">
         <is>
           <t>おやすみ ,壁</t>
         </is>
       </c>
     </row>
-    <row r="623">
-      <c r="A623" t="inlineStr">
+    <row r="622">
+      <c r="A622" t="inlineStr">
         <is>
           <t xml:space="preserve">「きみは何をえらぶ？」
 ماذا تختار؟
@@ -13527,19 +13506,19 @@
 2109 embadomjp org </t>
         </is>
       </c>
-      <c r="B623" t="inlineStr">
+      <c r="B622" t="inlineStr">
         <is>
           <t>images/「きみは何をえらぶ？」_img1.jpg</t>
         </is>
       </c>
-      <c r="C623" t="inlineStr">
+      <c r="C622" t="inlineStr">
         <is>
           <t>優柔不断 ,絵本</t>
         </is>
       </c>
     </row>
-    <row r="624">
-      <c r="A624" t="inlineStr">
+    <row r="623">
+      <c r="A623" t="inlineStr">
         <is>
           <t xml:space="preserve">「ちょっと静けさが必要な時もある」
 في بعض الأوقات نحتاج لشوية هدوء
@@ -13549,19 +13528,19 @@
 2308 IN49r </t>
         </is>
       </c>
-      <c r="B624" t="inlineStr">
+      <c r="B623" t="inlineStr">
         <is>
           <t>images/「ちょっと静けさが必要な時もある」_img1.jpg</t>
         </is>
       </c>
-      <c r="C624" t="inlineStr">
+      <c r="C623" t="inlineStr">
         <is>
           <t>ミュート ,精神</t>
         </is>
       </c>
     </row>
-    <row r="625">
-      <c r="A625" t="inlineStr">
+    <row r="624">
+      <c r="A624" t="inlineStr">
         <is>
           <t xml:space="preserve">「逃げるな。全力でぶつかれ」
 لا تهرب اصطدم بكل قوتك
@@ -13571,19 +13550,19 @@
 2308 https://risingvibes.tumblr.com/post/189545775129 </t>
         </is>
       </c>
-      <c r="B625" t="inlineStr">
+      <c r="B624" t="inlineStr">
         <is>
           <t>images/「逃げるな。全力でぶつかれ」_img1.jpg</t>
         </is>
       </c>
-      <c r="C625" t="inlineStr">
+      <c r="C624" t="inlineStr">
         <is>
           <t>応援 ,力</t>
         </is>
       </c>
     </row>
-    <row r="626">
-      <c r="A626" t="inlineStr">
+    <row r="625">
+      <c r="A625" t="inlineStr">
         <is>
           <t xml:space="preserve">「着るのだいすき」
 أُحِبُ أَن أَرتَدِيَ
@@ -13593,19 +13572,19 @@
 2308 https://kitab.firmabikes.ru/epub-_hb_n_rtdy_5187.html </t>
         </is>
       </c>
-      <c r="B626" t="inlineStr">
+      <c r="B625" t="inlineStr">
         <is>
           <t>images/「着るのだいすき」_img1.jpg</t>
         </is>
       </c>
-      <c r="C626" t="inlineStr">
+      <c r="C625" t="inlineStr">
         <is>
           <t xml:space="preserve">絵本 ,ファッション </t>
         </is>
       </c>
     </row>
-    <row r="627">
-      <c r="A627" t="inlineStr">
+    <row r="626">
+      <c r="A626" t="inlineStr">
         <is>
           <t xml:space="preserve">「車のバッテリーが要る！」
 نحتاج بطارية سيارة
@@ -13615,19 +13594,19 @@
 2308 instagram roaa_27 </t>
         </is>
       </c>
-      <c r="B627" t="inlineStr">
+      <c r="B626" t="inlineStr">
         <is>
           <t>images/「車のバッテリーが要る！」_img1.jpg</t>
         </is>
       </c>
-      <c r="C627" t="inlineStr">
+      <c r="C626" t="inlineStr">
         <is>
           <t>スマホ ,充電</t>
         </is>
       </c>
     </row>
-    <row r="628">
-      <c r="A628" t="inlineStr">
+    <row r="627">
+      <c r="A627" t="inlineStr">
         <is>
           <t xml:space="preserve">「今日は幸せでいることにしました」
 اخترت أن أكون سعيدا اليوم
@@ -13637,19 +13616,19 @@
 2109 awaasha tumblr </t>
         </is>
       </c>
-      <c r="B628" t="inlineStr">
+      <c r="B627" t="inlineStr">
         <is>
           <t>images/「今日は幸せでいることにしました」_img1.jpg</t>
         </is>
       </c>
-      <c r="C628" t="inlineStr">
+      <c r="C627" t="inlineStr">
         <is>
           <t>心構え ,happy</t>
         </is>
       </c>
     </row>
-    <row r="629">
-      <c r="A629" t="inlineStr">
+    <row r="628">
+      <c r="A628" t="inlineStr">
         <is>
           <t xml:space="preserve">「理想的なスイカの選び方」
 كيف تختار البطيخة المُثلى؟
@@ -13659,19 +13638,19 @@
 2308 bit ly/octmel </t>
         </is>
       </c>
-      <c r="B629" t="inlineStr">
+      <c r="B628" t="inlineStr">
         <is>
           <t>images/「理想的なスイカの選び方」_img1.jpg</t>
         </is>
       </c>
-      <c r="C629" t="inlineStr">
+      <c r="C628" t="inlineStr">
         <is>
           <t>八百屋 ,西瓜</t>
         </is>
       </c>
     </row>
-    <row r="630">
-      <c r="A630" t="inlineStr">
+    <row r="629">
+      <c r="A629" t="inlineStr">
         <is>
           <t xml:space="preserve">「お問い合わせください」
 اتصل بنا
@@ -13681,19 +13660,19 @@
 2308 mtawir.blogspot com </t>
         </is>
       </c>
-      <c r="B630" t="inlineStr">
+      <c r="B629" t="inlineStr">
         <is>
           <t>images/「お問い合わせください」_img1.jpg</t>
         </is>
       </c>
-      <c r="C630" t="inlineStr">
+      <c r="C629" t="inlineStr">
         <is>
           <t>広告 ,電話</t>
         </is>
       </c>
     </row>
-    <row r="631">
-      <c r="A631" t="inlineStr">
+    <row r="630">
+      <c r="A630" t="inlineStr">
         <is>
           <t xml:space="preserve">「両方の動物が海岸の火山岩の亀裂の中に定住している」
 يحتل كلا الحيوانين شقوقًا في صخور الساحل البركانية
@@ -13701,19 +13680,19 @@
 2507 https://x.com/NatGeoMagArab/status/1925167200056521151 </t>
         </is>
       </c>
-      <c r="B631" t="inlineStr">
+      <c r="B630" t="inlineStr">
         <is>
           <t>images/「両方の動物が海岸の火山岩の亀裂の中に_img1.jpg,images/「両方の動物が海岸の火山岩の亀裂の中に_img2.jpg</t>
         </is>
       </c>
-      <c r="C631" t="inlineStr">
+      <c r="C630" t="inlineStr">
         <is>
           <t>手書き語学 ,アラビア語 ,イグアナ</t>
         </is>
       </c>
     </row>
-    <row r="632">
-      <c r="A632" t="inlineStr">
+    <row r="631">
+      <c r="A631" t="inlineStr">
         <is>
           <t xml:space="preserve">「命じられたように正しき道を辿れ」
 واستقم كما أمرت
@@ -13723,19 +13702,19 @@
 2308 Ahmed Madyan </t>
         </is>
       </c>
-      <c r="B632" t="inlineStr">
+      <c r="B631" t="inlineStr">
         <is>
           <t>images/「命じられたように正しき道を辿れ」_img1.jpg</t>
         </is>
       </c>
-      <c r="C632" t="inlineStr">
+      <c r="C631" t="inlineStr">
         <is>
           <t>書道 ,アート</t>
         </is>
       </c>
     </row>
-    <row r="633">
-      <c r="A633" t="inlineStr">
+    <row r="632">
+      <c r="A632" t="inlineStr">
         <is>
           <t xml:space="preserve">「くつろぎなさい」استكن
 イスタキンナ [istakinna]
@@ -13743,19 +13722,19 @@
 2603 m2ff tumblr com </t>
         </is>
       </c>
-      <c r="B633" t="inlineStr">
+      <c r="B632" t="inlineStr">
         <is>
           <t>images/「くつろぎなさい」.jpeg</t>
         </is>
       </c>
-      <c r="C633" t="inlineStr">
+      <c r="C632" t="inlineStr">
         <is>
           <t>relax ,コーヒー</t>
         </is>
       </c>
     </row>
-    <row r="634">
-      <c r="A634" t="inlineStr">
+    <row r="633">
+      <c r="A633" t="inlineStr">
         <is>
           <t xml:space="preserve">「彼は応えるだろう」سيستجيب 
 サヤスタジーブ [sa-ya-stajiibu]
@@ -13764,19 +13743,19 @@
 1811 kareem mrghani </t>
         </is>
       </c>
-      <c r="B634" t="inlineStr">
+      <c r="B633" t="inlineStr">
         <is>
           <t>images/「彼は応えるだろう」_img1.jpg</t>
         </is>
       </c>
-      <c r="C634" t="inlineStr">
+      <c r="C633" t="inlineStr">
         <is>
           <t>縦書き ,現代アート</t>
         </is>
       </c>
     </row>
-    <row r="635">
-      <c r="A635" t="inlineStr">
+    <row r="634">
+      <c r="A634" t="inlineStr">
         <is>
           <t xml:space="preserve">「アラビア語が好き」
 أنا أُحبّ لُغتي
@@ -13786,19 +13765,19 @@
 2308 出典不明 </t>
         </is>
       </c>
-      <c r="B635" t="inlineStr">
+      <c r="B634" t="inlineStr">
         <is>
           <t>images/「アラビア語が好き」_img1.jpg</t>
         </is>
       </c>
-      <c r="C635" t="inlineStr">
+      <c r="C634" t="inlineStr">
         <is>
           <t>和訳 ,こども</t>
         </is>
       </c>
     </row>
-    <row r="636">
-      <c r="A636" t="inlineStr">
+    <row r="635">
+      <c r="A635" t="inlineStr">
         <is>
           <t xml:space="preserve">「私はサッカーが好きです」
 أنا أُحِبُّ كُرةَ القَدَم
@@ -13808,19 +13787,19 @@
 2109 Arabic With Nadia </t>
         </is>
       </c>
-      <c r="B636" t="inlineStr">
+      <c r="B635" t="inlineStr">
         <is>
           <t>images/「私はサッカーが好きです」_img1.jpg</t>
         </is>
       </c>
-      <c r="C636" t="inlineStr">
+      <c r="C635" t="inlineStr">
         <is>
           <t>自由時間 ,例文</t>
         </is>
       </c>
     </row>
-    <row r="637">
-      <c r="A637" t="inlineStr">
+    <row r="636">
+      <c r="A636" t="inlineStr">
         <is>
           <t xml:space="preserve">「これ、私の眼鏡じゃありません」
 هٰذِهِ لَيْسَتْ نَظَّارَاتِي
@@ -13830,19 +13809,19 @@
 2509 </t>
         </is>
       </c>
-      <c r="B637" t="inlineStr">
+      <c r="B636" t="inlineStr">
         <is>
           <t>images/「これ、私の眼鏡じゃありません」_img1.jpg</t>
         </is>
       </c>
-      <c r="C637" t="inlineStr">
+      <c r="C636" t="inlineStr">
         <is>
           <t>あらびあや</t>
         </is>
       </c>
     </row>
-    <row r="638">
-      <c r="A638" t="inlineStr">
+    <row r="637">
+      <c r="A637" t="inlineStr">
         <is>
           <t xml:space="preserve">「我らも米を食います」
 نحن أيضاً نأكل الأرز
@@ -13852,19 +13831,19 @@
 1809 </t>
         </is>
       </c>
-      <c r="B638" t="inlineStr">
+      <c r="B637" t="inlineStr">
         <is>
           <t>images/「我らも米を食います」_img1.jpg</t>
         </is>
       </c>
-      <c r="C638" t="inlineStr">
+      <c r="C637" t="inlineStr">
         <is>
           <t>あらびあや</t>
         </is>
       </c>
     </row>
-    <row r="639">
-      <c r="A639" t="inlineStr">
+    <row r="638">
+      <c r="A638" t="inlineStr">
         <is>
           <t xml:space="preserve">「ひとりでできるもん！」
 أنا أستطيع أن أفعله وحدي
@@ -13873,19 +13852,19 @@
 2105 </t>
         </is>
       </c>
-      <c r="B639" t="inlineStr">
+      <c r="B638" t="inlineStr">
         <is>
           <t>images/「ひとりでできるもん！」_img1.jpg</t>
         </is>
       </c>
-      <c r="C639" t="inlineStr">
+      <c r="C638" t="inlineStr">
         <is>
           <t>あらびあや</t>
         </is>
       </c>
     </row>
-    <row r="640">
-      <c r="A640" t="inlineStr">
+    <row r="639">
+      <c r="A639" t="inlineStr">
         <is>
           <t xml:space="preserve">「恋しくないと言っている時は恋しい」
 أُريدُك حينَ أَقُولُ أَنا لا أُريدُك
@@ -13895,19 +13874,19 @@
 2308 DARWISHISM </t>
         </is>
       </c>
-      <c r="B640" t="inlineStr">
+      <c r="B639" t="inlineStr">
         <is>
           <t>images/「恋しくないと言っている時は恋しい」_img1.jpg</t>
         </is>
       </c>
-      <c r="C640" t="inlineStr">
+      <c r="C639" t="inlineStr">
         <is>
           <t>本音 ,恋愛</t>
         </is>
       </c>
     </row>
-    <row r="641">
-      <c r="A641" t="inlineStr">
+    <row r="640">
+      <c r="A640" t="inlineStr">
         <is>
           <t xml:space="preserve">「私は〜する」
 ⁦「着る」：( أنا ألبس )['ana 'a-lbas]⁩
@@ -13918,19 +13897,19 @@
 2109 RABIE </t>
         </is>
       </c>
-      <c r="B641" t="inlineStr">
+      <c r="B640" t="inlineStr">
         <is>
           <t>images/「私は〜する」_img1.jpg,images/「私は〜する」_img2.jpg,images/「私は〜する」_img3.jpg,images/「私は〜する」_img4.jpg</t>
         </is>
       </c>
-      <c r="C641" t="inlineStr">
+      <c r="C640" t="inlineStr">
         <is>
           <t>動詞 ,絵本</t>
         </is>
       </c>
     </row>
-    <row r="642">
-      <c r="A642" t="inlineStr">
+    <row r="641">
+      <c r="A641" t="inlineStr">
         <is>
           <t xml:space="preserve">「彼は完璧ではない。私は彼の欠点については目をつむった」
 هو ليس كامل. أنا أعميت نفسي عن سيئاته
@@ -13939,19 +13918,19 @@
 2308 _NOHA </t>
         </is>
       </c>
-      <c r="B642" t="inlineStr">
+      <c r="B641" t="inlineStr">
         <is>
           <t>images/「彼は完璧ではない。私は彼の欠点につい_img1.jpg</t>
         </is>
       </c>
-      <c r="C642" t="inlineStr">
+      <c r="C641" t="inlineStr">
         <is>
           <t>愛 ,寛容</t>
         </is>
       </c>
     </row>
-    <row r="643">
-      <c r="A643" t="inlineStr">
+    <row r="642">
+      <c r="A642" t="inlineStr">
         <is>
           <t xml:space="preserve">「この子トラは検疫期間中に生まれた」
 صغير النمر هذا ولد في زمن الحجر الصحي
@@ -13960,19 +13939,19 @@
 2310 https://www.akhbaralaan.net/?p=434924 </t>
         </is>
       </c>
-      <c r="B643" t="inlineStr">
+      <c r="B642" t="inlineStr">
         <is>
           <t>images/「この子トラは検疫期間中に生まれた」_img1.jpg</t>
         </is>
       </c>
-      <c r="C643" t="inlineStr">
+      <c r="C642" t="inlineStr">
         <is>
           <t>Covid ,メキシコ</t>
         </is>
       </c>
     </row>
-    <row r="644">
-      <c r="A644" t="inlineStr">
+    <row r="643">
+      <c r="A643" t="inlineStr">
         <is>
           <t xml:space="preserve">「睡眠の素晴らしさに匹敵するものは無い！」
 وجمال النوم ليس له مثيل
@@ -13981,19 +13960,19 @@
 2308 arabzy tumblr </t>
         </is>
       </c>
-      <c r="B644" t="inlineStr">
+      <c r="B643" t="inlineStr">
         <is>
           <t>images/「睡眠の素晴らしさに匹敵するものは無い_img1.jpg</t>
         </is>
       </c>
-      <c r="C644" t="inlineStr">
+      <c r="C643" t="inlineStr">
         <is>
           <t>オフトゥン ,おやすみ</t>
         </is>
       </c>
     </row>
-    <row r="645">
-      <c r="A645" t="inlineStr">
+    <row r="644">
+      <c r="A644" t="inlineStr">
         <is>
           <t xml:space="preserve">「大器晩成」
 الأشياء العظيمة تأخذ وقت
@@ -14003,19 +13982,19 @@
 2109 出典不明 </t>
         </is>
       </c>
-      <c r="B645" t="inlineStr">
+      <c r="B644" t="inlineStr">
         <is>
           <t>images/「大器晩成」_img1.jpg</t>
         </is>
       </c>
-      <c r="C645" t="inlineStr">
+      <c r="C644" t="inlineStr">
         <is>
           <t>ことわざ ,和訳</t>
         </is>
       </c>
     </row>
-    <row r="646">
-      <c r="A646" t="inlineStr">
+    <row r="645">
+      <c r="A645" t="inlineStr">
         <is>
           <t xml:space="preserve">「コーヒーは急には飲まれない」
 القهْوة لا تشرَب عَلى عَجلْ
@@ -14026,19 +14005,19 @@
 2012 Ahmed Madyan </t>
         </is>
       </c>
-      <c r="B646" t="inlineStr">
+      <c r="B645" t="inlineStr">
         <is>
           <t>images/「コーヒーは急には飲まれない」_img1.jpg</t>
         </is>
       </c>
-      <c r="C646" t="inlineStr">
+      <c r="C645" t="inlineStr">
         <is>
           <t>名言</t>
         </is>
       </c>
     </row>
-    <row r="647">
-      <c r="A647" t="inlineStr">
+    <row r="646">
+      <c r="A646" t="inlineStr">
         <is>
           <t xml:space="preserve">「成功者は情報共有している」
 الناجحون يشاركون المعلومة
@@ -14048,19 +14027,19 @@
 2109 出典不明 </t>
         </is>
       </c>
-      <c r="B647" t="inlineStr">
+      <c r="B646" t="inlineStr">
         <is>
           <t>images/「成功者は情報共有している」_img1.jpg</t>
         </is>
       </c>
-      <c r="C647" t="inlineStr">
+      <c r="C646" t="inlineStr">
         <is>
           <t>鳥 ,シェア</t>
         </is>
       </c>
     </row>
-    <row r="648">
-      <c r="A648" t="inlineStr">
+    <row r="647">
+      <c r="A647" t="inlineStr">
         <is>
           <t xml:space="preserve">「間違いで賢くなる、痛みで強くなる」
 الأخطاء تجعلك حكيمًا، والألم يجعلك قويًا
@@ -14069,19 +14048,19 @@
 2111 https://alaminin.blogspot.com/2020/03/blog-post_6.html </t>
         </is>
       </c>
-      <c r="B648" t="inlineStr">
+      <c r="B647" t="inlineStr">
         <is>
           <t>images/「間違いで賢くなる、痛みで強くなる」_img1.jpg</t>
         </is>
       </c>
-      <c r="C648" t="inlineStr">
+      <c r="C647" t="inlineStr">
         <is>
           <t>名言</t>
         </is>
       </c>
     </row>
-    <row r="649">
-      <c r="A649" t="inlineStr">
+    <row r="648">
+      <c r="A648" t="inlineStr">
         <is>
           <t xml:space="preserve">「何事も永遠には続かない」
 لا شيء يبقى للأبد
@@ -14091,19 +14070,19 @@
 2308 KiTeLetZ </t>
         </is>
       </c>
-      <c r="B649" t="inlineStr">
+      <c r="B648" t="inlineStr">
         <is>
           <t>images/「何事も永遠には続かない」_img1.jpg</t>
         </is>
       </c>
-      <c r="C649" t="inlineStr">
+      <c r="C648" t="inlineStr">
         <is>
           <t>変化 ,名言</t>
         </is>
       </c>
     </row>
-    <row r="650">
-      <c r="A650" t="inlineStr">
+    <row r="649">
+      <c r="A649" t="inlineStr">
         <is>
           <t xml:space="preserve">「惑星地球はあなた方を歓迎します」
 كوكب الارض يرحّب بكم
@@ -14113,19 +14092,19 @@
 1811 iN49R </t>
         </is>
       </c>
-      <c r="B650" t="inlineStr">
+      <c r="B649" t="inlineStr">
         <is>
           <t>images/「惑星地球はあなた方を歓迎します」_img1.jpg</t>
         </is>
       </c>
-      <c r="C650" t="inlineStr">
+      <c r="C649" t="inlineStr">
         <is>
           <t>宇宙 ,人類</t>
         </is>
       </c>
     </row>
-    <row r="651">
-      <c r="A651" t="inlineStr">
+    <row r="650">
+      <c r="A650" t="inlineStr">
         <is>
           <t xml:space="preserve">「自分を信じなさい。人の言うことは尽きないのだから」
 ثق بنفسك فكلام الناس لا ينتهي
@@ -14134,19 +14113,19 @@
 2105 出典不明 </t>
         </is>
       </c>
-      <c r="B651" t="inlineStr">
+      <c r="B650" t="inlineStr">
         <is>
           <t>images/「自分を信じなさい。人の言うことは尽き_img1.jpg</t>
         </is>
       </c>
-      <c r="C651" t="inlineStr">
+      <c r="C650" t="inlineStr">
         <is>
           <t>自信 ,無視</t>
         </is>
       </c>
     </row>
-    <row r="652">
-      <c r="A652" t="inlineStr">
+    <row r="651">
+      <c r="A651" t="inlineStr">
         <is>
           <t xml:space="preserve">「弟が歩くぞ」أخي الصغير يمشي
 アキ_ッサギール・ヤムシー ['aKh-i ^_saGhiiru ya-mShii]
@@ -14155,19 +14134,19 @@
 2308 gulfkids com http://www.gulfkids.com/ar/book48-1909.htm </t>
         </is>
       </c>
-      <c r="B652" t="inlineStr">
+      <c r="B651" t="inlineStr">
         <is>
           <t>images/「弟が歩くぞ」_img1.jpg</t>
         </is>
       </c>
-      <c r="C652" t="inlineStr">
+      <c r="C651" t="inlineStr">
         <is>
           <t>兄弟 ,絵本</t>
         </is>
       </c>
     </row>
-    <row r="653">
-      <c r="A653" t="inlineStr">
+    <row r="652">
+      <c r="A652" t="inlineStr">
         <is>
           <t xml:space="preserve">花より団子おおお（違う）
 「誰もふさわしくない」[laa 'aHada ya-staHiqqu]
@@ -14175,19 +14154,19 @@
 2308 https://twitter.com/NatGeoMagArab/status/1370041991317233664 </t>
         </is>
       </c>
-      <c r="B653" t="inlineStr">
+      <c r="B652" t="inlineStr">
         <is>
           <t>images/花より団子おおお（違う）_img1.jpg</t>
         </is>
       </c>
-      <c r="C653" t="inlineStr">
+      <c r="C652" t="inlineStr">
         <is>
           <t>手書き語学 ,アラビア語 ,キノボリカンガルー</t>
         </is>
       </c>
     </row>
-    <row r="654">
-      <c r="A654" t="inlineStr">
+    <row r="653">
+      <c r="A653" t="inlineStr">
         <is>
           <t xml:space="preserve">「幸せな人生には弱い記憶力が必要」
 الحياة السعيدة تتطلب ذاكرة ضعيفة
@@ -14196,19 +14175,19 @@
 2012 出典不明 </t>
         </is>
       </c>
-      <c r="B654" t="inlineStr">
+      <c r="B653" t="inlineStr">
         <is>
           <t>images/「幸せな人生には弱い記憶力が必要」_img1.jpg</t>
         </is>
       </c>
-      <c r="C654" t="inlineStr">
+      <c r="C653" t="inlineStr">
         <is>
           <t>前向き</t>
         </is>
       </c>
     </row>
-    <row r="655">
-      <c r="A655" t="inlineStr">
+    <row r="654">
+      <c r="A654" t="inlineStr">
         <is>
           <t xml:space="preserve">「このパンダは私たちに、幸せは単純なことの中に隠れているのだと教えている」
 دب "الباندا" هذا يؤكد لنا أن السعادة تكمن في أبسط الأشياء
@@ -14216,19 +14195,19 @@
 2308 https://twitter.com/NatGeoMagArab/status/1309938472065486848 </t>
         </is>
       </c>
-      <c r="B655" t="inlineStr">
+      <c r="B654" t="inlineStr">
         <is>
           <t>images/「このパンダは私たちに、幸せは単純なこ.png</t>
         </is>
       </c>
-      <c r="C655" t="inlineStr">
+      <c r="C654" t="inlineStr">
         <is>
           <t>パンダ ,雪</t>
         </is>
       </c>
     </row>
-    <row r="656">
-      <c r="A656" t="inlineStr">
+    <row r="655">
+      <c r="A655" t="inlineStr">
         <is>
           <t xml:space="preserve">「良い時間は速く過ぎる」
 الأوقات الجميلة تمر بسرعة
@@ -14238,19 +14217,19 @@
 1810 Nasser.Tumblr </t>
         </is>
       </c>
-      <c r="B656" t="inlineStr">
+      <c r="B655" t="inlineStr">
         <is>
           <t>images/「良い時間は速く過ぎる」_img1.jpg</t>
         </is>
       </c>
-      <c r="C656" t="inlineStr">
+      <c r="C655" t="inlineStr">
         <is>
           <t>相対論 ,心理学</t>
         </is>
       </c>
     </row>
-    <row r="657">
-      <c r="A657" t="inlineStr">
+    <row r="656">
+      <c r="A656" t="inlineStr">
         <is>
           <t xml:space="preserve">「今日が始まりかもしれない」
 كل يوم ممكن يكون بداية
@@ -14260,19 +14239,19 @@
 2308 Ahmed Madyan </t>
         </is>
       </c>
-      <c r="B657" t="inlineStr">
+      <c r="B656" t="inlineStr">
         <is>
           <t>images/「今日が始まりかもしれない」_img1.jpg</t>
         </is>
       </c>
-      <c r="C657" t="inlineStr">
+      <c r="C656" t="inlineStr">
         <is>
           <t>吉日 ,開始</t>
         </is>
       </c>
     </row>
-    <row r="658">
-      <c r="A658" t="inlineStr">
+    <row r="657">
+      <c r="A657" t="inlineStr">
         <is>
           <t xml:space="preserve">「ヌール、歯医者さんに行く」
 نور تذهب إلى طبيب الأسنان
@@ -14282,19 +14261,19 @@
 2109 RABIE </t>
         </is>
       </c>
-      <c r="B658" t="inlineStr">
+      <c r="B657" t="inlineStr">
         <is>
           <t>images/「ヌール、歯医者さんに行く」_img1.jpg</t>
         </is>
       </c>
-      <c r="C658" t="inlineStr">
+      <c r="C657" t="inlineStr">
         <is>
           <t>絵本 ,歯科</t>
         </is>
       </c>
     </row>
-    <row r="659">
-      <c r="A659" t="inlineStr">
+    <row r="658">
+      <c r="A658" t="inlineStr">
         <is>
           <t xml:space="preserve">「ラヤンはねむれない」
 لَيان لا تَسْتَطيعُ أَنْ تَنام
@@ -14303,19 +14282,19 @@
 2308 出典不明 </t>
         </is>
       </c>
-      <c r="B659" t="inlineStr">
+      <c r="B658" t="inlineStr">
         <is>
           <t>images/「ラヤンはねむれない」_img1.jpg</t>
         </is>
       </c>
-      <c r="C659" t="inlineStr">
+      <c r="C658" t="inlineStr">
         <is>
           <t>絵本 ,不眠症</t>
         </is>
       </c>
     </row>
-    <row r="660">
-      <c r="A660" t="inlineStr">
+    <row r="659">
+      <c r="A659" t="inlineStr">
         <is>
           <t xml:space="preserve">「クネイトラ県、蜂の巣を約60%失う」
 القنيطرة تفقد حوالي 60 % من خلايا نحلها
@@ -14323,19 +14302,19 @@
 2403 nabd com/t/101679025-fb119f </t>
         </is>
       </c>
-      <c r="B660" t="inlineStr">
+      <c r="B659" t="inlineStr">
         <is>
           <t>images/「クネイトラ県、蜂の巣を約60%失う」_img1.jpg</t>
         </is>
       </c>
-      <c r="C660" t="inlineStr">
+      <c r="C659" t="inlineStr">
         <is>
           <t>蜂の巣 ,パーセント</t>
         </is>
       </c>
     </row>
-    <row r="661">
-      <c r="A661" t="inlineStr">
+    <row r="660">
+      <c r="A660" t="inlineStr">
         <is>
           <t xml:space="preserve">「結ばれしター」ة
 ⁦( تاء مربوطة )[taa' marbuu_ta]：ت「ター」( تاء )[taa']・「結ばれている」( مربوط )[marbuu_t]：( ربط )【結】⁩
@@ -14343,19 +14322,19 @@
 2308 出典不明 </t>
         </is>
       </c>
-      <c r="B661" t="inlineStr">
+      <c r="B660" t="inlineStr">
         <is>
           <t>images/「結ばれしター」_img1.jpg</t>
         </is>
       </c>
-      <c r="C661" t="inlineStr">
+      <c r="C660" t="inlineStr">
         <is>
           <t>アラビア文字 ,顔</t>
         </is>
       </c>
     </row>
-    <row r="662">
-      <c r="A662" t="inlineStr">
+    <row r="661">
+      <c r="A661" t="inlineStr">
         <is>
           <t xml:space="preserve">「忙しい」مشغول
 マシュグール [maShGhuul]
@@ -14364,19 +14343,19 @@
 1811 skyshinichi.instagram </t>
         </is>
       </c>
-      <c r="B662" t="inlineStr">
+      <c r="B661" t="inlineStr">
         <is>
           <t>images/「忙しい」_img1.jpg</t>
         </is>
       </c>
-      <c r="C662" t="inlineStr">
+      <c r="C661" t="inlineStr">
         <is>
           <t>スティッチ ,残業</t>
         </is>
       </c>
     </row>
-    <row r="663">
-      <c r="A663" t="inlineStr">
+    <row r="662">
+      <c r="A662" t="inlineStr">
         <is>
           <t xml:space="preserve">「駐車禁止」ممنوع الوقوف
 マムヌーア・アルウクーフ [mamnuu* al-wuquuf]
@@ -14385,19 +14364,19 @@
 2106 出典不明 </t>
         </is>
       </c>
-      <c r="B663" t="inlineStr">
+      <c r="B662" t="inlineStr">
         <is>
           <t>images/「駐車禁止」_img1.jpg</t>
         </is>
       </c>
-      <c r="C663" t="inlineStr">
+      <c r="C662" t="inlineStr">
         <is>
           <t>標識 ,ジョーク</t>
         </is>
       </c>
     </row>
-    <row r="664">
-      <c r="A664" t="inlineStr">
+    <row r="663">
+      <c r="A663" t="inlineStr">
         <is>
           <t xml:space="preserve">「一人ひとりが責任を」
 كُلنا مسؤول
@@ -14407,19 +14386,19 @@
 2308 covid19awareness sa </t>
         </is>
       </c>
-      <c r="B664" t="inlineStr">
+      <c r="B663" t="inlineStr">
         <is>
           <t>images/「一人ひとりが責任を」_img1.jpg</t>
         </is>
       </c>
-      <c r="C664" t="inlineStr">
+      <c r="C663" t="inlineStr">
         <is>
           <t>Covid ,感染拡大防止</t>
         </is>
       </c>
     </row>
-    <row r="665">
-      <c r="A665" t="inlineStr">
+    <row r="664">
+      <c r="A664" t="inlineStr">
         <is>
           <t xml:space="preserve">「おめでとうございます」مبروك
 マブルーク [mabruuk]
@@ -14428,19 +14407,19 @@
 2308 </t>
         </is>
       </c>
-      <c r="B665" t="inlineStr">
+      <c r="B664" t="inlineStr">
         <is>
           <t>images/「おめでとうございます」_img1.jpg</t>
         </is>
       </c>
-      <c r="C665" t="inlineStr">
+      <c r="C664" t="inlineStr">
         <is>
           <t>詐欺 ,広告</t>
         </is>
       </c>
     </row>
-    <row r="666">
-      <c r="A666" t="inlineStr">
+    <row r="665">
+      <c r="A665" t="inlineStr">
         <is>
           <t xml:space="preserve">「手書きフォント」
 خط مكتوب باليد
@@ -14450,19 +14429,19 @@
 1809 FahdAlFraikh Behance </t>
         </is>
       </c>
-      <c r="B666" t="inlineStr">
+      <c r="B665" t="inlineStr">
         <is>
           <t>images/「手書きフォント」_img1.jpg</t>
         </is>
       </c>
-      <c r="C666" t="inlineStr">
+      <c r="C665" t="inlineStr">
         <is>
           <t>可愛いフォント ,筆跡</t>
         </is>
       </c>
     </row>
-    <row r="667">
-      <c r="A667" t="inlineStr">
+    <row r="666">
+      <c r="A666" t="inlineStr">
         <is>
           <t xml:space="preserve">「開かれたターと結ばれたター」
 التاء المفتوحة والمربوطة
@@ -14472,19 +14451,19 @@
 2109 slideshare.net </t>
         </is>
       </c>
-      <c r="B667" t="inlineStr">
+      <c r="B666" t="inlineStr">
         <is>
           <t>images/「開かれたターと結ばれたター」_img1.jpg</t>
         </is>
       </c>
-      <c r="C667" t="inlineStr">
+      <c r="C666" t="inlineStr">
         <is>
           <t>アラビア文字 ,スマイリー</t>
         </is>
       </c>
     </row>
-    <row r="668">
-      <c r="A668" t="inlineStr">
+    <row r="667">
+      <c r="A667" t="inlineStr">
         <is>
           <t xml:space="preserve">「このラマは誇らしげにして立っている」
 تقف هذه اللاما مزهوة بنفسها
@@ -14492,19 +14471,19 @@
 2410 https://twitter.com/NatGeoMagArab/status/1597485552965935104 </t>
         </is>
       </c>
-      <c r="B668" t="inlineStr">
+      <c r="B667" t="inlineStr">
         <is>
           <t>images/「このラマは誇らしげにして立っている」_img1.jpg</t>
         </is>
       </c>
-      <c r="C668" t="inlineStr">
+      <c r="C667" t="inlineStr">
         <is>
           <t>手書き語学 ,アラビア語 ,マチュピチュ遺跡</t>
         </is>
       </c>
     </row>
-    <row r="669">
-      <c r="A669" t="inlineStr">
+    <row r="668">
+      <c r="A668" t="inlineStr">
         <is>
           <t xml:space="preserve">「小さな生き物にしては危険な名前だ」
 اسم خطير لمخلوق صغير
@@ -14513,19 +14492,19 @@
 2308 https://twitter.com/NatGeoMagArab/status/1495035772071669760 </t>
         </is>
       </c>
-      <c r="B669" t="inlineStr">
+      <c r="B668" t="inlineStr">
         <is>
           <t>images/「小さな生き物にしては危険な名前だ」_img1.jpg</t>
         </is>
       </c>
-      <c r="C669" t="inlineStr">
+      <c r="C668" t="inlineStr">
         <is>
           <t>有袋類 ,タスマニアデビル</t>
         </is>
       </c>
     </row>
-    <row r="670">
-      <c r="A670" t="inlineStr">
+    <row r="669">
+      <c r="A669" t="inlineStr">
         <is>
           <t xml:space="preserve">「こわれている」مكسر
 ムカッサル [mukassar]
@@ -14533,19 +14512,19 @@
 2105 behance Written-Visuals </t>
         </is>
       </c>
-      <c r="B670" t="inlineStr">
+      <c r="B669" t="inlineStr">
         <is>
           <t>images/「こわれている」_img1.jpg</t>
         </is>
       </c>
-      <c r="C670" t="inlineStr">
+      <c r="C669" t="inlineStr">
         <is>
           <t>バラバラ ,デザイン</t>
         </is>
       </c>
     </row>
-    <row r="671">
-      <c r="A671" t="inlineStr">
+    <row r="670">
+      <c r="A670" t="inlineStr">
         <is>
           <t xml:space="preserve">「早起きする方法」
 كيف تنهض مُبكّرًا
@@ -14555,19 +14534,19 @@
 2308 Funders and Founders </t>
         </is>
       </c>
-      <c r="B671" t="inlineStr">
+      <c r="B670" t="inlineStr">
         <is>
           <t>images/「早起きする方法」_img1.jpg</t>
         </is>
       </c>
-      <c r="C671" t="inlineStr">
+      <c r="C670" t="inlineStr">
         <is>
           <t>オフトゥン ,寝起き</t>
         </is>
       </c>
     </row>
-    <row r="672">
-      <c r="A672" t="inlineStr">
+    <row r="671">
+      <c r="A671" t="inlineStr">
         <is>
           <t xml:space="preserve">「アラブ・デザイン文字展覧会」
 معرض لتخطيط الحرف العربي
@@ -14577,38 +14556,38 @@
 2109 arabic lettering exhibition </t>
         </is>
       </c>
-      <c r="B672" t="inlineStr">
+      <c r="B671" t="inlineStr">
         <is>
           <t>images/「アラブ・デザイン文字展覧会」_img1.jpg</t>
         </is>
       </c>
-      <c r="C672" t="inlineStr">
+      <c r="C671" t="inlineStr">
         <is>
           <t>ポスター</t>
         </is>
       </c>
     </row>
-    <row r="673">
-      <c r="A673" t="inlineStr">
+    <row r="672">
+      <c r="A672" t="inlineStr">
         <is>
           <t xml:space="preserve">「お気に入りのおもちゃには触らせない」
 ⁦「彼は〜を許さない」[laa ya-smaHu bi-]：「彼は許す」( يسمح )[ya-smaH(u)]：「許した」( سمح )[samaHa]：( سَ )[sa]・( مَ )[ma]・( حَ )[Ha]⁩
 2209 https://pic.twitter.com/qWcIPB3fz2 </t>
         </is>
       </c>
-      <c r="B673" t="inlineStr">
+      <c r="B672" t="inlineStr">
         <is>
           <t>images/「お気に入りのおもちゃには触らせない」_img1.jpg</t>
         </is>
       </c>
-      <c r="C673" t="inlineStr">
+      <c r="C672" t="inlineStr">
         <is>
           <t>パンダ ,ボール</t>
         </is>
       </c>
     </row>
-    <row r="674">
-      <c r="A674" t="inlineStr">
+    <row r="673">
+      <c r="A673" t="inlineStr">
         <is>
           <t xml:space="preserve">「名探偵コナン」المحقق كونان
 アルムハッキク・コナン [al-muHaqqiq Conan]
@@ -14617,19 +14596,19 @@
 1809 wikipedia </t>
         </is>
       </c>
-      <c r="B674" t="inlineStr">
+      <c r="B673" t="inlineStr">
         <is>
           <t>images/「名探偵コナン」_img1.jpg</t>
         </is>
       </c>
-      <c r="C674" t="inlineStr">
+      <c r="C673" t="inlineStr">
         <is>
           <t>江戸川コナン ,ロゴ</t>
         </is>
       </c>
     </row>
-    <row r="675">
-      <c r="A675" t="inlineStr">
+    <row r="674">
+      <c r="A674" t="inlineStr">
         <is>
           <t xml:space="preserve">「イードおめでとう」عيد مبارك
 イード・ムバーラク [*iid mubaarak]
@@ -14637,19 +14616,19 @@
 2308 出典不明 </t>
         </is>
       </c>
-      <c r="B675" t="inlineStr">
+      <c r="B674" t="inlineStr">
         <is>
           <t>images/「イードおめでとう」_img1.jpg</t>
         </is>
       </c>
-      <c r="C675" t="inlineStr">
+      <c r="C674" t="inlineStr">
         <is>
           <t>عيد ,アラビア語</t>
         </is>
       </c>
     </row>
-    <row r="676">
-      <c r="A676" t="inlineStr">
+    <row r="675">
+      <c r="A675" t="inlineStr">
         <is>
           <t xml:space="preserve">「戦士」محارب
 ムハーリブ [muHaarib]
@@ -14658,19 +14637,19 @@
 1809 abudinges.tumblr </t>
         </is>
       </c>
-      <c r="B676" t="inlineStr">
+      <c r="B675" t="inlineStr">
         <is>
           <t>images/「戦士」_img1.jpg</t>
         </is>
       </c>
-      <c r="C676" t="inlineStr">
+      <c r="C675" t="inlineStr">
         <is>
           <t>ロゴ ,赤</t>
         </is>
       </c>
     </row>
-    <row r="677">
-      <c r="A677" t="inlineStr">
+    <row r="676">
+      <c r="A676" t="inlineStr">
         <is>
           <t xml:space="preserve">「ライブ」بث مباشر
 バッス・ムバーシル [ba^Th(un) mubaaShir(un)]
@@ -14679,19 +14658,19 @@
 2308 beIN SPORTS </t>
         </is>
       </c>
-      <c r="B677" t="inlineStr">
+      <c r="B676" t="inlineStr">
         <is>
           <t>images/「ライブ」_img1.jpg</t>
         </is>
       </c>
-      <c r="C677" t="inlineStr">
+      <c r="C676" t="inlineStr">
         <is>
           <t xml:space="preserve">生放送 ,試合 </t>
         </is>
       </c>
     </row>
-    <row r="678">
-      <c r="A678" t="inlineStr">
+    <row r="677">
+      <c r="A677" t="inlineStr">
         <is>
           <t xml:space="preserve">「信者」مُؤْمِنٌ
 ムッミン [mu'min(un)]
@@ -14700,19 +14679,19 @@
 2106 出典不明 </t>
         </is>
       </c>
-      <c r="B678" t="inlineStr">
+      <c r="B677" t="inlineStr">
         <is>
           <t>images/「信者」_img1.jpg</t>
         </is>
       </c>
-      <c r="C678" t="inlineStr">
+      <c r="C677" t="inlineStr">
         <is>
           <t>明暗 ,信仰</t>
         </is>
       </c>
     </row>
-    <row r="679">
-      <c r="A679" t="inlineStr">
+    <row r="678">
+      <c r="A678" t="inlineStr">
         <is>
           <t xml:space="preserve">「開⇔閉」
 مفتوح
@@ -14723,19 +14702,19 @@
 2312 Hussein Safina, behance </t>
         </is>
       </c>
-      <c r="B679" t="inlineStr">
+      <c r="B678" t="inlineStr">
         <is>
           <t>images/「開⇔閉」_img1.jpg</t>
         </is>
       </c>
-      <c r="C679" t="inlineStr">
+      <c r="C678" t="inlineStr">
         <is>
           <t>オープンマインド ,トグル</t>
         </is>
       </c>
     </row>
-    <row r="680">
-      <c r="A680" t="inlineStr">
+    <row r="679">
+      <c r="A679" t="inlineStr">
         <is>
           <t xml:space="preserve">「予想外な結末！」
 نهاية غير متوقعة
@@ -14743,19 +14722,19 @@
 2308 https://twitter.com/NatGeoMagArab/status/1159011433444593665 </t>
         </is>
       </c>
-      <c r="B680" t="inlineStr">
+      <c r="B679" t="inlineStr">
         <is>
           <t>images/「予想外な結末！」_img1.jpg</t>
         </is>
       </c>
-      <c r="C680" t="inlineStr">
+      <c r="C679" t="inlineStr">
         <is>
           <t>手書き語学 ,アラビア語 ,ウサギ</t>
         </is>
       </c>
     </row>
-    <row r="681">
-      <c r="A681" t="inlineStr">
+    <row r="680">
+      <c r="A680" t="inlineStr">
         <is>
           <t xml:space="preserve">「ベイルート・アニメイテッド」
 بیروت متحرّکة
@@ -14765,19 +14744,19 @@
 2308 arabic_script Instagram </t>
         </is>
       </c>
-      <c r="B681" t="inlineStr">
+      <c r="B680" t="inlineStr">
         <is>
           <t>images/「ベイルート・アニメイテッド」_img1.jpg</t>
         </is>
       </c>
-      <c r="C681" t="inlineStr">
+      <c r="C680" t="inlineStr">
         <is>
           <t>アニメ ,レバノン</t>
         </is>
       </c>
     </row>
-    <row r="682">
-      <c r="A682" t="inlineStr">
+    <row r="681">
+      <c r="A681" t="inlineStr">
         <is>
           <t xml:space="preserve">「夢みれば叶う」
 كُلُّ مُتَوَقَّعٍ آتٍ
@@ -14787,19 +14766,19 @@
 2108 Ahmed Madyan </t>
         </is>
       </c>
-      <c r="B682" t="inlineStr">
+      <c r="B681" t="inlineStr">
         <is>
           <t>images/「夢みれば叶う」_img1.jpg</t>
         </is>
       </c>
-      <c r="C682" t="inlineStr">
+      <c r="C681" t="inlineStr">
         <is>
           <t>希望 ,ドリカム</t>
         </is>
       </c>
     </row>
-    <row r="683">
-      <c r="A683" t="inlineStr">
+    <row r="682">
+      <c r="A682" t="inlineStr">
         <is>
           <t xml:space="preserve">「もし両者が人間のように鎧で武装して戦いに突入したら」
 لو خاضا معاركهما متسلحين بالدروع على غرار البش
@@ -14807,19 +14786,19 @@
 2404 https://x.com/NatGeoMagArab/status/1759284149456945464 </t>
         </is>
       </c>
-      <c r="B683" t="inlineStr">
+      <c r="B682" t="inlineStr">
         <is>
           <t>images/「もし両者が人間のように鎧で武装して戦_img1.jpg,images/「もし両者が人間のように鎧で武装して戦_img2.jpg</t>
         </is>
       </c>
-      <c r="C683" t="inlineStr">
+      <c r="C682" t="inlineStr">
         <is>
           <t>手書き語学 ,アラビア語 ,猫</t>
         </is>
       </c>
     </row>
-    <row r="684">
-      <c r="A684" t="inlineStr">
+    <row r="683">
+      <c r="A683" t="inlineStr">
         <is>
           <t xml:space="preserve">「全ては結びついている」
 كل شيء مترابط
@@ -14829,19 +14808,19 @@
 2308 Ahmed Madyan https://twitter.com/madyco22/status/1451990828298166273 </t>
         </is>
       </c>
-      <c r="B684" t="inlineStr">
+      <c r="B683" t="inlineStr">
         <is>
           <t>images/「全ては結びついている」_img1.jpg</t>
         </is>
       </c>
-      <c r="C684" t="inlineStr">
+      <c r="C683" t="inlineStr">
         <is>
           <t>一筆書き ,デザイン</t>
         </is>
       </c>
     </row>
-    <row r="685">
-      <c r="A685" t="inlineStr">
+    <row r="684">
+      <c r="A684" t="inlineStr">
         <is>
           <t xml:space="preserve">「初心者のためのスケッチトレーニング」
 تعليم الرسم للمبتدئين
@@ -14851,19 +14830,19 @@
 2308 free-bookspdf com </t>
         </is>
       </c>
-      <c r="B685" t="inlineStr">
+      <c r="B684" t="inlineStr">
         <is>
           <t>images/「初心者のためのスケッチトレーニング」_img1.jpg</t>
         </is>
       </c>
-      <c r="C685" t="inlineStr">
+      <c r="C684" t="inlineStr">
         <is>
           <t>イラスト ,絵</t>
         </is>
       </c>
     </row>
-    <row r="686">
-      <c r="A686" t="inlineStr">
+    <row r="685">
+      <c r="A685" t="inlineStr">
         <is>
           <t xml:space="preserve">「初心者のためのスルス体書道トレーニング」
 تعليم خط الثلث للمبتدئين
@@ -14873,19 +14852,19 @@
 2308 出典不明 </t>
         </is>
       </c>
-      <c r="B686" t="inlineStr">
+      <c r="B685" t="inlineStr">
         <is>
           <t>images/「初心者のためのスルス体書道トレーニン_img1.jpg</t>
         </is>
       </c>
-      <c r="C686" t="inlineStr">
+      <c r="C685" t="inlineStr">
         <is>
           <t>書道</t>
         </is>
       </c>
     </row>
-    <row r="687">
-      <c r="A687" t="inlineStr">
+    <row r="686">
+      <c r="A686" t="inlineStr">
         <is>
           <t xml:space="preserve">「笑顔でいなさい」خليك مبتسم
 カッリーク・ムブタスィム [Khallii-k mubtasim]
@@ -14894,19 +14873,19 @@
 2308 https://tmblr.co/Zj9tguYLXBvC </t>
         </is>
       </c>
-      <c r="B687" t="inlineStr">
+      <c r="B686" t="inlineStr">
         <is>
           <t>images/「笑顔でいなさい」_img1.jpg</t>
         </is>
       </c>
-      <c r="C687" t="inlineStr">
+      <c r="C686" t="inlineStr">
         <is>
           <t>スマイル ,名言</t>
         </is>
       </c>
     </row>
-    <row r="688">
-      <c r="A688" t="inlineStr">
+    <row r="687">
+      <c r="A687" t="inlineStr">
         <is>
           <t xml:space="preserve">自動車メーカー
 ⁦・「TOYOTA」( تويوتا )⁩
@@ -14918,19 +14897,19 @@
 2308 syarah com </t>
         </is>
       </c>
-      <c r="B688" t="inlineStr">
+      <c r="B687" t="inlineStr">
         <is>
           <t>images/自動車メーカー_img1.jpg,images/自動車メーカー_img2.jpg,images/自動車メーカー_img3.jpg,images/自動車メーカー_img4.jpg</t>
         </is>
       </c>
-      <c r="C688" t="inlineStr">
+      <c r="C687" t="inlineStr">
         <is>
           <t>日本車 ,韓国車</t>
         </is>
       </c>
     </row>
-    <row r="689">
-      <c r="A689" t="inlineStr">
+    <row r="688">
+      <c r="A688" t="inlineStr">
         <is>
           <t xml:space="preserve">「僕たちは協力して不可能を達成するよ」
 بالتعاون نحقق المحال
@@ -14940,19 +14919,19 @@
 2109 </t>
         </is>
       </c>
-      <c r="B689" t="inlineStr">
+      <c r="B688" t="inlineStr">
         <is>
           <t>images/「僕たちは協力して不可能を達成するよ」_img1.jpg</t>
         </is>
       </c>
-      <c r="C689" t="inlineStr">
+      <c r="C688" t="inlineStr">
         <is>
           <t>無理 ,ハム太郎</t>
         </is>
       </c>
     </row>
-    <row r="690">
-      <c r="A690" t="inlineStr">
+    <row r="689">
+      <c r="A689" t="inlineStr">
         <is>
           <t xml:space="preserve">「幸せは伝染性。喜びを広めよう」
 السعادة معدية فأشع الفرح
@@ -14962,19 +14941,19 @@
 2511 instagram　com/p/fVEfxEo7Va/ </t>
         </is>
       </c>
-      <c r="B690" t="inlineStr">
+      <c r="B689" t="inlineStr">
         <is>
           <t>images/「幸せは伝染性。喜びを広めよう」_img1.jpg</t>
         </is>
       </c>
-      <c r="C690" t="inlineStr">
+      <c r="C689" t="inlineStr">
         <is>
           <t>拡散希望</t>
         </is>
       </c>
     </row>
-    <row r="691">
-      <c r="A691" t="inlineStr">
+    <row r="690">
+      <c r="A690" t="inlineStr">
         <is>
           <t xml:space="preserve">「ストレスは人間だけのものではない」
 الشعور بالتوتر ليس حكرًا على البشر
@@ -14982,19 +14961,19 @@
 2408 https://x.com/NatGeoMagArab/status/1736755816911487420 </t>
         </is>
       </c>
-      <c r="B691" t="inlineStr">
+      <c r="B690" t="inlineStr">
         <is>
           <t>images/「ストレスは人間だけのものではない」_img1.jpg</t>
         </is>
       </c>
-      <c r="C691" t="inlineStr">
+      <c r="C690" t="inlineStr">
         <is>
           <t>手書き語学 ,アラビア語 ,ストレス</t>
         </is>
       </c>
     </row>
-    <row r="692">
-      <c r="A692" t="inlineStr">
+    <row r="691">
+      <c r="A691" t="inlineStr">
         <is>
           <t xml:space="preserve">「私達は出来ます！」
 نستطيع فعلها
@@ -15004,19 +14983,19 @@
 2308 NAHARBAHIJ com </t>
         </is>
       </c>
-      <c r="B692" t="inlineStr">
+      <c r="B691" t="inlineStr">
         <is>
           <t>images/「私達は出来ます！」_img1.jpg</t>
         </is>
       </c>
-      <c r="C692" t="inlineStr">
+      <c r="C691" t="inlineStr">
         <is>
           <t>女性 ,パロディ</t>
         </is>
       </c>
     </row>
-    <row r="693">
-      <c r="A693" t="inlineStr">
+    <row r="692">
+      <c r="A692" t="inlineStr">
         <is>
           <t xml:space="preserve">「全然分からん」ولا فاهم إشي
 ウラー・ファーヒム・イシ [w-laa faahim 'iShy]
@@ -15026,19 +15005,19 @@
 2209 出典不明 </t>
         </is>
       </c>
-      <c r="B693" t="inlineStr">
+      <c r="B692" t="inlineStr">
         <is>
           <t>images/「全然分からん」_img1.jpg</t>
         </is>
       </c>
-      <c r="C693" t="inlineStr">
+      <c r="C692" t="inlineStr">
         <is>
           <t>アラビア語</t>
         </is>
       </c>
     </row>
-    <row r="694">
-      <c r="A694" t="inlineStr">
+    <row r="693">
+      <c r="A693" t="inlineStr">
         <is>
           <t xml:space="preserve">「人間は一人ひとり、特別な才がある。だから自分を他人と比べるのはやめよう」
 لكل إنسان مواهبه الخاصة 
@@ -15047,19 +15026,19 @@
 1812 Gwid3 </t>
         </is>
       </c>
-      <c r="B694" t="inlineStr">
+      <c r="B693" t="inlineStr">
         <is>
           <t>images/「人間は一人ひとり、特別な才がある。だ_img1.jpg</t>
         </is>
       </c>
-      <c r="C694" t="inlineStr">
+      <c r="C693" t="inlineStr">
         <is>
           <t>自尊 ,プライド</t>
         </is>
       </c>
     </row>
-    <row r="695">
-      <c r="A695" t="inlineStr">
+    <row r="694">
+      <c r="A694" t="inlineStr">
         <is>
           <t xml:space="preserve">「デザイン」تَصْمِيمٌ
 タスミーム [ta_smiim(un)]
@@ -15067,19 +15046,19 @@
 1903 arabictypography com </t>
         </is>
       </c>
-      <c r="B695" t="inlineStr">
+      <c r="B694" t="inlineStr">
         <is>
           <t>images/「デザイン」_img1.jpg</t>
         </is>
       </c>
-      <c r="C695" t="inlineStr">
+      <c r="C694" t="inlineStr">
         <is>
           <t>文字 ,タイポグラフィー</t>
         </is>
       </c>
     </row>
-    <row r="696">
-      <c r="A696" t="inlineStr">
+    <row r="695">
+      <c r="A695" t="inlineStr">
         <is>
           <t xml:space="preserve">「この猫は食事をシェアするのが嫌い！」
 هذه القطة لا تحب مشاركة الطعام
@@ -15088,19 +15067,19 @@
 2605 facebook com/alahram/videos/2154923608133231/ </t>
         </is>
       </c>
-      <c r="B696" t="inlineStr">
+      <c r="B695" t="inlineStr">
         <is>
           <t>images/「この猫は食事をシェアするのが嫌い！」_img1.jpg</t>
         </is>
       </c>
-      <c r="C696" t="inlineStr">
+      <c r="C695" t="inlineStr">
         <is>
           <t>猫 ,ネコ</t>
         </is>
       </c>
     </row>
-    <row r="697">
-      <c r="A697" t="inlineStr">
+    <row r="696">
+      <c r="A696" t="inlineStr">
         <is>
           <t xml:space="preserve">「怪獣との戦いでは自分が怪獣化せぬよう警戒しなさい」
 احذر عند محاربة الوحوش ألا تصبح واحدا منهم
@@ -15110,19 +15089,19 @@
 2108 warag-3nb.tumblr </t>
         </is>
       </c>
-      <c r="B697" t="inlineStr">
+      <c r="B696" t="inlineStr">
         <is>
           <t>images/「怪獣との戦いでは自分が怪獣化せぬよう_img1.jpg,images/ 「怪獣との戦いでは自分が怪獣化せぬよう_img2.jpg</t>
         </is>
       </c>
-      <c r="C697" t="inlineStr">
+      <c r="C696" t="inlineStr">
         <is>
           <t>正気 ,モンスター</t>
         </is>
       </c>
     </row>
-    <row r="698">
-      <c r="A698" t="inlineStr">
+    <row r="697">
+      <c r="A697" t="inlineStr">
         <is>
           <t xml:space="preserve">「錯視アート」فن الخداع البصري
 ファンヌ_ルヒダーイ_ルバサリーイ [fannu l-Khidaa*i l-ba_sariyy]
@@ -15131,19 +15110,19 @@
 2409 https://online.pubhtml5.com/idtb/neft/ </t>
         </is>
       </c>
-      <c r="B698" t="inlineStr">
+      <c r="B697" t="inlineStr">
         <is>
           <t>images/「錯視アート」_img1.jpg</t>
         </is>
       </c>
-      <c r="C698" t="inlineStr">
+      <c r="C697" t="inlineStr">
         <is>
           <t>トリックアート</t>
         </is>
       </c>
     </row>
-    <row r="699">
-      <c r="A699" t="inlineStr">
+    <row r="698">
+      <c r="A698" t="inlineStr">
         <is>
           <t xml:space="preserve">「自然界の消防士の訓練」
 تدريبات رجال الإطفاء في الطبيعة
@@ -15151,19 +15130,19 @@
 2308 https://twitter.com/NatGeoMagArab/status/1462420543890608129 </t>
         </is>
       </c>
-      <c r="B699" t="inlineStr">
+      <c r="B698" t="inlineStr">
         <is>
           <t>images/「自然界の消防士の訓練」_img1.jpg,images/ 「自然界の消防士の訓練」_img2.jpg</t>
         </is>
       </c>
-      <c r="C699" t="inlineStr">
+      <c r="C698" t="inlineStr">
         <is>
           <t>手書き語学 ,アラビア語 ,ヒグマ</t>
         </is>
       </c>
     </row>
-    <row r="700">
-      <c r="A700" t="inlineStr">
+    <row r="699">
+      <c r="A699" t="inlineStr">
         <is>
           <t xml:space="preserve">「救助」إسعاف
 イスアーフ ['is*aaf]
@@ -15172,19 +15151,19 @@
 2109 ambulance gov ae </t>
         </is>
       </c>
-      <c r="B700" t="inlineStr">
+      <c r="B699" t="inlineStr">
         <is>
           <t>images/「救助」_img1.jpg</t>
         </is>
       </c>
-      <c r="C700" t="inlineStr">
+      <c r="C699" t="inlineStr">
         <is>
           <t>救急車 ,はたらくくるま</t>
         </is>
       </c>
     </row>
-    <row r="701">
-      <c r="A701" t="inlineStr">
+    <row r="700">
+      <c r="A700" t="inlineStr">
         <is>
           <t xml:space="preserve">「感情／感覚」الإحْسَاسْ
 アルイヒサース [al-'iHsaas]
@@ -15193,19 +15172,19 @@
 2308 iN49R </t>
         </is>
       </c>
-      <c r="B701" t="inlineStr">
+      <c r="B700" t="inlineStr">
         <is>
           <t>images/「感情／感覚」_img1.jpg</t>
         </is>
       </c>
-      <c r="C701" t="inlineStr">
+      <c r="C700" t="inlineStr">
         <is>
           <t>オフ ,一休み</t>
         </is>
       </c>
     </row>
-    <row r="702">
-      <c r="A702" t="inlineStr">
+    <row r="701">
+      <c r="A701" t="inlineStr">
         <is>
           <t xml:space="preserve">「ひらめき」إلهام
 イルハーム ['lhaam]
@@ -15217,19 +15196,19 @@
 2103 出典不明 </t>
         </is>
       </c>
-      <c r="B702" t="inlineStr">
+      <c r="B701" t="inlineStr">
         <is>
           <t>images/「ひらめき」_img1.jpg</t>
         </is>
       </c>
-      <c r="C702" t="inlineStr">
+      <c r="C701" t="inlineStr">
         <is>
           <t>アラビア語</t>
         </is>
       </c>
     </row>
-    <row r="703">
-      <c r="A703" t="inlineStr">
+    <row r="702">
+      <c r="A702" t="inlineStr">
         <is>
           <t xml:space="preserve">「Ibdaa／クリエイティビティ」
 إبداع
@@ -15238,19 +15217,19 @@
 2308 Ibdaa Design &amp; Decoration Office </t>
         </is>
       </c>
-      <c r="B703" t="inlineStr">
+      <c r="B702" t="inlineStr">
         <is>
           <t>images/「Ibdaa／クリエイティビティ」_img1.jpg</t>
         </is>
       </c>
-      <c r="C703" t="inlineStr">
+      <c r="C702" t="inlineStr">
         <is>
           <t>創造性 ,独自性</t>
         </is>
       </c>
     </row>
-    <row r="704">
-      <c r="A704" t="inlineStr">
+    <row r="703">
+      <c r="A703" t="inlineStr">
         <is>
           <t xml:space="preserve">「奮闘なくして進歩なし」
 بدون كفاح لايوجد تقدم
@@ -15260,19 +15239,19 @@
 2105 ROUYMS TUMBLR COM </t>
         </is>
       </c>
-      <c r="B704" t="inlineStr">
+      <c r="B703" t="inlineStr">
         <is>
           <t>images/「奮闘なくして進歩なし」_img1.jpg</t>
         </is>
       </c>
-      <c r="C704" t="inlineStr">
+      <c r="C703" t="inlineStr">
         <is>
           <t>努力 ,三角形</t>
         </is>
       </c>
     </row>
-    <row r="705">
-      <c r="A705" t="inlineStr">
+    <row r="704">
+      <c r="A704" t="inlineStr">
         <is>
           <t xml:space="preserve">「木に登れば熊の危険を避けられるとお考えなら、考え直しましょう！」 
 إن اعتقدت أنك بمنأى عن خطر الدب عند تسلق الأشجار.. راجع حساباتك
@@ -15280,19 +15259,19 @@
 2202 NatGeoMagArab </t>
         </is>
       </c>
-      <c r="B705" t="inlineStr">
+      <c r="B704" t="inlineStr">
         <is>
           <t>images/「木に登れば熊の危険を避けられるとお考.jpeg</t>
         </is>
       </c>
-      <c r="C705" t="inlineStr">
+      <c r="C704" t="inlineStr">
         <is>
           <t>クマ</t>
         </is>
       </c>
     </row>
-    <row r="706">
-      <c r="A706" t="inlineStr">
+    <row r="705">
+      <c r="A705" t="inlineStr">
         <is>
           <t xml:space="preserve">「卒業おめでとう」مبروك التخرج
 マブルーク・タカッルジ [mabruuk a^taKharruj]
@@ -15301,19 +15280,19 @@
 2308 https://instagram.com/fatoomworld </t>
         </is>
       </c>
-      <c r="B706" t="inlineStr">
+      <c r="B705" t="inlineStr">
         <is>
           <t>images/「卒業おめでとう」_img1.jpg</t>
         </is>
       </c>
-      <c r="C706" t="inlineStr">
+      <c r="C705" t="inlineStr">
         <is>
           <t>卒業 ,イラスト</t>
         </is>
       </c>
     </row>
-    <row r="707">
-      <c r="A707" t="inlineStr">
+    <row r="706">
+      <c r="A706" t="inlineStr">
         <is>
           <t xml:space="preserve">「停止距離の計算」
 حساب مسافة التوقف
@@ -15323,19 +15302,19 @@
 2109 assurance-auto-info </t>
         </is>
       </c>
-      <c r="B707" t="inlineStr">
+      <c r="B706" t="inlineStr">
         <is>
           <t>images/「停止距離の計算」_img1.jpg</t>
         </is>
       </c>
-      <c r="C707" t="inlineStr">
+      <c r="C706" t="inlineStr">
         <is>
           <t>保険 ,自動車</t>
         </is>
       </c>
     </row>
-    <row r="708">
-      <c r="A708" t="inlineStr">
+    <row r="707">
+      <c r="A707" t="inlineStr">
         <is>
           <t xml:space="preserve">「教師要らず：10日でフランス語会話」
 بدون معلم
@@ -15345,19 +15324,19 @@
 2308 englais-best com </t>
         </is>
       </c>
-      <c r="B708" t="inlineStr">
+      <c r="B707" t="inlineStr">
         <is>
           <t>images/「教師要らず：10日でフランス語会話」_img1.jpg</t>
         </is>
       </c>
-      <c r="C708" t="inlineStr">
+      <c r="C707" t="inlineStr">
         <is>
           <t>教師なし学習</t>
         </is>
       </c>
     </row>
-    <row r="709">
-      <c r="A709" t="inlineStr">
+    <row r="708">
+      <c r="A708" t="inlineStr">
         <is>
           <t xml:space="preserve">「衝突」تصادم
 タサードゥム [ta_saadum]
@@ -15366,19 +15345,19 @@
 1810 </t>
         </is>
       </c>
-      <c r="B709" t="inlineStr">
+      <c r="B708" t="inlineStr">
         <is>
           <t>images/「衝突」_img1.jpg</t>
         </is>
       </c>
-      <c r="C709" t="inlineStr">
+      <c r="C708" t="inlineStr">
         <is>
           <t>あらびあや</t>
         </is>
       </c>
     </row>
-    <row r="710">
-      <c r="A710" t="inlineStr">
+    <row r="709">
+      <c r="A709" t="inlineStr">
         <is>
           <t xml:space="preserve">「楽観主義」تَفَاؤُلٌ
 タファーウル [tafaa'ul(un)]
@@ -15387,19 +15366,19 @@
 1904 arabictypography com </t>
         </is>
       </c>
-      <c r="B710" t="inlineStr">
+      <c r="B709" t="inlineStr">
         <is>
           <t>images/「楽観主義」_img1.jpg</t>
         </is>
       </c>
-      <c r="C710" t="inlineStr">
+      <c r="C709" t="inlineStr">
         <is>
           <t>やわらか ,緑</t>
         </is>
       </c>
     </row>
-    <row r="711">
-      <c r="A711" t="inlineStr">
+    <row r="710">
+      <c r="A710" t="inlineStr">
         <is>
           <t xml:space="preserve">「シベリアジャコウジカは、絶滅の危機にあると見なされている」
 يعد "أيل المسك السيبيري" مهددًا بالانقراض
@@ -15407,19 +15386,19 @@
 2308 https://twitter.com/NatGeoMagArab/status/1320666649045790720 </t>
         </is>
       </c>
-      <c r="B711" t="inlineStr">
+      <c r="B710" t="inlineStr">
         <is>
           <t>images/「シベリアジャコウジカは、絶滅の危機に_img1.jpg,images/「シベリアジャコウジカは、絶滅の危機に_img2.jpg</t>
         </is>
       </c>
-      <c r="C711" t="inlineStr">
+      <c r="C710" t="inlineStr">
         <is>
           <t>手書き語学 ,シベリア</t>
         </is>
       </c>
     </row>
-    <row r="712">
-      <c r="A712" t="inlineStr">
+    <row r="711">
+      <c r="A711" t="inlineStr">
         <is>
           <t xml:space="preserve">「融合／折衷／フュージョン」
 انصهار
@@ -15428,38 +15407,38 @@
 1811 elmahdyart Instagram </t>
         </is>
       </c>
-      <c r="B712" t="inlineStr">
+      <c r="B711" t="inlineStr">
         <is>
           <t>images/「融合／折衷／フュージョン」_img1.jpg</t>
         </is>
       </c>
-      <c r="C712" t="inlineStr">
+      <c r="C711" t="inlineStr">
         <is>
           <t>カリグラフィー ,書道</t>
         </is>
       </c>
     </row>
-    <row r="713">
-      <c r="A713" t="inlineStr">
+    <row r="712">
+      <c r="A712" t="inlineStr">
         <is>
           <t xml:space="preserve">「この子供は、昼寝をしようとする母親を邪魔しているようだ」
 「場所はインドのトラ保護区、バンダウガル公園。トラは生態ピラミッドのトップの捕食動物だが、最もリスクの高い絶滅危惧種のひとつである」
 2308 https://twitter.com/natgeomagarab/status/1553681890665586689 </t>
         </is>
       </c>
-      <c r="B713" t="inlineStr">
+      <c r="B712" t="inlineStr">
         <is>
           <t>images/「この子供は、昼寝をしようとする母親を_img1.jpg,images/「この子供は、昼寝をしようとする母親を_img2.jpg</t>
         </is>
       </c>
-      <c r="C713" t="inlineStr">
+      <c r="C712" t="inlineStr">
         <is>
           <t>手書き語学 ,アラビア語 ,トラ</t>
         </is>
       </c>
     </row>
-    <row r="714">
-      <c r="A714" t="inlineStr">
+    <row r="713">
+      <c r="A713" t="inlineStr">
         <is>
           <t xml:space="preserve">「もし敬意が落ちたら、それと一緒に全部落ちるのだ」
 إن سقط الإحترام سقط معه كل شيء
@@ -15468,19 +15447,19 @@
 2109 出典不明 </t>
         </is>
       </c>
-      <c r="B714" t="inlineStr">
+      <c r="B713" t="inlineStr">
         <is>
           <t>images/「もし敬意が落ちたら、それと一緒に全部_img1.jpg</t>
         </is>
       </c>
-      <c r="C714" t="inlineStr">
+      <c r="C713" t="inlineStr">
         <is>
           <t>リスペクト ,落書き</t>
         </is>
       </c>
     </row>
-    <row r="715">
-      <c r="A715" t="inlineStr">
+    <row r="714">
+      <c r="A714" t="inlineStr">
         <is>
           <t xml:space="preserve">「エジプト特許庁」
 مكتب براءات الاختراع المصرى
@@ -15490,19 +15469,19 @@
 2312 </t>
         </is>
       </c>
-      <c r="B715" t="inlineStr">
+      <c r="B714" t="inlineStr">
         <is>
           <t>images/「エジプト特許庁」_img1.jpg</t>
         </is>
       </c>
-      <c r="C715" t="inlineStr">
+      <c r="C714" t="inlineStr">
         <is>
           <t>patent</t>
         </is>
       </c>
     </row>
-    <row r="716">
-      <c r="A716" t="inlineStr">
+    <row r="715">
+      <c r="A715" t="inlineStr">
         <is>
           <t xml:space="preserve">「選挙」إنتخابات
 インティカーバート [intiKhaabaat]
@@ -15511,19 +15490,19 @@
 2311 nna-leb gov lb </t>
         </is>
       </c>
-      <c r="B716" t="inlineStr">
+      <c r="B715" t="inlineStr">
         <is>
           <t>images/「選挙」_img1.jpg</t>
         </is>
       </c>
-      <c r="C716" t="inlineStr">
+      <c r="C715" t="inlineStr">
         <is>
           <t>選挙 ,投票</t>
         </is>
       </c>
     </row>
-    <row r="717">
-      <c r="A717" t="inlineStr">
+    <row r="716">
+      <c r="A716" t="inlineStr">
         <is>
           <t xml:space="preserve">「待ちぼうけ」إنتظار
 インティザール [inti_Dhaar]
@@ -15532,19 +15511,19 @@
 1809 in4sser.tumblr </t>
         </is>
       </c>
-      <c r="B717" t="inlineStr">
+      <c r="B716" t="inlineStr">
         <is>
           <t>images/「待ちぼうけ」_img1.jpg</t>
         </is>
       </c>
-      <c r="C717" t="inlineStr">
+      <c r="C716" t="inlineStr">
         <is>
           <t>遅すぎ ,辛抱</t>
         </is>
       </c>
     </row>
-    <row r="718">
-      <c r="A718" t="inlineStr">
+    <row r="717">
+      <c r="A717" t="inlineStr">
         <is>
           <t xml:space="preserve">「試験」إختبار
 イクティバール [iKhtibaar]
@@ -15553,19 +15532,19 @@
 2109 出典不明 </t>
         </is>
       </c>
-      <c r="B718" t="inlineStr">
+      <c r="B717" t="inlineStr">
         <is>
           <t>images/「試験」_img1.jpg</t>
         </is>
       </c>
-      <c r="C718" t="inlineStr">
+      <c r="C717" t="inlineStr">
         <is>
           <t>テスト ,考査</t>
         </is>
       </c>
     </row>
-    <row r="719">
-      <c r="A719" t="inlineStr">
+    <row r="718">
+      <c r="A718" t="inlineStr">
         <is>
           <t xml:space="preserve">「チャンネル登録」اشتراك
 イシティラーク [iShtiraak]
@@ -15574,19 +15553,19 @@
 2308 </t>
         </is>
       </c>
-      <c r="B719" t="inlineStr">
+      <c r="B718" t="inlineStr">
         <is>
           <t>images/「チャンネル登録」_img1.jpg</t>
         </is>
       </c>
-      <c r="C719" t="inlineStr">
+      <c r="C718" t="inlineStr">
         <is>
           <t>Subscribe ,YouTube</t>
         </is>
       </c>
     </row>
-    <row r="720">
-      <c r="A720" t="inlineStr">
+    <row r="719">
+      <c r="A719" t="inlineStr">
         <is>
           <t xml:space="preserve">「スマイル」ابتسام
 イブティサーム [ibtisaam]
@@ -15594,37 +15573,37 @@
 1903 behance Written-Visuals </t>
         </is>
       </c>
+      <c r="B719" t="inlineStr">
+        <is>
+          <t>images/「スマイル」_img1.jpg</t>
+        </is>
+      </c>
+      <c r="C719" t="inlineStr">
+        <is>
+          <t>スマイリー ,ツ</t>
+        </is>
+      </c>
+    </row>
+    <row r="720">
+      <c r="A720" t="inlineStr">
+        <is>
+          <t xml:space="preserve">「身体の一部として…」
+2308 https://twitter.com/NatGeoMagArab/status/1528292080337813504 </t>
+        </is>
+      </c>
       <c r="B720" t="inlineStr">
         <is>
-          <t>images/「スマイル」_img1.jpg</t>
+          <t>images/「身体の一部として…」_img1.jpg</t>
         </is>
       </c>
       <c r="C720" t="inlineStr">
         <is>
-          <t>スマイリー ,ツ</t>
+          <t>手書き語学 ,カンガルー</t>
         </is>
       </c>
     </row>
     <row r="721">
       <c r="A721" t="inlineStr">
-        <is>
-          <t xml:space="preserve">「身体の一部として…」
-2308 https://twitter.com/NatGeoMagArab/status/1528292080337813504 </t>
-        </is>
-      </c>
-      <c r="B721" t="inlineStr">
-        <is>
-          <t>images/「身体の一部として…」_img1.jpg</t>
-        </is>
-      </c>
-      <c r="C721" t="inlineStr">
-        <is>
-          <t>手書き語学 ,カンガルー</t>
-        </is>
-      </c>
-    </row>
-    <row r="722">
-      <c r="A722" t="inlineStr">
         <is>
           <t xml:space="preserve">「ディスカバリー」إكتشاف
 イクティシャーフ [iktiShaaf]
@@ -15632,19 +15611,19 @@
 2308 tephanegabrielli com </t>
         </is>
       </c>
-      <c r="B722" t="inlineStr">
+      <c r="B721" t="inlineStr">
         <is>
           <t>images/「ディスカバリー」_img1.jpg</t>
         </is>
       </c>
-      <c r="C722" t="inlineStr">
+      <c r="C721" t="inlineStr">
         <is>
           <t>discovery ,デザイン</t>
         </is>
       </c>
     </row>
-    <row r="723">
-      <c r="A723" t="inlineStr">
+    <row r="722">
+      <c r="A722" t="inlineStr">
         <is>
           <t xml:space="preserve">「重力波の発見は新しい窓を開いた」
 فتَح اكتشاف موجات الجاذبية نافذة جديدة
@@ -15652,19 +15631,19 @@
 2308 https://twitter.com/SciTalk2U/status/1454891943440289793 </t>
         </is>
       </c>
-      <c r="B723" t="inlineStr">
+      <c r="B722" t="inlineStr">
         <is>
           <t>images/「重力波の発見は新しい窓を開いた」_img1.jpg</t>
         </is>
       </c>
-      <c r="C723" t="inlineStr">
+      <c r="C722" t="inlineStr">
         <is>
           <t>手書き語学 ,アラビア語 ,重力波</t>
         </is>
       </c>
     </row>
-    <row r="724">
-      <c r="A724" t="inlineStr">
+    <row r="723">
+      <c r="A723" t="inlineStr">
         <is>
           <t xml:space="preserve">「微笑みに微笑み。先にした人の方が美しい」
 الإبتسامة بالإبتسامة والبادئ أجمل
@@ -15673,19 +15652,19 @@
 2104 出典不明 </t>
         </is>
       </c>
-      <c r="B724" t="inlineStr">
+      <c r="B723" t="inlineStr">
         <is>
           <t>images/「微笑みに微笑み。先にした人の方が美し_img1.jpg,images/「微笑みに微笑み。先にした人の方が美し_img2.jpg</t>
         </is>
       </c>
-      <c r="C724" t="inlineStr">
+      <c r="C723" t="inlineStr">
         <is>
           <t>スマイル ,名言</t>
         </is>
       </c>
     </row>
-    <row r="725">
-      <c r="A725" t="inlineStr">
+    <row r="724">
+      <c r="A724" t="inlineStr">
         <is>
           <t xml:space="preserve">「笑顔」ابتسامة
 イブティサーマ [ibtisaama(tun)]
@@ -15694,19 +15673,19 @@
 2308 satokomatsu, minne </t>
         </is>
       </c>
-      <c r="B725" t="inlineStr">
+      <c r="B724" t="inlineStr">
         <is>
           <t>images/「笑顔」_img1.jpg</t>
         </is>
       </c>
-      <c r="C725" t="inlineStr">
+      <c r="C724" t="inlineStr">
         <is>
           <t>スマイル ,ツ</t>
         </is>
       </c>
     </row>
-    <row r="726">
-      <c r="A726" t="inlineStr">
+    <row r="725">
+      <c r="A725" t="inlineStr">
         <is>
           <t xml:space="preserve">「信仰」ايمان
 イーマーン ['iimaan]
@@ -15715,19 +15694,19 @@
 2506 instagram com/p/6ST-WHOOkJ/ </t>
         </is>
       </c>
-      <c r="B726" t="inlineStr">
+      <c r="B725" t="inlineStr">
         <is>
           <t>images/「信仰」_img1.jpg</t>
         </is>
       </c>
-      <c r="C726" t="inlineStr">
+      <c r="C725" t="inlineStr">
         <is>
           <t>宗教 ,信念</t>
         </is>
       </c>
     </row>
-    <row r="727">
-      <c r="A727" t="inlineStr">
+    <row r="726">
+      <c r="A726" t="inlineStr">
         <is>
           <t xml:space="preserve">「放送」إذاعة
 イザーア ['iDhaa*a]
@@ -15736,19 +15715,19 @@
 2404 heemades, Instagram </t>
         </is>
       </c>
-      <c r="B727" t="inlineStr">
+      <c r="B726" t="inlineStr">
         <is>
           <t>images/「放送」_img1.jpg</t>
         </is>
       </c>
-      <c r="C727" t="inlineStr">
+      <c r="C726" t="inlineStr">
         <is>
           <t>デザイン ,ラジオ</t>
         </is>
       </c>
     </row>
-    <row r="728">
-      <c r="A728" t="inlineStr">
+    <row r="727">
+      <c r="A727" t="inlineStr">
         <is>
           <t xml:space="preserve">「かきとりのちから」
 مهاراتي الإملائية
@@ -15757,19 +15736,19 @@
 2308 iqrawaoktoub.wordpress com </t>
         </is>
       </c>
-      <c r="B728" t="inlineStr">
+      <c r="B727" t="inlineStr">
         <is>
           <t>images/「かきとりのちから」_img1.jpg</t>
         </is>
       </c>
-      <c r="C728" t="inlineStr">
+      <c r="C727" t="inlineStr">
         <is>
           <t>国語 ,教材</t>
         </is>
       </c>
     </row>
-    <row r="729">
-      <c r="A729" t="inlineStr">
+    <row r="728">
+      <c r="A728" t="inlineStr">
         <is>
           <t xml:space="preserve">「歴史を作った男たち」
 رجال صنعوا التاريخ
@@ -15779,38 +15758,38 @@
 2410 https://x.gd/Wl5rJ </t>
         </is>
       </c>
-      <c r="B729" t="inlineStr">
+      <c r="B728" t="inlineStr">
         <is>
           <t>images/「歴史を作った男たち」_img1.jpg</t>
         </is>
       </c>
-      <c r="C729" t="inlineStr">
+      <c r="C728" t="inlineStr">
         <is>
           <t>偉人</t>
         </is>
       </c>
     </row>
-    <row r="730">
-      <c r="A730" t="inlineStr">
+    <row r="729">
+      <c r="A729" t="inlineStr">
         <is>
           <t xml:space="preserve">「無限の宇宙を旅した光」
 「何百年もの末にジェイムズ・ウェッブ望遠鏡のレンズの上に落ち、我々に遠い宇宙の美しさを見せてくれる。最も純粋な形と最も素晴らしい姿で」
 2308 https://twitter.com/NatGeoMagArab/status/1557811592636485632 </t>
         </is>
       </c>
-      <c r="B730" t="inlineStr">
+      <c r="B729" t="inlineStr">
         <is>
           <t>images/「無限の宇宙を旅した光」_img1.jpg</t>
         </is>
       </c>
-      <c r="C730" t="inlineStr">
+      <c r="C729" t="inlineStr">
         <is>
           <t>手書き語学 ,宇宙</t>
         </is>
       </c>
     </row>
-    <row r="731">
-      <c r="A731" t="inlineStr">
+    <row r="730">
+      <c r="A730" t="inlineStr">
         <is>
           <t xml:space="preserve">「日本好きになり行きたくなる20項」
 عشرون شيئا يجعلك تحب اليابان وترغب في زيارتها
@@ -15819,19 +15798,19 @@
 2308 wattpad </t>
         </is>
       </c>
-      <c r="B731" t="inlineStr">
+      <c r="B730" t="inlineStr">
         <is>
           <t>images/「日本好きになり行きたくなる20項」_img1.jpg</t>
         </is>
       </c>
-      <c r="C731" t="inlineStr">
+      <c r="C730" t="inlineStr">
         <is>
           <t>اليابان ,Japan</t>
         </is>
       </c>
     </row>
-    <row r="732">
-      <c r="A732" t="inlineStr">
+    <row r="731">
+      <c r="A731" t="inlineStr">
         <is>
           <t xml:space="preserve">「ピッタリの瞬間に撮影され、ドラゴンが火を噴いているように見える」
 التُقطت في اللحظة المناسبة لتبدو مثل تنين ينفث اللهب
@@ -15839,19 +15818,19 @@
 2509 https://twitter.com/NatGeoMagArab/status/1588780660269150208 </t>
         </is>
       </c>
-      <c r="B732" t="inlineStr">
+      <c r="B731" t="inlineStr">
         <is>
           <t>images/「ピッタリの瞬間に撮影され、ドラゴンが_img1.jpg,images/ 「ピッタリの瞬間に撮影され、ドラゴンが_img2.jpg</t>
         </is>
       </c>
-      <c r="C732" t="inlineStr">
+      <c r="C731" t="inlineStr">
         <is>
           <t xml:space="preserve">ドラゴン </t>
         </is>
       </c>
     </row>
-    <row r="733">
-      <c r="A733" t="inlineStr">
+    <row r="732">
+      <c r="A732" t="inlineStr">
         <is>
           <t xml:space="preserve">「満足は不滅の宝である」
 القَناعَةُ كنز لا يَفنَى
@@ -15861,55 +15840,55 @@
 2308 kareem mrghani </t>
         </is>
       </c>
+      <c r="B732" t="inlineStr">
+        <is>
+          <t>images/「満足は不滅の宝である」_img1.jpg</t>
+        </is>
+      </c>
+      <c r="C732" t="inlineStr">
+        <is>
+          <t>幸福度</t>
+        </is>
+      </c>
+    </row>
+    <row r="733">
+      <c r="A733" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ゴシキセイガイインコ。
+2409 https://twitter.com/NatGeoMagArab/status/1600022262014676992 </t>
+        </is>
+      </c>
       <c r="B733" t="inlineStr">
         <is>
-          <t>images/「満足は不滅の宝である」_img1.jpg</t>
+          <t>images/ゴシキセイガイインコ。_img1.jpg</t>
         </is>
       </c>
       <c r="C733" t="inlineStr">
         <is>
-          <t>幸福度</t>
+          <t>手書き語学 ,アラビア語,オウム</t>
         </is>
       </c>
     </row>
     <row r="734">
       <c r="A734" t="inlineStr">
         <is>
-          <t xml:space="preserve">ゴシキセイガイインコ。
-2409 https://twitter.com/NatGeoMagArab/status/1600022262014676992 </t>
+          <t xml:space="preserve">モモンガ。
+2403 https://twitter.com/NatGeoMagArab/status/1552541872966344704 </t>
         </is>
       </c>
       <c r="B734" t="inlineStr">
         <is>
-          <t>images/ゴシキセイガイインコ。_img1.jpg</t>
+          <t>images/モモンガ。_img1.jpg,images/ モモンガ。_img2.jpg</t>
         </is>
       </c>
       <c r="C734" t="inlineStr">
         <is>
-          <t>手書き語学 ,アラビア語,オウム</t>
+          <t>手書き語学 ,アラビア語 ,モモンガ</t>
         </is>
       </c>
     </row>
     <row r="735">
       <c r="A735" t="inlineStr">
-        <is>
-          <t xml:space="preserve">モモンガ。
-2403 https://twitter.com/NatGeoMagArab/status/1552541872966344704 </t>
-        </is>
-      </c>
-      <c r="B735" t="inlineStr">
-        <is>
-          <t>images/モモンガ。_img1.jpg,images/ モモンガ。_img2.jpg</t>
-        </is>
-      </c>
-      <c r="C735" t="inlineStr">
-        <is>
-          <t>手書き語学 ,アラビア語 ,モモンガ</t>
-        </is>
-      </c>
-    </row>
-    <row r="736">
-      <c r="A736" t="inlineStr">
         <is>
           <t xml:space="preserve">「象の群れ。ドローンの音から逃げている」
 قطيع من الفيلة يفر هاربًا من صوت الدرون
@@ -15921,56 +15900,56 @@
 2009 https://twitter.com/NatGeoMagArab/status/1302970033627258881 </t>
         </is>
       </c>
+      <c r="B735" t="inlineStr">
+        <is>
+          <t>images/「象の群れ。ドローンの音から逃げている.jpg</t>
+        </is>
+      </c>
+      <c r="C735" t="inlineStr">
+        <is>
+          <t>ゾウ ,ドローン</t>
+        </is>
+      </c>
+    </row>
+    <row r="736">
+      <c r="A736" t="inlineStr">
+        <is>
+          <t xml:space="preserve">カルマン線。
+2308 https://twitter.com/NatGeoMagArab/status/1536436999522881536 </t>
+        </is>
+      </c>
       <c r="B736" t="inlineStr">
         <is>
-          <t>images/「象の群れ。ドローンの音から逃げている.jpg</t>
+          <t>images/カルマン線。_img1.jpg</t>
         </is>
       </c>
       <c r="C736" t="inlineStr">
         <is>
-          <t>ゾウ ,ドローン</t>
+          <t xml:space="preserve">手書き語学 ,アラビア語 ,宇宙 </t>
         </is>
       </c>
     </row>
     <row r="737">
       <c r="A737" t="inlineStr">
-        <is>
-          <t xml:space="preserve">カルマン線。
-2308 https://twitter.com/NatGeoMagArab/status/1536436999522881536 </t>
-        </is>
-      </c>
-      <c r="B737" t="inlineStr">
-        <is>
-          <t>images/カルマン線。_img1.jpg</t>
-        </is>
-      </c>
-      <c r="C737" t="inlineStr">
-        <is>
-          <t xml:space="preserve">手書き語学 ,アラビア語 ,宇宙 </t>
-        </is>
-      </c>
-    </row>
-    <row r="738">
-      <c r="A738" t="inlineStr">
         <is>
           <t xml:space="preserve">「恥ずかしがり屋のマヌルネコと暖かい朝の太陽光線」
 ⁦「二つの美しいもの」[Shay'-ayni jamiil-ayni] 属格：「物」( شيء )[Shay']・「美しい」( جميل )[jamiil]⁩
 2309 https://twitter.com/NatGeoMagArab/status/1697512148820504912 </t>
         </is>
       </c>
-      <c r="B738" t="inlineStr">
+      <c r="B737" t="inlineStr">
         <is>
           <t>images/「恥ずかしがり屋のマヌルネコと暖かい朝_img1.jpg</t>
         </is>
       </c>
-      <c r="C738" t="inlineStr">
+      <c r="C737" t="inlineStr">
         <is>
           <t>手書き語学 ,アラビア語 ,マヌルネコ</t>
         </is>
       </c>
     </row>
-    <row r="739">
-      <c r="A739" t="inlineStr">
+    <row r="738">
+      <c r="A738" t="inlineStr">
         <is>
           <t xml:space="preserve">「二回失敗しているペンギン」
 بطريق يفشل مرتين
@@ -15980,19 +15959,19 @@
 2308 https://twitter.com/NatGeoMagArab/status/1479483133766426626 </t>
         </is>
       </c>
-      <c r="B739" t="inlineStr">
+      <c r="B738" t="inlineStr">
         <is>
           <t>images/「二回失敗しているペンギン」_img1.jpg</t>
         </is>
       </c>
-      <c r="C739" t="inlineStr">
+      <c r="C738" t="inlineStr">
         <is>
           <t>ペンギン ,動物</t>
         </is>
       </c>
     </row>
-    <row r="740">
-      <c r="A740" t="inlineStr">
+    <row r="739">
+      <c r="A739" t="inlineStr">
         <is>
           <t xml:space="preserve">「2億光年の彼方できらめく炎と光」
 وهج ووميض يتلألأ على بعد 200 مليون سنة ضوئية
@@ -16003,15 +15982,15 @@
 2010 https://twitter.com/NatGeoMagArab/status/1303415502673342464 </t>
         </is>
       </c>
-      <c r="B740" t="inlineStr"/>
-      <c r="C740" t="inlineStr">
+      <c r="B739" t="inlineStr"/>
+      <c r="C739" t="inlineStr">
         <is>
           <t>宇宙 ,銀河</t>
         </is>
       </c>
     </row>
-    <row r="741">
-      <c r="A741" t="inlineStr">
+    <row r="740">
+      <c r="A740" t="inlineStr">
         <is>
           <t xml:space="preserve">「さまよう黒猫」قطة سوداء تجوب
 キッタトゥン・サウダーウ・タジューブ [qi^_tatun sawdaa'u ta-juub]
@@ -16020,19 +15999,19 @@
 2308 https://twitter.com/NatGeoMagArab/status/1532973177453760512 </t>
         </is>
       </c>
-      <c r="B741" t="inlineStr">
+      <c r="B740" t="inlineStr">
         <is>
           <t>images/「さまよう黒猫」_img1.jpg,images/ 「さまよう黒猫」_img2.jpg</t>
         </is>
       </c>
-      <c r="C741" t="inlineStr">
+      <c r="C740" t="inlineStr">
         <is>
           <t xml:space="preserve">手書き語学 ,モロッコ </t>
         </is>
       </c>
     </row>
-    <row r="742">
-      <c r="A742" t="inlineStr">
+    <row r="741">
+      <c r="A741" t="inlineStr">
         <is>
           <t xml:space="preserve">「サイのざらざらした皮を利用して自分の体を掻くネコ」
 قطة تستغل جلد الكركدن الخشن لحك جسدها
@@ -16041,19 +16020,19 @@
 2308 https://twitter.com/NatGeoMagArab/status/1476855740929216517 </t>
         </is>
       </c>
-      <c r="B742" t="inlineStr">
+      <c r="B741" t="inlineStr">
         <is>
           <t>images/「サイのざらざらした皮を利用して自分の_img1.jpg</t>
         </is>
       </c>
-      <c r="C742" t="inlineStr">
+      <c r="C741" t="inlineStr">
         <is>
           <t>サイ ,チェコ</t>
         </is>
       </c>
     </row>
-    <row r="743">
-      <c r="A743" t="inlineStr">
+    <row r="742">
+      <c r="A742" t="inlineStr">
         <is>
           <t xml:space="preserve">「沈まぬ太陽」شمس لا تغيب
 シャムス・ラー・タギーブ [Shams laa ta-Ghiib]
@@ -16062,19 +16041,19 @@
 2308 AHMED ELASSAL </t>
         </is>
       </c>
-      <c r="B743" t="inlineStr">
+      <c r="B742" t="inlineStr">
         <is>
           <t>images/「沈まぬ太陽」_img1.jpg</t>
         </is>
       </c>
-      <c r="C743" t="inlineStr">
+      <c r="C742" t="inlineStr">
         <is>
           <t>帝国 ,白夜</t>
         </is>
       </c>
     </row>
-    <row r="744">
-      <c r="A744" t="inlineStr">
+    <row r="743">
+      <c r="A743" t="inlineStr">
         <is>
           <t xml:space="preserve">「子供に食べさせている忍耐強い母親」
 أم صبورة تطعم صغيرها
@@ -16083,19 +16062,19 @@
 2308 https://twitter.com/natgeomagarab/status/1585572054509957120 </t>
         </is>
       </c>
-      <c r="B744" t="inlineStr">
+      <c r="B743" t="inlineStr">
         <is>
           <t>images/「子供に食べさせている忍耐強い母親」_img1.jpg</t>
         </is>
       </c>
-      <c r="C744" t="inlineStr">
+      <c r="C743" t="inlineStr">
         <is>
           <t>手書き語学 ,アラビア語 ,ミヤコドリ</t>
         </is>
       </c>
     </row>
-    <row r="745">
-      <c r="A745" t="inlineStr">
+    <row r="744">
+      <c r="A744" t="inlineStr">
         <is>
           <t xml:space="preserve">「コーヒーは繰り返さない恋物語」
 القهوة قصة عشق لن تتكرر
@@ -16105,19 +16084,19 @@
 2403 pin it/7tvd8Wc </t>
         </is>
       </c>
-      <c r="B745" t="inlineStr">
+      <c r="B744" t="inlineStr">
         <is>
           <t>images/「コーヒーは繰り返さない恋物語」_img1.jpg</t>
         </is>
       </c>
-      <c r="C745" t="inlineStr">
+      <c r="C744" t="inlineStr">
         <is>
           <t>コーヒー ,名言</t>
         </is>
       </c>
     </row>
-    <row r="746">
-      <c r="A746" t="inlineStr">
+    <row r="745">
+      <c r="A745" t="inlineStr">
         <is>
           <t xml:space="preserve">「星々で飾られた空。魅惑的な色合いで黄昏の美を満たしている」
 سماء مرصعة بالنجوم تضفي لمسة سحرية على جمال الشفق
@@ -16125,19 +16104,19 @@
 2010 https://twitter.com/NatGeoMagArab/status/1303777701975584768 </t>
         </is>
       </c>
-      <c r="B746" t="inlineStr">
+      <c r="B745" t="inlineStr">
         <is>
           <t>images/「星々で飾られた空。魅惑的な色合いで黄.png</t>
         </is>
       </c>
-      <c r="C746" t="inlineStr">
+      <c r="C745" t="inlineStr">
         <is>
           <t>星空 ,宇宙</t>
         </is>
       </c>
     </row>
-    <row r="747">
-      <c r="A747" t="inlineStr">
+    <row r="746">
+      <c r="A746" t="inlineStr">
         <is>
           <t xml:space="preserve">「国際宇宙ステーションからの写真。巨大な台風『ハイシェン（海神）』を映している」
 لقطات من محطة الفضاء الدولية تظهر إعصار "هايشن" الهائل
@@ -16145,19 +16124,19 @@
 2403 https://twitter.com/NatGeoMagArab/status/1302871968522235904 </t>
         </is>
       </c>
-      <c r="B747" t="inlineStr">
+      <c r="B746" t="inlineStr">
         <is>
           <t>images/「国際宇宙ステーションからの写真。巨大.png</t>
         </is>
       </c>
-      <c r="C747" t="inlineStr">
+      <c r="C746" t="inlineStr">
         <is>
           <t>台風</t>
         </is>
       </c>
     </row>
-    <row r="748">
-      <c r="A748" t="inlineStr">
+    <row r="747">
+      <c r="A747" t="inlineStr">
         <is>
           <t xml:space="preserve">「草を食む幸運な子羊たち」
 خراف محظوظة ترعى
@@ -16167,19 +16146,19 @@
 2308 https://twitter.com/NatGeoMagArab/status/1490211393554972676 </t>
         </is>
       </c>
-      <c r="B748" t="inlineStr">
+      <c r="B747" t="inlineStr">
         <is>
           <t>images/「草を食む幸運な子羊たち」_img1.jpg,images/ 「草を食む幸運な子羊たち」_img2.jpg</t>
         </is>
       </c>
-      <c r="C748" t="inlineStr">
+      <c r="C747" t="inlineStr">
         <is>
           <t>羊 ,アイルランド</t>
         </is>
       </c>
     </row>
-    <row r="749">
-      <c r="A749" t="inlineStr">
+    <row r="748">
+      <c r="A748" t="inlineStr">
         <is>
           <t xml:space="preserve">「お金で買えぬ10のもの」
 ١٠ أشياء لا تشترى بالمال
@@ -16189,19 +16168,19 @@
 2308 ayb124 </t>
         </is>
       </c>
-      <c r="B749" t="inlineStr">
+      <c r="B748" t="inlineStr">
         <is>
           <t>images/「お金で買えぬ10のもの」_img1.jpg</t>
         </is>
       </c>
-      <c r="C749" t="inlineStr">
+      <c r="C748" t="inlineStr">
         <is>
           <t>価値 ,購買</t>
         </is>
       </c>
     </row>
-    <row r="750">
-      <c r="A750" t="inlineStr">
+    <row r="749">
+      <c r="A749" t="inlineStr">
         <is>
           <t xml:space="preserve">「お金では買えないよ」
 هي أشْيَاءٌ لا تُشْتَرَى
@@ -16211,19 +16190,19 @@
 1906 mardy_zaawely, Instagram </t>
         </is>
       </c>
-      <c r="B750" t="inlineStr">
+      <c r="B749" t="inlineStr">
         <is>
           <t>images/「お金では買えないよ」_img1.jpg</t>
         </is>
       </c>
-      <c r="C750" t="inlineStr">
+      <c r="C749" t="inlineStr">
         <is>
           <t>マスターカード ,価値</t>
         </is>
       </c>
     </row>
-    <row r="751">
-      <c r="A751" t="inlineStr">
+    <row r="750">
+      <c r="A750" t="inlineStr">
         <is>
           <t xml:space="preserve">「好奇心旺盛なホッキョクギツネ」
 ثعلب قطبي يملؤه الفضول
@@ -16233,15 +16212,15 @@
 2308 https://twitter.com/natgeomagarab/status/1157592172968808449 </t>
         </is>
       </c>
-      <c r="B751" t="inlineStr"/>
-      <c r="C751" t="inlineStr">
+      <c r="B750" t="inlineStr"/>
+      <c r="C750" t="inlineStr">
         <is>
           <t>ファーストコンタクト ,キツネ</t>
         </is>
       </c>
     </row>
-    <row r="752">
-      <c r="A752" t="inlineStr">
+    <row r="751">
+      <c r="A751" t="inlineStr">
         <is>
           <t xml:space="preserve">「グレンダイザーのいる国は死にません」
 لنْ يَموتَ شَعبٌ لدَيهِ غرندايزر
@@ -16250,56 +16229,56 @@
 2308 https://www.aljarida.com/articles/1462241741574732100/ </t>
         </is>
       </c>
+      <c r="B751" t="inlineStr">
+        <is>
+          <t>images/「グレンダイザーのいる国は死にません」_img1.jpg</t>
+        </is>
+      </c>
+      <c r="C751" t="inlineStr">
+        <is>
+          <t>UFOロボ ,アニメ</t>
+        </is>
+      </c>
+    </row>
+    <row r="752">
+      <c r="A752" t="inlineStr">
+        <is>
+          <t xml:space="preserve">「凍結路面を運転中、彼女は嫌な場面に居合わせた」
+2408 https://twitter.com/NatGeoMagArab/status/1610305209657626625 </t>
+        </is>
+      </c>
       <c r="B752" t="inlineStr">
         <is>
-          <t>images/「グレンダイザーのいる国は死にません」_img1.jpg</t>
+          <t>images/「凍結路面を運転中、彼女は嫌な場面に居_img1.jpg</t>
         </is>
       </c>
       <c r="C752" t="inlineStr">
         <is>
-          <t>UFOロボ ,アニメ</t>
+          <t>手書き語学 ,アラビア語 ,路面凍結</t>
         </is>
       </c>
     </row>
     <row r="753">
       <c r="A753" t="inlineStr">
-        <is>
-          <t xml:space="preserve">「凍結路面を運転中、彼女は嫌な場面に居合わせた」
-2408 https://twitter.com/NatGeoMagArab/status/1610305209657626625 </t>
-        </is>
-      </c>
-      <c r="B753" t="inlineStr">
-        <is>
-          <t>images/「凍結路面を運転中、彼女は嫌な場面に居_img1.jpg</t>
-        </is>
-      </c>
-      <c r="C753" t="inlineStr">
-        <is>
-          <t>手書き語学 ,アラビア語 ,路面凍結</t>
-        </is>
-      </c>
-    </row>
-    <row r="754">
-      <c r="A754" t="inlineStr">
         <is>
           <t xml:space="preserve">「虹が美しさを加えている、アルパカという動物の美しいショット」
 ⁦「美しいショット」[laq_tatun jamiilatun]：「ショット」( لقطة )[laq_ta]：( ـلٌ )[-lun]・( ـقٌ )[-qun]・( ـطٌ )[-_tun]・( ـةٌ )[-tun]⁩
 2308 https://twitter.com/natgeomagarab/status/1155115655928004608 </t>
         </is>
       </c>
-      <c r="B754" t="inlineStr">
+      <c r="B753" t="inlineStr">
         <is>
           <t>images/「虹が美しさを加えている、アルパカとい_img1.jpg</t>
         </is>
       </c>
-      <c r="C754" t="inlineStr">
+      <c r="C753" t="inlineStr">
         <is>
           <t>モフモフ ,アルパカ</t>
         </is>
       </c>
     </row>
-    <row r="755">
-      <c r="A755" t="inlineStr">
+    <row r="754">
+      <c r="A754" t="inlineStr">
         <is>
           <t xml:space="preserve">「幸せは…全然思いもよらない所からやって来る」
 السعادة تأتينا من أماكن لم نكن نتوقعها أبداً
@@ -16308,19 +16287,19 @@
 2109 出典不明 </t>
         </is>
       </c>
-      <c r="B755" t="inlineStr">
+      <c r="B754" t="inlineStr">
         <is>
           <t>images/「幸せは…全然思いもよらない所からやっ_img1.jpg,images/ 「幸せは…全然思いもよらない所からやっ_img2.jpg</t>
         </is>
       </c>
-      <c r="C755" t="inlineStr">
+      <c r="C754" t="inlineStr">
         <is>
           <t>訪れ ,予想</t>
         </is>
       </c>
     </row>
-    <row r="756">
-      <c r="A756" t="inlineStr">
+    <row r="755">
+      <c r="A755" t="inlineStr">
         <is>
           <t xml:space="preserve">「あらゆる問題は、食べ物が解決してくれる」
 كل مشكلة ولها أكلة تحلها
@@ -16329,19 +16308,19 @@
 1909 ALQA AN 878 </t>
         </is>
       </c>
-      <c r="B756" t="inlineStr">
+      <c r="B755" t="inlineStr">
         <is>
           <t>images/「あらゆる問題は、食べ物が解決してくれ_img1.jpg</t>
         </is>
       </c>
-      <c r="C756" t="inlineStr">
+      <c r="C755" t="inlineStr">
         <is>
           <t>ストレス ,精神</t>
         </is>
       </c>
     </row>
-    <row r="757">
-      <c r="A757" t="inlineStr">
+    <row r="756">
+      <c r="A756" t="inlineStr">
         <is>
           <t xml:space="preserve">「冬で私が好きな物」
 أشياء أحبها بالشتاء
@@ -16351,19 +16330,19 @@
 2109 出典不明 </t>
         </is>
       </c>
-      <c r="B757" t="inlineStr">
+      <c r="B756" t="inlineStr">
         <is>
           <t>images/「冬で私が好きな物」_img1.jpg</t>
         </is>
       </c>
-      <c r="C757" t="inlineStr">
+      <c r="C756" t="inlineStr">
         <is>
           <t>季節 ,冬</t>
         </is>
       </c>
     </row>
-    <row r="758">
-      <c r="A758" t="inlineStr">
+    <row r="757">
+      <c r="A757" t="inlineStr">
         <is>
           <t xml:space="preserve">「お金で買うことの出来ない物」
 أشياء لا تستطيع شراءها بالمال
@@ -16373,19 +16352,19 @@
 2409 https://x.com/akhbarak/status/1038402708414373888 </t>
         </is>
       </c>
-      <c r="B758" t="inlineStr">
+      <c r="B757" t="inlineStr">
         <is>
           <t>images/「お金で買うことの出来ない物」_img1.jpg,images/ 「お金で買うことの出来ない物」_img2.jpg</t>
         </is>
       </c>
-      <c r="C758" t="inlineStr">
+      <c r="C757" t="inlineStr">
         <is>
           <t>ショッピング ,価値</t>
         </is>
       </c>
     </row>
-    <row r="759">
-      <c r="A759" t="inlineStr">
+    <row r="758">
+      <c r="A758" t="inlineStr">
         <is>
           <t xml:space="preserve">「私たちが愛する言葉」
 كلماتٌ نُحبّها
@@ -16395,19 +16374,19 @@
 2109 جليل خزعل </t>
         </is>
       </c>
-      <c r="B759" t="inlineStr">
+      <c r="B758" t="inlineStr">
         <is>
           <t>images/「私たちが愛する言葉」_img1.jpg</t>
         </is>
       </c>
-      <c r="C759" t="inlineStr">
+      <c r="C758" t="inlineStr">
         <is>
           <t>花 ,贈り物</t>
         </is>
       </c>
     </row>
-    <row r="760">
-      <c r="A760" t="inlineStr">
+    <row r="759">
+      <c r="A759" t="inlineStr">
         <is>
           <t xml:space="preserve">「お茶についてあなたが知らない10の事実」
 عشر معلومات لا تعرفها عن الشاي
@@ -16416,19 +16395,19 @@
 2012 http://ara.tv/6syq2 </t>
         </is>
       </c>
-      <c r="B760" t="inlineStr">
+      <c r="B759" t="inlineStr">
         <is>
           <t>images/「お茶についてあなたが知らない10の事_img1.jpg</t>
         </is>
       </c>
-      <c r="C760" t="inlineStr">
+      <c r="C759" t="inlineStr">
         <is>
           <t>神農</t>
         </is>
       </c>
     </row>
-    <row r="761">
-      <c r="A761" t="inlineStr">
+    <row r="760">
+      <c r="A760" t="inlineStr">
         <is>
           <t xml:space="preserve">「大きくなったウソ」
 الكذبة الّتي كبرت
@@ -16438,19 +16417,19 @@
 2509 سلسلة الحلزونة </t>
         </is>
       </c>
-      <c r="B761" t="inlineStr">
+      <c r="B760" t="inlineStr">
         <is>
           <t>images/「大きくなったウソ」_img1.jpg</t>
         </is>
       </c>
-      <c r="C761" t="inlineStr">
+      <c r="C760" t="inlineStr">
         <is>
           <t>絵本</t>
         </is>
       </c>
     </row>
-    <row r="762">
-      <c r="A762" t="inlineStr">
+    <row r="761">
+      <c r="A761" t="inlineStr">
         <is>
           <t xml:space="preserve">「自分に合った掃除機を買うには？」
 كيف تشتري المكنسة الكهربائية التي تناسبك؟
@@ -16459,19 +16438,19 @@
 2106 ts3a com </t>
         </is>
       </c>
-      <c r="B762" t="inlineStr">
+      <c r="B761" t="inlineStr">
         <is>
           <t>images/「自分に合った掃除機を買うには？」_img1.jpg</t>
         </is>
       </c>
-      <c r="C762" t="inlineStr">
+      <c r="C761" t="inlineStr">
         <is>
           <t>家電 ,掃除</t>
         </is>
       </c>
     </row>
-    <row r="763">
-      <c r="A763" t="inlineStr">
+    <row r="762">
+      <c r="A762" t="inlineStr">
         <is>
           <t xml:space="preserve">「仮にこれが批判の数としよう」
 لنفرض ان عدد الذين ينتقدونك
@@ -16482,19 +16461,19 @@
 2504 出典不明 </t>
         </is>
       </c>
-      <c r="B763" t="inlineStr">
+      <c r="B762" t="inlineStr">
         <is>
           <t>images/「仮にこれが批判の数としよう」_img1.jpg</t>
         </is>
       </c>
-      <c r="C763" t="inlineStr">
+      <c r="C762" t="inlineStr">
         <is>
           <t>アンチ</t>
         </is>
       </c>
     </row>
-    <row r="764">
-      <c r="A764" t="inlineStr">
+    <row r="763">
+      <c r="A763" t="inlineStr">
         <is>
           <t xml:space="preserve">「ここに見えるのは何？」
 ما الذي تراه هنا؟
@@ -16504,15 +16483,15 @@
 2204 https://twitter.com/NatGeoMagArab/status/1506933850617700352 </t>
         </is>
       </c>
-      <c r="B764" t="inlineStr"/>
-      <c r="C764" t="inlineStr">
+      <c r="B763" t="inlineStr"/>
+      <c r="C763" t="inlineStr">
         <is>
           <t xml:space="preserve">ペンギン </t>
         </is>
       </c>
     </row>
-    <row r="765">
-      <c r="A765" t="inlineStr">
+    <row r="764">
+      <c r="A764" t="inlineStr">
         <is>
           <t xml:space="preserve">「今日辛いこと、明日は平気だろう」
 ما يؤلم اليوم سيهون غدًا
@@ -16522,19 +16501,19 @@
 2308 basmahjeff </t>
         </is>
       </c>
-      <c r="B765" t="inlineStr">
+      <c r="B764" t="inlineStr">
         <is>
           <t>images/「今日辛いこと、明日は平気だろう」_img1.jpg</t>
         </is>
       </c>
-      <c r="C765" t="inlineStr">
+      <c r="C764" t="inlineStr">
         <is>
           <t>悩み ,達観</t>
         </is>
       </c>
     </row>
-    <row r="766">
-      <c r="A766" t="inlineStr">
+    <row r="765">
+      <c r="A765" t="inlineStr">
         <is>
           <t xml:space="preserve">「自分のすることを好きでなきゃ」
 عليك أن تحب ما تفعل
@@ -16543,19 +16522,19 @@
 1810 Ahmed Elhakeem </t>
         </is>
       </c>
-      <c r="B766" t="inlineStr">
+      <c r="B765" t="inlineStr">
         <is>
           <t>images/「自分のすることを好きでなきゃ」_img1.jpg</t>
         </is>
       </c>
-      <c r="C766" t="inlineStr">
+      <c r="C765" t="inlineStr">
         <is>
           <t>転職 ,かわいい</t>
         </is>
       </c>
     </row>
-    <row r="767">
-      <c r="A767" t="inlineStr">
+    <row r="766">
+      <c r="A766" t="inlineStr">
         <is>
           <t xml:space="preserve">「この地上に生き甲斐あり」
 على هذه الأرض ما يستحق الحياة
@@ -16565,19 +16544,19 @@
 2308 Mahmoud Gafar </t>
         </is>
       </c>
-      <c r="B767" t="inlineStr">
+      <c r="B766" t="inlineStr">
         <is>
           <t>images/「この地上に生き甲斐あり」_img1.jpg</t>
         </is>
       </c>
-      <c r="C767" t="inlineStr">
+      <c r="C766" t="inlineStr">
         <is>
           <t>詩</t>
         </is>
       </c>
     </row>
-    <row r="768">
-      <c r="A768" t="inlineStr">
+    <row r="767">
+      <c r="A767" t="inlineStr">
         <is>
           <t xml:space="preserve">「おそらく、あなたの求めるものはあるだろう」
 لعلَّ ما تَرجوهُ سيَكونُ
@@ -16587,19 +16566,19 @@
 2308 PIXEL Instagram </t>
         </is>
       </c>
-      <c r="B768" t="inlineStr">
+      <c r="B767" t="inlineStr">
         <is>
           <t>images/「おそらく、あなたの求めるものはあるだ_img1.jpg</t>
         </is>
       </c>
-      <c r="C768" t="inlineStr">
+      <c r="C767" t="inlineStr">
         <is>
           <t>願い ,信仰</t>
         </is>
       </c>
     </row>
-    <row r="769">
-      <c r="A769" t="inlineStr">
+    <row r="768">
+      <c r="A768" t="inlineStr">
         <is>
           <t xml:space="preserve">「オレンジの効能が何か知っていますか？」
 هل تعرف ما هي فوائد البرتقال؟
@@ -16609,19 +16588,19 @@
 2308 sadahadhramowt com </t>
         </is>
       </c>
-      <c r="B769" t="inlineStr">
+      <c r="B768" t="inlineStr">
         <is>
           <t>images/「オレンジの効能が何か知っていますか？_img1.jpg</t>
         </is>
       </c>
-      <c r="C769" t="inlineStr">
+      <c r="C768" t="inlineStr">
         <is>
           <t>オレンジ ,フルーツ</t>
         </is>
       </c>
     </row>
-    <row r="770">
-      <c r="A770" t="inlineStr">
+    <row r="769">
+      <c r="A769" t="inlineStr">
         <is>
           <t xml:space="preserve">「遊ぶパンダの光景より可愛いものがありますか？」
 هل هناك ما هو ألطف من مشاهدة الباندا وهي تلعب؟
@@ -16629,19 +16608,19 @@
 2308 https://twitter.com/NatGeoMagArab/status/1494612797858074626 </t>
         </is>
       </c>
-      <c r="B770" t="inlineStr">
+      <c r="B769" t="inlineStr">
         <is>
           <t>images/「遊ぶパンダの光景より可愛いものがあり_img1.jpg</t>
         </is>
       </c>
-      <c r="C770" t="inlineStr">
+      <c r="C769" t="inlineStr">
         <is>
           <t>パンダ ,モコモコ</t>
         </is>
       </c>
     </row>
-    <row r="771">
-      <c r="A771" t="inlineStr">
+    <row r="770">
+      <c r="A770" t="inlineStr">
         <is>
           <t xml:space="preserve">「大事なのは何者だったかじゃない。何者になるかだ」
 ليسَ المُهم ما كُنتَ بل مَا ستكون
@@ -16650,19 +16629,19 @@
 2308 出典不明 </t>
         </is>
       </c>
-      <c r="B771" t="inlineStr">
+      <c r="B770" t="inlineStr">
         <is>
           <t>images/「大事なのは何者だったかじゃない。何者_img1.jpg</t>
         </is>
       </c>
-      <c r="C771" t="inlineStr">
+      <c r="C770" t="inlineStr">
         <is>
           <t>自己実現 ,存在価値</t>
         </is>
       </c>
     </row>
-    <row r="772">
-      <c r="A772" t="inlineStr">
+    <row r="771">
+      <c r="A771" t="inlineStr">
         <is>
           <t xml:space="preserve">「あなたであれ。ありのままが美しいから」
 كُنْ أَنْتَ لأنك جميل كما أنت
@@ -16671,19 +16650,19 @@
 2308 IDREES DESIGN </t>
         </is>
       </c>
-      <c r="B772" t="inlineStr">
+      <c r="B771" t="inlineStr">
         <is>
           <t>images/「あなたであれ。ありのままが美しいから_img1.jpg</t>
         </is>
       </c>
-      <c r="C772" t="inlineStr">
+      <c r="C771" t="inlineStr">
         <is>
           <t>自己肯定 ,BeYourself</t>
         </is>
       </c>
     </row>
-    <row r="773">
-      <c r="A773" t="inlineStr">
+    <row r="772">
+      <c r="A772" t="inlineStr">
         <is>
           <t xml:space="preserve">「恐れの中に生きる者は決して自由になれない」
 من يعش في خوف لن يكون حرا أبدا
@@ -16692,19 +16671,19 @@
 2111 rjeem com </t>
         </is>
       </c>
-      <c r="B773" t="inlineStr">
+      <c r="B772" t="inlineStr">
         <is>
           <t>images/「恐れの中に生きる者は決して自由になれ_img1.jpg,images/ 「恐れの中に生きる者は決して自由になれ_img2.jpg</t>
         </is>
       </c>
-      <c r="C773" t="inlineStr">
+      <c r="C772" t="inlineStr">
         <is>
           <t>勇気 ,壁</t>
         </is>
       </c>
     </row>
-    <row r="774">
-      <c r="A774" t="inlineStr">
+    <row r="773">
+      <c r="A773" t="inlineStr">
         <is>
           <t xml:space="preserve">「己の翼を信じる者は己の重さを案じない」
 من يثق في جناحيه لن يهتم لوزنه
@@ -16713,19 +16692,19 @@
 2308 kmrghani </t>
         </is>
       </c>
-      <c r="B774" t="inlineStr">
+      <c r="B773" t="inlineStr">
         <is>
           <t>images/「己の翼を信じる者は己の重さを案じない_img1.jpg</t>
         </is>
       </c>
-      <c r="C774" t="inlineStr">
+      <c r="C773" t="inlineStr">
         <is>
           <t>自信</t>
         </is>
       </c>
     </row>
-    <row r="775">
-      <c r="A775" t="inlineStr">
+    <row r="774">
+      <c r="A774" t="inlineStr">
         <is>
           <t xml:space="preserve">「珈琲で一番大事な事！誰と飲むか？」
 الأهم من القهوة!! من ستشربها معه؟
@@ -16734,19 +16713,19 @@
 1812 gwid3.tumblr </t>
         </is>
       </c>
-      <c r="B775" t="inlineStr">
+      <c r="B774" t="inlineStr">
         <is>
           <t>images/「珈琲で一番大事な事！誰と飲むか？」_img1.jpg</t>
         </is>
       </c>
-      <c r="C775" t="inlineStr">
+      <c r="C774" t="inlineStr">
         <is>
           <t>コーヒー ,名言</t>
         </is>
       </c>
     </row>
-    <row r="776">
-      <c r="A776" t="inlineStr">
+    <row r="775">
+      <c r="A775" t="inlineStr">
         <is>
           <t xml:space="preserve">「人生は美しい、そう望んだ者には。」
 الحياة جَميلَة .. لمن أراد ذلك
@@ -16756,19 +16735,19 @@
 2109 出典不明 </t>
         </is>
       </c>
-      <c r="B776" t="inlineStr">
+      <c r="B775" t="inlineStr">
         <is>
           <t>images/「人生は美しい、そう望んだ者には。」_img1.jpg</t>
         </is>
       </c>
-      <c r="C776" t="inlineStr">
+      <c r="C775" t="inlineStr">
         <is>
           <t>名言 ,アート</t>
         </is>
       </c>
     </row>
-    <row r="777">
-      <c r="A777" t="inlineStr">
+    <row r="776">
+      <c r="A776" t="inlineStr">
         <is>
           <t xml:space="preserve">「ハム太郎って子を知ってるかい」
 هل تعرفون من هو هامتارو
@@ -16778,19 +16757,19 @@
 2109 </t>
         </is>
       </c>
-      <c r="B777" t="inlineStr">
+      <c r="B776" t="inlineStr">
         <is>
           <t>images/「ハム太郎って子を知ってるかい」_img1.jpg</t>
         </is>
       </c>
-      <c r="C777" t="inlineStr">
+      <c r="C776" t="inlineStr">
         <is>
           <t>オープニング ,ハム太郎</t>
         </is>
       </c>
     </row>
-    <row r="778">
-      <c r="A778" t="inlineStr">
+    <row r="777">
+      <c r="A777" t="inlineStr">
         <is>
           <t xml:space="preserve">「幸せを求める人もいれば、作る人もいる」
 هناك من يبحث عن السعادة وهناك من يصنعها
@@ -16799,19 +16778,19 @@
 2308 hindah tumblr </t>
         </is>
       </c>
-      <c r="B778" t="inlineStr">
+      <c r="B777" t="inlineStr">
         <is>
           <t>images/「幸せを求める人もいれば、作る人もいる_img1.jpg</t>
         </is>
       </c>
-      <c r="C778" t="inlineStr">
+      <c r="C777" t="inlineStr">
         <is>
           <t>幸せ ,名言 ,教訓</t>
         </is>
       </c>
     </row>
-    <row r="779">
-      <c r="A779" t="inlineStr">
+    <row r="778">
+      <c r="A778" t="inlineStr">
         <is>
           <t xml:space="preserve">「明白なるアラブの言葉によって」
 بلسان عربي مبين
@@ -16821,19 +16800,19 @@
 2109 Abdullah Barakat behance </t>
         </is>
       </c>
-      <c r="B779" t="inlineStr">
+      <c r="B778" t="inlineStr">
         <is>
           <t>images/「明白なるアラブの言葉によって」_img1.jpg</t>
         </is>
       </c>
-      <c r="C779" t="inlineStr">
+      <c r="C778" t="inlineStr">
         <is>
           <t>イスラム教 ,神聖</t>
         </is>
       </c>
     </row>
-    <row r="780">
-      <c r="A780" t="inlineStr">
+    <row r="779">
+      <c r="A779" t="inlineStr">
         <is>
           <t xml:space="preserve">「結婚前、結婚後」
 قبل الزواج، بعد الزواج
@@ -16843,19 +16822,19 @@
 2308 出典不明 </t>
         </is>
       </c>
-      <c r="B780" t="inlineStr">
+      <c r="B779" t="inlineStr">
         <is>
           <t>images/「結婚前、結婚後」_img1.jpg</t>
         </is>
       </c>
-      <c r="C780" t="inlineStr">
+      <c r="C779" t="inlineStr">
         <is>
           <t>BeforeAfter ,幸せ太り</t>
         </is>
       </c>
     </row>
-    <row r="781">
-      <c r="A781" t="inlineStr">
+    <row r="780">
+      <c r="A780" t="inlineStr">
         <is>
           <t xml:space="preserve">「驚きの価格で」بسعر رائع
 ビスィアル・ラーイア [bi-si*r raa'i*]
@@ -16864,19 +16843,19 @@
 2109 Jarir Bookstore </t>
         </is>
       </c>
-      <c r="B781" t="inlineStr">
+      <c r="B780" t="inlineStr">
         <is>
           <t>images/「驚きの価格で」_img1.jpg</t>
         </is>
       </c>
-      <c r="C781" t="inlineStr">
+      <c r="C780" t="inlineStr">
         <is>
           <t>広告 ,安値</t>
         </is>
       </c>
     </row>
-    <row r="782">
-      <c r="A782" t="inlineStr">
+    <row r="781">
+      <c r="A781" t="inlineStr">
         <is>
           <t xml:space="preserve">「我が魂と共に」مع نفسي
 マア・ナフスィ [ma*a nafs-iy]
@@ -16885,19 +16864,19 @@
 2110 出典不明 </t>
         </is>
       </c>
-      <c r="B782" t="inlineStr">
+      <c r="B781" t="inlineStr">
         <is>
           <t>images/「我が魂と共に」_img1.jpg</t>
         </is>
       </c>
-      <c r="C782" t="inlineStr">
+      <c r="C781" t="inlineStr">
         <is>
           <t>ソウル ,soul</t>
         </is>
       </c>
     </row>
-    <row r="783">
-      <c r="A783" t="inlineStr">
+    <row r="782">
+      <c r="A782" t="inlineStr">
         <is>
           <t xml:space="preserve">「暗い夜に」في ليلة مظلمة
  [fiy layla(tin) mu_Dhlima(tin)]
@@ -16906,19 +16885,19 @@
 2109 سلسلة الحلزونة </t>
         </is>
       </c>
-      <c r="B783" t="inlineStr">
+      <c r="B782" t="inlineStr">
         <is>
           <t>images/「暗い夜に」_img1.jpg</t>
         </is>
       </c>
-      <c r="C783" t="inlineStr">
+      <c r="C782" t="inlineStr">
         <is>
           <t>絵本</t>
         </is>
       </c>
     </row>
-    <row r="784">
-      <c r="A784" t="inlineStr">
+    <row r="783">
+      <c r="A783" t="inlineStr">
         <is>
           <t xml:space="preserve">「ゆっくりと」بشويش
 ビシワェーシ [bi-ShwySh]
@@ -16926,19 +16905,19 @@
 2109 出典不明 </t>
         </is>
       </c>
-      <c r="B784" t="inlineStr">
+      <c r="B783" t="inlineStr">
         <is>
           <t>images/「ゆっくりと」_img1.jpg</t>
         </is>
       </c>
-      <c r="C784" t="inlineStr">
+      <c r="C783" t="inlineStr">
         <is>
           <t>丸 ,円</t>
         </is>
       </c>
     </row>
-    <row r="785">
-      <c r="A785" t="inlineStr">
+    <row r="784">
+      <c r="A784" t="inlineStr">
         <is>
           <t xml:space="preserve">「この広い宇宙に…」
 في الكون الفسيح
@@ -16947,19 +16926,19 @@
 2308 wattpad </t>
         </is>
       </c>
-      <c r="B785" t="inlineStr">
+      <c r="B784" t="inlineStr">
         <is>
           <t>images/「この広い宇宙に…」_img1.jpg</t>
         </is>
       </c>
-      <c r="C785" t="inlineStr">
+      <c r="C784" t="inlineStr">
         <is>
           <t>アニメ ,宇宙</t>
         </is>
       </c>
     </row>
-    <row r="786">
-      <c r="A786" t="inlineStr">
+    <row r="785">
+      <c r="A785" t="inlineStr">
         <is>
           <t xml:space="preserve">「がんばって！」بالتوفيق
 ビッタウフィーク [bi^tawfiiq]
@@ -16967,19 +16946,19 @@
 2111 https://sites.google.com/site/mathmatic1905/ </t>
         </is>
       </c>
-      <c r="B786" t="inlineStr">
+      <c r="B785" t="inlineStr">
         <is>
           <t>images/「がんばって！」_img1.jpg</t>
         </is>
       </c>
-      <c r="C786" t="inlineStr">
+      <c r="C785" t="inlineStr">
         <is>
           <t>アラビア語</t>
         </is>
       </c>
     </row>
-    <row r="787">
-      <c r="A787" t="inlineStr">
+    <row r="786">
+      <c r="A786" t="inlineStr">
         <is>
           <t xml:space="preserve">「インターステラー」بين النجوم
 バイナ_ンヌジューム [bayna ^nujuum]
@@ -16987,19 +16966,19 @@
 2308 kmrghani </t>
         </is>
       </c>
-      <c r="B787" t="inlineStr">
+      <c r="B786" t="inlineStr">
         <is>
           <t>images/「インターステラー」_img1.jpg</t>
         </is>
       </c>
-      <c r="C787" t="inlineStr">
+      <c r="C786" t="inlineStr">
         <is>
           <t>映画 ,宇宙</t>
         </is>
       </c>
     </row>
-    <row r="788">
-      <c r="A788" t="inlineStr">
+    <row r="787">
+      <c r="A787" t="inlineStr">
         <is>
           <t xml:space="preserve">「アラビア語で」بالعربية
 ビ_ルアラビーヤ [bi-l-*arabiyya]
@@ -17008,19 +16987,19 @@
 1811 </t>
         </is>
       </c>
-      <c r="B788" t="inlineStr">
+      <c r="B787" t="inlineStr">
         <is>
           <t>images/「アラビア語で」_img1.jpg</t>
         </is>
       </c>
-      <c r="C788" t="inlineStr">
+      <c r="C787" t="inlineStr">
         <is>
           <t>ニュース ,CNN</t>
         </is>
       </c>
     </row>
-    <row r="789">
-      <c r="A789" t="inlineStr">
+    <row r="788">
+      <c r="A788" t="inlineStr">
         <is>
           <t xml:space="preserve">「17世紀に発明されて以来…」
 منذ اختراعه بالقرن السابع عشر
@@ -17028,19 +17007,19 @@
 2308 https://twitter.com/SciTalk2U/status/1450888395815854080 </t>
         </is>
       </c>
-      <c r="B789" t="inlineStr">
+      <c r="B788" t="inlineStr">
         <is>
           <t>images/「17世紀に発明されて以来…」_img1.jpg</t>
         </is>
       </c>
-      <c r="C789" t="inlineStr">
+      <c r="C788" t="inlineStr">
         <is>
           <t>手書き語学 ,アラビア語 ,望遠鏡</t>
         </is>
       </c>
     </row>
-    <row r="790">
-      <c r="A790" t="inlineStr">
+    <row r="789">
+      <c r="A789" t="inlineStr">
         <is>
           <t xml:space="preserve">「私できるよ」إنّني أستطيع
 インナニー・アスタティーウ ['inna-niy 'a-sta_tii*u]
@@ -17049,19 +17028,19 @@
 2412 سلسلة الحلزونة </t>
         </is>
       </c>
-      <c r="B790" t="inlineStr">
+      <c r="B789" t="inlineStr">
         <is>
           <t>images/「私できるよ」_img1.jpg</t>
         </is>
       </c>
-      <c r="C790" t="inlineStr">
+      <c r="C789" t="inlineStr">
         <is>
           <t>絵本 ,こども</t>
         </is>
       </c>
     </row>
-    <row r="791">
-      <c r="A791" t="inlineStr">
+    <row r="790">
+      <c r="A790" t="inlineStr">
         <is>
           <t xml:space="preserve">「問題なし」مافيش مشكلة
 マフィーシムシュキラ [ma-fy-Sh muShkila]
@@ -17070,19 +17049,19 @@
 2109 tanzerin.theshop </t>
         </is>
       </c>
-      <c r="B791" t="inlineStr">
+      <c r="B790" t="inlineStr">
         <is>
           <t>images/「問題なし」_img1.jpg</t>
         </is>
       </c>
-      <c r="C791" t="inlineStr">
+      <c r="C790" t="inlineStr">
         <is>
           <t>シャツ ,キッズ</t>
         </is>
       </c>
     </row>
-    <row r="792">
-      <c r="A792" t="inlineStr">
+    <row r="791">
+      <c r="A791" t="inlineStr">
         <is>
           <t xml:space="preserve">「不可能はない」مفيش مستحيل
 マフィーシ・ムスタヒール [ma-fy-Sh mustaHiil]
@@ -17091,19 +17070,19 @@
 2109 أموج </t>
         </is>
       </c>
-      <c r="B792" t="inlineStr">
+      <c r="B791" t="inlineStr">
         <is>
           <t>images/「不可能はない」_img1.jpg</t>
         </is>
       </c>
-      <c r="C792" t="inlineStr">
+      <c r="C791" t="inlineStr">
         <is>
           <t>ポジティブ ,挑戦</t>
         </is>
       </c>
     </row>
-    <row r="793">
-      <c r="A793" t="inlineStr">
+    <row r="792">
+      <c r="A792" t="inlineStr">
         <is>
           <t xml:space="preserve">「等々」إلخ
 イラク ['ilaKh]
@@ -17112,19 +17091,19 @@
 2201 出典不明 </t>
         </is>
       </c>
-      <c r="B793" t="inlineStr">
+      <c r="B792" t="inlineStr">
         <is>
           <t>images/「等々」_img1.jpg</t>
         </is>
       </c>
-      <c r="C793" t="inlineStr">
+      <c r="C792" t="inlineStr">
         <is>
           <t>etc ,とんち</t>
         </is>
       </c>
     </row>
-    <row r="794">
-      <c r="A794" t="inlineStr">
+    <row r="793">
+      <c r="A793" t="inlineStr">
         <is>
           <t xml:space="preserve">⁦「調子どう？」⁩شلونَك؟
 シュローナク？ [Sh-loon-ak?]
@@ -17133,19 +17112,19 @@
 2202 Jozoor Team. </t>
         </is>
       </c>
-      <c r="B794" t="inlineStr">
+      <c r="B793" t="inlineStr">
         <is>
           <t>images/⁦「調子どう？」⁩_img1.jpg</t>
         </is>
       </c>
-      <c r="C794" t="inlineStr">
+      <c r="C793" t="inlineStr">
         <is>
           <t>洒落 ,ルービックキューブ</t>
         </is>
       </c>
     </row>
-    <row r="795">
-      <c r="A795" t="inlineStr">
+    <row r="794">
+      <c r="A794" t="inlineStr">
         <is>
           <t xml:space="preserve">「行くな」ماتروحش
 マトロホシ [ma-troH-Sh]
@@ -17154,19 +17133,19 @@
 2411 triiq tumblr </t>
         </is>
       </c>
-      <c r="B795" t="inlineStr">
+      <c r="B794" t="inlineStr">
         <is>
           <t>images/「行くな」_img1.jpg</t>
         </is>
       </c>
-      <c r="C795" t="inlineStr">
+      <c r="C794" t="inlineStr">
         <is>
           <t>ロゴ ,デザイン ,嵐</t>
         </is>
       </c>
     </row>
-    <row r="796">
-      <c r="A796" t="inlineStr">
+    <row r="795">
+      <c r="A795" t="inlineStr">
         <is>
           <t xml:space="preserve">⁦「元気？」⁩شلونَك؟
 シュローナク？ [Sh-loon-ak?]
@@ -17177,19 +17156,19 @@
 2202 出典不明 </t>
         </is>
       </c>
-      <c r="B796" t="inlineStr">
+      <c r="B795" t="inlineStr">
         <is>
           <t>images/⁦「元気？」⁩_img1.jpg</t>
         </is>
       </c>
-      <c r="C796" t="inlineStr">
+      <c r="C795" t="inlineStr">
         <is>
           <t>洒落 ,挨拶</t>
         </is>
       </c>
     </row>
-    <row r="797">
-      <c r="A797" t="inlineStr">
+    <row r="796">
+      <c r="A796" t="inlineStr">
         <is>
           <t xml:space="preserve">「気分が良いぞう」I فيل GOOD
 アイ・フィール・グッド [ai fiyl gud]
@@ -17198,19 +17177,19 @@
 2308 出典不明 </t>
         </is>
       </c>
-      <c r="B797" t="inlineStr">
+      <c r="B796" t="inlineStr">
         <is>
           <t>images/「気分が良いぞう」_img1.jpg</t>
         </is>
       </c>
-      <c r="C797" t="inlineStr">
+      <c r="C796" t="inlineStr">
         <is>
           <t>洒落 ,和訳</t>
         </is>
       </c>
     </row>
-    <row r="798">
-      <c r="A798" t="inlineStr">
+    <row r="797">
+      <c r="A797" t="inlineStr">
         <is>
           <t xml:space="preserve">「レットイットゴー／let it go」
 ليت اِت غو
@@ -17219,19 +17198,19 @@
 2109 出典不明 </t>
         </is>
       </c>
-      <c r="B798" t="inlineStr">
+      <c r="B797" t="inlineStr">
         <is>
           <t>images/「レットイットゴー／let it go_img1.jpg</t>
         </is>
       </c>
-      <c r="C798" t="inlineStr">
+      <c r="C797" t="inlineStr">
         <is>
           <t>折衷 ,アナ雪</t>
         </is>
       </c>
     </row>
-    <row r="799">
-      <c r="A799" t="inlineStr">
+    <row r="798">
+      <c r="A798" t="inlineStr">
         <is>
           <t xml:space="preserve">「ようこそ」اهلا وسهلا
 アハラン・ワサハラン ['ahlan wa-sahlan]
@@ -17239,19 +17218,19 @@
 2106 behance Anwar Al Eissa </t>
         </is>
       </c>
-      <c r="B799" t="inlineStr">
+      <c r="B798" t="inlineStr">
         <is>
           <t>images/「ようこそ」_img1.jpg</t>
         </is>
       </c>
-      <c r="C799" t="inlineStr">
+      <c r="C798" t="inlineStr">
         <is>
           <t>アラビア語</t>
         </is>
       </c>
     </row>
-    <row r="800">
-      <c r="A800" t="inlineStr">
+    <row r="799">
+      <c r="A799" t="inlineStr">
         <is>
           <t xml:space="preserve">「まぁ何というサプライズでしょう」
 يا لها من مفاجأة
@@ -17262,19 +17241,19 @@
 2108 neelwafurat com </t>
         </is>
       </c>
-      <c r="B800" t="inlineStr">
+      <c r="B799" t="inlineStr">
         <is>
           <t>images/「まぁ何というサプライズでしょう」_img1.jpg</t>
         </is>
       </c>
-      <c r="C800" t="inlineStr">
+      <c r="C799" t="inlineStr">
         <is>
           <t>中国語 ,学習</t>
         </is>
       </c>
     </row>
-    <row r="801">
-      <c r="A801" t="inlineStr">
+    <row r="800">
+      <c r="A800" t="inlineStr">
         <is>
           <t xml:space="preserve">「ハックション」اتشوو
 アチュー！ ['aatShuu]
@@ -17282,19 +17261,19 @@
 1811 </t>
         </is>
       </c>
-      <c r="B801" t="inlineStr">
+      <c r="B800" t="inlineStr">
         <is>
           <t>images/「ハックション」_img1.jpg</t>
         </is>
       </c>
-      <c r="C801" t="inlineStr">
+      <c r="C800" t="inlineStr">
         <is>
           <t>あらびあや</t>
         </is>
       </c>
     </row>
-    <row r="802">
-      <c r="A802" t="inlineStr">
+    <row r="801">
+      <c r="A801" t="inlineStr">
         <is>
           <t xml:space="preserve">「スブハーナッラー」「アルハムドゥリッラー」「アッラーアクバル」
 سبحان الله
@@ -17305,19 +17284,19 @@
 2308 dribbble com </t>
         </is>
       </c>
-      <c r="B802" t="inlineStr">
+      <c r="B801" t="inlineStr">
         <is>
           <t>images/「スブハーナッラー」「アルハムドゥリッ_img1.jpg</t>
         </is>
       </c>
-      <c r="C802" t="inlineStr">
+      <c r="C801" t="inlineStr">
         <is>
           <t>四角 ,コンパクト</t>
         </is>
       </c>
     </row>
-    <row r="803">
-      <c r="A803" t="inlineStr">
+    <row r="802">
+      <c r="A802" t="inlineStr">
         <is>
           <t xml:space="preserve">「すごく美味しい！」لذيذ جدًا
 ラズィーズ・ジッダン [laDhiiDh jiddan]
@@ -17326,19 +17305,19 @@
 2109 goodreads com </t>
         </is>
       </c>
-      <c r="B803" t="inlineStr">
+      <c r="B802" t="inlineStr">
         <is>
           <t>images/「すごく美味しい！」_img1.jpg</t>
         </is>
       </c>
-      <c r="C803" t="inlineStr">
+      <c r="C802" t="inlineStr">
         <is>
           <t>フレーズ ,感想</t>
         </is>
       </c>
     </row>
-    <row r="804">
-      <c r="A804" t="inlineStr">
+    <row r="803">
+      <c r="A803" t="inlineStr">
         <is>
           <t xml:space="preserve">「しとしと、雨」تك تك يا مطر
 ティクティク [tik tik yaa ma_tar]
@@ -17347,19 +17326,19 @@
 2308 出典不明 </t>
         </is>
       </c>
-      <c r="B804" t="inlineStr">
+      <c r="B803" t="inlineStr">
         <is>
           <t>images/「しとしと、雨」_img1.jpg</t>
         </is>
       </c>
-      <c r="C804" t="inlineStr">
+      <c r="C803" t="inlineStr">
         <is>
           <t>天気 ,梅雨</t>
         </is>
       </c>
     </row>
-    <row r="805">
-      <c r="A805" t="inlineStr">
+    <row r="804">
+      <c r="A804" t="inlineStr">
         <is>
           <t xml:space="preserve">「さかさま」رأساً على عقب
 ラッアサン・アラー・アケブ [ra'san *alaa *aqib]
@@ -17367,19 +17346,19 @@
 2109 出典不明 </t>
         </is>
       </c>
-      <c r="B805" t="inlineStr">
+      <c r="B804" t="inlineStr">
         <is>
           <t>images/「さかさま」_img1.jpg</t>
         </is>
       </c>
-      <c r="C805" t="inlineStr">
+      <c r="C804" t="inlineStr">
         <is>
           <t>壁 ,上下</t>
         </is>
       </c>
     </row>
-    <row r="806">
-      <c r="A806" t="inlineStr">
+    <row r="805">
+      <c r="A805" t="inlineStr">
         <is>
           <t xml:space="preserve">「エジプトよどこへ行った」
 فينك يا مصر؟
@@ -17389,19 +17368,19 @@
 1809 shehabfawzy1.tumblr </t>
         </is>
       </c>
-      <c r="B806" t="inlineStr">
+      <c r="B805" t="inlineStr">
         <is>
           <t>images/「エジプトよどこへ行った」_img1.jpg</t>
         </is>
       </c>
-      <c r="C806" t="inlineStr">
+      <c r="C805" t="inlineStr">
         <is>
           <t>ピラミッド ,歴史</t>
         </is>
       </c>
     </row>
-    <row r="807">
-      <c r="A807" t="inlineStr">
+    <row r="806">
+      <c r="A806" t="inlineStr">
         <is>
           <t xml:space="preserve">「ありがとう」شكراً
 シュクラン [Shukran]
@@ -17409,19 +17388,19 @@
 2109 出典不明 </t>
         </is>
       </c>
-      <c r="B807" t="inlineStr">
+      <c r="B806" t="inlineStr">
         <is>
           <t>images/「ありがとう」_img1.jpg</t>
         </is>
       </c>
-      <c r="C807" t="inlineStr">
+      <c r="C806" t="inlineStr">
         <is>
           <t>挨拶 ,文字</t>
         </is>
       </c>
     </row>
-    <row r="808">
-      <c r="A808" t="inlineStr">
+    <row r="807">
+      <c r="A807" t="inlineStr">
         <is>
           <t xml:space="preserve">「昼寝の時間だ」
 إنه وقت القيلولة
@@ -17430,12 +17409,12 @@
 2501 https://x.com/NatGeoMagArab/status/1858049951579910486 </t>
         </is>
       </c>
-      <c r="B808" t="inlineStr">
+      <c r="B807" t="inlineStr">
         <is>
           <t>images/「昼寝の時間だ」_img1.jpg</t>
         </is>
       </c>
-      <c r="C808" t="inlineStr">
+      <c r="C807" t="inlineStr">
         <is>
           <t>手書き語学 ,アラビア語 ,ペンギン</t>
         </is>

--- a/posts.xlsx
+++ b/posts.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C807"/>
+  <dimension ref="A1:C806"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -15040,26 +15040,6 @@
     <row r="694">
       <c r="A694" t="inlineStr">
         <is>
-          <t xml:space="preserve">「デザイン」تَصْمِيمٌ
-タスミーム [ta_smiim(un)]
-⁦( تَـ )[ta-]・( ـصْـ )[-_s-]・( ـمِيـ )[-mii-]・( ـمٌ )[-mun]：( تـ )[t-]・( ـصـ )[-_s-]・( ـمـ )[-m-]・( ـم )[-m]：( ص )[_s]・( م )[m]⁩ 
-1903 arabictypography com </t>
-        </is>
-      </c>
-      <c r="B694" t="inlineStr">
-        <is>
-          <t>images/「デザイン」_img1.jpg</t>
-        </is>
-      </c>
-      <c r="C694" t="inlineStr">
-        <is>
-          <t>文字 ,タイポグラフィー</t>
-        </is>
-      </c>
-    </row>
-    <row r="695">
-      <c r="A695" t="inlineStr">
-        <is>
           <t xml:space="preserve">「この猫は食事をシェアするのが嫌い！」
 هذه القطة لا تحب مشاركة الطعام
 [haaDhihi l-qi^_tatu laa tu-Hibbu muShaarakata ^_ta*aam(i)]
@@ -15067,19 +15047,19 @@
 2605 facebook com/alahram/videos/2154923608133231/ </t>
         </is>
       </c>
-      <c r="B695" t="inlineStr">
+      <c r="B694" t="inlineStr">
         <is>
           <t>images/「この猫は食事をシェアするのが嫌い！」_img1.jpg</t>
         </is>
       </c>
-      <c r="C695" t="inlineStr">
+      <c r="C694" t="inlineStr">
         <is>
           <t>猫 ,ネコ</t>
         </is>
       </c>
     </row>
-    <row r="696">
-      <c r="A696" t="inlineStr">
+    <row r="695">
+      <c r="A695" t="inlineStr">
         <is>
           <t xml:space="preserve">「怪獣との戦いでは自分が怪獣化せぬよう警戒しなさい」
 احذر عند محاربة الوحوش ألا تصبح واحدا منهم
@@ -15089,19 +15069,19 @@
 2108 warag-3nb.tumblr </t>
         </is>
       </c>
-      <c r="B696" t="inlineStr">
+      <c r="B695" t="inlineStr">
         <is>
           <t>images/「怪獣との戦いでは自分が怪獣化せぬよう_img1.jpg,images/ 「怪獣との戦いでは自分が怪獣化せぬよう_img2.jpg</t>
         </is>
       </c>
-      <c r="C696" t="inlineStr">
+      <c r="C695" t="inlineStr">
         <is>
           <t>正気 ,モンスター</t>
         </is>
       </c>
     </row>
-    <row r="697">
-      <c r="A697" t="inlineStr">
+    <row r="696">
+      <c r="A696" t="inlineStr">
         <is>
           <t xml:space="preserve">「錯視アート」فن الخداع البصري
 ファンヌ_ルヒダーイ_ルバサリーイ [fannu l-Khidaa*i l-ba_sariyy]
@@ -15110,19 +15090,19 @@
 2409 https://online.pubhtml5.com/idtb/neft/ </t>
         </is>
       </c>
-      <c r="B697" t="inlineStr">
+      <c r="B696" t="inlineStr">
         <is>
           <t>images/「錯視アート」_img1.jpg</t>
         </is>
       </c>
-      <c r="C697" t="inlineStr">
+      <c r="C696" t="inlineStr">
         <is>
           <t>トリックアート</t>
         </is>
       </c>
     </row>
-    <row r="698">
-      <c r="A698" t="inlineStr">
+    <row r="697">
+      <c r="A697" t="inlineStr">
         <is>
           <t xml:space="preserve">「自然界の消防士の訓練」
 تدريبات رجال الإطفاء في الطبيعة
@@ -15130,19 +15110,19 @@
 2308 https://twitter.com/NatGeoMagArab/status/1462420543890608129 </t>
         </is>
       </c>
-      <c r="B698" t="inlineStr">
+      <c r="B697" t="inlineStr">
         <is>
           <t>images/「自然界の消防士の訓練」_img1.jpg,images/ 「自然界の消防士の訓練」_img2.jpg</t>
         </is>
       </c>
-      <c r="C698" t="inlineStr">
+      <c r="C697" t="inlineStr">
         <is>
           <t>手書き語学 ,アラビア語 ,ヒグマ</t>
         </is>
       </c>
     </row>
-    <row r="699">
-      <c r="A699" t="inlineStr">
+    <row r="698">
+      <c r="A698" t="inlineStr">
         <is>
           <t xml:space="preserve">「救助」إسعاف
 イスアーフ ['is*aaf]
@@ -15151,19 +15131,19 @@
 2109 ambulance gov ae </t>
         </is>
       </c>
-      <c r="B699" t="inlineStr">
+      <c r="B698" t="inlineStr">
         <is>
           <t>images/「救助」_img1.jpg</t>
         </is>
       </c>
-      <c r="C699" t="inlineStr">
+      <c r="C698" t="inlineStr">
         <is>
           <t>救急車 ,はたらくくるま</t>
         </is>
       </c>
     </row>
-    <row r="700">
-      <c r="A700" t="inlineStr">
+    <row r="699">
+      <c r="A699" t="inlineStr">
         <is>
           <t xml:space="preserve">「感情／感覚」الإحْسَاسْ
 アルイヒサース [al-'iHsaas]
@@ -15172,19 +15152,19 @@
 2308 iN49R </t>
         </is>
       </c>
-      <c r="B700" t="inlineStr">
+      <c r="B699" t="inlineStr">
         <is>
           <t>images/「感情／感覚」_img1.jpg</t>
         </is>
       </c>
-      <c r="C700" t="inlineStr">
+      <c r="C699" t="inlineStr">
         <is>
           <t>オフ ,一休み</t>
         </is>
       </c>
     </row>
-    <row r="701">
-      <c r="A701" t="inlineStr">
+    <row r="700">
+      <c r="A700" t="inlineStr">
         <is>
           <t xml:space="preserve">「ひらめき」إلهام
 イルハーム ['lhaam]
@@ -15196,19 +15176,19 @@
 2103 出典不明 </t>
         </is>
       </c>
-      <c r="B701" t="inlineStr">
+      <c r="B700" t="inlineStr">
         <is>
           <t>images/「ひらめき」_img1.jpg</t>
         </is>
       </c>
-      <c r="C701" t="inlineStr">
+      <c r="C700" t="inlineStr">
         <is>
           <t>アラビア語</t>
         </is>
       </c>
     </row>
-    <row r="702">
-      <c r="A702" t="inlineStr">
+    <row r="701">
+      <c r="A701" t="inlineStr">
         <is>
           <t xml:space="preserve">「Ibdaa／クリエイティビティ」
 إبداع
@@ -15217,19 +15197,19 @@
 2308 Ibdaa Design &amp; Decoration Office </t>
         </is>
       </c>
-      <c r="B702" t="inlineStr">
+      <c r="B701" t="inlineStr">
         <is>
           <t>images/「Ibdaa／クリエイティビティ」_img1.jpg</t>
         </is>
       </c>
-      <c r="C702" t="inlineStr">
+      <c r="C701" t="inlineStr">
         <is>
           <t>創造性 ,独自性</t>
         </is>
       </c>
     </row>
-    <row r="703">
-      <c r="A703" t="inlineStr">
+    <row r="702">
+      <c r="A702" t="inlineStr">
         <is>
           <t xml:space="preserve">「奮闘なくして進歩なし」
 بدون كفاح لايوجد تقدم
@@ -15239,19 +15219,19 @@
 2105 ROUYMS TUMBLR COM </t>
         </is>
       </c>
-      <c r="B703" t="inlineStr">
+      <c r="B702" t="inlineStr">
         <is>
           <t>images/「奮闘なくして進歩なし」_img1.jpg</t>
         </is>
       </c>
-      <c r="C703" t="inlineStr">
+      <c r="C702" t="inlineStr">
         <is>
           <t>努力 ,三角形</t>
         </is>
       </c>
     </row>
-    <row r="704">
-      <c r="A704" t="inlineStr">
+    <row r="703">
+      <c r="A703" t="inlineStr">
         <is>
           <t xml:space="preserve">「木に登れば熊の危険を避けられるとお考えなら、考え直しましょう！」 
 إن اعتقدت أنك بمنأى عن خطر الدب عند تسلق الأشجار.. راجع حساباتك
@@ -15259,19 +15239,19 @@
 2202 NatGeoMagArab </t>
         </is>
       </c>
-      <c r="B704" t="inlineStr">
+      <c r="B703" t="inlineStr">
         <is>
           <t>images/「木に登れば熊の危険を避けられるとお考.jpeg</t>
         </is>
       </c>
-      <c r="C704" t="inlineStr">
+      <c r="C703" t="inlineStr">
         <is>
           <t>クマ</t>
         </is>
       </c>
     </row>
-    <row r="705">
-      <c r="A705" t="inlineStr">
+    <row r="704">
+      <c r="A704" t="inlineStr">
         <is>
           <t xml:space="preserve">「卒業おめでとう」مبروك التخرج
 マブルーク・タカッルジ [mabruuk a^taKharruj]
@@ -15280,19 +15260,19 @@
 2308 https://instagram.com/fatoomworld </t>
         </is>
       </c>
-      <c r="B705" t="inlineStr">
+      <c r="B704" t="inlineStr">
         <is>
           <t>images/「卒業おめでとう」_img1.jpg</t>
         </is>
       </c>
-      <c r="C705" t="inlineStr">
+      <c r="C704" t="inlineStr">
         <is>
           <t>卒業 ,イラスト</t>
         </is>
       </c>
     </row>
-    <row r="706">
-      <c r="A706" t="inlineStr">
+    <row r="705">
+      <c r="A705" t="inlineStr">
         <is>
           <t xml:space="preserve">「停止距離の計算」
 حساب مسافة التوقف
@@ -15302,19 +15282,19 @@
 2109 assurance-auto-info </t>
         </is>
       </c>
-      <c r="B706" t="inlineStr">
+      <c r="B705" t="inlineStr">
         <is>
           <t>images/「停止距離の計算」_img1.jpg</t>
         </is>
       </c>
-      <c r="C706" t="inlineStr">
+      <c r="C705" t="inlineStr">
         <is>
           <t>保険 ,自動車</t>
         </is>
       </c>
     </row>
-    <row r="707">
-      <c r="A707" t="inlineStr">
+    <row r="706">
+      <c r="A706" t="inlineStr">
         <is>
           <t xml:space="preserve">「教師要らず：10日でフランス語会話」
 بدون معلم
@@ -15324,19 +15304,19 @@
 2308 englais-best com </t>
         </is>
       </c>
-      <c r="B707" t="inlineStr">
+      <c r="B706" t="inlineStr">
         <is>
           <t>images/「教師要らず：10日でフランス語会話」_img1.jpg</t>
         </is>
       </c>
-      <c r="C707" t="inlineStr">
+      <c r="C706" t="inlineStr">
         <is>
           <t>教師なし学習</t>
         </is>
       </c>
     </row>
-    <row r="708">
-      <c r="A708" t="inlineStr">
+    <row r="707">
+      <c r="A707" t="inlineStr">
         <is>
           <t xml:space="preserve">「衝突」تصادم
 タサードゥム [ta_saadum]
@@ -15345,19 +15325,19 @@
 1810 </t>
         </is>
       </c>
-      <c r="B708" t="inlineStr">
+      <c r="B707" t="inlineStr">
         <is>
           <t>images/「衝突」_img1.jpg</t>
         </is>
       </c>
-      <c r="C708" t="inlineStr">
+      <c r="C707" t="inlineStr">
         <is>
           <t>あらびあや</t>
         </is>
       </c>
     </row>
-    <row r="709">
-      <c r="A709" t="inlineStr">
+    <row r="708">
+      <c r="A708" t="inlineStr">
         <is>
           <t xml:space="preserve">「楽観主義」تَفَاؤُلٌ
 タファーウル [tafaa'ul(un)]
@@ -15366,19 +15346,19 @@
 1904 arabictypography com </t>
         </is>
       </c>
-      <c r="B709" t="inlineStr">
+      <c r="B708" t="inlineStr">
         <is>
           <t>images/「楽観主義」_img1.jpg</t>
         </is>
       </c>
-      <c r="C709" t="inlineStr">
+      <c r="C708" t="inlineStr">
         <is>
           <t>やわらか ,緑</t>
         </is>
       </c>
     </row>
-    <row r="710">
-      <c r="A710" t="inlineStr">
+    <row r="709">
+      <c r="A709" t="inlineStr">
         <is>
           <t xml:space="preserve">「シベリアジャコウジカは、絶滅の危機にあると見なされている」
 يعد "أيل المسك السيبيري" مهددًا بالانقراض
@@ -15386,19 +15366,19 @@
 2308 https://twitter.com/NatGeoMagArab/status/1320666649045790720 </t>
         </is>
       </c>
-      <c r="B710" t="inlineStr">
+      <c r="B709" t="inlineStr">
         <is>
           <t>images/「シベリアジャコウジカは、絶滅の危機に_img1.jpg,images/「シベリアジャコウジカは、絶滅の危機に_img2.jpg</t>
         </is>
       </c>
-      <c r="C710" t="inlineStr">
+      <c r="C709" t="inlineStr">
         <is>
           <t>手書き語学 ,シベリア</t>
         </is>
       </c>
     </row>
-    <row r="711">
-      <c r="A711" t="inlineStr">
+    <row r="710">
+      <c r="A710" t="inlineStr">
         <is>
           <t xml:space="preserve">「融合／折衷／フュージョン」
 انصهار
@@ -15407,38 +15387,38 @@
 1811 elmahdyart Instagram </t>
         </is>
       </c>
-      <c r="B711" t="inlineStr">
+      <c r="B710" t="inlineStr">
         <is>
           <t>images/「融合／折衷／フュージョン」_img1.jpg</t>
         </is>
       </c>
-      <c r="C711" t="inlineStr">
+      <c r="C710" t="inlineStr">
         <is>
           <t>カリグラフィー ,書道</t>
         </is>
       </c>
     </row>
-    <row r="712">
-      <c r="A712" t="inlineStr">
+    <row r="711">
+      <c r="A711" t="inlineStr">
         <is>
           <t xml:space="preserve">「この子供は、昼寝をしようとする母親を邪魔しているようだ」
 「場所はインドのトラ保護区、バンダウガル公園。トラは生態ピラミッドのトップの捕食動物だが、最もリスクの高い絶滅危惧種のひとつである」
 2308 https://twitter.com/natgeomagarab/status/1553681890665586689 </t>
         </is>
       </c>
-      <c r="B712" t="inlineStr">
+      <c r="B711" t="inlineStr">
         <is>
           <t>images/「この子供は、昼寝をしようとする母親を_img1.jpg,images/「この子供は、昼寝をしようとする母親を_img2.jpg</t>
         </is>
       </c>
-      <c r="C712" t="inlineStr">
+      <c r="C711" t="inlineStr">
         <is>
           <t>手書き語学 ,アラビア語 ,トラ</t>
         </is>
       </c>
     </row>
-    <row r="713">
-      <c r="A713" t="inlineStr">
+    <row r="712">
+      <c r="A712" t="inlineStr">
         <is>
           <t xml:space="preserve">「もし敬意が落ちたら、それと一緒に全部落ちるのだ」
 إن سقط الإحترام سقط معه كل شيء
@@ -15447,19 +15427,19 @@
 2109 出典不明 </t>
         </is>
       </c>
-      <c r="B713" t="inlineStr">
+      <c r="B712" t="inlineStr">
         <is>
           <t>images/「もし敬意が落ちたら、それと一緒に全部_img1.jpg</t>
         </is>
       </c>
-      <c r="C713" t="inlineStr">
+      <c r="C712" t="inlineStr">
         <is>
           <t>リスペクト ,落書き</t>
         </is>
       </c>
     </row>
-    <row r="714">
-      <c r="A714" t="inlineStr">
+    <row r="713">
+      <c r="A713" t="inlineStr">
         <is>
           <t xml:space="preserve">「エジプト特許庁」
 مكتب براءات الاختراع المصرى
@@ -15469,19 +15449,19 @@
 2312 </t>
         </is>
       </c>
-      <c r="B714" t="inlineStr">
+      <c r="B713" t="inlineStr">
         <is>
           <t>images/「エジプト特許庁」_img1.jpg</t>
         </is>
       </c>
-      <c r="C714" t="inlineStr">
+      <c r="C713" t="inlineStr">
         <is>
           <t>patent</t>
         </is>
       </c>
     </row>
-    <row r="715">
-      <c r="A715" t="inlineStr">
+    <row r="714">
+      <c r="A714" t="inlineStr">
         <is>
           <t xml:space="preserve">「選挙」إنتخابات
 インティカーバート [intiKhaabaat]
@@ -15490,19 +15470,19 @@
 2311 nna-leb gov lb </t>
         </is>
       </c>
-      <c r="B715" t="inlineStr">
+      <c r="B714" t="inlineStr">
         <is>
           <t>images/「選挙」_img1.jpg</t>
         </is>
       </c>
-      <c r="C715" t="inlineStr">
+      <c r="C714" t="inlineStr">
         <is>
           <t>選挙 ,投票</t>
         </is>
       </c>
     </row>
-    <row r="716">
-      <c r="A716" t="inlineStr">
+    <row r="715">
+      <c r="A715" t="inlineStr">
         <is>
           <t xml:space="preserve">「待ちぼうけ」إنتظار
 インティザール [inti_Dhaar]
@@ -15511,19 +15491,19 @@
 1809 in4sser.tumblr </t>
         </is>
       </c>
-      <c r="B716" t="inlineStr">
+      <c r="B715" t="inlineStr">
         <is>
           <t>images/「待ちぼうけ」_img1.jpg</t>
         </is>
       </c>
-      <c r="C716" t="inlineStr">
+      <c r="C715" t="inlineStr">
         <is>
           <t>遅すぎ ,辛抱</t>
         </is>
       </c>
     </row>
-    <row r="717">
-      <c r="A717" t="inlineStr">
+    <row r="716">
+      <c r="A716" t="inlineStr">
         <is>
           <t xml:space="preserve">「試験」إختبار
 イクティバール [iKhtibaar]
@@ -15532,19 +15512,19 @@
 2109 出典不明 </t>
         </is>
       </c>
-      <c r="B717" t="inlineStr">
+      <c r="B716" t="inlineStr">
         <is>
           <t>images/「試験」_img1.jpg</t>
         </is>
       </c>
-      <c r="C717" t="inlineStr">
+      <c r="C716" t="inlineStr">
         <is>
           <t>テスト ,考査</t>
         </is>
       </c>
     </row>
-    <row r="718">
-      <c r="A718" t="inlineStr">
+    <row r="717">
+      <c r="A717" t="inlineStr">
         <is>
           <t xml:space="preserve">「チャンネル登録」اشتراك
 イシティラーク [iShtiraak]
@@ -15553,19 +15533,19 @@
 2308 </t>
         </is>
       </c>
-      <c r="B718" t="inlineStr">
+      <c r="B717" t="inlineStr">
         <is>
           <t>images/「チャンネル登録」_img1.jpg</t>
         </is>
       </c>
-      <c r="C718" t="inlineStr">
+      <c r="C717" t="inlineStr">
         <is>
           <t>Subscribe ,YouTube</t>
         </is>
       </c>
     </row>
-    <row r="719">
-      <c r="A719" t="inlineStr">
+    <row r="718">
+      <c r="A718" t="inlineStr">
         <is>
           <t xml:space="preserve">「スマイル」ابتسام
 イブティサーム [ibtisaam]
@@ -15573,37 +15553,37 @@
 1903 behance Written-Visuals </t>
         </is>
       </c>
+      <c r="B718" t="inlineStr">
+        <is>
+          <t>images/「スマイル」_img1.jpg</t>
+        </is>
+      </c>
+      <c r="C718" t="inlineStr">
+        <is>
+          <t>スマイリー ,ツ</t>
+        </is>
+      </c>
+    </row>
+    <row r="719">
+      <c r="A719" t="inlineStr">
+        <is>
+          <t xml:space="preserve">「身体の一部として…」
+2308 https://twitter.com/NatGeoMagArab/status/1528292080337813504 </t>
+        </is>
+      </c>
       <c r="B719" t="inlineStr">
         <is>
-          <t>images/「スマイル」_img1.jpg</t>
+          <t>images/「身体の一部として…」_img1.jpg</t>
         </is>
       </c>
       <c r="C719" t="inlineStr">
         <is>
-          <t>スマイリー ,ツ</t>
+          <t>手書き語学 ,カンガルー</t>
         </is>
       </c>
     </row>
     <row r="720">
       <c r="A720" t="inlineStr">
-        <is>
-          <t xml:space="preserve">「身体の一部として…」
-2308 https://twitter.com/NatGeoMagArab/status/1528292080337813504 </t>
-        </is>
-      </c>
-      <c r="B720" t="inlineStr">
-        <is>
-          <t>images/「身体の一部として…」_img1.jpg</t>
-        </is>
-      </c>
-      <c r="C720" t="inlineStr">
-        <is>
-          <t>手書き語学 ,カンガルー</t>
-        </is>
-      </c>
-    </row>
-    <row r="721">
-      <c r="A721" t="inlineStr">
         <is>
           <t xml:space="preserve">「ディスカバリー」إكتشاف
 イクティシャーフ [iktiShaaf]
@@ -15611,19 +15591,19 @@
 2308 tephanegabrielli com </t>
         </is>
       </c>
-      <c r="B721" t="inlineStr">
+      <c r="B720" t="inlineStr">
         <is>
           <t>images/「ディスカバリー」_img1.jpg</t>
         </is>
       </c>
-      <c r="C721" t="inlineStr">
+      <c r="C720" t="inlineStr">
         <is>
           <t>discovery ,デザイン</t>
         </is>
       </c>
     </row>
-    <row r="722">
-      <c r="A722" t="inlineStr">
+    <row r="721">
+      <c r="A721" t="inlineStr">
         <is>
           <t xml:space="preserve">「重力波の発見は新しい窓を開いた」
 فتَح اكتشاف موجات الجاذبية نافذة جديدة
@@ -15631,19 +15611,19 @@
 2308 https://twitter.com/SciTalk2U/status/1454891943440289793 </t>
         </is>
       </c>
-      <c r="B722" t="inlineStr">
+      <c r="B721" t="inlineStr">
         <is>
           <t>images/「重力波の発見は新しい窓を開いた」_img1.jpg</t>
         </is>
       </c>
-      <c r="C722" t="inlineStr">
+      <c r="C721" t="inlineStr">
         <is>
           <t>手書き語学 ,アラビア語 ,重力波</t>
         </is>
       </c>
     </row>
-    <row r="723">
-      <c r="A723" t="inlineStr">
+    <row r="722">
+      <c r="A722" t="inlineStr">
         <is>
           <t xml:space="preserve">「微笑みに微笑み。先にした人の方が美しい」
 الإبتسامة بالإبتسامة والبادئ أجمل
@@ -15652,19 +15632,19 @@
 2104 出典不明 </t>
         </is>
       </c>
-      <c r="B723" t="inlineStr">
+      <c r="B722" t="inlineStr">
         <is>
           <t>images/「微笑みに微笑み。先にした人の方が美し_img1.jpg,images/「微笑みに微笑み。先にした人の方が美し_img2.jpg</t>
         </is>
       </c>
-      <c r="C723" t="inlineStr">
+      <c r="C722" t="inlineStr">
         <is>
           <t>スマイル ,名言</t>
         </is>
       </c>
     </row>
-    <row r="724">
-      <c r="A724" t="inlineStr">
+    <row r="723">
+      <c r="A723" t="inlineStr">
         <is>
           <t xml:space="preserve">「笑顔」ابتسامة
 イブティサーマ [ibtisaama(tun)]
@@ -15673,19 +15653,19 @@
 2308 satokomatsu, minne </t>
         </is>
       </c>
-      <c r="B724" t="inlineStr">
+      <c r="B723" t="inlineStr">
         <is>
           <t>images/「笑顔」_img1.jpg</t>
         </is>
       </c>
-      <c r="C724" t="inlineStr">
+      <c r="C723" t="inlineStr">
         <is>
           <t>スマイル ,ツ</t>
         </is>
       </c>
     </row>
-    <row r="725">
-      <c r="A725" t="inlineStr">
+    <row r="724">
+      <c r="A724" t="inlineStr">
         <is>
           <t xml:space="preserve">「信仰」ايمان
 イーマーン ['iimaan]
@@ -15694,19 +15674,19 @@
 2506 instagram com/p/6ST-WHOOkJ/ </t>
         </is>
       </c>
-      <c r="B725" t="inlineStr">
+      <c r="B724" t="inlineStr">
         <is>
           <t>images/「信仰」_img1.jpg</t>
         </is>
       </c>
-      <c r="C725" t="inlineStr">
+      <c r="C724" t="inlineStr">
         <is>
           <t>宗教 ,信念</t>
         </is>
       </c>
     </row>
-    <row r="726">
-      <c r="A726" t="inlineStr">
+    <row r="725">
+      <c r="A725" t="inlineStr">
         <is>
           <t xml:space="preserve">「放送」إذاعة
 イザーア ['iDhaa*a]
@@ -15715,19 +15695,19 @@
 2404 heemades, Instagram </t>
         </is>
       </c>
-      <c r="B726" t="inlineStr">
+      <c r="B725" t="inlineStr">
         <is>
           <t>images/「放送」_img1.jpg</t>
         </is>
       </c>
-      <c r="C726" t="inlineStr">
+      <c r="C725" t="inlineStr">
         <is>
           <t>デザイン ,ラジオ</t>
         </is>
       </c>
     </row>
-    <row r="727">
-      <c r="A727" t="inlineStr">
+    <row r="726">
+      <c r="A726" t="inlineStr">
         <is>
           <t xml:space="preserve">「かきとりのちから」
 مهاراتي الإملائية
@@ -15736,19 +15716,19 @@
 2308 iqrawaoktoub.wordpress com </t>
         </is>
       </c>
-      <c r="B727" t="inlineStr">
+      <c r="B726" t="inlineStr">
         <is>
           <t>images/「かきとりのちから」_img1.jpg</t>
         </is>
       </c>
-      <c r="C727" t="inlineStr">
+      <c r="C726" t="inlineStr">
         <is>
           <t>国語 ,教材</t>
         </is>
       </c>
     </row>
-    <row r="728">
-      <c r="A728" t="inlineStr">
+    <row r="727">
+      <c r="A727" t="inlineStr">
         <is>
           <t xml:space="preserve">「歴史を作った男たち」
 رجال صنعوا التاريخ
@@ -15758,38 +15738,38 @@
 2410 https://x.gd/Wl5rJ </t>
         </is>
       </c>
-      <c r="B728" t="inlineStr">
+      <c r="B727" t="inlineStr">
         <is>
           <t>images/「歴史を作った男たち」_img1.jpg</t>
         </is>
       </c>
-      <c r="C728" t="inlineStr">
+      <c r="C727" t="inlineStr">
         <is>
           <t>偉人</t>
         </is>
       </c>
     </row>
-    <row r="729">
-      <c r="A729" t="inlineStr">
+    <row r="728">
+      <c r="A728" t="inlineStr">
         <is>
           <t xml:space="preserve">「無限の宇宙を旅した光」
 「何百年もの末にジェイムズ・ウェッブ望遠鏡のレンズの上に落ち、我々に遠い宇宙の美しさを見せてくれる。最も純粋な形と最も素晴らしい姿で」
 2308 https://twitter.com/NatGeoMagArab/status/1557811592636485632 </t>
         </is>
       </c>
-      <c r="B729" t="inlineStr">
+      <c r="B728" t="inlineStr">
         <is>
           <t>images/「無限の宇宙を旅した光」_img1.jpg</t>
         </is>
       </c>
-      <c r="C729" t="inlineStr">
+      <c r="C728" t="inlineStr">
         <is>
           <t>手書き語学 ,宇宙</t>
         </is>
       </c>
     </row>
-    <row r="730">
-      <c r="A730" t="inlineStr">
+    <row r="729">
+      <c r="A729" t="inlineStr">
         <is>
           <t xml:space="preserve">「日本好きになり行きたくなる20項」
 عشرون شيئا يجعلك تحب اليابان وترغب في زيارتها
@@ -15798,19 +15778,19 @@
 2308 wattpad </t>
         </is>
       </c>
-      <c r="B730" t="inlineStr">
+      <c r="B729" t="inlineStr">
         <is>
           <t>images/「日本好きになり行きたくなる20項」_img1.jpg</t>
         </is>
       </c>
-      <c r="C730" t="inlineStr">
+      <c r="C729" t="inlineStr">
         <is>
           <t>اليابان ,Japan</t>
         </is>
       </c>
     </row>
-    <row r="731">
-      <c r="A731" t="inlineStr">
+    <row r="730">
+      <c r="A730" t="inlineStr">
         <is>
           <t xml:space="preserve">「ピッタリの瞬間に撮影され、ドラゴンが火を噴いているように見える」
 التُقطت في اللحظة المناسبة لتبدو مثل تنين ينفث اللهب
@@ -15818,19 +15798,19 @@
 2509 https://twitter.com/NatGeoMagArab/status/1588780660269150208 </t>
         </is>
       </c>
-      <c r="B731" t="inlineStr">
+      <c r="B730" t="inlineStr">
         <is>
           <t>images/「ピッタリの瞬間に撮影され、ドラゴンが_img1.jpg,images/ 「ピッタリの瞬間に撮影され、ドラゴンが_img2.jpg</t>
         </is>
       </c>
-      <c r="C731" t="inlineStr">
+      <c r="C730" t="inlineStr">
         <is>
           <t xml:space="preserve">ドラゴン </t>
         </is>
       </c>
     </row>
-    <row r="732">
-      <c r="A732" t="inlineStr">
+    <row r="731">
+      <c r="A731" t="inlineStr">
         <is>
           <t xml:space="preserve">「満足は不滅の宝である」
 القَناعَةُ كنز لا يَفنَى
@@ -15840,55 +15820,55 @@
 2308 kareem mrghani </t>
         </is>
       </c>
+      <c r="B731" t="inlineStr">
+        <is>
+          <t>images/「満足は不滅の宝である」_img1.jpg</t>
+        </is>
+      </c>
+      <c r="C731" t="inlineStr">
+        <is>
+          <t>幸福度</t>
+        </is>
+      </c>
+    </row>
+    <row r="732">
+      <c r="A732" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ゴシキセイガイインコ。
+2409 https://twitter.com/NatGeoMagArab/status/1600022262014676992 </t>
+        </is>
+      </c>
       <c r="B732" t="inlineStr">
         <is>
-          <t>images/「満足は不滅の宝である」_img1.jpg</t>
+          <t>images/ゴシキセイガイインコ。_img1.jpg</t>
         </is>
       </c>
       <c r="C732" t="inlineStr">
         <is>
-          <t>幸福度</t>
+          <t>手書き語学 ,アラビア語,オウム</t>
         </is>
       </c>
     </row>
     <row r="733">
       <c r="A733" t="inlineStr">
         <is>
-          <t xml:space="preserve">ゴシキセイガイインコ。
-2409 https://twitter.com/NatGeoMagArab/status/1600022262014676992 </t>
+          <t xml:space="preserve">モモンガ。
+2403 https://twitter.com/NatGeoMagArab/status/1552541872966344704 </t>
         </is>
       </c>
       <c r="B733" t="inlineStr">
         <is>
-          <t>images/ゴシキセイガイインコ。_img1.jpg</t>
+          <t>images/モモンガ。_img1.jpg,images/ モモンガ。_img2.jpg</t>
         </is>
       </c>
       <c r="C733" t="inlineStr">
         <is>
-          <t>手書き語学 ,アラビア語,オウム</t>
+          <t>手書き語学 ,アラビア語 ,モモンガ</t>
         </is>
       </c>
     </row>
     <row r="734">
       <c r="A734" t="inlineStr">
-        <is>
-          <t xml:space="preserve">モモンガ。
-2403 https://twitter.com/NatGeoMagArab/status/1552541872966344704 </t>
-        </is>
-      </c>
-      <c r="B734" t="inlineStr">
-        <is>
-          <t>images/モモンガ。_img1.jpg,images/ モモンガ。_img2.jpg</t>
-        </is>
-      </c>
-      <c r="C734" t="inlineStr">
-        <is>
-          <t>手書き語学 ,アラビア語 ,モモンガ</t>
-        </is>
-      </c>
-    </row>
-    <row r="735">
-      <c r="A735" t="inlineStr">
         <is>
           <t xml:space="preserve">「象の群れ。ドローンの音から逃げている」
 قطيع من الفيلة يفر هاربًا من صوت الدرون
@@ -15900,56 +15880,56 @@
 2009 https://twitter.com/NatGeoMagArab/status/1302970033627258881 </t>
         </is>
       </c>
+      <c r="B734" t="inlineStr">
+        <is>
+          <t>images/「象の群れ。ドローンの音から逃げている.jpg</t>
+        </is>
+      </c>
+      <c r="C734" t="inlineStr">
+        <is>
+          <t>ゾウ ,ドローン</t>
+        </is>
+      </c>
+    </row>
+    <row r="735">
+      <c r="A735" t="inlineStr">
+        <is>
+          <t xml:space="preserve">カルマン線。
+2308 https://twitter.com/NatGeoMagArab/status/1536436999522881536 </t>
+        </is>
+      </c>
       <c r="B735" t="inlineStr">
         <is>
-          <t>images/「象の群れ。ドローンの音から逃げている.jpg</t>
+          <t>images/カルマン線。_img1.jpg</t>
         </is>
       </c>
       <c r="C735" t="inlineStr">
         <is>
-          <t>ゾウ ,ドローン</t>
+          <t xml:space="preserve">手書き語学 ,アラビア語 ,宇宙 </t>
         </is>
       </c>
     </row>
     <row r="736">
       <c r="A736" t="inlineStr">
-        <is>
-          <t xml:space="preserve">カルマン線。
-2308 https://twitter.com/NatGeoMagArab/status/1536436999522881536 </t>
-        </is>
-      </c>
-      <c r="B736" t="inlineStr">
-        <is>
-          <t>images/カルマン線。_img1.jpg</t>
-        </is>
-      </c>
-      <c r="C736" t="inlineStr">
-        <is>
-          <t xml:space="preserve">手書き語学 ,アラビア語 ,宇宙 </t>
-        </is>
-      </c>
-    </row>
-    <row r="737">
-      <c r="A737" t="inlineStr">
         <is>
           <t xml:space="preserve">「恥ずかしがり屋のマヌルネコと暖かい朝の太陽光線」
 ⁦「二つの美しいもの」[Shay'-ayni jamiil-ayni] 属格：「物」( شيء )[Shay']・「美しい」( جميل )[jamiil]⁩
 2309 https://twitter.com/NatGeoMagArab/status/1697512148820504912 </t>
         </is>
       </c>
-      <c r="B737" t="inlineStr">
+      <c r="B736" t="inlineStr">
         <is>
           <t>images/「恥ずかしがり屋のマヌルネコと暖かい朝_img1.jpg</t>
         </is>
       </c>
-      <c r="C737" t="inlineStr">
+      <c r="C736" t="inlineStr">
         <is>
           <t>手書き語学 ,アラビア語 ,マヌルネコ</t>
         </is>
       </c>
     </row>
-    <row r="738">
-      <c r="A738" t="inlineStr">
+    <row r="737">
+      <c r="A737" t="inlineStr">
         <is>
           <t xml:space="preserve">「二回失敗しているペンギン」
 بطريق يفشل مرتين
@@ -15959,19 +15939,19 @@
 2308 https://twitter.com/NatGeoMagArab/status/1479483133766426626 </t>
         </is>
       </c>
-      <c r="B738" t="inlineStr">
+      <c r="B737" t="inlineStr">
         <is>
           <t>images/「二回失敗しているペンギン」_img1.jpg</t>
         </is>
       </c>
-      <c r="C738" t="inlineStr">
+      <c r="C737" t="inlineStr">
         <is>
           <t>ペンギン ,動物</t>
         </is>
       </c>
     </row>
-    <row r="739">
-      <c r="A739" t="inlineStr">
+    <row r="738">
+      <c r="A738" t="inlineStr">
         <is>
           <t xml:space="preserve">「2億光年の彼方できらめく炎と光」
 وهج ووميض يتلألأ على بعد 200 مليون سنة ضوئية
@@ -15982,15 +15962,15 @@
 2010 https://twitter.com/NatGeoMagArab/status/1303415502673342464 </t>
         </is>
       </c>
-      <c r="B739" t="inlineStr"/>
-      <c r="C739" t="inlineStr">
+      <c r="B738" t="inlineStr"/>
+      <c r="C738" t="inlineStr">
         <is>
           <t>宇宙 ,銀河</t>
         </is>
       </c>
     </row>
-    <row r="740">
-      <c r="A740" t="inlineStr">
+    <row r="739">
+      <c r="A739" t="inlineStr">
         <is>
           <t xml:space="preserve">「さまよう黒猫」قطة سوداء تجوب
 キッタトゥン・サウダーウ・タジューブ [qi^_tatun sawdaa'u ta-juub]
@@ -15999,19 +15979,19 @@
 2308 https://twitter.com/NatGeoMagArab/status/1532973177453760512 </t>
         </is>
       </c>
-      <c r="B740" t="inlineStr">
+      <c r="B739" t="inlineStr">
         <is>
           <t>images/「さまよう黒猫」_img1.jpg,images/ 「さまよう黒猫」_img2.jpg</t>
         </is>
       </c>
-      <c r="C740" t="inlineStr">
+      <c r="C739" t="inlineStr">
         <is>
           <t xml:space="preserve">手書き語学 ,モロッコ </t>
         </is>
       </c>
     </row>
-    <row r="741">
-      <c r="A741" t="inlineStr">
+    <row r="740">
+      <c r="A740" t="inlineStr">
         <is>
           <t xml:space="preserve">「サイのざらざらした皮を利用して自分の体を掻くネコ」
 قطة تستغل جلد الكركدن الخشن لحك جسدها
@@ -16020,19 +16000,19 @@
 2308 https://twitter.com/NatGeoMagArab/status/1476855740929216517 </t>
         </is>
       </c>
-      <c r="B741" t="inlineStr">
+      <c r="B740" t="inlineStr">
         <is>
           <t>images/「サイのざらざらした皮を利用して自分の_img1.jpg</t>
         </is>
       </c>
-      <c r="C741" t="inlineStr">
+      <c r="C740" t="inlineStr">
         <is>
           <t>サイ ,チェコ</t>
         </is>
       </c>
     </row>
-    <row r="742">
-      <c r="A742" t="inlineStr">
+    <row r="741">
+      <c r="A741" t="inlineStr">
         <is>
           <t xml:space="preserve">「沈まぬ太陽」شمس لا تغيب
 シャムス・ラー・タギーブ [Shams laa ta-Ghiib]
@@ -16041,19 +16021,19 @@
 2308 AHMED ELASSAL </t>
         </is>
       </c>
-      <c r="B742" t="inlineStr">
+      <c r="B741" t="inlineStr">
         <is>
           <t>images/「沈まぬ太陽」_img1.jpg</t>
         </is>
       </c>
-      <c r="C742" t="inlineStr">
+      <c r="C741" t="inlineStr">
         <is>
           <t>帝国 ,白夜</t>
         </is>
       </c>
     </row>
-    <row r="743">
-      <c r="A743" t="inlineStr">
+    <row r="742">
+      <c r="A742" t="inlineStr">
         <is>
           <t xml:space="preserve">「子供に食べさせている忍耐強い母親」
 أم صبورة تطعم صغيرها
@@ -16062,19 +16042,19 @@
 2308 https://twitter.com/natgeomagarab/status/1585572054509957120 </t>
         </is>
       </c>
-      <c r="B743" t="inlineStr">
+      <c r="B742" t="inlineStr">
         <is>
           <t>images/「子供に食べさせている忍耐強い母親」_img1.jpg</t>
         </is>
       </c>
-      <c r="C743" t="inlineStr">
+      <c r="C742" t="inlineStr">
         <is>
           <t>手書き語学 ,アラビア語 ,ミヤコドリ</t>
         </is>
       </c>
     </row>
-    <row r="744">
-      <c r="A744" t="inlineStr">
+    <row r="743">
+      <c r="A743" t="inlineStr">
         <is>
           <t xml:space="preserve">「コーヒーは繰り返さない恋物語」
 القهوة قصة عشق لن تتكرر
@@ -16084,19 +16064,19 @@
 2403 pin it/7tvd8Wc </t>
         </is>
       </c>
-      <c r="B744" t="inlineStr">
+      <c r="B743" t="inlineStr">
         <is>
           <t>images/「コーヒーは繰り返さない恋物語」_img1.jpg</t>
         </is>
       </c>
-      <c r="C744" t="inlineStr">
+      <c r="C743" t="inlineStr">
         <is>
           <t>コーヒー ,名言</t>
         </is>
       </c>
     </row>
-    <row r="745">
-      <c r="A745" t="inlineStr">
+    <row r="744">
+      <c r="A744" t="inlineStr">
         <is>
           <t xml:space="preserve">「星々で飾られた空。魅惑的な色合いで黄昏の美を満たしている」
 سماء مرصعة بالنجوم تضفي لمسة سحرية على جمال الشفق
@@ -16104,19 +16084,19 @@
 2010 https://twitter.com/NatGeoMagArab/status/1303777701975584768 </t>
         </is>
       </c>
-      <c r="B745" t="inlineStr">
+      <c r="B744" t="inlineStr">
         <is>
           <t>images/「星々で飾られた空。魅惑的な色合いで黄.png</t>
         </is>
       </c>
-      <c r="C745" t="inlineStr">
+      <c r="C744" t="inlineStr">
         <is>
           <t>星空 ,宇宙</t>
         </is>
       </c>
     </row>
-    <row r="746">
-      <c r="A746" t="inlineStr">
+    <row r="745">
+      <c r="A745" t="inlineStr">
         <is>
           <t xml:space="preserve">「国際宇宙ステーションからの写真。巨大な台風『ハイシェン（海神）』を映している」
 لقطات من محطة الفضاء الدولية تظهر إعصار "هايشن" الهائل
@@ -16124,19 +16104,19 @@
 2403 https://twitter.com/NatGeoMagArab/status/1302871968522235904 </t>
         </is>
       </c>
-      <c r="B746" t="inlineStr">
+      <c r="B745" t="inlineStr">
         <is>
           <t>images/「国際宇宙ステーションからの写真。巨大.png</t>
         </is>
       </c>
-      <c r="C746" t="inlineStr">
+      <c r="C745" t="inlineStr">
         <is>
           <t>台風</t>
         </is>
       </c>
     </row>
-    <row r="747">
-      <c r="A747" t="inlineStr">
+    <row r="746">
+      <c r="A746" t="inlineStr">
         <is>
           <t xml:space="preserve">「草を食む幸運な子羊たち」
 خراف محظوظة ترعى
@@ -16146,19 +16126,19 @@
 2308 https://twitter.com/NatGeoMagArab/status/1490211393554972676 </t>
         </is>
       </c>
-      <c r="B747" t="inlineStr">
+      <c r="B746" t="inlineStr">
         <is>
           <t>images/「草を食む幸運な子羊たち」_img1.jpg,images/ 「草を食む幸運な子羊たち」_img2.jpg</t>
         </is>
       </c>
-      <c r="C747" t="inlineStr">
+      <c r="C746" t="inlineStr">
         <is>
           <t>羊 ,アイルランド</t>
         </is>
       </c>
     </row>
-    <row r="748">
-      <c r="A748" t="inlineStr">
+    <row r="747">
+      <c r="A747" t="inlineStr">
         <is>
           <t xml:space="preserve">「お金で買えぬ10のもの」
 ١٠ أشياء لا تشترى بالمال
@@ -16168,19 +16148,19 @@
 2308 ayb124 </t>
         </is>
       </c>
-      <c r="B748" t="inlineStr">
+      <c r="B747" t="inlineStr">
         <is>
           <t>images/「お金で買えぬ10のもの」_img1.jpg</t>
         </is>
       </c>
-      <c r="C748" t="inlineStr">
+      <c r="C747" t="inlineStr">
         <is>
           <t>価値 ,購買</t>
         </is>
       </c>
     </row>
-    <row r="749">
-      <c r="A749" t="inlineStr">
+    <row r="748">
+      <c r="A748" t="inlineStr">
         <is>
           <t xml:space="preserve">「お金では買えないよ」
 هي أشْيَاءٌ لا تُشْتَرَى
@@ -16190,19 +16170,19 @@
 1906 mardy_zaawely, Instagram </t>
         </is>
       </c>
-      <c r="B749" t="inlineStr">
+      <c r="B748" t="inlineStr">
         <is>
           <t>images/「お金では買えないよ」_img1.jpg</t>
         </is>
       </c>
-      <c r="C749" t="inlineStr">
+      <c r="C748" t="inlineStr">
         <is>
           <t>マスターカード ,価値</t>
         </is>
       </c>
     </row>
-    <row r="750">
-      <c r="A750" t="inlineStr">
+    <row r="749">
+      <c r="A749" t="inlineStr">
         <is>
           <t xml:space="preserve">「好奇心旺盛なホッキョクギツネ」
 ثعلب قطبي يملؤه الفضول
@@ -16212,15 +16192,15 @@
 2308 https://twitter.com/natgeomagarab/status/1157592172968808449 </t>
         </is>
       </c>
-      <c r="B750" t="inlineStr"/>
-      <c r="C750" t="inlineStr">
+      <c r="B749" t="inlineStr"/>
+      <c r="C749" t="inlineStr">
         <is>
           <t>ファーストコンタクト ,キツネ</t>
         </is>
       </c>
     </row>
-    <row r="751">
-      <c r="A751" t="inlineStr">
+    <row r="750">
+      <c r="A750" t="inlineStr">
         <is>
           <t xml:space="preserve">「グレンダイザーのいる国は死にません」
 لنْ يَموتَ شَعبٌ لدَيهِ غرندايزر
@@ -16229,56 +16209,56 @@
 2308 https://www.aljarida.com/articles/1462241741574732100/ </t>
         </is>
       </c>
+      <c r="B750" t="inlineStr">
+        <is>
+          <t>images/「グレンダイザーのいる国は死にません」_img1.jpg</t>
+        </is>
+      </c>
+      <c r="C750" t="inlineStr">
+        <is>
+          <t>UFOロボ ,アニメ</t>
+        </is>
+      </c>
+    </row>
+    <row r="751">
+      <c r="A751" t="inlineStr">
+        <is>
+          <t xml:space="preserve">「凍結路面を運転中、彼女は嫌な場面に居合わせた」
+2408 https://twitter.com/NatGeoMagArab/status/1610305209657626625 </t>
+        </is>
+      </c>
       <c r="B751" t="inlineStr">
         <is>
-          <t>images/「グレンダイザーのいる国は死にません」_img1.jpg</t>
+          <t>images/「凍結路面を運転中、彼女は嫌な場面に居_img1.jpg</t>
         </is>
       </c>
       <c r="C751" t="inlineStr">
         <is>
-          <t>UFOロボ ,アニメ</t>
+          <t>手書き語学 ,アラビア語 ,路面凍結</t>
         </is>
       </c>
     </row>
     <row r="752">
       <c r="A752" t="inlineStr">
-        <is>
-          <t xml:space="preserve">「凍結路面を運転中、彼女は嫌な場面に居合わせた」
-2408 https://twitter.com/NatGeoMagArab/status/1610305209657626625 </t>
-        </is>
-      </c>
-      <c r="B752" t="inlineStr">
-        <is>
-          <t>images/「凍結路面を運転中、彼女は嫌な場面に居_img1.jpg</t>
-        </is>
-      </c>
-      <c r="C752" t="inlineStr">
-        <is>
-          <t>手書き語学 ,アラビア語 ,路面凍結</t>
-        </is>
-      </c>
-    </row>
-    <row r="753">
-      <c r="A753" t="inlineStr">
         <is>
           <t xml:space="preserve">「虹が美しさを加えている、アルパカという動物の美しいショット」
 ⁦「美しいショット」[laq_tatun jamiilatun]：「ショット」( لقطة )[laq_ta]：( ـلٌ )[-lun]・( ـقٌ )[-qun]・( ـطٌ )[-_tun]・( ـةٌ )[-tun]⁩
 2308 https://twitter.com/natgeomagarab/status/1155115655928004608 </t>
         </is>
       </c>
-      <c r="B753" t="inlineStr">
+      <c r="B752" t="inlineStr">
         <is>
           <t>images/「虹が美しさを加えている、アルパカとい_img1.jpg</t>
         </is>
       </c>
-      <c r="C753" t="inlineStr">
+      <c r="C752" t="inlineStr">
         <is>
           <t>モフモフ ,アルパカ</t>
         </is>
       </c>
     </row>
-    <row r="754">
-      <c r="A754" t="inlineStr">
+    <row r="753">
+      <c r="A753" t="inlineStr">
         <is>
           <t xml:space="preserve">「幸せは…全然思いもよらない所からやって来る」
 السعادة تأتينا من أماكن لم نكن نتوقعها أبداً
@@ -16287,19 +16267,19 @@
 2109 出典不明 </t>
         </is>
       </c>
-      <c r="B754" t="inlineStr">
+      <c r="B753" t="inlineStr">
         <is>
           <t>images/「幸せは…全然思いもよらない所からやっ_img1.jpg,images/ 「幸せは…全然思いもよらない所からやっ_img2.jpg</t>
         </is>
       </c>
-      <c r="C754" t="inlineStr">
+      <c r="C753" t="inlineStr">
         <is>
           <t>訪れ ,予想</t>
         </is>
       </c>
     </row>
-    <row r="755">
-      <c r="A755" t="inlineStr">
+    <row r="754">
+      <c r="A754" t="inlineStr">
         <is>
           <t xml:space="preserve">「あらゆる問題は、食べ物が解決してくれる」
 كل مشكلة ولها أكلة تحلها
@@ -16308,19 +16288,19 @@
 1909 ALQA AN 878 </t>
         </is>
       </c>
-      <c r="B755" t="inlineStr">
+      <c r="B754" t="inlineStr">
         <is>
           <t>images/「あらゆる問題は、食べ物が解決してくれ_img1.jpg</t>
         </is>
       </c>
-      <c r="C755" t="inlineStr">
+      <c r="C754" t="inlineStr">
         <is>
           <t>ストレス ,精神</t>
         </is>
       </c>
     </row>
-    <row r="756">
-      <c r="A756" t="inlineStr">
+    <row r="755">
+      <c r="A755" t="inlineStr">
         <is>
           <t xml:space="preserve">「冬で私が好きな物」
 أشياء أحبها بالشتاء
@@ -16330,19 +16310,19 @@
 2109 出典不明 </t>
         </is>
       </c>
-      <c r="B756" t="inlineStr">
+      <c r="B755" t="inlineStr">
         <is>
           <t>images/「冬で私が好きな物」_img1.jpg</t>
         </is>
       </c>
-      <c r="C756" t="inlineStr">
+      <c r="C755" t="inlineStr">
         <is>
           <t>季節 ,冬</t>
         </is>
       </c>
     </row>
-    <row r="757">
-      <c r="A757" t="inlineStr">
+    <row r="756">
+      <c r="A756" t="inlineStr">
         <is>
           <t xml:space="preserve">「お金で買うことの出来ない物」
 أشياء لا تستطيع شراءها بالمال
@@ -16352,19 +16332,19 @@
 2409 https://x.com/akhbarak/status/1038402708414373888 </t>
         </is>
       </c>
-      <c r="B757" t="inlineStr">
+      <c r="B756" t="inlineStr">
         <is>
           <t>images/「お金で買うことの出来ない物」_img1.jpg,images/ 「お金で買うことの出来ない物」_img2.jpg</t>
         </is>
       </c>
-      <c r="C757" t="inlineStr">
+      <c r="C756" t="inlineStr">
         <is>
           <t>ショッピング ,価値</t>
         </is>
       </c>
     </row>
-    <row r="758">
-      <c r="A758" t="inlineStr">
+    <row r="757">
+      <c r="A757" t="inlineStr">
         <is>
           <t xml:space="preserve">「私たちが愛する言葉」
 كلماتٌ نُحبّها
@@ -16374,19 +16354,19 @@
 2109 جليل خزعل </t>
         </is>
       </c>
-      <c r="B758" t="inlineStr">
+      <c r="B757" t="inlineStr">
         <is>
           <t>images/「私たちが愛する言葉」_img1.jpg</t>
         </is>
       </c>
-      <c r="C758" t="inlineStr">
+      <c r="C757" t="inlineStr">
         <is>
           <t>花 ,贈り物</t>
         </is>
       </c>
     </row>
-    <row r="759">
-      <c r="A759" t="inlineStr">
+    <row r="758">
+      <c r="A758" t="inlineStr">
         <is>
           <t xml:space="preserve">「お茶についてあなたが知らない10の事実」
 عشر معلومات لا تعرفها عن الشاي
@@ -16395,19 +16375,19 @@
 2012 http://ara.tv/6syq2 </t>
         </is>
       </c>
-      <c r="B759" t="inlineStr">
+      <c r="B758" t="inlineStr">
         <is>
           <t>images/「お茶についてあなたが知らない10の事_img1.jpg</t>
         </is>
       </c>
-      <c r="C759" t="inlineStr">
+      <c r="C758" t="inlineStr">
         <is>
           <t>神農</t>
         </is>
       </c>
     </row>
-    <row r="760">
-      <c r="A760" t="inlineStr">
+    <row r="759">
+      <c r="A759" t="inlineStr">
         <is>
           <t xml:space="preserve">「大きくなったウソ」
 الكذبة الّتي كبرت
@@ -16417,19 +16397,19 @@
 2509 سلسلة الحلزونة </t>
         </is>
       </c>
-      <c r="B760" t="inlineStr">
+      <c r="B759" t="inlineStr">
         <is>
           <t>images/「大きくなったウソ」_img1.jpg</t>
         </is>
       </c>
-      <c r="C760" t="inlineStr">
+      <c r="C759" t="inlineStr">
         <is>
           <t>絵本</t>
         </is>
       </c>
     </row>
-    <row r="761">
-      <c r="A761" t="inlineStr">
+    <row r="760">
+      <c r="A760" t="inlineStr">
         <is>
           <t xml:space="preserve">「自分に合った掃除機を買うには？」
 كيف تشتري المكنسة الكهربائية التي تناسبك؟
@@ -16438,19 +16418,19 @@
 2106 ts3a com </t>
         </is>
       </c>
-      <c r="B761" t="inlineStr">
+      <c r="B760" t="inlineStr">
         <is>
           <t>images/「自分に合った掃除機を買うには？」_img1.jpg</t>
         </is>
       </c>
-      <c r="C761" t="inlineStr">
+      <c r="C760" t="inlineStr">
         <is>
           <t>家電 ,掃除</t>
         </is>
       </c>
     </row>
-    <row r="762">
-      <c r="A762" t="inlineStr">
+    <row r="761">
+      <c r="A761" t="inlineStr">
         <is>
           <t xml:space="preserve">「仮にこれが批判の数としよう」
 لنفرض ان عدد الذين ينتقدونك
@@ -16461,19 +16441,19 @@
 2504 出典不明 </t>
         </is>
       </c>
-      <c r="B762" t="inlineStr">
+      <c r="B761" t="inlineStr">
         <is>
           <t>images/「仮にこれが批判の数としよう」_img1.jpg</t>
         </is>
       </c>
-      <c r="C762" t="inlineStr">
+      <c r="C761" t="inlineStr">
         <is>
           <t>アンチ</t>
         </is>
       </c>
     </row>
-    <row r="763">
-      <c r="A763" t="inlineStr">
+    <row r="762">
+      <c r="A762" t="inlineStr">
         <is>
           <t xml:space="preserve">「ここに見えるのは何？」
 ما الذي تراه هنا؟
@@ -16483,15 +16463,15 @@
 2204 https://twitter.com/NatGeoMagArab/status/1506933850617700352 </t>
         </is>
       </c>
-      <c r="B763" t="inlineStr"/>
-      <c r="C763" t="inlineStr">
+      <c r="B762" t="inlineStr"/>
+      <c r="C762" t="inlineStr">
         <is>
           <t xml:space="preserve">ペンギン </t>
         </is>
       </c>
     </row>
-    <row r="764">
-      <c r="A764" t="inlineStr">
+    <row r="763">
+      <c r="A763" t="inlineStr">
         <is>
           <t xml:space="preserve">「今日辛いこと、明日は平気だろう」
 ما يؤلم اليوم سيهون غدًا
@@ -16501,19 +16481,19 @@
 2308 basmahjeff </t>
         </is>
       </c>
-      <c r="B764" t="inlineStr">
+      <c r="B763" t="inlineStr">
         <is>
           <t>images/「今日辛いこと、明日は平気だろう」_img1.jpg</t>
         </is>
       </c>
-      <c r="C764" t="inlineStr">
+      <c r="C763" t="inlineStr">
         <is>
           <t>悩み ,達観</t>
         </is>
       </c>
     </row>
-    <row r="765">
-      <c r="A765" t="inlineStr">
+    <row r="764">
+      <c r="A764" t="inlineStr">
         <is>
           <t xml:space="preserve">「自分のすることを好きでなきゃ」
 عليك أن تحب ما تفعل
@@ -16522,19 +16502,19 @@
 1810 Ahmed Elhakeem </t>
         </is>
       </c>
-      <c r="B765" t="inlineStr">
+      <c r="B764" t="inlineStr">
         <is>
           <t>images/「自分のすることを好きでなきゃ」_img1.jpg</t>
         </is>
       </c>
-      <c r="C765" t="inlineStr">
+      <c r="C764" t="inlineStr">
         <is>
           <t>転職 ,かわいい</t>
         </is>
       </c>
     </row>
-    <row r="766">
-      <c r="A766" t="inlineStr">
+    <row r="765">
+      <c r="A765" t="inlineStr">
         <is>
           <t xml:space="preserve">「この地上に生き甲斐あり」
 على هذه الأرض ما يستحق الحياة
@@ -16544,19 +16524,19 @@
 2308 Mahmoud Gafar </t>
         </is>
       </c>
-      <c r="B766" t="inlineStr">
+      <c r="B765" t="inlineStr">
         <is>
           <t>images/「この地上に生き甲斐あり」_img1.jpg</t>
         </is>
       </c>
-      <c r="C766" t="inlineStr">
+      <c r="C765" t="inlineStr">
         <is>
           <t>詩</t>
         </is>
       </c>
     </row>
-    <row r="767">
-      <c r="A767" t="inlineStr">
+    <row r="766">
+      <c r="A766" t="inlineStr">
         <is>
           <t xml:space="preserve">「おそらく、あなたの求めるものはあるだろう」
 لعلَّ ما تَرجوهُ سيَكونُ
@@ -16566,19 +16546,19 @@
 2308 PIXEL Instagram </t>
         </is>
       </c>
-      <c r="B767" t="inlineStr">
+      <c r="B766" t="inlineStr">
         <is>
           <t>images/「おそらく、あなたの求めるものはあるだ_img1.jpg</t>
         </is>
       </c>
-      <c r="C767" t="inlineStr">
+      <c r="C766" t="inlineStr">
         <is>
           <t>願い ,信仰</t>
         </is>
       </c>
     </row>
-    <row r="768">
-      <c r="A768" t="inlineStr">
+    <row r="767">
+      <c r="A767" t="inlineStr">
         <is>
           <t xml:space="preserve">「オレンジの効能が何か知っていますか？」
 هل تعرف ما هي فوائد البرتقال؟
@@ -16588,19 +16568,19 @@
 2308 sadahadhramowt com </t>
         </is>
       </c>
-      <c r="B768" t="inlineStr">
+      <c r="B767" t="inlineStr">
         <is>
           <t>images/「オレンジの効能が何か知っていますか？_img1.jpg</t>
         </is>
       </c>
-      <c r="C768" t="inlineStr">
+      <c r="C767" t="inlineStr">
         <is>
           <t>オレンジ ,フルーツ</t>
         </is>
       </c>
     </row>
-    <row r="769">
-      <c r="A769" t="inlineStr">
+    <row r="768">
+      <c r="A768" t="inlineStr">
         <is>
           <t xml:space="preserve">「遊ぶパンダの光景より可愛いものがありますか？」
 هل هناك ما هو ألطف من مشاهدة الباندا وهي تلعب؟
@@ -16608,19 +16588,19 @@
 2308 https://twitter.com/NatGeoMagArab/status/1494612797858074626 </t>
         </is>
       </c>
-      <c r="B769" t="inlineStr">
+      <c r="B768" t="inlineStr">
         <is>
           <t>images/「遊ぶパンダの光景より可愛いものがあり_img1.jpg</t>
         </is>
       </c>
-      <c r="C769" t="inlineStr">
+      <c r="C768" t="inlineStr">
         <is>
           <t>パンダ ,モコモコ</t>
         </is>
       </c>
     </row>
-    <row r="770">
-      <c r="A770" t="inlineStr">
+    <row r="769">
+      <c r="A769" t="inlineStr">
         <is>
           <t xml:space="preserve">「大事なのは何者だったかじゃない。何者になるかだ」
 ليسَ المُهم ما كُنتَ بل مَا ستكون
@@ -16629,19 +16609,19 @@
 2308 出典不明 </t>
         </is>
       </c>
-      <c r="B770" t="inlineStr">
+      <c r="B769" t="inlineStr">
         <is>
           <t>images/「大事なのは何者だったかじゃない。何者_img1.jpg</t>
         </is>
       </c>
-      <c r="C770" t="inlineStr">
+      <c r="C769" t="inlineStr">
         <is>
           <t>自己実現 ,存在価値</t>
         </is>
       </c>
     </row>
-    <row r="771">
-      <c r="A771" t="inlineStr">
+    <row r="770">
+      <c r="A770" t="inlineStr">
         <is>
           <t xml:space="preserve">「あなたであれ。ありのままが美しいから」
 كُنْ أَنْتَ لأنك جميل كما أنت
@@ -16650,19 +16630,19 @@
 2308 IDREES DESIGN </t>
         </is>
       </c>
-      <c r="B771" t="inlineStr">
+      <c r="B770" t="inlineStr">
         <is>
           <t>images/「あなたであれ。ありのままが美しいから_img1.jpg</t>
         </is>
       </c>
-      <c r="C771" t="inlineStr">
+      <c r="C770" t="inlineStr">
         <is>
           <t>自己肯定 ,BeYourself</t>
         </is>
       </c>
     </row>
-    <row r="772">
-      <c r="A772" t="inlineStr">
+    <row r="771">
+      <c r="A771" t="inlineStr">
         <is>
           <t xml:space="preserve">「恐れの中に生きる者は決して自由になれない」
 من يعش في خوف لن يكون حرا أبدا
@@ -16671,19 +16651,19 @@
 2111 rjeem com </t>
         </is>
       </c>
-      <c r="B772" t="inlineStr">
+      <c r="B771" t="inlineStr">
         <is>
           <t>images/「恐れの中に生きる者は決して自由になれ_img1.jpg,images/ 「恐れの中に生きる者は決して自由になれ_img2.jpg</t>
         </is>
       </c>
-      <c r="C772" t="inlineStr">
+      <c r="C771" t="inlineStr">
         <is>
           <t>勇気 ,壁</t>
         </is>
       </c>
     </row>
-    <row r="773">
-      <c r="A773" t="inlineStr">
+    <row r="772">
+      <c r="A772" t="inlineStr">
         <is>
           <t xml:space="preserve">「己の翼を信じる者は己の重さを案じない」
 من يثق في جناحيه لن يهتم لوزنه
@@ -16692,19 +16672,19 @@
 2308 kmrghani </t>
         </is>
       </c>
-      <c r="B773" t="inlineStr">
+      <c r="B772" t="inlineStr">
         <is>
           <t>images/「己の翼を信じる者は己の重さを案じない_img1.jpg</t>
         </is>
       </c>
-      <c r="C773" t="inlineStr">
+      <c r="C772" t="inlineStr">
         <is>
           <t>自信</t>
         </is>
       </c>
     </row>
-    <row r="774">
-      <c r="A774" t="inlineStr">
+    <row r="773">
+      <c r="A773" t="inlineStr">
         <is>
           <t xml:space="preserve">「珈琲で一番大事な事！誰と飲むか？」
 الأهم من القهوة!! من ستشربها معه؟
@@ -16713,19 +16693,19 @@
 1812 gwid3.tumblr </t>
         </is>
       </c>
-      <c r="B774" t="inlineStr">
+      <c r="B773" t="inlineStr">
         <is>
           <t>images/「珈琲で一番大事な事！誰と飲むか？」_img1.jpg</t>
         </is>
       </c>
-      <c r="C774" t="inlineStr">
+      <c r="C773" t="inlineStr">
         <is>
           <t>コーヒー ,名言</t>
         </is>
       </c>
     </row>
-    <row r="775">
-      <c r="A775" t="inlineStr">
+    <row r="774">
+      <c r="A774" t="inlineStr">
         <is>
           <t xml:space="preserve">「人生は美しい、そう望んだ者には。」
 الحياة جَميلَة .. لمن أراد ذلك
@@ -16735,19 +16715,19 @@
 2109 出典不明 </t>
         </is>
       </c>
-      <c r="B775" t="inlineStr">
+      <c r="B774" t="inlineStr">
         <is>
           <t>images/「人生は美しい、そう望んだ者には。」_img1.jpg</t>
         </is>
       </c>
-      <c r="C775" t="inlineStr">
+      <c r="C774" t="inlineStr">
         <is>
           <t>名言 ,アート</t>
         </is>
       </c>
     </row>
-    <row r="776">
-      <c r="A776" t="inlineStr">
+    <row r="775">
+      <c r="A775" t="inlineStr">
         <is>
           <t xml:space="preserve">「ハム太郎って子を知ってるかい」
 هل تعرفون من هو هامتارو
@@ -16757,19 +16737,19 @@
 2109 </t>
         </is>
       </c>
-      <c r="B776" t="inlineStr">
+      <c r="B775" t="inlineStr">
         <is>
           <t>images/「ハム太郎って子を知ってるかい」_img1.jpg</t>
         </is>
       </c>
-      <c r="C776" t="inlineStr">
+      <c r="C775" t="inlineStr">
         <is>
           <t>オープニング ,ハム太郎</t>
         </is>
       </c>
     </row>
-    <row r="777">
-      <c r="A777" t="inlineStr">
+    <row r="776">
+      <c r="A776" t="inlineStr">
         <is>
           <t xml:space="preserve">「幸せを求める人もいれば、作る人もいる」
 هناك من يبحث عن السعادة وهناك من يصنعها
@@ -16778,19 +16758,19 @@
 2308 hindah tumblr </t>
         </is>
       </c>
-      <c r="B777" t="inlineStr">
+      <c r="B776" t="inlineStr">
         <is>
           <t>images/「幸せを求める人もいれば、作る人もいる_img1.jpg</t>
         </is>
       </c>
-      <c r="C777" t="inlineStr">
+      <c r="C776" t="inlineStr">
         <is>
           <t>幸せ ,名言 ,教訓</t>
         </is>
       </c>
     </row>
-    <row r="778">
-      <c r="A778" t="inlineStr">
+    <row r="777">
+      <c r="A777" t="inlineStr">
         <is>
           <t xml:space="preserve">「明白なるアラブの言葉によって」
 بلسان عربي مبين
@@ -16800,19 +16780,19 @@
 2109 Abdullah Barakat behance </t>
         </is>
       </c>
-      <c r="B778" t="inlineStr">
+      <c r="B777" t="inlineStr">
         <is>
           <t>images/「明白なるアラブの言葉によって」_img1.jpg</t>
         </is>
       </c>
-      <c r="C778" t="inlineStr">
+      <c r="C777" t="inlineStr">
         <is>
           <t>イスラム教 ,神聖</t>
         </is>
       </c>
     </row>
-    <row r="779">
-      <c r="A779" t="inlineStr">
+    <row r="778">
+      <c r="A778" t="inlineStr">
         <is>
           <t xml:space="preserve">「結婚前、結婚後」
 قبل الزواج، بعد الزواج
@@ -16822,19 +16802,19 @@
 2308 出典不明 </t>
         </is>
       </c>
-      <c r="B779" t="inlineStr">
+      <c r="B778" t="inlineStr">
         <is>
           <t>images/「結婚前、結婚後」_img1.jpg</t>
         </is>
       </c>
-      <c r="C779" t="inlineStr">
+      <c r="C778" t="inlineStr">
         <is>
           <t>BeforeAfter ,幸せ太り</t>
         </is>
       </c>
     </row>
-    <row r="780">
-      <c r="A780" t="inlineStr">
+    <row r="779">
+      <c r="A779" t="inlineStr">
         <is>
           <t xml:space="preserve">「驚きの価格で」بسعر رائع
 ビスィアル・ラーイア [bi-si*r raa'i*]
@@ -16843,19 +16823,19 @@
 2109 Jarir Bookstore </t>
         </is>
       </c>
-      <c r="B780" t="inlineStr">
+      <c r="B779" t="inlineStr">
         <is>
           <t>images/「驚きの価格で」_img1.jpg</t>
         </is>
       </c>
-      <c r="C780" t="inlineStr">
+      <c r="C779" t="inlineStr">
         <is>
           <t>広告 ,安値</t>
         </is>
       </c>
     </row>
-    <row r="781">
-      <c r="A781" t="inlineStr">
+    <row r="780">
+      <c r="A780" t="inlineStr">
         <is>
           <t xml:space="preserve">「我が魂と共に」مع نفسي
 マア・ナフスィ [ma*a nafs-iy]
@@ -16864,19 +16844,19 @@
 2110 出典不明 </t>
         </is>
       </c>
-      <c r="B781" t="inlineStr">
+      <c r="B780" t="inlineStr">
         <is>
           <t>images/「我が魂と共に」_img1.jpg</t>
         </is>
       </c>
-      <c r="C781" t="inlineStr">
+      <c r="C780" t="inlineStr">
         <is>
           <t>ソウル ,soul</t>
         </is>
       </c>
     </row>
-    <row r="782">
-      <c r="A782" t="inlineStr">
+    <row r="781">
+      <c r="A781" t="inlineStr">
         <is>
           <t xml:space="preserve">「暗い夜に」في ليلة مظلمة
  [fiy layla(tin) mu_Dhlima(tin)]
@@ -16885,19 +16865,19 @@
 2109 سلسلة الحلزونة </t>
         </is>
       </c>
-      <c r="B782" t="inlineStr">
+      <c r="B781" t="inlineStr">
         <is>
           <t>images/「暗い夜に」_img1.jpg</t>
         </is>
       </c>
-      <c r="C782" t="inlineStr">
+      <c r="C781" t="inlineStr">
         <is>
           <t>絵本</t>
         </is>
       </c>
     </row>
-    <row r="783">
-      <c r="A783" t="inlineStr">
+    <row r="782">
+      <c r="A782" t="inlineStr">
         <is>
           <t xml:space="preserve">「ゆっくりと」بشويش
 ビシワェーシ [bi-ShwySh]
@@ -16905,19 +16885,19 @@
 2109 出典不明 </t>
         </is>
       </c>
-      <c r="B783" t="inlineStr">
+      <c r="B782" t="inlineStr">
         <is>
           <t>images/「ゆっくりと」_img1.jpg</t>
         </is>
       </c>
-      <c r="C783" t="inlineStr">
+      <c r="C782" t="inlineStr">
         <is>
           <t>丸 ,円</t>
         </is>
       </c>
     </row>
-    <row r="784">
-      <c r="A784" t="inlineStr">
+    <row r="783">
+      <c r="A783" t="inlineStr">
         <is>
           <t xml:space="preserve">「この広い宇宙に…」
 في الكون الفسيح
@@ -16926,19 +16906,19 @@
 2308 wattpad </t>
         </is>
       </c>
-      <c r="B784" t="inlineStr">
+      <c r="B783" t="inlineStr">
         <is>
           <t>images/「この広い宇宙に…」_img1.jpg</t>
         </is>
       </c>
-      <c r="C784" t="inlineStr">
+      <c r="C783" t="inlineStr">
         <is>
           <t>アニメ ,宇宙</t>
         </is>
       </c>
     </row>
-    <row r="785">
-      <c r="A785" t="inlineStr">
+    <row r="784">
+      <c r="A784" t="inlineStr">
         <is>
           <t xml:space="preserve">「がんばって！」بالتوفيق
 ビッタウフィーク [bi^tawfiiq]
@@ -16946,19 +16926,19 @@
 2111 https://sites.google.com/site/mathmatic1905/ </t>
         </is>
       </c>
-      <c r="B785" t="inlineStr">
+      <c r="B784" t="inlineStr">
         <is>
           <t>images/「がんばって！」_img1.jpg</t>
         </is>
       </c>
-      <c r="C785" t="inlineStr">
+      <c r="C784" t="inlineStr">
         <is>
           <t>アラビア語</t>
         </is>
       </c>
     </row>
-    <row r="786">
-      <c r="A786" t="inlineStr">
+    <row r="785">
+      <c r="A785" t="inlineStr">
         <is>
           <t xml:space="preserve">「インターステラー」بين النجوم
 バイナ_ンヌジューム [bayna ^nujuum]
@@ -16966,19 +16946,19 @@
 2308 kmrghani </t>
         </is>
       </c>
-      <c r="B786" t="inlineStr">
+      <c r="B785" t="inlineStr">
         <is>
           <t>images/「インターステラー」_img1.jpg</t>
         </is>
       </c>
-      <c r="C786" t="inlineStr">
+      <c r="C785" t="inlineStr">
         <is>
           <t>映画 ,宇宙</t>
         </is>
       </c>
     </row>
-    <row r="787">
-      <c r="A787" t="inlineStr">
+    <row r="786">
+      <c r="A786" t="inlineStr">
         <is>
           <t xml:space="preserve">「アラビア語で」بالعربية
 ビ_ルアラビーヤ [bi-l-*arabiyya]
@@ -16987,19 +16967,19 @@
 1811 </t>
         </is>
       </c>
-      <c r="B787" t="inlineStr">
+      <c r="B786" t="inlineStr">
         <is>
           <t>images/「アラビア語で」_img1.jpg</t>
         </is>
       </c>
-      <c r="C787" t="inlineStr">
+      <c r="C786" t="inlineStr">
         <is>
           <t>ニュース ,CNN</t>
         </is>
       </c>
     </row>
-    <row r="788">
-      <c r="A788" t="inlineStr">
+    <row r="787">
+      <c r="A787" t="inlineStr">
         <is>
           <t xml:space="preserve">「17世紀に発明されて以来…」
 منذ اختراعه بالقرن السابع عشر
@@ -17007,19 +16987,19 @@
 2308 https://twitter.com/SciTalk2U/status/1450888395815854080 </t>
         </is>
       </c>
-      <c r="B788" t="inlineStr">
+      <c r="B787" t="inlineStr">
         <is>
           <t>images/「17世紀に発明されて以来…」_img1.jpg</t>
         </is>
       </c>
-      <c r="C788" t="inlineStr">
+      <c r="C787" t="inlineStr">
         <is>
           <t>手書き語学 ,アラビア語 ,望遠鏡</t>
         </is>
       </c>
     </row>
-    <row r="789">
-      <c r="A789" t="inlineStr">
+    <row r="788">
+      <c r="A788" t="inlineStr">
         <is>
           <t xml:space="preserve">「私できるよ」إنّني أستطيع
 インナニー・アスタティーウ ['inna-niy 'a-sta_tii*u]
@@ -17028,19 +17008,19 @@
 2412 سلسلة الحلزونة </t>
         </is>
       </c>
-      <c r="B789" t="inlineStr">
+      <c r="B788" t="inlineStr">
         <is>
           <t>images/「私できるよ」_img1.jpg</t>
         </is>
       </c>
-      <c r="C789" t="inlineStr">
+      <c r="C788" t="inlineStr">
         <is>
           <t>絵本 ,こども</t>
         </is>
       </c>
     </row>
-    <row r="790">
-      <c r="A790" t="inlineStr">
+    <row r="789">
+      <c r="A789" t="inlineStr">
         <is>
           <t xml:space="preserve">「問題なし」مافيش مشكلة
 マフィーシムシュキラ [ma-fy-Sh muShkila]
@@ -17049,19 +17029,19 @@
 2109 tanzerin.theshop </t>
         </is>
       </c>
-      <c r="B790" t="inlineStr">
+      <c r="B789" t="inlineStr">
         <is>
           <t>images/「問題なし」_img1.jpg</t>
         </is>
       </c>
-      <c r="C790" t="inlineStr">
+      <c r="C789" t="inlineStr">
         <is>
           <t>シャツ ,キッズ</t>
         </is>
       </c>
     </row>
-    <row r="791">
-      <c r="A791" t="inlineStr">
+    <row r="790">
+      <c r="A790" t="inlineStr">
         <is>
           <t xml:space="preserve">「不可能はない」مفيش مستحيل
 マフィーシ・ムスタヒール [ma-fy-Sh mustaHiil]
@@ -17070,19 +17050,19 @@
 2109 أموج </t>
         </is>
       </c>
-      <c r="B791" t="inlineStr">
+      <c r="B790" t="inlineStr">
         <is>
           <t>images/「不可能はない」_img1.jpg</t>
         </is>
       </c>
-      <c r="C791" t="inlineStr">
+      <c r="C790" t="inlineStr">
         <is>
           <t>ポジティブ ,挑戦</t>
         </is>
       </c>
     </row>
-    <row r="792">
-      <c r="A792" t="inlineStr">
+    <row r="791">
+      <c r="A791" t="inlineStr">
         <is>
           <t xml:space="preserve">「等々」إلخ
 イラク ['ilaKh]
@@ -17091,19 +17071,19 @@
 2201 出典不明 </t>
         </is>
       </c>
-      <c r="B792" t="inlineStr">
+      <c r="B791" t="inlineStr">
         <is>
           <t>images/「等々」_img1.jpg</t>
         </is>
       </c>
-      <c r="C792" t="inlineStr">
+      <c r="C791" t="inlineStr">
         <is>
           <t>etc ,とんち</t>
         </is>
       </c>
     </row>
-    <row r="793">
-      <c r="A793" t="inlineStr">
+    <row r="792">
+      <c r="A792" t="inlineStr">
         <is>
           <t xml:space="preserve">⁦「調子どう？」⁩شلونَك؟
 シュローナク？ [Sh-loon-ak?]
@@ -17112,19 +17092,19 @@
 2202 Jozoor Team. </t>
         </is>
       </c>
-      <c r="B793" t="inlineStr">
+      <c r="B792" t="inlineStr">
         <is>
           <t>images/⁦「調子どう？」⁩_img1.jpg</t>
         </is>
       </c>
-      <c r="C793" t="inlineStr">
+      <c r="C792" t="inlineStr">
         <is>
           <t>洒落 ,ルービックキューブ</t>
         </is>
       </c>
     </row>
-    <row r="794">
-      <c r="A794" t="inlineStr">
+    <row r="793">
+      <c r="A793" t="inlineStr">
         <is>
           <t xml:space="preserve">「行くな」ماتروحش
 マトロホシ [ma-troH-Sh]
@@ -17133,19 +17113,19 @@
 2411 triiq tumblr </t>
         </is>
       </c>
-      <c r="B794" t="inlineStr">
+      <c r="B793" t="inlineStr">
         <is>
           <t>images/「行くな」_img1.jpg</t>
         </is>
       </c>
-      <c r="C794" t="inlineStr">
+      <c r="C793" t="inlineStr">
         <is>
           <t>ロゴ ,デザイン ,嵐</t>
         </is>
       </c>
     </row>
-    <row r="795">
-      <c r="A795" t="inlineStr">
+    <row r="794">
+      <c r="A794" t="inlineStr">
         <is>
           <t xml:space="preserve">⁦「元気？」⁩شلونَك؟
 シュローナク？ [Sh-loon-ak?]
@@ -17156,19 +17136,19 @@
 2202 出典不明 </t>
         </is>
       </c>
-      <c r="B795" t="inlineStr">
+      <c r="B794" t="inlineStr">
         <is>
           <t>images/⁦「元気？」⁩_img1.jpg</t>
         </is>
       </c>
-      <c r="C795" t="inlineStr">
+      <c r="C794" t="inlineStr">
         <is>
           <t>洒落 ,挨拶</t>
         </is>
       </c>
     </row>
-    <row r="796">
-      <c r="A796" t="inlineStr">
+    <row r="795">
+      <c r="A795" t="inlineStr">
         <is>
           <t xml:space="preserve">「気分が良いぞう」I فيل GOOD
 アイ・フィール・グッド [ai fiyl gud]
@@ -17177,19 +17157,19 @@
 2308 出典不明 </t>
         </is>
       </c>
-      <c r="B796" t="inlineStr">
+      <c r="B795" t="inlineStr">
         <is>
           <t>images/「気分が良いぞう」_img1.jpg</t>
         </is>
       </c>
-      <c r="C796" t="inlineStr">
+      <c r="C795" t="inlineStr">
         <is>
           <t>洒落 ,和訳</t>
         </is>
       </c>
     </row>
-    <row r="797">
-      <c r="A797" t="inlineStr">
+    <row r="796">
+      <c r="A796" t="inlineStr">
         <is>
           <t xml:space="preserve">「レットイットゴー／let it go」
 ليت اِت غو
@@ -17198,19 +17178,19 @@
 2109 出典不明 </t>
         </is>
       </c>
-      <c r="B797" t="inlineStr">
+      <c r="B796" t="inlineStr">
         <is>
           <t>images/「レットイットゴー／let it go_img1.jpg</t>
         </is>
       </c>
-      <c r="C797" t="inlineStr">
+      <c r="C796" t="inlineStr">
         <is>
           <t>折衷 ,アナ雪</t>
         </is>
       </c>
     </row>
-    <row r="798">
-      <c r="A798" t="inlineStr">
+    <row r="797">
+      <c r="A797" t="inlineStr">
         <is>
           <t xml:space="preserve">「ようこそ」اهلا وسهلا
 アハラン・ワサハラン ['ahlan wa-sahlan]
@@ -17218,19 +17198,19 @@
 2106 behance Anwar Al Eissa </t>
         </is>
       </c>
-      <c r="B798" t="inlineStr">
+      <c r="B797" t="inlineStr">
         <is>
           <t>images/「ようこそ」_img1.jpg</t>
         </is>
       </c>
-      <c r="C798" t="inlineStr">
+      <c r="C797" t="inlineStr">
         <is>
           <t>アラビア語</t>
         </is>
       </c>
     </row>
-    <row r="799">
-      <c r="A799" t="inlineStr">
+    <row r="798">
+      <c r="A798" t="inlineStr">
         <is>
           <t xml:space="preserve">「まぁ何というサプライズでしょう」
 يا لها من مفاجأة
@@ -17241,19 +17221,19 @@
 2108 neelwafurat com </t>
         </is>
       </c>
-      <c r="B799" t="inlineStr">
+      <c r="B798" t="inlineStr">
         <is>
           <t>images/「まぁ何というサプライズでしょう」_img1.jpg</t>
         </is>
       </c>
-      <c r="C799" t="inlineStr">
+      <c r="C798" t="inlineStr">
         <is>
           <t>中国語 ,学習</t>
         </is>
       </c>
     </row>
-    <row r="800">
-      <c r="A800" t="inlineStr">
+    <row r="799">
+      <c r="A799" t="inlineStr">
         <is>
           <t xml:space="preserve">「ハックション」اتشوو
 アチュー！ ['aatShuu]
@@ -17261,19 +17241,19 @@
 1811 </t>
         </is>
       </c>
-      <c r="B800" t="inlineStr">
+      <c r="B799" t="inlineStr">
         <is>
           <t>images/「ハックション」_img1.jpg</t>
         </is>
       </c>
-      <c r="C800" t="inlineStr">
+      <c r="C799" t="inlineStr">
         <is>
           <t>あらびあや</t>
         </is>
       </c>
     </row>
-    <row r="801">
-      <c r="A801" t="inlineStr">
+    <row r="800">
+      <c r="A800" t="inlineStr">
         <is>
           <t xml:space="preserve">「スブハーナッラー」「アルハムドゥリッラー」「アッラーアクバル」
 سبحان الله
@@ -17284,19 +17264,19 @@
 2308 dribbble com </t>
         </is>
       </c>
-      <c r="B801" t="inlineStr">
+      <c r="B800" t="inlineStr">
         <is>
           <t>images/「スブハーナッラー」「アルハムドゥリッ_img1.jpg</t>
         </is>
       </c>
-      <c r="C801" t="inlineStr">
+      <c r="C800" t="inlineStr">
         <is>
           <t>四角 ,コンパクト</t>
         </is>
       </c>
     </row>
-    <row r="802">
-      <c r="A802" t="inlineStr">
+    <row r="801">
+      <c r="A801" t="inlineStr">
         <is>
           <t xml:space="preserve">「すごく美味しい！」لذيذ جدًا
 ラズィーズ・ジッダン [laDhiiDh jiddan]
@@ -17305,19 +17285,19 @@
 2109 goodreads com </t>
         </is>
       </c>
-      <c r="B802" t="inlineStr">
+      <c r="B801" t="inlineStr">
         <is>
           <t>images/「すごく美味しい！」_img1.jpg</t>
         </is>
       </c>
-      <c r="C802" t="inlineStr">
+      <c r="C801" t="inlineStr">
         <is>
           <t>フレーズ ,感想</t>
         </is>
       </c>
     </row>
-    <row r="803">
-      <c r="A803" t="inlineStr">
+    <row r="802">
+      <c r="A802" t="inlineStr">
         <is>
           <t xml:space="preserve">「しとしと、雨」تك تك يا مطر
 ティクティク [tik tik yaa ma_tar]
@@ -17326,19 +17306,19 @@
 2308 出典不明 </t>
         </is>
       </c>
-      <c r="B803" t="inlineStr">
+      <c r="B802" t="inlineStr">
         <is>
           <t>images/「しとしと、雨」_img1.jpg</t>
         </is>
       </c>
-      <c r="C803" t="inlineStr">
+      <c r="C802" t="inlineStr">
         <is>
           <t>天気 ,梅雨</t>
         </is>
       </c>
     </row>
-    <row r="804">
-      <c r="A804" t="inlineStr">
+    <row r="803">
+      <c r="A803" t="inlineStr">
         <is>
           <t xml:space="preserve">「さかさま」رأساً على عقب
 ラッアサン・アラー・アケブ [ra'san *alaa *aqib]
@@ -17346,19 +17326,19 @@
 2109 出典不明 </t>
         </is>
       </c>
-      <c r="B804" t="inlineStr">
+      <c r="B803" t="inlineStr">
         <is>
           <t>images/「さかさま」_img1.jpg</t>
         </is>
       </c>
-      <c r="C804" t="inlineStr">
+      <c r="C803" t="inlineStr">
         <is>
           <t>壁 ,上下</t>
         </is>
       </c>
     </row>
-    <row r="805">
-      <c r="A805" t="inlineStr">
+    <row r="804">
+      <c r="A804" t="inlineStr">
         <is>
           <t xml:space="preserve">「エジプトよどこへ行った」
 فينك يا مصر؟
@@ -17368,19 +17348,19 @@
 1809 shehabfawzy1.tumblr </t>
         </is>
       </c>
-      <c r="B805" t="inlineStr">
+      <c r="B804" t="inlineStr">
         <is>
           <t>images/「エジプトよどこへ行った」_img1.jpg</t>
         </is>
       </c>
-      <c r="C805" t="inlineStr">
+      <c r="C804" t="inlineStr">
         <is>
           <t>ピラミッド ,歴史</t>
         </is>
       </c>
     </row>
-    <row r="806">
-      <c r="A806" t="inlineStr">
+    <row r="805">
+      <c r="A805" t="inlineStr">
         <is>
           <t xml:space="preserve">「ありがとう」شكراً
 シュクラン [Shukran]
@@ -17388,19 +17368,19 @@
 2109 出典不明 </t>
         </is>
       </c>
-      <c r="B806" t="inlineStr">
+      <c r="B805" t="inlineStr">
         <is>
           <t>images/「ありがとう」_img1.jpg</t>
         </is>
       </c>
-      <c r="C806" t="inlineStr">
+      <c r="C805" t="inlineStr">
         <is>
           <t>挨拶 ,文字</t>
         </is>
       </c>
     </row>
-    <row r="807">
-      <c r="A807" t="inlineStr">
+    <row r="806">
+      <c r="A806" t="inlineStr">
         <is>
           <t xml:space="preserve">「昼寝の時間だ」
 إنه وقت القيلولة
@@ -17409,12 +17389,12 @@
 2501 https://x.com/NatGeoMagArab/status/1858049951579910486 </t>
         </is>
       </c>
-      <c r="B807" t="inlineStr">
+      <c r="B806" t="inlineStr">
         <is>
           <t>images/「昼寝の時間だ」_img1.jpg</t>
         </is>
       </c>
-      <c r="C807" t="inlineStr">
+      <c r="C806" t="inlineStr">
         <is>
           <t>手書き語学 ,アラビア語 ,ペンギン</t>
         </is>

--- a/posts.xlsx
+++ b/posts.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C805"/>
+  <dimension ref="A1:C804"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -12304,27 +12304,6 @@
     <row r="566">
       <c r="A566" t="inlineStr">
         <is>
-          <t xml:space="preserve">「クリエイティブになるには？」
-كيف تصبح مبدعًا؟
-[kayfa tu-_sbiHu mubdi*an?]
-「どう」[kayfa]・「あなたは〜になる」 [tu-_sbiH …]・「創造的に」[mubdi*an]：「創造的だ」[mubdi*]（b-d-*）
-2308 Gwid3 </t>
-        </is>
-      </c>
-      <c r="B566" t="inlineStr">
-        <is>
-          <t>images/「クリエイティブになるには？」_img1.jpg</t>
-        </is>
-      </c>
-      <c r="C566" t="inlineStr">
-        <is>
-          <t>心得 ,Tips</t>
-        </is>
-      </c>
-    </row>
-    <row r="567">
-      <c r="A567" t="inlineStr">
-        <is>
           <t xml:space="preserve">「彼らと友情を交わすよハム太郎」
 وبالإخاء يبادلهم هامتارو
 [wa-bi-l-'iKhaa'i yu-baadilu-hum hamtaro]
@@ -12333,19 +12312,19 @@
 2109 </t>
         </is>
       </c>
-      <c r="B567" t="inlineStr">
+      <c r="B566" t="inlineStr">
         <is>
           <t>images/「彼らと友情を交わすよハム太郎」_img1.jpg</t>
         </is>
       </c>
-      <c r="C567" t="inlineStr">
+      <c r="C566" t="inlineStr">
         <is>
           <t>アニメ ,ハム太郎</t>
         </is>
       </c>
     </row>
-    <row r="568">
-      <c r="A568" t="inlineStr">
+    <row r="567">
+      <c r="A567" t="inlineStr">
         <is>
           <t xml:space="preserve">「誰がニワトリを助ける？」
 من يساعد الدّجاجة؟
@@ -12355,19 +12334,19 @@
 2109 alnqsh com </t>
         </is>
       </c>
-      <c r="B568" t="inlineStr">
+      <c r="B567" t="inlineStr">
         <is>
           <t>images/「誰がニワトリを助ける？」_img1.jpg</t>
         </is>
       </c>
-      <c r="C568" t="inlineStr">
+      <c r="C567" t="inlineStr">
         <is>
           <t>絵本 ,チキン</t>
         </is>
       </c>
     </row>
-    <row r="569">
-      <c r="A569" t="inlineStr">
+    <row r="568">
+      <c r="A568" t="inlineStr">
         <is>
           <t xml:space="preserve">「心臓病を避けるには？」
 كيف تتجنب أمراض القلب؟
@@ -12377,37 +12356,37 @@
 2608 lanamedical_sa </t>
         </is>
       </c>
+      <c r="B568" t="inlineStr">
+        <is>
+          <t>images/「心臓病を避けるには？」.jpg</t>
+        </is>
+      </c>
+      <c r="C568" t="inlineStr">
+        <is>
+          <t>生活習慣病 ,心臓</t>
+        </is>
+      </c>
+    </row>
+    <row r="569">
+      <c r="A569" t="inlineStr">
+        <is>
+          <t xml:space="preserve">「どうやらこの好奇心旺盛なペンギンは…」
+2308 https://twitter.com/NatGeoMagArab/status/1591460860207443968 </t>
+        </is>
+      </c>
       <c r="B569" t="inlineStr">
         <is>
-          <t>images/「心臓病を避けるには？」.jpg</t>
+          <t>images/「どうやらこの好奇心旺盛なペンギンは…_img1.jpg,images/ 「どうやらこの好奇心旺盛なペンギンは…_img2.jpg</t>
         </is>
       </c>
       <c r="C569" t="inlineStr">
         <is>
-          <t>生活習慣病 ,心臓</t>
+          <t>手書き語学 ,アラビア語 ,オウサマペンギン</t>
         </is>
       </c>
     </row>
     <row r="570">
       <c r="A570" t="inlineStr">
-        <is>
-          <t xml:space="preserve">「どうやらこの好奇心旺盛なペンギンは…」
-2308 https://twitter.com/NatGeoMagArab/status/1591460860207443968 </t>
-        </is>
-      </c>
-      <c r="B570" t="inlineStr">
-        <is>
-          <t>images/「どうやらこの好奇心旺盛なペンギンは…_img1.jpg,images/ 「どうやらこの好奇心旺盛なペンギンは…_img2.jpg</t>
-        </is>
-      </c>
-      <c r="C570" t="inlineStr">
-        <is>
-          <t>手書き語学 ,アラビア語 ,オウサマペンギン</t>
-        </is>
-      </c>
-    </row>
-    <row r="571">
-      <c r="A571" t="inlineStr">
         <is>
           <t xml:space="preserve">「この生き物を見分けられますか？」
 هل تُميز هذا الكائن؟
@@ -12416,19 +12395,19 @@
 2308 https://twitter.com/NatGeoMagArab/status/1455121397827600388 </t>
         </is>
       </c>
-      <c r="B571" t="inlineStr">
+      <c r="B570" t="inlineStr">
         <is>
           <t>images/「この生き物を見分けられますか？」_img1.jpg</t>
         </is>
       </c>
-      <c r="C571" t="inlineStr">
+      <c r="C570" t="inlineStr">
         <is>
           <t xml:space="preserve">手書き語学 ,カバ </t>
         </is>
       </c>
     </row>
-    <row r="572">
-      <c r="A572" t="inlineStr">
+    <row r="571">
+      <c r="A571" t="inlineStr">
         <is>
           <t xml:space="preserve">「ひとを幸せにするには？」
 كيف تسعد غيرك؟
@@ -12438,19 +12417,19 @@
 2308 Gwid3 </t>
         </is>
       </c>
-      <c r="B572" t="inlineStr">
+      <c r="B571" t="inlineStr">
         <is>
           <t>images/「ひとを幸せにするには？」_img1.jpg</t>
         </is>
       </c>
-      <c r="C572" t="inlineStr">
+      <c r="C571" t="inlineStr">
         <is>
           <t>思いやり ,心</t>
         </is>
       </c>
     </row>
-    <row r="573">
-      <c r="A573" t="inlineStr">
+    <row r="572">
+      <c r="A572" t="inlineStr">
         <is>
           <t xml:space="preserve">「ラマダン月に口臭をおさえる方法は？」
 كيف تتجنب رائحة الفم في رمضان
@@ -12459,19 +12438,19 @@
 2109 AlArabiya </t>
         </is>
       </c>
-      <c r="B573" t="inlineStr">
+      <c r="B572" t="inlineStr">
         <is>
           <t>images/「ラマダン月に口臭をおさえる方法は？」_img1.jpg</t>
         </is>
       </c>
-      <c r="C573" t="inlineStr">
+      <c r="C572" t="inlineStr">
         <is>
           <t>イスラム教 ,ブレスケア</t>
         </is>
       </c>
     </row>
-    <row r="574">
-      <c r="A574" t="inlineStr">
+    <row r="573">
+      <c r="A573" t="inlineStr">
         <is>
           <t xml:space="preserve">「ヨユウなきユウヨ」
 يمهل ولا يهمل
@@ -12481,19 +12460,19 @@
 2512 instagram com/p/CK4CLqeJ3dy/ </t>
         </is>
       </c>
-      <c r="B574" t="inlineStr">
+      <c r="B573" t="inlineStr">
         <is>
           <t>images/「ヨユウなきユウヨ」_img1.jpg</t>
         </is>
       </c>
-      <c r="C574" t="inlineStr">
+      <c r="C573" t="inlineStr">
         <is>
           <t>時計 ,からくり</t>
         </is>
       </c>
     </row>
-    <row r="575">
-      <c r="A575" t="inlineStr">
+    <row r="574">
+      <c r="A574" t="inlineStr">
         <is>
           <t xml:space="preserve">「どうして？　動物は絶滅する」
 لماذا؟ تنقرض الحيوانات
@@ -12503,19 +12482,19 @@
 2308 goodreads com </t>
         </is>
       </c>
-      <c r="B575" t="inlineStr">
+      <c r="B574" t="inlineStr">
         <is>
           <t>images/「どうして？　動物は絶滅する」_img1.jpg</t>
         </is>
       </c>
-      <c r="C575" t="inlineStr">
+      <c r="C574" t="inlineStr">
         <is>
           <t>動物 ,子供用</t>
         </is>
       </c>
     </row>
-    <row r="576">
-      <c r="A576" t="inlineStr">
+    <row r="575">
+      <c r="A575" t="inlineStr">
         <is>
           <t xml:space="preserve">「私たちは異なる。だから調和する」
 نختلف.. لنأتلف
@@ -12525,19 +12504,19 @@
 2103 Nawal Saed </t>
         </is>
       </c>
-      <c r="B576" t="inlineStr">
+      <c r="B575" t="inlineStr">
         <is>
           <t>images/「私たちは異なる。だから調和する」_img1.jpg</t>
         </is>
       </c>
-      <c r="C576" t="inlineStr">
+      <c r="C575" t="inlineStr">
         <is>
           <t>異符号 ,ハーモニー</t>
         </is>
       </c>
     </row>
-    <row r="577">
-      <c r="A577" t="inlineStr">
+    <row r="576">
+      <c r="A576" t="inlineStr">
         <is>
           <t xml:space="preserve">「私の肺には蝶々が住んでいて、呼吸の度に羽ばたく」
 تسكن رئتيّ فراشة ترفرف كلما أتنفس
@@ -12546,19 +12525,19 @@
 2109 出典不明 </t>
         </is>
       </c>
-      <c r="B577" t="inlineStr">
+      <c r="B576" t="inlineStr">
         <is>
           <t>images/「私の肺には蝶々が住んでいて、呼吸の度_img1.jpg</t>
         </is>
       </c>
-      <c r="C577" t="inlineStr">
+      <c r="C576" t="inlineStr">
         <is>
           <t>人体 ,昆虫</t>
         </is>
       </c>
     </row>
-    <row r="578">
-      <c r="A578" t="inlineStr">
+    <row r="577">
+      <c r="A577" t="inlineStr">
         <is>
           <t xml:space="preserve">「安らぎを感じますか？」
 هل تستشعر السكينة؟
@@ -12567,19 +12546,19 @@
 2404 https://twitter.com/NatGeoMagArab/status/1541421154950209536 </t>
         </is>
       </c>
-      <c r="B578" t="inlineStr">
+      <c r="B577" t="inlineStr">
         <is>
           <t>images/「安らぎを感じますか？」_img1.jpg</t>
         </is>
       </c>
-      <c r="C578" t="inlineStr">
+      <c r="C577" t="inlineStr">
         <is>
           <t>手書き語学 ,アラビア語 ,エイ</t>
         </is>
       </c>
     </row>
-    <row r="579">
-      <c r="A579" t="inlineStr">
+    <row r="578">
+      <c r="A578" t="inlineStr">
         <is>
           <t xml:space="preserve">「たとえあなたの使うブラウザがChromeだろうとSafariだろうと」
 سواء كنت تستخدم متصفح كروم أو سفاري
@@ -12587,19 +12566,19 @@
 2308 https://twitter.com/ShaayTech/status/1536235333972635649 </t>
         </is>
       </c>
-      <c r="B579" t="inlineStr">
+      <c r="B578" t="inlineStr">
         <is>
           <t>images/「たとえあなたの使うブラウザがChro_img1.jpg</t>
         </is>
       </c>
-      <c r="C579" t="inlineStr">
+      <c r="C578" t="inlineStr">
         <is>
           <t xml:space="preserve">手書き語学 ,アラビア語 ,iPhone </t>
         </is>
       </c>
     </row>
-    <row r="580">
-      <c r="A580" t="inlineStr">
+    <row r="579">
+      <c r="A579" t="inlineStr">
         <is>
           <t xml:space="preserve">「このミドリモリヤツガシラは気づいて欲しい」
 يحرص "هدهد الخشب الأخضر" هذا على أن يدرك
@@ -12608,19 +12587,19 @@
 2308 https://twitter.com/NatGeoMagArab/status/1531161022928539648 </t>
         </is>
       </c>
-      <c r="B580" t="inlineStr">
+      <c r="B579" t="inlineStr">
         <is>
           <t>images/「このミドリモリヤツガシラは気づいて欲_img1.jpg</t>
         </is>
       </c>
-      <c r="C580" t="inlineStr">
+      <c r="C579" t="inlineStr">
         <is>
           <t xml:space="preserve">手書き語学 ,アラビア語 ,鳥 </t>
         </is>
       </c>
     </row>
-    <row r="581">
-      <c r="A581" t="inlineStr">
+    <row r="580">
+      <c r="A580" t="inlineStr">
         <is>
           <t xml:space="preserve">「あなたの怖いものは何ですか」
 ماهي مخاوفك؟
@@ -12632,15 +12611,15 @@
 2308 1112kok </t>
         </is>
       </c>
-      <c r="B581" t="inlineStr">
+      <c r="B580" t="inlineStr">
         <is>
           <t>images/「あなたの怖いものは何ですか」_img1.jpg</t>
         </is>
       </c>
-      <c r="C581" t="inlineStr"/>
-    </row>
-    <row r="582">
-      <c r="A582" t="inlineStr">
+      <c r="C580" t="inlineStr"/>
+    </row>
+    <row r="581">
+      <c r="A581" t="inlineStr">
         <is>
           <t xml:space="preserve">「美しい時は作るもの。待つものではない」
 اصنع اللحظات الجميلة. لا تنتظرها
@@ -12649,19 +12628,19 @@
 2308 abojamal.tumblr com </t>
         </is>
       </c>
-      <c r="B582" t="inlineStr">
+      <c r="B581" t="inlineStr">
         <is>
           <t>images/「美しい時は作るもの。待つものではない_img1.jpg</t>
         </is>
       </c>
-      <c r="C582" t="inlineStr">
+      <c r="C581" t="inlineStr">
         <is>
           <t>おうち時間</t>
         </is>
       </c>
     </row>
-    <row r="583">
-      <c r="A583" t="inlineStr">
+    <row r="582">
+      <c r="A582" t="inlineStr">
         <is>
           <t xml:space="preserve">「大切な時間を大切じゃないことに使わないこと」
 لا تضيع الوقت المهم في شيء غير مهم
@@ -12670,19 +12649,19 @@
 2308 Anwar_122_ </t>
         </is>
       </c>
-      <c r="B583" t="inlineStr">
+      <c r="B582" t="inlineStr">
         <is>
           <t>images/「大切な時間を大切じゃないことに使わな_img1.jpg</t>
         </is>
       </c>
-      <c r="C583" t="inlineStr">
+      <c r="C582" t="inlineStr">
         <is>
           <t>時間 ,貴重</t>
         </is>
       </c>
     </row>
-    <row r="584">
-      <c r="A584" t="inlineStr">
+    <row r="583">
+      <c r="A583" t="inlineStr">
         <is>
           <t xml:space="preserve">「このイノセントな目に騙されるな…」
 لا تنخدع بهذه العيون البريئة
@@ -12692,19 +12671,19 @@
 2201 https://twitter.com/NatGeoMagArab/status/1475715760202797056 </t>
         </is>
       </c>
-      <c r="B584" t="inlineStr">
+      <c r="B583" t="inlineStr">
         <is>
           <t>images/「このイノセントな目に騙されるな…」.png</t>
         </is>
       </c>
-      <c r="C584" t="inlineStr">
+      <c r="C583" t="inlineStr">
         <is>
           <t>がうがう ,カワイイ</t>
         </is>
       </c>
     </row>
-    <row r="585">
-      <c r="A585" t="inlineStr">
+    <row r="584">
+      <c r="A584" t="inlineStr">
         <is>
           <t xml:space="preserve">⁦「カメラを止めろ！」⁩
 أوقفوا التّصوير
@@ -12714,19 +12693,19 @@
 2509 alsalwabooks com </t>
         </is>
       </c>
-      <c r="B585" t="inlineStr">
+      <c r="B584" t="inlineStr">
         <is>
           <t>images/⁦「カメラを止めろ！」⁩_img1.jpg</t>
         </is>
       </c>
-      <c r="C585" t="inlineStr">
+      <c r="C584" t="inlineStr">
         <is>
           <t>絵本 ,撮影</t>
         </is>
       </c>
     </row>
-    <row r="586">
-      <c r="A586" t="inlineStr">
+    <row r="585">
+      <c r="A585" t="inlineStr">
         <is>
           <t xml:space="preserve">「話す前に考えなさい」
 فكر قبل ان تتكلم
@@ -12736,19 +12715,19 @@
 2308 Islamuna YouTube </t>
         </is>
       </c>
-      <c r="B586" t="inlineStr">
+      <c r="B585" t="inlineStr">
         <is>
           <t>images/「話す前に考えなさい」_img1.jpg</t>
         </is>
       </c>
-      <c r="C586" t="inlineStr">
+      <c r="C585" t="inlineStr">
         <is>
           <t>失言 ,発言</t>
         </is>
       </c>
     </row>
-    <row r="587">
-      <c r="A587" t="inlineStr">
+    <row r="586">
+      <c r="A586" t="inlineStr">
         <is>
           <t xml:space="preserve">「ツイッターでフォローして下さい」
 تابعونا على تويتر
@@ -12758,19 +12737,19 @@
 2109 出典不明 </t>
         </is>
       </c>
-      <c r="B587" t="inlineStr">
+      <c r="B586" t="inlineStr">
         <is>
           <t>images/「ツイッターでフォローして下さい」_img1.jpg</t>
         </is>
       </c>
-      <c r="C587" t="inlineStr">
+      <c r="C586" t="inlineStr">
         <is>
           <t>FollowUs ,バナー</t>
         </is>
       </c>
     </row>
-    <row r="588">
-      <c r="A588" t="inlineStr">
+    <row r="587">
+      <c r="A587" t="inlineStr">
         <is>
           <t xml:space="preserve">「敵を倒せ」دمّر العدو
 ダンミリ_ルアドゥーウ [dammiri l-*aduuw]
@@ -12779,19 +12758,19 @@
 2308 apkpure com </t>
         </is>
       </c>
-      <c r="B588" t="inlineStr">
+      <c r="B587" t="inlineStr">
         <is>
           <t>images/「敵を倒せ」_img1.jpg</t>
         </is>
       </c>
-      <c r="C588" t="inlineStr">
+      <c r="C587" t="inlineStr">
         <is>
           <t>ゲーム ,パンダ</t>
         </is>
       </c>
     </row>
-    <row r="589">
-      <c r="A589" t="inlineStr">
+    <row r="588">
+      <c r="A588" t="inlineStr">
         <is>
           <t xml:space="preserve">「咲け。蒔かれたらどこであろうと」
 أزهر أيْنمَا زرعت
@@ -12800,19 +12779,19 @@
 2407 Ahmed Madyan </t>
         </is>
       </c>
-      <c r="B589" t="inlineStr">
+      <c r="B588" t="inlineStr">
         <is>
           <t>images/「咲け。蒔かれたらどこであろうと」_img1.jpg</t>
         </is>
       </c>
-      <c r="C589" t="inlineStr">
+      <c r="C588" t="inlineStr">
         <is>
           <t>環境のせいにしない ,花</t>
         </is>
       </c>
     </row>
-    <row r="590">
-      <c r="A590" t="inlineStr">
+    <row r="589">
+      <c r="A589" t="inlineStr">
         <is>
           <t xml:space="preserve">「頭を働かせろ」شغل مخك
 シャッギル・ムッハク [Sha^Ghil mu^Kha-k]
@@ -12821,19 +12800,19 @@
 2103 facebook elpage </t>
         </is>
       </c>
-      <c r="B590" t="inlineStr">
+      <c r="B589" t="inlineStr">
         <is>
           <t>images/「頭を働かせろ」_img1.jpg</t>
         </is>
       </c>
-      <c r="C590" t="inlineStr">
+      <c r="C589" t="inlineStr">
         <is>
           <t>電源 ,頭脳</t>
         </is>
       </c>
     </row>
-    <row r="591">
-      <c r="A591" t="inlineStr">
+    <row r="590">
+      <c r="A590" t="inlineStr">
         <is>
           <t xml:space="preserve">「傷跡は星にかえなさい」
 حوّل نُدوبكَ إلى نُجومْ
@@ -12843,19 +12822,19 @@
 2107 saramj1992 Instagram </t>
         </is>
       </c>
-      <c r="B591" t="inlineStr">
+      <c r="B590" t="inlineStr">
         <is>
           <t>images/「傷跡は星にかえなさい」_img1.jpg</t>
         </is>
       </c>
-      <c r="C591" t="inlineStr">
+      <c r="C590" t="inlineStr">
         <is>
           <t>勲章 ,証</t>
         </is>
       </c>
     </row>
-    <row r="592">
-      <c r="A592" t="inlineStr">
+    <row r="591">
+      <c r="A591" t="inlineStr">
         <is>
           <t xml:space="preserve">「あなたの主の栄光を誉め称え、また（御赦しを請え。本当にかれは、度々赦される御方である）」
 فسَبِّح بحمد ربك و
@@ -12864,19 +12843,19 @@
 2109 出典不明 </t>
         </is>
       </c>
-      <c r="B592" t="inlineStr">
+      <c r="B591" t="inlineStr">
         <is>
           <t>images/「あなたの主の栄光を誉め称え、また（御_img1.jpg</t>
         </is>
       </c>
-      <c r="C592" t="inlineStr">
+      <c r="C591" t="inlineStr">
         <is>
           <t>イスラム教 ,カリグラフィー</t>
         </is>
       </c>
     </row>
-    <row r="593">
-      <c r="A593" t="inlineStr">
+    <row r="592">
+      <c r="A592" t="inlineStr">
         <is>
           <t xml:space="preserve">「誰かを幸福にしなさい」
 أسْعِد أحدهم
@@ -12886,19 +12865,19 @@
 1810 in4sser.tumblr </t>
         </is>
       </c>
-      <c r="B593" t="inlineStr">
+      <c r="B592" t="inlineStr">
         <is>
           <t>images/「誰かを幸福にしなさい」_img1.jpg</t>
         </is>
       </c>
-      <c r="C593" t="inlineStr">
+      <c r="C592" t="inlineStr">
         <is>
           <t>人生 ,happy</t>
         </is>
       </c>
     </row>
-    <row r="594">
-      <c r="A594" t="inlineStr">
+    <row r="593">
+      <c r="A593" t="inlineStr">
         <is>
           <t xml:space="preserve">「見よ」أبْصِرْ
 アブスィル ['ab_sir]
@@ -12907,19 +12886,19 @@
 1811 Ruh Al-Alam, via Behance </t>
         </is>
       </c>
-      <c r="B594" t="inlineStr">
+      <c r="B593" t="inlineStr">
         <is>
           <t>images/「見よ」_img1.jpg</t>
         </is>
       </c>
-      <c r="C594" t="inlineStr">
+      <c r="C593" t="inlineStr">
         <is>
           <t>目 ,瞳</t>
         </is>
       </c>
     </row>
-    <row r="595">
-      <c r="A595" t="inlineStr">
+    <row r="594">
+      <c r="A594" t="inlineStr">
         <is>
           <t xml:space="preserve">「言葉は口から出す前に味わいなさい」
 ‪تذوق كلماتك قبل أن تنطقها‬
@@ -12929,19 +12908,19 @@
 2109 Reham-des </t>
         </is>
       </c>
-      <c r="B595" t="inlineStr">
+      <c r="B594" t="inlineStr">
         <is>
           <t>images/「言葉は口から出す前に味わいなさい」_img1.jpg</t>
         </is>
       </c>
-      <c r="C595" t="inlineStr">
+      <c r="C594" t="inlineStr">
         <is>
           <t>言葉</t>
         </is>
       </c>
     </row>
-    <row r="596">
-      <c r="A596" t="inlineStr">
+    <row r="595">
+      <c r="A595" t="inlineStr">
         <is>
           <t xml:space="preserve">「テレビを観るのをやめて下さい」
 توقفي عن مشاهدة التلفاز
@@ -12951,19 +12930,19 @@
 1809 </t>
         </is>
       </c>
-      <c r="B596" t="inlineStr">
+      <c r="B595" t="inlineStr">
         <is>
           <t>images/「テレビを観るのをやめて下さい」_img1.jpg</t>
         </is>
       </c>
-      <c r="C596" t="inlineStr">
+      <c r="C595" t="inlineStr">
         <is>
           <t>あらびあや</t>
         </is>
       </c>
     </row>
-    <row r="597">
-      <c r="A597" t="inlineStr">
+    <row r="596">
+      <c r="A596" t="inlineStr">
         <is>
           <t xml:space="preserve">「言わぬが花」
 انْطِقْ جَمَالاً أو تجَمَّلْ بالسّكُوت
@@ -12973,19 +12952,19 @@
 2411 Ahmed Madyan </t>
         </is>
       </c>
-      <c r="B597" t="inlineStr">
+      <c r="B596" t="inlineStr">
         <is>
           <t>images/「言わぬが花」_img1.jpg</t>
         </is>
       </c>
-      <c r="C597" t="inlineStr">
+      <c r="C596" t="inlineStr">
         <is>
           <t>ことわざ ,デザイン</t>
         </is>
       </c>
     </row>
-    <row r="598">
-      <c r="A598" t="inlineStr">
+    <row r="597">
+      <c r="A597" t="inlineStr">
         <is>
           <t xml:space="preserve">「たくさん考えて、少し話すこと」
 فكّر كثيرا. تكلم قليلا
@@ -12995,19 +12974,19 @@
 2105 In49r </t>
         </is>
       </c>
-      <c r="B598" t="inlineStr">
+      <c r="B597" t="inlineStr">
         <is>
           <t>images/「たくさん考えて、少し話すこと」_img1.jpg</t>
         </is>
       </c>
-      <c r="C598" t="inlineStr">
+      <c r="C597" t="inlineStr">
         <is>
           <t>思慮 ,会話</t>
         </is>
       </c>
     </row>
-    <row r="599">
-      <c r="A599" t="inlineStr">
+    <row r="598">
+      <c r="A598" t="inlineStr">
         <is>
           <t xml:space="preserve">「子供たちよ、いつでも思い出すんだよ」
 تذكروا دوما يا أطفال
@@ -13017,19 +12996,19 @@
 1809 </t>
         </is>
       </c>
-      <c r="B599" t="inlineStr">
+      <c r="B598" t="inlineStr">
         <is>
           <t>images/「子供たちよ、いつでも思い出すんだよ」_img1.jpg</t>
         </is>
       </c>
-      <c r="C599" t="inlineStr">
+      <c r="C598" t="inlineStr">
         <is>
           <t>オープニング ,ハム太郎</t>
         </is>
       </c>
     </row>
-    <row r="600">
-      <c r="A600" t="inlineStr">
+    <row r="599">
+      <c r="A599" t="inlineStr">
         <is>
           <t xml:space="preserve">「分かってから話しなさい」
 تعلَّم ثمَّ تكلَّم
@@ -13039,19 +13018,19 @@
 1903 Hashem Al Shareef, Pinterest </t>
         </is>
       </c>
-      <c r="B600" t="inlineStr">
+      <c r="B599" t="inlineStr">
         <is>
           <t>images/「分かってから話しなさい」_img1.jpg</t>
         </is>
       </c>
-      <c r="C600" t="inlineStr">
+      <c r="C599" t="inlineStr">
         <is>
           <t>教訓 ,トーク</t>
         </is>
       </c>
     </row>
-    <row r="601">
-      <c r="A601" t="inlineStr">
+    <row r="600">
+      <c r="A600" t="inlineStr">
         <is>
           <t xml:space="preserve">「蟻に学べ」تعلم من النملة
 タアッラム・ミナ_ンナムラ [ta*allam mina ^namla]
@@ -13060,19 +13039,19 @@
 2308 fatakat com </t>
         </is>
       </c>
-      <c r="B601" t="inlineStr">
+      <c r="B600" t="inlineStr">
         <is>
           <t>images/「蟻に学べ」_img1.jpg</t>
         </is>
       </c>
-      <c r="C601" t="inlineStr">
+      <c r="C600" t="inlineStr">
         <is>
           <t>教訓 ,問題解決</t>
         </is>
       </c>
     </row>
-    <row r="602">
-      <c r="A602" t="inlineStr">
+    <row r="601">
+      <c r="A601" t="inlineStr">
         <is>
           <t xml:space="preserve">「自分と仲直りしよう、一杯の珈琲で！」
 تصالح مع نفسك بكوب قهوة
@@ -13082,19 +13061,19 @@
 2308 asm95_ </t>
         </is>
       </c>
-      <c r="B602" t="inlineStr">
+      <c r="B601" t="inlineStr">
         <is>
           <t>images/「自分と仲直りしよう、一杯の珈琲で！」_img1.jpg</t>
         </is>
       </c>
-      <c r="C602" t="inlineStr">
+      <c r="C601" t="inlineStr">
         <is>
           <t>一服 ,リラックス</t>
         </is>
       </c>
     </row>
-    <row r="603">
-      <c r="A603" t="inlineStr">
+    <row r="602">
+      <c r="A602" t="inlineStr">
         <is>
           <t xml:space="preserve">「気をつけて　ジュード」
 انتبهي يا جود
@@ -13104,19 +13083,19 @@
 2109 سلسلة الحلزونة </t>
         </is>
       </c>
-      <c r="B603" t="inlineStr">
+      <c r="B602" t="inlineStr">
         <is>
           <t>images/「気をつけて　ジュード」_img1.jpg</t>
         </is>
       </c>
-      <c r="C603" t="inlineStr">
+      <c r="C602" t="inlineStr">
         <is>
           <t>絵本 ,わんぱく</t>
         </is>
       </c>
     </row>
-    <row r="604">
-      <c r="A604" t="inlineStr">
+    <row r="603">
+      <c r="A603" t="inlineStr">
         <is>
           <t xml:space="preserve">「coming soon」
 انتظرونا قريبا
@@ -13125,19 +13104,19 @@
 2307 出典不明 </t>
         </is>
       </c>
-      <c r="B604" t="inlineStr">
+      <c r="B603" t="inlineStr">
         <is>
           <t>images/「coming soon」_img1.jpg</t>
         </is>
       </c>
-      <c r="C604" t="inlineStr">
+      <c r="C603" t="inlineStr">
         <is>
           <t>フレーズ ,カミングスーン</t>
         </is>
       </c>
     </row>
-    <row r="605">
-      <c r="A605" t="inlineStr">
+    <row r="604">
+      <c r="A604" t="inlineStr">
         <is>
           <t xml:space="preserve">「自分の胸に聞きなさい。それが全て知っています」
 استمع لقلبك.. إنه يعرف كل شيء
@@ -13146,19 +13125,19 @@
 1811 </t>
         </is>
       </c>
-      <c r="B605" t="inlineStr">
+      <c r="B604" t="inlineStr">
         <is>
           <t>images/「自分の胸に聞きなさい。それが全て知っ_img1.jpg</t>
         </is>
       </c>
-      <c r="C605" t="inlineStr">
+      <c r="C604" t="inlineStr">
         <is>
           <t>あらびあや</t>
         </is>
       </c>
     </row>
-    <row r="606">
-      <c r="A606" t="inlineStr">
+    <row r="605">
+      <c r="A605" t="inlineStr">
         <is>
           <t xml:space="preserve">「笑ってくれ、絶望を癒すのは君の笑みだから」
 ابتسمي فإن دواء اليأس بسمتك
@@ -13167,19 +13146,19 @@
 2308 arab-quotes tumblr </t>
         </is>
       </c>
-      <c r="B606" t="inlineStr">
+      <c r="B605" t="inlineStr">
         <is>
           <t>images/「笑ってくれ、絶望を癒すのは君の笑みだ_img1.jpg</t>
         </is>
       </c>
-      <c r="C606" t="inlineStr">
+      <c r="C605" t="inlineStr">
         <is>
           <t>癒し ,スマイル</t>
         </is>
       </c>
     </row>
-    <row r="607">
-      <c r="A607" t="inlineStr">
+    <row r="606">
+      <c r="A606" t="inlineStr">
         <is>
           <t xml:space="preserve">「自分を頼りなさい。宇宙で最も確かな物が自分だと思って。」
 استند على نفسك وكأنك أكثر الأشياء ثباتًا بهذا الكون
@@ -13187,19 +13166,19 @@
 2308 x_nourh.15 </t>
         </is>
       </c>
-      <c r="B607" t="inlineStr">
+      <c r="B606" t="inlineStr">
         <is>
           <t>images/「自分を頼りなさい。宇宙で最も確かな物_img1.jpg</t>
         </is>
       </c>
-      <c r="C607" t="inlineStr">
+      <c r="C606" t="inlineStr">
         <is>
           <t>自我 ,宇宙</t>
         </is>
       </c>
     </row>
-    <row r="608">
-      <c r="A608" t="inlineStr">
+    <row r="607">
+      <c r="A607" t="inlineStr">
         <is>
           <t xml:space="preserve">「古いデバイスを交換して新品をゲットしよう」
 استبدل جهازك القديم واحصل على واحد جديد
@@ -13208,19 +13187,19 @@
 2406 stc </t>
         </is>
       </c>
-      <c r="B608" t="inlineStr">
+      <c r="B607" t="inlineStr">
         <is>
           <t>images/「古いデバイスを交換して新品をゲットし_img1.jpg</t>
         </is>
       </c>
-      <c r="C608" t="inlineStr">
+      <c r="C607" t="inlineStr">
         <is>
           <t>キャンペーン ,下取り</t>
         </is>
       </c>
     </row>
-    <row r="609">
-      <c r="A609" t="inlineStr">
+    <row r="608">
+      <c r="A608" t="inlineStr">
         <is>
           <t xml:space="preserve">「あなたの声を聞かせてください。私の心を彩ってください」
 هات صوتك، لوّن قلبي
@@ -13229,19 +13208,19 @@
 2105 3a2esha_ Instagram </t>
         </is>
       </c>
-      <c r="B609" t="inlineStr">
+      <c r="B608" t="inlineStr">
         <is>
           <t>images/「あなたの声を聞かせてください。私の心_img1.jpg</t>
         </is>
       </c>
-      <c r="C609" t="inlineStr">
+      <c r="C608" t="inlineStr">
         <is>
           <t>電話 ,肉声</t>
         </is>
       </c>
     </row>
-    <row r="610">
-      <c r="A610" t="inlineStr">
+    <row r="609">
+      <c r="A609" t="inlineStr">
         <is>
           <t xml:space="preserve">「この子カンガルーは抱っこが好き」
 يُحب صغير الكنغر هذا أن يؤخذ في الأحضان
@@ -13249,19 +13228,19 @@
 2308 NatGeoMagArab </t>
         </is>
       </c>
-      <c r="B610" t="inlineStr">
+      <c r="B609" t="inlineStr">
         <is>
           <t>images/「この子カンガルーは抱っこが好き」.png</t>
         </is>
       </c>
-      <c r="C610" t="inlineStr">
+      <c r="C609" t="inlineStr">
         <is>
           <t>カンガルー ,人肌</t>
         </is>
       </c>
     </row>
-    <row r="611">
-      <c r="A611" t="inlineStr">
+    <row r="610">
+      <c r="A610" t="inlineStr">
         <is>
           <t xml:space="preserve">「カタールが好き」أحب قطر
 ウヒッブ・カタル ['u-Hibb qa_tar]
@@ -13270,19 +13249,19 @@
 1810 出典不明 </t>
         </is>
       </c>
-      <c r="B611" t="inlineStr">
+      <c r="B610" t="inlineStr">
         <is>
           <t>images/「カタールが好き」_img1.jpg</t>
         </is>
       </c>
-      <c r="C611" t="inlineStr">
+      <c r="C610" t="inlineStr">
         <is>
           <t>カタール</t>
         </is>
       </c>
     </row>
-    <row r="612">
-      <c r="A612" t="inlineStr">
+    <row r="611">
+      <c r="A611" t="inlineStr">
         <is>
           <t xml:space="preserve">「一緒に読むのが好き」
 أُحبُّ أن نَقْرَأَ مَعاً
@@ -13292,19 +13271,19 @@
 2509 www.neelwafurat com,  id=lbb212750-185765 </t>
         </is>
       </c>
-      <c r="B612" t="inlineStr">
+      <c r="B611" t="inlineStr">
         <is>
           <t>images/「一緒に読むのが好き」_img1.jpg</t>
         </is>
       </c>
-      <c r="C612" t="inlineStr">
+      <c r="C611" t="inlineStr">
         <is>
           <t>好き ,本</t>
         </is>
       </c>
     </row>
-    <row r="613">
-      <c r="A613" t="inlineStr">
+    <row r="612">
+      <c r="A612" t="inlineStr">
         <is>
           <t xml:space="preserve">「病院に行きたくない」
 لا أريد أن أذهب إلى المشفى
@@ -13314,19 +13293,19 @@
 2508 Tony Ross https://education.hachette-antoine.com/ar/component/%D9%84%D8%A7-%D8%A3%D8%B1%D9%8A%D8%AF-%D8%A3%D9%86-%D8%A3%D8%B0%D9%87%D8%A8-%D8%A5%D9%84%D9%89-%D8%A7%D9%84%D9%85%D8%B4%D9%81%D9%89/ </t>
         </is>
       </c>
-      <c r="B613" t="inlineStr">
+      <c r="B612" t="inlineStr">
         <is>
           <t>images/「病院に行きたくない」_img1.jpg</t>
         </is>
       </c>
-      <c r="C613" t="inlineStr">
+      <c r="C612" t="inlineStr">
         <is>
           <t>絵本 ,子供</t>
         </is>
       </c>
     </row>
-    <row r="614">
-      <c r="A614" t="inlineStr">
+    <row r="613">
+      <c r="A613" t="inlineStr">
         <is>
           <t xml:space="preserve">「男性はいくら？」「女性はいくら？」
 كم يساوى الرجل؟ ..وكم تساوى المرأة؟
@@ -13335,19 +13314,19 @@
 2308 Pinterest, Masr Elmahrousa, Farah Noweir </t>
         </is>
       </c>
-      <c r="B614" t="inlineStr">
+      <c r="B613" t="inlineStr">
         <is>
           <t>images/「男性はいくら？」「女性はいくら？」_img1.jpg,images/「男性はいくら？」「女性はいくら？」_img2.jpg</t>
         </is>
       </c>
-      <c r="C614" t="inlineStr">
+      <c r="C613" t="inlineStr">
         <is>
           <t xml:space="preserve">全身コーデ ,相場 </t>
         </is>
       </c>
     </row>
-    <row r="615">
-      <c r="A615" t="inlineStr">
+    <row r="614">
+      <c r="A614" t="inlineStr">
         <is>
           <t xml:space="preserve">「黙ってもらえます？」
 ممكن تعيرنا سكوتك؟
@@ -13357,19 +13336,19 @@
 2308 Basel26 </t>
         </is>
       </c>
-      <c r="B615" t="inlineStr">
+      <c r="B614" t="inlineStr">
         <is>
           <t>images/「黙ってもらえます？」_img1.jpg</t>
         </is>
       </c>
-      <c r="C615" t="inlineStr">
+      <c r="C614" t="inlineStr">
         <is>
           <t>音量 ,ボリューム</t>
         </is>
       </c>
     </row>
-    <row r="616">
-      <c r="A616" t="inlineStr">
+    <row r="615">
+      <c r="A615" t="inlineStr">
         <is>
           <t xml:space="preserve">「眠りたいです」
 أُريدُ أَن أَنام
@@ -13379,19 +13358,19 @@
 2109 goodreads com </t>
         </is>
       </c>
-      <c r="B616" t="inlineStr">
+      <c r="B615" t="inlineStr">
         <is>
           <t>images/「眠りたいです」_img1.jpg</t>
         </is>
       </c>
-      <c r="C616" t="inlineStr">
+      <c r="C615" t="inlineStr">
         <is>
           <t>絵本</t>
         </is>
       </c>
     </row>
-    <row r="617">
-      <c r="A617" t="inlineStr">
+    <row r="616">
+      <c r="A616" t="inlineStr">
         <is>
           <t xml:space="preserve">「飛びたい！」أُريد أن أطير
 ウリードゥ・アン・アティール ['u-riidu 'an 'a-_tiir]
@@ -13400,19 +13379,19 @@
 2308 出典不明 </t>
         </is>
       </c>
-      <c r="B617" t="inlineStr">
+      <c r="B616" t="inlineStr">
         <is>
           <t>images/「飛びたい！」_img1.jpg</t>
         </is>
       </c>
-      <c r="C617" t="inlineStr">
+      <c r="C616" t="inlineStr">
         <is>
           <t>鳥 ,希望</t>
         </is>
       </c>
     </row>
-    <row r="618">
-      <c r="A618" t="inlineStr">
+    <row r="617">
+      <c r="A617" t="inlineStr">
         <is>
           <t xml:space="preserve">「うちゅうへとびたい」
 أُريدُ أَنْ أَطيرَ إلى الفَضاء
@@ -13421,19 +13400,19 @@
 2308 mybookshelf co </t>
         </is>
       </c>
-      <c r="B618" t="inlineStr">
+      <c r="B617" t="inlineStr">
         <is>
           <t>images/「うちゅうへとびたい」_img1.jpg</t>
         </is>
       </c>
-      <c r="C618" t="inlineStr">
+      <c r="C617" t="inlineStr">
         <is>
           <t>絵本 ,宇宙</t>
         </is>
       </c>
     </row>
-    <row r="619">
-      <c r="A619" t="inlineStr">
+    <row r="618">
+      <c r="A618" t="inlineStr">
         <is>
           <t xml:space="preserve">「とても愛しています」
 أُحِبّك جِدّاً
@@ -13443,19 +13422,19 @@
 2308 hobe cc </t>
         </is>
       </c>
-      <c r="B619" t="inlineStr">
+      <c r="B618" t="inlineStr">
         <is>
           <t>images/「とても愛しています」_img1.jpg</t>
         </is>
       </c>
-      <c r="C619" t="inlineStr">
+      <c r="C618" t="inlineStr">
         <is>
           <t>恋 ,love</t>
         </is>
       </c>
     </row>
-    <row r="620">
-      <c r="A620" t="inlineStr">
+    <row r="619">
+      <c r="A619" t="inlineStr">
         <is>
           <t xml:space="preserve">「あす日が昇るだろう。私は朝が大好きだ」
 غدا ستشرق الشمس وأحب الصباح كثيرا
@@ -13464,19 +13443,19 @@
 2105 warag-3nb.tumblr com </t>
         </is>
       </c>
-      <c r="B620" t="inlineStr">
+      <c r="B619" t="inlineStr">
         <is>
           <t>images/「あす日が昇るだろう。私は朝が大好きだ_img1.jpg,images/ 「あす日が昇るだろう。私は朝が大好きだ_img2.jpg</t>
         </is>
       </c>
-      <c r="C620" t="inlineStr">
+      <c r="C619" t="inlineStr">
         <is>
           <t>おやすみ ,壁</t>
         </is>
       </c>
     </row>
-    <row r="621">
-      <c r="A621" t="inlineStr">
+    <row r="620">
+      <c r="A620" t="inlineStr">
         <is>
           <t xml:space="preserve">「きみは何をえらぶ？」
 ماذا تختار؟
@@ -13486,19 +13465,19 @@
 2109 embadomjp org </t>
         </is>
       </c>
-      <c r="B621" t="inlineStr">
+      <c r="B620" t="inlineStr">
         <is>
           <t>images/「きみは何をえらぶ？」_img1.jpg</t>
         </is>
       </c>
-      <c r="C621" t="inlineStr">
+      <c r="C620" t="inlineStr">
         <is>
           <t>優柔不断 ,絵本</t>
         </is>
       </c>
     </row>
-    <row r="622">
-      <c r="A622" t="inlineStr">
+    <row r="621">
+      <c r="A621" t="inlineStr">
         <is>
           <t xml:space="preserve">「ちょっと静けさが必要な時もある」
 في بعض الأوقات نحتاج لشوية هدوء
@@ -13508,19 +13487,19 @@
 2308 IN49r </t>
         </is>
       </c>
-      <c r="B622" t="inlineStr">
+      <c r="B621" t="inlineStr">
         <is>
           <t>images/「ちょっと静けさが必要な時もある」_img1.jpg</t>
         </is>
       </c>
-      <c r="C622" t="inlineStr">
+      <c r="C621" t="inlineStr">
         <is>
           <t>ミュート ,精神</t>
         </is>
       </c>
     </row>
-    <row r="623">
-      <c r="A623" t="inlineStr">
+    <row r="622">
+      <c r="A622" t="inlineStr">
         <is>
           <t xml:space="preserve">「逃げるな。全力でぶつかれ」
 لا تهرب اصطدم بكل قوتك
@@ -13530,19 +13509,19 @@
 2308 https://risingvibes.tumblr.com/post/189545775129 </t>
         </is>
       </c>
-      <c r="B623" t="inlineStr">
+      <c r="B622" t="inlineStr">
         <is>
           <t>images/「逃げるな。全力でぶつかれ」_img1.jpg</t>
         </is>
       </c>
-      <c r="C623" t="inlineStr">
+      <c r="C622" t="inlineStr">
         <is>
           <t>応援 ,力</t>
         </is>
       </c>
     </row>
-    <row r="624">
-      <c r="A624" t="inlineStr">
+    <row r="623">
+      <c r="A623" t="inlineStr">
         <is>
           <t xml:space="preserve">「着るのだいすき」
 أُحِبُ أَن أَرتَدِيَ
@@ -13552,19 +13531,19 @@
 2308 https://kitab.firmabikes.ru/epub-_hb_n_rtdy_5187.html </t>
         </is>
       </c>
-      <c r="B624" t="inlineStr">
+      <c r="B623" t="inlineStr">
         <is>
           <t>images/「着るのだいすき」_img1.jpg</t>
         </is>
       </c>
-      <c r="C624" t="inlineStr">
+      <c r="C623" t="inlineStr">
         <is>
           <t xml:space="preserve">絵本 ,ファッション </t>
         </is>
       </c>
     </row>
-    <row r="625">
-      <c r="A625" t="inlineStr">
+    <row r="624">
+      <c r="A624" t="inlineStr">
         <is>
           <t xml:space="preserve">「車のバッテリーが要る！」
 نحتاج بطارية سيارة
@@ -13574,19 +13553,19 @@
 2308 instagram roaa_27 </t>
         </is>
       </c>
-      <c r="B625" t="inlineStr">
+      <c r="B624" t="inlineStr">
         <is>
           <t>images/「車のバッテリーが要る！」_img1.jpg</t>
         </is>
       </c>
-      <c r="C625" t="inlineStr">
+      <c r="C624" t="inlineStr">
         <is>
           <t>スマホ ,充電</t>
         </is>
       </c>
     </row>
-    <row r="626">
-      <c r="A626" t="inlineStr">
+    <row r="625">
+      <c r="A625" t="inlineStr">
         <is>
           <t xml:space="preserve">「今日は幸せでいることにしました」
 اخترت أن أكون سعيدا اليوم
@@ -13596,19 +13575,19 @@
 2109 awaasha tumblr </t>
         </is>
       </c>
-      <c r="B626" t="inlineStr">
+      <c r="B625" t="inlineStr">
         <is>
           <t>images/「今日は幸せでいることにしました」_img1.jpg</t>
         </is>
       </c>
-      <c r="C626" t="inlineStr">
+      <c r="C625" t="inlineStr">
         <is>
           <t>心構え ,happy</t>
         </is>
       </c>
     </row>
-    <row r="627">
-      <c r="A627" t="inlineStr">
+    <row r="626">
+      <c r="A626" t="inlineStr">
         <is>
           <t xml:space="preserve">「理想的なスイカの選び方」
 كيف تختار البطيخة المُثلى؟
@@ -13618,19 +13597,19 @@
 2308 bit ly/octmel </t>
         </is>
       </c>
-      <c r="B627" t="inlineStr">
+      <c r="B626" t="inlineStr">
         <is>
           <t>images/「理想的なスイカの選び方」_img1.jpg</t>
         </is>
       </c>
-      <c r="C627" t="inlineStr">
+      <c r="C626" t="inlineStr">
         <is>
           <t>八百屋 ,西瓜</t>
         </is>
       </c>
     </row>
-    <row r="628">
-      <c r="A628" t="inlineStr">
+    <row r="627">
+      <c r="A627" t="inlineStr">
         <is>
           <t xml:space="preserve">「お問い合わせください」
 اتصل بنا
@@ -13640,19 +13619,19 @@
 2308 mtawir.blogspot com </t>
         </is>
       </c>
-      <c r="B628" t="inlineStr">
+      <c r="B627" t="inlineStr">
         <is>
           <t>images/「お問い合わせください」_img1.jpg</t>
         </is>
       </c>
-      <c r="C628" t="inlineStr">
+      <c r="C627" t="inlineStr">
         <is>
           <t>広告 ,電話</t>
         </is>
       </c>
     </row>
-    <row r="629">
-      <c r="A629" t="inlineStr">
+    <row r="628">
+      <c r="A628" t="inlineStr">
         <is>
           <t xml:space="preserve">「両方の動物が海岸の火山岩の亀裂の中に定住している」
 يحتل كلا الحيوانين شقوقًا في صخور الساحل البركانية
@@ -13660,19 +13639,19 @@
 2507 https://x.com/NatGeoMagArab/status/1925167200056521151 </t>
         </is>
       </c>
-      <c r="B629" t="inlineStr">
+      <c r="B628" t="inlineStr">
         <is>
           <t>images/「両方の動物が海岸の火山岩の亀裂の中に_img1.jpg,images/「両方の動物が海岸の火山岩の亀裂の中に_img2.jpg</t>
         </is>
       </c>
-      <c r="C629" t="inlineStr">
+      <c r="C628" t="inlineStr">
         <is>
           <t>手書き語学 ,アラビア語 ,イグアナ</t>
         </is>
       </c>
     </row>
-    <row r="630">
-      <c r="A630" t="inlineStr">
+    <row r="629">
+      <c r="A629" t="inlineStr">
         <is>
           <t xml:space="preserve">「命じられたように正しき道を辿れ」
 واستقم كما أمرت
@@ -13682,19 +13661,19 @@
 2308 Ahmed Madyan </t>
         </is>
       </c>
-      <c r="B630" t="inlineStr">
+      <c r="B629" t="inlineStr">
         <is>
           <t>images/「命じられたように正しき道を辿れ」_img1.jpg</t>
         </is>
       </c>
-      <c r="C630" t="inlineStr">
+      <c r="C629" t="inlineStr">
         <is>
           <t>書道 ,アート</t>
         </is>
       </c>
     </row>
-    <row r="631">
-      <c r="A631" t="inlineStr">
+    <row r="630">
+      <c r="A630" t="inlineStr">
         <is>
           <t xml:space="preserve">「くつろぎなさい」استكن
 イスタキンナ [istakinna]
@@ -13702,19 +13681,19 @@
 2603 m2ff tumblr com </t>
         </is>
       </c>
-      <c r="B631" t="inlineStr">
+      <c r="B630" t="inlineStr">
         <is>
           <t>images/「くつろぎなさい」.jpeg</t>
         </is>
       </c>
-      <c r="C631" t="inlineStr">
+      <c r="C630" t="inlineStr">
         <is>
           <t>relax ,コーヒー</t>
         </is>
       </c>
     </row>
-    <row r="632">
-      <c r="A632" t="inlineStr">
+    <row r="631">
+      <c r="A631" t="inlineStr">
         <is>
           <t xml:space="preserve">「彼は応えるだろう」سيستجيب 
 サヤスタジーブ [sa-ya-stajiibu]
@@ -13723,19 +13702,19 @@
 1811 kareem mrghani </t>
         </is>
       </c>
-      <c r="B632" t="inlineStr">
+      <c r="B631" t="inlineStr">
         <is>
           <t>images/「彼は応えるだろう」_img1.jpg</t>
         </is>
       </c>
-      <c r="C632" t="inlineStr">
+      <c r="C631" t="inlineStr">
         <is>
           <t>縦書き ,現代アート</t>
         </is>
       </c>
     </row>
-    <row r="633">
-      <c r="A633" t="inlineStr">
+    <row r="632">
+      <c r="A632" t="inlineStr">
         <is>
           <t xml:space="preserve">「アラビア語が好き」
 أنا أُحبّ لُغتي
@@ -13745,19 +13724,19 @@
 2308 出典不明 </t>
         </is>
       </c>
-      <c r="B633" t="inlineStr">
+      <c r="B632" t="inlineStr">
         <is>
           <t>images/「アラビア語が好き」_img1.jpg</t>
         </is>
       </c>
-      <c r="C633" t="inlineStr">
+      <c r="C632" t="inlineStr">
         <is>
           <t>和訳 ,こども</t>
         </is>
       </c>
     </row>
-    <row r="634">
-      <c r="A634" t="inlineStr">
+    <row r="633">
+      <c r="A633" t="inlineStr">
         <is>
           <t xml:space="preserve">「私はサッカーが好きです」
 أنا أُحِبُّ كُرةَ القَدَم
@@ -13767,19 +13746,19 @@
 2109 Arabic With Nadia </t>
         </is>
       </c>
-      <c r="B634" t="inlineStr">
+      <c r="B633" t="inlineStr">
         <is>
           <t>images/「私はサッカーが好きです」_img1.jpg</t>
         </is>
       </c>
-      <c r="C634" t="inlineStr">
+      <c r="C633" t="inlineStr">
         <is>
           <t>自由時間 ,例文</t>
         </is>
       </c>
     </row>
-    <row r="635">
-      <c r="A635" t="inlineStr">
+    <row r="634">
+      <c r="A634" t="inlineStr">
         <is>
           <t xml:space="preserve">「これ、私の眼鏡じゃありません」
 هٰذِهِ لَيْسَتْ نَظَّارَاتِي
@@ -13789,19 +13768,19 @@
 2509 </t>
         </is>
       </c>
-      <c r="B635" t="inlineStr">
+      <c r="B634" t="inlineStr">
         <is>
           <t>images/「これ、私の眼鏡じゃありません」_img1.jpg</t>
         </is>
       </c>
-      <c r="C635" t="inlineStr">
+      <c r="C634" t="inlineStr">
         <is>
           <t>あらびあや</t>
         </is>
       </c>
     </row>
-    <row r="636">
-      <c r="A636" t="inlineStr">
+    <row r="635">
+      <c r="A635" t="inlineStr">
         <is>
           <t xml:space="preserve">「我らも米を食います」
 نحن أيضاً نأكل الأرز
@@ -13811,19 +13790,19 @@
 1809 </t>
         </is>
       </c>
-      <c r="B636" t="inlineStr">
+      <c r="B635" t="inlineStr">
         <is>
           <t>images/「我らも米を食います」_img1.jpg</t>
         </is>
       </c>
-      <c r="C636" t="inlineStr">
+      <c r="C635" t="inlineStr">
         <is>
           <t>あらびあや</t>
         </is>
       </c>
     </row>
-    <row r="637">
-      <c r="A637" t="inlineStr">
+    <row r="636">
+      <c r="A636" t="inlineStr">
         <is>
           <t xml:space="preserve">「ひとりでできるもん！」
 أنا أستطيع أن أفعله وحدي
@@ -13832,19 +13811,19 @@
 2105 </t>
         </is>
       </c>
-      <c r="B637" t="inlineStr">
+      <c r="B636" t="inlineStr">
         <is>
           <t>images/「ひとりでできるもん！」_img1.jpg</t>
         </is>
       </c>
-      <c r="C637" t="inlineStr">
+      <c r="C636" t="inlineStr">
         <is>
           <t>あらびあや</t>
         </is>
       </c>
     </row>
-    <row r="638">
-      <c r="A638" t="inlineStr">
+    <row r="637">
+      <c r="A637" t="inlineStr">
         <is>
           <t xml:space="preserve">「恋しくないと言っている時は恋しい」
 أُريدُك حينَ أَقُولُ أَنا لا أُريدُك
@@ -13854,19 +13833,19 @@
 2308 DARWISHISM </t>
         </is>
       </c>
-      <c r="B638" t="inlineStr">
+      <c r="B637" t="inlineStr">
         <is>
           <t>images/「恋しくないと言っている時は恋しい」_img1.jpg</t>
         </is>
       </c>
-      <c r="C638" t="inlineStr">
+      <c r="C637" t="inlineStr">
         <is>
           <t>本音 ,恋愛</t>
         </is>
       </c>
     </row>
-    <row r="639">
-      <c r="A639" t="inlineStr">
+    <row r="638">
+      <c r="A638" t="inlineStr">
         <is>
           <t xml:space="preserve">「私は〜する」
 ⁦「着る」：( أنا ألبس )['ana 'a-lbas]⁩
@@ -13877,19 +13856,19 @@
 2109 RABIE </t>
         </is>
       </c>
-      <c r="B639" t="inlineStr">
+      <c r="B638" t="inlineStr">
         <is>
           <t>images/「私は〜する」_img1.jpg,images/「私は〜する」_img2.jpg,images/「私は〜する」_img3.jpg,images/「私は〜する」_img4.jpg</t>
         </is>
       </c>
-      <c r="C639" t="inlineStr">
+      <c r="C638" t="inlineStr">
         <is>
           <t>動詞 ,絵本</t>
         </is>
       </c>
     </row>
-    <row r="640">
-      <c r="A640" t="inlineStr">
+    <row r="639">
+      <c r="A639" t="inlineStr">
         <is>
           <t xml:space="preserve">「彼は完璧ではない。私は彼の欠点については目をつむった」
 هو ليس كامل. أنا أعميت نفسي عن سيئاته
@@ -13898,19 +13877,19 @@
 2308 _NOHA </t>
         </is>
       </c>
-      <c r="B640" t="inlineStr">
+      <c r="B639" t="inlineStr">
         <is>
           <t>images/「彼は完璧ではない。私は彼の欠点につい_img1.jpg</t>
         </is>
       </c>
-      <c r="C640" t="inlineStr">
+      <c r="C639" t="inlineStr">
         <is>
           <t>愛 ,寛容</t>
         </is>
       </c>
     </row>
-    <row r="641">
-      <c r="A641" t="inlineStr">
+    <row r="640">
+      <c r="A640" t="inlineStr">
         <is>
           <t xml:space="preserve">「この子トラは検疫期間中に生まれた」
 صغير النمر هذا ولد في زمن الحجر الصحي
@@ -13919,19 +13898,19 @@
 2310 https://www.akhbaralaan.net/?p=434924 </t>
         </is>
       </c>
-      <c r="B641" t="inlineStr">
+      <c r="B640" t="inlineStr">
         <is>
           <t>images/「この子トラは検疫期間中に生まれた」_img1.jpg</t>
         </is>
       </c>
-      <c r="C641" t="inlineStr">
+      <c r="C640" t="inlineStr">
         <is>
           <t>Covid ,メキシコ</t>
         </is>
       </c>
     </row>
-    <row r="642">
-      <c r="A642" t="inlineStr">
+    <row r="641">
+      <c r="A641" t="inlineStr">
         <is>
           <t xml:space="preserve">「睡眠の素晴らしさに匹敵するものは無い！」
 وجمال النوم ليس له مثيل
@@ -13940,19 +13919,19 @@
 2308 arabzy tumblr </t>
         </is>
       </c>
-      <c r="B642" t="inlineStr">
+      <c r="B641" t="inlineStr">
         <is>
           <t>images/「睡眠の素晴らしさに匹敵するものは無い_img1.jpg</t>
         </is>
       </c>
-      <c r="C642" t="inlineStr">
+      <c r="C641" t="inlineStr">
         <is>
           <t>オフトゥン ,おやすみ</t>
         </is>
       </c>
     </row>
-    <row r="643">
-      <c r="A643" t="inlineStr">
+    <row r="642">
+      <c r="A642" t="inlineStr">
         <is>
           <t xml:space="preserve">「大器晩成」
 الأشياء العظيمة تأخذ وقت
@@ -13962,19 +13941,19 @@
 2109 出典不明 </t>
         </is>
       </c>
-      <c r="B643" t="inlineStr">
+      <c r="B642" t="inlineStr">
         <is>
           <t>images/「大器晩成」_img1.jpg</t>
         </is>
       </c>
-      <c r="C643" t="inlineStr">
+      <c r="C642" t="inlineStr">
         <is>
           <t>ことわざ ,和訳</t>
         </is>
       </c>
     </row>
-    <row r="644">
-      <c r="A644" t="inlineStr">
+    <row r="643">
+      <c r="A643" t="inlineStr">
         <is>
           <t xml:space="preserve">「コーヒーは急には飲まれない」
 القهْوة لا تشرَب عَلى عَجلْ
@@ -13985,19 +13964,19 @@
 2012 Ahmed Madyan </t>
         </is>
       </c>
-      <c r="B644" t="inlineStr">
+      <c r="B643" t="inlineStr">
         <is>
           <t>images/「コーヒーは急には飲まれない」_img1.jpg</t>
         </is>
       </c>
-      <c r="C644" t="inlineStr">
+      <c r="C643" t="inlineStr">
         <is>
           <t>名言</t>
         </is>
       </c>
     </row>
-    <row r="645">
-      <c r="A645" t="inlineStr">
+    <row r="644">
+      <c r="A644" t="inlineStr">
         <is>
           <t xml:space="preserve">「成功者は情報共有している」
 الناجحون يشاركون المعلومة
@@ -14007,19 +13986,19 @@
 2109 出典不明 </t>
         </is>
       </c>
-      <c r="B645" t="inlineStr">
+      <c r="B644" t="inlineStr">
         <is>
           <t>images/「成功者は情報共有している」_img1.jpg</t>
         </is>
       </c>
-      <c r="C645" t="inlineStr">
+      <c r="C644" t="inlineStr">
         <is>
           <t>鳥 ,シェア</t>
         </is>
       </c>
     </row>
-    <row r="646">
-      <c r="A646" t="inlineStr">
+    <row r="645">
+      <c r="A645" t="inlineStr">
         <is>
           <t xml:space="preserve">「間違いで賢くなる、痛みで強くなる」
 الأخطاء تجعلك حكيمًا، والألم يجعلك قويًا
@@ -14028,19 +14007,19 @@
 2111 https://alaminin.blogspot.com/2020/03/blog-post_6.html </t>
         </is>
       </c>
-      <c r="B646" t="inlineStr">
+      <c r="B645" t="inlineStr">
         <is>
           <t>images/「間違いで賢くなる、痛みで強くなる」_img1.jpg</t>
         </is>
       </c>
-      <c r="C646" t="inlineStr">
+      <c r="C645" t="inlineStr">
         <is>
           <t>名言</t>
         </is>
       </c>
     </row>
-    <row r="647">
-      <c r="A647" t="inlineStr">
+    <row r="646">
+      <c r="A646" t="inlineStr">
         <is>
           <t xml:space="preserve">「何事も永遠には続かない」
 لا شيء يبقى للأبد
@@ -14050,19 +14029,19 @@
 2308 KiTeLetZ </t>
         </is>
       </c>
-      <c r="B647" t="inlineStr">
+      <c r="B646" t="inlineStr">
         <is>
           <t>images/「何事も永遠には続かない」_img1.jpg</t>
         </is>
       </c>
-      <c r="C647" t="inlineStr">
+      <c r="C646" t="inlineStr">
         <is>
           <t>変化 ,名言</t>
         </is>
       </c>
     </row>
-    <row r="648">
-      <c r="A648" t="inlineStr">
+    <row r="647">
+      <c r="A647" t="inlineStr">
         <is>
           <t xml:space="preserve">「惑星地球はあなた方を歓迎します」
 كوكب الارض يرحّب بكم
@@ -14072,19 +14051,19 @@
 1811 iN49R </t>
         </is>
       </c>
-      <c r="B648" t="inlineStr">
+      <c r="B647" t="inlineStr">
         <is>
           <t>images/「惑星地球はあなた方を歓迎します」_img1.jpg</t>
         </is>
       </c>
-      <c r="C648" t="inlineStr">
+      <c r="C647" t="inlineStr">
         <is>
           <t>宇宙 ,人類</t>
         </is>
       </c>
     </row>
-    <row r="649">
-      <c r="A649" t="inlineStr">
+    <row r="648">
+      <c r="A648" t="inlineStr">
         <is>
           <t xml:space="preserve">「自分を信じなさい。人の言うことは尽きないのだから」
 ثق بنفسك فكلام الناس لا ينتهي
@@ -14093,19 +14072,19 @@
 2105 出典不明 </t>
         </is>
       </c>
-      <c r="B649" t="inlineStr">
+      <c r="B648" t="inlineStr">
         <is>
           <t>images/「自分を信じなさい。人の言うことは尽き_img1.jpg</t>
         </is>
       </c>
-      <c r="C649" t="inlineStr">
+      <c r="C648" t="inlineStr">
         <is>
           <t>自信 ,無視</t>
         </is>
       </c>
     </row>
-    <row r="650">
-      <c r="A650" t="inlineStr">
+    <row r="649">
+      <c r="A649" t="inlineStr">
         <is>
           <t xml:space="preserve">「弟が歩くぞ」أخي الصغير يمشي
 アキ_ッサギール・ヤムシー ['aKh-i ^_saGhiiru ya-mShii]
@@ -14114,19 +14093,19 @@
 2308 gulfkids com http://www.gulfkids.com/ar/book48-1909.htm </t>
         </is>
       </c>
-      <c r="B650" t="inlineStr">
+      <c r="B649" t="inlineStr">
         <is>
           <t>images/「弟が歩くぞ」_img1.jpg</t>
         </is>
       </c>
-      <c r="C650" t="inlineStr">
+      <c r="C649" t="inlineStr">
         <is>
           <t>兄弟 ,絵本</t>
         </is>
       </c>
     </row>
-    <row r="651">
-      <c r="A651" t="inlineStr">
+    <row r="650">
+      <c r="A650" t="inlineStr">
         <is>
           <t xml:space="preserve">花より団子おおお（違う）
 「誰もふさわしくない」[laa 'aHada ya-staHiqqu]
@@ -14134,19 +14113,19 @@
 2308 https://twitter.com/NatGeoMagArab/status/1370041991317233664 </t>
         </is>
       </c>
-      <c r="B651" t="inlineStr">
+      <c r="B650" t="inlineStr">
         <is>
           <t>images/花より団子おおお（違う）_img1.jpg</t>
         </is>
       </c>
-      <c r="C651" t="inlineStr">
+      <c r="C650" t="inlineStr">
         <is>
           <t>手書き語学 ,アラビア語 ,キノボリカンガルー</t>
         </is>
       </c>
     </row>
-    <row r="652">
-      <c r="A652" t="inlineStr">
+    <row r="651">
+      <c r="A651" t="inlineStr">
         <is>
           <t xml:space="preserve">「幸せな人生には弱い記憶力が必要」
 الحياة السعيدة تتطلب ذاكرة ضعيفة
@@ -14155,19 +14134,19 @@
 2012 出典不明 </t>
         </is>
       </c>
-      <c r="B652" t="inlineStr">
+      <c r="B651" t="inlineStr">
         <is>
           <t>images/「幸せな人生には弱い記憶力が必要」_img1.jpg</t>
         </is>
       </c>
-      <c r="C652" t="inlineStr">
+      <c r="C651" t="inlineStr">
         <is>
           <t>前向き</t>
         </is>
       </c>
     </row>
-    <row r="653">
-      <c r="A653" t="inlineStr">
+    <row r="652">
+      <c r="A652" t="inlineStr">
         <is>
           <t xml:space="preserve">「このパンダは私たちに、幸せは単純なことの中に隠れているのだと教えている」
 دب "الباندا" هذا يؤكد لنا أن السعادة تكمن في أبسط الأشياء
@@ -14175,19 +14154,19 @@
 2308 https://twitter.com/NatGeoMagArab/status/1309938472065486848 </t>
         </is>
       </c>
-      <c r="B653" t="inlineStr">
+      <c r="B652" t="inlineStr">
         <is>
           <t>images/「このパンダは私たちに、幸せは単純なこ.png</t>
         </is>
       </c>
-      <c r="C653" t="inlineStr">
+      <c r="C652" t="inlineStr">
         <is>
           <t>パンダ ,雪</t>
         </is>
       </c>
     </row>
-    <row r="654">
-      <c r="A654" t="inlineStr">
+    <row r="653">
+      <c r="A653" t="inlineStr">
         <is>
           <t xml:space="preserve">「良い時間は速く過ぎる」
 الأوقات الجميلة تمر بسرعة
@@ -14197,19 +14176,19 @@
 1810 Nasser.Tumblr </t>
         </is>
       </c>
-      <c r="B654" t="inlineStr">
+      <c r="B653" t="inlineStr">
         <is>
           <t>images/「良い時間は速く過ぎる」_img1.jpg</t>
         </is>
       </c>
-      <c r="C654" t="inlineStr">
+      <c r="C653" t="inlineStr">
         <is>
           <t>相対論 ,心理学</t>
         </is>
       </c>
     </row>
-    <row r="655">
-      <c r="A655" t="inlineStr">
+    <row r="654">
+      <c r="A654" t="inlineStr">
         <is>
           <t xml:space="preserve">「今日が始まりかもしれない」
 كل يوم ممكن يكون بداية
@@ -14219,19 +14198,19 @@
 2308 Ahmed Madyan </t>
         </is>
       </c>
-      <c r="B655" t="inlineStr">
+      <c r="B654" t="inlineStr">
         <is>
           <t>images/「今日が始まりかもしれない」_img1.jpg</t>
         </is>
       </c>
-      <c r="C655" t="inlineStr">
+      <c r="C654" t="inlineStr">
         <is>
           <t>吉日 ,開始</t>
         </is>
       </c>
     </row>
-    <row r="656">
-      <c r="A656" t="inlineStr">
+    <row r="655">
+      <c r="A655" t="inlineStr">
         <is>
           <t xml:space="preserve">「ヌール、歯医者さんに行く」
 نور تذهب إلى طبيب الأسنان
@@ -14241,19 +14220,19 @@
 2109 RABIE </t>
         </is>
       </c>
-      <c r="B656" t="inlineStr">
+      <c r="B655" t="inlineStr">
         <is>
           <t>images/「ヌール、歯医者さんに行く」_img1.jpg</t>
         </is>
       </c>
-      <c r="C656" t="inlineStr">
+      <c r="C655" t="inlineStr">
         <is>
           <t>絵本 ,歯科</t>
         </is>
       </c>
     </row>
-    <row r="657">
-      <c r="A657" t="inlineStr">
+    <row r="656">
+      <c r="A656" t="inlineStr">
         <is>
           <t xml:space="preserve">「ラヤンはねむれない」
 لَيان لا تَسْتَطيعُ أَنْ تَنام
@@ -14262,19 +14241,19 @@
 2308 出典不明 </t>
         </is>
       </c>
-      <c r="B657" t="inlineStr">
+      <c r="B656" t="inlineStr">
         <is>
           <t>images/「ラヤンはねむれない」_img1.jpg</t>
         </is>
       </c>
-      <c r="C657" t="inlineStr">
+      <c r="C656" t="inlineStr">
         <is>
           <t>絵本 ,不眠症</t>
         </is>
       </c>
     </row>
-    <row r="658">
-      <c r="A658" t="inlineStr">
+    <row r="657">
+      <c r="A657" t="inlineStr">
         <is>
           <t xml:space="preserve">「クネイトラ県、蜂の巣を約60%失う」
 القنيطرة تفقد حوالي 60 % من خلايا نحلها
@@ -14282,19 +14261,19 @@
 2403 nabd com/t/101679025-fb119f </t>
         </is>
       </c>
-      <c r="B658" t="inlineStr">
+      <c r="B657" t="inlineStr">
         <is>
           <t>images/「クネイトラ県、蜂の巣を約60%失う」_img1.jpg</t>
         </is>
       </c>
-      <c r="C658" t="inlineStr">
+      <c r="C657" t="inlineStr">
         <is>
           <t>蜂の巣 ,パーセント</t>
         </is>
       </c>
     </row>
-    <row r="659">
-      <c r="A659" t="inlineStr">
+    <row r="658">
+      <c r="A658" t="inlineStr">
         <is>
           <t xml:space="preserve">「結ばれしター」ة
 ⁦( تاء مربوطة )[taa' marbuu_ta]：ت「ター」( تاء )[taa']・「結ばれている」( مربوط )[marbuu_t]：( ربط )【結】⁩
@@ -14302,19 +14281,19 @@
 2308 出典不明 </t>
         </is>
       </c>
-      <c r="B659" t="inlineStr">
+      <c r="B658" t="inlineStr">
         <is>
           <t>images/「結ばれしター」_img1.jpg</t>
         </is>
       </c>
-      <c r="C659" t="inlineStr">
+      <c r="C658" t="inlineStr">
         <is>
           <t>アラビア文字 ,顔</t>
         </is>
       </c>
     </row>
-    <row r="660">
-      <c r="A660" t="inlineStr">
+    <row r="659">
+      <c r="A659" t="inlineStr">
         <is>
           <t xml:space="preserve">「忙しい」مشغول
 マシュグール [maShGhuul]
@@ -14323,19 +14302,19 @@
 1811 skyshinichi.instagram </t>
         </is>
       </c>
-      <c r="B660" t="inlineStr">
+      <c r="B659" t="inlineStr">
         <is>
           <t>images/「忙しい」_img1.jpg</t>
         </is>
       </c>
-      <c r="C660" t="inlineStr">
+      <c r="C659" t="inlineStr">
         <is>
           <t>スティッチ ,残業</t>
         </is>
       </c>
     </row>
-    <row r="661">
-      <c r="A661" t="inlineStr">
+    <row r="660">
+      <c r="A660" t="inlineStr">
         <is>
           <t xml:space="preserve">「駐車禁止」ممنوع الوقوف
 マムヌーア・アルウクーフ [mamnuu* al-wuquuf]
@@ -14344,19 +14323,19 @@
 2106 出典不明 </t>
         </is>
       </c>
-      <c r="B661" t="inlineStr">
+      <c r="B660" t="inlineStr">
         <is>
           <t>images/「駐車禁止」_img1.jpg</t>
         </is>
       </c>
-      <c r="C661" t="inlineStr">
+      <c r="C660" t="inlineStr">
         <is>
           <t>標識 ,ジョーク</t>
         </is>
       </c>
     </row>
-    <row r="662">
-      <c r="A662" t="inlineStr">
+    <row r="661">
+      <c r="A661" t="inlineStr">
         <is>
           <t xml:space="preserve">「一人ひとりが責任を」
 كُلنا مسؤول
@@ -14366,19 +14345,19 @@
 2308 covid19awareness sa </t>
         </is>
       </c>
-      <c r="B662" t="inlineStr">
+      <c r="B661" t="inlineStr">
         <is>
           <t>images/「一人ひとりが責任を」_img1.jpg</t>
         </is>
       </c>
-      <c r="C662" t="inlineStr">
+      <c r="C661" t="inlineStr">
         <is>
           <t>Covid ,感染拡大防止</t>
         </is>
       </c>
     </row>
-    <row r="663">
-      <c r="A663" t="inlineStr">
+    <row r="662">
+      <c r="A662" t="inlineStr">
         <is>
           <t xml:space="preserve">「おめでとうございます」مبروك
 マブルーク [mabruuk]
@@ -14387,19 +14366,19 @@
 2308 </t>
         </is>
       </c>
-      <c r="B663" t="inlineStr">
+      <c r="B662" t="inlineStr">
         <is>
           <t>images/「おめでとうございます」_img1.jpg</t>
         </is>
       </c>
-      <c r="C663" t="inlineStr">
+      <c r="C662" t="inlineStr">
         <is>
           <t>詐欺 ,広告</t>
         </is>
       </c>
     </row>
-    <row r="664">
-      <c r="A664" t="inlineStr">
+    <row r="663">
+      <c r="A663" t="inlineStr">
         <is>
           <t xml:space="preserve">「手書きフォント」
 خط مكتوب باليد
@@ -14409,19 +14388,19 @@
 1809 FahdAlFraikh Behance </t>
         </is>
       </c>
-      <c r="B664" t="inlineStr">
+      <c r="B663" t="inlineStr">
         <is>
           <t>images/「手書きフォント」_img1.jpg</t>
         </is>
       </c>
-      <c r="C664" t="inlineStr">
+      <c r="C663" t="inlineStr">
         <is>
           <t>可愛いフォント ,筆跡</t>
         </is>
       </c>
     </row>
-    <row r="665">
-      <c r="A665" t="inlineStr">
+    <row r="664">
+      <c r="A664" t="inlineStr">
         <is>
           <t xml:space="preserve">「開かれたターと結ばれたター」
 التاء المفتوحة والمربوطة
@@ -14431,19 +14410,19 @@
 2109 slideshare.net </t>
         </is>
       </c>
-      <c r="B665" t="inlineStr">
+      <c r="B664" t="inlineStr">
         <is>
           <t>images/「開かれたターと結ばれたター」_img1.jpg</t>
         </is>
       </c>
-      <c r="C665" t="inlineStr">
+      <c r="C664" t="inlineStr">
         <is>
           <t>アラビア文字 ,スマイリー</t>
         </is>
       </c>
     </row>
-    <row r="666">
-      <c r="A666" t="inlineStr">
+    <row r="665">
+      <c r="A665" t="inlineStr">
         <is>
           <t xml:space="preserve">「このラマは誇らしげにして立っている」
 تقف هذه اللاما مزهوة بنفسها
@@ -14451,19 +14430,19 @@
 2410 https://twitter.com/NatGeoMagArab/status/1597485552965935104 </t>
         </is>
       </c>
-      <c r="B666" t="inlineStr">
+      <c r="B665" t="inlineStr">
         <is>
           <t>images/「このラマは誇らしげにして立っている」_img1.jpg</t>
         </is>
       </c>
-      <c r="C666" t="inlineStr">
+      <c r="C665" t="inlineStr">
         <is>
           <t>手書き語学 ,アラビア語 ,マチュピチュ遺跡</t>
         </is>
       </c>
     </row>
-    <row r="667">
-      <c r="A667" t="inlineStr">
+    <row r="666">
+      <c r="A666" t="inlineStr">
         <is>
           <t xml:space="preserve">「小さな生き物にしては危険な名前だ」
 اسم خطير لمخلوق صغير
@@ -14472,19 +14451,19 @@
 2308 https://twitter.com/NatGeoMagArab/status/1495035772071669760 </t>
         </is>
       </c>
-      <c r="B667" t="inlineStr">
+      <c r="B666" t="inlineStr">
         <is>
           <t>images/「小さな生き物にしては危険な名前だ」_img1.jpg</t>
         </is>
       </c>
-      <c r="C667" t="inlineStr">
+      <c r="C666" t="inlineStr">
         <is>
           <t>有袋類 ,タスマニアデビル</t>
         </is>
       </c>
     </row>
-    <row r="668">
-      <c r="A668" t="inlineStr">
+    <row r="667">
+      <c r="A667" t="inlineStr">
         <is>
           <t xml:space="preserve">「こわれている」مكسر
 ムカッサル [mukassar]
@@ -14492,19 +14471,19 @@
 2105 behance Written-Visuals </t>
         </is>
       </c>
-      <c r="B668" t="inlineStr">
+      <c r="B667" t="inlineStr">
         <is>
           <t>images/「こわれている」_img1.jpg</t>
         </is>
       </c>
-      <c r="C668" t="inlineStr">
+      <c r="C667" t="inlineStr">
         <is>
           <t>バラバラ ,デザイン</t>
         </is>
       </c>
     </row>
-    <row r="669">
-      <c r="A669" t="inlineStr">
+    <row r="668">
+      <c r="A668" t="inlineStr">
         <is>
           <t xml:space="preserve">「早起きする方法」
 كيف تنهض مُبكّرًا
@@ -14514,19 +14493,19 @@
 2308 Funders and Founders </t>
         </is>
       </c>
-      <c r="B669" t="inlineStr">
+      <c r="B668" t="inlineStr">
         <is>
           <t>images/「早起きする方法」_img1.jpg</t>
         </is>
       </c>
-      <c r="C669" t="inlineStr">
+      <c r="C668" t="inlineStr">
         <is>
           <t>オフトゥン ,寝起き</t>
         </is>
       </c>
     </row>
-    <row r="670">
-      <c r="A670" t="inlineStr">
+    <row r="669">
+      <c r="A669" t="inlineStr">
         <is>
           <t xml:space="preserve">「アラブ・デザイン文字展覧会」
 معرض لتخطيط الحرف العربي
@@ -14536,38 +14515,38 @@
 2109 arabic lettering exhibition </t>
         </is>
       </c>
-      <c r="B670" t="inlineStr">
+      <c r="B669" t="inlineStr">
         <is>
           <t>images/「アラブ・デザイン文字展覧会」_img1.jpg</t>
         </is>
       </c>
-      <c r="C670" t="inlineStr">
+      <c r="C669" t="inlineStr">
         <is>
           <t>ポスター</t>
         </is>
       </c>
     </row>
-    <row r="671">
-      <c r="A671" t="inlineStr">
+    <row r="670">
+      <c r="A670" t="inlineStr">
         <is>
           <t xml:space="preserve">「お気に入りのおもちゃには触らせない」
 ⁦「彼は〜を許さない」[laa ya-smaHu bi-]：「彼は許す」( يسمح )[ya-smaH(u)]：「許した」( سمح )[samaHa]：( سَ )[sa]・( مَ )[ma]・( حَ )[Ha]⁩
 2209 https://pic.twitter.com/qWcIPB3fz2 </t>
         </is>
       </c>
-      <c r="B671" t="inlineStr">
+      <c r="B670" t="inlineStr">
         <is>
           <t>images/「お気に入りのおもちゃには触らせない」_img1.jpg</t>
         </is>
       </c>
-      <c r="C671" t="inlineStr">
+      <c r="C670" t="inlineStr">
         <is>
           <t>パンダ ,ボール</t>
         </is>
       </c>
     </row>
-    <row r="672">
-      <c r="A672" t="inlineStr">
+    <row r="671">
+      <c r="A671" t="inlineStr">
         <is>
           <t xml:space="preserve">「名探偵コナン」المحقق كونان
 アルムハッキク・コナン [al-muHaqqiq Conan]
@@ -14576,19 +14555,19 @@
 1809 wikipedia </t>
         </is>
       </c>
-      <c r="B672" t="inlineStr">
+      <c r="B671" t="inlineStr">
         <is>
           <t>images/「名探偵コナン」_img1.jpg</t>
         </is>
       </c>
-      <c r="C672" t="inlineStr">
+      <c r="C671" t="inlineStr">
         <is>
           <t>江戸川コナン ,ロゴ</t>
         </is>
       </c>
     </row>
-    <row r="673">
-      <c r="A673" t="inlineStr">
+    <row r="672">
+      <c r="A672" t="inlineStr">
         <is>
           <t xml:space="preserve">「イードおめでとう」عيد مبارك
 イード・ムバーラク [*iid mubaarak]
@@ -14596,19 +14575,19 @@
 2308 出典不明 </t>
         </is>
       </c>
-      <c r="B673" t="inlineStr">
+      <c r="B672" t="inlineStr">
         <is>
           <t>images/「イードおめでとう」_img1.jpg</t>
         </is>
       </c>
-      <c r="C673" t="inlineStr">
+      <c r="C672" t="inlineStr">
         <is>
           <t>عيد ,アラビア語</t>
         </is>
       </c>
     </row>
-    <row r="674">
-      <c r="A674" t="inlineStr">
+    <row r="673">
+      <c r="A673" t="inlineStr">
         <is>
           <t xml:space="preserve">「戦士」محارب
 ムハーリブ [muHaarib]
@@ -14617,19 +14596,19 @@
 1809 abudinges.tumblr </t>
         </is>
       </c>
-      <c r="B674" t="inlineStr">
+      <c r="B673" t="inlineStr">
         <is>
           <t>images/「戦士」_img1.jpg</t>
         </is>
       </c>
-      <c r="C674" t="inlineStr">
+      <c r="C673" t="inlineStr">
         <is>
           <t>ロゴ ,赤</t>
         </is>
       </c>
     </row>
-    <row r="675">
-      <c r="A675" t="inlineStr">
+    <row r="674">
+      <c r="A674" t="inlineStr">
         <is>
           <t xml:space="preserve">「ライブ」بث مباشر
 バッス・ムバーシル [ba^Th(un) mubaaShir(un)]
@@ -14638,19 +14617,19 @@
 2308 beIN SPORTS </t>
         </is>
       </c>
-      <c r="B675" t="inlineStr">
+      <c r="B674" t="inlineStr">
         <is>
           <t>images/「ライブ」_img1.jpg</t>
         </is>
       </c>
-      <c r="C675" t="inlineStr">
+      <c r="C674" t="inlineStr">
         <is>
           <t xml:space="preserve">生放送 ,試合 </t>
         </is>
       </c>
     </row>
-    <row r="676">
-      <c r="A676" t="inlineStr">
+    <row r="675">
+      <c r="A675" t="inlineStr">
         <is>
           <t xml:space="preserve">「信者」مُؤْمِنٌ
 ムッミン [mu'min(un)]
@@ -14659,19 +14638,19 @@
 2106 出典不明 </t>
         </is>
       </c>
-      <c r="B676" t="inlineStr">
+      <c r="B675" t="inlineStr">
         <is>
           <t>images/「信者」_img1.jpg</t>
         </is>
       </c>
-      <c r="C676" t="inlineStr">
+      <c r="C675" t="inlineStr">
         <is>
           <t>明暗 ,信仰</t>
         </is>
       </c>
     </row>
-    <row r="677">
-      <c r="A677" t="inlineStr">
+    <row r="676">
+      <c r="A676" t="inlineStr">
         <is>
           <t xml:space="preserve">「開⇔閉」
 مفتوح
@@ -14682,19 +14661,19 @@
 2312 Hussein Safina, behance </t>
         </is>
       </c>
-      <c r="B677" t="inlineStr">
+      <c r="B676" t="inlineStr">
         <is>
           <t>images/「開⇔閉」_img1.jpg</t>
         </is>
       </c>
-      <c r="C677" t="inlineStr">
+      <c r="C676" t="inlineStr">
         <is>
           <t>オープンマインド ,トグル</t>
         </is>
       </c>
     </row>
-    <row r="678">
-      <c r="A678" t="inlineStr">
+    <row r="677">
+      <c r="A677" t="inlineStr">
         <is>
           <t xml:space="preserve">「予想外な結末！」
 نهاية غير متوقعة
@@ -14702,19 +14681,19 @@
 2308 https://twitter.com/NatGeoMagArab/status/1159011433444593665 </t>
         </is>
       </c>
-      <c r="B678" t="inlineStr">
+      <c r="B677" t="inlineStr">
         <is>
           <t>images/「予想外な結末！」_img1.jpg</t>
         </is>
       </c>
-      <c r="C678" t="inlineStr">
+      <c r="C677" t="inlineStr">
         <is>
           <t>手書き語学 ,アラビア語 ,ウサギ</t>
         </is>
       </c>
     </row>
-    <row r="679">
-      <c r="A679" t="inlineStr">
+    <row r="678">
+      <c r="A678" t="inlineStr">
         <is>
           <t xml:space="preserve">「ベイルート・アニメイテッド」
 بیروت متحرّکة
@@ -14724,19 +14703,19 @@
 2308 arabic_script Instagram </t>
         </is>
       </c>
-      <c r="B679" t="inlineStr">
+      <c r="B678" t="inlineStr">
         <is>
           <t>images/「ベイルート・アニメイテッド」_img1.jpg</t>
         </is>
       </c>
-      <c r="C679" t="inlineStr">
+      <c r="C678" t="inlineStr">
         <is>
           <t>アニメ ,レバノン</t>
         </is>
       </c>
     </row>
-    <row r="680">
-      <c r="A680" t="inlineStr">
+    <row r="679">
+      <c r="A679" t="inlineStr">
         <is>
           <t xml:space="preserve">「夢みれば叶う」
 كُلُّ مُتَوَقَّعٍ آتٍ
@@ -14746,19 +14725,19 @@
 2108 Ahmed Madyan </t>
         </is>
       </c>
-      <c r="B680" t="inlineStr">
+      <c r="B679" t="inlineStr">
         <is>
           <t>images/「夢みれば叶う」_img1.jpg</t>
         </is>
       </c>
-      <c r="C680" t="inlineStr">
+      <c r="C679" t="inlineStr">
         <is>
           <t>希望 ,ドリカム</t>
         </is>
       </c>
     </row>
-    <row r="681">
-      <c r="A681" t="inlineStr">
+    <row r="680">
+      <c r="A680" t="inlineStr">
         <is>
           <t xml:space="preserve">「もし両者が人間のように鎧で武装して戦いに突入したら」
 لو خاضا معاركهما متسلحين بالدروع على غرار البش
@@ -14766,19 +14745,19 @@
 2404 https://x.com/NatGeoMagArab/status/1759284149456945464 </t>
         </is>
       </c>
-      <c r="B681" t="inlineStr">
+      <c r="B680" t="inlineStr">
         <is>
           <t>images/「もし両者が人間のように鎧で武装して戦_img1.jpg,images/「もし両者が人間のように鎧で武装して戦_img2.jpg</t>
         </is>
       </c>
-      <c r="C681" t="inlineStr">
+      <c r="C680" t="inlineStr">
         <is>
           <t>手書き語学 ,アラビア語 ,猫</t>
         </is>
       </c>
     </row>
-    <row r="682">
-      <c r="A682" t="inlineStr">
+    <row r="681">
+      <c r="A681" t="inlineStr">
         <is>
           <t xml:space="preserve">「全ては結びついている」
 كل شيء مترابط
@@ -14788,19 +14767,19 @@
 2308 Ahmed Madyan https://twitter.com/madyco22/status/1451990828298166273 </t>
         </is>
       </c>
-      <c r="B682" t="inlineStr">
+      <c r="B681" t="inlineStr">
         <is>
           <t>images/「全ては結びついている」_img1.jpg</t>
         </is>
       </c>
-      <c r="C682" t="inlineStr">
+      <c r="C681" t="inlineStr">
         <is>
           <t>一筆書き ,デザイン</t>
         </is>
       </c>
     </row>
-    <row r="683">
-      <c r="A683" t="inlineStr">
+    <row r="682">
+      <c r="A682" t="inlineStr">
         <is>
           <t xml:space="preserve">「初心者のためのスケッチトレーニング」
 تعليم الرسم للمبتدئين
@@ -14810,19 +14789,19 @@
 2308 free-bookspdf com </t>
         </is>
       </c>
-      <c r="B683" t="inlineStr">
+      <c r="B682" t="inlineStr">
         <is>
           <t>images/「初心者のためのスケッチトレーニング」_img1.jpg</t>
         </is>
       </c>
-      <c r="C683" t="inlineStr">
+      <c r="C682" t="inlineStr">
         <is>
           <t>イラスト ,絵</t>
         </is>
       </c>
     </row>
-    <row r="684">
-      <c r="A684" t="inlineStr">
+    <row r="683">
+      <c r="A683" t="inlineStr">
         <is>
           <t xml:space="preserve">「初心者のためのスルス体書道トレーニング」
 تعليم خط الثلث للمبتدئين
@@ -14832,19 +14811,19 @@
 2308 出典不明 </t>
         </is>
       </c>
-      <c r="B684" t="inlineStr">
+      <c r="B683" t="inlineStr">
         <is>
           <t>images/「初心者のためのスルス体書道トレーニン_img1.jpg</t>
         </is>
       </c>
-      <c r="C684" t="inlineStr">
+      <c r="C683" t="inlineStr">
         <is>
           <t>書道</t>
         </is>
       </c>
     </row>
-    <row r="685">
-      <c r="A685" t="inlineStr">
+    <row r="684">
+      <c r="A684" t="inlineStr">
         <is>
           <t xml:space="preserve">「笑顔でいなさい」خليك مبتسم
 カッリーク・ムブタスィム [Khallii-k mubtasim]
@@ -14853,19 +14832,19 @@
 2308 https://tmblr.co/Zj9tguYLXBvC </t>
         </is>
       </c>
-      <c r="B685" t="inlineStr">
+      <c r="B684" t="inlineStr">
         <is>
           <t>images/「笑顔でいなさい」_img1.jpg</t>
         </is>
       </c>
-      <c r="C685" t="inlineStr">
+      <c r="C684" t="inlineStr">
         <is>
           <t>スマイル ,名言</t>
         </is>
       </c>
     </row>
-    <row r="686">
-      <c r="A686" t="inlineStr">
+    <row r="685">
+      <c r="A685" t="inlineStr">
         <is>
           <t xml:space="preserve">自動車メーカー
 ⁦・「TOYOTA」( تويوتا )⁩
@@ -14877,19 +14856,19 @@
 2308 syarah com </t>
         </is>
       </c>
-      <c r="B686" t="inlineStr">
+      <c r="B685" t="inlineStr">
         <is>
           <t>images/自動車メーカー_img1.jpg,images/自動車メーカー_img2.jpg,images/自動車メーカー_img3.jpg,images/自動車メーカー_img4.jpg</t>
         </is>
       </c>
-      <c r="C686" t="inlineStr">
+      <c r="C685" t="inlineStr">
         <is>
           <t>日本車 ,韓国車</t>
         </is>
       </c>
     </row>
-    <row r="687">
-      <c r="A687" t="inlineStr">
+    <row r="686">
+      <c r="A686" t="inlineStr">
         <is>
           <t xml:space="preserve">「僕たちは協力して不可能を達成するよ」
 بالتعاون نحقق المحال
@@ -14899,19 +14878,19 @@
 2109 </t>
         </is>
       </c>
-      <c r="B687" t="inlineStr">
+      <c r="B686" t="inlineStr">
         <is>
           <t>images/「僕たちは協力して不可能を達成するよ」_img1.jpg</t>
         </is>
       </c>
-      <c r="C687" t="inlineStr">
+      <c r="C686" t="inlineStr">
         <is>
           <t>無理 ,ハム太郎</t>
         </is>
       </c>
     </row>
-    <row r="688">
-      <c r="A688" t="inlineStr">
+    <row r="687">
+      <c r="A687" t="inlineStr">
         <is>
           <t xml:space="preserve">「幸せは伝染性。喜びを広めよう」
 السعادة معدية فأشع الفرح
@@ -14921,19 +14900,19 @@
 2511 instagram　com/p/fVEfxEo7Va/ </t>
         </is>
       </c>
-      <c r="B688" t="inlineStr">
+      <c r="B687" t="inlineStr">
         <is>
           <t>images/「幸せは伝染性。喜びを広めよう」_img1.jpg</t>
         </is>
       </c>
-      <c r="C688" t="inlineStr">
+      <c r="C687" t="inlineStr">
         <is>
           <t>拡散希望</t>
         </is>
       </c>
     </row>
-    <row r="689">
-      <c r="A689" t="inlineStr">
+    <row r="688">
+      <c r="A688" t="inlineStr">
         <is>
           <t xml:space="preserve">「ストレスは人間だけのものではない」
 الشعور بالتوتر ليس حكرًا على البشر
@@ -14941,19 +14920,19 @@
 2408 https://x.com/NatGeoMagArab/status/1736755816911487420 </t>
         </is>
       </c>
-      <c r="B689" t="inlineStr">
+      <c r="B688" t="inlineStr">
         <is>
           <t>images/「ストレスは人間だけのものではない」_img1.jpg</t>
         </is>
       </c>
-      <c r="C689" t="inlineStr">
+      <c r="C688" t="inlineStr">
         <is>
           <t>手書き語学 ,アラビア語 ,ストレス</t>
         </is>
       </c>
     </row>
-    <row r="690">
-      <c r="A690" t="inlineStr">
+    <row r="689">
+      <c r="A689" t="inlineStr">
         <is>
           <t xml:space="preserve">「私達は出来ます！」
 نستطيع فعلها
@@ -14963,19 +14942,19 @@
 2308 NAHARBAHIJ com </t>
         </is>
       </c>
-      <c r="B690" t="inlineStr">
+      <c r="B689" t="inlineStr">
         <is>
           <t>images/「私達は出来ます！」_img1.jpg</t>
         </is>
       </c>
-      <c r="C690" t="inlineStr">
+      <c r="C689" t="inlineStr">
         <is>
           <t>女性 ,パロディ</t>
         </is>
       </c>
     </row>
-    <row r="691">
-      <c r="A691" t="inlineStr">
+    <row r="690">
+      <c r="A690" t="inlineStr">
         <is>
           <t xml:space="preserve">「全然分からん」ولا فاهم إشي
 ウラー・ファーヒム・イシ [w-laa faahim 'iShy]
@@ -14985,19 +14964,19 @@
 2209 出典不明 </t>
         </is>
       </c>
-      <c r="B691" t="inlineStr">
+      <c r="B690" t="inlineStr">
         <is>
           <t>images/「全然分からん」_img1.jpg</t>
         </is>
       </c>
-      <c r="C691" t="inlineStr">
+      <c r="C690" t="inlineStr">
         <is>
           <t>アラビア語</t>
         </is>
       </c>
     </row>
-    <row r="692">
-      <c r="A692" t="inlineStr">
+    <row r="691">
+      <c r="A691" t="inlineStr">
         <is>
           <t xml:space="preserve">「人間は一人ひとり、特別な才がある。だから自分を他人と比べるのはやめよう」
 لكل إنسان مواهبه الخاصة 
@@ -15006,19 +14985,19 @@
 1812 Gwid3 </t>
         </is>
       </c>
-      <c r="B692" t="inlineStr">
+      <c r="B691" t="inlineStr">
         <is>
           <t>images/「人間は一人ひとり、特別な才がある。だ_img1.jpg</t>
         </is>
       </c>
-      <c r="C692" t="inlineStr">
+      <c r="C691" t="inlineStr">
         <is>
           <t>自尊 ,プライド</t>
         </is>
       </c>
     </row>
-    <row r="693">
-      <c r="A693" t="inlineStr">
+    <row r="692">
+      <c r="A692" t="inlineStr">
         <is>
           <t xml:space="preserve">「この猫は食事をシェアするのが嫌い！」
 هذه القطة لا تحب مشاركة الطعام
@@ -15027,19 +15006,19 @@
 2605 facebook com/alahram/videos/2154923608133231/ </t>
         </is>
       </c>
-      <c r="B693" t="inlineStr">
+      <c r="B692" t="inlineStr">
         <is>
           <t>images/「この猫は食事をシェアするのが嫌い！」_img1.jpg</t>
         </is>
       </c>
-      <c r="C693" t="inlineStr">
+      <c r="C692" t="inlineStr">
         <is>
           <t>猫 ,ネコ</t>
         </is>
       </c>
     </row>
-    <row r="694">
-      <c r="A694" t="inlineStr">
+    <row r="693">
+      <c r="A693" t="inlineStr">
         <is>
           <t xml:space="preserve">「怪獣との戦いでは自分が怪獣化せぬよう警戒しなさい」
 احذر عند محاربة الوحوش ألا تصبح واحدا منهم
@@ -15049,19 +15028,19 @@
 2108 warag-3nb.tumblr </t>
         </is>
       </c>
-      <c r="B694" t="inlineStr">
+      <c r="B693" t="inlineStr">
         <is>
           <t>images/「怪獣との戦いでは自分が怪獣化せぬよう_img1.jpg,images/ 「怪獣との戦いでは自分が怪獣化せぬよう_img2.jpg</t>
         </is>
       </c>
-      <c r="C694" t="inlineStr">
+      <c r="C693" t="inlineStr">
         <is>
           <t>正気 ,モンスター</t>
         </is>
       </c>
     </row>
-    <row r="695">
-      <c r="A695" t="inlineStr">
+    <row r="694">
+      <c r="A694" t="inlineStr">
         <is>
           <t xml:space="preserve">「錯視アート」فن الخداع البصري
 ファンヌ_ルヒダーイ_ルバサリーイ [fannu l-Khidaa*i l-ba_sariyy]
@@ -15070,19 +15049,19 @@
 2409 https://online.pubhtml5.com/idtb/neft/ </t>
         </is>
       </c>
-      <c r="B695" t="inlineStr">
+      <c r="B694" t="inlineStr">
         <is>
           <t>images/「錯視アート」_img1.jpg</t>
         </is>
       </c>
-      <c r="C695" t="inlineStr">
+      <c r="C694" t="inlineStr">
         <is>
           <t>トリックアート</t>
         </is>
       </c>
     </row>
-    <row r="696">
-      <c r="A696" t="inlineStr">
+    <row r="695">
+      <c r="A695" t="inlineStr">
         <is>
           <t xml:space="preserve">「自然界の消防士の訓練」
 تدريبات رجال الإطفاء في الطبيعة
@@ -15090,19 +15069,19 @@
 2308 https://twitter.com/NatGeoMagArab/status/1462420543890608129 </t>
         </is>
       </c>
-      <c r="B696" t="inlineStr">
+      <c r="B695" t="inlineStr">
         <is>
           <t>images/「自然界の消防士の訓練」_img1.jpg,images/ 「自然界の消防士の訓練」_img2.jpg</t>
         </is>
       </c>
-      <c r="C696" t="inlineStr">
+      <c r="C695" t="inlineStr">
         <is>
           <t>手書き語学 ,アラビア語 ,ヒグマ</t>
         </is>
       </c>
     </row>
-    <row r="697">
-      <c r="A697" t="inlineStr">
+    <row r="696">
+      <c r="A696" t="inlineStr">
         <is>
           <t xml:space="preserve">「救助」إسعاف
 イスアーフ ['is*aaf]
@@ -15111,19 +15090,19 @@
 2109 ambulance gov ae </t>
         </is>
       </c>
-      <c r="B697" t="inlineStr">
+      <c r="B696" t="inlineStr">
         <is>
           <t>images/「救助」_img1.jpg</t>
         </is>
       </c>
-      <c r="C697" t="inlineStr">
+      <c r="C696" t="inlineStr">
         <is>
           <t>救急車 ,はたらくくるま</t>
         </is>
       </c>
     </row>
-    <row r="698">
-      <c r="A698" t="inlineStr">
+    <row r="697">
+      <c r="A697" t="inlineStr">
         <is>
           <t xml:space="preserve">「感情／感覚」الإحْسَاسْ
 アルイヒサース [al-'iHsaas]
@@ -15132,19 +15111,19 @@
 2308 iN49R </t>
         </is>
       </c>
-      <c r="B698" t="inlineStr">
+      <c r="B697" t="inlineStr">
         <is>
           <t>images/「感情／感覚」_img1.jpg</t>
         </is>
       </c>
-      <c r="C698" t="inlineStr">
+      <c r="C697" t="inlineStr">
         <is>
           <t>オフ ,一休み</t>
         </is>
       </c>
     </row>
-    <row r="699">
-      <c r="A699" t="inlineStr">
+    <row r="698">
+      <c r="A698" t="inlineStr">
         <is>
           <t xml:space="preserve">「ひらめき」إلهام
 イルハーム ['lhaam]
@@ -15156,19 +15135,19 @@
 2103 出典不明 </t>
         </is>
       </c>
-      <c r="B699" t="inlineStr">
+      <c r="B698" t="inlineStr">
         <is>
           <t>images/「ひらめき」_img1.jpg</t>
         </is>
       </c>
-      <c r="C699" t="inlineStr">
+      <c r="C698" t="inlineStr">
         <is>
           <t>アラビア語</t>
         </is>
       </c>
     </row>
-    <row r="700">
-      <c r="A700" t="inlineStr">
+    <row r="699">
+      <c r="A699" t="inlineStr">
         <is>
           <t xml:space="preserve">「Ibdaa／クリエイティビティ」
 إبداع
@@ -15177,19 +15156,19 @@
 2308 Ibdaa Design &amp; Decoration Office </t>
         </is>
       </c>
-      <c r="B700" t="inlineStr">
+      <c r="B699" t="inlineStr">
         <is>
           <t>images/「Ibdaa／クリエイティビティ」_img1.jpg</t>
         </is>
       </c>
-      <c r="C700" t="inlineStr">
+      <c r="C699" t="inlineStr">
         <is>
           <t>創造性 ,独自性</t>
         </is>
       </c>
     </row>
-    <row r="701">
-      <c r="A701" t="inlineStr">
+    <row r="700">
+      <c r="A700" t="inlineStr">
         <is>
           <t xml:space="preserve">「奮闘なくして進歩なし」
 بدون كفاح لايوجد تقدم
@@ -15199,19 +15178,19 @@
 2105 ROUYMS TUMBLR COM </t>
         </is>
       </c>
-      <c r="B701" t="inlineStr">
+      <c r="B700" t="inlineStr">
         <is>
           <t>images/「奮闘なくして進歩なし」_img1.jpg</t>
         </is>
       </c>
-      <c r="C701" t="inlineStr">
+      <c r="C700" t="inlineStr">
         <is>
           <t>努力 ,三角形</t>
         </is>
       </c>
     </row>
-    <row r="702">
-      <c r="A702" t="inlineStr">
+    <row r="701">
+      <c r="A701" t="inlineStr">
         <is>
           <t xml:space="preserve">「木に登れば熊の危険を避けられるとお考えなら、考え直しましょう！」 
 إن اعتقدت أنك بمنأى عن خطر الدب عند تسلق الأشجار.. راجع حساباتك
@@ -15219,19 +15198,19 @@
 2202 NatGeoMagArab </t>
         </is>
       </c>
-      <c r="B702" t="inlineStr">
+      <c r="B701" t="inlineStr">
         <is>
           <t>images/「木に登れば熊の危険を避けられるとお考.jpeg</t>
         </is>
       </c>
-      <c r="C702" t="inlineStr">
+      <c r="C701" t="inlineStr">
         <is>
           <t>クマ</t>
         </is>
       </c>
     </row>
-    <row r="703">
-      <c r="A703" t="inlineStr">
+    <row r="702">
+      <c r="A702" t="inlineStr">
         <is>
           <t xml:space="preserve">「卒業おめでとう」مبروك التخرج
 マブルーク・タカッルジ [mabruuk a^taKharruj]
@@ -15240,19 +15219,19 @@
 2308 https://instagram.com/fatoomworld </t>
         </is>
       </c>
-      <c r="B703" t="inlineStr">
+      <c r="B702" t="inlineStr">
         <is>
           <t>images/「卒業おめでとう」_img1.jpg</t>
         </is>
       </c>
-      <c r="C703" t="inlineStr">
+      <c r="C702" t="inlineStr">
         <is>
           <t>卒業 ,イラスト</t>
         </is>
       </c>
     </row>
-    <row r="704">
-      <c r="A704" t="inlineStr">
+    <row r="703">
+      <c r="A703" t="inlineStr">
         <is>
           <t xml:space="preserve">「停止距離の計算」
 حساب مسافة التوقف
@@ -15262,19 +15241,19 @@
 2109 assurance-auto-info </t>
         </is>
       </c>
-      <c r="B704" t="inlineStr">
+      <c r="B703" t="inlineStr">
         <is>
           <t>images/「停止距離の計算」_img1.jpg</t>
         </is>
       </c>
-      <c r="C704" t="inlineStr">
+      <c r="C703" t="inlineStr">
         <is>
           <t>保険 ,自動車</t>
         </is>
       </c>
     </row>
-    <row r="705">
-      <c r="A705" t="inlineStr">
+    <row r="704">
+      <c r="A704" t="inlineStr">
         <is>
           <t xml:space="preserve">「教師要らず：10日でフランス語会話」
 بدون معلم
@@ -15284,19 +15263,19 @@
 2308 englais-best com </t>
         </is>
       </c>
-      <c r="B705" t="inlineStr">
+      <c r="B704" t="inlineStr">
         <is>
           <t>images/「教師要らず：10日でフランス語会話」_img1.jpg</t>
         </is>
       </c>
-      <c r="C705" t="inlineStr">
+      <c r="C704" t="inlineStr">
         <is>
           <t>教師なし学習</t>
         </is>
       </c>
     </row>
-    <row r="706">
-      <c r="A706" t="inlineStr">
+    <row r="705">
+      <c r="A705" t="inlineStr">
         <is>
           <t xml:space="preserve">「衝突」تصادم
 タサードゥム [ta_saadum]
@@ -15305,19 +15284,19 @@
 1810 </t>
         </is>
       </c>
-      <c r="B706" t="inlineStr">
+      <c r="B705" t="inlineStr">
         <is>
           <t>images/「衝突」_img1.jpg</t>
         </is>
       </c>
-      <c r="C706" t="inlineStr">
+      <c r="C705" t="inlineStr">
         <is>
           <t>あらびあや</t>
         </is>
       </c>
     </row>
-    <row r="707">
-      <c r="A707" t="inlineStr">
+    <row r="706">
+      <c r="A706" t="inlineStr">
         <is>
           <t xml:space="preserve">「楽観主義」تَفَاؤُلٌ
 タファーウル [tafaa'ul(un)]
@@ -15326,19 +15305,19 @@
 1904 arabictypography com </t>
         </is>
       </c>
-      <c r="B707" t="inlineStr">
+      <c r="B706" t="inlineStr">
         <is>
           <t>images/「楽観主義」_img1.jpg</t>
         </is>
       </c>
-      <c r="C707" t="inlineStr">
+      <c r="C706" t="inlineStr">
         <is>
           <t>やわらか ,緑</t>
         </is>
       </c>
     </row>
-    <row r="708">
-      <c r="A708" t="inlineStr">
+    <row r="707">
+      <c r="A707" t="inlineStr">
         <is>
           <t xml:space="preserve">「シベリアジャコウジカは、絶滅の危機にあると見なされている」
 يعد "أيل المسك السيبيري" مهددًا بالانقراض
@@ -15346,19 +15325,19 @@
 2308 https://twitter.com/NatGeoMagArab/status/1320666649045790720 </t>
         </is>
       </c>
-      <c r="B708" t="inlineStr">
+      <c r="B707" t="inlineStr">
         <is>
           <t>images/「シベリアジャコウジカは、絶滅の危機に_img1.jpg,images/「シベリアジャコウジカは、絶滅の危機に_img2.jpg</t>
         </is>
       </c>
-      <c r="C708" t="inlineStr">
+      <c r="C707" t="inlineStr">
         <is>
           <t>手書き語学 ,シベリア</t>
         </is>
       </c>
     </row>
-    <row r="709">
-      <c r="A709" t="inlineStr">
+    <row r="708">
+      <c r="A708" t="inlineStr">
         <is>
           <t xml:space="preserve">「融合／折衷／フュージョン」
 انصهار
@@ -15367,38 +15346,38 @@
 1811 elmahdyart Instagram </t>
         </is>
       </c>
-      <c r="B709" t="inlineStr">
+      <c r="B708" t="inlineStr">
         <is>
           <t>images/「融合／折衷／フュージョン」_img1.jpg</t>
         </is>
       </c>
-      <c r="C709" t="inlineStr">
+      <c r="C708" t="inlineStr">
         <is>
           <t>カリグラフィー ,書道</t>
         </is>
       </c>
     </row>
-    <row r="710">
-      <c r="A710" t="inlineStr">
+    <row r="709">
+      <c r="A709" t="inlineStr">
         <is>
           <t xml:space="preserve">「この子供は、昼寝をしようとする母親を邪魔しているようだ」
 「場所はインドのトラ保護区、バンダウガル公園。トラは生態ピラミッドのトップの捕食動物だが、最もリスクの高い絶滅危惧種のひとつである」
 2308 https://twitter.com/natgeomagarab/status/1553681890665586689 </t>
         </is>
       </c>
-      <c r="B710" t="inlineStr">
+      <c r="B709" t="inlineStr">
         <is>
           <t>images/「この子供は、昼寝をしようとする母親を_img1.jpg,images/「この子供は、昼寝をしようとする母親を_img2.jpg</t>
         </is>
       </c>
-      <c r="C710" t="inlineStr">
+      <c r="C709" t="inlineStr">
         <is>
           <t>手書き語学 ,アラビア語 ,トラ</t>
         </is>
       </c>
     </row>
-    <row r="711">
-      <c r="A711" t="inlineStr">
+    <row r="710">
+      <c r="A710" t="inlineStr">
         <is>
           <t xml:space="preserve">「もし敬意が落ちたら、それと一緒に全部落ちるのだ」
 إن سقط الإحترام سقط معه كل شيء
@@ -15407,19 +15386,19 @@
 2109 出典不明 </t>
         </is>
       </c>
-      <c r="B711" t="inlineStr">
+      <c r="B710" t="inlineStr">
         <is>
           <t>images/「もし敬意が落ちたら、それと一緒に全部_img1.jpg</t>
         </is>
       </c>
-      <c r="C711" t="inlineStr">
+      <c r="C710" t="inlineStr">
         <is>
           <t>リスペクト ,落書き</t>
         </is>
       </c>
     </row>
-    <row r="712">
-      <c r="A712" t="inlineStr">
+    <row r="711">
+      <c r="A711" t="inlineStr">
         <is>
           <t xml:space="preserve">「エジプト特許庁」
 مكتب براءات الاختراع المصرى
@@ -15429,19 +15408,19 @@
 2312 </t>
         </is>
       </c>
-      <c r="B712" t="inlineStr">
+      <c r="B711" t="inlineStr">
         <is>
           <t>images/「エジプト特許庁」_img1.jpg</t>
         </is>
       </c>
-      <c r="C712" t="inlineStr">
+      <c r="C711" t="inlineStr">
         <is>
           <t>patent</t>
         </is>
       </c>
     </row>
-    <row r="713">
-      <c r="A713" t="inlineStr">
+    <row r="712">
+      <c r="A712" t="inlineStr">
         <is>
           <t xml:space="preserve">「選挙」إنتخابات
 インティカーバート [intiKhaabaat]
@@ -15450,19 +15429,19 @@
 2311 nna-leb gov lb </t>
         </is>
       </c>
-      <c r="B713" t="inlineStr">
+      <c r="B712" t="inlineStr">
         <is>
           <t>images/「選挙」_img1.jpg</t>
         </is>
       </c>
-      <c r="C713" t="inlineStr">
+      <c r="C712" t="inlineStr">
         <is>
           <t>選挙 ,投票</t>
         </is>
       </c>
     </row>
-    <row r="714">
-      <c r="A714" t="inlineStr">
+    <row r="713">
+      <c r="A713" t="inlineStr">
         <is>
           <t xml:space="preserve">「待ちぼうけ」إنتظار
 インティザール [inti_Dhaar]
@@ -15471,19 +15450,19 @@
 1809 in4sser.tumblr </t>
         </is>
       </c>
-      <c r="B714" t="inlineStr">
+      <c r="B713" t="inlineStr">
         <is>
           <t>images/「待ちぼうけ」_img1.jpg</t>
         </is>
       </c>
-      <c r="C714" t="inlineStr">
+      <c r="C713" t="inlineStr">
         <is>
           <t>遅すぎ ,辛抱</t>
         </is>
       </c>
     </row>
-    <row r="715">
-      <c r="A715" t="inlineStr">
+    <row r="714">
+      <c r="A714" t="inlineStr">
         <is>
           <t xml:space="preserve">「試験」إختبار
 イクティバール [iKhtibaar]
@@ -15492,19 +15471,19 @@
 2109 出典不明 </t>
         </is>
       </c>
-      <c r="B715" t="inlineStr">
+      <c r="B714" t="inlineStr">
         <is>
           <t>images/「試験」_img1.jpg</t>
         </is>
       </c>
-      <c r="C715" t="inlineStr">
+      <c r="C714" t="inlineStr">
         <is>
           <t>テスト ,考査</t>
         </is>
       </c>
     </row>
-    <row r="716">
-      <c r="A716" t="inlineStr">
+    <row r="715">
+      <c r="A715" t="inlineStr">
         <is>
           <t xml:space="preserve">「チャンネル登録」اشتراك
 イシティラーク [iShtiraak]
@@ -15513,19 +15492,19 @@
 2308 </t>
         </is>
       </c>
-      <c r="B716" t="inlineStr">
+      <c r="B715" t="inlineStr">
         <is>
           <t>images/「チャンネル登録」_img1.jpg</t>
         </is>
       </c>
-      <c r="C716" t="inlineStr">
+      <c r="C715" t="inlineStr">
         <is>
           <t>Subscribe ,YouTube</t>
         </is>
       </c>
     </row>
-    <row r="717">
-      <c r="A717" t="inlineStr">
+    <row r="716">
+      <c r="A716" t="inlineStr">
         <is>
           <t xml:space="preserve">「スマイル」ابتسام
 イブティサーム [ibtisaam]
@@ -15533,37 +15512,37 @@
 1903 behance Written-Visuals </t>
         </is>
       </c>
+      <c r="B716" t="inlineStr">
+        <is>
+          <t>images/「スマイル」_img1.jpg</t>
+        </is>
+      </c>
+      <c r="C716" t="inlineStr">
+        <is>
+          <t>スマイリー ,ツ</t>
+        </is>
+      </c>
+    </row>
+    <row r="717">
+      <c r="A717" t="inlineStr">
+        <is>
+          <t xml:space="preserve">「身体の一部として…」
+2308 https://twitter.com/NatGeoMagArab/status/1528292080337813504 </t>
+        </is>
+      </c>
       <c r="B717" t="inlineStr">
         <is>
-          <t>images/「スマイル」_img1.jpg</t>
+          <t>images/「身体の一部として…」_img1.jpg</t>
         </is>
       </c>
       <c r="C717" t="inlineStr">
         <is>
-          <t>スマイリー ,ツ</t>
+          <t>手書き語学 ,カンガルー</t>
         </is>
       </c>
     </row>
     <row r="718">
       <c r="A718" t="inlineStr">
-        <is>
-          <t xml:space="preserve">「身体の一部として…」
-2308 https://twitter.com/NatGeoMagArab/status/1528292080337813504 </t>
-        </is>
-      </c>
-      <c r="B718" t="inlineStr">
-        <is>
-          <t>images/「身体の一部として…」_img1.jpg</t>
-        </is>
-      </c>
-      <c r="C718" t="inlineStr">
-        <is>
-          <t>手書き語学 ,カンガルー</t>
-        </is>
-      </c>
-    </row>
-    <row r="719">
-      <c r="A719" t="inlineStr">
         <is>
           <t xml:space="preserve">「ディスカバリー」إكتشاف
 イクティシャーフ [iktiShaaf]
@@ -15571,19 +15550,19 @@
 2308 tephanegabrielli com </t>
         </is>
       </c>
-      <c r="B719" t="inlineStr">
+      <c r="B718" t="inlineStr">
         <is>
           <t>images/「ディスカバリー」_img1.jpg</t>
         </is>
       </c>
-      <c r="C719" t="inlineStr">
+      <c r="C718" t="inlineStr">
         <is>
           <t>discovery ,デザイン</t>
         </is>
       </c>
     </row>
-    <row r="720">
-      <c r="A720" t="inlineStr">
+    <row r="719">
+      <c r="A719" t="inlineStr">
         <is>
           <t xml:space="preserve">「重力波の発見は新しい窓を開いた」
 فتَح اكتشاف موجات الجاذبية نافذة جديدة
@@ -15591,19 +15570,19 @@
 2308 https://twitter.com/SciTalk2U/status/1454891943440289793 </t>
         </is>
       </c>
-      <c r="B720" t="inlineStr">
+      <c r="B719" t="inlineStr">
         <is>
           <t>images/「重力波の発見は新しい窓を開いた」_img1.jpg</t>
         </is>
       </c>
-      <c r="C720" t="inlineStr">
+      <c r="C719" t="inlineStr">
         <is>
           <t>手書き語学 ,アラビア語 ,重力波</t>
         </is>
       </c>
     </row>
-    <row r="721">
-      <c r="A721" t="inlineStr">
+    <row r="720">
+      <c r="A720" t="inlineStr">
         <is>
           <t xml:space="preserve">「微笑みに微笑み。先にした人の方が美しい」
 الإبتسامة بالإبتسامة والبادئ أجمل
@@ -15612,19 +15591,19 @@
 2104 出典不明 </t>
         </is>
       </c>
-      <c r="B721" t="inlineStr">
+      <c r="B720" t="inlineStr">
         <is>
           <t>images/「微笑みに微笑み。先にした人の方が美し_img1.jpg,images/「微笑みに微笑み。先にした人の方が美し_img2.jpg</t>
         </is>
       </c>
-      <c r="C721" t="inlineStr">
+      <c r="C720" t="inlineStr">
         <is>
           <t>スマイル ,名言</t>
         </is>
       </c>
     </row>
-    <row r="722">
-      <c r="A722" t="inlineStr">
+    <row r="721">
+      <c r="A721" t="inlineStr">
         <is>
           <t xml:space="preserve">「笑顔」ابتسامة
 イブティサーマ [ibtisaama(tun)]
@@ -15633,19 +15612,19 @@
 2308 satokomatsu, minne </t>
         </is>
       </c>
-      <c r="B722" t="inlineStr">
+      <c r="B721" t="inlineStr">
         <is>
           <t>images/「笑顔」_img1.jpg</t>
         </is>
       </c>
-      <c r="C722" t="inlineStr">
+      <c r="C721" t="inlineStr">
         <is>
           <t>スマイル ,ツ</t>
         </is>
       </c>
     </row>
-    <row r="723">
-      <c r="A723" t="inlineStr">
+    <row r="722">
+      <c r="A722" t="inlineStr">
         <is>
           <t xml:space="preserve">「信仰」ايمان
 イーマーン ['iimaan]
@@ -15654,19 +15633,19 @@
 2506 instagram com/p/6ST-WHOOkJ/ </t>
         </is>
       </c>
-      <c r="B723" t="inlineStr">
+      <c r="B722" t="inlineStr">
         <is>
           <t>images/「信仰」_img1.jpg</t>
         </is>
       </c>
-      <c r="C723" t="inlineStr">
+      <c r="C722" t="inlineStr">
         <is>
           <t>宗教 ,信念</t>
         </is>
       </c>
     </row>
-    <row r="724">
-      <c r="A724" t="inlineStr">
+    <row r="723">
+      <c r="A723" t="inlineStr">
         <is>
           <t xml:space="preserve">「放送」إذاعة
 イザーア ['iDhaa*a]
@@ -15675,19 +15654,19 @@
 2404 heemades, Instagram </t>
         </is>
       </c>
-      <c r="B724" t="inlineStr">
+      <c r="B723" t="inlineStr">
         <is>
           <t>images/「放送」_img1.jpg</t>
         </is>
       </c>
-      <c r="C724" t="inlineStr">
+      <c r="C723" t="inlineStr">
         <is>
           <t>デザイン ,ラジオ</t>
         </is>
       </c>
     </row>
-    <row r="725">
-      <c r="A725" t="inlineStr">
+    <row r="724">
+      <c r="A724" t="inlineStr">
         <is>
           <t xml:space="preserve">「かきとりのちから」
 مهاراتي الإملائية
@@ -15696,19 +15675,19 @@
 2308 iqrawaoktoub.wordpress com </t>
         </is>
       </c>
-      <c r="B725" t="inlineStr">
+      <c r="B724" t="inlineStr">
         <is>
           <t>images/「かきとりのちから」_img1.jpg</t>
         </is>
       </c>
-      <c r="C725" t="inlineStr">
+      <c r="C724" t="inlineStr">
         <is>
           <t>国語 ,教材</t>
         </is>
       </c>
     </row>
-    <row r="726">
-      <c r="A726" t="inlineStr">
+    <row r="725">
+      <c r="A725" t="inlineStr">
         <is>
           <t xml:space="preserve">「歴史を作った男たち」
 رجال صنعوا التاريخ
@@ -15718,38 +15697,38 @@
 2410 https://x.gd/Wl5rJ </t>
         </is>
       </c>
-      <c r="B726" t="inlineStr">
+      <c r="B725" t="inlineStr">
         <is>
           <t>images/「歴史を作った男たち」_img1.jpg</t>
         </is>
       </c>
-      <c r="C726" t="inlineStr">
+      <c r="C725" t="inlineStr">
         <is>
           <t>偉人</t>
         </is>
       </c>
     </row>
-    <row r="727">
-      <c r="A727" t="inlineStr">
+    <row r="726">
+      <c r="A726" t="inlineStr">
         <is>
           <t xml:space="preserve">「無限の宇宙を旅した光」
 「何百年もの末にジェイムズ・ウェッブ望遠鏡のレンズの上に落ち、我々に遠い宇宙の美しさを見せてくれる。最も純粋な形と最も素晴らしい姿で」
 2308 https://twitter.com/NatGeoMagArab/status/1557811592636485632 </t>
         </is>
       </c>
-      <c r="B727" t="inlineStr">
+      <c r="B726" t="inlineStr">
         <is>
           <t>images/「無限の宇宙を旅した光」_img1.jpg</t>
         </is>
       </c>
-      <c r="C727" t="inlineStr">
+      <c r="C726" t="inlineStr">
         <is>
           <t>手書き語学 ,宇宙</t>
         </is>
       </c>
     </row>
-    <row r="728">
-      <c r="A728" t="inlineStr">
+    <row r="727">
+      <c r="A727" t="inlineStr">
         <is>
           <t xml:space="preserve">「日本好きになり行きたくなる20項」
 عشرون شيئا يجعلك تحب اليابان وترغب في زيارتها
@@ -15758,19 +15737,19 @@
 2308 wattpad </t>
         </is>
       </c>
-      <c r="B728" t="inlineStr">
+      <c r="B727" t="inlineStr">
         <is>
           <t>images/「日本好きになり行きたくなる20項」_img1.jpg</t>
         </is>
       </c>
-      <c r="C728" t="inlineStr">
+      <c r="C727" t="inlineStr">
         <is>
           <t>اليابان ,Japan</t>
         </is>
       </c>
     </row>
-    <row r="729">
-      <c r="A729" t="inlineStr">
+    <row r="728">
+      <c r="A728" t="inlineStr">
         <is>
           <t xml:space="preserve">「ピッタリの瞬間に撮影され、ドラゴンが火を噴いているように見える」
 التُقطت في اللحظة المناسبة لتبدو مثل تنين ينفث اللهب
@@ -15778,19 +15757,19 @@
 2509 https://twitter.com/NatGeoMagArab/status/1588780660269150208 </t>
         </is>
       </c>
-      <c r="B729" t="inlineStr">
+      <c r="B728" t="inlineStr">
         <is>
           <t>images/「ピッタリの瞬間に撮影され、ドラゴンが_img1.jpg,images/ 「ピッタリの瞬間に撮影され、ドラゴンが_img2.jpg</t>
         </is>
       </c>
-      <c r="C729" t="inlineStr">
+      <c r="C728" t="inlineStr">
         <is>
           <t xml:space="preserve">ドラゴン </t>
         </is>
       </c>
     </row>
-    <row r="730">
-      <c r="A730" t="inlineStr">
+    <row r="729">
+      <c r="A729" t="inlineStr">
         <is>
           <t xml:space="preserve">「満足は不滅の宝である」
 القَناعَةُ كنز لا يَفنَى
@@ -15800,55 +15779,55 @@
 2308 kareem mrghani </t>
         </is>
       </c>
+      <c r="B729" t="inlineStr">
+        <is>
+          <t>images/「満足は不滅の宝である」_img1.jpg</t>
+        </is>
+      </c>
+      <c r="C729" t="inlineStr">
+        <is>
+          <t>幸福度</t>
+        </is>
+      </c>
+    </row>
+    <row r="730">
+      <c r="A730" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ゴシキセイガイインコ。
+2409 https://twitter.com/NatGeoMagArab/status/1600022262014676992 </t>
+        </is>
+      </c>
       <c r="B730" t="inlineStr">
         <is>
-          <t>images/「満足は不滅の宝である」_img1.jpg</t>
+          <t>images/ゴシキセイガイインコ。_img1.jpg</t>
         </is>
       </c>
       <c r="C730" t="inlineStr">
         <is>
-          <t>幸福度</t>
+          <t>手書き語学 ,アラビア語,オウム</t>
         </is>
       </c>
     </row>
     <row r="731">
       <c r="A731" t="inlineStr">
         <is>
-          <t xml:space="preserve">ゴシキセイガイインコ。
-2409 https://twitter.com/NatGeoMagArab/status/1600022262014676992 </t>
+          <t xml:space="preserve">モモンガ。
+2403 https://twitter.com/NatGeoMagArab/status/1552541872966344704 </t>
         </is>
       </c>
       <c r="B731" t="inlineStr">
         <is>
-          <t>images/ゴシキセイガイインコ。_img1.jpg</t>
+          <t>images/モモンガ。_img1.jpg,images/ モモンガ。_img2.jpg</t>
         </is>
       </c>
       <c r="C731" t="inlineStr">
         <is>
-          <t>手書き語学 ,アラビア語,オウム</t>
+          <t>手書き語学 ,アラビア語 ,モモンガ</t>
         </is>
       </c>
     </row>
     <row r="732">
       <c r="A732" t="inlineStr">
-        <is>
-          <t xml:space="preserve">モモンガ。
-2403 https://twitter.com/NatGeoMagArab/status/1552541872966344704 </t>
-        </is>
-      </c>
-      <c r="B732" t="inlineStr">
-        <is>
-          <t>images/モモンガ。_img1.jpg,images/ モモンガ。_img2.jpg</t>
-        </is>
-      </c>
-      <c r="C732" t="inlineStr">
-        <is>
-          <t>手書き語学 ,アラビア語 ,モモンガ</t>
-        </is>
-      </c>
-    </row>
-    <row r="733">
-      <c r="A733" t="inlineStr">
         <is>
           <t xml:space="preserve">「象の群れ。ドローンの音から逃げている」
 قطيع من الفيلة يفر هاربًا من صوت الدرون
@@ -15860,56 +15839,56 @@
 2009 https://twitter.com/NatGeoMagArab/status/1302970033627258881 </t>
         </is>
       </c>
+      <c r="B732" t="inlineStr">
+        <is>
+          <t>images/「象の群れ。ドローンの音から逃げている.jpg</t>
+        </is>
+      </c>
+      <c r="C732" t="inlineStr">
+        <is>
+          <t>ゾウ ,ドローン</t>
+        </is>
+      </c>
+    </row>
+    <row r="733">
+      <c r="A733" t="inlineStr">
+        <is>
+          <t xml:space="preserve">カルマン線。
+2308 https://twitter.com/NatGeoMagArab/status/1536436999522881536 </t>
+        </is>
+      </c>
       <c r="B733" t="inlineStr">
         <is>
-          <t>images/「象の群れ。ドローンの音から逃げている.jpg</t>
+          <t>images/カルマン線。_img1.jpg</t>
         </is>
       </c>
       <c r="C733" t="inlineStr">
         <is>
-          <t>ゾウ ,ドローン</t>
+          <t xml:space="preserve">手書き語学 ,アラビア語 ,宇宙 </t>
         </is>
       </c>
     </row>
     <row r="734">
       <c r="A734" t="inlineStr">
-        <is>
-          <t xml:space="preserve">カルマン線。
-2308 https://twitter.com/NatGeoMagArab/status/1536436999522881536 </t>
-        </is>
-      </c>
-      <c r="B734" t="inlineStr">
-        <is>
-          <t>images/カルマン線。_img1.jpg</t>
-        </is>
-      </c>
-      <c r="C734" t="inlineStr">
-        <is>
-          <t xml:space="preserve">手書き語学 ,アラビア語 ,宇宙 </t>
-        </is>
-      </c>
-    </row>
-    <row r="735">
-      <c r="A735" t="inlineStr">
         <is>
           <t xml:space="preserve">「恥ずかしがり屋のマヌルネコと暖かい朝の太陽光線」
 ⁦「二つの美しいもの」[Shay'-ayni jamiil-ayni] 属格：「物」( شيء )[Shay']・「美しい」( جميل )[jamiil]⁩
 2309 https://twitter.com/NatGeoMagArab/status/1697512148820504912 </t>
         </is>
       </c>
-      <c r="B735" t="inlineStr">
+      <c r="B734" t="inlineStr">
         <is>
           <t>images/「恥ずかしがり屋のマヌルネコと暖かい朝_img1.jpg</t>
         </is>
       </c>
-      <c r="C735" t="inlineStr">
+      <c r="C734" t="inlineStr">
         <is>
           <t>手書き語学 ,アラビア語 ,マヌルネコ</t>
         </is>
       </c>
     </row>
-    <row r="736">
-      <c r="A736" t="inlineStr">
+    <row r="735">
+      <c r="A735" t="inlineStr">
         <is>
           <t xml:space="preserve">「二回失敗しているペンギン」
 بطريق يفشل مرتين
@@ -15919,19 +15898,19 @@
 2308 https://twitter.com/NatGeoMagArab/status/1479483133766426626 </t>
         </is>
       </c>
-      <c r="B736" t="inlineStr">
+      <c r="B735" t="inlineStr">
         <is>
           <t>images/「二回失敗しているペンギン」_img1.jpg</t>
         </is>
       </c>
-      <c r="C736" t="inlineStr">
+      <c r="C735" t="inlineStr">
         <is>
           <t>ペンギン ,動物</t>
         </is>
       </c>
     </row>
-    <row r="737">
-      <c r="A737" t="inlineStr">
+    <row r="736">
+      <c r="A736" t="inlineStr">
         <is>
           <t xml:space="preserve">「2億光年の彼方できらめく炎と光」
 وهج ووميض يتلألأ على بعد 200 مليون سنة ضوئية
@@ -15942,15 +15921,15 @@
 2010 https://twitter.com/NatGeoMagArab/status/1303415502673342464 </t>
         </is>
       </c>
-      <c r="B737" t="inlineStr"/>
-      <c r="C737" t="inlineStr">
+      <c r="B736" t="inlineStr"/>
+      <c r="C736" t="inlineStr">
         <is>
           <t>宇宙 ,銀河</t>
         </is>
       </c>
     </row>
-    <row r="738">
-      <c r="A738" t="inlineStr">
+    <row r="737">
+      <c r="A737" t="inlineStr">
         <is>
           <t xml:space="preserve">「さまよう黒猫」قطة سوداء تجوب
 キッタトゥン・サウダーウ・タジューブ [qi^_tatun sawdaa'u ta-juub]
@@ -15959,19 +15938,19 @@
 2308 https://twitter.com/NatGeoMagArab/status/1532973177453760512 </t>
         </is>
       </c>
-      <c r="B738" t="inlineStr">
+      <c r="B737" t="inlineStr">
         <is>
           <t>images/「さまよう黒猫」_img1.jpg,images/ 「さまよう黒猫」_img2.jpg</t>
         </is>
       </c>
-      <c r="C738" t="inlineStr">
+      <c r="C737" t="inlineStr">
         <is>
           <t xml:space="preserve">手書き語学 ,モロッコ </t>
         </is>
       </c>
     </row>
-    <row r="739">
-      <c r="A739" t="inlineStr">
+    <row r="738">
+      <c r="A738" t="inlineStr">
         <is>
           <t xml:space="preserve">「サイのざらざらした皮を利用して自分の体を掻くネコ」
 قطة تستغل جلد الكركدن الخشن لحك جسدها
@@ -15980,19 +15959,19 @@
 2308 https://twitter.com/NatGeoMagArab/status/1476855740929216517 </t>
         </is>
       </c>
-      <c r="B739" t="inlineStr">
+      <c r="B738" t="inlineStr">
         <is>
           <t>images/「サイのざらざらした皮を利用して自分の_img1.jpg</t>
         </is>
       </c>
-      <c r="C739" t="inlineStr">
+      <c r="C738" t="inlineStr">
         <is>
           <t>サイ ,チェコ</t>
         </is>
       </c>
     </row>
-    <row r="740">
-      <c r="A740" t="inlineStr">
+    <row r="739">
+      <c r="A739" t="inlineStr">
         <is>
           <t xml:space="preserve">「沈まぬ太陽」شمس لا تغيب
 シャムス・ラー・タギーブ [Shams laa ta-Ghiib]
@@ -16001,19 +15980,19 @@
 2308 AHMED ELASSAL </t>
         </is>
       </c>
-      <c r="B740" t="inlineStr">
+      <c r="B739" t="inlineStr">
         <is>
           <t>images/「沈まぬ太陽」_img1.jpg</t>
         </is>
       </c>
-      <c r="C740" t="inlineStr">
+      <c r="C739" t="inlineStr">
         <is>
           <t>帝国 ,白夜</t>
         </is>
       </c>
     </row>
-    <row r="741">
-      <c r="A741" t="inlineStr">
+    <row r="740">
+      <c r="A740" t="inlineStr">
         <is>
           <t xml:space="preserve">「子供に食べさせている忍耐強い母親」
 أم صبورة تطعم صغيرها
@@ -16022,19 +16001,19 @@
 2308 https://twitter.com/natgeomagarab/status/1585572054509957120 </t>
         </is>
       </c>
-      <c r="B741" t="inlineStr">
+      <c r="B740" t="inlineStr">
         <is>
           <t>images/「子供に食べさせている忍耐強い母親」_img1.jpg</t>
         </is>
       </c>
-      <c r="C741" t="inlineStr">
+      <c r="C740" t="inlineStr">
         <is>
           <t>手書き語学 ,アラビア語 ,ミヤコドリ</t>
         </is>
       </c>
     </row>
-    <row r="742">
-      <c r="A742" t="inlineStr">
+    <row r="741">
+      <c r="A741" t="inlineStr">
         <is>
           <t xml:space="preserve">「コーヒーは繰り返さない恋物語」
 القهوة قصة عشق لن تتكرر
@@ -16044,19 +16023,19 @@
 2403 pin it/7tvd8Wc </t>
         </is>
       </c>
-      <c r="B742" t="inlineStr">
+      <c r="B741" t="inlineStr">
         <is>
           <t>images/「コーヒーは繰り返さない恋物語」_img1.jpg</t>
         </is>
       </c>
-      <c r="C742" t="inlineStr">
+      <c r="C741" t="inlineStr">
         <is>
           <t>コーヒー ,名言</t>
         </is>
       </c>
     </row>
-    <row r="743">
-      <c r="A743" t="inlineStr">
+    <row r="742">
+      <c r="A742" t="inlineStr">
         <is>
           <t xml:space="preserve">「星々で飾られた空。魅惑的な色合いで黄昏の美を満たしている」
 سماء مرصعة بالنجوم تضفي لمسة سحرية على جمال الشفق
@@ -16064,19 +16043,19 @@
 2010 https://twitter.com/NatGeoMagArab/status/1303777701975584768 </t>
         </is>
       </c>
-      <c r="B743" t="inlineStr">
+      <c r="B742" t="inlineStr">
         <is>
           <t>images/「星々で飾られた空。魅惑的な色合いで黄.png</t>
         </is>
       </c>
-      <c r="C743" t="inlineStr">
+      <c r="C742" t="inlineStr">
         <is>
           <t>星空 ,宇宙</t>
         </is>
       </c>
     </row>
-    <row r="744">
-      <c r="A744" t="inlineStr">
+    <row r="743">
+      <c r="A743" t="inlineStr">
         <is>
           <t xml:space="preserve">「国際宇宙ステーションからの写真。巨大な台風『ハイシェン（海神）』を映している」
 لقطات من محطة الفضاء الدولية تظهر إعصار "هايشن" الهائل
@@ -16084,19 +16063,19 @@
 2403 https://twitter.com/NatGeoMagArab/status/1302871968522235904 </t>
         </is>
       </c>
-      <c r="B744" t="inlineStr">
+      <c r="B743" t="inlineStr">
         <is>
           <t>images/「国際宇宙ステーションからの写真。巨大.png</t>
         </is>
       </c>
-      <c r="C744" t="inlineStr">
+      <c r="C743" t="inlineStr">
         <is>
           <t>台風</t>
         </is>
       </c>
     </row>
-    <row r="745">
-      <c r="A745" t="inlineStr">
+    <row r="744">
+      <c r="A744" t="inlineStr">
         <is>
           <t xml:space="preserve">「草を食む幸運な子羊たち」
 خراف محظوظة ترعى
@@ -16106,19 +16085,19 @@
 2308 https://twitter.com/NatGeoMagArab/status/1490211393554972676 </t>
         </is>
       </c>
-      <c r="B745" t="inlineStr">
+      <c r="B744" t="inlineStr">
         <is>
           <t>images/「草を食む幸運な子羊たち」_img1.jpg,images/ 「草を食む幸運な子羊たち」_img2.jpg</t>
         </is>
       </c>
-      <c r="C745" t="inlineStr">
+      <c r="C744" t="inlineStr">
         <is>
           <t>羊 ,アイルランド</t>
         </is>
       </c>
     </row>
-    <row r="746">
-      <c r="A746" t="inlineStr">
+    <row r="745">
+      <c r="A745" t="inlineStr">
         <is>
           <t xml:space="preserve">「お金で買えぬ10のもの」
 ١٠ أشياء لا تشترى بالمال
@@ -16128,19 +16107,19 @@
 2308 ayb124 </t>
         </is>
       </c>
-      <c r="B746" t="inlineStr">
+      <c r="B745" t="inlineStr">
         <is>
           <t>images/「お金で買えぬ10のもの」_img1.jpg</t>
         </is>
       </c>
-      <c r="C746" t="inlineStr">
+      <c r="C745" t="inlineStr">
         <is>
           <t>価値 ,購買</t>
         </is>
       </c>
     </row>
-    <row r="747">
-      <c r="A747" t="inlineStr">
+    <row r="746">
+      <c r="A746" t="inlineStr">
         <is>
           <t xml:space="preserve">「お金では買えないよ」
 هي أشْيَاءٌ لا تُشْتَرَى
@@ -16150,19 +16129,19 @@
 1906 mardy_zaawely, Instagram </t>
         </is>
       </c>
-      <c r="B747" t="inlineStr">
+      <c r="B746" t="inlineStr">
         <is>
           <t>images/「お金では買えないよ」_img1.jpg</t>
         </is>
       </c>
-      <c r="C747" t="inlineStr">
+      <c r="C746" t="inlineStr">
         <is>
           <t>マスターカード ,価値</t>
         </is>
       </c>
     </row>
-    <row r="748">
-      <c r="A748" t="inlineStr">
+    <row r="747">
+      <c r="A747" t="inlineStr">
         <is>
           <t xml:space="preserve">「好奇心旺盛なホッキョクギツネ」
 ثعلب قطبي يملؤه الفضول
@@ -16172,15 +16151,15 @@
 2308 https://twitter.com/natgeomagarab/status/1157592172968808449 </t>
         </is>
       </c>
-      <c r="B748" t="inlineStr"/>
-      <c r="C748" t="inlineStr">
+      <c r="B747" t="inlineStr"/>
+      <c r="C747" t="inlineStr">
         <is>
           <t>ファーストコンタクト ,キツネ</t>
         </is>
       </c>
     </row>
-    <row r="749">
-      <c r="A749" t="inlineStr">
+    <row r="748">
+      <c r="A748" t="inlineStr">
         <is>
           <t xml:space="preserve">「グレンダイザーのいる国は死にません」
 لنْ يَموتَ شَعبٌ لدَيهِ غرندايزر
@@ -16189,56 +16168,56 @@
 2308 https://www.aljarida.com/articles/1462241741574732100/ </t>
         </is>
       </c>
+      <c r="B748" t="inlineStr">
+        <is>
+          <t>images/「グレンダイザーのいる国は死にません」_img1.jpg</t>
+        </is>
+      </c>
+      <c r="C748" t="inlineStr">
+        <is>
+          <t>UFOロボ ,アニメ</t>
+        </is>
+      </c>
+    </row>
+    <row r="749">
+      <c r="A749" t="inlineStr">
+        <is>
+          <t xml:space="preserve">「凍結路面を運転中、彼女は嫌な場面に居合わせた」
+2408 https://twitter.com/NatGeoMagArab/status/1610305209657626625 </t>
+        </is>
+      </c>
       <c r="B749" t="inlineStr">
         <is>
-          <t>images/「グレンダイザーのいる国は死にません」_img1.jpg</t>
+          <t>images/「凍結路面を運転中、彼女は嫌な場面に居_img1.jpg</t>
         </is>
       </c>
       <c r="C749" t="inlineStr">
         <is>
-          <t>UFOロボ ,アニメ</t>
+          <t>手書き語学 ,アラビア語 ,路面凍結</t>
         </is>
       </c>
     </row>
     <row r="750">
       <c r="A750" t="inlineStr">
-        <is>
-          <t xml:space="preserve">「凍結路面を運転中、彼女は嫌な場面に居合わせた」
-2408 https://twitter.com/NatGeoMagArab/status/1610305209657626625 </t>
-        </is>
-      </c>
-      <c r="B750" t="inlineStr">
-        <is>
-          <t>images/「凍結路面を運転中、彼女は嫌な場面に居_img1.jpg</t>
-        </is>
-      </c>
-      <c r="C750" t="inlineStr">
-        <is>
-          <t>手書き語学 ,アラビア語 ,路面凍結</t>
-        </is>
-      </c>
-    </row>
-    <row r="751">
-      <c r="A751" t="inlineStr">
         <is>
           <t xml:space="preserve">「虹が美しさを加えている、アルパカという動物の美しいショット」
 ⁦「美しいショット」[laq_tatun jamiilatun]：「ショット」( لقطة )[laq_ta]：( ـلٌ )[-lun]・( ـقٌ )[-qun]・( ـطٌ )[-_tun]・( ـةٌ )[-tun]⁩
 2308 https://twitter.com/natgeomagarab/status/1155115655928004608 </t>
         </is>
       </c>
-      <c r="B751" t="inlineStr">
+      <c r="B750" t="inlineStr">
         <is>
           <t>images/「虹が美しさを加えている、アルパカとい_img1.jpg</t>
         </is>
       </c>
-      <c r="C751" t="inlineStr">
+      <c r="C750" t="inlineStr">
         <is>
           <t>モフモフ ,アルパカ</t>
         </is>
       </c>
     </row>
-    <row r="752">
-      <c r="A752" t="inlineStr">
+    <row r="751">
+      <c r="A751" t="inlineStr">
         <is>
           <t xml:space="preserve">「幸せは…全然思いもよらない所からやって来る」
 السعادة تأتينا من أماكن لم نكن نتوقعها أبداً
@@ -16247,19 +16226,19 @@
 2109 出典不明 </t>
         </is>
       </c>
-      <c r="B752" t="inlineStr">
+      <c r="B751" t="inlineStr">
         <is>
           <t>images/「幸せは…全然思いもよらない所からやっ_img1.jpg,images/ 「幸せは…全然思いもよらない所からやっ_img2.jpg</t>
         </is>
       </c>
-      <c r="C752" t="inlineStr">
+      <c r="C751" t="inlineStr">
         <is>
           <t>訪れ ,予想</t>
         </is>
       </c>
     </row>
-    <row r="753">
-      <c r="A753" t="inlineStr">
+    <row r="752">
+      <c r="A752" t="inlineStr">
         <is>
           <t xml:space="preserve">「あらゆる問題は、食べ物が解決してくれる」
 كل مشكلة ولها أكلة تحلها
@@ -16268,19 +16247,19 @@
 1909 ALQA AN 878 </t>
         </is>
       </c>
-      <c r="B753" t="inlineStr">
+      <c r="B752" t="inlineStr">
         <is>
           <t>images/「あらゆる問題は、食べ物が解決してくれ_img1.jpg</t>
         </is>
       </c>
-      <c r="C753" t="inlineStr">
+      <c r="C752" t="inlineStr">
         <is>
           <t>ストレス ,精神</t>
         </is>
       </c>
     </row>
-    <row r="754">
-      <c r="A754" t="inlineStr">
+    <row r="753">
+      <c r="A753" t="inlineStr">
         <is>
           <t xml:space="preserve">「冬で私が好きな物」
 أشياء أحبها بالشتاء
@@ -16290,19 +16269,19 @@
 2109 出典不明 </t>
         </is>
       </c>
-      <c r="B754" t="inlineStr">
+      <c r="B753" t="inlineStr">
         <is>
           <t>images/「冬で私が好きな物」_img1.jpg</t>
         </is>
       </c>
-      <c r="C754" t="inlineStr">
+      <c r="C753" t="inlineStr">
         <is>
           <t>季節 ,冬</t>
         </is>
       </c>
     </row>
-    <row r="755">
-      <c r="A755" t="inlineStr">
+    <row r="754">
+      <c r="A754" t="inlineStr">
         <is>
           <t xml:space="preserve">「お金で買うことの出来ない物」
 أشياء لا تستطيع شراءها بالمال
@@ -16312,19 +16291,19 @@
 2409 https://x.com/akhbarak/status/1038402708414373888 </t>
         </is>
       </c>
-      <c r="B755" t="inlineStr">
+      <c r="B754" t="inlineStr">
         <is>
           <t>images/「お金で買うことの出来ない物」_img1.jpg,images/ 「お金で買うことの出来ない物」_img2.jpg</t>
         </is>
       </c>
-      <c r="C755" t="inlineStr">
+      <c r="C754" t="inlineStr">
         <is>
           <t>ショッピング ,価値</t>
         </is>
       </c>
     </row>
-    <row r="756">
-      <c r="A756" t="inlineStr">
+    <row r="755">
+      <c r="A755" t="inlineStr">
         <is>
           <t xml:space="preserve">「私たちが愛する言葉」
 كلماتٌ نُحبّها
@@ -16334,19 +16313,19 @@
 2109 جليل خزعل </t>
         </is>
       </c>
-      <c r="B756" t="inlineStr">
+      <c r="B755" t="inlineStr">
         <is>
           <t>images/「私たちが愛する言葉」_img1.jpg</t>
         </is>
       </c>
-      <c r="C756" t="inlineStr">
+      <c r="C755" t="inlineStr">
         <is>
           <t>花 ,贈り物</t>
         </is>
       </c>
     </row>
-    <row r="757">
-      <c r="A757" t="inlineStr">
+    <row r="756">
+      <c r="A756" t="inlineStr">
         <is>
           <t xml:space="preserve">「お茶についてあなたが知らない10の事実」
 عشر معلومات لا تعرفها عن الشاي
@@ -16355,19 +16334,19 @@
 2012 http://ara.tv/6syq2 </t>
         </is>
       </c>
-      <c r="B757" t="inlineStr">
+      <c r="B756" t="inlineStr">
         <is>
           <t>images/「お茶についてあなたが知らない10の事_img1.jpg</t>
         </is>
       </c>
-      <c r="C757" t="inlineStr">
+      <c r="C756" t="inlineStr">
         <is>
           <t>神農</t>
         </is>
       </c>
     </row>
-    <row r="758">
-      <c r="A758" t="inlineStr">
+    <row r="757">
+      <c r="A757" t="inlineStr">
         <is>
           <t xml:space="preserve">「大きくなったウソ」
 الكذبة الّتي كبرت
@@ -16377,19 +16356,19 @@
 2509 سلسلة الحلزونة </t>
         </is>
       </c>
-      <c r="B758" t="inlineStr">
+      <c r="B757" t="inlineStr">
         <is>
           <t>images/「大きくなったウソ」_img1.jpg</t>
         </is>
       </c>
-      <c r="C758" t="inlineStr">
+      <c r="C757" t="inlineStr">
         <is>
           <t>絵本</t>
         </is>
       </c>
     </row>
-    <row r="759">
-      <c r="A759" t="inlineStr">
+    <row r="758">
+      <c r="A758" t="inlineStr">
         <is>
           <t xml:space="preserve">「自分に合った掃除機を買うには？」
 كيف تشتري المكنسة الكهربائية التي تناسبك؟
@@ -16398,19 +16377,19 @@
 2106 ts3a com </t>
         </is>
       </c>
-      <c r="B759" t="inlineStr">
+      <c r="B758" t="inlineStr">
         <is>
           <t>images/「自分に合った掃除機を買うには？」_img1.jpg</t>
         </is>
       </c>
-      <c r="C759" t="inlineStr">
+      <c r="C758" t="inlineStr">
         <is>
           <t>家電 ,掃除</t>
         </is>
       </c>
     </row>
-    <row r="760">
-      <c r="A760" t="inlineStr">
+    <row r="759">
+      <c r="A759" t="inlineStr">
         <is>
           <t xml:space="preserve">「仮にこれが批判の数としよう」
 لنفرض ان عدد الذين ينتقدونك
@@ -16421,19 +16400,19 @@
 2504 出典不明 </t>
         </is>
       </c>
-      <c r="B760" t="inlineStr">
+      <c r="B759" t="inlineStr">
         <is>
           <t>images/「仮にこれが批判の数としよう」_img1.jpg</t>
         </is>
       </c>
-      <c r="C760" t="inlineStr">
+      <c r="C759" t="inlineStr">
         <is>
           <t>アンチ</t>
         </is>
       </c>
     </row>
-    <row r="761">
-      <c r="A761" t="inlineStr">
+    <row r="760">
+      <c r="A760" t="inlineStr">
         <is>
           <t xml:space="preserve">「ここに見えるのは何？」
 ما الذي تراه هنا؟
@@ -16443,15 +16422,15 @@
 2204 https://twitter.com/NatGeoMagArab/status/1506933850617700352 </t>
         </is>
       </c>
-      <c r="B761" t="inlineStr"/>
-      <c r="C761" t="inlineStr">
+      <c r="B760" t="inlineStr"/>
+      <c r="C760" t="inlineStr">
         <is>
           <t xml:space="preserve">ペンギン </t>
         </is>
       </c>
     </row>
-    <row r="762">
-      <c r="A762" t="inlineStr">
+    <row r="761">
+      <c r="A761" t="inlineStr">
         <is>
           <t xml:space="preserve">「今日辛いこと、明日は平気だろう」
 ما يؤلم اليوم سيهون غدًا
@@ -16461,19 +16440,19 @@
 2308 basmahjeff </t>
         </is>
       </c>
-      <c r="B762" t="inlineStr">
+      <c r="B761" t="inlineStr">
         <is>
           <t>images/「今日辛いこと、明日は平気だろう」_img1.jpg</t>
         </is>
       </c>
-      <c r="C762" t="inlineStr">
+      <c r="C761" t="inlineStr">
         <is>
           <t>悩み ,達観</t>
         </is>
       </c>
     </row>
-    <row r="763">
-      <c r="A763" t="inlineStr">
+    <row r="762">
+      <c r="A762" t="inlineStr">
         <is>
           <t xml:space="preserve">「自分のすることを好きでなきゃ」
 عليك أن تحب ما تفعل
@@ -16482,19 +16461,19 @@
 1810 Ahmed Elhakeem </t>
         </is>
       </c>
-      <c r="B763" t="inlineStr">
+      <c r="B762" t="inlineStr">
         <is>
           <t>images/「自分のすることを好きでなきゃ」_img1.jpg</t>
         </is>
       </c>
-      <c r="C763" t="inlineStr">
+      <c r="C762" t="inlineStr">
         <is>
           <t>転職 ,かわいい</t>
         </is>
       </c>
     </row>
-    <row r="764">
-      <c r="A764" t="inlineStr">
+    <row r="763">
+      <c r="A763" t="inlineStr">
         <is>
           <t xml:space="preserve">「この地上に生き甲斐あり」
 على هذه الأرض ما يستحق الحياة
@@ -16504,19 +16483,19 @@
 2308 Mahmoud Gafar </t>
         </is>
       </c>
-      <c r="B764" t="inlineStr">
+      <c r="B763" t="inlineStr">
         <is>
           <t>images/「この地上に生き甲斐あり」_img1.jpg</t>
         </is>
       </c>
-      <c r="C764" t="inlineStr">
+      <c r="C763" t="inlineStr">
         <is>
           <t>詩</t>
         </is>
       </c>
     </row>
-    <row r="765">
-      <c r="A765" t="inlineStr">
+    <row r="764">
+      <c r="A764" t="inlineStr">
         <is>
           <t xml:space="preserve">「おそらく、あなたの求めるものはあるだろう」
 لعلَّ ما تَرجوهُ سيَكونُ
@@ -16526,19 +16505,19 @@
 2308 PIXEL Instagram </t>
         </is>
       </c>
-      <c r="B765" t="inlineStr">
+      <c r="B764" t="inlineStr">
         <is>
           <t>images/「おそらく、あなたの求めるものはあるだ_img1.jpg</t>
         </is>
       </c>
-      <c r="C765" t="inlineStr">
+      <c r="C764" t="inlineStr">
         <is>
           <t>願い ,信仰</t>
         </is>
       </c>
     </row>
-    <row r="766">
-      <c r="A766" t="inlineStr">
+    <row r="765">
+      <c r="A765" t="inlineStr">
         <is>
           <t xml:space="preserve">「オレンジの効能が何か知っていますか？」
 هل تعرف ما هي فوائد البرتقال؟
@@ -16548,19 +16527,19 @@
 2308 sadahadhramowt com </t>
         </is>
       </c>
-      <c r="B766" t="inlineStr">
+      <c r="B765" t="inlineStr">
         <is>
           <t>images/「オレンジの効能が何か知っていますか？_img1.jpg</t>
         </is>
       </c>
-      <c r="C766" t="inlineStr">
+      <c r="C765" t="inlineStr">
         <is>
           <t>オレンジ ,フルーツ</t>
         </is>
       </c>
     </row>
-    <row r="767">
-      <c r="A767" t="inlineStr">
+    <row r="766">
+      <c r="A766" t="inlineStr">
         <is>
           <t xml:space="preserve">「遊ぶパンダの光景より可愛いものがありますか？」
 هل هناك ما هو ألطف من مشاهدة الباندا وهي تلعب؟
@@ -16568,19 +16547,19 @@
 2308 https://twitter.com/NatGeoMagArab/status/1494612797858074626 </t>
         </is>
       </c>
-      <c r="B767" t="inlineStr">
+      <c r="B766" t="inlineStr">
         <is>
           <t>images/「遊ぶパンダの光景より可愛いものがあり_img1.jpg</t>
         </is>
       </c>
-      <c r="C767" t="inlineStr">
+      <c r="C766" t="inlineStr">
         <is>
           <t>パンダ ,モコモコ</t>
         </is>
       </c>
     </row>
-    <row r="768">
-      <c r="A768" t="inlineStr">
+    <row r="767">
+      <c r="A767" t="inlineStr">
         <is>
           <t xml:space="preserve">「大事なのは何者だったかじゃない。何者になるかだ」
 ليسَ المُهم ما كُنتَ بل مَا ستكون
@@ -16589,19 +16568,19 @@
 2308 出典不明 </t>
         </is>
       </c>
-      <c r="B768" t="inlineStr">
+      <c r="B767" t="inlineStr">
         <is>
           <t>images/「大事なのは何者だったかじゃない。何者_img1.jpg</t>
         </is>
       </c>
-      <c r="C768" t="inlineStr">
+      <c r="C767" t="inlineStr">
         <is>
           <t>自己実現 ,存在価値</t>
         </is>
       </c>
     </row>
-    <row r="769">
-      <c r="A769" t="inlineStr">
+    <row r="768">
+      <c r="A768" t="inlineStr">
         <is>
           <t xml:space="preserve">「あなたであれ。ありのままが美しいから」
 كُنْ أَنْتَ لأنك جميل كما أنت
@@ -16610,19 +16589,19 @@
 2308 IDREES DESIGN </t>
         </is>
       </c>
-      <c r="B769" t="inlineStr">
+      <c r="B768" t="inlineStr">
         <is>
           <t>images/「あなたであれ。ありのままが美しいから_img1.jpg</t>
         </is>
       </c>
-      <c r="C769" t="inlineStr">
+      <c r="C768" t="inlineStr">
         <is>
           <t>自己肯定 ,BeYourself</t>
         </is>
       </c>
     </row>
-    <row r="770">
-      <c r="A770" t="inlineStr">
+    <row r="769">
+      <c r="A769" t="inlineStr">
         <is>
           <t xml:space="preserve">「恐れの中に生きる者は決して自由になれない」
 من يعش في خوف لن يكون حرا أبدا
@@ -16631,19 +16610,19 @@
 2111 rjeem com </t>
         </is>
       </c>
-      <c r="B770" t="inlineStr">
+      <c r="B769" t="inlineStr">
         <is>
           <t>images/「恐れの中に生きる者は決して自由になれ_img1.jpg,images/ 「恐れの中に生きる者は決して自由になれ_img2.jpg</t>
         </is>
       </c>
-      <c r="C770" t="inlineStr">
+      <c r="C769" t="inlineStr">
         <is>
           <t>勇気 ,壁</t>
         </is>
       </c>
     </row>
-    <row r="771">
-      <c r="A771" t="inlineStr">
+    <row r="770">
+      <c r="A770" t="inlineStr">
         <is>
           <t xml:space="preserve">「己の翼を信じる者は己の重さを案じない」
 من يثق في جناحيه لن يهتم لوزنه
@@ -16652,19 +16631,19 @@
 2308 kmrghani </t>
         </is>
       </c>
-      <c r="B771" t="inlineStr">
+      <c r="B770" t="inlineStr">
         <is>
           <t>images/「己の翼を信じる者は己の重さを案じない_img1.jpg</t>
         </is>
       </c>
-      <c r="C771" t="inlineStr">
+      <c r="C770" t="inlineStr">
         <is>
           <t>自信</t>
         </is>
       </c>
     </row>
-    <row r="772">
-      <c r="A772" t="inlineStr">
+    <row r="771">
+      <c r="A771" t="inlineStr">
         <is>
           <t xml:space="preserve">「珈琲で一番大事な事！誰と飲むか？」
 الأهم من القهوة!! من ستشربها معه؟
@@ -16673,19 +16652,19 @@
 1812 gwid3.tumblr </t>
         </is>
       </c>
-      <c r="B772" t="inlineStr">
+      <c r="B771" t="inlineStr">
         <is>
           <t>images/「珈琲で一番大事な事！誰と飲むか？」_img1.jpg</t>
         </is>
       </c>
-      <c r="C772" t="inlineStr">
+      <c r="C771" t="inlineStr">
         <is>
           <t>コーヒー ,名言</t>
         </is>
       </c>
     </row>
-    <row r="773">
-      <c r="A773" t="inlineStr">
+    <row r="772">
+      <c r="A772" t="inlineStr">
         <is>
           <t xml:space="preserve">「人生は美しい、そう望んだ者には。」
 الحياة جَميلَة .. لمن أراد ذلك
@@ -16695,19 +16674,19 @@
 2109 出典不明 </t>
         </is>
       </c>
-      <c r="B773" t="inlineStr">
+      <c r="B772" t="inlineStr">
         <is>
           <t>images/「人生は美しい、そう望んだ者には。」_img1.jpg</t>
         </is>
       </c>
-      <c r="C773" t="inlineStr">
+      <c r="C772" t="inlineStr">
         <is>
           <t>名言 ,アート</t>
         </is>
       </c>
     </row>
-    <row r="774">
-      <c r="A774" t="inlineStr">
+    <row r="773">
+      <c r="A773" t="inlineStr">
         <is>
           <t xml:space="preserve">「ハム太郎って子を知ってるかい」
 هل تعرفون من هو هامتارو
@@ -16717,19 +16696,19 @@
 2109 </t>
         </is>
       </c>
-      <c r="B774" t="inlineStr">
+      <c r="B773" t="inlineStr">
         <is>
           <t>images/「ハム太郎って子を知ってるかい」_img1.jpg</t>
         </is>
       </c>
-      <c r="C774" t="inlineStr">
+      <c r="C773" t="inlineStr">
         <is>
           <t>オープニング ,ハム太郎</t>
         </is>
       </c>
     </row>
-    <row r="775">
-      <c r="A775" t="inlineStr">
+    <row r="774">
+      <c r="A774" t="inlineStr">
         <is>
           <t xml:space="preserve">「幸せを求める人もいれば、作る人もいる」
 هناك من يبحث عن السعادة وهناك من يصنعها
@@ -16738,19 +16717,19 @@
 2308 hindah tumblr </t>
         </is>
       </c>
-      <c r="B775" t="inlineStr">
+      <c r="B774" t="inlineStr">
         <is>
           <t>images/「幸せを求める人もいれば、作る人もいる_img1.jpg</t>
         </is>
       </c>
-      <c r="C775" t="inlineStr">
+      <c r="C774" t="inlineStr">
         <is>
           <t>幸せ ,名言 ,教訓</t>
         </is>
       </c>
     </row>
-    <row r="776">
-      <c r="A776" t="inlineStr">
+    <row r="775">
+      <c r="A775" t="inlineStr">
         <is>
           <t xml:space="preserve">「明白なるアラブの言葉によって」
 بلسان عربي مبين
@@ -16760,19 +16739,19 @@
 2109 Abdullah Barakat behance </t>
         </is>
       </c>
-      <c r="B776" t="inlineStr">
+      <c r="B775" t="inlineStr">
         <is>
           <t>images/「明白なるアラブの言葉によって」_img1.jpg</t>
         </is>
       </c>
-      <c r="C776" t="inlineStr">
+      <c r="C775" t="inlineStr">
         <is>
           <t>イスラム教 ,神聖</t>
         </is>
       </c>
     </row>
-    <row r="777">
-      <c r="A777" t="inlineStr">
+    <row r="776">
+      <c r="A776" t="inlineStr">
         <is>
           <t xml:space="preserve">「結婚前、結婚後」
 قبل الزواج، بعد الزواج
@@ -16782,19 +16761,19 @@
 2308 出典不明 </t>
         </is>
       </c>
-      <c r="B777" t="inlineStr">
+      <c r="B776" t="inlineStr">
         <is>
           <t>images/「結婚前、結婚後」_img1.jpg</t>
         </is>
       </c>
-      <c r="C777" t="inlineStr">
+      <c r="C776" t="inlineStr">
         <is>
           <t>BeforeAfter ,幸せ太り</t>
         </is>
       </c>
     </row>
-    <row r="778">
-      <c r="A778" t="inlineStr">
+    <row r="777">
+      <c r="A777" t="inlineStr">
         <is>
           <t xml:space="preserve">「驚きの価格で」بسعر رائع
 ビスィアル・ラーイア [bi-si*r raa'i*]
@@ -16803,19 +16782,19 @@
 2109 Jarir Bookstore </t>
         </is>
       </c>
-      <c r="B778" t="inlineStr">
+      <c r="B777" t="inlineStr">
         <is>
           <t>images/「驚きの価格で」_img1.jpg</t>
         </is>
       </c>
-      <c r="C778" t="inlineStr">
+      <c r="C777" t="inlineStr">
         <is>
           <t>広告 ,安値</t>
         </is>
       </c>
     </row>
-    <row r="779">
-      <c r="A779" t="inlineStr">
+    <row r="778">
+      <c r="A778" t="inlineStr">
         <is>
           <t xml:space="preserve">「我が魂と共に」مع نفسي
 マア・ナフスィ [ma*a nafs-iy]
@@ -16824,19 +16803,19 @@
 2110 出典不明 </t>
         </is>
       </c>
-      <c r="B779" t="inlineStr">
+      <c r="B778" t="inlineStr">
         <is>
           <t>images/「我が魂と共に」_img1.jpg</t>
         </is>
       </c>
-      <c r="C779" t="inlineStr">
+      <c r="C778" t="inlineStr">
         <is>
           <t>ソウル ,soul</t>
         </is>
       </c>
     </row>
-    <row r="780">
-      <c r="A780" t="inlineStr">
+    <row r="779">
+      <c r="A779" t="inlineStr">
         <is>
           <t xml:space="preserve">「暗い夜に」في ليلة مظلمة
  [fiy layla(tin) mu_Dhlima(tin)]
@@ -16845,19 +16824,19 @@
 2109 سلسلة الحلزونة </t>
         </is>
       </c>
-      <c r="B780" t="inlineStr">
+      <c r="B779" t="inlineStr">
         <is>
           <t>images/「暗い夜に」_img1.jpg</t>
         </is>
       </c>
-      <c r="C780" t="inlineStr">
+      <c r="C779" t="inlineStr">
         <is>
           <t>絵本</t>
         </is>
       </c>
     </row>
-    <row r="781">
-      <c r="A781" t="inlineStr">
+    <row r="780">
+      <c r="A780" t="inlineStr">
         <is>
           <t xml:space="preserve">「ゆっくりと」بشويش
 ビシワェーシ [bi-ShwySh]
@@ -16865,19 +16844,19 @@
 2109 出典不明 </t>
         </is>
       </c>
-      <c r="B781" t="inlineStr">
+      <c r="B780" t="inlineStr">
         <is>
           <t>images/「ゆっくりと」_img1.jpg</t>
         </is>
       </c>
-      <c r="C781" t="inlineStr">
+      <c r="C780" t="inlineStr">
         <is>
           <t>丸 ,円</t>
         </is>
       </c>
     </row>
-    <row r="782">
-      <c r="A782" t="inlineStr">
+    <row r="781">
+      <c r="A781" t="inlineStr">
         <is>
           <t xml:space="preserve">「この広い宇宙に…」
 في الكون الفسيح
@@ -16886,19 +16865,19 @@
 2308 wattpad </t>
         </is>
       </c>
-      <c r="B782" t="inlineStr">
+      <c r="B781" t="inlineStr">
         <is>
           <t>images/「この広い宇宙に…」_img1.jpg</t>
         </is>
       </c>
-      <c r="C782" t="inlineStr">
+      <c r="C781" t="inlineStr">
         <is>
           <t>アニメ ,宇宙</t>
         </is>
       </c>
     </row>
-    <row r="783">
-      <c r="A783" t="inlineStr">
+    <row r="782">
+      <c r="A782" t="inlineStr">
         <is>
           <t xml:space="preserve">「がんばって！」بالتوفيق
 ビッタウフィーク [bi^tawfiiq]
@@ -16906,19 +16885,19 @@
 2111 https://sites.google.com/site/mathmatic1905/ </t>
         </is>
       </c>
-      <c r="B783" t="inlineStr">
+      <c r="B782" t="inlineStr">
         <is>
           <t>images/「がんばって！」_img1.jpg</t>
         </is>
       </c>
-      <c r="C783" t="inlineStr">
+      <c r="C782" t="inlineStr">
         <is>
           <t>アラビア語</t>
         </is>
       </c>
     </row>
-    <row r="784">
-      <c r="A784" t="inlineStr">
+    <row r="783">
+      <c r="A783" t="inlineStr">
         <is>
           <t xml:space="preserve">「インターステラー」بين النجوم
 バイナ_ンヌジューム [bayna ^nujuum]
@@ -16926,19 +16905,19 @@
 2308 kmrghani </t>
         </is>
       </c>
-      <c r="B784" t="inlineStr">
+      <c r="B783" t="inlineStr">
         <is>
           <t>images/「インターステラー」_img1.jpg</t>
         </is>
       </c>
-      <c r="C784" t="inlineStr">
+      <c r="C783" t="inlineStr">
         <is>
           <t>映画 ,宇宙</t>
         </is>
       </c>
     </row>
-    <row r="785">
-      <c r="A785" t="inlineStr">
+    <row r="784">
+      <c r="A784" t="inlineStr">
         <is>
           <t xml:space="preserve">「アラビア語で」بالعربية
 ビ_ルアラビーヤ [bi-l-*arabiyya]
@@ -16947,19 +16926,19 @@
 1811 </t>
         </is>
       </c>
-      <c r="B785" t="inlineStr">
+      <c r="B784" t="inlineStr">
         <is>
           <t>images/「アラビア語で」_img1.jpg</t>
         </is>
       </c>
-      <c r="C785" t="inlineStr">
+      <c r="C784" t="inlineStr">
         <is>
           <t>ニュース ,CNN</t>
         </is>
       </c>
     </row>
-    <row r="786">
-      <c r="A786" t="inlineStr">
+    <row r="785">
+      <c r="A785" t="inlineStr">
         <is>
           <t xml:space="preserve">「17世紀に発明されて以来…」
 منذ اختراعه بالقرن السابع عشر
@@ -16967,19 +16946,19 @@
 2308 https://twitter.com/SciTalk2U/status/1450888395815854080 </t>
         </is>
       </c>
-      <c r="B786" t="inlineStr">
+      <c r="B785" t="inlineStr">
         <is>
           <t>images/「17世紀に発明されて以来…」_img1.jpg</t>
         </is>
       </c>
-      <c r="C786" t="inlineStr">
+      <c r="C785" t="inlineStr">
         <is>
           <t>手書き語学 ,アラビア語 ,望遠鏡</t>
         </is>
       </c>
     </row>
-    <row r="787">
-      <c r="A787" t="inlineStr">
+    <row r="786">
+      <c r="A786" t="inlineStr">
         <is>
           <t xml:space="preserve">「私できるよ」إنّني أستطيع
 インナニー・アスタティーウ ['inna-niy 'a-sta_tii*u]
@@ -16988,19 +16967,19 @@
 2412 سلسلة الحلزونة </t>
         </is>
       </c>
-      <c r="B787" t="inlineStr">
+      <c r="B786" t="inlineStr">
         <is>
           <t>images/「私できるよ」_img1.jpg</t>
         </is>
       </c>
-      <c r="C787" t="inlineStr">
+      <c r="C786" t="inlineStr">
         <is>
           <t>絵本 ,こども</t>
         </is>
       </c>
     </row>
-    <row r="788">
-      <c r="A788" t="inlineStr">
+    <row r="787">
+      <c r="A787" t="inlineStr">
         <is>
           <t xml:space="preserve">「問題なし」مافيش مشكلة
 マフィーシムシュキラ [ma-fy-Sh muShkila]
@@ -17009,19 +16988,19 @@
 2109 tanzerin.theshop </t>
         </is>
       </c>
-      <c r="B788" t="inlineStr">
+      <c r="B787" t="inlineStr">
         <is>
           <t>images/「問題なし」_img1.jpg</t>
         </is>
       </c>
-      <c r="C788" t="inlineStr">
+      <c r="C787" t="inlineStr">
         <is>
           <t>シャツ ,キッズ</t>
         </is>
       </c>
     </row>
-    <row r="789">
-      <c r="A789" t="inlineStr">
+    <row r="788">
+      <c r="A788" t="inlineStr">
         <is>
           <t xml:space="preserve">「不可能はない」مفيش مستحيل
 マフィーシ・ムスタヒール [ma-fy-Sh mustaHiil]
@@ -17030,19 +17009,19 @@
 2109 أموج </t>
         </is>
       </c>
-      <c r="B789" t="inlineStr">
+      <c r="B788" t="inlineStr">
         <is>
           <t>images/「不可能はない」_img1.jpg</t>
         </is>
       </c>
-      <c r="C789" t="inlineStr">
+      <c r="C788" t="inlineStr">
         <is>
           <t>ポジティブ ,挑戦</t>
         </is>
       </c>
     </row>
-    <row r="790">
-      <c r="A790" t="inlineStr">
+    <row r="789">
+      <c r="A789" t="inlineStr">
         <is>
           <t xml:space="preserve">「等々」إلخ
 イラク ['ilaKh]
@@ -17051,19 +17030,19 @@
 2201 出典不明 </t>
         </is>
       </c>
-      <c r="B790" t="inlineStr">
+      <c r="B789" t="inlineStr">
         <is>
           <t>images/「等々」_img1.jpg</t>
         </is>
       </c>
-      <c r="C790" t="inlineStr">
+      <c r="C789" t="inlineStr">
         <is>
           <t>etc ,とんち</t>
         </is>
       </c>
     </row>
-    <row r="791">
-      <c r="A791" t="inlineStr">
+    <row r="790">
+      <c r="A790" t="inlineStr">
         <is>
           <t xml:space="preserve">⁦「調子どう？」⁩شلونَك؟
 シュローナク？ [Sh-loon-ak?]
@@ -17072,19 +17051,19 @@
 2202 Jozoor Team. </t>
         </is>
       </c>
-      <c r="B791" t="inlineStr">
+      <c r="B790" t="inlineStr">
         <is>
           <t>images/⁦「調子どう？」⁩_img1.jpg</t>
         </is>
       </c>
-      <c r="C791" t="inlineStr">
+      <c r="C790" t="inlineStr">
         <is>
           <t>洒落 ,ルービックキューブ</t>
         </is>
       </c>
     </row>
-    <row r="792">
-      <c r="A792" t="inlineStr">
+    <row r="791">
+      <c r="A791" t="inlineStr">
         <is>
           <t xml:space="preserve">「行くな」ماتروحش
 マトロホシ [ma-troH-Sh]
@@ -17093,19 +17072,19 @@
 2411 triiq tumblr </t>
         </is>
       </c>
-      <c r="B792" t="inlineStr">
+      <c r="B791" t="inlineStr">
         <is>
           <t>images/「行くな」_img1.jpg</t>
         </is>
       </c>
-      <c r="C792" t="inlineStr">
+      <c r="C791" t="inlineStr">
         <is>
           <t>ロゴ ,デザイン ,嵐</t>
         </is>
       </c>
     </row>
-    <row r="793">
-      <c r="A793" t="inlineStr">
+    <row r="792">
+      <c r="A792" t="inlineStr">
         <is>
           <t xml:space="preserve">⁦「元気？」⁩شلونَك؟
 シュローナク？ [Sh-loon-ak?]
@@ -17116,19 +17095,19 @@
 2202 出典不明 </t>
         </is>
       </c>
-      <c r="B793" t="inlineStr">
+      <c r="B792" t="inlineStr">
         <is>
           <t>images/⁦「元気？」⁩_img1.jpg</t>
         </is>
       </c>
-      <c r="C793" t="inlineStr">
+      <c r="C792" t="inlineStr">
         <is>
           <t>洒落 ,挨拶</t>
         </is>
       </c>
     </row>
-    <row r="794">
-      <c r="A794" t="inlineStr">
+    <row r="793">
+      <c r="A793" t="inlineStr">
         <is>
           <t xml:space="preserve">「気分が良いぞう」I فيل GOOD
 アイ・フィール・グッド [ai fiyl gud]
@@ -17137,19 +17116,19 @@
 2308 出典不明 </t>
         </is>
       </c>
-      <c r="B794" t="inlineStr">
+      <c r="B793" t="inlineStr">
         <is>
           <t>images/「気分が良いぞう」_img1.jpg</t>
         </is>
       </c>
-      <c r="C794" t="inlineStr">
+      <c r="C793" t="inlineStr">
         <is>
           <t>洒落 ,和訳</t>
         </is>
       </c>
     </row>
-    <row r="795">
-      <c r="A795" t="inlineStr">
+    <row r="794">
+      <c r="A794" t="inlineStr">
         <is>
           <t xml:space="preserve">「レットイットゴー／let it go」
 ليت اِت غو
@@ -17158,19 +17137,19 @@
 2109 出典不明 </t>
         </is>
       </c>
-      <c r="B795" t="inlineStr">
+      <c r="B794" t="inlineStr">
         <is>
           <t>images/「レットイットゴー／let it go_img1.jpg</t>
         </is>
       </c>
-      <c r="C795" t="inlineStr">
+      <c r="C794" t="inlineStr">
         <is>
           <t>折衷 ,アナ雪</t>
         </is>
       </c>
     </row>
-    <row r="796">
-      <c r="A796" t="inlineStr">
+    <row r="795">
+      <c r="A795" t="inlineStr">
         <is>
           <t xml:space="preserve">「ようこそ」اهلا وسهلا
 アハラン・ワサハラン ['ahlan wa-sahlan]
@@ -17178,19 +17157,19 @@
 2106 behance Anwar Al Eissa </t>
         </is>
       </c>
-      <c r="B796" t="inlineStr">
+      <c r="B795" t="inlineStr">
         <is>
           <t>images/「ようこそ」_img1.jpg</t>
         </is>
       </c>
-      <c r="C796" t="inlineStr">
+      <c r="C795" t="inlineStr">
         <is>
           <t>アラビア語</t>
         </is>
       </c>
     </row>
-    <row r="797">
-      <c r="A797" t="inlineStr">
+    <row r="796">
+      <c r="A796" t="inlineStr">
         <is>
           <t xml:space="preserve">「まぁ何というサプライズでしょう」
 يا لها من مفاجأة
@@ -17201,19 +17180,19 @@
 2108 neelwafurat com </t>
         </is>
       </c>
-      <c r="B797" t="inlineStr">
+      <c r="B796" t="inlineStr">
         <is>
           <t>images/「まぁ何というサプライズでしょう」_img1.jpg</t>
         </is>
       </c>
-      <c r="C797" t="inlineStr">
+      <c r="C796" t="inlineStr">
         <is>
           <t>中国語 ,学習</t>
         </is>
       </c>
     </row>
-    <row r="798">
-      <c r="A798" t="inlineStr">
+    <row r="797">
+      <c r="A797" t="inlineStr">
         <is>
           <t xml:space="preserve">「ハックション」اتشوو
 アチュー！ ['aatShuu]
@@ -17221,19 +17200,19 @@
 1811 </t>
         </is>
       </c>
-      <c r="B798" t="inlineStr">
+      <c r="B797" t="inlineStr">
         <is>
           <t>images/「ハックション」_img1.jpg</t>
         </is>
       </c>
-      <c r="C798" t="inlineStr">
+      <c r="C797" t="inlineStr">
         <is>
           <t>あらびあや</t>
         </is>
       </c>
     </row>
-    <row r="799">
-      <c r="A799" t="inlineStr">
+    <row r="798">
+      <c r="A798" t="inlineStr">
         <is>
           <t xml:space="preserve">「スブハーナッラー」「アルハムドゥリッラー」「アッラーアクバル」
 سبحان الله
@@ -17244,19 +17223,19 @@
 2308 dribbble com </t>
         </is>
       </c>
-      <c r="B799" t="inlineStr">
+      <c r="B798" t="inlineStr">
         <is>
           <t>images/「スブハーナッラー」「アルハムドゥリッ_img1.jpg</t>
         </is>
       </c>
-      <c r="C799" t="inlineStr">
+      <c r="C798" t="inlineStr">
         <is>
           <t>四角 ,コンパクト</t>
         </is>
       </c>
     </row>
-    <row r="800">
-      <c r="A800" t="inlineStr">
+    <row r="799">
+      <c r="A799" t="inlineStr">
         <is>
           <t xml:space="preserve">「すごく美味しい！」لذيذ جدًا
 ラズィーズ・ジッダン [laDhiiDh jiddan]
@@ -17265,19 +17244,19 @@
 2109 goodreads com </t>
         </is>
       </c>
-      <c r="B800" t="inlineStr">
+      <c r="B799" t="inlineStr">
         <is>
           <t>images/「すごく美味しい！」_img1.jpg</t>
         </is>
       </c>
-      <c r="C800" t="inlineStr">
+      <c r="C799" t="inlineStr">
         <is>
           <t>フレーズ ,感想</t>
         </is>
       </c>
     </row>
-    <row r="801">
-      <c r="A801" t="inlineStr">
+    <row r="800">
+      <c r="A800" t="inlineStr">
         <is>
           <t xml:space="preserve">「しとしと、雨」تك تك يا مطر
 ティクティク [tik tik yaa ma_tar]
@@ -17286,19 +17265,19 @@
 2308 出典不明 </t>
         </is>
       </c>
-      <c r="B801" t="inlineStr">
+      <c r="B800" t="inlineStr">
         <is>
           <t>images/「しとしと、雨」_img1.jpg</t>
         </is>
       </c>
-      <c r="C801" t="inlineStr">
+      <c r="C800" t="inlineStr">
         <is>
           <t>天気 ,梅雨</t>
         </is>
       </c>
     </row>
-    <row r="802">
-      <c r="A802" t="inlineStr">
+    <row r="801">
+      <c r="A801" t="inlineStr">
         <is>
           <t xml:space="preserve">「さかさま」رأساً على عقب
 ラッアサン・アラー・アケブ [ra'san *alaa *aqib]
@@ -17306,19 +17285,19 @@
 2109 出典不明 </t>
         </is>
       </c>
-      <c r="B802" t="inlineStr">
+      <c r="B801" t="inlineStr">
         <is>
           <t>images/「さかさま」_img1.jpg</t>
         </is>
       </c>
-      <c r="C802" t="inlineStr">
+      <c r="C801" t="inlineStr">
         <is>
           <t>壁 ,上下</t>
         </is>
       </c>
     </row>
-    <row r="803">
-      <c r="A803" t="inlineStr">
+    <row r="802">
+      <c r="A802" t="inlineStr">
         <is>
           <t xml:space="preserve">「エジプトよどこへ行った」
 فينك يا مصر؟
@@ -17328,19 +17307,19 @@
 1809 shehabfawzy1.tumblr </t>
         </is>
       </c>
-      <c r="B803" t="inlineStr">
+      <c r="B802" t="inlineStr">
         <is>
           <t>images/「エジプトよどこへ行った」_img1.jpg</t>
         </is>
       </c>
-      <c r="C803" t="inlineStr">
+      <c r="C802" t="inlineStr">
         <is>
           <t>ピラミッド ,歴史</t>
         </is>
       </c>
     </row>
-    <row r="804">
-      <c r="A804" t="inlineStr">
+    <row r="803">
+      <c r="A803" t="inlineStr">
         <is>
           <t xml:space="preserve">「ありがとう」شكراً
 シュクラン [Shukran]
@@ -17348,19 +17327,19 @@
 2109 出典不明 </t>
         </is>
       </c>
-      <c r="B804" t="inlineStr">
+      <c r="B803" t="inlineStr">
         <is>
           <t>images/「ありがとう」_img1.jpg</t>
         </is>
       </c>
-      <c r="C804" t="inlineStr">
+      <c r="C803" t="inlineStr">
         <is>
           <t>挨拶 ,文字</t>
         </is>
       </c>
     </row>
-    <row r="805">
-      <c r="A805" t="inlineStr">
+    <row r="804">
+      <c r="A804" t="inlineStr">
         <is>
           <t xml:space="preserve">「昼寝の時間だ」
 إنه وقت القيلولة
@@ -17369,12 +17348,12 @@
 2501 https://x.com/NatGeoMagArab/status/1858049951579910486 </t>
         </is>
       </c>
-      <c r="B805" t="inlineStr">
+      <c r="B804" t="inlineStr">
         <is>
           <t>images/「昼寝の時間だ」_img1.jpg</t>
         </is>
       </c>
-      <c r="C805" t="inlineStr">
+      <c r="C804" t="inlineStr">
         <is>
           <t>手書き語学 ,アラビア語 ,ペンギン</t>
         </is>

--- a/posts.xlsx
+++ b/posts.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C801"/>
+  <dimension ref="A1:C800"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -11924,28 +11924,6 @@
     <row r="548">
       <c r="A548" t="inlineStr">
         <is>
-          <t xml:space="preserve">「賢くバカであれ」
-كن غبياً بطريقة ذكية
-[kun Ghabiiyan bi-_tariiqatin Dhakiiya]
-⁦「馬鹿だ」( غَبِيّ )[Ghabiiy]・「賢い方法で」[bi-_tariiqatin Dhakiiyatin]⁩
-賢い（かしこい）
-2110 ALADMIRAL jony </t>
-        </is>
-      </c>
-      <c r="B548" t="inlineStr">
-        <is>
-          <t>images/「賢くバカであれ」_img1.jpg</t>
-        </is>
-      </c>
-      <c r="C548" t="inlineStr">
-        <is>
-          <t>逆説的 ,キツネ</t>
-        </is>
-      </c>
-    </row>
-    <row r="549">
-      <c r="A549" t="inlineStr">
-        <is>
           <t xml:space="preserve">「どこでも自分でありなさい」
 كن أنت أينما كنت
 [kun 'anta 'ayna-maa kun-ta]
@@ -11954,19 +11932,19 @@
 2605 souqfann com/r/15987  </t>
         </is>
       </c>
-      <c r="B549" t="inlineStr">
+      <c r="B548" t="inlineStr">
         <is>
           <t>images/「どこでも自分でありなさい」_img1.jpg</t>
         </is>
       </c>
-      <c r="C549" t="inlineStr">
+      <c r="C548" t="inlineStr">
         <is>
           <t>デザイン ,アート</t>
         </is>
       </c>
     </row>
-    <row r="550">
-      <c r="A550" t="inlineStr">
+    <row r="549">
+      <c r="A549" t="inlineStr">
         <is>
           <t xml:space="preserve">「止まれ。検問中」قف للتفتيش
 キフ。リッタフティーシ [qif li^taftiiSh]
@@ -11975,19 +11953,19 @@
 2109 Marcel Musil flickr </t>
         </is>
       </c>
-      <c r="B550" t="inlineStr">
+      <c r="B549" t="inlineStr">
         <is>
           <t>images/「止まれ。検問中」_img1.jpg</t>
         </is>
       </c>
-      <c r="C550" t="inlineStr">
+      <c r="C549" t="inlineStr">
         <is>
           <t>標識</t>
         </is>
       </c>
     </row>
-    <row r="551">
-      <c r="A551" t="inlineStr">
+    <row r="550">
+      <c r="A550" t="inlineStr">
         <is>
           <t xml:space="preserve">「さあおやすみ」هَيّا نَمْ
 ハイヤー・ナム [hayyaa nam]
@@ -11995,19 +11973,19 @@
 2308 Maktabatee com </t>
         </is>
       </c>
-      <c r="B551" t="inlineStr">
+      <c r="B550" t="inlineStr">
         <is>
           <t>images/「さあおやすみ」_img1.jpg</t>
         </is>
       </c>
-      <c r="C551" t="inlineStr">
+      <c r="C550" t="inlineStr">
         <is>
           <t>就寝 ,絵本</t>
         </is>
       </c>
     </row>
-    <row r="552">
-      <c r="A552" t="inlineStr">
+    <row r="551">
+      <c r="A551" t="inlineStr">
         <is>
           <t xml:space="preserve">「あなたであれ」كن أنت
 クン・アンタ [ku 'anta]
@@ -12015,19 +11993,19 @@
 1809 madyan22.tumblr </t>
         </is>
       </c>
-      <c r="B552" t="inlineStr">
+      <c r="B551" t="inlineStr">
         <is>
           <t>images/「あなたであれ」_img1.jpg</t>
         </is>
       </c>
-      <c r="C552" t="inlineStr">
+      <c r="C551" t="inlineStr">
         <is>
           <t>個性 ,自尊心</t>
         </is>
       </c>
     </row>
-    <row r="553">
-      <c r="A553" t="inlineStr">
+    <row r="552">
+      <c r="A552" t="inlineStr">
         <is>
           <t xml:space="preserve">「過去を忘れろ。だが教訓は忘れるな」
 إنسَ الماضي ولكن لاتنسَ الدرس
@@ -12037,19 +12015,19 @@
 2308 https://www.instagram.com/emanalyafai </t>
         </is>
       </c>
-      <c r="B553" t="inlineStr">
+      <c r="B552" t="inlineStr">
         <is>
           <t>images/「過去を忘れろ。だが教訓は忘れるな」_img1.jpg</t>
         </is>
       </c>
-      <c r="C553" t="inlineStr">
+      <c r="C552" t="inlineStr">
         <is>
           <t>名言 ,未来</t>
         </is>
       </c>
     </row>
-    <row r="554">
-      <c r="A554" t="inlineStr">
+    <row r="553">
+      <c r="A553" t="inlineStr">
         <is>
           <t xml:space="preserve">「この世界で君も何かを持っている。だから立ち上がれ！」
 لَكْ شيءٌ في هَذَا العَالَم… فَقُمْ
@@ -12057,19 +12035,19 @@
 2511 mjdal7arbi tumblr, Ghassan Kanafani </t>
         </is>
       </c>
-      <c r="B554" t="inlineStr">
+      <c r="B553" t="inlineStr">
         <is>
           <t>images/「この世界で君も何かを持っている。だか.jpg</t>
         </is>
       </c>
-      <c r="C554" t="inlineStr">
+      <c r="C553" t="inlineStr">
         <is>
           <t>鼓舞 ,ハンカチ王子</t>
         </is>
       </c>
     </row>
-    <row r="555">
-      <c r="A555" t="inlineStr">
+    <row r="554">
+      <c r="A554" t="inlineStr">
         <is>
           <t xml:space="preserve">「かぞえてかずをかきましょう」
 عد واكتب العدد
@@ -12078,19 +12056,19 @@
 2604 facebook Qsre alawani </t>
         </is>
       </c>
-      <c r="B555" t="inlineStr">
+      <c r="B554" t="inlineStr">
         <is>
           <t>images/「かぞえてかずをかきましょう」.JPG</t>
         </is>
       </c>
-      <c r="C555" t="inlineStr">
+      <c r="C554" t="inlineStr">
         <is>
           <t>算数 ,さんすう</t>
         </is>
       </c>
     </row>
-    <row r="556">
-      <c r="A556" t="inlineStr">
+    <row r="555">
+      <c r="A555" t="inlineStr">
         <is>
           <t xml:space="preserve">「いつも人助けしなさい」
 كن عونا للناس دوما
@@ -12100,19 +12078,19 @@
 2109 Muhammad ElMahdy </t>
         </is>
       </c>
-      <c r="B556" t="inlineStr">
+      <c r="B555" t="inlineStr">
         <is>
           <t>images/「いつも人助けしなさい」_img1.jpg</t>
         </is>
       </c>
-      <c r="C556" t="inlineStr">
+      <c r="C555" t="inlineStr">
         <is>
           <t>教訓 ,助っ人</t>
         </is>
       </c>
     </row>
-    <row r="557">
-      <c r="A557" t="inlineStr">
+    <row r="556">
+      <c r="A556" t="inlineStr">
         <is>
           <t xml:space="preserve">「毎年、ノーベル賞が授けられる」
 في كل عام تُمنح جوائز نوبل
@@ -12120,19 +12098,19 @@
 2404 https://twitter.com/SciTalk2U/status/1462482447627661319 </t>
         </is>
       </c>
-      <c r="B557" t="inlineStr">
+      <c r="B556" t="inlineStr">
         <is>
           <t>images/「毎年、ノーベル賞が授けられる」_img1.jpg</t>
         </is>
       </c>
-      <c r="C557" t="inlineStr">
+      <c r="C556" t="inlineStr">
         <is>
           <t>手書き語学 ,アラビア語 ,ノーベル賞</t>
         </is>
       </c>
     </row>
-    <row r="558">
-      <c r="A558" t="inlineStr">
+    <row r="557">
+      <c r="A557" t="inlineStr">
         <is>
           <t xml:space="preserve">「あなたはアラビア語を話しますか」
 هل تتكلم العربية؟
@@ -12142,19 +12120,19 @@
 2109 al3arabiya com </t>
         </is>
       </c>
-      <c r="B558" t="inlineStr">
+      <c r="B557" t="inlineStr">
         <is>
           <t>images/「あなたはアラビア語を話しますか」_img1.jpg</t>
         </is>
       </c>
-      <c r="C558" t="inlineStr">
+      <c r="C557" t="inlineStr">
         <is>
           <t>教科書 ,テキスト</t>
         </is>
       </c>
     </row>
-    <row r="559">
-      <c r="A559" t="inlineStr">
+    <row r="558">
+      <c r="A558" t="inlineStr">
         <is>
           <t xml:space="preserve">「このインコは亜熱帯が起源である」
 يتحدر هذا الباراكيت من المناطق شبه الاستوائية
@@ -12162,19 +12140,19 @@
 2402 https://x.com/NatGeoMagArab/status/1690626751578439680 </t>
         </is>
       </c>
-      <c r="B559" t="inlineStr">
+      <c r="B558" t="inlineStr">
         <is>
           <t>images/「このインコは亜熱帯が起源である」_img1.jpg,images/「このインコは亜熱帯が起源である」_img2.jpg</t>
         </is>
       </c>
-      <c r="C559" t="inlineStr">
+      <c r="C558" t="inlineStr">
         <is>
           <t>手書き語学 ,アラビア語 ,オナガミドリインコ</t>
         </is>
       </c>
     </row>
-    <row r="560">
-      <c r="A560" t="inlineStr">
+    <row r="559">
+      <c r="A559" t="inlineStr">
         <is>
           <t xml:space="preserve">「彼を覚えていますか」
 هل تتذكرونه؟
@@ -12184,19 +12162,19 @@
 2308 http://newsfacetruth.blogspot.com/2017/07/blog-post_11.html </t>
         </is>
       </c>
-      <c r="B560" t="inlineStr">
+      <c r="B559" t="inlineStr">
         <is>
           <t>images/「彼を覚えていますか」_img1.jpg</t>
         </is>
       </c>
-      <c r="C560" t="inlineStr">
+      <c r="C559" t="inlineStr">
         <is>
           <t>グレンダイザー ,UFOロボ</t>
         </is>
       </c>
     </row>
-    <row r="561">
-      <c r="A561" t="inlineStr">
+    <row r="560">
+      <c r="A560" t="inlineStr">
         <is>
           <t xml:space="preserve">「内面が変われば周りが変わる」
 عندما تتغير الأشياء داخلك، تتغير الأشياء من حولك
@@ -12205,19 +12183,19 @@
 2501 Facebook, Cairo Mockingbird </t>
         </is>
       </c>
-      <c r="B561" t="inlineStr">
+      <c r="B560" t="inlineStr">
         <is>
           <t>images/「内面が変われば周りが変わる」_img1.jpg</t>
         </is>
       </c>
-      <c r="C561" t="inlineStr">
+      <c r="C560" t="inlineStr">
         <is>
           <t>ポジティブ</t>
         </is>
       </c>
     </row>
-    <row r="562">
-      <c r="A562" t="inlineStr">
+    <row r="561">
+      <c r="A561" t="inlineStr">
         <is>
           <t xml:space="preserve">「天才になるには？」
 كيف تصبح عبقريا؟
@@ -12226,19 +12204,19 @@
 2109 Infographics Samah Faris </t>
         </is>
       </c>
-      <c r="B562" t="inlineStr">
+      <c r="B561" t="inlineStr">
         <is>
           <t>images/「天才になるには？」_img1.jpg</t>
         </is>
       </c>
-      <c r="C562" t="inlineStr">
+      <c r="C561" t="inlineStr">
         <is>
           <t>秘訣 ,コツ</t>
         </is>
       </c>
     </row>
-    <row r="563">
-      <c r="A563" t="inlineStr">
+    <row r="562">
+      <c r="A562" t="inlineStr">
         <is>
           <t xml:space="preserve">「彼らと友情を交わすよハム太郎」
 وبالإخاء يبادلهم هامتارو
@@ -12248,19 +12226,19 @@
 2109 </t>
         </is>
       </c>
-      <c r="B563" t="inlineStr">
+      <c r="B562" t="inlineStr">
         <is>
           <t>images/「彼らと友情を交わすよハム太郎」_img1.jpg</t>
         </is>
       </c>
-      <c r="C563" t="inlineStr">
+      <c r="C562" t="inlineStr">
         <is>
           <t>アニメ ,ハム太郎</t>
         </is>
       </c>
     </row>
-    <row r="564">
-      <c r="A564" t="inlineStr">
+    <row r="563">
+      <c r="A563" t="inlineStr">
         <is>
           <t xml:space="preserve">「誰がニワトリを助ける？」
 من يساعد الدّجاجة؟
@@ -12270,19 +12248,19 @@
 2109 alnqsh com </t>
         </is>
       </c>
-      <c r="B564" t="inlineStr">
+      <c r="B563" t="inlineStr">
         <is>
           <t>images/「誰がニワトリを助ける？」_img1.jpg</t>
         </is>
       </c>
-      <c r="C564" t="inlineStr">
+      <c r="C563" t="inlineStr">
         <is>
           <t>絵本 ,チキン</t>
         </is>
       </c>
     </row>
-    <row r="565">
-      <c r="A565" t="inlineStr">
+    <row r="564">
+      <c r="A564" t="inlineStr">
         <is>
           <t xml:space="preserve">「心臓病を避けるには？」
 كيف تتجنب أمراض القلب؟
@@ -12292,37 +12270,37 @@
 2608 lanamedical_sa </t>
         </is>
       </c>
+      <c r="B564" t="inlineStr">
+        <is>
+          <t>images/「心臓病を避けるには？」.jpg</t>
+        </is>
+      </c>
+      <c r="C564" t="inlineStr">
+        <is>
+          <t>生活習慣病 ,心臓</t>
+        </is>
+      </c>
+    </row>
+    <row r="565">
+      <c r="A565" t="inlineStr">
+        <is>
+          <t xml:space="preserve">「どうやらこの好奇心旺盛なペンギンは…」
+2308 https://twitter.com/NatGeoMagArab/status/1591460860207443968 </t>
+        </is>
+      </c>
       <c r="B565" t="inlineStr">
         <is>
-          <t>images/「心臓病を避けるには？」.jpg</t>
+          <t>images/「どうやらこの好奇心旺盛なペンギンは…_img1.jpg,images/ 「どうやらこの好奇心旺盛なペンギンは…_img2.jpg</t>
         </is>
       </c>
       <c r="C565" t="inlineStr">
         <is>
-          <t>生活習慣病 ,心臓</t>
+          <t>手書き語学 ,アラビア語 ,オウサマペンギン</t>
         </is>
       </c>
     </row>
     <row r="566">
       <c r="A566" t="inlineStr">
-        <is>
-          <t xml:space="preserve">「どうやらこの好奇心旺盛なペンギンは…」
-2308 https://twitter.com/NatGeoMagArab/status/1591460860207443968 </t>
-        </is>
-      </c>
-      <c r="B566" t="inlineStr">
-        <is>
-          <t>images/「どうやらこの好奇心旺盛なペンギンは…_img1.jpg,images/ 「どうやらこの好奇心旺盛なペンギンは…_img2.jpg</t>
-        </is>
-      </c>
-      <c r="C566" t="inlineStr">
-        <is>
-          <t>手書き語学 ,アラビア語 ,オウサマペンギン</t>
-        </is>
-      </c>
-    </row>
-    <row r="567">
-      <c r="A567" t="inlineStr">
         <is>
           <t xml:space="preserve">「この生き物を見分けられますか？」
 هل تُميز هذا الكائن؟
@@ -12331,19 +12309,19 @@
 2308 https://twitter.com/NatGeoMagArab/status/1455121397827600388 </t>
         </is>
       </c>
-      <c r="B567" t="inlineStr">
+      <c r="B566" t="inlineStr">
         <is>
           <t>images/「この生き物を見分けられますか？」_img1.jpg</t>
         </is>
       </c>
-      <c r="C567" t="inlineStr">
+      <c r="C566" t="inlineStr">
         <is>
           <t xml:space="preserve">手書き語学 ,カバ </t>
         </is>
       </c>
     </row>
-    <row r="568">
-      <c r="A568" t="inlineStr">
+    <row r="567">
+      <c r="A567" t="inlineStr">
         <is>
           <t xml:space="preserve">「ひとを幸せにするには？」
 كيف تسعد غيرك؟
@@ -12353,19 +12331,19 @@
 2308 Gwid3 </t>
         </is>
       </c>
-      <c r="B568" t="inlineStr">
+      <c r="B567" t="inlineStr">
         <is>
           <t>images/「ひとを幸せにするには？」_img1.jpg</t>
         </is>
       </c>
-      <c r="C568" t="inlineStr">
+      <c r="C567" t="inlineStr">
         <is>
           <t>思いやり ,心</t>
         </is>
       </c>
     </row>
-    <row r="569">
-      <c r="A569" t="inlineStr">
+    <row r="568">
+      <c r="A568" t="inlineStr">
         <is>
           <t xml:space="preserve">「ラマダン月に口臭をおさえる方法は？」
 كيف تتجنب رائحة الفم في رمضان
@@ -12374,19 +12352,19 @@
 2109 AlArabiya </t>
         </is>
       </c>
-      <c r="B569" t="inlineStr">
+      <c r="B568" t="inlineStr">
         <is>
           <t>images/「ラマダン月に口臭をおさえる方法は？」_img1.jpg</t>
         </is>
       </c>
-      <c r="C569" t="inlineStr">
+      <c r="C568" t="inlineStr">
         <is>
           <t>イスラム教 ,ブレスケア</t>
         </is>
       </c>
     </row>
-    <row r="570">
-      <c r="A570" t="inlineStr">
+    <row r="569">
+      <c r="A569" t="inlineStr">
         <is>
           <t xml:space="preserve">「ヨユウなきユウヨ」
 يمهل ولا يهمل
@@ -12396,19 +12374,19 @@
 2512 instagram com/p/CK4CLqeJ3dy/ </t>
         </is>
       </c>
-      <c r="B570" t="inlineStr">
+      <c r="B569" t="inlineStr">
         <is>
           <t>images/「ヨユウなきユウヨ」_img1.jpg</t>
         </is>
       </c>
-      <c r="C570" t="inlineStr">
+      <c r="C569" t="inlineStr">
         <is>
           <t>時計 ,からくり</t>
         </is>
       </c>
     </row>
-    <row r="571">
-      <c r="A571" t="inlineStr">
+    <row r="570">
+      <c r="A570" t="inlineStr">
         <is>
           <t xml:space="preserve">「どうして？　動物は絶滅する」
 لماذا؟ تنقرض الحيوانات
@@ -12418,19 +12396,19 @@
 2308 goodreads com </t>
         </is>
       </c>
-      <c r="B571" t="inlineStr">
+      <c r="B570" t="inlineStr">
         <is>
           <t>images/「どうして？　動物は絶滅する」_img1.jpg</t>
         </is>
       </c>
-      <c r="C571" t="inlineStr">
+      <c r="C570" t="inlineStr">
         <is>
           <t>動物 ,子供用</t>
         </is>
       </c>
     </row>
-    <row r="572">
-      <c r="A572" t="inlineStr">
+    <row r="571">
+      <c r="A571" t="inlineStr">
         <is>
           <t xml:space="preserve">「私たちは異なる。だから調和する」
 نختلف.. لنأتلف
@@ -12440,19 +12418,19 @@
 2103 Nawal Saed </t>
         </is>
       </c>
-      <c r="B572" t="inlineStr">
+      <c r="B571" t="inlineStr">
         <is>
           <t>images/「私たちは異なる。だから調和する」_img1.jpg</t>
         </is>
       </c>
-      <c r="C572" t="inlineStr">
+      <c r="C571" t="inlineStr">
         <is>
           <t>異符号 ,ハーモニー</t>
         </is>
       </c>
     </row>
-    <row r="573">
-      <c r="A573" t="inlineStr">
+    <row r="572">
+      <c r="A572" t="inlineStr">
         <is>
           <t xml:space="preserve">「私の肺には蝶々が住んでいて、呼吸の度に羽ばたく」
 تسكن رئتيّ فراشة ترفرف كلما أتنفس
@@ -12461,19 +12439,19 @@
 2109 出典不明 </t>
         </is>
       </c>
-      <c r="B573" t="inlineStr">
+      <c r="B572" t="inlineStr">
         <is>
           <t>images/「私の肺には蝶々が住んでいて、呼吸の度_img1.jpg</t>
         </is>
       </c>
-      <c r="C573" t="inlineStr">
+      <c r="C572" t="inlineStr">
         <is>
           <t>人体 ,昆虫</t>
         </is>
       </c>
     </row>
-    <row r="574">
-      <c r="A574" t="inlineStr">
+    <row r="573">
+      <c r="A573" t="inlineStr">
         <is>
           <t xml:space="preserve">「安らぎを感じますか？」
 هل تستشعر السكينة؟
@@ -12482,19 +12460,19 @@
 2404 https://twitter.com/NatGeoMagArab/status/1541421154950209536 </t>
         </is>
       </c>
-      <c r="B574" t="inlineStr">
+      <c r="B573" t="inlineStr">
         <is>
           <t>images/「安らぎを感じますか？」_img1.jpg</t>
         </is>
       </c>
-      <c r="C574" t="inlineStr">
+      <c r="C573" t="inlineStr">
         <is>
           <t>手書き語学 ,アラビア語 ,エイ</t>
         </is>
       </c>
     </row>
-    <row r="575">
-      <c r="A575" t="inlineStr">
+    <row r="574">
+      <c r="A574" t="inlineStr">
         <is>
           <t xml:space="preserve">「たとえあなたの使うブラウザがChromeだろうとSafariだろうと」
 سواء كنت تستخدم متصفح كروم أو سفاري
@@ -12502,19 +12480,19 @@
 2308 https://twitter.com/ShaayTech/status/1536235333972635649 </t>
         </is>
       </c>
-      <c r="B575" t="inlineStr">
+      <c r="B574" t="inlineStr">
         <is>
           <t>images/「たとえあなたの使うブラウザがChro_img1.jpg</t>
         </is>
       </c>
-      <c r="C575" t="inlineStr">
+      <c r="C574" t="inlineStr">
         <is>
           <t xml:space="preserve">手書き語学 ,アラビア語 ,iPhone </t>
         </is>
       </c>
     </row>
-    <row r="576">
-      <c r="A576" t="inlineStr">
+    <row r="575">
+      <c r="A575" t="inlineStr">
         <is>
           <t xml:space="preserve">「このミドリモリヤツガシラは気づいて欲しい」
 يحرص "هدهد الخشب الأخضر" هذا على أن يدرك
@@ -12523,19 +12501,19 @@
 2308 https://twitter.com/NatGeoMagArab/status/1531161022928539648 </t>
         </is>
       </c>
-      <c r="B576" t="inlineStr">
+      <c r="B575" t="inlineStr">
         <is>
           <t>images/「このミドリモリヤツガシラは気づいて欲_img1.jpg</t>
         </is>
       </c>
-      <c r="C576" t="inlineStr">
+      <c r="C575" t="inlineStr">
         <is>
           <t xml:space="preserve">手書き語学 ,アラビア語 ,鳥 </t>
         </is>
       </c>
     </row>
-    <row r="577">
-      <c r="A577" t="inlineStr">
+    <row r="576">
+      <c r="A576" t="inlineStr">
         <is>
           <t xml:space="preserve">「あなたの怖いものは何ですか」
 ماهي مخاوفك؟
@@ -12547,15 +12525,15 @@
 2308 1112kok </t>
         </is>
       </c>
-      <c r="B577" t="inlineStr">
+      <c r="B576" t="inlineStr">
         <is>
           <t>images/「あなたの怖いものは何ですか」_img1.jpg</t>
         </is>
       </c>
-      <c r="C577" t="inlineStr"/>
-    </row>
-    <row r="578">
-      <c r="A578" t="inlineStr">
+      <c r="C576" t="inlineStr"/>
+    </row>
+    <row r="577">
+      <c r="A577" t="inlineStr">
         <is>
           <t xml:space="preserve">「美しい時は作るもの。待つものではない」
 اصنع اللحظات الجميلة. لا تنتظرها
@@ -12564,19 +12542,19 @@
 2308 abojamal.tumblr com </t>
         </is>
       </c>
-      <c r="B578" t="inlineStr">
+      <c r="B577" t="inlineStr">
         <is>
           <t>images/「美しい時は作るもの。待つものではない_img1.jpg</t>
         </is>
       </c>
-      <c r="C578" t="inlineStr">
+      <c r="C577" t="inlineStr">
         <is>
           <t>おうち時間</t>
         </is>
       </c>
     </row>
-    <row r="579">
-      <c r="A579" t="inlineStr">
+    <row r="578">
+      <c r="A578" t="inlineStr">
         <is>
           <t xml:space="preserve">「大切な時間を大切じゃないことに使わないこと」
 لا تضيع الوقت المهم في شيء غير مهم
@@ -12585,19 +12563,19 @@
 2308 Anwar_122_ </t>
         </is>
       </c>
-      <c r="B579" t="inlineStr">
+      <c r="B578" t="inlineStr">
         <is>
           <t>images/「大切な時間を大切じゃないことに使わな_img1.jpg</t>
         </is>
       </c>
-      <c r="C579" t="inlineStr">
+      <c r="C578" t="inlineStr">
         <is>
           <t>時間 ,貴重</t>
         </is>
       </c>
     </row>
-    <row r="580">
-      <c r="A580" t="inlineStr">
+    <row r="579">
+      <c r="A579" t="inlineStr">
         <is>
           <t xml:space="preserve">「このイノセントな目に騙されるな…」
 لا تنخدع بهذه العيون البريئة
@@ -12607,19 +12585,19 @@
 2201 https://twitter.com/NatGeoMagArab/status/1475715760202797056 </t>
         </is>
       </c>
-      <c r="B580" t="inlineStr">
+      <c r="B579" t="inlineStr">
         <is>
           <t>images/「このイノセントな目に騙されるな…」.png</t>
         </is>
       </c>
-      <c r="C580" t="inlineStr">
+      <c r="C579" t="inlineStr">
         <is>
           <t>がうがう ,カワイイ</t>
         </is>
       </c>
     </row>
-    <row r="581">
-      <c r="A581" t="inlineStr">
+    <row r="580">
+      <c r="A580" t="inlineStr">
         <is>
           <t xml:space="preserve">⁦「カメラを止めろ！」⁩
 أوقفوا التّصوير
@@ -12629,19 +12607,19 @@
 2509 alsalwabooks com </t>
         </is>
       </c>
-      <c r="B581" t="inlineStr">
+      <c r="B580" t="inlineStr">
         <is>
           <t>images/⁦「カメラを止めろ！」⁩_img1.jpg</t>
         </is>
       </c>
-      <c r="C581" t="inlineStr">
+      <c r="C580" t="inlineStr">
         <is>
           <t>絵本 ,撮影</t>
         </is>
       </c>
     </row>
-    <row r="582">
-      <c r="A582" t="inlineStr">
+    <row r="581">
+      <c r="A581" t="inlineStr">
         <is>
           <t xml:space="preserve">「話す前に考えなさい」
 فكر قبل ان تتكلم
@@ -12651,19 +12629,19 @@
 2308 Islamuna YouTube </t>
         </is>
       </c>
-      <c r="B582" t="inlineStr">
+      <c r="B581" t="inlineStr">
         <is>
           <t>images/「話す前に考えなさい」_img1.jpg</t>
         </is>
       </c>
-      <c r="C582" t="inlineStr">
+      <c r="C581" t="inlineStr">
         <is>
           <t>失言 ,発言</t>
         </is>
       </c>
     </row>
-    <row r="583">
-      <c r="A583" t="inlineStr">
+    <row r="582">
+      <c r="A582" t="inlineStr">
         <is>
           <t xml:space="preserve">「ツイッターでフォローして下さい」
 تابعونا على تويتر
@@ -12673,19 +12651,19 @@
 2109 出典不明 </t>
         </is>
       </c>
-      <c r="B583" t="inlineStr">
+      <c r="B582" t="inlineStr">
         <is>
           <t>images/「ツイッターでフォローして下さい」_img1.jpg</t>
         </is>
       </c>
-      <c r="C583" t="inlineStr">
+      <c r="C582" t="inlineStr">
         <is>
           <t>FollowUs ,バナー</t>
         </is>
       </c>
     </row>
-    <row r="584">
-      <c r="A584" t="inlineStr">
+    <row r="583">
+      <c r="A583" t="inlineStr">
         <is>
           <t xml:space="preserve">「敵を倒せ」دمّر العدو
 ダンミリ_ルアドゥーウ [dammiri l-*aduuw]
@@ -12694,19 +12672,19 @@
 2308 apkpure com </t>
         </is>
       </c>
-      <c r="B584" t="inlineStr">
+      <c r="B583" t="inlineStr">
         <is>
           <t>images/「敵を倒せ」_img1.jpg</t>
         </is>
       </c>
-      <c r="C584" t="inlineStr">
+      <c r="C583" t="inlineStr">
         <is>
           <t>ゲーム ,パンダ</t>
         </is>
       </c>
     </row>
-    <row r="585">
-      <c r="A585" t="inlineStr">
+    <row r="584">
+      <c r="A584" t="inlineStr">
         <is>
           <t xml:space="preserve">「咲け。蒔かれたらどこであろうと」
 أزهر أيْنمَا زرعت
@@ -12715,19 +12693,19 @@
 2407 Ahmed Madyan </t>
         </is>
       </c>
-      <c r="B585" t="inlineStr">
+      <c r="B584" t="inlineStr">
         <is>
           <t>images/「咲け。蒔かれたらどこであろうと」_img1.jpg</t>
         </is>
       </c>
-      <c r="C585" t="inlineStr">
+      <c r="C584" t="inlineStr">
         <is>
           <t>環境のせいにしない ,花</t>
         </is>
       </c>
     </row>
-    <row r="586">
-      <c r="A586" t="inlineStr">
+    <row r="585">
+      <c r="A585" t="inlineStr">
         <is>
           <t xml:space="preserve">「頭を働かせろ」شغل مخك
 シャッギル・ムッハク [Sha^Ghil mu^Kha-k]
@@ -12736,19 +12714,19 @@
 2103 facebook elpage </t>
         </is>
       </c>
-      <c r="B586" t="inlineStr">
+      <c r="B585" t="inlineStr">
         <is>
           <t>images/「頭を働かせろ」_img1.jpg</t>
         </is>
       </c>
-      <c r="C586" t="inlineStr">
+      <c r="C585" t="inlineStr">
         <is>
           <t>電源 ,頭脳</t>
         </is>
       </c>
     </row>
-    <row r="587">
-      <c r="A587" t="inlineStr">
+    <row r="586">
+      <c r="A586" t="inlineStr">
         <is>
           <t xml:space="preserve">「傷跡は星にかえなさい」
 حوّل نُدوبكَ إلى نُجومْ
@@ -12758,19 +12736,19 @@
 2107 saramj1992 Instagram </t>
         </is>
       </c>
-      <c r="B587" t="inlineStr">
+      <c r="B586" t="inlineStr">
         <is>
           <t>images/「傷跡は星にかえなさい」_img1.jpg</t>
         </is>
       </c>
-      <c r="C587" t="inlineStr">
+      <c r="C586" t="inlineStr">
         <is>
           <t>勲章 ,証</t>
         </is>
       </c>
     </row>
-    <row r="588">
-      <c r="A588" t="inlineStr">
+    <row r="587">
+      <c r="A587" t="inlineStr">
         <is>
           <t xml:space="preserve">「あなたの主の栄光を誉め称え、また（御赦しを請え。本当にかれは、度々赦される御方である）」
 فسَبِّح بحمد ربك و
@@ -12779,19 +12757,19 @@
 2109 出典不明 </t>
         </is>
       </c>
-      <c r="B588" t="inlineStr">
+      <c r="B587" t="inlineStr">
         <is>
           <t>images/「あなたの主の栄光を誉め称え、また（御_img1.jpg</t>
         </is>
       </c>
-      <c r="C588" t="inlineStr">
+      <c r="C587" t="inlineStr">
         <is>
           <t>イスラム教 ,カリグラフィー</t>
         </is>
       </c>
     </row>
-    <row r="589">
-      <c r="A589" t="inlineStr">
+    <row r="588">
+      <c r="A588" t="inlineStr">
         <is>
           <t xml:space="preserve">「誰かを幸福にしなさい」
 أسْعِد أحدهم
@@ -12801,19 +12779,19 @@
 1810 in4sser.tumblr </t>
         </is>
       </c>
-      <c r="B589" t="inlineStr">
+      <c r="B588" t="inlineStr">
         <is>
           <t>images/「誰かを幸福にしなさい」_img1.jpg</t>
         </is>
       </c>
-      <c r="C589" t="inlineStr">
+      <c r="C588" t="inlineStr">
         <is>
           <t>人生 ,happy</t>
         </is>
       </c>
     </row>
-    <row r="590">
-      <c r="A590" t="inlineStr">
+    <row r="589">
+      <c r="A589" t="inlineStr">
         <is>
           <t xml:space="preserve">「見よ」أبْصِرْ
 アブスィル ['ab_sir]
@@ -12822,19 +12800,19 @@
 1811 Ruh Al-Alam, via Behance </t>
         </is>
       </c>
-      <c r="B590" t="inlineStr">
+      <c r="B589" t="inlineStr">
         <is>
           <t>images/「見よ」_img1.jpg</t>
         </is>
       </c>
-      <c r="C590" t="inlineStr">
+      <c r="C589" t="inlineStr">
         <is>
           <t>目 ,瞳</t>
         </is>
       </c>
     </row>
-    <row r="591">
-      <c r="A591" t="inlineStr">
+    <row r="590">
+      <c r="A590" t="inlineStr">
         <is>
           <t xml:space="preserve">「言葉は口から出す前に味わいなさい」
 ‪تذوق كلماتك قبل أن تنطقها‬
@@ -12844,19 +12822,19 @@
 2109 Reham-des </t>
         </is>
       </c>
-      <c r="B591" t="inlineStr">
+      <c r="B590" t="inlineStr">
         <is>
           <t>images/「言葉は口から出す前に味わいなさい」_img1.jpg</t>
         </is>
       </c>
-      <c r="C591" t="inlineStr">
+      <c r="C590" t="inlineStr">
         <is>
           <t>言葉</t>
         </is>
       </c>
     </row>
-    <row r="592">
-      <c r="A592" t="inlineStr">
+    <row r="591">
+      <c r="A591" t="inlineStr">
         <is>
           <t xml:space="preserve">「テレビを観るのをやめて下さい」
 توقفي عن مشاهدة التلفاز
@@ -12866,19 +12844,19 @@
 1809 </t>
         </is>
       </c>
-      <c r="B592" t="inlineStr">
+      <c r="B591" t="inlineStr">
         <is>
           <t>images/「テレビを観るのをやめて下さい」_img1.jpg</t>
         </is>
       </c>
-      <c r="C592" t="inlineStr">
+      <c r="C591" t="inlineStr">
         <is>
           <t>あらびあや</t>
         </is>
       </c>
     </row>
-    <row r="593">
-      <c r="A593" t="inlineStr">
+    <row r="592">
+      <c r="A592" t="inlineStr">
         <is>
           <t xml:space="preserve">「言わぬが花」
 انْطِقْ جَمَالاً أو تجَمَّلْ بالسّكُوت
@@ -12888,19 +12866,19 @@
 2411 Ahmed Madyan </t>
         </is>
       </c>
-      <c r="B593" t="inlineStr">
+      <c r="B592" t="inlineStr">
         <is>
           <t>images/「言わぬが花」_img1.jpg</t>
         </is>
       </c>
-      <c r="C593" t="inlineStr">
+      <c r="C592" t="inlineStr">
         <is>
           <t>ことわざ ,デザイン</t>
         </is>
       </c>
     </row>
-    <row r="594">
-      <c r="A594" t="inlineStr">
+    <row r="593">
+      <c r="A593" t="inlineStr">
         <is>
           <t xml:space="preserve">「たくさん考えて、少し話すこと」
 فكّر كثيرا. تكلم قليلا
@@ -12910,19 +12888,19 @@
 2105 In49r </t>
         </is>
       </c>
-      <c r="B594" t="inlineStr">
+      <c r="B593" t="inlineStr">
         <is>
           <t>images/「たくさん考えて、少し話すこと」_img1.jpg</t>
         </is>
       </c>
-      <c r="C594" t="inlineStr">
+      <c r="C593" t="inlineStr">
         <is>
           <t>思慮 ,会話</t>
         </is>
       </c>
     </row>
-    <row r="595">
-      <c r="A595" t="inlineStr">
+    <row r="594">
+      <c r="A594" t="inlineStr">
         <is>
           <t xml:space="preserve">「子供たちよ、いつでも思い出すんだよ」
 تذكروا دوما يا أطفال
@@ -12932,19 +12910,19 @@
 1809 </t>
         </is>
       </c>
-      <c r="B595" t="inlineStr">
+      <c r="B594" t="inlineStr">
         <is>
           <t>images/「子供たちよ、いつでも思い出すんだよ」_img1.jpg</t>
         </is>
       </c>
-      <c r="C595" t="inlineStr">
+      <c r="C594" t="inlineStr">
         <is>
           <t>オープニング ,ハム太郎</t>
         </is>
       </c>
     </row>
-    <row r="596">
-      <c r="A596" t="inlineStr">
+    <row r="595">
+      <c r="A595" t="inlineStr">
         <is>
           <t xml:space="preserve">「分かってから話しなさい」
 تعلَّم ثمَّ تكلَّم
@@ -12954,19 +12932,19 @@
 1903 Hashem Al Shareef, Pinterest </t>
         </is>
       </c>
-      <c r="B596" t="inlineStr">
+      <c r="B595" t="inlineStr">
         <is>
           <t>images/「分かってから話しなさい」_img1.jpg</t>
         </is>
       </c>
-      <c r="C596" t="inlineStr">
+      <c r="C595" t="inlineStr">
         <is>
           <t>教訓 ,トーク</t>
         </is>
       </c>
     </row>
-    <row r="597">
-      <c r="A597" t="inlineStr">
+    <row r="596">
+      <c r="A596" t="inlineStr">
         <is>
           <t xml:space="preserve">「蟻に学べ」تعلم من النملة
 タアッラム・ミナ_ンナムラ [ta*allam mina ^namla]
@@ -12975,19 +12953,19 @@
 2308 fatakat com </t>
         </is>
       </c>
-      <c r="B597" t="inlineStr">
+      <c r="B596" t="inlineStr">
         <is>
           <t>images/「蟻に学べ」_img1.jpg</t>
         </is>
       </c>
-      <c r="C597" t="inlineStr">
+      <c r="C596" t="inlineStr">
         <is>
           <t>教訓 ,問題解決</t>
         </is>
       </c>
     </row>
-    <row r="598">
-      <c r="A598" t="inlineStr">
+    <row r="597">
+      <c r="A597" t="inlineStr">
         <is>
           <t xml:space="preserve">「自分と仲直りしよう、一杯の珈琲で！」
 تصالح مع نفسك بكوب قهوة
@@ -12997,19 +12975,19 @@
 2308 asm95_ </t>
         </is>
       </c>
-      <c r="B598" t="inlineStr">
+      <c r="B597" t="inlineStr">
         <is>
           <t>images/「自分と仲直りしよう、一杯の珈琲で！」_img1.jpg</t>
         </is>
       </c>
-      <c r="C598" t="inlineStr">
+      <c r="C597" t="inlineStr">
         <is>
           <t>一服 ,リラックス</t>
         </is>
       </c>
     </row>
-    <row r="599">
-      <c r="A599" t="inlineStr">
+    <row r="598">
+      <c r="A598" t="inlineStr">
         <is>
           <t xml:space="preserve">「気をつけて　ジュード」
 انتبهي يا جود
@@ -13019,19 +12997,19 @@
 2109 سلسلة الحلزونة </t>
         </is>
       </c>
-      <c r="B599" t="inlineStr">
+      <c r="B598" t="inlineStr">
         <is>
           <t>images/「気をつけて　ジュード」_img1.jpg</t>
         </is>
       </c>
-      <c r="C599" t="inlineStr">
+      <c r="C598" t="inlineStr">
         <is>
           <t>絵本 ,わんぱく</t>
         </is>
       </c>
     </row>
-    <row r="600">
-      <c r="A600" t="inlineStr">
+    <row r="599">
+      <c r="A599" t="inlineStr">
         <is>
           <t xml:space="preserve">「coming soon」
 انتظرونا قريبا
@@ -13040,19 +13018,19 @@
 2307 出典不明 </t>
         </is>
       </c>
-      <c r="B600" t="inlineStr">
+      <c r="B599" t="inlineStr">
         <is>
           <t>images/「coming soon」_img1.jpg</t>
         </is>
       </c>
-      <c r="C600" t="inlineStr">
+      <c r="C599" t="inlineStr">
         <is>
           <t>フレーズ ,カミングスーン</t>
         </is>
       </c>
     </row>
-    <row r="601">
-      <c r="A601" t="inlineStr">
+    <row r="600">
+      <c r="A600" t="inlineStr">
         <is>
           <t xml:space="preserve">「自分の胸に聞きなさい。それが全て知っています」
 استمع لقلبك.. إنه يعرف كل شيء
@@ -13061,19 +13039,19 @@
 1811 </t>
         </is>
       </c>
-      <c r="B601" t="inlineStr">
+      <c r="B600" t="inlineStr">
         <is>
           <t>images/「自分の胸に聞きなさい。それが全て知っ_img1.jpg</t>
         </is>
       </c>
-      <c r="C601" t="inlineStr">
+      <c r="C600" t="inlineStr">
         <is>
           <t>あらびあや</t>
         </is>
       </c>
     </row>
-    <row r="602">
-      <c r="A602" t="inlineStr">
+    <row r="601">
+      <c r="A601" t="inlineStr">
         <is>
           <t xml:space="preserve">「笑ってくれ、絶望を癒すのは君の笑みだから」
 ابتسمي فإن دواء اليأس بسمتك
@@ -13082,19 +13060,19 @@
 2308 arab-quotes tumblr </t>
         </is>
       </c>
-      <c r="B602" t="inlineStr">
+      <c r="B601" t="inlineStr">
         <is>
           <t>images/「笑ってくれ、絶望を癒すのは君の笑みだ_img1.jpg</t>
         </is>
       </c>
-      <c r="C602" t="inlineStr">
+      <c r="C601" t="inlineStr">
         <is>
           <t>癒し ,スマイル</t>
         </is>
       </c>
     </row>
-    <row r="603">
-      <c r="A603" t="inlineStr">
+    <row r="602">
+      <c r="A602" t="inlineStr">
         <is>
           <t xml:space="preserve">「自分を頼りなさい。宇宙で最も確かな物が自分だと思って。」
 استند على نفسك وكأنك أكثر الأشياء ثباتًا بهذا الكون
@@ -13102,19 +13080,19 @@
 2308 x_nourh.15 </t>
         </is>
       </c>
-      <c r="B603" t="inlineStr">
+      <c r="B602" t="inlineStr">
         <is>
           <t>images/「自分を頼りなさい。宇宙で最も確かな物_img1.jpg</t>
         </is>
       </c>
-      <c r="C603" t="inlineStr">
+      <c r="C602" t="inlineStr">
         <is>
           <t>自我 ,宇宙</t>
         </is>
       </c>
     </row>
-    <row r="604">
-      <c r="A604" t="inlineStr">
+    <row r="603">
+      <c r="A603" t="inlineStr">
         <is>
           <t xml:space="preserve">「古いデバイスを交換して新品をゲットしよう」
 استبدل جهازك القديم واحصل على واحد جديد
@@ -13123,19 +13101,19 @@
 2406 stc </t>
         </is>
       </c>
-      <c r="B604" t="inlineStr">
+      <c r="B603" t="inlineStr">
         <is>
           <t>images/「古いデバイスを交換して新品をゲットし_img1.jpg</t>
         </is>
       </c>
-      <c r="C604" t="inlineStr">
+      <c r="C603" t="inlineStr">
         <is>
           <t>キャンペーン ,下取り</t>
         </is>
       </c>
     </row>
-    <row r="605">
-      <c r="A605" t="inlineStr">
+    <row r="604">
+      <c r="A604" t="inlineStr">
         <is>
           <t xml:space="preserve">「あなたの声を聞かせてください。私の心を彩ってください」
 هات صوتك، لوّن قلبي
@@ -13144,19 +13122,19 @@
 2105 3a2esha_ Instagram </t>
         </is>
       </c>
-      <c r="B605" t="inlineStr">
+      <c r="B604" t="inlineStr">
         <is>
           <t>images/「あなたの声を聞かせてください。私の心_img1.jpg</t>
         </is>
       </c>
-      <c r="C605" t="inlineStr">
+      <c r="C604" t="inlineStr">
         <is>
           <t>電話 ,肉声</t>
         </is>
       </c>
     </row>
-    <row r="606">
-      <c r="A606" t="inlineStr">
+    <row r="605">
+      <c r="A605" t="inlineStr">
         <is>
           <t xml:space="preserve">「この子カンガルーは抱っこが好き」
 يُحب صغير الكنغر هذا أن يؤخذ في الأحضان
@@ -13164,19 +13142,19 @@
 2308 NatGeoMagArab </t>
         </is>
       </c>
-      <c r="B606" t="inlineStr">
+      <c r="B605" t="inlineStr">
         <is>
           <t>images/「この子カンガルーは抱っこが好き」.png</t>
         </is>
       </c>
-      <c r="C606" t="inlineStr">
+      <c r="C605" t="inlineStr">
         <is>
           <t>カンガルー ,人肌</t>
         </is>
       </c>
     </row>
-    <row r="607">
-      <c r="A607" t="inlineStr">
+    <row r="606">
+      <c r="A606" t="inlineStr">
         <is>
           <t xml:space="preserve">「カタールが好き」أحب قطر
 ウヒッブ・カタル ['u-Hibb qa_tar]
@@ -13185,19 +13163,19 @@
 1810 出典不明 </t>
         </is>
       </c>
-      <c r="B607" t="inlineStr">
+      <c r="B606" t="inlineStr">
         <is>
           <t>images/「カタールが好き」_img1.jpg</t>
         </is>
       </c>
-      <c r="C607" t="inlineStr">
+      <c r="C606" t="inlineStr">
         <is>
           <t>カタール</t>
         </is>
       </c>
     </row>
-    <row r="608">
-      <c r="A608" t="inlineStr">
+    <row r="607">
+      <c r="A607" t="inlineStr">
         <is>
           <t xml:space="preserve">「一緒に読むのが好き」
 أُحبُّ أن نَقْرَأَ مَعاً
@@ -13207,19 +13185,19 @@
 2509 www.neelwafurat com,  id=lbb212750-185765 </t>
         </is>
       </c>
-      <c r="B608" t="inlineStr">
+      <c r="B607" t="inlineStr">
         <is>
           <t>images/「一緒に読むのが好き」_img1.jpg</t>
         </is>
       </c>
-      <c r="C608" t="inlineStr">
+      <c r="C607" t="inlineStr">
         <is>
           <t>好き ,本</t>
         </is>
       </c>
     </row>
-    <row r="609">
-      <c r="A609" t="inlineStr">
+    <row r="608">
+      <c r="A608" t="inlineStr">
         <is>
           <t xml:space="preserve">「病院に行きたくない」
 لا أريد أن أذهب إلى المشفى
@@ -13229,19 +13207,19 @@
 2508 Tony Ross https://education.hachette-antoine.com/ar/component/%D9%84%D8%A7-%D8%A3%D8%B1%D9%8A%D8%AF-%D8%A3%D9%86-%D8%A3%D8%B0%D9%87%D8%A8-%D8%A5%D9%84%D9%89-%D8%A7%D9%84%D9%85%D8%B4%D9%81%D9%89/ </t>
         </is>
       </c>
-      <c r="B609" t="inlineStr">
+      <c r="B608" t="inlineStr">
         <is>
           <t>images/「病院に行きたくない」_img1.jpg</t>
         </is>
       </c>
-      <c r="C609" t="inlineStr">
+      <c r="C608" t="inlineStr">
         <is>
           <t>絵本 ,子供</t>
         </is>
       </c>
     </row>
-    <row r="610">
-      <c r="A610" t="inlineStr">
+    <row r="609">
+      <c r="A609" t="inlineStr">
         <is>
           <t xml:space="preserve">「男性はいくら？」「女性はいくら？」
 كم يساوى الرجل؟ ..وكم تساوى المرأة؟
@@ -13250,19 +13228,19 @@
 2308 Pinterest, Masr Elmahrousa, Farah Noweir </t>
         </is>
       </c>
-      <c r="B610" t="inlineStr">
+      <c r="B609" t="inlineStr">
         <is>
           <t>images/「男性はいくら？」「女性はいくら？」_img1.jpg,images/「男性はいくら？」「女性はいくら？」_img2.jpg</t>
         </is>
       </c>
-      <c r="C610" t="inlineStr">
+      <c r="C609" t="inlineStr">
         <is>
           <t xml:space="preserve">全身コーデ ,相場 </t>
         </is>
       </c>
     </row>
-    <row r="611">
-      <c r="A611" t="inlineStr">
+    <row r="610">
+      <c r="A610" t="inlineStr">
         <is>
           <t xml:space="preserve">「黙ってもらえます？」
 ممكن تعيرنا سكوتك؟
@@ -13272,19 +13250,19 @@
 2308 Basel26 </t>
         </is>
       </c>
-      <c r="B611" t="inlineStr">
+      <c r="B610" t="inlineStr">
         <is>
           <t>images/「黙ってもらえます？」_img1.jpg</t>
         </is>
       </c>
-      <c r="C611" t="inlineStr">
+      <c r="C610" t="inlineStr">
         <is>
           <t>音量 ,ボリューム</t>
         </is>
       </c>
     </row>
-    <row r="612">
-      <c r="A612" t="inlineStr">
+    <row r="611">
+      <c r="A611" t="inlineStr">
         <is>
           <t xml:space="preserve">「眠りたいです」
 أُريدُ أَن أَنام
@@ -13294,19 +13272,19 @@
 2109 goodreads com </t>
         </is>
       </c>
-      <c r="B612" t="inlineStr">
+      <c r="B611" t="inlineStr">
         <is>
           <t>images/「眠りたいです」_img1.jpg</t>
         </is>
       </c>
-      <c r="C612" t="inlineStr">
+      <c r="C611" t="inlineStr">
         <is>
           <t>絵本</t>
         </is>
       </c>
     </row>
-    <row r="613">
-      <c r="A613" t="inlineStr">
+    <row r="612">
+      <c r="A612" t="inlineStr">
         <is>
           <t xml:space="preserve">「飛びたい！」أُريد أن أطير
 ウリードゥ・アン・アティール ['u-riidu 'an 'a-_tiir]
@@ -13315,19 +13293,19 @@
 2308 出典不明 </t>
         </is>
       </c>
-      <c r="B613" t="inlineStr">
+      <c r="B612" t="inlineStr">
         <is>
           <t>images/「飛びたい！」_img1.jpg</t>
         </is>
       </c>
-      <c r="C613" t="inlineStr">
+      <c r="C612" t="inlineStr">
         <is>
           <t>鳥 ,希望</t>
         </is>
       </c>
     </row>
-    <row r="614">
-      <c r="A614" t="inlineStr">
+    <row r="613">
+      <c r="A613" t="inlineStr">
         <is>
           <t xml:space="preserve">「うちゅうへとびたい」
 أُريدُ أَنْ أَطيرَ إلى الفَضاء
@@ -13336,19 +13314,19 @@
 2308 mybookshelf co </t>
         </is>
       </c>
-      <c r="B614" t="inlineStr">
+      <c r="B613" t="inlineStr">
         <is>
           <t>images/「うちゅうへとびたい」_img1.jpg</t>
         </is>
       </c>
-      <c r="C614" t="inlineStr">
+      <c r="C613" t="inlineStr">
         <is>
           <t>絵本 ,宇宙</t>
         </is>
       </c>
     </row>
-    <row r="615">
-      <c r="A615" t="inlineStr">
+    <row r="614">
+      <c r="A614" t="inlineStr">
         <is>
           <t xml:space="preserve">「とても愛しています」
 أُحِبّك جِدّاً
@@ -13358,19 +13336,19 @@
 2308 hobe cc </t>
         </is>
       </c>
-      <c r="B615" t="inlineStr">
+      <c r="B614" t="inlineStr">
         <is>
           <t>images/「とても愛しています」_img1.jpg</t>
         </is>
       </c>
-      <c r="C615" t="inlineStr">
+      <c r="C614" t="inlineStr">
         <is>
           <t>恋 ,love</t>
         </is>
       </c>
     </row>
-    <row r="616">
-      <c r="A616" t="inlineStr">
+    <row r="615">
+      <c r="A615" t="inlineStr">
         <is>
           <t xml:space="preserve">「あす日が昇るだろう。私は朝が大好きだ」
 غدا ستشرق الشمس وأحب الصباح كثيرا
@@ -13379,19 +13357,19 @@
 2105 warag-3nb.tumblr com </t>
         </is>
       </c>
-      <c r="B616" t="inlineStr">
+      <c r="B615" t="inlineStr">
         <is>
           <t>images/「あす日が昇るだろう。私は朝が大好きだ_img1.jpg,images/ 「あす日が昇るだろう。私は朝が大好きだ_img2.jpg</t>
         </is>
       </c>
-      <c r="C616" t="inlineStr">
+      <c r="C615" t="inlineStr">
         <is>
           <t>おやすみ ,壁</t>
         </is>
       </c>
     </row>
-    <row r="617">
-      <c r="A617" t="inlineStr">
+    <row r="616">
+      <c r="A616" t="inlineStr">
         <is>
           <t xml:space="preserve">「きみは何をえらぶ？」
 ماذا تختار؟
@@ -13401,19 +13379,19 @@
 2109 embadomjp org </t>
         </is>
       </c>
-      <c r="B617" t="inlineStr">
+      <c r="B616" t="inlineStr">
         <is>
           <t>images/「きみは何をえらぶ？」_img1.jpg</t>
         </is>
       </c>
-      <c r="C617" t="inlineStr">
+      <c r="C616" t="inlineStr">
         <is>
           <t>優柔不断 ,絵本</t>
         </is>
       </c>
     </row>
-    <row r="618">
-      <c r="A618" t="inlineStr">
+    <row r="617">
+      <c r="A617" t="inlineStr">
         <is>
           <t xml:space="preserve">「ちょっと静けさが必要な時もある」
 في بعض الأوقات نحتاج لشوية هدوء
@@ -13423,19 +13401,19 @@
 2308 IN49r </t>
         </is>
       </c>
-      <c r="B618" t="inlineStr">
+      <c r="B617" t="inlineStr">
         <is>
           <t>images/「ちょっと静けさが必要な時もある」_img1.jpg</t>
         </is>
       </c>
-      <c r="C618" t="inlineStr">
+      <c r="C617" t="inlineStr">
         <is>
           <t>ミュート ,精神</t>
         </is>
       </c>
     </row>
-    <row r="619">
-      <c r="A619" t="inlineStr">
+    <row r="618">
+      <c r="A618" t="inlineStr">
         <is>
           <t xml:space="preserve">「逃げるな。全力でぶつかれ」
 لا تهرب اصطدم بكل قوتك
@@ -13445,19 +13423,19 @@
 2308 https://risingvibes.tumblr.com/post/189545775129 </t>
         </is>
       </c>
-      <c r="B619" t="inlineStr">
+      <c r="B618" t="inlineStr">
         <is>
           <t>images/「逃げるな。全力でぶつかれ」_img1.jpg</t>
         </is>
       </c>
-      <c r="C619" t="inlineStr">
+      <c r="C618" t="inlineStr">
         <is>
           <t>応援 ,力</t>
         </is>
       </c>
     </row>
-    <row r="620">
-      <c r="A620" t="inlineStr">
+    <row r="619">
+      <c r="A619" t="inlineStr">
         <is>
           <t xml:space="preserve">「着るのだいすき」
 أُحِبُ أَن أَرتَدِيَ
@@ -13467,19 +13445,19 @@
 2308 https://kitab.firmabikes.ru/epub-_hb_n_rtdy_5187.html </t>
         </is>
       </c>
-      <c r="B620" t="inlineStr">
+      <c r="B619" t="inlineStr">
         <is>
           <t>images/「着るのだいすき」_img1.jpg</t>
         </is>
       </c>
-      <c r="C620" t="inlineStr">
+      <c r="C619" t="inlineStr">
         <is>
           <t xml:space="preserve">絵本 ,ファッション </t>
         </is>
       </c>
     </row>
-    <row r="621">
-      <c r="A621" t="inlineStr">
+    <row r="620">
+      <c r="A620" t="inlineStr">
         <is>
           <t xml:space="preserve">「車のバッテリーが要る！」
 نحتاج بطارية سيارة
@@ -13489,19 +13467,19 @@
 2308 instagram roaa_27 </t>
         </is>
       </c>
-      <c r="B621" t="inlineStr">
+      <c r="B620" t="inlineStr">
         <is>
           <t>images/「車のバッテリーが要る！」_img1.jpg</t>
         </is>
       </c>
-      <c r="C621" t="inlineStr">
+      <c r="C620" t="inlineStr">
         <is>
           <t>スマホ ,充電</t>
         </is>
       </c>
     </row>
-    <row r="622">
-      <c r="A622" t="inlineStr">
+    <row r="621">
+      <c r="A621" t="inlineStr">
         <is>
           <t xml:space="preserve">「今日は幸せでいることにしました」
 اخترت أن أكون سعيدا اليوم
@@ -13511,19 +13489,19 @@
 2109 awaasha tumblr </t>
         </is>
       </c>
-      <c r="B622" t="inlineStr">
+      <c r="B621" t="inlineStr">
         <is>
           <t>images/「今日は幸せでいることにしました」_img1.jpg</t>
         </is>
       </c>
-      <c r="C622" t="inlineStr">
+      <c r="C621" t="inlineStr">
         <is>
           <t>心構え ,happy</t>
         </is>
       </c>
     </row>
-    <row r="623">
-      <c r="A623" t="inlineStr">
+    <row r="622">
+      <c r="A622" t="inlineStr">
         <is>
           <t xml:space="preserve">「理想的なスイカの選び方」
 كيف تختار البطيخة المُثلى؟
@@ -13533,19 +13511,19 @@
 2308 bit ly/octmel </t>
         </is>
       </c>
-      <c r="B623" t="inlineStr">
+      <c r="B622" t="inlineStr">
         <is>
           <t>images/「理想的なスイカの選び方」_img1.jpg</t>
         </is>
       </c>
-      <c r="C623" t="inlineStr">
+      <c r="C622" t="inlineStr">
         <is>
           <t>八百屋 ,西瓜</t>
         </is>
       </c>
     </row>
-    <row r="624">
-      <c r="A624" t="inlineStr">
+    <row r="623">
+      <c r="A623" t="inlineStr">
         <is>
           <t xml:space="preserve">「お問い合わせください」
 اتصل بنا
@@ -13555,19 +13533,19 @@
 2308 mtawir.blogspot com </t>
         </is>
       </c>
-      <c r="B624" t="inlineStr">
+      <c r="B623" t="inlineStr">
         <is>
           <t>images/「お問い合わせください」_img1.jpg</t>
         </is>
       </c>
-      <c r="C624" t="inlineStr">
+      <c r="C623" t="inlineStr">
         <is>
           <t>広告 ,電話</t>
         </is>
       </c>
     </row>
-    <row r="625">
-      <c r="A625" t="inlineStr">
+    <row r="624">
+      <c r="A624" t="inlineStr">
         <is>
           <t xml:space="preserve">「両方の動物が海岸の火山岩の亀裂の中に定住している」
 يحتل كلا الحيوانين شقوقًا في صخور الساحل البركانية
@@ -13575,19 +13553,19 @@
 2507 https://x.com/NatGeoMagArab/status/1925167200056521151 </t>
         </is>
       </c>
-      <c r="B625" t="inlineStr">
+      <c r="B624" t="inlineStr">
         <is>
           <t>images/「両方の動物が海岸の火山岩の亀裂の中に_img1.jpg,images/「両方の動物が海岸の火山岩の亀裂の中に_img2.jpg</t>
         </is>
       </c>
-      <c r="C625" t="inlineStr">
+      <c r="C624" t="inlineStr">
         <is>
           <t>手書き語学 ,アラビア語 ,イグアナ</t>
         </is>
       </c>
     </row>
-    <row r="626">
-      <c r="A626" t="inlineStr">
+    <row r="625">
+      <c r="A625" t="inlineStr">
         <is>
           <t xml:space="preserve">「命じられたように正しき道を辿れ」
 واستقم كما أمرت
@@ -13597,19 +13575,19 @@
 2308 Ahmed Madyan </t>
         </is>
       </c>
-      <c r="B626" t="inlineStr">
+      <c r="B625" t="inlineStr">
         <is>
           <t>images/「命じられたように正しき道を辿れ」_img1.jpg</t>
         </is>
       </c>
-      <c r="C626" t="inlineStr">
+      <c r="C625" t="inlineStr">
         <is>
           <t>書道 ,アート</t>
         </is>
       </c>
     </row>
-    <row r="627">
-      <c r="A627" t="inlineStr">
+    <row r="626">
+      <c r="A626" t="inlineStr">
         <is>
           <t xml:space="preserve">「くつろぎなさい」استكن
 イスタキンナ [istakinna]
@@ -13617,19 +13595,19 @@
 2603 m2ff tumblr com </t>
         </is>
       </c>
-      <c r="B627" t="inlineStr">
+      <c r="B626" t="inlineStr">
         <is>
           <t>images/「くつろぎなさい」.jpeg</t>
         </is>
       </c>
-      <c r="C627" t="inlineStr">
+      <c r="C626" t="inlineStr">
         <is>
           <t>relax ,コーヒー</t>
         </is>
       </c>
     </row>
-    <row r="628">
-      <c r="A628" t="inlineStr">
+    <row r="627">
+      <c r="A627" t="inlineStr">
         <is>
           <t xml:space="preserve">「彼は応えるだろう」سيستجيب 
 サヤスタジーブ [sa-ya-stajiibu]
@@ -13638,19 +13616,19 @@
 1811 kareem mrghani </t>
         </is>
       </c>
-      <c r="B628" t="inlineStr">
+      <c r="B627" t="inlineStr">
         <is>
           <t>images/「彼は応えるだろう」_img1.jpg</t>
         </is>
       </c>
-      <c r="C628" t="inlineStr">
+      <c r="C627" t="inlineStr">
         <is>
           <t>縦書き ,現代アート</t>
         </is>
       </c>
     </row>
-    <row r="629">
-      <c r="A629" t="inlineStr">
+    <row r="628">
+      <c r="A628" t="inlineStr">
         <is>
           <t xml:space="preserve">「アラビア語が好き」
 أنا أُحبّ لُغتي
@@ -13660,19 +13638,19 @@
 2308 出典不明 </t>
         </is>
       </c>
-      <c r="B629" t="inlineStr">
+      <c r="B628" t="inlineStr">
         <is>
           <t>images/「アラビア語が好き」_img1.jpg</t>
         </is>
       </c>
-      <c r="C629" t="inlineStr">
+      <c r="C628" t="inlineStr">
         <is>
           <t>和訳 ,こども</t>
         </is>
       </c>
     </row>
-    <row r="630">
-      <c r="A630" t="inlineStr">
+    <row r="629">
+      <c r="A629" t="inlineStr">
         <is>
           <t xml:space="preserve">「私はサッカーが好きです」
 أنا أُحِبُّ كُرةَ القَدَم
@@ -13682,19 +13660,19 @@
 2109 Arabic With Nadia </t>
         </is>
       </c>
-      <c r="B630" t="inlineStr">
+      <c r="B629" t="inlineStr">
         <is>
           <t>images/「私はサッカーが好きです」_img1.jpg</t>
         </is>
       </c>
-      <c r="C630" t="inlineStr">
+      <c r="C629" t="inlineStr">
         <is>
           <t>自由時間 ,例文</t>
         </is>
       </c>
     </row>
-    <row r="631">
-      <c r="A631" t="inlineStr">
+    <row r="630">
+      <c r="A630" t="inlineStr">
         <is>
           <t xml:space="preserve">「これ、私の眼鏡じゃありません」
 هٰذِهِ لَيْسَتْ نَظَّارَاتِي
@@ -13704,19 +13682,19 @@
 2509 </t>
         </is>
       </c>
-      <c r="B631" t="inlineStr">
+      <c r="B630" t="inlineStr">
         <is>
           <t>images/「これ、私の眼鏡じゃありません」_img1.jpg</t>
         </is>
       </c>
-      <c r="C631" t="inlineStr">
+      <c r="C630" t="inlineStr">
         <is>
           <t>あらびあや</t>
         </is>
       </c>
     </row>
-    <row r="632">
-      <c r="A632" t="inlineStr">
+    <row r="631">
+      <c r="A631" t="inlineStr">
         <is>
           <t xml:space="preserve">「我らも米を食います」
 نحن أيضاً نأكل الأرز
@@ -13726,19 +13704,19 @@
 1809 </t>
         </is>
       </c>
-      <c r="B632" t="inlineStr">
+      <c r="B631" t="inlineStr">
         <is>
           <t>images/「我らも米を食います」_img1.jpg</t>
         </is>
       </c>
-      <c r="C632" t="inlineStr">
+      <c r="C631" t="inlineStr">
         <is>
           <t>あらびあや</t>
         </is>
       </c>
     </row>
-    <row r="633">
-      <c r="A633" t="inlineStr">
+    <row r="632">
+      <c r="A632" t="inlineStr">
         <is>
           <t xml:space="preserve">「ひとりでできるもん！」
 أنا أستطيع أن أفعله وحدي
@@ -13747,19 +13725,19 @@
 2105 </t>
         </is>
       </c>
-      <c r="B633" t="inlineStr">
+      <c r="B632" t="inlineStr">
         <is>
           <t>images/「ひとりでできるもん！」_img1.jpg</t>
         </is>
       </c>
-      <c r="C633" t="inlineStr">
+      <c r="C632" t="inlineStr">
         <is>
           <t>あらびあや</t>
         </is>
       </c>
     </row>
-    <row r="634">
-      <c r="A634" t="inlineStr">
+    <row r="633">
+      <c r="A633" t="inlineStr">
         <is>
           <t xml:space="preserve">「恋しくないと言っている時は恋しい」
 أُريدُك حينَ أَقُولُ أَنا لا أُريدُك
@@ -13769,19 +13747,19 @@
 2308 DARWISHISM </t>
         </is>
       </c>
-      <c r="B634" t="inlineStr">
+      <c r="B633" t="inlineStr">
         <is>
           <t>images/「恋しくないと言っている時は恋しい」_img1.jpg</t>
         </is>
       </c>
-      <c r="C634" t="inlineStr">
+      <c r="C633" t="inlineStr">
         <is>
           <t>本音 ,恋愛</t>
         </is>
       </c>
     </row>
-    <row r="635">
-      <c r="A635" t="inlineStr">
+    <row r="634">
+      <c r="A634" t="inlineStr">
         <is>
           <t xml:space="preserve">「私は〜する」
 ⁦「着る」：( أنا ألبس )['ana 'a-lbas]⁩
@@ -13792,19 +13770,19 @@
 2109 RABIE </t>
         </is>
       </c>
-      <c r="B635" t="inlineStr">
+      <c r="B634" t="inlineStr">
         <is>
           <t>images/「私は〜する」_img1.jpg,images/「私は〜する」_img2.jpg,images/「私は〜する」_img3.jpg,images/「私は〜する」_img4.jpg</t>
         </is>
       </c>
-      <c r="C635" t="inlineStr">
+      <c r="C634" t="inlineStr">
         <is>
           <t>動詞 ,絵本</t>
         </is>
       </c>
     </row>
-    <row r="636">
-      <c r="A636" t="inlineStr">
+    <row r="635">
+      <c r="A635" t="inlineStr">
         <is>
           <t xml:space="preserve">「彼は完璧ではない。私は彼の欠点については目をつむった」
 هو ليس كامل. أنا أعميت نفسي عن سيئاته
@@ -13813,19 +13791,19 @@
 2308 _NOHA </t>
         </is>
       </c>
-      <c r="B636" t="inlineStr">
+      <c r="B635" t="inlineStr">
         <is>
           <t>images/「彼は完璧ではない。私は彼の欠点につい_img1.jpg</t>
         </is>
       </c>
-      <c r="C636" t="inlineStr">
+      <c r="C635" t="inlineStr">
         <is>
           <t>愛 ,寛容</t>
         </is>
       </c>
     </row>
-    <row r="637">
-      <c r="A637" t="inlineStr">
+    <row r="636">
+      <c r="A636" t="inlineStr">
         <is>
           <t xml:space="preserve">「この子トラは検疫期間中に生まれた」
 صغير النمر هذا ولد في زمن الحجر الصحي
@@ -13834,19 +13812,19 @@
 2310 https://www.akhbaralaan.net/?p=434924 </t>
         </is>
       </c>
-      <c r="B637" t="inlineStr">
+      <c r="B636" t="inlineStr">
         <is>
           <t>images/「この子トラは検疫期間中に生まれた」_img1.jpg</t>
         </is>
       </c>
-      <c r="C637" t="inlineStr">
+      <c r="C636" t="inlineStr">
         <is>
           <t>Covid ,メキシコ</t>
         </is>
       </c>
     </row>
-    <row r="638">
-      <c r="A638" t="inlineStr">
+    <row r="637">
+      <c r="A637" t="inlineStr">
         <is>
           <t xml:space="preserve">「睡眠の素晴らしさに匹敵するものは無い！」
 وجمال النوم ليس له مثيل
@@ -13855,19 +13833,19 @@
 2308 arabzy tumblr </t>
         </is>
       </c>
-      <c r="B638" t="inlineStr">
+      <c r="B637" t="inlineStr">
         <is>
           <t>images/「睡眠の素晴らしさに匹敵するものは無い_img1.jpg</t>
         </is>
       </c>
-      <c r="C638" t="inlineStr">
+      <c r="C637" t="inlineStr">
         <is>
           <t>オフトゥン ,おやすみ</t>
         </is>
       </c>
     </row>
-    <row r="639">
-      <c r="A639" t="inlineStr">
+    <row r="638">
+      <c r="A638" t="inlineStr">
         <is>
           <t xml:space="preserve">「大器晩成」
 الأشياء العظيمة تأخذ وقت
@@ -13877,19 +13855,19 @@
 2109 出典不明 </t>
         </is>
       </c>
-      <c r="B639" t="inlineStr">
+      <c r="B638" t="inlineStr">
         <is>
           <t>images/「大器晩成」_img1.jpg</t>
         </is>
       </c>
-      <c r="C639" t="inlineStr">
+      <c r="C638" t="inlineStr">
         <is>
           <t>ことわざ ,和訳</t>
         </is>
       </c>
     </row>
-    <row r="640">
-      <c r="A640" t="inlineStr">
+    <row r="639">
+      <c r="A639" t="inlineStr">
         <is>
           <t xml:space="preserve">「コーヒーは急には飲まれない」
 القهْوة لا تشرَب عَلى عَجلْ
@@ -13900,19 +13878,19 @@
 2012 Ahmed Madyan </t>
         </is>
       </c>
-      <c r="B640" t="inlineStr">
+      <c r="B639" t="inlineStr">
         <is>
           <t>images/「コーヒーは急には飲まれない」_img1.jpg</t>
         </is>
       </c>
-      <c r="C640" t="inlineStr">
+      <c r="C639" t="inlineStr">
         <is>
           <t>名言</t>
         </is>
       </c>
     </row>
-    <row r="641">
-      <c r="A641" t="inlineStr">
+    <row r="640">
+      <c r="A640" t="inlineStr">
         <is>
           <t xml:space="preserve">「成功者は情報共有している」
 الناجحون يشاركون المعلومة
@@ -13922,19 +13900,19 @@
 2109 出典不明 </t>
         </is>
       </c>
-      <c r="B641" t="inlineStr">
+      <c r="B640" t="inlineStr">
         <is>
           <t>images/「成功者は情報共有している」_img1.jpg</t>
         </is>
       </c>
-      <c r="C641" t="inlineStr">
+      <c r="C640" t="inlineStr">
         <is>
           <t>鳥 ,シェア</t>
         </is>
       </c>
     </row>
-    <row r="642">
-      <c r="A642" t="inlineStr">
+    <row r="641">
+      <c r="A641" t="inlineStr">
         <is>
           <t xml:space="preserve">「間違いで賢くなる、痛みで強くなる」
 الأخطاء تجعلك حكيمًا، والألم يجعلك قويًا
@@ -13943,19 +13921,19 @@
 2111 https://alaminin.blogspot.com/2020/03/blog-post_6.html </t>
         </is>
       </c>
-      <c r="B642" t="inlineStr">
+      <c r="B641" t="inlineStr">
         <is>
           <t>images/「間違いで賢くなる、痛みで強くなる」_img1.jpg</t>
         </is>
       </c>
-      <c r="C642" t="inlineStr">
+      <c r="C641" t="inlineStr">
         <is>
           <t>名言</t>
         </is>
       </c>
     </row>
-    <row r="643">
-      <c r="A643" t="inlineStr">
+    <row r="642">
+      <c r="A642" t="inlineStr">
         <is>
           <t xml:space="preserve">「何事も永遠には続かない」
 لا شيء يبقى للأبد
@@ -13965,19 +13943,19 @@
 2308 KiTeLetZ </t>
         </is>
       </c>
-      <c r="B643" t="inlineStr">
+      <c r="B642" t="inlineStr">
         <is>
           <t>images/「何事も永遠には続かない」_img1.jpg</t>
         </is>
       </c>
-      <c r="C643" t="inlineStr">
+      <c r="C642" t="inlineStr">
         <is>
           <t>変化 ,名言</t>
         </is>
       </c>
     </row>
-    <row r="644">
-      <c r="A644" t="inlineStr">
+    <row r="643">
+      <c r="A643" t="inlineStr">
         <is>
           <t xml:space="preserve">「惑星地球はあなた方を歓迎します」
 كوكب الارض يرحّب بكم
@@ -13987,19 +13965,19 @@
 1811 iN49R </t>
         </is>
       </c>
-      <c r="B644" t="inlineStr">
+      <c r="B643" t="inlineStr">
         <is>
           <t>images/「惑星地球はあなた方を歓迎します」_img1.jpg</t>
         </is>
       </c>
-      <c r="C644" t="inlineStr">
+      <c r="C643" t="inlineStr">
         <is>
           <t>宇宙 ,人類</t>
         </is>
       </c>
     </row>
-    <row r="645">
-      <c r="A645" t="inlineStr">
+    <row r="644">
+      <c r="A644" t="inlineStr">
         <is>
           <t xml:space="preserve">「自分を信じなさい。人の言うことは尽きないのだから」
 ثق بنفسك فكلام الناس لا ينتهي
@@ -14008,19 +13986,19 @@
 2105 出典不明 </t>
         </is>
       </c>
-      <c r="B645" t="inlineStr">
+      <c r="B644" t="inlineStr">
         <is>
           <t>images/「自分を信じなさい。人の言うことは尽き_img1.jpg</t>
         </is>
       </c>
-      <c r="C645" t="inlineStr">
+      <c r="C644" t="inlineStr">
         <is>
           <t>自信 ,無視</t>
         </is>
       </c>
     </row>
-    <row r="646">
-      <c r="A646" t="inlineStr">
+    <row r="645">
+      <c r="A645" t="inlineStr">
         <is>
           <t xml:space="preserve">「弟が歩くぞ」أخي الصغير يمشي
 アキ_ッサギール・ヤムシー ['aKh-i ^_saGhiiru ya-mShii]
@@ -14029,19 +14007,19 @@
 2308 gulfkids com http://www.gulfkids.com/ar/book48-1909.htm </t>
         </is>
       </c>
-      <c r="B646" t="inlineStr">
+      <c r="B645" t="inlineStr">
         <is>
           <t>images/「弟が歩くぞ」_img1.jpg</t>
         </is>
       </c>
-      <c r="C646" t="inlineStr">
+      <c r="C645" t="inlineStr">
         <is>
           <t>兄弟 ,絵本</t>
         </is>
       </c>
     </row>
-    <row r="647">
-      <c r="A647" t="inlineStr">
+    <row r="646">
+      <c r="A646" t="inlineStr">
         <is>
           <t xml:space="preserve">花より団子おおお（違う）
 「誰もふさわしくない」[laa 'aHada ya-staHiqqu]
@@ -14049,19 +14027,19 @@
 2308 https://twitter.com/NatGeoMagArab/status/1370041991317233664 </t>
         </is>
       </c>
-      <c r="B647" t="inlineStr">
+      <c r="B646" t="inlineStr">
         <is>
           <t>images/花より団子おおお（違う）_img1.jpg</t>
         </is>
       </c>
-      <c r="C647" t="inlineStr">
+      <c r="C646" t="inlineStr">
         <is>
           <t>手書き語学 ,アラビア語 ,キノボリカンガルー</t>
         </is>
       </c>
     </row>
-    <row r="648">
-      <c r="A648" t="inlineStr">
+    <row r="647">
+      <c r="A647" t="inlineStr">
         <is>
           <t xml:space="preserve">「幸せな人生には弱い記憶力が必要」
 الحياة السعيدة تتطلب ذاكرة ضعيفة
@@ -14070,19 +14048,19 @@
 2012 出典不明 </t>
         </is>
       </c>
-      <c r="B648" t="inlineStr">
+      <c r="B647" t="inlineStr">
         <is>
           <t>images/「幸せな人生には弱い記憶力が必要」_img1.jpg</t>
         </is>
       </c>
-      <c r="C648" t="inlineStr">
+      <c r="C647" t="inlineStr">
         <is>
           <t>前向き</t>
         </is>
       </c>
     </row>
-    <row r="649">
-      <c r="A649" t="inlineStr">
+    <row r="648">
+      <c r="A648" t="inlineStr">
         <is>
           <t xml:space="preserve">「このパンダは私たちに、幸せは単純なことの中に隠れているのだと教えている」
 دب "الباندا" هذا يؤكد لنا أن السعادة تكمن في أبسط الأشياء
@@ -14090,19 +14068,19 @@
 2308 https://twitter.com/NatGeoMagArab/status/1309938472065486848 </t>
         </is>
       </c>
-      <c r="B649" t="inlineStr">
+      <c r="B648" t="inlineStr">
         <is>
           <t>images/「このパンダは私たちに、幸せは単純なこ.png</t>
         </is>
       </c>
-      <c r="C649" t="inlineStr">
+      <c r="C648" t="inlineStr">
         <is>
           <t>パンダ ,雪</t>
         </is>
       </c>
     </row>
-    <row r="650">
-      <c r="A650" t="inlineStr">
+    <row r="649">
+      <c r="A649" t="inlineStr">
         <is>
           <t xml:space="preserve">「良い時間は速く過ぎる」
 الأوقات الجميلة تمر بسرعة
@@ -14112,19 +14090,19 @@
 1810 Nasser.Tumblr </t>
         </is>
       </c>
-      <c r="B650" t="inlineStr">
+      <c r="B649" t="inlineStr">
         <is>
           <t>images/「良い時間は速く過ぎる」_img1.jpg</t>
         </is>
       </c>
-      <c r="C650" t="inlineStr">
+      <c r="C649" t="inlineStr">
         <is>
           <t>相対論 ,心理学</t>
         </is>
       </c>
     </row>
-    <row r="651">
-      <c r="A651" t="inlineStr">
+    <row r="650">
+      <c r="A650" t="inlineStr">
         <is>
           <t xml:space="preserve">「今日が始まりかもしれない」
 كل يوم ممكن يكون بداية
@@ -14134,19 +14112,19 @@
 2308 Ahmed Madyan </t>
         </is>
       </c>
-      <c r="B651" t="inlineStr">
+      <c r="B650" t="inlineStr">
         <is>
           <t>images/「今日が始まりかもしれない」_img1.jpg</t>
         </is>
       </c>
-      <c r="C651" t="inlineStr">
+      <c r="C650" t="inlineStr">
         <is>
           <t>吉日 ,開始</t>
         </is>
       </c>
     </row>
-    <row r="652">
-      <c r="A652" t="inlineStr">
+    <row r="651">
+      <c r="A651" t="inlineStr">
         <is>
           <t xml:space="preserve">「ヌール、歯医者さんに行く」
 نور تذهب إلى طبيب الأسنان
@@ -14156,19 +14134,19 @@
 2109 RABIE </t>
         </is>
       </c>
-      <c r="B652" t="inlineStr">
+      <c r="B651" t="inlineStr">
         <is>
           <t>images/「ヌール、歯医者さんに行く」_img1.jpg</t>
         </is>
       </c>
-      <c r="C652" t="inlineStr">
+      <c r="C651" t="inlineStr">
         <is>
           <t>絵本 ,歯科</t>
         </is>
       </c>
     </row>
-    <row r="653">
-      <c r="A653" t="inlineStr">
+    <row r="652">
+      <c r="A652" t="inlineStr">
         <is>
           <t xml:space="preserve">「ラヤンはねむれない」
 لَيان لا تَسْتَطيعُ أَنْ تَنام
@@ -14177,19 +14155,19 @@
 2308 出典不明 </t>
         </is>
       </c>
-      <c r="B653" t="inlineStr">
+      <c r="B652" t="inlineStr">
         <is>
           <t>images/「ラヤンはねむれない」_img1.jpg</t>
         </is>
       </c>
-      <c r="C653" t="inlineStr">
+      <c r="C652" t="inlineStr">
         <is>
           <t>絵本 ,不眠症</t>
         </is>
       </c>
     </row>
-    <row r="654">
-      <c r="A654" t="inlineStr">
+    <row r="653">
+      <c r="A653" t="inlineStr">
         <is>
           <t xml:space="preserve">「クネイトラ県、蜂の巣を約60%失う」
 القنيطرة تفقد حوالي 60 % من خلايا نحلها
@@ -14197,19 +14175,19 @@
 2403 nabd com/t/101679025-fb119f </t>
         </is>
       </c>
-      <c r="B654" t="inlineStr">
+      <c r="B653" t="inlineStr">
         <is>
           <t>images/「クネイトラ県、蜂の巣を約60%失う」_img1.jpg</t>
         </is>
       </c>
-      <c r="C654" t="inlineStr">
+      <c r="C653" t="inlineStr">
         <is>
           <t>蜂の巣 ,パーセント</t>
         </is>
       </c>
     </row>
-    <row r="655">
-      <c r="A655" t="inlineStr">
+    <row r="654">
+      <c r="A654" t="inlineStr">
         <is>
           <t xml:space="preserve">「結ばれしター」ة
 ⁦( تاء مربوطة )[taa' marbuu_ta]：ت「ター」( تاء )[taa']・「結ばれている」( مربوط )[marbuu_t]：( ربط )【結】⁩
@@ -14217,19 +14195,19 @@
 2308 出典不明 </t>
         </is>
       </c>
-      <c r="B655" t="inlineStr">
+      <c r="B654" t="inlineStr">
         <is>
           <t>images/「結ばれしター」_img1.jpg</t>
         </is>
       </c>
-      <c r="C655" t="inlineStr">
+      <c r="C654" t="inlineStr">
         <is>
           <t>アラビア文字 ,顔</t>
         </is>
       </c>
     </row>
-    <row r="656">
-      <c r="A656" t="inlineStr">
+    <row r="655">
+      <c r="A655" t="inlineStr">
         <is>
           <t xml:space="preserve">「忙しい」مشغول
 マシュグール [maShGhuul]
@@ -14238,19 +14216,19 @@
 1811 skyshinichi.instagram </t>
         </is>
       </c>
-      <c r="B656" t="inlineStr">
+      <c r="B655" t="inlineStr">
         <is>
           <t>images/「忙しい」_img1.jpg</t>
         </is>
       </c>
-      <c r="C656" t="inlineStr">
+      <c r="C655" t="inlineStr">
         <is>
           <t>スティッチ ,残業</t>
         </is>
       </c>
     </row>
-    <row r="657">
-      <c r="A657" t="inlineStr">
+    <row r="656">
+      <c r="A656" t="inlineStr">
         <is>
           <t xml:space="preserve">「駐車禁止」ممنوع الوقوف
 マムヌーア・アルウクーフ [mamnuu* al-wuquuf]
@@ -14259,19 +14237,19 @@
 2106 出典不明 </t>
         </is>
       </c>
-      <c r="B657" t="inlineStr">
+      <c r="B656" t="inlineStr">
         <is>
           <t>images/「駐車禁止」_img1.jpg</t>
         </is>
       </c>
-      <c r="C657" t="inlineStr">
+      <c r="C656" t="inlineStr">
         <is>
           <t>標識 ,ジョーク</t>
         </is>
       </c>
     </row>
-    <row r="658">
-      <c r="A658" t="inlineStr">
+    <row r="657">
+      <c r="A657" t="inlineStr">
         <is>
           <t xml:space="preserve">「一人ひとりが責任を」
 كُلنا مسؤول
@@ -14281,19 +14259,19 @@
 2308 covid19awareness sa </t>
         </is>
       </c>
-      <c r="B658" t="inlineStr">
+      <c r="B657" t="inlineStr">
         <is>
           <t>images/「一人ひとりが責任を」_img1.jpg</t>
         </is>
       </c>
-      <c r="C658" t="inlineStr">
+      <c r="C657" t="inlineStr">
         <is>
           <t>Covid ,感染拡大防止</t>
         </is>
       </c>
     </row>
-    <row r="659">
-      <c r="A659" t="inlineStr">
+    <row r="658">
+      <c r="A658" t="inlineStr">
         <is>
           <t xml:space="preserve">「おめでとうございます」مبروك
 マブルーク [mabruuk]
@@ -14302,19 +14280,19 @@
 2308 </t>
         </is>
       </c>
-      <c r="B659" t="inlineStr">
+      <c r="B658" t="inlineStr">
         <is>
           <t>images/「おめでとうございます」_img1.jpg</t>
         </is>
       </c>
-      <c r="C659" t="inlineStr">
+      <c r="C658" t="inlineStr">
         <is>
           <t>詐欺 ,広告</t>
         </is>
       </c>
     </row>
-    <row r="660">
-      <c r="A660" t="inlineStr">
+    <row r="659">
+      <c r="A659" t="inlineStr">
         <is>
           <t xml:space="preserve">「手書きフォント」
 خط مكتوب باليد
@@ -14324,19 +14302,19 @@
 1809 FahdAlFraikh Behance </t>
         </is>
       </c>
-      <c r="B660" t="inlineStr">
+      <c r="B659" t="inlineStr">
         <is>
           <t>images/「手書きフォント」_img1.jpg</t>
         </is>
       </c>
-      <c r="C660" t="inlineStr">
+      <c r="C659" t="inlineStr">
         <is>
           <t>可愛いフォント ,筆跡</t>
         </is>
       </c>
     </row>
-    <row r="661">
-      <c r="A661" t="inlineStr">
+    <row r="660">
+      <c r="A660" t="inlineStr">
         <is>
           <t xml:space="preserve">「開かれたターと結ばれたター」
 التاء المفتوحة والمربوطة
@@ -14346,19 +14324,19 @@
 2109 slideshare.net </t>
         </is>
       </c>
-      <c r="B661" t="inlineStr">
+      <c r="B660" t="inlineStr">
         <is>
           <t>images/「開かれたターと結ばれたター」_img1.jpg</t>
         </is>
       </c>
-      <c r="C661" t="inlineStr">
+      <c r="C660" t="inlineStr">
         <is>
           <t>アラビア文字 ,スマイリー</t>
         </is>
       </c>
     </row>
-    <row r="662">
-      <c r="A662" t="inlineStr">
+    <row r="661">
+      <c r="A661" t="inlineStr">
         <is>
           <t xml:space="preserve">「このラマは誇らしげにして立っている」
 تقف هذه اللاما مزهوة بنفسها
@@ -14366,19 +14344,19 @@
 2410 https://twitter.com/NatGeoMagArab/status/1597485552965935104 </t>
         </is>
       </c>
-      <c r="B662" t="inlineStr">
+      <c r="B661" t="inlineStr">
         <is>
           <t>images/「このラマは誇らしげにして立っている」_img1.jpg</t>
         </is>
       </c>
-      <c r="C662" t="inlineStr">
+      <c r="C661" t="inlineStr">
         <is>
           <t>手書き語学 ,アラビア語 ,マチュピチュ遺跡</t>
         </is>
       </c>
     </row>
-    <row r="663">
-      <c r="A663" t="inlineStr">
+    <row r="662">
+      <c r="A662" t="inlineStr">
         <is>
           <t xml:space="preserve">「小さな生き物にしては危険な名前だ」
 اسم خطير لمخلوق صغير
@@ -14387,19 +14365,19 @@
 2308 https://twitter.com/NatGeoMagArab/status/1495035772071669760 </t>
         </is>
       </c>
-      <c r="B663" t="inlineStr">
+      <c r="B662" t="inlineStr">
         <is>
           <t>images/「小さな生き物にしては危険な名前だ」_img1.jpg</t>
         </is>
       </c>
-      <c r="C663" t="inlineStr">
+      <c r="C662" t="inlineStr">
         <is>
           <t>有袋類 ,タスマニアデビル</t>
         </is>
       </c>
     </row>
-    <row r="664">
-      <c r="A664" t="inlineStr">
+    <row r="663">
+      <c r="A663" t="inlineStr">
         <is>
           <t xml:space="preserve">「こわれている」مكسر
 ムカッサル [mukassar]
@@ -14407,19 +14385,19 @@
 2105 behance Written-Visuals </t>
         </is>
       </c>
-      <c r="B664" t="inlineStr">
+      <c r="B663" t="inlineStr">
         <is>
           <t>images/「こわれている」_img1.jpg</t>
         </is>
       </c>
-      <c r="C664" t="inlineStr">
+      <c r="C663" t="inlineStr">
         <is>
           <t>バラバラ ,デザイン</t>
         </is>
       </c>
     </row>
-    <row r="665">
-      <c r="A665" t="inlineStr">
+    <row r="664">
+      <c r="A664" t="inlineStr">
         <is>
           <t xml:space="preserve">「早起きする方法」
 كيف تنهض مُبكّرًا
@@ -14429,19 +14407,19 @@
 2308 Funders and Founders </t>
         </is>
       </c>
-      <c r="B665" t="inlineStr">
+      <c r="B664" t="inlineStr">
         <is>
           <t>images/「早起きする方法」_img1.jpg</t>
         </is>
       </c>
-      <c r="C665" t="inlineStr">
+      <c r="C664" t="inlineStr">
         <is>
           <t>オフトゥン ,寝起き</t>
         </is>
       </c>
     </row>
-    <row r="666">
-      <c r="A666" t="inlineStr">
+    <row r="665">
+      <c r="A665" t="inlineStr">
         <is>
           <t xml:space="preserve">「アラブ・デザイン文字展覧会」
 معرض لتخطيط الحرف العربي
@@ -14451,38 +14429,38 @@
 2109 arabic lettering exhibition </t>
         </is>
       </c>
-      <c r="B666" t="inlineStr">
+      <c r="B665" t="inlineStr">
         <is>
           <t>images/「アラブ・デザイン文字展覧会」_img1.jpg</t>
         </is>
       </c>
-      <c r="C666" t="inlineStr">
+      <c r="C665" t="inlineStr">
         <is>
           <t>ポスター</t>
         </is>
       </c>
     </row>
-    <row r="667">
-      <c r="A667" t="inlineStr">
+    <row r="666">
+      <c r="A666" t="inlineStr">
         <is>
           <t xml:space="preserve">「お気に入りのおもちゃには触らせない」
 ⁦「彼は〜を許さない」[laa ya-smaHu bi-]：「彼は許す」( يسمح )[ya-smaH(u)]：「許した」( سمح )[samaHa]：( سَ )[sa]・( مَ )[ma]・( حَ )[Ha]⁩
 2209 https://pic.twitter.com/qWcIPB3fz2 </t>
         </is>
       </c>
-      <c r="B667" t="inlineStr">
+      <c r="B666" t="inlineStr">
         <is>
           <t>images/「お気に入りのおもちゃには触らせない」_img1.jpg</t>
         </is>
       </c>
-      <c r="C667" t="inlineStr">
+      <c r="C666" t="inlineStr">
         <is>
           <t>パンダ ,ボール</t>
         </is>
       </c>
     </row>
-    <row r="668">
-      <c r="A668" t="inlineStr">
+    <row r="667">
+      <c r="A667" t="inlineStr">
         <is>
           <t xml:space="preserve">「名探偵コナン」المحقق كونان
 アルムハッキク・コナン [al-muHaqqiq Conan]
@@ -14491,19 +14469,19 @@
 1809 wikipedia </t>
         </is>
       </c>
-      <c r="B668" t="inlineStr">
+      <c r="B667" t="inlineStr">
         <is>
           <t>images/「名探偵コナン」_img1.jpg</t>
         </is>
       </c>
-      <c r="C668" t="inlineStr">
+      <c r="C667" t="inlineStr">
         <is>
           <t>江戸川コナン ,ロゴ</t>
         </is>
       </c>
     </row>
-    <row r="669">
-      <c r="A669" t="inlineStr">
+    <row r="668">
+      <c r="A668" t="inlineStr">
         <is>
           <t xml:space="preserve">「イードおめでとう」عيد مبارك
 イード・ムバーラク [*iid mubaarak]
@@ -14511,19 +14489,19 @@
 2308 出典不明 </t>
         </is>
       </c>
-      <c r="B669" t="inlineStr">
+      <c r="B668" t="inlineStr">
         <is>
           <t>images/「イードおめでとう」_img1.jpg</t>
         </is>
       </c>
-      <c r="C669" t="inlineStr">
+      <c r="C668" t="inlineStr">
         <is>
           <t>عيد ,アラビア語</t>
         </is>
       </c>
     </row>
-    <row r="670">
-      <c r="A670" t="inlineStr">
+    <row r="669">
+      <c r="A669" t="inlineStr">
         <is>
           <t xml:space="preserve">「戦士」محارب
 ムハーリブ [muHaarib]
@@ -14532,19 +14510,19 @@
 1809 abudinges.tumblr </t>
         </is>
       </c>
-      <c r="B670" t="inlineStr">
+      <c r="B669" t="inlineStr">
         <is>
           <t>images/「戦士」_img1.jpg</t>
         </is>
       </c>
-      <c r="C670" t="inlineStr">
+      <c r="C669" t="inlineStr">
         <is>
           <t>ロゴ ,赤</t>
         </is>
       </c>
     </row>
-    <row r="671">
-      <c r="A671" t="inlineStr">
+    <row r="670">
+      <c r="A670" t="inlineStr">
         <is>
           <t xml:space="preserve">「ライブ」بث مباشر
 バッス・ムバーシル [ba^Th(un) mubaaShir(un)]
@@ -14553,19 +14531,19 @@
 2308 beIN SPORTS </t>
         </is>
       </c>
-      <c r="B671" t="inlineStr">
+      <c r="B670" t="inlineStr">
         <is>
           <t>images/「ライブ」_img1.jpg</t>
         </is>
       </c>
-      <c r="C671" t="inlineStr">
+      <c r="C670" t="inlineStr">
         <is>
           <t xml:space="preserve">生放送 ,試合 </t>
         </is>
       </c>
     </row>
-    <row r="672">
-      <c r="A672" t="inlineStr">
+    <row r="671">
+      <c r="A671" t="inlineStr">
         <is>
           <t xml:space="preserve">「信者」مُؤْمِنٌ
 ムッミン [mu'min(un)]
@@ -14574,19 +14552,19 @@
 2106 出典不明 </t>
         </is>
       </c>
-      <c r="B672" t="inlineStr">
+      <c r="B671" t="inlineStr">
         <is>
           <t>images/「信者」_img1.jpg</t>
         </is>
       </c>
-      <c r="C672" t="inlineStr">
+      <c r="C671" t="inlineStr">
         <is>
           <t>明暗 ,信仰</t>
         </is>
       </c>
     </row>
-    <row r="673">
-      <c r="A673" t="inlineStr">
+    <row r="672">
+      <c r="A672" t="inlineStr">
         <is>
           <t xml:space="preserve">「開⇔閉」
 مفتوح
@@ -14597,19 +14575,19 @@
 2312 Hussein Safina, behance </t>
         </is>
       </c>
-      <c r="B673" t="inlineStr">
+      <c r="B672" t="inlineStr">
         <is>
           <t>images/「開⇔閉」_img1.jpg</t>
         </is>
       </c>
-      <c r="C673" t="inlineStr">
+      <c r="C672" t="inlineStr">
         <is>
           <t>オープンマインド ,トグル</t>
         </is>
       </c>
     </row>
-    <row r="674">
-      <c r="A674" t="inlineStr">
+    <row r="673">
+      <c r="A673" t="inlineStr">
         <is>
           <t xml:space="preserve">「予想外な結末！」
 نهاية غير متوقعة
@@ -14617,19 +14595,19 @@
 2308 https://twitter.com/NatGeoMagArab/status/1159011433444593665 </t>
         </is>
       </c>
-      <c r="B674" t="inlineStr">
+      <c r="B673" t="inlineStr">
         <is>
           <t>images/「予想外な結末！」_img1.jpg</t>
         </is>
       </c>
-      <c r="C674" t="inlineStr">
+      <c r="C673" t="inlineStr">
         <is>
           <t>手書き語学 ,アラビア語 ,ウサギ</t>
         </is>
       </c>
     </row>
-    <row r="675">
-      <c r="A675" t="inlineStr">
+    <row r="674">
+      <c r="A674" t="inlineStr">
         <is>
           <t xml:space="preserve">「ベイルート・アニメイテッド」
 بیروت متحرّکة
@@ -14639,19 +14617,19 @@
 2308 arabic_script Instagram </t>
         </is>
       </c>
-      <c r="B675" t="inlineStr">
+      <c r="B674" t="inlineStr">
         <is>
           <t>images/「ベイルート・アニメイテッド」_img1.jpg</t>
         </is>
       </c>
-      <c r="C675" t="inlineStr">
+      <c r="C674" t="inlineStr">
         <is>
           <t>アニメ ,レバノン</t>
         </is>
       </c>
     </row>
-    <row r="676">
-      <c r="A676" t="inlineStr">
+    <row r="675">
+      <c r="A675" t="inlineStr">
         <is>
           <t xml:space="preserve">「夢みれば叶う」
 كُلُّ مُتَوَقَّعٍ آتٍ
@@ -14661,19 +14639,19 @@
 2108 Ahmed Madyan </t>
         </is>
       </c>
-      <c r="B676" t="inlineStr">
+      <c r="B675" t="inlineStr">
         <is>
           <t>images/「夢みれば叶う」_img1.jpg</t>
         </is>
       </c>
-      <c r="C676" t="inlineStr">
+      <c r="C675" t="inlineStr">
         <is>
           <t>希望 ,ドリカム</t>
         </is>
       </c>
     </row>
-    <row r="677">
-      <c r="A677" t="inlineStr">
+    <row r="676">
+      <c r="A676" t="inlineStr">
         <is>
           <t xml:space="preserve">「もし両者が人間のように鎧で武装して戦いに突入したら」
 لو خاضا معاركهما متسلحين بالدروع على غرار البش
@@ -14681,19 +14659,19 @@
 2404 https://x.com/NatGeoMagArab/status/1759284149456945464 </t>
         </is>
       </c>
-      <c r="B677" t="inlineStr">
+      <c r="B676" t="inlineStr">
         <is>
           <t>images/「もし両者が人間のように鎧で武装して戦_img1.jpg,images/「もし両者が人間のように鎧で武装して戦_img2.jpg</t>
         </is>
       </c>
-      <c r="C677" t="inlineStr">
+      <c r="C676" t="inlineStr">
         <is>
           <t>手書き語学 ,アラビア語 ,猫</t>
         </is>
       </c>
     </row>
-    <row r="678">
-      <c r="A678" t="inlineStr">
+    <row r="677">
+      <c r="A677" t="inlineStr">
         <is>
           <t xml:space="preserve">「全ては結びついている」
 كل شيء مترابط
@@ -14703,19 +14681,19 @@
 2308 Ahmed Madyan https://twitter.com/madyco22/status/1451990828298166273 </t>
         </is>
       </c>
-      <c r="B678" t="inlineStr">
+      <c r="B677" t="inlineStr">
         <is>
           <t>images/「全ては結びついている」_img1.jpg</t>
         </is>
       </c>
-      <c r="C678" t="inlineStr">
+      <c r="C677" t="inlineStr">
         <is>
           <t>一筆書き ,デザイン</t>
         </is>
       </c>
     </row>
-    <row r="679">
-      <c r="A679" t="inlineStr">
+    <row r="678">
+      <c r="A678" t="inlineStr">
         <is>
           <t xml:space="preserve">「初心者のためのスケッチトレーニング」
 تعليم الرسم للمبتدئين
@@ -14725,19 +14703,19 @@
 2308 free-bookspdf com </t>
         </is>
       </c>
-      <c r="B679" t="inlineStr">
+      <c r="B678" t="inlineStr">
         <is>
           <t>images/「初心者のためのスケッチトレーニング」_img1.jpg</t>
         </is>
       </c>
-      <c r="C679" t="inlineStr">
+      <c r="C678" t="inlineStr">
         <is>
           <t>イラスト ,絵</t>
         </is>
       </c>
     </row>
-    <row r="680">
-      <c r="A680" t="inlineStr">
+    <row r="679">
+      <c r="A679" t="inlineStr">
         <is>
           <t xml:space="preserve">「初心者のためのスルス体書道トレーニング」
 تعليم خط الثلث للمبتدئين
@@ -14747,19 +14725,19 @@
 2308 出典不明 </t>
         </is>
       </c>
-      <c r="B680" t="inlineStr">
+      <c r="B679" t="inlineStr">
         <is>
           <t>images/「初心者のためのスルス体書道トレーニン_img1.jpg</t>
         </is>
       </c>
-      <c r="C680" t="inlineStr">
+      <c r="C679" t="inlineStr">
         <is>
           <t>書道</t>
         </is>
       </c>
     </row>
-    <row r="681">
-      <c r="A681" t="inlineStr">
+    <row r="680">
+      <c r="A680" t="inlineStr">
         <is>
           <t xml:space="preserve">「笑顔でいなさい」خليك مبتسم
 カッリーク・ムブタスィム [Khallii-k mubtasim]
@@ -14768,19 +14746,19 @@
 2308 https://tmblr.co/Zj9tguYLXBvC </t>
         </is>
       </c>
-      <c r="B681" t="inlineStr">
+      <c r="B680" t="inlineStr">
         <is>
           <t>images/「笑顔でいなさい」_img1.jpg</t>
         </is>
       </c>
-      <c r="C681" t="inlineStr">
+      <c r="C680" t="inlineStr">
         <is>
           <t>スマイル ,名言</t>
         </is>
       </c>
     </row>
-    <row r="682">
-      <c r="A682" t="inlineStr">
+    <row r="681">
+      <c r="A681" t="inlineStr">
         <is>
           <t xml:space="preserve">自動車メーカー
 ⁦・「TOYOTA」( تويوتا )⁩
@@ -14792,19 +14770,19 @@
 2308 syarah com </t>
         </is>
       </c>
-      <c r="B682" t="inlineStr">
+      <c r="B681" t="inlineStr">
         <is>
           <t>images/自動車メーカー_img1.jpg,images/自動車メーカー_img2.jpg,images/自動車メーカー_img3.jpg,images/自動車メーカー_img4.jpg</t>
         </is>
       </c>
-      <c r="C682" t="inlineStr">
+      <c r="C681" t="inlineStr">
         <is>
           <t>日本車 ,韓国車</t>
         </is>
       </c>
     </row>
-    <row r="683">
-      <c r="A683" t="inlineStr">
+    <row r="682">
+      <c r="A682" t="inlineStr">
         <is>
           <t xml:space="preserve">「僕たちは協力して不可能を達成するよ」
 بالتعاون نحقق المحال
@@ -14814,19 +14792,19 @@
 2109 </t>
         </is>
       </c>
-      <c r="B683" t="inlineStr">
+      <c r="B682" t="inlineStr">
         <is>
           <t>images/「僕たちは協力して不可能を達成するよ」_img1.jpg</t>
         </is>
       </c>
-      <c r="C683" t="inlineStr">
+      <c r="C682" t="inlineStr">
         <is>
           <t>無理 ,ハム太郎</t>
         </is>
       </c>
     </row>
-    <row r="684">
-      <c r="A684" t="inlineStr">
+    <row r="683">
+      <c r="A683" t="inlineStr">
         <is>
           <t xml:space="preserve">「幸せは伝染性。喜びを広めよう」
 السعادة معدية فأشع الفرح
@@ -14836,19 +14814,19 @@
 2511 instagram　com/p/fVEfxEo7Va/ </t>
         </is>
       </c>
-      <c r="B684" t="inlineStr">
+      <c r="B683" t="inlineStr">
         <is>
           <t>images/「幸せは伝染性。喜びを広めよう」_img1.jpg</t>
         </is>
       </c>
-      <c r="C684" t="inlineStr">
+      <c r="C683" t="inlineStr">
         <is>
           <t>拡散希望</t>
         </is>
       </c>
     </row>
-    <row r="685">
-      <c r="A685" t="inlineStr">
+    <row r="684">
+      <c r="A684" t="inlineStr">
         <is>
           <t xml:space="preserve">「ストレスは人間だけのものではない」
 الشعور بالتوتر ليس حكرًا على البشر
@@ -14856,19 +14834,19 @@
 2408 https://x.com/NatGeoMagArab/status/1736755816911487420 </t>
         </is>
       </c>
-      <c r="B685" t="inlineStr">
+      <c r="B684" t="inlineStr">
         <is>
           <t>images/「ストレスは人間だけのものではない」_img1.jpg</t>
         </is>
       </c>
-      <c r="C685" t="inlineStr">
+      <c r="C684" t="inlineStr">
         <is>
           <t>手書き語学 ,アラビア語 ,ストレス</t>
         </is>
       </c>
     </row>
-    <row r="686">
-      <c r="A686" t="inlineStr">
+    <row r="685">
+      <c r="A685" t="inlineStr">
         <is>
           <t xml:space="preserve">「私達は出来ます！」
 نستطيع فعلها
@@ -14878,19 +14856,19 @@
 2308 NAHARBAHIJ com </t>
         </is>
       </c>
-      <c r="B686" t="inlineStr">
+      <c r="B685" t="inlineStr">
         <is>
           <t>images/「私達は出来ます！」_img1.jpg</t>
         </is>
       </c>
-      <c r="C686" t="inlineStr">
+      <c r="C685" t="inlineStr">
         <is>
           <t>女性 ,パロディ</t>
         </is>
       </c>
     </row>
-    <row r="687">
-      <c r="A687" t="inlineStr">
+    <row r="686">
+      <c r="A686" t="inlineStr">
         <is>
           <t xml:space="preserve">「全然分からん」ولا فاهم إشي
 ウラー・ファーヒム・イシ [w-laa faahim 'iShy]
@@ -14900,19 +14878,19 @@
 2209 出典不明 </t>
         </is>
       </c>
-      <c r="B687" t="inlineStr">
+      <c r="B686" t="inlineStr">
         <is>
           <t>images/「全然分からん」_img1.jpg</t>
         </is>
       </c>
-      <c r="C687" t="inlineStr">
+      <c r="C686" t="inlineStr">
         <is>
           <t>アラビア語</t>
         </is>
       </c>
     </row>
-    <row r="688">
-      <c r="A688" t="inlineStr">
+    <row r="687">
+      <c r="A687" t="inlineStr">
         <is>
           <t xml:space="preserve">「人間は一人ひとり、特別な才がある。だから自分を他人と比べるのはやめよう」
 لكل إنسان مواهبه الخاصة 
@@ -14921,19 +14899,19 @@
 1812 Gwid3 </t>
         </is>
       </c>
-      <c r="B688" t="inlineStr">
+      <c r="B687" t="inlineStr">
         <is>
           <t>images/「人間は一人ひとり、特別な才がある。だ_img1.jpg</t>
         </is>
       </c>
-      <c r="C688" t="inlineStr">
+      <c r="C687" t="inlineStr">
         <is>
           <t>自尊 ,プライド</t>
         </is>
       </c>
     </row>
-    <row r="689">
-      <c r="A689" t="inlineStr">
+    <row r="688">
+      <c r="A688" t="inlineStr">
         <is>
           <t xml:space="preserve">「この猫は食事をシェアするのが嫌い！」
 هذه القطة لا تحب مشاركة الطعام
@@ -14942,19 +14920,19 @@
 2605 facebook com/alahram/videos/2154923608133231/ </t>
         </is>
       </c>
-      <c r="B689" t="inlineStr">
+      <c r="B688" t="inlineStr">
         <is>
           <t>images/「この猫は食事をシェアするのが嫌い！」_img1.jpg</t>
         </is>
       </c>
-      <c r="C689" t="inlineStr">
+      <c r="C688" t="inlineStr">
         <is>
           <t>猫 ,ネコ</t>
         </is>
       </c>
     </row>
-    <row r="690">
-      <c r="A690" t="inlineStr">
+    <row r="689">
+      <c r="A689" t="inlineStr">
         <is>
           <t xml:space="preserve">「怪獣との戦いでは自分が怪獣化せぬよう警戒しなさい」
 احذر عند محاربة الوحوش ألا تصبح واحدا منهم
@@ -14964,19 +14942,19 @@
 2108 warag-3nb.tumblr </t>
         </is>
       </c>
-      <c r="B690" t="inlineStr">
+      <c r="B689" t="inlineStr">
         <is>
           <t>images/「怪獣との戦いでは自分が怪獣化せぬよう_img1.jpg,images/ 「怪獣との戦いでは自分が怪獣化せぬよう_img2.jpg</t>
         </is>
       </c>
-      <c r="C690" t="inlineStr">
+      <c r="C689" t="inlineStr">
         <is>
           <t>正気 ,モンスター</t>
         </is>
       </c>
     </row>
-    <row r="691">
-      <c r="A691" t="inlineStr">
+    <row r="690">
+      <c r="A690" t="inlineStr">
         <is>
           <t xml:space="preserve">「錯視アート」فن الخداع البصري
 ファンヌ_ルヒダーイ_ルバサリーイ [fannu l-Khidaa*i l-ba_sariyy]
@@ -14985,19 +14963,19 @@
 2409 https://online.pubhtml5.com/idtb/neft/ </t>
         </is>
       </c>
-      <c r="B691" t="inlineStr">
+      <c r="B690" t="inlineStr">
         <is>
           <t>images/「錯視アート」_img1.jpg</t>
         </is>
       </c>
-      <c r="C691" t="inlineStr">
+      <c r="C690" t="inlineStr">
         <is>
           <t>トリックアート</t>
         </is>
       </c>
     </row>
-    <row r="692">
-      <c r="A692" t="inlineStr">
+    <row r="691">
+      <c r="A691" t="inlineStr">
         <is>
           <t xml:space="preserve">「自然界の消防士の訓練」
 تدريبات رجال الإطفاء في الطبيعة
@@ -15005,19 +14983,19 @@
 2308 https://twitter.com/NatGeoMagArab/status/1462420543890608129 </t>
         </is>
       </c>
-      <c r="B692" t="inlineStr">
+      <c r="B691" t="inlineStr">
         <is>
           <t>images/「自然界の消防士の訓練」_img1.jpg,images/ 「自然界の消防士の訓練」_img2.jpg</t>
         </is>
       </c>
-      <c r="C692" t="inlineStr">
+      <c r="C691" t="inlineStr">
         <is>
           <t>手書き語学 ,アラビア語 ,ヒグマ</t>
         </is>
       </c>
     </row>
-    <row r="693">
-      <c r="A693" t="inlineStr">
+    <row r="692">
+      <c r="A692" t="inlineStr">
         <is>
           <t xml:space="preserve">「救助」إسعاف
 イスアーフ ['is*aaf]
@@ -15026,19 +15004,19 @@
 2109 ambulance gov ae </t>
         </is>
       </c>
-      <c r="B693" t="inlineStr">
+      <c r="B692" t="inlineStr">
         <is>
           <t>images/「救助」_img1.jpg</t>
         </is>
       </c>
-      <c r="C693" t="inlineStr">
+      <c r="C692" t="inlineStr">
         <is>
           <t>救急車 ,はたらくくるま</t>
         </is>
       </c>
     </row>
-    <row r="694">
-      <c r="A694" t="inlineStr">
+    <row r="693">
+      <c r="A693" t="inlineStr">
         <is>
           <t xml:space="preserve">「感情／感覚」الإحْسَاسْ
 アルイヒサース [al-'iHsaas]
@@ -15047,19 +15025,19 @@
 2308 iN49R </t>
         </is>
       </c>
-      <c r="B694" t="inlineStr">
+      <c r="B693" t="inlineStr">
         <is>
           <t>images/「感情／感覚」_img1.jpg</t>
         </is>
       </c>
-      <c r="C694" t="inlineStr">
+      <c r="C693" t="inlineStr">
         <is>
           <t>オフ ,一休み</t>
         </is>
       </c>
     </row>
-    <row r="695">
-      <c r="A695" t="inlineStr">
+    <row r="694">
+      <c r="A694" t="inlineStr">
         <is>
           <t xml:space="preserve">「ひらめき」إلهام
 イルハーム ['lhaam]
@@ -15071,19 +15049,19 @@
 2103 出典不明 </t>
         </is>
       </c>
-      <c r="B695" t="inlineStr">
+      <c r="B694" t="inlineStr">
         <is>
           <t>images/「ひらめき」_img1.jpg</t>
         </is>
       </c>
-      <c r="C695" t="inlineStr">
+      <c r="C694" t="inlineStr">
         <is>
           <t>アラビア語</t>
         </is>
       </c>
     </row>
-    <row r="696">
-      <c r="A696" t="inlineStr">
+    <row r="695">
+      <c r="A695" t="inlineStr">
         <is>
           <t xml:space="preserve">「Ibdaa／クリエイティビティ」
 إبداع
@@ -15092,19 +15070,19 @@
 2308 Ibdaa Design &amp; Decoration Office </t>
         </is>
       </c>
-      <c r="B696" t="inlineStr">
+      <c r="B695" t="inlineStr">
         <is>
           <t>images/「Ibdaa／クリエイティビティ」_img1.jpg</t>
         </is>
       </c>
-      <c r="C696" t="inlineStr">
+      <c r="C695" t="inlineStr">
         <is>
           <t>創造性 ,独自性</t>
         </is>
       </c>
     </row>
-    <row r="697">
-      <c r="A697" t="inlineStr">
+    <row r="696">
+      <c r="A696" t="inlineStr">
         <is>
           <t xml:space="preserve">「奮闘なくして進歩なし」
 بدون كفاح لايوجد تقدم
@@ -15114,19 +15092,19 @@
 2105 ROUYMS TUMBLR COM </t>
         </is>
       </c>
-      <c r="B697" t="inlineStr">
+      <c r="B696" t="inlineStr">
         <is>
           <t>images/「奮闘なくして進歩なし」_img1.jpg</t>
         </is>
       </c>
-      <c r="C697" t="inlineStr">
+      <c r="C696" t="inlineStr">
         <is>
           <t>努力 ,三角形</t>
         </is>
       </c>
     </row>
-    <row r="698">
-      <c r="A698" t="inlineStr">
+    <row r="697">
+      <c r="A697" t="inlineStr">
         <is>
           <t xml:space="preserve">「木に登れば熊の危険を避けられるとお考えなら、考え直しましょう！」 
 إن اعتقدت أنك بمنأى عن خطر الدب عند تسلق الأشجار.. راجع حساباتك
@@ -15134,19 +15112,19 @@
 2202 NatGeoMagArab </t>
         </is>
       </c>
-      <c r="B698" t="inlineStr">
+      <c r="B697" t="inlineStr">
         <is>
           <t>images/「木に登れば熊の危険を避けられるとお考.jpeg</t>
         </is>
       </c>
-      <c r="C698" t="inlineStr">
+      <c r="C697" t="inlineStr">
         <is>
           <t>クマ</t>
         </is>
       </c>
     </row>
-    <row r="699">
-      <c r="A699" t="inlineStr">
+    <row r="698">
+      <c r="A698" t="inlineStr">
         <is>
           <t xml:space="preserve">「卒業おめでとう」مبروك التخرج
 マブルーク・タカッルジ [mabruuk a^taKharruj]
@@ -15155,19 +15133,19 @@
 2308 https://instagram.com/fatoomworld </t>
         </is>
       </c>
-      <c r="B699" t="inlineStr">
+      <c r="B698" t="inlineStr">
         <is>
           <t>images/「卒業おめでとう」_img1.jpg</t>
         </is>
       </c>
-      <c r="C699" t="inlineStr">
+      <c r="C698" t="inlineStr">
         <is>
           <t>卒業 ,イラスト</t>
         </is>
       </c>
     </row>
-    <row r="700">
-      <c r="A700" t="inlineStr">
+    <row r="699">
+      <c r="A699" t="inlineStr">
         <is>
           <t xml:space="preserve">「停止距離の計算」
 حساب مسافة التوقف
@@ -15177,19 +15155,19 @@
 2109 assurance-auto-info </t>
         </is>
       </c>
-      <c r="B700" t="inlineStr">
+      <c r="B699" t="inlineStr">
         <is>
           <t>images/「停止距離の計算」_img1.jpg</t>
         </is>
       </c>
-      <c r="C700" t="inlineStr">
+      <c r="C699" t="inlineStr">
         <is>
           <t>保険 ,自動車</t>
         </is>
       </c>
     </row>
-    <row r="701">
-      <c r="A701" t="inlineStr">
+    <row r="700">
+      <c r="A700" t="inlineStr">
         <is>
           <t xml:space="preserve">「教師要らず：10日でフランス語会話」
 بدون معلم
@@ -15199,19 +15177,19 @@
 2308 englais-best com </t>
         </is>
       </c>
-      <c r="B701" t="inlineStr">
+      <c r="B700" t="inlineStr">
         <is>
           <t>images/「教師要らず：10日でフランス語会話」_img1.jpg</t>
         </is>
       </c>
-      <c r="C701" t="inlineStr">
+      <c r="C700" t="inlineStr">
         <is>
           <t>教師なし学習</t>
         </is>
       </c>
     </row>
-    <row r="702">
-      <c r="A702" t="inlineStr">
+    <row r="701">
+      <c r="A701" t="inlineStr">
         <is>
           <t xml:space="preserve">「衝突」تصادم
 タサードゥム [ta_saadum]
@@ -15220,19 +15198,19 @@
 1810 </t>
         </is>
       </c>
-      <c r="B702" t="inlineStr">
+      <c r="B701" t="inlineStr">
         <is>
           <t>images/「衝突」_img1.jpg</t>
         </is>
       </c>
-      <c r="C702" t="inlineStr">
+      <c r="C701" t="inlineStr">
         <is>
           <t>あらびあや</t>
         </is>
       </c>
     </row>
-    <row r="703">
-      <c r="A703" t="inlineStr">
+    <row r="702">
+      <c r="A702" t="inlineStr">
         <is>
           <t xml:space="preserve">「楽観主義」تَفَاؤُلٌ
 タファーウル [tafaa'ul(un)]
@@ -15241,19 +15219,19 @@
 1904 arabictypography com </t>
         </is>
       </c>
-      <c r="B703" t="inlineStr">
+      <c r="B702" t="inlineStr">
         <is>
           <t>images/「楽観主義」_img1.jpg</t>
         </is>
       </c>
-      <c r="C703" t="inlineStr">
+      <c r="C702" t="inlineStr">
         <is>
           <t>やわらか ,緑</t>
         </is>
       </c>
     </row>
-    <row r="704">
-      <c r="A704" t="inlineStr">
+    <row r="703">
+      <c r="A703" t="inlineStr">
         <is>
           <t xml:space="preserve">「シベリアジャコウジカは、絶滅の危機にあると見なされている」
 يعد "أيل المسك السيبيري" مهددًا بالانقراض
@@ -15261,19 +15239,19 @@
 2308 https://twitter.com/NatGeoMagArab/status/1320666649045790720 </t>
         </is>
       </c>
-      <c r="B704" t="inlineStr">
+      <c r="B703" t="inlineStr">
         <is>
           <t>images/「シベリアジャコウジカは、絶滅の危機に_img1.jpg,images/「シベリアジャコウジカは、絶滅の危機に_img2.jpg</t>
         </is>
       </c>
-      <c r="C704" t="inlineStr">
+      <c r="C703" t="inlineStr">
         <is>
           <t>手書き語学 ,シベリア</t>
         </is>
       </c>
     </row>
-    <row r="705">
-      <c r="A705" t="inlineStr">
+    <row r="704">
+      <c r="A704" t="inlineStr">
         <is>
           <t xml:space="preserve">「融合／折衷／フュージョン」
 انصهار
@@ -15282,38 +15260,38 @@
 1811 elmahdyart Instagram </t>
         </is>
       </c>
-      <c r="B705" t="inlineStr">
+      <c r="B704" t="inlineStr">
         <is>
           <t>images/「融合／折衷／フュージョン」_img1.jpg</t>
         </is>
       </c>
-      <c r="C705" t="inlineStr">
+      <c r="C704" t="inlineStr">
         <is>
           <t>カリグラフィー ,書道</t>
         </is>
       </c>
     </row>
-    <row r="706">
-      <c r="A706" t="inlineStr">
+    <row r="705">
+      <c r="A705" t="inlineStr">
         <is>
           <t xml:space="preserve">「この子供は、昼寝をしようとする母親を邪魔しているようだ」
 「場所はインドのトラ保護区、バンダウガル公園。トラは生態ピラミッドのトップの捕食動物だが、最もリスクの高い絶滅危惧種のひとつである」
 2308 https://twitter.com/natgeomagarab/status/1553681890665586689 </t>
         </is>
       </c>
-      <c r="B706" t="inlineStr">
+      <c r="B705" t="inlineStr">
         <is>
           <t>images/「この子供は、昼寝をしようとする母親を_img1.jpg,images/「この子供は、昼寝をしようとする母親を_img2.jpg</t>
         </is>
       </c>
-      <c r="C706" t="inlineStr">
+      <c r="C705" t="inlineStr">
         <is>
           <t>手書き語学 ,アラビア語 ,トラ</t>
         </is>
       </c>
     </row>
-    <row r="707">
-      <c r="A707" t="inlineStr">
+    <row r="706">
+      <c r="A706" t="inlineStr">
         <is>
           <t xml:space="preserve">「もし敬意が落ちたら、それと一緒に全部落ちるのだ」
 إن سقط الإحترام سقط معه كل شيء
@@ -15322,19 +15300,19 @@
 2109 出典不明 </t>
         </is>
       </c>
-      <c r="B707" t="inlineStr">
+      <c r="B706" t="inlineStr">
         <is>
           <t>images/「もし敬意が落ちたら、それと一緒に全部_img1.jpg</t>
         </is>
       </c>
-      <c r="C707" t="inlineStr">
+      <c r="C706" t="inlineStr">
         <is>
           <t>リスペクト ,落書き</t>
         </is>
       </c>
     </row>
-    <row r="708">
-      <c r="A708" t="inlineStr">
+    <row r="707">
+      <c r="A707" t="inlineStr">
         <is>
           <t xml:space="preserve">「エジプト特許庁」
 مكتب براءات الاختراع المصرى
@@ -15344,19 +15322,19 @@
 2312 </t>
         </is>
       </c>
-      <c r="B708" t="inlineStr">
+      <c r="B707" t="inlineStr">
         <is>
           <t>images/「エジプト特許庁」_img1.jpg</t>
         </is>
       </c>
-      <c r="C708" t="inlineStr">
+      <c r="C707" t="inlineStr">
         <is>
           <t>patent</t>
         </is>
       </c>
     </row>
-    <row r="709">
-      <c r="A709" t="inlineStr">
+    <row r="708">
+      <c r="A708" t="inlineStr">
         <is>
           <t xml:space="preserve">「選挙」إنتخابات
 インティカーバート [intiKhaabaat]
@@ -15365,19 +15343,19 @@
 2311 nna-leb gov lb </t>
         </is>
       </c>
-      <c r="B709" t="inlineStr">
+      <c r="B708" t="inlineStr">
         <is>
           <t>images/「選挙」_img1.jpg</t>
         </is>
       </c>
-      <c r="C709" t="inlineStr">
+      <c r="C708" t="inlineStr">
         <is>
           <t>選挙 ,投票</t>
         </is>
       </c>
     </row>
-    <row r="710">
-      <c r="A710" t="inlineStr">
+    <row r="709">
+      <c r="A709" t="inlineStr">
         <is>
           <t xml:space="preserve">「待ちぼうけ」إنتظار
 インティザール [inti_Dhaar]
@@ -15386,19 +15364,19 @@
 1809 in4sser.tumblr </t>
         </is>
       </c>
-      <c r="B710" t="inlineStr">
+      <c r="B709" t="inlineStr">
         <is>
           <t>images/「待ちぼうけ」_img1.jpg</t>
         </is>
       </c>
-      <c r="C710" t="inlineStr">
+      <c r="C709" t="inlineStr">
         <is>
           <t>遅すぎ ,辛抱</t>
         </is>
       </c>
     </row>
-    <row r="711">
-      <c r="A711" t="inlineStr">
+    <row r="710">
+      <c r="A710" t="inlineStr">
         <is>
           <t xml:space="preserve">「試験」إختبار
 イクティバール [iKhtibaar]
@@ -15407,19 +15385,19 @@
 2109 出典不明 </t>
         </is>
       </c>
-      <c r="B711" t="inlineStr">
+      <c r="B710" t="inlineStr">
         <is>
           <t>images/「試験」_img1.jpg</t>
         </is>
       </c>
-      <c r="C711" t="inlineStr">
+      <c r="C710" t="inlineStr">
         <is>
           <t>テスト ,考査</t>
         </is>
       </c>
     </row>
-    <row r="712">
-      <c r="A712" t="inlineStr">
+    <row r="711">
+      <c r="A711" t="inlineStr">
         <is>
           <t xml:space="preserve">「チャンネル登録」اشتراك
 イシティラーク [iShtiraak]
@@ -15428,19 +15406,19 @@
 2308 </t>
         </is>
       </c>
-      <c r="B712" t="inlineStr">
+      <c r="B711" t="inlineStr">
         <is>
           <t>images/「チャンネル登録」_img1.jpg</t>
         </is>
       </c>
-      <c r="C712" t="inlineStr">
+      <c r="C711" t="inlineStr">
         <is>
           <t>Subscribe ,YouTube</t>
         </is>
       </c>
     </row>
-    <row r="713">
-      <c r="A713" t="inlineStr">
+    <row r="712">
+      <c r="A712" t="inlineStr">
         <is>
           <t xml:space="preserve">「スマイル」ابتسام
 イブティサーム [ibtisaam]
@@ -15448,37 +15426,37 @@
 1903 behance Written-Visuals </t>
         </is>
       </c>
+      <c r="B712" t="inlineStr">
+        <is>
+          <t>images/「スマイル」_img1.jpg</t>
+        </is>
+      </c>
+      <c r="C712" t="inlineStr">
+        <is>
+          <t>スマイリー ,ツ</t>
+        </is>
+      </c>
+    </row>
+    <row r="713">
+      <c r="A713" t="inlineStr">
+        <is>
+          <t xml:space="preserve">「身体の一部として…」
+2308 https://twitter.com/NatGeoMagArab/status/1528292080337813504 </t>
+        </is>
+      </c>
       <c r="B713" t="inlineStr">
         <is>
-          <t>images/「スマイル」_img1.jpg</t>
+          <t>images/「身体の一部として…」_img1.jpg</t>
         </is>
       </c>
       <c r="C713" t="inlineStr">
         <is>
-          <t>スマイリー ,ツ</t>
+          <t>手書き語学 ,カンガルー</t>
         </is>
       </c>
     </row>
     <row r="714">
       <c r="A714" t="inlineStr">
-        <is>
-          <t xml:space="preserve">「身体の一部として…」
-2308 https://twitter.com/NatGeoMagArab/status/1528292080337813504 </t>
-        </is>
-      </c>
-      <c r="B714" t="inlineStr">
-        <is>
-          <t>images/「身体の一部として…」_img1.jpg</t>
-        </is>
-      </c>
-      <c r="C714" t="inlineStr">
-        <is>
-          <t>手書き語学 ,カンガルー</t>
-        </is>
-      </c>
-    </row>
-    <row r="715">
-      <c r="A715" t="inlineStr">
         <is>
           <t xml:space="preserve">「ディスカバリー」إكتشاف
 イクティシャーフ [iktiShaaf]
@@ -15486,19 +15464,19 @@
 2308 tephanegabrielli com </t>
         </is>
       </c>
-      <c r="B715" t="inlineStr">
+      <c r="B714" t="inlineStr">
         <is>
           <t>images/「ディスカバリー」_img1.jpg</t>
         </is>
       </c>
-      <c r="C715" t="inlineStr">
+      <c r="C714" t="inlineStr">
         <is>
           <t>discovery ,デザイン</t>
         </is>
       </c>
     </row>
-    <row r="716">
-      <c r="A716" t="inlineStr">
+    <row r="715">
+      <c r="A715" t="inlineStr">
         <is>
           <t xml:space="preserve">「重力波の発見は新しい窓を開いた」
 فتَح اكتشاف موجات الجاذبية نافذة جديدة
@@ -15506,19 +15484,19 @@
 2308 https://twitter.com/SciTalk2U/status/1454891943440289793 </t>
         </is>
       </c>
-      <c r="B716" t="inlineStr">
+      <c r="B715" t="inlineStr">
         <is>
           <t>images/「重力波の発見は新しい窓を開いた」_img1.jpg</t>
         </is>
       </c>
-      <c r="C716" t="inlineStr">
+      <c r="C715" t="inlineStr">
         <is>
           <t>手書き語学 ,アラビア語 ,重力波</t>
         </is>
       </c>
     </row>
-    <row r="717">
-      <c r="A717" t="inlineStr">
+    <row r="716">
+      <c r="A716" t="inlineStr">
         <is>
           <t xml:space="preserve">「微笑みに微笑み。先にした人の方が美しい」
 الإبتسامة بالإبتسامة والبادئ أجمل
@@ -15527,19 +15505,19 @@
 2104 出典不明 </t>
         </is>
       </c>
-      <c r="B717" t="inlineStr">
+      <c r="B716" t="inlineStr">
         <is>
           <t>images/「微笑みに微笑み。先にした人の方が美し_img1.jpg,images/「微笑みに微笑み。先にした人の方が美し_img2.jpg</t>
         </is>
       </c>
-      <c r="C717" t="inlineStr">
+      <c r="C716" t="inlineStr">
         <is>
           <t>スマイル ,名言</t>
         </is>
       </c>
     </row>
-    <row r="718">
-      <c r="A718" t="inlineStr">
+    <row r="717">
+      <c r="A717" t="inlineStr">
         <is>
           <t xml:space="preserve">「笑顔」ابتسامة
 イブティサーマ [ibtisaama(tun)]
@@ -15548,19 +15526,19 @@
 2308 satokomatsu, minne </t>
         </is>
       </c>
-      <c r="B718" t="inlineStr">
+      <c r="B717" t="inlineStr">
         <is>
           <t>images/「笑顔」_img1.jpg</t>
         </is>
       </c>
-      <c r="C718" t="inlineStr">
+      <c r="C717" t="inlineStr">
         <is>
           <t>スマイル ,ツ</t>
         </is>
       </c>
     </row>
-    <row r="719">
-      <c r="A719" t="inlineStr">
+    <row r="718">
+      <c r="A718" t="inlineStr">
         <is>
           <t xml:space="preserve">「信仰」ايمان
 イーマーン ['iimaan]
@@ -15569,19 +15547,19 @@
 2506 instagram com/p/6ST-WHOOkJ/ </t>
         </is>
       </c>
-      <c r="B719" t="inlineStr">
+      <c r="B718" t="inlineStr">
         <is>
           <t>images/「信仰」_img1.jpg</t>
         </is>
       </c>
-      <c r="C719" t="inlineStr">
+      <c r="C718" t="inlineStr">
         <is>
           <t>宗教 ,信念</t>
         </is>
       </c>
     </row>
-    <row r="720">
-      <c r="A720" t="inlineStr">
+    <row r="719">
+      <c r="A719" t="inlineStr">
         <is>
           <t xml:space="preserve">「放送」إذاعة
 イザーア ['iDhaa*a]
@@ -15590,19 +15568,19 @@
 2404 heemades, Instagram </t>
         </is>
       </c>
-      <c r="B720" t="inlineStr">
+      <c r="B719" t="inlineStr">
         <is>
           <t>images/「放送」_img1.jpg</t>
         </is>
       </c>
-      <c r="C720" t="inlineStr">
+      <c r="C719" t="inlineStr">
         <is>
           <t>デザイン ,ラジオ</t>
         </is>
       </c>
     </row>
-    <row r="721">
-      <c r="A721" t="inlineStr">
+    <row r="720">
+      <c r="A720" t="inlineStr">
         <is>
           <t xml:space="preserve">「かきとりのちから」
 مهاراتي الإملائية
@@ -15611,19 +15589,19 @@
 2308 iqrawaoktoub.wordpress com </t>
         </is>
       </c>
-      <c r="B721" t="inlineStr">
+      <c r="B720" t="inlineStr">
         <is>
           <t>images/「かきとりのちから」_img1.jpg</t>
         </is>
       </c>
-      <c r="C721" t="inlineStr">
+      <c r="C720" t="inlineStr">
         <is>
           <t>国語 ,教材</t>
         </is>
       </c>
     </row>
-    <row r="722">
-      <c r="A722" t="inlineStr">
+    <row r="721">
+      <c r="A721" t="inlineStr">
         <is>
           <t xml:space="preserve">「歴史を作った男たち」
 رجال صنعوا التاريخ
@@ -15633,38 +15611,38 @@
 2410 https://x.gd/Wl5rJ </t>
         </is>
       </c>
-      <c r="B722" t="inlineStr">
+      <c r="B721" t="inlineStr">
         <is>
           <t>images/「歴史を作った男たち」_img1.jpg</t>
         </is>
       </c>
-      <c r="C722" t="inlineStr">
+      <c r="C721" t="inlineStr">
         <is>
           <t>偉人</t>
         </is>
       </c>
     </row>
-    <row r="723">
-      <c r="A723" t="inlineStr">
+    <row r="722">
+      <c r="A722" t="inlineStr">
         <is>
           <t xml:space="preserve">「無限の宇宙を旅した光」
 「何百年もの末にジェイムズ・ウェッブ望遠鏡のレンズの上に落ち、我々に遠い宇宙の美しさを見せてくれる。最も純粋な形と最も素晴らしい姿で」
 2308 https://twitter.com/NatGeoMagArab/status/1557811592636485632 </t>
         </is>
       </c>
-      <c r="B723" t="inlineStr">
+      <c r="B722" t="inlineStr">
         <is>
           <t>images/「無限の宇宙を旅した光」_img1.jpg</t>
         </is>
       </c>
-      <c r="C723" t="inlineStr">
+      <c r="C722" t="inlineStr">
         <is>
           <t>手書き語学 ,宇宙</t>
         </is>
       </c>
     </row>
-    <row r="724">
-      <c r="A724" t="inlineStr">
+    <row r="723">
+      <c r="A723" t="inlineStr">
         <is>
           <t xml:space="preserve">「日本好きになり行きたくなる20項」
 عشرون شيئا يجعلك تحب اليابان وترغب في زيارتها
@@ -15673,19 +15651,19 @@
 2308 wattpad </t>
         </is>
       </c>
-      <c r="B724" t="inlineStr">
+      <c r="B723" t="inlineStr">
         <is>
           <t>images/「日本好きになり行きたくなる20項」_img1.jpg</t>
         </is>
       </c>
-      <c r="C724" t="inlineStr">
+      <c r="C723" t="inlineStr">
         <is>
           <t>اليابان ,Japan</t>
         </is>
       </c>
     </row>
-    <row r="725">
-      <c r="A725" t="inlineStr">
+    <row r="724">
+      <c r="A724" t="inlineStr">
         <is>
           <t xml:space="preserve">「ピッタリの瞬間に撮影され、ドラゴンが火を噴いているように見える」
 التُقطت في اللحظة المناسبة لتبدو مثل تنين ينفث اللهب
@@ -15693,19 +15671,19 @@
 2509 https://twitter.com/NatGeoMagArab/status/1588780660269150208 </t>
         </is>
       </c>
-      <c r="B725" t="inlineStr">
+      <c r="B724" t="inlineStr">
         <is>
           <t>images/「ピッタリの瞬間に撮影され、ドラゴンが_img1.jpg,images/ 「ピッタリの瞬間に撮影され、ドラゴンが_img2.jpg</t>
         </is>
       </c>
-      <c r="C725" t="inlineStr">
+      <c r="C724" t="inlineStr">
         <is>
           <t xml:space="preserve">ドラゴン </t>
         </is>
       </c>
     </row>
-    <row r="726">
-      <c r="A726" t="inlineStr">
+    <row r="725">
+      <c r="A725" t="inlineStr">
         <is>
           <t xml:space="preserve">「満足は不滅の宝である」
 القَناعَةُ كنز لا يَفنَى
@@ -15715,55 +15693,55 @@
 2308 kareem mrghani </t>
         </is>
       </c>
+      <c r="B725" t="inlineStr">
+        <is>
+          <t>images/「満足は不滅の宝である」_img1.jpg</t>
+        </is>
+      </c>
+      <c r="C725" t="inlineStr">
+        <is>
+          <t>幸福度</t>
+        </is>
+      </c>
+    </row>
+    <row r="726">
+      <c r="A726" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ゴシキセイガイインコ。
+2409 https://twitter.com/NatGeoMagArab/status/1600022262014676992 </t>
+        </is>
+      </c>
       <c r="B726" t="inlineStr">
         <is>
-          <t>images/「満足は不滅の宝である」_img1.jpg</t>
+          <t>images/ゴシキセイガイインコ。_img1.jpg</t>
         </is>
       </c>
       <c r="C726" t="inlineStr">
         <is>
-          <t>幸福度</t>
+          <t>手書き語学 ,アラビア語,オウム</t>
         </is>
       </c>
     </row>
     <row r="727">
       <c r="A727" t="inlineStr">
         <is>
-          <t xml:space="preserve">ゴシキセイガイインコ。
-2409 https://twitter.com/NatGeoMagArab/status/1600022262014676992 </t>
+          <t xml:space="preserve">モモンガ。
+2403 https://twitter.com/NatGeoMagArab/status/1552541872966344704 </t>
         </is>
       </c>
       <c r="B727" t="inlineStr">
         <is>
-          <t>images/ゴシキセイガイインコ。_img1.jpg</t>
+          <t>images/モモンガ。_img1.jpg,images/ モモンガ。_img2.jpg</t>
         </is>
       </c>
       <c r="C727" t="inlineStr">
         <is>
-          <t>手書き語学 ,アラビア語,オウム</t>
+          <t>手書き語学 ,アラビア語 ,モモンガ</t>
         </is>
       </c>
     </row>
     <row r="728">
       <c r="A728" t="inlineStr">
-        <is>
-          <t xml:space="preserve">モモンガ。
-2403 https://twitter.com/NatGeoMagArab/status/1552541872966344704 </t>
-        </is>
-      </c>
-      <c r="B728" t="inlineStr">
-        <is>
-          <t>images/モモンガ。_img1.jpg,images/ モモンガ。_img2.jpg</t>
-        </is>
-      </c>
-      <c r="C728" t="inlineStr">
-        <is>
-          <t>手書き語学 ,アラビア語 ,モモンガ</t>
-        </is>
-      </c>
-    </row>
-    <row r="729">
-      <c r="A729" t="inlineStr">
         <is>
           <t xml:space="preserve">「象の群れ。ドローンの音から逃げている」
 قطيع من الفيلة يفر هاربًا من صوت الدرون
@@ -15775,56 +15753,56 @@
 2009 https://twitter.com/NatGeoMagArab/status/1302970033627258881 </t>
         </is>
       </c>
+      <c r="B728" t="inlineStr">
+        <is>
+          <t>images/「象の群れ。ドローンの音から逃げている.jpg</t>
+        </is>
+      </c>
+      <c r="C728" t="inlineStr">
+        <is>
+          <t>ゾウ ,ドローン</t>
+        </is>
+      </c>
+    </row>
+    <row r="729">
+      <c r="A729" t="inlineStr">
+        <is>
+          <t xml:space="preserve">カルマン線。
+2308 https://twitter.com/NatGeoMagArab/status/1536436999522881536 </t>
+        </is>
+      </c>
       <c r="B729" t="inlineStr">
         <is>
-          <t>images/「象の群れ。ドローンの音から逃げている.jpg</t>
+          <t>images/カルマン線。_img1.jpg</t>
         </is>
       </c>
       <c r="C729" t="inlineStr">
         <is>
-          <t>ゾウ ,ドローン</t>
+          <t xml:space="preserve">手書き語学 ,アラビア語 ,宇宙 </t>
         </is>
       </c>
     </row>
     <row r="730">
       <c r="A730" t="inlineStr">
-        <is>
-          <t xml:space="preserve">カルマン線。
-2308 https://twitter.com/NatGeoMagArab/status/1536436999522881536 </t>
-        </is>
-      </c>
-      <c r="B730" t="inlineStr">
-        <is>
-          <t>images/カルマン線。_img1.jpg</t>
-        </is>
-      </c>
-      <c r="C730" t="inlineStr">
-        <is>
-          <t xml:space="preserve">手書き語学 ,アラビア語 ,宇宙 </t>
-        </is>
-      </c>
-    </row>
-    <row r="731">
-      <c r="A731" t="inlineStr">
         <is>
           <t xml:space="preserve">「恥ずかしがり屋のマヌルネコと暖かい朝の太陽光線」
 ⁦「二つの美しいもの」[Shay'-ayni jamiil-ayni] 属格：「物」( شيء )[Shay']・「美しい」( جميل )[jamiil]⁩
 2309 https://twitter.com/NatGeoMagArab/status/1697512148820504912 </t>
         </is>
       </c>
-      <c r="B731" t="inlineStr">
+      <c r="B730" t="inlineStr">
         <is>
           <t>images/「恥ずかしがり屋のマヌルネコと暖かい朝_img1.jpg</t>
         </is>
       </c>
-      <c r="C731" t="inlineStr">
+      <c r="C730" t="inlineStr">
         <is>
           <t>手書き語学 ,アラビア語 ,マヌルネコ</t>
         </is>
       </c>
     </row>
-    <row r="732">
-      <c r="A732" t="inlineStr">
+    <row r="731">
+      <c r="A731" t="inlineStr">
         <is>
           <t xml:space="preserve">「二回失敗しているペンギン」
 بطريق يفشل مرتين
@@ -15834,19 +15812,19 @@
 2308 https://twitter.com/NatGeoMagArab/status/1479483133766426626 </t>
         </is>
       </c>
-      <c r="B732" t="inlineStr">
+      <c r="B731" t="inlineStr">
         <is>
           <t>images/「二回失敗しているペンギン」_img1.jpg</t>
         </is>
       </c>
-      <c r="C732" t="inlineStr">
+      <c r="C731" t="inlineStr">
         <is>
           <t>ペンギン ,動物</t>
         </is>
       </c>
     </row>
-    <row r="733">
-      <c r="A733" t="inlineStr">
+    <row r="732">
+      <c r="A732" t="inlineStr">
         <is>
           <t xml:space="preserve">「2億光年の彼方できらめく炎と光」
 وهج ووميض يتلألأ على بعد 200 مليون سنة ضوئية
@@ -15857,15 +15835,15 @@
 2010 https://twitter.com/NatGeoMagArab/status/1303415502673342464 </t>
         </is>
       </c>
-      <c r="B733" t="inlineStr"/>
-      <c r="C733" t="inlineStr">
+      <c r="B732" t="inlineStr"/>
+      <c r="C732" t="inlineStr">
         <is>
           <t>宇宙 ,銀河</t>
         </is>
       </c>
     </row>
-    <row r="734">
-      <c r="A734" t="inlineStr">
+    <row r="733">
+      <c r="A733" t="inlineStr">
         <is>
           <t xml:space="preserve">「さまよう黒猫」قطة سوداء تجوب
 キッタトゥン・サウダーウ・タジューブ [qi^_tatun sawdaa'u ta-juub]
@@ -15874,19 +15852,19 @@
 2308 https://twitter.com/NatGeoMagArab/status/1532973177453760512 </t>
         </is>
       </c>
-      <c r="B734" t="inlineStr">
+      <c r="B733" t="inlineStr">
         <is>
           <t>images/「さまよう黒猫」_img1.jpg,images/ 「さまよう黒猫」_img2.jpg</t>
         </is>
       </c>
-      <c r="C734" t="inlineStr">
+      <c r="C733" t="inlineStr">
         <is>
           <t xml:space="preserve">手書き語学 ,モロッコ </t>
         </is>
       </c>
     </row>
-    <row r="735">
-      <c r="A735" t="inlineStr">
+    <row r="734">
+      <c r="A734" t="inlineStr">
         <is>
           <t xml:space="preserve">「サイのざらざらした皮を利用して自分の体を掻くネコ」
 قطة تستغل جلد الكركدن الخشن لحك جسدها
@@ -15895,19 +15873,19 @@
 2308 https://twitter.com/NatGeoMagArab/status/1476855740929216517 </t>
         </is>
       </c>
-      <c r="B735" t="inlineStr">
+      <c r="B734" t="inlineStr">
         <is>
           <t>images/「サイのざらざらした皮を利用して自分の_img1.jpg</t>
         </is>
       </c>
-      <c r="C735" t="inlineStr">
+      <c r="C734" t="inlineStr">
         <is>
           <t>サイ ,チェコ</t>
         </is>
       </c>
     </row>
-    <row r="736">
-      <c r="A736" t="inlineStr">
+    <row r="735">
+      <c r="A735" t="inlineStr">
         <is>
           <t xml:space="preserve">「沈まぬ太陽」شمس لا تغيب
 シャムス・ラー・タギーブ [Shams laa ta-Ghiib]
@@ -15916,19 +15894,19 @@
 2308 AHMED ELASSAL </t>
         </is>
       </c>
-      <c r="B736" t="inlineStr">
+      <c r="B735" t="inlineStr">
         <is>
           <t>images/「沈まぬ太陽」_img1.jpg</t>
         </is>
       </c>
-      <c r="C736" t="inlineStr">
+      <c r="C735" t="inlineStr">
         <is>
           <t>帝国 ,白夜</t>
         </is>
       </c>
     </row>
-    <row r="737">
-      <c r="A737" t="inlineStr">
+    <row r="736">
+      <c r="A736" t="inlineStr">
         <is>
           <t xml:space="preserve">「子供に食べさせている忍耐強い母親」
 أم صبورة تطعم صغيرها
@@ -15937,19 +15915,19 @@
 2308 https://twitter.com/natgeomagarab/status/1585572054509957120 </t>
         </is>
       </c>
-      <c r="B737" t="inlineStr">
+      <c r="B736" t="inlineStr">
         <is>
           <t>images/「子供に食べさせている忍耐強い母親」_img1.jpg</t>
         </is>
       </c>
-      <c r="C737" t="inlineStr">
+      <c r="C736" t="inlineStr">
         <is>
           <t>手書き語学 ,アラビア語 ,ミヤコドリ</t>
         </is>
       </c>
     </row>
-    <row r="738">
-      <c r="A738" t="inlineStr">
+    <row r="737">
+      <c r="A737" t="inlineStr">
         <is>
           <t xml:space="preserve">「コーヒーは繰り返さない恋物語」
 القهوة قصة عشق لن تتكرر
@@ -15959,19 +15937,19 @@
 2403 pin it/7tvd8Wc </t>
         </is>
       </c>
-      <c r="B738" t="inlineStr">
+      <c r="B737" t="inlineStr">
         <is>
           <t>images/「コーヒーは繰り返さない恋物語」_img1.jpg</t>
         </is>
       </c>
-      <c r="C738" t="inlineStr">
+      <c r="C737" t="inlineStr">
         <is>
           <t>コーヒー ,名言</t>
         </is>
       </c>
     </row>
-    <row r="739">
-      <c r="A739" t="inlineStr">
+    <row r="738">
+      <c r="A738" t="inlineStr">
         <is>
           <t xml:space="preserve">「星々で飾られた空。魅惑的な色合いで黄昏の美を満たしている」
 سماء مرصعة بالنجوم تضفي لمسة سحرية على جمال الشفق
@@ -15979,19 +15957,19 @@
 2010 https://twitter.com/NatGeoMagArab/status/1303777701975584768 </t>
         </is>
       </c>
-      <c r="B739" t="inlineStr">
+      <c r="B738" t="inlineStr">
         <is>
           <t>images/「星々で飾られた空。魅惑的な色合いで黄.png</t>
         </is>
       </c>
-      <c r="C739" t="inlineStr">
+      <c r="C738" t="inlineStr">
         <is>
           <t>星空 ,宇宙</t>
         </is>
       </c>
     </row>
-    <row r="740">
-      <c r="A740" t="inlineStr">
+    <row r="739">
+      <c r="A739" t="inlineStr">
         <is>
           <t xml:space="preserve">「国際宇宙ステーションからの写真。巨大な台風『ハイシェン（海神）』を映している」
 لقطات من محطة الفضاء الدولية تظهر إعصار "هايشن" الهائل
@@ -15999,19 +15977,19 @@
 2403 https://twitter.com/NatGeoMagArab/status/1302871968522235904 </t>
         </is>
       </c>
-      <c r="B740" t="inlineStr">
+      <c r="B739" t="inlineStr">
         <is>
           <t>images/「国際宇宙ステーションからの写真。巨大.png</t>
         </is>
       </c>
-      <c r="C740" t="inlineStr">
+      <c r="C739" t="inlineStr">
         <is>
           <t>台風</t>
         </is>
       </c>
     </row>
-    <row r="741">
-      <c r="A741" t="inlineStr">
+    <row r="740">
+      <c r="A740" t="inlineStr">
         <is>
           <t xml:space="preserve">「草を食む幸運な子羊たち」
 خراف محظوظة ترعى
@@ -16021,19 +15999,19 @@
 2308 https://twitter.com/NatGeoMagArab/status/1490211393554972676 </t>
         </is>
       </c>
-      <c r="B741" t="inlineStr">
+      <c r="B740" t="inlineStr">
         <is>
           <t>images/「草を食む幸運な子羊たち」_img1.jpg,images/ 「草を食む幸運な子羊たち」_img2.jpg</t>
         </is>
       </c>
-      <c r="C741" t="inlineStr">
+      <c r="C740" t="inlineStr">
         <is>
           <t>羊 ,アイルランド</t>
         </is>
       </c>
     </row>
-    <row r="742">
-      <c r="A742" t="inlineStr">
+    <row r="741">
+      <c r="A741" t="inlineStr">
         <is>
           <t xml:space="preserve">「お金で買えぬ10のもの」
 ١٠ أشياء لا تشترى بالمال
@@ -16043,19 +16021,19 @@
 2308 ayb124 </t>
         </is>
       </c>
-      <c r="B742" t="inlineStr">
+      <c r="B741" t="inlineStr">
         <is>
           <t>images/「お金で買えぬ10のもの」_img1.jpg</t>
         </is>
       </c>
-      <c r="C742" t="inlineStr">
+      <c r="C741" t="inlineStr">
         <is>
           <t>価値 ,購買</t>
         </is>
       </c>
     </row>
-    <row r="743">
-      <c r="A743" t="inlineStr">
+    <row r="742">
+      <c r="A742" t="inlineStr">
         <is>
           <t xml:space="preserve">「お金では買えないよ」
 هي أشْيَاءٌ لا تُشْتَرَى
@@ -16065,19 +16043,19 @@
 1906 mardy_zaawely, Instagram </t>
         </is>
       </c>
-      <c r="B743" t="inlineStr">
+      <c r="B742" t="inlineStr">
         <is>
           <t>images/「お金では買えないよ」_img1.jpg</t>
         </is>
       </c>
-      <c r="C743" t="inlineStr">
+      <c r="C742" t="inlineStr">
         <is>
           <t>マスターカード ,価値</t>
         </is>
       </c>
     </row>
-    <row r="744">
-      <c r="A744" t="inlineStr">
+    <row r="743">
+      <c r="A743" t="inlineStr">
         <is>
           <t xml:space="preserve">「好奇心旺盛なホッキョクギツネ」
 ثعلب قطبي يملؤه الفضول
@@ -16087,15 +16065,15 @@
 2308 https://twitter.com/natgeomagarab/status/1157592172968808449 </t>
         </is>
       </c>
-      <c r="B744" t="inlineStr"/>
-      <c r="C744" t="inlineStr">
+      <c r="B743" t="inlineStr"/>
+      <c r="C743" t="inlineStr">
         <is>
           <t>ファーストコンタクト ,キツネ</t>
         </is>
       </c>
     </row>
-    <row r="745">
-      <c r="A745" t="inlineStr">
+    <row r="744">
+      <c r="A744" t="inlineStr">
         <is>
           <t xml:space="preserve">「グレンダイザーのいる国は死にません」
 لنْ يَموتَ شَعبٌ لدَيهِ غرندايزر
@@ -16104,56 +16082,56 @@
 2308 https://www.aljarida.com/articles/1462241741574732100/ </t>
         </is>
       </c>
+      <c r="B744" t="inlineStr">
+        <is>
+          <t>images/「グレンダイザーのいる国は死にません」_img1.jpg</t>
+        </is>
+      </c>
+      <c r="C744" t="inlineStr">
+        <is>
+          <t>UFOロボ ,アニメ</t>
+        </is>
+      </c>
+    </row>
+    <row r="745">
+      <c r="A745" t="inlineStr">
+        <is>
+          <t xml:space="preserve">「凍結路面を運転中、彼女は嫌な場面に居合わせた」
+2408 https://twitter.com/NatGeoMagArab/status/1610305209657626625 </t>
+        </is>
+      </c>
       <c r="B745" t="inlineStr">
         <is>
-          <t>images/「グレンダイザーのいる国は死にません」_img1.jpg</t>
+          <t>images/「凍結路面を運転中、彼女は嫌な場面に居_img1.jpg</t>
         </is>
       </c>
       <c r="C745" t="inlineStr">
         <is>
-          <t>UFOロボ ,アニメ</t>
+          <t>手書き語学 ,アラビア語 ,路面凍結</t>
         </is>
       </c>
     </row>
     <row r="746">
       <c r="A746" t="inlineStr">
-        <is>
-          <t xml:space="preserve">「凍結路面を運転中、彼女は嫌な場面に居合わせた」
-2408 https://twitter.com/NatGeoMagArab/status/1610305209657626625 </t>
-        </is>
-      </c>
-      <c r="B746" t="inlineStr">
-        <is>
-          <t>images/「凍結路面を運転中、彼女は嫌な場面に居_img1.jpg</t>
-        </is>
-      </c>
-      <c r="C746" t="inlineStr">
-        <is>
-          <t>手書き語学 ,アラビア語 ,路面凍結</t>
-        </is>
-      </c>
-    </row>
-    <row r="747">
-      <c r="A747" t="inlineStr">
         <is>
           <t xml:space="preserve">「虹が美しさを加えている、アルパカという動物の美しいショット」
 ⁦「美しいショット」[laq_tatun jamiilatun]：「ショット」( لقطة )[laq_ta]：( ـلٌ )[-lun]・( ـقٌ )[-qun]・( ـطٌ )[-_tun]・( ـةٌ )[-tun]⁩
 2308 https://twitter.com/natgeomagarab/status/1155115655928004608 </t>
         </is>
       </c>
-      <c r="B747" t="inlineStr">
+      <c r="B746" t="inlineStr">
         <is>
           <t>images/「虹が美しさを加えている、アルパカとい_img1.jpg</t>
         </is>
       </c>
-      <c r="C747" t="inlineStr">
+      <c r="C746" t="inlineStr">
         <is>
           <t>モフモフ ,アルパカ</t>
         </is>
       </c>
     </row>
-    <row r="748">
-      <c r="A748" t="inlineStr">
+    <row r="747">
+      <c r="A747" t="inlineStr">
         <is>
           <t xml:space="preserve">「幸せは…全然思いもよらない所からやって来る」
 السعادة تأتينا من أماكن لم نكن نتوقعها أبداً
@@ -16162,19 +16140,19 @@
 2109 出典不明 </t>
         </is>
       </c>
-      <c r="B748" t="inlineStr">
+      <c r="B747" t="inlineStr">
         <is>
           <t>images/「幸せは…全然思いもよらない所からやっ_img1.jpg,images/ 「幸せは…全然思いもよらない所からやっ_img2.jpg</t>
         </is>
       </c>
-      <c r="C748" t="inlineStr">
+      <c r="C747" t="inlineStr">
         <is>
           <t>訪れ ,予想</t>
         </is>
       </c>
     </row>
-    <row r="749">
-      <c r="A749" t="inlineStr">
+    <row r="748">
+      <c r="A748" t="inlineStr">
         <is>
           <t xml:space="preserve">「あらゆる問題は、食べ物が解決してくれる」
 كل مشكلة ولها أكلة تحلها
@@ -16183,19 +16161,19 @@
 1909 ALQA AN 878 </t>
         </is>
       </c>
-      <c r="B749" t="inlineStr">
+      <c r="B748" t="inlineStr">
         <is>
           <t>images/「あらゆる問題は、食べ物が解決してくれ_img1.jpg</t>
         </is>
       </c>
-      <c r="C749" t="inlineStr">
+      <c r="C748" t="inlineStr">
         <is>
           <t>ストレス ,精神</t>
         </is>
       </c>
     </row>
-    <row r="750">
-      <c r="A750" t="inlineStr">
+    <row r="749">
+      <c r="A749" t="inlineStr">
         <is>
           <t xml:space="preserve">「冬で私が好きな物」
 أشياء أحبها بالشتاء
@@ -16205,19 +16183,19 @@
 2109 出典不明 </t>
         </is>
       </c>
-      <c r="B750" t="inlineStr">
+      <c r="B749" t="inlineStr">
         <is>
           <t>images/「冬で私が好きな物」_img1.jpg</t>
         </is>
       </c>
-      <c r="C750" t="inlineStr">
+      <c r="C749" t="inlineStr">
         <is>
           <t>季節 ,冬</t>
         </is>
       </c>
     </row>
-    <row r="751">
-      <c r="A751" t="inlineStr">
+    <row r="750">
+      <c r="A750" t="inlineStr">
         <is>
           <t xml:space="preserve">「お金で買うことの出来ない物」
 أشياء لا تستطيع شراءها بالمال
@@ -16227,19 +16205,19 @@
 2409 https://x.com/akhbarak/status/1038402708414373888 </t>
         </is>
       </c>
-      <c r="B751" t="inlineStr">
+      <c r="B750" t="inlineStr">
         <is>
           <t>images/「お金で買うことの出来ない物」_img1.jpg,images/ 「お金で買うことの出来ない物」_img2.jpg</t>
         </is>
       </c>
-      <c r="C751" t="inlineStr">
+      <c r="C750" t="inlineStr">
         <is>
           <t>ショッピング ,価値</t>
         </is>
       </c>
     </row>
-    <row r="752">
-      <c r="A752" t="inlineStr">
+    <row r="751">
+      <c r="A751" t="inlineStr">
         <is>
           <t xml:space="preserve">「私たちが愛する言葉」
 كلماتٌ نُحبّها
@@ -16249,19 +16227,19 @@
 2109 جليل خزعل </t>
         </is>
       </c>
-      <c r="B752" t="inlineStr">
+      <c r="B751" t="inlineStr">
         <is>
           <t>images/「私たちが愛する言葉」_img1.jpg</t>
         </is>
       </c>
-      <c r="C752" t="inlineStr">
+      <c r="C751" t="inlineStr">
         <is>
           <t>花 ,贈り物</t>
         </is>
       </c>
     </row>
-    <row r="753">
-      <c r="A753" t="inlineStr">
+    <row r="752">
+      <c r="A752" t="inlineStr">
         <is>
           <t xml:space="preserve">「お茶についてあなたが知らない10の事実」
 عشر معلومات لا تعرفها عن الشاي
@@ -16270,19 +16248,19 @@
 2012 http://ara.tv/6syq2 </t>
         </is>
       </c>
-      <c r="B753" t="inlineStr">
+      <c r="B752" t="inlineStr">
         <is>
           <t>images/「お茶についてあなたが知らない10の事_img1.jpg</t>
         </is>
       </c>
-      <c r="C753" t="inlineStr">
+      <c r="C752" t="inlineStr">
         <is>
           <t>神農</t>
         </is>
       </c>
     </row>
-    <row r="754">
-      <c r="A754" t="inlineStr">
+    <row r="753">
+      <c r="A753" t="inlineStr">
         <is>
           <t xml:space="preserve">「大きくなったウソ」
 الكذبة الّتي كبرت
@@ -16292,19 +16270,19 @@
 2509 سلسلة الحلزونة </t>
         </is>
       </c>
-      <c r="B754" t="inlineStr">
+      <c r="B753" t="inlineStr">
         <is>
           <t>images/「大きくなったウソ」_img1.jpg</t>
         </is>
       </c>
-      <c r="C754" t="inlineStr">
+      <c r="C753" t="inlineStr">
         <is>
           <t>絵本</t>
         </is>
       </c>
     </row>
-    <row r="755">
-      <c r="A755" t="inlineStr">
+    <row r="754">
+      <c r="A754" t="inlineStr">
         <is>
           <t xml:space="preserve">「自分に合った掃除機を買うには？」
 كيف تشتري المكنسة الكهربائية التي تناسبك؟
@@ -16313,19 +16291,19 @@
 2106 ts3a com </t>
         </is>
       </c>
-      <c r="B755" t="inlineStr">
+      <c r="B754" t="inlineStr">
         <is>
           <t>images/「自分に合った掃除機を買うには？」_img1.jpg</t>
         </is>
       </c>
-      <c r="C755" t="inlineStr">
+      <c r="C754" t="inlineStr">
         <is>
           <t>家電 ,掃除</t>
         </is>
       </c>
     </row>
-    <row r="756">
-      <c r="A756" t="inlineStr">
+    <row r="755">
+      <c r="A755" t="inlineStr">
         <is>
           <t xml:space="preserve">「仮にこれが批判の数としよう」
 لنفرض ان عدد الذين ينتقدونك
@@ -16336,19 +16314,19 @@
 2504 出典不明 </t>
         </is>
       </c>
-      <c r="B756" t="inlineStr">
+      <c r="B755" t="inlineStr">
         <is>
           <t>images/「仮にこれが批判の数としよう」_img1.jpg</t>
         </is>
       </c>
-      <c r="C756" t="inlineStr">
+      <c r="C755" t="inlineStr">
         <is>
           <t>アンチ</t>
         </is>
       </c>
     </row>
-    <row r="757">
-      <c r="A757" t="inlineStr">
+    <row r="756">
+      <c r="A756" t="inlineStr">
         <is>
           <t xml:space="preserve">「ここに見えるのは何？」
 ما الذي تراه هنا؟
@@ -16358,15 +16336,15 @@
 2204 https://twitter.com/NatGeoMagArab/status/1506933850617700352 </t>
         </is>
       </c>
-      <c r="B757" t="inlineStr"/>
-      <c r="C757" t="inlineStr">
+      <c r="B756" t="inlineStr"/>
+      <c r="C756" t="inlineStr">
         <is>
           <t xml:space="preserve">ペンギン </t>
         </is>
       </c>
     </row>
-    <row r="758">
-      <c r="A758" t="inlineStr">
+    <row r="757">
+      <c r="A757" t="inlineStr">
         <is>
           <t xml:space="preserve">「今日辛いこと、明日は平気だろう」
 ما يؤلم اليوم سيهون غدًا
@@ -16376,19 +16354,19 @@
 2308 basmahjeff </t>
         </is>
       </c>
-      <c r="B758" t="inlineStr">
+      <c r="B757" t="inlineStr">
         <is>
           <t>images/「今日辛いこと、明日は平気だろう」_img1.jpg</t>
         </is>
       </c>
-      <c r="C758" t="inlineStr">
+      <c r="C757" t="inlineStr">
         <is>
           <t>悩み ,達観</t>
         </is>
       </c>
     </row>
-    <row r="759">
-      <c r="A759" t="inlineStr">
+    <row r="758">
+      <c r="A758" t="inlineStr">
         <is>
           <t xml:space="preserve">「自分のすることを好きでなきゃ」
 عليك أن تحب ما تفعل
@@ -16397,19 +16375,19 @@
 1810 Ahmed Elhakeem </t>
         </is>
       </c>
-      <c r="B759" t="inlineStr">
+      <c r="B758" t="inlineStr">
         <is>
           <t>images/「自分のすることを好きでなきゃ」_img1.jpg</t>
         </is>
       </c>
-      <c r="C759" t="inlineStr">
+      <c r="C758" t="inlineStr">
         <is>
           <t>転職 ,かわいい</t>
         </is>
       </c>
     </row>
-    <row r="760">
-      <c r="A760" t="inlineStr">
+    <row r="759">
+      <c r="A759" t="inlineStr">
         <is>
           <t xml:space="preserve">「この地上に生き甲斐あり」
 على هذه الأرض ما يستحق الحياة
@@ -16419,19 +16397,19 @@
 2308 Mahmoud Gafar </t>
         </is>
       </c>
-      <c r="B760" t="inlineStr">
+      <c r="B759" t="inlineStr">
         <is>
           <t>images/「この地上に生き甲斐あり」_img1.jpg</t>
         </is>
       </c>
-      <c r="C760" t="inlineStr">
+      <c r="C759" t="inlineStr">
         <is>
           <t>詩</t>
         </is>
       </c>
     </row>
-    <row r="761">
-      <c r="A761" t="inlineStr">
+    <row r="760">
+      <c r="A760" t="inlineStr">
         <is>
           <t xml:space="preserve">「おそらく、あなたの求めるものはあるだろう」
 لعلَّ ما تَرجوهُ سيَكونُ
@@ -16441,19 +16419,19 @@
 2308 PIXEL Instagram </t>
         </is>
       </c>
-      <c r="B761" t="inlineStr">
+      <c r="B760" t="inlineStr">
         <is>
           <t>images/「おそらく、あなたの求めるものはあるだ_img1.jpg</t>
         </is>
       </c>
-      <c r="C761" t="inlineStr">
+      <c r="C760" t="inlineStr">
         <is>
           <t>願い ,信仰</t>
         </is>
       </c>
     </row>
-    <row r="762">
-      <c r="A762" t="inlineStr">
+    <row r="761">
+      <c r="A761" t="inlineStr">
         <is>
           <t xml:space="preserve">「オレンジの効能が何か知っていますか？」
 هل تعرف ما هي فوائد البرتقال؟
@@ -16463,19 +16441,19 @@
 2308 sadahadhramowt com </t>
         </is>
       </c>
-      <c r="B762" t="inlineStr">
+      <c r="B761" t="inlineStr">
         <is>
           <t>images/「オレンジの効能が何か知っていますか？_img1.jpg</t>
         </is>
       </c>
-      <c r="C762" t="inlineStr">
+      <c r="C761" t="inlineStr">
         <is>
           <t>オレンジ ,フルーツ</t>
         </is>
       </c>
     </row>
-    <row r="763">
-      <c r="A763" t="inlineStr">
+    <row r="762">
+      <c r="A762" t="inlineStr">
         <is>
           <t xml:space="preserve">「遊ぶパンダの光景より可愛いものがありますか？」
 هل هناك ما هو ألطف من مشاهدة الباندا وهي تلعب؟
@@ -16483,19 +16461,19 @@
 2308 https://twitter.com/NatGeoMagArab/status/1494612797858074626 </t>
         </is>
       </c>
-      <c r="B763" t="inlineStr">
+      <c r="B762" t="inlineStr">
         <is>
           <t>images/「遊ぶパンダの光景より可愛いものがあり_img1.jpg</t>
         </is>
       </c>
-      <c r="C763" t="inlineStr">
+      <c r="C762" t="inlineStr">
         <is>
           <t>パンダ ,モコモコ</t>
         </is>
       </c>
     </row>
-    <row r="764">
-      <c r="A764" t="inlineStr">
+    <row r="763">
+      <c r="A763" t="inlineStr">
         <is>
           <t xml:space="preserve">「大事なのは何者だったかじゃない。何者になるかだ」
 ليسَ المُهم ما كُنتَ بل مَا ستكون
@@ -16504,19 +16482,19 @@
 2308 出典不明 </t>
         </is>
       </c>
-      <c r="B764" t="inlineStr">
+      <c r="B763" t="inlineStr">
         <is>
           <t>images/「大事なのは何者だったかじゃない。何者_img1.jpg</t>
         </is>
       </c>
-      <c r="C764" t="inlineStr">
+      <c r="C763" t="inlineStr">
         <is>
           <t>自己実現 ,存在価値</t>
         </is>
       </c>
     </row>
-    <row r="765">
-      <c r="A765" t="inlineStr">
+    <row r="764">
+      <c r="A764" t="inlineStr">
         <is>
           <t xml:space="preserve">「あなたであれ。ありのままが美しいから」
 كُنْ أَنْتَ لأنك جميل كما أنت
@@ -16525,19 +16503,19 @@
 2308 IDREES DESIGN </t>
         </is>
       </c>
-      <c r="B765" t="inlineStr">
+      <c r="B764" t="inlineStr">
         <is>
           <t>images/「あなたであれ。ありのままが美しいから_img1.jpg</t>
         </is>
       </c>
-      <c r="C765" t="inlineStr">
+      <c r="C764" t="inlineStr">
         <is>
           <t>自己肯定 ,BeYourself</t>
         </is>
       </c>
     </row>
-    <row r="766">
-      <c r="A766" t="inlineStr">
+    <row r="765">
+      <c r="A765" t="inlineStr">
         <is>
           <t xml:space="preserve">「恐れの中に生きる者は決して自由になれない」
 من يعش في خوف لن يكون حرا أبدا
@@ -16546,19 +16524,19 @@
 2111 rjeem com </t>
         </is>
       </c>
-      <c r="B766" t="inlineStr">
+      <c r="B765" t="inlineStr">
         <is>
           <t>images/「恐れの中に生きる者は決して自由になれ_img1.jpg,images/ 「恐れの中に生きる者は決して自由になれ_img2.jpg</t>
         </is>
       </c>
-      <c r="C766" t="inlineStr">
+      <c r="C765" t="inlineStr">
         <is>
           <t>勇気 ,壁</t>
         </is>
       </c>
     </row>
-    <row r="767">
-      <c r="A767" t="inlineStr">
+    <row r="766">
+      <c r="A766" t="inlineStr">
         <is>
           <t xml:space="preserve">「己の翼を信じる者は己の重さを案じない」
 من يثق في جناحيه لن يهتم لوزنه
@@ -16567,19 +16545,19 @@
 2308 kmrghani </t>
         </is>
       </c>
-      <c r="B767" t="inlineStr">
+      <c r="B766" t="inlineStr">
         <is>
           <t>images/「己の翼を信じる者は己の重さを案じない_img1.jpg</t>
         </is>
       </c>
-      <c r="C767" t="inlineStr">
+      <c r="C766" t="inlineStr">
         <is>
           <t>自信</t>
         </is>
       </c>
     </row>
-    <row r="768">
-      <c r="A768" t="inlineStr">
+    <row r="767">
+      <c r="A767" t="inlineStr">
         <is>
           <t xml:space="preserve">「珈琲で一番大事な事！誰と飲むか？」
 الأهم من القهوة!! من ستشربها معه؟
@@ -16588,19 +16566,19 @@
 1812 gwid3.tumblr </t>
         </is>
       </c>
-      <c r="B768" t="inlineStr">
+      <c r="B767" t="inlineStr">
         <is>
           <t>images/「珈琲で一番大事な事！誰と飲むか？」_img1.jpg</t>
         </is>
       </c>
-      <c r="C768" t="inlineStr">
+      <c r="C767" t="inlineStr">
         <is>
           <t>コーヒー ,名言</t>
         </is>
       </c>
     </row>
-    <row r="769">
-      <c r="A769" t="inlineStr">
+    <row r="768">
+      <c r="A768" t="inlineStr">
         <is>
           <t xml:space="preserve">「人生は美しい、そう望んだ者には。」
 الحياة جَميلَة .. لمن أراد ذلك
@@ -16610,19 +16588,19 @@
 2109 出典不明 </t>
         </is>
       </c>
-      <c r="B769" t="inlineStr">
+      <c r="B768" t="inlineStr">
         <is>
           <t>images/「人生は美しい、そう望んだ者には。」_img1.jpg</t>
         </is>
       </c>
-      <c r="C769" t="inlineStr">
+      <c r="C768" t="inlineStr">
         <is>
           <t>名言 ,アート</t>
         </is>
       </c>
     </row>
-    <row r="770">
-      <c r="A770" t="inlineStr">
+    <row r="769">
+      <c r="A769" t="inlineStr">
         <is>
           <t xml:space="preserve">「ハム太郎って子を知ってるかい」
 هل تعرفون من هو هامتارو
@@ -16632,19 +16610,19 @@
 2109 </t>
         </is>
       </c>
-      <c r="B770" t="inlineStr">
+      <c r="B769" t="inlineStr">
         <is>
           <t>images/「ハム太郎って子を知ってるかい」_img1.jpg</t>
         </is>
       </c>
-      <c r="C770" t="inlineStr">
+      <c r="C769" t="inlineStr">
         <is>
           <t>オープニング ,ハム太郎</t>
         </is>
       </c>
     </row>
-    <row r="771">
-      <c r="A771" t="inlineStr">
+    <row r="770">
+      <c r="A770" t="inlineStr">
         <is>
           <t xml:space="preserve">「幸せを求める人もいれば、作る人もいる」
 هناك من يبحث عن السعادة وهناك من يصنعها
@@ -16653,19 +16631,19 @@
 2308 hindah tumblr </t>
         </is>
       </c>
-      <c r="B771" t="inlineStr">
+      <c r="B770" t="inlineStr">
         <is>
           <t>images/「幸せを求める人もいれば、作る人もいる_img1.jpg</t>
         </is>
       </c>
-      <c r="C771" t="inlineStr">
+      <c r="C770" t="inlineStr">
         <is>
           <t>幸せ ,名言 ,教訓</t>
         </is>
       </c>
     </row>
-    <row r="772">
-      <c r="A772" t="inlineStr">
+    <row r="771">
+      <c r="A771" t="inlineStr">
         <is>
           <t xml:space="preserve">「明白なるアラブの言葉によって」
 بلسان عربي مبين
@@ -16675,19 +16653,19 @@
 2109 Abdullah Barakat behance </t>
         </is>
       </c>
-      <c r="B772" t="inlineStr">
+      <c r="B771" t="inlineStr">
         <is>
           <t>images/「明白なるアラブの言葉によって」_img1.jpg</t>
         </is>
       </c>
-      <c r="C772" t="inlineStr">
+      <c r="C771" t="inlineStr">
         <is>
           <t>イスラム教 ,神聖</t>
         </is>
       </c>
     </row>
-    <row r="773">
-      <c r="A773" t="inlineStr">
+    <row r="772">
+      <c r="A772" t="inlineStr">
         <is>
           <t xml:space="preserve">「結婚前、結婚後」
 قبل الزواج، بعد الزواج
@@ -16697,19 +16675,19 @@
 2308 出典不明 </t>
         </is>
       </c>
-      <c r="B773" t="inlineStr">
+      <c r="B772" t="inlineStr">
         <is>
           <t>images/「結婚前、結婚後」_img1.jpg</t>
         </is>
       </c>
-      <c r="C773" t="inlineStr">
+      <c r="C772" t="inlineStr">
         <is>
           <t>BeforeAfter ,幸せ太り</t>
         </is>
       </c>
     </row>
-    <row r="774">
-      <c r="A774" t="inlineStr">
+    <row r="773">
+      <c r="A773" t="inlineStr">
         <is>
           <t xml:space="preserve">「驚きの価格で」بسعر رائع
 ビスィアル・ラーイア [bi-si*r raa'i*]
@@ -16718,19 +16696,19 @@
 2109 Jarir Bookstore </t>
         </is>
       </c>
-      <c r="B774" t="inlineStr">
+      <c r="B773" t="inlineStr">
         <is>
           <t>images/「驚きの価格で」_img1.jpg</t>
         </is>
       </c>
-      <c r="C774" t="inlineStr">
+      <c r="C773" t="inlineStr">
         <is>
           <t>広告 ,安値</t>
         </is>
       </c>
     </row>
-    <row r="775">
-      <c r="A775" t="inlineStr">
+    <row r="774">
+      <c r="A774" t="inlineStr">
         <is>
           <t xml:space="preserve">「我が魂と共に」مع نفسي
 マア・ナフスィ [ma*a nafs-iy]
@@ -16739,19 +16717,19 @@
 2110 出典不明 </t>
         </is>
       </c>
-      <c r="B775" t="inlineStr">
+      <c r="B774" t="inlineStr">
         <is>
           <t>images/「我が魂と共に」_img1.jpg</t>
         </is>
       </c>
-      <c r="C775" t="inlineStr">
+      <c r="C774" t="inlineStr">
         <is>
           <t>ソウル ,soul</t>
         </is>
       </c>
     </row>
-    <row r="776">
-      <c r="A776" t="inlineStr">
+    <row r="775">
+      <c r="A775" t="inlineStr">
         <is>
           <t xml:space="preserve">「暗い夜に」في ليلة مظلمة
  [fiy layla(tin) mu_Dhlima(tin)]
@@ -16760,19 +16738,19 @@
 2109 سلسلة الحلزونة </t>
         </is>
       </c>
-      <c r="B776" t="inlineStr">
+      <c r="B775" t="inlineStr">
         <is>
           <t>images/「暗い夜に」_img1.jpg</t>
         </is>
       </c>
-      <c r="C776" t="inlineStr">
+      <c r="C775" t="inlineStr">
         <is>
           <t>絵本</t>
         </is>
       </c>
     </row>
-    <row r="777">
-      <c r="A777" t="inlineStr">
+    <row r="776">
+      <c r="A776" t="inlineStr">
         <is>
           <t xml:space="preserve">「ゆっくりと」بشويش
 ビシワェーシ [bi-ShwySh]
@@ -16780,19 +16758,19 @@
 2109 出典不明 </t>
         </is>
       </c>
-      <c r="B777" t="inlineStr">
+      <c r="B776" t="inlineStr">
         <is>
           <t>images/「ゆっくりと」_img1.jpg</t>
         </is>
       </c>
-      <c r="C777" t="inlineStr">
+      <c r="C776" t="inlineStr">
         <is>
           <t>丸 ,円</t>
         </is>
       </c>
     </row>
-    <row r="778">
-      <c r="A778" t="inlineStr">
+    <row r="777">
+      <c r="A777" t="inlineStr">
         <is>
           <t xml:space="preserve">「この広い宇宙に…」
 في الكون الفسيح
@@ -16801,19 +16779,19 @@
 2308 wattpad </t>
         </is>
       </c>
-      <c r="B778" t="inlineStr">
+      <c r="B777" t="inlineStr">
         <is>
           <t>images/「この広い宇宙に…」_img1.jpg</t>
         </is>
       </c>
-      <c r="C778" t="inlineStr">
+      <c r="C777" t="inlineStr">
         <is>
           <t>アニメ ,宇宙</t>
         </is>
       </c>
     </row>
-    <row r="779">
-      <c r="A779" t="inlineStr">
+    <row r="778">
+      <c r="A778" t="inlineStr">
         <is>
           <t xml:space="preserve">「がんばって！」بالتوفيق
 ビッタウフィーク [bi^tawfiiq]
@@ -16821,19 +16799,19 @@
 2111 https://sites.google.com/site/mathmatic1905/ </t>
         </is>
       </c>
-      <c r="B779" t="inlineStr">
+      <c r="B778" t="inlineStr">
         <is>
           <t>images/「がんばって！」_img1.jpg</t>
         </is>
       </c>
-      <c r="C779" t="inlineStr">
+      <c r="C778" t="inlineStr">
         <is>
           <t>アラビア語</t>
         </is>
       </c>
     </row>
-    <row r="780">
-      <c r="A780" t="inlineStr">
+    <row r="779">
+      <c r="A779" t="inlineStr">
         <is>
           <t xml:space="preserve">「インターステラー」بين النجوم
 バイナ_ンヌジューム [bayna ^nujuum]
@@ -16841,19 +16819,19 @@
 2308 kmrghani </t>
         </is>
       </c>
-      <c r="B780" t="inlineStr">
+      <c r="B779" t="inlineStr">
         <is>
           <t>images/「インターステラー」_img1.jpg</t>
         </is>
       </c>
-      <c r="C780" t="inlineStr">
+      <c r="C779" t="inlineStr">
         <is>
           <t>映画 ,宇宙</t>
         </is>
       </c>
     </row>
-    <row r="781">
-      <c r="A781" t="inlineStr">
+    <row r="780">
+      <c r="A780" t="inlineStr">
         <is>
           <t xml:space="preserve">「アラビア語で」بالعربية
 ビ_ルアラビーヤ [bi-l-*arabiyya]
@@ -16862,19 +16840,19 @@
 1811 </t>
         </is>
       </c>
-      <c r="B781" t="inlineStr">
+      <c r="B780" t="inlineStr">
         <is>
           <t>images/「アラビア語で」_img1.jpg</t>
         </is>
       </c>
-      <c r="C781" t="inlineStr">
+      <c r="C780" t="inlineStr">
         <is>
           <t>ニュース ,CNN</t>
         </is>
       </c>
     </row>
-    <row r="782">
-      <c r="A782" t="inlineStr">
+    <row r="781">
+      <c r="A781" t="inlineStr">
         <is>
           <t xml:space="preserve">「17世紀に発明されて以来…」
 منذ اختراعه بالقرن السابع عشر
@@ -16882,19 +16860,19 @@
 2308 https://twitter.com/SciTalk2U/status/1450888395815854080 </t>
         </is>
       </c>
-      <c r="B782" t="inlineStr">
+      <c r="B781" t="inlineStr">
         <is>
           <t>images/「17世紀に発明されて以来…」_img1.jpg</t>
         </is>
       </c>
-      <c r="C782" t="inlineStr">
+      <c r="C781" t="inlineStr">
         <is>
           <t>手書き語学 ,アラビア語 ,望遠鏡</t>
         </is>
       </c>
     </row>
-    <row r="783">
-      <c r="A783" t="inlineStr">
+    <row r="782">
+      <c r="A782" t="inlineStr">
         <is>
           <t xml:space="preserve">「私できるよ」إنّني أستطيع
 インナニー・アスタティーウ ['inna-niy 'a-sta_tii*u]
@@ -16903,19 +16881,19 @@
 2412 سلسلة الحلزونة </t>
         </is>
       </c>
-      <c r="B783" t="inlineStr">
+      <c r="B782" t="inlineStr">
         <is>
           <t>images/「私できるよ」_img1.jpg</t>
         </is>
       </c>
-      <c r="C783" t="inlineStr">
+      <c r="C782" t="inlineStr">
         <is>
           <t>絵本 ,こども</t>
         </is>
       </c>
     </row>
-    <row r="784">
-      <c r="A784" t="inlineStr">
+    <row r="783">
+      <c r="A783" t="inlineStr">
         <is>
           <t xml:space="preserve">「問題なし」مافيش مشكلة
 マフィーシムシュキラ [ma-fy-Sh muShkila]
@@ -16924,19 +16902,19 @@
 2109 tanzerin.theshop </t>
         </is>
       </c>
-      <c r="B784" t="inlineStr">
+      <c r="B783" t="inlineStr">
         <is>
           <t>images/「問題なし」_img1.jpg</t>
         </is>
       </c>
-      <c r="C784" t="inlineStr">
+      <c r="C783" t="inlineStr">
         <is>
           <t>シャツ ,キッズ</t>
         </is>
       </c>
     </row>
-    <row r="785">
-      <c r="A785" t="inlineStr">
+    <row r="784">
+      <c r="A784" t="inlineStr">
         <is>
           <t xml:space="preserve">「不可能はない」مفيش مستحيل
 マフィーシ・ムスタヒール [ma-fy-Sh mustaHiil]
@@ -16945,19 +16923,19 @@
 2109 أموج </t>
         </is>
       </c>
-      <c r="B785" t="inlineStr">
+      <c r="B784" t="inlineStr">
         <is>
           <t>images/「不可能はない」_img1.jpg</t>
         </is>
       </c>
-      <c r="C785" t="inlineStr">
+      <c r="C784" t="inlineStr">
         <is>
           <t>ポジティブ ,挑戦</t>
         </is>
       </c>
     </row>
-    <row r="786">
-      <c r="A786" t="inlineStr">
+    <row r="785">
+      <c r="A785" t="inlineStr">
         <is>
           <t xml:space="preserve">「等々」إلخ
 イラク ['ilaKh]
@@ -16966,19 +16944,19 @@
 2201 出典不明 </t>
         </is>
       </c>
-      <c r="B786" t="inlineStr">
+      <c r="B785" t="inlineStr">
         <is>
           <t>images/「等々」_img1.jpg</t>
         </is>
       </c>
-      <c r="C786" t="inlineStr">
+      <c r="C785" t="inlineStr">
         <is>
           <t>etc ,とんち</t>
         </is>
       </c>
     </row>
-    <row r="787">
-      <c r="A787" t="inlineStr">
+    <row r="786">
+      <c r="A786" t="inlineStr">
         <is>
           <t xml:space="preserve">⁦「調子どう？」⁩شلونَك؟
 シュローナク？ [Sh-loon-ak?]
@@ -16987,19 +16965,19 @@
 2202 Jozoor Team. </t>
         </is>
       </c>
-      <c r="B787" t="inlineStr">
+      <c r="B786" t="inlineStr">
         <is>
           <t>images/⁦「調子どう？」⁩_img1.jpg</t>
         </is>
       </c>
-      <c r="C787" t="inlineStr">
+      <c r="C786" t="inlineStr">
         <is>
           <t>洒落 ,ルービックキューブ</t>
         </is>
       </c>
     </row>
-    <row r="788">
-      <c r="A788" t="inlineStr">
+    <row r="787">
+      <c r="A787" t="inlineStr">
         <is>
           <t xml:space="preserve">「行くな」ماتروحش
 マトロホシ [ma-troH-Sh]
@@ -17008,19 +16986,19 @@
 2411 triiq tumblr </t>
         </is>
       </c>
-      <c r="B788" t="inlineStr">
+      <c r="B787" t="inlineStr">
         <is>
           <t>images/「行くな」_img1.jpg</t>
         </is>
       </c>
-      <c r="C788" t="inlineStr">
+      <c r="C787" t="inlineStr">
         <is>
           <t>ロゴ ,デザイン ,嵐</t>
         </is>
       </c>
     </row>
-    <row r="789">
-      <c r="A789" t="inlineStr">
+    <row r="788">
+      <c r="A788" t="inlineStr">
         <is>
           <t xml:space="preserve">⁦「元気？」⁩شلونَك؟
 シュローナク？ [Sh-loon-ak?]
@@ -17031,19 +17009,19 @@
 2202 出典不明 </t>
         </is>
       </c>
-      <c r="B789" t="inlineStr">
+      <c r="B788" t="inlineStr">
         <is>
           <t>images/⁦「元気？」⁩_img1.jpg</t>
         </is>
       </c>
-      <c r="C789" t="inlineStr">
+      <c r="C788" t="inlineStr">
         <is>
           <t>洒落 ,挨拶</t>
         </is>
       </c>
     </row>
-    <row r="790">
-      <c r="A790" t="inlineStr">
+    <row r="789">
+      <c r="A789" t="inlineStr">
         <is>
           <t xml:space="preserve">「気分が良いぞう」I فيل GOOD
 アイ・フィール・グッド [ai fiyl gud]
@@ -17052,19 +17030,19 @@
 2308 出典不明 </t>
         </is>
       </c>
-      <c r="B790" t="inlineStr">
+      <c r="B789" t="inlineStr">
         <is>
           <t>images/「気分が良いぞう」_img1.jpg</t>
         </is>
       </c>
-      <c r="C790" t="inlineStr">
+      <c r="C789" t="inlineStr">
         <is>
           <t>洒落 ,和訳</t>
         </is>
       </c>
     </row>
-    <row r="791">
-      <c r="A791" t="inlineStr">
+    <row r="790">
+      <c r="A790" t="inlineStr">
         <is>
           <t xml:space="preserve">「レットイットゴー／let it go」
 ليت اِت غو
@@ -17073,19 +17051,19 @@
 2109 出典不明 </t>
         </is>
       </c>
-      <c r="B791" t="inlineStr">
+      <c r="B790" t="inlineStr">
         <is>
           <t>images/「レットイットゴー／let it go_img1.jpg</t>
         </is>
       </c>
-      <c r="C791" t="inlineStr">
+      <c r="C790" t="inlineStr">
         <is>
           <t>折衷 ,アナ雪</t>
         </is>
       </c>
     </row>
-    <row r="792">
-      <c r="A792" t="inlineStr">
+    <row r="791">
+      <c r="A791" t="inlineStr">
         <is>
           <t xml:space="preserve">「ようこそ」اهلا وسهلا
 アハラン・ワサハラン ['ahlan wa-sahlan]
@@ -17093,19 +17071,19 @@
 2106 behance Anwar Al Eissa </t>
         </is>
       </c>
-      <c r="B792" t="inlineStr">
+      <c r="B791" t="inlineStr">
         <is>
           <t>images/「ようこそ」_img1.jpg</t>
         </is>
       </c>
-      <c r="C792" t="inlineStr">
+      <c r="C791" t="inlineStr">
         <is>
           <t>アラビア語</t>
         </is>
       </c>
     </row>
-    <row r="793">
-      <c r="A793" t="inlineStr">
+    <row r="792">
+      <c r="A792" t="inlineStr">
         <is>
           <t xml:space="preserve">「まぁ何というサプライズでしょう」
 يا لها من مفاجأة
@@ -17116,19 +17094,19 @@
 2108 neelwafurat com </t>
         </is>
       </c>
-      <c r="B793" t="inlineStr">
+      <c r="B792" t="inlineStr">
         <is>
           <t>images/「まぁ何というサプライズでしょう」_img1.jpg</t>
         </is>
       </c>
-      <c r="C793" t="inlineStr">
+      <c r="C792" t="inlineStr">
         <is>
           <t>中国語 ,学習</t>
         </is>
       </c>
     </row>
-    <row r="794">
-      <c r="A794" t="inlineStr">
+    <row r="793">
+      <c r="A793" t="inlineStr">
         <is>
           <t xml:space="preserve">「ハックション」اتشوو
 アチュー！ ['aatShuu]
@@ -17136,19 +17114,19 @@
 1811 </t>
         </is>
       </c>
-      <c r="B794" t="inlineStr">
+      <c r="B793" t="inlineStr">
         <is>
           <t>images/「ハックション」_img1.jpg</t>
         </is>
       </c>
-      <c r="C794" t="inlineStr">
+      <c r="C793" t="inlineStr">
         <is>
           <t>あらびあや</t>
         </is>
       </c>
     </row>
-    <row r="795">
-      <c r="A795" t="inlineStr">
+    <row r="794">
+      <c r="A794" t="inlineStr">
         <is>
           <t xml:space="preserve">「スブハーナッラー」「アルハムドゥリッラー」「アッラーアクバル」
 سبحان الله
@@ -17159,19 +17137,19 @@
 2308 dribbble com </t>
         </is>
       </c>
-      <c r="B795" t="inlineStr">
+      <c r="B794" t="inlineStr">
         <is>
           <t>images/「スブハーナッラー」「アルハムドゥリッ_img1.jpg</t>
         </is>
       </c>
-      <c r="C795" t="inlineStr">
+      <c r="C794" t="inlineStr">
         <is>
           <t>四角 ,コンパクト</t>
         </is>
       </c>
     </row>
-    <row r="796">
-      <c r="A796" t="inlineStr">
+    <row r="795">
+      <c r="A795" t="inlineStr">
         <is>
           <t xml:space="preserve">「すごく美味しい！」لذيذ جدًا
 ラズィーズ・ジッダン [laDhiiDh jiddan]
@@ -17180,19 +17158,19 @@
 2109 goodreads com </t>
         </is>
       </c>
-      <c r="B796" t="inlineStr">
+      <c r="B795" t="inlineStr">
         <is>
           <t>images/「すごく美味しい！」_img1.jpg</t>
         </is>
       </c>
-      <c r="C796" t="inlineStr">
+      <c r="C795" t="inlineStr">
         <is>
           <t>フレーズ ,感想</t>
         </is>
       </c>
     </row>
-    <row r="797">
-      <c r="A797" t="inlineStr">
+    <row r="796">
+      <c r="A796" t="inlineStr">
         <is>
           <t xml:space="preserve">「しとしと、雨」تك تك يا مطر
 ティクティク [tik tik yaa ma_tar]
@@ -17201,19 +17179,19 @@
 2308 出典不明 </t>
         </is>
       </c>
-      <c r="B797" t="inlineStr">
+      <c r="B796" t="inlineStr">
         <is>
           <t>images/「しとしと、雨」_img1.jpg</t>
         </is>
       </c>
-      <c r="C797" t="inlineStr">
+      <c r="C796" t="inlineStr">
         <is>
           <t>天気 ,梅雨</t>
         </is>
       </c>
     </row>
-    <row r="798">
-      <c r="A798" t="inlineStr">
+    <row r="797">
+      <c r="A797" t="inlineStr">
         <is>
           <t xml:space="preserve">「さかさま」رأساً على عقب
 ラッアサン・アラー・アケブ [ra'san *alaa *aqib]
@@ -17221,19 +17199,19 @@
 2109 出典不明 </t>
         </is>
       </c>
-      <c r="B798" t="inlineStr">
+      <c r="B797" t="inlineStr">
         <is>
           <t>images/「さかさま」_img1.jpg</t>
         </is>
       </c>
-      <c r="C798" t="inlineStr">
+      <c r="C797" t="inlineStr">
         <is>
           <t>壁 ,上下</t>
         </is>
       </c>
     </row>
-    <row r="799">
-      <c r="A799" t="inlineStr">
+    <row r="798">
+      <c r="A798" t="inlineStr">
         <is>
           <t xml:space="preserve">「エジプトよどこへ行った」
 فينك يا مصر؟
@@ -17243,19 +17221,19 @@
 1809 shehabfawzy1.tumblr </t>
         </is>
       </c>
-      <c r="B799" t="inlineStr">
+      <c r="B798" t="inlineStr">
         <is>
           <t>images/「エジプトよどこへ行った」_img1.jpg</t>
         </is>
       </c>
-      <c r="C799" t="inlineStr">
+      <c r="C798" t="inlineStr">
         <is>
           <t>ピラミッド ,歴史</t>
         </is>
       </c>
     </row>
-    <row r="800">
-      <c r="A800" t="inlineStr">
+    <row r="799">
+      <c r="A799" t="inlineStr">
         <is>
           <t xml:space="preserve">「ありがとう」شكراً
 シュクラン [Shukran]
@@ -17263,19 +17241,19 @@
 2109 出典不明 </t>
         </is>
       </c>
-      <c r="B800" t="inlineStr">
+      <c r="B799" t="inlineStr">
         <is>
           <t>images/「ありがとう」_img1.jpg</t>
         </is>
       </c>
-      <c r="C800" t="inlineStr">
+      <c r="C799" t="inlineStr">
         <is>
           <t>挨拶 ,文字</t>
         </is>
       </c>
     </row>
-    <row r="801">
-      <c r="A801" t="inlineStr">
+    <row r="800">
+      <c r="A800" t="inlineStr">
         <is>
           <t xml:space="preserve">「昼寝の時間だ」
 إنه وقت القيلولة
@@ -17284,12 +17262,12 @@
 2501 https://x.com/NatGeoMagArab/status/1858049951579910486 </t>
         </is>
       </c>
-      <c r="B801" t="inlineStr">
+      <c r="B800" t="inlineStr">
         <is>
           <t>images/「昼寝の時間だ」_img1.jpg</t>
         </is>
       </c>
-      <c r="C801" t="inlineStr">
+      <c r="C800" t="inlineStr">
         <is>
           <t>手書き語学 ,アラビア語 ,ペンギン</t>
         </is>

--- a/posts.xlsx
+++ b/posts.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C800"/>
+  <dimension ref="A1:C799"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -14443,25 +14443,6 @@
     <row r="666">
       <c r="A666" t="inlineStr">
         <is>
-          <t xml:space="preserve">「お気に入りのおもちゃには触らせない」
-⁦「彼は〜を許さない」[laa ya-smaHu bi-]：「彼は許す」( يسمح )[ya-smaH(u)]：「許した」( سمح )[samaHa]：( سَ )[sa]・( مَ )[ma]・( حَ )[Ha]⁩
-2209 https://pic.twitter.com/qWcIPB3fz2 </t>
-        </is>
-      </c>
-      <c r="B666" t="inlineStr">
-        <is>
-          <t>images/「お気に入りのおもちゃには触らせない」_img1.jpg</t>
-        </is>
-      </c>
-      <c r="C666" t="inlineStr">
-        <is>
-          <t>パンダ ,ボール</t>
-        </is>
-      </c>
-    </row>
-    <row r="667">
-      <c r="A667" t="inlineStr">
-        <is>
           <t xml:space="preserve">「名探偵コナン」المحقق كونان
 アルムハッキク・コナン [al-muHaqqiq Conan]
 ⁦「調査官／探偵」( محقق )[muHaqqiq]：ン ( ن )[n]⁩
@@ -14469,19 +14450,19 @@
 1809 wikipedia </t>
         </is>
       </c>
-      <c r="B667" t="inlineStr">
+      <c r="B666" t="inlineStr">
         <is>
           <t>images/「名探偵コナン」_img1.jpg</t>
         </is>
       </c>
-      <c r="C667" t="inlineStr">
+      <c r="C666" t="inlineStr">
         <is>
           <t>江戸川コナン ,ロゴ</t>
         </is>
       </c>
     </row>
-    <row r="668">
-      <c r="A668" t="inlineStr">
+    <row r="667">
+      <c r="A667" t="inlineStr">
         <is>
           <t xml:space="preserve">「イードおめでとう」عيد مبارك
 イード・ムバーラク [*iid mubaarak]
@@ -14489,19 +14470,19 @@
 2308 出典不明 </t>
         </is>
       </c>
-      <c r="B668" t="inlineStr">
+      <c r="B667" t="inlineStr">
         <is>
           <t>images/「イードおめでとう」_img1.jpg</t>
         </is>
       </c>
-      <c r="C668" t="inlineStr">
+      <c r="C667" t="inlineStr">
         <is>
           <t>عيد ,アラビア語</t>
         </is>
       </c>
     </row>
-    <row r="669">
-      <c r="A669" t="inlineStr">
+    <row r="668">
+      <c r="A668" t="inlineStr">
         <is>
           <t xml:space="preserve">「戦士」محارب
 ムハーリブ [muHaarib]
@@ -14510,19 +14491,19 @@
 1809 abudinges.tumblr </t>
         </is>
       </c>
-      <c r="B669" t="inlineStr">
+      <c r="B668" t="inlineStr">
         <is>
           <t>images/「戦士」_img1.jpg</t>
         </is>
       </c>
-      <c r="C669" t="inlineStr">
+      <c r="C668" t="inlineStr">
         <is>
           <t>ロゴ ,赤</t>
         </is>
       </c>
     </row>
-    <row r="670">
-      <c r="A670" t="inlineStr">
+    <row r="669">
+      <c r="A669" t="inlineStr">
         <is>
           <t xml:space="preserve">「ライブ」بث مباشر
 バッス・ムバーシル [ba^Th(un) mubaaShir(un)]
@@ -14531,19 +14512,19 @@
 2308 beIN SPORTS </t>
         </is>
       </c>
-      <c r="B670" t="inlineStr">
+      <c r="B669" t="inlineStr">
         <is>
           <t>images/「ライブ」_img1.jpg</t>
         </is>
       </c>
-      <c r="C670" t="inlineStr">
+      <c r="C669" t="inlineStr">
         <is>
           <t xml:space="preserve">生放送 ,試合 </t>
         </is>
       </c>
     </row>
-    <row r="671">
-      <c r="A671" t="inlineStr">
+    <row r="670">
+      <c r="A670" t="inlineStr">
         <is>
           <t xml:space="preserve">「信者」مُؤْمِنٌ
 ムッミン [mu'min(un)]
@@ -14552,19 +14533,19 @@
 2106 出典不明 </t>
         </is>
       </c>
-      <c r="B671" t="inlineStr">
+      <c r="B670" t="inlineStr">
         <is>
           <t>images/「信者」_img1.jpg</t>
         </is>
       </c>
-      <c r="C671" t="inlineStr">
+      <c r="C670" t="inlineStr">
         <is>
           <t>明暗 ,信仰</t>
         </is>
       </c>
     </row>
-    <row r="672">
-      <c r="A672" t="inlineStr">
+    <row r="671">
+      <c r="A671" t="inlineStr">
         <is>
           <t xml:space="preserve">「開⇔閉」
 مفتوح
@@ -14575,19 +14556,19 @@
 2312 Hussein Safina, behance </t>
         </is>
       </c>
-      <c r="B672" t="inlineStr">
+      <c r="B671" t="inlineStr">
         <is>
           <t>images/「開⇔閉」_img1.jpg</t>
         </is>
       </c>
-      <c r="C672" t="inlineStr">
+      <c r="C671" t="inlineStr">
         <is>
           <t>オープンマインド ,トグル</t>
         </is>
       </c>
     </row>
-    <row r="673">
-      <c r="A673" t="inlineStr">
+    <row r="672">
+      <c r="A672" t="inlineStr">
         <is>
           <t xml:space="preserve">「予想外な結末！」
 نهاية غير متوقعة
@@ -14595,19 +14576,19 @@
 2308 https://twitter.com/NatGeoMagArab/status/1159011433444593665 </t>
         </is>
       </c>
-      <c r="B673" t="inlineStr">
+      <c r="B672" t="inlineStr">
         <is>
           <t>images/「予想外な結末！」_img1.jpg</t>
         </is>
       </c>
-      <c r="C673" t="inlineStr">
+      <c r="C672" t="inlineStr">
         <is>
           <t>手書き語学 ,アラビア語 ,ウサギ</t>
         </is>
       </c>
     </row>
-    <row r="674">
-      <c r="A674" t="inlineStr">
+    <row r="673">
+      <c r="A673" t="inlineStr">
         <is>
           <t xml:space="preserve">「ベイルート・アニメイテッド」
 بیروت متحرّکة
@@ -14617,19 +14598,19 @@
 2308 arabic_script Instagram </t>
         </is>
       </c>
-      <c r="B674" t="inlineStr">
+      <c r="B673" t="inlineStr">
         <is>
           <t>images/「ベイルート・アニメイテッド」_img1.jpg</t>
         </is>
       </c>
-      <c r="C674" t="inlineStr">
+      <c r="C673" t="inlineStr">
         <is>
           <t>アニメ ,レバノン</t>
         </is>
       </c>
     </row>
-    <row r="675">
-      <c r="A675" t="inlineStr">
+    <row r="674">
+      <c r="A674" t="inlineStr">
         <is>
           <t xml:space="preserve">「夢みれば叶う」
 كُلُّ مُتَوَقَّعٍ آتٍ
@@ -14639,19 +14620,19 @@
 2108 Ahmed Madyan </t>
         </is>
       </c>
-      <c r="B675" t="inlineStr">
+      <c r="B674" t="inlineStr">
         <is>
           <t>images/「夢みれば叶う」_img1.jpg</t>
         </is>
       </c>
-      <c r="C675" t="inlineStr">
+      <c r="C674" t="inlineStr">
         <is>
           <t>希望 ,ドリカム</t>
         </is>
       </c>
     </row>
-    <row r="676">
-      <c r="A676" t="inlineStr">
+    <row r="675">
+      <c r="A675" t="inlineStr">
         <is>
           <t xml:space="preserve">「もし両者が人間のように鎧で武装して戦いに突入したら」
 لو خاضا معاركهما متسلحين بالدروع على غرار البش
@@ -14659,19 +14640,19 @@
 2404 https://x.com/NatGeoMagArab/status/1759284149456945464 </t>
         </is>
       </c>
-      <c r="B676" t="inlineStr">
+      <c r="B675" t="inlineStr">
         <is>
           <t>images/「もし両者が人間のように鎧で武装して戦_img1.jpg,images/「もし両者が人間のように鎧で武装して戦_img2.jpg</t>
         </is>
       </c>
-      <c r="C676" t="inlineStr">
+      <c r="C675" t="inlineStr">
         <is>
           <t>手書き語学 ,アラビア語 ,猫</t>
         </is>
       </c>
     </row>
-    <row r="677">
-      <c r="A677" t="inlineStr">
+    <row r="676">
+      <c r="A676" t="inlineStr">
         <is>
           <t xml:space="preserve">「全ては結びついている」
 كل شيء مترابط
@@ -14681,19 +14662,19 @@
 2308 Ahmed Madyan https://twitter.com/madyco22/status/1451990828298166273 </t>
         </is>
       </c>
-      <c r="B677" t="inlineStr">
+      <c r="B676" t="inlineStr">
         <is>
           <t>images/「全ては結びついている」_img1.jpg</t>
         </is>
       </c>
-      <c r="C677" t="inlineStr">
+      <c r="C676" t="inlineStr">
         <is>
           <t>一筆書き ,デザイン</t>
         </is>
       </c>
     </row>
-    <row r="678">
-      <c r="A678" t="inlineStr">
+    <row r="677">
+      <c r="A677" t="inlineStr">
         <is>
           <t xml:space="preserve">「初心者のためのスケッチトレーニング」
 تعليم الرسم للمبتدئين
@@ -14703,19 +14684,19 @@
 2308 free-bookspdf com </t>
         </is>
       </c>
-      <c r="B678" t="inlineStr">
+      <c r="B677" t="inlineStr">
         <is>
           <t>images/「初心者のためのスケッチトレーニング」_img1.jpg</t>
         </is>
       </c>
-      <c r="C678" t="inlineStr">
+      <c r="C677" t="inlineStr">
         <is>
           <t>イラスト ,絵</t>
         </is>
       </c>
     </row>
-    <row r="679">
-      <c r="A679" t="inlineStr">
+    <row r="678">
+      <c r="A678" t="inlineStr">
         <is>
           <t xml:space="preserve">「初心者のためのスルス体書道トレーニング」
 تعليم خط الثلث للمبتدئين
@@ -14725,19 +14706,19 @@
 2308 出典不明 </t>
         </is>
       </c>
-      <c r="B679" t="inlineStr">
+      <c r="B678" t="inlineStr">
         <is>
           <t>images/「初心者のためのスルス体書道トレーニン_img1.jpg</t>
         </is>
       </c>
-      <c r="C679" t="inlineStr">
+      <c r="C678" t="inlineStr">
         <is>
           <t>書道</t>
         </is>
       </c>
     </row>
-    <row r="680">
-      <c r="A680" t="inlineStr">
+    <row r="679">
+      <c r="A679" t="inlineStr">
         <is>
           <t xml:space="preserve">「笑顔でいなさい」خليك مبتسم
 カッリーク・ムブタスィム [Khallii-k mubtasim]
@@ -14746,19 +14727,19 @@
 2308 https://tmblr.co/Zj9tguYLXBvC </t>
         </is>
       </c>
-      <c r="B680" t="inlineStr">
+      <c r="B679" t="inlineStr">
         <is>
           <t>images/「笑顔でいなさい」_img1.jpg</t>
         </is>
       </c>
-      <c r="C680" t="inlineStr">
+      <c r="C679" t="inlineStr">
         <is>
           <t>スマイル ,名言</t>
         </is>
       </c>
     </row>
-    <row r="681">
-      <c r="A681" t="inlineStr">
+    <row r="680">
+      <c r="A680" t="inlineStr">
         <is>
           <t xml:space="preserve">自動車メーカー
 ⁦・「TOYOTA」( تويوتا )⁩
@@ -14770,19 +14751,19 @@
 2308 syarah com </t>
         </is>
       </c>
-      <c r="B681" t="inlineStr">
+      <c r="B680" t="inlineStr">
         <is>
           <t>images/自動車メーカー_img1.jpg,images/自動車メーカー_img2.jpg,images/自動車メーカー_img3.jpg,images/自動車メーカー_img4.jpg</t>
         </is>
       </c>
-      <c r="C681" t="inlineStr">
+      <c r="C680" t="inlineStr">
         <is>
           <t>日本車 ,韓国車</t>
         </is>
       </c>
     </row>
-    <row r="682">
-      <c r="A682" t="inlineStr">
+    <row r="681">
+      <c r="A681" t="inlineStr">
         <is>
           <t xml:space="preserve">「僕たちは協力して不可能を達成するよ」
 بالتعاون نحقق المحال
@@ -14792,19 +14773,19 @@
 2109 </t>
         </is>
       </c>
-      <c r="B682" t="inlineStr">
+      <c r="B681" t="inlineStr">
         <is>
           <t>images/「僕たちは協力して不可能を達成するよ」_img1.jpg</t>
         </is>
       </c>
-      <c r="C682" t="inlineStr">
+      <c r="C681" t="inlineStr">
         <is>
           <t>無理 ,ハム太郎</t>
         </is>
       </c>
     </row>
-    <row r="683">
-      <c r="A683" t="inlineStr">
+    <row r="682">
+      <c r="A682" t="inlineStr">
         <is>
           <t xml:space="preserve">「幸せは伝染性。喜びを広めよう」
 السعادة معدية فأشع الفرح
@@ -14814,19 +14795,19 @@
 2511 instagram　com/p/fVEfxEo7Va/ </t>
         </is>
       </c>
-      <c r="B683" t="inlineStr">
+      <c r="B682" t="inlineStr">
         <is>
           <t>images/「幸せは伝染性。喜びを広めよう」_img1.jpg</t>
         </is>
       </c>
-      <c r="C683" t="inlineStr">
+      <c r="C682" t="inlineStr">
         <is>
           <t>拡散希望</t>
         </is>
       </c>
     </row>
-    <row r="684">
-      <c r="A684" t="inlineStr">
+    <row r="683">
+      <c r="A683" t="inlineStr">
         <is>
           <t xml:space="preserve">「ストレスは人間だけのものではない」
 الشعور بالتوتر ليس حكرًا على البشر
@@ -14834,19 +14815,19 @@
 2408 https://x.com/NatGeoMagArab/status/1736755816911487420 </t>
         </is>
       </c>
-      <c r="B684" t="inlineStr">
+      <c r="B683" t="inlineStr">
         <is>
           <t>images/「ストレスは人間だけのものではない」_img1.jpg</t>
         </is>
       </c>
-      <c r="C684" t="inlineStr">
+      <c r="C683" t="inlineStr">
         <is>
           <t>手書き語学 ,アラビア語 ,ストレス</t>
         </is>
       </c>
     </row>
-    <row r="685">
-      <c r="A685" t="inlineStr">
+    <row r="684">
+      <c r="A684" t="inlineStr">
         <is>
           <t xml:space="preserve">「私達は出来ます！」
 نستطيع فعلها
@@ -14856,19 +14837,19 @@
 2308 NAHARBAHIJ com </t>
         </is>
       </c>
-      <c r="B685" t="inlineStr">
+      <c r="B684" t="inlineStr">
         <is>
           <t>images/「私達は出来ます！」_img1.jpg</t>
         </is>
       </c>
-      <c r="C685" t="inlineStr">
+      <c r="C684" t="inlineStr">
         <is>
           <t>女性 ,パロディ</t>
         </is>
       </c>
     </row>
-    <row r="686">
-      <c r="A686" t="inlineStr">
+    <row r="685">
+      <c r="A685" t="inlineStr">
         <is>
           <t xml:space="preserve">「全然分からん」ولا فاهم إشي
 ウラー・ファーヒム・イシ [w-laa faahim 'iShy]
@@ -14878,19 +14859,19 @@
 2209 出典不明 </t>
         </is>
       </c>
-      <c r="B686" t="inlineStr">
+      <c r="B685" t="inlineStr">
         <is>
           <t>images/「全然分からん」_img1.jpg</t>
         </is>
       </c>
-      <c r="C686" t="inlineStr">
+      <c r="C685" t="inlineStr">
         <is>
           <t>アラビア語</t>
         </is>
       </c>
     </row>
-    <row r="687">
-      <c r="A687" t="inlineStr">
+    <row r="686">
+      <c r="A686" t="inlineStr">
         <is>
           <t xml:space="preserve">「人間は一人ひとり、特別な才がある。だから自分を他人と比べるのはやめよう」
 لكل إنسان مواهبه الخاصة 
@@ -14899,19 +14880,19 @@
 1812 Gwid3 </t>
         </is>
       </c>
-      <c r="B687" t="inlineStr">
+      <c r="B686" t="inlineStr">
         <is>
           <t>images/「人間は一人ひとり、特別な才がある。だ_img1.jpg</t>
         </is>
       </c>
-      <c r="C687" t="inlineStr">
+      <c r="C686" t="inlineStr">
         <is>
           <t>自尊 ,プライド</t>
         </is>
       </c>
     </row>
-    <row r="688">
-      <c r="A688" t="inlineStr">
+    <row r="687">
+      <c r="A687" t="inlineStr">
         <is>
           <t xml:space="preserve">「この猫は食事をシェアするのが嫌い！」
 هذه القطة لا تحب مشاركة الطعام
@@ -14920,19 +14901,19 @@
 2605 facebook com/alahram/videos/2154923608133231/ </t>
         </is>
       </c>
-      <c r="B688" t="inlineStr">
+      <c r="B687" t="inlineStr">
         <is>
           <t>images/「この猫は食事をシェアするのが嫌い！」_img1.jpg</t>
         </is>
       </c>
-      <c r="C688" t="inlineStr">
+      <c r="C687" t="inlineStr">
         <is>
           <t>猫 ,ネコ</t>
         </is>
       </c>
     </row>
-    <row r="689">
-      <c r="A689" t="inlineStr">
+    <row r="688">
+      <c r="A688" t="inlineStr">
         <is>
           <t xml:space="preserve">「怪獣との戦いでは自分が怪獣化せぬよう警戒しなさい」
 احذر عند محاربة الوحوش ألا تصبح واحدا منهم
@@ -14942,19 +14923,19 @@
 2108 warag-3nb.tumblr </t>
         </is>
       </c>
-      <c r="B689" t="inlineStr">
+      <c r="B688" t="inlineStr">
         <is>
           <t>images/「怪獣との戦いでは自分が怪獣化せぬよう_img1.jpg,images/ 「怪獣との戦いでは自分が怪獣化せぬよう_img2.jpg</t>
         </is>
       </c>
-      <c r="C689" t="inlineStr">
+      <c r="C688" t="inlineStr">
         <is>
           <t>正気 ,モンスター</t>
         </is>
       </c>
     </row>
-    <row r="690">
-      <c r="A690" t="inlineStr">
+    <row r="689">
+      <c r="A689" t="inlineStr">
         <is>
           <t xml:space="preserve">「錯視アート」فن الخداع البصري
 ファンヌ_ルヒダーイ_ルバサリーイ [fannu l-Khidaa*i l-ba_sariyy]
@@ -14963,19 +14944,19 @@
 2409 https://online.pubhtml5.com/idtb/neft/ </t>
         </is>
       </c>
-      <c r="B690" t="inlineStr">
+      <c r="B689" t="inlineStr">
         <is>
           <t>images/「錯視アート」_img1.jpg</t>
         </is>
       </c>
-      <c r="C690" t="inlineStr">
+      <c r="C689" t="inlineStr">
         <is>
           <t>トリックアート</t>
         </is>
       </c>
     </row>
-    <row r="691">
-      <c r="A691" t="inlineStr">
+    <row r="690">
+      <c r="A690" t="inlineStr">
         <is>
           <t xml:space="preserve">「自然界の消防士の訓練」
 تدريبات رجال الإطفاء في الطبيعة
@@ -14983,19 +14964,19 @@
 2308 https://twitter.com/NatGeoMagArab/status/1462420543890608129 </t>
         </is>
       </c>
-      <c r="B691" t="inlineStr">
+      <c r="B690" t="inlineStr">
         <is>
           <t>images/「自然界の消防士の訓練」_img1.jpg,images/ 「自然界の消防士の訓練」_img2.jpg</t>
         </is>
       </c>
-      <c r="C691" t="inlineStr">
+      <c r="C690" t="inlineStr">
         <is>
           <t>手書き語学 ,アラビア語 ,ヒグマ</t>
         </is>
       </c>
     </row>
-    <row r="692">
-      <c r="A692" t="inlineStr">
+    <row r="691">
+      <c r="A691" t="inlineStr">
         <is>
           <t xml:space="preserve">「救助」إسعاف
 イスアーフ ['is*aaf]
@@ -15004,19 +14985,19 @@
 2109 ambulance gov ae </t>
         </is>
       </c>
-      <c r="B692" t="inlineStr">
+      <c r="B691" t="inlineStr">
         <is>
           <t>images/「救助」_img1.jpg</t>
         </is>
       </c>
-      <c r="C692" t="inlineStr">
+      <c r="C691" t="inlineStr">
         <is>
           <t>救急車 ,はたらくくるま</t>
         </is>
       </c>
     </row>
-    <row r="693">
-      <c r="A693" t="inlineStr">
+    <row r="692">
+      <c r="A692" t="inlineStr">
         <is>
           <t xml:space="preserve">「感情／感覚」الإحْسَاسْ
 アルイヒサース [al-'iHsaas]
@@ -15025,19 +15006,19 @@
 2308 iN49R </t>
         </is>
       </c>
-      <c r="B693" t="inlineStr">
+      <c r="B692" t="inlineStr">
         <is>
           <t>images/「感情／感覚」_img1.jpg</t>
         </is>
       </c>
-      <c r="C693" t="inlineStr">
+      <c r="C692" t="inlineStr">
         <is>
           <t>オフ ,一休み</t>
         </is>
       </c>
     </row>
-    <row r="694">
-      <c r="A694" t="inlineStr">
+    <row r="693">
+      <c r="A693" t="inlineStr">
         <is>
           <t xml:space="preserve">「ひらめき」إلهام
 イルハーム ['lhaam]
@@ -15049,19 +15030,19 @@
 2103 出典不明 </t>
         </is>
       </c>
-      <c r="B694" t="inlineStr">
+      <c r="B693" t="inlineStr">
         <is>
           <t>images/「ひらめき」_img1.jpg</t>
         </is>
       </c>
-      <c r="C694" t="inlineStr">
+      <c r="C693" t="inlineStr">
         <is>
           <t>アラビア語</t>
         </is>
       </c>
     </row>
-    <row r="695">
-      <c r="A695" t="inlineStr">
+    <row r="694">
+      <c r="A694" t="inlineStr">
         <is>
           <t xml:space="preserve">「Ibdaa／クリエイティビティ」
 إبداع
@@ -15070,19 +15051,19 @@
 2308 Ibdaa Design &amp; Decoration Office </t>
         </is>
       </c>
-      <c r="B695" t="inlineStr">
+      <c r="B694" t="inlineStr">
         <is>
           <t>images/「Ibdaa／クリエイティビティ」_img1.jpg</t>
         </is>
       </c>
-      <c r="C695" t="inlineStr">
+      <c r="C694" t="inlineStr">
         <is>
           <t>創造性 ,独自性</t>
         </is>
       </c>
     </row>
-    <row r="696">
-      <c r="A696" t="inlineStr">
+    <row r="695">
+      <c r="A695" t="inlineStr">
         <is>
           <t xml:space="preserve">「奮闘なくして進歩なし」
 بدون كفاح لايوجد تقدم
@@ -15092,19 +15073,19 @@
 2105 ROUYMS TUMBLR COM </t>
         </is>
       </c>
-      <c r="B696" t="inlineStr">
+      <c r="B695" t="inlineStr">
         <is>
           <t>images/「奮闘なくして進歩なし」_img1.jpg</t>
         </is>
       </c>
-      <c r="C696" t="inlineStr">
+      <c r="C695" t="inlineStr">
         <is>
           <t>努力 ,三角形</t>
         </is>
       </c>
     </row>
-    <row r="697">
-      <c r="A697" t="inlineStr">
+    <row r="696">
+      <c r="A696" t="inlineStr">
         <is>
           <t xml:space="preserve">「木に登れば熊の危険を避けられるとお考えなら、考え直しましょう！」 
 إن اعتقدت أنك بمنأى عن خطر الدب عند تسلق الأشجار.. راجع حساباتك
@@ -15112,19 +15093,19 @@
 2202 NatGeoMagArab </t>
         </is>
       </c>
-      <c r="B697" t="inlineStr">
+      <c r="B696" t="inlineStr">
         <is>
           <t>images/「木に登れば熊の危険を避けられるとお考.jpeg</t>
         </is>
       </c>
-      <c r="C697" t="inlineStr">
+      <c r="C696" t="inlineStr">
         <is>
           <t>クマ</t>
         </is>
       </c>
     </row>
-    <row r="698">
-      <c r="A698" t="inlineStr">
+    <row r="697">
+      <c r="A697" t="inlineStr">
         <is>
           <t xml:space="preserve">「卒業おめでとう」مبروك التخرج
 マブルーク・タカッルジ [mabruuk a^taKharruj]
@@ -15133,19 +15114,19 @@
 2308 https://instagram.com/fatoomworld </t>
         </is>
       </c>
-      <c r="B698" t="inlineStr">
+      <c r="B697" t="inlineStr">
         <is>
           <t>images/「卒業おめでとう」_img1.jpg</t>
         </is>
       </c>
-      <c r="C698" t="inlineStr">
+      <c r="C697" t="inlineStr">
         <is>
           <t>卒業 ,イラスト</t>
         </is>
       </c>
     </row>
-    <row r="699">
-      <c r="A699" t="inlineStr">
+    <row r="698">
+      <c r="A698" t="inlineStr">
         <is>
           <t xml:space="preserve">「停止距離の計算」
 حساب مسافة التوقف
@@ -15155,19 +15136,19 @@
 2109 assurance-auto-info </t>
         </is>
       </c>
-      <c r="B699" t="inlineStr">
+      <c r="B698" t="inlineStr">
         <is>
           <t>images/「停止距離の計算」_img1.jpg</t>
         </is>
       </c>
-      <c r="C699" t="inlineStr">
+      <c r="C698" t="inlineStr">
         <is>
           <t>保険 ,自動車</t>
         </is>
       </c>
     </row>
-    <row r="700">
-      <c r="A700" t="inlineStr">
+    <row r="699">
+      <c r="A699" t="inlineStr">
         <is>
           <t xml:space="preserve">「教師要らず：10日でフランス語会話」
 بدون معلم
@@ -15177,19 +15158,19 @@
 2308 englais-best com </t>
         </is>
       </c>
-      <c r="B700" t="inlineStr">
+      <c r="B699" t="inlineStr">
         <is>
           <t>images/「教師要らず：10日でフランス語会話」_img1.jpg</t>
         </is>
       </c>
-      <c r="C700" t="inlineStr">
+      <c r="C699" t="inlineStr">
         <is>
           <t>教師なし学習</t>
         </is>
       </c>
     </row>
-    <row r="701">
-      <c r="A701" t="inlineStr">
+    <row r="700">
+      <c r="A700" t="inlineStr">
         <is>
           <t xml:space="preserve">「衝突」تصادم
 タサードゥム [ta_saadum]
@@ -15198,19 +15179,19 @@
 1810 </t>
         </is>
       </c>
-      <c r="B701" t="inlineStr">
+      <c r="B700" t="inlineStr">
         <is>
           <t>images/「衝突」_img1.jpg</t>
         </is>
       </c>
-      <c r="C701" t="inlineStr">
+      <c r="C700" t="inlineStr">
         <is>
           <t>あらびあや</t>
         </is>
       </c>
     </row>
-    <row r="702">
-      <c r="A702" t="inlineStr">
+    <row r="701">
+      <c r="A701" t="inlineStr">
         <is>
           <t xml:space="preserve">「楽観主義」تَفَاؤُلٌ
 タファーウル [tafaa'ul(un)]
@@ -15219,19 +15200,19 @@
 1904 arabictypography com </t>
         </is>
       </c>
-      <c r="B702" t="inlineStr">
+      <c r="B701" t="inlineStr">
         <is>
           <t>images/「楽観主義」_img1.jpg</t>
         </is>
       </c>
-      <c r="C702" t="inlineStr">
+      <c r="C701" t="inlineStr">
         <is>
           <t>やわらか ,緑</t>
         </is>
       </c>
     </row>
-    <row r="703">
-      <c r="A703" t="inlineStr">
+    <row r="702">
+      <c r="A702" t="inlineStr">
         <is>
           <t xml:space="preserve">「シベリアジャコウジカは、絶滅の危機にあると見なされている」
 يعد "أيل المسك السيبيري" مهددًا بالانقراض
@@ -15239,19 +15220,19 @@
 2308 https://twitter.com/NatGeoMagArab/status/1320666649045790720 </t>
         </is>
       </c>
-      <c r="B703" t="inlineStr">
+      <c r="B702" t="inlineStr">
         <is>
           <t>images/「シベリアジャコウジカは、絶滅の危機に_img1.jpg,images/「シベリアジャコウジカは、絶滅の危機に_img2.jpg</t>
         </is>
       </c>
-      <c r="C703" t="inlineStr">
+      <c r="C702" t="inlineStr">
         <is>
           <t>手書き語学 ,シベリア</t>
         </is>
       </c>
     </row>
-    <row r="704">
-      <c r="A704" t="inlineStr">
+    <row r="703">
+      <c r="A703" t="inlineStr">
         <is>
           <t xml:space="preserve">「融合／折衷／フュージョン」
 انصهار
@@ -15260,38 +15241,38 @@
 1811 elmahdyart Instagram </t>
         </is>
       </c>
-      <c r="B704" t="inlineStr">
+      <c r="B703" t="inlineStr">
         <is>
           <t>images/「融合／折衷／フュージョン」_img1.jpg</t>
         </is>
       </c>
-      <c r="C704" t="inlineStr">
+      <c r="C703" t="inlineStr">
         <is>
           <t>カリグラフィー ,書道</t>
         </is>
       </c>
     </row>
-    <row r="705">
-      <c r="A705" t="inlineStr">
+    <row r="704">
+      <c r="A704" t="inlineStr">
         <is>
           <t xml:space="preserve">「この子供は、昼寝をしようとする母親を邪魔しているようだ」
 「場所はインドのトラ保護区、バンダウガル公園。トラは生態ピラミッドのトップの捕食動物だが、最もリスクの高い絶滅危惧種のひとつである」
 2308 https://twitter.com/natgeomagarab/status/1553681890665586689 </t>
         </is>
       </c>
-      <c r="B705" t="inlineStr">
+      <c r="B704" t="inlineStr">
         <is>
           <t>images/「この子供は、昼寝をしようとする母親を_img1.jpg,images/「この子供は、昼寝をしようとする母親を_img2.jpg</t>
         </is>
       </c>
-      <c r="C705" t="inlineStr">
+      <c r="C704" t="inlineStr">
         <is>
           <t>手書き語学 ,アラビア語 ,トラ</t>
         </is>
       </c>
     </row>
-    <row r="706">
-      <c r="A706" t="inlineStr">
+    <row r="705">
+      <c r="A705" t="inlineStr">
         <is>
           <t xml:space="preserve">「もし敬意が落ちたら、それと一緒に全部落ちるのだ」
 إن سقط الإحترام سقط معه كل شيء
@@ -15300,19 +15281,19 @@
 2109 出典不明 </t>
         </is>
       </c>
-      <c r="B706" t="inlineStr">
+      <c r="B705" t="inlineStr">
         <is>
           <t>images/「もし敬意が落ちたら、それと一緒に全部_img1.jpg</t>
         </is>
       </c>
-      <c r="C706" t="inlineStr">
+      <c r="C705" t="inlineStr">
         <is>
           <t>リスペクト ,落書き</t>
         </is>
       </c>
     </row>
-    <row r="707">
-      <c r="A707" t="inlineStr">
+    <row r="706">
+      <c r="A706" t="inlineStr">
         <is>
           <t xml:space="preserve">「エジプト特許庁」
 مكتب براءات الاختراع المصرى
@@ -15322,19 +15303,19 @@
 2312 </t>
         </is>
       </c>
-      <c r="B707" t="inlineStr">
+      <c r="B706" t="inlineStr">
         <is>
           <t>images/「エジプト特許庁」_img1.jpg</t>
         </is>
       </c>
-      <c r="C707" t="inlineStr">
+      <c r="C706" t="inlineStr">
         <is>
           <t>patent</t>
         </is>
       </c>
     </row>
-    <row r="708">
-      <c r="A708" t="inlineStr">
+    <row r="707">
+      <c r="A707" t="inlineStr">
         <is>
           <t xml:space="preserve">「選挙」إنتخابات
 インティカーバート [intiKhaabaat]
@@ -15343,19 +15324,19 @@
 2311 nna-leb gov lb </t>
         </is>
       </c>
-      <c r="B708" t="inlineStr">
+      <c r="B707" t="inlineStr">
         <is>
           <t>images/「選挙」_img1.jpg</t>
         </is>
       </c>
-      <c r="C708" t="inlineStr">
+      <c r="C707" t="inlineStr">
         <is>
           <t>選挙 ,投票</t>
         </is>
       </c>
     </row>
-    <row r="709">
-      <c r="A709" t="inlineStr">
+    <row r="708">
+      <c r="A708" t="inlineStr">
         <is>
           <t xml:space="preserve">「待ちぼうけ」إنتظار
 インティザール [inti_Dhaar]
@@ -15364,19 +15345,19 @@
 1809 in4sser.tumblr </t>
         </is>
       </c>
-      <c r="B709" t="inlineStr">
+      <c r="B708" t="inlineStr">
         <is>
           <t>images/「待ちぼうけ」_img1.jpg</t>
         </is>
       </c>
-      <c r="C709" t="inlineStr">
+      <c r="C708" t="inlineStr">
         <is>
           <t>遅すぎ ,辛抱</t>
         </is>
       </c>
     </row>
-    <row r="710">
-      <c r="A710" t="inlineStr">
+    <row r="709">
+      <c r="A709" t="inlineStr">
         <is>
           <t xml:space="preserve">「試験」إختبار
 イクティバール [iKhtibaar]
@@ -15385,19 +15366,19 @@
 2109 出典不明 </t>
         </is>
       </c>
-      <c r="B710" t="inlineStr">
+      <c r="B709" t="inlineStr">
         <is>
           <t>images/「試験」_img1.jpg</t>
         </is>
       </c>
-      <c r="C710" t="inlineStr">
+      <c r="C709" t="inlineStr">
         <is>
           <t>テスト ,考査</t>
         </is>
       </c>
     </row>
-    <row r="711">
-      <c r="A711" t="inlineStr">
+    <row r="710">
+      <c r="A710" t="inlineStr">
         <is>
           <t xml:space="preserve">「チャンネル登録」اشتراك
 イシティラーク [iShtiraak]
@@ -15406,19 +15387,19 @@
 2308 </t>
         </is>
       </c>
-      <c r="B711" t="inlineStr">
+      <c r="B710" t="inlineStr">
         <is>
           <t>images/「チャンネル登録」_img1.jpg</t>
         </is>
       </c>
-      <c r="C711" t="inlineStr">
+      <c r="C710" t="inlineStr">
         <is>
           <t>Subscribe ,YouTube</t>
         </is>
       </c>
     </row>
-    <row r="712">
-      <c r="A712" t="inlineStr">
+    <row r="711">
+      <c r="A711" t="inlineStr">
         <is>
           <t xml:space="preserve">「スマイル」ابتسام
 イブティサーム [ibtisaam]
@@ -15426,37 +15407,37 @@
 1903 behance Written-Visuals </t>
         </is>
       </c>
+      <c r="B711" t="inlineStr">
+        <is>
+          <t>images/「スマイル」_img1.jpg</t>
+        </is>
+      </c>
+      <c r="C711" t="inlineStr">
+        <is>
+          <t>スマイリー ,ツ</t>
+        </is>
+      </c>
+    </row>
+    <row r="712">
+      <c r="A712" t="inlineStr">
+        <is>
+          <t xml:space="preserve">「身体の一部として…」
+2308 https://twitter.com/NatGeoMagArab/status/1528292080337813504 </t>
+        </is>
+      </c>
       <c r="B712" t="inlineStr">
         <is>
-          <t>images/「スマイル」_img1.jpg</t>
+          <t>images/「身体の一部として…」_img1.jpg</t>
         </is>
       </c>
       <c r="C712" t="inlineStr">
         <is>
-          <t>スマイリー ,ツ</t>
+          <t>手書き語学 ,カンガルー</t>
         </is>
       </c>
     </row>
     <row r="713">
       <c r="A713" t="inlineStr">
-        <is>
-          <t xml:space="preserve">「身体の一部として…」
-2308 https://twitter.com/NatGeoMagArab/status/1528292080337813504 </t>
-        </is>
-      </c>
-      <c r="B713" t="inlineStr">
-        <is>
-          <t>images/「身体の一部として…」_img1.jpg</t>
-        </is>
-      </c>
-      <c r="C713" t="inlineStr">
-        <is>
-          <t>手書き語学 ,カンガルー</t>
-        </is>
-      </c>
-    </row>
-    <row r="714">
-      <c r="A714" t="inlineStr">
         <is>
           <t xml:space="preserve">「ディスカバリー」إكتشاف
 イクティシャーフ [iktiShaaf]
@@ -15464,19 +15445,19 @@
 2308 tephanegabrielli com </t>
         </is>
       </c>
-      <c r="B714" t="inlineStr">
+      <c r="B713" t="inlineStr">
         <is>
           <t>images/「ディスカバリー」_img1.jpg</t>
         </is>
       </c>
-      <c r="C714" t="inlineStr">
+      <c r="C713" t="inlineStr">
         <is>
           <t>discovery ,デザイン</t>
         </is>
       </c>
     </row>
-    <row r="715">
-      <c r="A715" t="inlineStr">
+    <row r="714">
+      <c r="A714" t="inlineStr">
         <is>
           <t xml:space="preserve">「重力波の発見は新しい窓を開いた」
 فتَح اكتشاف موجات الجاذبية نافذة جديدة
@@ -15484,19 +15465,19 @@
 2308 https://twitter.com/SciTalk2U/status/1454891943440289793 </t>
         </is>
       </c>
-      <c r="B715" t="inlineStr">
+      <c r="B714" t="inlineStr">
         <is>
           <t>images/「重力波の発見は新しい窓を開いた」_img1.jpg</t>
         </is>
       </c>
-      <c r="C715" t="inlineStr">
+      <c r="C714" t="inlineStr">
         <is>
           <t>手書き語学 ,アラビア語 ,重力波</t>
         </is>
       </c>
     </row>
-    <row r="716">
-      <c r="A716" t="inlineStr">
+    <row r="715">
+      <c r="A715" t="inlineStr">
         <is>
           <t xml:space="preserve">「微笑みに微笑み。先にした人の方が美しい」
 الإبتسامة بالإبتسامة والبادئ أجمل
@@ -15505,19 +15486,19 @@
 2104 出典不明 </t>
         </is>
       </c>
-      <c r="B716" t="inlineStr">
+      <c r="B715" t="inlineStr">
         <is>
           <t>images/「微笑みに微笑み。先にした人の方が美し_img1.jpg,images/「微笑みに微笑み。先にした人の方が美し_img2.jpg</t>
         </is>
       </c>
-      <c r="C716" t="inlineStr">
+      <c r="C715" t="inlineStr">
         <is>
           <t>スマイル ,名言</t>
         </is>
       </c>
     </row>
-    <row r="717">
-      <c r="A717" t="inlineStr">
+    <row r="716">
+      <c r="A716" t="inlineStr">
         <is>
           <t xml:space="preserve">「笑顔」ابتسامة
 イブティサーマ [ibtisaama(tun)]
@@ -15526,19 +15507,19 @@
 2308 satokomatsu, minne </t>
         </is>
       </c>
-      <c r="B717" t="inlineStr">
+      <c r="B716" t="inlineStr">
         <is>
           <t>images/「笑顔」_img1.jpg</t>
         </is>
       </c>
-      <c r="C717" t="inlineStr">
+      <c r="C716" t="inlineStr">
         <is>
           <t>スマイル ,ツ</t>
         </is>
       </c>
     </row>
-    <row r="718">
-      <c r="A718" t="inlineStr">
+    <row r="717">
+      <c r="A717" t="inlineStr">
         <is>
           <t xml:space="preserve">「信仰」ايمان
 イーマーン ['iimaan]
@@ -15547,19 +15528,19 @@
 2506 instagram com/p/6ST-WHOOkJ/ </t>
         </is>
       </c>
-      <c r="B718" t="inlineStr">
+      <c r="B717" t="inlineStr">
         <is>
           <t>images/「信仰」_img1.jpg</t>
         </is>
       </c>
-      <c r="C718" t="inlineStr">
+      <c r="C717" t="inlineStr">
         <is>
           <t>宗教 ,信念</t>
         </is>
       </c>
     </row>
-    <row r="719">
-      <c r="A719" t="inlineStr">
+    <row r="718">
+      <c r="A718" t="inlineStr">
         <is>
           <t xml:space="preserve">「放送」إذاعة
 イザーア ['iDhaa*a]
@@ -15568,19 +15549,19 @@
 2404 heemades, Instagram </t>
         </is>
       </c>
-      <c r="B719" t="inlineStr">
+      <c r="B718" t="inlineStr">
         <is>
           <t>images/「放送」_img1.jpg</t>
         </is>
       </c>
-      <c r="C719" t="inlineStr">
+      <c r="C718" t="inlineStr">
         <is>
           <t>デザイン ,ラジオ</t>
         </is>
       </c>
     </row>
-    <row r="720">
-      <c r="A720" t="inlineStr">
+    <row r="719">
+      <c r="A719" t="inlineStr">
         <is>
           <t xml:space="preserve">「かきとりのちから」
 مهاراتي الإملائية
@@ -15589,19 +15570,19 @@
 2308 iqrawaoktoub.wordpress com </t>
         </is>
       </c>
-      <c r="B720" t="inlineStr">
+      <c r="B719" t="inlineStr">
         <is>
           <t>images/「かきとりのちから」_img1.jpg</t>
         </is>
       </c>
-      <c r="C720" t="inlineStr">
+      <c r="C719" t="inlineStr">
         <is>
           <t>国語 ,教材</t>
         </is>
       </c>
     </row>
-    <row r="721">
-      <c r="A721" t="inlineStr">
+    <row r="720">
+      <c r="A720" t="inlineStr">
         <is>
           <t xml:space="preserve">「歴史を作った男たち」
 رجال صنعوا التاريخ
@@ -15611,38 +15592,38 @@
 2410 https://x.gd/Wl5rJ </t>
         </is>
       </c>
-      <c r="B721" t="inlineStr">
+      <c r="B720" t="inlineStr">
         <is>
           <t>images/「歴史を作った男たち」_img1.jpg</t>
         </is>
       </c>
-      <c r="C721" t="inlineStr">
+      <c r="C720" t="inlineStr">
         <is>
           <t>偉人</t>
         </is>
       </c>
     </row>
-    <row r="722">
-      <c r="A722" t="inlineStr">
+    <row r="721">
+      <c r="A721" t="inlineStr">
         <is>
           <t xml:space="preserve">「無限の宇宙を旅した光」
 「何百年もの末にジェイムズ・ウェッブ望遠鏡のレンズの上に落ち、我々に遠い宇宙の美しさを見せてくれる。最も純粋な形と最も素晴らしい姿で」
 2308 https://twitter.com/NatGeoMagArab/status/1557811592636485632 </t>
         </is>
       </c>
-      <c r="B722" t="inlineStr">
+      <c r="B721" t="inlineStr">
         <is>
           <t>images/「無限の宇宙を旅した光」_img1.jpg</t>
         </is>
       </c>
-      <c r="C722" t="inlineStr">
+      <c r="C721" t="inlineStr">
         <is>
           <t>手書き語学 ,宇宙</t>
         </is>
       </c>
     </row>
-    <row r="723">
-      <c r="A723" t="inlineStr">
+    <row r="722">
+      <c r="A722" t="inlineStr">
         <is>
           <t xml:space="preserve">「日本好きになり行きたくなる20項」
 عشرون شيئا يجعلك تحب اليابان وترغب في زيارتها
@@ -15651,19 +15632,19 @@
 2308 wattpad </t>
         </is>
       </c>
-      <c r="B723" t="inlineStr">
+      <c r="B722" t="inlineStr">
         <is>
           <t>images/「日本好きになり行きたくなる20項」_img1.jpg</t>
         </is>
       </c>
-      <c r="C723" t="inlineStr">
+      <c r="C722" t="inlineStr">
         <is>
           <t>اليابان ,Japan</t>
         </is>
       </c>
     </row>
-    <row r="724">
-      <c r="A724" t="inlineStr">
+    <row r="723">
+      <c r="A723" t="inlineStr">
         <is>
           <t xml:space="preserve">「ピッタリの瞬間に撮影され、ドラゴンが火を噴いているように見える」
 التُقطت في اللحظة المناسبة لتبدو مثل تنين ينفث اللهب
@@ -15671,19 +15652,19 @@
 2509 https://twitter.com/NatGeoMagArab/status/1588780660269150208 </t>
         </is>
       </c>
-      <c r="B724" t="inlineStr">
+      <c r="B723" t="inlineStr">
         <is>
           <t>images/「ピッタリの瞬間に撮影され、ドラゴンが_img1.jpg,images/ 「ピッタリの瞬間に撮影され、ドラゴンが_img2.jpg</t>
         </is>
       </c>
-      <c r="C724" t="inlineStr">
+      <c r="C723" t="inlineStr">
         <is>
           <t xml:space="preserve">ドラゴン </t>
         </is>
       </c>
     </row>
-    <row r="725">
-      <c r="A725" t="inlineStr">
+    <row r="724">
+      <c r="A724" t="inlineStr">
         <is>
           <t xml:space="preserve">「満足は不滅の宝である」
 القَناعَةُ كنز لا يَفنَى
@@ -15693,55 +15674,55 @@
 2308 kareem mrghani </t>
         </is>
       </c>
+      <c r="B724" t="inlineStr">
+        <is>
+          <t>images/「満足は不滅の宝である」_img1.jpg</t>
+        </is>
+      </c>
+      <c r="C724" t="inlineStr">
+        <is>
+          <t>幸福度</t>
+        </is>
+      </c>
+    </row>
+    <row r="725">
+      <c r="A725" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ゴシキセイガイインコ。
+2409 https://twitter.com/NatGeoMagArab/status/1600022262014676992 </t>
+        </is>
+      </c>
       <c r="B725" t="inlineStr">
         <is>
-          <t>images/「満足は不滅の宝である」_img1.jpg</t>
+          <t>images/ゴシキセイガイインコ。_img1.jpg</t>
         </is>
       </c>
       <c r="C725" t="inlineStr">
         <is>
-          <t>幸福度</t>
+          <t>手書き語学 ,アラビア語,オウム</t>
         </is>
       </c>
     </row>
     <row r="726">
       <c r="A726" t="inlineStr">
         <is>
-          <t xml:space="preserve">ゴシキセイガイインコ。
-2409 https://twitter.com/NatGeoMagArab/status/1600022262014676992 </t>
+          <t xml:space="preserve">モモンガ。
+2403 https://twitter.com/NatGeoMagArab/status/1552541872966344704 </t>
         </is>
       </c>
       <c r="B726" t="inlineStr">
         <is>
-          <t>images/ゴシキセイガイインコ。_img1.jpg</t>
+          <t>images/モモンガ。_img1.jpg,images/ モモンガ。_img2.jpg</t>
         </is>
       </c>
       <c r="C726" t="inlineStr">
         <is>
-          <t>手書き語学 ,アラビア語,オウム</t>
+          <t>手書き語学 ,アラビア語 ,モモンガ</t>
         </is>
       </c>
     </row>
     <row r="727">
       <c r="A727" t="inlineStr">
-        <is>
-          <t xml:space="preserve">モモンガ。
-2403 https://twitter.com/NatGeoMagArab/status/1552541872966344704 </t>
-        </is>
-      </c>
-      <c r="B727" t="inlineStr">
-        <is>
-          <t>images/モモンガ。_img1.jpg,images/ モモンガ。_img2.jpg</t>
-        </is>
-      </c>
-      <c r="C727" t="inlineStr">
-        <is>
-          <t>手書き語学 ,アラビア語 ,モモンガ</t>
-        </is>
-      </c>
-    </row>
-    <row r="728">
-      <c r="A728" t="inlineStr">
         <is>
           <t xml:space="preserve">「象の群れ。ドローンの音から逃げている」
 قطيع من الفيلة يفر هاربًا من صوت الدرون
@@ -15753,56 +15734,56 @@
 2009 https://twitter.com/NatGeoMagArab/status/1302970033627258881 </t>
         </is>
       </c>
+      <c r="B727" t="inlineStr">
+        <is>
+          <t>images/「象の群れ。ドローンの音から逃げている.jpg</t>
+        </is>
+      </c>
+      <c r="C727" t="inlineStr">
+        <is>
+          <t>ゾウ ,ドローン</t>
+        </is>
+      </c>
+    </row>
+    <row r="728">
+      <c r="A728" t="inlineStr">
+        <is>
+          <t xml:space="preserve">カルマン線。
+2308 https://twitter.com/NatGeoMagArab/status/1536436999522881536 </t>
+        </is>
+      </c>
       <c r="B728" t="inlineStr">
         <is>
-          <t>images/「象の群れ。ドローンの音から逃げている.jpg</t>
+          <t>images/カルマン線。_img1.jpg</t>
         </is>
       </c>
       <c r="C728" t="inlineStr">
         <is>
-          <t>ゾウ ,ドローン</t>
+          <t xml:space="preserve">手書き語学 ,アラビア語 ,宇宙 </t>
         </is>
       </c>
     </row>
     <row r="729">
       <c r="A729" t="inlineStr">
-        <is>
-          <t xml:space="preserve">カルマン線。
-2308 https://twitter.com/NatGeoMagArab/status/1536436999522881536 </t>
-        </is>
-      </c>
-      <c r="B729" t="inlineStr">
-        <is>
-          <t>images/カルマン線。_img1.jpg</t>
-        </is>
-      </c>
-      <c r="C729" t="inlineStr">
-        <is>
-          <t xml:space="preserve">手書き語学 ,アラビア語 ,宇宙 </t>
-        </is>
-      </c>
-    </row>
-    <row r="730">
-      <c r="A730" t="inlineStr">
         <is>
           <t xml:space="preserve">「恥ずかしがり屋のマヌルネコと暖かい朝の太陽光線」
 ⁦「二つの美しいもの」[Shay'-ayni jamiil-ayni] 属格：「物」( شيء )[Shay']・「美しい」( جميل )[jamiil]⁩
 2309 https://twitter.com/NatGeoMagArab/status/1697512148820504912 </t>
         </is>
       </c>
-      <c r="B730" t="inlineStr">
+      <c r="B729" t="inlineStr">
         <is>
           <t>images/「恥ずかしがり屋のマヌルネコと暖かい朝_img1.jpg</t>
         </is>
       </c>
-      <c r="C730" t="inlineStr">
+      <c r="C729" t="inlineStr">
         <is>
           <t>手書き語学 ,アラビア語 ,マヌルネコ</t>
         </is>
       </c>
     </row>
-    <row r="731">
-      <c r="A731" t="inlineStr">
+    <row r="730">
+      <c r="A730" t="inlineStr">
         <is>
           <t xml:space="preserve">「二回失敗しているペンギン」
 بطريق يفشل مرتين
@@ -15812,19 +15793,19 @@
 2308 https://twitter.com/NatGeoMagArab/status/1479483133766426626 </t>
         </is>
       </c>
-      <c r="B731" t="inlineStr">
+      <c r="B730" t="inlineStr">
         <is>
           <t>images/「二回失敗しているペンギン」_img1.jpg</t>
         </is>
       </c>
-      <c r="C731" t="inlineStr">
+      <c r="C730" t="inlineStr">
         <is>
           <t>ペンギン ,動物</t>
         </is>
       </c>
     </row>
-    <row r="732">
-      <c r="A732" t="inlineStr">
+    <row r="731">
+      <c r="A731" t="inlineStr">
         <is>
           <t xml:space="preserve">「2億光年の彼方できらめく炎と光」
 وهج ووميض يتلألأ على بعد 200 مليون سنة ضوئية
@@ -15835,15 +15816,15 @@
 2010 https://twitter.com/NatGeoMagArab/status/1303415502673342464 </t>
         </is>
       </c>
-      <c r="B732" t="inlineStr"/>
-      <c r="C732" t="inlineStr">
+      <c r="B731" t="inlineStr"/>
+      <c r="C731" t="inlineStr">
         <is>
           <t>宇宙 ,銀河</t>
         </is>
       </c>
     </row>
-    <row r="733">
-      <c r="A733" t="inlineStr">
+    <row r="732">
+      <c r="A732" t="inlineStr">
         <is>
           <t xml:space="preserve">「さまよう黒猫」قطة سوداء تجوب
 キッタトゥン・サウダーウ・タジューブ [qi^_tatun sawdaa'u ta-juub]
@@ -15852,19 +15833,19 @@
 2308 https://twitter.com/NatGeoMagArab/status/1532973177453760512 </t>
         </is>
       </c>
-      <c r="B733" t="inlineStr">
+      <c r="B732" t="inlineStr">
         <is>
           <t>images/「さまよう黒猫」_img1.jpg,images/ 「さまよう黒猫」_img2.jpg</t>
         </is>
       </c>
-      <c r="C733" t="inlineStr">
+      <c r="C732" t="inlineStr">
         <is>
           <t xml:space="preserve">手書き語学 ,モロッコ </t>
         </is>
       </c>
     </row>
-    <row r="734">
-      <c r="A734" t="inlineStr">
+    <row r="733">
+      <c r="A733" t="inlineStr">
         <is>
           <t xml:space="preserve">「サイのざらざらした皮を利用して自分の体を掻くネコ」
 قطة تستغل جلد الكركدن الخشن لحك جسدها
@@ -15873,19 +15854,19 @@
 2308 https://twitter.com/NatGeoMagArab/status/1476855740929216517 </t>
         </is>
       </c>
-      <c r="B734" t="inlineStr">
+      <c r="B733" t="inlineStr">
         <is>
           <t>images/「サイのざらざらした皮を利用して自分の_img1.jpg</t>
         </is>
       </c>
-      <c r="C734" t="inlineStr">
+      <c r="C733" t="inlineStr">
         <is>
           <t>サイ ,チェコ</t>
         </is>
       </c>
     </row>
-    <row r="735">
-      <c r="A735" t="inlineStr">
+    <row r="734">
+      <c r="A734" t="inlineStr">
         <is>
           <t xml:space="preserve">「沈まぬ太陽」شمس لا تغيب
 シャムス・ラー・タギーブ [Shams laa ta-Ghiib]
@@ -15894,19 +15875,19 @@
 2308 AHMED ELASSAL </t>
         </is>
       </c>
-      <c r="B735" t="inlineStr">
+      <c r="B734" t="inlineStr">
         <is>
           <t>images/「沈まぬ太陽」_img1.jpg</t>
         </is>
       </c>
-      <c r="C735" t="inlineStr">
+      <c r="C734" t="inlineStr">
         <is>
           <t>帝国 ,白夜</t>
         </is>
       </c>
     </row>
-    <row r="736">
-      <c r="A736" t="inlineStr">
+    <row r="735">
+      <c r="A735" t="inlineStr">
         <is>
           <t xml:space="preserve">「子供に食べさせている忍耐強い母親」
 أم صبورة تطعم صغيرها
@@ -15915,19 +15896,19 @@
 2308 https://twitter.com/natgeomagarab/status/1585572054509957120 </t>
         </is>
       </c>
-      <c r="B736" t="inlineStr">
+      <c r="B735" t="inlineStr">
         <is>
           <t>images/「子供に食べさせている忍耐強い母親」_img1.jpg</t>
         </is>
       </c>
-      <c r="C736" t="inlineStr">
+      <c r="C735" t="inlineStr">
         <is>
           <t>手書き語学 ,アラビア語 ,ミヤコドリ</t>
         </is>
       </c>
     </row>
-    <row r="737">
-      <c r="A737" t="inlineStr">
+    <row r="736">
+      <c r="A736" t="inlineStr">
         <is>
           <t xml:space="preserve">「コーヒーは繰り返さない恋物語」
 القهوة قصة عشق لن تتكرر
@@ -15937,19 +15918,19 @@
 2403 pin it/7tvd8Wc </t>
         </is>
       </c>
-      <c r="B737" t="inlineStr">
+      <c r="B736" t="inlineStr">
         <is>
           <t>images/「コーヒーは繰り返さない恋物語」_img1.jpg</t>
         </is>
       </c>
-      <c r="C737" t="inlineStr">
+      <c r="C736" t="inlineStr">
         <is>
           <t>コーヒー ,名言</t>
         </is>
       </c>
     </row>
-    <row r="738">
-      <c r="A738" t="inlineStr">
+    <row r="737">
+      <c r="A737" t="inlineStr">
         <is>
           <t xml:space="preserve">「星々で飾られた空。魅惑的な色合いで黄昏の美を満たしている」
 سماء مرصعة بالنجوم تضفي لمسة سحرية على جمال الشفق
@@ -15957,19 +15938,19 @@
 2010 https://twitter.com/NatGeoMagArab/status/1303777701975584768 </t>
         </is>
       </c>
-      <c r="B738" t="inlineStr">
+      <c r="B737" t="inlineStr">
         <is>
           <t>images/「星々で飾られた空。魅惑的な色合いで黄.png</t>
         </is>
       </c>
-      <c r="C738" t="inlineStr">
+      <c r="C737" t="inlineStr">
         <is>
           <t>星空 ,宇宙</t>
         </is>
       </c>
     </row>
-    <row r="739">
-      <c r="A739" t="inlineStr">
+    <row r="738">
+      <c r="A738" t="inlineStr">
         <is>
           <t xml:space="preserve">「国際宇宙ステーションからの写真。巨大な台風『ハイシェン（海神）』を映している」
 لقطات من محطة الفضاء الدولية تظهر إعصار "هايشن" الهائل
@@ -15977,19 +15958,19 @@
 2403 https://twitter.com/NatGeoMagArab/status/1302871968522235904 </t>
         </is>
       </c>
-      <c r="B739" t="inlineStr">
+      <c r="B738" t="inlineStr">
         <is>
           <t>images/「国際宇宙ステーションからの写真。巨大.png</t>
         </is>
       </c>
-      <c r="C739" t="inlineStr">
+      <c r="C738" t="inlineStr">
         <is>
           <t>台風</t>
         </is>
       </c>
     </row>
-    <row r="740">
-      <c r="A740" t="inlineStr">
+    <row r="739">
+      <c r="A739" t="inlineStr">
         <is>
           <t xml:space="preserve">「草を食む幸運な子羊たち」
 خراف محظوظة ترعى
@@ -15999,19 +15980,19 @@
 2308 https://twitter.com/NatGeoMagArab/status/1490211393554972676 </t>
         </is>
       </c>
-      <c r="B740" t="inlineStr">
+      <c r="B739" t="inlineStr">
         <is>
           <t>images/「草を食む幸運な子羊たち」_img1.jpg,images/ 「草を食む幸運な子羊たち」_img2.jpg</t>
         </is>
       </c>
-      <c r="C740" t="inlineStr">
+      <c r="C739" t="inlineStr">
         <is>
           <t>羊 ,アイルランド</t>
         </is>
       </c>
     </row>
-    <row r="741">
-      <c r="A741" t="inlineStr">
+    <row r="740">
+      <c r="A740" t="inlineStr">
         <is>
           <t xml:space="preserve">「お金で買えぬ10のもの」
 ١٠ أشياء لا تشترى بالمال
@@ -16021,19 +16002,19 @@
 2308 ayb124 </t>
         </is>
       </c>
-      <c r="B741" t="inlineStr">
+      <c r="B740" t="inlineStr">
         <is>
           <t>images/「お金で買えぬ10のもの」_img1.jpg</t>
         </is>
       </c>
-      <c r="C741" t="inlineStr">
+      <c r="C740" t="inlineStr">
         <is>
           <t>価値 ,購買</t>
         </is>
       </c>
     </row>
-    <row r="742">
-      <c r="A742" t="inlineStr">
+    <row r="741">
+      <c r="A741" t="inlineStr">
         <is>
           <t xml:space="preserve">「お金では買えないよ」
 هي أشْيَاءٌ لا تُشْتَرَى
@@ -16043,19 +16024,19 @@
 1906 mardy_zaawely, Instagram </t>
         </is>
       </c>
-      <c r="B742" t="inlineStr">
+      <c r="B741" t="inlineStr">
         <is>
           <t>images/「お金では買えないよ」_img1.jpg</t>
         </is>
       </c>
-      <c r="C742" t="inlineStr">
+      <c r="C741" t="inlineStr">
         <is>
           <t>マスターカード ,価値</t>
         </is>
       </c>
     </row>
-    <row r="743">
-      <c r="A743" t="inlineStr">
+    <row r="742">
+      <c r="A742" t="inlineStr">
         <is>
           <t xml:space="preserve">「好奇心旺盛なホッキョクギツネ」
 ثعلب قطبي يملؤه الفضول
@@ -16065,15 +16046,15 @@
 2308 https://twitter.com/natgeomagarab/status/1157592172968808449 </t>
         </is>
       </c>
-      <c r="B743" t="inlineStr"/>
-      <c r="C743" t="inlineStr">
+      <c r="B742" t="inlineStr"/>
+      <c r="C742" t="inlineStr">
         <is>
           <t>ファーストコンタクト ,キツネ</t>
         </is>
       </c>
     </row>
-    <row r="744">
-      <c r="A744" t="inlineStr">
+    <row r="743">
+      <c r="A743" t="inlineStr">
         <is>
           <t xml:space="preserve">「グレンダイザーのいる国は死にません」
 لنْ يَموتَ شَعبٌ لدَيهِ غرندايزر
@@ -16082,56 +16063,56 @@
 2308 https://www.aljarida.com/articles/1462241741574732100/ </t>
         </is>
       </c>
+      <c r="B743" t="inlineStr">
+        <is>
+          <t>images/「グレンダイザーのいる国は死にません」_img1.jpg</t>
+        </is>
+      </c>
+      <c r="C743" t="inlineStr">
+        <is>
+          <t>UFOロボ ,アニメ</t>
+        </is>
+      </c>
+    </row>
+    <row r="744">
+      <c r="A744" t="inlineStr">
+        <is>
+          <t xml:space="preserve">「凍結路面を運転中、彼女は嫌な場面に居合わせた」
+2408 https://twitter.com/NatGeoMagArab/status/1610305209657626625 </t>
+        </is>
+      </c>
       <c r="B744" t="inlineStr">
         <is>
-          <t>images/「グレンダイザーのいる国は死にません」_img1.jpg</t>
+          <t>images/「凍結路面を運転中、彼女は嫌な場面に居_img1.jpg</t>
         </is>
       </c>
       <c r="C744" t="inlineStr">
         <is>
-          <t>UFOロボ ,アニメ</t>
+          <t>手書き語学 ,アラビア語 ,路面凍結</t>
         </is>
       </c>
     </row>
     <row r="745">
       <c r="A745" t="inlineStr">
-        <is>
-          <t xml:space="preserve">「凍結路面を運転中、彼女は嫌な場面に居合わせた」
-2408 https://twitter.com/NatGeoMagArab/status/1610305209657626625 </t>
-        </is>
-      </c>
-      <c r="B745" t="inlineStr">
-        <is>
-          <t>images/「凍結路面を運転中、彼女は嫌な場面に居_img1.jpg</t>
-        </is>
-      </c>
-      <c r="C745" t="inlineStr">
-        <is>
-          <t>手書き語学 ,アラビア語 ,路面凍結</t>
-        </is>
-      </c>
-    </row>
-    <row r="746">
-      <c r="A746" t="inlineStr">
         <is>
           <t xml:space="preserve">「虹が美しさを加えている、アルパカという動物の美しいショット」
 ⁦「美しいショット」[laq_tatun jamiilatun]：「ショット」( لقطة )[laq_ta]：( ـلٌ )[-lun]・( ـقٌ )[-qun]・( ـطٌ )[-_tun]・( ـةٌ )[-tun]⁩
 2308 https://twitter.com/natgeomagarab/status/1155115655928004608 </t>
         </is>
       </c>
-      <c r="B746" t="inlineStr">
+      <c r="B745" t="inlineStr">
         <is>
           <t>images/「虹が美しさを加えている、アルパカとい_img1.jpg</t>
         </is>
       </c>
-      <c r="C746" t="inlineStr">
+      <c r="C745" t="inlineStr">
         <is>
           <t>モフモフ ,アルパカ</t>
         </is>
       </c>
     </row>
-    <row r="747">
-      <c r="A747" t="inlineStr">
+    <row r="746">
+      <c r="A746" t="inlineStr">
         <is>
           <t xml:space="preserve">「幸せは…全然思いもよらない所からやって来る」
 السعادة تأتينا من أماكن لم نكن نتوقعها أبداً
@@ -16140,19 +16121,19 @@
 2109 出典不明 </t>
         </is>
       </c>
-      <c r="B747" t="inlineStr">
+      <c r="B746" t="inlineStr">
         <is>
           <t>images/「幸せは…全然思いもよらない所からやっ_img1.jpg,images/ 「幸せは…全然思いもよらない所からやっ_img2.jpg</t>
         </is>
       </c>
-      <c r="C747" t="inlineStr">
+      <c r="C746" t="inlineStr">
         <is>
           <t>訪れ ,予想</t>
         </is>
       </c>
     </row>
-    <row r="748">
-      <c r="A748" t="inlineStr">
+    <row r="747">
+      <c r="A747" t="inlineStr">
         <is>
           <t xml:space="preserve">「あらゆる問題は、食べ物が解決してくれる」
 كل مشكلة ولها أكلة تحلها
@@ -16161,19 +16142,19 @@
 1909 ALQA AN 878 </t>
         </is>
       </c>
-      <c r="B748" t="inlineStr">
+      <c r="B747" t="inlineStr">
         <is>
           <t>images/「あらゆる問題は、食べ物が解決してくれ_img1.jpg</t>
         </is>
       </c>
-      <c r="C748" t="inlineStr">
+      <c r="C747" t="inlineStr">
         <is>
           <t>ストレス ,精神</t>
         </is>
       </c>
     </row>
-    <row r="749">
-      <c r="A749" t="inlineStr">
+    <row r="748">
+      <c r="A748" t="inlineStr">
         <is>
           <t xml:space="preserve">「冬で私が好きな物」
 أشياء أحبها بالشتاء
@@ -16183,19 +16164,19 @@
 2109 出典不明 </t>
         </is>
       </c>
-      <c r="B749" t="inlineStr">
+      <c r="B748" t="inlineStr">
         <is>
           <t>images/「冬で私が好きな物」_img1.jpg</t>
         </is>
       </c>
-      <c r="C749" t="inlineStr">
+      <c r="C748" t="inlineStr">
         <is>
           <t>季節 ,冬</t>
         </is>
       </c>
     </row>
-    <row r="750">
-      <c r="A750" t="inlineStr">
+    <row r="749">
+      <c r="A749" t="inlineStr">
         <is>
           <t xml:space="preserve">「お金で買うことの出来ない物」
 أشياء لا تستطيع شراءها بالمال
@@ -16205,19 +16186,19 @@
 2409 https://x.com/akhbarak/status/1038402708414373888 </t>
         </is>
       </c>
-      <c r="B750" t="inlineStr">
+      <c r="B749" t="inlineStr">
         <is>
           <t>images/「お金で買うことの出来ない物」_img1.jpg,images/ 「お金で買うことの出来ない物」_img2.jpg</t>
         </is>
       </c>
-      <c r="C750" t="inlineStr">
+      <c r="C749" t="inlineStr">
         <is>
           <t>ショッピング ,価値</t>
         </is>
       </c>
     </row>
-    <row r="751">
-      <c r="A751" t="inlineStr">
+    <row r="750">
+      <c r="A750" t="inlineStr">
         <is>
           <t xml:space="preserve">「私たちが愛する言葉」
 كلماتٌ نُحبّها
@@ -16227,19 +16208,19 @@
 2109 جليل خزعل </t>
         </is>
       </c>
-      <c r="B751" t="inlineStr">
+      <c r="B750" t="inlineStr">
         <is>
           <t>images/「私たちが愛する言葉」_img1.jpg</t>
         </is>
       </c>
-      <c r="C751" t="inlineStr">
+      <c r="C750" t="inlineStr">
         <is>
           <t>花 ,贈り物</t>
         </is>
       </c>
     </row>
-    <row r="752">
-      <c r="A752" t="inlineStr">
+    <row r="751">
+      <c r="A751" t="inlineStr">
         <is>
           <t xml:space="preserve">「お茶についてあなたが知らない10の事実」
 عشر معلومات لا تعرفها عن الشاي
@@ -16248,19 +16229,19 @@
 2012 http://ara.tv/6syq2 </t>
         </is>
       </c>
-      <c r="B752" t="inlineStr">
+      <c r="B751" t="inlineStr">
         <is>
           <t>images/「お茶についてあなたが知らない10の事_img1.jpg</t>
         </is>
       </c>
-      <c r="C752" t="inlineStr">
+      <c r="C751" t="inlineStr">
         <is>
           <t>神農</t>
         </is>
       </c>
     </row>
-    <row r="753">
-      <c r="A753" t="inlineStr">
+    <row r="752">
+      <c r="A752" t="inlineStr">
         <is>
           <t xml:space="preserve">「大きくなったウソ」
 الكذبة الّتي كبرت
@@ -16270,19 +16251,19 @@
 2509 سلسلة الحلزونة </t>
         </is>
       </c>
-      <c r="B753" t="inlineStr">
+      <c r="B752" t="inlineStr">
         <is>
           <t>images/「大きくなったウソ」_img1.jpg</t>
         </is>
       </c>
-      <c r="C753" t="inlineStr">
+      <c r="C752" t="inlineStr">
         <is>
           <t>絵本</t>
         </is>
       </c>
     </row>
-    <row r="754">
-      <c r="A754" t="inlineStr">
+    <row r="753">
+      <c r="A753" t="inlineStr">
         <is>
           <t xml:space="preserve">「自分に合った掃除機を買うには？」
 كيف تشتري المكنسة الكهربائية التي تناسبك؟
@@ -16291,19 +16272,19 @@
 2106 ts3a com </t>
         </is>
       </c>
-      <c r="B754" t="inlineStr">
+      <c r="B753" t="inlineStr">
         <is>
           <t>images/「自分に合った掃除機を買うには？」_img1.jpg</t>
         </is>
       </c>
-      <c r="C754" t="inlineStr">
+      <c r="C753" t="inlineStr">
         <is>
           <t>家電 ,掃除</t>
         </is>
       </c>
     </row>
-    <row r="755">
-      <c r="A755" t="inlineStr">
+    <row r="754">
+      <c r="A754" t="inlineStr">
         <is>
           <t xml:space="preserve">「仮にこれが批判の数としよう」
 لنفرض ان عدد الذين ينتقدونك
@@ -16314,19 +16295,19 @@
 2504 出典不明 </t>
         </is>
       </c>
-      <c r="B755" t="inlineStr">
+      <c r="B754" t="inlineStr">
         <is>
           <t>images/「仮にこれが批判の数としよう」_img1.jpg</t>
         </is>
       </c>
-      <c r="C755" t="inlineStr">
+      <c r="C754" t="inlineStr">
         <is>
           <t>アンチ</t>
         </is>
       </c>
     </row>
-    <row r="756">
-      <c r="A756" t="inlineStr">
+    <row r="755">
+      <c r="A755" t="inlineStr">
         <is>
           <t xml:space="preserve">「ここに見えるのは何？」
 ما الذي تراه هنا؟
@@ -16336,15 +16317,15 @@
 2204 https://twitter.com/NatGeoMagArab/status/1506933850617700352 </t>
         </is>
       </c>
-      <c r="B756" t="inlineStr"/>
-      <c r="C756" t="inlineStr">
+      <c r="B755" t="inlineStr"/>
+      <c r="C755" t="inlineStr">
         <is>
           <t xml:space="preserve">ペンギン </t>
         </is>
       </c>
     </row>
-    <row r="757">
-      <c r="A757" t="inlineStr">
+    <row r="756">
+      <c r="A756" t="inlineStr">
         <is>
           <t xml:space="preserve">「今日辛いこと、明日は平気だろう」
 ما يؤلم اليوم سيهون غدًا
@@ -16354,19 +16335,19 @@
 2308 basmahjeff </t>
         </is>
       </c>
-      <c r="B757" t="inlineStr">
+      <c r="B756" t="inlineStr">
         <is>
           <t>images/「今日辛いこと、明日は平気だろう」_img1.jpg</t>
         </is>
       </c>
-      <c r="C757" t="inlineStr">
+      <c r="C756" t="inlineStr">
         <is>
           <t>悩み ,達観</t>
         </is>
       </c>
     </row>
-    <row r="758">
-      <c r="A758" t="inlineStr">
+    <row r="757">
+      <c r="A757" t="inlineStr">
         <is>
           <t xml:space="preserve">「自分のすることを好きでなきゃ」
 عليك أن تحب ما تفعل
@@ -16375,19 +16356,19 @@
 1810 Ahmed Elhakeem </t>
         </is>
       </c>
-      <c r="B758" t="inlineStr">
+      <c r="B757" t="inlineStr">
         <is>
           <t>images/「自分のすることを好きでなきゃ」_img1.jpg</t>
         </is>
       </c>
-      <c r="C758" t="inlineStr">
+      <c r="C757" t="inlineStr">
         <is>
           <t>転職 ,かわいい</t>
         </is>
       </c>
     </row>
-    <row r="759">
-      <c r="A759" t="inlineStr">
+    <row r="758">
+      <c r="A758" t="inlineStr">
         <is>
           <t xml:space="preserve">「この地上に生き甲斐あり」
 على هذه الأرض ما يستحق الحياة
@@ -16397,19 +16378,19 @@
 2308 Mahmoud Gafar </t>
         </is>
       </c>
-      <c r="B759" t="inlineStr">
+      <c r="B758" t="inlineStr">
         <is>
           <t>images/「この地上に生き甲斐あり」_img1.jpg</t>
         </is>
       </c>
-      <c r="C759" t="inlineStr">
+      <c r="C758" t="inlineStr">
         <is>
           <t>詩</t>
         </is>
       </c>
     </row>
-    <row r="760">
-      <c r="A760" t="inlineStr">
+    <row r="759">
+      <c r="A759" t="inlineStr">
         <is>
           <t xml:space="preserve">「おそらく、あなたの求めるものはあるだろう」
 لعلَّ ما تَرجوهُ سيَكونُ
@@ -16419,19 +16400,19 @@
 2308 PIXEL Instagram </t>
         </is>
       </c>
-      <c r="B760" t="inlineStr">
+      <c r="B759" t="inlineStr">
         <is>
           <t>images/「おそらく、あなたの求めるものはあるだ_img1.jpg</t>
         </is>
       </c>
-      <c r="C760" t="inlineStr">
+      <c r="C759" t="inlineStr">
         <is>
           <t>願い ,信仰</t>
         </is>
       </c>
     </row>
-    <row r="761">
-      <c r="A761" t="inlineStr">
+    <row r="760">
+      <c r="A760" t="inlineStr">
         <is>
           <t xml:space="preserve">「オレンジの効能が何か知っていますか？」
 هل تعرف ما هي فوائد البرتقال؟
@@ -16441,19 +16422,19 @@
 2308 sadahadhramowt com </t>
         </is>
       </c>
-      <c r="B761" t="inlineStr">
+      <c r="B760" t="inlineStr">
         <is>
           <t>images/「オレンジの効能が何か知っていますか？_img1.jpg</t>
         </is>
       </c>
-      <c r="C761" t="inlineStr">
+      <c r="C760" t="inlineStr">
         <is>
           <t>オレンジ ,フルーツ</t>
         </is>
       </c>
     </row>
-    <row r="762">
-      <c r="A762" t="inlineStr">
+    <row r="761">
+      <c r="A761" t="inlineStr">
         <is>
           <t xml:space="preserve">「遊ぶパンダの光景より可愛いものがありますか？」
 هل هناك ما هو ألطف من مشاهدة الباندا وهي تلعب؟
@@ -16461,19 +16442,19 @@
 2308 https://twitter.com/NatGeoMagArab/status/1494612797858074626 </t>
         </is>
       </c>
-      <c r="B762" t="inlineStr">
+      <c r="B761" t="inlineStr">
         <is>
           <t>images/「遊ぶパンダの光景より可愛いものがあり_img1.jpg</t>
         </is>
       </c>
-      <c r="C762" t="inlineStr">
+      <c r="C761" t="inlineStr">
         <is>
           <t>パンダ ,モコモコ</t>
         </is>
       </c>
     </row>
-    <row r="763">
-      <c r="A763" t="inlineStr">
+    <row r="762">
+      <c r="A762" t="inlineStr">
         <is>
           <t xml:space="preserve">「大事なのは何者だったかじゃない。何者になるかだ」
 ليسَ المُهم ما كُنتَ بل مَا ستكون
@@ -16482,19 +16463,19 @@
 2308 出典不明 </t>
         </is>
       </c>
-      <c r="B763" t="inlineStr">
+      <c r="B762" t="inlineStr">
         <is>
           <t>images/「大事なのは何者だったかじゃない。何者_img1.jpg</t>
         </is>
       </c>
-      <c r="C763" t="inlineStr">
+      <c r="C762" t="inlineStr">
         <is>
           <t>自己実現 ,存在価値</t>
         </is>
       </c>
     </row>
-    <row r="764">
-      <c r="A764" t="inlineStr">
+    <row r="763">
+      <c r="A763" t="inlineStr">
         <is>
           <t xml:space="preserve">「あなたであれ。ありのままが美しいから」
 كُنْ أَنْتَ لأنك جميل كما أنت
@@ -16503,19 +16484,19 @@
 2308 IDREES DESIGN </t>
         </is>
       </c>
-      <c r="B764" t="inlineStr">
+      <c r="B763" t="inlineStr">
         <is>
           <t>images/「あなたであれ。ありのままが美しいから_img1.jpg</t>
         </is>
       </c>
-      <c r="C764" t="inlineStr">
+      <c r="C763" t="inlineStr">
         <is>
           <t>自己肯定 ,BeYourself</t>
         </is>
       </c>
     </row>
-    <row r="765">
-      <c r="A765" t="inlineStr">
+    <row r="764">
+      <c r="A764" t="inlineStr">
         <is>
           <t xml:space="preserve">「恐れの中に生きる者は決して自由になれない」
 من يعش في خوف لن يكون حرا أبدا
@@ -16524,19 +16505,19 @@
 2111 rjeem com </t>
         </is>
       </c>
-      <c r="B765" t="inlineStr">
+      <c r="B764" t="inlineStr">
         <is>
           <t>images/「恐れの中に生きる者は決して自由になれ_img1.jpg,images/ 「恐れの中に生きる者は決して自由になれ_img2.jpg</t>
         </is>
       </c>
-      <c r="C765" t="inlineStr">
+      <c r="C764" t="inlineStr">
         <is>
           <t>勇気 ,壁</t>
         </is>
       </c>
     </row>
-    <row r="766">
-      <c r="A766" t="inlineStr">
+    <row r="765">
+      <c r="A765" t="inlineStr">
         <is>
           <t xml:space="preserve">「己の翼を信じる者は己の重さを案じない」
 من يثق في جناحيه لن يهتم لوزنه
@@ -16545,19 +16526,19 @@
 2308 kmrghani </t>
         </is>
       </c>
-      <c r="B766" t="inlineStr">
+      <c r="B765" t="inlineStr">
         <is>
           <t>images/「己の翼を信じる者は己の重さを案じない_img1.jpg</t>
         </is>
       </c>
-      <c r="C766" t="inlineStr">
+      <c r="C765" t="inlineStr">
         <is>
           <t>自信</t>
         </is>
       </c>
     </row>
-    <row r="767">
-      <c r="A767" t="inlineStr">
+    <row r="766">
+      <c r="A766" t="inlineStr">
         <is>
           <t xml:space="preserve">「珈琲で一番大事な事！誰と飲むか？」
 الأهم من القهوة!! من ستشربها معه؟
@@ -16566,19 +16547,19 @@
 1812 gwid3.tumblr </t>
         </is>
       </c>
-      <c r="B767" t="inlineStr">
+      <c r="B766" t="inlineStr">
         <is>
           <t>images/「珈琲で一番大事な事！誰と飲むか？」_img1.jpg</t>
         </is>
       </c>
-      <c r="C767" t="inlineStr">
+      <c r="C766" t="inlineStr">
         <is>
           <t>コーヒー ,名言</t>
         </is>
       </c>
     </row>
-    <row r="768">
-      <c r="A768" t="inlineStr">
+    <row r="767">
+      <c r="A767" t="inlineStr">
         <is>
           <t xml:space="preserve">「人生は美しい、そう望んだ者には。」
 الحياة جَميلَة .. لمن أراد ذلك
@@ -16588,19 +16569,19 @@
 2109 出典不明 </t>
         </is>
       </c>
-      <c r="B768" t="inlineStr">
+      <c r="B767" t="inlineStr">
         <is>
           <t>images/「人生は美しい、そう望んだ者には。」_img1.jpg</t>
         </is>
       </c>
-      <c r="C768" t="inlineStr">
+      <c r="C767" t="inlineStr">
         <is>
           <t>名言 ,アート</t>
         </is>
       </c>
     </row>
-    <row r="769">
-      <c r="A769" t="inlineStr">
+    <row r="768">
+      <c r="A768" t="inlineStr">
         <is>
           <t xml:space="preserve">「ハム太郎って子を知ってるかい」
 هل تعرفون من هو هامتارو
@@ -16610,19 +16591,19 @@
 2109 </t>
         </is>
       </c>
-      <c r="B769" t="inlineStr">
+      <c r="B768" t="inlineStr">
         <is>
           <t>images/「ハム太郎って子を知ってるかい」_img1.jpg</t>
         </is>
       </c>
-      <c r="C769" t="inlineStr">
+      <c r="C768" t="inlineStr">
         <is>
           <t>オープニング ,ハム太郎</t>
         </is>
       </c>
     </row>
-    <row r="770">
-      <c r="A770" t="inlineStr">
+    <row r="769">
+      <c r="A769" t="inlineStr">
         <is>
           <t xml:space="preserve">「幸せを求める人もいれば、作る人もいる」
 هناك من يبحث عن السعادة وهناك من يصنعها
@@ -16631,19 +16612,19 @@
 2308 hindah tumblr </t>
         </is>
       </c>
-      <c r="B770" t="inlineStr">
+      <c r="B769" t="inlineStr">
         <is>
           <t>images/「幸せを求める人もいれば、作る人もいる_img1.jpg</t>
         </is>
       </c>
-      <c r="C770" t="inlineStr">
+      <c r="C769" t="inlineStr">
         <is>
           <t>幸せ ,名言 ,教訓</t>
         </is>
       </c>
     </row>
-    <row r="771">
-      <c r="A771" t="inlineStr">
+    <row r="770">
+      <c r="A770" t="inlineStr">
         <is>
           <t xml:space="preserve">「明白なるアラブの言葉によって」
 بلسان عربي مبين
@@ -16653,19 +16634,19 @@
 2109 Abdullah Barakat behance </t>
         </is>
       </c>
-      <c r="B771" t="inlineStr">
+      <c r="B770" t="inlineStr">
         <is>
           <t>images/「明白なるアラブの言葉によって」_img1.jpg</t>
         </is>
       </c>
-      <c r="C771" t="inlineStr">
+      <c r="C770" t="inlineStr">
         <is>
           <t>イスラム教 ,神聖</t>
         </is>
       </c>
     </row>
-    <row r="772">
-      <c r="A772" t="inlineStr">
+    <row r="771">
+      <c r="A771" t="inlineStr">
         <is>
           <t xml:space="preserve">「結婚前、結婚後」
 قبل الزواج، بعد الزواج
@@ -16675,19 +16656,19 @@
 2308 出典不明 </t>
         </is>
       </c>
-      <c r="B772" t="inlineStr">
+      <c r="B771" t="inlineStr">
         <is>
           <t>images/「結婚前、結婚後」_img1.jpg</t>
         </is>
       </c>
-      <c r="C772" t="inlineStr">
+      <c r="C771" t="inlineStr">
         <is>
           <t>BeforeAfter ,幸せ太り</t>
         </is>
       </c>
     </row>
-    <row r="773">
-      <c r="A773" t="inlineStr">
+    <row r="772">
+      <c r="A772" t="inlineStr">
         <is>
           <t xml:space="preserve">「驚きの価格で」بسعر رائع
 ビスィアル・ラーイア [bi-si*r raa'i*]
@@ -16696,19 +16677,19 @@
 2109 Jarir Bookstore </t>
         </is>
       </c>
-      <c r="B773" t="inlineStr">
+      <c r="B772" t="inlineStr">
         <is>
           <t>images/「驚きの価格で」_img1.jpg</t>
         </is>
       </c>
-      <c r="C773" t="inlineStr">
+      <c r="C772" t="inlineStr">
         <is>
           <t>広告 ,安値</t>
         </is>
       </c>
     </row>
-    <row r="774">
-      <c r="A774" t="inlineStr">
+    <row r="773">
+      <c r="A773" t="inlineStr">
         <is>
           <t xml:space="preserve">「我が魂と共に」مع نفسي
 マア・ナフスィ [ma*a nafs-iy]
@@ -16717,19 +16698,19 @@
 2110 出典不明 </t>
         </is>
       </c>
-      <c r="B774" t="inlineStr">
+      <c r="B773" t="inlineStr">
         <is>
           <t>images/「我が魂と共に」_img1.jpg</t>
         </is>
       </c>
-      <c r="C774" t="inlineStr">
+      <c r="C773" t="inlineStr">
         <is>
           <t>ソウル ,soul</t>
         </is>
       </c>
     </row>
-    <row r="775">
-      <c r="A775" t="inlineStr">
+    <row r="774">
+      <c r="A774" t="inlineStr">
         <is>
           <t xml:space="preserve">「暗い夜に」في ليلة مظلمة
  [fiy layla(tin) mu_Dhlima(tin)]
@@ -16738,19 +16719,19 @@
 2109 سلسلة الحلزونة </t>
         </is>
       </c>
-      <c r="B775" t="inlineStr">
+      <c r="B774" t="inlineStr">
         <is>
           <t>images/「暗い夜に」_img1.jpg</t>
         </is>
       </c>
-      <c r="C775" t="inlineStr">
+      <c r="C774" t="inlineStr">
         <is>
           <t>絵本</t>
         </is>
       </c>
     </row>
-    <row r="776">
-      <c r="A776" t="inlineStr">
+    <row r="775">
+      <c r="A775" t="inlineStr">
         <is>
           <t xml:space="preserve">「ゆっくりと」بشويش
 ビシワェーシ [bi-ShwySh]
@@ -16758,19 +16739,19 @@
 2109 出典不明 </t>
         </is>
       </c>
-      <c r="B776" t="inlineStr">
+      <c r="B775" t="inlineStr">
         <is>
           <t>images/「ゆっくりと」_img1.jpg</t>
         </is>
       </c>
-      <c r="C776" t="inlineStr">
+      <c r="C775" t="inlineStr">
         <is>
           <t>丸 ,円</t>
         </is>
       </c>
     </row>
-    <row r="777">
-      <c r="A777" t="inlineStr">
+    <row r="776">
+      <c r="A776" t="inlineStr">
         <is>
           <t xml:space="preserve">「この広い宇宙に…」
 في الكون الفسيح
@@ -16779,19 +16760,19 @@
 2308 wattpad </t>
         </is>
       </c>
-      <c r="B777" t="inlineStr">
+      <c r="B776" t="inlineStr">
         <is>
           <t>images/「この広い宇宙に…」_img1.jpg</t>
         </is>
       </c>
-      <c r="C777" t="inlineStr">
+      <c r="C776" t="inlineStr">
         <is>
           <t>アニメ ,宇宙</t>
         </is>
       </c>
     </row>
-    <row r="778">
-      <c r="A778" t="inlineStr">
+    <row r="777">
+      <c r="A777" t="inlineStr">
         <is>
           <t xml:space="preserve">「がんばって！」بالتوفيق
 ビッタウフィーク [bi^tawfiiq]
@@ -16799,19 +16780,19 @@
 2111 https://sites.google.com/site/mathmatic1905/ </t>
         </is>
       </c>
-      <c r="B778" t="inlineStr">
+      <c r="B777" t="inlineStr">
         <is>
           <t>images/「がんばって！」_img1.jpg</t>
         </is>
       </c>
-      <c r="C778" t="inlineStr">
+      <c r="C777" t="inlineStr">
         <is>
           <t>アラビア語</t>
         </is>
       </c>
     </row>
-    <row r="779">
-      <c r="A779" t="inlineStr">
+    <row r="778">
+      <c r="A778" t="inlineStr">
         <is>
           <t xml:space="preserve">「インターステラー」بين النجوم
 バイナ_ンヌジューム [bayna ^nujuum]
@@ -16819,19 +16800,19 @@
 2308 kmrghani </t>
         </is>
       </c>
-      <c r="B779" t="inlineStr">
+      <c r="B778" t="inlineStr">
         <is>
           <t>images/「インターステラー」_img1.jpg</t>
         </is>
       </c>
-      <c r="C779" t="inlineStr">
+      <c r="C778" t="inlineStr">
         <is>
           <t>映画 ,宇宙</t>
         </is>
       </c>
     </row>
-    <row r="780">
-      <c r="A780" t="inlineStr">
+    <row r="779">
+      <c r="A779" t="inlineStr">
         <is>
           <t xml:space="preserve">「アラビア語で」بالعربية
 ビ_ルアラビーヤ [bi-l-*arabiyya]
@@ -16840,19 +16821,19 @@
 1811 </t>
         </is>
       </c>
-      <c r="B780" t="inlineStr">
+      <c r="B779" t="inlineStr">
         <is>
           <t>images/「アラビア語で」_img1.jpg</t>
         </is>
       </c>
-      <c r="C780" t="inlineStr">
+      <c r="C779" t="inlineStr">
         <is>
           <t>ニュース ,CNN</t>
         </is>
       </c>
     </row>
-    <row r="781">
-      <c r="A781" t="inlineStr">
+    <row r="780">
+      <c r="A780" t="inlineStr">
         <is>
           <t xml:space="preserve">「17世紀に発明されて以来…」
 منذ اختراعه بالقرن السابع عشر
@@ -16860,19 +16841,19 @@
 2308 https://twitter.com/SciTalk2U/status/1450888395815854080 </t>
         </is>
       </c>
-      <c r="B781" t="inlineStr">
+      <c r="B780" t="inlineStr">
         <is>
           <t>images/「17世紀に発明されて以来…」_img1.jpg</t>
         </is>
       </c>
-      <c r="C781" t="inlineStr">
+      <c r="C780" t="inlineStr">
         <is>
           <t>手書き語学 ,アラビア語 ,望遠鏡</t>
         </is>
       </c>
     </row>
-    <row r="782">
-      <c r="A782" t="inlineStr">
+    <row r="781">
+      <c r="A781" t="inlineStr">
         <is>
           <t xml:space="preserve">「私できるよ」إنّني أستطيع
 インナニー・アスタティーウ ['inna-niy 'a-sta_tii*u]
@@ -16881,19 +16862,19 @@
 2412 سلسلة الحلزونة </t>
         </is>
       </c>
-      <c r="B782" t="inlineStr">
+      <c r="B781" t="inlineStr">
         <is>
           <t>images/「私できるよ」_img1.jpg</t>
         </is>
       </c>
-      <c r="C782" t="inlineStr">
+      <c r="C781" t="inlineStr">
         <is>
           <t>絵本 ,こども</t>
         </is>
       </c>
     </row>
-    <row r="783">
-      <c r="A783" t="inlineStr">
+    <row r="782">
+      <c r="A782" t="inlineStr">
         <is>
           <t xml:space="preserve">「問題なし」مافيش مشكلة
 マフィーシムシュキラ [ma-fy-Sh muShkila]
@@ -16902,19 +16883,19 @@
 2109 tanzerin.theshop </t>
         </is>
       </c>
-      <c r="B783" t="inlineStr">
+      <c r="B782" t="inlineStr">
         <is>
           <t>images/「問題なし」_img1.jpg</t>
         </is>
       </c>
-      <c r="C783" t="inlineStr">
+      <c r="C782" t="inlineStr">
         <is>
           <t>シャツ ,キッズ</t>
         </is>
       </c>
     </row>
-    <row r="784">
-      <c r="A784" t="inlineStr">
+    <row r="783">
+      <c r="A783" t="inlineStr">
         <is>
           <t xml:space="preserve">「不可能はない」مفيش مستحيل
 マフィーシ・ムスタヒール [ma-fy-Sh mustaHiil]
@@ -16923,19 +16904,19 @@
 2109 أموج </t>
         </is>
       </c>
-      <c r="B784" t="inlineStr">
+      <c r="B783" t="inlineStr">
         <is>
           <t>images/「不可能はない」_img1.jpg</t>
         </is>
       </c>
-      <c r="C784" t="inlineStr">
+      <c r="C783" t="inlineStr">
         <is>
           <t>ポジティブ ,挑戦</t>
         </is>
       </c>
     </row>
-    <row r="785">
-      <c r="A785" t="inlineStr">
+    <row r="784">
+      <c r="A784" t="inlineStr">
         <is>
           <t xml:space="preserve">「等々」إلخ
 イラク ['ilaKh]
@@ -16944,19 +16925,19 @@
 2201 出典不明 </t>
         </is>
       </c>
-      <c r="B785" t="inlineStr">
+      <c r="B784" t="inlineStr">
         <is>
           <t>images/「等々」_img1.jpg</t>
         </is>
       </c>
-      <c r="C785" t="inlineStr">
+      <c r="C784" t="inlineStr">
         <is>
           <t>etc ,とんち</t>
         </is>
       </c>
     </row>
-    <row r="786">
-      <c r="A786" t="inlineStr">
+    <row r="785">
+      <c r="A785" t="inlineStr">
         <is>
           <t xml:space="preserve">⁦「調子どう？」⁩شلونَك؟
 シュローナク？ [Sh-loon-ak?]
@@ -16965,19 +16946,19 @@
 2202 Jozoor Team. </t>
         </is>
       </c>
-      <c r="B786" t="inlineStr">
+      <c r="B785" t="inlineStr">
         <is>
           <t>images/⁦「調子どう？」⁩_img1.jpg</t>
         </is>
       </c>
-      <c r="C786" t="inlineStr">
+      <c r="C785" t="inlineStr">
         <is>
           <t>洒落 ,ルービックキューブ</t>
         </is>
       </c>
     </row>
-    <row r="787">
-      <c r="A787" t="inlineStr">
+    <row r="786">
+      <c r="A786" t="inlineStr">
         <is>
           <t xml:space="preserve">「行くな」ماتروحش
 マトロホシ [ma-troH-Sh]
@@ -16986,19 +16967,19 @@
 2411 triiq tumblr </t>
         </is>
       </c>
-      <c r="B787" t="inlineStr">
+      <c r="B786" t="inlineStr">
         <is>
           <t>images/「行くな」_img1.jpg</t>
         </is>
       </c>
-      <c r="C787" t="inlineStr">
+      <c r="C786" t="inlineStr">
         <is>
           <t>ロゴ ,デザイン ,嵐</t>
         </is>
       </c>
     </row>
-    <row r="788">
-      <c r="A788" t="inlineStr">
+    <row r="787">
+      <c r="A787" t="inlineStr">
         <is>
           <t xml:space="preserve">⁦「元気？」⁩شلونَك؟
 シュローナク？ [Sh-loon-ak?]
@@ -17009,19 +16990,19 @@
 2202 出典不明 </t>
         </is>
       </c>
-      <c r="B788" t="inlineStr">
+      <c r="B787" t="inlineStr">
         <is>
           <t>images/⁦「元気？」⁩_img1.jpg</t>
         </is>
       </c>
-      <c r="C788" t="inlineStr">
+      <c r="C787" t="inlineStr">
         <is>
           <t>洒落 ,挨拶</t>
         </is>
       </c>
     </row>
-    <row r="789">
-      <c r="A789" t="inlineStr">
+    <row r="788">
+      <c r="A788" t="inlineStr">
         <is>
           <t xml:space="preserve">「気分が良いぞう」I فيل GOOD
 アイ・フィール・グッド [ai fiyl gud]
@@ -17030,19 +17011,19 @@
 2308 出典不明 </t>
         </is>
       </c>
-      <c r="B789" t="inlineStr">
+      <c r="B788" t="inlineStr">
         <is>
           <t>images/「気分が良いぞう」_img1.jpg</t>
         </is>
       </c>
-      <c r="C789" t="inlineStr">
+      <c r="C788" t="inlineStr">
         <is>
           <t>洒落 ,和訳</t>
         </is>
       </c>
     </row>
-    <row r="790">
-      <c r="A790" t="inlineStr">
+    <row r="789">
+      <c r="A789" t="inlineStr">
         <is>
           <t xml:space="preserve">「レットイットゴー／let it go」
 ليت اِت غو
@@ -17051,19 +17032,19 @@
 2109 出典不明 </t>
         </is>
       </c>
-      <c r="B790" t="inlineStr">
+      <c r="B789" t="inlineStr">
         <is>
           <t>images/「レットイットゴー／let it go_img1.jpg</t>
         </is>
       </c>
-      <c r="C790" t="inlineStr">
+      <c r="C789" t="inlineStr">
         <is>
           <t>折衷 ,アナ雪</t>
         </is>
       </c>
     </row>
-    <row r="791">
-      <c r="A791" t="inlineStr">
+    <row r="790">
+      <c r="A790" t="inlineStr">
         <is>
           <t xml:space="preserve">「ようこそ」اهلا وسهلا
 アハラン・ワサハラン ['ahlan wa-sahlan]
@@ -17071,19 +17052,19 @@
 2106 behance Anwar Al Eissa </t>
         </is>
       </c>
-      <c r="B791" t="inlineStr">
+      <c r="B790" t="inlineStr">
         <is>
           <t>images/「ようこそ」_img1.jpg</t>
         </is>
       </c>
-      <c r="C791" t="inlineStr">
+      <c r="C790" t="inlineStr">
         <is>
           <t>アラビア語</t>
         </is>
       </c>
     </row>
-    <row r="792">
-      <c r="A792" t="inlineStr">
+    <row r="791">
+      <c r="A791" t="inlineStr">
         <is>
           <t xml:space="preserve">「まぁ何というサプライズでしょう」
 يا لها من مفاجأة
@@ -17094,19 +17075,19 @@
 2108 neelwafurat com </t>
         </is>
       </c>
-      <c r="B792" t="inlineStr">
+      <c r="B791" t="inlineStr">
         <is>
           <t>images/「まぁ何というサプライズでしょう」_img1.jpg</t>
         </is>
       </c>
-      <c r="C792" t="inlineStr">
+      <c r="C791" t="inlineStr">
         <is>
           <t>中国語 ,学習</t>
         </is>
       </c>
     </row>
-    <row r="793">
-      <c r="A793" t="inlineStr">
+    <row r="792">
+      <c r="A792" t="inlineStr">
         <is>
           <t xml:space="preserve">「ハックション」اتشوو
 アチュー！ ['aatShuu]
@@ -17114,19 +17095,19 @@
 1811 </t>
         </is>
       </c>
-      <c r="B793" t="inlineStr">
+      <c r="B792" t="inlineStr">
         <is>
           <t>images/「ハックション」_img1.jpg</t>
         </is>
       </c>
-      <c r="C793" t="inlineStr">
+      <c r="C792" t="inlineStr">
         <is>
           <t>あらびあや</t>
         </is>
       </c>
     </row>
-    <row r="794">
-      <c r="A794" t="inlineStr">
+    <row r="793">
+      <c r="A793" t="inlineStr">
         <is>
           <t xml:space="preserve">「スブハーナッラー」「アルハムドゥリッラー」「アッラーアクバル」
 سبحان الله
@@ -17137,19 +17118,19 @@
 2308 dribbble com </t>
         </is>
       </c>
-      <c r="B794" t="inlineStr">
+      <c r="B793" t="inlineStr">
         <is>
           <t>images/「スブハーナッラー」「アルハムドゥリッ_img1.jpg</t>
         </is>
       </c>
-      <c r="C794" t="inlineStr">
+      <c r="C793" t="inlineStr">
         <is>
           <t>四角 ,コンパクト</t>
         </is>
       </c>
     </row>
-    <row r="795">
-      <c r="A795" t="inlineStr">
+    <row r="794">
+      <c r="A794" t="inlineStr">
         <is>
           <t xml:space="preserve">「すごく美味しい！」لذيذ جدًا
 ラズィーズ・ジッダン [laDhiiDh jiddan]
@@ -17158,19 +17139,19 @@
 2109 goodreads com </t>
         </is>
       </c>
-      <c r="B795" t="inlineStr">
+      <c r="B794" t="inlineStr">
         <is>
           <t>images/「すごく美味しい！」_img1.jpg</t>
         </is>
       </c>
-      <c r="C795" t="inlineStr">
+      <c r="C794" t="inlineStr">
         <is>
           <t>フレーズ ,感想</t>
         </is>
       </c>
     </row>
-    <row r="796">
-      <c r="A796" t="inlineStr">
+    <row r="795">
+      <c r="A795" t="inlineStr">
         <is>
           <t xml:space="preserve">「しとしと、雨」تك تك يا مطر
 ティクティク [tik tik yaa ma_tar]
@@ -17179,19 +17160,19 @@
 2308 出典不明 </t>
         </is>
       </c>
-      <c r="B796" t="inlineStr">
+      <c r="B795" t="inlineStr">
         <is>
           <t>images/「しとしと、雨」_img1.jpg</t>
         </is>
       </c>
-      <c r="C796" t="inlineStr">
+      <c r="C795" t="inlineStr">
         <is>
           <t>天気 ,梅雨</t>
         </is>
       </c>
     </row>
-    <row r="797">
-      <c r="A797" t="inlineStr">
+    <row r="796">
+      <c r="A796" t="inlineStr">
         <is>
           <t xml:space="preserve">「さかさま」رأساً على عقب
 ラッアサン・アラー・アケブ [ra'san *alaa *aqib]
@@ -17199,19 +17180,19 @@
 2109 出典不明 </t>
         </is>
       </c>
-      <c r="B797" t="inlineStr">
+      <c r="B796" t="inlineStr">
         <is>
           <t>images/「さかさま」_img1.jpg</t>
         </is>
       </c>
-      <c r="C797" t="inlineStr">
+      <c r="C796" t="inlineStr">
         <is>
           <t>壁 ,上下</t>
         </is>
       </c>
     </row>
-    <row r="798">
-      <c r="A798" t="inlineStr">
+    <row r="797">
+      <c r="A797" t="inlineStr">
         <is>
           <t xml:space="preserve">「エジプトよどこへ行った」
 فينك يا مصر؟
@@ -17221,19 +17202,19 @@
 1809 shehabfawzy1.tumblr </t>
         </is>
       </c>
-      <c r="B798" t="inlineStr">
+      <c r="B797" t="inlineStr">
         <is>
           <t>images/「エジプトよどこへ行った」_img1.jpg</t>
         </is>
       </c>
-      <c r="C798" t="inlineStr">
+      <c r="C797" t="inlineStr">
         <is>
           <t>ピラミッド ,歴史</t>
         </is>
       </c>
     </row>
-    <row r="799">
-      <c r="A799" t="inlineStr">
+    <row r="798">
+      <c r="A798" t="inlineStr">
         <is>
           <t xml:space="preserve">「ありがとう」شكراً
 シュクラン [Shukran]
@@ -17241,19 +17222,19 @@
 2109 出典不明 </t>
         </is>
       </c>
-      <c r="B799" t="inlineStr">
+      <c r="B798" t="inlineStr">
         <is>
           <t>images/「ありがとう」_img1.jpg</t>
         </is>
       </c>
-      <c r="C799" t="inlineStr">
+      <c r="C798" t="inlineStr">
         <is>
           <t>挨拶 ,文字</t>
         </is>
       </c>
     </row>
-    <row r="800">
-      <c r="A800" t="inlineStr">
+    <row r="799">
+      <c r="A799" t="inlineStr">
         <is>
           <t xml:space="preserve">「昼寝の時間だ」
 إنه وقت القيلولة
@@ -17262,12 +17243,12 @@
 2501 https://x.com/NatGeoMagArab/status/1858049951579910486 </t>
         </is>
       </c>
-      <c r="B800" t="inlineStr">
+      <c r="B799" t="inlineStr">
         <is>
           <t>images/「昼寝の時間だ」_img1.jpg</t>
         </is>
       </c>
-      <c r="C800" t="inlineStr">
+      <c r="C799" t="inlineStr">
         <is>
           <t>手書き語学 ,アラビア語 ,ペンギン</t>
         </is>

--- a/posts.xlsx
+++ b/posts.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C799"/>
+  <dimension ref="A1:C798"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -11645,27 +11645,6 @@
     <row r="535">
       <c r="A535" t="inlineStr">
         <is>
-          <t xml:space="preserve">「私は戻らない」لن اعود
-ラン・アウード [lan 'a-*uud(a)]
-⁦「私は戻る」( أعود )['a-*uud]・「私が戻るということ」( أن أعود )['an 'a-*uuda]：「戻った」( عاد )[*aada]⁩
-私（わたし）・戻る（もどる）
-2109 elcinema com </t>
-        </is>
-      </c>
-      <c r="B535" t="inlineStr">
-        <is>
-          <t>images/「私は戻らない」_img1.jpg</t>
-        </is>
-      </c>
-      <c r="C535" t="inlineStr">
-        <is>
-          <t>タイトル ,なんちゅう顔しとる</t>
-        </is>
-      </c>
-    </row>
-    <row r="536">
-      <c r="A536" t="inlineStr">
-        <is>
           <t xml:space="preserve">「私は作家になるのが夢です」
 أحلُمُ أن أكونَ كاتبة
 ['a-Hlumu 'an 'a-kuuna kaatiba]
@@ -11674,19 +11653,19 @@
 2308 Maktabatee com </t>
         </is>
       </c>
-      <c r="B536" t="inlineStr">
+      <c r="B535" t="inlineStr">
         <is>
           <t>images/「私は作家になるのが夢です」_img1.jpg</t>
         </is>
       </c>
-      <c r="C536" t="inlineStr">
+      <c r="C535" t="inlineStr">
         <is>
           <t>作家志望 ,ライター</t>
         </is>
       </c>
     </row>
-    <row r="537">
-      <c r="A537" t="inlineStr">
+    <row r="536">
+      <c r="A536" t="inlineStr">
         <is>
           <t xml:space="preserve">「あなたが去った後も波は止みません」
 لن يقف الموج بعد رحيلك
@@ -11696,19 +11675,19 @@
 2308 ريم الشاوش https://ar.arabwomanmag.com/%D9%84%D9%86-%D9%8A%D9%82%D9%81-%D8%A7%D9%84%D9%85%D9%88%D8%AC-%D8%A8%D8%B9%D8%AF-%D8%B1%D8%AD%D9%8A%D9%84%D9%83-%D8%A8%D8%B9%D8%AF-%D8%B1%D8%AD%D9%8A%D9%84%D9%83/ </t>
         </is>
       </c>
-      <c r="B537" t="inlineStr">
+      <c r="B536" t="inlineStr">
         <is>
           <t>images/「あなたが去った後も波は止みません」_img1.jpg</t>
         </is>
       </c>
-      <c r="C537" t="inlineStr">
+      <c r="C536" t="inlineStr">
         <is>
           <t>海 ,哲学</t>
         </is>
       </c>
     </row>
-    <row r="538">
-      <c r="A538" t="inlineStr">
+    <row r="537">
+      <c r="A537" t="inlineStr">
         <is>
           <t xml:space="preserve">「彼の尖った牙を心配するな」
 لا تدع أنيابه المدببة تقلقك
@@ -11717,19 +11696,19 @@
 2308 https://twitter.com/NatGeoMagArab/status/1524691046818406400 </t>
         </is>
       </c>
-      <c r="B538" t="inlineStr">
+      <c r="B537" t="inlineStr">
         <is>
           <t>images/「彼の尖った牙を心配するな」_img1.jpg,images/「彼の尖った牙を心配するな」_img2.jpg,images/「彼の尖った牙を心配するな」_img3.jpg</t>
         </is>
       </c>
-      <c r="C538" t="inlineStr">
+      <c r="C537" t="inlineStr">
         <is>
           <t xml:space="preserve">手書き語学 ,アラビア語 ,キバノロ </t>
         </is>
       </c>
     </row>
-    <row r="539">
-      <c r="A539" t="inlineStr">
+    <row r="538">
+      <c r="A538" t="inlineStr">
         <is>
           <t xml:space="preserve">「恐れるな」لا تخف
 ラー・タカフ [laa ta-Khaf]
@@ -11738,19 +11717,19 @@
 2308 KiTeLetZ </t>
         </is>
       </c>
-      <c r="B539" t="inlineStr">
+      <c r="B538" t="inlineStr">
         <is>
           <t>images/「恐れるな」_img1.jpg</t>
         </is>
       </c>
-      <c r="C539" t="inlineStr">
+      <c r="C538" t="inlineStr">
         <is>
           <t>カリグラフィー ,緑</t>
         </is>
       </c>
     </row>
-    <row r="540">
-      <c r="A540" t="inlineStr">
+    <row r="539">
+      <c r="A539" t="inlineStr">
         <is>
           <t xml:space="preserve">「立ち上がれ。遅すぎることはない」
 انهض. لم يفت الأوان بعد
@@ -11760,19 +11739,19 @@
 2308 typo_g </t>
         </is>
       </c>
-      <c r="B540" t="inlineStr">
+      <c r="B539" t="inlineStr">
         <is>
           <t>images/「立ち上がれ。遅すぎることはない」_img1.jpg</t>
         </is>
       </c>
-      <c r="C540" t="inlineStr">
+      <c r="C539" t="inlineStr">
         <is>
           <t>出発</t>
         </is>
       </c>
     </row>
-    <row r="541">
-      <c r="A541" t="inlineStr">
+    <row r="540">
+      <c r="A540" t="inlineStr">
         <is>
           <t xml:space="preserve">「泣かないで」لا تَبْكِ
 ラー・タブキ [laa ta-bki]
@@ -11781,19 +11760,19 @@
 2203 arwa </t>
         </is>
       </c>
-      <c r="B541" t="inlineStr">
+      <c r="B540" t="inlineStr">
         <is>
           <t>images/「泣かないで」_img1.jpg</t>
         </is>
       </c>
-      <c r="C541" t="inlineStr">
+      <c r="C540" t="inlineStr">
         <is>
           <t>傘 ,虹</t>
         </is>
       </c>
     </row>
-    <row r="542">
-      <c r="A542" t="inlineStr">
+    <row r="541">
+      <c r="A541" t="inlineStr">
         <is>
           <t xml:space="preserve">「強くあるしかない」
 لا تكنْ الا قوِيا
@@ -11803,19 +11782,19 @@
 2401 AHMED ELASSAL </t>
         </is>
       </c>
-      <c r="B542" t="inlineStr">
+      <c r="B541" t="inlineStr">
         <is>
           <t>images/「強くあるしかない」_img1.jpg</t>
         </is>
       </c>
-      <c r="C542" t="inlineStr">
+      <c r="C541" t="inlineStr">
         <is>
           <t>二重否定 ,心構え</t>
         </is>
       </c>
     </row>
-    <row r="543">
-      <c r="A543" t="inlineStr">
+    <row r="542">
+      <c r="A542" t="inlineStr">
         <is>
           <t xml:space="preserve">「止まりなさい」قف
 キフ [qif]
@@ -11825,19 +11804,19 @@
 2308 出典不明（英語版：同内容。中国語版：「今日も可愛いね」） </t>
         </is>
       </c>
-      <c r="B543" t="inlineStr">
+      <c r="B542" t="inlineStr">
         <is>
           <t>images/「止まりなさい」_img1.jpg,images/「止まりなさい」_img2.jpg,images/「止まりなさい」_img3.jpg,images/「止まりなさい」_img4.jpg</t>
         </is>
       </c>
-      <c r="C543" t="inlineStr">
+      <c r="C542" t="inlineStr">
         <is>
           <t>かわいい ,職質</t>
         </is>
       </c>
     </row>
-    <row r="544">
-      <c r="A544" t="inlineStr">
+    <row r="543">
+      <c r="A543" t="inlineStr">
         <is>
           <t xml:space="preserve">「自分の人生を生きろ」عش حياتك
 イシ・ハヤータク [*iSh Hayaata-k]
@@ -11846,19 +11825,19 @@
 2607 Pinterest, hus2013asr </t>
         </is>
       </c>
-      <c r="B544" t="inlineStr">
+      <c r="B543" t="inlineStr">
         <is>
           <t>images/「自分の人生を生きろ」_img1.jpg</t>
         </is>
       </c>
-      <c r="C544" t="inlineStr">
+      <c r="C543" t="inlineStr">
         <is>
           <t>iPhone ,壁紙</t>
         </is>
       </c>
     </row>
-    <row r="545">
-      <c r="A545" t="inlineStr">
+    <row r="544">
+      <c r="A544" t="inlineStr">
         <is>
           <t xml:space="preserve">「おやすみザイナ」نامي يا زينة
 ナーミー・ヤー・ザイナ [naam-ii yaa zayna]
@@ -11867,19 +11846,19 @@
 2511 Dar Alsalwa </t>
         </is>
       </c>
-      <c r="B545" t="inlineStr">
+      <c r="B544" t="inlineStr">
         <is>
           <t>images/「おやすみザイナ」_img1.jpg</t>
         </is>
       </c>
-      <c r="C545" t="inlineStr">
+      <c r="C544" t="inlineStr">
         <is>
           <t>絵本 ,ベッド</t>
         </is>
       </c>
     </row>
-    <row r="546">
-      <c r="A546" t="inlineStr">
+    <row r="545">
+      <c r="A545" t="inlineStr">
         <is>
           <t xml:space="preserve">「強くありなさい」كُن قَوياً
 クン・カウィーヤン [kun qawiiyan]
@@ -11888,19 +11867,19 @@
 2109 MJCODEZ </t>
         </is>
       </c>
-      <c r="B546" t="inlineStr">
+      <c r="B545" t="inlineStr">
         <is>
           <t>images/「強くありなさい」_img1.jpg</t>
         </is>
       </c>
-      <c r="C546" t="inlineStr">
+      <c r="C545" t="inlineStr">
         <is>
           <t>名言 ,強い</t>
         </is>
       </c>
     </row>
-    <row r="547">
-      <c r="A547" t="inlineStr">
+    <row r="546">
+      <c r="A546" t="inlineStr">
         <is>
           <t xml:space="preserve">「強くありなさい、自分のために」
 كُن قويًا لأجلك
@@ -11910,19 +11889,19 @@
 1809 gwid3.tumblr </t>
         </is>
       </c>
-      <c r="B547" t="inlineStr">
+      <c r="B546" t="inlineStr">
         <is>
           <t>images/「強くありなさい、自分のために」_img1.jpg</t>
         </is>
       </c>
-      <c r="C547" t="inlineStr">
+      <c r="C546" t="inlineStr">
         <is>
           <t>名言 ,強い</t>
         </is>
       </c>
     </row>
-    <row r="548">
-      <c r="A548" t="inlineStr">
+    <row r="547">
+      <c r="A547" t="inlineStr">
         <is>
           <t xml:space="preserve">「どこでも自分でありなさい」
 كن أنت أينما كنت
@@ -11932,19 +11911,19 @@
 2605 souqfann com/r/15987  </t>
         </is>
       </c>
-      <c r="B548" t="inlineStr">
+      <c r="B547" t="inlineStr">
         <is>
           <t>images/「どこでも自分でありなさい」_img1.jpg</t>
         </is>
       </c>
-      <c r="C548" t="inlineStr">
+      <c r="C547" t="inlineStr">
         <is>
           <t>デザイン ,アート</t>
         </is>
       </c>
     </row>
-    <row r="549">
-      <c r="A549" t="inlineStr">
+    <row r="548">
+      <c r="A548" t="inlineStr">
         <is>
           <t xml:space="preserve">「止まれ。検問中」قف للتفتيش
 キフ。リッタフティーシ [qif li^taftiiSh]
@@ -11953,19 +11932,19 @@
 2109 Marcel Musil flickr </t>
         </is>
       </c>
-      <c r="B549" t="inlineStr">
+      <c r="B548" t="inlineStr">
         <is>
           <t>images/「止まれ。検問中」_img1.jpg</t>
         </is>
       </c>
-      <c r="C549" t="inlineStr">
+      <c r="C548" t="inlineStr">
         <is>
           <t>標識</t>
         </is>
       </c>
     </row>
-    <row r="550">
-      <c r="A550" t="inlineStr">
+    <row r="549">
+      <c r="A549" t="inlineStr">
         <is>
           <t xml:space="preserve">「さあおやすみ」هَيّا نَمْ
 ハイヤー・ナム [hayyaa nam]
@@ -11973,19 +11952,19 @@
 2308 Maktabatee com </t>
         </is>
       </c>
-      <c r="B550" t="inlineStr">
+      <c r="B549" t="inlineStr">
         <is>
           <t>images/「さあおやすみ」_img1.jpg</t>
         </is>
       </c>
-      <c r="C550" t="inlineStr">
+      <c r="C549" t="inlineStr">
         <is>
           <t>就寝 ,絵本</t>
         </is>
       </c>
     </row>
-    <row r="551">
-      <c r="A551" t="inlineStr">
+    <row r="550">
+      <c r="A550" t="inlineStr">
         <is>
           <t xml:space="preserve">「あなたであれ」كن أنت
 クン・アンタ [ku 'anta]
@@ -11993,19 +11972,19 @@
 1809 madyan22.tumblr </t>
         </is>
       </c>
-      <c r="B551" t="inlineStr">
+      <c r="B550" t="inlineStr">
         <is>
           <t>images/「あなたであれ」_img1.jpg</t>
         </is>
       </c>
-      <c r="C551" t="inlineStr">
+      <c r="C550" t="inlineStr">
         <is>
           <t>個性 ,自尊心</t>
         </is>
       </c>
     </row>
-    <row r="552">
-      <c r="A552" t="inlineStr">
+    <row r="551">
+      <c r="A551" t="inlineStr">
         <is>
           <t xml:space="preserve">「過去を忘れろ。だが教訓は忘れるな」
 إنسَ الماضي ولكن لاتنسَ الدرس
@@ -12015,19 +11994,19 @@
 2308 https://www.instagram.com/emanalyafai </t>
         </is>
       </c>
-      <c r="B552" t="inlineStr">
+      <c r="B551" t="inlineStr">
         <is>
           <t>images/「過去を忘れろ。だが教訓は忘れるな」_img1.jpg</t>
         </is>
       </c>
-      <c r="C552" t="inlineStr">
+      <c r="C551" t="inlineStr">
         <is>
           <t>名言 ,未来</t>
         </is>
       </c>
     </row>
-    <row r="553">
-      <c r="A553" t="inlineStr">
+    <row r="552">
+      <c r="A552" t="inlineStr">
         <is>
           <t xml:space="preserve">「この世界で君も何かを持っている。だから立ち上がれ！」
 لَكْ شيءٌ في هَذَا العَالَم… فَقُمْ
@@ -12035,19 +12014,19 @@
 2511 mjdal7arbi tumblr, Ghassan Kanafani </t>
         </is>
       </c>
-      <c r="B553" t="inlineStr">
+      <c r="B552" t="inlineStr">
         <is>
           <t>images/「この世界で君も何かを持っている。だか.jpg</t>
         </is>
       </c>
-      <c r="C553" t="inlineStr">
+      <c r="C552" t="inlineStr">
         <is>
           <t>鼓舞 ,ハンカチ王子</t>
         </is>
       </c>
     </row>
-    <row r="554">
-      <c r="A554" t="inlineStr">
+    <row r="553">
+      <c r="A553" t="inlineStr">
         <is>
           <t xml:space="preserve">「かぞえてかずをかきましょう」
 عد واكتب العدد
@@ -12056,19 +12035,19 @@
 2604 facebook Qsre alawani </t>
         </is>
       </c>
-      <c r="B554" t="inlineStr">
+      <c r="B553" t="inlineStr">
         <is>
           <t>images/「かぞえてかずをかきましょう」.JPG</t>
         </is>
       </c>
-      <c r="C554" t="inlineStr">
+      <c r="C553" t="inlineStr">
         <is>
           <t>算数 ,さんすう</t>
         </is>
       </c>
     </row>
-    <row r="555">
-      <c r="A555" t="inlineStr">
+    <row r="554">
+      <c r="A554" t="inlineStr">
         <is>
           <t xml:space="preserve">「いつも人助けしなさい」
 كن عونا للناس دوما
@@ -12078,19 +12057,19 @@
 2109 Muhammad ElMahdy </t>
         </is>
       </c>
-      <c r="B555" t="inlineStr">
+      <c r="B554" t="inlineStr">
         <is>
           <t>images/「いつも人助けしなさい」_img1.jpg</t>
         </is>
       </c>
-      <c r="C555" t="inlineStr">
+      <c r="C554" t="inlineStr">
         <is>
           <t>教訓 ,助っ人</t>
         </is>
       </c>
     </row>
-    <row r="556">
-      <c r="A556" t="inlineStr">
+    <row r="555">
+      <c r="A555" t="inlineStr">
         <is>
           <t xml:space="preserve">「毎年、ノーベル賞が授けられる」
 في كل عام تُمنح جوائز نوبل
@@ -12098,19 +12077,19 @@
 2404 https://twitter.com/SciTalk2U/status/1462482447627661319 </t>
         </is>
       </c>
-      <c r="B556" t="inlineStr">
+      <c r="B555" t="inlineStr">
         <is>
           <t>images/「毎年、ノーベル賞が授けられる」_img1.jpg</t>
         </is>
       </c>
-      <c r="C556" t="inlineStr">
+      <c r="C555" t="inlineStr">
         <is>
           <t>手書き語学 ,アラビア語 ,ノーベル賞</t>
         </is>
       </c>
     </row>
-    <row r="557">
-      <c r="A557" t="inlineStr">
+    <row r="556">
+      <c r="A556" t="inlineStr">
         <is>
           <t xml:space="preserve">「あなたはアラビア語を話しますか」
 هل تتكلم العربية؟
@@ -12120,19 +12099,19 @@
 2109 al3arabiya com </t>
         </is>
       </c>
-      <c r="B557" t="inlineStr">
+      <c r="B556" t="inlineStr">
         <is>
           <t>images/「あなたはアラビア語を話しますか」_img1.jpg</t>
         </is>
       </c>
-      <c r="C557" t="inlineStr">
+      <c r="C556" t="inlineStr">
         <is>
           <t>教科書 ,テキスト</t>
         </is>
       </c>
     </row>
-    <row r="558">
-      <c r="A558" t="inlineStr">
+    <row r="557">
+      <c r="A557" t="inlineStr">
         <is>
           <t xml:space="preserve">「このインコは亜熱帯が起源である」
 يتحدر هذا الباراكيت من المناطق شبه الاستوائية
@@ -12140,19 +12119,19 @@
 2402 https://x.com/NatGeoMagArab/status/1690626751578439680 </t>
         </is>
       </c>
-      <c r="B558" t="inlineStr">
+      <c r="B557" t="inlineStr">
         <is>
           <t>images/「このインコは亜熱帯が起源である」_img1.jpg,images/「このインコは亜熱帯が起源である」_img2.jpg</t>
         </is>
       </c>
-      <c r="C558" t="inlineStr">
+      <c r="C557" t="inlineStr">
         <is>
           <t>手書き語学 ,アラビア語 ,オナガミドリインコ</t>
         </is>
       </c>
     </row>
-    <row r="559">
-      <c r="A559" t="inlineStr">
+    <row r="558">
+      <c r="A558" t="inlineStr">
         <is>
           <t xml:space="preserve">「彼を覚えていますか」
 هل تتذكرونه؟
@@ -12162,19 +12141,19 @@
 2308 http://newsfacetruth.blogspot.com/2017/07/blog-post_11.html </t>
         </is>
       </c>
-      <c r="B559" t="inlineStr">
+      <c r="B558" t="inlineStr">
         <is>
           <t>images/「彼を覚えていますか」_img1.jpg</t>
         </is>
       </c>
-      <c r="C559" t="inlineStr">
+      <c r="C558" t="inlineStr">
         <is>
           <t>グレンダイザー ,UFOロボ</t>
         </is>
       </c>
     </row>
-    <row r="560">
-      <c r="A560" t="inlineStr">
+    <row r="559">
+      <c r="A559" t="inlineStr">
         <is>
           <t xml:space="preserve">「内面が変われば周りが変わる」
 عندما تتغير الأشياء داخلك، تتغير الأشياء من حولك
@@ -12183,19 +12162,19 @@
 2501 Facebook, Cairo Mockingbird </t>
         </is>
       </c>
-      <c r="B560" t="inlineStr">
+      <c r="B559" t="inlineStr">
         <is>
           <t>images/「内面が変われば周りが変わる」_img1.jpg</t>
         </is>
       </c>
-      <c r="C560" t="inlineStr">
+      <c r="C559" t="inlineStr">
         <is>
           <t>ポジティブ</t>
         </is>
       </c>
     </row>
-    <row r="561">
-      <c r="A561" t="inlineStr">
+    <row r="560">
+      <c r="A560" t="inlineStr">
         <is>
           <t xml:space="preserve">「天才になるには？」
 كيف تصبح عبقريا؟
@@ -12204,19 +12183,19 @@
 2109 Infographics Samah Faris </t>
         </is>
       </c>
-      <c r="B561" t="inlineStr">
+      <c r="B560" t="inlineStr">
         <is>
           <t>images/「天才になるには？」_img1.jpg</t>
         </is>
       </c>
-      <c r="C561" t="inlineStr">
+      <c r="C560" t="inlineStr">
         <is>
           <t>秘訣 ,コツ</t>
         </is>
       </c>
     </row>
-    <row r="562">
-      <c r="A562" t="inlineStr">
+    <row r="561">
+      <c r="A561" t="inlineStr">
         <is>
           <t xml:space="preserve">「彼らと友情を交わすよハム太郎」
 وبالإخاء يبادلهم هامتارو
@@ -12226,19 +12205,19 @@
 2109 </t>
         </is>
       </c>
-      <c r="B562" t="inlineStr">
+      <c r="B561" t="inlineStr">
         <is>
           <t>images/「彼らと友情を交わすよハム太郎」_img1.jpg</t>
         </is>
       </c>
-      <c r="C562" t="inlineStr">
+      <c r="C561" t="inlineStr">
         <is>
           <t>アニメ ,ハム太郎</t>
         </is>
       </c>
     </row>
-    <row r="563">
-      <c r="A563" t="inlineStr">
+    <row r="562">
+      <c r="A562" t="inlineStr">
         <is>
           <t xml:space="preserve">「誰がニワトリを助ける？」
 من يساعد الدّجاجة؟
@@ -12248,19 +12227,19 @@
 2109 alnqsh com </t>
         </is>
       </c>
-      <c r="B563" t="inlineStr">
+      <c r="B562" t="inlineStr">
         <is>
           <t>images/「誰がニワトリを助ける？」_img1.jpg</t>
         </is>
       </c>
-      <c r="C563" t="inlineStr">
+      <c r="C562" t="inlineStr">
         <is>
           <t>絵本 ,チキン</t>
         </is>
       </c>
     </row>
-    <row r="564">
-      <c r="A564" t="inlineStr">
+    <row r="563">
+      <c r="A563" t="inlineStr">
         <is>
           <t xml:space="preserve">「心臓病を避けるには？」
 كيف تتجنب أمراض القلب؟
@@ -12270,37 +12249,37 @@
 2608 lanamedical_sa </t>
         </is>
       </c>
+      <c r="B563" t="inlineStr">
+        <is>
+          <t>images/「心臓病を避けるには？」.jpg</t>
+        </is>
+      </c>
+      <c r="C563" t="inlineStr">
+        <is>
+          <t>生活習慣病 ,心臓</t>
+        </is>
+      </c>
+    </row>
+    <row r="564">
+      <c r="A564" t="inlineStr">
+        <is>
+          <t xml:space="preserve">「どうやらこの好奇心旺盛なペンギンは…」
+2308 https://twitter.com/NatGeoMagArab/status/1591460860207443968 </t>
+        </is>
+      </c>
       <c r="B564" t="inlineStr">
         <is>
-          <t>images/「心臓病を避けるには？」.jpg</t>
+          <t>images/「どうやらこの好奇心旺盛なペンギンは…_img1.jpg,images/ 「どうやらこの好奇心旺盛なペンギンは…_img2.jpg</t>
         </is>
       </c>
       <c r="C564" t="inlineStr">
         <is>
-          <t>生活習慣病 ,心臓</t>
+          <t>手書き語学 ,アラビア語 ,オウサマペンギン</t>
         </is>
       </c>
     </row>
     <row r="565">
       <c r="A565" t="inlineStr">
-        <is>
-          <t xml:space="preserve">「どうやらこの好奇心旺盛なペンギンは…」
-2308 https://twitter.com/NatGeoMagArab/status/1591460860207443968 </t>
-        </is>
-      </c>
-      <c r="B565" t="inlineStr">
-        <is>
-          <t>images/「どうやらこの好奇心旺盛なペンギンは…_img1.jpg,images/ 「どうやらこの好奇心旺盛なペンギンは…_img2.jpg</t>
-        </is>
-      </c>
-      <c r="C565" t="inlineStr">
-        <is>
-          <t>手書き語学 ,アラビア語 ,オウサマペンギン</t>
-        </is>
-      </c>
-    </row>
-    <row r="566">
-      <c r="A566" t="inlineStr">
         <is>
           <t xml:space="preserve">「この生き物を見分けられますか？」
 هل تُميز هذا الكائن؟
@@ -12309,19 +12288,19 @@
 2308 https://twitter.com/NatGeoMagArab/status/1455121397827600388 </t>
         </is>
       </c>
-      <c r="B566" t="inlineStr">
+      <c r="B565" t="inlineStr">
         <is>
           <t>images/「この生き物を見分けられますか？」_img1.jpg</t>
         </is>
       </c>
-      <c r="C566" t="inlineStr">
+      <c r="C565" t="inlineStr">
         <is>
           <t xml:space="preserve">手書き語学 ,カバ </t>
         </is>
       </c>
     </row>
-    <row r="567">
-      <c r="A567" t="inlineStr">
+    <row r="566">
+      <c r="A566" t="inlineStr">
         <is>
           <t xml:space="preserve">「ひとを幸せにするには？」
 كيف تسعد غيرك؟
@@ -12331,19 +12310,19 @@
 2308 Gwid3 </t>
         </is>
       </c>
-      <c r="B567" t="inlineStr">
+      <c r="B566" t="inlineStr">
         <is>
           <t>images/「ひとを幸せにするには？」_img1.jpg</t>
         </is>
       </c>
-      <c r="C567" t="inlineStr">
+      <c r="C566" t="inlineStr">
         <is>
           <t>思いやり ,心</t>
         </is>
       </c>
     </row>
-    <row r="568">
-      <c r="A568" t="inlineStr">
+    <row r="567">
+      <c r="A567" t="inlineStr">
         <is>
           <t xml:space="preserve">「ラマダン月に口臭をおさえる方法は？」
 كيف تتجنب رائحة الفم في رمضان
@@ -12352,19 +12331,19 @@
 2109 AlArabiya </t>
         </is>
       </c>
-      <c r="B568" t="inlineStr">
+      <c r="B567" t="inlineStr">
         <is>
           <t>images/「ラマダン月に口臭をおさえる方法は？」_img1.jpg</t>
         </is>
       </c>
-      <c r="C568" t="inlineStr">
+      <c r="C567" t="inlineStr">
         <is>
           <t>イスラム教 ,ブレスケア</t>
         </is>
       </c>
     </row>
-    <row r="569">
-      <c r="A569" t="inlineStr">
+    <row r="568">
+      <c r="A568" t="inlineStr">
         <is>
           <t xml:space="preserve">「ヨユウなきユウヨ」
 يمهل ولا يهمل
@@ -12374,19 +12353,19 @@
 2512 instagram com/p/CK4CLqeJ3dy/ </t>
         </is>
       </c>
-      <c r="B569" t="inlineStr">
+      <c r="B568" t="inlineStr">
         <is>
           <t>images/「ヨユウなきユウヨ」_img1.jpg</t>
         </is>
       </c>
-      <c r="C569" t="inlineStr">
+      <c r="C568" t="inlineStr">
         <is>
           <t>時計 ,からくり</t>
         </is>
       </c>
     </row>
-    <row r="570">
-      <c r="A570" t="inlineStr">
+    <row r="569">
+      <c r="A569" t="inlineStr">
         <is>
           <t xml:space="preserve">「どうして？　動物は絶滅する」
 لماذا؟ تنقرض الحيوانات
@@ -12396,19 +12375,19 @@
 2308 goodreads com </t>
         </is>
       </c>
-      <c r="B570" t="inlineStr">
+      <c r="B569" t="inlineStr">
         <is>
           <t>images/「どうして？　動物は絶滅する」_img1.jpg</t>
         </is>
       </c>
-      <c r="C570" t="inlineStr">
+      <c r="C569" t="inlineStr">
         <is>
           <t>動物 ,子供用</t>
         </is>
       </c>
     </row>
-    <row r="571">
-      <c r="A571" t="inlineStr">
+    <row r="570">
+      <c r="A570" t="inlineStr">
         <is>
           <t xml:space="preserve">「私たちは異なる。だから調和する」
 نختلف.. لنأتلف
@@ -12418,19 +12397,19 @@
 2103 Nawal Saed </t>
         </is>
       </c>
-      <c r="B571" t="inlineStr">
+      <c r="B570" t="inlineStr">
         <is>
           <t>images/「私たちは異なる。だから調和する」_img1.jpg</t>
         </is>
       </c>
-      <c r="C571" t="inlineStr">
+      <c r="C570" t="inlineStr">
         <is>
           <t>異符号 ,ハーモニー</t>
         </is>
       </c>
     </row>
-    <row r="572">
-      <c r="A572" t="inlineStr">
+    <row r="571">
+      <c r="A571" t="inlineStr">
         <is>
           <t xml:space="preserve">「私の肺には蝶々が住んでいて、呼吸の度に羽ばたく」
 تسكن رئتيّ فراشة ترفرف كلما أتنفس
@@ -12439,19 +12418,19 @@
 2109 出典不明 </t>
         </is>
       </c>
-      <c r="B572" t="inlineStr">
+      <c r="B571" t="inlineStr">
         <is>
           <t>images/「私の肺には蝶々が住んでいて、呼吸の度_img1.jpg</t>
         </is>
       </c>
-      <c r="C572" t="inlineStr">
+      <c r="C571" t="inlineStr">
         <is>
           <t>人体 ,昆虫</t>
         </is>
       </c>
     </row>
-    <row r="573">
-      <c r="A573" t="inlineStr">
+    <row r="572">
+      <c r="A572" t="inlineStr">
         <is>
           <t xml:space="preserve">「安らぎを感じますか？」
 هل تستشعر السكينة؟
@@ -12460,19 +12439,19 @@
 2404 https://twitter.com/NatGeoMagArab/status/1541421154950209536 </t>
         </is>
       </c>
-      <c r="B573" t="inlineStr">
+      <c r="B572" t="inlineStr">
         <is>
           <t>images/「安らぎを感じますか？」_img1.jpg</t>
         </is>
       </c>
-      <c r="C573" t="inlineStr">
+      <c r="C572" t="inlineStr">
         <is>
           <t>手書き語学 ,アラビア語 ,エイ</t>
         </is>
       </c>
     </row>
-    <row r="574">
-      <c r="A574" t="inlineStr">
+    <row r="573">
+      <c r="A573" t="inlineStr">
         <is>
           <t xml:space="preserve">「たとえあなたの使うブラウザがChromeだろうとSafariだろうと」
 سواء كنت تستخدم متصفح كروم أو سفاري
@@ -12480,19 +12459,19 @@
 2308 https://twitter.com/ShaayTech/status/1536235333972635649 </t>
         </is>
       </c>
-      <c r="B574" t="inlineStr">
+      <c r="B573" t="inlineStr">
         <is>
           <t>images/「たとえあなたの使うブラウザがChro_img1.jpg</t>
         </is>
       </c>
-      <c r="C574" t="inlineStr">
+      <c r="C573" t="inlineStr">
         <is>
           <t xml:space="preserve">手書き語学 ,アラビア語 ,iPhone </t>
         </is>
       </c>
     </row>
-    <row r="575">
-      <c r="A575" t="inlineStr">
+    <row r="574">
+      <c r="A574" t="inlineStr">
         <is>
           <t xml:space="preserve">「このミドリモリヤツガシラは気づいて欲しい」
 يحرص "هدهد الخشب الأخضر" هذا على أن يدرك
@@ -12501,19 +12480,19 @@
 2308 https://twitter.com/NatGeoMagArab/status/1531161022928539648 </t>
         </is>
       </c>
-      <c r="B575" t="inlineStr">
+      <c r="B574" t="inlineStr">
         <is>
           <t>images/「このミドリモリヤツガシラは気づいて欲_img1.jpg</t>
         </is>
       </c>
-      <c r="C575" t="inlineStr">
+      <c r="C574" t="inlineStr">
         <is>
           <t xml:space="preserve">手書き語学 ,アラビア語 ,鳥 </t>
         </is>
       </c>
     </row>
-    <row r="576">
-      <c r="A576" t="inlineStr">
+    <row r="575">
+      <c r="A575" t="inlineStr">
         <is>
           <t xml:space="preserve">「あなたの怖いものは何ですか」
 ماهي مخاوفك؟
@@ -12525,15 +12504,15 @@
 2308 1112kok </t>
         </is>
       </c>
-      <c r="B576" t="inlineStr">
+      <c r="B575" t="inlineStr">
         <is>
           <t>images/「あなたの怖いものは何ですか」_img1.jpg</t>
         </is>
       </c>
-      <c r="C576" t="inlineStr"/>
-    </row>
-    <row r="577">
-      <c r="A577" t="inlineStr">
+      <c r="C575" t="inlineStr"/>
+    </row>
+    <row r="576">
+      <c r="A576" t="inlineStr">
         <is>
           <t xml:space="preserve">「美しい時は作るもの。待つものではない」
 اصنع اللحظات الجميلة. لا تنتظرها
@@ -12542,19 +12521,19 @@
 2308 abojamal.tumblr com </t>
         </is>
       </c>
-      <c r="B577" t="inlineStr">
+      <c r="B576" t="inlineStr">
         <is>
           <t>images/「美しい時は作るもの。待つものではない_img1.jpg</t>
         </is>
       </c>
-      <c r="C577" t="inlineStr">
+      <c r="C576" t="inlineStr">
         <is>
           <t>おうち時間</t>
         </is>
       </c>
     </row>
-    <row r="578">
-      <c r="A578" t="inlineStr">
+    <row r="577">
+      <c r="A577" t="inlineStr">
         <is>
           <t xml:space="preserve">「大切な時間を大切じゃないことに使わないこと」
 لا تضيع الوقت المهم في شيء غير مهم
@@ -12563,19 +12542,19 @@
 2308 Anwar_122_ </t>
         </is>
       </c>
-      <c r="B578" t="inlineStr">
+      <c r="B577" t="inlineStr">
         <is>
           <t>images/「大切な時間を大切じゃないことに使わな_img1.jpg</t>
         </is>
       </c>
-      <c r="C578" t="inlineStr">
+      <c r="C577" t="inlineStr">
         <is>
           <t>時間 ,貴重</t>
         </is>
       </c>
     </row>
-    <row r="579">
-      <c r="A579" t="inlineStr">
+    <row r="578">
+      <c r="A578" t="inlineStr">
         <is>
           <t xml:space="preserve">「このイノセントな目に騙されるな…」
 لا تنخدع بهذه العيون البريئة
@@ -12585,19 +12564,19 @@
 2201 https://twitter.com/NatGeoMagArab/status/1475715760202797056 </t>
         </is>
       </c>
-      <c r="B579" t="inlineStr">
+      <c r="B578" t="inlineStr">
         <is>
           <t>images/「このイノセントな目に騙されるな…」.png</t>
         </is>
       </c>
-      <c r="C579" t="inlineStr">
+      <c r="C578" t="inlineStr">
         <is>
           <t>がうがう ,カワイイ</t>
         </is>
       </c>
     </row>
-    <row r="580">
-      <c r="A580" t="inlineStr">
+    <row r="579">
+      <c r="A579" t="inlineStr">
         <is>
           <t xml:space="preserve">⁦「カメラを止めろ！」⁩
 أوقفوا التّصوير
@@ -12607,19 +12586,19 @@
 2509 alsalwabooks com </t>
         </is>
       </c>
-      <c r="B580" t="inlineStr">
+      <c r="B579" t="inlineStr">
         <is>
           <t>images/⁦「カメラを止めろ！」⁩_img1.jpg</t>
         </is>
       </c>
-      <c r="C580" t="inlineStr">
+      <c r="C579" t="inlineStr">
         <is>
           <t>絵本 ,撮影</t>
         </is>
       </c>
     </row>
-    <row r="581">
-      <c r="A581" t="inlineStr">
+    <row r="580">
+      <c r="A580" t="inlineStr">
         <is>
           <t xml:space="preserve">「話す前に考えなさい」
 فكر قبل ان تتكلم
@@ -12629,19 +12608,19 @@
 2308 Islamuna YouTube </t>
         </is>
       </c>
-      <c r="B581" t="inlineStr">
+      <c r="B580" t="inlineStr">
         <is>
           <t>images/「話す前に考えなさい」_img1.jpg</t>
         </is>
       </c>
-      <c r="C581" t="inlineStr">
+      <c r="C580" t="inlineStr">
         <is>
           <t>失言 ,発言</t>
         </is>
       </c>
     </row>
-    <row r="582">
-      <c r="A582" t="inlineStr">
+    <row r="581">
+      <c r="A581" t="inlineStr">
         <is>
           <t xml:space="preserve">「ツイッターでフォローして下さい」
 تابعونا على تويتر
@@ -12651,19 +12630,19 @@
 2109 出典不明 </t>
         </is>
       </c>
-      <c r="B582" t="inlineStr">
+      <c r="B581" t="inlineStr">
         <is>
           <t>images/「ツイッターでフォローして下さい」_img1.jpg</t>
         </is>
       </c>
-      <c r="C582" t="inlineStr">
+      <c r="C581" t="inlineStr">
         <is>
           <t>FollowUs ,バナー</t>
         </is>
       </c>
     </row>
-    <row r="583">
-      <c r="A583" t="inlineStr">
+    <row r="582">
+      <c r="A582" t="inlineStr">
         <is>
           <t xml:space="preserve">「敵を倒せ」دمّر العدو
 ダンミリ_ルアドゥーウ [dammiri l-*aduuw]
@@ -12672,19 +12651,19 @@
 2308 apkpure com </t>
         </is>
       </c>
-      <c r="B583" t="inlineStr">
+      <c r="B582" t="inlineStr">
         <is>
           <t>images/「敵を倒せ」_img1.jpg</t>
         </is>
       </c>
-      <c r="C583" t="inlineStr">
+      <c r="C582" t="inlineStr">
         <is>
           <t>ゲーム ,パンダ</t>
         </is>
       </c>
     </row>
-    <row r="584">
-      <c r="A584" t="inlineStr">
+    <row r="583">
+      <c r="A583" t="inlineStr">
         <is>
           <t xml:space="preserve">「咲け。蒔かれたらどこであろうと」
 أزهر أيْنمَا زرعت
@@ -12693,19 +12672,19 @@
 2407 Ahmed Madyan </t>
         </is>
       </c>
-      <c r="B584" t="inlineStr">
+      <c r="B583" t="inlineStr">
         <is>
           <t>images/「咲け。蒔かれたらどこであろうと」_img1.jpg</t>
         </is>
       </c>
-      <c r="C584" t="inlineStr">
+      <c r="C583" t="inlineStr">
         <is>
           <t>環境のせいにしない ,花</t>
         </is>
       </c>
     </row>
-    <row r="585">
-      <c r="A585" t="inlineStr">
+    <row r="584">
+      <c r="A584" t="inlineStr">
         <is>
           <t xml:space="preserve">「頭を働かせろ」شغل مخك
 シャッギル・ムッハク [Sha^Ghil mu^Kha-k]
@@ -12714,19 +12693,19 @@
 2103 facebook elpage </t>
         </is>
       </c>
-      <c r="B585" t="inlineStr">
+      <c r="B584" t="inlineStr">
         <is>
           <t>images/「頭を働かせろ」_img1.jpg</t>
         </is>
       </c>
-      <c r="C585" t="inlineStr">
+      <c r="C584" t="inlineStr">
         <is>
           <t>電源 ,頭脳</t>
         </is>
       </c>
     </row>
-    <row r="586">
-      <c r="A586" t="inlineStr">
+    <row r="585">
+      <c r="A585" t="inlineStr">
         <is>
           <t xml:space="preserve">「傷跡は星にかえなさい」
 حوّل نُدوبكَ إلى نُجومْ
@@ -12736,19 +12715,19 @@
 2107 saramj1992 Instagram </t>
         </is>
       </c>
-      <c r="B586" t="inlineStr">
+      <c r="B585" t="inlineStr">
         <is>
           <t>images/「傷跡は星にかえなさい」_img1.jpg</t>
         </is>
       </c>
-      <c r="C586" t="inlineStr">
+      <c r="C585" t="inlineStr">
         <is>
           <t>勲章 ,証</t>
         </is>
       </c>
     </row>
-    <row r="587">
-      <c r="A587" t="inlineStr">
+    <row r="586">
+      <c r="A586" t="inlineStr">
         <is>
           <t xml:space="preserve">「あなたの主の栄光を誉め称え、また（御赦しを請え。本当にかれは、度々赦される御方である）」
 فسَبِّح بحمد ربك و
@@ -12757,19 +12736,19 @@
 2109 出典不明 </t>
         </is>
       </c>
-      <c r="B587" t="inlineStr">
+      <c r="B586" t="inlineStr">
         <is>
           <t>images/「あなたの主の栄光を誉め称え、また（御_img1.jpg</t>
         </is>
       </c>
-      <c r="C587" t="inlineStr">
+      <c r="C586" t="inlineStr">
         <is>
           <t>イスラム教 ,カリグラフィー</t>
         </is>
       </c>
     </row>
-    <row r="588">
-      <c r="A588" t="inlineStr">
+    <row r="587">
+      <c r="A587" t="inlineStr">
         <is>
           <t xml:space="preserve">「誰かを幸福にしなさい」
 أسْعِد أحدهم
@@ -12779,19 +12758,19 @@
 1810 in4sser.tumblr </t>
         </is>
       </c>
-      <c r="B588" t="inlineStr">
+      <c r="B587" t="inlineStr">
         <is>
           <t>images/「誰かを幸福にしなさい」_img1.jpg</t>
         </is>
       </c>
-      <c r="C588" t="inlineStr">
+      <c r="C587" t="inlineStr">
         <is>
           <t>人生 ,happy</t>
         </is>
       </c>
     </row>
-    <row r="589">
-      <c r="A589" t="inlineStr">
+    <row r="588">
+      <c r="A588" t="inlineStr">
         <is>
           <t xml:space="preserve">「見よ」أبْصِرْ
 アブスィル ['ab_sir]
@@ -12800,19 +12779,19 @@
 1811 Ruh Al-Alam, via Behance </t>
         </is>
       </c>
-      <c r="B589" t="inlineStr">
+      <c r="B588" t="inlineStr">
         <is>
           <t>images/「見よ」_img1.jpg</t>
         </is>
       </c>
-      <c r="C589" t="inlineStr">
+      <c r="C588" t="inlineStr">
         <is>
           <t>目 ,瞳</t>
         </is>
       </c>
     </row>
-    <row r="590">
-      <c r="A590" t="inlineStr">
+    <row r="589">
+      <c r="A589" t="inlineStr">
         <is>
           <t xml:space="preserve">「言葉は口から出す前に味わいなさい」
 ‪تذوق كلماتك قبل أن تنطقها‬
@@ -12822,19 +12801,19 @@
 2109 Reham-des </t>
         </is>
       </c>
-      <c r="B590" t="inlineStr">
+      <c r="B589" t="inlineStr">
         <is>
           <t>images/「言葉は口から出す前に味わいなさい」_img1.jpg</t>
         </is>
       </c>
-      <c r="C590" t="inlineStr">
+      <c r="C589" t="inlineStr">
         <is>
           <t>言葉</t>
         </is>
       </c>
     </row>
-    <row r="591">
-      <c r="A591" t="inlineStr">
+    <row r="590">
+      <c r="A590" t="inlineStr">
         <is>
           <t xml:space="preserve">「テレビを観るのをやめて下さい」
 توقفي عن مشاهدة التلفاز
@@ -12844,19 +12823,19 @@
 1809 </t>
         </is>
       </c>
-      <c r="B591" t="inlineStr">
+      <c r="B590" t="inlineStr">
         <is>
           <t>images/「テレビを観るのをやめて下さい」_img1.jpg</t>
         </is>
       </c>
-      <c r="C591" t="inlineStr">
+      <c r="C590" t="inlineStr">
         <is>
           <t>あらびあや</t>
         </is>
       </c>
     </row>
-    <row r="592">
-      <c r="A592" t="inlineStr">
+    <row r="591">
+      <c r="A591" t="inlineStr">
         <is>
           <t xml:space="preserve">「言わぬが花」
 انْطِقْ جَمَالاً أو تجَمَّلْ بالسّكُوت
@@ -12866,19 +12845,19 @@
 2411 Ahmed Madyan </t>
         </is>
       </c>
-      <c r="B592" t="inlineStr">
+      <c r="B591" t="inlineStr">
         <is>
           <t>images/「言わぬが花」_img1.jpg</t>
         </is>
       </c>
-      <c r="C592" t="inlineStr">
+      <c r="C591" t="inlineStr">
         <is>
           <t>ことわざ ,デザイン</t>
         </is>
       </c>
     </row>
-    <row r="593">
-      <c r="A593" t="inlineStr">
+    <row r="592">
+      <c r="A592" t="inlineStr">
         <is>
           <t xml:space="preserve">「たくさん考えて、少し話すこと」
 فكّر كثيرا. تكلم قليلا
@@ -12888,19 +12867,19 @@
 2105 In49r </t>
         </is>
       </c>
-      <c r="B593" t="inlineStr">
+      <c r="B592" t="inlineStr">
         <is>
           <t>images/「たくさん考えて、少し話すこと」_img1.jpg</t>
         </is>
       </c>
-      <c r="C593" t="inlineStr">
+      <c r="C592" t="inlineStr">
         <is>
           <t>思慮 ,会話</t>
         </is>
       </c>
     </row>
-    <row r="594">
-      <c r="A594" t="inlineStr">
+    <row r="593">
+      <c r="A593" t="inlineStr">
         <is>
           <t xml:space="preserve">「子供たちよ、いつでも思い出すんだよ」
 تذكروا دوما يا أطفال
@@ -12910,19 +12889,19 @@
 1809 </t>
         </is>
       </c>
-      <c r="B594" t="inlineStr">
+      <c r="B593" t="inlineStr">
         <is>
           <t>images/「子供たちよ、いつでも思い出すんだよ」_img1.jpg</t>
         </is>
       </c>
-      <c r="C594" t="inlineStr">
+      <c r="C593" t="inlineStr">
         <is>
           <t>オープニング ,ハム太郎</t>
         </is>
       </c>
     </row>
-    <row r="595">
-      <c r="A595" t="inlineStr">
+    <row r="594">
+      <c r="A594" t="inlineStr">
         <is>
           <t xml:space="preserve">「分かってから話しなさい」
 تعلَّم ثمَّ تكلَّم
@@ -12932,19 +12911,19 @@
 1903 Hashem Al Shareef, Pinterest </t>
         </is>
       </c>
-      <c r="B595" t="inlineStr">
+      <c r="B594" t="inlineStr">
         <is>
           <t>images/「分かってから話しなさい」_img1.jpg</t>
         </is>
       </c>
-      <c r="C595" t="inlineStr">
+      <c r="C594" t="inlineStr">
         <is>
           <t>教訓 ,トーク</t>
         </is>
       </c>
     </row>
-    <row r="596">
-      <c r="A596" t="inlineStr">
+    <row r="595">
+      <c r="A595" t="inlineStr">
         <is>
           <t xml:space="preserve">「蟻に学べ」تعلم من النملة
 タアッラム・ミナ_ンナムラ [ta*allam mina ^namla]
@@ -12953,19 +12932,19 @@
 2308 fatakat com </t>
         </is>
       </c>
-      <c r="B596" t="inlineStr">
+      <c r="B595" t="inlineStr">
         <is>
           <t>images/「蟻に学べ」_img1.jpg</t>
         </is>
       </c>
-      <c r="C596" t="inlineStr">
+      <c r="C595" t="inlineStr">
         <is>
           <t>教訓 ,問題解決</t>
         </is>
       </c>
     </row>
-    <row r="597">
-      <c r="A597" t="inlineStr">
+    <row r="596">
+      <c r="A596" t="inlineStr">
         <is>
           <t xml:space="preserve">「自分と仲直りしよう、一杯の珈琲で！」
 تصالح مع نفسك بكوب قهوة
@@ -12975,19 +12954,19 @@
 2308 asm95_ </t>
         </is>
       </c>
-      <c r="B597" t="inlineStr">
+      <c r="B596" t="inlineStr">
         <is>
           <t>images/「自分と仲直りしよう、一杯の珈琲で！」_img1.jpg</t>
         </is>
       </c>
-      <c r="C597" t="inlineStr">
+      <c r="C596" t="inlineStr">
         <is>
           <t>一服 ,リラックス</t>
         </is>
       </c>
     </row>
-    <row r="598">
-      <c r="A598" t="inlineStr">
+    <row r="597">
+      <c r="A597" t="inlineStr">
         <is>
           <t xml:space="preserve">「気をつけて　ジュード」
 انتبهي يا جود
@@ -12997,19 +12976,19 @@
 2109 سلسلة الحلزونة </t>
         </is>
       </c>
-      <c r="B598" t="inlineStr">
+      <c r="B597" t="inlineStr">
         <is>
           <t>images/「気をつけて　ジュード」_img1.jpg</t>
         </is>
       </c>
-      <c r="C598" t="inlineStr">
+      <c r="C597" t="inlineStr">
         <is>
           <t>絵本 ,わんぱく</t>
         </is>
       </c>
     </row>
-    <row r="599">
-      <c r="A599" t="inlineStr">
+    <row r="598">
+      <c r="A598" t="inlineStr">
         <is>
           <t xml:space="preserve">「coming soon」
 انتظرونا قريبا
@@ -13018,19 +12997,19 @@
 2307 出典不明 </t>
         </is>
       </c>
-      <c r="B599" t="inlineStr">
+      <c r="B598" t="inlineStr">
         <is>
           <t>images/「coming soon」_img1.jpg</t>
         </is>
       </c>
-      <c r="C599" t="inlineStr">
+      <c r="C598" t="inlineStr">
         <is>
           <t>フレーズ ,カミングスーン</t>
         </is>
       </c>
     </row>
-    <row r="600">
-      <c r="A600" t="inlineStr">
+    <row r="599">
+      <c r="A599" t="inlineStr">
         <is>
           <t xml:space="preserve">「自分の胸に聞きなさい。それが全て知っています」
 استمع لقلبك.. إنه يعرف كل شيء
@@ -13039,19 +13018,19 @@
 1811 </t>
         </is>
       </c>
-      <c r="B600" t="inlineStr">
+      <c r="B599" t="inlineStr">
         <is>
           <t>images/「自分の胸に聞きなさい。それが全て知っ_img1.jpg</t>
         </is>
       </c>
-      <c r="C600" t="inlineStr">
+      <c r="C599" t="inlineStr">
         <is>
           <t>あらびあや</t>
         </is>
       </c>
     </row>
-    <row r="601">
-      <c r="A601" t="inlineStr">
+    <row r="600">
+      <c r="A600" t="inlineStr">
         <is>
           <t xml:space="preserve">「笑ってくれ、絶望を癒すのは君の笑みだから」
 ابتسمي فإن دواء اليأس بسمتك
@@ -13060,19 +13039,19 @@
 2308 arab-quotes tumblr </t>
         </is>
       </c>
-      <c r="B601" t="inlineStr">
+      <c r="B600" t="inlineStr">
         <is>
           <t>images/「笑ってくれ、絶望を癒すのは君の笑みだ_img1.jpg</t>
         </is>
       </c>
-      <c r="C601" t="inlineStr">
+      <c r="C600" t="inlineStr">
         <is>
           <t>癒し ,スマイル</t>
         </is>
       </c>
     </row>
-    <row r="602">
-      <c r="A602" t="inlineStr">
+    <row r="601">
+      <c r="A601" t="inlineStr">
         <is>
           <t xml:space="preserve">「自分を頼りなさい。宇宙で最も確かな物が自分だと思って。」
 استند على نفسك وكأنك أكثر الأشياء ثباتًا بهذا الكون
@@ -13080,19 +13059,19 @@
 2308 x_nourh.15 </t>
         </is>
       </c>
-      <c r="B602" t="inlineStr">
+      <c r="B601" t="inlineStr">
         <is>
           <t>images/「自分を頼りなさい。宇宙で最も確かな物_img1.jpg</t>
         </is>
       </c>
-      <c r="C602" t="inlineStr">
+      <c r="C601" t="inlineStr">
         <is>
           <t>自我 ,宇宙</t>
         </is>
       </c>
     </row>
-    <row r="603">
-      <c r="A603" t="inlineStr">
+    <row r="602">
+      <c r="A602" t="inlineStr">
         <is>
           <t xml:space="preserve">「古いデバイスを交換して新品をゲットしよう」
 استبدل جهازك القديم واحصل على واحد جديد
@@ -13101,19 +13080,19 @@
 2406 stc </t>
         </is>
       </c>
-      <c r="B603" t="inlineStr">
+      <c r="B602" t="inlineStr">
         <is>
           <t>images/「古いデバイスを交換して新品をゲットし_img1.jpg</t>
         </is>
       </c>
-      <c r="C603" t="inlineStr">
+      <c r="C602" t="inlineStr">
         <is>
           <t>キャンペーン ,下取り</t>
         </is>
       </c>
     </row>
-    <row r="604">
-      <c r="A604" t="inlineStr">
+    <row r="603">
+      <c r="A603" t="inlineStr">
         <is>
           <t xml:space="preserve">「あなたの声を聞かせてください。私の心を彩ってください」
 هات صوتك، لوّن قلبي
@@ -13122,19 +13101,19 @@
 2105 3a2esha_ Instagram </t>
         </is>
       </c>
-      <c r="B604" t="inlineStr">
+      <c r="B603" t="inlineStr">
         <is>
           <t>images/「あなたの声を聞かせてください。私の心_img1.jpg</t>
         </is>
       </c>
-      <c r="C604" t="inlineStr">
+      <c r="C603" t="inlineStr">
         <is>
           <t>電話 ,肉声</t>
         </is>
       </c>
     </row>
-    <row r="605">
-      <c r="A605" t="inlineStr">
+    <row r="604">
+      <c r="A604" t="inlineStr">
         <is>
           <t xml:space="preserve">「この子カンガルーは抱っこが好き」
 يُحب صغير الكنغر هذا أن يؤخذ في الأحضان
@@ -13142,19 +13121,19 @@
 2308 NatGeoMagArab </t>
         </is>
       </c>
-      <c r="B605" t="inlineStr">
+      <c r="B604" t="inlineStr">
         <is>
           <t>images/「この子カンガルーは抱っこが好き」.png</t>
         </is>
       </c>
-      <c r="C605" t="inlineStr">
+      <c r="C604" t="inlineStr">
         <is>
           <t>カンガルー ,人肌</t>
         </is>
       </c>
     </row>
-    <row r="606">
-      <c r="A606" t="inlineStr">
+    <row r="605">
+      <c r="A605" t="inlineStr">
         <is>
           <t xml:space="preserve">「カタールが好き」أحب قطر
 ウヒッブ・カタル ['u-Hibb qa_tar]
@@ -13163,19 +13142,19 @@
 1810 出典不明 </t>
         </is>
       </c>
-      <c r="B606" t="inlineStr">
+      <c r="B605" t="inlineStr">
         <is>
           <t>images/「カタールが好き」_img1.jpg</t>
         </is>
       </c>
-      <c r="C606" t="inlineStr">
+      <c r="C605" t="inlineStr">
         <is>
           <t>カタール</t>
         </is>
       </c>
     </row>
-    <row r="607">
-      <c r="A607" t="inlineStr">
+    <row r="606">
+      <c r="A606" t="inlineStr">
         <is>
           <t xml:space="preserve">「一緒に読むのが好き」
 أُحبُّ أن نَقْرَأَ مَعاً
@@ -13185,19 +13164,19 @@
 2509 www.neelwafurat com,  id=lbb212750-185765 </t>
         </is>
       </c>
-      <c r="B607" t="inlineStr">
+      <c r="B606" t="inlineStr">
         <is>
           <t>images/「一緒に読むのが好き」_img1.jpg</t>
         </is>
       </c>
-      <c r="C607" t="inlineStr">
+      <c r="C606" t="inlineStr">
         <is>
           <t>好き ,本</t>
         </is>
       </c>
     </row>
-    <row r="608">
-      <c r="A608" t="inlineStr">
+    <row r="607">
+      <c r="A607" t="inlineStr">
         <is>
           <t xml:space="preserve">「病院に行きたくない」
 لا أريد أن أذهب إلى المشفى
@@ -13207,19 +13186,19 @@
 2508 Tony Ross https://education.hachette-antoine.com/ar/component/%D9%84%D8%A7-%D8%A3%D8%B1%D9%8A%D8%AF-%D8%A3%D9%86-%D8%A3%D8%B0%D9%87%D8%A8-%D8%A5%D9%84%D9%89-%D8%A7%D9%84%D9%85%D8%B4%D9%81%D9%89/ </t>
         </is>
       </c>
-      <c r="B608" t="inlineStr">
+      <c r="B607" t="inlineStr">
         <is>
           <t>images/「病院に行きたくない」_img1.jpg</t>
         </is>
       </c>
-      <c r="C608" t="inlineStr">
+      <c r="C607" t="inlineStr">
         <is>
           <t>絵本 ,子供</t>
         </is>
       </c>
     </row>
-    <row r="609">
-      <c r="A609" t="inlineStr">
+    <row r="608">
+      <c r="A608" t="inlineStr">
         <is>
           <t xml:space="preserve">「男性はいくら？」「女性はいくら？」
 كم يساوى الرجل؟ ..وكم تساوى المرأة؟
@@ -13228,19 +13207,19 @@
 2308 Pinterest, Masr Elmahrousa, Farah Noweir </t>
         </is>
       </c>
-      <c r="B609" t="inlineStr">
+      <c r="B608" t="inlineStr">
         <is>
           <t>images/「男性はいくら？」「女性はいくら？」_img1.jpg,images/「男性はいくら？」「女性はいくら？」_img2.jpg</t>
         </is>
       </c>
-      <c r="C609" t="inlineStr">
+      <c r="C608" t="inlineStr">
         <is>
           <t xml:space="preserve">全身コーデ ,相場 </t>
         </is>
       </c>
     </row>
-    <row r="610">
-      <c r="A610" t="inlineStr">
+    <row r="609">
+      <c r="A609" t="inlineStr">
         <is>
           <t xml:space="preserve">「黙ってもらえます？」
 ممكن تعيرنا سكوتك؟
@@ -13250,19 +13229,19 @@
 2308 Basel26 </t>
         </is>
       </c>
-      <c r="B610" t="inlineStr">
+      <c r="B609" t="inlineStr">
         <is>
           <t>images/「黙ってもらえます？」_img1.jpg</t>
         </is>
       </c>
-      <c r="C610" t="inlineStr">
+      <c r="C609" t="inlineStr">
         <is>
           <t>音量 ,ボリューム</t>
         </is>
       </c>
     </row>
-    <row r="611">
-      <c r="A611" t="inlineStr">
+    <row r="610">
+      <c r="A610" t="inlineStr">
         <is>
           <t xml:space="preserve">「眠りたいです」
 أُريدُ أَن أَنام
@@ -13272,19 +13251,19 @@
 2109 goodreads com </t>
         </is>
       </c>
-      <c r="B611" t="inlineStr">
+      <c r="B610" t="inlineStr">
         <is>
           <t>images/「眠りたいです」_img1.jpg</t>
         </is>
       </c>
-      <c r="C611" t="inlineStr">
+      <c r="C610" t="inlineStr">
         <is>
           <t>絵本</t>
         </is>
       </c>
     </row>
-    <row r="612">
-      <c r="A612" t="inlineStr">
+    <row r="611">
+      <c r="A611" t="inlineStr">
         <is>
           <t xml:space="preserve">「飛びたい！」أُريد أن أطير
 ウリードゥ・アン・アティール ['u-riidu 'an 'a-_tiir]
@@ -13293,19 +13272,19 @@
 2308 出典不明 </t>
         </is>
       </c>
-      <c r="B612" t="inlineStr">
+      <c r="B611" t="inlineStr">
         <is>
           <t>images/「飛びたい！」_img1.jpg</t>
         </is>
       </c>
-      <c r="C612" t="inlineStr">
+      <c r="C611" t="inlineStr">
         <is>
           <t>鳥 ,希望</t>
         </is>
       </c>
     </row>
-    <row r="613">
-      <c r="A613" t="inlineStr">
+    <row r="612">
+      <c r="A612" t="inlineStr">
         <is>
           <t xml:space="preserve">「うちゅうへとびたい」
 أُريدُ أَنْ أَطيرَ إلى الفَضاء
@@ -13314,19 +13293,19 @@
 2308 mybookshelf co </t>
         </is>
       </c>
-      <c r="B613" t="inlineStr">
+      <c r="B612" t="inlineStr">
         <is>
           <t>images/「うちゅうへとびたい」_img1.jpg</t>
         </is>
       </c>
-      <c r="C613" t="inlineStr">
+      <c r="C612" t="inlineStr">
         <is>
           <t>絵本 ,宇宙</t>
         </is>
       </c>
     </row>
-    <row r="614">
-      <c r="A614" t="inlineStr">
+    <row r="613">
+      <c r="A613" t="inlineStr">
         <is>
           <t xml:space="preserve">「とても愛しています」
 أُحِبّك جِدّاً
@@ -13336,19 +13315,19 @@
 2308 hobe cc </t>
         </is>
       </c>
-      <c r="B614" t="inlineStr">
+      <c r="B613" t="inlineStr">
         <is>
           <t>images/「とても愛しています」_img1.jpg</t>
         </is>
       </c>
-      <c r="C614" t="inlineStr">
+      <c r="C613" t="inlineStr">
         <is>
           <t>恋 ,love</t>
         </is>
       </c>
     </row>
-    <row r="615">
-      <c r="A615" t="inlineStr">
+    <row r="614">
+      <c r="A614" t="inlineStr">
         <is>
           <t xml:space="preserve">「あす日が昇るだろう。私は朝が大好きだ」
 غدا ستشرق الشمس وأحب الصباح كثيرا
@@ -13357,19 +13336,19 @@
 2105 warag-3nb.tumblr com </t>
         </is>
       </c>
-      <c r="B615" t="inlineStr">
+      <c r="B614" t="inlineStr">
         <is>
           <t>images/「あす日が昇るだろう。私は朝が大好きだ_img1.jpg,images/ 「あす日が昇るだろう。私は朝が大好きだ_img2.jpg</t>
         </is>
       </c>
-      <c r="C615" t="inlineStr">
+      <c r="C614" t="inlineStr">
         <is>
           <t>おやすみ ,壁</t>
         </is>
       </c>
     </row>
-    <row r="616">
-      <c r="A616" t="inlineStr">
+    <row r="615">
+      <c r="A615" t="inlineStr">
         <is>
           <t xml:space="preserve">「きみは何をえらぶ？」
 ماذا تختار؟
@@ -13379,19 +13358,19 @@
 2109 embadomjp org </t>
         </is>
       </c>
-      <c r="B616" t="inlineStr">
+      <c r="B615" t="inlineStr">
         <is>
           <t>images/「きみは何をえらぶ？」_img1.jpg</t>
         </is>
       </c>
-      <c r="C616" t="inlineStr">
+      <c r="C615" t="inlineStr">
         <is>
           <t>優柔不断 ,絵本</t>
         </is>
       </c>
     </row>
-    <row r="617">
-      <c r="A617" t="inlineStr">
+    <row r="616">
+      <c r="A616" t="inlineStr">
         <is>
           <t xml:space="preserve">「ちょっと静けさが必要な時もある」
 في بعض الأوقات نحتاج لشوية هدوء
@@ -13401,19 +13380,19 @@
 2308 IN49r </t>
         </is>
       </c>
-      <c r="B617" t="inlineStr">
+      <c r="B616" t="inlineStr">
         <is>
           <t>images/「ちょっと静けさが必要な時もある」_img1.jpg</t>
         </is>
       </c>
-      <c r="C617" t="inlineStr">
+      <c r="C616" t="inlineStr">
         <is>
           <t>ミュート ,精神</t>
         </is>
       </c>
     </row>
-    <row r="618">
-      <c r="A618" t="inlineStr">
+    <row r="617">
+      <c r="A617" t="inlineStr">
         <is>
           <t xml:space="preserve">「逃げるな。全力でぶつかれ」
 لا تهرب اصطدم بكل قوتك
@@ -13423,19 +13402,19 @@
 2308 https://risingvibes.tumblr.com/post/189545775129 </t>
         </is>
       </c>
-      <c r="B618" t="inlineStr">
+      <c r="B617" t="inlineStr">
         <is>
           <t>images/「逃げるな。全力でぶつかれ」_img1.jpg</t>
         </is>
       </c>
-      <c r="C618" t="inlineStr">
+      <c r="C617" t="inlineStr">
         <is>
           <t>応援 ,力</t>
         </is>
       </c>
     </row>
-    <row r="619">
-      <c r="A619" t="inlineStr">
+    <row r="618">
+      <c r="A618" t="inlineStr">
         <is>
           <t xml:space="preserve">「着るのだいすき」
 أُحِبُ أَن أَرتَدِيَ
@@ -13445,19 +13424,19 @@
 2308 https://kitab.firmabikes.ru/epub-_hb_n_rtdy_5187.html </t>
         </is>
       </c>
-      <c r="B619" t="inlineStr">
+      <c r="B618" t="inlineStr">
         <is>
           <t>images/「着るのだいすき」_img1.jpg</t>
         </is>
       </c>
-      <c r="C619" t="inlineStr">
+      <c r="C618" t="inlineStr">
         <is>
           <t xml:space="preserve">絵本 ,ファッション </t>
         </is>
       </c>
     </row>
-    <row r="620">
-      <c r="A620" t="inlineStr">
+    <row r="619">
+      <c r="A619" t="inlineStr">
         <is>
           <t xml:space="preserve">「車のバッテリーが要る！」
 نحتاج بطارية سيارة
@@ -13467,19 +13446,19 @@
 2308 instagram roaa_27 </t>
         </is>
       </c>
-      <c r="B620" t="inlineStr">
+      <c r="B619" t="inlineStr">
         <is>
           <t>images/「車のバッテリーが要る！」_img1.jpg</t>
         </is>
       </c>
-      <c r="C620" t="inlineStr">
+      <c r="C619" t="inlineStr">
         <is>
           <t>スマホ ,充電</t>
         </is>
       </c>
     </row>
-    <row r="621">
-      <c r="A621" t="inlineStr">
+    <row r="620">
+      <c r="A620" t="inlineStr">
         <is>
           <t xml:space="preserve">「今日は幸せでいることにしました」
 اخترت أن أكون سعيدا اليوم
@@ -13489,19 +13468,19 @@
 2109 awaasha tumblr </t>
         </is>
       </c>
-      <c r="B621" t="inlineStr">
+      <c r="B620" t="inlineStr">
         <is>
           <t>images/「今日は幸せでいることにしました」_img1.jpg</t>
         </is>
       </c>
-      <c r="C621" t="inlineStr">
+      <c r="C620" t="inlineStr">
         <is>
           <t>心構え ,happy</t>
         </is>
       </c>
     </row>
-    <row r="622">
-      <c r="A622" t="inlineStr">
+    <row r="621">
+      <c r="A621" t="inlineStr">
         <is>
           <t xml:space="preserve">「理想的なスイカの選び方」
 كيف تختار البطيخة المُثلى؟
@@ -13511,19 +13490,19 @@
 2308 bit ly/octmel </t>
         </is>
       </c>
-      <c r="B622" t="inlineStr">
+      <c r="B621" t="inlineStr">
         <is>
           <t>images/「理想的なスイカの選び方」_img1.jpg</t>
         </is>
       </c>
-      <c r="C622" t="inlineStr">
+      <c r="C621" t="inlineStr">
         <is>
           <t>八百屋 ,西瓜</t>
         </is>
       </c>
     </row>
-    <row r="623">
-      <c r="A623" t="inlineStr">
+    <row r="622">
+      <c r="A622" t="inlineStr">
         <is>
           <t xml:space="preserve">「お問い合わせください」
 اتصل بنا
@@ -13533,19 +13512,19 @@
 2308 mtawir.blogspot com </t>
         </is>
       </c>
-      <c r="B623" t="inlineStr">
+      <c r="B622" t="inlineStr">
         <is>
           <t>images/「お問い合わせください」_img1.jpg</t>
         </is>
       </c>
-      <c r="C623" t="inlineStr">
+      <c r="C622" t="inlineStr">
         <is>
           <t>広告 ,電話</t>
         </is>
       </c>
     </row>
-    <row r="624">
-      <c r="A624" t="inlineStr">
+    <row r="623">
+      <c r="A623" t="inlineStr">
         <is>
           <t xml:space="preserve">「両方の動物が海岸の火山岩の亀裂の中に定住している」
 يحتل كلا الحيوانين شقوقًا في صخور الساحل البركانية
@@ -13553,19 +13532,19 @@
 2507 https://x.com/NatGeoMagArab/status/1925167200056521151 </t>
         </is>
       </c>
-      <c r="B624" t="inlineStr">
+      <c r="B623" t="inlineStr">
         <is>
           <t>images/「両方の動物が海岸の火山岩の亀裂の中に_img1.jpg,images/「両方の動物が海岸の火山岩の亀裂の中に_img2.jpg</t>
         </is>
       </c>
-      <c r="C624" t="inlineStr">
+      <c r="C623" t="inlineStr">
         <is>
           <t>手書き語学 ,アラビア語 ,イグアナ</t>
         </is>
       </c>
     </row>
-    <row r="625">
-      <c r="A625" t="inlineStr">
+    <row r="624">
+      <c r="A624" t="inlineStr">
         <is>
           <t xml:space="preserve">「命じられたように正しき道を辿れ」
 واستقم كما أمرت
@@ -13575,19 +13554,19 @@
 2308 Ahmed Madyan </t>
         </is>
       </c>
-      <c r="B625" t="inlineStr">
+      <c r="B624" t="inlineStr">
         <is>
           <t>images/「命じられたように正しき道を辿れ」_img1.jpg</t>
         </is>
       </c>
-      <c r="C625" t="inlineStr">
+      <c r="C624" t="inlineStr">
         <is>
           <t>書道 ,アート</t>
         </is>
       </c>
     </row>
-    <row r="626">
-      <c r="A626" t="inlineStr">
+    <row r="625">
+      <c r="A625" t="inlineStr">
         <is>
           <t xml:space="preserve">「くつろぎなさい」استكن
 イスタキンナ [istakinna]
@@ -13595,19 +13574,19 @@
 2603 m2ff tumblr com </t>
         </is>
       </c>
-      <c r="B626" t="inlineStr">
+      <c r="B625" t="inlineStr">
         <is>
           <t>images/「くつろぎなさい」.jpeg</t>
         </is>
       </c>
-      <c r="C626" t="inlineStr">
+      <c r="C625" t="inlineStr">
         <is>
           <t>relax ,コーヒー</t>
         </is>
       </c>
     </row>
-    <row r="627">
-      <c r="A627" t="inlineStr">
+    <row r="626">
+      <c r="A626" t="inlineStr">
         <is>
           <t xml:space="preserve">「彼は応えるだろう」سيستجيب 
 サヤスタジーブ [sa-ya-stajiibu]
@@ -13616,19 +13595,19 @@
 1811 kareem mrghani </t>
         </is>
       </c>
-      <c r="B627" t="inlineStr">
+      <c r="B626" t="inlineStr">
         <is>
           <t>images/「彼は応えるだろう」_img1.jpg</t>
         </is>
       </c>
-      <c r="C627" t="inlineStr">
+      <c r="C626" t="inlineStr">
         <is>
           <t>縦書き ,現代アート</t>
         </is>
       </c>
     </row>
-    <row r="628">
-      <c r="A628" t="inlineStr">
+    <row r="627">
+      <c r="A627" t="inlineStr">
         <is>
           <t xml:space="preserve">「アラビア語が好き」
 أنا أُحبّ لُغتي
@@ -13638,19 +13617,19 @@
 2308 出典不明 </t>
         </is>
       </c>
-      <c r="B628" t="inlineStr">
+      <c r="B627" t="inlineStr">
         <is>
           <t>images/「アラビア語が好き」_img1.jpg</t>
         </is>
       </c>
-      <c r="C628" t="inlineStr">
+      <c r="C627" t="inlineStr">
         <is>
           <t>和訳 ,こども</t>
         </is>
       </c>
     </row>
-    <row r="629">
-      <c r="A629" t="inlineStr">
+    <row r="628">
+      <c r="A628" t="inlineStr">
         <is>
           <t xml:space="preserve">「私はサッカーが好きです」
 أنا أُحِبُّ كُرةَ القَدَم
@@ -13660,19 +13639,19 @@
 2109 Arabic With Nadia </t>
         </is>
       </c>
-      <c r="B629" t="inlineStr">
+      <c r="B628" t="inlineStr">
         <is>
           <t>images/「私はサッカーが好きです」_img1.jpg</t>
         </is>
       </c>
-      <c r="C629" t="inlineStr">
+      <c r="C628" t="inlineStr">
         <is>
           <t>自由時間 ,例文</t>
         </is>
       </c>
     </row>
-    <row r="630">
-      <c r="A630" t="inlineStr">
+    <row r="629">
+      <c r="A629" t="inlineStr">
         <is>
           <t xml:space="preserve">「これ、私の眼鏡じゃありません」
 هٰذِهِ لَيْسَتْ نَظَّارَاتِي
@@ -13682,19 +13661,19 @@
 2509 </t>
         </is>
       </c>
-      <c r="B630" t="inlineStr">
+      <c r="B629" t="inlineStr">
         <is>
           <t>images/「これ、私の眼鏡じゃありません」_img1.jpg</t>
         </is>
       </c>
-      <c r="C630" t="inlineStr">
+      <c r="C629" t="inlineStr">
         <is>
           <t>あらびあや</t>
         </is>
       </c>
     </row>
-    <row r="631">
-      <c r="A631" t="inlineStr">
+    <row r="630">
+      <c r="A630" t="inlineStr">
         <is>
           <t xml:space="preserve">「我らも米を食います」
 نحن أيضاً نأكل الأرز
@@ -13704,19 +13683,19 @@
 1809 </t>
         </is>
       </c>
-      <c r="B631" t="inlineStr">
+      <c r="B630" t="inlineStr">
         <is>
           <t>images/「我らも米を食います」_img1.jpg</t>
         </is>
       </c>
-      <c r="C631" t="inlineStr">
+      <c r="C630" t="inlineStr">
         <is>
           <t>あらびあや</t>
         </is>
       </c>
     </row>
-    <row r="632">
-      <c r="A632" t="inlineStr">
+    <row r="631">
+      <c r="A631" t="inlineStr">
         <is>
           <t xml:space="preserve">「ひとりでできるもん！」
 أنا أستطيع أن أفعله وحدي
@@ -13725,19 +13704,19 @@
 2105 </t>
         </is>
       </c>
-      <c r="B632" t="inlineStr">
+      <c r="B631" t="inlineStr">
         <is>
           <t>images/「ひとりでできるもん！」_img1.jpg</t>
         </is>
       </c>
-      <c r="C632" t="inlineStr">
+      <c r="C631" t="inlineStr">
         <is>
           <t>あらびあや</t>
         </is>
       </c>
     </row>
-    <row r="633">
-      <c r="A633" t="inlineStr">
+    <row r="632">
+      <c r="A632" t="inlineStr">
         <is>
           <t xml:space="preserve">「恋しくないと言っている時は恋しい」
 أُريدُك حينَ أَقُولُ أَنا لا أُريدُك
@@ -13747,19 +13726,19 @@
 2308 DARWISHISM </t>
         </is>
       </c>
-      <c r="B633" t="inlineStr">
+      <c r="B632" t="inlineStr">
         <is>
           <t>images/「恋しくないと言っている時は恋しい」_img1.jpg</t>
         </is>
       </c>
-      <c r="C633" t="inlineStr">
+      <c r="C632" t="inlineStr">
         <is>
           <t>本音 ,恋愛</t>
         </is>
       </c>
     </row>
-    <row r="634">
-      <c r="A634" t="inlineStr">
+    <row r="633">
+      <c r="A633" t="inlineStr">
         <is>
           <t xml:space="preserve">「私は〜する」
 ⁦「着る」：( أنا ألبس )['ana 'a-lbas]⁩
@@ -13770,19 +13749,19 @@
 2109 RABIE </t>
         </is>
       </c>
-      <c r="B634" t="inlineStr">
+      <c r="B633" t="inlineStr">
         <is>
           <t>images/「私は〜する」_img1.jpg,images/「私は〜する」_img2.jpg,images/「私は〜する」_img3.jpg,images/「私は〜する」_img4.jpg</t>
         </is>
       </c>
-      <c r="C634" t="inlineStr">
+      <c r="C633" t="inlineStr">
         <is>
           <t>動詞 ,絵本</t>
         </is>
       </c>
     </row>
-    <row r="635">
-      <c r="A635" t="inlineStr">
+    <row r="634">
+      <c r="A634" t="inlineStr">
         <is>
           <t xml:space="preserve">「彼は完璧ではない。私は彼の欠点については目をつむった」
 هو ليس كامل. أنا أعميت نفسي عن سيئاته
@@ -13791,19 +13770,19 @@
 2308 _NOHA </t>
         </is>
       </c>
-      <c r="B635" t="inlineStr">
+      <c r="B634" t="inlineStr">
         <is>
           <t>images/「彼は完璧ではない。私は彼の欠点につい_img1.jpg</t>
         </is>
       </c>
-      <c r="C635" t="inlineStr">
+      <c r="C634" t="inlineStr">
         <is>
           <t>愛 ,寛容</t>
         </is>
       </c>
     </row>
-    <row r="636">
-      <c r="A636" t="inlineStr">
+    <row r="635">
+      <c r="A635" t="inlineStr">
         <is>
           <t xml:space="preserve">「この子トラは検疫期間中に生まれた」
 صغير النمر هذا ولد في زمن الحجر الصحي
@@ -13812,19 +13791,19 @@
 2310 https://www.akhbaralaan.net/?p=434924 </t>
         </is>
       </c>
-      <c r="B636" t="inlineStr">
+      <c r="B635" t="inlineStr">
         <is>
           <t>images/「この子トラは検疫期間中に生まれた」_img1.jpg</t>
         </is>
       </c>
-      <c r="C636" t="inlineStr">
+      <c r="C635" t="inlineStr">
         <is>
           <t>Covid ,メキシコ</t>
         </is>
       </c>
     </row>
-    <row r="637">
-      <c r="A637" t="inlineStr">
+    <row r="636">
+      <c r="A636" t="inlineStr">
         <is>
           <t xml:space="preserve">「睡眠の素晴らしさに匹敵するものは無い！」
 وجمال النوم ليس له مثيل
@@ -13833,19 +13812,19 @@
 2308 arabzy tumblr </t>
         </is>
       </c>
-      <c r="B637" t="inlineStr">
+      <c r="B636" t="inlineStr">
         <is>
           <t>images/「睡眠の素晴らしさに匹敵するものは無い_img1.jpg</t>
         </is>
       </c>
-      <c r="C637" t="inlineStr">
+      <c r="C636" t="inlineStr">
         <is>
           <t>オフトゥン ,おやすみ</t>
         </is>
       </c>
     </row>
-    <row r="638">
-      <c r="A638" t="inlineStr">
+    <row r="637">
+      <c r="A637" t="inlineStr">
         <is>
           <t xml:space="preserve">「大器晩成」
 الأشياء العظيمة تأخذ وقت
@@ -13855,19 +13834,19 @@
 2109 出典不明 </t>
         </is>
       </c>
-      <c r="B638" t="inlineStr">
+      <c r="B637" t="inlineStr">
         <is>
           <t>images/「大器晩成」_img1.jpg</t>
         </is>
       </c>
-      <c r="C638" t="inlineStr">
+      <c r="C637" t="inlineStr">
         <is>
           <t>ことわざ ,和訳</t>
         </is>
       </c>
     </row>
-    <row r="639">
-      <c r="A639" t="inlineStr">
+    <row r="638">
+      <c r="A638" t="inlineStr">
         <is>
           <t xml:space="preserve">「コーヒーは急には飲まれない」
 القهْوة لا تشرَب عَلى عَجلْ
@@ -13878,19 +13857,19 @@
 2012 Ahmed Madyan </t>
         </is>
       </c>
-      <c r="B639" t="inlineStr">
+      <c r="B638" t="inlineStr">
         <is>
           <t>images/「コーヒーは急には飲まれない」_img1.jpg</t>
         </is>
       </c>
-      <c r="C639" t="inlineStr">
+      <c r="C638" t="inlineStr">
         <is>
           <t>名言</t>
         </is>
       </c>
     </row>
-    <row r="640">
-      <c r="A640" t="inlineStr">
+    <row r="639">
+      <c r="A639" t="inlineStr">
         <is>
           <t xml:space="preserve">「成功者は情報共有している」
 الناجحون يشاركون المعلومة
@@ -13900,19 +13879,19 @@
 2109 出典不明 </t>
         </is>
       </c>
-      <c r="B640" t="inlineStr">
+      <c r="B639" t="inlineStr">
         <is>
           <t>images/「成功者は情報共有している」_img1.jpg</t>
         </is>
       </c>
-      <c r="C640" t="inlineStr">
+      <c r="C639" t="inlineStr">
         <is>
           <t>鳥 ,シェア</t>
         </is>
       </c>
     </row>
-    <row r="641">
-      <c r="A641" t="inlineStr">
+    <row r="640">
+      <c r="A640" t="inlineStr">
         <is>
           <t xml:space="preserve">「間違いで賢くなる、痛みで強くなる」
 الأخطاء تجعلك حكيمًا، والألم يجعلك قويًا
@@ -13921,19 +13900,19 @@
 2111 https://alaminin.blogspot.com/2020/03/blog-post_6.html </t>
         </is>
       </c>
-      <c r="B641" t="inlineStr">
+      <c r="B640" t="inlineStr">
         <is>
           <t>images/「間違いで賢くなる、痛みで強くなる」_img1.jpg</t>
         </is>
       </c>
-      <c r="C641" t="inlineStr">
+      <c r="C640" t="inlineStr">
         <is>
           <t>名言</t>
         </is>
       </c>
     </row>
-    <row r="642">
-      <c r="A642" t="inlineStr">
+    <row r="641">
+      <c r="A641" t="inlineStr">
         <is>
           <t xml:space="preserve">「何事も永遠には続かない」
 لا شيء يبقى للأبد
@@ -13943,19 +13922,19 @@
 2308 KiTeLetZ </t>
         </is>
       </c>
-      <c r="B642" t="inlineStr">
+      <c r="B641" t="inlineStr">
         <is>
           <t>images/「何事も永遠には続かない」_img1.jpg</t>
         </is>
       </c>
-      <c r="C642" t="inlineStr">
+      <c r="C641" t="inlineStr">
         <is>
           <t>変化 ,名言</t>
         </is>
       </c>
     </row>
-    <row r="643">
-      <c r="A643" t="inlineStr">
+    <row r="642">
+      <c r="A642" t="inlineStr">
         <is>
           <t xml:space="preserve">「惑星地球はあなた方を歓迎します」
 كوكب الارض يرحّب بكم
@@ -13965,19 +13944,19 @@
 1811 iN49R </t>
         </is>
       </c>
-      <c r="B643" t="inlineStr">
+      <c r="B642" t="inlineStr">
         <is>
           <t>images/「惑星地球はあなた方を歓迎します」_img1.jpg</t>
         </is>
       </c>
-      <c r="C643" t="inlineStr">
+      <c r="C642" t="inlineStr">
         <is>
           <t>宇宙 ,人類</t>
         </is>
       </c>
     </row>
-    <row r="644">
-      <c r="A644" t="inlineStr">
+    <row r="643">
+      <c r="A643" t="inlineStr">
         <is>
           <t xml:space="preserve">「自分を信じなさい。人の言うことは尽きないのだから」
 ثق بنفسك فكلام الناس لا ينتهي
@@ -13986,19 +13965,19 @@
 2105 出典不明 </t>
         </is>
       </c>
-      <c r="B644" t="inlineStr">
+      <c r="B643" t="inlineStr">
         <is>
           <t>images/「自分を信じなさい。人の言うことは尽き_img1.jpg</t>
         </is>
       </c>
-      <c r="C644" t="inlineStr">
+      <c r="C643" t="inlineStr">
         <is>
           <t>自信 ,無視</t>
         </is>
       </c>
     </row>
-    <row r="645">
-      <c r="A645" t="inlineStr">
+    <row r="644">
+      <c r="A644" t="inlineStr">
         <is>
           <t xml:space="preserve">「弟が歩くぞ」أخي الصغير يمشي
 アキ_ッサギール・ヤムシー ['aKh-i ^_saGhiiru ya-mShii]
@@ -14007,19 +13986,19 @@
 2308 gulfkids com http://www.gulfkids.com/ar/book48-1909.htm </t>
         </is>
       </c>
-      <c r="B645" t="inlineStr">
+      <c r="B644" t="inlineStr">
         <is>
           <t>images/「弟が歩くぞ」_img1.jpg</t>
         </is>
       </c>
-      <c r="C645" t="inlineStr">
+      <c r="C644" t="inlineStr">
         <is>
           <t>兄弟 ,絵本</t>
         </is>
       </c>
     </row>
-    <row r="646">
-      <c r="A646" t="inlineStr">
+    <row r="645">
+      <c r="A645" t="inlineStr">
         <is>
           <t xml:space="preserve">花より団子おおお（違う）
 「誰もふさわしくない」[laa 'aHada ya-staHiqqu]
@@ -14027,19 +14006,19 @@
 2308 https://twitter.com/NatGeoMagArab/status/1370041991317233664 </t>
         </is>
       </c>
-      <c r="B646" t="inlineStr">
+      <c r="B645" t="inlineStr">
         <is>
           <t>images/花より団子おおお（違う）_img1.jpg</t>
         </is>
       </c>
-      <c r="C646" t="inlineStr">
+      <c r="C645" t="inlineStr">
         <is>
           <t>手書き語学 ,アラビア語 ,キノボリカンガルー</t>
         </is>
       </c>
     </row>
-    <row r="647">
-      <c r="A647" t="inlineStr">
+    <row r="646">
+      <c r="A646" t="inlineStr">
         <is>
           <t xml:space="preserve">「幸せな人生には弱い記憶力が必要」
 الحياة السعيدة تتطلب ذاكرة ضعيفة
@@ -14048,19 +14027,19 @@
 2012 出典不明 </t>
         </is>
       </c>
-      <c r="B647" t="inlineStr">
+      <c r="B646" t="inlineStr">
         <is>
           <t>images/「幸せな人生には弱い記憶力が必要」_img1.jpg</t>
         </is>
       </c>
-      <c r="C647" t="inlineStr">
+      <c r="C646" t="inlineStr">
         <is>
           <t>前向き</t>
         </is>
       </c>
     </row>
-    <row r="648">
-      <c r="A648" t="inlineStr">
+    <row r="647">
+      <c r="A647" t="inlineStr">
         <is>
           <t xml:space="preserve">「このパンダは私たちに、幸せは単純なことの中に隠れているのだと教えている」
 دب "الباندا" هذا يؤكد لنا أن السعادة تكمن في أبسط الأشياء
@@ -14068,19 +14047,19 @@
 2308 https://twitter.com/NatGeoMagArab/status/1309938472065486848 </t>
         </is>
       </c>
-      <c r="B648" t="inlineStr">
+      <c r="B647" t="inlineStr">
         <is>
           <t>images/「このパンダは私たちに、幸せは単純なこ.png</t>
         </is>
       </c>
-      <c r="C648" t="inlineStr">
+      <c r="C647" t="inlineStr">
         <is>
           <t>パンダ ,雪</t>
         </is>
       </c>
     </row>
-    <row r="649">
-      <c r="A649" t="inlineStr">
+    <row r="648">
+      <c r="A648" t="inlineStr">
         <is>
           <t xml:space="preserve">「良い時間は速く過ぎる」
 الأوقات الجميلة تمر بسرعة
@@ -14090,19 +14069,19 @@
 1810 Nasser.Tumblr </t>
         </is>
       </c>
-      <c r="B649" t="inlineStr">
+      <c r="B648" t="inlineStr">
         <is>
           <t>images/「良い時間は速く過ぎる」_img1.jpg</t>
         </is>
       </c>
-      <c r="C649" t="inlineStr">
+      <c r="C648" t="inlineStr">
         <is>
           <t>相対論 ,心理学</t>
         </is>
       </c>
     </row>
-    <row r="650">
-      <c r="A650" t="inlineStr">
+    <row r="649">
+      <c r="A649" t="inlineStr">
         <is>
           <t xml:space="preserve">「今日が始まりかもしれない」
 كل يوم ممكن يكون بداية
@@ -14112,19 +14091,19 @@
 2308 Ahmed Madyan </t>
         </is>
       </c>
-      <c r="B650" t="inlineStr">
+      <c r="B649" t="inlineStr">
         <is>
           <t>images/「今日が始まりかもしれない」_img1.jpg</t>
         </is>
       </c>
-      <c r="C650" t="inlineStr">
+      <c r="C649" t="inlineStr">
         <is>
           <t>吉日 ,開始</t>
         </is>
       </c>
     </row>
-    <row r="651">
-      <c r="A651" t="inlineStr">
+    <row r="650">
+      <c r="A650" t="inlineStr">
         <is>
           <t xml:space="preserve">「ヌール、歯医者さんに行く」
 نور تذهب إلى طبيب الأسنان
@@ -14134,19 +14113,19 @@
 2109 RABIE </t>
         </is>
       </c>
-      <c r="B651" t="inlineStr">
+      <c r="B650" t="inlineStr">
         <is>
           <t>images/「ヌール、歯医者さんに行く」_img1.jpg</t>
         </is>
       </c>
-      <c r="C651" t="inlineStr">
+      <c r="C650" t="inlineStr">
         <is>
           <t>絵本 ,歯科</t>
         </is>
       </c>
     </row>
-    <row r="652">
-      <c r="A652" t="inlineStr">
+    <row r="651">
+      <c r="A651" t="inlineStr">
         <is>
           <t xml:space="preserve">「ラヤンはねむれない」
 لَيان لا تَسْتَطيعُ أَنْ تَنام
@@ -14155,19 +14134,19 @@
 2308 出典不明 </t>
         </is>
       </c>
-      <c r="B652" t="inlineStr">
+      <c r="B651" t="inlineStr">
         <is>
           <t>images/「ラヤンはねむれない」_img1.jpg</t>
         </is>
       </c>
-      <c r="C652" t="inlineStr">
+      <c r="C651" t="inlineStr">
         <is>
           <t>絵本 ,不眠症</t>
         </is>
       </c>
     </row>
-    <row r="653">
-      <c r="A653" t="inlineStr">
+    <row r="652">
+      <c r="A652" t="inlineStr">
         <is>
           <t xml:space="preserve">「クネイトラ県、蜂の巣を約60%失う」
 القنيطرة تفقد حوالي 60 % من خلايا نحلها
@@ -14175,19 +14154,19 @@
 2403 nabd com/t/101679025-fb119f </t>
         </is>
       </c>
-      <c r="B653" t="inlineStr">
+      <c r="B652" t="inlineStr">
         <is>
           <t>images/「クネイトラ県、蜂の巣を約60%失う」_img1.jpg</t>
         </is>
       </c>
-      <c r="C653" t="inlineStr">
+      <c r="C652" t="inlineStr">
         <is>
           <t>蜂の巣 ,パーセント</t>
         </is>
       </c>
     </row>
-    <row r="654">
-      <c r="A654" t="inlineStr">
+    <row r="653">
+      <c r="A653" t="inlineStr">
         <is>
           <t xml:space="preserve">「結ばれしター」ة
 ⁦( تاء مربوطة )[taa' marbuu_ta]：ت「ター」( تاء )[taa']・「結ばれている」( مربوط )[marbuu_t]：( ربط )【結】⁩
@@ -14195,19 +14174,19 @@
 2308 出典不明 </t>
         </is>
       </c>
-      <c r="B654" t="inlineStr">
+      <c r="B653" t="inlineStr">
         <is>
           <t>images/「結ばれしター」_img1.jpg</t>
         </is>
       </c>
-      <c r="C654" t="inlineStr">
+      <c r="C653" t="inlineStr">
         <is>
           <t>アラビア文字 ,顔</t>
         </is>
       </c>
     </row>
-    <row r="655">
-      <c r="A655" t="inlineStr">
+    <row r="654">
+      <c r="A654" t="inlineStr">
         <is>
           <t xml:space="preserve">「忙しい」مشغول
 マシュグール [maShGhuul]
@@ -14216,19 +14195,19 @@
 1811 skyshinichi.instagram </t>
         </is>
       </c>
-      <c r="B655" t="inlineStr">
+      <c r="B654" t="inlineStr">
         <is>
           <t>images/「忙しい」_img1.jpg</t>
         </is>
       </c>
-      <c r="C655" t="inlineStr">
+      <c r="C654" t="inlineStr">
         <is>
           <t>スティッチ ,残業</t>
         </is>
       </c>
     </row>
-    <row r="656">
-      <c r="A656" t="inlineStr">
+    <row r="655">
+      <c r="A655" t="inlineStr">
         <is>
           <t xml:space="preserve">「駐車禁止」ممنوع الوقوف
 マムヌーア・アルウクーフ [mamnuu* al-wuquuf]
@@ -14237,19 +14216,19 @@
 2106 出典不明 </t>
         </is>
       </c>
-      <c r="B656" t="inlineStr">
+      <c r="B655" t="inlineStr">
         <is>
           <t>images/「駐車禁止」_img1.jpg</t>
         </is>
       </c>
-      <c r="C656" t="inlineStr">
+      <c r="C655" t="inlineStr">
         <is>
           <t>標識 ,ジョーク</t>
         </is>
       </c>
     </row>
-    <row r="657">
-      <c r="A657" t="inlineStr">
+    <row r="656">
+      <c r="A656" t="inlineStr">
         <is>
           <t xml:space="preserve">「一人ひとりが責任を」
 كُلنا مسؤول
@@ -14259,19 +14238,19 @@
 2308 covid19awareness sa </t>
         </is>
       </c>
-      <c r="B657" t="inlineStr">
+      <c r="B656" t="inlineStr">
         <is>
           <t>images/「一人ひとりが責任を」_img1.jpg</t>
         </is>
       </c>
-      <c r="C657" t="inlineStr">
+      <c r="C656" t="inlineStr">
         <is>
           <t>Covid ,感染拡大防止</t>
         </is>
       </c>
     </row>
-    <row r="658">
-      <c r="A658" t="inlineStr">
+    <row r="657">
+      <c r="A657" t="inlineStr">
         <is>
           <t xml:space="preserve">「おめでとうございます」مبروك
 マブルーク [mabruuk]
@@ -14280,19 +14259,19 @@
 2308 </t>
         </is>
       </c>
-      <c r="B658" t="inlineStr">
+      <c r="B657" t="inlineStr">
         <is>
           <t>images/「おめでとうございます」_img1.jpg</t>
         </is>
       </c>
-      <c r="C658" t="inlineStr">
+      <c r="C657" t="inlineStr">
         <is>
           <t>詐欺 ,広告</t>
         </is>
       </c>
     </row>
-    <row r="659">
-      <c r="A659" t="inlineStr">
+    <row r="658">
+      <c r="A658" t="inlineStr">
         <is>
           <t xml:space="preserve">「手書きフォント」
 خط مكتوب باليد
@@ -14302,19 +14281,19 @@
 1809 FahdAlFraikh Behance </t>
         </is>
       </c>
-      <c r="B659" t="inlineStr">
+      <c r="B658" t="inlineStr">
         <is>
           <t>images/「手書きフォント」_img1.jpg</t>
         </is>
       </c>
-      <c r="C659" t="inlineStr">
+      <c r="C658" t="inlineStr">
         <is>
           <t>可愛いフォント ,筆跡</t>
         </is>
       </c>
     </row>
-    <row r="660">
-      <c r="A660" t="inlineStr">
+    <row r="659">
+      <c r="A659" t="inlineStr">
         <is>
           <t xml:space="preserve">「開かれたターと結ばれたター」
 التاء المفتوحة والمربوطة
@@ -14324,19 +14303,19 @@
 2109 slideshare.net </t>
         </is>
       </c>
-      <c r="B660" t="inlineStr">
+      <c r="B659" t="inlineStr">
         <is>
           <t>images/「開かれたターと結ばれたター」_img1.jpg</t>
         </is>
       </c>
-      <c r="C660" t="inlineStr">
+      <c r="C659" t="inlineStr">
         <is>
           <t>アラビア文字 ,スマイリー</t>
         </is>
       </c>
     </row>
-    <row r="661">
-      <c r="A661" t="inlineStr">
+    <row r="660">
+      <c r="A660" t="inlineStr">
         <is>
           <t xml:space="preserve">「このラマは誇らしげにして立っている」
 تقف هذه اللاما مزهوة بنفسها
@@ -14344,19 +14323,19 @@
 2410 https://twitter.com/NatGeoMagArab/status/1597485552965935104 </t>
         </is>
       </c>
-      <c r="B661" t="inlineStr">
+      <c r="B660" t="inlineStr">
         <is>
           <t>images/「このラマは誇らしげにして立っている」_img1.jpg</t>
         </is>
       </c>
-      <c r="C661" t="inlineStr">
+      <c r="C660" t="inlineStr">
         <is>
           <t>手書き語学 ,アラビア語 ,マチュピチュ遺跡</t>
         </is>
       </c>
     </row>
-    <row r="662">
-      <c r="A662" t="inlineStr">
+    <row r="661">
+      <c r="A661" t="inlineStr">
         <is>
           <t xml:space="preserve">「小さな生き物にしては危険な名前だ」
 اسم خطير لمخلوق صغير
@@ -14365,19 +14344,19 @@
 2308 https://twitter.com/NatGeoMagArab/status/1495035772071669760 </t>
         </is>
       </c>
-      <c r="B662" t="inlineStr">
+      <c r="B661" t="inlineStr">
         <is>
           <t>images/「小さな生き物にしては危険な名前だ」_img1.jpg</t>
         </is>
       </c>
-      <c r="C662" t="inlineStr">
+      <c r="C661" t="inlineStr">
         <is>
           <t>有袋類 ,タスマニアデビル</t>
         </is>
       </c>
     </row>
-    <row r="663">
-      <c r="A663" t="inlineStr">
+    <row r="662">
+      <c r="A662" t="inlineStr">
         <is>
           <t xml:space="preserve">「こわれている」مكسر
 ムカッサル [mukassar]
@@ -14385,19 +14364,19 @@
 2105 behance Written-Visuals </t>
         </is>
       </c>
-      <c r="B663" t="inlineStr">
+      <c r="B662" t="inlineStr">
         <is>
           <t>images/「こわれている」_img1.jpg</t>
         </is>
       </c>
-      <c r="C663" t="inlineStr">
+      <c r="C662" t="inlineStr">
         <is>
           <t>バラバラ ,デザイン</t>
         </is>
       </c>
     </row>
-    <row r="664">
-      <c r="A664" t="inlineStr">
+    <row r="663">
+      <c r="A663" t="inlineStr">
         <is>
           <t xml:space="preserve">「早起きする方法」
 كيف تنهض مُبكّرًا
@@ -14407,19 +14386,19 @@
 2308 Funders and Founders </t>
         </is>
       </c>
-      <c r="B664" t="inlineStr">
+      <c r="B663" t="inlineStr">
         <is>
           <t>images/「早起きする方法」_img1.jpg</t>
         </is>
       </c>
-      <c r="C664" t="inlineStr">
+      <c r="C663" t="inlineStr">
         <is>
           <t>オフトゥン ,寝起き</t>
         </is>
       </c>
     </row>
-    <row r="665">
-      <c r="A665" t="inlineStr">
+    <row r="664">
+      <c r="A664" t="inlineStr">
         <is>
           <t xml:space="preserve">「アラブ・デザイン文字展覧会」
 معرض لتخطيط الحرف العربي
@@ -14429,19 +14408,19 @@
 2109 arabic lettering exhibition </t>
         </is>
       </c>
-      <c r="B665" t="inlineStr">
+      <c r="B664" t="inlineStr">
         <is>
           <t>images/「アラブ・デザイン文字展覧会」_img1.jpg</t>
         </is>
       </c>
-      <c r="C665" t="inlineStr">
+      <c r="C664" t="inlineStr">
         <is>
           <t>ポスター</t>
         </is>
       </c>
     </row>
-    <row r="666">
-      <c r="A666" t="inlineStr">
+    <row r="665">
+      <c r="A665" t="inlineStr">
         <is>
           <t xml:space="preserve">「名探偵コナン」المحقق كونان
 アルムハッキク・コナン [al-muHaqqiq Conan]
@@ -14450,19 +14429,19 @@
 1809 wikipedia </t>
         </is>
       </c>
-      <c r="B666" t="inlineStr">
+      <c r="B665" t="inlineStr">
         <is>
           <t>images/「名探偵コナン」_img1.jpg</t>
         </is>
       </c>
-      <c r="C666" t="inlineStr">
+      <c r="C665" t="inlineStr">
         <is>
           <t>江戸川コナン ,ロゴ</t>
         </is>
       </c>
     </row>
-    <row r="667">
-      <c r="A667" t="inlineStr">
+    <row r="666">
+      <c r="A666" t="inlineStr">
         <is>
           <t xml:space="preserve">「イードおめでとう」عيد مبارك
 イード・ムバーラク [*iid mubaarak]
@@ -14470,19 +14449,19 @@
 2308 出典不明 </t>
         </is>
       </c>
-      <c r="B667" t="inlineStr">
+      <c r="B666" t="inlineStr">
         <is>
           <t>images/「イードおめでとう」_img1.jpg</t>
         </is>
       </c>
-      <c r="C667" t="inlineStr">
+      <c r="C666" t="inlineStr">
         <is>
           <t>عيد ,アラビア語</t>
         </is>
       </c>
     </row>
-    <row r="668">
-      <c r="A668" t="inlineStr">
+    <row r="667">
+      <c r="A667" t="inlineStr">
         <is>
           <t xml:space="preserve">「戦士」محارب
 ムハーリブ [muHaarib]
@@ -14491,19 +14470,19 @@
 1809 abudinges.tumblr </t>
         </is>
       </c>
-      <c r="B668" t="inlineStr">
+      <c r="B667" t="inlineStr">
         <is>
           <t>images/「戦士」_img1.jpg</t>
         </is>
       </c>
-      <c r="C668" t="inlineStr">
+      <c r="C667" t="inlineStr">
         <is>
           <t>ロゴ ,赤</t>
         </is>
       </c>
     </row>
-    <row r="669">
-      <c r="A669" t="inlineStr">
+    <row r="668">
+      <c r="A668" t="inlineStr">
         <is>
           <t xml:space="preserve">「ライブ」بث مباشر
 バッス・ムバーシル [ba^Th(un) mubaaShir(un)]
@@ -14512,19 +14491,19 @@
 2308 beIN SPORTS </t>
         </is>
       </c>
-      <c r="B669" t="inlineStr">
+      <c r="B668" t="inlineStr">
         <is>
           <t>images/「ライブ」_img1.jpg</t>
         </is>
       </c>
-      <c r="C669" t="inlineStr">
+      <c r="C668" t="inlineStr">
         <is>
           <t xml:space="preserve">生放送 ,試合 </t>
         </is>
       </c>
     </row>
-    <row r="670">
-      <c r="A670" t="inlineStr">
+    <row r="669">
+      <c r="A669" t="inlineStr">
         <is>
           <t xml:space="preserve">「信者」مُؤْمِنٌ
 ムッミン [mu'min(un)]
@@ -14533,19 +14512,19 @@
 2106 出典不明 </t>
         </is>
       </c>
-      <c r="B670" t="inlineStr">
+      <c r="B669" t="inlineStr">
         <is>
           <t>images/「信者」_img1.jpg</t>
         </is>
       </c>
-      <c r="C670" t="inlineStr">
+      <c r="C669" t="inlineStr">
         <is>
           <t>明暗 ,信仰</t>
         </is>
       </c>
     </row>
-    <row r="671">
-      <c r="A671" t="inlineStr">
+    <row r="670">
+      <c r="A670" t="inlineStr">
         <is>
           <t xml:space="preserve">「開⇔閉」
 مفتوح
@@ -14556,19 +14535,19 @@
 2312 Hussein Safina, behance </t>
         </is>
       </c>
-      <c r="B671" t="inlineStr">
+      <c r="B670" t="inlineStr">
         <is>
           <t>images/「開⇔閉」_img1.jpg</t>
         </is>
       </c>
-      <c r="C671" t="inlineStr">
+      <c r="C670" t="inlineStr">
         <is>
           <t>オープンマインド ,トグル</t>
         </is>
       </c>
     </row>
-    <row r="672">
-      <c r="A672" t="inlineStr">
+    <row r="671">
+      <c r="A671" t="inlineStr">
         <is>
           <t xml:space="preserve">「予想外な結末！」
 نهاية غير متوقعة
@@ -14576,19 +14555,19 @@
 2308 https://twitter.com/NatGeoMagArab/status/1159011433444593665 </t>
         </is>
       </c>
-      <c r="B672" t="inlineStr">
+      <c r="B671" t="inlineStr">
         <is>
           <t>images/「予想外な結末！」_img1.jpg</t>
         </is>
       </c>
-      <c r="C672" t="inlineStr">
+      <c r="C671" t="inlineStr">
         <is>
           <t>手書き語学 ,アラビア語 ,ウサギ</t>
         </is>
       </c>
     </row>
-    <row r="673">
-      <c r="A673" t="inlineStr">
+    <row r="672">
+      <c r="A672" t="inlineStr">
         <is>
           <t xml:space="preserve">「ベイルート・アニメイテッド」
 بیروت متحرّکة
@@ -14598,19 +14577,19 @@
 2308 arabic_script Instagram </t>
         </is>
       </c>
-      <c r="B673" t="inlineStr">
+      <c r="B672" t="inlineStr">
         <is>
           <t>images/「ベイルート・アニメイテッド」_img1.jpg</t>
         </is>
       </c>
-      <c r="C673" t="inlineStr">
+      <c r="C672" t="inlineStr">
         <is>
           <t>アニメ ,レバノン</t>
         </is>
       </c>
     </row>
-    <row r="674">
-      <c r="A674" t="inlineStr">
+    <row r="673">
+      <c r="A673" t="inlineStr">
         <is>
           <t xml:space="preserve">「夢みれば叶う」
 كُلُّ مُتَوَقَّعٍ آتٍ
@@ -14620,19 +14599,19 @@
 2108 Ahmed Madyan </t>
         </is>
       </c>
-      <c r="B674" t="inlineStr">
+      <c r="B673" t="inlineStr">
         <is>
           <t>images/「夢みれば叶う」_img1.jpg</t>
         </is>
       </c>
-      <c r="C674" t="inlineStr">
+      <c r="C673" t="inlineStr">
         <is>
           <t>希望 ,ドリカム</t>
         </is>
       </c>
     </row>
-    <row r="675">
-      <c r="A675" t="inlineStr">
+    <row r="674">
+      <c r="A674" t="inlineStr">
         <is>
           <t xml:space="preserve">「もし両者が人間のように鎧で武装して戦いに突入したら」
 لو خاضا معاركهما متسلحين بالدروع على غرار البش
@@ -14640,19 +14619,19 @@
 2404 https://x.com/NatGeoMagArab/status/1759284149456945464 </t>
         </is>
       </c>
-      <c r="B675" t="inlineStr">
+      <c r="B674" t="inlineStr">
         <is>
           <t>images/「もし両者が人間のように鎧で武装して戦_img1.jpg,images/「もし両者が人間のように鎧で武装して戦_img2.jpg</t>
         </is>
       </c>
-      <c r="C675" t="inlineStr">
+      <c r="C674" t="inlineStr">
         <is>
           <t>手書き語学 ,アラビア語 ,猫</t>
         </is>
       </c>
     </row>
-    <row r="676">
-      <c r="A676" t="inlineStr">
+    <row r="675">
+      <c r="A675" t="inlineStr">
         <is>
           <t xml:space="preserve">「全ては結びついている」
 كل شيء مترابط
@@ -14662,19 +14641,19 @@
 2308 Ahmed Madyan https://twitter.com/madyco22/status/1451990828298166273 </t>
         </is>
       </c>
-      <c r="B676" t="inlineStr">
+      <c r="B675" t="inlineStr">
         <is>
           <t>images/「全ては結びついている」_img1.jpg</t>
         </is>
       </c>
-      <c r="C676" t="inlineStr">
+      <c r="C675" t="inlineStr">
         <is>
           <t>一筆書き ,デザイン</t>
         </is>
       </c>
     </row>
-    <row r="677">
-      <c r="A677" t="inlineStr">
+    <row r="676">
+      <c r="A676" t="inlineStr">
         <is>
           <t xml:space="preserve">「初心者のためのスケッチトレーニング」
 تعليم الرسم للمبتدئين
@@ -14684,19 +14663,19 @@
 2308 free-bookspdf com </t>
         </is>
       </c>
-      <c r="B677" t="inlineStr">
+      <c r="B676" t="inlineStr">
         <is>
           <t>images/「初心者のためのスケッチトレーニング」_img1.jpg</t>
         </is>
       </c>
-      <c r="C677" t="inlineStr">
+      <c r="C676" t="inlineStr">
         <is>
           <t>イラスト ,絵</t>
         </is>
       </c>
     </row>
-    <row r="678">
-      <c r="A678" t="inlineStr">
+    <row r="677">
+      <c r="A677" t="inlineStr">
         <is>
           <t xml:space="preserve">「初心者のためのスルス体書道トレーニング」
 تعليم خط الثلث للمبتدئين
@@ -14706,19 +14685,19 @@
 2308 出典不明 </t>
         </is>
       </c>
-      <c r="B678" t="inlineStr">
+      <c r="B677" t="inlineStr">
         <is>
           <t>images/「初心者のためのスルス体書道トレーニン_img1.jpg</t>
         </is>
       </c>
-      <c r="C678" t="inlineStr">
+      <c r="C677" t="inlineStr">
         <is>
           <t>書道</t>
         </is>
       </c>
     </row>
-    <row r="679">
-      <c r="A679" t="inlineStr">
+    <row r="678">
+      <c r="A678" t="inlineStr">
         <is>
           <t xml:space="preserve">「笑顔でいなさい」خليك مبتسم
 カッリーク・ムブタスィム [Khallii-k mubtasim]
@@ -14727,19 +14706,19 @@
 2308 https://tmblr.co/Zj9tguYLXBvC </t>
         </is>
       </c>
-      <c r="B679" t="inlineStr">
+      <c r="B678" t="inlineStr">
         <is>
           <t>images/「笑顔でいなさい」_img1.jpg</t>
         </is>
       </c>
-      <c r="C679" t="inlineStr">
+      <c r="C678" t="inlineStr">
         <is>
           <t>スマイル ,名言</t>
         </is>
       </c>
     </row>
-    <row r="680">
-      <c r="A680" t="inlineStr">
+    <row r="679">
+      <c r="A679" t="inlineStr">
         <is>
           <t xml:space="preserve">自動車メーカー
 ⁦・「TOYOTA」( تويوتا )⁩
@@ -14751,19 +14730,19 @@
 2308 syarah com </t>
         </is>
       </c>
-      <c r="B680" t="inlineStr">
+      <c r="B679" t="inlineStr">
         <is>
           <t>images/自動車メーカー_img1.jpg,images/自動車メーカー_img2.jpg,images/自動車メーカー_img3.jpg,images/自動車メーカー_img4.jpg</t>
         </is>
       </c>
-      <c r="C680" t="inlineStr">
+      <c r="C679" t="inlineStr">
         <is>
           <t>日本車 ,韓国車</t>
         </is>
       </c>
     </row>
-    <row r="681">
-      <c r="A681" t="inlineStr">
+    <row r="680">
+      <c r="A680" t="inlineStr">
         <is>
           <t xml:space="preserve">「僕たちは協力して不可能を達成するよ」
 بالتعاون نحقق المحال
@@ -14773,19 +14752,19 @@
 2109 </t>
         </is>
       </c>
-      <c r="B681" t="inlineStr">
+      <c r="B680" t="inlineStr">
         <is>
           <t>images/「僕たちは協力して不可能を達成するよ」_img1.jpg</t>
         </is>
       </c>
-      <c r="C681" t="inlineStr">
+      <c r="C680" t="inlineStr">
         <is>
           <t>無理 ,ハム太郎</t>
         </is>
       </c>
     </row>
-    <row r="682">
-      <c r="A682" t="inlineStr">
+    <row r="681">
+      <c r="A681" t="inlineStr">
         <is>
           <t xml:space="preserve">「幸せは伝染性。喜びを広めよう」
 السعادة معدية فأشع الفرح
@@ -14795,19 +14774,19 @@
 2511 instagram　com/p/fVEfxEo7Va/ </t>
         </is>
       </c>
-      <c r="B682" t="inlineStr">
+      <c r="B681" t="inlineStr">
         <is>
           <t>images/「幸せは伝染性。喜びを広めよう」_img1.jpg</t>
         </is>
       </c>
-      <c r="C682" t="inlineStr">
+      <c r="C681" t="inlineStr">
         <is>
           <t>拡散希望</t>
         </is>
       </c>
     </row>
-    <row r="683">
-      <c r="A683" t="inlineStr">
+    <row r="682">
+      <c r="A682" t="inlineStr">
         <is>
           <t xml:space="preserve">「ストレスは人間だけのものではない」
 الشعور بالتوتر ليس حكرًا على البشر
@@ -14815,19 +14794,19 @@
 2408 https://x.com/NatGeoMagArab/status/1736755816911487420 </t>
         </is>
       </c>
-      <c r="B683" t="inlineStr">
+      <c r="B682" t="inlineStr">
         <is>
           <t>images/「ストレスは人間だけのものではない」_img1.jpg</t>
         </is>
       </c>
-      <c r="C683" t="inlineStr">
+      <c r="C682" t="inlineStr">
         <is>
           <t>手書き語学 ,アラビア語 ,ストレス</t>
         </is>
       </c>
     </row>
-    <row r="684">
-      <c r="A684" t="inlineStr">
+    <row r="683">
+      <c r="A683" t="inlineStr">
         <is>
           <t xml:space="preserve">「私達は出来ます！」
 نستطيع فعلها
@@ -14837,19 +14816,19 @@
 2308 NAHARBAHIJ com </t>
         </is>
       </c>
-      <c r="B684" t="inlineStr">
+      <c r="B683" t="inlineStr">
         <is>
           <t>images/「私達は出来ます！」_img1.jpg</t>
         </is>
       </c>
-      <c r="C684" t="inlineStr">
+      <c r="C683" t="inlineStr">
         <is>
           <t>女性 ,パロディ</t>
         </is>
       </c>
     </row>
-    <row r="685">
-      <c r="A685" t="inlineStr">
+    <row r="684">
+      <c r="A684" t="inlineStr">
         <is>
           <t xml:space="preserve">「全然分からん」ولا فاهم إشي
 ウラー・ファーヒム・イシ [w-laa faahim 'iShy]
@@ -14859,19 +14838,19 @@
 2209 出典不明 </t>
         </is>
       </c>
-      <c r="B685" t="inlineStr">
+      <c r="B684" t="inlineStr">
         <is>
           <t>images/「全然分からん」_img1.jpg</t>
         </is>
       </c>
-      <c r="C685" t="inlineStr">
+      <c r="C684" t="inlineStr">
         <is>
           <t>アラビア語</t>
         </is>
       </c>
     </row>
-    <row r="686">
-      <c r="A686" t="inlineStr">
+    <row r="685">
+      <c r="A685" t="inlineStr">
         <is>
           <t xml:space="preserve">「人間は一人ひとり、特別な才がある。だから自分を他人と比べるのはやめよう」
 لكل إنسان مواهبه الخاصة 
@@ -14880,19 +14859,19 @@
 1812 Gwid3 </t>
         </is>
       </c>
-      <c r="B686" t="inlineStr">
+      <c r="B685" t="inlineStr">
         <is>
           <t>images/「人間は一人ひとり、特別な才がある。だ_img1.jpg</t>
         </is>
       </c>
-      <c r="C686" t="inlineStr">
+      <c r="C685" t="inlineStr">
         <is>
           <t>自尊 ,プライド</t>
         </is>
       </c>
     </row>
-    <row r="687">
-      <c r="A687" t="inlineStr">
+    <row r="686">
+      <c r="A686" t="inlineStr">
         <is>
           <t xml:space="preserve">「この猫は食事をシェアするのが嫌い！」
 هذه القطة لا تحب مشاركة الطعام
@@ -14901,19 +14880,19 @@
 2605 facebook com/alahram/videos/2154923608133231/ </t>
         </is>
       </c>
-      <c r="B687" t="inlineStr">
+      <c r="B686" t="inlineStr">
         <is>
           <t>images/「この猫は食事をシェアするのが嫌い！」_img1.jpg</t>
         </is>
       </c>
-      <c r="C687" t="inlineStr">
+      <c r="C686" t="inlineStr">
         <is>
           <t>猫 ,ネコ</t>
         </is>
       </c>
     </row>
-    <row r="688">
-      <c r="A688" t="inlineStr">
+    <row r="687">
+      <c r="A687" t="inlineStr">
         <is>
           <t xml:space="preserve">「怪獣との戦いでは自分が怪獣化せぬよう警戒しなさい」
 احذر عند محاربة الوحوش ألا تصبح واحدا منهم
@@ -14923,19 +14902,19 @@
 2108 warag-3nb.tumblr </t>
         </is>
       </c>
-      <c r="B688" t="inlineStr">
+      <c r="B687" t="inlineStr">
         <is>
           <t>images/「怪獣との戦いでは自分が怪獣化せぬよう_img1.jpg,images/ 「怪獣との戦いでは自分が怪獣化せぬよう_img2.jpg</t>
         </is>
       </c>
-      <c r="C688" t="inlineStr">
+      <c r="C687" t="inlineStr">
         <is>
           <t>正気 ,モンスター</t>
         </is>
       </c>
     </row>
-    <row r="689">
-      <c r="A689" t="inlineStr">
+    <row r="688">
+      <c r="A688" t="inlineStr">
         <is>
           <t xml:space="preserve">「錯視アート」فن الخداع البصري
 ファンヌ_ルヒダーイ_ルバサリーイ [fannu l-Khidaa*i l-ba_sariyy]
@@ -14944,19 +14923,19 @@
 2409 https://online.pubhtml5.com/idtb/neft/ </t>
         </is>
       </c>
-      <c r="B689" t="inlineStr">
+      <c r="B688" t="inlineStr">
         <is>
           <t>images/「錯視アート」_img1.jpg</t>
         </is>
       </c>
-      <c r="C689" t="inlineStr">
+      <c r="C688" t="inlineStr">
         <is>
           <t>トリックアート</t>
         </is>
       </c>
     </row>
-    <row r="690">
-      <c r="A690" t="inlineStr">
+    <row r="689">
+      <c r="A689" t="inlineStr">
         <is>
           <t xml:space="preserve">「自然界の消防士の訓練」
 تدريبات رجال الإطفاء في الطبيعة
@@ -14964,19 +14943,19 @@
 2308 https://twitter.com/NatGeoMagArab/status/1462420543890608129 </t>
         </is>
       </c>
-      <c r="B690" t="inlineStr">
+      <c r="B689" t="inlineStr">
         <is>
           <t>images/「自然界の消防士の訓練」_img1.jpg,images/ 「自然界の消防士の訓練」_img2.jpg</t>
         </is>
       </c>
-      <c r="C690" t="inlineStr">
+      <c r="C689" t="inlineStr">
         <is>
           <t>手書き語学 ,アラビア語 ,ヒグマ</t>
         </is>
       </c>
     </row>
-    <row r="691">
-      <c r="A691" t="inlineStr">
+    <row r="690">
+      <c r="A690" t="inlineStr">
         <is>
           <t xml:space="preserve">「救助」إسعاف
 イスアーフ ['is*aaf]
@@ -14985,19 +14964,19 @@
 2109 ambulance gov ae </t>
         </is>
       </c>
-      <c r="B691" t="inlineStr">
+      <c r="B690" t="inlineStr">
         <is>
           <t>images/「救助」_img1.jpg</t>
         </is>
       </c>
-      <c r="C691" t="inlineStr">
+      <c r="C690" t="inlineStr">
         <is>
           <t>救急車 ,はたらくくるま</t>
         </is>
       </c>
     </row>
-    <row r="692">
-      <c r="A692" t="inlineStr">
+    <row r="691">
+      <c r="A691" t="inlineStr">
         <is>
           <t xml:space="preserve">「感情／感覚」الإحْسَاسْ
 アルイヒサース [al-'iHsaas]
@@ -15006,19 +14985,19 @@
 2308 iN49R </t>
         </is>
       </c>
-      <c r="B692" t="inlineStr">
+      <c r="B691" t="inlineStr">
         <is>
           <t>images/「感情／感覚」_img1.jpg</t>
         </is>
       </c>
-      <c r="C692" t="inlineStr">
+      <c r="C691" t="inlineStr">
         <is>
           <t>オフ ,一休み</t>
         </is>
       </c>
     </row>
-    <row r="693">
-      <c r="A693" t="inlineStr">
+    <row r="692">
+      <c r="A692" t="inlineStr">
         <is>
           <t xml:space="preserve">「ひらめき」إلهام
 イルハーム ['lhaam]
@@ -15030,19 +15009,19 @@
 2103 出典不明 </t>
         </is>
       </c>
-      <c r="B693" t="inlineStr">
+      <c r="B692" t="inlineStr">
         <is>
           <t>images/「ひらめき」_img1.jpg</t>
         </is>
       </c>
-      <c r="C693" t="inlineStr">
+      <c r="C692" t="inlineStr">
         <is>
           <t>アラビア語</t>
         </is>
       </c>
     </row>
-    <row r="694">
-      <c r="A694" t="inlineStr">
+    <row r="693">
+      <c r="A693" t="inlineStr">
         <is>
           <t xml:space="preserve">「Ibdaa／クリエイティビティ」
 إبداع
@@ -15051,19 +15030,19 @@
 2308 Ibdaa Design &amp; Decoration Office </t>
         </is>
       </c>
-      <c r="B694" t="inlineStr">
+      <c r="B693" t="inlineStr">
         <is>
           <t>images/「Ibdaa／クリエイティビティ」_img1.jpg</t>
         </is>
       </c>
-      <c r="C694" t="inlineStr">
+      <c r="C693" t="inlineStr">
         <is>
           <t>創造性 ,独自性</t>
         </is>
       </c>
     </row>
-    <row r="695">
-      <c r="A695" t="inlineStr">
+    <row r="694">
+      <c r="A694" t="inlineStr">
         <is>
           <t xml:space="preserve">「奮闘なくして進歩なし」
 بدون كفاح لايوجد تقدم
@@ -15073,19 +15052,19 @@
 2105 ROUYMS TUMBLR COM </t>
         </is>
       </c>
-      <c r="B695" t="inlineStr">
+      <c r="B694" t="inlineStr">
         <is>
           <t>images/「奮闘なくして進歩なし」_img1.jpg</t>
         </is>
       </c>
-      <c r="C695" t="inlineStr">
+      <c r="C694" t="inlineStr">
         <is>
           <t>努力 ,三角形</t>
         </is>
       </c>
     </row>
-    <row r="696">
-      <c r="A696" t="inlineStr">
+    <row r="695">
+      <c r="A695" t="inlineStr">
         <is>
           <t xml:space="preserve">「木に登れば熊の危険を避けられるとお考えなら、考え直しましょう！」 
 إن اعتقدت أنك بمنأى عن خطر الدب عند تسلق الأشجار.. راجع حساباتك
@@ -15093,19 +15072,19 @@
 2202 NatGeoMagArab </t>
         </is>
       </c>
-      <c r="B696" t="inlineStr">
+      <c r="B695" t="inlineStr">
         <is>
           <t>images/「木に登れば熊の危険を避けられるとお考.jpeg</t>
         </is>
       </c>
-      <c r="C696" t="inlineStr">
+      <c r="C695" t="inlineStr">
         <is>
           <t>クマ</t>
         </is>
       </c>
     </row>
-    <row r="697">
-      <c r="A697" t="inlineStr">
+    <row r="696">
+      <c r="A696" t="inlineStr">
         <is>
           <t xml:space="preserve">「卒業おめでとう」مبروك التخرج
 マブルーク・タカッルジ [mabruuk a^taKharruj]
@@ -15114,19 +15093,19 @@
 2308 https://instagram.com/fatoomworld </t>
         </is>
       </c>
-      <c r="B697" t="inlineStr">
+      <c r="B696" t="inlineStr">
         <is>
           <t>images/「卒業おめでとう」_img1.jpg</t>
         </is>
       </c>
-      <c r="C697" t="inlineStr">
+      <c r="C696" t="inlineStr">
         <is>
           <t>卒業 ,イラスト</t>
         </is>
       </c>
     </row>
-    <row r="698">
-      <c r="A698" t="inlineStr">
+    <row r="697">
+      <c r="A697" t="inlineStr">
         <is>
           <t xml:space="preserve">「停止距離の計算」
 حساب مسافة التوقف
@@ -15136,19 +15115,19 @@
 2109 assurance-auto-info </t>
         </is>
       </c>
-      <c r="B698" t="inlineStr">
+      <c r="B697" t="inlineStr">
         <is>
           <t>images/「停止距離の計算」_img1.jpg</t>
         </is>
       </c>
-      <c r="C698" t="inlineStr">
+      <c r="C697" t="inlineStr">
         <is>
           <t>保険 ,自動車</t>
         </is>
       </c>
     </row>
-    <row r="699">
-      <c r="A699" t="inlineStr">
+    <row r="698">
+      <c r="A698" t="inlineStr">
         <is>
           <t xml:space="preserve">「教師要らず：10日でフランス語会話」
 بدون معلم
@@ -15158,19 +15137,19 @@
 2308 englais-best com </t>
         </is>
       </c>
-      <c r="B699" t="inlineStr">
+      <c r="B698" t="inlineStr">
         <is>
           <t>images/「教師要らず：10日でフランス語会話」_img1.jpg</t>
         </is>
       </c>
-      <c r="C699" t="inlineStr">
+      <c r="C698" t="inlineStr">
         <is>
           <t>教師なし学習</t>
         </is>
       </c>
     </row>
-    <row r="700">
-      <c r="A700" t="inlineStr">
+    <row r="699">
+      <c r="A699" t="inlineStr">
         <is>
           <t xml:space="preserve">「衝突」تصادم
 タサードゥム [ta_saadum]
@@ -15179,19 +15158,19 @@
 1810 </t>
         </is>
       </c>
-      <c r="B700" t="inlineStr">
+      <c r="B699" t="inlineStr">
         <is>
           <t>images/「衝突」_img1.jpg</t>
         </is>
       </c>
-      <c r="C700" t="inlineStr">
+      <c r="C699" t="inlineStr">
         <is>
           <t>あらびあや</t>
         </is>
       </c>
     </row>
-    <row r="701">
-      <c r="A701" t="inlineStr">
+    <row r="700">
+      <c r="A700" t="inlineStr">
         <is>
           <t xml:space="preserve">「楽観主義」تَفَاؤُلٌ
 タファーウル [tafaa'ul(un)]
@@ -15200,19 +15179,19 @@
 1904 arabictypography com </t>
         </is>
       </c>
-      <c r="B701" t="inlineStr">
+      <c r="B700" t="inlineStr">
         <is>
           <t>images/「楽観主義」_img1.jpg</t>
         </is>
       </c>
-      <c r="C701" t="inlineStr">
+      <c r="C700" t="inlineStr">
         <is>
           <t>やわらか ,緑</t>
         </is>
       </c>
     </row>
-    <row r="702">
-      <c r="A702" t="inlineStr">
+    <row r="701">
+      <c r="A701" t="inlineStr">
         <is>
           <t xml:space="preserve">「シベリアジャコウジカは、絶滅の危機にあると見なされている」
 يعد "أيل المسك السيبيري" مهددًا بالانقراض
@@ -15220,19 +15199,19 @@
 2308 https://twitter.com/NatGeoMagArab/status/1320666649045790720 </t>
         </is>
       </c>
-      <c r="B702" t="inlineStr">
+      <c r="B701" t="inlineStr">
         <is>
           <t>images/「シベリアジャコウジカは、絶滅の危機に_img1.jpg,images/「シベリアジャコウジカは、絶滅の危機に_img2.jpg</t>
         </is>
       </c>
-      <c r="C702" t="inlineStr">
+      <c r="C701" t="inlineStr">
         <is>
           <t>手書き語学 ,シベリア</t>
         </is>
       </c>
     </row>
-    <row r="703">
-      <c r="A703" t="inlineStr">
+    <row r="702">
+      <c r="A702" t="inlineStr">
         <is>
           <t xml:space="preserve">「融合／折衷／フュージョン」
 انصهار
@@ -15241,38 +15220,38 @@
 1811 elmahdyart Instagram </t>
         </is>
       </c>
-      <c r="B703" t="inlineStr">
+      <c r="B702" t="inlineStr">
         <is>
           <t>images/「融合／折衷／フュージョン」_img1.jpg</t>
         </is>
       </c>
-      <c r="C703" t="inlineStr">
+      <c r="C702" t="inlineStr">
         <is>
           <t>カリグラフィー ,書道</t>
         </is>
       </c>
     </row>
-    <row r="704">
-      <c r="A704" t="inlineStr">
+    <row r="703">
+      <c r="A703" t="inlineStr">
         <is>
           <t xml:space="preserve">「この子供は、昼寝をしようとする母親を邪魔しているようだ」
 「場所はインドのトラ保護区、バンダウガル公園。トラは生態ピラミッドのトップの捕食動物だが、最もリスクの高い絶滅危惧種のひとつである」
 2308 https://twitter.com/natgeomagarab/status/1553681890665586689 </t>
         </is>
       </c>
-      <c r="B704" t="inlineStr">
+      <c r="B703" t="inlineStr">
         <is>
           <t>images/「この子供は、昼寝をしようとする母親を_img1.jpg,images/「この子供は、昼寝をしようとする母親を_img2.jpg</t>
         </is>
       </c>
-      <c r="C704" t="inlineStr">
+      <c r="C703" t="inlineStr">
         <is>
           <t>手書き語学 ,アラビア語 ,トラ</t>
         </is>
       </c>
     </row>
-    <row r="705">
-      <c r="A705" t="inlineStr">
+    <row r="704">
+      <c r="A704" t="inlineStr">
         <is>
           <t xml:space="preserve">「もし敬意が落ちたら、それと一緒に全部落ちるのだ」
 إن سقط الإحترام سقط معه كل شيء
@@ -15281,19 +15260,19 @@
 2109 出典不明 </t>
         </is>
       </c>
-      <c r="B705" t="inlineStr">
+      <c r="B704" t="inlineStr">
         <is>
           <t>images/「もし敬意が落ちたら、それと一緒に全部_img1.jpg</t>
         </is>
       </c>
-      <c r="C705" t="inlineStr">
+      <c r="C704" t="inlineStr">
         <is>
           <t>リスペクト ,落書き</t>
         </is>
       </c>
     </row>
-    <row r="706">
-      <c r="A706" t="inlineStr">
+    <row r="705">
+      <c r="A705" t="inlineStr">
         <is>
           <t xml:space="preserve">「エジプト特許庁」
 مكتب براءات الاختراع المصرى
@@ -15303,19 +15282,19 @@
 2312 </t>
         </is>
       </c>
-      <c r="B706" t="inlineStr">
+      <c r="B705" t="inlineStr">
         <is>
           <t>images/「エジプト特許庁」_img1.jpg</t>
         </is>
       </c>
-      <c r="C706" t="inlineStr">
+      <c r="C705" t="inlineStr">
         <is>
           <t>patent</t>
         </is>
       </c>
     </row>
-    <row r="707">
-      <c r="A707" t="inlineStr">
+    <row r="706">
+      <c r="A706" t="inlineStr">
         <is>
           <t xml:space="preserve">「選挙」إنتخابات
 インティカーバート [intiKhaabaat]
@@ -15324,19 +15303,19 @@
 2311 nna-leb gov lb </t>
         </is>
       </c>
-      <c r="B707" t="inlineStr">
+      <c r="B706" t="inlineStr">
         <is>
           <t>images/「選挙」_img1.jpg</t>
         </is>
       </c>
-      <c r="C707" t="inlineStr">
+      <c r="C706" t="inlineStr">
         <is>
           <t>選挙 ,投票</t>
         </is>
       </c>
     </row>
-    <row r="708">
-      <c r="A708" t="inlineStr">
+    <row r="707">
+      <c r="A707" t="inlineStr">
         <is>
           <t xml:space="preserve">「待ちぼうけ」إنتظار
 インティザール [inti_Dhaar]
@@ -15345,19 +15324,19 @@
 1809 in4sser.tumblr </t>
         </is>
       </c>
-      <c r="B708" t="inlineStr">
+      <c r="B707" t="inlineStr">
         <is>
           <t>images/「待ちぼうけ」_img1.jpg</t>
         </is>
       </c>
-      <c r="C708" t="inlineStr">
+      <c r="C707" t="inlineStr">
         <is>
           <t>遅すぎ ,辛抱</t>
         </is>
       </c>
     </row>
-    <row r="709">
-      <c r="A709" t="inlineStr">
+    <row r="708">
+      <c r="A708" t="inlineStr">
         <is>
           <t xml:space="preserve">「試験」إختبار
 イクティバール [iKhtibaar]
@@ -15366,19 +15345,19 @@
 2109 出典不明 </t>
         </is>
       </c>
-      <c r="B709" t="inlineStr">
+      <c r="B708" t="inlineStr">
         <is>
           <t>images/「試験」_img1.jpg</t>
         </is>
       </c>
-      <c r="C709" t="inlineStr">
+      <c r="C708" t="inlineStr">
         <is>
           <t>テスト ,考査</t>
         </is>
       </c>
     </row>
-    <row r="710">
-      <c r="A710" t="inlineStr">
+    <row r="709">
+      <c r="A709" t="inlineStr">
         <is>
           <t xml:space="preserve">「チャンネル登録」اشتراك
 イシティラーク [iShtiraak]
@@ -15387,19 +15366,19 @@
 2308 </t>
         </is>
       </c>
-      <c r="B710" t="inlineStr">
+      <c r="B709" t="inlineStr">
         <is>
           <t>images/「チャンネル登録」_img1.jpg</t>
         </is>
       </c>
-      <c r="C710" t="inlineStr">
+      <c r="C709" t="inlineStr">
         <is>
           <t>Subscribe ,YouTube</t>
         </is>
       </c>
     </row>
-    <row r="711">
-      <c r="A711" t="inlineStr">
+    <row r="710">
+      <c r="A710" t="inlineStr">
         <is>
           <t xml:space="preserve">「スマイル」ابتسام
 イブティサーム [ibtisaam]
@@ -15407,37 +15386,37 @@
 1903 behance Written-Visuals </t>
         </is>
       </c>
+      <c r="B710" t="inlineStr">
+        <is>
+          <t>images/「スマイル」_img1.jpg</t>
+        </is>
+      </c>
+      <c r="C710" t="inlineStr">
+        <is>
+          <t>スマイリー ,ツ</t>
+        </is>
+      </c>
+    </row>
+    <row r="711">
+      <c r="A711" t="inlineStr">
+        <is>
+          <t xml:space="preserve">「身体の一部として…」
+2308 https://twitter.com/NatGeoMagArab/status/1528292080337813504 </t>
+        </is>
+      </c>
       <c r="B711" t="inlineStr">
         <is>
-          <t>images/「スマイル」_img1.jpg</t>
+          <t>images/「身体の一部として…」_img1.jpg</t>
         </is>
       </c>
       <c r="C711" t="inlineStr">
         <is>
-          <t>スマイリー ,ツ</t>
+          <t>手書き語学 ,カンガルー</t>
         </is>
       </c>
     </row>
     <row r="712">
       <c r="A712" t="inlineStr">
-        <is>
-          <t xml:space="preserve">「身体の一部として…」
-2308 https://twitter.com/NatGeoMagArab/status/1528292080337813504 </t>
-        </is>
-      </c>
-      <c r="B712" t="inlineStr">
-        <is>
-          <t>images/「身体の一部として…」_img1.jpg</t>
-        </is>
-      </c>
-      <c r="C712" t="inlineStr">
-        <is>
-          <t>手書き語学 ,カンガルー</t>
-        </is>
-      </c>
-    </row>
-    <row r="713">
-      <c r="A713" t="inlineStr">
         <is>
           <t xml:space="preserve">「ディスカバリー」إكتشاف
 イクティシャーフ [iktiShaaf]
@@ -15445,19 +15424,19 @@
 2308 tephanegabrielli com </t>
         </is>
       </c>
-      <c r="B713" t="inlineStr">
+      <c r="B712" t="inlineStr">
         <is>
           <t>images/「ディスカバリー」_img1.jpg</t>
         </is>
       </c>
-      <c r="C713" t="inlineStr">
+      <c r="C712" t="inlineStr">
         <is>
           <t>discovery ,デザイン</t>
         </is>
       </c>
     </row>
-    <row r="714">
-      <c r="A714" t="inlineStr">
+    <row r="713">
+      <c r="A713" t="inlineStr">
         <is>
           <t xml:space="preserve">「重力波の発見は新しい窓を開いた」
 فتَح اكتشاف موجات الجاذبية نافذة جديدة
@@ -15465,19 +15444,19 @@
 2308 https://twitter.com/SciTalk2U/status/1454891943440289793 </t>
         </is>
       </c>
-      <c r="B714" t="inlineStr">
+      <c r="B713" t="inlineStr">
         <is>
           <t>images/「重力波の発見は新しい窓を開いた」_img1.jpg</t>
         </is>
       </c>
-      <c r="C714" t="inlineStr">
+      <c r="C713" t="inlineStr">
         <is>
           <t>手書き語学 ,アラビア語 ,重力波</t>
         </is>
       </c>
     </row>
-    <row r="715">
-      <c r="A715" t="inlineStr">
+    <row r="714">
+      <c r="A714" t="inlineStr">
         <is>
           <t xml:space="preserve">「微笑みに微笑み。先にした人の方が美しい」
 الإبتسامة بالإبتسامة والبادئ أجمل
@@ -15486,19 +15465,19 @@
 2104 出典不明 </t>
         </is>
       </c>
-      <c r="B715" t="inlineStr">
+      <c r="B714" t="inlineStr">
         <is>
           <t>images/「微笑みに微笑み。先にした人の方が美し_img1.jpg,images/「微笑みに微笑み。先にした人の方が美し_img2.jpg</t>
         </is>
       </c>
-      <c r="C715" t="inlineStr">
+      <c r="C714" t="inlineStr">
         <is>
           <t>スマイル ,名言</t>
         </is>
       </c>
     </row>
-    <row r="716">
-      <c r="A716" t="inlineStr">
+    <row r="715">
+      <c r="A715" t="inlineStr">
         <is>
           <t xml:space="preserve">「笑顔」ابتسامة
 イブティサーマ [ibtisaama(tun)]
@@ -15507,19 +15486,19 @@
 2308 satokomatsu, minne </t>
         </is>
       </c>
-      <c r="B716" t="inlineStr">
+      <c r="B715" t="inlineStr">
         <is>
           <t>images/「笑顔」_img1.jpg</t>
         </is>
       </c>
-      <c r="C716" t="inlineStr">
+      <c r="C715" t="inlineStr">
         <is>
           <t>スマイル ,ツ</t>
         </is>
       </c>
     </row>
-    <row r="717">
-      <c r="A717" t="inlineStr">
+    <row r="716">
+      <c r="A716" t="inlineStr">
         <is>
           <t xml:space="preserve">「信仰」ايمان
 イーマーン ['iimaan]
@@ -15528,19 +15507,19 @@
 2506 instagram com/p/6ST-WHOOkJ/ </t>
         </is>
       </c>
-      <c r="B717" t="inlineStr">
+      <c r="B716" t="inlineStr">
         <is>
           <t>images/「信仰」_img1.jpg</t>
         </is>
       </c>
-      <c r="C717" t="inlineStr">
+      <c r="C716" t="inlineStr">
         <is>
           <t>宗教 ,信念</t>
         </is>
       </c>
     </row>
-    <row r="718">
-      <c r="A718" t="inlineStr">
+    <row r="717">
+      <c r="A717" t="inlineStr">
         <is>
           <t xml:space="preserve">「放送」إذاعة
 イザーア ['iDhaa*a]
@@ -15549,19 +15528,19 @@
 2404 heemades, Instagram </t>
         </is>
       </c>
-      <c r="B718" t="inlineStr">
+      <c r="B717" t="inlineStr">
         <is>
           <t>images/「放送」_img1.jpg</t>
         </is>
       </c>
-      <c r="C718" t="inlineStr">
+      <c r="C717" t="inlineStr">
         <is>
           <t>デザイン ,ラジオ</t>
         </is>
       </c>
     </row>
-    <row r="719">
-      <c r="A719" t="inlineStr">
+    <row r="718">
+      <c r="A718" t="inlineStr">
         <is>
           <t xml:space="preserve">「かきとりのちから」
 مهاراتي الإملائية
@@ -15570,19 +15549,19 @@
 2308 iqrawaoktoub.wordpress com </t>
         </is>
       </c>
-      <c r="B719" t="inlineStr">
+      <c r="B718" t="inlineStr">
         <is>
           <t>images/「かきとりのちから」_img1.jpg</t>
         </is>
       </c>
-      <c r="C719" t="inlineStr">
+      <c r="C718" t="inlineStr">
         <is>
           <t>国語 ,教材</t>
         </is>
       </c>
     </row>
-    <row r="720">
-      <c r="A720" t="inlineStr">
+    <row r="719">
+      <c r="A719" t="inlineStr">
         <is>
           <t xml:space="preserve">「歴史を作った男たち」
 رجال صنعوا التاريخ
@@ -15592,38 +15571,38 @@
 2410 https://x.gd/Wl5rJ </t>
         </is>
       </c>
-      <c r="B720" t="inlineStr">
+      <c r="B719" t="inlineStr">
         <is>
           <t>images/「歴史を作った男たち」_img1.jpg</t>
         </is>
       </c>
-      <c r="C720" t="inlineStr">
+      <c r="C719" t="inlineStr">
         <is>
           <t>偉人</t>
         </is>
       </c>
     </row>
-    <row r="721">
-      <c r="A721" t="inlineStr">
+    <row r="720">
+      <c r="A720" t="inlineStr">
         <is>
           <t xml:space="preserve">「無限の宇宙を旅した光」
 「何百年もの末にジェイムズ・ウェッブ望遠鏡のレンズの上に落ち、我々に遠い宇宙の美しさを見せてくれる。最も純粋な形と最も素晴らしい姿で」
 2308 https://twitter.com/NatGeoMagArab/status/1557811592636485632 </t>
         </is>
       </c>
-      <c r="B721" t="inlineStr">
+      <c r="B720" t="inlineStr">
         <is>
           <t>images/「無限の宇宙を旅した光」_img1.jpg</t>
         </is>
       </c>
-      <c r="C721" t="inlineStr">
+      <c r="C720" t="inlineStr">
         <is>
           <t>手書き語学 ,宇宙</t>
         </is>
       </c>
     </row>
-    <row r="722">
-      <c r="A722" t="inlineStr">
+    <row r="721">
+      <c r="A721" t="inlineStr">
         <is>
           <t xml:space="preserve">「日本好きになり行きたくなる20項」
 عشرون شيئا يجعلك تحب اليابان وترغب في زيارتها
@@ -15632,19 +15611,19 @@
 2308 wattpad </t>
         </is>
       </c>
-      <c r="B722" t="inlineStr">
+      <c r="B721" t="inlineStr">
         <is>
           <t>images/「日本好きになり行きたくなる20項」_img1.jpg</t>
         </is>
       </c>
-      <c r="C722" t="inlineStr">
+      <c r="C721" t="inlineStr">
         <is>
           <t>اليابان ,Japan</t>
         </is>
       </c>
     </row>
-    <row r="723">
-      <c r="A723" t="inlineStr">
+    <row r="722">
+      <c r="A722" t="inlineStr">
         <is>
           <t xml:space="preserve">「ピッタリの瞬間に撮影され、ドラゴンが火を噴いているように見える」
 التُقطت في اللحظة المناسبة لتبدو مثل تنين ينفث اللهب
@@ -15652,19 +15631,19 @@
 2509 https://twitter.com/NatGeoMagArab/status/1588780660269150208 </t>
         </is>
       </c>
-      <c r="B723" t="inlineStr">
+      <c r="B722" t="inlineStr">
         <is>
           <t>images/「ピッタリの瞬間に撮影され、ドラゴンが_img1.jpg,images/ 「ピッタリの瞬間に撮影され、ドラゴンが_img2.jpg</t>
         </is>
       </c>
-      <c r="C723" t="inlineStr">
+      <c r="C722" t="inlineStr">
         <is>
           <t xml:space="preserve">ドラゴン </t>
         </is>
       </c>
     </row>
-    <row r="724">
-      <c r="A724" t="inlineStr">
+    <row r="723">
+      <c r="A723" t="inlineStr">
         <is>
           <t xml:space="preserve">「満足は不滅の宝である」
 القَناعَةُ كنز لا يَفنَى
@@ -15674,55 +15653,55 @@
 2308 kareem mrghani </t>
         </is>
       </c>
+      <c r="B723" t="inlineStr">
+        <is>
+          <t>images/「満足は不滅の宝である」_img1.jpg</t>
+        </is>
+      </c>
+      <c r="C723" t="inlineStr">
+        <is>
+          <t>幸福度</t>
+        </is>
+      </c>
+    </row>
+    <row r="724">
+      <c r="A724" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ゴシキセイガイインコ。
+2409 https://twitter.com/NatGeoMagArab/status/1600022262014676992 </t>
+        </is>
+      </c>
       <c r="B724" t="inlineStr">
         <is>
-          <t>images/「満足は不滅の宝である」_img1.jpg</t>
+          <t>images/ゴシキセイガイインコ。_img1.jpg</t>
         </is>
       </c>
       <c r="C724" t="inlineStr">
         <is>
-          <t>幸福度</t>
+          <t>手書き語学 ,アラビア語,オウム</t>
         </is>
       </c>
     </row>
     <row r="725">
       <c r="A725" t="inlineStr">
         <is>
-          <t xml:space="preserve">ゴシキセイガイインコ。
-2409 https://twitter.com/NatGeoMagArab/status/1600022262014676992 </t>
+          <t xml:space="preserve">モモンガ。
+2403 https://twitter.com/NatGeoMagArab/status/1552541872966344704 </t>
         </is>
       </c>
       <c r="B725" t="inlineStr">
         <is>
-          <t>images/ゴシキセイガイインコ。_img1.jpg</t>
+          <t>images/モモンガ。_img1.jpg,images/ モモンガ。_img2.jpg</t>
         </is>
       </c>
       <c r="C725" t="inlineStr">
         <is>
-          <t>手書き語学 ,アラビア語,オウム</t>
+          <t>手書き語学 ,アラビア語 ,モモンガ</t>
         </is>
       </c>
     </row>
     <row r="726">
       <c r="A726" t="inlineStr">
-        <is>
-          <t xml:space="preserve">モモンガ。
-2403 https://twitter.com/NatGeoMagArab/status/1552541872966344704 </t>
-        </is>
-      </c>
-      <c r="B726" t="inlineStr">
-        <is>
-          <t>images/モモンガ。_img1.jpg,images/ モモンガ。_img2.jpg</t>
-        </is>
-      </c>
-      <c r="C726" t="inlineStr">
-        <is>
-          <t>手書き語学 ,アラビア語 ,モモンガ</t>
-        </is>
-      </c>
-    </row>
-    <row r="727">
-      <c r="A727" t="inlineStr">
         <is>
           <t xml:space="preserve">「象の群れ。ドローンの音から逃げている」
 قطيع من الفيلة يفر هاربًا من صوت الدرون
@@ -15734,56 +15713,56 @@
 2009 https://twitter.com/NatGeoMagArab/status/1302970033627258881 </t>
         </is>
       </c>
+      <c r="B726" t="inlineStr">
+        <is>
+          <t>images/「象の群れ。ドローンの音から逃げている.jpg</t>
+        </is>
+      </c>
+      <c r="C726" t="inlineStr">
+        <is>
+          <t>ゾウ ,ドローン</t>
+        </is>
+      </c>
+    </row>
+    <row r="727">
+      <c r="A727" t="inlineStr">
+        <is>
+          <t xml:space="preserve">カルマン線。
+2308 https://twitter.com/NatGeoMagArab/status/1536436999522881536 </t>
+        </is>
+      </c>
       <c r="B727" t="inlineStr">
         <is>
-          <t>images/「象の群れ。ドローンの音から逃げている.jpg</t>
+          <t>images/カルマン線。_img1.jpg</t>
         </is>
       </c>
       <c r="C727" t="inlineStr">
         <is>
-          <t>ゾウ ,ドローン</t>
+          <t xml:space="preserve">手書き語学 ,アラビア語 ,宇宙 </t>
         </is>
       </c>
     </row>
     <row r="728">
       <c r="A728" t="inlineStr">
-        <is>
-          <t xml:space="preserve">カルマン線。
-2308 https://twitter.com/NatGeoMagArab/status/1536436999522881536 </t>
-        </is>
-      </c>
-      <c r="B728" t="inlineStr">
-        <is>
-          <t>images/カルマン線。_img1.jpg</t>
-        </is>
-      </c>
-      <c r="C728" t="inlineStr">
-        <is>
-          <t xml:space="preserve">手書き語学 ,アラビア語 ,宇宙 </t>
-        </is>
-      </c>
-    </row>
-    <row r="729">
-      <c r="A729" t="inlineStr">
         <is>
           <t xml:space="preserve">「恥ずかしがり屋のマヌルネコと暖かい朝の太陽光線」
 ⁦「二つの美しいもの」[Shay'-ayni jamiil-ayni] 属格：「物」( شيء )[Shay']・「美しい」( جميل )[jamiil]⁩
 2309 https://twitter.com/NatGeoMagArab/status/1697512148820504912 </t>
         </is>
       </c>
-      <c r="B729" t="inlineStr">
+      <c r="B728" t="inlineStr">
         <is>
           <t>images/「恥ずかしがり屋のマヌルネコと暖かい朝_img1.jpg</t>
         </is>
       </c>
-      <c r="C729" t="inlineStr">
+      <c r="C728" t="inlineStr">
         <is>
           <t>手書き語学 ,アラビア語 ,マヌルネコ</t>
         </is>
       </c>
     </row>
-    <row r="730">
-      <c r="A730" t="inlineStr">
+    <row r="729">
+      <c r="A729" t="inlineStr">
         <is>
           <t xml:space="preserve">「二回失敗しているペンギン」
 بطريق يفشل مرتين
@@ -15793,19 +15772,19 @@
 2308 https://twitter.com/NatGeoMagArab/status/1479483133766426626 </t>
         </is>
       </c>
-      <c r="B730" t="inlineStr">
+      <c r="B729" t="inlineStr">
         <is>
           <t>images/「二回失敗しているペンギン」_img1.jpg</t>
         </is>
       </c>
-      <c r="C730" t="inlineStr">
+      <c r="C729" t="inlineStr">
         <is>
           <t>ペンギン ,動物</t>
         </is>
       </c>
     </row>
-    <row r="731">
-      <c r="A731" t="inlineStr">
+    <row r="730">
+      <c r="A730" t="inlineStr">
         <is>
           <t xml:space="preserve">「2億光年の彼方できらめく炎と光」
 وهج ووميض يتلألأ على بعد 200 مليون سنة ضوئية
@@ -15816,15 +15795,15 @@
 2010 https://twitter.com/NatGeoMagArab/status/1303415502673342464 </t>
         </is>
       </c>
-      <c r="B731" t="inlineStr"/>
-      <c r="C731" t="inlineStr">
+      <c r="B730" t="inlineStr"/>
+      <c r="C730" t="inlineStr">
         <is>
           <t>宇宙 ,銀河</t>
         </is>
       </c>
     </row>
-    <row r="732">
-      <c r="A732" t="inlineStr">
+    <row r="731">
+      <c r="A731" t="inlineStr">
         <is>
           <t xml:space="preserve">「さまよう黒猫」قطة سوداء تجوب
 キッタトゥン・サウダーウ・タジューブ [qi^_tatun sawdaa'u ta-juub]
@@ -15833,19 +15812,19 @@
 2308 https://twitter.com/NatGeoMagArab/status/1532973177453760512 </t>
         </is>
       </c>
-      <c r="B732" t="inlineStr">
+      <c r="B731" t="inlineStr">
         <is>
           <t>images/「さまよう黒猫」_img1.jpg,images/ 「さまよう黒猫」_img2.jpg</t>
         </is>
       </c>
-      <c r="C732" t="inlineStr">
+      <c r="C731" t="inlineStr">
         <is>
           <t xml:space="preserve">手書き語学 ,モロッコ </t>
         </is>
       </c>
     </row>
-    <row r="733">
-      <c r="A733" t="inlineStr">
+    <row r="732">
+      <c r="A732" t="inlineStr">
         <is>
           <t xml:space="preserve">「サイのざらざらした皮を利用して自分の体を掻くネコ」
 قطة تستغل جلد الكركدن الخشن لحك جسدها
@@ -15854,19 +15833,19 @@
 2308 https://twitter.com/NatGeoMagArab/status/1476855740929216517 </t>
         </is>
       </c>
-      <c r="B733" t="inlineStr">
+      <c r="B732" t="inlineStr">
         <is>
           <t>images/「サイのざらざらした皮を利用して自分の_img1.jpg</t>
         </is>
       </c>
-      <c r="C733" t="inlineStr">
+      <c r="C732" t="inlineStr">
         <is>
           <t>サイ ,チェコ</t>
         </is>
       </c>
     </row>
-    <row r="734">
-      <c r="A734" t="inlineStr">
+    <row r="733">
+      <c r="A733" t="inlineStr">
         <is>
           <t xml:space="preserve">「沈まぬ太陽」شمس لا تغيب
 シャムス・ラー・タギーブ [Shams laa ta-Ghiib]
@@ -15875,19 +15854,19 @@
 2308 AHMED ELASSAL </t>
         </is>
       </c>
-      <c r="B734" t="inlineStr">
+      <c r="B733" t="inlineStr">
         <is>
           <t>images/「沈まぬ太陽」_img1.jpg</t>
         </is>
       </c>
-      <c r="C734" t="inlineStr">
+      <c r="C733" t="inlineStr">
         <is>
           <t>帝国 ,白夜</t>
         </is>
       </c>
     </row>
-    <row r="735">
-      <c r="A735" t="inlineStr">
+    <row r="734">
+      <c r="A734" t="inlineStr">
         <is>
           <t xml:space="preserve">「子供に食べさせている忍耐強い母親」
 أم صبورة تطعم صغيرها
@@ -15896,19 +15875,19 @@
 2308 https://twitter.com/natgeomagarab/status/1585572054509957120 </t>
         </is>
       </c>
-      <c r="B735" t="inlineStr">
+      <c r="B734" t="inlineStr">
         <is>
           <t>images/「子供に食べさせている忍耐強い母親」_img1.jpg</t>
         </is>
       </c>
-      <c r="C735" t="inlineStr">
+      <c r="C734" t="inlineStr">
         <is>
           <t>手書き語学 ,アラビア語 ,ミヤコドリ</t>
         </is>
       </c>
     </row>
-    <row r="736">
-      <c r="A736" t="inlineStr">
+    <row r="735">
+      <c r="A735" t="inlineStr">
         <is>
           <t xml:space="preserve">「コーヒーは繰り返さない恋物語」
 القهوة قصة عشق لن تتكرر
@@ -15918,19 +15897,19 @@
 2403 pin it/7tvd8Wc </t>
         </is>
       </c>
-      <c r="B736" t="inlineStr">
+      <c r="B735" t="inlineStr">
         <is>
           <t>images/「コーヒーは繰り返さない恋物語」_img1.jpg</t>
         </is>
       </c>
-      <c r="C736" t="inlineStr">
+      <c r="C735" t="inlineStr">
         <is>
           <t>コーヒー ,名言</t>
         </is>
       </c>
     </row>
-    <row r="737">
-      <c r="A737" t="inlineStr">
+    <row r="736">
+      <c r="A736" t="inlineStr">
         <is>
           <t xml:space="preserve">「星々で飾られた空。魅惑的な色合いで黄昏の美を満たしている」
 سماء مرصعة بالنجوم تضفي لمسة سحرية على جمال الشفق
@@ -15938,19 +15917,19 @@
 2010 https://twitter.com/NatGeoMagArab/status/1303777701975584768 </t>
         </is>
       </c>
-      <c r="B737" t="inlineStr">
+      <c r="B736" t="inlineStr">
         <is>
           <t>images/「星々で飾られた空。魅惑的な色合いで黄.png</t>
         </is>
       </c>
-      <c r="C737" t="inlineStr">
+      <c r="C736" t="inlineStr">
         <is>
           <t>星空 ,宇宙</t>
         </is>
       </c>
     </row>
-    <row r="738">
-      <c r="A738" t="inlineStr">
+    <row r="737">
+      <c r="A737" t="inlineStr">
         <is>
           <t xml:space="preserve">「国際宇宙ステーションからの写真。巨大な台風『ハイシェン（海神）』を映している」
 لقطات من محطة الفضاء الدولية تظهر إعصار "هايشن" الهائل
@@ -15958,19 +15937,19 @@
 2403 https://twitter.com/NatGeoMagArab/status/1302871968522235904 </t>
         </is>
       </c>
-      <c r="B738" t="inlineStr">
+      <c r="B737" t="inlineStr">
         <is>
           <t>images/「国際宇宙ステーションからの写真。巨大.png</t>
         </is>
       </c>
-      <c r="C738" t="inlineStr">
+      <c r="C737" t="inlineStr">
         <is>
           <t>台風</t>
         </is>
       </c>
     </row>
-    <row r="739">
-      <c r="A739" t="inlineStr">
+    <row r="738">
+      <c r="A738" t="inlineStr">
         <is>
           <t xml:space="preserve">「草を食む幸運な子羊たち」
 خراف محظوظة ترعى
@@ -15980,19 +15959,19 @@
 2308 https://twitter.com/NatGeoMagArab/status/1490211393554972676 </t>
         </is>
       </c>
-      <c r="B739" t="inlineStr">
+      <c r="B738" t="inlineStr">
         <is>
           <t>images/「草を食む幸運な子羊たち」_img1.jpg,images/ 「草を食む幸運な子羊たち」_img2.jpg</t>
         </is>
       </c>
-      <c r="C739" t="inlineStr">
+      <c r="C738" t="inlineStr">
         <is>
           <t>羊 ,アイルランド</t>
         </is>
       </c>
     </row>
-    <row r="740">
-      <c r="A740" t="inlineStr">
+    <row r="739">
+      <c r="A739" t="inlineStr">
         <is>
           <t xml:space="preserve">「お金で買えぬ10のもの」
 ١٠ أشياء لا تشترى بالمال
@@ -16002,19 +15981,19 @@
 2308 ayb124 </t>
         </is>
       </c>
-      <c r="B740" t="inlineStr">
+      <c r="B739" t="inlineStr">
         <is>
           <t>images/「お金で買えぬ10のもの」_img1.jpg</t>
         </is>
       </c>
-      <c r="C740" t="inlineStr">
+      <c r="C739" t="inlineStr">
         <is>
           <t>価値 ,購買</t>
         </is>
       </c>
     </row>
-    <row r="741">
-      <c r="A741" t="inlineStr">
+    <row r="740">
+      <c r="A740" t="inlineStr">
         <is>
           <t xml:space="preserve">「お金では買えないよ」
 هي أشْيَاءٌ لا تُشْتَرَى
@@ -16024,19 +16003,19 @@
 1906 mardy_zaawely, Instagram </t>
         </is>
       </c>
-      <c r="B741" t="inlineStr">
+      <c r="B740" t="inlineStr">
         <is>
           <t>images/「お金では買えないよ」_img1.jpg</t>
         </is>
       </c>
-      <c r="C741" t="inlineStr">
+      <c r="C740" t="inlineStr">
         <is>
           <t>マスターカード ,価値</t>
         </is>
       </c>
     </row>
-    <row r="742">
-      <c r="A742" t="inlineStr">
+    <row r="741">
+      <c r="A741" t="inlineStr">
         <is>
           <t xml:space="preserve">「好奇心旺盛なホッキョクギツネ」
 ثعلب قطبي يملؤه الفضول
@@ -16046,15 +16025,15 @@
 2308 https://twitter.com/natgeomagarab/status/1157592172968808449 </t>
         </is>
       </c>
-      <c r="B742" t="inlineStr"/>
-      <c r="C742" t="inlineStr">
+      <c r="B741" t="inlineStr"/>
+      <c r="C741" t="inlineStr">
         <is>
           <t>ファーストコンタクト ,キツネ</t>
         </is>
       </c>
     </row>
-    <row r="743">
-      <c r="A743" t="inlineStr">
+    <row r="742">
+      <c r="A742" t="inlineStr">
         <is>
           <t xml:space="preserve">「グレンダイザーのいる国は死にません」
 لنْ يَموتَ شَعبٌ لدَيهِ غرندايزر
@@ -16063,56 +16042,56 @@
 2308 https://www.aljarida.com/articles/1462241741574732100/ </t>
         </is>
       </c>
+      <c r="B742" t="inlineStr">
+        <is>
+          <t>images/「グレンダイザーのいる国は死にません」_img1.jpg</t>
+        </is>
+      </c>
+      <c r="C742" t="inlineStr">
+        <is>
+          <t>UFOロボ ,アニメ</t>
+        </is>
+      </c>
+    </row>
+    <row r="743">
+      <c r="A743" t="inlineStr">
+        <is>
+          <t xml:space="preserve">「凍結路面を運転中、彼女は嫌な場面に居合わせた」
+2408 https://twitter.com/NatGeoMagArab/status/1610305209657626625 </t>
+        </is>
+      </c>
       <c r="B743" t="inlineStr">
         <is>
-          <t>images/「グレンダイザーのいる国は死にません」_img1.jpg</t>
+          <t>images/「凍結路面を運転中、彼女は嫌な場面に居_img1.jpg</t>
         </is>
       </c>
       <c r="C743" t="inlineStr">
         <is>
-          <t>UFOロボ ,アニメ</t>
+          <t>手書き語学 ,アラビア語 ,路面凍結</t>
         </is>
       </c>
     </row>
     <row r="744">
       <c r="A744" t="inlineStr">
-        <is>
-          <t xml:space="preserve">「凍結路面を運転中、彼女は嫌な場面に居合わせた」
-2408 https://twitter.com/NatGeoMagArab/status/1610305209657626625 </t>
-        </is>
-      </c>
-      <c r="B744" t="inlineStr">
-        <is>
-          <t>images/「凍結路面を運転中、彼女は嫌な場面に居_img1.jpg</t>
-        </is>
-      </c>
-      <c r="C744" t="inlineStr">
-        <is>
-          <t>手書き語学 ,アラビア語 ,路面凍結</t>
-        </is>
-      </c>
-    </row>
-    <row r="745">
-      <c r="A745" t="inlineStr">
         <is>
           <t xml:space="preserve">「虹が美しさを加えている、アルパカという動物の美しいショット」
 ⁦「美しいショット」[laq_tatun jamiilatun]：「ショット」( لقطة )[laq_ta]：( ـلٌ )[-lun]・( ـقٌ )[-qun]・( ـطٌ )[-_tun]・( ـةٌ )[-tun]⁩
 2308 https://twitter.com/natgeomagarab/status/1155115655928004608 </t>
         </is>
       </c>
-      <c r="B745" t="inlineStr">
+      <c r="B744" t="inlineStr">
         <is>
           <t>images/「虹が美しさを加えている、アルパカとい_img1.jpg</t>
         </is>
       </c>
-      <c r="C745" t="inlineStr">
+      <c r="C744" t="inlineStr">
         <is>
           <t>モフモフ ,アルパカ</t>
         </is>
       </c>
     </row>
-    <row r="746">
-      <c r="A746" t="inlineStr">
+    <row r="745">
+      <c r="A745" t="inlineStr">
         <is>
           <t xml:space="preserve">「幸せは…全然思いもよらない所からやって来る」
 السعادة تأتينا من أماكن لم نكن نتوقعها أبداً
@@ -16121,19 +16100,19 @@
 2109 出典不明 </t>
         </is>
       </c>
-      <c r="B746" t="inlineStr">
+      <c r="B745" t="inlineStr">
         <is>
           <t>images/「幸せは…全然思いもよらない所からやっ_img1.jpg,images/ 「幸せは…全然思いもよらない所からやっ_img2.jpg</t>
         </is>
       </c>
-      <c r="C746" t="inlineStr">
+      <c r="C745" t="inlineStr">
         <is>
           <t>訪れ ,予想</t>
         </is>
       </c>
     </row>
-    <row r="747">
-      <c r="A747" t="inlineStr">
+    <row r="746">
+      <c r="A746" t="inlineStr">
         <is>
           <t xml:space="preserve">「あらゆる問題は、食べ物が解決してくれる」
 كل مشكلة ولها أكلة تحلها
@@ -16142,19 +16121,19 @@
 1909 ALQA AN 878 </t>
         </is>
       </c>
-      <c r="B747" t="inlineStr">
+      <c r="B746" t="inlineStr">
         <is>
           <t>images/「あらゆる問題は、食べ物が解決してくれ_img1.jpg</t>
         </is>
       </c>
-      <c r="C747" t="inlineStr">
+      <c r="C746" t="inlineStr">
         <is>
           <t>ストレス ,精神</t>
         </is>
       </c>
     </row>
-    <row r="748">
-      <c r="A748" t="inlineStr">
+    <row r="747">
+      <c r="A747" t="inlineStr">
         <is>
           <t xml:space="preserve">「冬で私が好きな物」
 أشياء أحبها بالشتاء
@@ -16164,19 +16143,19 @@
 2109 出典不明 </t>
         </is>
       </c>
-      <c r="B748" t="inlineStr">
+      <c r="B747" t="inlineStr">
         <is>
           <t>images/「冬で私が好きな物」_img1.jpg</t>
         </is>
       </c>
-      <c r="C748" t="inlineStr">
+      <c r="C747" t="inlineStr">
         <is>
           <t>季節 ,冬</t>
         </is>
       </c>
     </row>
-    <row r="749">
-      <c r="A749" t="inlineStr">
+    <row r="748">
+      <c r="A748" t="inlineStr">
         <is>
           <t xml:space="preserve">「お金で買うことの出来ない物」
 أشياء لا تستطيع شراءها بالمال
@@ -16186,19 +16165,19 @@
 2409 https://x.com/akhbarak/status/1038402708414373888 </t>
         </is>
       </c>
-      <c r="B749" t="inlineStr">
+      <c r="B748" t="inlineStr">
         <is>
           <t>images/「お金で買うことの出来ない物」_img1.jpg,images/ 「お金で買うことの出来ない物」_img2.jpg</t>
         </is>
       </c>
-      <c r="C749" t="inlineStr">
+      <c r="C748" t="inlineStr">
         <is>
           <t>ショッピング ,価値</t>
         </is>
       </c>
     </row>
-    <row r="750">
-      <c r="A750" t="inlineStr">
+    <row r="749">
+      <c r="A749" t="inlineStr">
         <is>
           <t xml:space="preserve">「私たちが愛する言葉」
 كلماتٌ نُحبّها
@@ -16208,19 +16187,19 @@
 2109 جليل خزعل </t>
         </is>
       </c>
-      <c r="B750" t="inlineStr">
+      <c r="B749" t="inlineStr">
         <is>
           <t>images/「私たちが愛する言葉」_img1.jpg</t>
         </is>
       </c>
-      <c r="C750" t="inlineStr">
+      <c r="C749" t="inlineStr">
         <is>
           <t>花 ,贈り物</t>
         </is>
       </c>
     </row>
-    <row r="751">
-      <c r="A751" t="inlineStr">
+    <row r="750">
+      <c r="A750" t="inlineStr">
         <is>
           <t xml:space="preserve">「お茶についてあなたが知らない10の事実」
 عشر معلومات لا تعرفها عن الشاي
@@ -16229,19 +16208,19 @@
 2012 http://ara.tv/6syq2 </t>
         </is>
       </c>
-      <c r="B751" t="inlineStr">
+      <c r="B750" t="inlineStr">
         <is>
           <t>images/「お茶についてあなたが知らない10の事_img1.jpg</t>
         </is>
       </c>
-      <c r="C751" t="inlineStr">
+      <c r="C750" t="inlineStr">
         <is>
           <t>神農</t>
         </is>
       </c>
     </row>
-    <row r="752">
-      <c r="A752" t="inlineStr">
+    <row r="751">
+      <c r="A751" t="inlineStr">
         <is>
           <t xml:space="preserve">「大きくなったウソ」
 الكذبة الّتي كبرت
@@ -16251,19 +16230,19 @@
 2509 سلسلة الحلزونة </t>
         </is>
       </c>
-      <c r="B752" t="inlineStr">
+      <c r="B751" t="inlineStr">
         <is>
           <t>images/「大きくなったウソ」_img1.jpg</t>
         </is>
       </c>
-      <c r="C752" t="inlineStr">
+      <c r="C751" t="inlineStr">
         <is>
           <t>絵本</t>
         </is>
       </c>
     </row>
-    <row r="753">
-      <c r="A753" t="inlineStr">
+    <row r="752">
+      <c r="A752" t="inlineStr">
         <is>
           <t xml:space="preserve">「自分に合った掃除機を買うには？」
 كيف تشتري المكنسة الكهربائية التي تناسبك؟
@@ -16272,19 +16251,19 @@
 2106 ts3a com </t>
         </is>
       </c>
-      <c r="B753" t="inlineStr">
+      <c r="B752" t="inlineStr">
         <is>
           <t>images/「自分に合った掃除機を買うには？」_img1.jpg</t>
         </is>
       </c>
-      <c r="C753" t="inlineStr">
+      <c r="C752" t="inlineStr">
         <is>
           <t>家電 ,掃除</t>
         </is>
       </c>
     </row>
-    <row r="754">
-      <c r="A754" t="inlineStr">
+    <row r="753">
+      <c r="A753" t="inlineStr">
         <is>
           <t xml:space="preserve">「仮にこれが批判の数としよう」
 لنفرض ان عدد الذين ينتقدونك
@@ -16295,19 +16274,19 @@
 2504 出典不明 </t>
         </is>
       </c>
-      <c r="B754" t="inlineStr">
+      <c r="B753" t="inlineStr">
         <is>
           <t>images/「仮にこれが批判の数としよう」_img1.jpg</t>
         </is>
       </c>
-      <c r="C754" t="inlineStr">
+      <c r="C753" t="inlineStr">
         <is>
           <t>アンチ</t>
         </is>
       </c>
     </row>
-    <row r="755">
-      <c r="A755" t="inlineStr">
+    <row r="754">
+      <c r="A754" t="inlineStr">
         <is>
           <t xml:space="preserve">「ここに見えるのは何？」
 ما الذي تراه هنا؟
@@ -16317,15 +16296,15 @@
 2204 https://twitter.com/NatGeoMagArab/status/1506933850617700352 </t>
         </is>
       </c>
-      <c r="B755" t="inlineStr"/>
-      <c r="C755" t="inlineStr">
+      <c r="B754" t="inlineStr"/>
+      <c r="C754" t="inlineStr">
         <is>
           <t xml:space="preserve">ペンギン </t>
         </is>
       </c>
     </row>
-    <row r="756">
-      <c r="A756" t="inlineStr">
+    <row r="755">
+      <c r="A755" t="inlineStr">
         <is>
           <t xml:space="preserve">「今日辛いこと、明日は平気だろう」
 ما يؤلم اليوم سيهون غدًا
@@ -16335,19 +16314,19 @@
 2308 basmahjeff </t>
         </is>
       </c>
-      <c r="B756" t="inlineStr">
+      <c r="B755" t="inlineStr">
         <is>
           <t>images/「今日辛いこと、明日は平気だろう」_img1.jpg</t>
         </is>
       </c>
-      <c r="C756" t="inlineStr">
+      <c r="C755" t="inlineStr">
         <is>
           <t>悩み ,達観</t>
         </is>
       </c>
     </row>
-    <row r="757">
-      <c r="A757" t="inlineStr">
+    <row r="756">
+      <c r="A756" t="inlineStr">
         <is>
           <t xml:space="preserve">「自分のすることを好きでなきゃ」
 عليك أن تحب ما تفعل
@@ -16356,19 +16335,19 @@
 1810 Ahmed Elhakeem </t>
         </is>
       </c>
-      <c r="B757" t="inlineStr">
+      <c r="B756" t="inlineStr">
         <is>
           <t>images/「自分のすることを好きでなきゃ」_img1.jpg</t>
         </is>
       </c>
-      <c r="C757" t="inlineStr">
+      <c r="C756" t="inlineStr">
         <is>
           <t>転職 ,かわいい</t>
         </is>
       </c>
     </row>
-    <row r="758">
-      <c r="A758" t="inlineStr">
+    <row r="757">
+      <c r="A757" t="inlineStr">
         <is>
           <t xml:space="preserve">「この地上に生き甲斐あり」
 على هذه الأرض ما يستحق الحياة
@@ -16378,19 +16357,19 @@
 2308 Mahmoud Gafar </t>
         </is>
       </c>
-      <c r="B758" t="inlineStr">
+      <c r="B757" t="inlineStr">
         <is>
           <t>images/「この地上に生き甲斐あり」_img1.jpg</t>
         </is>
       </c>
-      <c r="C758" t="inlineStr">
+      <c r="C757" t="inlineStr">
         <is>
           <t>詩</t>
         </is>
       </c>
     </row>
-    <row r="759">
-      <c r="A759" t="inlineStr">
+    <row r="758">
+      <c r="A758" t="inlineStr">
         <is>
           <t xml:space="preserve">「おそらく、あなたの求めるものはあるだろう」
 لعلَّ ما تَرجوهُ سيَكونُ
@@ -16400,19 +16379,19 @@
 2308 PIXEL Instagram </t>
         </is>
       </c>
-      <c r="B759" t="inlineStr">
+      <c r="B758" t="inlineStr">
         <is>
           <t>images/「おそらく、あなたの求めるものはあるだ_img1.jpg</t>
         </is>
       </c>
-      <c r="C759" t="inlineStr">
+      <c r="C758" t="inlineStr">
         <is>
           <t>願い ,信仰</t>
         </is>
       </c>
     </row>
-    <row r="760">
-      <c r="A760" t="inlineStr">
+    <row r="759">
+      <c r="A759" t="inlineStr">
         <is>
           <t xml:space="preserve">「オレンジの効能が何か知っていますか？」
 هل تعرف ما هي فوائد البرتقال؟
@@ -16422,19 +16401,19 @@
 2308 sadahadhramowt com </t>
         </is>
       </c>
-      <c r="B760" t="inlineStr">
+      <c r="B759" t="inlineStr">
         <is>
           <t>images/「オレンジの効能が何か知っていますか？_img1.jpg</t>
         </is>
       </c>
-      <c r="C760" t="inlineStr">
+      <c r="C759" t="inlineStr">
         <is>
           <t>オレンジ ,フルーツ</t>
         </is>
       </c>
     </row>
-    <row r="761">
-      <c r="A761" t="inlineStr">
+    <row r="760">
+      <c r="A760" t="inlineStr">
         <is>
           <t xml:space="preserve">「遊ぶパンダの光景より可愛いものがありますか？」
 هل هناك ما هو ألطف من مشاهدة الباندا وهي تلعب؟
@@ -16442,19 +16421,19 @@
 2308 https://twitter.com/NatGeoMagArab/status/1494612797858074626 </t>
         </is>
       </c>
-      <c r="B761" t="inlineStr">
+      <c r="B760" t="inlineStr">
         <is>
           <t>images/「遊ぶパンダの光景より可愛いものがあり_img1.jpg</t>
         </is>
       </c>
-      <c r="C761" t="inlineStr">
+      <c r="C760" t="inlineStr">
         <is>
           <t>パンダ ,モコモコ</t>
         </is>
       </c>
     </row>
-    <row r="762">
-      <c r="A762" t="inlineStr">
+    <row r="761">
+      <c r="A761" t="inlineStr">
         <is>
           <t xml:space="preserve">「大事なのは何者だったかじゃない。何者になるかだ」
 ليسَ المُهم ما كُنتَ بل مَا ستكون
@@ -16463,19 +16442,19 @@
 2308 出典不明 </t>
         </is>
       </c>
-      <c r="B762" t="inlineStr">
+      <c r="B761" t="inlineStr">
         <is>
           <t>images/「大事なのは何者だったかじゃない。何者_img1.jpg</t>
         </is>
       </c>
-      <c r="C762" t="inlineStr">
+      <c r="C761" t="inlineStr">
         <is>
           <t>自己実現 ,存在価値</t>
         </is>
       </c>
     </row>
-    <row r="763">
-      <c r="A763" t="inlineStr">
+    <row r="762">
+      <c r="A762" t="inlineStr">
         <is>
           <t xml:space="preserve">「あなたであれ。ありのままが美しいから」
 كُنْ أَنْتَ لأنك جميل كما أنت
@@ -16484,19 +16463,19 @@
 2308 IDREES DESIGN </t>
         </is>
       </c>
-      <c r="B763" t="inlineStr">
+      <c r="B762" t="inlineStr">
         <is>
           <t>images/「あなたであれ。ありのままが美しいから_img1.jpg</t>
         </is>
       </c>
-      <c r="C763" t="inlineStr">
+      <c r="C762" t="inlineStr">
         <is>
           <t>自己肯定 ,BeYourself</t>
         </is>
       </c>
     </row>
-    <row r="764">
-      <c r="A764" t="inlineStr">
+    <row r="763">
+      <c r="A763" t="inlineStr">
         <is>
           <t xml:space="preserve">「恐れの中に生きる者は決して自由になれない」
 من يعش في خوف لن يكون حرا أبدا
@@ -16505,19 +16484,19 @@
 2111 rjeem com </t>
         </is>
       </c>
-      <c r="B764" t="inlineStr">
+      <c r="B763" t="inlineStr">
         <is>
           <t>images/「恐れの中に生きる者は決して自由になれ_img1.jpg,images/ 「恐れの中に生きる者は決して自由になれ_img2.jpg</t>
         </is>
       </c>
-      <c r="C764" t="inlineStr">
+      <c r="C763" t="inlineStr">
         <is>
           <t>勇気 ,壁</t>
         </is>
       </c>
     </row>
-    <row r="765">
-      <c r="A765" t="inlineStr">
+    <row r="764">
+      <c r="A764" t="inlineStr">
         <is>
           <t xml:space="preserve">「己の翼を信じる者は己の重さを案じない」
 من يثق في جناحيه لن يهتم لوزنه
@@ -16526,19 +16505,19 @@
 2308 kmrghani </t>
         </is>
       </c>
-      <c r="B765" t="inlineStr">
+      <c r="B764" t="inlineStr">
         <is>
           <t>images/「己の翼を信じる者は己の重さを案じない_img1.jpg</t>
         </is>
       </c>
-      <c r="C765" t="inlineStr">
+      <c r="C764" t="inlineStr">
         <is>
           <t>自信</t>
         </is>
       </c>
     </row>
-    <row r="766">
-      <c r="A766" t="inlineStr">
+    <row r="765">
+      <c r="A765" t="inlineStr">
         <is>
           <t xml:space="preserve">「珈琲で一番大事な事！誰と飲むか？」
 الأهم من القهوة!! من ستشربها معه؟
@@ -16547,19 +16526,19 @@
 1812 gwid3.tumblr </t>
         </is>
       </c>
-      <c r="B766" t="inlineStr">
+      <c r="B765" t="inlineStr">
         <is>
           <t>images/「珈琲で一番大事な事！誰と飲むか？」_img1.jpg</t>
         </is>
       </c>
-      <c r="C766" t="inlineStr">
+      <c r="C765" t="inlineStr">
         <is>
           <t>コーヒー ,名言</t>
         </is>
       </c>
     </row>
-    <row r="767">
-      <c r="A767" t="inlineStr">
+    <row r="766">
+      <c r="A766" t="inlineStr">
         <is>
           <t xml:space="preserve">「人生は美しい、そう望んだ者には。」
 الحياة جَميلَة .. لمن أراد ذلك
@@ -16569,19 +16548,19 @@
 2109 出典不明 </t>
         </is>
       </c>
-      <c r="B767" t="inlineStr">
+      <c r="B766" t="inlineStr">
         <is>
           <t>images/「人生は美しい、そう望んだ者には。」_img1.jpg</t>
         </is>
       </c>
-      <c r="C767" t="inlineStr">
+      <c r="C766" t="inlineStr">
         <is>
           <t>名言 ,アート</t>
         </is>
       </c>
     </row>
-    <row r="768">
-      <c r="A768" t="inlineStr">
+    <row r="767">
+      <c r="A767" t="inlineStr">
         <is>
           <t xml:space="preserve">「ハム太郎って子を知ってるかい」
 هل تعرفون من هو هامتارو
@@ -16591,19 +16570,19 @@
 2109 </t>
         </is>
       </c>
-      <c r="B768" t="inlineStr">
+      <c r="B767" t="inlineStr">
         <is>
           <t>images/「ハム太郎って子を知ってるかい」_img1.jpg</t>
         </is>
       </c>
-      <c r="C768" t="inlineStr">
+      <c r="C767" t="inlineStr">
         <is>
           <t>オープニング ,ハム太郎</t>
         </is>
       </c>
     </row>
-    <row r="769">
-      <c r="A769" t="inlineStr">
+    <row r="768">
+      <c r="A768" t="inlineStr">
         <is>
           <t xml:space="preserve">「幸せを求める人もいれば、作る人もいる」
 هناك من يبحث عن السعادة وهناك من يصنعها
@@ -16612,19 +16591,19 @@
 2308 hindah tumblr </t>
         </is>
       </c>
-      <c r="B769" t="inlineStr">
+      <c r="B768" t="inlineStr">
         <is>
           <t>images/「幸せを求める人もいれば、作る人もいる_img1.jpg</t>
         </is>
       </c>
-      <c r="C769" t="inlineStr">
+      <c r="C768" t="inlineStr">
         <is>
           <t>幸せ ,名言 ,教訓</t>
         </is>
       </c>
     </row>
-    <row r="770">
-      <c r="A770" t="inlineStr">
+    <row r="769">
+      <c r="A769" t="inlineStr">
         <is>
           <t xml:space="preserve">「明白なるアラブの言葉によって」
 بلسان عربي مبين
@@ -16634,19 +16613,19 @@
 2109 Abdullah Barakat behance </t>
         </is>
       </c>
-      <c r="B770" t="inlineStr">
+      <c r="B769" t="inlineStr">
         <is>
           <t>images/「明白なるアラブの言葉によって」_img1.jpg</t>
         </is>
       </c>
-      <c r="C770" t="inlineStr">
+      <c r="C769" t="inlineStr">
         <is>
           <t>イスラム教 ,神聖</t>
         </is>
       </c>
     </row>
-    <row r="771">
-      <c r="A771" t="inlineStr">
+    <row r="770">
+      <c r="A770" t="inlineStr">
         <is>
           <t xml:space="preserve">「結婚前、結婚後」
 قبل الزواج، بعد الزواج
@@ -16656,19 +16635,19 @@
 2308 出典不明 </t>
         </is>
       </c>
-      <c r="B771" t="inlineStr">
+      <c r="B770" t="inlineStr">
         <is>
           <t>images/「結婚前、結婚後」_img1.jpg</t>
         </is>
       </c>
-      <c r="C771" t="inlineStr">
+      <c r="C770" t="inlineStr">
         <is>
           <t>BeforeAfter ,幸せ太り</t>
         </is>
       </c>
     </row>
-    <row r="772">
-      <c r="A772" t="inlineStr">
+    <row r="771">
+      <c r="A771" t="inlineStr">
         <is>
           <t xml:space="preserve">「驚きの価格で」بسعر رائع
 ビスィアル・ラーイア [bi-si*r raa'i*]
@@ -16677,19 +16656,19 @@
 2109 Jarir Bookstore </t>
         </is>
       </c>
-      <c r="B772" t="inlineStr">
+      <c r="B771" t="inlineStr">
         <is>
           <t>images/「驚きの価格で」_img1.jpg</t>
         </is>
       </c>
-      <c r="C772" t="inlineStr">
+      <c r="C771" t="inlineStr">
         <is>
           <t>広告 ,安値</t>
         </is>
       </c>
     </row>
-    <row r="773">
-      <c r="A773" t="inlineStr">
+    <row r="772">
+      <c r="A772" t="inlineStr">
         <is>
           <t xml:space="preserve">「我が魂と共に」مع نفسي
 マア・ナフスィ [ma*a nafs-iy]
@@ -16698,19 +16677,19 @@
 2110 出典不明 </t>
         </is>
       </c>
-      <c r="B773" t="inlineStr">
+      <c r="B772" t="inlineStr">
         <is>
           <t>images/「我が魂と共に」_img1.jpg</t>
         </is>
       </c>
-      <c r="C773" t="inlineStr">
+      <c r="C772" t="inlineStr">
         <is>
           <t>ソウル ,soul</t>
         </is>
       </c>
     </row>
-    <row r="774">
-      <c r="A774" t="inlineStr">
+    <row r="773">
+      <c r="A773" t="inlineStr">
         <is>
           <t xml:space="preserve">「暗い夜に」في ليلة مظلمة
  [fiy layla(tin) mu_Dhlima(tin)]
@@ -16719,19 +16698,19 @@
 2109 سلسلة الحلزونة </t>
         </is>
       </c>
-      <c r="B774" t="inlineStr">
+      <c r="B773" t="inlineStr">
         <is>
           <t>images/「暗い夜に」_img1.jpg</t>
         </is>
       </c>
-      <c r="C774" t="inlineStr">
+      <c r="C773" t="inlineStr">
         <is>
           <t>絵本</t>
         </is>
       </c>
     </row>
-    <row r="775">
-      <c r="A775" t="inlineStr">
+    <row r="774">
+      <c r="A774" t="inlineStr">
         <is>
           <t xml:space="preserve">「ゆっくりと」بشويش
 ビシワェーシ [bi-ShwySh]
@@ -16739,19 +16718,19 @@
 2109 出典不明 </t>
         </is>
       </c>
-      <c r="B775" t="inlineStr">
+      <c r="B774" t="inlineStr">
         <is>
           <t>images/「ゆっくりと」_img1.jpg</t>
         </is>
       </c>
-      <c r="C775" t="inlineStr">
+      <c r="C774" t="inlineStr">
         <is>
           <t>丸 ,円</t>
         </is>
       </c>
     </row>
-    <row r="776">
-      <c r="A776" t="inlineStr">
+    <row r="775">
+      <c r="A775" t="inlineStr">
         <is>
           <t xml:space="preserve">「この広い宇宙に…」
 في الكون الفسيح
@@ -16760,19 +16739,19 @@
 2308 wattpad </t>
         </is>
       </c>
-      <c r="B776" t="inlineStr">
+      <c r="B775" t="inlineStr">
         <is>
           <t>images/「この広い宇宙に…」_img1.jpg</t>
         </is>
       </c>
-      <c r="C776" t="inlineStr">
+      <c r="C775" t="inlineStr">
         <is>
           <t>アニメ ,宇宙</t>
         </is>
       </c>
     </row>
-    <row r="777">
-      <c r="A777" t="inlineStr">
+    <row r="776">
+      <c r="A776" t="inlineStr">
         <is>
           <t xml:space="preserve">「がんばって！」بالتوفيق
 ビッタウフィーク [bi^tawfiiq]
@@ -16780,19 +16759,19 @@
 2111 https://sites.google.com/site/mathmatic1905/ </t>
         </is>
       </c>
-      <c r="B777" t="inlineStr">
+      <c r="B776" t="inlineStr">
         <is>
           <t>images/「がんばって！」_img1.jpg</t>
         </is>
       </c>
-      <c r="C777" t="inlineStr">
+      <c r="C776" t="inlineStr">
         <is>
           <t>アラビア語</t>
         </is>
       </c>
     </row>
-    <row r="778">
-      <c r="A778" t="inlineStr">
+    <row r="777">
+      <c r="A777" t="inlineStr">
         <is>
           <t xml:space="preserve">「インターステラー」بين النجوم
 バイナ_ンヌジューム [bayna ^nujuum]
@@ -16800,19 +16779,19 @@
 2308 kmrghani </t>
         </is>
       </c>
-      <c r="B778" t="inlineStr">
+      <c r="B777" t="inlineStr">
         <is>
           <t>images/「インターステラー」_img1.jpg</t>
         </is>
       </c>
-      <c r="C778" t="inlineStr">
+      <c r="C777" t="inlineStr">
         <is>
           <t>映画 ,宇宙</t>
         </is>
       </c>
     </row>
-    <row r="779">
-      <c r="A779" t="inlineStr">
+    <row r="778">
+      <c r="A778" t="inlineStr">
         <is>
           <t xml:space="preserve">「アラビア語で」بالعربية
 ビ_ルアラビーヤ [bi-l-*arabiyya]
@@ -16821,19 +16800,19 @@
 1811 </t>
         </is>
       </c>
-      <c r="B779" t="inlineStr">
+      <c r="B778" t="inlineStr">
         <is>
           <t>images/「アラビア語で」_img1.jpg</t>
         </is>
       </c>
-      <c r="C779" t="inlineStr">
+      <c r="C778" t="inlineStr">
         <is>
           <t>ニュース ,CNN</t>
         </is>
       </c>
     </row>
-    <row r="780">
-      <c r="A780" t="inlineStr">
+    <row r="779">
+      <c r="A779" t="inlineStr">
         <is>
           <t xml:space="preserve">「17世紀に発明されて以来…」
 منذ اختراعه بالقرن السابع عشر
@@ -16841,19 +16820,19 @@
 2308 https://twitter.com/SciTalk2U/status/1450888395815854080 </t>
         </is>
       </c>
-      <c r="B780" t="inlineStr">
+      <c r="B779" t="inlineStr">
         <is>
           <t>images/「17世紀に発明されて以来…」_img1.jpg</t>
         </is>
       </c>
-      <c r="C780" t="inlineStr">
+      <c r="C779" t="inlineStr">
         <is>
           <t>手書き語学 ,アラビア語 ,望遠鏡</t>
         </is>
       </c>
     </row>
-    <row r="781">
-      <c r="A781" t="inlineStr">
+    <row r="780">
+      <c r="A780" t="inlineStr">
         <is>
           <t xml:space="preserve">「私できるよ」إنّني أستطيع
 インナニー・アスタティーウ ['inna-niy 'a-sta_tii*u]
@@ -16862,19 +16841,19 @@
 2412 سلسلة الحلزونة </t>
         </is>
       </c>
-      <c r="B781" t="inlineStr">
+      <c r="B780" t="inlineStr">
         <is>
           <t>images/「私できるよ」_img1.jpg</t>
         </is>
       </c>
-      <c r="C781" t="inlineStr">
+      <c r="C780" t="inlineStr">
         <is>
           <t>絵本 ,こども</t>
         </is>
       </c>
     </row>
-    <row r="782">
-      <c r="A782" t="inlineStr">
+    <row r="781">
+      <c r="A781" t="inlineStr">
         <is>
           <t xml:space="preserve">「問題なし」مافيش مشكلة
 マフィーシムシュキラ [ma-fy-Sh muShkila]
@@ -16883,19 +16862,19 @@
 2109 tanzerin.theshop </t>
         </is>
       </c>
-      <c r="B782" t="inlineStr">
+      <c r="B781" t="inlineStr">
         <is>
           <t>images/「問題なし」_img1.jpg</t>
         </is>
       </c>
-      <c r="C782" t="inlineStr">
+      <c r="C781" t="inlineStr">
         <is>
           <t>シャツ ,キッズ</t>
         </is>
       </c>
     </row>
-    <row r="783">
-      <c r="A783" t="inlineStr">
+    <row r="782">
+      <c r="A782" t="inlineStr">
         <is>
           <t xml:space="preserve">「不可能はない」مفيش مستحيل
 マフィーシ・ムスタヒール [ma-fy-Sh mustaHiil]
@@ -16904,19 +16883,19 @@
 2109 أموج </t>
         </is>
       </c>
-      <c r="B783" t="inlineStr">
+      <c r="B782" t="inlineStr">
         <is>
           <t>images/「不可能はない」_img1.jpg</t>
         </is>
       </c>
-      <c r="C783" t="inlineStr">
+      <c r="C782" t="inlineStr">
         <is>
           <t>ポジティブ ,挑戦</t>
         </is>
       </c>
     </row>
-    <row r="784">
-      <c r="A784" t="inlineStr">
+    <row r="783">
+      <c r="A783" t="inlineStr">
         <is>
           <t xml:space="preserve">「等々」إلخ
 イラク ['ilaKh]
@@ -16925,19 +16904,19 @@
 2201 出典不明 </t>
         </is>
       </c>
-      <c r="B784" t="inlineStr">
+      <c r="B783" t="inlineStr">
         <is>
           <t>images/「等々」_img1.jpg</t>
         </is>
       </c>
-      <c r="C784" t="inlineStr">
+      <c r="C783" t="inlineStr">
         <is>
           <t>etc ,とんち</t>
         </is>
       </c>
     </row>
-    <row r="785">
-      <c r="A785" t="inlineStr">
+    <row r="784">
+      <c r="A784" t="inlineStr">
         <is>
           <t xml:space="preserve">⁦「調子どう？」⁩شلونَك؟
 シュローナク？ [Sh-loon-ak?]
@@ -16946,19 +16925,19 @@
 2202 Jozoor Team. </t>
         </is>
       </c>
-      <c r="B785" t="inlineStr">
+      <c r="B784" t="inlineStr">
         <is>
           <t>images/⁦「調子どう？」⁩_img1.jpg</t>
         </is>
       </c>
-      <c r="C785" t="inlineStr">
+      <c r="C784" t="inlineStr">
         <is>
           <t>洒落 ,ルービックキューブ</t>
         </is>
       </c>
     </row>
-    <row r="786">
-      <c r="A786" t="inlineStr">
+    <row r="785">
+      <c r="A785" t="inlineStr">
         <is>
           <t xml:space="preserve">「行くな」ماتروحش
 マトロホシ [ma-troH-Sh]
@@ -16967,19 +16946,19 @@
 2411 triiq tumblr </t>
         </is>
       </c>
-      <c r="B786" t="inlineStr">
+      <c r="B785" t="inlineStr">
         <is>
           <t>images/「行くな」_img1.jpg</t>
         </is>
       </c>
-      <c r="C786" t="inlineStr">
+      <c r="C785" t="inlineStr">
         <is>
           <t>ロゴ ,デザイン ,嵐</t>
         </is>
       </c>
     </row>
-    <row r="787">
-      <c r="A787" t="inlineStr">
+    <row r="786">
+      <c r="A786" t="inlineStr">
         <is>
           <t xml:space="preserve">⁦「元気？」⁩شلونَك؟
 シュローナク？ [Sh-loon-ak?]
@@ -16990,19 +16969,19 @@
 2202 出典不明 </t>
         </is>
       </c>
-      <c r="B787" t="inlineStr">
+      <c r="B786" t="inlineStr">
         <is>
           <t>images/⁦「元気？」⁩_img1.jpg</t>
         </is>
       </c>
-      <c r="C787" t="inlineStr">
+      <c r="C786" t="inlineStr">
         <is>
           <t>洒落 ,挨拶</t>
         </is>
       </c>
     </row>
-    <row r="788">
-      <c r="A788" t="inlineStr">
+    <row r="787">
+      <c r="A787" t="inlineStr">
         <is>
           <t xml:space="preserve">「気分が良いぞう」I فيل GOOD
 アイ・フィール・グッド [ai fiyl gud]
@@ -17011,19 +16990,19 @@
 2308 出典不明 </t>
         </is>
       </c>
-      <c r="B788" t="inlineStr">
+      <c r="B787" t="inlineStr">
         <is>
           <t>images/「気分が良いぞう」_img1.jpg</t>
         </is>
       </c>
-      <c r="C788" t="inlineStr">
+      <c r="C787" t="inlineStr">
         <is>
           <t>洒落 ,和訳</t>
         </is>
       </c>
     </row>
-    <row r="789">
-      <c r="A789" t="inlineStr">
+    <row r="788">
+      <c r="A788" t="inlineStr">
         <is>
           <t xml:space="preserve">「レットイットゴー／let it go」
 ليت اِت غو
@@ -17032,19 +17011,19 @@
 2109 出典不明 </t>
         </is>
       </c>
-      <c r="B789" t="inlineStr">
+      <c r="B788" t="inlineStr">
         <is>
           <t>images/「レットイットゴー／let it go_img1.jpg</t>
         </is>
       </c>
-      <c r="C789" t="inlineStr">
+      <c r="C788" t="inlineStr">
         <is>
           <t>折衷 ,アナ雪</t>
         </is>
       </c>
     </row>
-    <row r="790">
-      <c r="A790" t="inlineStr">
+    <row r="789">
+      <c r="A789" t="inlineStr">
         <is>
           <t xml:space="preserve">「ようこそ」اهلا وسهلا
 アハラン・ワサハラン ['ahlan wa-sahlan]
@@ -17052,19 +17031,19 @@
 2106 behance Anwar Al Eissa </t>
         </is>
       </c>
-      <c r="B790" t="inlineStr">
+      <c r="B789" t="inlineStr">
         <is>
           <t>images/「ようこそ」_img1.jpg</t>
         </is>
       </c>
-      <c r="C790" t="inlineStr">
+      <c r="C789" t="inlineStr">
         <is>
           <t>アラビア語</t>
         </is>
       </c>
     </row>
-    <row r="791">
-      <c r="A791" t="inlineStr">
+    <row r="790">
+      <c r="A790" t="inlineStr">
         <is>
           <t xml:space="preserve">「まぁ何というサプライズでしょう」
 يا لها من مفاجأة
@@ -17075,19 +17054,19 @@
 2108 neelwafurat com </t>
         </is>
       </c>
-      <c r="B791" t="inlineStr">
+      <c r="B790" t="inlineStr">
         <is>
           <t>images/「まぁ何というサプライズでしょう」_img1.jpg</t>
         </is>
       </c>
-      <c r="C791" t="inlineStr">
+      <c r="C790" t="inlineStr">
         <is>
           <t>中国語 ,学習</t>
         </is>
       </c>
     </row>
-    <row r="792">
-      <c r="A792" t="inlineStr">
+    <row r="791">
+      <c r="A791" t="inlineStr">
         <is>
           <t xml:space="preserve">「ハックション」اتشوو
 アチュー！ ['aatShuu]
@@ -17095,19 +17074,19 @@
 1811 </t>
         </is>
       </c>
-      <c r="B792" t="inlineStr">
+      <c r="B791" t="inlineStr">
         <is>
           <t>images/「ハックション」_img1.jpg</t>
         </is>
       </c>
-      <c r="C792" t="inlineStr">
+      <c r="C791" t="inlineStr">
         <is>
           <t>あらびあや</t>
         </is>
       </c>
     </row>
-    <row r="793">
-      <c r="A793" t="inlineStr">
+    <row r="792">
+      <c r="A792" t="inlineStr">
         <is>
           <t xml:space="preserve">「スブハーナッラー」「アルハムドゥリッラー」「アッラーアクバル」
 سبحان الله
@@ -17118,19 +17097,19 @@
 2308 dribbble com </t>
         </is>
       </c>
-      <c r="B793" t="inlineStr">
+      <c r="B792" t="inlineStr">
         <is>
           <t>images/「スブハーナッラー」「アルハムドゥリッ_img1.jpg</t>
         </is>
       </c>
-      <c r="C793" t="inlineStr">
+      <c r="C792" t="inlineStr">
         <is>
           <t>四角 ,コンパクト</t>
         </is>
       </c>
     </row>
-    <row r="794">
-      <c r="A794" t="inlineStr">
+    <row r="793">
+      <c r="A793" t="inlineStr">
         <is>
           <t xml:space="preserve">「すごく美味しい！」لذيذ جدًا
 ラズィーズ・ジッダン [laDhiiDh jiddan]
@@ -17139,19 +17118,19 @@
 2109 goodreads com </t>
         </is>
       </c>
-      <c r="B794" t="inlineStr">
+      <c r="B793" t="inlineStr">
         <is>
           <t>images/「すごく美味しい！」_img1.jpg</t>
         </is>
       </c>
-      <c r="C794" t="inlineStr">
+      <c r="C793" t="inlineStr">
         <is>
           <t>フレーズ ,感想</t>
         </is>
       </c>
     </row>
-    <row r="795">
-      <c r="A795" t="inlineStr">
+    <row r="794">
+      <c r="A794" t="inlineStr">
         <is>
           <t xml:space="preserve">「しとしと、雨」تك تك يا مطر
 ティクティク [tik tik yaa ma_tar]
@@ -17160,19 +17139,19 @@
 2308 出典不明 </t>
         </is>
       </c>
-      <c r="B795" t="inlineStr">
+      <c r="B794" t="inlineStr">
         <is>
           <t>images/「しとしと、雨」_img1.jpg</t>
         </is>
       </c>
-      <c r="C795" t="inlineStr">
+      <c r="C794" t="inlineStr">
         <is>
           <t>天気 ,梅雨</t>
         </is>
       </c>
     </row>
-    <row r="796">
-      <c r="A796" t="inlineStr">
+    <row r="795">
+      <c r="A795" t="inlineStr">
         <is>
           <t xml:space="preserve">「さかさま」رأساً على عقب
 ラッアサン・アラー・アケブ [ra'san *alaa *aqib]
@@ -17180,19 +17159,19 @@
 2109 出典不明 </t>
         </is>
       </c>
-      <c r="B796" t="inlineStr">
+      <c r="B795" t="inlineStr">
         <is>
           <t>images/「さかさま」_img1.jpg</t>
         </is>
       </c>
-      <c r="C796" t="inlineStr">
+      <c r="C795" t="inlineStr">
         <is>
           <t>壁 ,上下</t>
         </is>
       </c>
     </row>
-    <row r="797">
-      <c r="A797" t="inlineStr">
+    <row r="796">
+      <c r="A796" t="inlineStr">
         <is>
           <t xml:space="preserve">「エジプトよどこへ行った」
 فينك يا مصر؟
@@ -17202,19 +17181,19 @@
 1809 shehabfawzy1.tumblr </t>
         </is>
       </c>
-      <c r="B797" t="inlineStr">
+      <c r="B796" t="inlineStr">
         <is>
           <t>images/「エジプトよどこへ行った」_img1.jpg</t>
         </is>
       </c>
-      <c r="C797" t="inlineStr">
+      <c r="C796" t="inlineStr">
         <is>
           <t>ピラミッド ,歴史</t>
         </is>
       </c>
     </row>
-    <row r="798">
-      <c r="A798" t="inlineStr">
+    <row r="797">
+      <c r="A797" t="inlineStr">
         <is>
           <t xml:space="preserve">「ありがとう」شكراً
 シュクラン [Shukran]
@@ -17222,19 +17201,19 @@
 2109 出典不明 </t>
         </is>
       </c>
-      <c r="B798" t="inlineStr">
+      <c r="B797" t="inlineStr">
         <is>
           <t>images/「ありがとう」_img1.jpg</t>
         </is>
       </c>
-      <c r="C798" t="inlineStr">
+      <c r="C797" t="inlineStr">
         <is>
           <t>挨拶 ,文字</t>
         </is>
       </c>
     </row>
-    <row r="799">
-      <c r="A799" t="inlineStr">
+    <row r="798">
+      <c r="A798" t="inlineStr">
         <is>
           <t xml:space="preserve">「昼寝の時間だ」
 إنه وقت القيلولة
@@ -17243,12 +17222,12 @@
 2501 https://x.com/NatGeoMagArab/status/1858049951579910486 </t>
         </is>
       </c>
-      <c r="B799" t="inlineStr">
+      <c r="B798" t="inlineStr">
         <is>
           <t>images/「昼寝の時間だ」_img1.jpg</t>
         </is>
       </c>
-      <c r="C799" t="inlineStr">
+      <c r="C798" t="inlineStr">
         <is>
           <t>手書き語学 ,アラビア語 ,ペンギン</t>
         </is>

--- a/posts.xlsx
+++ b/posts.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C798"/>
+  <dimension ref="A1:C797"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -12281,27 +12281,6 @@
     <row r="565">
       <c r="A565" t="inlineStr">
         <is>
-          <t xml:space="preserve">「この生き物を見分けられますか？」
-هل تُميز هذا الكائن؟
-[hal tu-mayyizu haaDha l-kaa'in?]
-生き物（いき・もの）・見分ける（み・わける）
-2308 https://twitter.com/NatGeoMagArab/status/1455121397827600388 </t>
-        </is>
-      </c>
-      <c r="B565" t="inlineStr">
-        <is>
-          <t>images/「この生き物を見分けられますか？」_img1.jpg</t>
-        </is>
-      </c>
-      <c r="C565" t="inlineStr">
-        <is>
-          <t xml:space="preserve">手書き語学 ,カバ </t>
-        </is>
-      </c>
-    </row>
-    <row r="566">
-      <c r="A566" t="inlineStr">
-        <is>
           <t xml:space="preserve">「ひとを幸せにするには？」
 كيف تسعد غيرك؟
 [kayfa tu-s*idu Ghayra-k?]
@@ -12310,19 +12289,19 @@
 2308 Gwid3 </t>
         </is>
       </c>
-      <c r="B566" t="inlineStr">
+      <c r="B565" t="inlineStr">
         <is>
           <t>images/「ひとを幸せにするには？」_img1.jpg</t>
         </is>
       </c>
-      <c r="C566" t="inlineStr">
+      <c r="C565" t="inlineStr">
         <is>
           <t>思いやり ,心</t>
         </is>
       </c>
     </row>
-    <row r="567">
-      <c r="A567" t="inlineStr">
+    <row r="566">
+      <c r="A566" t="inlineStr">
         <is>
           <t xml:space="preserve">「ラマダン月に口臭をおさえる方法は？」
 كيف تتجنب رائحة الفم في رمضان
@@ -12331,19 +12310,19 @@
 2109 AlArabiya </t>
         </is>
       </c>
-      <c r="B567" t="inlineStr">
+      <c r="B566" t="inlineStr">
         <is>
           <t>images/「ラマダン月に口臭をおさえる方法は？」_img1.jpg</t>
         </is>
       </c>
-      <c r="C567" t="inlineStr">
+      <c r="C566" t="inlineStr">
         <is>
           <t>イスラム教 ,ブレスケア</t>
         </is>
       </c>
     </row>
-    <row r="568">
-      <c r="A568" t="inlineStr">
+    <row r="567">
+      <c r="A567" t="inlineStr">
         <is>
           <t xml:space="preserve">「ヨユウなきユウヨ」
 يمهل ولا يهمل
@@ -12353,19 +12332,19 @@
 2512 instagram com/p/CK4CLqeJ3dy/ </t>
         </is>
       </c>
-      <c r="B568" t="inlineStr">
+      <c r="B567" t="inlineStr">
         <is>
           <t>images/「ヨユウなきユウヨ」_img1.jpg</t>
         </is>
       </c>
-      <c r="C568" t="inlineStr">
+      <c r="C567" t="inlineStr">
         <is>
           <t>時計 ,からくり</t>
         </is>
       </c>
     </row>
-    <row r="569">
-      <c r="A569" t="inlineStr">
+    <row r="568">
+      <c r="A568" t="inlineStr">
         <is>
           <t xml:space="preserve">「どうして？　動物は絶滅する」
 لماذا؟ تنقرض الحيوانات
@@ -12375,19 +12354,19 @@
 2308 goodreads com </t>
         </is>
       </c>
-      <c r="B569" t="inlineStr">
+      <c r="B568" t="inlineStr">
         <is>
           <t>images/「どうして？　動物は絶滅する」_img1.jpg</t>
         </is>
       </c>
-      <c r="C569" t="inlineStr">
+      <c r="C568" t="inlineStr">
         <is>
           <t>動物 ,子供用</t>
         </is>
       </c>
     </row>
-    <row r="570">
-      <c r="A570" t="inlineStr">
+    <row r="569">
+      <c r="A569" t="inlineStr">
         <is>
           <t xml:space="preserve">「私たちは異なる。だから調和する」
 نختلف.. لنأتلف
@@ -12397,19 +12376,19 @@
 2103 Nawal Saed </t>
         </is>
       </c>
-      <c r="B570" t="inlineStr">
+      <c r="B569" t="inlineStr">
         <is>
           <t>images/「私たちは異なる。だから調和する」_img1.jpg</t>
         </is>
       </c>
-      <c r="C570" t="inlineStr">
+      <c r="C569" t="inlineStr">
         <is>
           <t>異符号 ,ハーモニー</t>
         </is>
       </c>
     </row>
-    <row r="571">
-      <c r="A571" t="inlineStr">
+    <row r="570">
+      <c r="A570" t="inlineStr">
         <is>
           <t xml:space="preserve">「私の肺には蝶々が住んでいて、呼吸の度に羽ばたく」
 تسكن رئتيّ فراشة ترفرف كلما أتنفس
@@ -12418,19 +12397,19 @@
 2109 出典不明 </t>
         </is>
       </c>
-      <c r="B571" t="inlineStr">
+      <c r="B570" t="inlineStr">
         <is>
           <t>images/「私の肺には蝶々が住んでいて、呼吸の度_img1.jpg</t>
         </is>
       </c>
-      <c r="C571" t="inlineStr">
+      <c r="C570" t="inlineStr">
         <is>
           <t>人体 ,昆虫</t>
         </is>
       </c>
     </row>
-    <row r="572">
-      <c r="A572" t="inlineStr">
+    <row r="571">
+      <c r="A571" t="inlineStr">
         <is>
           <t xml:space="preserve">「安らぎを感じますか？」
 هل تستشعر السكينة؟
@@ -12439,19 +12418,19 @@
 2404 https://twitter.com/NatGeoMagArab/status/1541421154950209536 </t>
         </is>
       </c>
-      <c r="B572" t="inlineStr">
+      <c r="B571" t="inlineStr">
         <is>
           <t>images/「安らぎを感じますか？」_img1.jpg</t>
         </is>
       </c>
-      <c r="C572" t="inlineStr">
+      <c r="C571" t="inlineStr">
         <is>
           <t>手書き語学 ,アラビア語 ,エイ</t>
         </is>
       </c>
     </row>
-    <row r="573">
-      <c r="A573" t="inlineStr">
+    <row r="572">
+      <c r="A572" t="inlineStr">
         <is>
           <t xml:space="preserve">「たとえあなたの使うブラウザがChromeだろうとSafariだろうと」
 سواء كنت تستخدم متصفح كروم أو سفاري
@@ -12459,19 +12438,19 @@
 2308 https://twitter.com/ShaayTech/status/1536235333972635649 </t>
         </is>
       </c>
-      <c r="B573" t="inlineStr">
+      <c r="B572" t="inlineStr">
         <is>
           <t>images/「たとえあなたの使うブラウザがChro_img1.jpg</t>
         </is>
       </c>
-      <c r="C573" t="inlineStr">
+      <c r="C572" t="inlineStr">
         <is>
           <t xml:space="preserve">手書き語学 ,アラビア語 ,iPhone </t>
         </is>
       </c>
     </row>
-    <row r="574">
-      <c r="A574" t="inlineStr">
+    <row r="573">
+      <c r="A573" t="inlineStr">
         <is>
           <t xml:space="preserve">「このミドリモリヤツガシラは気づいて欲しい」
 يحرص "هدهد الخشب الأخضر" هذا على أن يدرك
@@ -12480,19 +12459,19 @@
 2308 https://twitter.com/NatGeoMagArab/status/1531161022928539648 </t>
         </is>
       </c>
-      <c r="B574" t="inlineStr">
+      <c r="B573" t="inlineStr">
         <is>
           <t>images/「このミドリモリヤツガシラは気づいて欲_img1.jpg</t>
         </is>
       </c>
-      <c r="C574" t="inlineStr">
+      <c r="C573" t="inlineStr">
         <is>
           <t xml:space="preserve">手書き語学 ,アラビア語 ,鳥 </t>
         </is>
       </c>
     </row>
-    <row r="575">
-      <c r="A575" t="inlineStr">
+    <row r="574">
+      <c r="A574" t="inlineStr">
         <is>
           <t xml:space="preserve">「あなたの怖いものは何ですか」
 ماهي مخاوفك؟
@@ -12504,15 +12483,15 @@
 2308 1112kok </t>
         </is>
       </c>
-      <c r="B575" t="inlineStr">
+      <c r="B574" t="inlineStr">
         <is>
           <t>images/「あなたの怖いものは何ですか」_img1.jpg</t>
         </is>
       </c>
-      <c r="C575" t="inlineStr"/>
-    </row>
-    <row r="576">
-      <c r="A576" t="inlineStr">
+      <c r="C574" t="inlineStr"/>
+    </row>
+    <row r="575">
+      <c r="A575" t="inlineStr">
         <is>
           <t xml:space="preserve">「美しい時は作るもの。待つものではない」
 اصنع اللحظات الجميلة. لا تنتظرها
@@ -12521,19 +12500,19 @@
 2308 abojamal.tumblr com </t>
         </is>
       </c>
-      <c r="B576" t="inlineStr">
+      <c r="B575" t="inlineStr">
         <is>
           <t>images/「美しい時は作るもの。待つものではない_img1.jpg</t>
         </is>
       </c>
-      <c r="C576" t="inlineStr">
+      <c r="C575" t="inlineStr">
         <is>
           <t>おうち時間</t>
         </is>
       </c>
     </row>
-    <row r="577">
-      <c r="A577" t="inlineStr">
+    <row r="576">
+      <c r="A576" t="inlineStr">
         <is>
           <t xml:space="preserve">「大切な時間を大切じゃないことに使わないこと」
 لا تضيع الوقت المهم في شيء غير مهم
@@ -12542,19 +12521,19 @@
 2308 Anwar_122_ </t>
         </is>
       </c>
-      <c r="B577" t="inlineStr">
+      <c r="B576" t="inlineStr">
         <is>
           <t>images/「大切な時間を大切じゃないことに使わな_img1.jpg</t>
         </is>
       </c>
-      <c r="C577" t="inlineStr">
+      <c r="C576" t="inlineStr">
         <is>
           <t>時間 ,貴重</t>
         </is>
       </c>
     </row>
-    <row r="578">
-      <c r="A578" t="inlineStr">
+    <row r="577">
+      <c r="A577" t="inlineStr">
         <is>
           <t xml:space="preserve">「このイノセントな目に騙されるな…」
 لا تنخدع بهذه العيون البريئة
@@ -12564,19 +12543,19 @@
 2201 https://twitter.com/NatGeoMagArab/status/1475715760202797056 </t>
         </is>
       </c>
-      <c r="B578" t="inlineStr">
+      <c r="B577" t="inlineStr">
         <is>
           <t>images/「このイノセントな目に騙されるな…」.png</t>
         </is>
       </c>
-      <c r="C578" t="inlineStr">
+      <c r="C577" t="inlineStr">
         <is>
           <t>がうがう ,カワイイ</t>
         </is>
       </c>
     </row>
-    <row r="579">
-      <c r="A579" t="inlineStr">
+    <row r="578">
+      <c r="A578" t="inlineStr">
         <is>
           <t xml:space="preserve">⁦「カメラを止めろ！」⁩
 أوقفوا التّصوير
@@ -12586,19 +12565,19 @@
 2509 alsalwabooks com </t>
         </is>
       </c>
-      <c r="B579" t="inlineStr">
+      <c r="B578" t="inlineStr">
         <is>
           <t>images/⁦「カメラを止めろ！」⁩_img1.jpg</t>
         </is>
       </c>
-      <c r="C579" t="inlineStr">
+      <c r="C578" t="inlineStr">
         <is>
           <t>絵本 ,撮影</t>
         </is>
       </c>
     </row>
-    <row r="580">
-      <c r="A580" t="inlineStr">
+    <row r="579">
+      <c r="A579" t="inlineStr">
         <is>
           <t xml:space="preserve">「話す前に考えなさい」
 فكر قبل ان تتكلم
@@ -12608,19 +12587,19 @@
 2308 Islamuna YouTube </t>
         </is>
       </c>
-      <c r="B580" t="inlineStr">
+      <c r="B579" t="inlineStr">
         <is>
           <t>images/「話す前に考えなさい」_img1.jpg</t>
         </is>
       </c>
-      <c r="C580" t="inlineStr">
+      <c r="C579" t="inlineStr">
         <is>
           <t>失言 ,発言</t>
         </is>
       </c>
     </row>
-    <row r="581">
-      <c r="A581" t="inlineStr">
+    <row r="580">
+      <c r="A580" t="inlineStr">
         <is>
           <t xml:space="preserve">「ツイッターでフォローして下さい」
 تابعونا على تويتر
@@ -12630,19 +12609,19 @@
 2109 出典不明 </t>
         </is>
       </c>
-      <c r="B581" t="inlineStr">
+      <c r="B580" t="inlineStr">
         <is>
           <t>images/「ツイッターでフォローして下さい」_img1.jpg</t>
         </is>
       </c>
-      <c r="C581" t="inlineStr">
+      <c r="C580" t="inlineStr">
         <is>
           <t>FollowUs ,バナー</t>
         </is>
       </c>
     </row>
-    <row r="582">
-      <c r="A582" t="inlineStr">
+    <row r="581">
+      <c r="A581" t="inlineStr">
         <is>
           <t xml:space="preserve">「敵を倒せ」دمّر العدو
 ダンミリ_ルアドゥーウ [dammiri l-*aduuw]
@@ -12651,19 +12630,19 @@
 2308 apkpure com </t>
         </is>
       </c>
-      <c r="B582" t="inlineStr">
+      <c r="B581" t="inlineStr">
         <is>
           <t>images/「敵を倒せ」_img1.jpg</t>
         </is>
       </c>
-      <c r="C582" t="inlineStr">
+      <c r="C581" t="inlineStr">
         <is>
           <t>ゲーム ,パンダ</t>
         </is>
       </c>
     </row>
-    <row r="583">
-      <c r="A583" t="inlineStr">
+    <row r="582">
+      <c r="A582" t="inlineStr">
         <is>
           <t xml:space="preserve">「咲け。蒔かれたらどこであろうと」
 أزهر أيْنمَا زرعت
@@ -12672,19 +12651,19 @@
 2407 Ahmed Madyan </t>
         </is>
       </c>
-      <c r="B583" t="inlineStr">
+      <c r="B582" t="inlineStr">
         <is>
           <t>images/「咲け。蒔かれたらどこであろうと」_img1.jpg</t>
         </is>
       </c>
-      <c r="C583" t="inlineStr">
+      <c r="C582" t="inlineStr">
         <is>
           <t>環境のせいにしない ,花</t>
         </is>
       </c>
     </row>
-    <row r="584">
-      <c r="A584" t="inlineStr">
+    <row r="583">
+      <c r="A583" t="inlineStr">
         <is>
           <t xml:space="preserve">「頭を働かせろ」شغل مخك
 シャッギル・ムッハク [Sha^Ghil mu^Kha-k]
@@ -12693,19 +12672,19 @@
 2103 facebook elpage </t>
         </is>
       </c>
-      <c r="B584" t="inlineStr">
+      <c r="B583" t="inlineStr">
         <is>
           <t>images/「頭を働かせろ」_img1.jpg</t>
         </is>
       </c>
-      <c r="C584" t="inlineStr">
+      <c r="C583" t="inlineStr">
         <is>
           <t>電源 ,頭脳</t>
         </is>
       </c>
     </row>
-    <row r="585">
-      <c r="A585" t="inlineStr">
+    <row r="584">
+      <c r="A584" t="inlineStr">
         <is>
           <t xml:space="preserve">「傷跡は星にかえなさい」
 حوّل نُدوبكَ إلى نُجومْ
@@ -12715,19 +12694,19 @@
 2107 saramj1992 Instagram </t>
         </is>
       </c>
-      <c r="B585" t="inlineStr">
+      <c r="B584" t="inlineStr">
         <is>
           <t>images/「傷跡は星にかえなさい」_img1.jpg</t>
         </is>
       </c>
-      <c r="C585" t="inlineStr">
+      <c r="C584" t="inlineStr">
         <is>
           <t>勲章 ,証</t>
         </is>
       </c>
     </row>
-    <row r="586">
-      <c r="A586" t="inlineStr">
+    <row r="585">
+      <c r="A585" t="inlineStr">
         <is>
           <t xml:space="preserve">「あなたの主の栄光を誉め称え、また（御赦しを請え。本当にかれは、度々赦される御方である）」
 فسَبِّح بحمد ربك و
@@ -12736,19 +12715,19 @@
 2109 出典不明 </t>
         </is>
       </c>
-      <c r="B586" t="inlineStr">
+      <c r="B585" t="inlineStr">
         <is>
           <t>images/「あなたの主の栄光を誉め称え、また（御_img1.jpg</t>
         </is>
       </c>
-      <c r="C586" t="inlineStr">
+      <c r="C585" t="inlineStr">
         <is>
           <t>イスラム教 ,カリグラフィー</t>
         </is>
       </c>
     </row>
-    <row r="587">
-      <c r="A587" t="inlineStr">
+    <row r="586">
+      <c r="A586" t="inlineStr">
         <is>
           <t xml:space="preserve">「誰かを幸福にしなさい」
 أسْعِد أحدهم
@@ -12758,19 +12737,19 @@
 1810 in4sser.tumblr </t>
         </is>
       </c>
-      <c r="B587" t="inlineStr">
+      <c r="B586" t="inlineStr">
         <is>
           <t>images/「誰かを幸福にしなさい」_img1.jpg</t>
         </is>
       </c>
-      <c r="C587" t="inlineStr">
+      <c r="C586" t="inlineStr">
         <is>
           <t>人生 ,happy</t>
         </is>
       </c>
     </row>
-    <row r="588">
-      <c r="A588" t="inlineStr">
+    <row r="587">
+      <c r="A587" t="inlineStr">
         <is>
           <t xml:space="preserve">「見よ」أبْصِرْ
 アブスィル ['ab_sir]
@@ -12779,19 +12758,19 @@
 1811 Ruh Al-Alam, via Behance </t>
         </is>
       </c>
-      <c r="B588" t="inlineStr">
+      <c r="B587" t="inlineStr">
         <is>
           <t>images/「見よ」_img1.jpg</t>
         </is>
       </c>
-      <c r="C588" t="inlineStr">
+      <c r="C587" t="inlineStr">
         <is>
           <t>目 ,瞳</t>
         </is>
       </c>
     </row>
-    <row r="589">
-      <c r="A589" t="inlineStr">
+    <row r="588">
+      <c r="A588" t="inlineStr">
         <is>
           <t xml:space="preserve">「言葉は口から出す前に味わいなさい」
 ‪تذوق كلماتك قبل أن تنطقها‬
@@ -12801,19 +12780,19 @@
 2109 Reham-des </t>
         </is>
       </c>
-      <c r="B589" t="inlineStr">
+      <c r="B588" t="inlineStr">
         <is>
           <t>images/「言葉は口から出す前に味わいなさい」_img1.jpg</t>
         </is>
       </c>
-      <c r="C589" t="inlineStr">
+      <c r="C588" t="inlineStr">
         <is>
           <t>言葉</t>
         </is>
       </c>
     </row>
-    <row r="590">
-      <c r="A590" t="inlineStr">
+    <row r="589">
+      <c r="A589" t="inlineStr">
         <is>
           <t xml:space="preserve">「テレビを観るのをやめて下さい」
 توقفي عن مشاهدة التلفاز
@@ -12823,19 +12802,19 @@
 1809 </t>
         </is>
       </c>
-      <c r="B590" t="inlineStr">
+      <c r="B589" t="inlineStr">
         <is>
           <t>images/「テレビを観るのをやめて下さい」_img1.jpg</t>
         </is>
       </c>
-      <c r="C590" t="inlineStr">
+      <c r="C589" t="inlineStr">
         <is>
           <t>あらびあや</t>
         </is>
       </c>
     </row>
-    <row r="591">
-      <c r="A591" t="inlineStr">
+    <row r="590">
+      <c r="A590" t="inlineStr">
         <is>
           <t xml:space="preserve">「言わぬが花」
 انْطِقْ جَمَالاً أو تجَمَّلْ بالسّكُوت
@@ -12845,19 +12824,19 @@
 2411 Ahmed Madyan </t>
         </is>
       </c>
-      <c r="B591" t="inlineStr">
+      <c r="B590" t="inlineStr">
         <is>
           <t>images/「言わぬが花」_img1.jpg</t>
         </is>
       </c>
-      <c r="C591" t="inlineStr">
+      <c r="C590" t="inlineStr">
         <is>
           <t>ことわざ ,デザイン</t>
         </is>
       </c>
     </row>
-    <row r="592">
-      <c r="A592" t="inlineStr">
+    <row r="591">
+      <c r="A591" t="inlineStr">
         <is>
           <t xml:space="preserve">「たくさん考えて、少し話すこと」
 فكّر كثيرا. تكلم قليلا
@@ -12867,19 +12846,19 @@
 2105 In49r </t>
         </is>
       </c>
-      <c r="B592" t="inlineStr">
+      <c r="B591" t="inlineStr">
         <is>
           <t>images/「たくさん考えて、少し話すこと」_img1.jpg</t>
         </is>
       </c>
-      <c r="C592" t="inlineStr">
+      <c r="C591" t="inlineStr">
         <is>
           <t>思慮 ,会話</t>
         </is>
       </c>
     </row>
-    <row r="593">
-      <c r="A593" t="inlineStr">
+    <row r="592">
+      <c r="A592" t="inlineStr">
         <is>
           <t xml:space="preserve">「子供たちよ、いつでも思い出すんだよ」
 تذكروا دوما يا أطفال
@@ -12889,19 +12868,19 @@
 1809 </t>
         </is>
       </c>
-      <c r="B593" t="inlineStr">
+      <c r="B592" t="inlineStr">
         <is>
           <t>images/「子供たちよ、いつでも思い出すんだよ」_img1.jpg</t>
         </is>
       </c>
-      <c r="C593" t="inlineStr">
+      <c r="C592" t="inlineStr">
         <is>
           <t>オープニング ,ハム太郎</t>
         </is>
       </c>
     </row>
-    <row r="594">
-      <c r="A594" t="inlineStr">
+    <row r="593">
+      <c r="A593" t="inlineStr">
         <is>
           <t xml:space="preserve">「分かってから話しなさい」
 تعلَّم ثمَّ تكلَّم
@@ -12911,19 +12890,19 @@
 1903 Hashem Al Shareef, Pinterest </t>
         </is>
       </c>
-      <c r="B594" t="inlineStr">
+      <c r="B593" t="inlineStr">
         <is>
           <t>images/「分かってから話しなさい」_img1.jpg</t>
         </is>
       </c>
-      <c r="C594" t="inlineStr">
+      <c r="C593" t="inlineStr">
         <is>
           <t>教訓 ,トーク</t>
         </is>
       </c>
     </row>
-    <row r="595">
-      <c r="A595" t="inlineStr">
+    <row r="594">
+      <c r="A594" t="inlineStr">
         <is>
           <t xml:space="preserve">「蟻に学べ」تعلم من النملة
 タアッラム・ミナ_ンナムラ [ta*allam mina ^namla]
@@ -12932,19 +12911,19 @@
 2308 fatakat com </t>
         </is>
       </c>
-      <c r="B595" t="inlineStr">
+      <c r="B594" t="inlineStr">
         <is>
           <t>images/「蟻に学べ」_img1.jpg</t>
         </is>
       </c>
-      <c r="C595" t="inlineStr">
+      <c r="C594" t="inlineStr">
         <is>
           <t>教訓 ,問題解決</t>
         </is>
       </c>
     </row>
-    <row r="596">
-      <c r="A596" t="inlineStr">
+    <row r="595">
+      <c r="A595" t="inlineStr">
         <is>
           <t xml:space="preserve">「自分と仲直りしよう、一杯の珈琲で！」
 تصالح مع نفسك بكوب قهوة
@@ -12954,19 +12933,19 @@
 2308 asm95_ </t>
         </is>
       </c>
-      <c r="B596" t="inlineStr">
+      <c r="B595" t="inlineStr">
         <is>
           <t>images/「自分と仲直りしよう、一杯の珈琲で！」_img1.jpg</t>
         </is>
       </c>
-      <c r="C596" t="inlineStr">
+      <c r="C595" t="inlineStr">
         <is>
           <t>一服 ,リラックス</t>
         </is>
       </c>
     </row>
-    <row r="597">
-      <c r="A597" t="inlineStr">
+    <row r="596">
+      <c r="A596" t="inlineStr">
         <is>
           <t xml:space="preserve">「気をつけて　ジュード」
 انتبهي يا جود
@@ -12976,19 +12955,19 @@
 2109 سلسلة الحلزونة </t>
         </is>
       </c>
-      <c r="B597" t="inlineStr">
+      <c r="B596" t="inlineStr">
         <is>
           <t>images/「気をつけて　ジュード」_img1.jpg</t>
         </is>
       </c>
-      <c r="C597" t="inlineStr">
+      <c r="C596" t="inlineStr">
         <is>
           <t>絵本 ,わんぱく</t>
         </is>
       </c>
     </row>
-    <row r="598">
-      <c r="A598" t="inlineStr">
+    <row r="597">
+      <c r="A597" t="inlineStr">
         <is>
           <t xml:space="preserve">「coming soon」
 انتظرونا قريبا
@@ -12997,19 +12976,19 @@
 2307 出典不明 </t>
         </is>
       </c>
-      <c r="B598" t="inlineStr">
+      <c r="B597" t="inlineStr">
         <is>
           <t>images/「coming soon」_img1.jpg</t>
         </is>
       </c>
-      <c r="C598" t="inlineStr">
+      <c r="C597" t="inlineStr">
         <is>
           <t>フレーズ ,カミングスーン</t>
         </is>
       </c>
     </row>
-    <row r="599">
-      <c r="A599" t="inlineStr">
+    <row r="598">
+      <c r="A598" t="inlineStr">
         <is>
           <t xml:space="preserve">「自分の胸に聞きなさい。それが全て知っています」
 استمع لقلبك.. إنه يعرف كل شيء
@@ -13018,19 +12997,19 @@
 1811 </t>
         </is>
       </c>
-      <c r="B599" t="inlineStr">
+      <c r="B598" t="inlineStr">
         <is>
           <t>images/「自分の胸に聞きなさい。それが全て知っ_img1.jpg</t>
         </is>
       </c>
-      <c r="C599" t="inlineStr">
+      <c r="C598" t="inlineStr">
         <is>
           <t>あらびあや</t>
         </is>
       </c>
     </row>
-    <row r="600">
-      <c r="A600" t="inlineStr">
+    <row r="599">
+      <c r="A599" t="inlineStr">
         <is>
           <t xml:space="preserve">「笑ってくれ、絶望を癒すのは君の笑みだから」
 ابتسمي فإن دواء اليأس بسمتك
@@ -13039,19 +13018,19 @@
 2308 arab-quotes tumblr </t>
         </is>
       </c>
-      <c r="B600" t="inlineStr">
+      <c r="B599" t="inlineStr">
         <is>
           <t>images/「笑ってくれ、絶望を癒すのは君の笑みだ_img1.jpg</t>
         </is>
       </c>
-      <c r="C600" t="inlineStr">
+      <c r="C599" t="inlineStr">
         <is>
           <t>癒し ,スマイル</t>
         </is>
       </c>
     </row>
-    <row r="601">
-      <c r="A601" t="inlineStr">
+    <row r="600">
+      <c r="A600" t="inlineStr">
         <is>
           <t xml:space="preserve">「自分を頼りなさい。宇宙で最も確かな物が自分だと思って。」
 استند على نفسك وكأنك أكثر الأشياء ثباتًا بهذا الكون
@@ -13059,19 +13038,19 @@
 2308 x_nourh.15 </t>
         </is>
       </c>
-      <c r="B601" t="inlineStr">
+      <c r="B600" t="inlineStr">
         <is>
           <t>images/「自分を頼りなさい。宇宙で最も確かな物_img1.jpg</t>
         </is>
       </c>
-      <c r="C601" t="inlineStr">
+      <c r="C600" t="inlineStr">
         <is>
           <t>自我 ,宇宙</t>
         </is>
       </c>
     </row>
-    <row r="602">
-      <c r="A602" t="inlineStr">
+    <row r="601">
+      <c r="A601" t="inlineStr">
         <is>
           <t xml:space="preserve">「古いデバイスを交換して新品をゲットしよう」
 استبدل جهازك القديم واحصل على واحد جديد
@@ -13080,19 +13059,19 @@
 2406 stc </t>
         </is>
       </c>
-      <c r="B602" t="inlineStr">
+      <c r="B601" t="inlineStr">
         <is>
           <t>images/「古いデバイスを交換して新品をゲットし_img1.jpg</t>
         </is>
       </c>
-      <c r="C602" t="inlineStr">
+      <c r="C601" t="inlineStr">
         <is>
           <t>キャンペーン ,下取り</t>
         </is>
       </c>
     </row>
-    <row r="603">
-      <c r="A603" t="inlineStr">
+    <row r="602">
+      <c r="A602" t="inlineStr">
         <is>
           <t xml:space="preserve">「あなたの声を聞かせてください。私の心を彩ってください」
 هات صوتك، لوّن قلبي
@@ -13101,19 +13080,19 @@
 2105 3a2esha_ Instagram </t>
         </is>
       </c>
-      <c r="B603" t="inlineStr">
+      <c r="B602" t="inlineStr">
         <is>
           <t>images/「あなたの声を聞かせてください。私の心_img1.jpg</t>
         </is>
       </c>
-      <c r="C603" t="inlineStr">
+      <c r="C602" t="inlineStr">
         <is>
           <t>電話 ,肉声</t>
         </is>
       </c>
     </row>
-    <row r="604">
-      <c r="A604" t="inlineStr">
+    <row r="603">
+      <c r="A603" t="inlineStr">
         <is>
           <t xml:space="preserve">「この子カンガルーは抱っこが好き」
 يُحب صغير الكنغر هذا أن يؤخذ في الأحضان
@@ -13121,19 +13100,19 @@
 2308 NatGeoMagArab </t>
         </is>
       </c>
-      <c r="B604" t="inlineStr">
+      <c r="B603" t="inlineStr">
         <is>
           <t>images/「この子カンガルーは抱っこが好き」.png</t>
         </is>
       </c>
-      <c r="C604" t="inlineStr">
+      <c r="C603" t="inlineStr">
         <is>
           <t>カンガルー ,人肌</t>
         </is>
       </c>
     </row>
-    <row r="605">
-      <c r="A605" t="inlineStr">
+    <row r="604">
+      <c r="A604" t="inlineStr">
         <is>
           <t xml:space="preserve">「カタールが好き」أحب قطر
 ウヒッブ・カタル ['u-Hibb qa_tar]
@@ -13142,19 +13121,19 @@
 1810 出典不明 </t>
         </is>
       </c>
-      <c r="B605" t="inlineStr">
+      <c r="B604" t="inlineStr">
         <is>
           <t>images/「カタールが好き」_img1.jpg</t>
         </is>
       </c>
-      <c r="C605" t="inlineStr">
+      <c r="C604" t="inlineStr">
         <is>
           <t>カタール</t>
         </is>
       </c>
     </row>
-    <row r="606">
-      <c r="A606" t="inlineStr">
+    <row r="605">
+      <c r="A605" t="inlineStr">
         <is>
           <t xml:space="preserve">「一緒に読むのが好き」
 أُحبُّ أن نَقْرَأَ مَعاً
@@ -13164,19 +13143,19 @@
 2509 www.neelwafurat com,  id=lbb212750-185765 </t>
         </is>
       </c>
-      <c r="B606" t="inlineStr">
+      <c r="B605" t="inlineStr">
         <is>
           <t>images/「一緒に読むのが好き」_img1.jpg</t>
         </is>
       </c>
-      <c r="C606" t="inlineStr">
+      <c r="C605" t="inlineStr">
         <is>
           <t>好き ,本</t>
         </is>
       </c>
     </row>
-    <row r="607">
-      <c r="A607" t="inlineStr">
+    <row r="606">
+      <c r="A606" t="inlineStr">
         <is>
           <t xml:space="preserve">「病院に行きたくない」
 لا أريد أن أذهب إلى المشفى
@@ -13186,19 +13165,19 @@
 2508 Tony Ross https://education.hachette-antoine.com/ar/component/%D9%84%D8%A7-%D8%A3%D8%B1%D9%8A%D8%AF-%D8%A3%D9%86-%D8%A3%D8%B0%D9%87%D8%A8-%D8%A5%D9%84%D9%89-%D8%A7%D9%84%D9%85%D8%B4%D9%81%D9%89/ </t>
         </is>
       </c>
-      <c r="B607" t="inlineStr">
+      <c r="B606" t="inlineStr">
         <is>
           <t>images/「病院に行きたくない」_img1.jpg</t>
         </is>
       </c>
-      <c r="C607" t="inlineStr">
+      <c r="C606" t="inlineStr">
         <is>
           <t>絵本 ,子供</t>
         </is>
       </c>
     </row>
-    <row r="608">
-      <c r="A608" t="inlineStr">
+    <row r="607">
+      <c r="A607" t="inlineStr">
         <is>
           <t xml:space="preserve">「男性はいくら？」「女性はいくら？」
 كم يساوى الرجل؟ ..وكم تساوى المرأة؟
@@ -13207,19 +13186,19 @@
 2308 Pinterest, Masr Elmahrousa, Farah Noweir </t>
         </is>
       </c>
-      <c r="B608" t="inlineStr">
+      <c r="B607" t="inlineStr">
         <is>
           <t>images/「男性はいくら？」「女性はいくら？」_img1.jpg,images/「男性はいくら？」「女性はいくら？」_img2.jpg</t>
         </is>
       </c>
-      <c r="C608" t="inlineStr">
+      <c r="C607" t="inlineStr">
         <is>
           <t xml:space="preserve">全身コーデ ,相場 </t>
         </is>
       </c>
     </row>
-    <row r="609">
-      <c r="A609" t="inlineStr">
+    <row r="608">
+      <c r="A608" t="inlineStr">
         <is>
           <t xml:space="preserve">「黙ってもらえます？」
 ممكن تعيرنا سكوتك؟
@@ -13229,19 +13208,19 @@
 2308 Basel26 </t>
         </is>
       </c>
-      <c r="B609" t="inlineStr">
+      <c r="B608" t="inlineStr">
         <is>
           <t>images/「黙ってもらえます？」_img1.jpg</t>
         </is>
       </c>
-      <c r="C609" t="inlineStr">
+      <c r="C608" t="inlineStr">
         <is>
           <t>音量 ,ボリューム</t>
         </is>
       </c>
     </row>
-    <row r="610">
-      <c r="A610" t="inlineStr">
+    <row r="609">
+      <c r="A609" t="inlineStr">
         <is>
           <t xml:space="preserve">「眠りたいです」
 أُريدُ أَن أَنام
@@ -13251,19 +13230,19 @@
 2109 goodreads com </t>
         </is>
       </c>
-      <c r="B610" t="inlineStr">
+      <c r="B609" t="inlineStr">
         <is>
           <t>images/「眠りたいです」_img1.jpg</t>
         </is>
       </c>
-      <c r="C610" t="inlineStr">
+      <c r="C609" t="inlineStr">
         <is>
           <t>絵本</t>
         </is>
       </c>
     </row>
-    <row r="611">
-      <c r="A611" t="inlineStr">
+    <row r="610">
+      <c r="A610" t="inlineStr">
         <is>
           <t xml:space="preserve">「飛びたい！」أُريد أن أطير
 ウリードゥ・アン・アティール ['u-riidu 'an 'a-_tiir]
@@ -13272,19 +13251,19 @@
 2308 出典不明 </t>
         </is>
       </c>
-      <c r="B611" t="inlineStr">
+      <c r="B610" t="inlineStr">
         <is>
           <t>images/「飛びたい！」_img1.jpg</t>
         </is>
       </c>
-      <c r="C611" t="inlineStr">
+      <c r="C610" t="inlineStr">
         <is>
           <t>鳥 ,希望</t>
         </is>
       </c>
     </row>
-    <row r="612">
-      <c r="A612" t="inlineStr">
+    <row r="611">
+      <c r="A611" t="inlineStr">
         <is>
           <t xml:space="preserve">「うちゅうへとびたい」
 أُريدُ أَنْ أَطيرَ إلى الفَضاء
@@ -13293,19 +13272,19 @@
 2308 mybookshelf co </t>
         </is>
       </c>
-      <c r="B612" t="inlineStr">
+      <c r="B611" t="inlineStr">
         <is>
           <t>images/「うちゅうへとびたい」_img1.jpg</t>
         </is>
       </c>
-      <c r="C612" t="inlineStr">
+      <c r="C611" t="inlineStr">
         <is>
           <t>絵本 ,宇宙</t>
         </is>
       </c>
     </row>
-    <row r="613">
-      <c r="A613" t="inlineStr">
+    <row r="612">
+      <c r="A612" t="inlineStr">
         <is>
           <t xml:space="preserve">「とても愛しています」
 أُحِبّك جِدّاً
@@ -13315,19 +13294,19 @@
 2308 hobe cc </t>
         </is>
       </c>
-      <c r="B613" t="inlineStr">
+      <c r="B612" t="inlineStr">
         <is>
           <t>images/「とても愛しています」_img1.jpg</t>
         </is>
       </c>
-      <c r="C613" t="inlineStr">
+      <c r="C612" t="inlineStr">
         <is>
           <t>恋 ,love</t>
         </is>
       </c>
     </row>
-    <row r="614">
-      <c r="A614" t="inlineStr">
+    <row r="613">
+      <c r="A613" t="inlineStr">
         <is>
           <t xml:space="preserve">「あす日が昇るだろう。私は朝が大好きだ」
 غدا ستشرق الشمس وأحب الصباح كثيرا
@@ -13336,19 +13315,19 @@
 2105 warag-3nb.tumblr com </t>
         </is>
       </c>
-      <c r="B614" t="inlineStr">
+      <c r="B613" t="inlineStr">
         <is>
           <t>images/「あす日が昇るだろう。私は朝が大好きだ_img1.jpg,images/ 「あす日が昇るだろう。私は朝が大好きだ_img2.jpg</t>
         </is>
       </c>
-      <c r="C614" t="inlineStr">
+      <c r="C613" t="inlineStr">
         <is>
           <t>おやすみ ,壁</t>
         </is>
       </c>
     </row>
-    <row r="615">
-      <c r="A615" t="inlineStr">
+    <row r="614">
+      <c r="A614" t="inlineStr">
         <is>
           <t xml:space="preserve">「きみは何をえらぶ？」
 ماذا تختار؟
@@ -13358,19 +13337,19 @@
 2109 embadomjp org </t>
         </is>
       </c>
-      <c r="B615" t="inlineStr">
+      <c r="B614" t="inlineStr">
         <is>
           <t>images/「きみは何をえらぶ？」_img1.jpg</t>
         </is>
       </c>
-      <c r="C615" t="inlineStr">
+      <c r="C614" t="inlineStr">
         <is>
           <t>優柔不断 ,絵本</t>
         </is>
       </c>
     </row>
-    <row r="616">
-      <c r="A616" t="inlineStr">
+    <row r="615">
+      <c r="A615" t="inlineStr">
         <is>
           <t xml:space="preserve">「ちょっと静けさが必要な時もある」
 في بعض الأوقات نحتاج لشوية هدوء
@@ -13380,19 +13359,19 @@
 2308 IN49r </t>
         </is>
       </c>
-      <c r="B616" t="inlineStr">
+      <c r="B615" t="inlineStr">
         <is>
           <t>images/「ちょっと静けさが必要な時もある」_img1.jpg</t>
         </is>
       </c>
-      <c r="C616" t="inlineStr">
+      <c r="C615" t="inlineStr">
         <is>
           <t>ミュート ,精神</t>
         </is>
       </c>
     </row>
-    <row r="617">
-      <c r="A617" t="inlineStr">
+    <row r="616">
+      <c r="A616" t="inlineStr">
         <is>
           <t xml:space="preserve">「逃げるな。全力でぶつかれ」
 لا تهرب اصطدم بكل قوتك
@@ -13402,19 +13381,19 @@
 2308 https://risingvibes.tumblr.com/post/189545775129 </t>
         </is>
       </c>
-      <c r="B617" t="inlineStr">
+      <c r="B616" t="inlineStr">
         <is>
           <t>images/「逃げるな。全力でぶつかれ」_img1.jpg</t>
         </is>
       </c>
-      <c r="C617" t="inlineStr">
+      <c r="C616" t="inlineStr">
         <is>
           <t>応援 ,力</t>
         </is>
       </c>
     </row>
-    <row r="618">
-      <c r="A618" t="inlineStr">
+    <row r="617">
+      <c r="A617" t="inlineStr">
         <is>
           <t xml:space="preserve">「着るのだいすき」
 أُحِبُ أَن أَرتَدِيَ
@@ -13424,19 +13403,19 @@
 2308 https://kitab.firmabikes.ru/epub-_hb_n_rtdy_5187.html </t>
         </is>
       </c>
-      <c r="B618" t="inlineStr">
+      <c r="B617" t="inlineStr">
         <is>
           <t>images/「着るのだいすき」_img1.jpg</t>
         </is>
       </c>
-      <c r="C618" t="inlineStr">
+      <c r="C617" t="inlineStr">
         <is>
           <t xml:space="preserve">絵本 ,ファッション </t>
         </is>
       </c>
     </row>
-    <row r="619">
-      <c r="A619" t="inlineStr">
+    <row r="618">
+      <c r="A618" t="inlineStr">
         <is>
           <t xml:space="preserve">「車のバッテリーが要る！」
 نحتاج بطارية سيارة
@@ -13446,19 +13425,19 @@
 2308 instagram roaa_27 </t>
         </is>
       </c>
-      <c r="B619" t="inlineStr">
+      <c r="B618" t="inlineStr">
         <is>
           <t>images/「車のバッテリーが要る！」_img1.jpg</t>
         </is>
       </c>
-      <c r="C619" t="inlineStr">
+      <c r="C618" t="inlineStr">
         <is>
           <t>スマホ ,充電</t>
         </is>
       </c>
     </row>
-    <row r="620">
-      <c r="A620" t="inlineStr">
+    <row r="619">
+      <c r="A619" t="inlineStr">
         <is>
           <t xml:space="preserve">「今日は幸せでいることにしました」
 اخترت أن أكون سعيدا اليوم
@@ -13468,19 +13447,19 @@
 2109 awaasha tumblr </t>
         </is>
       </c>
-      <c r="B620" t="inlineStr">
+      <c r="B619" t="inlineStr">
         <is>
           <t>images/「今日は幸せでいることにしました」_img1.jpg</t>
         </is>
       </c>
-      <c r="C620" t="inlineStr">
+      <c r="C619" t="inlineStr">
         <is>
           <t>心構え ,happy</t>
         </is>
       </c>
     </row>
-    <row r="621">
-      <c r="A621" t="inlineStr">
+    <row r="620">
+      <c r="A620" t="inlineStr">
         <is>
           <t xml:space="preserve">「理想的なスイカの選び方」
 كيف تختار البطيخة المُثلى؟
@@ -13490,19 +13469,19 @@
 2308 bit ly/octmel </t>
         </is>
       </c>
-      <c r="B621" t="inlineStr">
+      <c r="B620" t="inlineStr">
         <is>
           <t>images/「理想的なスイカの選び方」_img1.jpg</t>
         </is>
       </c>
-      <c r="C621" t="inlineStr">
+      <c r="C620" t="inlineStr">
         <is>
           <t>八百屋 ,西瓜</t>
         </is>
       </c>
     </row>
-    <row r="622">
-      <c r="A622" t="inlineStr">
+    <row r="621">
+      <c r="A621" t="inlineStr">
         <is>
           <t xml:space="preserve">「お問い合わせください」
 اتصل بنا
@@ -13512,19 +13491,19 @@
 2308 mtawir.blogspot com </t>
         </is>
       </c>
-      <c r="B622" t="inlineStr">
+      <c r="B621" t="inlineStr">
         <is>
           <t>images/「お問い合わせください」_img1.jpg</t>
         </is>
       </c>
-      <c r="C622" t="inlineStr">
+      <c r="C621" t="inlineStr">
         <is>
           <t>広告 ,電話</t>
         </is>
       </c>
     </row>
-    <row r="623">
-      <c r="A623" t="inlineStr">
+    <row r="622">
+      <c r="A622" t="inlineStr">
         <is>
           <t xml:space="preserve">「両方の動物が海岸の火山岩の亀裂の中に定住している」
 يحتل كلا الحيوانين شقوقًا في صخور الساحل البركانية
@@ -13532,19 +13511,19 @@
 2507 https://x.com/NatGeoMagArab/status/1925167200056521151 </t>
         </is>
       </c>
-      <c r="B623" t="inlineStr">
+      <c r="B622" t="inlineStr">
         <is>
           <t>images/「両方の動物が海岸の火山岩の亀裂の中に_img1.jpg,images/「両方の動物が海岸の火山岩の亀裂の中に_img2.jpg</t>
         </is>
       </c>
-      <c r="C623" t="inlineStr">
+      <c r="C622" t="inlineStr">
         <is>
           <t>手書き語学 ,アラビア語 ,イグアナ</t>
         </is>
       </c>
     </row>
-    <row r="624">
-      <c r="A624" t="inlineStr">
+    <row r="623">
+      <c r="A623" t="inlineStr">
         <is>
           <t xml:space="preserve">「命じられたように正しき道を辿れ」
 واستقم كما أمرت
@@ -13554,19 +13533,19 @@
 2308 Ahmed Madyan </t>
         </is>
       </c>
-      <c r="B624" t="inlineStr">
+      <c r="B623" t="inlineStr">
         <is>
           <t>images/「命じられたように正しき道を辿れ」_img1.jpg</t>
         </is>
       </c>
-      <c r="C624" t="inlineStr">
+      <c r="C623" t="inlineStr">
         <is>
           <t>書道 ,アート</t>
         </is>
       </c>
     </row>
-    <row r="625">
-      <c r="A625" t="inlineStr">
+    <row r="624">
+      <c r="A624" t="inlineStr">
         <is>
           <t xml:space="preserve">「くつろぎなさい」استكن
 イスタキンナ [istakinna]
@@ -13574,19 +13553,19 @@
 2603 m2ff tumblr com </t>
         </is>
       </c>
-      <c r="B625" t="inlineStr">
+      <c r="B624" t="inlineStr">
         <is>
           <t>images/「くつろぎなさい」.jpeg</t>
         </is>
       </c>
-      <c r="C625" t="inlineStr">
+      <c r="C624" t="inlineStr">
         <is>
           <t>relax ,コーヒー</t>
         </is>
       </c>
     </row>
-    <row r="626">
-      <c r="A626" t="inlineStr">
+    <row r="625">
+      <c r="A625" t="inlineStr">
         <is>
           <t xml:space="preserve">「彼は応えるだろう」سيستجيب 
 サヤスタジーブ [sa-ya-stajiibu]
@@ -13595,19 +13574,19 @@
 1811 kareem mrghani </t>
         </is>
       </c>
-      <c r="B626" t="inlineStr">
+      <c r="B625" t="inlineStr">
         <is>
           <t>images/「彼は応えるだろう」_img1.jpg</t>
         </is>
       </c>
-      <c r="C626" t="inlineStr">
+      <c r="C625" t="inlineStr">
         <is>
           <t>縦書き ,現代アート</t>
         </is>
       </c>
     </row>
-    <row r="627">
-      <c r="A627" t="inlineStr">
+    <row r="626">
+      <c r="A626" t="inlineStr">
         <is>
           <t xml:space="preserve">「アラビア語が好き」
 أنا أُحبّ لُغتي
@@ -13617,19 +13596,19 @@
 2308 出典不明 </t>
         </is>
       </c>
-      <c r="B627" t="inlineStr">
+      <c r="B626" t="inlineStr">
         <is>
           <t>images/「アラビア語が好き」_img1.jpg</t>
         </is>
       </c>
-      <c r="C627" t="inlineStr">
+      <c r="C626" t="inlineStr">
         <is>
           <t>和訳 ,こども</t>
         </is>
       </c>
     </row>
-    <row r="628">
-      <c r="A628" t="inlineStr">
+    <row r="627">
+      <c r="A627" t="inlineStr">
         <is>
           <t xml:space="preserve">「私はサッカーが好きです」
 أنا أُحِبُّ كُرةَ القَدَم
@@ -13639,19 +13618,19 @@
 2109 Arabic With Nadia </t>
         </is>
       </c>
-      <c r="B628" t="inlineStr">
+      <c r="B627" t="inlineStr">
         <is>
           <t>images/「私はサッカーが好きです」_img1.jpg</t>
         </is>
       </c>
-      <c r="C628" t="inlineStr">
+      <c r="C627" t="inlineStr">
         <is>
           <t>自由時間 ,例文</t>
         </is>
       </c>
     </row>
-    <row r="629">
-      <c r="A629" t="inlineStr">
+    <row r="628">
+      <c r="A628" t="inlineStr">
         <is>
           <t xml:space="preserve">「これ、私の眼鏡じゃありません」
 هٰذِهِ لَيْسَتْ نَظَّارَاتِي
@@ -13661,19 +13640,19 @@
 2509 </t>
         </is>
       </c>
-      <c r="B629" t="inlineStr">
+      <c r="B628" t="inlineStr">
         <is>
           <t>images/「これ、私の眼鏡じゃありません」_img1.jpg</t>
         </is>
       </c>
-      <c r="C629" t="inlineStr">
+      <c r="C628" t="inlineStr">
         <is>
           <t>あらびあや</t>
         </is>
       </c>
     </row>
-    <row r="630">
-      <c r="A630" t="inlineStr">
+    <row r="629">
+      <c r="A629" t="inlineStr">
         <is>
           <t xml:space="preserve">「我らも米を食います」
 نحن أيضاً نأكل الأرز
@@ -13683,19 +13662,19 @@
 1809 </t>
         </is>
       </c>
-      <c r="B630" t="inlineStr">
+      <c r="B629" t="inlineStr">
         <is>
           <t>images/「我らも米を食います」_img1.jpg</t>
         </is>
       </c>
-      <c r="C630" t="inlineStr">
+      <c r="C629" t="inlineStr">
         <is>
           <t>あらびあや</t>
         </is>
       </c>
     </row>
-    <row r="631">
-      <c r="A631" t="inlineStr">
+    <row r="630">
+      <c r="A630" t="inlineStr">
         <is>
           <t xml:space="preserve">「ひとりでできるもん！」
 أنا أستطيع أن أفعله وحدي
@@ -13704,19 +13683,19 @@
 2105 </t>
         </is>
       </c>
-      <c r="B631" t="inlineStr">
+      <c r="B630" t="inlineStr">
         <is>
           <t>images/「ひとりでできるもん！」_img1.jpg</t>
         </is>
       </c>
-      <c r="C631" t="inlineStr">
+      <c r="C630" t="inlineStr">
         <is>
           <t>あらびあや</t>
         </is>
       </c>
     </row>
-    <row r="632">
-      <c r="A632" t="inlineStr">
+    <row r="631">
+      <c r="A631" t="inlineStr">
         <is>
           <t xml:space="preserve">「恋しくないと言っている時は恋しい」
 أُريدُك حينَ أَقُولُ أَنا لا أُريدُك
@@ -13726,19 +13705,19 @@
 2308 DARWISHISM </t>
         </is>
       </c>
-      <c r="B632" t="inlineStr">
+      <c r="B631" t="inlineStr">
         <is>
           <t>images/「恋しくないと言っている時は恋しい」_img1.jpg</t>
         </is>
       </c>
-      <c r="C632" t="inlineStr">
+      <c r="C631" t="inlineStr">
         <is>
           <t>本音 ,恋愛</t>
         </is>
       </c>
     </row>
-    <row r="633">
-      <c r="A633" t="inlineStr">
+    <row r="632">
+      <c r="A632" t="inlineStr">
         <is>
           <t xml:space="preserve">「私は〜する」
 ⁦「着る」：( أنا ألبس )['ana 'a-lbas]⁩
@@ -13749,19 +13728,19 @@
 2109 RABIE </t>
         </is>
       </c>
-      <c r="B633" t="inlineStr">
+      <c r="B632" t="inlineStr">
         <is>
           <t>images/「私は〜する」_img1.jpg,images/「私は〜する」_img2.jpg,images/「私は〜する」_img3.jpg,images/「私は〜する」_img4.jpg</t>
         </is>
       </c>
-      <c r="C633" t="inlineStr">
+      <c r="C632" t="inlineStr">
         <is>
           <t>動詞 ,絵本</t>
         </is>
       </c>
     </row>
-    <row r="634">
-      <c r="A634" t="inlineStr">
+    <row r="633">
+      <c r="A633" t="inlineStr">
         <is>
           <t xml:space="preserve">「彼は完璧ではない。私は彼の欠点については目をつむった」
 هو ليس كامل. أنا أعميت نفسي عن سيئاته
@@ -13770,19 +13749,19 @@
 2308 _NOHA </t>
         </is>
       </c>
-      <c r="B634" t="inlineStr">
+      <c r="B633" t="inlineStr">
         <is>
           <t>images/「彼は完璧ではない。私は彼の欠点につい_img1.jpg</t>
         </is>
       </c>
-      <c r="C634" t="inlineStr">
+      <c r="C633" t="inlineStr">
         <is>
           <t>愛 ,寛容</t>
         </is>
       </c>
     </row>
-    <row r="635">
-      <c r="A635" t="inlineStr">
+    <row r="634">
+      <c r="A634" t="inlineStr">
         <is>
           <t xml:space="preserve">「この子トラは検疫期間中に生まれた」
 صغير النمر هذا ولد في زمن الحجر الصحي
@@ -13791,19 +13770,19 @@
 2310 https://www.akhbaralaan.net/?p=434924 </t>
         </is>
       </c>
-      <c r="B635" t="inlineStr">
+      <c r="B634" t="inlineStr">
         <is>
           <t>images/「この子トラは検疫期間中に生まれた」_img1.jpg</t>
         </is>
       </c>
-      <c r="C635" t="inlineStr">
+      <c r="C634" t="inlineStr">
         <is>
           <t>Covid ,メキシコ</t>
         </is>
       </c>
     </row>
-    <row r="636">
-      <c r="A636" t="inlineStr">
+    <row r="635">
+      <c r="A635" t="inlineStr">
         <is>
           <t xml:space="preserve">「睡眠の素晴らしさに匹敵するものは無い！」
 وجمال النوم ليس له مثيل
@@ -13812,19 +13791,19 @@
 2308 arabzy tumblr </t>
         </is>
       </c>
-      <c r="B636" t="inlineStr">
+      <c r="B635" t="inlineStr">
         <is>
           <t>images/「睡眠の素晴らしさに匹敵するものは無い_img1.jpg</t>
         </is>
       </c>
-      <c r="C636" t="inlineStr">
+      <c r="C635" t="inlineStr">
         <is>
           <t>オフトゥン ,おやすみ</t>
         </is>
       </c>
     </row>
-    <row r="637">
-      <c r="A637" t="inlineStr">
+    <row r="636">
+      <c r="A636" t="inlineStr">
         <is>
           <t xml:space="preserve">「大器晩成」
 الأشياء العظيمة تأخذ وقت
@@ -13834,19 +13813,19 @@
 2109 出典不明 </t>
         </is>
       </c>
-      <c r="B637" t="inlineStr">
+      <c r="B636" t="inlineStr">
         <is>
           <t>images/「大器晩成」_img1.jpg</t>
         </is>
       </c>
-      <c r="C637" t="inlineStr">
+      <c r="C636" t="inlineStr">
         <is>
           <t>ことわざ ,和訳</t>
         </is>
       </c>
     </row>
-    <row r="638">
-      <c r="A638" t="inlineStr">
+    <row r="637">
+      <c r="A637" t="inlineStr">
         <is>
           <t xml:space="preserve">「コーヒーは急には飲まれない」
 القهْوة لا تشرَب عَلى عَجلْ
@@ -13857,19 +13836,19 @@
 2012 Ahmed Madyan </t>
         </is>
       </c>
-      <c r="B638" t="inlineStr">
+      <c r="B637" t="inlineStr">
         <is>
           <t>images/「コーヒーは急には飲まれない」_img1.jpg</t>
         </is>
       </c>
-      <c r="C638" t="inlineStr">
+      <c r="C637" t="inlineStr">
         <is>
           <t>名言</t>
         </is>
       </c>
     </row>
-    <row r="639">
-      <c r="A639" t="inlineStr">
+    <row r="638">
+      <c r="A638" t="inlineStr">
         <is>
           <t xml:space="preserve">「成功者は情報共有している」
 الناجحون يشاركون المعلومة
@@ -13879,19 +13858,19 @@
 2109 出典不明 </t>
         </is>
       </c>
-      <c r="B639" t="inlineStr">
+      <c r="B638" t="inlineStr">
         <is>
           <t>images/「成功者は情報共有している」_img1.jpg</t>
         </is>
       </c>
-      <c r="C639" t="inlineStr">
+      <c r="C638" t="inlineStr">
         <is>
           <t>鳥 ,シェア</t>
         </is>
       </c>
     </row>
-    <row r="640">
-      <c r="A640" t="inlineStr">
+    <row r="639">
+      <c r="A639" t="inlineStr">
         <is>
           <t xml:space="preserve">「間違いで賢くなる、痛みで強くなる」
 الأخطاء تجعلك حكيمًا، والألم يجعلك قويًا
@@ -13900,19 +13879,19 @@
 2111 https://alaminin.blogspot.com/2020/03/blog-post_6.html </t>
         </is>
       </c>
-      <c r="B640" t="inlineStr">
+      <c r="B639" t="inlineStr">
         <is>
           <t>images/「間違いで賢くなる、痛みで強くなる」_img1.jpg</t>
         </is>
       </c>
-      <c r="C640" t="inlineStr">
+      <c r="C639" t="inlineStr">
         <is>
           <t>名言</t>
         </is>
       </c>
     </row>
-    <row r="641">
-      <c r="A641" t="inlineStr">
+    <row r="640">
+      <c r="A640" t="inlineStr">
         <is>
           <t xml:space="preserve">「何事も永遠には続かない」
 لا شيء يبقى للأبد
@@ -13922,19 +13901,19 @@
 2308 KiTeLetZ </t>
         </is>
       </c>
-      <c r="B641" t="inlineStr">
+      <c r="B640" t="inlineStr">
         <is>
           <t>images/「何事も永遠には続かない」_img1.jpg</t>
         </is>
       </c>
-      <c r="C641" t="inlineStr">
+      <c r="C640" t="inlineStr">
         <is>
           <t>変化 ,名言</t>
         </is>
       </c>
     </row>
-    <row r="642">
-      <c r="A642" t="inlineStr">
+    <row r="641">
+      <c r="A641" t="inlineStr">
         <is>
           <t xml:space="preserve">「惑星地球はあなた方を歓迎します」
 كوكب الارض يرحّب بكم
@@ -13944,19 +13923,19 @@
 1811 iN49R </t>
         </is>
       </c>
-      <c r="B642" t="inlineStr">
+      <c r="B641" t="inlineStr">
         <is>
           <t>images/「惑星地球はあなた方を歓迎します」_img1.jpg</t>
         </is>
       </c>
-      <c r="C642" t="inlineStr">
+      <c r="C641" t="inlineStr">
         <is>
           <t>宇宙 ,人類</t>
         </is>
       </c>
     </row>
-    <row r="643">
-      <c r="A643" t="inlineStr">
+    <row r="642">
+      <c r="A642" t="inlineStr">
         <is>
           <t xml:space="preserve">「自分を信じなさい。人の言うことは尽きないのだから」
 ثق بنفسك فكلام الناس لا ينتهي
@@ -13965,19 +13944,19 @@
 2105 出典不明 </t>
         </is>
       </c>
-      <c r="B643" t="inlineStr">
+      <c r="B642" t="inlineStr">
         <is>
           <t>images/「自分を信じなさい。人の言うことは尽き_img1.jpg</t>
         </is>
       </c>
-      <c r="C643" t="inlineStr">
+      <c r="C642" t="inlineStr">
         <is>
           <t>自信 ,無視</t>
         </is>
       </c>
     </row>
-    <row r="644">
-      <c r="A644" t="inlineStr">
+    <row r="643">
+      <c r="A643" t="inlineStr">
         <is>
           <t xml:space="preserve">「弟が歩くぞ」أخي الصغير يمشي
 アキ_ッサギール・ヤムシー ['aKh-i ^_saGhiiru ya-mShii]
@@ -13986,19 +13965,19 @@
 2308 gulfkids com http://www.gulfkids.com/ar/book48-1909.htm </t>
         </is>
       </c>
-      <c r="B644" t="inlineStr">
+      <c r="B643" t="inlineStr">
         <is>
           <t>images/「弟が歩くぞ」_img1.jpg</t>
         </is>
       </c>
-      <c r="C644" t="inlineStr">
+      <c r="C643" t="inlineStr">
         <is>
           <t>兄弟 ,絵本</t>
         </is>
       </c>
     </row>
-    <row r="645">
-      <c r="A645" t="inlineStr">
+    <row r="644">
+      <c r="A644" t="inlineStr">
         <is>
           <t xml:space="preserve">花より団子おおお（違う）
 「誰もふさわしくない」[laa 'aHada ya-staHiqqu]
@@ -14006,19 +13985,19 @@
 2308 https://twitter.com/NatGeoMagArab/status/1370041991317233664 </t>
         </is>
       </c>
-      <c r="B645" t="inlineStr">
+      <c r="B644" t="inlineStr">
         <is>
           <t>images/花より団子おおお（違う）_img1.jpg</t>
         </is>
       </c>
-      <c r="C645" t="inlineStr">
+      <c r="C644" t="inlineStr">
         <is>
           <t>手書き語学 ,アラビア語 ,キノボリカンガルー</t>
         </is>
       </c>
     </row>
-    <row r="646">
-      <c r="A646" t="inlineStr">
+    <row r="645">
+      <c r="A645" t="inlineStr">
         <is>
           <t xml:space="preserve">「幸せな人生には弱い記憶力が必要」
 الحياة السعيدة تتطلب ذاكرة ضعيفة
@@ -14027,19 +14006,19 @@
 2012 出典不明 </t>
         </is>
       </c>
-      <c r="B646" t="inlineStr">
+      <c r="B645" t="inlineStr">
         <is>
           <t>images/「幸せな人生には弱い記憶力が必要」_img1.jpg</t>
         </is>
       </c>
-      <c r="C646" t="inlineStr">
+      <c r="C645" t="inlineStr">
         <is>
           <t>前向き</t>
         </is>
       </c>
     </row>
-    <row r="647">
-      <c r="A647" t="inlineStr">
+    <row r="646">
+      <c r="A646" t="inlineStr">
         <is>
           <t xml:space="preserve">「このパンダは私たちに、幸せは単純なことの中に隠れているのだと教えている」
 دب "الباندا" هذا يؤكد لنا أن السعادة تكمن في أبسط الأشياء
@@ -14047,19 +14026,19 @@
 2308 https://twitter.com/NatGeoMagArab/status/1309938472065486848 </t>
         </is>
       </c>
-      <c r="B647" t="inlineStr">
+      <c r="B646" t="inlineStr">
         <is>
           <t>images/「このパンダは私たちに、幸せは単純なこ.png</t>
         </is>
       </c>
-      <c r="C647" t="inlineStr">
+      <c r="C646" t="inlineStr">
         <is>
           <t>パンダ ,雪</t>
         </is>
       </c>
     </row>
-    <row r="648">
-      <c r="A648" t="inlineStr">
+    <row r="647">
+      <c r="A647" t="inlineStr">
         <is>
           <t xml:space="preserve">「良い時間は速く過ぎる」
 الأوقات الجميلة تمر بسرعة
@@ -14069,19 +14048,19 @@
 1810 Nasser.Tumblr </t>
         </is>
       </c>
-      <c r="B648" t="inlineStr">
+      <c r="B647" t="inlineStr">
         <is>
           <t>images/「良い時間は速く過ぎる」_img1.jpg</t>
         </is>
       </c>
-      <c r="C648" t="inlineStr">
+      <c r="C647" t="inlineStr">
         <is>
           <t>相対論 ,心理学</t>
         </is>
       </c>
     </row>
-    <row r="649">
-      <c r="A649" t="inlineStr">
+    <row r="648">
+      <c r="A648" t="inlineStr">
         <is>
           <t xml:space="preserve">「今日が始まりかもしれない」
 كل يوم ممكن يكون بداية
@@ -14091,19 +14070,19 @@
 2308 Ahmed Madyan </t>
         </is>
       </c>
-      <c r="B649" t="inlineStr">
+      <c r="B648" t="inlineStr">
         <is>
           <t>images/「今日が始まりかもしれない」_img1.jpg</t>
         </is>
       </c>
-      <c r="C649" t="inlineStr">
+      <c r="C648" t="inlineStr">
         <is>
           <t>吉日 ,開始</t>
         </is>
       </c>
     </row>
-    <row r="650">
-      <c r="A650" t="inlineStr">
+    <row r="649">
+      <c r="A649" t="inlineStr">
         <is>
           <t xml:space="preserve">「ヌール、歯医者さんに行く」
 نور تذهب إلى طبيب الأسنان
@@ -14113,19 +14092,19 @@
 2109 RABIE </t>
         </is>
       </c>
-      <c r="B650" t="inlineStr">
+      <c r="B649" t="inlineStr">
         <is>
           <t>images/「ヌール、歯医者さんに行く」_img1.jpg</t>
         </is>
       </c>
-      <c r="C650" t="inlineStr">
+      <c r="C649" t="inlineStr">
         <is>
           <t>絵本 ,歯科</t>
         </is>
       </c>
     </row>
-    <row r="651">
-      <c r="A651" t="inlineStr">
+    <row r="650">
+      <c r="A650" t="inlineStr">
         <is>
           <t xml:space="preserve">「ラヤンはねむれない」
 لَيان لا تَسْتَطيعُ أَنْ تَنام
@@ -14134,19 +14113,19 @@
 2308 出典不明 </t>
         </is>
       </c>
-      <c r="B651" t="inlineStr">
+      <c r="B650" t="inlineStr">
         <is>
           <t>images/「ラヤンはねむれない」_img1.jpg</t>
         </is>
       </c>
-      <c r="C651" t="inlineStr">
+      <c r="C650" t="inlineStr">
         <is>
           <t>絵本 ,不眠症</t>
         </is>
       </c>
     </row>
-    <row r="652">
-      <c r="A652" t="inlineStr">
+    <row r="651">
+      <c r="A651" t="inlineStr">
         <is>
           <t xml:space="preserve">「クネイトラ県、蜂の巣を約60%失う」
 القنيطرة تفقد حوالي 60 % من خلايا نحلها
@@ -14154,19 +14133,19 @@
 2403 nabd com/t/101679025-fb119f </t>
         </is>
       </c>
-      <c r="B652" t="inlineStr">
+      <c r="B651" t="inlineStr">
         <is>
           <t>images/「クネイトラ県、蜂の巣を約60%失う」_img1.jpg</t>
         </is>
       </c>
-      <c r="C652" t="inlineStr">
+      <c r="C651" t="inlineStr">
         <is>
           <t>蜂の巣 ,パーセント</t>
         </is>
       </c>
     </row>
-    <row r="653">
-      <c r="A653" t="inlineStr">
+    <row r="652">
+      <c r="A652" t="inlineStr">
         <is>
           <t xml:space="preserve">「結ばれしター」ة
 ⁦( تاء مربوطة )[taa' marbuu_ta]：ت「ター」( تاء )[taa']・「結ばれている」( مربوط )[marbuu_t]：( ربط )【結】⁩
@@ -14174,19 +14153,19 @@
 2308 出典不明 </t>
         </is>
       </c>
-      <c r="B653" t="inlineStr">
+      <c r="B652" t="inlineStr">
         <is>
           <t>images/「結ばれしター」_img1.jpg</t>
         </is>
       </c>
-      <c r="C653" t="inlineStr">
+      <c r="C652" t="inlineStr">
         <is>
           <t>アラビア文字 ,顔</t>
         </is>
       </c>
     </row>
-    <row r="654">
-      <c r="A654" t="inlineStr">
+    <row r="653">
+      <c r="A653" t="inlineStr">
         <is>
           <t xml:space="preserve">「忙しい」مشغول
 マシュグール [maShGhuul]
@@ -14195,19 +14174,19 @@
 1811 skyshinichi.instagram </t>
         </is>
       </c>
-      <c r="B654" t="inlineStr">
+      <c r="B653" t="inlineStr">
         <is>
           <t>images/「忙しい」_img1.jpg</t>
         </is>
       </c>
-      <c r="C654" t="inlineStr">
+      <c r="C653" t="inlineStr">
         <is>
           <t>スティッチ ,残業</t>
         </is>
       </c>
     </row>
-    <row r="655">
-      <c r="A655" t="inlineStr">
+    <row r="654">
+      <c r="A654" t="inlineStr">
         <is>
           <t xml:space="preserve">「駐車禁止」ممنوع الوقوف
 マムヌーア・アルウクーフ [mamnuu* al-wuquuf]
@@ -14216,19 +14195,19 @@
 2106 出典不明 </t>
         </is>
       </c>
-      <c r="B655" t="inlineStr">
+      <c r="B654" t="inlineStr">
         <is>
           <t>images/「駐車禁止」_img1.jpg</t>
         </is>
       </c>
-      <c r="C655" t="inlineStr">
+      <c r="C654" t="inlineStr">
         <is>
           <t>標識 ,ジョーク</t>
         </is>
       </c>
     </row>
-    <row r="656">
-      <c r="A656" t="inlineStr">
+    <row r="655">
+      <c r="A655" t="inlineStr">
         <is>
           <t xml:space="preserve">「一人ひとりが責任を」
 كُلنا مسؤول
@@ -14238,19 +14217,19 @@
 2308 covid19awareness sa </t>
         </is>
       </c>
-      <c r="B656" t="inlineStr">
+      <c r="B655" t="inlineStr">
         <is>
           <t>images/「一人ひとりが責任を」_img1.jpg</t>
         </is>
       </c>
-      <c r="C656" t="inlineStr">
+      <c r="C655" t="inlineStr">
         <is>
           <t>Covid ,感染拡大防止</t>
         </is>
       </c>
     </row>
-    <row r="657">
-      <c r="A657" t="inlineStr">
+    <row r="656">
+      <c r="A656" t="inlineStr">
         <is>
           <t xml:space="preserve">「おめでとうございます」مبروك
 マブルーク [mabruuk]
@@ -14259,19 +14238,19 @@
 2308 </t>
         </is>
       </c>
-      <c r="B657" t="inlineStr">
+      <c r="B656" t="inlineStr">
         <is>
           <t>images/「おめでとうございます」_img1.jpg</t>
         </is>
       </c>
-      <c r="C657" t="inlineStr">
+      <c r="C656" t="inlineStr">
         <is>
           <t>詐欺 ,広告</t>
         </is>
       </c>
     </row>
-    <row r="658">
-      <c r="A658" t="inlineStr">
+    <row r="657">
+      <c r="A657" t="inlineStr">
         <is>
           <t xml:space="preserve">「手書きフォント」
 خط مكتوب باليد
@@ -14281,19 +14260,19 @@
 1809 FahdAlFraikh Behance </t>
         </is>
       </c>
-      <c r="B658" t="inlineStr">
+      <c r="B657" t="inlineStr">
         <is>
           <t>images/「手書きフォント」_img1.jpg</t>
         </is>
       </c>
-      <c r="C658" t="inlineStr">
+      <c r="C657" t="inlineStr">
         <is>
           <t>可愛いフォント ,筆跡</t>
         </is>
       </c>
     </row>
-    <row r="659">
-      <c r="A659" t="inlineStr">
+    <row r="658">
+      <c r="A658" t="inlineStr">
         <is>
           <t xml:space="preserve">「開かれたターと結ばれたター」
 التاء المفتوحة والمربوطة
@@ -14303,19 +14282,19 @@
 2109 slideshare.net </t>
         </is>
       </c>
-      <c r="B659" t="inlineStr">
+      <c r="B658" t="inlineStr">
         <is>
           <t>images/「開かれたターと結ばれたター」_img1.jpg</t>
         </is>
       </c>
-      <c r="C659" t="inlineStr">
+      <c r="C658" t="inlineStr">
         <is>
           <t>アラビア文字 ,スマイリー</t>
         </is>
       </c>
     </row>
-    <row r="660">
-      <c r="A660" t="inlineStr">
+    <row r="659">
+      <c r="A659" t="inlineStr">
         <is>
           <t xml:space="preserve">「このラマは誇らしげにして立っている」
 تقف هذه اللاما مزهوة بنفسها
@@ -14323,19 +14302,19 @@
 2410 https://twitter.com/NatGeoMagArab/status/1597485552965935104 </t>
         </is>
       </c>
-      <c r="B660" t="inlineStr">
+      <c r="B659" t="inlineStr">
         <is>
           <t>images/「このラマは誇らしげにして立っている」_img1.jpg</t>
         </is>
       </c>
-      <c r="C660" t="inlineStr">
+      <c r="C659" t="inlineStr">
         <is>
           <t>手書き語学 ,アラビア語 ,マチュピチュ遺跡</t>
         </is>
       </c>
     </row>
-    <row r="661">
-      <c r="A661" t="inlineStr">
+    <row r="660">
+      <c r="A660" t="inlineStr">
         <is>
           <t xml:space="preserve">「小さな生き物にしては危険な名前だ」
 اسم خطير لمخلوق صغير
@@ -14344,19 +14323,19 @@
 2308 https://twitter.com/NatGeoMagArab/status/1495035772071669760 </t>
         </is>
       </c>
-      <c r="B661" t="inlineStr">
+      <c r="B660" t="inlineStr">
         <is>
           <t>images/「小さな生き物にしては危険な名前だ」_img1.jpg</t>
         </is>
       </c>
-      <c r="C661" t="inlineStr">
+      <c r="C660" t="inlineStr">
         <is>
           <t>有袋類 ,タスマニアデビル</t>
         </is>
       </c>
     </row>
-    <row r="662">
-      <c r="A662" t="inlineStr">
+    <row r="661">
+      <c r="A661" t="inlineStr">
         <is>
           <t xml:space="preserve">「こわれている」مكسر
 ムカッサル [mukassar]
@@ -14364,19 +14343,19 @@
 2105 behance Written-Visuals </t>
         </is>
       </c>
-      <c r="B662" t="inlineStr">
+      <c r="B661" t="inlineStr">
         <is>
           <t>images/「こわれている」_img1.jpg</t>
         </is>
       </c>
-      <c r="C662" t="inlineStr">
+      <c r="C661" t="inlineStr">
         <is>
           <t>バラバラ ,デザイン</t>
         </is>
       </c>
     </row>
-    <row r="663">
-      <c r="A663" t="inlineStr">
+    <row r="662">
+      <c r="A662" t="inlineStr">
         <is>
           <t xml:space="preserve">「早起きする方法」
 كيف تنهض مُبكّرًا
@@ -14386,19 +14365,19 @@
 2308 Funders and Founders </t>
         </is>
       </c>
-      <c r="B663" t="inlineStr">
+      <c r="B662" t="inlineStr">
         <is>
           <t>images/「早起きする方法」_img1.jpg</t>
         </is>
       </c>
-      <c r="C663" t="inlineStr">
+      <c r="C662" t="inlineStr">
         <is>
           <t>オフトゥン ,寝起き</t>
         </is>
       </c>
     </row>
-    <row r="664">
-      <c r="A664" t="inlineStr">
+    <row r="663">
+      <c r="A663" t="inlineStr">
         <is>
           <t xml:space="preserve">「アラブ・デザイン文字展覧会」
 معرض لتخطيط الحرف العربي
@@ -14408,19 +14387,19 @@
 2109 arabic lettering exhibition </t>
         </is>
       </c>
-      <c r="B664" t="inlineStr">
+      <c r="B663" t="inlineStr">
         <is>
           <t>images/「アラブ・デザイン文字展覧会」_img1.jpg</t>
         </is>
       </c>
-      <c r="C664" t="inlineStr">
+      <c r="C663" t="inlineStr">
         <is>
           <t>ポスター</t>
         </is>
       </c>
     </row>
-    <row r="665">
-      <c r="A665" t="inlineStr">
+    <row r="664">
+      <c r="A664" t="inlineStr">
         <is>
           <t xml:space="preserve">「名探偵コナン」المحقق كونان
 アルムハッキク・コナン [al-muHaqqiq Conan]
@@ -14429,19 +14408,19 @@
 1809 wikipedia </t>
         </is>
       </c>
-      <c r="B665" t="inlineStr">
+      <c r="B664" t="inlineStr">
         <is>
           <t>images/「名探偵コナン」_img1.jpg</t>
         </is>
       </c>
-      <c r="C665" t="inlineStr">
+      <c r="C664" t="inlineStr">
         <is>
           <t>江戸川コナン ,ロゴ</t>
         </is>
       </c>
     </row>
-    <row r="666">
-      <c r="A666" t="inlineStr">
+    <row r="665">
+      <c r="A665" t="inlineStr">
         <is>
           <t xml:space="preserve">「イードおめでとう」عيد مبارك
 イード・ムバーラク [*iid mubaarak]
@@ -14449,19 +14428,19 @@
 2308 出典不明 </t>
         </is>
       </c>
-      <c r="B666" t="inlineStr">
+      <c r="B665" t="inlineStr">
         <is>
           <t>images/「イードおめでとう」_img1.jpg</t>
         </is>
       </c>
-      <c r="C666" t="inlineStr">
+      <c r="C665" t="inlineStr">
         <is>
           <t>عيد ,アラビア語</t>
         </is>
       </c>
     </row>
-    <row r="667">
-      <c r="A667" t="inlineStr">
+    <row r="666">
+      <c r="A666" t="inlineStr">
         <is>
           <t xml:space="preserve">「戦士」محارب
 ムハーリブ [muHaarib]
@@ -14470,19 +14449,19 @@
 1809 abudinges.tumblr </t>
         </is>
       </c>
-      <c r="B667" t="inlineStr">
+      <c r="B666" t="inlineStr">
         <is>
           <t>images/「戦士」_img1.jpg</t>
         </is>
       </c>
-      <c r="C667" t="inlineStr">
+      <c r="C666" t="inlineStr">
         <is>
           <t>ロゴ ,赤</t>
         </is>
       </c>
     </row>
-    <row r="668">
-      <c r="A668" t="inlineStr">
+    <row r="667">
+      <c r="A667" t="inlineStr">
         <is>
           <t xml:space="preserve">「ライブ」بث مباشر
 バッス・ムバーシル [ba^Th(un) mubaaShir(un)]
@@ -14491,19 +14470,19 @@
 2308 beIN SPORTS </t>
         </is>
       </c>
-      <c r="B668" t="inlineStr">
+      <c r="B667" t="inlineStr">
         <is>
           <t>images/「ライブ」_img1.jpg</t>
         </is>
       </c>
-      <c r="C668" t="inlineStr">
+      <c r="C667" t="inlineStr">
         <is>
           <t xml:space="preserve">生放送 ,試合 </t>
         </is>
       </c>
     </row>
-    <row r="669">
-      <c r="A669" t="inlineStr">
+    <row r="668">
+      <c r="A668" t="inlineStr">
         <is>
           <t xml:space="preserve">「信者」مُؤْمِنٌ
 ムッミン [mu'min(un)]
@@ -14512,19 +14491,19 @@
 2106 出典不明 </t>
         </is>
       </c>
-      <c r="B669" t="inlineStr">
+      <c r="B668" t="inlineStr">
         <is>
           <t>images/「信者」_img1.jpg</t>
         </is>
       </c>
-      <c r="C669" t="inlineStr">
+      <c r="C668" t="inlineStr">
         <is>
           <t>明暗 ,信仰</t>
         </is>
       </c>
     </row>
-    <row r="670">
-      <c r="A670" t="inlineStr">
+    <row r="669">
+      <c r="A669" t="inlineStr">
         <is>
           <t xml:space="preserve">「開⇔閉」
 مفتوح
@@ -14535,19 +14514,19 @@
 2312 Hussein Safina, behance </t>
         </is>
       </c>
-      <c r="B670" t="inlineStr">
+      <c r="B669" t="inlineStr">
         <is>
           <t>images/「開⇔閉」_img1.jpg</t>
         </is>
       </c>
-      <c r="C670" t="inlineStr">
+      <c r="C669" t="inlineStr">
         <is>
           <t>オープンマインド ,トグル</t>
         </is>
       </c>
     </row>
-    <row r="671">
-      <c r="A671" t="inlineStr">
+    <row r="670">
+      <c r="A670" t="inlineStr">
         <is>
           <t xml:space="preserve">「予想外な結末！」
 نهاية غير متوقعة
@@ -14555,19 +14534,19 @@
 2308 https://twitter.com/NatGeoMagArab/status/1159011433444593665 </t>
         </is>
       </c>
-      <c r="B671" t="inlineStr">
+      <c r="B670" t="inlineStr">
         <is>
           <t>images/「予想外な結末！」_img1.jpg</t>
         </is>
       </c>
-      <c r="C671" t="inlineStr">
+      <c r="C670" t="inlineStr">
         <is>
           <t>手書き語学 ,アラビア語 ,ウサギ</t>
         </is>
       </c>
     </row>
-    <row r="672">
-      <c r="A672" t="inlineStr">
+    <row r="671">
+      <c r="A671" t="inlineStr">
         <is>
           <t xml:space="preserve">「ベイルート・アニメイテッド」
 بیروت متحرّکة
@@ -14577,19 +14556,19 @@
 2308 arabic_script Instagram </t>
         </is>
       </c>
-      <c r="B672" t="inlineStr">
+      <c r="B671" t="inlineStr">
         <is>
           <t>images/「ベイルート・アニメイテッド」_img1.jpg</t>
         </is>
       </c>
-      <c r="C672" t="inlineStr">
+      <c r="C671" t="inlineStr">
         <is>
           <t>アニメ ,レバノン</t>
         </is>
       </c>
     </row>
-    <row r="673">
-      <c r="A673" t="inlineStr">
+    <row r="672">
+      <c r="A672" t="inlineStr">
         <is>
           <t xml:space="preserve">「夢みれば叶う」
 كُلُّ مُتَوَقَّعٍ آتٍ
@@ -14599,19 +14578,19 @@
 2108 Ahmed Madyan </t>
         </is>
       </c>
-      <c r="B673" t="inlineStr">
+      <c r="B672" t="inlineStr">
         <is>
           <t>images/「夢みれば叶う」_img1.jpg</t>
         </is>
       </c>
-      <c r="C673" t="inlineStr">
+      <c r="C672" t="inlineStr">
         <is>
           <t>希望 ,ドリカム</t>
         </is>
       </c>
     </row>
-    <row r="674">
-      <c r="A674" t="inlineStr">
+    <row r="673">
+      <c r="A673" t="inlineStr">
         <is>
           <t xml:space="preserve">「もし両者が人間のように鎧で武装して戦いに突入したら」
 لو خاضا معاركهما متسلحين بالدروع على غرار البش
@@ -14619,19 +14598,19 @@
 2404 https://x.com/NatGeoMagArab/status/1759284149456945464 </t>
         </is>
       </c>
-      <c r="B674" t="inlineStr">
+      <c r="B673" t="inlineStr">
         <is>
           <t>images/「もし両者が人間のように鎧で武装して戦_img1.jpg,images/「もし両者が人間のように鎧で武装して戦_img2.jpg</t>
         </is>
       </c>
-      <c r="C674" t="inlineStr">
+      <c r="C673" t="inlineStr">
         <is>
           <t>手書き語学 ,アラビア語 ,猫</t>
         </is>
       </c>
     </row>
-    <row r="675">
-      <c r="A675" t="inlineStr">
+    <row r="674">
+      <c r="A674" t="inlineStr">
         <is>
           <t xml:space="preserve">「全ては結びついている」
 كل شيء مترابط
@@ -14641,19 +14620,19 @@
 2308 Ahmed Madyan https://twitter.com/madyco22/status/1451990828298166273 </t>
         </is>
       </c>
-      <c r="B675" t="inlineStr">
+      <c r="B674" t="inlineStr">
         <is>
           <t>images/「全ては結びついている」_img1.jpg</t>
         </is>
       </c>
-      <c r="C675" t="inlineStr">
+      <c r="C674" t="inlineStr">
         <is>
           <t>一筆書き ,デザイン</t>
         </is>
       </c>
     </row>
-    <row r="676">
-      <c r="A676" t="inlineStr">
+    <row r="675">
+      <c r="A675" t="inlineStr">
         <is>
           <t xml:space="preserve">「初心者のためのスケッチトレーニング」
 تعليم الرسم للمبتدئين
@@ -14663,19 +14642,19 @@
 2308 free-bookspdf com </t>
         </is>
       </c>
-      <c r="B676" t="inlineStr">
+      <c r="B675" t="inlineStr">
         <is>
           <t>images/「初心者のためのスケッチトレーニング」_img1.jpg</t>
         </is>
       </c>
-      <c r="C676" t="inlineStr">
+      <c r="C675" t="inlineStr">
         <is>
           <t>イラスト ,絵</t>
         </is>
       </c>
     </row>
-    <row r="677">
-      <c r="A677" t="inlineStr">
+    <row r="676">
+      <c r="A676" t="inlineStr">
         <is>
           <t xml:space="preserve">「初心者のためのスルス体書道トレーニング」
 تعليم خط الثلث للمبتدئين
@@ -14685,19 +14664,19 @@
 2308 出典不明 </t>
         </is>
       </c>
-      <c r="B677" t="inlineStr">
+      <c r="B676" t="inlineStr">
         <is>
           <t>images/「初心者のためのスルス体書道トレーニン_img1.jpg</t>
         </is>
       </c>
-      <c r="C677" t="inlineStr">
+      <c r="C676" t="inlineStr">
         <is>
           <t>書道</t>
         </is>
       </c>
     </row>
-    <row r="678">
-      <c r="A678" t="inlineStr">
+    <row r="677">
+      <c r="A677" t="inlineStr">
         <is>
           <t xml:space="preserve">「笑顔でいなさい」خليك مبتسم
 カッリーク・ムブタスィム [Khallii-k mubtasim]
@@ -14706,19 +14685,19 @@
 2308 https://tmblr.co/Zj9tguYLXBvC </t>
         </is>
       </c>
-      <c r="B678" t="inlineStr">
+      <c r="B677" t="inlineStr">
         <is>
           <t>images/「笑顔でいなさい」_img1.jpg</t>
         </is>
       </c>
-      <c r="C678" t="inlineStr">
+      <c r="C677" t="inlineStr">
         <is>
           <t>スマイル ,名言</t>
         </is>
       </c>
     </row>
-    <row r="679">
-      <c r="A679" t="inlineStr">
+    <row r="678">
+      <c r="A678" t="inlineStr">
         <is>
           <t xml:space="preserve">自動車メーカー
 ⁦・「TOYOTA」( تويوتا )⁩
@@ -14730,19 +14709,19 @@
 2308 syarah com </t>
         </is>
       </c>
-      <c r="B679" t="inlineStr">
+      <c r="B678" t="inlineStr">
         <is>
           <t>images/自動車メーカー_img1.jpg,images/自動車メーカー_img2.jpg,images/自動車メーカー_img3.jpg,images/自動車メーカー_img4.jpg</t>
         </is>
       </c>
-      <c r="C679" t="inlineStr">
+      <c r="C678" t="inlineStr">
         <is>
           <t>日本車 ,韓国車</t>
         </is>
       </c>
     </row>
-    <row r="680">
-      <c r="A680" t="inlineStr">
+    <row r="679">
+      <c r="A679" t="inlineStr">
         <is>
           <t xml:space="preserve">「僕たちは協力して不可能を達成するよ」
 بالتعاون نحقق المحال
@@ -14752,19 +14731,19 @@
 2109 </t>
         </is>
       </c>
-      <c r="B680" t="inlineStr">
+      <c r="B679" t="inlineStr">
         <is>
           <t>images/「僕たちは協力して不可能を達成するよ」_img1.jpg</t>
         </is>
       </c>
-      <c r="C680" t="inlineStr">
+      <c r="C679" t="inlineStr">
         <is>
           <t>無理 ,ハム太郎</t>
         </is>
       </c>
     </row>
-    <row r="681">
-      <c r="A681" t="inlineStr">
+    <row r="680">
+      <c r="A680" t="inlineStr">
         <is>
           <t xml:space="preserve">「幸せは伝染性。喜びを広めよう」
 السعادة معدية فأشع الفرح
@@ -14774,19 +14753,19 @@
 2511 instagram　com/p/fVEfxEo7Va/ </t>
         </is>
       </c>
-      <c r="B681" t="inlineStr">
+      <c r="B680" t="inlineStr">
         <is>
           <t>images/「幸せは伝染性。喜びを広めよう」_img1.jpg</t>
         </is>
       </c>
-      <c r="C681" t="inlineStr">
+      <c r="C680" t="inlineStr">
         <is>
           <t>拡散希望</t>
         </is>
       </c>
     </row>
-    <row r="682">
-      <c r="A682" t="inlineStr">
+    <row r="681">
+      <c r="A681" t="inlineStr">
         <is>
           <t xml:space="preserve">「ストレスは人間だけのものではない」
 الشعور بالتوتر ليس حكرًا على البشر
@@ -14794,19 +14773,19 @@
 2408 https://x.com/NatGeoMagArab/status/1736755816911487420 </t>
         </is>
       </c>
-      <c r="B682" t="inlineStr">
+      <c r="B681" t="inlineStr">
         <is>
           <t>images/「ストレスは人間だけのものではない」_img1.jpg</t>
         </is>
       </c>
-      <c r="C682" t="inlineStr">
+      <c r="C681" t="inlineStr">
         <is>
           <t>手書き語学 ,アラビア語 ,ストレス</t>
         </is>
       </c>
     </row>
-    <row r="683">
-      <c r="A683" t="inlineStr">
+    <row r="682">
+      <c r="A682" t="inlineStr">
         <is>
           <t xml:space="preserve">「私達は出来ます！」
 نستطيع فعلها
@@ -14816,19 +14795,19 @@
 2308 NAHARBAHIJ com </t>
         </is>
       </c>
-      <c r="B683" t="inlineStr">
+      <c r="B682" t="inlineStr">
         <is>
           <t>images/「私達は出来ます！」_img1.jpg</t>
         </is>
       </c>
-      <c r="C683" t="inlineStr">
+      <c r="C682" t="inlineStr">
         <is>
           <t>女性 ,パロディ</t>
         </is>
       </c>
     </row>
-    <row r="684">
-      <c r="A684" t="inlineStr">
+    <row r="683">
+      <c r="A683" t="inlineStr">
         <is>
           <t xml:space="preserve">「全然分からん」ولا فاهم إشي
 ウラー・ファーヒム・イシ [w-laa faahim 'iShy]
@@ -14838,19 +14817,19 @@
 2209 出典不明 </t>
         </is>
       </c>
-      <c r="B684" t="inlineStr">
+      <c r="B683" t="inlineStr">
         <is>
           <t>images/「全然分からん」_img1.jpg</t>
         </is>
       </c>
-      <c r="C684" t="inlineStr">
+      <c r="C683" t="inlineStr">
         <is>
           <t>アラビア語</t>
         </is>
       </c>
     </row>
-    <row r="685">
-      <c r="A685" t="inlineStr">
+    <row r="684">
+      <c r="A684" t="inlineStr">
         <is>
           <t xml:space="preserve">「人間は一人ひとり、特別な才がある。だから自分を他人と比べるのはやめよう」
 لكل إنسان مواهبه الخاصة 
@@ -14859,19 +14838,19 @@
 1812 Gwid3 </t>
         </is>
       </c>
-      <c r="B685" t="inlineStr">
+      <c r="B684" t="inlineStr">
         <is>
           <t>images/「人間は一人ひとり、特別な才がある。だ_img1.jpg</t>
         </is>
       </c>
-      <c r="C685" t="inlineStr">
+      <c r="C684" t="inlineStr">
         <is>
           <t>自尊 ,プライド</t>
         </is>
       </c>
     </row>
-    <row r="686">
-      <c r="A686" t="inlineStr">
+    <row r="685">
+      <c r="A685" t="inlineStr">
         <is>
           <t xml:space="preserve">「この猫は食事をシェアするのが嫌い！」
 هذه القطة لا تحب مشاركة الطعام
@@ -14880,19 +14859,19 @@
 2605 facebook com/alahram/videos/2154923608133231/ </t>
         </is>
       </c>
-      <c r="B686" t="inlineStr">
+      <c r="B685" t="inlineStr">
         <is>
           <t>images/「この猫は食事をシェアするのが嫌い！」_img1.jpg</t>
         </is>
       </c>
-      <c r="C686" t="inlineStr">
+      <c r="C685" t="inlineStr">
         <is>
           <t>猫 ,ネコ</t>
         </is>
       </c>
     </row>
-    <row r="687">
-      <c r="A687" t="inlineStr">
+    <row r="686">
+      <c r="A686" t="inlineStr">
         <is>
           <t xml:space="preserve">「怪獣との戦いでは自分が怪獣化せぬよう警戒しなさい」
 احذر عند محاربة الوحوش ألا تصبح واحدا منهم
@@ -14902,19 +14881,19 @@
 2108 warag-3nb.tumblr </t>
         </is>
       </c>
-      <c r="B687" t="inlineStr">
+      <c r="B686" t="inlineStr">
         <is>
           <t>images/「怪獣との戦いでは自分が怪獣化せぬよう_img1.jpg,images/ 「怪獣との戦いでは自分が怪獣化せぬよう_img2.jpg</t>
         </is>
       </c>
-      <c r="C687" t="inlineStr">
+      <c r="C686" t="inlineStr">
         <is>
           <t>正気 ,モンスター</t>
         </is>
       </c>
     </row>
-    <row r="688">
-      <c r="A688" t="inlineStr">
+    <row r="687">
+      <c r="A687" t="inlineStr">
         <is>
           <t xml:space="preserve">「錯視アート」فن الخداع البصري
 ファンヌ_ルヒダーイ_ルバサリーイ [fannu l-Khidaa*i l-ba_sariyy]
@@ -14923,19 +14902,19 @@
 2409 https://online.pubhtml5.com/idtb/neft/ </t>
         </is>
       </c>
-      <c r="B688" t="inlineStr">
+      <c r="B687" t="inlineStr">
         <is>
           <t>images/「錯視アート」_img1.jpg</t>
         </is>
       </c>
-      <c r="C688" t="inlineStr">
+      <c r="C687" t="inlineStr">
         <is>
           <t>トリックアート</t>
         </is>
       </c>
     </row>
-    <row r="689">
-      <c r="A689" t="inlineStr">
+    <row r="688">
+      <c r="A688" t="inlineStr">
         <is>
           <t xml:space="preserve">「自然界の消防士の訓練」
 تدريبات رجال الإطفاء في الطبيعة
@@ -14943,19 +14922,19 @@
 2308 https://twitter.com/NatGeoMagArab/status/1462420543890608129 </t>
         </is>
       </c>
-      <c r="B689" t="inlineStr">
+      <c r="B688" t="inlineStr">
         <is>
           <t>images/「自然界の消防士の訓練」_img1.jpg,images/ 「自然界の消防士の訓練」_img2.jpg</t>
         </is>
       </c>
-      <c r="C689" t="inlineStr">
+      <c r="C688" t="inlineStr">
         <is>
           <t>手書き語学 ,アラビア語 ,ヒグマ</t>
         </is>
       </c>
     </row>
-    <row r="690">
-      <c r="A690" t="inlineStr">
+    <row r="689">
+      <c r="A689" t="inlineStr">
         <is>
           <t xml:space="preserve">「救助」إسعاف
 イスアーフ ['is*aaf]
@@ -14964,19 +14943,19 @@
 2109 ambulance gov ae </t>
         </is>
       </c>
-      <c r="B690" t="inlineStr">
+      <c r="B689" t="inlineStr">
         <is>
           <t>images/「救助」_img1.jpg</t>
         </is>
       </c>
-      <c r="C690" t="inlineStr">
+      <c r="C689" t="inlineStr">
         <is>
           <t>救急車 ,はたらくくるま</t>
         </is>
       </c>
     </row>
-    <row r="691">
-      <c r="A691" t="inlineStr">
+    <row r="690">
+      <c r="A690" t="inlineStr">
         <is>
           <t xml:space="preserve">「感情／感覚」الإحْسَاسْ
 アルイヒサース [al-'iHsaas]
@@ -14985,19 +14964,19 @@
 2308 iN49R </t>
         </is>
       </c>
-      <c r="B691" t="inlineStr">
+      <c r="B690" t="inlineStr">
         <is>
           <t>images/「感情／感覚」_img1.jpg</t>
         </is>
       </c>
-      <c r="C691" t="inlineStr">
+      <c r="C690" t="inlineStr">
         <is>
           <t>オフ ,一休み</t>
         </is>
       </c>
     </row>
-    <row r="692">
-      <c r="A692" t="inlineStr">
+    <row r="691">
+      <c r="A691" t="inlineStr">
         <is>
           <t xml:space="preserve">「ひらめき」إلهام
 イルハーム ['lhaam]
@@ -15009,19 +14988,19 @@
 2103 出典不明 </t>
         </is>
       </c>
-      <c r="B692" t="inlineStr">
+      <c r="B691" t="inlineStr">
         <is>
           <t>images/「ひらめき」_img1.jpg</t>
         </is>
       </c>
-      <c r="C692" t="inlineStr">
+      <c r="C691" t="inlineStr">
         <is>
           <t>アラビア語</t>
         </is>
       </c>
     </row>
-    <row r="693">
-      <c r="A693" t="inlineStr">
+    <row r="692">
+      <c r="A692" t="inlineStr">
         <is>
           <t xml:space="preserve">「Ibdaa／クリエイティビティ」
 إبداع
@@ -15030,19 +15009,19 @@
 2308 Ibdaa Design &amp; Decoration Office </t>
         </is>
       </c>
-      <c r="B693" t="inlineStr">
+      <c r="B692" t="inlineStr">
         <is>
           <t>images/「Ibdaa／クリエイティビティ」_img1.jpg</t>
         </is>
       </c>
-      <c r="C693" t="inlineStr">
+      <c r="C692" t="inlineStr">
         <is>
           <t>創造性 ,独自性</t>
         </is>
       </c>
     </row>
-    <row r="694">
-      <c r="A694" t="inlineStr">
+    <row r="693">
+      <c r="A693" t="inlineStr">
         <is>
           <t xml:space="preserve">「奮闘なくして進歩なし」
 بدون كفاح لايوجد تقدم
@@ -15052,19 +15031,19 @@
 2105 ROUYMS TUMBLR COM </t>
         </is>
       </c>
-      <c r="B694" t="inlineStr">
+      <c r="B693" t="inlineStr">
         <is>
           <t>images/「奮闘なくして進歩なし」_img1.jpg</t>
         </is>
       </c>
-      <c r="C694" t="inlineStr">
+      <c r="C693" t="inlineStr">
         <is>
           <t>努力 ,三角形</t>
         </is>
       </c>
     </row>
-    <row r="695">
-      <c r="A695" t="inlineStr">
+    <row r="694">
+      <c r="A694" t="inlineStr">
         <is>
           <t xml:space="preserve">「木に登れば熊の危険を避けられるとお考えなら、考え直しましょう！」 
 إن اعتقدت أنك بمنأى عن خطر الدب عند تسلق الأشجار.. راجع حساباتك
@@ -15072,19 +15051,19 @@
 2202 NatGeoMagArab </t>
         </is>
       </c>
-      <c r="B695" t="inlineStr">
+      <c r="B694" t="inlineStr">
         <is>
           <t>images/「木に登れば熊の危険を避けられるとお考.jpeg</t>
         </is>
       </c>
-      <c r="C695" t="inlineStr">
+      <c r="C694" t="inlineStr">
         <is>
           <t>クマ</t>
         </is>
       </c>
     </row>
-    <row r="696">
-      <c r="A696" t="inlineStr">
+    <row r="695">
+      <c r="A695" t="inlineStr">
         <is>
           <t xml:space="preserve">「卒業おめでとう」مبروك التخرج
 マブルーク・タカッルジ [mabruuk a^taKharruj]
@@ -15093,19 +15072,19 @@
 2308 https://instagram.com/fatoomworld </t>
         </is>
       </c>
-      <c r="B696" t="inlineStr">
+      <c r="B695" t="inlineStr">
         <is>
           <t>images/「卒業おめでとう」_img1.jpg</t>
         </is>
       </c>
-      <c r="C696" t="inlineStr">
+      <c r="C695" t="inlineStr">
         <is>
           <t>卒業 ,イラスト</t>
         </is>
       </c>
     </row>
-    <row r="697">
-      <c r="A697" t="inlineStr">
+    <row r="696">
+      <c r="A696" t="inlineStr">
         <is>
           <t xml:space="preserve">「停止距離の計算」
 حساب مسافة التوقف
@@ -15115,19 +15094,19 @@
 2109 assurance-auto-info </t>
         </is>
       </c>
-      <c r="B697" t="inlineStr">
+      <c r="B696" t="inlineStr">
         <is>
           <t>images/「停止距離の計算」_img1.jpg</t>
         </is>
       </c>
-      <c r="C697" t="inlineStr">
+      <c r="C696" t="inlineStr">
         <is>
           <t>保険 ,自動車</t>
         </is>
       </c>
     </row>
-    <row r="698">
-      <c r="A698" t="inlineStr">
+    <row r="697">
+      <c r="A697" t="inlineStr">
         <is>
           <t xml:space="preserve">「教師要らず：10日でフランス語会話」
 بدون معلم
@@ -15137,19 +15116,19 @@
 2308 englais-best com </t>
         </is>
       </c>
-      <c r="B698" t="inlineStr">
+      <c r="B697" t="inlineStr">
         <is>
           <t>images/「教師要らず：10日でフランス語会話」_img1.jpg</t>
         </is>
       </c>
-      <c r="C698" t="inlineStr">
+      <c r="C697" t="inlineStr">
         <is>
           <t>教師なし学習</t>
         </is>
       </c>
     </row>
-    <row r="699">
-      <c r="A699" t="inlineStr">
+    <row r="698">
+      <c r="A698" t="inlineStr">
         <is>
           <t xml:space="preserve">「衝突」تصادم
 タサードゥム [ta_saadum]
@@ -15158,19 +15137,19 @@
 1810 </t>
         </is>
       </c>
-      <c r="B699" t="inlineStr">
+      <c r="B698" t="inlineStr">
         <is>
           <t>images/「衝突」_img1.jpg</t>
         </is>
       </c>
-      <c r="C699" t="inlineStr">
+      <c r="C698" t="inlineStr">
         <is>
           <t>あらびあや</t>
         </is>
       </c>
     </row>
-    <row r="700">
-      <c r="A700" t="inlineStr">
+    <row r="699">
+      <c r="A699" t="inlineStr">
         <is>
           <t xml:space="preserve">「楽観主義」تَفَاؤُلٌ
 タファーウル [tafaa'ul(un)]
@@ -15179,19 +15158,19 @@
 1904 arabictypography com </t>
         </is>
       </c>
-      <c r="B700" t="inlineStr">
+      <c r="B699" t="inlineStr">
         <is>
           <t>images/「楽観主義」_img1.jpg</t>
         </is>
       </c>
-      <c r="C700" t="inlineStr">
+      <c r="C699" t="inlineStr">
         <is>
           <t>やわらか ,緑</t>
         </is>
       </c>
     </row>
-    <row r="701">
-      <c r="A701" t="inlineStr">
+    <row r="700">
+      <c r="A700" t="inlineStr">
         <is>
           <t xml:space="preserve">「シベリアジャコウジカは、絶滅の危機にあると見なされている」
 يعد "أيل المسك السيبيري" مهددًا بالانقراض
@@ -15199,19 +15178,19 @@
 2308 https://twitter.com/NatGeoMagArab/status/1320666649045790720 </t>
         </is>
       </c>
-      <c r="B701" t="inlineStr">
+      <c r="B700" t="inlineStr">
         <is>
           <t>images/「シベリアジャコウジカは、絶滅の危機に_img1.jpg,images/「シベリアジャコウジカは、絶滅の危機に_img2.jpg</t>
         </is>
       </c>
-      <c r="C701" t="inlineStr">
+      <c r="C700" t="inlineStr">
         <is>
           <t>手書き語学 ,シベリア</t>
         </is>
       </c>
     </row>
-    <row r="702">
-      <c r="A702" t="inlineStr">
+    <row r="701">
+      <c r="A701" t="inlineStr">
         <is>
           <t xml:space="preserve">「融合／折衷／フュージョン」
 انصهار
@@ -15220,38 +15199,38 @@
 1811 elmahdyart Instagram </t>
         </is>
       </c>
-      <c r="B702" t="inlineStr">
+      <c r="B701" t="inlineStr">
         <is>
           <t>images/「融合／折衷／フュージョン」_img1.jpg</t>
         </is>
       </c>
-      <c r="C702" t="inlineStr">
+      <c r="C701" t="inlineStr">
         <is>
           <t>カリグラフィー ,書道</t>
         </is>
       </c>
     </row>
-    <row r="703">
-      <c r="A703" t="inlineStr">
+    <row r="702">
+      <c r="A702" t="inlineStr">
         <is>
           <t xml:space="preserve">「この子供は、昼寝をしようとする母親を邪魔しているようだ」
 「場所はインドのトラ保護区、バンダウガル公園。トラは生態ピラミッドのトップの捕食動物だが、最もリスクの高い絶滅危惧種のひとつである」
 2308 https://twitter.com/natgeomagarab/status/1553681890665586689 </t>
         </is>
       </c>
-      <c r="B703" t="inlineStr">
+      <c r="B702" t="inlineStr">
         <is>
           <t>images/「この子供は、昼寝をしようとする母親を_img1.jpg,images/「この子供は、昼寝をしようとする母親を_img2.jpg</t>
         </is>
       </c>
-      <c r="C703" t="inlineStr">
+      <c r="C702" t="inlineStr">
         <is>
           <t>手書き語学 ,アラビア語 ,トラ</t>
         </is>
       </c>
     </row>
-    <row r="704">
-      <c r="A704" t="inlineStr">
+    <row r="703">
+      <c r="A703" t="inlineStr">
         <is>
           <t xml:space="preserve">「もし敬意が落ちたら、それと一緒に全部落ちるのだ」
 إن سقط الإحترام سقط معه كل شيء
@@ -15260,19 +15239,19 @@
 2109 出典不明 </t>
         </is>
       </c>
-      <c r="B704" t="inlineStr">
+      <c r="B703" t="inlineStr">
         <is>
           <t>images/「もし敬意が落ちたら、それと一緒に全部_img1.jpg</t>
         </is>
       </c>
-      <c r="C704" t="inlineStr">
+      <c r="C703" t="inlineStr">
         <is>
           <t>リスペクト ,落書き</t>
         </is>
       </c>
     </row>
-    <row r="705">
-      <c r="A705" t="inlineStr">
+    <row r="704">
+      <c r="A704" t="inlineStr">
         <is>
           <t xml:space="preserve">「エジプト特許庁」
 مكتب براءات الاختراع المصرى
@@ -15282,19 +15261,19 @@
 2312 </t>
         </is>
       </c>
-      <c r="B705" t="inlineStr">
+      <c r="B704" t="inlineStr">
         <is>
           <t>images/「エジプト特許庁」_img1.jpg</t>
         </is>
       </c>
-      <c r="C705" t="inlineStr">
+      <c r="C704" t="inlineStr">
         <is>
           <t>patent</t>
         </is>
       </c>
     </row>
-    <row r="706">
-      <c r="A706" t="inlineStr">
+    <row r="705">
+      <c r="A705" t="inlineStr">
         <is>
           <t xml:space="preserve">「選挙」إنتخابات
 インティカーバート [intiKhaabaat]
@@ -15303,19 +15282,19 @@
 2311 nna-leb gov lb </t>
         </is>
       </c>
-      <c r="B706" t="inlineStr">
+      <c r="B705" t="inlineStr">
         <is>
           <t>images/「選挙」_img1.jpg</t>
         </is>
       </c>
-      <c r="C706" t="inlineStr">
+      <c r="C705" t="inlineStr">
         <is>
           <t>選挙 ,投票</t>
         </is>
       </c>
     </row>
-    <row r="707">
-      <c r="A707" t="inlineStr">
+    <row r="706">
+      <c r="A706" t="inlineStr">
         <is>
           <t xml:space="preserve">「待ちぼうけ」إنتظار
 インティザール [inti_Dhaar]
@@ -15324,19 +15303,19 @@
 1809 in4sser.tumblr </t>
         </is>
       </c>
-      <c r="B707" t="inlineStr">
+      <c r="B706" t="inlineStr">
         <is>
           <t>images/「待ちぼうけ」_img1.jpg</t>
         </is>
       </c>
-      <c r="C707" t="inlineStr">
+      <c r="C706" t="inlineStr">
         <is>
           <t>遅すぎ ,辛抱</t>
         </is>
       </c>
     </row>
-    <row r="708">
-      <c r="A708" t="inlineStr">
+    <row r="707">
+      <c r="A707" t="inlineStr">
         <is>
           <t xml:space="preserve">「試験」إختبار
 イクティバール [iKhtibaar]
@@ -15345,19 +15324,19 @@
 2109 出典不明 </t>
         </is>
       </c>
-      <c r="B708" t="inlineStr">
+      <c r="B707" t="inlineStr">
         <is>
           <t>images/「試験」_img1.jpg</t>
         </is>
       </c>
-      <c r="C708" t="inlineStr">
+      <c r="C707" t="inlineStr">
         <is>
           <t>テスト ,考査</t>
         </is>
       </c>
     </row>
-    <row r="709">
-      <c r="A709" t="inlineStr">
+    <row r="708">
+      <c r="A708" t="inlineStr">
         <is>
           <t xml:space="preserve">「チャンネル登録」اشتراك
 イシティラーク [iShtiraak]
@@ -15366,19 +15345,19 @@
 2308 </t>
         </is>
       </c>
-      <c r="B709" t="inlineStr">
+      <c r="B708" t="inlineStr">
         <is>
           <t>images/「チャンネル登録」_img1.jpg</t>
         </is>
       </c>
-      <c r="C709" t="inlineStr">
+      <c r="C708" t="inlineStr">
         <is>
           <t>Subscribe ,YouTube</t>
         </is>
       </c>
     </row>
-    <row r="710">
-      <c r="A710" t="inlineStr">
+    <row r="709">
+      <c r="A709" t="inlineStr">
         <is>
           <t xml:space="preserve">「スマイル」ابتسام
 イブティサーム [ibtisaam]
@@ -15386,37 +15365,37 @@
 1903 behance Written-Visuals </t>
         </is>
       </c>
+      <c r="B709" t="inlineStr">
+        <is>
+          <t>images/「スマイル」_img1.jpg</t>
+        </is>
+      </c>
+      <c r="C709" t="inlineStr">
+        <is>
+          <t>スマイリー ,ツ</t>
+        </is>
+      </c>
+    </row>
+    <row r="710">
+      <c r="A710" t="inlineStr">
+        <is>
+          <t xml:space="preserve">「身体の一部として…」
+2308 https://twitter.com/NatGeoMagArab/status/1528292080337813504 </t>
+        </is>
+      </c>
       <c r="B710" t="inlineStr">
         <is>
-          <t>images/「スマイル」_img1.jpg</t>
+          <t>images/「身体の一部として…」_img1.jpg</t>
         </is>
       </c>
       <c r="C710" t="inlineStr">
         <is>
-          <t>スマイリー ,ツ</t>
+          <t>手書き語学 ,カンガルー</t>
         </is>
       </c>
     </row>
     <row r="711">
       <c r="A711" t="inlineStr">
-        <is>
-          <t xml:space="preserve">「身体の一部として…」
-2308 https://twitter.com/NatGeoMagArab/status/1528292080337813504 </t>
-        </is>
-      </c>
-      <c r="B711" t="inlineStr">
-        <is>
-          <t>images/「身体の一部として…」_img1.jpg</t>
-        </is>
-      </c>
-      <c r="C711" t="inlineStr">
-        <is>
-          <t>手書き語学 ,カンガルー</t>
-        </is>
-      </c>
-    </row>
-    <row r="712">
-      <c r="A712" t="inlineStr">
         <is>
           <t xml:space="preserve">「ディスカバリー」إكتشاف
 イクティシャーフ [iktiShaaf]
@@ -15424,19 +15403,19 @@
 2308 tephanegabrielli com </t>
         </is>
       </c>
-      <c r="B712" t="inlineStr">
+      <c r="B711" t="inlineStr">
         <is>
           <t>images/「ディスカバリー」_img1.jpg</t>
         </is>
       </c>
-      <c r="C712" t="inlineStr">
+      <c r="C711" t="inlineStr">
         <is>
           <t>discovery ,デザイン</t>
         </is>
       </c>
     </row>
-    <row r="713">
-      <c r="A713" t="inlineStr">
+    <row r="712">
+      <c r="A712" t="inlineStr">
         <is>
           <t xml:space="preserve">「重力波の発見は新しい窓を開いた」
 فتَح اكتشاف موجات الجاذبية نافذة جديدة
@@ -15444,19 +15423,19 @@
 2308 https://twitter.com/SciTalk2U/status/1454891943440289793 </t>
         </is>
       </c>
-      <c r="B713" t="inlineStr">
+      <c r="B712" t="inlineStr">
         <is>
           <t>images/「重力波の発見は新しい窓を開いた」_img1.jpg</t>
         </is>
       </c>
-      <c r="C713" t="inlineStr">
+      <c r="C712" t="inlineStr">
         <is>
           <t>手書き語学 ,アラビア語 ,重力波</t>
         </is>
       </c>
     </row>
-    <row r="714">
-      <c r="A714" t="inlineStr">
+    <row r="713">
+      <c r="A713" t="inlineStr">
         <is>
           <t xml:space="preserve">「微笑みに微笑み。先にした人の方が美しい」
 الإبتسامة بالإبتسامة والبادئ أجمل
@@ -15465,19 +15444,19 @@
 2104 出典不明 </t>
         </is>
       </c>
-      <c r="B714" t="inlineStr">
+      <c r="B713" t="inlineStr">
         <is>
           <t>images/「微笑みに微笑み。先にした人の方が美し_img1.jpg,images/「微笑みに微笑み。先にした人の方が美し_img2.jpg</t>
         </is>
       </c>
-      <c r="C714" t="inlineStr">
+      <c r="C713" t="inlineStr">
         <is>
           <t>スマイル ,名言</t>
         </is>
       </c>
     </row>
-    <row r="715">
-      <c r="A715" t="inlineStr">
+    <row r="714">
+      <c r="A714" t="inlineStr">
         <is>
           <t xml:space="preserve">「笑顔」ابتسامة
 イブティサーマ [ibtisaama(tun)]
@@ -15486,19 +15465,19 @@
 2308 satokomatsu, minne </t>
         </is>
       </c>
-      <c r="B715" t="inlineStr">
+      <c r="B714" t="inlineStr">
         <is>
           <t>images/「笑顔」_img1.jpg</t>
         </is>
       </c>
-      <c r="C715" t="inlineStr">
+      <c r="C714" t="inlineStr">
         <is>
           <t>スマイル ,ツ</t>
         </is>
       </c>
     </row>
-    <row r="716">
-      <c r="A716" t="inlineStr">
+    <row r="715">
+      <c r="A715" t="inlineStr">
         <is>
           <t xml:space="preserve">「信仰」ايمان
 イーマーン ['iimaan]
@@ -15507,19 +15486,19 @@
 2506 instagram com/p/6ST-WHOOkJ/ </t>
         </is>
       </c>
-      <c r="B716" t="inlineStr">
+      <c r="B715" t="inlineStr">
         <is>
           <t>images/「信仰」_img1.jpg</t>
         </is>
       </c>
-      <c r="C716" t="inlineStr">
+      <c r="C715" t="inlineStr">
         <is>
           <t>宗教 ,信念</t>
         </is>
       </c>
     </row>
-    <row r="717">
-      <c r="A717" t="inlineStr">
+    <row r="716">
+      <c r="A716" t="inlineStr">
         <is>
           <t xml:space="preserve">「放送」إذاعة
 イザーア ['iDhaa*a]
@@ -15528,19 +15507,19 @@
 2404 heemades, Instagram </t>
         </is>
       </c>
-      <c r="B717" t="inlineStr">
+      <c r="B716" t="inlineStr">
         <is>
           <t>images/「放送」_img1.jpg</t>
         </is>
       </c>
-      <c r="C717" t="inlineStr">
+      <c r="C716" t="inlineStr">
         <is>
           <t>デザイン ,ラジオ</t>
         </is>
       </c>
     </row>
-    <row r="718">
-      <c r="A718" t="inlineStr">
+    <row r="717">
+      <c r="A717" t="inlineStr">
         <is>
           <t xml:space="preserve">「かきとりのちから」
 مهاراتي الإملائية
@@ -15549,19 +15528,19 @@
 2308 iqrawaoktoub.wordpress com </t>
         </is>
       </c>
-      <c r="B718" t="inlineStr">
+      <c r="B717" t="inlineStr">
         <is>
           <t>images/「かきとりのちから」_img1.jpg</t>
         </is>
       </c>
-      <c r="C718" t="inlineStr">
+      <c r="C717" t="inlineStr">
         <is>
           <t>国語 ,教材</t>
         </is>
       </c>
     </row>
-    <row r="719">
-      <c r="A719" t="inlineStr">
+    <row r="718">
+      <c r="A718" t="inlineStr">
         <is>
           <t xml:space="preserve">「歴史を作った男たち」
 رجال صنعوا التاريخ
@@ -15571,38 +15550,38 @@
 2410 https://x.gd/Wl5rJ </t>
         </is>
       </c>
-      <c r="B719" t="inlineStr">
+      <c r="B718" t="inlineStr">
         <is>
           <t>images/「歴史を作った男たち」_img1.jpg</t>
         </is>
       </c>
-      <c r="C719" t="inlineStr">
+      <c r="C718" t="inlineStr">
         <is>
           <t>偉人</t>
         </is>
       </c>
     </row>
-    <row r="720">
-      <c r="A720" t="inlineStr">
+    <row r="719">
+      <c r="A719" t="inlineStr">
         <is>
           <t xml:space="preserve">「無限の宇宙を旅した光」
 「何百年もの末にジェイムズ・ウェッブ望遠鏡のレンズの上に落ち、我々に遠い宇宙の美しさを見せてくれる。最も純粋な形と最も素晴らしい姿で」
 2308 https://twitter.com/NatGeoMagArab/status/1557811592636485632 </t>
         </is>
       </c>
-      <c r="B720" t="inlineStr">
+      <c r="B719" t="inlineStr">
         <is>
           <t>images/「無限の宇宙を旅した光」_img1.jpg</t>
         </is>
       </c>
-      <c r="C720" t="inlineStr">
+      <c r="C719" t="inlineStr">
         <is>
           <t>手書き語学 ,宇宙</t>
         </is>
       </c>
     </row>
-    <row r="721">
-      <c r="A721" t="inlineStr">
+    <row r="720">
+      <c r="A720" t="inlineStr">
         <is>
           <t xml:space="preserve">「日本好きになり行きたくなる20項」
 عشرون شيئا يجعلك تحب اليابان وترغب في زيارتها
@@ -15611,19 +15590,19 @@
 2308 wattpad </t>
         </is>
       </c>
-      <c r="B721" t="inlineStr">
+      <c r="B720" t="inlineStr">
         <is>
           <t>images/「日本好きになり行きたくなる20項」_img1.jpg</t>
         </is>
       </c>
-      <c r="C721" t="inlineStr">
+      <c r="C720" t="inlineStr">
         <is>
           <t>اليابان ,Japan</t>
         </is>
       </c>
     </row>
-    <row r="722">
-      <c r="A722" t="inlineStr">
+    <row r="721">
+      <c r="A721" t="inlineStr">
         <is>
           <t xml:space="preserve">「ピッタリの瞬間に撮影され、ドラゴンが火を噴いているように見える」
 التُقطت في اللحظة المناسبة لتبدو مثل تنين ينفث اللهب
@@ -15631,19 +15610,19 @@
 2509 https://twitter.com/NatGeoMagArab/status/1588780660269150208 </t>
         </is>
       </c>
-      <c r="B722" t="inlineStr">
+      <c r="B721" t="inlineStr">
         <is>
           <t>images/「ピッタリの瞬間に撮影され、ドラゴンが_img1.jpg,images/ 「ピッタリの瞬間に撮影され、ドラゴンが_img2.jpg</t>
         </is>
       </c>
-      <c r="C722" t="inlineStr">
+      <c r="C721" t="inlineStr">
         <is>
           <t xml:space="preserve">ドラゴン </t>
         </is>
       </c>
     </row>
-    <row r="723">
-      <c r="A723" t="inlineStr">
+    <row r="722">
+      <c r="A722" t="inlineStr">
         <is>
           <t xml:space="preserve">「満足は不滅の宝である」
 القَناعَةُ كنز لا يَفنَى
@@ -15653,55 +15632,55 @@
 2308 kareem mrghani </t>
         </is>
       </c>
+      <c r="B722" t="inlineStr">
+        <is>
+          <t>images/「満足は不滅の宝である」_img1.jpg</t>
+        </is>
+      </c>
+      <c r="C722" t="inlineStr">
+        <is>
+          <t>幸福度</t>
+        </is>
+      </c>
+    </row>
+    <row r="723">
+      <c r="A723" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ゴシキセイガイインコ。
+2409 https://twitter.com/NatGeoMagArab/status/1600022262014676992 </t>
+        </is>
+      </c>
       <c r="B723" t="inlineStr">
         <is>
-          <t>images/「満足は不滅の宝である」_img1.jpg</t>
+          <t>images/ゴシキセイガイインコ。_img1.jpg</t>
         </is>
       </c>
       <c r="C723" t="inlineStr">
         <is>
-          <t>幸福度</t>
+          <t>手書き語学 ,アラビア語,オウム</t>
         </is>
       </c>
     </row>
     <row r="724">
       <c r="A724" t="inlineStr">
         <is>
-          <t xml:space="preserve">ゴシキセイガイインコ。
-2409 https://twitter.com/NatGeoMagArab/status/1600022262014676992 </t>
+          <t xml:space="preserve">モモンガ。
+2403 https://twitter.com/NatGeoMagArab/status/1552541872966344704 </t>
         </is>
       </c>
       <c r="B724" t="inlineStr">
         <is>
-          <t>images/ゴシキセイガイインコ。_img1.jpg</t>
+          <t>images/モモンガ。_img1.jpg,images/ モモンガ。_img2.jpg</t>
         </is>
       </c>
       <c r="C724" t="inlineStr">
         <is>
-          <t>手書き語学 ,アラビア語,オウム</t>
+          <t>手書き語学 ,アラビア語 ,モモンガ</t>
         </is>
       </c>
     </row>
     <row r="725">
       <c r="A725" t="inlineStr">
-        <is>
-          <t xml:space="preserve">モモンガ。
-2403 https://twitter.com/NatGeoMagArab/status/1552541872966344704 </t>
-        </is>
-      </c>
-      <c r="B725" t="inlineStr">
-        <is>
-          <t>images/モモンガ。_img1.jpg,images/ モモンガ。_img2.jpg</t>
-        </is>
-      </c>
-      <c r="C725" t="inlineStr">
-        <is>
-          <t>手書き語学 ,アラビア語 ,モモンガ</t>
-        </is>
-      </c>
-    </row>
-    <row r="726">
-      <c r="A726" t="inlineStr">
         <is>
           <t xml:space="preserve">「象の群れ。ドローンの音から逃げている」
 قطيع من الفيلة يفر هاربًا من صوت الدرون
@@ -15713,56 +15692,56 @@
 2009 https://twitter.com/NatGeoMagArab/status/1302970033627258881 </t>
         </is>
       </c>
+      <c r="B725" t="inlineStr">
+        <is>
+          <t>images/「象の群れ。ドローンの音から逃げている.jpg</t>
+        </is>
+      </c>
+      <c r="C725" t="inlineStr">
+        <is>
+          <t>ゾウ ,ドローン</t>
+        </is>
+      </c>
+    </row>
+    <row r="726">
+      <c r="A726" t="inlineStr">
+        <is>
+          <t xml:space="preserve">カルマン線。
+2308 https://twitter.com/NatGeoMagArab/status/1536436999522881536 </t>
+        </is>
+      </c>
       <c r="B726" t="inlineStr">
         <is>
-          <t>images/「象の群れ。ドローンの音から逃げている.jpg</t>
+          <t>images/カルマン線。_img1.jpg</t>
         </is>
       </c>
       <c r="C726" t="inlineStr">
         <is>
-          <t>ゾウ ,ドローン</t>
+          <t xml:space="preserve">手書き語学 ,アラビア語 ,宇宙 </t>
         </is>
       </c>
     </row>
     <row r="727">
       <c r="A727" t="inlineStr">
-        <is>
-          <t xml:space="preserve">カルマン線。
-2308 https://twitter.com/NatGeoMagArab/status/1536436999522881536 </t>
-        </is>
-      </c>
-      <c r="B727" t="inlineStr">
-        <is>
-          <t>images/カルマン線。_img1.jpg</t>
-        </is>
-      </c>
-      <c r="C727" t="inlineStr">
-        <is>
-          <t xml:space="preserve">手書き語学 ,アラビア語 ,宇宙 </t>
-        </is>
-      </c>
-    </row>
-    <row r="728">
-      <c r="A728" t="inlineStr">
         <is>
           <t xml:space="preserve">「恥ずかしがり屋のマヌルネコと暖かい朝の太陽光線」
 ⁦「二つの美しいもの」[Shay'-ayni jamiil-ayni] 属格：「物」( شيء )[Shay']・「美しい」( جميل )[jamiil]⁩
 2309 https://twitter.com/NatGeoMagArab/status/1697512148820504912 </t>
         </is>
       </c>
-      <c r="B728" t="inlineStr">
+      <c r="B727" t="inlineStr">
         <is>
           <t>images/「恥ずかしがり屋のマヌルネコと暖かい朝_img1.jpg</t>
         </is>
       </c>
-      <c r="C728" t="inlineStr">
+      <c r="C727" t="inlineStr">
         <is>
           <t>手書き語学 ,アラビア語 ,マヌルネコ</t>
         </is>
       </c>
     </row>
-    <row r="729">
-      <c r="A729" t="inlineStr">
+    <row r="728">
+      <c r="A728" t="inlineStr">
         <is>
           <t xml:space="preserve">「二回失敗しているペンギン」
 بطريق يفشل مرتين
@@ -15772,19 +15751,19 @@
 2308 https://twitter.com/NatGeoMagArab/status/1479483133766426626 </t>
         </is>
       </c>
-      <c r="B729" t="inlineStr">
+      <c r="B728" t="inlineStr">
         <is>
           <t>images/「二回失敗しているペンギン」_img1.jpg</t>
         </is>
       </c>
-      <c r="C729" t="inlineStr">
+      <c r="C728" t="inlineStr">
         <is>
           <t>ペンギン ,動物</t>
         </is>
       </c>
     </row>
-    <row r="730">
-      <c r="A730" t="inlineStr">
+    <row r="729">
+      <c r="A729" t="inlineStr">
         <is>
           <t xml:space="preserve">「2億光年の彼方できらめく炎と光」
 وهج ووميض يتلألأ على بعد 200 مليون سنة ضوئية
@@ -15795,15 +15774,15 @@
 2010 https://twitter.com/NatGeoMagArab/status/1303415502673342464 </t>
         </is>
       </c>
-      <c r="B730" t="inlineStr"/>
-      <c r="C730" t="inlineStr">
+      <c r="B729" t="inlineStr"/>
+      <c r="C729" t="inlineStr">
         <is>
           <t>宇宙 ,銀河</t>
         </is>
       </c>
     </row>
-    <row r="731">
-      <c r="A731" t="inlineStr">
+    <row r="730">
+      <c r="A730" t="inlineStr">
         <is>
           <t xml:space="preserve">「さまよう黒猫」قطة سوداء تجوب
 キッタトゥン・サウダーウ・タジューブ [qi^_tatun sawdaa'u ta-juub]
@@ -15812,19 +15791,19 @@
 2308 https://twitter.com/NatGeoMagArab/status/1532973177453760512 </t>
         </is>
       </c>
-      <c r="B731" t="inlineStr">
+      <c r="B730" t="inlineStr">
         <is>
           <t>images/「さまよう黒猫」_img1.jpg,images/ 「さまよう黒猫」_img2.jpg</t>
         </is>
       </c>
-      <c r="C731" t="inlineStr">
+      <c r="C730" t="inlineStr">
         <is>
           <t xml:space="preserve">手書き語学 ,モロッコ </t>
         </is>
       </c>
     </row>
-    <row r="732">
-      <c r="A732" t="inlineStr">
+    <row r="731">
+      <c r="A731" t="inlineStr">
         <is>
           <t xml:space="preserve">「サイのざらざらした皮を利用して自分の体を掻くネコ」
 قطة تستغل جلد الكركدن الخشن لحك جسدها
@@ -15833,19 +15812,19 @@
 2308 https://twitter.com/NatGeoMagArab/status/1476855740929216517 </t>
         </is>
       </c>
-      <c r="B732" t="inlineStr">
+      <c r="B731" t="inlineStr">
         <is>
           <t>images/「サイのざらざらした皮を利用して自分の_img1.jpg</t>
         </is>
       </c>
-      <c r="C732" t="inlineStr">
+      <c r="C731" t="inlineStr">
         <is>
           <t>サイ ,チェコ</t>
         </is>
       </c>
     </row>
-    <row r="733">
-      <c r="A733" t="inlineStr">
+    <row r="732">
+      <c r="A732" t="inlineStr">
         <is>
           <t xml:space="preserve">「沈まぬ太陽」شمس لا تغيب
 シャムス・ラー・タギーブ [Shams laa ta-Ghiib]
@@ -15854,19 +15833,19 @@
 2308 AHMED ELASSAL </t>
         </is>
       </c>
-      <c r="B733" t="inlineStr">
+      <c r="B732" t="inlineStr">
         <is>
           <t>images/「沈まぬ太陽」_img1.jpg</t>
         </is>
       </c>
-      <c r="C733" t="inlineStr">
+      <c r="C732" t="inlineStr">
         <is>
           <t>帝国 ,白夜</t>
         </is>
       </c>
     </row>
-    <row r="734">
-      <c r="A734" t="inlineStr">
+    <row r="733">
+      <c r="A733" t="inlineStr">
         <is>
           <t xml:space="preserve">「子供に食べさせている忍耐強い母親」
 أم صبورة تطعم صغيرها
@@ -15875,19 +15854,19 @@
 2308 https://twitter.com/natgeomagarab/status/1585572054509957120 </t>
         </is>
       </c>
-      <c r="B734" t="inlineStr">
+      <c r="B733" t="inlineStr">
         <is>
           <t>images/「子供に食べさせている忍耐強い母親」_img1.jpg</t>
         </is>
       </c>
-      <c r="C734" t="inlineStr">
+      <c r="C733" t="inlineStr">
         <is>
           <t>手書き語学 ,アラビア語 ,ミヤコドリ</t>
         </is>
       </c>
     </row>
-    <row r="735">
-      <c r="A735" t="inlineStr">
+    <row r="734">
+      <c r="A734" t="inlineStr">
         <is>
           <t xml:space="preserve">「コーヒーは繰り返さない恋物語」
 القهوة قصة عشق لن تتكرر
@@ -15897,19 +15876,19 @@
 2403 pin it/7tvd8Wc </t>
         </is>
       </c>
-      <c r="B735" t="inlineStr">
+      <c r="B734" t="inlineStr">
         <is>
           <t>images/「コーヒーは繰り返さない恋物語」_img1.jpg</t>
         </is>
       </c>
-      <c r="C735" t="inlineStr">
+      <c r="C734" t="inlineStr">
         <is>
           <t>コーヒー ,名言</t>
         </is>
       </c>
     </row>
-    <row r="736">
-      <c r="A736" t="inlineStr">
+    <row r="735">
+      <c r="A735" t="inlineStr">
         <is>
           <t xml:space="preserve">「星々で飾られた空。魅惑的な色合いで黄昏の美を満たしている」
 سماء مرصعة بالنجوم تضفي لمسة سحرية على جمال الشفق
@@ -15917,19 +15896,19 @@
 2010 https://twitter.com/NatGeoMagArab/status/1303777701975584768 </t>
         </is>
       </c>
-      <c r="B736" t="inlineStr">
+      <c r="B735" t="inlineStr">
         <is>
           <t>images/「星々で飾られた空。魅惑的な色合いで黄.png</t>
         </is>
       </c>
-      <c r="C736" t="inlineStr">
+      <c r="C735" t="inlineStr">
         <is>
           <t>星空 ,宇宙</t>
         </is>
       </c>
     </row>
-    <row r="737">
-      <c r="A737" t="inlineStr">
+    <row r="736">
+      <c r="A736" t="inlineStr">
         <is>
           <t xml:space="preserve">「国際宇宙ステーションからの写真。巨大な台風『ハイシェン（海神）』を映している」
 لقطات من محطة الفضاء الدولية تظهر إعصار "هايشن" الهائل
@@ -15937,19 +15916,19 @@
 2403 https://twitter.com/NatGeoMagArab/status/1302871968522235904 </t>
         </is>
       </c>
-      <c r="B737" t="inlineStr">
+      <c r="B736" t="inlineStr">
         <is>
           <t>images/「国際宇宙ステーションからの写真。巨大.png</t>
         </is>
       </c>
-      <c r="C737" t="inlineStr">
+      <c r="C736" t="inlineStr">
         <is>
           <t>台風</t>
         </is>
       </c>
     </row>
-    <row r="738">
-      <c r="A738" t="inlineStr">
+    <row r="737">
+      <c r="A737" t="inlineStr">
         <is>
           <t xml:space="preserve">「草を食む幸運な子羊たち」
 خراف محظوظة ترعى
@@ -15959,19 +15938,19 @@
 2308 https://twitter.com/NatGeoMagArab/status/1490211393554972676 </t>
         </is>
       </c>
-      <c r="B738" t="inlineStr">
+      <c r="B737" t="inlineStr">
         <is>
           <t>images/「草を食む幸運な子羊たち」_img1.jpg,images/ 「草を食む幸運な子羊たち」_img2.jpg</t>
         </is>
       </c>
-      <c r="C738" t="inlineStr">
+      <c r="C737" t="inlineStr">
         <is>
           <t>羊 ,アイルランド</t>
         </is>
       </c>
     </row>
-    <row r="739">
-      <c r="A739" t="inlineStr">
+    <row r="738">
+      <c r="A738" t="inlineStr">
         <is>
           <t xml:space="preserve">「お金で買えぬ10のもの」
 ١٠ أشياء لا تشترى بالمال
@@ -15981,19 +15960,19 @@
 2308 ayb124 </t>
         </is>
       </c>
-      <c r="B739" t="inlineStr">
+      <c r="B738" t="inlineStr">
         <is>
           <t>images/「お金で買えぬ10のもの」_img1.jpg</t>
         </is>
       </c>
-      <c r="C739" t="inlineStr">
+      <c r="C738" t="inlineStr">
         <is>
           <t>価値 ,購買</t>
         </is>
       </c>
     </row>
-    <row r="740">
-      <c r="A740" t="inlineStr">
+    <row r="739">
+      <c r="A739" t="inlineStr">
         <is>
           <t xml:space="preserve">「お金では買えないよ」
 هي أشْيَاءٌ لا تُشْتَرَى
@@ -16003,19 +15982,19 @@
 1906 mardy_zaawely, Instagram </t>
         </is>
       </c>
-      <c r="B740" t="inlineStr">
+      <c r="B739" t="inlineStr">
         <is>
           <t>images/「お金では買えないよ」_img1.jpg</t>
         </is>
       </c>
-      <c r="C740" t="inlineStr">
+      <c r="C739" t="inlineStr">
         <is>
           <t>マスターカード ,価値</t>
         </is>
       </c>
     </row>
-    <row r="741">
-      <c r="A741" t="inlineStr">
+    <row r="740">
+      <c r="A740" t="inlineStr">
         <is>
           <t xml:space="preserve">「好奇心旺盛なホッキョクギツネ」
 ثعلب قطبي يملؤه الفضول
@@ -16025,15 +16004,15 @@
 2308 https://twitter.com/natgeomagarab/status/1157592172968808449 </t>
         </is>
       </c>
-      <c r="B741" t="inlineStr"/>
-      <c r="C741" t="inlineStr">
+      <c r="B740" t="inlineStr"/>
+      <c r="C740" t="inlineStr">
         <is>
           <t>ファーストコンタクト ,キツネ</t>
         </is>
       </c>
     </row>
-    <row r="742">
-      <c r="A742" t="inlineStr">
+    <row r="741">
+      <c r="A741" t="inlineStr">
         <is>
           <t xml:space="preserve">「グレンダイザーのいる国は死にません」
 لنْ يَموتَ شَعبٌ لدَيهِ غرندايزر
@@ -16042,56 +16021,56 @@
 2308 https://www.aljarida.com/articles/1462241741574732100/ </t>
         </is>
       </c>
+      <c r="B741" t="inlineStr">
+        <is>
+          <t>images/「グレンダイザーのいる国は死にません」_img1.jpg</t>
+        </is>
+      </c>
+      <c r="C741" t="inlineStr">
+        <is>
+          <t>UFOロボ ,アニメ</t>
+        </is>
+      </c>
+    </row>
+    <row r="742">
+      <c r="A742" t="inlineStr">
+        <is>
+          <t xml:space="preserve">「凍結路面を運転中、彼女は嫌な場面に居合わせた」
+2408 https://twitter.com/NatGeoMagArab/status/1610305209657626625 </t>
+        </is>
+      </c>
       <c r="B742" t="inlineStr">
         <is>
-          <t>images/「グレンダイザーのいる国は死にません」_img1.jpg</t>
+          <t>images/「凍結路面を運転中、彼女は嫌な場面に居_img1.jpg</t>
         </is>
       </c>
       <c r="C742" t="inlineStr">
         <is>
-          <t>UFOロボ ,アニメ</t>
+          <t>手書き語学 ,アラビア語 ,路面凍結</t>
         </is>
       </c>
     </row>
     <row r="743">
       <c r="A743" t="inlineStr">
-        <is>
-          <t xml:space="preserve">「凍結路面を運転中、彼女は嫌な場面に居合わせた」
-2408 https://twitter.com/NatGeoMagArab/status/1610305209657626625 </t>
-        </is>
-      </c>
-      <c r="B743" t="inlineStr">
-        <is>
-          <t>images/「凍結路面を運転中、彼女は嫌な場面に居_img1.jpg</t>
-        </is>
-      </c>
-      <c r="C743" t="inlineStr">
-        <is>
-          <t>手書き語学 ,アラビア語 ,路面凍結</t>
-        </is>
-      </c>
-    </row>
-    <row r="744">
-      <c r="A744" t="inlineStr">
         <is>
           <t xml:space="preserve">「虹が美しさを加えている、アルパカという動物の美しいショット」
 ⁦「美しいショット」[laq_tatun jamiilatun]：「ショット」( لقطة )[laq_ta]：( ـلٌ )[-lun]・( ـقٌ )[-qun]・( ـطٌ )[-_tun]・( ـةٌ )[-tun]⁩
 2308 https://twitter.com/natgeomagarab/status/1155115655928004608 </t>
         </is>
       </c>
-      <c r="B744" t="inlineStr">
+      <c r="B743" t="inlineStr">
         <is>
           <t>images/「虹が美しさを加えている、アルパカとい_img1.jpg</t>
         </is>
       </c>
-      <c r="C744" t="inlineStr">
+      <c r="C743" t="inlineStr">
         <is>
           <t>モフモフ ,アルパカ</t>
         </is>
       </c>
     </row>
-    <row r="745">
-      <c r="A745" t="inlineStr">
+    <row r="744">
+      <c r="A744" t="inlineStr">
         <is>
           <t xml:space="preserve">「幸せは…全然思いもよらない所からやって来る」
 السعادة تأتينا من أماكن لم نكن نتوقعها أبداً
@@ -16100,19 +16079,19 @@
 2109 出典不明 </t>
         </is>
       </c>
-      <c r="B745" t="inlineStr">
+      <c r="B744" t="inlineStr">
         <is>
           <t>images/「幸せは…全然思いもよらない所からやっ_img1.jpg,images/ 「幸せは…全然思いもよらない所からやっ_img2.jpg</t>
         </is>
       </c>
-      <c r="C745" t="inlineStr">
+      <c r="C744" t="inlineStr">
         <is>
           <t>訪れ ,予想</t>
         </is>
       </c>
     </row>
-    <row r="746">
-      <c r="A746" t="inlineStr">
+    <row r="745">
+      <c r="A745" t="inlineStr">
         <is>
           <t xml:space="preserve">「あらゆる問題は、食べ物が解決してくれる」
 كل مشكلة ولها أكلة تحلها
@@ -16121,19 +16100,19 @@
 1909 ALQA AN 878 </t>
         </is>
       </c>
-      <c r="B746" t="inlineStr">
+      <c r="B745" t="inlineStr">
         <is>
           <t>images/「あらゆる問題は、食べ物が解決してくれ_img1.jpg</t>
         </is>
       </c>
-      <c r="C746" t="inlineStr">
+      <c r="C745" t="inlineStr">
         <is>
           <t>ストレス ,精神</t>
         </is>
       </c>
     </row>
-    <row r="747">
-      <c r="A747" t="inlineStr">
+    <row r="746">
+      <c r="A746" t="inlineStr">
         <is>
           <t xml:space="preserve">「冬で私が好きな物」
 أشياء أحبها بالشتاء
@@ -16143,19 +16122,19 @@
 2109 出典不明 </t>
         </is>
       </c>
-      <c r="B747" t="inlineStr">
+      <c r="B746" t="inlineStr">
         <is>
           <t>images/「冬で私が好きな物」_img1.jpg</t>
         </is>
       </c>
-      <c r="C747" t="inlineStr">
+      <c r="C746" t="inlineStr">
         <is>
           <t>季節 ,冬</t>
         </is>
       </c>
     </row>
-    <row r="748">
-      <c r="A748" t="inlineStr">
+    <row r="747">
+      <c r="A747" t="inlineStr">
         <is>
           <t xml:space="preserve">「お金で買うことの出来ない物」
 أشياء لا تستطيع شراءها بالمال
@@ -16165,19 +16144,19 @@
 2409 https://x.com/akhbarak/status/1038402708414373888 </t>
         </is>
       </c>
-      <c r="B748" t="inlineStr">
+      <c r="B747" t="inlineStr">
         <is>
           <t>images/「お金で買うことの出来ない物」_img1.jpg,images/ 「お金で買うことの出来ない物」_img2.jpg</t>
         </is>
       </c>
-      <c r="C748" t="inlineStr">
+      <c r="C747" t="inlineStr">
         <is>
           <t>ショッピング ,価値</t>
         </is>
       </c>
     </row>
-    <row r="749">
-      <c r="A749" t="inlineStr">
+    <row r="748">
+      <c r="A748" t="inlineStr">
         <is>
           <t xml:space="preserve">「私たちが愛する言葉」
 كلماتٌ نُحبّها
@@ -16187,19 +16166,19 @@
 2109 جليل خزعل </t>
         </is>
       </c>
-      <c r="B749" t="inlineStr">
+      <c r="B748" t="inlineStr">
         <is>
           <t>images/「私たちが愛する言葉」_img1.jpg</t>
         </is>
       </c>
-      <c r="C749" t="inlineStr">
+      <c r="C748" t="inlineStr">
         <is>
           <t>花 ,贈り物</t>
         </is>
       </c>
     </row>
-    <row r="750">
-      <c r="A750" t="inlineStr">
+    <row r="749">
+      <c r="A749" t="inlineStr">
         <is>
           <t xml:space="preserve">「お茶についてあなたが知らない10の事実」
 عشر معلومات لا تعرفها عن الشاي
@@ -16208,19 +16187,19 @@
 2012 http://ara.tv/6syq2 </t>
         </is>
       </c>
-      <c r="B750" t="inlineStr">
+      <c r="B749" t="inlineStr">
         <is>
           <t>images/「お茶についてあなたが知らない10の事_img1.jpg</t>
         </is>
       </c>
-      <c r="C750" t="inlineStr">
+      <c r="C749" t="inlineStr">
         <is>
           <t>神農</t>
         </is>
       </c>
     </row>
-    <row r="751">
-      <c r="A751" t="inlineStr">
+    <row r="750">
+      <c r="A750" t="inlineStr">
         <is>
           <t xml:space="preserve">「大きくなったウソ」
 الكذبة الّتي كبرت
@@ -16230,19 +16209,19 @@
 2509 سلسلة الحلزونة </t>
         </is>
       </c>
-      <c r="B751" t="inlineStr">
+      <c r="B750" t="inlineStr">
         <is>
           <t>images/「大きくなったウソ」_img1.jpg</t>
         </is>
       </c>
-      <c r="C751" t="inlineStr">
+      <c r="C750" t="inlineStr">
         <is>
           <t>絵本</t>
         </is>
       </c>
     </row>
-    <row r="752">
-      <c r="A752" t="inlineStr">
+    <row r="751">
+      <c r="A751" t="inlineStr">
         <is>
           <t xml:space="preserve">「自分に合った掃除機を買うには？」
 كيف تشتري المكنسة الكهربائية التي تناسبك؟
@@ -16251,19 +16230,19 @@
 2106 ts3a com </t>
         </is>
       </c>
-      <c r="B752" t="inlineStr">
+      <c r="B751" t="inlineStr">
         <is>
           <t>images/「自分に合った掃除機を買うには？」_img1.jpg</t>
         </is>
       </c>
-      <c r="C752" t="inlineStr">
+      <c r="C751" t="inlineStr">
         <is>
           <t>家電 ,掃除</t>
         </is>
       </c>
     </row>
-    <row r="753">
-      <c r="A753" t="inlineStr">
+    <row r="752">
+      <c r="A752" t="inlineStr">
         <is>
           <t xml:space="preserve">「仮にこれが批判の数としよう」
 لنفرض ان عدد الذين ينتقدونك
@@ -16274,19 +16253,19 @@
 2504 出典不明 </t>
         </is>
       </c>
-      <c r="B753" t="inlineStr">
+      <c r="B752" t="inlineStr">
         <is>
           <t>images/「仮にこれが批判の数としよう」_img1.jpg</t>
         </is>
       </c>
-      <c r="C753" t="inlineStr">
+      <c r="C752" t="inlineStr">
         <is>
           <t>アンチ</t>
         </is>
       </c>
     </row>
-    <row r="754">
-      <c r="A754" t="inlineStr">
+    <row r="753">
+      <c r="A753" t="inlineStr">
         <is>
           <t xml:space="preserve">「ここに見えるのは何？」
 ما الذي تراه هنا؟
@@ -16296,15 +16275,15 @@
 2204 https://twitter.com/NatGeoMagArab/status/1506933850617700352 </t>
         </is>
       </c>
-      <c r="B754" t="inlineStr"/>
-      <c r="C754" t="inlineStr">
+      <c r="B753" t="inlineStr"/>
+      <c r="C753" t="inlineStr">
         <is>
           <t xml:space="preserve">ペンギン </t>
         </is>
       </c>
     </row>
-    <row r="755">
-      <c r="A755" t="inlineStr">
+    <row r="754">
+      <c r="A754" t="inlineStr">
         <is>
           <t xml:space="preserve">「今日辛いこと、明日は平気だろう」
 ما يؤلم اليوم سيهون غدًا
@@ -16314,19 +16293,19 @@
 2308 basmahjeff </t>
         </is>
       </c>
-      <c r="B755" t="inlineStr">
+      <c r="B754" t="inlineStr">
         <is>
           <t>images/「今日辛いこと、明日は平気だろう」_img1.jpg</t>
         </is>
       </c>
-      <c r="C755" t="inlineStr">
+      <c r="C754" t="inlineStr">
         <is>
           <t>悩み ,達観</t>
         </is>
       </c>
     </row>
-    <row r="756">
-      <c r="A756" t="inlineStr">
+    <row r="755">
+      <c r="A755" t="inlineStr">
         <is>
           <t xml:space="preserve">「自分のすることを好きでなきゃ」
 عليك أن تحب ما تفعل
@@ -16335,19 +16314,19 @@
 1810 Ahmed Elhakeem </t>
         </is>
       </c>
-      <c r="B756" t="inlineStr">
+      <c r="B755" t="inlineStr">
         <is>
           <t>images/「自分のすることを好きでなきゃ」_img1.jpg</t>
         </is>
       </c>
-      <c r="C756" t="inlineStr">
+      <c r="C755" t="inlineStr">
         <is>
           <t>転職 ,かわいい</t>
         </is>
       </c>
     </row>
-    <row r="757">
-      <c r="A757" t="inlineStr">
+    <row r="756">
+      <c r="A756" t="inlineStr">
         <is>
           <t xml:space="preserve">「この地上に生き甲斐あり」
 على هذه الأرض ما يستحق الحياة
@@ -16357,19 +16336,19 @@
 2308 Mahmoud Gafar </t>
         </is>
       </c>
-      <c r="B757" t="inlineStr">
+      <c r="B756" t="inlineStr">
         <is>
           <t>images/「この地上に生き甲斐あり」_img1.jpg</t>
         </is>
       </c>
-      <c r="C757" t="inlineStr">
+      <c r="C756" t="inlineStr">
         <is>
           <t>詩</t>
         </is>
       </c>
     </row>
-    <row r="758">
-      <c r="A758" t="inlineStr">
+    <row r="757">
+      <c r="A757" t="inlineStr">
         <is>
           <t xml:space="preserve">「おそらく、あなたの求めるものはあるだろう」
 لعلَّ ما تَرجوهُ سيَكونُ
@@ -16379,19 +16358,19 @@
 2308 PIXEL Instagram </t>
         </is>
       </c>
-      <c r="B758" t="inlineStr">
+      <c r="B757" t="inlineStr">
         <is>
           <t>images/「おそらく、あなたの求めるものはあるだ_img1.jpg</t>
         </is>
       </c>
-      <c r="C758" t="inlineStr">
+      <c r="C757" t="inlineStr">
         <is>
           <t>願い ,信仰</t>
         </is>
       </c>
     </row>
-    <row r="759">
-      <c r="A759" t="inlineStr">
+    <row r="758">
+      <c r="A758" t="inlineStr">
         <is>
           <t xml:space="preserve">「オレンジの効能が何か知っていますか？」
 هل تعرف ما هي فوائد البرتقال؟
@@ -16401,19 +16380,19 @@
 2308 sadahadhramowt com </t>
         </is>
       </c>
-      <c r="B759" t="inlineStr">
+      <c r="B758" t="inlineStr">
         <is>
           <t>images/「オレンジの効能が何か知っていますか？_img1.jpg</t>
         </is>
       </c>
-      <c r="C759" t="inlineStr">
+      <c r="C758" t="inlineStr">
         <is>
           <t>オレンジ ,フルーツ</t>
         </is>
       </c>
     </row>
-    <row r="760">
-      <c r="A760" t="inlineStr">
+    <row r="759">
+      <c r="A759" t="inlineStr">
         <is>
           <t xml:space="preserve">「遊ぶパンダの光景より可愛いものがありますか？」
 هل هناك ما هو ألطف من مشاهدة الباندا وهي تلعب؟
@@ -16421,19 +16400,19 @@
 2308 https://twitter.com/NatGeoMagArab/status/1494612797858074626 </t>
         </is>
       </c>
-      <c r="B760" t="inlineStr">
+      <c r="B759" t="inlineStr">
         <is>
           <t>images/「遊ぶパンダの光景より可愛いものがあり_img1.jpg</t>
         </is>
       </c>
-      <c r="C760" t="inlineStr">
+      <c r="C759" t="inlineStr">
         <is>
           <t>パンダ ,モコモコ</t>
         </is>
       </c>
     </row>
-    <row r="761">
-      <c r="A761" t="inlineStr">
+    <row r="760">
+      <c r="A760" t="inlineStr">
         <is>
           <t xml:space="preserve">「大事なのは何者だったかじゃない。何者になるかだ」
 ليسَ المُهم ما كُنتَ بل مَا ستكون
@@ -16442,19 +16421,19 @@
 2308 出典不明 </t>
         </is>
       </c>
-      <c r="B761" t="inlineStr">
+      <c r="B760" t="inlineStr">
         <is>
           <t>images/「大事なのは何者だったかじゃない。何者_img1.jpg</t>
         </is>
       </c>
-      <c r="C761" t="inlineStr">
+      <c r="C760" t="inlineStr">
         <is>
           <t>自己実現 ,存在価値</t>
         </is>
       </c>
     </row>
-    <row r="762">
-      <c r="A762" t="inlineStr">
+    <row r="761">
+      <c r="A761" t="inlineStr">
         <is>
           <t xml:space="preserve">「あなたであれ。ありのままが美しいから」
 كُنْ أَنْتَ لأنك جميل كما أنت
@@ -16463,19 +16442,19 @@
 2308 IDREES DESIGN </t>
         </is>
       </c>
-      <c r="B762" t="inlineStr">
+      <c r="B761" t="inlineStr">
         <is>
           <t>images/「あなたであれ。ありのままが美しいから_img1.jpg</t>
         </is>
       </c>
-      <c r="C762" t="inlineStr">
+      <c r="C761" t="inlineStr">
         <is>
           <t>自己肯定 ,BeYourself</t>
         </is>
       </c>
     </row>
-    <row r="763">
-      <c r="A763" t="inlineStr">
+    <row r="762">
+      <c r="A762" t="inlineStr">
         <is>
           <t xml:space="preserve">「恐れの中に生きる者は決して自由になれない」
 من يعش في خوف لن يكون حرا أبدا
@@ -16484,19 +16463,19 @@
 2111 rjeem com </t>
         </is>
       </c>
-      <c r="B763" t="inlineStr">
+      <c r="B762" t="inlineStr">
         <is>
           <t>images/「恐れの中に生きる者は決して自由になれ_img1.jpg,images/ 「恐れの中に生きる者は決して自由になれ_img2.jpg</t>
         </is>
       </c>
-      <c r="C763" t="inlineStr">
+      <c r="C762" t="inlineStr">
         <is>
           <t>勇気 ,壁</t>
         </is>
       </c>
     </row>
-    <row r="764">
-      <c r="A764" t="inlineStr">
+    <row r="763">
+      <c r="A763" t="inlineStr">
         <is>
           <t xml:space="preserve">「己の翼を信じる者は己の重さを案じない」
 من يثق في جناحيه لن يهتم لوزنه
@@ -16505,19 +16484,19 @@
 2308 kmrghani </t>
         </is>
       </c>
-      <c r="B764" t="inlineStr">
+      <c r="B763" t="inlineStr">
         <is>
           <t>images/「己の翼を信じる者は己の重さを案じない_img1.jpg</t>
         </is>
       </c>
-      <c r="C764" t="inlineStr">
+      <c r="C763" t="inlineStr">
         <is>
           <t>自信</t>
         </is>
       </c>
     </row>
-    <row r="765">
-      <c r="A765" t="inlineStr">
+    <row r="764">
+      <c r="A764" t="inlineStr">
         <is>
           <t xml:space="preserve">「珈琲で一番大事な事！誰と飲むか？」
 الأهم من القهوة!! من ستشربها معه؟
@@ -16526,19 +16505,19 @@
 1812 gwid3.tumblr </t>
         </is>
       </c>
-      <c r="B765" t="inlineStr">
+      <c r="B764" t="inlineStr">
         <is>
           <t>images/「珈琲で一番大事な事！誰と飲むか？」_img1.jpg</t>
         </is>
       </c>
-      <c r="C765" t="inlineStr">
+      <c r="C764" t="inlineStr">
         <is>
           <t>コーヒー ,名言</t>
         </is>
       </c>
     </row>
-    <row r="766">
-      <c r="A766" t="inlineStr">
+    <row r="765">
+      <c r="A765" t="inlineStr">
         <is>
           <t xml:space="preserve">「人生は美しい、そう望んだ者には。」
 الحياة جَميلَة .. لمن أراد ذلك
@@ -16548,19 +16527,19 @@
 2109 出典不明 </t>
         </is>
       </c>
-      <c r="B766" t="inlineStr">
+      <c r="B765" t="inlineStr">
         <is>
           <t>images/「人生は美しい、そう望んだ者には。」_img1.jpg</t>
         </is>
       </c>
-      <c r="C766" t="inlineStr">
+      <c r="C765" t="inlineStr">
         <is>
           <t>名言 ,アート</t>
         </is>
       </c>
     </row>
-    <row r="767">
-      <c r="A767" t="inlineStr">
+    <row r="766">
+      <c r="A766" t="inlineStr">
         <is>
           <t xml:space="preserve">「ハム太郎って子を知ってるかい」
 هل تعرفون من هو هامتارو
@@ -16570,19 +16549,19 @@
 2109 </t>
         </is>
       </c>
-      <c r="B767" t="inlineStr">
+      <c r="B766" t="inlineStr">
         <is>
           <t>images/「ハム太郎って子を知ってるかい」_img1.jpg</t>
         </is>
       </c>
-      <c r="C767" t="inlineStr">
+      <c r="C766" t="inlineStr">
         <is>
           <t>オープニング ,ハム太郎</t>
         </is>
       </c>
     </row>
-    <row r="768">
-      <c r="A768" t="inlineStr">
+    <row r="767">
+      <c r="A767" t="inlineStr">
         <is>
           <t xml:space="preserve">「幸せを求める人もいれば、作る人もいる」
 هناك من يبحث عن السعادة وهناك من يصنعها
@@ -16591,19 +16570,19 @@
 2308 hindah tumblr </t>
         </is>
       </c>
-      <c r="B768" t="inlineStr">
+      <c r="B767" t="inlineStr">
         <is>
           <t>images/「幸せを求める人もいれば、作る人もいる_img1.jpg</t>
         </is>
       </c>
-      <c r="C768" t="inlineStr">
+      <c r="C767" t="inlineStr">
         <is>
           <t>幸せ ,名言 ,教訓</t>
         </is>
       </c>
     </row>
-    <row r="769">
-      <c r="A769" t="inlineStr">
+    <row r="768">
+      <c r="A768" t="inlineStr">
         <is>
           <t xml:space="preserve">「明白なるアラブの言葉によって」
 بلسان عربي مبين
@@ -16613,19 +16592,19 @@
 2109 Abdullah Barakat behance </t>
         </is>
       </c>
-      <c r="B769" t="inlineStr">
+      <c r="B768" t="inlineStr">
         <is>
           <t>images/「明白なるアラブの言葉によって」_img1.jpg</t>
         </is>
       </c>
-      <c r="C769" t="inlineStr">
+      <c r="C768" t="inlineStr">
         <is>
           <t>イスラム教 ,神聖</t>
         </is>
       </c>
     </row>
-    <row r="770">
-      <c r="A770" t="inlineStr">
+    <row r="769">
+      <c r="A769" t="inlineStr">
         <is>
           <t xml:space="preserve">「結婚前、結婚後」
 قبل الزواج، بعد الزواج
@@ -16635,19 +16614,19 @@
 2308 出典不明 </t>
         </is>
       </c>
-      <c r="B770" t="inlineStr">
+      <c r="B769" t="inlineStr">
         <is>
           <t>images/「結婚前、結婚後」_img1.jpg</t>
         </is>
       </c>
-      <c r="C770" t="inlineStr">
+      <c r="C769" t="inlineStr">
         <is>
           <t>BeforeAfter ,幸せ太り</t>
         </is>
       </c>
     </row>
-    <row r="771">
-      <c r="A771" t="inlineStr">
+    <row r="770">
+      <c r="A770" t="inlineStr">
         <is>
           <t xml:space="preserve">「驚きの価格で」بسعر رائع
 ビスィアル・ラーイア [bi-si*r raa'i*]
@@ -16656,19 +16635,19 @@
 2109 Jarir Bookstore </t>
         </is>
       </c>
-      <c r="B771" t="inlineStr">
+      <c r="B770" t="inlineStr">
         <is>
           <t>images/「驚きの価格で」_img1.jpg</t>
         </is>
       </c>
-      <c r="C771" t="inlineStr">
+      <c r="C770" t="inlineStr">
         <is>
           <t>広告 ,安値</t>
         </is>
       </c>
     </row>
-    <row r="772">
-      <c r="A772" t="inlineStr">
+    <row r="771">
+      <c r="A771" t="inlineStr">
         <is>
           <t xml:space="preserve">「我が魂と共に」مع نفسي
 マア・ナフスィ [ma*a nafs-iy]
@@ -16677,19 +16656,19 @@
 2110 出典不明 </t>
         </is>
       </c>
-      <c r="B772" t="inlineStr">
+      <c r="B771" t="inlineStr">
         <is>
           <t>images/「我が魂と共に」_img1.jpg</t>
         </is>
       </c>
-      <c r="C772" t="inlineStr">
+      <c r="C771" t="inlineStr">
         <is>
           <t>ソウル ,soul</t>
         </is>
       </c>
     </row>
-    <row r="773">
-      <c r="A773" t="inlineStr">
+    <row r="772">
+      <c r="A772" t="inlineStr">
         <is>
           <t xml:space="preserve">「暗い夜に」في ليلة مظلمة
  [fiy layla(tin) mu_Dhlima(tin)]
@@ -16698,19 +16677,19 @@
 2109 سلسلة الحلزونة </t>
         </is>
       </c>
-      <c r="B773" t="inlineStr">
+      <c r="B772" t="inlineStr">
         <is>
           <t>images/「暗い夜に」_img1.jpg</t>
         </is>
       </c>
-      <c r="C773" t="inlineStr">
+      <c r="C772" t="inlineStr">
         <is>
           <t>絵本</t>
         </is>
       </c>
     </row>
-    <row r="774">
-      <c r="A774" t="inlineStr">
+    <row r="773">
+      <c r="A773" t="inlineStr">
         <is>
           <t xml:space="preserve">「ゆっくりと」بشويش
 ビシワェーシ [bi-ShwySh]
@@ -16718,19 +16697,19 @@
 2109 出典不明 </t>
         </is>
       </c>
-      <c r="B774" t="inlineStr">
+      <c r="B773" t="inlineStr">
         <is>
           <t>images/「ゆっくりと」_img1.jpg</t>
         </is>
       </c>
-      <c r="C774" t="inlineStr">
+      <c r="C773" t="inlineStr">
         <is>
           <t>丸 ,円</t>
         </is>
       </c>
     </row>
-    <row r="775">
-      <c r="A775" t="inlineStr">
+    <row r="774">
+      <c r="A774" t="inlineStr">
         <is>
           <t xml:space="preserve">「この広い宇宙に…」
 في الكون الفسيح
@@ -16739,19 +16718,19 @@
 2308 wattpad </t>
         </is>
       </c>
-      <c r="B775" t="inlineStr">
+      <c r="B774" t="inlineStr">
         <is>
           <t>images/「この広い宇宙に…」_img1.jpg</t>
         </is>
       </c>
-      <c r="C775" t="inlineStr">
+      <c r="C774" t="inlineStr">
         <is>
           <t>アニメ ,宇宙</t>
         </is>
       </c>
     </row>
-    <row r="776">
-      <c r="A776" t="inlineStr">
+    <row r="775">
+      <c r="A775" t="inlineStr">
         <is>
           <t xml:space="preserve">「がんばって！」بالتوفيق
 ビッタウフィーク [bi^tawfiiq]
@@ -16759,19 +16738,19 @@
 2111 https://sites.google.com/site/mathmatic1905/ </t>
         </is>
       </c>
-      <c r="B776" t="inlineStr">
+      <c r="B775" t="inlineStr">
         <is>
           <t>images/「がんばって！」_img1.jpg</t>
         </is>
       </c>
-      <c r="C776" t="inlineStr">
+      <c r="C775" t="inlineStr">
         <is>
           <t>アラビア語</t>
         </is>
       </c>
     </row>
-    <row r="777">
-      <c r="A777" t="inlineStr">
+    <row r="776">
+      <c r="A776" t="inlineStr">
         <is>
           <t xml:space="preserve">「インターステラー」بين النجوم
 バイナ_ンヌジューム [bayna ^nujuum]
@@ -16779,19 +16758,19 @@
 2308 kmrghani </t>
         </is>
       </c>
-      <c r="B777" t="inlineStr">
+      <c r="B776" t="inlineStr">
         <is>
           <t>images/「インターステラー」_img1.jpg</t>
         </is>
       </c>
-      <c r="C777" t="inlineStr">
+      <c r="C776" t="inlineStr">
         <is>
           <t>映画 ,宇宙</t>
         </is>
       </c>
     </row>
-    <row r="778">
-      <c r="A778" t="inlineStr">
+    <row r="777">
+      <c r="A777" t="inlineStr">
         <is>
           <t xml:space="preserve">「アラビア語で」بالعربية
 ビ_ルアラビーヤ [bi-l-*arabiyya]
@@ -16800,19 +16779,19 @@
 1811 </t>
         </is>
       </c>
-      <c r="B778" t="inlineStr">
+      <c r="B777" t="inlineStr">
         <is>
           <t>images/「アラビア語で」_img1.jpg</t>
         </is>
       </c>
-      <c r="C778" t="inlineStr">
+      <c r="C777" t="inlineStr">
         <is>
           <t>ニュース ,CNN</t>
         </is>
       </c>
     </row>
-    <row r="779">
-      <c r="A779" t="inlineStr">
+    <row r="778">
+      <c r="A778" t="inlineStr">
         <is>
           <t xml:space="preserve">「17世紀に発明されて以来…」
 منذ اختراعه بالقرن السابع عشر
@@ -16820,19 +16799,19 @@
 2308 https://twitter.com/SciTalk2U/status/1450888395815854080 </t>
         </is>
       </c>
-      <c r="B779" t="inlineStr">
+      <c r="B778" t="inlineStr">
         <is>
           <t>images/「17世紀に発明されて以来…」_img1.jpg</t>
         </is>
       </c>
-      <c r="C779" t="inlineStr">
+      <c r="C778" t="inlineStr">
         <is>
           <t>手書き語学 ,アラビア語 ,望遠鏡</t>
         </is>
       </c>
     </row>
-    <row r="780">
-      <c r="A780" t="inlineStr">
+    <row r="779">
+      <c r="A779" t="inlineStr">
         <is>
           <t xml:space="preserve">「私できるよ」إنّني أستطيع
 インナニー・アスタティーウ ['inna-niy 'a-sta_tii*u]
@@ -16841,19 +16820,19 @@
 2412 سلسلة الحلزونة </t>
         </is>
       </c>
-      <c r="B780" t="inlineStr">
+      <c r="B779" t="inlineStr">
         <is>
           <t>images/「私できるよ」_img1.jpg</t>
         </is>
       </c>
-      <c r="C780" t="inlineStr">
+      <c r="C779" t="inlineStr">
         <is>
           <t>絵本 ,こども</t>
         </is>
       </c>
     </row>
-    <row r="781">
-      <c r="A781" t="inlineStr">
+    <row r="780">
+      <c r="A780" t="inlineStr">
         <is>
           <t xml:space="preserve">「問題なし」مافيش مشكلة
 マフィーシムシュキラ [ma-fy-Sh muShkila]
@@ -16862,19 +16841,19 @@
 2109 tanzerin.theshop </t>
         </is>
       </c>
-      <c r="B781" t="inlineStr">
+      <c r="B780" t="inlineStr">
         <is>
           <t>images/「問題なし」_img1.jpg</t>
         </is>
       </c>
-      <c r="C781" t="inlineStr">
+      <c r="C780" t="inlineStr">
         <is>
           <t>シャツ ,キッズ</t>
         </is>
       </c>
     </row>
-    <row r="782">
-      <c r="A782" t="inlineStr">
+    <row r="781">
+      <c r="A781" t="inlineStr">
         <is>
           <t xml:space="preserve">「不可能はない」مفيش مستحيل
 マフィーシ・ムスタヒール [ma-fy-Sh mustaHiil]
@@ -16883,19 +16862,19 @@
 2109 أموج </t>
         </is>
       </c>
-      <c r="B782" t="inlineStr">
+      <c r="B781" t="inlineStr">
         <is>
           <t>images/「不可能はない」_img1.jpg</t>
         </is>
       </c>
-      <c r="C782" t="inlineStr">
+      <c r="C781" t="inlineStr">
         <is>
           <t>ポジティブ ,挑戦</t>
         </is>
       </c>
     </row>
-    <row r="783">
-      <c r="A783" t="inlineStr">
+    <row r="782">
+      <c r="A782" t="inlineStr">
         <is>
           <t xml:space="preserve">「等々」إلخ
 イラク ['ilaKh]
@@ -16904,19 +16883,19 @@
 2201 出典不明 </t>
         </is>
       </c>
-      <c r="B783" t="inlineStr">
+      <c r="B782" t="inlineStr">
         <is>
           <t>images/「等々」_img1.jpg</t>
         </is>
       </c>
-      <c r="C783" t="inlineStr">
+      <c r="C782" t="inlineStr">
         <is>
           <t>etc ,とんち</t>
         </is>
       </c>
     </row>
-    <row r="784">
-      <c r="A784" t="inlineStr">
+    <row r="783">
+      <c r="A783" t="inlineStr">
         <is>
           <t xml:space="preserve">⁦「調子どう？」⁩شلونَك؟
 シュローナク？ [Sh-loon-ak?]
@@ -16925,19 +16904,19 @@
 2202 Jozoor Team. </t>
         </is>
       </c>
-      <c r="B784" t="inlineStr">
+      <c r="B783" t="inlineStr">
         <is>
           <t>images/⁦「調子どう？」⁩_img1.jpg</t>
         </is>
       </c>
-      <c r="C784" t="inlineStr">
+      <c r="C783" t="inlineStr">
         <is>
           <t>洒落 ,ルービックキューブ</t>
         </is>
       </c>
     </row>
-    <row r="785">
-      <c r="A785" t="inlineStr">
+    <row r="784">
+      <c r="A784" t="inlineStr">
         <is>
           <t xml:space="preserve">「行くな」ماتروحش
 マトロホシ [ma-troH-Sh]
@@ -16946,19 +16925,19 @@
 2411 triiq tumblr </t>
         </is>
       </c>
-      <c r="B785" t="inlineStr">
+      <c r="B784" t="inlineStr">
         <is>
           <t>images/「行くな」_img1.jpg</t>
         </is>
       </c>
-      <c r="C785" t="inlineStr">
+      <c r="C784" t="inlineStr">
         <is>
           <t>ロゴ ,デザイン ,嵐</t>
         </is>
       </c>
     </row>
-    <row r="786">
-      <c r="A786" t="inlineStr">
+    <row r="785">
+      <c r="A785" t="inlineStr">
         <is>
           <t xml:space="preserve">⁦「元気？」⁩شلونَك؟
 シュローナク？ [Sh-loon-ak?]
@@ -16969,19 +16948,19 @@
 2202 出典不明 </t>
         </is>
       </c>
-      <c r="B786" t="inlineStr">
+      <c r="B785" t="inlineStr">
         <is>
           <t>images/⁦「元気？」⁩_img1.jpg</t>
         </is>
       </c>
-      <c r="C786" t="inlineStr">
+      <c r="C785" t="inlineStr">
         <is>
           <t>洒落 ,挨拶</t>
         </is>
       </c>
     </row>
-    <row r="787">
-      <c r="A787" t="inlineStr">
+    <row r="786">
+      <c r="A786" t="inlineStr">
         <is>
           <t xml:space="preserve">「気分が良いぞう」I فيل GOOD
 アイ・フィール・グッド [ai fiyl gud]
@@ -16990,19 +16969,19 @@
 2308 出典不明 </t>
         </is>
       </c>
-      <c r="B787" t="inlineStr">
+      <c r="B786" t="inlineStr">
         <is>
           <t>images/「気分が良いぞう」_img1.jpg</t>
         </is>
       </c>
-      <c r="C787" t="inlineStr">
+      <c r="C786" t="inlineStr">
         <is>
           <t>洒落 ,和訳</t>
         </is>
       </c>
     </row>
-    <row r="788">
-      <c r="A788" t="inlineStr">
+    <row r="787">
+      <c r="A787" t="inlineStr">
         <is>
           <t xml:space="preserve">「レットイットゴー／let it go」
 ليت اِت غو
@@ -17011,19 +16990,19 @@
 2109 出典不明 </t>
         </is>
       </c>
-      <c r="B788" t="inlineStr">
+      <c r="B787" t="inlineStr">
         <is>
           <t>images/「レットイットゴー／let it go_img1.jpg</t>
         </is>
       </c>
-      <c r="C788" t="inlineStr">
+      <c r="C787" t="inlineStr">
         <is>
           <t>折衷 ,アナ雪</t>
         </is>
       </c>
     </row>
-    <row r="789">
-      <c r="A789" t="inlineStr">
+    <row r="788">
+      <c r="A788" t="inlineStr">
         <is>
           <t xml:space="preserve">「ようこそ」اهلا وسهلا
 アハラン・ワサハラン ['ahlan wa-sahlan]
@@ -17031,19 +17010,19 @@
 2106 behance Anwar Al Eissa </t>
         </is>
       </c>
-      <c r="B789" t="inlineStr">
+      <c r="B788" t="inlineStr">
         <is>
           <t>images/「ようこそ」_img1.jpg</t>
         </is>
       </c>
-      <c r="C789" t="inlineStr">
+      <c r="C788" t="inlineStr">
         <is>
           <t>アラビア語</t>
         </is>
       </c>
     </row>
-    <row r="790">
-      <c r="A790" t="inlineStr">
+    <row r="789">
+      <c r="A789" t="inlineStr">
         <is>
           <t xml:space="preserve">「まぁ何というサプライズでしょう」
 يا لها من مفاجأة
@@ -17054,19 +17033,19 @@
 2108 neelwafurat com </t>
         </is>
       </c>
-      <c r="B790" t="inlineStr">
+      <c r="B789" t="inlineStr">
         <is>
           <t>images/「まぁ何というサプライズでしょう」_img1.jpg</t>
         </is>
       </c>
-      <c r="C790" t="inlineStr">
+      <c r="C789" t="inlineStr">
         <is>
           <t>中国語 ,学習</t>
         </is>
       </c>
     </row>
-    <row r="791">
-      <c r="A791" t="inlineStr">
+    <row r="790">
+      <c r="A790" t="inlineStr">
         <is>
           <t xml:space="preserve">「ハックション」اتشوو
 アチュー！ ['aatShuu]
@@ -17074,19 +17053,19 @@
 1811 </t>
         </is>
       </c>
-      <c r="B791" t="inlineStr">
+      <c r="B790" t="inlineStr">
         <is>
           <t>images/「ハックション」_img1.jpg</t>
         </is>
       </c>
-      <c r="C791" t="inlineStr">
+      <c r="C790" t="inlineStr">
         <is>
           <t>あらびあや</t>
         </is>
       </c>
     </row>
-    <row r="792">
-      <c r="A792" t="inlineStr">
+    <row r="791">
+      <c r="A791" t="inlineStr">
         <is>
           <t xml:space="preserve">「スブハーナッラー」「アルハムドゥリッラー」「アッラーアクバル」
 سبحان الله
@@ -17097,19 +17076,19 @@
 2308 dribbble com </t>
         </is>
       </c>
-      <c r="B792" t="inlineStr">
+      <c r="B791" t="inlineStr">
         <is>
           <t>images/「スブハーナッラー」「アルハムドゥリッ_img1.jpg</t>
         </is>
       </c>
-      <c r="C792" t="inlineStr">
+      <c r="C791" t="inlineStr">
         <is>
           <t>四角 ,コンパクト</t>
         </is>
       </c>
     </row>
-    <row r="793">
-      <c r="A793" t="inlineStr">
+    <row r="792">
+      <c r="A792" t="inlineStr">
         <is>
           <t xml:space="preserve">「すごく美味しい！」لذيذ جدًا
 ラズィーズ・ジッダン [laDhiiDh jiddan]
@@ -17118,19 +17097,19 @@
 2109 goodreads com </t>
         </is>
       </c>
-      <c r="B793" t="inlineStr">
+      <c r="B792" t="inlineStr">
         <is>
           <t>images/「すごく美味しい！」_img1.jpg</t>
         </is>
       </c>
-      <c r="C793" t="inlineStr">
+      <c r="C792" t="inlineStr">
         <is>
           <t>フレーズ ,感想</t>
         </is>
       </c>
     </row>
-    <row r="794">
-      <c r="A794" t="inlineStr">
+    <row r="793">
+      <c r="A793" t="inlineStr">
         <is>
           <t xml:space="preserve">「しとしと、雨」تك تك يا مطر
 ティクティク [tik tik yaa ma_tar]
@@ -17139,19 +17118,19 @@
 2308 出典不明 </t>
         </is>
       </c>
-      <c r="B794" t="inlineStr">
+      <c r="B793" t="inlineStr">
         <is>
           <t>images/「しとしと、雨」_img1.jpg</t>
         </is>
       </c>
-      <c r="C794" t="inlineStr">
+      <c r="C793" t="inlineStr">
         <is>
           <t>天気 ,梅雨</t>
         </is>
       </c>
     </row>
-    <row r="795">
-      <c r="A795" t="inlineStr">
+    <row r="794">
+      <c r="A794" t="inlineStr">
         <is>
           <t xml:space="preserve">「さかさま」رأساً على عقب
 ラッアサン・アラー・アケブ [ra'san *alaa *aqib]
@@ -17159,19 +17138,19 @@
 2109 出典不明 </t>
         </is>
       </c>
-      <c r="B795" t="inlineStr">
+      <c r="B794" t="inlineStr">
         <is>
           <t>images/「さかさま」_img1.jpg</t>
         </is>
       </c>
-      <c r="C795" t="inlineStr">
+      <c r="C794" t="inlineStr">
         <is>
           <t>壁 ,上下</t>
         </is>
       </c>
     </row>
-    <row r="796">
-      <c r="A796" t="inlineStr">
+    <row r="795">
+      <c r="A795" t="inlineStr">
         <is>
           <t xml:space="preserve">「エジプトよどこへ行った」
 فينك يا مصر؟
@@ -17181,19 +17160,19 @@
 1809 shehabfawzy1.tumblr </t>
         </is>
       </c>
-      <c r="B796" t="inlineStr">
+      <c r="B795" t="inlineStr">
         <is>
           <t>images/「エジプトよどこへ行った」_img1.jpg</t>
         </is>
       </c>
-      <c r="C796" t="inlineStr">
+      <c r="C795" t="inlineStr">
         <is>
           <t>ピラミッド ,歴史</t>
         </is>
       </c>
     </row>
-    <row r="797">
-      <c r="A797" t="inlineStr">
+    <row r="796">
+      <c r="A796" t="inlineStr">
         <is>
           <t xml:space="preserve">「ありがとう」شكراً
 シュクラン [Shukran]
@@ -17201,19 +17180,19 @@
 2109 出典不明 </t>
         </is>
       </c>
-      <c r="B797" t="inlineStr">
+      <c r="B796" t="inlineStr">
         <is>
           <t>images/「ありがとう」_img1.jpg</t>
         </is>
       </c>
-      <c r="C797" t="inlineStr">
+      <c r="C796" t="inlineStr">
         <is>
           <t>挨拶 ,文字</t>
         </is>
       </c>
     </row>
-    <row r="798">
-      <c r="A798" t="inlineStr">
+    <row r="797">
+      <c r="A797" t="inlineStr">
         <is>
           <t xml:space="preserve">「昼寝の時間だ」
 إنه وقت القيلولة
@@ -17222,12 +17201,12 @@
 2501 https://x.com/NatGeoMagArab/status/1858049951579910486 </t>
         </is>
       </c>
-      <c r="B798" t="inlineStr">
+      <c r="B797" t="inlineStr">
         <is>
           <t>images/「昼寝の時間だ」_img1.jpg</t>
         </is>
       </c>
-      <c r="C798" t="inlineStr">
+      <c r="C797" t="inlineStr">
         <is>
           <t>手書き語学 ,アラビア語 ,ペンギン</t>
         </is>

--- a/posts.xlsx
+++ b/posts.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C797"/>
+  <dimension ref="A1:C796"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -8641,27 +8641,6 @@
     <row r="393">
       <c r="A393" t="inlineStr">
         <is>
-          <t xml:space="preserve">「満足は幸福」الرضا سعادة
-アッリダー・サアーダ [a^ri_daa sa*aada]
-「満足は」[a^ri_daa]・「幸福である」[sa*aadatun]
-満足（マンゾク）・幸福（コウフク）
-2304 Tip Of The Day, Pinterest </t>
-        </is>
-      </c>
-      <c r="B393" t="inlineStr">
-        <is>
-          <t>images/「満足は幸福」_img1.jpg</t>
-        </is>
-      </c>
-      <c r="C393" t="inlineStr">
-        <is>
-          <t>happiness ,satisfaction</t>
-        </is>
-      </c>
-    </row>
-    <row r="394">
-      <c r="A394" t="inlineStr">
-        <is>
           <t xml:space="preserve">「美しい字は目で見る音楽」
 الخط الجميل موسيقى العيون
 [al-Kha^_tu l-jamiilu muusiiqa l-*uyuun]
@@ -8670,19 +8649,19 @@
 2308 Noha Raheem, Behance </t>
         </is>
       </c>
-      <c r="B394" t="inlineStr">
+      <c r="B393" t="inlineStr">
         <is>
           <t>images/「美しい字は目で見る音楽」_img1.jpg</t>
         </is>
       </c>
-      <c r="C394" t="inlineStr">
+      <c r="C393" t="inlineStr">
         <is>
           <t>デザイン ,四角</t>
         </is>
       </c>
     </row>
-    <row r="395">
-      <c r="A395" t="inlineStr">
+    <row r="394">
+      <c r="A394" t="inlineStr">
         <is>
           <t xml:space="preserve">「目は心の窓」
 العيون نوافذ الروح
@@ -8692,19 +8671,19 @@
 2308 amani-m.tumblr.com </t>
         </is>
       </c>
-      <c r="B395" t="inlineStr">
+      <c r="B394" t="inlineStr">
         <is>
           <t>images/「目は心の窓」_img1.jpg</t>
         </is>
       </c>
-      <c r="C395" t="inlineStr">
+      <c r="C394" t="inlineStr">
         <is>
           <t>知覚 ,情報</t>
         </is>
       </c>
     </row>
-    <row r="396">
-      <c r="A396" t="inlineStr">
+    <row r="395">
+      <c r="A395" t="inlineStr">
         <is>
           <t xml:space="preserve">「美は心の美」
 الجمال جمال الروح
@@ -8714,19 +8693,19 @@
 2308 KiTeLetZ </t>
         </is>
       </c>
-      <c r="B396" t="inlineStr">
+      <c r="B395" t="inlineStr">
         <is>
           <t>images/「美は心の美」_img1.jpg</t>
         </is>
       </c>
-      <c r="C396" t="inlineStr">
+      <c r="C395" t="inlineStr">
         <is>
           <t>内面 ,外面</t>
         </is>
       </c>
     </row>
-    <row r="397">
-      <c r="A397" t="inlineStr">
+    <row r="396">
+      <c r="A396" t="inlineStr">
         <is>
           <t xml:space="preserve">「字は手による声なり」
 الخط لسان اليد
@@ -8736,19 +8715,19 @@
 2301 出典不明 </t>
         </is>
       </c>
-      <c r="B397" t="inlineStr">
+      <c r="B396" t="inlineStr">
         <is>
           <t>images/「字は手による声なり」_img1.jpg</t>
         </is>
       </c>
-      <c r="C397" t="inlineStr">
+      <c r="C396" t="inlineStr">
         <is>
           <t>筆跡 ,達筆</t>
         </is>
       </c>
     </row>
-    <row r="398">
-      <c r="A398" t="inlineStr">
+    <row r="397">
+      <c r="A397" t="inlineStr">
         <is>
           <t xml:space="preserve">「忍耐は幸福の鍵」
 الصبر مفتاح الفرج
@@ -8758,19 +8737,19 @@
 2109 GEEMARTWORKS </t>
         </is>
       </c>
-      <c r="B398" t="inlineStr">
+      <c r="B397" t="inlineStr">
         <is>
           <t>images/「忍耐は幸福の鍵」_img1.jpg</t>
         </is>
       </c>
-      <c r="C398" t="inlineStr">
+      <c r="C397" t="inlineStr">
         <is>
           <t>キー ,ことわざ</t>
         </is>
       </c>
     </row>
-    <row r="399">
-      <c r="A399" t="inlineStr">
+    <row r="398">
+      <c r="A398" t="inlineStr">
         <is>
           <t xml:space="preserve">「失敗は成功の始まり」
 الفشل بداية النجاح
@@ -8780,19 +8759,19 @@
 2308 Emad, dribbble com </t>
         </is>
       </c>
-      <c r="B399" t="inlineStr">
+      <c r="B398" t="inlineStr">
         <is>
           <t>images/「失敗は成功の始まり」_img1.jpg</t>
         </is>
       </c>
-      <c r="C399" t="inlineStr">
+      <c r="C398" t="inlineStr">
         <is>
           <t>練習 ,研究</t>
         </is>
       </c>
     </row>
-    <row r="400">
-      <c r="A400" t="inlineStr">
+    <row r="399">
+      <c r="A399" t="inlineStr">
         <is>
           <t xml:space="preserve">「俺は大きいパズル、理解不能」
 أنا لغز كبير، مش فاهمه
@@ -8802,19 +8781,19 @@
 2109 AHMED-ELDARS tumblr </t>
         </is>
       </c>
-      <c r="B400" t="inlineStr">
+      <c r="B399" t="inlineStr">
         <is>
           <t>images/「俺は大きいパズル、理解不能」_img1.jpg</t>
         </is>
       </c>
-      <c r="C400" t="inlineStr">
+      <c r="C399" t="inlineStr">
         <is>
           <t>ルービックキューブ</t>
         </is>
       </c>
     </row>
-    <row r="401">
-      <c r="A401" t="inlineStr">
+    <row r="400">
+      <c r="A400" t="inlineStr">
         <is>
           <t xml:space="preserve">「わたしは夜行人間だ」
 أنا انسان ليلي
@@ -8824,37 +8803,37 @@
 1811 Nasser.Tumblr </t>
         </is>
       </c>
+      <c r="B400" t="inlineStr">
+        <is>
+          <t>images/「わたしは夜行人間だ」.jpg</t>
+        </is>
+      </c>
+      <c r="C400" t="inlineStr">
+        <is>
+          <t>夜型 ,ネオン</t>
+        </is>
+      </c>
+    </row>
+    <row r="401">
+      <c r="A401" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ツノメドリ。
+2308 https://twitter.com/NatGeoMagArab/status/1523188657288466433 </t>
+        </is>
+      </c>
       <c r="B401" t="inlineStr">
         <is>
-          <t>images/「わたしは夜行人間だ」.jpg</t>
+          <t>images/ツノメドリ。_img1.jpg,images/ツノメドリ。_img2.jpg,images/ツノメドリ。_img3.jpg</t>
         </is>
       </c>
       <c r="C401" t="inlineStr">
         <is>
-          <t>夜型 ,ネオン</t>
+          <t>手書き語学 ,アラビア語 ,ツノメドリ</t>
         </is>
       </c>
     </row>
     <row r="402">
       <c r="A402" t="inlineStr">
-        <is>
-          <t xml:space="preserve">ツノメドリ。
-2308 https://twitter.com/NatGeoMagArab/status/1523188657288466433 </t>
-        </is>
-      </c>
-      <c r="B402" t="inlineStr">
-        <is>
-          <t>images/ツノメドリ。_img1.jpg,images/ツノメドリ。_img2.jpg,images/ツノメドリ。_img3.jpg</t>
-        </is>
-      </c>
-      <c r="C402" t="inlineStr">
-        <is>
-          <t>手書き語学 ,アラビア語 ,ツノメドリ</t>
-        </is>
-      </c>
-    </row>
-    <row r="403">
-      <c r="A403" t="inlineStr">
         <is>
           <t xml:space="preserve">「沈黙は神聖な言語である」
 الصمت لغة قدسية
@@ -8864,19 +8843,19 @@
 2308 Behance, Noha Raheem </t>
         </is>
       </c>
-      <c r="B403" t="inlineStr">
+      <c r="B402" t="inlineStr">
         <is>
           <t>images/「沈黙は神聖な言語である」_img1.jpg</t>
         </is>
       </c>
-      <c r="C403" t="inlineStr">
+      <c r="C402" t="inlineStr">
         <is>
           <t>四角 ,名言</t>
         </is>
       </c>
     </row>
-    <row r="404">
-      <c r="A404" t="inlineStr">
+    <row r="403">
+      <c r="A403" t="inlineStr">
         <is>
           <t xml:space="preserve">「このメスヒグマはベテランハンターだ」
 أنثى الدب البني هذه صيادة مخضرمة
@@ -8884,19 +8863,19 @@
 2308 https://twitter.com/NatGeoMagArab/status/1534422596367708161 </t>
         </is>
       </c>
-      <c r="B404" t="inlineStr">
+      <c r="B403" t="inlineStr">
         <is>
           <t>images/「このメスヒグマはベテランハンターだ」_img1.jpg</t>
         </is>
       </c>
-      <c r="C404" t="inlineStr">
+      <c r="C403" t="inlineStr">
         <is>
           <t xml:space="preserve">手書き語学 ,ヒグマ </t>
         </is>
       </c>
     </row>
-    <row r="405">
-      <c r="A405" t="inlineStr">
+    <row r="404">
+      <c r="A404" t="inlineStr">
         <is>
           <t xml:space="preserve">「希望の窓は開いている」
 شباك الأمل مفتوح
@@ -8906,19 +8885,19 @@
 2511 www facebook com/people/شباك-الامل-مفتوح/100069119657701/ </t>
         </is>
       </c>
-      <c r="B405" t="inlineStr">
+      <c r="B404" t="inlineStr">
         <is>
           <t>images/「希望の窓は開いている」_img1.jpg</t>
         </is>
       </c>
-      <c r="C405" t="inlineStr">
+      <c r="C404" t="inlineStr">
         <is>
           <t>窓 ,希望の光</t>
         </is>
       </c>
     </row>
-    <row r="406">
-      <c r="A406" t="inlineStr">
+    <row r="405">
+      <c r="A405" t="inlineStr">
         <is>
           <t xml:space="preserve">「あなたの夏は涼しい」
 صيفك بارد
@@ -8928,19 +8907,19 @@
 2108 Othaim Markets </t>
         </is>
       </c>
-      <c r="B406" t="inlineStr">
+      <c r="B405" t="inlineStr">
         <is>
           <t>images/「あなたの夏は涼しい」_img1.jpg</t>
         </is>
       </c>
-      <c r="C406" t="inlineStr">
+      <c r="C405" t="inlineStr">
         <is>
           <t>アラビア語</t>
         </is>
       </c>
     </row>
-    <row r="407">
-      <c r="A407" t="inlineStr">
+    <row r="406">
+      <c r="A406" t="inlineStr">
         <is>
           <t xml:space="preserve">「あなたがこのネコに出会う確率はほぼゼロだ」
 احتمالات لقائك هذا السنور شبه منعدمة
@@ -8949,15 +8928,15 @@
 2607 https://x.com/NatGeoMagArab/status/1977275594099622012 </t>
         </is>
       </c>
-      <c r="B407" t="inlineStr"/>
-      <c r="C407" t="inlineStr">
+      <c r="B406" t="inlineStr"/>
+      <c r="C406" t="inlineStr">
         <is>
           <t>手書き語学 ,アラビア語 ,ヒョウ</t>
         </is>
       </c>
     </row>
-    <row r="408">
-      <c r="A408" t="inlineStr">
+    <row r="407">
+      <c r="A407" t="inlineStr">
         <is>
           <t xml:space="preserve">「このシャツは2000リヤルです」
 هذا القميص سعره 2000 ريال
@@ -8967,19 +8946,19 @@
 2102 </t>
         </is>
       </c>
-      <c r="B408" t="inlineStr">
+      <c r="B407" t="inlineStr">
         <is>
           <t>images/「このシャツは2000リヤルです」_img1.jpg</t>
         </is>
       </c>
-      <c r="C408" t="inlineStr">
+      <c r="C407" t="inlineStr">
         <is>
           <t>あらびあや</t>
         </is>
       </c>
     </row>
-    <row r="409">
-      <c r="A409" t="inlineStr">
+    <row r="408">
+      <c r="A408" t="inlineStr">
         <is>
           <t xml:space="preserve">「これが人生」هذه هي الحياة
 ハーズィヒ・ヒヤ・アルハヤート [haaDhihi hiya al-Hayaat]
@@ -8988,19 +8967,19 @@
 2108 flickr com, abdoegypt16 </t>
         </is>
       </c>
-      <c r="B409" t="inlineStr">
+      <c r="B408" t="inlineStr">
         <is>
           <t>images/「これが人生」_img1.jpg</t>
         </is>
       </c>
-      <c r="C409" t="inlineStr">
+      <c r="C408" t="inlineStr">
         <is>
           <t>陰陽 ,life</t>
         </is>
       </c>
     </row>
-    <row r="410">
-      <c r="A410" t="inlineStr">
+    <row r="409">
+      <c r="A409" t="inlineStr">
         <is>
           <t xml:space="preserve">「おとうさんといっしょ」
 أبي معي
@@ -9009,19 +8988,19 @@
 2402 darashjar com/products/abi_ma3i </t>
         </is>
       </c>
-      <c r="B410" t="inlineStr">
+      <c r="B409" t="inlineStr">
         <is>
           <t>images/「おとうさんといっしょ」_img1.jpg,images/ 「おとうさんといっしょ」_img2.jpg</t>
         </is>
       </c>
-      <c r="C410" t="inlineStr">
+      <c r="C409" t="inlineStr">
         <is>
           <t>絵本 ,父</t>
         </is>
       </c>
     </row>
-    <row r="411">
-      <c r="A411" t="inlineStr">
+    <row r="410">
+      <c r="A410" t="inlineStr">
         <is>
           <t xml:space="preserve">「コーヒー無料です」
 قهوتك علينا
@@ -9031,19 +9010,19 @@
 2506 Capital Bank </t>
         </is>
       </c>
-      <c r="B411" t="inlineStr">
+      <c r="B410" t="inlineStr">
         <is>
           <t>images/「コーヒー無料です」_img1.jpg</t>
         </is>
       </c>
-      <c r="C411" t="inlineStr">
+      <c r="C410" t="inlineStr">
         <is>
           <t>キャンペーン ,会員限定</t>
         </is>
       </c>
     </row>
-    <row r="412">
-      <c r="A412" t="inlineStr">
+    <row r="411">
+      <c r="A411" t="inlineStr">
         <is>
           <t xml:space="preserve">「祖母が私を待っています」
 جدتي في انتظاري
@@ -9053,19 +9032,19 @@
 2103 </t>
         </is>
       </c>
-      <c r="B412" t="inlineStr">
+      <c r="B411" t="inlineStr">
         <is>
           <t>images/「祖母が私を待っています」_img1.jpg</t>
         </is>
       </c>
-      <c r="C412" t="inlineStr">
+      <c r="C411" t="inlineStr">
         <is>
           <t>あらびあや</t>
         </is>
       </c>
     </row>
-    <row r="413">
-      <c r="A413" t="inlineStr">
+    <row r="412">
+      <c r="A412" t="inlineStr">
         <is>
           <t xml:space="preserve">「アルハムドゥリッラー」
 الحمد لله
@@ -9075,19 +9054,19 @@
 2108 出典不明 </t>
         </is>
       </c>
-      <c r="B413" t="inlineStr">
+      <c r="B412" t="inlineStr">
         <is>
           <t>images/「アルハムドゥリッラー」_img1.jpg</t>
         </is>
       </c>
-      <c r="C413" t="inlineStr">
+      <c r="C412" t="inlineStr">
         <is>
           <t>挨拶 ,ThankGod</t>
         </is>
       </c>
     </row>
-    <row r="414">
-      <c r="A414" t="inlineStr">
+    <row r="413">
+      <c r="A413" t="inlineStr">
         <is>
           <t xml:space="preserve">「こんにちは」
 السلام عليكم ورحمة الله وبركاته
@@ -9095,19 +9074,19 @@
 2109 出典不明 </t>
         </is>
       </c>
-      <c r="B414" t="inlineStr">
+      <c r="B413" t="inlineStr">
         <is>
           <t>images/「こんにちは」_img1.jpg</t>
         </is>
       </c>
-      <c r="C414" t="inlineStr">
+      <c r="C413" t="inlineStr">
         <is>
           <t>挨拶 ,四角</t>
         </is>
       </c>
     </row>
-    <row r="415">
-      <c r="A415" t="inlineStr">
+    <row r="414">
+      <c r="A414" t="inlineStr">
         <is>
           <t xml:space="preserve">「力は団結にあり」
 قوتنا في وحدتنا
@@ -9117,19 +9096,19 @@
 2308 Mahmoud Elhosary </t>
         </is>
       </c>
-      <c r="B415" t="inlineStr">
+      <c r="B414" t="inlineStr">
         <is>
           <t>images/「力は団結にあり」_img1.jpg</t>
         </is>
       </c>
-      <c r="C415" t="inlineStr">
+      <c r="C414" t="inlineStr">
         <is>
           <t>パワー ,unity</t>
         </is>
       </c>
     </row>
-    <row r="416">
-      <c r="A416" t="inlineStr">
+    <row r="415">
+      <c r="A415" t="inlineStr">
         <is>
           <t xml:space="preserve">「貴女の両目は聖堂の灯火のよう」
 عيناك كقنديلي معبد
@@ -9139,19 +9118,19 @@
 2108 TASNEEM A. A-AWAD </t>
         </is>
       </c>
-      <c r="B416" t="inlineStr">
+      <c r="B415" t="inlineStr">
         <is>
           <t>images/「貴女の両目は聖堂の灯火のよう」_img1.jpg</t>
         </is>
       </c>
-      <c r="C416" t="inlineStr">
+      <c r="C415" t="inlineStr">
         <is>
           <t>恋 ,双数形</t>
         </is>
       </c>
     </row>
-    <row r="417">
-      <c r="A417" t="inlineStr">
+    <row r="416">
+      <c r="A416" t="inlineStr">
         <is>
           <t xml:space="preserve">「こんにちは」3Dクーフィー体
 السلام عليكم
@@ -9160,19 +9139,19 @@
 2309 mohd zaid </t>
         </is>
       </c>
-      <c r="B417" t="inlineStr">
+      <c r="B416" t="inlineStr">
         <is>
           <t>images/「こんにちは」3Dクーフィー体_img1.jpg</t>
         </is>
       </c>
-      <c r="C417" t="inlineStr">
+      <c r="C416" t="inlineStr">
         <is>
           <t>挨拶 ,3D</t>
         </is>
       </c>
     </row>
-    <row r="418">
-      <c r="A418" t="inlineStr">
+    <row r="417">
+      <c r="A417" t="inlineStr">
         <is>
           <t xml:space="preserve">「我が子は心の一部」
 أولادي قطعة من قلبي
@@ -9182,19 +9161,19 @@
 2308 出典不明 </t>
         </is>
       </c>
-      <c r="B418" t="inlineStr">
+      <c r="B417" t="inlineStr">
         <is>
           <t>images/「我が子は心の一部」_img1.jpg</t>
         </is>
       </c>
-      <c r="C418" t="inlineStr">
+      <c r="C417" t="inlineStr">
         <is>
           <t>親心 ,愛</t>
         </is>
       </c>
     </row>
-    <row r="419">
-      <c r="A419" t="inlineStr">
+    <row r="418">
+      <c r="A418" t="inlineStr">
         <is>
           <t xml:space="preserve">「あなた達の世界では私は変わり者だ」
 أنا غَريب بعالمكم
@@ -9204,19 +9183,19 @@
 2308 https://instagram.com/p/mifbZlQEUv/ </t>
         </is>
       </c>
-      <c r="B419" t="inlineStr">
+      <c r="B418" t="inlineStr">
         <is>
           <t>images/「あなた達の世界では私は変わり者だ」_img1.jpg</t>
         </is>
       </c>
-      <c r="C419" t="inlineStr">
+      <c r="C418" t="inlineStr">
         <is>
           <t>特異点 ,ユニーク</t>
         </is>
       </c>
     </row>
-    <row r="420">
-      <c r="A420" t="inlineStr">
+    <row r="419">
+      <c r="A419" t="inlineStr">
         <is>
           <t xml:space="preserve">「ぼくのズボンが短すぎる」
 بنطالي قصير عليّ
@@ -9226,19 +9205,19 @@
 2506 alsawlabooks </t>
         </is>
       </c>
-      <c r="B420" t="inlineStr">
+      <c r="B419" t="inlineStr">
         <is>
           <t>images/「ぼくのズボンが短すぎる」_img1.jpg</t>
         </is>
       </c>
-      <c r="C420" t="inlineStr">
+      <c r="C419" t="inlineStr">
         <is>
           <t>絵本 ,成長期</t>
         </is>
       </c>
     </row>
-    <row r="421">
-      <c r="A421" t="inlineStr">
+    <row r="420">
+      <c r="A420" t="inlineStr">
         <is>
           <t xml:space="preserve">「行動は口頭よりも雄弁」
 الأفعَال أبلغ مِن الأقوَال
@@ -9248,19 +9227,19 @@
 2506 tamtam chat/sosoayosh/AXhWnemZHH0 </t>
         </is>
       </c>
-      <c r="B421" t="inlineStr">
+      <c r="B420" t="inlineStr">
         <is>
           <t>images/「行動は口頭よりも雄弁」_img1.jpg</t>
         </is>
       </c>
-      <c r="C421" t="inlineStr">
+      <c r="C420" t="inlineStr">
         <is>
           <t>和訳 ,諺</t>
         </is>
       </c>
     </row>
-    <row r="422">
-      <c r="A422" t="inlineStr">
+    <row r="421">
+      <c r="A421" t="inlineStr">
         <is>
           <t xml:space="preserve">「ウサイン・ボルトは彼ら二人よりも速い」
 يوسين بولت أسرع منهما
@@ -9270,19 +9249,19 @@
 2108 </t>
         </is>
       </c>
-      <c r="B422" t="inlineStr">
+      <c r="B421" t="inlineStr">
         <is>
           <t>images/「ウサイン・ボルトは彼ら二人よりも速い_img1.jpg</t>
         </is>
       </c>
-      <c r="C422" t="inlineStr">
+      <c r="C421" t="inlineStr">
         <is>
           <t>あらびあや</t>
         </is>
       </c>
     </row>
-    <row r="423">
-      <c r="A423" t="inlineStr">
+    <row r="422">
+      <c r="A422" t="inlineStr">
         <is>
           <t xml:space="preserve">「自宅とは毎日の終わりを過ごす最高の場所」
 منزلك هو مكانك المفضل في نهاية كل يوم
@@ -9291,19 +9270,19 @@
 2508 Ecotectt 害虫駆除サービス </t>
         </is>
       </c>
-      <c r="B423" t="inlineStr">
+      <c r="B422" t="inlineStr">
         <is>
           <t>images/「自宅とは毎日の終わりを過ごす最高の場_img1.jpg</t>
         </is>
       </c>
-      <c r="C423" t="inlineStr">
+      <c r="C422" t="inlineStr">
         <is>
           <t>おうち</t>
         </is>
       </c>
     </row>
-    <row r="424">
-      <c r="A424" t="inlineStr">
+    <row r="423">
+      <c r="A423" t="inlineStr">
         <is>
           <t xml:space="preserve">「サイフォのへやにはもりがある」
 في غرفة سيفو غابة
@@ -9312,19 +9291,19 @@
 2308 Maktabatee com </t>
         </is>
       </c>
-      <c r="B424" t="inlineStr">
+      <c r="B423" t="inlineStr">
         <is>
           <t>images/「サイフォのへやにはもりがある」_img1.jpg</t>
         </is>
       </c>
-      <c r="C424" t="inlineStr">
+      <c r="C423" t="inlineStr">
         <is>
           <t>絵本 ,ジャングル</t>
         </is>
       </c>
     </row>
-    <row r="425">
-      <c r="A425" t="inlineStr">
+    <row r="424">
+      <c r="A424" t="inlineStr">
         <is>
           <t xml:space="preserve">「大きい夢には小さい始まりがある」
 للأحلام الكبيرة بدايات صغيرة
@@ -9333,19 +9312,19 @@
 2109 in4sser.tumblr </t>
         </is>
       </c>
-      <c r="B425" t="inlineStr">
+      <c r="B424" t="inlineStr">
         <is>
           <t>images/「大きい夢には小さい始まりがある」_img1.jpg</t>
         </is>
       </c>
-      <c r="C425" t="inlineStr">
+      <c r="C424" t="inlineStr">
         <is>
           <t>きっかけ ,イラスト</t>
         </is>
       </c>
     </row>
-    <row r="426">
-      <c r="A426" t="inlineStr">
+    <row r="425">
+      <c r="A425" t="inlineStr">
         <is>
           <t xml:space="preserve">「私に考えがある」عندي فكرة
 インディー・フィクラ [*ind-iy fikra]
@@ -9354,19 +9333,19 @@
 2506 facebook 3endy.fekra </t>
         </is>
       </c>
-      <c r="B426" t="inlineStr">
+      <c r="B425" t="inlineStr">
         <is>
           <t>images/「私に考えがある」_img1.jpg</t>
         </is>
       </c>
-      <c r="C426" t="inlineStr">
+      <c r="C425" t="inlineStr">
         <is>
           <t>アイデア ,ロゴ</t>
         </is>
       </c>
     </row>
-    <row r="427">
-      <c r="A427" t="inlineStr">
+    <row r="426">
+      <c r="A426" t="inlineStr">
         <is>
           <t xml:space="preserve">「私はペンを持っています」
 عِنْدِي قَلَم
@@ -9376,19 +9355,19 @@
 2103 </t>
         </is>
       </c>
-      <c r="B427" t="inlineStr">
+      <c r="B426" t="inlineStr">
         <is>
           <t>images/「私はペンを持っています」_img1.jpg</t>
         </is>
       </c>
-      <c r="C427" t="inlineStr">
+      <c r="C426" t="inlineStr">
         <is>
           <t>あらびあや</t>
         </is>
       </c>
     </row>
-    <row r="428">
-      <c r="A428" t="inlineStr">
+    <row r="427">
+      <c r="A427" t="inlineStr">
         <is>
           <t xml:space="preserve">「先史時代の驚くべき真実」
 حقائق مدهشة ما قبل التاريخ
@@ -9398,19 +9377,19 @@
 2311 agatha-christie site </t>
         </is>
       </c>
-      <c r="B428" t="inlineStr">
+      <c r="B427" t="inlineStr">
         <is>
           <t>images/「先史時代の驚くべき真実」_img1.jpg</t>
         </is>
       </c>
-      <c r="C428" t="inlineStr">
+      <c r="C427" t="inlineStr">
         <is>
           <t>歴史 ,恐竜</t>
         </is>
       </c>
     </row>
-    <row r="429">
-      <c r="A429" t="inlineStr">
+    <row r="428">
+      <c r="A428" t="inlineStr">
         <is>
           <t xml:space="preserve">「私たちは一人一人胸の中に物語を持っている」
 كل واحد منا في قلبه حكاية
@@ -9419,19 +9398,19 @@
 2308 出典不明 </t>
         </is>
       </c>
-      <c r="B429" t="inlineStr">
+      <c r="B428" t="inlineStr">
         <is>
           <t>images/「私たちは一人一人胸の中に物語を持って_img1.jpg</t>
         </is>
       </c>
-      <c r="C429" t="inlineStr">
+      <c r="C428" t="inlineStr">
         <is>
           <t>ハート ,心臓</t>
         </is>
       </c>
     </row>
-    <row r="430">
-      <c r="A430" t="inlineStr">
+    <row r="429">
+      <c r="A429" t="inlineStr">
         <is>
           <t xml:space="preserve">「旅にはいくつかの利点がある」
 في السفر عدة فوائد
@@ -9441,19 +9420,19 @@
 2105 PRIVATE NAIL SALON KEYS </t>
         </is>
       </c>
-      <c r="B430" t="inlineStr">
+      <c r="B429" t="inlineStr">
         <is>
           <t>images/「旅にはいくつかの利点がある」_img1.jpg</t>
         </is>
       </c>
-      <c r="C430" t="inlineStr">
+      <c r="C429" t="inlineStr">
         <is>
           <t>可愛い子には ,ネイルサロン</t>
         </is>
       </c>
     </row>
-    <row r="431">
-      <c r="A431" t="inlineStr">
+    <row r="430">
+      <c r="A430" t="inlineStr">
         <is>
           <t xml:space="preserve">「全ての窓の奥に物語がある」
 وراء كل نافذة حكاية
@@ -9463,19 +9442,19 @@
 2308 maram </t>
         </is>
       </c>
-      <c r="B431" t="inlineStr">
+      <c r="B430" t="inlineStr">
         <is>
           <t>images/「全ての窓の奥に物語がある」_img1.jpg</t>
         </is>
       </c>
-      <c r="C431" t="inlineStr">
+      <c r="C430" t="inlineStr">
         <is>
           <t>ストーリー ,マンション</t>
         </is>
       </c>
     </row>
-    <row r="432">
-      <c r="A432" t="inlineStr">
+    <row r="431">
+      <c r="A431" t="inlineStr">
         <is>
           <t xml:space="preserve">「恐れていては生きていけぬ」
 لا عيش لخائف
@@ -9485,19 +9464,19 @@
 2608 elshaarani </t>
         </is>
       </c>
-      <c r="B432" t="inlineStr">
+      <c r="B431" t="inlineStr">
         <is>
           <t>images/「恐れていては生きていけぬ」_img1.jpg</t>
         </is>
       </c>
-      <c r="C432" t="inlineStr">
+      <c r="C431" t="inlineStr">
         <is>
           <t>勇気 ,恐怖</t>
         </is>
       </c>
     </row>
-    <row r="433">
-      <c r="A433" t="inlineStr">
+    <row r="432">
+      <c r="A432" t="inlineStr">
         <is>
           <t xml:space="preserve">「宗教には強制があってはならない」
 لا إكراه في الدين
@@ -9507,19 +9486,19 @@
 2107 出典不明 </t>
         </is>
       </c>
-      <c r="B433" t="inlineStr">
+      <c r="B432" t="inlineStr">
         <is>
           <t>images/「宗教には強制があってはならない」_img1.jpg</t>
         </is>
       </c>
-      <c r="C433" t="inlineStr">
+      <c r="C432" t="inlineStr">
         <is>
           <t>イスラム教 ,言葉</t>
         </is>
       </c>
     </row>
-    <row r="434">
-      <c r="A434" t="inlineStr">
+    <row r="433">
+      <c r="A433" t="inlineStr">
         <is>
           <t xml:space="preserve">「君の目以前に歴史なし」
 لَا تَارِيخَ قَبلَ عَينيكِ
@@ -9529,19 +9508,19 @@
 2410 facebook com/photo/?fbid=418502147070626 </t>
         </is>
       </c>
-      <c r="B434" t="inlineStr">
+      <c r="B433" t="inlineStr">
         <is>
           <t>images/「君の目以前に歴史なし」_img1.jpg</t>
         </is>
       </c>
-      <c r="C434" t="inlineStr">
+      <c r="C433" t="inlineStr">
         <is>
           <t>一目惚れ ,有史</t>
         </is>
       </c>
     </row>
-    <row r="435">
-      <c r="A435" t="inlineStr">
+    <row r="434">
+      <c r="A434" t="inlineStr">
         <is>
           <t xml:space="preserve">「これはスシですか」
 هل هذا سوشي؟
@@ -9550,19 +9529,19 @@
 2302 </t>
         </is>
       </c>
-      <c r="B435" t="inlineStr">
+      <c r="B434" t="inlineStr">
         <is>
           <t>images/「これはスシですか」_img1.jpg</t>
         </is>
       </c>
-      <c r="C435" t="inlineStr">
+      <c r="C434" t="inlineStr">
         <is>
           <t>あらびあや</t>
         </is>
       </c>
     </row>
-    <row r="436">
-      <c r="A436" t="inlineStr">
+    <row r="435">
+      <c r="A435" t="inlineStr">
         <is>
           <t xml:space="preserve">⁦「おばけって本当にいるの？」⁩
 هل الوحوش حقيقيّة؟
@@ -9572,19 +9551,19 @@
 2605 alnqsh com/books/2365/ </t>
         </is>
       </c>
-      <c r="B436" t="inlineStr">
+      <c r="B435" t="inlineStr">
         <is>
           <t>images/⁦「おばけって本当にいるの？」⁩_img1.jpg</t>
         </is>
       </c>
-      <c r="C436" t="inlineStr">
+      <c r="C435" t="inlineStr">
         <is>
           <t>お化け ,実在</t>
         </is>
       </c>
     </row>
-    <row r="437">
-      <c r="A437" t="inlineStr">
+    <row r="436">
+      <c r="A436" t="inlineStr">
         <is>
           <t xml:space="preserve">「食べ物はどこ？」
 أَيْنَ الطَّعام؟
@@ -9594,19 +9573,19 @@
 2012 ArabicWorkSheets </t>
         </is>
       </c>
-      <c r="B437" t="inlineStr">
+      <c r="B436" t="inlineStr">
         <is>
           <t>images/「食べ物はどこ？」_img1.jpg</t>
         </is>
       </c>
-      <c r="C437" t="inlineStr">
+      <c r="C436" t="inlineStr">
         <is>
           <t>パズル ,ワード</t>
         </is>
       </c>
     </row>
-    <row r="438">
-      <c r="A438" t="inlineStr">
+    <row r="437">
+      <c r="A437" t="inlineStr">
         <is>
           <t xml:space="preserve">「ヤスミンのネコはどこ？」
 أين قطة ياسمين؟
@@ -9615,19 +9594,19 @@
 2502 www.syraj com </t>
         </is>
       </c>
-      <c r="B438" t="inlineStr">
+      <c r="B437" t="inlineStr">
         <is>
           <t>images/「ヤスミンのネコはどこ？」_img1.jpg</t>
         </is>
       </c>
-      <c r="C438" t="inlineStr">
+      <c r="C437" t="inlineStr">
         <is>
           <t>猫 ,絵本</t>
         </is>
       </c>
     </row>
-    <row r="439">
-      <c r="A439" t="inlineStr">
+    <row r="438">
+      <c r="A438" t="inlineStr">
         <is>
           <t xml:space="preserve">「何時ですか」كم الساعة
 カミ_ッサーア [kami ^saa*a]
@@ -9636,19 +9615,19 @@
 2308 دنيا الأطفال </t>
         </is>
       </c>
-      <c r="B439" t="inlineStr">
+      <c r="B438" t="inlineStr">
         <is>
           <t>images/「何時ですか」_img1.jpg</t>
         </is>
       </c>
-      <c r="C439" t="inlineStr">
+      <c r="C438" t="inlineStr">
         <is>
           <t>猫 ,絵本</t>
         </is>
       </c>
     </row>
-    <row r="440">
-      <c r="A440" t="inlineStr">
+    <row r="439">
+      <c r="A439" t="inlineStr">
         <is>
           <t xml:space="preserve">「図形の中に三角形はいくつ？」
 كم عدد المثلثات في الشكل؟
@@ -9658,19 +9637,19 @@
 2308 出典不明 </t>
         </is>
       </c>
-      <c r="B440" t="inlineStr">
+      <c r="B439" t="inlineStr">
         <is>
           <t>images/「図形の中に三角形はいくつ？」_img1.jpg</t>
         </is>
       </c>
-      <c r="C440" t="inlineStr">
+      <c r="C439" t="inlineStr">
         <is>
           <t>クイズ</t>
         </is>
       </c>
     </row>
-    <row r="441">
-      <c r="A441" t="inlineStr">
+    <row r="440">
+      <c r="A440" t="inlineStr">
         <is>
           <t xml:space="preserve">「データサイエンスとは？」
 ما هو علم البيانات؟
@@ -9679,19 +9658,19 @@
 2308 datasciencearabi com </t>
         </is>
       </c>
-      <c r="B441" t="inlineStr">
+      <c r="B440" t="inlineStr">
         <is>
           <t>images/「データサイエンスとは？」_img1.jpg</t>
         </is>
       </c>
-      <c r="C441" t="inlineStr">
+      <c r="C440" t="inlineStr">
         <is>
           <t>データサイエンス ,data</t>
         </is>
       </c>
     </row>
-    <row r="442">
-      <c r="A442" t="inlineStr">
+    <row r="441">
+      <c r="A441" t="inlineStr">
         <is>
           <t xml:space="preserve">「タバコの成分は？」
 ماهي مكونات السيجارة؟
@@ -9701,19 +9680,19 @@
 2109 Prince Mohammed Medical City </t>
         </is>
       </c>
-      <c r="B442" t="inlineStr">
+      <c r="B441" t="inlineStr">
         <is>
           <t>images/「タバコの成分は？」_img1.jpg</t>
         </is>
       </c>
-      <c r="C442" t="inlineStr">
+      <c r="C441" t="inlineStr">
         <is>
           <t>喫煙 ,禁煙</t>
         </is>
       </c>
     </row>
-    <row r="443">
-      <c r="A443" t="inlineStr">
+    <row r="442">
+      <c r="A442" t="inlineStr">
         <is>
           <t xml:space="preserve">「光と電気の違いは何か？」
 ما الفرق بين الضوء والكهرباء؟
@@ -9723,19 +9702,19 @@
 2508 www.facebook com/BOUSDER </t>
         </is>
       </c>
-      <c r="B443" t="inlineStr">
+      <c r="B442" t="inlineStr">
         <is>
           <t>images/「光と電気の違いは何か？」_img1.jpg</t>
         </is>
       </c>
-      <c r="C443" t="inlineStr">
+      <c r="C442" t="inlineStr">
         <is>
           <t>物理 ,電磁気学</t>
         </is>
       </c>
     </row>
-    <row r="444">
-      <c r="A444" t="inlineStr">
+    <row r="443">
+      <c r="A443" t="inlineStr">
         <is>
           <t xml:space="preserve">「アドバタイズメント、プロモーション、マーケティングの違いは何か？」
 ما الفرق بين الاعلان والترويج والتسويق؟
@@ -9744,19 +9723,19 @@
 2508 https://nafezly.com/portfolio/57972 </t>
         </is>
       </c>
-      <c r="B444" t="inlineStr">
+      <c r="B443" t="inlineStr">
         <is>
           <t>images/「アドバタイズメント、プロモーション、_img1.jpg</t>
         </is>
       </c>
-      <c r="C444" t="inlineStr">
+      <c r="C443" t="inlineStr">
         <is>
           <t>営業 ,ビジネス</t>
         </is>
       </c>
     </row>
-    <row r="445">
-      <c r="A445" t="inlineStr">
+    <row r="444">
+      <c r="A444" t="inlineStr">
         <is>
           <t xml:space="preserve">「才能か努力か、どちらのほうが重要か？」
 أيهما أهم الموهبة أم العمل الجاد؟
@@ -9765,19 +9744,19 @@
 2508 almukhtasaralbasit com </t>
         </is>
       </c>
-      <c r="B445" t="inlineStr">
+      <c r="B444" t="inlineStr">
         <is>
           <t>images/「才能か努力か、どちらのほうが重要か？_img1.jpg</t>
         </is>
       </c>
-      <c r="C445" t="inlineStr">
+      <c r="C444" t="inlineStr">
         <is>
           <t>天才 ,秀才</t>
         </is>
       </c>
     </row>
-    <row r="446">
-      <c r="A446" t="inlineStr">
+    <row r="445">
+      <c r="A445" t="inlineStr">
         <is>
           <t xml:space="preserve">「今日元気？」كيف حالك اليوم؟
  [kayfa Haalu-ka al-yawm?]
@@ -9786,19 +9765,19 @@
 2108 zazzle.com fluentinarabic </t>
         </is>
       </c>
-      <c r="B446" t="inlineStr">
+      <c r="B445" t="inlineStr">
         <is>
           <t>images/「今日元気？」_img1.jpg</t>
         </is>
       </c>
-      <c r="C446" t="inlineStr">
+      <c r="C445" t="inlineStr">
         <is>
           <t>シャツ ,顔文字</t>
         </is>
       </c>
     </row>
-    <row r="447">
-      <c r="A447" t="inlineStr">
+    <row r="446">
+      <c r="A446" t="inlineStr">
         <is>
           <t xml:space="preserve">「風と共に去りぬ」
 ذهَبَ مَع الرّيح
@@ -9808,19 +9787,19 @@
 2308 darkalemat.com/product/1746 </t>
         </is>
       </c>
-      <c r="B447" t="inlineStr">
+      <c r="B446" t="inlineStr">
         <is>
           <t>images/「風と共に去りぬ」_img1.jpg</t>
         </is>
       </c>
-      <c r="C447" t="inlineStr">
+      <c r="C446" t="inlineStr">
         <is>
           <t>小説 ,マーガレット・ミッチェル</t>
         </is>
       </c>
     </row>
-    <row r="448">
-      <c r="A448" t="inlineStr">
+    <row r="447">
+      <c r="A447" t="inlineStr">
         <is>
           <t xml:space="preserve">「春が来た」جاء الربيع
 ジャーアッラビーア [jaa'a ^rabii*]
@@ -9829,19 +9808,19 @@
 2109 ELKHLIFI CHAKIB </t>
         </is>
       </c>
-      <c r="B448" t="inlineStr">
+      <c r="B447" t="inlineStr">
         <is>
           <t>images/「春が来た」_img1.jpg</t>
         </is>
       </c>
-      <c r="C448" t="inlineStr">
+      <c r="C447" t="inlineStr">
         <is>
           <t>季節 ,新学期</t>
         </is>
       </c>
     </row>
-    <row r="449">
-      <c r="A449" t="inlineStr">
+    <row r="448">
+      <c r="A448" t="inlineStr">
         <is>
           <t xml:space="preserve">「ザイナとターリク　寝る時間だよ」
 ⁦「睡眠の時間が訪れた」( حانَ وَقْتُ النّوْمِ )[Haana waqtu ^nawm(i)]⁩
@@ -9850,19 +9829,19 @@
 2108 دار المعرفة </t>
         </is>
       </c>
-      <c r="B449" t="inlineStr">
+      <c r="B448" t="inlineStr">
         <is>
           <t>images/「ザイナとターリク　寝る時間だよ」_img1.jpg</t>
         </is>
       </c>
-      <c r="C449" t="inlineStr">
+      <c r="C448" t="inlineStr">
         <is>
           <t>絵本 ,兄弟</t>
         </is>
       </c>
     </row>
-    <row r="450">
-      <c r="A450" t="inlineStr">
+    <row r="449">
+      <c r="A449" t="inlineStr">
         <is>
           <t xml:space="preserve">「かれに比べられるものは何もない」
 ليس كمثله شيء
@@ -9872,19 +9851,19 @@
 2109 وحيد الزواوي </t>
         </is>
       </c>
-      <c r="B450" t="inlineStr">
+      <c r="B449" t="inlineStr">
         <is>
           <t>images/「かれに比べられるものは何もない」_img1.jpg,images/ 「かれに比べられるものは何もない」_img2.jpg</t>
         </is>
       </c>
-      <c r="C450" t="inlineStr">
+      <c r="C449" t="inlineStr">
         <is>
           <t>神 ,絶対</t>
         </is>
       </c>
     </row>
-    <row r="451">
-      <c r="A451" t="inlineStr">
+    <row r="450">
+      <c r="A450" t="inlineStr">
         <is>
           <t xml:space="preserve">「まだだよ」ليس بعد
 ライサ・バアド [laysa ba*d]
@@ -9892,19 +9871,19 @@
 2108 سلسلة الحلزونة </t>
         </is>
       </c>
-      <c r="B451" t="inlineStr">
+      <c r="B450" t="inlineStr">
         <is>
           <t>images/「まだだよ」_img1.jpg</t>
         </is>
       </c>
-      <c r="C451" t="inlineStr">
+      <c r="C450" t="inlineStr">
         <is>
           <t>絵本 ,こども</t>
         </is>
       </c>
     </row>
-    <row r="452">
-      <c r="A452" t="inlineStr">
+    <row r="451">
+      <c r="A451" t="inlineStr">
         <is>
           <t xml:space="preserve">「今日はどんな日だった？」
 كيف كان يومك؟
@@ -9914,19 +9893,19 @@
 2109 出典不明 </t>
         </is>
       </c>
-      <c r="B452" t="inlineStr">
+      <c r="B451" t="inlineStr">
         <is>
           <t>images/「今日はどんな日だった？」_img1.jpg</t>
         </is>
       </c>
-      <c r="C452" t="inlineStr">
+      <c r="C451" t="inlineStr">
         <is>
           <t>振り返り ,日記</t>
         </is>
       </c>
     </row>
-    <row r="453">
-      <c r="A453" t="inlineStr">
+    <row r="452">
+      <c r="A452" t="inlineStr">
         <is>
           <t xml:space="preserve">「ではこの酸素はどこから来たのか？」
 فمن أين أتى هذا الأوكسجين؟
@@ -9935,19 +9914,19 @@
 2308 https://twitter.com/NatGeoMagArab/status/1484805649846263811 </t>
         </is>
       </c>
-      <c r="B453" t="inlineStr">
+      <c r="B452" t="inlineStr">
         <is>
           <t>images/「ではこの酸素はどこから来たのか？」_img1.jpg</t>
         </is>
       </c>
-      <c r="C453" t="inlineStr">
+      <c r="C452" t="inlineStr">
         <is>
           <t>手書き語学 ,アラビア語 ,地球</t>
         </is>
       </c>
     </row>
-    <row r="454">
-      <c r="A454" t="inlineStr">
+    <row r="453">
+      <c r="A453" t="inlineStr">
         <is>
           <t xml:space="preserve">「忍耐を一杯もらえますか」
 كُوبٌ مِن الصَّبر لو سَمحت
@@ -9957,37 +9936,37 @@
 2109 facebook </t>
         </is>
       </c>
+      <c r="B453" t="inlineStr">
+        <is>
+          <t>images/「忍耐を一杯もらえますか」_img1.jpg</t>
+        </is>
+      </c>
+      <c r="C453" t="inlineStr">
+        <is>
+          <t>注文 ,一服</t>
+        </is>
+      </c>
+    </row>
+    <row r="454">
+      <c r="A454" t="inlineStr">
+        <is>
+          <t xml:space="preserve">「ぎょおおおおおお？」
+2308 https://twitter.com/NatGeoMagArab/status/1364877957576019970 </t>
+        </is>
+      </c>
       <c r="B454" t="inlineStr">
         <is>
-          <t>images/「忍耐を一杯もらえますか」_img1.jpg</t>
+          <t>images/「ぎょおおおおおお？」_img1.jpg</t>
         </is>
       </c>
       <c r="C454" t="inlineStr">
         <is>
-          <t>注文 ,一服</t>
+          <t>手書き語学 ,アラビア語 ,ヘラジカ</t>
         </is>
       </c>
     </row>
     <row r="455">
       <c r="A455" t="inlineStr">
-        <is>
-          <t xml:space="preserve">「ぎょおおおおおお？」
-2308 https://twitter.com/NatGeoMagArab/status/1364877957576019970 </t>
-        </is>
-      </c>
-      <c r="B455" t="inlineStr">
-        <is>
-          <t>images/「ぎょおおおおおお？」_img1.jpg</t>
-        </is>
-      </c>
-      <c r="C455" t="inlineStr">
-        <is>
-          <t>手書き語学 ,アラビア語 ,ヘラジカ</t>
-        </is>
-      </c>
-    </row>
-    <row r="456">
-      <c r="A456" t="inlineStr">
         <is>
           <t xml:space="preserve">「彼女は夢の世界に潜りました」
 غاصت في عالم الأحلام
@@ -9997,19 +9976,19 @@
 2509 arabiya.tumblr </t>
         </is>
       </c>
-      <c r="B456" t="inlineStr">
+      <c r="B455" t="inlineStr">
         <is>
           <t>images/「彼女は夢の世界に潜りました」_img1.jpg</t>
         </is>
       </c>
-      <c r="C456" t="inlineStr">
+      <c r="C455" t="inlineStr">
         <is>
           <t>絵本 ,睡眠</t>
         </is>
       </c>
     </row>
-    <row r="457">
-      <c r="A457" t="inlineStr">
+    <row r="456">
+      <c r="A456" t="inlineStr">
         <is>
           <t xml:space="preserve">「私の心の中に。貴女がどこに居ようとも」
 في قلبي.. أينما كنت أنت
@@ -10018,19 +9997,19 @@
 2109 出典不明 </t>
         </is>
       </c>
-      <c r="B457" t="inlineStr">
+      <c r="B456" t="inlineStr">
         <is>
           <t>images/「私の心の中に。貴女がどこに居ようとも_img1.jpg</t>
         </is>
       </c>
-      <c r="C457" t="inlineStr">
+      <c r="C456" t="inlineStr">
         <is>
           <t>ハート ,右下</t>
         </is>
       </c>
     </row>
-    <row r="458">
-      <c r="A458" t="inlineStr">
+    <row r="457">
+      <c r="A457" t="inlineStr">
         <is>
           <t xml:space="preserve">「リズムを失った」فقدت ايقاعي
 ファカットゥ・イーカーイー [faqad-tu 'iiqaa*-iy]
@@ -10039,15 +10018,15 @@
 2404 </t>
         </is>
       </c>
-      <c r="B458" t="inlineStr"/>
-      <c r="C458" t="inlineStr">
+      <c r="B457" t="inlineStr"/>
+      <c r="C457" t="inlineStr">
         <is>
           <t>吹替 ,フィニアスとファーブ</t>
         </is>
       </c>
     </row>
-    <row r="459">
-      <c r="A459" t="inlineStr">
+    <row r="458">
+      <c r="A458" t="inlineStr">
         <is>
           <t xml:space="preserve">「もしとらをみたら」
 إذا رَأَيْتَ نَمِرًا
@@ -10056,19 +10035,19 @@
 2312 www.neelwafurat com </t>
         </is>
       </c>
-      <c r="B459" t="inlineStr">
+      <c r="B458" t="inlineStr">
         <is>
           <t>images/「もしとらをみたら」_img1.jpg</t>
         </is>
       </c>
-      <c r="C459" t="inlineStr">
+      <c r="C458" t="inlineStr">
         <is>
           <t>ヘタウマ ,絵本</t>
         </is>
       </c>
     </row>
-    <row r="460">
-      <c r="A460" t="inlineStr">
+    <row r="459">
+      <c r="A459" t="inlineStr">
         <is>
           <t xml:space="preserve">「分かったぞ」وجدتها
 ワジャットゥハー [wajad-tu-haa]
@@ -10077,19 +10056,19 @@
 2109 bodor-hoppy.blogspot com </t>
         </is>
       </c>
-      <c r="B460" t="inlineStr">
+      <c r="B459" t="inlineStr">
         <is>
           <t>images/「分かったぞ」_img1.jpg</t>
         </is>
       </c>
-      <c r="C460" t="inlineStr">
+      <c r="C459" t="inlineStr">
         <is>
           <t>発見 ,電球</t>
         </is>
       </c>
     </row>
-    <row r="461">
-      <c r="A461" t="inlineStr">
+    <row r="460">
+      <c r="A460" t="inlineStr">
         <is>
           <t xml:space="preserve">「誰がこれをしたの？」
 من فعل هذا؟
@@ -10099,37 +10078,37 @@
 1903 syraj com </t>
         </is>
       </c>
+      <c r="B460" t="inlineStr">
+        <is>
+          <t>images/「誰がこれをしたの？」_img1.jpg</t>
+        </is>
+      </c>
+      <c r="C460" t="inlineStr">
+        <is>
+          <t>絵本 ,こども</t>
+        </is>
+      </c>
+    </row>
+    <row r="461">
+      <c r="A461" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ネコやん。ネコちゃうし。
+2308 https://twitter.com/NatGeoMagArab/status/1364153030564700165 </t>
+        </is>
+      </c>
       <c r="B461" t="inlineStr">
         <is>
-          <t>images/「誰がこれをしたの？」_img1.jpg</t>
+          <t>images/ネコやん。ネコちゃうし。_img1.jpg,images/ネコやん。ネコちゃうし。_img2.jpg</t>
         </is>
       </c>
       <c r="C461" t="inlineStr">
         <is>
-          <t>絵本 ,こども</t>
+          <t>手書き語学 ,アラビア語 ,虎</t>
         </is>
       </c>
     </row>
     <row r="462">
       <c r="A462" t="inlineStr">
-        <is>
-          <t xml:space="preserve">ネコやん。ネコちゃうし。
-2308 https://twitter.com/NatGeoMagArab/status/1364153030564700165 </t>
-        </is>
-      </c>
-      <c r="B462" t="inlineStr">
-        <is>
-          <t>images/ネコやん。ネコちゃうし。_img1.jpg,images/ネコやん。ネコちゃうし。_img2.jpg</t>
-        </is>
-      </c>
-      <c r="C462" t="inlineStr">
-        <is>
-          <t>手書き語学 ,アラビア語 ,虎</t>
-        </is>
-      </c>
-    </row>
-    <row r="463">
-      <c r="A463" t="inlineStr">
         <is>
           <t xml:space="preserve">「ポケモンゲットだぜ」
 صدنا بوكيمون
@@ -10138,19 +10117,19 @@
 1809 in4sser.tumblr </t>
         </is>
       </c>
-      <c r="B463" t="inlineStr">
+      <c r="B462" t="inlineStr">
         <is>
           <t>images/「ポケモンゲットだぜ」_img1.jpg</t>
         </is>
       </c>
-      <c r="C463" t="inlineStr">
+      <c r="C462" t="inlineStr">
         <is>
           <t>Pokemon ,コラージュ</t>
         </is>
       </c>
     </row>
-    <row r="464">
-      <c r="A464" t="inlineStr">
+    <row r="463">
+      <c r="A463" t="inlineStr">
         <is>
           <t xml:space="preserve">「ゴキブリを見た女子」
 شكل بعض البنات اذا شافوا صرصور
@@ -10160,19 +10139,19 @@
 2308 出典不明 </t>
         </is>
       </c>
-      <c r="B464" t="inlineStr">
+      <c r="B463" t="inlineStr">
         <is>
           <t>images/「ゴキブリを見た女子」_img1.jpg</t>
         </is>
       </c>
-      <c r="C464" t="inlineStr">
+      <c r="C463" t="inlineStr">
         <is>
           <t>SHINee</t>
         </is>
       </c>
     </row>
-    <row r="465">
-      <c r="A465" t="inlineStr">
+    <row r="464">
+      <c r="A464" t="inlineStr">
         <is>
           <t xml:space="preserve">「このかわいい羊がピョンピョンあなたの所に来たら」
 إن جاءك هذا الخروف اللطيف قافزًا
@@ -10180,19 +10159,19 @@
 2308 https://twitter.com/NatGeoMagArab/status/1506881275897933827 </t>
         </is>
       </c>
-      <c r="B465" t="inlineStr">
+      <c r="B464" t="inlineStr">
         <is>
           <t>images/「このかわいい羊がピョンピョンあなたの_img1.jpg</t>
         </is>
       </c>
-      <c r="C465" t="inlineStr">
+      <c r="C464" t="inlineStr">
         <is>
           <t xml:space="preserve">手書き語学 ,羊 </t>
         </is>
       </c>
     </row>
-    <row r="466">
-      <c r="A466" t="inlineStr">
+    <row r="465">
+      <c r="A465" t="inlineStr">
         <is>
           <t xml:space="preserve">「中国製」صنع في الصين
 スニア・フィ_ッスィーン [_suni*a fi ^_siin]
@@ -10201,19 +10180,19 @@
 2103 </t>
         </is>
       </c>
-      <c r="B466" t="inlineStr">
+      <c r="B465" t="inlineStr">
         <is>
           <t>images/「中国製」_img1.jpg</t>
         </is>
       </c>
-      <c r="C466" t="inlineStr">
+      <c r="C465" t="inlineStr">
         <is>
           <t>あらびあや</t>
         </is>
       </c>
     </row>
-    <row r="467">
-      <c r="A467" t="inlineStr">
+    <row r="466">
+      <c r="A466" t="inlineStr">
         <is>
           <t xml:space="preserve">「七面鳥製」صنع في ديك رومي
  [_suni*a fiy diik ruumiyy]
@@ -10222,19 +10201,19 @@
 2108 www.fay3.com/i6a6t474H </t>
         </is>
       </c>
-      <c r="B467" t="inlineStr">
+      <c r="B466" t="inlineStr">
         <is>
           <t>images/「七面鳥製」_img1.jpg</t>
         </is>
       </c>
-      <c r="C467" t="inlineStr">
+      <c r="C466" t="inlineStr">
         <is>
           <t>誤訳 ,面白画像</t>
         </is>
       </c>
     </row>
-    <row r="468">
-      <c r="A468" t="inlineStr">
+    <row r="467">
+      <c r="A467" t="inlineStr">
         <is>
           <t xml:space="preserve">「人生は私に忍耐を教えた」
 علمتني الحياه صبرا
@@ -10244,19 +10223,19 @@
 2105 nw5tha|tumblr </t>
         </is>
       </c>
-      <c r="B468" t="inlineStr">
+      <c r="B467" t="inlineStr">
         <is>
           <t>images/「人生は私に忍耐を教えた」_img1.jpg</t>
         </is>
       </c>
-      <c r="C468" t="inlineStr">
+      <c r="C467" t="inlineStr">
         <is>
           <t>我慢 ,擬人化</t>
         </is>
       </c>
     </row>
-    <row r="469">
-      <c r="A469" t="inlineStr">
+    <row r="468">
+      <c r="A468" t="inlineStr">
         <is>
           <t xml:space="preserve">「でかした／よく出来ましたね！」
 ‎أحسنت
@@ -10266,19 +10245,19 @@
 2308 AhsantApp </t>
         </is>
       </c>
-      <c r="B469" t="inlineStr">
+      <c r="B468" t="inlineStr">
         <is>
           <t>images/「でかした／よく出来ましたね！」_img1.jpg</t>
         </is>
       </c>
-      <c r="C469" t="inlineStr">
+      <c r="C468" t="inlineStr">
         <is>
           <t>子供 ,褒め方</t>
         </is>
       </c>
     </row>
-    <row r="470">
-      <c r="A470" t="inlineStr">
+    <row r="469">
+      <c r="A469" t="inlineStr">
         <is>
           <t xml:space="preserve">「漢字の成り立ち」
 كيف تشكلت حُروف الكانجي
@@ -10288,19 +10267,19 @@
 2509 web-japan org </t>
         </is>
       </c>
-      <c r="B470" t="inlineStr">
+      <c r="B469" t="inlineStr">
         <is>
           <t>images/「漢字の成り立ち」_img1.jpg</t>
         </is>
       </c>
-      <c r="C470" t="inlineStr">
+      <c r="C469" t="inlineStr">
         <is>
           <t>にほんご ,象形文字</t>
         </is>
       </c>
     </row>
-    <row r="471">
-      <c r="A471" t="inlineStr">
+    <row r="470">
+      <c r="A470" t="inlineStr">
         <is>
           <t xml:space="preserve">「いいね！」أعجبني
 アアジャバニー ['a*jaba-niy]
@@ -10308,37 +10287,37 @@
 2412 facebook </t>
         </is>
       </c>
+      <c r="B470" t="inlineStr">
+        <is>
+          <t>images/「いいね！」_img1.jpg</t>
+        </is>
+      </c>
+      <c r="C470" t="inlineStr">
+        <is>
+          <t>like ,good</t>
+        </is>
+      </c>
+    </row>
+    <row r="471">
+      <c r="A471" t="inlineStr">
+        <is>
+          <t xml:space="preserve">瞬間顔面乾燥法。
+2308 https://twitter.com/NatGeoMagArab/status/1359532643822366720 </t>
+        </is>
+      </c>
       <c r="B471" t="inlineStr">
         <is>
-          <t>images/「いいね！」_img1.jpg</t>
+          <t>images/瞬間顔面乾燥法。_img1.jpg</t>
         </is>
       </c>
       <c r="C471" t="inlineStr">
         <is>
-          <t>like ,good</t>
+          <t>ジャガー ,手書き語学</t>
         </is>
       </c>
     </row>
     <row r="472">
       <c r="A472" t="inlineStr">
-        <is>
-          <t xml:space="preserve">瞬間顔面乾燥法。
-2308 https://twitter.com/NatGeoMagArab/status/1359532643822366720 </t>
-        </is>
-      </c>
-      <c r="B472" t="inlineStr">
-        <is>
-          <t>images/瞬間顔面乾燥法。_img1.jpg</t>
-        </is>
-      </c>
-      <c r="C472" t="inlineStr">
-        <is>
-          <t>ジャガー ,手書き語学</t>
-        </is>
-      </c>
-    </row>
-    <row r="473">
-      <c r="A473" t="inlineStr">
         <is>
           <t xml:space="preserve">「子供時代にこうやって坂道で遊んだ人はどれくらいいますか？」
 كم منا مارس اللعب على المنحدرات بهذه الطريقة في الطفولة؟
@@ -10346,19 +10325,19 @@
 2109 NatGeoMagArab </t>
         </is>
       </c>
-      <c r="B473" t="inlineStr">
+      <c r="B472" t="inlineStr">
         <is>
           <t>images/「子供時代にこうやって坂道で遊んだ人は.png</t>
         </is>
       </c>
-      <c r="C473" t="inlineStr">
+      <c r="C472" t="inlineStr">
         <is>
           <t>パンダ ,動物</t>
         </is>
       </c>
     </row>
-    <row r="474">
-      <c r="A474" t="inlineStr">
+    <row r="473">
+      <c r="A473" t="inlineStr">
         <is>
           <t xml:space="preserve">「このユニークな動物がなんだか分かりましたか？」
 هل ميزت هذا الحيوان الفريد؟
@@ -10366,19 +10345,19 @@
 2601 https://twitter.com/NatGeoMagArab/status/1579049044516941826 </t>
         </is>
       </c>
-      <c r="B474" t="inlineStr">
+      <c r="B473" t="inlineStr">
         <is>
           <t>images/「このユニークな動物がなんだか分かりま_img1.png,images/ 「このユニークな動物がなんだか分かりま_img2.jpg</t>
         </is>
       </c>
-      <c r="C474" t="inlineStr">
+      <c r="C473" t="inlineStr">
         <is>
           <t>手書き語学 ,アラビア語 ,バク</t>
         </is>
       </c>
     </row>
-    <row r="475">
-      <c r="A475" t="inlineStr">
+    <row r="474">
+      <c r="A474" t="inlineStr">
         <is>
           <t xml:space="preserve">「他が色づくなら私は白だ」
 أنا الأبيض إذا غيري تلون
@@ -10387,19 +10366,19 @@
 2108 出典不明 </t>
         </is>
       </c>
-      <c r="B475" t="inlineStr">
+      <c r="B474" t="inlineStr">
         <is>
           <t>images/「他が色づくなら私は白だ」_img1.jpg</t>
         </is>
       </c>
-      <c r="C475" t="inlineStr">
+      <c r="C474" t="inlineStr">
         <is>
           <t>オリジナリティ ,自分</t>
         </is>
       </c>
     </row>
-    <row r="476">
-      <c r="A476" t="inlineStr">
+    <row r="475">
+      <c r="A475" t="inlineStr">
         <is>
           <t xml:space="preserve">「はじめまして」تشرفنا
 タシャッラフナー [taSharraf-naa]
@@ -10407,19 +10386,19 @@
 2308 https://eddirasa.com/forum/t10271-2/ </t>
         </is>
       </c>
-      <c r="B476" t="inlineStr">
+      <c r="B475" t="inlineStr">
         <is>
           <t>images/「はじめまして」.jpg</t>
         </is>
       </c>
-      <c r="C476" t="inlineStr">
+      <c r="C475" t="inlineStr">
         <is>
           <t>挨拶 ,イラスト</t>
         </is>
       </c>
     </row>
-    <row r="477">
-      <c r="A477" t="inlineStr">
+    <row r="476">
+      <c r="A476" t="inlineStr">
         <is>
           <t xml:space="preserve">「このアザラシがホッキョクグマの子供にホラーを喰らわせた」
 أذاقت هذه الفقمة صغير الدب القطبي طعم الرعب
@@ -10428,19 +10407,19 @@
 2509 NatGeoMagArab </t>
         </is>
       </c>
-      <c r="B477" t="inlineStr">
+      <c r="B476" t="inlineStr">
         <is>
           <t>images/「このアザラシがホッキョクグマの子供に.jpg</t>
         </is>
       </c>
-      <c r="C477" t="inlineStr">
+      <c r="C476" t="inlineStr">
         <is>
           <t xml:space="preserve">シロクマ </t>
         </is>
       </c>
     </row>
-    <row r="478">
-      <c r="A478" t="inlineStr">
+    <row r="477">
+      <c r="A477" t="inlineStr">
         <is>
           <t xml:space="preserve">⁦「月はどこへ消えた？」⁩
 أين اختفى القمر؟
@@ -10450,19 +10429,19 @@
 2508 msheirebmuseums </t>
         </is>
       </c>
-      <c r="B478" t="inlineStr">
+      <c r="B477" t="inlineStr">
         <is>
           <t>images/⁦「月はどこへ消えた？」⁩_img1.jpg</t>
         </is>
       </c>
-      <c r="C478" t="inlineStr">
+      <c r="C477" t="inlineStr">
         <is>
           <t>表紙 ,月食</t>
         </is>
       </c>
     </row>
-    <row r="479">
-      <c r="A479" t="inlineStr">
+    <row r="478">
+      <c r="A478" t="inlineStr">
         <is>
           <t xml:space="preserve">「お父さんが僕にこの庭を買ってくれた」
 اشترى لي أبي هذا البستان
@@ -10472,19 +10451,19 @@
 2105 </t>
         </is>
       </c>
-      <c r="B479" t="inlineStr">
+      <c r="B478" t="inlineStr">
         <is>
           <t>images/「お父さんが僕にこの庭を買ってくれた」_img1.jpg</t>
         </is>
       </c>
-      <c r="C479" t="inlineStr">
+      <c r="C478" t="inlineStr">
         <is>
           <t>あらびあや</t>
         </is>
       </c>
     </row>
-    <row r="480">
-      <c r="A480" t="inlineStr">
+    <row r="479">
+      <c r="A479" t="inlineStr">
         <is>
           <t xml:space="preserve">「もしキリンさんにネクタイを9本あげたら」
 لو أعطيت زرافة تسع ربطات عنق
@@ -10493,19 +10472,19 @@
 2404 darashjar com </t>
         </is>
       </c>
-      <c r="B480" t="inlineStr">
+      <c r="B479" t="inlineStr">
         <is>
           <t>images/「もしキリンさんにネクタイを9本あげた_img1.jpg,images/ 「もしキリンさんにネクタイを9本あげた_img2.jpg</t>
         </is>
       </c>
-      <c r="C480" t="inlineStr">
+      <c r="C479" t="inlineStr">
         <is>
           <t>絵本</t>
         </is>
       </c>
     </row>
-    <row r="481">
-      <c r="A481" t="inlineStr">
+    <row r="480">
+      <c r="A480" t="inlineStr">
         <is>
           <t xml:space="preserve">「十億年前、ブラックホールが死んだ星と衝突した」
 قبل مليار سنة، اصطدم ثقب أسود بنجم ميت
@@ -10513,19 +10492,19 @@
 2404 https://twitter.com/NatGeoMagArab/status/1482412441879203843 </t>
         </is>
       </c>
-      <c r="B481" t="inlineStr">
+      <c r="B480" t="inlineStr">
         <is>
           <t>images/「十億年前、ブラックホールが死んだ星と_img1.jpg</t>
         </is>
       </c>
-      <c r="C481" t="inlineStr">
+      <c r="C480" t="inlineStr">
         <is>
           <t>手書き語学 ,アラビア語 ,ブラックホール</t>
         </is>
       </c>
     </row>
-    <row r="482">
-      <c r="A482" t="inlineStr">
+    <row r="481">
+      <c r="A481" t="inlineStr">
         <is>
           <t xml:space="preserve">「それが彼らの生存戦略を支えている」
 يدعم ذلك استراتيجيتها للبقاء على قيد الحياة
@@ -10533,19 +10512,19 @@
 2507 https://x.com/NatGeoMagArab/status/1811075438728597895 </t>
         </is>
       </c>
-      <c r="B482" t="inlineStr">
+      <c r="B481" t="inlineStr">
         <is>
           <t>images/「それが彼らの生存戦略を支えている」_img1.jpg</t>
         </is>
       </c>
-      <c r="C482" t="inlineStr">
+      <c r="C481" t="inlineStr">
         <is>
           <t>手書き語学 ,アラビア語 ,サバイバル</t>
         </is>
       </c>
     </row>
-    <row r="483">
-      <c r="A483" t="inlineStr">
+    <row r="482">
+      <c r="A482" t="inlineStr">
         <is>
           <t xml:space="preserve">「私と珈琲を飲みます？　毎日。」
 تشرب معي قهوة؟ كل يوم
@@ -10554,19 +10533,19 @@
 2308 ضياء </t>
         </is>
       </c>
-      <c r="B483" t="inlineStr">
+      <c r="B482" t="inlineStr">
         <is>
           <t>images/「私と珈琲を飲みます？　毎日。」_img1.jpg</t>
         </is>
       </c>
-      <c r="C483" t="inlineStr">
+      <c r="C482" t="inlineStr">
         <is>
           <t>プロポーズ ,喫茶</t>
         </is>
       </c>
     </row>
-    <row r="484">
-      <c r="A484" t="inlineStr">
+    <row r="483">
+      <c r="A483" t="inlineStr">
         <is>
           <t xml:space="preserve">「わしの妹は歯を磨いておる」
 تغسل أختي الصغيرة أسنانها
@@ -10576,19 +10555,19 @@
 2103 </t>
         </is>
       </c>
-      <c r="B484" t="inlineStr">
+      <c r="B483" t="inlineStr">
         <is>
           <t>images/「わしの妹は歯を磨いておる」_img1.jpg</t>
         </is>
       </c>
-      <c r="C484" t="inlineStr">
+      <c r="C483" t="inlineStr">
         <is>
           <t>あらびあや</t>
         </is>
       </c>
     </row>
-    <row r="485">
-      <c r="A485" t="inlineStr">
+    <row r="484">
+      <c r="A484" t="inlineStr">
         <is>
           <t xml:space="preserve">「お母さんがこの方法で僕を運ぶ時、暴れる余地はない」
 حين تحملني أمي بهذه الطريقة، فلا مجال للشغب
@@ -10596,19 +10575,19 @@
 2412 https://twitter.com/NatGeoMagArab/status/1540945459396546562 </t>
         </is>
       </c>
-      <c r="B485" t="inlineStr">
+      <c r="B484" t="inlineStr">
         <is>
           <t>images/「お母さんがこの方法で僕を運ぶ時、暴れ_img1.jpg,images/ 「お母さんがこの方法で僕を運ぶ時、暴れ_img2.jpg</t>
         </is>
       </c>
-      <c r="C485" t="inlineStr">
+      <c r="C484" t="inlineStr">
         <is>
           <t xml:space="preserve">手書き語学 ,アラビア語 ,ピューマ </t>
         </is>
       </c>
     </row>
-    <row r="486">
-      <c r="A486" t="inlineStr">
+    <row r="485">
+      <c r="A485" t="inlineStr">
         <is>
           <t xml:space="preserve">「これには小さいスナネコが写っている」
 يظهر من خلالها قط رمال صغير
@@ -10617,19 +10596,19 @@
 2604 https://x.com/NatGeoMagArab/status/1934317490534019202 </t>
         </is>
       </c>
-      <c r="B486" t="inlineStr">
+      <c r="B485" t="inlineStr">
         <is>
           <t>images/「これには小さいスナネコが写っている」_img1.jpg,images/ 「これには小さいスナネコが写っている」_img2.jpg</t>
         </is>
       </c>
-      <c r="C486" t="inlineStr">
+      <c r="C485" t="inlineStr">
         <is>
           <t>手書き語学 ,アラビア語 ,スナネコ</t>
         </is>
       </c>
     </row>
-    <row r="487">
-      <c r="A487" t="inlineStr">
+    <row r="486">
+      <c r="A486" t="inlineStr">
         <is>
           <t xml:space="preserve">「アイデアを手に入れる方法」
 كيف تحصل على أفكار
@@ -10639,19 +10618,19 @@
 2312 ibtesamah com </t>
         </is>
       </c>
-      <c r="B487" t="inlineStr">
+      <c r="B486" t="inlineStr">
         <is>
           <t>images/「アイデアを手に入れる方法」_img1.jpg</t>
         </is>
       </c>
-      <c r="C487" t="inlineStr">
+      <c r="C486" t="inlineStr">
         <is>
           <t>電球 ,魚</t>
         </is>
       </c>
     </row>
-    <row r="488">
-      <c r="A488" t="inlineStr">
+    <row r="487">
+      <c r="A487" t="inlineStr">
         <is>
           <t xml:space="preserve">「仕事で成功するでしょう」
 ستنجح في عملك
@@ -10661,19 +10640,19 @@
 2105 </t>
         </is>
       </c>
-      <c r="B488" t="inlineStr">
+      <c r="B487" t="inlineStr">
         <is>
           <t>images/「仕事で成功するでしょう」_img1.jpg</t>
         </is>
       </c>
-      <c r="C488" t="inlineStr">
+      <c r="C487" t="inlineStr">
         <is>
           <t>手相 ,あらびあや</t>
         </is>
       </c>
     </row>
-    <row r="489">
-      <c r="A489" t="inlineStr">
+    <row r="488">
+      <c r="A488" t="inlineStr">
         <is>
           <t xml:space="preserve">「わかりません」لا أَعْرِفُ
 ラー・アアリフ [laa 'a-*rifu]
@@ -10681,19 +10660,19 @@
 1809 </t>
         </is>
       </c>
-      <c r="B489" t="inlineStr">
+      <c r="B488" t="inlineStr">
         <is>
           <t>images/「わかりません」_img1.jpg</t>
         </is>
       </c>
-      <c r="C489" t="inlineStr">
+      <c r="C488" t="inlineStr">
         <is>
           <t>あらびあや</t>
         </is>
       </c>
     </row>
-    <row r="490">
-      <c r="A490" t="inlineStr">
+    <row r="489">
+      <c r="A489" t="inlineStr">
         <is>
           <t xml:space="preserve">「母リスは、子供たちが心配じゃないのだろうか」
 ألا تشعر أم السناجب بالقلق على صغارها
@@ -10702,19 +10681,19 @@
 2109 NatGeoMagArab </t>
         </is>
       </c>
-      <c r="B490" t="inlineStr">
+      <c r="B489" t="inlineStr">
         <is>
           <t>images/「母リスは、子供たちが心配じゃないのだ.png</t>
         </is>
       </c>
-      <c r="C490" t="inlineStr">
+      <c r="C489" t="inlineStr">
         <is>
           <t>リス ,元気</t>
         </is>
       </c>
     </row>
-    <row r="491">
-      <c r="A491" t="inlineStr">
+    <row r="490">
+      <c r="A490" t="inlineStr">
         <is>
           <t xml:space="preserve">「分かりません」لا أفهم
 ラー・アフハム [laa 'a-fham]
@@ -10723,19 +10702,19 @@
 2303 https://www.vogue.fr/fashion-culture/fashion-exhibitions/diaporama/middle-east-art-scene/12755/amp </t>
         </is>
       </c>
-      <c r="B491" t="inlineStr">
+      <c r="B490" t="inlineStr">
         <is>
           <t>images/「分かりません」_img1.jpg</t>
         </is>
       </c>
-      <c r="C491" t="inlineStr">
+      <c r="C490" t="inlineStr">
         <is>
           <t>イミフ ,否定</t>
         </is>
       </c>
     </row>
-    <row r="492">
-      <c r="A492" t="inlineStr">
+    <row r="491">
+      <c r="A491" t="inlineStr">
         <is>
           <t xml:space="preserve">「クイズ ミリオネア／100万を獲るのは誰だ」
 من سيربح المليون
@@ -10745,19 +10724,19 @@
 2308 MBC 1 </t>
         </is>
       </c>
-      <c r="B492" t="inlineStr">
+      <c r="B491" t="inlineStr">
         <is>
           <t>images/「クイズ ミリオネア／100万を獲るの_img1.jpg</t>
         </is>
       </c>
-      <c r="C492" t="inlineStr">
+      <c r="C491" t="inlineStr">
         <is>
           <t>テレビ ,みのもんた</t>
         </is>
       </c>
     </row>
-    <row r="493">
-      <c r="A493" t="inlineStr">
+    <row r="492">
+      <c r="A492" t="inlineStr">
         <is>
           <t xml:space="preserve">「知っていますか？」هل تعلم؟
 ハル・タアラム？ [hal ta-*lam?]
@@ -10766,19 +10745,19 @@
 2103 el-ma3lomaa com </t>
         </is>
       </c>
-      <c r="B493" t="inlineStr">
+      <c r="B492" t="inlineStr">
         <is>
           <t>images/「知っていますか？」_img1.jpg</t>
         </is>
       </c>
-      <c r="C493" t="inlineStr">
+      <c r="C492" t="inlineStr">
         <is>
           <t>知識 ,クイズ</t>
         </is>
       </c>
     </row>
-    <row r="494">
-      <c r="A494" t="inlineStr">
+    <row r="493">
+      <c r="A493" t="inlineStr">
         <is>
           <t xml:space="preserve">「貴女はどこに住んでいますか」
 أين تسكنين؟
@@ -10788,19 +10767,19 @@
 1811 </t>
         </is>
       </c>
-      <c r="B494" t="inlineStr">
+      <c r="B493" t="inlineStr">
         <is>
           <t>images/「貴女はどこに住んでいますか」_img1.jpg</t>
         </is>
       </c>
-      <c r="C494" t="inlineStr">
+      <c r="C493" t="inlineStr">
         <is>
           <t>あらびあや</t>
         </is>
       </c>
     </row>
-    <row r="495">
-      <c r="A495" t="inlineStr">
+    <row r="494">
+      <c r="A494" t="inlineStr">
         <is>
           <t xml:space="preserve">「きょうりゅうはどうやってがっこうにいくの？」
 كَيْفَ تَذْهَبُ الدِّيناصوراتُ إلى الْمَدْرَسَةِ؟
@@ -10809,19 +10788,19 @@
 2308 sanabilbooks.com </t>
         </is>
       </c>
-      <c r="B495" t="inlineStr">
+      <c r="B494" t="inlineStr">
         <is>
           <t>images/「きょうりゅうはどうやってがっこうにい_img1.jpg</t>
         </is>
       </c>
-      <c r="C495" t="inlineStr">
+      <c r="C494" t="inlineStr">
         <is>
           <t>絵本 ,恐竜</t>
         </is>
       </c>
     </row>
-    <row r="496">
-      <c r="A496" t="inlineStr">
+    <row r="495">
+      <c r="A495" t="inlineStr">
         <is>
           <t xml:space="preserve">「私たちにはどれだけの時間があるのか？」
 كم من الوقت نملك؟
@@ -10831,19 +10810,19 @@
 2308 Founders and Founders </t>
         </is>
       </c>
-      <c r="B496" t="inlineStr">
+      <c r="B495" t="inlineStr">
         <is>
           <t>images/「私たちにはどれだけの時間があるのか？_img1.jpg</t>
         </is>
       </c>
-      <c r="C496" t="inlineStr">
+      <c r="C495" t="inlineStr">
         <is>
           <t>チャート</t>
         </is>
       </c>
     </row>
-    <row r="497">
-      <c r="A497" t="inlineStr">
+    <row r="496">
+      <c r="A496" t="inlineStr">
         <is>
           <t xml:space="preserve">「コーヒーが冷めないうちに」
 قبل أن تبرد القهوة
@@ -10853,19 +10832,19 @@
 2403 https://a.co d/7jizZfE </t>
         </is>
       </c>
-      <c r="B497" t="inlineStr">
+      <c r="B496" t="inlineStr">
         <is>
           <t>images/「コーヒーが冷めないうちに」_img1.jpg</t>
         </is>
       </c>
-      <c r="C497" t="inlineStr">
+      <c r="C496" t="inlineStr">
         <is>
           <t>小説 ,表紙</t>
         </is>
       </c>
     </row>
-    <row r="498">
-      <c r="A498" t="inlineStr">
+    <row r="497">
+      <c r="A497" t="inlineStr">
         <is>
           <t xml:space="preserve">「悲しむな」Don't be sad
 لا تحزَنْ
@@ -10875,15 +10854,15 @@
 2402 MADYAN </t>
         </is>
       </c>
-      <c r="B498" t="inlineStr">
+      <c r="B497" t="inlineStr">
         <is>
           <t>images/「悲しむな」Don't be sad_img1.jpg</t>
         </is>
       </c>
-      <c r="C498" t="inlineStr"/>
-    </row>
-    <row r="499">
-      <c r="A499" t="inlineStr">
+      <c r="C497" t="inlineStr"/>
+    </row>
+    <row r="498">
+      <c r="A498" t="inlineStr">
         <is>
           <t xml:space="preserve">「悲しむな」لا تحزن
 ラー・タハザン [laa ta-Hzan]
@@ -10892,19 +10871,19 @@
 1903 fadli7 deviantart com </t>
         </is>
       </c>
-      <c r="B499" t="inlineStr">
+      <c r="B498" t="inlineStr">
         <is>
           <t>images/「悲しむな」_img1.jpg</t>
         </is>
       </c>
-      <c r="C499" t="inlineStr">
+      <c r="C498" t="inlineStr">
         <is>
           <t>書道 ,カリグラフィー</t>
         </is>
       </c>
     </row>
-    <row r="500">
-      <c r="A500" t="inlineStr">
+    <row r="499">
+      <c r="A499" t="inlineStr">
         <is>
           <t xml:space="preserve">「心配しないで、パパ」
 لا تقلق يا بابا
@@ -10914,19 +10893,19 @@
 2308 alsalwabooks </t>
         </is>
       </c>
-      <c r="B500" t="inlineStr">
+      <c r="B499" t="inlineStr">
         <is>
           <t>images/「心配しないで、パパ」_img1.jpg</t>
         </is>
       </c>
-      <c r="C500" t="inlineStr">
+      <c r="C499" t="inlineStr">
         <is>
           <t>絵本 ,親子</t>
         </is>
       </c>
     </row>
-    <row r="501">
-      <c r="A501" t="inlineStr">
+    <row r="500">
+      <c r="A500" t="inlineStr">
         <is>
           <t xml:space="preserve">「時は剣のごとし。あなたが割かなければあなたが割かれる」
 الوقت كالسيف إن لم تقطعه قطعك
@@ -10935,19 +10914,19 @@
 2308 sultanart </t>
         </is>
       </c>
-      <c r="B501" t="inlineStr">
+      <c r="B500" t="inlineStr">
         <is>
           <t>images/「時は剣のごとし。あなたが割かなければ_img1.jpg</t>
         </is>
       </c>
-      <c r="C501" t="inlineStr">
+      <c r="C500" t="inlineStr">
         <is>
           <t>ことわざ</t>
         </is>
       </c>
     </row>
-    <row r="502">
-      <c r="A502" t="inlineStr">
+    <row r="501">
+      <c r="A501" t="inlineStr">
         <is>
           <t xml:space="preserve">「そんな風に私を見ないで」
 لا تنظر إلي هكذا
@@ -10957,19 +10936,19 @@
 1810 </t>
         </is>
       </c>
-      <c r="B502" t="inlineStr">
+      <c r="B501" t="inlineStr">
         <is>
           <t>images/「そんな風に私を見ないで」_img1.jpg</t>
         </is>
       </c>
-      <c r="C502" t="inlineStr">
+      <c r="C501" t="inlineStr">
         <is>
           <t>あらびあや</t>
         </is>
       </c>
     </row>
-    <row r="503">
-      <c r="A503" t="inlineStr">
+    <row r="502">
+      <c r="A502" t="inlineStr">
         <is>
           <t xml:space="preserve">「必要以上に勉強するな」
 لا تدرس أكثر من اللازم
@@ -10979,19 +10958,19 @@
 2109 出典不明 </t>
         </is>
       </c>
-      <c r="B503" t="inlineStr">
+      <c r="B502" t="inlineStr">
         <is>
           <t>images/「必要以上に勉強するな」_img1.jpg</t>
         </is>
       </c>
-      <c r="C503" t="inlineStr">
+      <c r="C502" t="inlineStr">
         <is>
           <t>徹夜 ,計画</t>
         </is>
       </c>
     </row>
-    <row r="504">
-      <c r="A504" t="inlineStr">
+    <row r="503">
+      <c r="A503" t="inlineStr">
         <is>
           <t xml:space="preserve">「翼を広げなさい」
 افْرِدْ جَنَاحَكَ
@@ -11001,19 +10980,19 @@
 2308 Librairie SANA </t>
         </is>
       </c>
-      <c r="B504" t="inlineStr">
+      <c r="B503" t="inlineStr">
         <is>
           <t>images/「翼を広げなさい」_img1.jpg</t>
         </is>
       </c>
-      <c r="C504" t="inlineStr">
+      <c r="C503" t="inlineStr">
         <is>
           <t>絵本 ,鳥</t>
         </is>
       </c>
     </row>
-    <row r="505">
-      <c r="A505" t="inlineStr">
+    <row r="504">
+      <c r="A504" t="inlineStr">
         <is>
           <t xml:space="preserve">「作ろう。自分の幸せは自分で」
 اصنع سعادتك بنفسك
@@ -11023,19 +11002,19 @@
 1812 fado1997 tumblr </t>
         </is>
       </c>
-      <c r="B505" t="inlineStr">
+      <c r="B504" t="inlineStr">
         <is>
           <t>images/「作ろう。自分の幸せは自分で」_img1.jpg</t>
         </is>
       </c>
-      <c r="C505" t="inlineStr">
+      <c r="C504" t="inlineStr">
         <is>
           <t>ポジティブ</t>
         </is>
       </c>
     </row>
-    <row r="506">
-      <c r="A506" t="inlineStr">
+    <row r="505">
+      <c r="A505" t="inlineStr">
         <is>
           <t xml:space="preserve">「あなたの栄光を作れ」
 اصنَع مجدَك
@@ -11045,19 +11024,19 @@
 1811 Ahmed Madyan </t>
         </is>
       </c>
-      <c r="B506" t="inlineStr">
+      <c r="B505" t="inlineStr">
         <is>
           <t>images/「あなたの栄光を作れ」_img1.jpg</t>
         </is>
       </c>
-      <c r="C506" t="inlineStr">
+      <c r="C505" t="inlineStr">
         <is>
           <t>ヒーロー ,自分</t>
         </is>
       </c>
     </row>
-    <row r="507">
-      <c r="A507" t="inlineStr">
+    <row r="506">
+      <c r="A506" t="inlineStr">
         <is>
           <t xml:space="preserve">「声を上げろ」إرفع صوتك
 イルファア・サウタク [irfa* _sawta-k]
@@ -11066,19 +11045,19 @@
 2109 ALHURRA </t>
         </is>
       </c>
-      <c r="B507" t="inlineStr">
+      <c r="B506" t="inlineStr">
         <is>
           <t>images/「声を上げろ」_img1.jpg</t>
         </is>
       </c>
-      <c r="C507" t="inlineStr">
+      <c r="C506" t="inlineStr">
         <is>
           <t>発言 ,言論</t>
         </is>
       </c>
     </row>
-    <row r="508">
-      <c r="A508" t="inlineStr">
+    <row r="507">
+      <c r="A507" t="inlineStr">
         <is>
           <t xml:space="preserve">「口を開く前に、心を開きなさい」
 افتح عقلك قبل أن تفتح فمك
@@ -11088,19 +11067,19 @@
 2308 出典不明 </t>
         </is>
       </c>
-      <c r="B508" t="inlineStr">
+      <c r="B507" t="inlineStr">
         <is>
           <t>images/「口を開く前に、心を開きなさい」_img1.jpg</t>
         </is>
       </c>
-      <c r="C508" t="inlineStr">
+      <c r="C507" t="inlineStr">
         <is>
           <t>教訓 ,名言</t>
         </is>
       </c>
     </row>
-    <row r="509">
-      <c r="A509" t="inlineStr">
+    <row r="508">
+      <c r="A508" t="inlineStr">
         <is>
           <t xml:space="preserve">「読んでちょうだい、読んであげるよ」
 اِقرأ لي، أقرأ لك
@@ -11110,19 +11089,19 @@
 2308 archive org </t>
         </is>
       </c>
-      <c r="B509" t="inlineStr">
+      <c r="B508" t="inlineStr">
         <is>
           <t>images/「読んでちょうだい、読んであげるよ」_img1.jpg,images/「読んでちょうだい、読んであげるよ」_img2.jpg</t>
         </is>
       </c>
-      <c r="C509" t="inlineStr">
+      <c r="C508" t="inlineStr">
         <is>
           <t xml:space="preserve">絵本 ,読み聞かせ </t>
         </is>
       </c>
     </row>
-    <row r="510">
-      <c r="A510" t="inlineStr">
+    <row r="509">
+      <c r="A509" t="inlineStr">
         <is>
           <t xml:space="preserve">「がんばれ」ابذل جهدك
 ウブズル・ジャハダク [ubDhul jahda-k]
@@ -11130,19 +11109,19 @@
 2308 https://twitter.com/Ishaiookh/status/1469579864915288068 </t>
         </is>
       </c>
-      <c r="B510" t="inlineStr">
+      <c r="B509" t="inlineStr">
         <is>
           <t>images/「がんばれ」_img1.jpg</t>
         </is>
       </c>
-      <c r="C510" t="inlineStr">
+      <c r="C509" t="inlineStr">
         <is>
           <t>文字 ,下办つ_ぺ中ヵ可</t>
         </is>
       </c>
     </row>
-    <row r="511">
-      <c r="A511" t="inlineStr">
+    <row r="510">
+      <c r="A510" t="inlineStr">
         <is>
           <t xml:space="preserve">「窓を開けよ。そこに光がある」
 افتح النافذة ثمة ضوء
@@ -11152,19 +11131,19 @@
 2308 الدكتور خالد المنيف </t>
         </is>
       </c>
-      <c r="B511" t="inlineStr">
+      <c r="B510" t="inlineStr">
         <is>
           <t>images/「窓を開けよ。そこに光がある」_img1.jpg</t>
         </is>
       </c>
-      <c r="C511" t="inlineStr">
+      <c r="C510" t="inlineStr">
         <is>
           <t>換気 ,ウインドウズ</t>
         </is>
       </c>
     </row>
-    <row r="512">
-      <c r="A512" t="inlineStr">
+    <row r="511">
+      <c r="A511" t="inlineStr">
         <is>
           <t xml:space="preserve">「笑えよ」اضحك
 イドハク [i_dHak]
@@ -11173,19 +11152,19 @@
 1809 </t>
         </is>
       </c>
-      <c r="B512" t="inlineStr">
+      <c r="B511" t="inlineStr">
         <is>
           <t>images/「笑えよ」_img1.jpg</t>
         </is>
       </c>
-      <c r="C512" t="inlineStr">
+      <c r="C511" t="inlineStr">
         <is>
           <t>あらびあや</t>
         </is>
       </c>
     </row>
-    <row r="513">
-      <c r="A513" t="inlineStr">
+    <row r="512">
+      <c r="A512" t="inlineStr">
         <is>
           <t xml:space="preserve">「よろこべ」افرح
 イフラハ [ifraH]
@@ -11193,19 +11172,19 @@
 2308 https://samia-khalil.blogspot.jp/2014/08/blog-post.html?m=1 </t>
         </is>
       </c>
-      <c r="B513" t="inlineStr">
+      <c r="B512" t="inlineStr">
         <is>
           <t>images/「よろこべ」_img1.jpg</t>
         </is>
       </c>
-      <c r="C513" t="inlineStr">
+      <c r="C512" t="inlineStr">
         <is>
           <t>子供 ,笑顔</t>
         </is>
       </c>
     </row>
-    <row r="514">
-      <c r="A514" t="inlineStr">
+    <row r="513">
+      <c r="A513" t="inlineStr">
         <is>
           <t xml:space="preserve">「いつでも正しいことをしなさい」
 دائما افعل الشيء الصحيح
@@ -11215,19 +11194,19 @@
 2508 instagram com/p/zNNDYAsNaG/ </t>
         </is>
       </c>
-      <c r="B514" t="inlineStr">
+      <c r="B513" t="inlineStr">
         <is>
           <t>images/「いつでも正しいことをしなさい」_img1.jpg</t>
         </is>
       </c>
-      <c r="C514" t="inlineStr">
+      <c r="C513" t="inlineStr">
         <is>
           <t>教訓 ,正義</t>
         </is>
       </c>
     </row>
-    <row r="515">
-      <c r="A515" t="inlineStr">
+    <row r="514">
+      <c r="A514" t="inlineStr">
         <is>
           <t xml:space="preserve">「コンフォートゾーンから、出よう」
 اخرج من منطقة الراحة
@@ -11237,37 +11216,37 @@
 2010 kareem mrghani </t>
         </is>
       </c>
+      <c r="B514" t="inlineStr">
+        <is>
+          <t>images/「コンフォートゾーンから、出よう」_img1.jpg</t>
+        </is>
+      </c>
+      <c r="C514" t="inlineStr">
+        <is>
+          <t>鳥 ,勇気</t>
+        </is>
+      </c>
+    </row>
+    <row r="515">
+      <c r="A515" t="inlineStr">
+        <is>
+          <t xml:space="preserve">オットセイ。
+2308 https://twitter.com/NatGeoMagArab/status/1602604286109970432 </t>
+        </is>
+      </c>
       <c r="B515" t="inlineStr">
         <is>
-          <t>images/「コンフォートゾーンから、出よう」_img1.jpg</t>
+          <t>images/オットセイ。_img1.jpg,images/オットセイ。_img2.jpg</t>
         </is>
       </c>
       <c r="C515" t="inlineStr">
         <is>
-          <t>鳥 ,勇気</t>
+          <t>手書き語学 ,アラビア語 ,オットセイ</t>
         </is>
       </c>
     </row>
     <row r="516">
       <c r="A516" t="inlineStr">
-        <is>
-          <t xml:space="preserve">オットセイ。
-2308 https://twitter.com/NatGeoMagArab/status/1602604286109970432 </t>
-        </is>
-      </c>
-      <c r="B516" t="inlineStr">
-        <is>
-          <t>images/オットセイ。_img1.jpg,images/オットセイ。_img2.jpg</t>
-        </is>
-      </c>
-      <c r="C516" t="inlineStr">
-        <is>
-          <t>手書き語学 ,アラビア語 ,オットセイ</t>
-        </is>
-      </c>
-    </row>
-    <row r="517">
-      <c r="A517" t="inlineStr">
         <is>
           <t xml:space="preserve">「かわいい家に住む」
 يعيش في بيت لطيف
@@ -11277,19 +11256,19 @@
 2607 </t>
         </is>
       </c>
-      <c r="B517" t="inlineStr">
+      <c r="B516" t="inlineStr">
         <is>
           <t>images/「かわいい家に住む」_img1.jpg</t>
         </is>
       </c>
-      <c r="C517" t="inlineStr">
+      <c r="C516" t="inlineStr">
         <is>
           <t>アニメ ,ハム太郎</t>
         </is>
       </c>
     </row>
-    <row r="518">
-      <c r="A518" t="inlineStr">
+    <row r="517">
+      <c r="A517" t="inlineStr">
         <is>
           <t xml:space="preserve">「私の美しい町で大きい家に住んでいます」
 أعيش في بيت كبير في مدينتي الجميلة
@@ -11298,15 +11277,15 @@
 2410 Arabic With Nadia youtu be ocbg19GPCWE </t>
         </is>
       </c>
-      <c r="B518" t="inlineStr">
+      <c r="B517" t="inlineStr">
         <is>
           <t>images/「私の美しい町で大きい家に住んでいます_img1.jpg</t>
         </is>
       </c>
-      <c r="C518" t="inlineStr"/>
-    </row>
-    <row r="519">
-      <c r="A519" t="inlineStr">
+      <c r="C517" t="inlineStr"/>
+    </row>
+    <row r="518">
+      <c r="A518" t="inlineStr">
         <is>
           <t xml:space="preserve">「どうして早く寝るのかな」
 لماذا أنام باكراً؟
@@ -11316,19 +11295,19 @@
 2511 سلسلة الحلزونة </t>
         </is>
       </c>
-      <c r="B519" t="inlineStr">
+      <c r="B518" t="inlineStr">
         <is>
           <t>images/「どうして早く寝るのかな」_img1.jpg</t>
         </is>
       </c>
-      <c r="C519" t="inlineStr">
+      <c r="C518" t="inlineStr">
         <is>
           <t>絵本 ,ホルモン</t>
         </is>
       </c>
     </row>
-    <row r="520">
-      <c r="A520" t="inlineStr">
+    <row r="519">
+      <c r="A519" t="inlineStr">
         <is>
           <t xml:space="preserve">⁦「この絵文字はどんな意味？」⁩
 ماذا يعني هذا الايموجي؟؟
@@ -11338,19 +11317,19 @@
 2407 YouTube Smail Tech </t>
         </is>
       </c>
-      <c r="B520" t="inlineStr">
+      <c r="B519" t="inlineStr">
         <is>
           <t>images/⁦「この絵文字はどんな意味？」⁩_img1.jpg</t>
         </is>
       </c>
-      <c r="C520" t="inlineStr">
+      <c r="C519" t="inlineStr">
         <is>
           <t>顔 ,絵文字</t>
         </is>
       </c>
     </row>
-    <row r="521">
-      <c r="A521" t="inlineStr">
+    <row r="520">
+      <c r="A520" t="inlineStr">
         <is>
           <t xml:space="preserve">「回し車の中で回る」
 يدور في دولاب خفيف
@@ -11360,19 +11339,19 @@
 2109 </t>
         </is>
       </c>
-      <c r="B521" t="inlineStr">
+      <c r="B520" t="inlineStr">
         <is>
           <t>images/「回し車の中で回る」_img1.jpg</t>
         </is>
       </c>
-      <c r="C521" t="inlineStr">
+      <c r="C520" t="inlineStr">
         <is>
           <t>ハムスター  ,ハム太郎</t>
         </is>
       </c>
     </row>
-    <row r="522">
-      <c r="A522" t="inlineStr">
+    <row r="521">
+      <c r="A521" t="inlineStr">
         <is>
           <t xml:space="preserve">「自信を持つには？」
 كيف تثق بنفسك؟
@@ -11382,19 +11361,19 @@
 2411 Gwid3, tumblr </t>
         </is>
       </c>
-      <c r="B522" t="inlineStr">
+      <c r="B521" t="inlineStr">
         <is>
           <t>images/「自信を持つには？」_img1.jpg</t>
         </is>
       </c>
-      <c r="C522" t="inlineStr">
+      <c r="C521" t="inlineStr">
         <is>
           <t>イラスト ,自信</t>
         </is>
       </c>
     </row>
-    <row r="523">
-      <c r="A523" t="inlineStr">
+    <row r="522">
+      <c r="A522" t="inlineStr">
         <is>
           <t xml:space="preserve">「幸せな眠り…。この子ライオンは深い眠りに落ちている」
 نوم هانئ.. يغط هذا الشبل في نوم عميق
@@ -11405,19 +11384,19 @@
 2105 https://twitter.com/NatGeoMagArab/status/1305084013141319682 </t>
         </is>
       </c>
-      <c r="B523" t="inlineStr">
+      <c r="B522" t="inlineStr">
         <is>
           <t>images/「幸せな眠り…。この子ライオンは深い眠.jpeg</t>
         </is>
       </c>
-      <c r="C523" t="inlineStr">
+      <c r="C522" t="inlineStr">
         <is>
           <t>お昼寝 ,ｽﾔｧ</t>
         </is>
       </c>
     </row>
-    <row r="524">
-      <c r="A524" t="inlineStr">
+    <row r="523">
+      <c r="A523" t="inlineStr">
         <is>
           <t xml:space="preserve">「いつ思いつきますか？」
 متى تأتي الأفكار؟
@@ -11427,19 +11406,19 @@
 2103 alyaum com </t>
         </is>
       </c>
-      <c r="B524" t="inlineStr">
+      <c r="B523" t="inlineStr">
         <is>
           <t>images/「いつ思いつきますか？」_img1.jpg</t>
         </is>
       </c>
-      <c r="C524" t="inlineStr">
+      <c r="C523" t="inlineStr">
         <is>
           <t>ひらめき ,メモ</t>
         </is>
       </c>
     </row>
-    <row r="525">
-      <c r="A525" t="inlineStr">
+    <row r="524">
+      <c r="A524" t="inlineStr">
         <is>
           <t xml:space="preserve">「美しくありなさい。世界が美しく見えますよ」
 كن جميلا ترىٰ الوجود جميلا
@@ -11449,19 +11428,19 @@
 2111 https://iiislam.tumblr.com/post/90505498218 </t>
         </is>
       </c>
-      <c r="B525" t="inlineStr">
+      <c r="B524" t="inlineStr">
         <is>
           <t>images/「美しくありなさい。世界が美しく見えま_img1.jpg</t>
         </is>
       </c>
-      <c r="C525" t="inlineStr">
+      <c r="C524" t="inlineStr">
         <is>
           <t>壁 ,宇宙</t>
         </is>
       </c>
     </row>
-    <row r="526">
-      <c r="A526" t="inlineStr">
+    <row r="525">
+      <c r="A525" t="inlineStr">
         <is>
           <t xml:space="preserve">「まもなくNASAがジェイムズ・ウェッブ宇宙望遠鏡の打ち上げを行う」
 بعد ساعات قليلة ستقوم وكالة ناسا بإطلاق تلسكوب جيمس ويب
@@ -11469,19 +11448,19 @@
 2308 https://twitter.com/scitalk2u/status/1474643899603947524 </t>
         </is>
       </c>
-      <c r="B526" t="inlineStr">
+      <c r="B525" t="inlineStr">
         <is>
           <t>images/「まもなくNASAがジェイムズ・ウェッ_img1.jpg</t>
         </is>
       </c>
-      <c r="C526" t="inlineStr">
+      <c r="C525" t="inlineStr">
         <is>
           <t>NASA ,望遠鏡</t>
         </is>
       </c>
     </row>
-    <row r="527">
-      <c r="A527" t="inlineStr">
+    <row r="526">
+      <c r="A526" t="inlineStr">
         <is>
           <t xml:space="preserve">「お疲れ様です」يعطيك العافية
 ヤーアティーキルアーフィエ [ya-*_tiy-k el-*aafyeh]
@@ -11490,15 +11469,15 @@
 2109 محمد و ديمة بشار </t>
         </is>
       </c>
-      <c r="B527" t="inlineStr"/>
-      <c r="C527" t="inlineStr">
+      <c r="B526" t="inlineStr"/>
+      <c r="C526" t="inlineStr">
         <is>
           <t>歌 ,労い</t>
         </is>
       </c>
     </row>
-    <row r="528">
-      <c r="A528" t="inlineStr">
+    <row r="527">
+      <c r="A527" t="inlineStr">
         <is>
           <t xml:space="preserve">「まるでこのペンギンは大声で叫んでいるかのようだ」
 يبدو هذا البطريق وكأنه يصيح بعلو صوته
@@ -11506,19 +11485,19 @@
 2308 https://twitter.com/NatGeoMagArab/status/1492023331846967296 </t>
         </is>
       </c>
-      <c r="B528" t="inlineStr">
+      <c r="B527" t="inlineStr">
         <is>
           <t>images/「まるでこのペンギンは大声で叫んでいる_img1.jpg</t>
         </is>
       </c>
-      <c r="C528" t="inlineStr">
+      <c r="C527" t="inlineStr">
         <is>
           <t>手書き語学 ,ペンギン</t>
         </is>
       </c>
     </row>
-    <row r="529">
-      <c r="A529" t="inlineStr">
+    <row r="528">
+      <c r="A528" t="inlineStr">
         <is>
           <t xml:space="preserve">「Reteti Elephant Sanctuaryではゾウの孤児たちが良質な世話を受けている」
 تحظى الفيلة اليتيمة في "ملاذ ريتِيتِي لرعاية الفِيَلة" برعاية فائقة
@@ -11526,19 +11505,19 @@
 2209 https://twitter.com/NatGeoMagArab/status/1568683277845942273 </t>
         </is>
       </c>
-      <c r="B529" t="inlineStr">
+      <c r="B528" t="inlineStr">
         <is>
           <t>images/「Reteti Elephant Sa.jpg</t>
         </is>
       </c>
-      <c r="C529" t="inlineStr">
+      <c r="C528" t="inlineStr">
         <is>
           <t>ケニア</t>
         </is>
       </c>
     </row>
-    <row r="530">
-      <c r="A530" t="inlineStr">
+    <row r="529">
+      <c r="A529" t="inlineStr">
         <is>
           <t xml:space="preserve">「すぐ戻ります」سنعود بعد قليل
 サナウード・バアド・カリール [sa-na-*uud ba*d qaliil]
@@ -11547,19 +11526,19 @@
 2308 Clacket Media </t>
         </is>
       </c>
-      <c r="B530" t="inlineStr">
+      <c r="B529" t="inlineStr">
         <is>
           <t>images/「すぐ戻ります」_img1.jpg</t>
         </is>
       </c>
-      <c r="C530" t="inlineStr">
+      <c r="C529" t="inlineStr">
         <is>
           <t>プレート ,ドラマ</t>
         </is>
       </c>
     </row>
-    <row r="531">
-      <c r="A531" t="inlineStr">
+    <row r="530">
+      <c r="A530" t="inlineStr">
         <is>
           <t xml:space="preserve">「いつの日か、私は飛ぶんだ」
 يوم من الأيام سأطير
@@ -11569,19 +11548,19 @@
 2105 a-d-a-y-d-r-e-a-m-e-r.tumblr com </t>
         </is>
       </c>
-      <c r="B531" t="inlineStr">
+      <c r="B530" t="inlineStr">
         <is>
           <t>images/「いつの日か、私は飛ぶんだ」_img1.jpg</t>
         </is>
       </c>
-      <c r="C531" t="inlineStr">
+      <c r="C530" t="inlineStr">
         <is>
           <t>希望 ,未来</t>
         </is>
       </c>
     </row>
-    <row r="532">
-      <c r="A532" t="inlineStr">
+    <row r="531">
+      <c r="A531" t="inlineStr">
         <is>
           <t xml:space="preserve">「彼の声がこんなふうだと想像しましたか？」
 هل تخيلت أن يكون صوته هكذا؟
@@ -11589,19 +11568,19 @@
 2504 https://twitter.com/NatGeoMagArab/status/1567543266954067970 </t>
         </is>
       </c>
-      <c r="B532" t="inlineStr">
+      <c r="B531" t="inlineStr">
         <is>
           <t>images/「彼の声がこんなふうだと想像しましたか_img1.jpg</t>
         </is>
       </c>
-      <c r="C532" t="inlineStr">
+      <c r="C531" t="inlineStr">
         <is>
           <t>手書き語学 ,アラビア語 ,齧歯類</t>
         </is>
       </c>
     </row>
-    <row r="533">
-      <c r="A533" t="inlineStr">
+    <row r="532">
+      <c r="A532" t="inlineStr">
         <is>
           <t xml:space="preserve">「幸せでいるための10の科学的方法」
 عشر طرق علمية لتكون سعيدا
@@ -11610,19 +11589,19 @@
 2308 Founders and Founders </t>
         </is>
       </c>
-      <c r="B533" t="inlineStr">
+      <c r="B532" t="inlineStr">
         <is>
           <t>images/「幸せでいるための10の科学的方法」_img1.jpg</t>
         </is>
       </c>
-      <c r="C533" t="inlineStr">
+      <c r="C532" t="inlineStr">
         <is>
           <t>happy ,コツ</t>
         </is>
       </c>
     </row>
-    <row r="534">
-      <c r="A534" t="inlineStr">
+    <row r="533">
+      <c r="A533" t="inlineStr">
         <is>
           <t xml:space="preserve">「何事も難しい。簡単になる前は」
 كل شيء صعب قبل أن يصير سهل
@@ -11631,19 +11610,19 @@
 1809 nihad me </t>
         </is>
       </c>
-      <c r="B534" t="inlineStr">
+      <c r="B533" t="inlineStr">
         <is>
           <t>images/「何事も難しい。簡単になる前は」_img1.jpg</t>
         </is>
       </c>
-      <c r="C534" t="inlineStr">
+      <c r="C533" t="inlineStr">
         <is>
           <t>初心者 ,教訓</t>
         </is>
       </c>
     </row>
-    <row r="535">
-      <c r="A535" t="inlineStr">
+    <row r="534">
+      <c r="A534" t="inlineStr">
         <is>
           <t xml:space="preserve">「私は作家になるのが夢です」
 أحلُمُ أن أكونَ كاتبة
@@ -11653,19 +11632,19 @@
 2308 Maktabatee com </t>
         </is>
       </c>
-      <c r="B535" t="inlineStr">
+      <c r="B534" t="inlineStr">
         <is>
           <t>images/「私は作家になるのが夢です」_img1.jpg</t>
         </is>
       </c>
-      <c r="C535" t="inlineStr">
+      <c r="C534" t="inlineStr">
         <is>
           <t>作家志望 ,ライター</t>
         </is>
       </c>
     </row>
-    <row r="536">
-      <c r="A536" t="inlineStr">
+    <row r="535">
+      <c r="A535" t="inlineStr">
         <is>
           <t xml:space="preserve">「あなたが去った後も波は止みません」
 لن يقف الموج بعد رحيلك
@@ -11675,19 +11654,19 @@
 2308 ريم الشاوش https://ar.arabwomanmag.com/%D9%84%D9%86-%D9%8A%D9%82%D9%81-%D8%A7%D9%84%D9%85%D9%88%D8%AC-%D8%A8%D8%B9%D8%AF-%D8%B1%D8%AD%D9%8A%D9%84%D9%83-%D8%A8%D8%B9%D8%AF-%D8%B1%D8%AD%D9%8A%D9%84%D9%83/ </t>
         </is>
       </c>
-      <c r="B536" t="inlineStr">
+      <c r="B535" t="inlineStr">
         <is>
           <t>images/「あなたが去った後も波は止みません」_img1.jpg</t>
         </is>
       </c>
-      <c r="C536" t="inlineStr">
+      <c r="C535" t="inlineStr">
         <is>
           <t>海 ,哲学</t>
         </is>
       </c>
     </row>
-    <row r="537">
-      <c r="A537" t="inlineStr">
+    <row r="536">
+      <c r="A536" t="inlineStr">
         <is>
           <t xml:space="preserve">「彼の尖った牙を心配するな」
 لا تدع أنيابه المدببة تقلقك
@@ -11696,19 +11675,19 @@
 2308 https://twitter.com/NatGeoMagArab/status/1524691046818406400 </t>
         </is>
       </c>
-      <c r="B537" t="inlineStr">
+      <c r="B536" t="inlineStr">
         <is>
           <t>images/「彼の尖った牙を心配するな」_img1.jpg,images/「彼の尖った牙を心配するな」_img2.jpg,images/「彼の尖った牙を心配するな」_img3.jpg</t>
         </is>
       </c>
-      <c r="C537" t="inlineStr">
+      <c r="C536" t="inlineStr">
         <is>
           <t xml:space="preserve">手書き語学 ,アラビア語 ,キバノロ </t>
         </is>
       </c>
     </row>
-    <row r="538">
-      <c r="A538" t="inlineStr">
+    <row r="537">
+      <c r="A537" t="inlineStr">
         <is>
           <t xml:space="preserve">「恐れるな」لا تخف
 ラー・タカフ [laa ta-Khaf]
@@ -11717,19 +11696,19 @@
 2308 KiTeLetZ </t>
         </is>
       </c>
-      <c r="B538" t="inlineStr">
+      <c r="B537" t="inlineStr">
         <is>
           <t>images/「恐れるな」_img1.jpg</t>
         </is>
       </c>
-      <c r="C538" t="inlineStr">
+      <c r="C537" t="inlineStr">
         <is>
           <t>カリグラフィー ,緑</t>
         </is>
       </c>
     </row>
-    <row r="539">
-      <c r="A539" t="inlineStr">
+    <row r="538">
+      <c r="A538" t="inlineStr">
         <is>
           <t xml:space="preserve">「立ち上がれ。遅すぎることはない」
 انهض. لم يفت الأوان بعد
@@ -11739,19 +11718,19 @@
 2308 typo_g </t>
         </is>
       </c>
-      <c r="B539" t="inlineStr">
+      <c r="B538" t="inlineStr">
         <is>
           <t>images/「立ち上がれ。遅すぎることはない」_img1.jpg</t>
         </is>
       </c>
-      <c r="C539" t="inlineStr">
+      <c r="C538" t="inlineStr">
         <is>
           <t>出発</t>
         </is>
       </c>
     </row>
-    <row r="540">
-      <c r="A540" t="inlineStr">
+    <row r="539">
+      <c r="A539" t="inlineStr">
         <is>
           <t xml:space="preserve">「泣かないで」لا تَبْكِ
 ラー・タブキ [laa ta-bki]
@@ -11760,19 +11739,19 @@
 2203 arwa </t>
         </is>
       </c>
-      <c r="B540" t="inlineStr">
+      <c r="B539" t="inlineStr">
         <is>
           <t>images/「泣かないで」_img1.jpg</t>
         </is>
       </c>
-      <c r="C540" t="inlineStr">
+      <c r="C539" t="inlineStr">
         <is>
           <t>傘 ,虹</t>
         </is>
       </c>
     </row>
-    <row r="541">
-      <c r="A541" t="inlineStr">
+    <row r="540">
+      <c r="A540" t="inlineStr">
         <is>
           <t xml:space="preserve">「強くあるしかない」
 لا تكنْ الا قوِيا
@@ -11782,19 +11761,19 @@
 2401 AHMED ELASSAL </t>
         </is>
       </c>
-      <c r="B541" t="inlineStr">
+      <c r="B540" t="inlineStr">
         <is>
           <t>images/「強くあるしかない」_img1.jpg</t>
         </is>
       </c>
-      <c r="C541" t="inlineStr">
+      <c r="C540" t="inlineStr">
         <is>
           <t>二重否定 ,心構え</t>
         </is>
       </c>
     </row>
-    <row r="542">
-      <c r="A542" t="inlineStr">
+    <row r="541">
+      <c r="A541" t="inlineStr">
         <is>
           <t xml:space="preserve">「止まりなさい」قف
 キフ [qif]
@@ -11804,19 +11783,19 @@
 2308 出典不明（英語版：同内容。中国語版：「今日も可愛いね」） </t>
         </is>
       </c>
-      <c r="B542" t="inlineStr">
+      <c r="B541" t="inlineStr">
         <is>
           <t>images/「止まりなさい」_img1.jpg,images/「止まりなさい」_img2.jpg,images/「止まりなさい」_img3.jpg,images/「止まりなさい」_img4.jpg</t>
         </is>
       </c>
-      <c r="C542" t="inlineStr">
+      <c r="C541" t="inlineStr">
         <is>
           <t>かわいい ,職質</t>
         </is>
       </c>
     </row>
-    <row r="543">
-      <c r="A543" t="inlineStr">
+    <row r="542">
+      <c r="A542" t="inlineStr">
         <is>
           <t xml:space="preserve">「自分の人生を生きろ」عش حياتك
 イシ・ハヤータク [*iSh Hayaata-k]
@@ -11825,19 +11804,19 @@
 2607 Pinterest, hus2013asr </t>
         </is>
       </c>
-      <c r="B543" t="inlineStr">
+      <c r="B542" t="inlineStr">
         <is>
           <t>images/「自分の人生を生きろ」_img1.jpg</t>
         </is>
       </c>
-      <c r="C543" t="inlineStr">
+      <c r="C542" t="inlineStr">
         <is>
           <t>iPhone ,壁紙</t>
         </is>
       </c>
     </row>
-    <row r="544">
-      <c r="A544" t="inlineStr">
+    <row r="543">
+      <c r="A543" t="inlineStr">
         <is>
           <t xml:space="preserve">「おやすみザイナ」نامي يا زينة
 ナーミー・ヤー・ザイナ [naam-ii yaa zayna]
@@ -11846,19 +11825,19 @@
 2511 Dar Alsalwa </t>
         </is>
       </c>
-      <c r="B544" t="inlineStr">
+      <c r="B543" t="inlineStr">
         <is>
           <t>images/「おやすみザイナ」_img1.jpg</t>
         </is>
       </c>
-      <c r="C544" t="inlineStr">
+      <c r="C543" t="inlineStr">
         <is>
           <t>絵本 ,ベッド</t>
         </is>
       </c>
     </row>
-    <row r="545">
-      <c r="A545" t="inlineStr">
+    <row r="544">
+      <c r="A544" t="inlineStr">
         <is>
           <t xml:space="preserve">「強くありなさい」كُن قَوياً
 クン・カウィーヤン [kun qawiiyan]
@@ -11867,19 +11846,19 @@
 2109 MJCODEZ </t>
         </is>
       </c>
-      <c r="B545" t="inlineStr">
+      <c r="B544" t="inlineStr">
         <is>
           <t>images/「強くありなさい」_img1.jpg</t>
         </is>
       </c>
-      <c r="C545" t="inlineStr">
+      <c r="C544" t="inlineStr">
         <is>
           <t>名言 ,強い</t>
         </is>
       </c>
     </row>
-    <row r="546">
-      <c r="A546" t="inlineStr">
+    <row r="545">
+      <c r="A545" t="inlineStr">
         <is>
           <t xml:space="preserve">「強くありなさい、自分のために」
 كُن قويًا لأجلك
@@ -11889,19 +11868,19 @@
 1809 gwid3.tumblr </t>
         </is>
       </c>
-      <c r="B546" t="inlineStr">
+      <c r="B545" t="inlineStr">
         <is>
           <t>images/「強くありなさい、自分のために」_img1.jpg</t>
         </is>
       </c>
-      <c r="C546" t="inlineStr">
+      <c r="C545" t="inlineStr">
         <is>
           <t>名言 ,強い</t>
         </is>
       </c>
     </row>
-    <row r="547">
-      <c r="A547" t="inlineStr">
+    <row r="546">
+      <c r="A546" t="inlineStr">
         <is>
           <t xml:space="preserve">「どこでも自分でありなさい」
 كن أنت أينما كنت
@@ -11911,19 +11890,19 @@
 2605 souqfann com/r/15987  </t>
         </is>
       </c>
-      <c r="B547" t="inlineStr">
+      <c r="B546" t="inlineStr">
         <is>
           <t>images/「どこでも自分でありなさい」_img1.jpg</t>
         </is>
       </c>
-      <c r="C547" t="inlineStr">
+      <c r="C546" t="inlineStr">
         <is>
           <t>デザイン ,アート</t>
         </is>
       </c>
     </row>
-    <row r="548">
-      <c r="A548" t="inlineStr">
+    <row r="547">
+      <c r="A547" t="inlineStr">
         <is>
           <t xml:space="preserve">「止まれ。検問中」قف للتفتيش
 キフ。リッタフティーシ [qif li^taftiiSh]
@@ -11932,19 +11911,19 @@
 2109 Marcel Musil flickr </t>
         </is>
       </c>
-      <c r="B548" t="inlineStr">
+      <c r="B547" t="inlineStr">
         <is>
           <t>images/「止まれ。検問中」_img1.jpg</t>
         </is>
       </c>
-      <c r="C548" t="inlineStr">
+      <c r="C547" t="inlineStr">
         <is>
           <t>標識</t>
         </is>
       </c>
     </row>
-    <row r="549">
-      <c r="A549" t="inlineStr">
+    <row r="548">
+      <c r="A548" t="inlineStr">
         <is>
           <t xml:space="preserve">「さあおやすみ」هَيّا نَمْ
 ハイヤー・ナム [hayyaa nam]
@@ -11952,19 +11931,19 @@
 2308 Maktabatee com </t>
         </is>
       </c>
-      <c r="B549" t="inlineStr">
+      <c r="B548" t="inlineStr">
         <is>
           <t>images/「さあおやすみ」_img1.jpg</t>
         </is>
       </c>
-      <c r="C549" t="inlineStr">
+      <c r="C548" t="inlineStr">
         <is>
           <t>就寝 ,絵本</t>
         </is>
       </c>
     </row>
-    <row r="550">
-      <c r="A550" t="inlineStr">
+    <row r="549">
+      <c r="A549" t="inlineStr">
         <is>
           <t xml:space="preserve">「あなたであれ」كن أنت
 クン・アンタ [ku 'anta]
@@ -11972,19 +11951,19 @@
 1809 madyan22.tumblr </t>
         </is>
       </c>
-      <c r="B550" t="inlineStr">
+      <c r="B549" t="inlineStr">
         <is>
           <t>images/「あなたであれ」_img1.jpg</t>
         </is>
       </c>
-      <c r="C550" t="inlineStr">
+      <c r="C549" t="inlineStr">
         <is>
           <t>個性 ,自尊心</t>
         </is>
       </c>
     </row>
-    <row r="551">
-      <c r="A551" t="inlineStr">
+    <row r="550">
+      <c r="A550" t="inlineStr">
         <is>
           <t xml:space="preserve">「過去を忘れろ。だが教訓は忘れるな」
 إنسَ الماضي ولكن لاتنسَ الدرس
@@ -11994,19 +11973,19 @@
 2308 https://www.instagram.com/emanalyafai </t>
         </is>
       </c>
-      <c r="B551" t="inlineStr">
+      <c r="B550" t="inlineStr">
         <is>
           <t>images/「過去を忘れろ。だが教訓は忘れるな」_img1.jpg</t>
         </is>
       </c>
-      <c r="C551" t="inlineStr">
+      <c r="C550" t="inlineStr">
         <is>
           <t>名言 ,未来</t>
         </is>
       </c>
     </row>
-    <row r="552">
-      <c r="A552" t="inlineStr">
+    <row r="551">
+      <c r="A551" t="inlineStr">
         <is>
           <t xml:space="preserve">「この世界で君も何かを持っている。だから立ち上がれ！」
 لَكْ شيءٌ في هَذَا العَالَم… فَقُمْ
@@ -12014,19 +11993,19 @@
 2511 mjdal7arbi tumblr, Ghassan Kanafani </t>
         </is>
       </c>
-      <c r="B552" t="inlineStr">
+      <c r="B551" t="inlineStr">
         <is>
           <t>images/「この世界で君も何かを持っている。だか.jpg</t>
         </is>
       </c>
-      <c r="C552" t="inlineStr">
+      <c r="C551" t="inlineStr">
         <is>
           <t>鼓舞 ,ハンカチ王子</t>
         </is>
       </c>
     </row>
-    <row r="553">
-      <c r="A553" t="inlineStr">
+    <row r="552">
+      <c r="A552" t="inlineStr">
         <is>
           <t xml:space="preserve">「かぞえてかずをかきましょう」
 عد واكتب العدد
@@ -12035,19 +12014,19 @@
 2604 facebook Qsre alawani </t>
         </is>
       </c>
-      <c r="B553" t="inlineStr">
+      <c r="B552" t="inlineStr">
         <is>
           <t>images/「かぞえてかずをかきましょう」.JPG</t>
         </is>
       </c>
-      <c r="C553" t="inlineStr">
+      <c r="C552" t="inlineStr">
         <is>
           <t>算数 ,さんすう</t>
         </is>
       </c>
     </row>
-    <row r="554">
-      <c r="A554" t="inlineStr">
+    <row r="553">
+      <c r="A553" t="inlineStr">
         <is>
           <t xml:space="preserve">「いつも人助けしなさい」
 كن عونا للناس دوما
@@ -12057,19 +12036,19 @@
 2109 Muhammad ElMahdy </t>
         </is>
       </c>
-      <c r="B554" t="inlineStr">
+      <c r="B553" t="inlineStr">
         <is>
           <t>images/「いつも人助けしなさい」_img1.jpg</t>
         </is>
       </c>
-      <c r="C554" t="inlineStr">
+      <c r="C553" t="inlineStr">
         <is>
           <t>教訓 ,助っ人</t>
         </is>
       </c>
     </row>
-    <row r="555">
-      <c r="A555" t="inlineStr">
+    <row r="554">
+      <c r="A554" t="inlineStr">
         <is>
           <t xml:space="preserve">「毎年、ノーベル賞が授けられる」
 في كل عام تُمنح جوائز نوبل
@@ -12077,19 +12056,19 @@
 2404 https://twitter.com/SciTalk2U/status/1462482447627661319 </t>
         </is>
       </c>
-      <c r="B555" t="inlineStr">
+      <c r="B554" t="inlineStr">
         <is>
           <t>images/「毎年、ノーベル賞が授けられる」_img1.jpg</t>
         </is>
       </c>
-      <c r="C555" t="inlineStr">
+      <c r="C554" t="inlineStr">
         <is>
           <t>手書き語学 ,アラビア語 ,ノーベル賞</t>
         </is>
       </c>
     </row>
-    <row r="556">
-      <c r="A556" t="inlineStr">
+    <row r="555">
+      <c r="A555" t="inlineStr">
         <is>
           <t xml:space="preserve">「あなたはアラビア語を話しますか」
 هل تتكلم العربية؟
@@ -12099,19 +12078,19 @@
 2109 al3arabiya com </t>
         </is>
       </c>
-      <c r="B556" t="inlineStr">
+      <c r="B555" t="inlineStr">
         <is>
           <t>images/「あなたはアラビア語を話しますか」_img1.jpg</t>
         </is>
       </c>
-      <c r="C556" t="inlineStr">
+      <c r="C555" t="inlineStr">
         <is>
           <t>教科書 ,テキスト</t>
         </is>
       </c>
     </row>
-    <row r="557">
-      <c r="A557" t="inlineStr">
+    <row r="556">
+      <c r="A556" t="inlineStr">
         <is>
           <t xml:space="preserve">「このインコは亜熱帯が起源である」
 يتحدر هذا الباراكيت من المناطق شبه الاستوائية
@@ -12119,19 +12098,19 @@
 2402 https://x.com/NatGeoMagArab/status/1690626751578439680 </t>
         </is>
       </c>
-      <c r="B557" t="inlineStr">
+      <c r="B556" t="inlineStr">
         <is>
           <t>images/「このインコは亜熱帯が起源である」_img1.jpg,images/「このインコは亜熱帯が起源である」_img2.jpg</t>
         </is>
       </c>
-      <c r="C557" t="inlineStr">
+      <c r="C556" t="inlineStr">
         <is>
           <t>手書き語学 ,アラビア語 ,オナガミドリインコ</t>
         </is>
       </c>
     </row>
-    <row r="558">
-      <c r="A558" t="inlineStr">
+    <row r="557">
+      <c r="A557" t="inlineStr">
         <is>
           <t xml:space="preserve">「彼を覚えていますか」
 هل تتذكرونه؟
@@ -12141,19 +12120,19 @@
 2308 http://newsfacetruth.blogspot.com/2017/07/blog-post_11.html </t>
         </is>
       </c>
-      <c r="B558" t="inlineStr">
+      <c r="B557" t="inlineStr">
         <is>
           <t>images/「彼を覚えていますか」_img1.jpg</t>
         </is>
       </c>
-      <c r="C558" t="inlineStr">
+      <c r="C557" t="inlineStr">
         <is>
           <t>グレンダイザー ,UFOロボ</t>
         </is>
       </c>
     </row>
-    <row r="559">
-      <c r="A559" t="inlineStr">
+    <row r="558">
+      <c r="A558" t="inlineStr">
         <is>
           <t xml:space="preserve">「内面が変われば周りが変わる」
 عندما تتغير الأشياء داخلك، تتغير الأشياء من حولك
@@ -12162,19 +12141,19 @@
 2501 Facebook, Cairo Mockingbird </t>
         </is>
       </c>
-      <c r="B559" t="inlineStr">
+      <c r="B558" t="inlineStr">
         <is>
           <t>images/「内面が変われば周りが変わる」_img1.jpg</t>
         </is>
       </c>
-      <c r="C559" t="inlineStr">
+      <c r="C558" t="inlineStr">
         <is>
           <t>ポジティブ</t>
         </is>
       </c>
     </row>
-    <row r="560">
-      <c r="A560" t="inlineStr">
+    <row r="559">
+      <c r="A559" t="inlineStr">
         <is>
           <t xml:space="preserve">「天才になるには？」
 كيف تصبح عبقريا؟
@@ -12183,19 +12162,19 @@
 2109 Infographics Samah Faris </t>
         </is>
       </c>
-      <c r="B560" t="inlineStr">
+      <c r="B559" t="inlineStr">
         <is>
           <t>images/「天才になるには？」_img1.jpg</t>
         </is>
       </c>
-      <c r="C560" t="inlineStr">
+      <c r="C559" t="inlineStr">
         <is>
           <t>秘訣 ,コツ</t>
         </is>
       </c>
     </row>
-    <row r="561">
-      <c r="A561" t="inlineStr">
+    <row r="560">
+      <c r="A560" t="inlineStr">
         <is>
           <t xml:space="preserve">「彼らと友情を交わすよハム太郎」
 وبالإخاء يبادلهم هامتارو
@@ -12205,19 +12184,19 @@
 2109 </t>
         </is>
       </c>
-      <c r="B561" t="inlineStr">
+      <c r="B560" t="inlineStr">
         <is>
           <t>images/「彼らと友情を交わすよハム太郎」_img1.jpg</t>
         </is>
       </c>
-      <c r="C561" t="inlineStr">
+      <c r="C560" t="inlineStr">
         <is>
           <t>アニメ ,ハム太郎</t>
         </is>
       </c>
     </row>
-    <row r="562">
-      <c r="A562" t="inlineStr">
+    <row r="561">
+      <c r="A561" t="inlineStr">
         <is>
           <t xml:space="preserve">「誰がニワトリを助ける？」
 من يساعد الدّجاجة؟
@@ -12227,19 +12206,19 @@
 2109 alnqsh com </t>
         </is>
       </c>
-      <c r="B562" t="inlineStr">
+      <c r="B561" t="inlineStr">
         <is>
           <t>images/「誰がニワトリを助ける？」_img1.jpg</t>
         </is>
       </c>
-      <c r="C562" t="inlineStr">
+      <c r="C561" t="inlineStr">
         <is>
           <t>絵本 ,チキン</t>
         </is>
       </c>
     </row>
-    <row r="563">
-      <c r="A563" t="inlineStr">
+    <row r="562">
+      <c r="A562" t="inlineStr">
         <is>
           <t xml:space="preserve">「心臓病を避けるには？」
 كيف تتجنب أمراض القلب؟
@@ -12249,37 +12228,37 @@
 2608 lanamedical_sa </t>
         </is>
       </c>
+      <c r="B562" t="inlineStr">
+        <is>
+          <t>images/「心臓病を避けるには？」.jpg</t>
+        </is>
+      </c>
+      <c r="C562" t="inlineStr">
+        <is>
+          <t>生活習慣病 ,心臓</t>
+        </is>
+      </c>
+    </row>
+    <row r="563">
+      <c r="A563" t="inlineStr">
+        <is>
+          <t xml:space="preserve">「どうやらこの好奇心旺盛なペンギンは…」
+2308 https://twitter.com/NatGeoMagArab/status/1591460860207443968 </t>
+        </is>
+      </c>
       <c r="B563" t="inlineStr">
         <is>
-          <t>images/「心臓病を避けるには？」.jpg</t>
+          <t>images/「どうやらこの好奇心旺盛なペンギンは…_img1.jpg,images/ 「どうやらこの好奇心旺盛なペンギンは…_img2.jpg</t>
         </is>
       </c>
       <c r="C563" t="inlineStr">
         <is>
-          <t>生活習慣病 ,心臓</t>
+          <t>手書き語学 ,アラビア語 ,オウサマペンギン</t>
         </is>
       </c>
     </row>
     <row r="564">
       <c r="A564" t="inlineStr">
-        <is>
-          <t xml:space="preserve">「どうやらこの好奇心旺盛なペンギンは…」
-2308 https://twitter.com/NatGeoMagArab/status/1591460860207443968 </t>
-        </is>
-      </c>
-      <c r="B564" t="inlineStr">
-        <is>
-          <t>images/「どうやらこの好奇心旺盛なペンギンは…_img1.jpg,images/ 「どうやらこの好奇心旺盛なペンギンは…_img2.jpg</t>
-        </is>
-      </c>
-      <c r="C564" t="inlineStr">
-        <is>
-          <t>手書き語学 ,アラビア語 ,オウサマペンギン</t>
-        </is>
-      </c>
-    </row>
-    <row r="565">
-      <c r="A565" t="inlineStr">
         <is>
           <t xml:space="preserve">「ひとを幸せにするには？」
 كيف تسعد غيرك؟
@@ -12289,19 +12268,19 @@
 2308 Gwid3 </t>
         </is>
       </c>
-      <c r="B565" t="inlineStr">
+      <c r="B564" t="inlineStr">
         <is>
           <t>images/「ひとを幸せにするには？」_img1.jpg</t>
         </is>
       </c>
-      <c r="C565" t="inlineStr">
+      <c r="C564" t="inlineStr">
         <is>
           <t>思いやり ,心</t>
         </is>
       </c>
     </row>
-    <row r="566">
-      <c r="A566" t="inlineStr">
+    <row r="565">
+      <c r="A565" t="inlineStr">
         <is>
           <t xml:space="preserve">「ラマダン月に口臭をおさえる方法は？」
 كيف تتجنب رائحة الفم في رمضان
@@ -12310,19 +12289,19 @@
 2109 AlArabiya </t>
         </is>
       </c>
-      <c r="B566" t="inlineStr">
+      <c r="B565" t="inlineStr">
         <is>
           <t>images/「ラマダン月に口臭をおさえる方法は？」_img1.jpg</t>
         </is>
       </c>
-      <c r="C566" t="inlineStr">
+      <c r="C565" t="inlineStr">
         <is>
           <t>イスラム教 ,ブレスケア</t>
         </is>
       </c>
     </row>
-    <row r="567">
-      <c r="A567" t="inlineStr">
+    <row r="566">
+      <c r="A566" t="inlineStr">
         <is>
           <t xml:space="preserve">「ヨユウなきユウヨ」
 يمهل ولا يهمل
@@ -12332,19 +12311,19 @@
 2512 instagram com/p/CK4CLqeJ3dy/ </t>
         </is>
       </c>
-      <c r="B567" t="inlineStr">
+      <c r="B566" t="inlineStr">
         <is>
           <t>images/「ヨユウなきユウヨ」_img1.jpg</t>
         </is>
       </c>
-      <c r="C567" t="inlineStr">
+      <c r="C566" t="inlineStr">
         <is>
           <t>時計 ,からくり</t>
         </is>
       </c>
     </row>
-    <row r="568">
-      <c r="A568" t="inlineStr">
+    <row r="567">
+      <c r="A567" t="inlineStr">
         <is>
           <t xml:space="preserve">「どうして？　動物は絶滅する」
 لماذا؟ تنقرض الحيوانات
@@ -12354,19 +12333,19 @@
 2308 goodreads com </t>
         </is>
       </c>
-      <c r="B568" t="inlineStr">
+      <c r="B567" t="inlineStr">
         <is>
           <t>images/「どうして？　動物は絶滅する」_img1.jpg</t>
         </is>
       </c>
-      <c r="C568" t="inlineStr">
+      <c r="C567" t="inlineStr">
         <is>
           <t>動物 ,子供用</t>
         </is>
       </c>
     </row>
-    <row r="569">
-      <c r="A569" t="inlineStr">
+    <row r="568">
+      <c r="A568" t="inlineStr">
         <is>
           <t xml:space="preserve">「私たちは異なる。だから調和する」
 نختلف.. لنأتلف
@@ -12376,19 +12355,19 @@
 2103 Nawal Saed </t>
         </is>
       </c>
-      <c r="B569" t="inlineStr">
+      <c r="B568" t="inlineStr">
         <is>
           <t>images/「私たちは異なる。だから調和する」_img1.jpg</t>
         </is>
       </c>
-      <c r="C569" t="inlineStr">
+      <c r="C568" t="inlineStr">
         <is>
           <t>異符号 ,ハーモニー</t>
         </is>
       </c>
     </row>
-    <row r="570">
-      <c r="A570" t="inlineStr">
+    <row r="569">
+      <c r="A569" t="inlineStr">
         <is>
           <t xml:space="preserve">「私の肺には蝶々が住んでいて、呼吸の度に羽ばたく」
 تسكن رئتيّ فراشة ترفرف كلما أتنفس
@@ -12397,19 +12376,19 @@
 2109 出典不明 </t>
         </is>
       </c>
-      <c r="B570" t="inlineStr">
+      <c r="B569" t="inlineStr">
         <is>
           <t>images/「私の肺には蝶々が住んでいて、呼吸の度_img1.jpg</t>
         </is>
       </c>
-      <c r="C570" t="inlineStr">
+      <c r="C569" t="inlineStr">
         <is>
           <t>人体 ,昆虫</t>
         </is>
       </c>
     </row>
-    <row r="571">
-      <c r="A571" t="inlineStr">
+    <row r="570">
+      <c r="A570" t="inlineStr">
         <is>
           <t xml:space="preserve">「安らぎを感じますか？」
 هل تستشعر السكينة؟
@@ -12418,19 +12397,19 @@
 2404 https://twitter.com/NatGeoMagArab/status/1541421154950209536 </t>
         </is>
       </c>
-      <c r="B571" t="inlineStr">
+      <c r="B570" t="inlineStr">
         <is>
           <t>images/「安らぎを感じますか？」_img1.jpg</t>
         </is>
       </c>
-      <c r="C571" t="inlineStr">
+      <c r="C570" t="inlineStr">
         <is>
           <t>手書き語学 ,アラビア語 ,エイ</t>
         </is>
       </c>
     </row>
-    <row r="572">
-      <c r="A572" t="inlineStr">
+    <row r="571">
+      <c r="A571" t="inlineStr">
         <is>
           <t xml:space="preserve">「たとえあなたの使うブラウザがChromeだろうとSafariだろうと」
 سواء كنت تستخدم متصفح كروم أو سفاري
@@ -12438,19 +12417,19 @@
 2308 https://twitter.com/ShaayTech/status/1536235333972635649 </t>
         </is>
       </c>
-      <c r="B572" t="inlineStr">
+      <c r="B571" t="inlineStr">
         <is>
           <t>images/「たとえあなたの使うブラウザがChro_img1.jpg</t>
         </is>
       </c>
-      <c r="C572" t="inlineStr">
+      <c r="C571" t="inlineStr">
         <is>
           <t xml:space="preserve">手書き語学 ,アラビア語 ,iPhone </t>
         </is>
       </c>
     </row>
-    <row r="573">
-      <c r="A573" t="inlineStr">
+    <row r="572">
+      <c r="A572" t="inlineStr">
         <is>
           <t xml:space="preserve">「このミドリモリヤツガシラは気づいて欲しい」
 يحرص "هدهد الخشب الأخضر" هذا على أن يدرك
@@ -12459,19 +12438,19 @@
 2308 https://twitter.com/NatGeoMagArab/status/1531161022928539648 </t>
         </is>
       </c>
-      <c r="B573" t="inlineStr">
+      <c r="B572" t="inlineStr">
         <is>
           <t>images/「このミドリモリヤツガシラは気づいて欲_img1.jpg</t>
         </is>
       </c>
-      <c r="C573" t="inlineStr">
+      <c r="C572" t="inlineStr">
         <is>
           <t xml:space="preserve">手書き語学 ,アラビア語 ,鳥 </t>
         </is>
       </c>
     </row>
-    <row r="574">
-      <c r="A574" t="inlineStr">
+    <row r="573">
+      <c r="A573" t="inlineStr">
         <is>
           <t xml:space="preserve">「あなたの怖いものは何ですか」
 ماهي مخاوفك؟
@@ -12483,15 +12462,15 @@
 2308 1112kok </t>
         </is>
       </c>
-      <c r="B574" t="inlineStr">
+      <c r="B573" t="inlineStr">
         <is>
           <t>images/「あなたの怖いものは何ですか」_img1.jpg</t>
         </is>
       </c>
-      <c r="C574" t="inlineStr"/>
-    </row>
-    <row r="575">
-      <c r="A575" t="inlineStr">
+      <c r="C573" t="inlineStr"/>
+    </row>
+    <row r="574">
+      <c r="A574" t="inlineStr">
         <is>
           <t xml:space="preserve">「美しい時は作るもの。待つものではない」
 اصنع اللحظات الجميلة. لا تنتظرها
@@ -12500,19 +12479,19 @@
 2308 abojamal.tumblr com </t>
         </is>
       </c>
-      <c r="B575" t="inlineStr">
+      <c r="B574" t="inlineStr">
         <is>
           <t>images/「美しい時は作るもの。待つものではない_img1.jpg</t>
         </is>
       </c>
-      <c r="C575" t="inlineStr">
+      <c r="C574" t="inlineStr">
         <is>
           <t>おうち時間</t>
         </is>
       </c>
     </row>
-    <row r="576">
-      <c r="A576" t="inlineStr">
+    <row r="575">
+      <c r="A575" t="inlineStr">
         <is>
           <t xml:space="preserve">「大切な時間を大切じゃないことに使わないこと」
 لا تضيع الوقت المهم في شيء غير مهم
@@ -12521,19 +12500,19 @@
 2308 Anwar_122_ </t>
         </is>
       </c>
-      <c r="B576" t="inlineStr">
+      <c r="B575" t="inlineStr">
         <is>
           <t>images/「大切な時間を大切じゃないことに使わな_img1.jpg</t>
         </is>
       </c>
-      <c r="C576" t="inlineStr">
+      <c r="C575" t="inlineStr">
         <is>
           <t>時間 ,貴重</t>
         </is>
       </c>
     </row>
-    <row r="577">
-      <c r="A577" t="inlineStr">
+    <row r="576">
+      <c r="A576" t="inlineStr">
         <is>
           <t xml:space="preserve">「このイノセントな目に騙されるな…」
 لا تنخدع بهذه العيون البريئة
@@ -12543,19 +12522,19 @@
 2201 https://twitter.com/NatGeoMagArab/status/1475715760202797056 </t>
         </is>
       </c>
-      <c r="B577" t="inlineStr">
+      <c r="B576" t="inlineStr">
         <is>
           <t>images/「このイノセントな目に騙されるな…」.png</t>
         </is>
       </c>
-      <c r="C577" t="inlineStr">
+      <c r="C576" t="inlineStr">
         <is>
           <t>がうがう ,カワイイ</t>
         </is>
       </c>
     </row>
-    <row r="578">
-      <c r="A578" t="inlineStr">
+    <row r="577">
+      <c r="A577" t="inlineStr">
         <is>
           <t xml:space="preserve">⁦「カメラを止めろ！」⁩
 أوقفوا التّصوير
@@ -12565,19 +12544,19 @@
 2509 alsalwabooks com </t>
         </is>
       </c>
-      <c r="B578" t="inlineStr">
+      <c r="B577" t="inlineStr">
         <is>
           <t>images/⁦「カメラを止めろ！」⁩_img1.jpg</t>
         </is>
       </c>
-      <c r="C578" t="inlineStr">
+      <c r="C577" t="inlineStr">
         <is>
           <t>絵本 ,撮影</t>
         </is>
       </c>
     </row>
-    <row r="579">
-      <c r="A579" t="inlineStr">
+    <row r="578">
+      <c r="A578" t="inlineStr">
         <is>
           <t xml:space="preserve">「話す前に考えなさい」
 فكر قبل ان تتكلم
@@ -12587,19 +12566,19 @@
 2308 Islamuna YouTube </t>
         </is>
       </c>
-      <c r="B579" t="inlineStr">
+      <c r="B578" t="inlineStr">
         <is>
           <t>images/「話す前に考えなさい」_img1.jpg</t>
         </is>
       </c>
-      <c r="C579" t="inlineStr">
+      <c r="C578" t="inlineStr">
         <is>
           <t>失言 ,発言</t>
         </is>
       </c>
     </row>
-    <row r="580">
-      <c r="A580" t="inlineStr">
+    <row r="579">
+      <c r="A579" t="inlineStr">
         <is>
           <t xml:space="preserve">「ツイッターでフォローして下さい」
 تابعونا على تويتر
@@ -12609,19 +12588,19 @@
 2109 出典不明 </t>
         </is>
       </c>
-      <c r="B580" t="inlineStr">
+      <c r="B579" t="inlineStr">
         <is>
           <t>images/「ツイッターでフォローして下さい」_img1.jpg</t>
         </is>
       </c>
-      <c r="C580" t="inlineStr">
+      <c r="C579" t="inlineStr">
         <is>
           <t>FollowUs ,バナー</t>
         </is>
       </c>
     </row>
-    <row r="581">
-      <c r="A581" t="inlineStr">
+    <row r="580">
+      <c r="A580" t="inlineStr">
         <is>
           <t xml:space="preserve">「敵を倒せ」دمّر العدو
 ダンミリ_ルアドゥーウ [dammiri l-*aduuw]
@@ -12630,19 +12609,19 @@
 2308 apkpure com </t>
         </is>
       </c>
-      <c r="B581" t="inlineStr">
+      <c r="B580" t="inlineStr">
         <is>
           <t>images/「敵を倒せ」_img1.jpg</t>
         </is>
       </c>
-      <c r="C581" t="inlineStr">
+      <c r="C580" t="inlineStr">
         <is>
           <t>ゲーム ,パンダ</t>
         </is>
       </c>
     </row>
-    <row r="582">
-      <c r="A582" t="inlineStr">
+    <row r="581">
+      <c r="A581" t="inlineStr">
         <is>
           <t xml:space="preserve">「咲け。蒔かれたらどこであろうと」
 أزهر أيْنمَا زرعت
@@ -12651,19 +12630,19 @@
 2407 Ahmed Madyan </t>
         </is>
       </c>
-      <c r="B582" t="inlineStr">
+      <c r="B581" t="inlineStr">
         <is>
           <t>images/「咲け。蒔かれたらどこであろうと」_img1.jpg</t>
         </is>
       </c>
-      <c r="C582" t="inlineStr">
+      <c r="C581" t="inlineStr">
         <is>
           <t>環境のせいにしない ,花</t>
         </is>
       </c>
     </row>
-    <row r="583">
-      <c r="A583" t="inlineStr">
+    <row r="582">
+      <c r="A582" t="inlineStr">
         <is>
           <t xml:space="preserve">「頭を働かせろ」شغل مخك
 シャッギル・ムッハク [Sha^Ghil mu^Kha-k]
@@ -12672,19 +12651,19 @@
 2103 facebook elpage </t>
         </is>
       </c>
-      <c r="B583" t="inlineStr">
+      <c r="B582" t="inlineStr">
         <is>
           <t>images/「頭を働かせろ」_img1.jpg</t>
         </is>
       </c>
-      <c r="C583" t="inlineStr">
+      <c r="C582" t="inlineStr">
         <is>
           <t>電源 ,頭脳</t>
         </is>
       </c>
     </row>
-    <row r="584">
-      <c r="A584" t="inlineStr">
+    <row r="583">
+      <c r="A583" t="inlineStr">
         <is>
           <t xml:space="preserve">「傷跡は星にかえなさい」
 حوّل نُدوبكَ إلى نُجومْ
@@ -12694,19 +12673,19 @@
 2107 saramj1992 Instagram </t>
         </is>
       </c>
-      <c r="B584" t="inlineStr">
+      <c r="B583" t="inlineStr">
         <is>
           <t>images/「傷跡は星にかえなさい」_img1.jpg</t>
         </is>
       </c>
-      <c r="C584" t="inlineStr">
+      <c r="C583" t="inlineStr">
         <is>
           <t>勲章 ,証</t>
         </is>
       </c>
     </row>
-    <row r="585">
-      <c r="A585" t="inlineStr">
+    <row r="584">
+      <c r="A584" t="inlineStr">
         <is>
           <t xml:space="preserve">「あなたの主の栄光を誉め称え、また（御赦しを請え。本当にかれは、度々赦される御方である）」
 فسَبِّح بحمد ربك و
@@ -12715,19 +12694,19 @@
 2109 出典不明 </t>
         </is>
       </c>
-      <c r="B585" t="inlineStr">
+      <c r="B584" t="inlineStr">
         <is>
           <t>images/「あなたの主の栄光を誉め称え、また（御_img1.jpg</t>
         </is>
       </c>
-      <c r="C585" t="inlineStr">
+      <c r="C584" t="inlineStr">
         <is>
           <t>イスラム教 ,カリグラフィー</t>
         </is>
       </c>
     </row>
-    <row r="586">
-      <c r="A586" t="inlineStr">
+    <row r="585">
+      <c r="A585" t="inlineStr">
         <is>
           <t xml:space="preserve">「誰かを幸福にしなさい」
 أسْعِد أحدهم
@@ -12737,19 +12716,19 @@
 1810 in4sser.tumblr </t>
         </is>
       </c>
-      <c r="B586" t="inlineStr">
+      <c r="B585" t="inlineStr">
         <is>
           <t>images/「誰かを幸福にしなさい」_img1.jpg</t>
         </is>
       </c>
-      <c r="C586" t="inlineStr">
+      <c r="C585" t="inlineStr">
         <is>
           <t>人生 ,happy</t>
         </is>
       </c>
     </row>
-    <row r="587">
-      <c r="A587" t="inlineStr">
+    <row r="586">
+      <c r="A586" t="inlineStr">
         <is>
           <t xml:space="preserve">「見よ」أبْصِرْ
 アブスィル ['ab_sir]
@@ -12758,19 +12737,19 @@
 1811 Ruh Al-Alam, via Behance </t>
         </is>
       </c>
-      <c r="B587" t="inlineStr">
+      <c r="B586" t="inlineStr">
         <is>
           <t>images/「見よ」_img1.jpg</t>
         </is>
       </c>
-      <c r="C587" t="inlineStr">
+      <c r="C586" t="inlineStr">
         <is>
           <t>目 ,瞳</t>
         </is>
       </c>
     </row>
-    <row r="588">
-      <c r="A588" t="inlineStr">
+    <row r="587">
+      <c r="A587" t="inlineStr">
         <is>
           <t xml:space="preserve">「言葉は口から出す前に味わいなさい」
 ‪تذوق كلماتك قبل أن تنطقها‬
@@ -12780,19 +12759,19 @@
 2109 Reham-des </t>
         </is>
       </c>
-      <c r="B588" t="inlineStr">
+      <c r="B587" t="inlineStr">
         <is>
           <t>images/「言葉は口から出す前に味わいなさい」_img1.jpg</t>
         </is>
       </c>
-      <c r="C588" t="inlineStr">
+      <c r="C587" t="inlineStr">
         <is>
           <t>言葉</t>
         </is>
       </c>
     </row>
-    <row r="589">
-      <c r="A589" t="inlineStr">
+    <row r="588">
+      <c r="A588" t="inlineStr">
         <is>
           <t xml:space="preserve">「テレビを観るのをやめて下さい」
 توقفي عن مشاهدة التلفاز
@@ -12802,19 +12781,19 @@
 1809 </t>
         </is>
       </c>
-      <c r="B589" t="inlineStr">
+      <c r="B588" t="inlineStr">
         <is>
           <t>images/「テレビを観るのをやめて下さい」_img1.jpg</t>
         </is>
       </c>
-      <c r="C589" t="inlineStr">
+      <c r="C588" t="inlineStr">
         <is>
           <t>あらびあや</t>
         </is>
       </c>
     </row>
-    <row r="590">
-      <c r="A590" t="inlineStr">
+    <row r="589">
+      <c r="A589" t="inlineStr">
         <is>
           <t xml:space="preserve">「言わぬが花」
 انْطِقْ جَمَالاً أو تجَمَّلْ بالسّكُوت
@@ -12824,19 +12803,19 @@
 2411 Ahmed Madyan </t>
         </is>
       </c>
-      <c r="B590" t="inlineStr">
+      <c r="B589" t="inlineStr">
         <is>
           <t>images/「言わぬが花」_img1.jpg</t>
         </is>
       </c>
-      <c r="C590" t="inlineStr">
+      <c r="C589" t="inlineStr">
         <is>
           <t>ことわざ ,デザイン</t>
         </is>
       </c>
     </row>
-    <row r="591">
-      <c r="A591" t="inlineStr">
+    <row r="590">
+      <c r="A590" t="inlineStr">
         <is>
           <t xml:space="preserve">「たくさん考えて、少し話すこと」
 فكّر كثيرا. تكلم قليلا
@@ -12846,19 +12825,19 @@
 2105 In49r </t>
         </is>
       </c>
-      <c r="B591" t="inlineStr">
+      <c r="B590" t="inlineStr">
         <is>
           <t>images/「たくさん考えて、少し話すこと」_img1.jpg</t>
         </is>
       </c>
-      <c r="C591" t="inlineStr">
+      <c r="C590" t="inlineStr">
         <is>
           <t>思慮 ,会話</t>
         </is>
       </c>
     </row>
-    <row r="592">
-      <c r="A592" t="inlineStr">
+    <row r="591">
+      <c r="A591" t="inlineStr">
         <is>
           <t xml:space="preserve">「子供たちよ、いつでも思い出すんだよ」
 تذكروا دوما يا أطفال
@@ -12868,19 +12847,19 @@
 1809 </t>
         </is>
       </c>
-      <c r="B592" t="inlineStr">
+      <c r="B591" t="inlineStr">
         <is>
           <t>images/「子供たちよ、いつでも思い出すんだよ」_img1.jpg</t>
         </is>
       </c>
-      <c r="C592" t="inlineStr">
+      <c r="C591" t="inlineStr">
         <is>
           <t>オープニング ,ハム太郎</t>
         </is>
       </c>
     </row>
-    <row r="593">
-      <c r="A593" t="inlineStr">
+    <row r="592">
+      <c r="A592" t="inlineStr">
         <is>
           <t xml:space="preserve">「分かってから話しなさい」
 تعلَّم ثمَّ تكلَّم
@@ -12890,19 +12869,19 @@
 1903 Hashem Al Shareef, Pinterest </t>
         </is>
       </c>
-      <c r="B593" t="inlineStr">
+      <c r="B592" t="inlineStr">
         <is>
           <t>images/「分かってから話しなさい」_img1.jpg</t>
         </is>
       </c>
-      <c r="C593" t="inlineStr">
+      <c r="C592" t="inlineStr">
         <is>
           <t>教訓 ,トーク</t>
         </is>
       </c>
     </row>
-    <row r="594">
-      <c r="A594" t="inlineStr">
+    <row r="593">
+      <c r="A593" t="inlineStr">
         <is>
           <t xml:space="preserve">「蟻に学べ」تعلم من النملة
 タアッラム・ミナ_ンナムラ [ta*allam mina ^namla]
@@ -12911,19 +12890,19 @@
 2308 fatakat com </t>
         </is>
       </c>
-      <c r="B594" t="inlineStr">
+      <c r="B593" t="inlineStr">
         <is>
           <t>images/「蟻に学べ」_img1.jpg</t>
         </is>
       </c>
-      <c r="C594" t="inlineStr">
+      <c r="C593" t="inlineStr">
         <is>
           <t>教訓 ,問題解決</t>
         </is>
       </c>
     </row>
-    <row r="595">
-      <c r="A595" t="inlineStr">
+    <row r="594">
+      <c r="A594" t="inlineStr">
         <is>
           <t xml:space="preserve">「自分と仲直りしよう、一杯の珈琲で！」
 تصالح مع نفسك بكوب قهوة
@@ -12933,19 +12912,19 @@
 2308 asm95_ </t>
         </is>
       </c>
-      <c r="B595" t="inlineStr">
+      <c r="B594" t="inlineStr">
         <is>
           <t>images/「自分と仲直りしよう、一杯の珈琲で！」_img1.jpg</t>
         </is>
       </c>
-      <c r="C595" t="inlineStr">
+      <c r="C594" t="inlineStr">
         <is>
           <t>一服 ,リラックス</t>
         </is>
       </c>
     </row>
-    <row r="596">
-      <c r="A596" t="inlineStr">
+    <row r="595">
+      <c r="A595" t="inlineStr">
         <is>
           <t xml:space="preserve">「気をつけて　ジュード」
 انتبهي يا جود
@@ -12955,19 +12934,19 @@
 2109 سلسلة الحلزونة </t>
         </is>
       </c>
-      <c r="B596" t="inlineStr">
+      <c r="B595" t="inlineStr">
         <is>
           <t>images/「気をつけて　ジュード」_img1.jpg</t>
         </is>
       </c>
-      <c r="C596" t="inlineStr">
+      <c r="C595" t="inlineStr">
         <is>
           <t>絵本 ,わんぱく</t>
         </is>
       </c>
     </row>
-    <row r="597">
-      <c r="A597" t="inlineStr">
+    <row r="596">
+      <c r="A596" t="inlineStr">
         <is>
           <t xml:space="preserve">「coming soon」
 انتظرونا قريبا
@@ -12976,19 +12955,19 @@
 2307 出典不明 </t>
         </is>
       </c>
-      <c r="B597" t="inlineStr">
+      <c r="B596" t="inlineStr">
         <is>
           <t>images/「coming soon」_img1.jpg</t>
         </is>
       </c>
-      <c r="C597" t="inlineStr">
+      <c r="C596" t="inlineStr">
         <is>
           <t>フレーズ ,カミングスーン</t>
         </is>
       </c>
     </row>
-    <row r="598">
-      <c r="A598" t="inlineStr">
+    <row r="597">
+      <c r="A597" t="inlineStr">
         <is>
           <t xml:space="preserve">「自分の胸に聞きなさい。それが全て知っています」
 استمع لقلبك.. إنه يعرف كل شيء
@@ -12997,19 +12976,19 @@
 1811 </t>
         </is>
       </c>
-      <c r="B598" t="inlineStr">
+      <c r="B597" t="inlineStr">
         <is>
           <t>images/「自分の胸に聞きなさい。それが全て知っ_img1.jpg</t>
         </is>
       </c>
-      <c r="C598" t="inlineStr">
+      <c r="C597" t="inlineStr">
         <is>
           <t>あらびあや</t>
         </is>
       </c>
     </row>
-    <row r="599">
-      <c r="A599" t="inlineStr">
+    <row r="598">
+      <c r="A598" t="inlineStr">
         <is>
           <t xml:space="preserve">「笑ってくれ、絶望を癒すのは君の笑みだから」
 ابتسمي فإن دواء اليأس بسمتك
@@ -13018,19 +12997,19 @@
 2308 arab-quotes tumblr </t>
         </is>
       </c>
-      <c r="B599" t="inlineStr">
+      <c r="B598" t="inlineStr">
         <is>
           <t>images/「笑ってくれ、絶望を癒すのは君の笑みだ_img1.jpg</t>
         </is>
       </c>
-      <c r="C599" t="inlineStr">
+      <c r="C598" t="inlineStr">
         <is>
           <t>癒し ,スマイル</t>
         </is>
       </c>
     </row>
-    <row r="600">
-      <c r="A600" t="inlineStr">
+    <row r="599">
+      <c r="A599" t="inlineStr">
         <is>
           <t xml:space="preserve">「自分を頼りなさい。宇宙で最も確かな物が自分だと思って。」
 استند على نفسك وكأنك أكثر الأشياء ثباتًا بهذا الكون
@@ -13038,19 +13017,19 @@
 2308 x_nourh.15 </t>
         </is>
       </c>
-      <c r="B600" t="inlineStr">
+      <c r="B599" t="inlineStr">
         <is>
           <t>images/「自分を頼りなさい。宇宙で最も確かな物_img1.jpg</t>
         </is>
       </c>
-      <c r="C600" t="inlineStr">
+      <c r="C599" t="inlineStr">
         <is>
           <t>自我 ,宇宙</t>
         </is>
       </c>
     </row>
-    <row r="601">
-      <c r="A601" t="inlineStr">
+    <row r="600">
+      <c r="A600" t="inlineStr">
         <is>
           <t xml:space="preserve">「古いデバイスを交換して新品をゲットしよう」
 استبدل جهازك القديم واحصل على واحد جديد
@@ -13059,19 +13038,19 @@
 2406 stc </t>
         </is>
       </c>
-      <c r="B601" t="inlineStr">
+      <c r="B600" t="inlineStr">
         <is>
           <t>images/「古いデバイスを交換して新品をゲットし_img1.jpg</t>
         </is>
       </c>
-      <c r="C601" t="inlineStr">
+      <c r="C600" t="inlineStr">
         <is>
           <t>キャンペーン ,下取り</t>
         </is>
       </c>
     </row>
-    <row r="602">
-      <c r="A602" t="inlineStr">
+    <row r="601">
+      <c r="A601" t="inlineStr">
         <is>
           <t xml:space="preserve">「あなたの声を聞かせてください。私の心を彩ってください」
 هات صوتك، لوّن قلبي
@@ -13080,19 +13059,19 @@
 2105 3a2esha_ Instagram </t>
         </is>
       </c>
-      <c r="B602" t="inlineStr">
+      <c r="B601" t="inlineStr">
         <is>
           <t>images/「あなたの声を聞かせてください。私の心_img1.jpg</t>
         </is>
       </c>
-      <c r="C602" t="inlineStr">
+      <c r="C601" t="inlineStr">
         <is>
           <t>電話 ,肉声</t>
         </is>
       </c>
     </row>
-    <row r="603">
-      <c r="A603" t="inlineStr">
+    <row r="602">
+      <c r="A602" t="inlineStr">
         <is>
           <t xml:space="preserve">「この子カンガルーは抱っこが好き」
 يُحب صغير الكنغر هذا أن يؤخذ في الأحضان
@@ -13100,19 +13079,19 @@
 2308 NatGeoMagArab </t>
         </is>
       </c>
-      <c r="B603" t="inlineStr">
+      <c r="B602" t="inlineStr">
         <is>
           <t>images/「この子カンガルーは抱っこが好き」.png</t>
         </is>
       </c>
-      <c r="C603" t="inlineStr">
+      <c r="C602" t="inlineStr">
         <is>
           <t>カンガルー ,人肌</t>
         </is>
       </c>
     </row>
-    <row r="604">
-      <c r="A604" t="inlineStr">
+    <row r="603">
+      <c r="A603" t="inlineStr">
         <is>
           <t xml:space="preserve">「カタールが好き」أحب قطر
 ウヒッブ・カタル ['u-Hibb qa_tar]
@@ -13121,19 +13100,19 @@
 1810 出典不明 </t>
         </is>
       </c>
-      <c r="B604" t="inlineStr">
+      <c r="B603" t="inlineStr">
         <is>
           <t>images/「カタールが好き」_img1.jpg</t>
         </is>
       </c>
-      <c r="C604" t="inlineStr">
+      <c r="C603" t="inlineStr">
         <is>
           <t>カタール</t>
         </is>
       </c>
     </row>
-    <row r="605">
-      <c r="A605" t="inlineStr">
+    <row r="604">
+      <c r="A604" t="inlineStr">
         <is>
           <t xml:space="preserve">「一緒に読むのが好き」
 أُحبُّ أن نَقْرَأَ مَعاً
@@ -13143,19 +13122,19 @@
 2509 www.neelwafurat com,  id=lbb212750-185765 </t>
         </is>
       </c>
-      <c r="B605" t="inlineStr">
+      <c r="B604" t="inlineStr">
         <is>
           <t>images/「一緒に読むのが好き」_img1.jpg</t>
         </is>
       </c>
-      <c r="C605" t="inlineStr">
+      <c r="C604" t="inlineStr">
         <is>
           <t>好き ,本</t>
         </is>
       </c>
     </row>
-    <row r="606">
-      <c r="A606" t="inlineStr">
+    <row r="605">
+      <c r="A605" t="inlineStr">
         <is>
           <t xml:space="preserve">「病院に行きたくない」
 لا أريد أن أذهب إلى المشفى
@@ -13165,19 +13144,19 @@
 2508 Tony Ross https://education.hachette-antoine.com/ar/component/%D9%84%D8%A7-%D8%A3%D8%B1%D9%8A%D8%AF-%D8%A3%D9%86-%D8%A3%D8%B0%D9%87%D8%A8-%D8%A5%D9%84%D9%89-%D8%A7%D9%84%D9%85%D8%B4%D9%81%D9%89/ </t>
         </is>
       </c>
-      <c r="B606" t="inlineStr">
+      <c r="B605" t="inlineStr">
         <is>
           <t>images/「病院に行きたくない」_img1.jpg</t>
         </is>
       </c>
-      <c r="C606" t="inlineStr">
+      <c r="C605" t="inlineStr">
         <is>
           <t>絵本 ,子供</t>
         </is>
       </c>
     </row>
-    <row r="607">
-      <c r="A607" t="inlineStr">
+    <row r="606">
+      <c r="A606" t="inlineStr">
         <is>
           <t xml:space="preserve">「男性はいくら？」「女性はいくら？」
 كم يساوى الرجل؟ ..وكم تساوى المرأة؟
@@ -13186,19 +13165,19 @@
 2308 Pinterest, Masr Elmahrousa, Farah Noweir </t>
         </is>
       </c>
-      <c r="B607" t="inlineStr">
+      <c r="B606" t="inlineStr">
         <is>
           <t>images/「男性はいくら？」「女性はいくら？」_img1.jpg,images/「男性はいくら？」「女性はいくら？」_img2.jpg</t>
         </is>
       </c>
-      <c r="C607" t="inlineStr">
+      <c r="C606" t="inlineStr">
         <is>
           <t xml:space="preserve">全身コーデ ,相場 </t>
         </is>
       </c>
     </row>
-    <row r="608">
-      <c r="A608" t="inlineStr">
+    <row r="607">
+      <c r="A607" t="inlineStr">
         <is>
           <t xml:space="preserve">「黙ってもらえます？」
 ممكن تعيرنا سكوتك؟
@@ -13208,19 +13187,19 @@
 2308 Basel26 </t>
         </is>
       </c>
-      <c r="B608" t="inlineStr">
+      <c r="B607" t="inlineStr">
         <is>
           <t>images/「黙ってもらえます？」_img1.jpg</t>
         </is>
       </c>
-      <c r="C608" t="inlineStr">
+      <c r="C607" t="inlineStr">
         <is>
           <t>音量 ,ボリューム</t>
         </is>
       </c>
     </row>
-    <row r="609">
-      <c r="A609" t="inlineStr">
+    <row r="608">
+      <c r="A608" t="inlineStr">
         <is>
           <t xml:space="preserve">「眠りたいです」
 أُريدُ أَن أَنام
@@ -13230,19 +13209,19 @@
 2109 goodreads com </t>
         </is>
       </c>
-      <c r="B609" t="inlineStr">
+      <c r="B608" t="inlineStr">
         <is>
           <t>images/「眠りたいです」_img1.jpg</t>
         </is>
       </c>
-      <c r="C609" t="inlineStr">
+      <c r="C608" t="inlineStr">
         <is>
           <t>絵本</t>
         </is>
       </c>
     </row>
-    <row r="610">
-      <c r="A610" t="inlineStr">
+    <row r="609">
+      <c r="A609" t="inlineStr">
         <is>
           <t xml:space="preserve">「飛びたい！」أُريد أن أطير
 ウリードゥ・アン・アティール ['u-riidu 'an 'a-_tiir]
@@ -13251,19 +13230,19 @@
 2308 出典不明 </t>
         </is>
       </c>
-      <c r="B610" t="inlineStr">
+      <c r="B609" t="inlineStr">
         <is>
           <t>images/「飛びたい！」_img1.jpg</t>
         </is>
       </c>
-      <c r="C610" t="inlineStr">
+      <c r="C609" t="inlineStr">
         <is>
           <t>鳥 ,希望</t>
         </is>
       </c>
     </row>
-    <row r="611">
-      <c r="A611" t="inlineStr">
+    <row r="610">
+      <c r="A610" t="inlineStr">
         <is>
           <t xml:space="preserve">「うちゅうへとびたい」
 أُريدُ أَنْ أَطيرَ إلى الفَضاء
@@ -13272,19 +13251,19 @@
 2308 mybookshelf co </t>
         </is>
       </c>
-      <c r="B611" t="inlineStr">
+      <c r="B610" t="inlineStr">
         <is>
           <t>images/「うちゅうへとびたい」_img1.jpg</t>
         </is>
       </c>
-      <c r="C611" t="inlineStr">
+      <c r="C610" t="inlineStr">
         <is>
           <t>絵本 ,宇宙</t>
         </is>
       </c>
     </row>
-    <row r="612">
-      <c r="A612" t="inlineStr">
+    <row r="611">
+      <c r="A611" t="inlineStr">
         <is>
           <t xml:space="preserve">「とても愛しています」
 أُحِبّك جِدّاً
@@ -13294,19 +13273,19 @@
 2308 hobe cc </t>
         </is>
       </c>
-      <c r="B612" t="inlineStr">
+      <c r="B611" t="inlineStr">
         <is>
           <t>images/「とても愛しています」_img1.jpg</t>
         </is>
       </c>
-      <c r="C612" t="inlineStr">
+      <c r="C611" t="inlineStr">
         <is>
           <t>恋 ,love</t>
         </is>
       </c>
     </row>
-    <row r="613">
-      <c r="A613" t="inlineStr">
+    <row r="612">
+      <c r="A612" t="inlineStr">
         <is>
           <t xml:space="preserve">「あす日が昇るだろう。私は朝が大好きだ」
 غدا ستشرق الشمس وأحب الصباح كثيرا
@@ -13315,19 +13294,19 @@
 2105 warag-3nb.tumblr com </t>
         </is>
       </c>
-      <c r="B613" t="inlineStr">
+      <c r="B612" t="inlineStr">
         <is>
           <t>images/「あす日が昇るだろう。私は朝が大好きだ_img1.jpg,images/ 「あす日が昇るだろう。私は朝が大好きだ_img2.jpg</t>
         </is>
       </c>
-      <c r="C613" t="inlineStr">
+      <c r="C612" t="inlineStr">
         <is>
           <t>おやすみ ,壁</t>
         </is>
       </c>
     </row>
-    <row r="614">
-      <c r="A614" t="inlineStr">
+    <row r="613">
+      <c r="A613" t="inlineStr">
         <is>
           <t xml:space="preserve">「きみは何をえらぶ？」
 ماذا تختار؟
@@ -13337,19 +13316,19 @@
 2109 embadomjp org </t>
         </is>
       </c>
-      <c r="B614" t="inlineStr">
+      <c r="B613" t="inlineStr">
         <is>
           <t>images/「きみは何をえらぶ？」_img1.jpg</t>
         </is>
       </c>
-      <c r="C614" t="inlineStr">
+      <c r="C613" t="inlineStr">
         <is>
           <t>優柔不断 ,絵本</t>
         </is>
       </c>
     </row>
-    <row r="615">
-      <c r="A615" t="inlineStr">
+    <row r="614">
+      <c r="A614" t="inlineStr">
         <is>
           <t xml:space="preserve">「ちょっと静けさが必要な時もある」
 في بعض الأوقات نحتاج لشوية هدوء
@@ -13359,19 +13338,19 @@
 2308 IN49r </t>
         </is>
       </c>
-      <c r="B615" t="inlineStr">
+      <c r="B614" t="inlineStr">
         <is>
           <t>images/「ちょっと静けさが必要な時もある」_img1.jpg</t>
         </is>
       </c>
-      <c r="C615" t="inlineStr">
+      <c r="C614" t="inlineStr">
         <is>
           <t>ミュート ,精神</t>
         </is>
       </c>
     </row>
-    <row r="616">
-      <c r="A616" t="inlineStr">
+    <row r="615">
+      <c r="A615" t="inlineStr">
         <is>
           <t xml:space="preserve">「逃げるな。全力でぶつかれ」
 لا تهرب اصطدم بكل قوتك
@@ -13381,19 +13360,19 @@
 2308 https://risingvibes.tumblr.com/post/189545775129 </t>
         </is>
       </c>
-      <c r="B616" t="inlineStr">
+      <c r="B615" t="inlineStr">
         <is>
           <t>images/「逃げるな。全力でぶつかれ」_img1.jpg</t>
         </is>
       </c>
-      <c r="C616" t="inlineStr">
+      <c r="C615" t="inlineStr">
         <is>
           <t>応援 ,力</t>
         </is>
       </c>
     </row>
-    <row r="617">
-      <c r="A617" t="inlineStr">
+    <row r="616">
+      <c r="A616" t="inlineStr">
         <is>
           <t xml:space="preserve">「着るのだいすき」
 أُحِبُ أَن أَرتَدِيَ
@@ -13403,19 +13382,19 @@
 2308 https://kitab.firmabikes.ru/epub-_hb_n_rtdy_5187.html </t>
         </is>
       </c>
-      <c r="B617" t="inlineStr">
+      <c r="B616" t="inlineStr">
         <is>
           <t>images/「着るのだいすき」_img1.jpg</t>
         </is>
       </c>
-      <c r="C617" t="inlineStr">
+      <c r="C616" t="inlineStr">
         <is>
           <t xml:space="preserve">絵本 ,ファッション </t>
         </is>
       </c>
     </row>
-    <row r="618">
-      <c r="A618" t="inlineStr">
+    <row r="617">
+      <c r="A617" t="inlineStr">
         <is>
           <t xml:space="preserve">「車のバッテリーが要る！」
 نحتاج بطارية سيارة
@@ -13425,19 +13404,19 @@
 2308 instagram roaa_27 </t>
         </is>
       </c>
-      <c r="B618" t="inlineStr">
+      <c r="B617" t="inlineStr">
         <is>
           <t>images/「車のバッテリーが要る！」_img1.jpg</t>
         </is>
       </c>
-      <c r="C618" t="inlineStr">
+      <c r="C617" t="inlineStr">
         <is>
           <t>スマホ ,充電</t>
         </is>
       </c>
     </row>
-    <row r="619">
-      <c r="A619" t="inlineStr">
+    <row r="618">
+      <c r="A618" t="inlineStr">
         <is>
           <t xml:space="preserve">「今日は幸せでいることにしました」
 اخترت أن أكون سعيدا اليوم
@@ -13447,19 +13426,19 @@
 2109 awaasha tumblr </t>
         </is>
       </c>
-      <c r="B619" t="inlineStr">
+      <c r="B618" t="inlineStr">
         <is>
           <t>images/「今日は幸せでいることにしました」_img1.jpg</t>
         </is>
       </c>
-      <c r="C619" t="inlineStr">
+      <c r="C618" t="inlineStr">
         <is>
           <t>心構え ,happy</t>
         </is>
       </c>
     </row>
-    <row r="620">
-      <c r="A620" t="inlineStr">
+    <row r="619">
+      <c r="A619" t="inlineStr">
         <is>
           <t xml:space="preserve">「理想的なスイカの選び方」
 كيف تختار البطيخة المُثلى؟
@@ -13469,19 +13448,19 @@
 2308 bit ly/octmel </t>
         </is>
       </c>
-      <c r="B620" t="inlineStr">
+      <c r="B619" t="inlineStr">
         <is>
           <t>images/「理想的なスイカの選び方」_img1.jpg</t>
         </is>
       </c>
-      <c r="C620" t="inlineStr">
+      <c r="C619" t="inlineStr">
         <is>
           <t>八百屋 ,西瓜</t>
         </is>
       </c>
     </row>
-    <row r="621">
-      <c r="A621" t="inlineStr">
+    <row r="620">
+      <c r="A620" t="inlineStr">
         <is>
           <t xml:space="preserve">「お問い合わせください」
 اتصل بنا
@@ -13491,19 +13470,19 @@
 2308 mtawir.blogspot com </t>
         </is>
       </c>
-      <c r="B621" t="inlineStr">
+      <c r="B620" t="inlineStr">
         <is>
           <t>images/「お問い合わせください」_img1.jpg</t>
         </is>
       </c>
-      <c r="C621" t="inlineStr">
+      <c r="C620" t="inlineStr">
         <is>
           <t>広告 ,電話</t>
         </is>
       </c>
     </row>
-    <row r="622">
-      <c r="A622" t="inlineStr">
+    <row r="621">
+      <c r="A621" t="inlineStr">
         <is>
           <t xml:space="preserve">「両方の動物が海岸の火山岩の亀裂の中に定住している」
 يحتل كلا الحيوانين شقوقًا في صخور الساحل البركانية
@@ -13511,19 +13490,19 @@
 2507 https://x.com/NatGeoMagArab/status/1925167200056521151 </t>
         </is>
       </c>
-      <c r="B622" t="inlineStr">
+      <c r="B621" t="inlineStr">
         <is>
           <t>images/「両方の動物が海岸の火山岩の亀裂の中に_img1.jpg,images/「両方の動物が海岸の火山岩の亀裂の中に_img2.jpg</t>
         </is>
       </c>
-      <c r="C622" t="inlineStr">
+      <c r="C621" t="inlineStr">
         <is>
           <t>手書き語学 ,アラビア語 ,イグアナ</t>
         </is>
       </c>
     </row>
-    <row r="623">
-      <c r="A623" t="inlineStr">
+    <row r="622">
+      <c r="A622" t="inlineStr">
         <is>
           <t xml:space="preserve">「命じられたように正しき道を辿れ」
 واستقم كما أمرت
@@ -13533,19 +13512,19 @@
 2308 Ahmed Madyan </t>
         </is>
       </c>
-      <c r="B623" t="inlineStr">
+      <c r="B622" t="inlineStr">
         <is>
           <t>images/「命じられたように正しき道を辿れ」_img1.jpg</t>
         </is>
       </c>
-      <c r="C623" t="inlineStr">
+      <c r="C622" t="inlineStr">
         <is>
           <t>書道 ,アート</t>
         </is>
       </c>
     </row>
-    <row r="624">
-      <c r="A624" t="inlineStr">
+    <row r="623">
+      <c r="A623" t="inlineStr">
         <is>
           <t xml:space="preserve">「くつろぎなさい」استكن
 イスタキンナ [istakinna]
@@ -13553,19 +13532,19 @@
 2603 m2ff tumblr com </t>
         </is>
       </c>
-      <c r="B624" t="inlineStr">
+      <c r="B623" t="inlineStr">
         <is>
           <t>images/「くつろぎなさい」.jpeg</t>
         </is>
       </c>
-      <c r="C624" t="inlineStr">
+      <c r="C623" t="inlineStr">
         <is>
           <t>relax ,コーヒー</t>
         </is>
       </c>
     </row>
-    <row r="625">
-      <c r="A625" t="inlineStr">
+    <row r="624">
+      <c r="A624" t="inlineStr">
         <is>
           <t xml:space="preserve">「彼は応えるだろう」سيستجيب 
 サヤスタジーブ [sa-ya-stajiibu]
@@ -13574,19 +13553,19 @@
 1811 kareem mrghani </t>
         </is>
       </c>
-      <c r="B625" t="inlineStr">
+      <c r="B624" t="inlineStr">
         <is>
           <t>images/「彼は応えるだろう」_img1.jpg</t>
         </is>
       </c>
-      <c r="C625" t="inlineStr">
+      <c r="C624" t="inlineStr">
         <is>
           <t>縦書き ,現代アート</t>
         </is>
       </c>
     </row>
-    <row r="626">
-      <c r="A626" t="inlineStr">
+    <row r="625">
+      <c r="A625" t="inlineStr">
         <is>
           <t xml:space="preserve">「アラビア語が好き」
 أنا أُحبّ لُغتي
@@ -13596,19 +13575,19 @@
 2308 出典不明 </t>
         </is>
       </c>
-      <c r="B626" t="inlineStr">
+      <c r="B625" t="inlineStr">
         <is>
           <t>images/「アラビア語が好き」_img1.jpg</t>
         </is>
       </c>
-      <c r="C626" t="inlineStr">
+      <c r="C625" t="inlineStr">
         <is>
           <t>和訳 ,こども</t>
         </is>
       </c>
     </row>
-    <row r="627">
-      <c r="A627" t="inlineStr">
+    <row r="626">
+      <c r="A626" t="inlineStr">
         <is>
           <t xml:space="preserve">「私はサッカーが好きです」
 أنا أُحِبُّ كُرةَ القَدَم
@@ -13618,19 +13597,19 @@
 2109 Arabic With Nadia </t>
         </is>
       </c>
-      <c r="B627" t="inlineStr">
+      <c r="B626" t="inlineStr">
         <is>
           <t>images/「私はサッカーが好きです」_img1.jpg</t>
         </is>
       </c>
-      <c r="C627" t="inlineStr">
+      <c r="C626" t="inlineStr">
         <is>
           <t>自由時間 ,例文</t>
         </is>
       </c>
     </row>
-    <row r="628">
-      <c r="A628" t="inlineStr">
+    <row r="627">
+      <c r="A627" t="inlineStr">
         <is>
           <t xml:space="preserve">「これ、私の眼鏡じゃありません」
 هٰذِهِ لَيْسَتْ نَظَّارَاتِي
@@ -13640,19 +13619,19 @@
 2509 </t>
         </is>
       </c>
-      <c r="B628" t="inlineStr">
+      <c r="B627" t="inlineStr">
         <is>
           <t>images/「これ、私の眼鏡じゃありません」_img1.jpg</t>
         </is>
       </c>
-      <c r="C628" t="inlineStr">
+      <c r="C627" t="inlineStr">
         <is>
           <t>あらびあや</t>
         </is>
       </c>
     </row>
-    <row r="629">
-      <c r="A629" t="inlineStr">
+    <row r="628">
+      <c r="A628" t="inlineStr">
         <is>
           <t xml:space="preserve">「我らも米を食います」
 نحن أيضاً نأكل الأرز
@@ -13662,19 +13641,19 @@
 1809 </t>
         </is>
       </c>
-      <c r="B629" t="inlineStr">
+      <c r="B628" t="inlineStr">
         <is>
           <t>images/「我らも米を食います」_img1.jpg</t>
         </is>
       </c>
-      <c r="C629" t="inlineStr">
+      <c r="C628" t="inlineStr">
         <is>
           <t>あらびあや</t>
         </is>
       </c>
     </row>
-    <row r="630">
-      <c r="A630" t="inlineStr">
+    <row r="629">
+      <c r="A629" t="inlineStr">
         <is>
           <t xml:space="preserve">「ひとりでできるもん！」
 أنا أستطيع أن أفعله وحدي
@@ -13683,19 +13662,19 @@
 2105 </t>
         </is>
       </c>
-      <c r="B630" t="inlineStr">
+      <c r="B629" t="inlineStr">
         <is>
           <t>images/「ひとりでできるもん！」_img1.jpg</t>
         </is>
       </c>
-      <c r="C630" t="inlineStr">
+      <c r="C629" t="inlineStr">
         <is>
           <t>あらびあや</t>
         </is>
       </c>
     </row>
-    <row r="631">
-      <c r="A631" t="inlineStr">
+    <row r="630">
+      <c r="A630" t="inlineStr">
         <is>
           <t xml:space="preserve">「恋しくないと言っている時は恋しい」
 أُريدُك حينَ أَقُولُ أَنا لا أُريدُك
@@ -13705,19 +13684,19 @@
 2308 DARWISHISM </t>
         </is>
       </c>
-      <c r="B631" t="inlineStr">
+      <c r="B630" t="inlineStr">
         <is>
           <t>images/「恋しくないと言っている時は恋しい」_img1.jpg</t>
         </is>
       </c>
-      <c r="C631" t="inlineStr">
+      <c r="C630" t="inlineStr">
         <is>
           <t>本音 ,恋愛</t>
         </is>
       </c>
     </row>
-    <row r="632">
-      <c r="A632" t="inlineStr">
+    <row r="631">
+      <c r="A631" t="inlineStr">
         <is>
           <t xml:space="preserve">「私は〜する」
 ⁦「着る」：( أنا ألبس )['ana 'a-lbas]⁩
@@ -13728,19 +13707,19 @@
 2109 RABIE </t>
         </is>
       </c>
-      <c r="B632" t="inlineStr">
+      <c r="B631" t="inlineStr">
         <is>
           <t>images/「私は〜する」_img1.jpg,images/「私は〜する」_img2.jpg,images/「私は〜する」_img3.jpg,images/「私は〜する」_img4.jpg</t>
         </is>
       </c>
-      <c r="C632" t="inlineStr">
+      <c r="C631" t="inlineStr">
         <is>
           <t>動詞 ,絵本</t>
         </is>
       </c>
     </row>
-    <row r="633">
-      <c r="A633" t="inlineStr">
+    <row r="632">
+      <c r="A632" t="inlineStr">
         <is>
           <t xml:space="preserve">「彼は完璧ではない。私は彼の欠点については目をつむった」
 هو ليس كامل. أنا أعميت نفسي عن سيئاته
@@ -13749,19 +13728,19 @@
 2308 _NOHA </t>
         </is>
       </c>
-      <c r="B633" t="inlineStr">
+      <c r="B632" t="inlineStr">
         <is>
           <t>images/「彼は完璧ではない。私は彼の欠点につい_img1.jpg</t>
         </is>
       </c>
-      <c r="C633" t="inlineStr">
+      <c r="C632" t="inlineStr">
         <is>
           <t>愛 ,寛容</t>
         </is>
       </c>
     </row>
-    <row r="634">
-      <c r="A634" t="inlineStr">
+    <row r="633">
+      <c r="A633" t="inlineStr">
         <is>
           <t xml:space="preserve">「この子トラは検疫期間中に生まれた」
 صغير النمر هذا ولد في زمن الحجر الصحي
@@ -13770,19 +13749,19 @@
 2310 https://www.akhbaralaan.net/?p=434924 </t>
         </is>
       </c>
-      <c r="B634" t="inlineStr">
+      <c r="B633" t="inlineStr">
         <is>
           <t>images/「この子トラは検疫期間中に生まれた」_img1.jpg</t>
         </is>
       </c>
-      <c r="C634" t="inlineStr">
+      <c r="C633" t="inlineStr">
         <is>
           <t>Covid ,メキシコ</t>
         </is>
       </c>
     </row>
-    <row r="635">
-      <c r="A635" t="inlineStr">
+    <row r="634">
+      <c r="A634" t="inlineStr">
         <is>
           <t xml:space="preserve">「睡眠の素晴らしさに匹敵するものは無い！」
 وجمال النوم ليس له مثيل
@@ -13791,19 +13770,19 @@
 2308 arabzy tumblr </t>
         </is>
       </c>
-      <c r="B635" t="inlineStr">
+      <c r="B634" t="inlineStr">
         <is>
           <t>images/「睡眠の素晴らしさに匹敵するものは無い_img1.jpg</t>
         </is>
       </c>
-      <c r="C635" t="inlineStr">
+      <c r="C634" t="inlineStr">
         <is>
           <t>オフトゥン ,おやすみ</t>
         </is>
       </c>
     </row>
-    <row r="636">
-      <c r="A636" t="inlineStr">
+    <row r="635">
+      <c r="A635" t="inlineStr">
         <is>
           <t xml:space="preserve">「大器晩成」
 الأشياء العظيمة تأخذ وقت
@@ -13813,19 +13792,19 @@
 2109 出典不明 </t>
         </is>
       </c>
-      <c r="B636" t="inlineStr">
+      <c r="B635" t="inlineStr">
         <is>
           <t>images/「大器晩成」_img1.jpg</t>
         </is>
       </c>
-      <c r="C636" t="inlineStr">
+      <c r="C635" t="inlineStr">
         <is>
           <t>ことわざ ,和訳</t>
         </is>
       </c>
     </row>
-    <row r="637">
-      <c r="A637" t="inlineStr">
+    <row r="636">
+      <c r="A636" t="inlineStr">
         <is>
           <t xml:space="preserve">「コーヒーは急には飲まれない」
 القهْوة لا تشرَب عَلى عَجلْ
@@ -13836,19 +13815,19 @@
 2012 Ahmed Madyan </t>
         </is>
       </c>
-      <c r="B637" t="inlineStr">
+      <c r="B636" t="inlineStr">
         <is>
           <t>images/「コーヒーは急には飲まれない」_img1.jpg</t>
         </is>
       </c>
-      <c r="C637" t="inlineStr">
+      <c r="C636" t="inlineStr">
         <is>
           <t>名言</t>
         </is>
       </c>
     </row>
-    <row r="638">
-      <c r="A638" t="inlineStr">
+    <row r="637">
+      <c r="A637" t="inlineStr">
         <is>
           <t xml:space="preserve">「成功者は情報共有している」
 الناجحون يشاركون المعلومة
@@ -13858,19 +13837,19 @@
 2109 出典不明 </t>
         </is>
       </c>
-      <c r="B638" t="inlineStr">
+      <c r="B637" t="inlineStr">
         <is>
           <t>images/「成功者は情報共有している」_img1.jpg</t>
         </is>
       </c>
-      <c r="C638" t="inlineStr">
+      <c r="C637" t="inlineStr">
         <is>
           <t>鳥 ,シェア</t>
         </is>
       </c>
     </row>
-    <row r="639">
-      <c r="A639" t="inlineStr">
+    <row r="638">
+      <c r="A638" t="inlineStr">
         <is>
           <t xml:space="preserve">「間違いで賢くなる、痛みで強くなる」
 الأخطاء تجعلك حكيمًا، والألم يجعلك قويًا
@@ -13879,19 +13858,19 @@
 2111 https://alaminin.blogspot.com/2020/03/blog-post_6.html </t>
         </is>
       </c>
-      <c r="B639" t="inlineStr">
+      <c r="B638" t="inlineStr">
         <is>
           <t>images/「間違いで賢くなる、痛みで強くなる」_img1.jpg</t>
         </is>
       </c>
-      <c r="C639" t="inlineStr">
+      <c r="C638" t="inlineStr">
         <is>
           <t>名言</t>
         </is>
       </c>
     </row>
-    <row r="640">
-      <c r="A640" t="inlineStr">
+    <row r="639">
+      <c r="A639" t="inlineStr">
         <is>
           <t xml:space="preserve">「何事も永遠には続かない」
 لا شيء يبقى للأبد
@@ -13901,19 +13880,19 @@
 2308 KiTeLetZ </t>
         </is>
       </c>
-      <c r="B640" t="inlineStr">
+      <c r="B639" t="inlineStr">
         <is>
           <t>images/「何事も永遠には続かない」_img1.jpg</t>
         </is>
       </c>
-      <c r="C640" t="inlineStr">
+      <c r="C639" t="inlineStr">
         <is>
           <t>変化 ,名言</t>
         </is>
       </c>
     </row>
-    <row r="641">
-      <c r="A641" t="inlineStr">
+    <row r="640">
+      <c r="A640" t="inlineStr">
         <is>
           <t xml:space="preserve">「惑星地球はあなた方を歓迎します」
 كوكب الارض يرحّب بكم
@@ -13923,19 +13902,19 @@
 1811 iN49R </t>
         </is>
       </c>
-      <c r="B641" t="inlineStr">
+      <c r="B640" t="inlineStr">
         <is>
           <t>images/「惑星地球はあなた方を歓迎します」_img1.jpg</t>
         </is>
       </c>
-      <c r="C641" t="inlineStr">
+      <c r="C640" t="inlineStr">
         <is>
           <t>宇宙 ,人類</t>
         </is>
       </c>
     </row>
-    <row r="642">
-      <c r="A642" t="inlineStr">
+    <row r="641">
+      <c r="A641" t="inlineStr">
         <is>
           <t xml:space="preserve">「自分を信じなさい。人の言うことは尽きないのだから」
 ثق بنفسك فكلام الناس لا ينتهي
@@ -13944,19 +13923,19 @@
 2105 出典不明 </t>
         </is>
       </c>
-      <c r="B642" t="inlineStr">
+      <c r="B641" t="inlineStr">
         <is>
           <t>images/「自分を信じなさい。人の言うことは尽き_img1.jpg</t>
         </is>
       </c>
-      <c r="C642" t="inlineStr">
+      <c r="C641" t="inlineStr">
         <is>
           <t>自信 ,無視</t>
         </is>
       </c>
     </row>
-    <row r="643">
-      <c r="A643" t="inlineStr">
+    <row r="642">
+      <c r="A642" t="inlineStr">
         <is>
           <t xml:space="preserve">「弟が歩くぞ」أخي الصغير يمشي
 アキ_ッサギール・ヤムシー ['aKh-i ^_saGhiiru ya-mShii]
@@ -13965,19 +13944,19 @@
 2308 gulfkids com http://www.gulfkids.com/ar/book48-1909.htm </t>
         </is>
       </c>
-      <c r="B643" t="inlineStr">
+      <c r="B642" t="inlineStr">
         <is>
           <t>images/「弟が歩くぞ」_img1.jpg</t>
         </is>
       </c>
-      <c r="C643" t="inlineStr">
+      <c r="C642" t="inlineStr">
         <is>
           <t>兄弟 ,絵本</t>
         </is>
       </c>
     </row>
-    <row r="644">
-      <c r="A644" t="inlineStr">
+    <row r="643">
+      <c r="A643" t="inlineStr">
         <is>
           <t xml:space="preserve">花より団子おおお（違う）
 「誰もふさわしくない」[laa 'aHada ya-staHiqqu]
@@ -13985,19 +13964,19 @@
 2308 https://twitter.com/NatGeoMagArab/status/1370041991317233664 </t>
         </is>
       </c>
-      <c r="B644" t="inlineStr">
+      <c r="B643" t="inlineStr">
         <is>
           <t>images/花より団子おおお（違う）_img1.jpg</t>
         </is>
       </c>
-      <c r="C644" t="inlineStr">
+      <c r="C643" t="inlineStr">
         <is>
           <t>手書き語学 ,アラビア語 ,キノボリカンガルー</t>
         </is>
       </c>
     </row>
-    <row r="645">
-      <c r="A645" t="inlineStr">
+    <row r="644">
+      <c r="A644" t="inlineStr">
         <is>
           <t xml:space="preserve">「幸せな人生には弱い記憶力が必要」
 الحياة السعيدة تتطلب ذاكرة ضعيفة
@@ -14006,19 +13985,19 @@
 2012 出典不明 </t>
         </is>
       </c>
-      <c r="B645" t="inlineStr">
+      <c r="B644" t="inlineStr">
         <is>
           <t>images/「幸せな人生には弱い記憶力が必要」_img1.jpg</t>
         </is>
       </c>
-      <c r="C645" t="inlineStr">
+      <c r="C644" t="inlineStr">
         <is>
           <t>前向き</t>
         </is>
       </c>
     </row>
-    <row r="646">
-      <c r="A646" t="inlineStr">
+    <row r="645">
+      <c r="A645" t="inlineStr">
         <is>
           <t xml:space="preserve">「このパンダは私たちに、幸せは単純なことの中に隠れているのだと教えている」
 دب "الباندا" هذا يؤكد لنا أن السعادة تكمن في أبسط الأشياء
@@ -14026,19 +14005,19 @@
 2308 https://twitter.com/NatGeoMagArab/status/1309938472065486848 </t>
         </is>
       </c>
-      <c r="B646" t="inlineStr">
+      <c r="B645" t="inlineStr">
         <is>
           <t>images/「このパンダは私たちに、幸せは単純なこ.png</t>
         </is>
       </c>
-      <c r="C646" t="inlineStr">
+      <c r="C645" t="inlineStr">
         <is>
           <t>パンダ ,雪</t>
         </is>
       </c>
     </row>
-    <row r="647">
-      <c r="A647" t="inlineStr">
+    <row r="646">
+      <c r="A646" t="inlineStr">
         <is>
           <t xml:space="preserve">「良い時間は速く過ぎる」
 الأوقات الجميلة تمر بسرعة
@@ -14048,19 +14027,19 @@
 1810 Nasser.Tumblr </t>
         </is>
       </c>
-      <c r="B647" t="inlineStr">
+      <c r="B646" t="inlineStr">
         <is>
           <t>images/「良い時間は速く過ぎる」_img1.jpg</t>
         </is>
       </c>
-      <c r="C647" t="inlineStr">
+      <c r="C646" t="inlineStr">
         <is>
           <t>相対論 ,心理学</t>
         </is>
       </c>
     </row>
-    <row r="648">
-      <c r="A648" t="inlineStr">
+    <row r="647">
+      <c r="A647" t="inlineStr">
         <is>
           <t xml:space="preserve">「今日が始まりかもしれない」
 كل يوم ممكن يكون بداية
@@ -14070,19 +14049,19 @@
 2308 Ahmed Madyan </t>
         </is>
       </c>
-      <c r="B648" t="inlineStr">
+      <c r="B647" t="inlineStr">
         <is>
           <t>images/「今日が始まりかもしれない」_img1.jpg</t>
         </is>
       </c>
-      <c r="C648" t="inlineStr">
+      <c r="C647" t="inlineStr">
         <is>
           <t>吉日 ,開始</t>
         </is>
       </c>
     </row>
-    <row r="649">
-      <c r="A649" t="inlineStr">
+    <row r="648">
+      <c r="A648" t="inlineStr">
         <is>
           <t xml:space="preserve">「ヌール、歯医者さんに行く」
 نور تذهب إلى طبيب الأسنان
@@ -14092,19 +14071,19 @@
 2109 RABIE </t>
         </is>
       </c>
-      <c r="B649" t="inlineStr">
+      <c r="B648" t="inlineStr">
         <is>
           <t>images/「ヌール、歯医者さんに行く」_img1.jpg</t>
         </is>
       </c>
-      <c r="C649" t="inlineStr">
+      <c r="C648" t="inlineStr">
         <is>
           <t>絵本 ,歯科</t>
         </is>
       </c>
     </row>
-    <row r="650">
-      <c r="A650" t="inlineStr">
+    <row r="649">
+      <c r="A649" t="inlineStr">
         <is>
           <t xml:space="preserve">「ラヤンはねむれない」
 لَيان لا تَسْتَطيعُ أَنْ تَنام
@@ -14113,19 +14092,19 @@
 2308 出典不明 </t>
         </is>
       </c>
-      <c r="B650" t="inlineStr">
+      <c r="B649" t="inlineStr">
         <is>
           <t>images/「ラヤンはねむれない」_img1.jpg</t>
         </is>
       </c>
-      <c r="C650" t="inlineStr">
+      <c r="C649" t="inlineStr">
         <is>
           <t>絵本 ,不眠症</t>
         </is>
       </c>
     </row>
-    <row r="651">
-      <c r="A651" t="inlineStr">
+    <row r="650">
+      <c r="A650" t="inlineStr">
         <is>
           <t xml:space="preserve">「クネイトラ県、蜂の巣を約60%失う」
 القنيطرة تفقد حوالي 60 % من خلايا نحلها
@@ -14133,19 +14112,19 @@
 2403 nabd com/t/101679025-fb119f </t>
         </is>
       </c>
-      <c r="B651" t="inlineStr">
+      <c r="B650" t="inlineStr">
         <is>
           <t>images/「クネイトラ県、蜂の巣を約60%失う」_img1.jpg</t>
         </is>
       </c>
-      <c r="C651" t="inlineStr">
+      <c r="C650" t="inlineStr">
         <is>
           <t>蜂の巣 ,パーセント</t>
         </is>
       </c>
     </row>
-    <row r="652">
-      <c r="A652" t="inlineStr">
+    <row r="651">
+      <c r="A651" t="inlineStr">
         <is>
           <t xml:space="preserve">「結ばれしター」ة
 ⁦( تاء مربوطة )[taa' marbuu_ta]：ت「ター」( تاء )[taa']・「結ばれている」( مربوط )[marbuu_t]：( ربط )【結】⁩
@@ -14153,19 +14132,19 @@
 2308 出典不明 </t>
         </is>
       </c>
-      <c r="B652" t="inlineStr">
+      <c r="B651" t="inlineStr">
         <is>
           <t>images/「結ばれしター」_img1.jpg</t>
         </is>
       </c>
-      <c r="C652" t="inlineStr">
+      <c r="C651" t="inlineStr">
         <is>
           <t>アラビア文字 ,顔</t>
         </is>
       </c>
     </row>
-    <row r="653">
-      <c r="A653" t="inlineStr">
+    <row r="652">
+      <c r="A652" t="inlineStr">
         <is>
           <t xml:space="preserve">「忙しい」مشغول
 マシュグール [maShGhuul]
@@ -14174,19 +14153,19 @@
 1811 skyshinichi.instagram </t>
         </is>
       </c>
-      <c r="B653" t="inlineStr">
+      <c r="B652" t="inlineStr">
         <is>
           <t>images/「忙しい」_img1.jpg</t>
         </is>
       </c>
-      <c r="C653" t="inlineStr">
+      <c r="C652" t="inlineStr">
         <is>
           <t>スティッチ ,残業</t>
         </is>
       </c>
     </row>
-    <row r="654">
-      <c r="A654" t="inlineStr">
+    <row r="653">
+      <c r="A653" t="inlineStr">
         <is>
           <t xml:space="preserve">「駐車禁止」ممنوع الوقوف
 マムヌーア・アルウクーフ [mamnuu* al-wuquuf]
@@ -14195,19 +14174,19 @@
 2106 出典不明 </t>
         </is>
       </c>
-      <c r="B654" t="inlineStr">
+      <c r="B653" t="inlineStr">
         <is>
           <t>images/「駐車禁止」_img1.jpg</t>
         </is>
       </c>
-      <c r="C654" t="inlineStr">
+      <c r="C653" t="inlineStr">
         <is>
           <t>標識 ,ジョーク</t>
         </is>
       </c>
     </row>
-    <row r="655">
-      <c r="A655" t="inlineStr">
+    <row r="654">
+      <c r="A654" t="inlineStr">
         <is>
           <t xml:space="preserve">「一人ひとりが責任を」
 كُلنا مسؤول
@@ -14217,19 +14196,19 @@
 2308 covid19awareness sa </t>
         </is>
       </c>
-      <c r="B655" t="inlineStr">
+      <c r="B654" t="inlineStr">
         <is>
           <t>images/「一人ひとりが責任を」_img1.jpg</t>
         </is>
       </c>
-      <c r="C655" t="inlineStr">
+      <c r="C654" t="inlineStr">
         <is>
           <t>Covid ,感染拡大防止</t>
         </is>
       </c>
     </row>
-    <row r="656">
-      <c r="A656" t="inlineStr">
+    <row r="655">
+      <c r="A655" t="inlineStr">
         <is>
           <t xml:space="preserve">「おめでとうございます」مبروك
 マブルーク [mabruuk]
@@ -14238,19 +14217,19 @@
 2308 </t>
         </is>
       </c>
-      <c r="B656" t="inlineStr">
+      <c r="B655" t="inlineStr">
         <is>
           <t>images/「おめでとうございます」_img1.jpg</t>
         </is>
       </c>
-      <c r="C656" t="inlineStr">
+      <c r="C655" t="inlineStr">
         <is>
           <t>詐欺 ,広告</t>
         </is>
       </c>
     </row>
-    <row r="657">
-      <c r="A657" t="inlineStr">
+    <row r="656">
+      <c r="A656" t="inlineStr">
         <is>
           <t xml:space="preserve">「手書きフォント」
 خط مكتوب باليد
@@ -14260,19 +14239,19 @@
 1809 FahdAlFraikh Behance </t>
         </is>
       </c>
-      <c r="B657" t="inlineStr">
+      <c r="B656" t="inlineStr">
         <is>
           <t>images/「手書きフォント」_img1.jpg</t>
         </is>
       </c>
-      <c r="C657" t="inlineStr">
+      <c r="C656" t="inlineStr">
         <is>
           <t>可愛いフォント ,筆跡</t>
         </is>
       </c>
     </row>
-    <row r="658">
-      <c r="A658" t="inlineStr">
+    <row r="657">
+      <c r="A657" t="inlineStr">
         <is>
           <t xml:space="preserve">「開かれたターと結ばれたター」
 التاء المفتوحة والمربوطة
@@ -14282,19 +14261,19 @@
 2109 slideshare.net </t>
         </is>
       </c>
-      <c r="B658" t="inlineStr">
+      <c r="B657" t="inlineStr">
         <is>
           <t>images/「開かれたターと結ばれたター」_img1.jpg</t>
         </is>
       </c>
-      <c r="C658" t="inlineStr">
+      <c r="C657" t="inlineStr">
         <is>
           <t>アラビア文字 ,スマイリー</t>
         </is>
       </c>
     </row>
-    <row r="659">
-      <c r="A659" t="inlineStr">
+    <row r="658">
+      <c r="A658" t="inlineStr">
         <is>
           <t xml:space="preserve">「このラマは誇らしげにして立っている」
 تقف هذه اللاما مزهوة بنفسها
@@ -14302,19 +14281,19 @@
 2410 https://twitter.com/NatGeoMagArab/status/1597485552965935104 </t>
         </is>
       </c>
-      <c r="B659" t="inlineStr">
+      <c r="B658" t="inlineStr">
         <is>
           <t>images/「このラマは誇らしげにして立っている」_img1.jpg</t>
         </is>
       </c>
-      <c r="C659" t="inlineStr">
+      <c r="C658" t="inlineStr">
         <is>
           <t>手書き語学 ,アラビア語 ,マチュピチュ遺跡</t>
         </is>
       </c>
     </row>
-    <row r="660">
-      <c r="A660" t="inlineStr">
+    <row r="659">
+      <c r="A659" t="inlineStr">
         <is>
           <t xml:space="preserve">「小さな生き物にしては危険な名前だ」
 اسم خطير لمخلوق صغير
@@ -14323,19 +14302,19 @@
 2308 https://twitter.com/NatGeoMagArab/status/1495035772071669760 </t>
         </is>
       </c>
-      <c r="B660" t="inlineStr">
+      <c r="B659" t="inlineStr">
         <is>
           <t>images/「小さな生き物にしては危険な名前だ」_img1.jpg</t>
         </is>
       </c>
-      <c r="C660" t="inlineStr">
+      <c r="C659" t="inlineStr">
         <is>
           <t>有袋類 ,タスマニアデビル</t>
         </is>
       </c>
     </row>
-    <row r="661">
-      <c r="A661" t="inlineStr">
+    <row r="660">
+      <c r="A660" t="inlineStr">
         <is>
           <t xml:space="preserve">「こわれている」مكسر
 ムカッサル [mukassar]
@@ -14343,19 +14322,19 @@
 2105 behance Written-Visuals </t>
         </is>
       </c>
-      <c r="B661" t="inlineStr">
+      <c r="B660" t="inlineStr">
         <is>
           <t>images/「こわれている」_img1.jpg</t>
         </is>
       </c>
-      <c r="C661" t="inlineStr">
+      <c r="C660" t="inlineStr">
         <is>
           <t>バラバラ ,デザイン</t>
         </is>
       </c>
     </row>
-    <row r="662">
-      <c r="A662" t="inlineStr">
+    <row r="661">
+      <c r="A661" t="inlineStr">
         <is>
           <t xml:space="preserve">「早起きする方法」
 كيف تنهض مُبكّرًا
@@ -14365,19 +14344,19 @@
 2308 Funders and Founders </t>
         </is>
       </c>
-      <c r="B662" t="inlineStr">
+      <c r="B661" t="inlineStr">
         <is>
           <t>images/「早起きする方法」_img1.jpg</t>
         </is>
       </c>
-      <c r="C662" t="inlineStr">
+      <c r="C661" t="inlineStr">
         <is>
           <t>オフトゥン ,寝起き</t>
         </is>
       </c>
     </row>
-    <row r="663">
-      <c r="A663" t="inlineStr">
+    <row r="662">
+      <c r="A662" t="inlineStr">
         <is>
           <t xml:space="preserve">「アラブ・デザイン文字展覧会」
 معرض لتخطيط الحرف العربي
@@ -14387,19 +14366,19 @@
 2109 arabic lettering exhibition </t>
         </is>
       </c>
-      <c r="B663" t="inlineStr">
+      <c r="B662" t="inlineStr">
         <is>
           <t>images/「アラブ・デザイン文字展覧会」_img1.jpg</t>
         </is>
       </c>
-      <c r="C663" t="inlineStr">
+      <c r="C662" t="inlineStr">
         <is>
           <t>ポスター</t>
         </is>
       </c>
     </row>
-    <row r="664">
-      <c r="A664" t="inlineStr">
+    <row r="663">
+      <c r="A663" t="inlineStr">
         <is>
           <t xml:space="preserve">「名探偵コナン」المحقق كونان
 アルムハッキク・コナン [al-muHaqqiq Conan]
@@ -14408,19 +14387,19 @@
 1809 wikipedia </t>
         </is>
       </c>
-      <c r="B664" t="inlineStr">
+      <c r="B663" t="inlineStr">
         <is>
           <t>images/「名探偵コナン」_img1.jpg</t>
         </is>
       </c>
-      <c r="C664" t="inlineStr">
+      <c r="C663" t="inlineStr">
         <is>
           <t>江戸川コナン ,ロゴ</t>
         </is>
       </c>
     </row>
-    <row r="665">
-      <c r="A665" t="inlineStr">
+    <row r="664">
+      <c r="A664" t="inlineStr">
         <is>
           <t xml:space="preserve">「イードおめでとう」عيد مبارك
 イード・ムバーラク [*iid mubaarak]
@@ -14428,19 +14407,19 @@
 2308 出典不明 </t>
         </is>
       </c>
-      <c r="B665" t="inlineStr">
+      <c r="B664" t="inlineStr">
         <is>
           <t>images/「イードおめでとう」_img1.jpg</t>
         </is>
       </c>
-      <c r="C665" t="inlineStr">
+      <c r="C664" t="inlineStr">
         <is>
           <t>عيد ,アラビア語</t>
         </is>
       </c>
     </row>
-    <row r="666">
-      <c r="A666" t="inlineStr">
+    <row r="665">
+      <c r="A665" t="inlineStr">
         <is>
           <t xml:space="preserve">「戦士」محارب
 ムハーリブ [muHaarib]
@@ -14449,19 +14428,19 @@
 1809 abudinges.tumblr </t>
         </is>
       </c>
-      <c r="B666" t="inlineStr">
+      <c r="B665" t="inlineStr">
         <is>
           <t>images/「戦士」_img1.jpg</t>
         </is>
       </c>
-      <c r="C666" t="inlineStr">
+      <c r="C665" t="inlineStr">
         <is>
           <t>ロゴ ,赤</t>
         </is>
       </c>
     </row>
-    <row r="667">
-      <c r="A667" t="inlineStr">
+    <row r="666">
+      <c r="A666" t="inlineStr">
         <is>
           <t xml:space="preserve">「ライブ」بث مباشر
 バッス・ムバーシル [ba^Th(un) mubaaShir(un)]
@@ -14470,19 +14449,19 @@
 2308 beIN SPORTS </t>
         </is>
       </c>
-      <c r="B667" t="inlineStr">
+      <c r="B666" t="inlineStr">
         <is>
           <t>images/「ライブ」_img1.jpg</t>
         </is>
       </c>
-      <c r="C667" t="inlineStr">
+      <c r="C666" t="inlineStr">
         <is>
           <t xml:space="preserve">生放送 ,試合 </t>
         </is>
       </c>
     </row>
-    <row r="668">
-      <c r="A668" t="inlineStr">
+    <row r="667">
+      <c r="A667" t="inlineStr">
         <is>
           <t xml:space="preserve">「信者」مُؤْمِنٌ
 ムッミン [mu'min(un)]
@@ -14491,19 +14470,19 @@
 2106 出典不明 </t>
         </is>
       </c>
-      <c r="B668" t="inlineStr">
+      <c r="B667" t="inlineStr">
         <is>
           <t>images/「信者」_img1.jpg</t>
         </is>
       </c>
-      <c r="C668" t="inlineStr">
+      <c r="C667" t="inlineStr">
         <is>
           <t>明暗 ,信仰</t>
         </is>
       </c>
     </row>
-    <row r="669">
-      <c r="A669" t="inlineStr">
+    <row r="668">
+      <c r="A668" t="inlineStr">
         <is>
           <t xml:space="preserve">「開⇔閉」
 مفتوح
@@ -14514,19 +14493,19 @@
 2312 Hussein Safina, behance </t>
         </is>
       </c>
-      <c r="B669" t="inlineStr">
+      <c r="B668" t="inlineStr">
         <is>
           <t>images/「開⇔閉」_img1.jpg</t>
         </is>
       </c>
-      <c r="C669" t="inlineStr">
+      <c r="C668" t="inlineStr">
         <is>
           <t>オープンマインド ,トグル</t>
         </is>
       </c>
     </row>
-    <row r="670">
-      <c r="A670" t="inlineStr">
+    <row r="669">
+      <c r="A669" t="inlineStr">
         <is>
           <t xml:space="preserve">「予想外な結末！」
 نهاية غير متوقعة
@@ -14534,19 +14513,19 @@
 2308 https://twitter.com/NatGeoMagArab/status/1159011433444593665 </t>
         </is>
       </c>
-      <c r="B670" t="inlineStr">
+      <c r="B669" t="inlineStr">
         <is>
           <t>images/「予想外な結末！」_img1.jpg</t>
         </is>
       </c>
-      <c r="C670" t="inlineStr">
+      <c r="C669" t="inlineStr">
         <is>
           <t>手書き語学 ,アラビア語 ,ウサギ</t>
         </is>
       </c>
     </row>
-    <row r="671">
-      <c r="A671" t="inlineStr">
+    <row r="670">
+      <c r="A670" t="inlineStr">
         <is>
           <t xml:space="preserve">「ベイルート・アニメイテッド」
 بیروت متحرّکة
@@ -14556,19 +14535,19 @@
 2308 arabic_script Instagram </t>
         </is>
       </c>
-      <c r="B671" t="inlineStr">
+      <c r="B670" t="inlineStr">
         <is>
           <t>images/「ベイルート・アニメイテッド」_img1.jpg</t>
         </is>
       </c>
-      <c r="C671" t="inlineStr">
+      <c r="C670" t="inlineStr">
         <is>
           <t>アニメ ,レバノン</t>
         </is>
       </c>
     </row>
-    <row r="672">
-      <c r="A672" t="inlineStr">
+    <row r="671">
+      <c r="A671" t="inlineStr">
         <is>
           <t xml:space="preserve">「夢みれば叶う」
 كُلُّ مُتَوَقَّعٍ آتٍ
@@ -14578,19 +14557,19 @@
 2108 Ahmed Madyan </t>
         </is>
       </c>
-      <c r="B672" t="inlineStr">
+      <c r="B671" t="inlineStr">
         <is>
           <t>images/「夢みれば叶う」_img1.jpg</t>
         </is>
       </c>
-      <c r="C672" t="inlineStr">
+      <c r="C671" t="inlineStr">
         <is>
           <t>希望 ,ドリカム</t>
         </is>
       </c>
     </row>
-    <row r="673">
-      <c r="A673" t="inlineStr">
+    <row r="672">
+      <c r="A672" t="inlineStr">
         <is>
           <t xml:space="preserve">「もし両者が人間のように鎧で武装して戦いに突入したら」
 لو خاضا معاركهما متسلحين بالدروع على غرار البش
@@ -14598,19 +14577,19 @@
 2404 https://x.com/NatGeoMagArab/status/1759284149456945464 </t>
         </is>
       </c>
-      <c r="B673" t="inlineStr">
+      <c r="B672" t="inlineStr">
         <is>
           <t>images/「もし両者が人間のように鎧で武装して戦_img1.jpg,images/「もし両者が人間のように鎧で武装して戦_img2.jpg</t>
         </is>
       </c>
-      <c r="C673" t="inlineStr">
+      <c r="C672" t="inlineStr">
         <is>
           <t>手書き語学 ,アラビア語 ,猫</t>
         </is>
       </c>
     </row>
-    <row r="674">
-      <c r="A674" t="inlineStr">
+    <row r="673">
+      <c r="A673" t="inlineStr">
         <is>
           <t xml:space="preserve">「全ては結びついている」
 كل شيء مترابط
@@ -14620,19 +14599,19 @@
 2308 Ahmed Madyan https://twitter.com/madyco22/status/1451990828298166273 </t>
         </is>
       </c>
-      <c r="B674" t="inlineStr">
+      <c r="B673" t="inlineStr">
         <is>
           <t>images/「全ては結びついている」_img1.jpg</t>
         </is>
       </c>
-      <c r="C674" t="inlineStr">
+      <c r="C673" t="inlineStr">
         <is>
           <t>一筆書き ,デザイン</t>
         </is>
       </c>
     </row>
-    <row r="675">
-      <c r="A675" t="inlineStr">
+    <row r="674">
+      <c r="A674" t="inlineStr">
         <is>
           <t xml:space="preserve">「初心者のためのスケッチトレーニング」
 تعليم الرسم للمبتدئين
@@ -14642,19 +14621,19 @@
 2308 free-bookspdf com </t>
         </is>
       </c>
-      <c r="B675" t="inlineStr">
+      <c r="B674" t="inlineStr">
         <is>
           <t>images/「初心者のためのスケッチトレーニング」_img1.jpg</t>
         </is>
       </c>
-      <c r="C675" t="inlineStr">
+      <c r="C674" t="inlineStr">
         <is>
           <t>イラスト ,絵</t>
         </is>
       </c>
     </row>
-    <row r="676">
-      <c r="A676" t="inlineStr">
+    <row r="675">
+      <c r="A675" t="inlineStr">
         <is>
           <t xml:space="preserve">「初心者のためのスルス体書道トレーニング」
 تعليم خط الثلث للمبتدئين
@@ -14664,19 +14643,19 @@
 2308 出典不明 </t>
         </is>
       </c>
-      <c r="B676" t="inlineStr">
+      <c r="B675" t="inlineStr">
         <is>
           <t>images/「初心者のためのスルス体書道トレーニン_img1.jpg</t>
         </is>
       </c>
-      <c r="C676" t="inlineStr">
+      <c r="C675" t="inlineStr">
         <is>
           <t>書道</t>
         </is>
       </c>
     </row>
-    <row r="677">
-      <c r="A677" t="inlineStr">
+    <row r="676">
+      <c r="A676" t="inlineStr">
         <is>
           <t xml:space="preserve">「笑顔でいなさい」خليك مبتسم
 カッリーク・ムブタスィム [Khallii-k mubtasim]
@@ -14685,19 +14664,19 @@
 2308 https://tmblr.co/Zj9tguYLXBvC </t>
         </is>
       </c>
-      <c r="B677" t="inlineStr">
+      <c r="B676" t="inlineStr">
         <is>
           <t>images/「笑顔でいなさい」_img1.jpg</t>
         </is>
       </c>
-      <c r="C677" t="inlineStr">
+      <c r="C676" t="inlineStr">
         <is>
           <t>スマイル ,名言</t>
         </is>
       </c>
     </row>
-    <row r="678">
-      <c r="A678" t="inlineStr">
+    <row r="677">
+      <c r="A677" t="inlineStr">
         <is>
           <t xml:space="preserve">自動車メーカー
 ⁦・「TOYOTA」( تويوتا )⁩
@@ -14709,19 +14688,19 @@
 2308 syarah com </t>
         </is>
       </c>
-      <c r="B678" t="inlineStr">
+      <c r="B677" t="inlineStr">
         <is>
           <t>images/自動車メーカー_img1.jpg,images/自動車メーカー_img2.jpg,images/自動車メーカー_img3.jpg,images/自動車メーカー_img4.jpg</t>
         </is>
       </c>
-      <c r="C678" t="inlineStr">
+      <c r="C677" t="inlineStr">
         <is>
           <t>日本車 ,韓国車</t>
         </is>
       </c>
     </row>
-    <row r="679">
-      <c r="A679" t="inlineStr">
+    <row r="678">
+      <c r="A678" t="inlineStr">
         <is>
           <t xml:space="preserve">「僕たちは協力して不可能を達成するよ」
 بالتعاون نحقق المحال
@@ -14731,19 +14710,19 @@
 2109 </t>
         </is>
       </c>
-      <c r="B679" t="inlineStr">
+      <c r="B678" t="inlineStr">
         <is>
           <t>images/「僕たちは協力して不可能を達成するよ」_img1.jpg</t>
         </is>
       </c>
-      <c r="C679" t="inlineStr">
+      <c r="C678" t="inlineStr">
         <is>
           <t>無理 ,ハム太郎</t>
         </is>
       </c>
     </row>
-    <row r="680">
-      <c r="A680" t="inlineStr">
+    <row r="679">
+      <c r="A679" t="inlineStr">
         <is>
           <t xml:space="preserve">「幸せは伝染性。喜びを広めよう」
 السعادة معدية فأشع الفرح
@@ -14753,19 +14732,19 @@
 2511 instagram　com/p/fVEfxEo7Va/ </t>
         </is>
       </c>
-      <c r="B680" t="inlineStr">
+      <c r="B679" t="inlineStr">
         <is>
           <t>images/「幸せは伝染性。喜びを広めよう」_img1.jpg</t>
         </is>
       </c>
-      <c r="C680" t="inlineStr">
+      <c r="C679" t="inlineStr">
         <is>
           <t>拡散希望</t>
         </is>
       </c>
     </row>
-    <row r="681">
-      <c r="A681" t="inlineStr">
+    <row r="680">
+      <c r="A680" t="inlineStr">
         <is>
           <t xml:space="preserve">「ストレスは人間だけのものではない」
 الشعور بالتوتر ليس حكرًا على البشر
@@ -14773,19 +14752,19 @@
 2408 https://x.com/NatGeoMagArab/status/1736755816911487420 </t>
         </is>
       </c>
-      <c r="B681" t="inlineStr">
+      <c r="B680" t="inlineStr">
         <is>
           <t>images/「ストレスは人間だけのものではない」_img1.jpg</t>
         </is>
       </c>
-      <c r="C681" t="inlineStr">
+      <c r="C680" t="inlineStr">
         <is>
           <t>手書き語学 ,アラビア語 ,ストレス</t>
         </is>
       </c>
     </row>
-    <row r="682">
-      <c r="A682" t="inlineStr">
+    <row r="681">
+      <c r="A681" t="inlineStr">
         <is>
           <t xml:space="preserve">「私達は出来ます！」
 نستطيع فعلها
@@ -14795,19 +14774,19 @@
 2308 NAHARBAHIJ com </t>
         </is>
       </c>
-      <c r="B682" t="inlineStr">
+      <c r="B681" t="inlineStr">
         <is>
           <t>images/「私達は出来ます！」_img1.jpg</t>
         </is>
       </c>
-      <c r="C682" t="inlineStr">
+      <c r="C681" t="inlineStr">
         <is>
           <t>女性 ,パロディ</t>
         </is>
       </c>
     </row>
-    <row r="683">
-      <c r="A683" t="inlineStr">
+    <row r="682">
+      <c r="A682" t="inlineStr">
         <is>
           <t xml:space="preserve">「全然分からん」ولا فاهم إشي
 ウラー・ファーヒム・イシ [w-laa faahim 'iShy]
@@ -14817,19 +14796,19 @@
 2209 出典不明 </t>
         </is>
       </c>
-      <c r="B683" t="inlineStr">
+      <c r="B682" t="inlineStr">
         <is>
           <t>images/「全然分からん」_img1.jpg</t>
         </is>
       </c>
-      <c r="C683" t="inlineStr">
+      <c r="C682" t="inlineStr">
         <is>
           <t>アラビア語</t>
         </is>
       </c>
     </row>
-    <row r="684">
-      <c r="A684" t="inlineStr">
+    <row r="683">
+      <c r="A683" t="inlineStr">
         <is>
           <t xml:space="preserve">「人間は一人ひとり、特別な才がある。だから自分を他人と比べるのはやめよう」
 لكل إنسان مواهبه الخاصة 
@@ -14838,19 +14817,19 @@
 1812 Gwid3 </t>
         </is>
       </c>
-      <c r="B684" t="inlineStr">
+      <c r="B683" t="inlineStr">
         <is>
           <t>images/「人間は一人ひとり、特別な才がある。だ_img1.jpg</t>
         </is>
       </c>
-      <c r="C684" t="inlineStr">
+      <c r="C683" t="inlineStr">
         <is>
           <t>自尊 ,プライド</t>
         </is>
       </c>
     </row>
-    <row r="685">
-      <c r="A685" t="inlineStr">
+    <row r="684">
+      <c r="A684" t="inlineStr">
         <is>
           <t xml:space="preserve">「この猫は食事をシェアするのが嫌い！」
 هذه القطة لا تحب مشاركة الطعام
@@ -14859,19 +14838,19 @@
 2605 facebook com/alahram/videos/2154923608133231/ </t>
         </is>
       </c>
-      <c r="B685" t="inlineStr">
+      <c r="B684" t="inlineStr">
         <is>
           <t>images/「この猫は食事をシェアするのが嫌い！」_img1.jpg</t>
         </is>
       </c>
-      <c r="C685" t="inlineStr">
+      <c r="C684" t="inlineStr">
         <is>
           <t>猫 ,ネコ</t>
         </is>
       </c>
     </row>
-    <row r="686">
-      <c r="A686" t="inlineStr">
+    <row r="685">
+      <c r="A685" t="inlineStr">
         <is>
           <t xml:space="preserve">「怪獣との戦いでは自分が怪獣化せぬよう警戒しなさい」
 احذر عند محاربة الوحوش ألا تصبح واحدا منهم
@@ -14881,19 +14860,19 @@
 2108 warag-3nb.tumblr </t>
         </is>
       </c>
-      <c r="B686" t="inlineStr">
+      <c r="B685" t="inlineStr">
         <is>
           <t>images/「怪獣との戦いでは自分が怪獣化せぬよう_img1.jpg,images/ 「怪獣との戦いでは自分が怪獣化せぬよう_img2.jpg</t>
         </is>
       </c>
-      <c r="C686" t="inlineStr">
+      <c r="C685" t="inlineStr">
         <is>
           <t>正気 ,モンスター</t>
         </is>
       </c>
     </row>
-    <row r="687">
-      <c r="A687" t="inlineStr">
+    <row r="686">
+      <c r="A686" t="inlineStr">
         <is>
           <t xml:space="preserve">「錯視アート」فن الخداع البصري
 ファンヌ_ルヒダーイ_ルバサリーイ [fannu l-Khidaa*i l-ba_sariyy]
@@ -14902,19 +14881,19 @@
 2409 https://online.pubhtml5.com/idtb/neft/ </t>
         </is>
       </c>
-      <c r="B687" t="inlineStr">
+      <c r="B686" t="inlineStr">
         <is>
           <t>images/「錯視アート」_img1.jpg</t>
         </is>
       </c>
-      <c r="C687" t="inlineStr">
+      <c r="C686" t="inlineStr">
         <is>
           <t>トリックアート</t>
         </is>
       </c>
     </row>
-    <row r="688">
-      <c r="A688" t="inlineStr">
+    <row r="687">
+      <c r="A687" t="inlineStr">
         <is>
           <t xml:space="preserve">「自然界の消防士の訓練」
 تدريبات رجال الإطفاء في الطبيعة
@@ -14922,19 +14901,19 @@
 2308 https://twitter.com/NatGeoMagArab/status/1462420543890608129 </t>
         </is>
       </c>
-      <c r="B688" t="inlineStr">
+      <c r="B687" t="inlineStr">
         <is>
           <t>images/「自然界の消防士の訓練」_img1.jpg,images/ 「自然界の消防士の訓練」_img2.jpg</t>
         </is>
       </c>
-      <c r="C688" t="inlineStr">
+      <c r="C687" t="inlineStr">
         <is>
           <t>手書き語学 ,アラビア語 ,ヒグマ</t>
         </is>
       </c>
     </row>
-    <row r="689">
-      <c r="A689" t="inlineStr">
+    <row r="688">
+      <c r="A688" t="inlineStr">
         <is>
           <t xml:space="preserve">「救助」إسعاف
 イスアーフ ['is*aaf]
@@ -14943,19 +14922,19 @@
 2109 ambulance gov ae </t>
         </is>
       </c>
-      <c r="B689" t="inlineStr">
+      <c r="B688" t="inlineStr">
         <is>
           <t>images/「救助」_img1.jpg</t>
         </is>
       </c>
-      <c r="C689" t="inlineStr">
+      <c r="C688" t="inlineStr">
         <is>
           <t>救急車 ,はたらくくるま</t>
         </is>
       </c>
     </row>
-    <row r="690">
-      <c r="A690" t="inlineStr">
+    <row r="689">
+      <c r="A689" t="inlineStr">
         <is>
           <t xml:space="preserve">「感情／感覚」الإحْسَاسْ
 アルイヒサース [al-'iHsaas]
@@ -14964,19 +14943,19 @@
 2308 iN49R </t>
         </is>
       </c>
-      <c r="B690" t="inlineStr">
+      <c r="B689" t="inlineStr">
         <is>
           <t>images/「感情／感覚」_img1.jpg</t>
         </is>
       </c>
-      <c r="C690" t="inlineStr">
+      <c r="C689" t="inlineStr">
         <is>
           <t>オフ ,一休み</t>
         </is>
       </c>
     </row>
-    <row r="691">
-      <c r="A691" t="inlineStr">
+    <row r="690">
+      <c r="A690" t="inlineStr">
         <is>
           <t xml:space="preserve">「ひらめき」إلهام
 イルハーム ['lhaam]
@@ -14988,19 +14967,19 @@
 2103 出典不明 </t>
         </is>
       </c>
-      <c r="B691" t="inlineStr">
+      <c r="B690" t="inlineStr">
         <is>
           <t>images/「ひらめき」_img1.jpg</t>
         </is>
       </c>
-      <c r="C691" t="inlineStr">
+      <c r="C690" t="inlineStr">
         <is>
           <t>アラビア語</t>
         </is>
       </c>
     </row>
-    <row r="692">
-      <c r="A692" t="inlineStr">
+    <row r="691">
+      <c r="A691" t="inlineStr">
         <is>
           <t xml:space="preserve">「Ibdaa／クリエイティビティ」
 إبداع
@@ -15009,19 +14988,19 @@
 2308 Ibdaa Design &amp; Decoration Office </t>
         </is>
       </c>
-      <c r="B692" t="inlineStr">
+      <c r="B691" t="inlineStr">
         <is>
           <t>images/「Ibdaa／クリエイティビティ」_img1.jpg</t>
         </is>
       </c>
-      <c r="C692" t="inlineStr">
+      <c r="C691" t="inlineStr">
         <is>
           <t>創造性 ,独自性</t>
         </is>
       </c>
     </row>
-    <row r="693">
-      <c r="A693" t="inlineStr">
+    <row r="692">
+      <c r="A692" t="inlineStr">
         <is>
           <t xml:space="preserve">「奮闘なくして進歩なし」
 بدون كفاح لايوجد تقدم
@@ -15031,19 +15010,19 @@
 2105 ROUYMS TUMBLR COM </t>
         </is>
       </c>
-      <c r="B693" t="inlineStr">
+      <c r="B692" t="inlineStr">
         <is>
           <t>images/「奮闘なくして進歩なし」_img1.jpg</t>
         </is>
       </c>
-      <c r="C693" t="inlineStr">
+      <c r="C692" t="inlineStr">
         <is>
           <t>努力 ,三角形</t>
         </is>
       </c>
     </row>
-    <row r="694">
-      <c r="A694" t="inlineStr">
+    <row r="693">
+      <c r="A693" t="inlineStr">
         <is>
           <t xml:space="preserve">「木に登れば熊の危険を避けられるとお考えなら、考え直しましょう！」 
 إن اعتقدت أنك بمنأى عن خطر الدب عند تسلق الأشجار.. راجع حساباتك
@@ -15051,19 +15030,19 @@
 2202 NatGeoMagArab </t>
         </is>
       </c>
-      <c r="B694" t="inlineStr">
+      <c r="B693" t="inlineStr">
         <is>
           <t>images/「木に登れば熊の危険を避けられるとお考.jpeg</t>
         </is>
       </c>
-      <c r="C694" t="inlineStr">
+      <c r="C693" t="inlineStr">
         <is>
           <t>クマ</t>
         </is>
       </c>
     </row>
-    <row r="695">
-      <c r="A695" t="inlineStr">
+    <row r="694">
+      <c r="A694" t="inlineStr">
         <is>
           <t xml:space="preserve">「卒業おめでとう」مبروك التخرج
 マブルーク・タカッルジ [mabruuk a^taKharruj]
@@ -15072,19 +15051,19 @@
 2308 https://instagram.com/fatoomworld </t>
         </is>
       </c>
-      <c r="B695" t="inlineStr">
+      <c r="B694" t="inlineStr">
         <is>
           <t>images/「卒業おめでとう」_img1.jpg</t>
         </is>
       </c>
-      <c r="C695" t="inlineStr">
+      <c r="C694" t="inlineStr">
         <is>
           <t>卒業 ,イラスト</t>
         </is>
       </c>
     </row>
-    <row r="696">
-      <c r="A696" t="inlineStr">
+    <row r="695">
+      <c r="A695" t="inlineStr">
         <is>
           <t xml:space="preserve">「停止距離の計算」
 حساب مسافة التوقف
@@ -15094,19 +15073,19 @@
 2109 assurance-auto-info </t>
         </is>
       </c>
-      <c r="B696" t="inlineStr">
+      <c r="B695" t="inlineStr">
         <is>
           <t>images/「停止距離の計算」_img1.jpg</t>
         </is>
       </c>
-      <c r="C696" t="inlineStr">
+      <c r="C695" t="inlineStr">
         <is>
           <t>保険 ,自動車</t>
         </is>
       </c>
     </row>
-    <row r="697">
-      <c r="A697" t="inlineStr">
+    <row r="696">
+      <c r="A696" t="inlineStr">
         <is>
           <t xml:space="preserve">「教師要らず：10日でフランス語会話」
 بدون معلم
@@ -15116,19 +15095,19 @@
 2308 englais-best com </t>
         </is>
       </c>
-      <c r="B697" t="inlineStr">
+      <c r="B696" t="inlineStr">
         <is>
           <t>images/「教師要らず：10日でフランス語会話」_img1.jpg</t>
         </is>
       </c>
-      <c r="C697" t="inlineStr">
+      <c r="C696" t="inlineStr">
         <is>
           <t>教師なし学習</t>
         </is>
       </c>
     </row>
-    <row r="698">
-      <c r="A698" t="inlineStr">
+    <row r="697">
+      <c r="A697" t="inlineStr">
         <is>
           <t xml:space="preserve">「衝突」تصادم
 タサードゥム [ta_saadum]
@@ -15137,19 +15116,19 @@
 1810 </t>
         </is>
       </c>
-      <c r="B698" t="inlineStr">
+      <c r="B697" t="inlineStr">
         <is>
           <t>images/「衝突」_img1.jpg</t>
         </is>
       </c>
-      <c r="C698" t="inlineStr">
+      <c r="C697" t="inlineStr">
         <is>
           <t>あらびあや</t>
         </is>
       </c>
     </row>
-    <row r="699">
-      <c r="A699" t="inlineStr">
+    <row r="698">
+      <c r="A698" t="inlineStr">
         <is>
           <t xml:space="preserve">「楽観主義」تَفَاؤُلٌ
 タファーウル [tafaa'ul(un)]
@@ -15158,19 +15137,19 @@
 1904 arabictypography com </t>
         </is>
       </c>
-      <c r="B699" t="inlineStr">
+      <c r="B698" t="inlineStr">
         <is>
           <t>images/「楽観主義」_img1.jpg</t>
         </is>
       </c>
-      <c r="C699" t="inlineStr">
+      <c r="C698" t="inlineStr">
         <is>
           <t>やわらか ,緑</t>
         </is>
       </c>
     </row>
-    <row r="700">
-      <c r="A700" t="inlineStr">
+    <row r="699">
+      <c r="A699" t="inlineStr">
         <is>
           <t xml:space="preserve">「シベリアジャコウジカは、絶滅の危機にあると見なされている」
 يعد "أيل المسك السيبيري" مهددًا بالانقراض
@@ -15178,19 +15157,19 @@
 2308 https://twitter.com/NatGeoMagArab/status/1320666649045790720 </t>
         </is>
       </c>
-      <c r="B700" t="inlineStr">
+      <c r="B699" t="inlineStr">
         <is>
           <t>images/「シベリアジャコウジカは、絶滅の危機に_img1.jpg,images/「シベリアジャコウジカは、絶滅の危機に_img2.jpg</t>
         </is>
       </c>
-      <c r="C700" t="inlineStr">
+      <c r="C699" t="inlineStr">
         <is>
           <t>手書き語学 ,シベリア</t>
         </is>
       </c>
     </row>
-    <row r="701">
-      <c r="A701" t="inlineStr">
+    <row r="700">
+      <c r="A700" t="inlineStr">
         <is>
           <t xml:space="preserve">「融合／折衷／フュージョン」
 انصهار
@@ -15199,38 +15178,38 @@
 1811 elmahdyart Instagram </t>
         </is>
       </c>
-      <c r="B701" t="inlineStr">
+      <c r="B700" t="inlineStr">
         <is>
           <t>images/「融合／折衷／フュージョン」_img1.jpg</t>
         </is>
       </c>
-      <c r="C701" t="inlineStr">
+      <c r="C700" t="inlineStr">
         <is>
           <t>カリグラフィー ,書道</t>
         </is>
       </c>
     </row>
-    <row r="702">
-      <c r="A702" t="inlineStr">
+    <row r="701">
+      <c r="A701" t="inlineStr">
         <is>
           <t xml:space="preserve">「この子供は、昼寝をしようとする母親を邪魔しているようだ」
 「場所はインドのトラ保護区、バンダウガル公園。トラは生態ピラミッドのトップの捕食動物だが、最もリスクの高い絶滅危惧種のひとつである」
 2308 https://twitter.com/natgeomagarab/status/1553681890665586689 </t>
         </is>
       </c>
-      <c r="B702" t="inlineStr">
+      <c r="B701" t="inlineStr">
         <is>
           <t>images/「この子供は、昼寝をしようとする母親を_img1.jpg,images/「この子供は、昼寝をしようとする母親を_img2.jpg</t>
         </is>
       </c>
-      <c r="C702" t="inlineStr">
+      <c r="C701" t="inlineStr">
         <is>
           <t>手書き語学 ,アラビア語 ,トラ</t>
         </is>
       </c>
     </row>
-    <row r="703">
-      <c r="A703" t="inlineStr">
+    <row r="702">
+      <c r="A702" t="inlineStr">
         <is>
           <t xml:space="preserve">「もし敬意が落ちたら、それと一緒に全部落ちるのだ」
 إن سقط الإحترام سقط معه كل شيء
@@ -15239,19 +15218,19 @@
 2109 出典不明 </t>
         </is>
       </c>
-      <c r="B703" t="inlineStr">
+      <c r="B702" t="inlineStr">
         <is>
           <t>images/「もし敬意が落ちたら、それと一緒に全部_img1.jpg</t>
         </is>
       </c>
-      <c r="C703" t="inlineStr">
+      <c r="C702" t="inlineStr">
         <is>
           <t>リスペクト ,落書き</t>
         </is>
       </c>
     </row>
-    <row r="704">
-      <c r="A704" t="inlineStr">
+    <row r="703">
+      <c r="A703" t="inlineStr">
         <is>
           <t xml:space="preserve">「エジプト特許庁」
 مكتب براءات الاختراع المصرى
@@ -15261,19 +15240,19 @@
 2312 </t>
         </is>
       </c>
-      <c r="B704" t="inlineStr">
+      <c r="B703" t="inlineStr">
         <is>
           <t>images/「エジプト特許庁」_img1.jpg</t>
         </is>
       </c>
-      <c r="C704" t="inlineStr">
+      <c r="C703" t="inlineStr">
         <is>
           <t>patent</t>
         </is>
       </c>
     </row>
-    <row r="705">
-      <c r="A705" t="inlineStr">
+    <row r="704">
+      <c r="A704" t="inlineStr">
         <is>
           <t xml:space="preserve">「選挙」إنتخابات
 インティカーバート [intiKhaabaat]
@@ -15282,19 +15261,19 @@
 2311 nna-leb gov lb </t>
         </is>
       </c>
-      <c r="B705" t="inlineStr">
+      <c r="B704" t="inlineStr">
         <is>
           <t>images/「選挙」_img1.jpg</t>
         </is>
       </c>
-      <c r="C705" t="inlineStr">
+      <c r="C704" t="inlineStr">
         <is>
           <t>選挙 ,投票</t>
         </is>
       </c>
     </row>
-    <row r="706">
-      <c r="A706" t="inlineStr">
+    <row r="705">
+      <c r="A705" t="inlineStr">
         <is>
           <t xml:space="preserve">「待ちぼうけ」إنتظار
 インティザール [inti_Dhaar]
@@ -15303,19 +15282,19 @@
 1809 in4sser.tumblr </t>
         </is>
       </c>
-      <c r="B706" t="inlineStr">
+      <c r="B705" t="inlineStr">
         <is>
           <t>images/「待ちぼうけ」_img1.jpg</t>
         </is>
       </c>
-      <c r="C706" t="inlineStr">
+      <c r="C705" t="inlineStr">
         <is>
           <t>遅すぎ ,辛抱</t>
         </is>
       </c>
     </row>
-    <row r="707">
-      <c r="A707" t="inlineStr">
+    <row r="706">
+      <c r="A706" t="inlineStr">
         <is>
           <t xml:space="preserve">「試験」إختبار
 イクティバール [iKhtibaar]
@@ -15324,19 +15303,19 @@
 2109 出典不明 </t>
         </is>
       </c>
-      <c r="B707" t="inlineStr">
+      <c r="B706" t="inlineStr">
         <is>
           <t>images/「試験」_img1.jpg</t>
         </is>
       </c>
-      <c r="C707" t="inlineStr">
+      <c r="C706" t="inlineStr">
         <is>
           <t>テスト ,考査</t>
         </is>
       </c>
     </row>
-    <row r="708">
-      <c r="A708" t="inlineStr">
+    <row r="707">
+      <c r="A707" t="inlineStr">
         <is>
           <t xml:space="preserve">「チャンネル登録」اشتراك
 イシティラーク [iShtiraak]
@@ -15345,19 +15324,19 @@
 2308 </t>
         </is>
       </c>
-      <c r="B708" t="inlineStr">
+      <c r="B707" t="inlineStr">
         <is>
           <t>images/「チャンネル登録」_img1.jpg</t>
         </is>
       </c>
-      <c r="C708" t="inlineStr">
+      <c r="C707" t="inlineStr">
         <is>
           <t>Subscribe ,YouTube</t>
         </is>
       </c>
     </row>
-    <row r="709">
-      <c r="A709" t="inlineStr">
+    <row r="708">
+      <c r="A708" t="inlineStr">
         <is>
           <t xml:space="preserve">「スマイル」ابتسام
 イブティサーム [ibtisaam]
@@ -15365,37 +15344,37 @@
 1903 behance Written-Visuals </t>
         </is>
       </c>
+      <c r="B708" t="inlineStr">
+        <is>
+          <t>images/「スマイル」_img1.jpg</t>
+        </is>
+      </c>
+      <c r="C708" t="inlineStr">
+        <is>
+          <t>スマイリー ,ツ</t>
+        </is>
+      </c>
+    </row>
+    <row r="709">
+      <c r="A709" t="inlineStr">
+        <is>
+          <t xml:space="preserve">「身体の一部として…」
+2308 https://twitter.com/NatGeoMagArab/status/1528292080337813504 </t>
+        </is>
+      </c>
       <c r="B709" t="inlineStr">
         <is>
-          <t>images/「スマイル」_img1.jpg</t>
+          <t>images/「身体の一部として…」_img1.jpg</t>
         </is>
       </c>
       <c r="C709" t="inlineStr">
         <is>
-          <t>スマイリー ,ツ</t>
+          <t>手書き語学 ,カンガルー</t>
         </is>
       </c>
     </row>
     <row r="710">
       <c r="A710" t="inlineStr">
-        <is>
-          <t xml:space="preserve">「身体の一部として…」
-2308 https://twitter.com/NatGeoMagArab/status/1528292080337813504 </t>
-        </is>
-      </c>
-      <c r="B710" t="inlineStr">
-        <is>
-          <t>images/「身体の一部として…」_img1.jpg</t>
-        </is>
-      </c>
-      <c r="C710" t="inlineStr">
-        <is>
-          <t>手書き語学 ,カンガルー</t>
-        </is>
-      </c>
-    </row>
-    <row r="711">
-      <c r="A711" t="inlineStr">
         <is>
           <t xml:space="preserve">「ディスカバリー」إكتشاف
 イクティシャーフ [iktiShaaf]
@@ -15403,19 +15382,19 @@
 2308 tephanegabrielli com </t>
         </is>
       </c>
-      <c r="B711" t="inlineStr">
+      <c r="B710" t="inlineStr">
         <is>
           <t>images/「ディスカバリー」_img1.jpg</t>
         </is>
       </c>
-      <c r="C711" t="inlineStr">
+      <c r="C710" t="inlineStr">
         <is>
           <t>discovery ,デザイン</t>
         </is>
       </c>
     </row>
-    <row r="712">
-      <c r="A712" t="inlineStr">
+    <row r="711">
+      <c r="A711" t="inlineStr">
         <is>
           <t xml:space="preserve">「重力波の発見は新しい窓を開いた」
 فتَح اكتشاف موجات الجاذبية نافذة جديدة
@@ -15423,19 +15402,19 @@
 2308 https://twitter.com/SciTalk2U/status/1454891943440289793 </t>
         </is>
       </c>
-      <c r="B712" t="inlineStr">
+      <c r="B711" t="inlineStr">
         <is>
           <t>images/「重力波の発見は新しい窓を開いた」_img1.jpg</t>
         </is>
       </c>
-      <c r="C712" t="inlineStr">
+      <c r="C711" t="inlineStr">
         <is>
           <t>手書き語学 ,アラビア語 ,重力波</t>
         </is>
       </c>
     </row>
-    <row r="713">
-      <c r="A713" t="inlineStr">
+    <row r="712">
+      <c r="A712" t="inlineStr">
         <is>
           <t xml:space="preserve">「微笑みに微笑み。先にした人の方が美しい」
 الإبتسامة بالإبتسامة والبادئ أجمل
@@ -15444,19 +15423,19 @@
 2104 出典不明 </t>
         </is>
       </c>
-      <c r="B713" t="inlineStr">
+      <c r="B712" t="inlineStr">
         <is>
           <t>images/「微笑みに微笑み。先にした人の方が美し_img1.jpg,images/「微笑みに微笑み。先にした人の方が美し_img2.jpg</t>
         </is>
       </c>
-      <c r="C713" t="inlineStr">
+      <c r="C712" t="inlineStr">
         <is>
           <t>スマイル ,名言</t>
         </is>
       </c>
     </row>
-    <row r="714">
-      <c r="A714" t="inlineStr">
+    <row r="713">
+      <c r="A713" t="inlineStr">
         <is>
           <t xml:space="preserve">「笑顔」ابتسامة
 イブティサーマ [ibtisaama(tun)]
@@ -15465,19 +15444,19 @@
 2308 satokomatsu, minne </t>
         </is>
       </c>
-      <c r="B714" t="inlineStr">
+      <c r="B713" t="inlineStr">
         <is>
           <t>images/「笑顔」_img1.jpg</t>
         </is>
       </c>
-      <c r="C714" t="inlineStr">
+      <c r="C713" t="inlineStr">
         <is>
           <t>スマイル ,ツ</t>
         </is>
       </c>
     </row>
-    <row r="715">
-      <c r="A715" t="inlineStr">
+    <row r="714">
+      <c r="A714" t="inlineStr">
         <is>
           <t xml:space="preserve">「信仰」ايمان
 イーマーン ['iimaan]
@@ -15486,19 +15465,19 @@
 2506 instagram com/p/6ST-WHOOkJ/ </t>
         </is>
       </c>
-      <c r="B715" t="inlineStr">
+      <c r="B714" t="inlineStr">
         <is>
           <t>images/「信仰」_img1.jpg</t>
         </is>
       </c>
-      <c r="C715" t="inlineStr">
+      <c r="C714" t="inlineStr">
         <is>
           <t>宗教 ,信念</t>
         </is>
       </c>
     </row>
-    <row r="716">
-      <c r="A716" t="inlineStr">
+    <row r="715">
+      <c r="A715" t="inlineStr">
         <is>
           <t xml:space="preserve">「放送」إذاعة
 イザーア ['iDhaa*a]
@@ -15507,19 +15486,19 @@
 2404 heemades, Instagram </t>
         </is>
       </c>
-      <c r="B716" t="inlineStr">
+      <c r="B715" t="inlineStr">
         <is>
           <t>images/「放送」_img1.jpg</t>
         </is>
       </c>
-      <c r="C716" t="inlineStr">
+      <c r="C715" t="inlineStr">
         <is>
           <t>デザイン ,ラジオ</t>
         </is>
       </c>
     </row>
-    <row r="717">
-      <c r="A717" t="inlineStr">
+    <row r="716">
+      <c r="A716" t="inlineStr">
         <is>
           <t xml:space="preserve">「かきとりのちから」
 مهاراتي الإملائية
@@ -15528,19 +15507,19 @@
 2308 iqrawaoktoub.wordpress com </t>
         </is>
       </c>
-      <c r="B717" t="inlineStr">
+      <c r="B716" t="inlineStr">
         <is>
           <t>images/「かきとりのちから」_img1.jpg</t>
         </is>
       </c>
-      <c r="C717" t="inlineStr">
+      <c r="C716" t="inlineStr">
         <is>
           <t>国語 ,教材</t>
         </is>
       </c>
     </row>
-    <row r="718">
-      <c r="A718" t="inlineStr">
+    <row r="717">
+      <c r="A717" t="inlineStr">
         <is>
           <t xml:space="preserve">「歴史を作った男たち」
 رجال صنعوا التاريخ
@@ -15550,38 +15529,38 @@
 2410 https://x.gd/Wl5rJ </t>
         </is>
       </c>
-      <c r="B718" t="inlineStr">
+      <c r="B717" t="inlineStr">
         <is>
           <t>images/「歴史を作った男たち」_img1.jpg</t>
         </is>
       </c>
-      <c r="C718" t="inlineStr">
+      <c r="C717" t="inlineStr">
         <is>
           <t>偉人</t>
         </is>
       </c>
     </row>
-    <row r="719">
-      <c r="A719" t="inlineStr">
+    <row r="718">
+      <c r="A718" t="inlineStr">
         <is>
           <t xml:space="preserve">「無限の宇宙を旅した光」
 「何百年もの末にジェイムズ・ウェッブ望遠鏡のレンズの上に落ち、我々に遠い宇宙の美しさを見せてくれる。最も純粋な形と最も素晴らしい姿で」
 2308 https://twitter.com/NatGeoMagArab/status/1557811592636485632 </t>
         </is>
       </c>
-      <c r="B719" t="inlineStr">
+      <c r="B718" t="inlineStr">
         <is>
           <t>images/「無限の宇宙を旅した光」_img1.jpg</t>
         </is>
       </c>
-      <c r="C719" t="inlineStr">
+      <c r="C718" t="inlineStr">
         <is>
           <t>手書き語学 ,宇宙</t>
         </is>
       </c>
     </row>
-    <row r="720">
-      <c r="A720" t="inlineStr">
+    <row r="719">
+      <c r="A719" t="inlineStr">
         <is>
           <t xml:space="preserve">「日本好きになり行きたくなる20項」
 عشرون شيئا يجعلك تحب اليابان وترغب في زيارتها
@@ -15590,19 +15569,19 @@
 2308 wattpad </t>
         </is>
       </c>
-      <c r="B720" t="inlineStr">
+      <c r="B719" t="inlineStr">
         <is>
           <t>images/「日本好きになり行きたくなる20項」_img1.jpg</t>
         </is>
       </c>
-      <c r="C720" t="inlineStr">
+      <c r="C719" t="inlineStr">
         <is>
           <t>اليابان ,Japan</t>
         </is>
       </c>
     </row>
-    <row r="721">
-      <c r="A721" t="inlineStr">
+    <row r="720">
+      <c r="A720" t="inlineStr">
         <is>
           <t xml:space="preserve">「ピッタリの瞬間に撮影され、ドラゴンが火を噴いているように見える」
 التُقطت في اللحظة المناسبة لتبدو مثل تنين ينفث اللهب
@@ -15610,19 +15589,19 @@
 2509 https://twitter.com/NatGeoMagArab/status/1588780660269150208 </t>
         </is>
       </c>
-      <c r="B721" t="inlineStr">
+      <c r="B720" t="inlineStr">
         <is>
           <t>images/「ピッタリの瞬間に撮影され、ドラゴンが_img1.jpg,images/ 「ピッタリの瞬間に撮影され、ドラゴンが_img2.jpg</t>
         </is>
       </c>
-      <c r="C721" t="inlineStr">
+      <c r="C720" t="inlineStr">
         <is>
           <t xml:space="preserve">ドラゴン </t>
         </is>
       </c>
     </row>
-    <row r="722">
-      <c r="A722" t="inlineStr">
+    <row r="721">
+      <c r="A721" t="inlineStr">
         <is>
           <t xml:space="preserve">「満足は不滅の宝である」
 القَناعَةُ كنز لا يَفنَى
@@ -15632,55 +15611,55 @@
 2308 kareem mrghani </t>
         </is>
       </c>
+      <c r="B721" t="inlineStr">
+        <is>
+          <t>images/「満足は不滅の宝である」_img1.jpg</t>
+        </is>
+      </c>
+      <c r="C721" t="inlineStr">
+        <is>
+          <t>幸福度</t>
+        </is>
+      </c>
+    </row>
+    <row r="722">
+      <c r="A722" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ゴシキセイガイインコ。
+2409 https://twitter.com/NatGeoMagArab/status/1600022262014676992 </t>
+        </is>
+      </c>
       <c r="B722" t="inlineStr">
         <is>
-          <t>images/「満足は不滅の宝である」_img1.jpg</t>
+          <t>images/ゴシキセイガイインコ。_img1.jpg</t>
         </is>
       </c>
       <c r="C722" t="inlineStr">
         <is>
-          <t>幸福度</t>
+          <t>手書き語学 ,アラビア語,オウム</t>
         </is>
       </c>
     </row>
     <row r="723">
       <c r="A723" t="inlineStr">
         <is>
-          <t xml:space="preserve">ゴシキセイガイインコ。
-2409 https://twitter.com/NatGeoMagArab/status/1600022262014676992 </t>
+          <t xml:space="preserve">モモンガ。
+2403 https://twitter.com/NatGeoMagArab/status/1552541872966344704 </t>
         </is>
       </c>
       <c r="B723" t="inlineStr">
         <is>
-          <t>images/ゴシキセイガイインコ。_img1.jpg</t>
+          <t>images/モモンガ。_img1.jpg,images/ モモンガ。_img2.jpg</t>
         </is>
       </c>
       <c r="C723" t="inlineStr">
         <is>
-          <t>手書き語学 ,アラビア語,オウム</t>
+          <t>手書き語学 ,アラビア語 ,モモンガ</t>
         </is>
       </c>
     </row>
     <row r="724">
       <c r="A724" t="inlineStr">
-        <is>
-          <t xml:space="preserve">モモンガ。
-2403 https://twitter.com/NatGeoMagArab/status/1552541872966344704 </t>
-        </is>
-      </c>
-      <c r="B724" t="inlineStr">
-        <is>
-          <t>images/モモンガ。_img1.jpg,images/ モモンガ。_img2.jpg</t>
-        </is>
-      </c>
-      <c r="C724" t="inlineStr">
-        <is>
-          <t>手書き語学 ,アラビア語 ,モモンガ</t>
-        </is>
-      </c>
-    </row>
-    <row r="725">
-      <c r="A725" t="inlineStr">
         <is>
           <t xml:space="preserve">「象の群れ。ドローンの音から逃げている」
 قطيع من الفيلة يفر هاربًا من صوت الدرون
@@ -15692,56 +15671,56 @@
 2009 https://twitter.com/NatGeoMagArab/status/1302970033627258881 </t>
         </is>
       </c>
+      <c r="B724" t="inlineStr">
+        <is>
+          <t>images/「象の群れ。ドローンの音から逃げている.jpg</t>
+        </is>
+      </c>
+      <c r="C724" t="inlineStr">
+        <is>
+          <t>ゾウ ,ドローン</t>
+        </is>
+      </c>
+    </row>
+    <row r="725">
+      <c r="A725" t="inlineStr">
+        <is>
+          <t xml:space="preserve">カルマン線。
+2308 https://twitter.com/NatGeoMagArab/status/1536436999522881536 </t>
+        </is>
+      </c>
       <c r="B725" t="inlineStr">
         <is>
-          <t>images/「象の群れ。ドローンの音から逃げている.jpg</t>
+          <t>images/カルマン線。_img1.jpg</t>
         </is>
       </c>
       <c r="C725" t="inlineStr">
         <is>
-          <t>ゾウ ,ドローン</t>
+          <t xml:space="preserve">手書き語学 ,アラビア語 ,宇宙 </t>
         </is>
       </c>
     </row>
     <row r="726">
       <c r="A726" t="inlineStr">
-        <is>
-          <t xml:space="preserve">カルマン線。
-2308 https://twitter.com/NatGeoMagArab/status/1536436999522881536 </t>
-        </is>
-      </c>
-      <c r="B726" t="inlineStr">
-        <is>
-          <t>images/カルマン線。_img1.jpg</t>
-        </is>
-      </c>
-      <c r="C726" t="inlineStr">
-        <is>
-          <t xml:space="preserve">手書き語学 ,アラビア語 ,宇宙 </t>
-        </is>
-      </c>
-    </row>
-    <row r="727">
-      <c r="A727" t="inlineStr">
         <is>
           <t xml:space="preserve">「恥ずかしがり屋のマヌルネコと暖かい朝の太陽光線」
 ⁦「二つの美しいもの」[Shay'-ayni jamiil-ayni] 属格：「物」( شيء )[Shay']・「美しい」( جميل )[jamiil]⁩
 2309 https://twitter.com/NatGeoMagArab/status/1697512148820504912 </t>
         </is>
       </c>
-      <c r="B727" t="inlineStr">
+      <c r="B726" t="inlineStr">
         <is>
           <t>images/「恥ずかしがり屋のマヌルネコと暖かい朝_img1.jpg</t>
         </is>
       </c>
-      <c r="C727" t="inlineStr">
+      <c r="C726" t="inlineStr">
         <is>
           <t>手書き語学 ,アラビア語 ,マヌルネコ</t>
         </is>
       </c>
     </row>
-    <row r="728">
-      <c r="A728" t="inlineStr">
+    <row r="727">
+      <c r="A727" t="inlineStr">
         <is>
           <t xml:space="preserve">「二回失敗しているペンギン」
 بطريق يفشل مرتين
@@ -15751,19 +15730,19 @@
 2308 https://twitter.com/NatGeoMagArab/status/1479483133766426626 </t>
         </is>
       </c>
-      <c r="B728" t="inlineStr">
+      <c r="B727" t="inlineStr">
         <is>
           <t>images/「二回失敗しているペンギン」_img1.jpg</t>
         </is>
       </c>
-      <c r="C728" t="inlineStr">
+      <c r="C727" t="inlineStr">
         <is>
           <t>ペンギン ,動物</t>
         </is>
       </c>
     </row>
-    <row r="729">
-      <c r="A729" t="inlineStr">
+    <row r="728">
+      <c r="A728" t="inlineStr">
         <is>
           <t xml:space="preserve">「2億光年の彼方できらめく炎と光」
 وهج ووميض يتلألأ على بعد 200 مليون سنة ضوئية
@@ -15774,15 +15753,15 @@
 2010 https://twitter.com/NatGeoMagArab/status/1303415502673342464 </t>
         </is>
       </c>
-      <c r="B729" t="inlineStr"/>
-      <c r="C729" t="inlineStr">
+      <c r="B728" t="inlineStr"/>
+      <c r="C728" t="inlineStr">
         <is>
           <t>宇宙 ,銀河</t>
         </is>
       </c>
     </row>
-    <row r="730">
-      <c r="A730" t="inlineStr">
+    <row r="729">
+      <c r="A729" t="inlineStr">
         <is>
           <t xml:space="preserve">「さまよう黒猫」قطة سوداء تجوب
 キッタトゥン・サウダーウ・タジューブ [qi^_tatun sawdaa'u ta-juub]
@@ -15791,19 +15770,19 @@
 2308 https://twitter.com/NatGeoMagArab/status/1532973177453760512 </t>
         </is>
       </c>
-      <c r="B730" t="inlineStr">
+      <c r="B729" t="inlineStr">
         <is>
           <t>images/「さまよう黒猫」_img1.jpg,images/ 「さまよう黒猫」_img2.jpg</t>
         </is>
       </c>
-      <c r="C730" t="inlineStr">
+      <c r="C729" t="inlineStr">
         <is>
           <t xml:space="preserve">手書き語学 ,モロッコ </t>
         </is>
       </c>
     </row>
-    <row r="731">
-      <c r="A731" t="inlineStr">
+    <row r="730">
+      <c r="A730" t="inlineStr">
         <is>
           <t xml:space="preserve">「サイのざらざらした皮を利用して自分の体を掻くネコ」
 قطة تستغل جلد الكركدن الخشن لحك جسدها
@@ -15812,19 +15791,19 @@
 2308 https://twitter.com/NatGeoMagArab/status/1476855740929216517 </t>
         </is>
       </c>
-      <c r="B731" t="inlineStr">
+      <c r="B730" t="inlineStr">
         <is>
           <t>images/「サイのざらざらした皮を利用して自分の_img1.jpg</t>
         </is>
       </c>
-      <c r="C731" t="inlineStr">
+      <c r="C730" t="inlineStr">
         <is>
           <t>サイ ,チェコ</t>
         </is>
       </c>
     </row>
-    <row r="732">
-      <c r="A732" t="inlineStr">
+    <row r="731">
+      <c r="A731" t="inlineStr">
         <is>
           <t xml:space="preserve">「沈まぬ太陽」شمس لا تغيب
 シャムス・ラー・タギーブ [Shams laa ta-Ghiib]
@@ -15833,19 +15812,19 @@
 2308 AHMED ELASSAL </t>
         </is>
       </c>
-      <c r="B732" t="inlineStr">
+      <c r="B731" t="inlineStr">
         <is>
           <t>images/「沈まぬ太陽」_img1.jpg</t>
         </is>
       </c>
-      <c r="C732" t="inlineStr">
+      <c r="C731" t="inlineStr">
         <is>
           <t>帝国 ,白夜</t>
         </is>
       </c>
     </row>
-    <row r="733">
-      <c r="A733" t="inlineStr">
+    <row r="732">
+      <c r="A732" t="inlineStr">
         <is>
           <t xml:space="preserve">「子供に食べさせている忍耐強い母親」
 أم صبورة تطعم صغيرها
@@ -15854,19 +15833,19 @@
 2308 https://twitter.com/natgeomagarab/status/1585572054509957120 </t>
         </is>
       </c>
-      <c r="B733" t="inlineStr">
+      <c r="B732" t="inlineStr">
         <is>
           <t>images/「子供に食べさせている忍耐強い母親」_img1.jpg</t>
         </is>
       </c>
-      <c r="C733" t="inlineStr">
+      <c r="C732" t="inlineStr">
         <is>
           <t>手書き語学 ,アラビア語 ,ミヤコドリ</t>
         </is>
       </c>
     </row>
-    <row r="734">
-      <c r="A734" t="inlineStr">
+    <row r="733">
+      <c r="A733" t="inlineStr">
         <is>
           <t xml:space="preserve">「コーヒーは繰り返さない恋物語」
 القهوة قصة عشق لن تتكرر
@@ -15876,19 +15855,19 @@
 2403 pin it/7tvd8Wc </t>
         </is>
       </c>
-      <c r="B734" t="inlineStr">
+      <c r="B733" t="inlineStr">
         <is>
           <t>images/「コーヒーは繰り返さない恋物語」_img1.jpg</t>
         </is>
       </c>
-      <c r="C734" t="inlineStr">
+      <c r="C733" t="inlineStr">
         <is>
           <t>コーヒー ,名言</t>
         </is>
       </c>
     </row>
-    <row r="735">
-      <c r="A735" t="inlineStr">
+    <row r="734">
+      <c r="A734" t="inlineStr">
         <is>
           <t xml:space="preserve">「星々で飾られた空。魅惑的な色合いで黄昏の美を満たしている」
 سماء مرصعة بالنجوم تضفي لمسة سحرية على جمال الشفق
@@ -15896,19 +15875,19 @@
 2010 https://twitter.com/NatGeoMagArab/status/1303777701975584768 </t>
         </is>
       </c>
-      <c r="B735" t="inlineStr">
+      <c r="B734" t="inlineStr">
         <is>
           <t>images/「星々で飾られた空。魅惑的な色合いで黄.png</t>
         </is>
       </c>
-      <c r="C735" t="inlineStr">
+      <c r="C734" t="inlineStr">
         <is>
           <t>星空 ,宇宙</t>
         </is>
       </c>
     </row>
-    <row r="736">
-      <c r="A736" t="inlineStr">
+    <row r="735">
+      <c r="A735" t="inlineStr">
         <is>
           <t xml:space="preserve">「国際宇宙ステーションからの写真。巨大な台風『ハイシェン（海神）』を映している」
 لقطات من محطة الفضاء الدولية تظهر إعصار "هايشن" الهائل
@@ -15916,19 +15895,19 @@
 2403 https://twitter.com/NatGeoMagArab/status/1302871968522235904 </t>
         </is>
       </c>
-      <c r="B736" t="inlineStr">
+      <c r="B735" t="inlineStr">
         <is>
           <t>images/「国際宇宙ステーションからの写真。巨大.png</t>
         </is>
       </c>
-      <c r="C736" t="inlineStr">
+      <c r="C735" t="inlineStr">
         <is>
           <t>台風</t>
         </is>
       </c>
     </row>
-    <row r="737">
-      <c r="A737" t="inlineStr">
+    <row r="736">
+      <c r="A736" t="inlineStr">
         <is>
           <t xml:space="preserve">「草を食む幸運な子羊たち」
 خراف محظوظة ترعى
@@ -15938,19 +15917,19 @@
 2308 https://twitter.com/NatGeoMagArab/status/1490211393554972676 </t>
         </is>
       </c>
-      <c r="B737" t="inlineStr">
+      <c r="B736" t="inlineStr">
         <is>
           <t>images/「草を食む幸運な子羊たち」_img1.jpg,images/ 「草を食む幸運な子羊たち」_img2.jpg</t>
         </is>
       </c>
-      <c r="C737" t="inlineStr">
+      <c r="C736" t="inlineStr">
         <is>
           <t>羊 ,アイルランド</t>
         </is>
       </c>
     </row>
-    <row r="738">
-      <c r="A738" t="inlineStr">
+    <row r="737">
+      <c r="A737" t="inlineStr">
         <is>
           <t xml:space="preserve">「お金で買えぬ10のもの」
 ١٠ أشياء لا تشترى بالمال
@@ -15960,19 +15939,19 @@
 2308 ayb124 </t>
         </is>
       </c>
-      <c r="B738" t="inlineStr">
+      <c r="B737" t="inlineStr">
         <is>
           <t>images/「お金で買えぬ10のもの」_img1.jpg</t>
         </is>
       </c>
-      <c r="C738" t="inlineStr">
+      <c r="C737" t="inlineStr">
         <is>
           <t>価値 ,購買</t>
         </is>
       </c>
     </row>
-    <row r="739">
-      <c r="A739" t="inlineStr">
+    <row r="738">
+      <c r="A738" t="inlineStr">
         <is>
           <t xml:space="preserve">「お金では買えないよ」
 هي أشْيَاءٌ لا تُشْتَرَى
@@ -15982,19 +15961,19 @@
 1906 mardy_zaawely, Instagram </t>
         </is>
       </c>
-      <c r="B739" t="inlineStr">
+      <c r="B738" t="inlineStr">
         <is>
           <t>images/「お金では買えないよ」_img1.jpg</t>
         </is>
       </c>
-      <c r="C739" t="inlineStr">
+      <c r="C738" t="inlineStr">
         <is>
           <t>マスターカード ,価値</t>
         </is>
       </c>
     </row>
-    <row r="740">
-      <c r="A740" t="inlineStr">
+    <row r="739">
+      <c r="A739" t="inlineStr">
         <is>
           <t xml:space="preserve">「好奇心旺盛なホッキョクギツネ」
 ثعلب قطبي يملؤه الفضول
@@ -16004,15 +15983,15 @@
 2308 https://twitter.com/natgeomagarab/status/1157592172968808449 </t>
         </is>
       </c>
-      <c r="B740" t="inlineStr"/>
-      <c r="C740" t="inlineStr">
+      <c r="B739" t="inlineStr"/>
+      <c r="C739" t="inlineStr">
         <is>
           <t>ファーストコンタクト ,キツネ</t>
         </is>
       </c>
     </row>
-    <row r="741">
-      <c r="A741" t="inlineStr">
+    <row r="740">
+      <c r="A740" t="inlineStr">
         <is>
           <t xml:space="preserve">「グレンダイザーのいる国は死にません」
 لنْ يَموتَ شَعبٌ لدَيهِ غرندايزر
@@ -16021,56 +16000,56 @@
 2308 https://www.aljarida.com/articles/1462241741574732100/ </t>
         </is>
       </c>
+      <c r="B740" t="inlineStr">
+        <is>
+          <t>images/「グレンダイザーのいる国は死にません」_img1.jpg</t>
+        </is>
+      </c>
+      <c r="C740" t="inlineStr">
+        <is>
+          <t>UFOロボ ,アニメ</t>
+        </is>
+      </c>
+    </row>
+    <row r="741">
+      <c r="A741" t="inlineStr">
+        <is>
+          <t xml:space="preserve">「凍結路面を運転中、彼女は嫌な場面に居合わせた」
+2408 https://twitter.com/NatGeoMagArab/status/1610305209657626625 </t>
+        </is>
+      </c>
       <c r="B741" t="inlineStr">
         <is>
-          <t>images/「グレンダイザーのいる国は死にません」_img1.jpg</t>
+          <t>images/「凍結路面を運転中、彼女は嫌な場面に居_img1.jpg</t>
         </is>
       </c>
       <c r="C741" t="inlineStr">
         <is>
-          <t>UFOロボ ,アニメ</t>
+          <t>手書き語学 ,アラビア語 ,路面凍結</t>
         </is>
       </c>
     </row>
     <row r="742">
       <c r="A742" t="inlineStr">
-        <is>
-          <t xml:space="preserve">「凍結路面を運転中、彼女は嫌な場面に居合わせた」
-2408 https://twitter.com/NatGeoMagArab/status/1610305209657626625 </t>
-        </is>
-      </c>
-      <c r="B742" t="inlineStr">
-        <is>
-          <t>images/「凍結路面を運転中、彼女は嫌な場面に居_img1.jpg</t>
-        </is>
-      </c>
-      <c r="C742" t="inlineStr">
-        <is>
-          <t>手書き語学 ,アラビア語 ,路面凍結</t>
-        </is>
-      </c>
-    </row>
-    <row r="743">
-      <c r="A743" t="inlineStr">
         <is>
           <t xml:space="preserve">「虹が美しさを加えている、アルパカという動物の美しいショット」
 ⁦「美しいショット」[laq_tatun jamiilatun]：「ショット」( لقطة )[laq_ta]：( ـلٌ )[-lun]・( ـقٌ )[-qun]・( ـطٌ )[-_tun]・( ـةٌ )[-tun]⁩
 2308 https://twitter.com/natgeomagarab/status/1155115655928004608 </t>
         </is>
       </c>
-      <c r="B743" t="inlineStr">
+      <c r="B742" t="inlineStr">
         <is>
           <t>images/「虹が美しさを加えている、アルパカとい_img1.jpg</t>
         </is>
       </c>
-      <c r="C743" t="inlineStr">
+      <c r="C742" t="inlineStr">
         <is>
           <t>モフモフ ,アルパカ</t>
         </is>
       </c>
     </row>
-    <row r="744">
-      <c r="A744" t="inlineStr">
+    <row r="743">
+      <c r="A743" t="inlineStr">
         <is>
           <t xml:space="preserve">「幸せは…全然思いもよらない所からやって来る」
 السعادة تأتينا من أماكن لم نكن نتوقعها أبداً
@@ -16079,19 +16058,19 @@
 2109 出典不明 </t>
         </is>
       </c>
-      <c r="B744" t="inlineStr">
+      <c r="B743" t="inlineStr">
         <is>
           <t>images/「幸せは…全然思いもよらない所からやっ_img1.jpg,images/ 「幸せは…全然思いもよらない所からやっ_img2.jpg</t>
         </is>
       </c>
-      <c r="C744" t="inlineStr">
+      <c r="C743" t="inlineStr">
         <is>
           <t>訪れ ,予想</t>
         </is>
       </c>
     </row>
-    <row r="745">
-      <c r="A745" t="inlineStr">
+    <row r="744">
+      <c r="A744" t="inlineStr">
         <is>
           <t xml:space="preserve">「あらゆる問題は、食べ物が解決してくれる」
 كل مشكلة ولها أكلة تحلها
@@ -16100,19 +16079,19 @@
 1909 ALQA AN 878 </t>
         </is>
       </c>
-      <c r="B745" t="inlineStr">
+      <c r="B744" t="inlineStr">
         <is>
           <t>images/「あらゆる問題は、食べ物が解決してくれ_img1.jpg</t>
         </is>
       </c>
-      <c r="C745" t="inlineStr">
+      <c r="C744" t="inlineStr">
         <is>
           <t>ストレス ,精神</t>
         </is>
       </c>
     </row>
-    <row r="746">
-      <c r="A746" t="inlineStr">
+    <row r="745">
+      <c r="A745" t="inlineStr">
         <is>
           <t xml:space="preserve">「冬で私が好きな物」
 أشياء أحبها بالشتاء
@@ -16122,19 +16101,19 @@
 2109 出典不明 </t>
         </is>
       </c>
-      <c r="B746" t="inlineStr">
+      <c r="B745" t="inlineStr">
         <is>
           <t>images/「冬で私が好きな物」_img1.jpg</t>
         </is>
       </c>
-      <c r="C746" t="inlineStr">
+      <c r="C745" t="inlineStr">
         <is>
           <t>季節 ,冬</t>
         </is>
       </c>
     </row>
-    <row r="747">
-      <c r="A747" t="inlineStr">
+    <row r="746">
+      <c r="A746" t="inlineStr">
         <is>
           <t xml:space="preserve">「お金で買うことの出来ない物」
 أشياء لا تستطيع شراءها بالمال
@@ -16144,19 +16123,19 @@
 2409 https://x.com/akhbarak/status/1038402708414373888 </t>
         </is>
       </c>
-      <c r="B747" t="inlineStr">
+      <c r="B746" t="inlineStr">
         <is>
           <t>images/「お金で買うことの出来ない物」_img1.jpg,images/ 「お金で買うことの出来ない物」_img2.jpg</t>
         </is>
       </c>
-      <c r="C747" t="inlineStr">
+      <c r="C746" t="inlineStr">
         <is>
           <t>ショッピング ,価値</t>
         </is>
       </c>
     </row>
-    <row r="748">
-      <c r="A748" t="inlineStr">
+    <row r="747">
+      <c r="A747" t="inlineStr">
         <is>
           <t xml:space="preserve">「私たちが愛する言葉」
 كلماتٌ نُحبّها
@@ -16166,19 +16145,19 @@
 2109 جليل خزعل </t>
         </is>
       </c>
-      <c r="B748" t="inlineStr">
+      <c r="B747" t="inlineStr">
         <is>
           <t>images/「私たちが愛する言葉」_img1.jpg</t>
         </is>
       </c>
-      <c r="C748" t="inlineStr">
+      <c r="C747" t="inlineStr">
         <is>
           <t>花 ,贈り物</t>
         </is>
       </c>
     </row>
-    <row r="749">
-      <c r="A749" t="inlineStr">
+    <row r="748">
+      <c r="A748" t="inlineStr">
         <is>
           <t xml:space="preserve">「お茶についてあなたが知らない10の事実」
 عشر معلومات لا تعرفها عن الشاي
@@ -16187,19 +16166,19 @@
 2012 http://ara.tv/6syq2 </t>
         </is>
       </c>
-      <c r="B749" t="inlineStr">
+      <c r="B748" t="inlineStr">
         <is>
           <t>images/「お茶についてあなたが知らない10の事_img1.jpg</t>
         </is>
       </c>
-      <c r="C749" t="inlineStr">
+      <c r="C748" t="inlineStr">
         <is>
           <t>神農</t>
         </is>
       </c>
     </row>
-    <row r="750">
-      <c r="A750" t="inlineStr">
+    <row r="749">
+      <c r="A749" t="inlineStr">
         <is>
           <t xml:space="preserve">「大きくなったウソ」
 الكذبة الّتي كبرت
@@ -16209,19 +16188,19 @@
 2509 سلسلة الحلزونة </t>
         </is>
       </c>
-      <c r="B750" t="inlineStr">
+      <c r="B749" t="inlineStr">
         <is>
           <t>images/「大きくなったウソ」_img1.jpg</t>
         </is>
       </c>
-      <c r="C750" t="inlineStr">
+      <c r="C749" t="inlineStr">
         <is>
           <t>絵本</t>
         </is>
       </c>
     </row>
-    <row r="751">
-      <c r="A751" t="inlineStr">
+    <row r="750">
+      <c r="A750" t="inlineStr">
         <is>
           <t xml:space="preserve">「自分に合った掃除機を買うには？」
 كيف تشتري المكنسة الكهربائية التي تناسبك؟
@@ -16230,19 +16209,19 @@
 2106 ts3a com </t>
         </is>
       </c>
-      <c r="B751" t="inlineStr">
+      <c r="B750" t="inlineStr">
         <is>
           <t>images/「自分に合った掃除機を買うには？」_img1.jpg</t>
         </is>
       </c>
-      <c r="C751" t="inlineStr">
+      <c r="C750" t="inlineStr">
         <is>
           <t>家電 ,掃除</t>
         </is>
       </c>
     </row>
-    <row r="752">
-      <c r="A752" t="inlineStr">
+    <row r="751">
+      <c r="A751" t="inlineStr">
         <is>
           <t xml:space="preserve">「仮にこれが批判の数としよう」
 لنفرض ان عدد الذين ينتقدونك
@@ -16253,19 +16232,19 @@
 2504 出典不明 </t>
         </is>
       </c>
-      <c r="B752" t="inlineStr">
+      <c r="B751" t="inlineStr">
         <is>
           <t>images/「仮にこれが批判の数としよう」_img1.jpg</t>
         </is>
       </c>
-      <c r="C752" t="inlineStr">
+      <c r="C751" t="inlineStr">
         <is>
           <t>アンチ</t>
         </is>
       </c>
     </row>
-    <row r="753">
-      <c r="A753" t="inlineStr">
+    <row r="752">
+      <c r="A752" t="inlineStr">
         <is>
           <t xml:space="preserve">「ここに見えるのは何？」
 ما الذي تراه هنا؟
@@ -16275,15 +16254,15 @@
 2204 https://twitter.com/NatGeoMagArab/status/1506933850617700352 </t>
         </is>
       </c>
-      <c r="B753" t="inlineStr"/>
-      <c r="C753" t="inlineStr">
+      <c r="B752" t="inlineStr"/>
+      <c r="C752" t="inlineStr">
         <is>
           <t xml:space="preserve">ペンギン </t>
         </is>
       </c>
     </row>
-    <row r="754">
-      <c r="A754" t="inlineStr">
+    <row r="753">
+      <c r="A753" t="inlineStr">
         <is>
           <t xml:space="preserve">「今日辛いこと、明日は平気だろう」
 ما يؤلم اليوم سيهون غدًا
@@ -16293,19 +16272,19 @@
 2308 basmahjeff </t>
         </is>
       </c>
-      <c r="B754" t="inlineStr">
+      <c r="B753" t="inlineStr">
         <is>
           <t>images/「今日辛いこと、明日は平気だろう」_img1.jpg</t>
         </is>
       </c>
-      <c r="C754" t="inlineStr">
+      <c r="C753" t="inlineStr">
         <is>
           <t>悩み ,達観</t>
         </is>
       </c>
     </row>
-    <row r="755">
-      <c r="A755" t="inlineStr">
+    <row r="754">
+      <c r="A754" t="inlineStr">
         <is>
           <t xml:space="preserve">「自分のすることを好きでなきゃ」
 عليك أن تحب ما تفعل
@@ -16314,19 +16293,19 @@
 1810 Ahmed Elhakeem </t>
         </is>
       </c>
-      <c r="B755" t="inlineStr">
+      <c r="B754" t="inlineStr">
         <is>
           <t>images/「自分のすることを好きでなきゃ」_img1.jpg</t>
         </is>
       </c>
-      <c r="C755" t="inlineStr">
+      <c r="C754" t="inlineStr">
         <is>
           <t>転職 ,かわいい</t>
         </is>
       </c>
     </row>
-    <row r="756">
-      <c r="A756" t="inlineStr">
+    <row r="755">
+      <c r="A755" t="inlineStr">
         <is>
           <t xml:space="preserve">「この地上に生き甲斐あり」
 على هذه الأرض ما يستحق الحياة
@@ -16336,19 +16315,19 @@
 2308 Mahmoud Gafar </t>
         </is>
       </c>
-      <c r="B756" t="inlineStr">
+      <c r="B755" t="inlineStr">
         <is>
           <t>images/「この地上に生き甲斐あり」_img1.jpg</t>
         </is>
       </c>
-      <c r="C756" t="inlineStr">
+      <c r="C755" t="inlineStr">
         <is>
           <t>詩</t>
         </is>
       </c>
     </row>
-    <row r="757">
-      <c r="A757" t="inlineStr">
+    <row r="756">
+      <c r="A756" t="inlineStr">
         <is>
           <t xml:space="preserve">「おそらく、あなたの求めるものはあるだろう」
 لعلَّ ما تَرجوهُ سيَكونُ
@@ -16358,19 +16337,19 @@
 2308 PIXEL Instagram </t>
         </is>
       </c>
-      <c r="B757" t="inlineStr">
+      <c r="B756" t="inlineStr">
         <is>
           <t>images/「おそらく、あなたの求めるものはあるだ_img1.jpg</t>
         </is>
       </c>
-      <c r="C757" t="inlineStr">
+      <c r="C756" t="inlineStr">
         <is>
           <t>願い ,信仰</t>
         </is>
       </c>
     </row>
-    <row r="758">
-      <c r="A758" t="inlineStr">
+    <row r="757">
+      <c r="A757" t="inlineStr">
         <is>
           <t xml:space="preserve">「オレンジの効能が何か知っていますか？」
 هل تعرف ما هي فوائد البرتقال؟
@@ -16380,19 +16359,19 @@
 2308 sadahadhramowt com </t>
         </is>
       </c>
-      <c r="B758" t="inlineStr">
+      <c r="B757" t="inlineStr">
         <is>
           <t>images/「オレンジの効能が何か知っていますか？_img1.jpg</t>
         </is>
       </c>
-      <c r="C758" t="inlineStr">
+      <c r="C757" t="inlineStr">
         <is>
           <t>オレンジ ,フルーツ</t>
         </is>
       </c>
     </row>
-    <row r="759">
-      <c r="A759" t="inlineStr">
+    <row r="758">
+      <c r="A758" t="inlineStr">
         <is>
           <t xml:space="preserve">「遊ぶパンダの光景より可愛いものがありますか？」
 هل هناك ما هو ألطف من مشاهدة الباندا وهي تلعب؟
@@ -16400,19 +16379,19 @@
 2308 https://twitter.com/NatGeoMagArab/status/1494612797858074626 </t>
         </is>
       </c>
-      <c r="B759" t="inlineStr">
+      <c r="B758" t="inlineStr">
         <is>
           <t>images/「遊ぶパンダの光景より可愛いものがあり_img1.jpg</t>
         </is>
       </c>
-      <c r="C759" t="inlineStr">
+      <c r="C758" t="inlineStr">
         <is>
           <t>パンダ ,モコモコ</t>
         </is>
       </c>
     </row>
-    <row r="760">
-      <c r="A760" t="inlineStr">
+    <row r="759">
+      <c r="A759" t="inlineStr">
         <is>
           <t xml:space="preserve">「大事なのは何者だったかじゃない。何者になるかだ」
 ليسَ المُهم ما كُنتَ بل مَا ستكون
@@ -16421,19 +16400,19 @@
 2308 出典不明 </t>
         </is>
       </c>
-      <c r="B760" t="inlineStr">
+      <c r="B759" t="inlineStr">
         <is>
           <t>images/「大事なのは何者だったかじゃない。何者_img1.jpg</t>
         </is>
       </c>
-      <c r="C760" t="inlineStr">
+      <c r="C759" t="inlineStr">
         <is>
           <t>自己実現 ,存在価値</t>
         </is>
       </c>
     </row>
-    <row r="761">
-      <c r="A761" t="inlineStr">
+    <row r="760">
+      <c r="A760" t="inlineStr">
         <is>
           <t xml:space="preserve">「あなたであれ。ありのままが美しいから」
 كُنْ أَنْتَ لأنك جميل كما أنت
@@ -16442,19 +16421,19 @@
 2308 IDREES DESIGN </t>
         </is>
       </c>
-      <c r="B761" t="inlineStr">
+      <c r="B760" t="inlineStr">
         <is>
           <t>images/「あなたであれ。ありのままが美しいから_img1.jpg</t>
         </is>
       </c>
-      <c r="C761" t="inlineStr">
+      <c r="C760" t="inlineStr">
         <is>
           <t>自己肯定 ,BeYourself</t>
         </is>
       </c>
     </row>
-    <row r="762">
-      <c r="A762" t="inlineStr">
+    <row r="761">
+      <c r="A761" t="inlineStr">
         <is>
           <t xml:space="preserve">「恐れの中に生きる者は決して自由になれない」
 من يعش في خوف لن يكون حرا أبدا
@@ -16463,19 +16442,19 @@
 2111 rjeem com </t>
         </is>
       </c>
-      <c r="B762" t="inlineStr">
+      <c r="B761" t="inlineStr">
         <is>
           <t>images/「恐れの中に生きる者は決して自由になれ_img1.jpg,images/ 「恐れの中に生きる者は決して自由になれ_img2.jpg</t>
         </is>
       </c>
-      <c r="C762" t="inlineStr">
+      <c r="C761" t="inlineStr">
         <is>
           <t>勇気 ,壁</t>
         </is>
       </c>
     </row>
-    <row r="763">
-      <c r="A763" t="inlineStr">
+    <row r="762">
+      <c r="A762" t="inlineStr">
         <is>
           <t xml:space="preserve">「己の翼を信じる者は己の重さを案じない」
 من يثق في جناحيه لن يهتم لوزنه
@@ -16484,19 +16463,19 @@
 2308 kmrghani </t>
         </is>
       </c>
-      <c r="B763" t="inlineStr">
+      <c r="B762" t="inlineStr">
         <is>
           <t>images/「己の翼を信じる者は己の重さを案じない_img1.jpg</t>
         </is>
       </c>
-      <c r="C763" t="inlineStr">
+      <c r="C762" t="inlineStr">
         <is>
           <t>自信</t>
         </is>
       </c>
     </row>
-    <row r="764">
-      <c r="A764" t="inlineStr">
+    <row r="763">
+      <c r="A763" t="inlineStr">
         <is>
           <t xml:space="preserve">「珈琲で一番大事な事！誰と飲むか？」
 الأهم من القهوة!! من ستشربها معه؟
@@ -16505,19 +16484,19 @@
 1812 gwid3.tumblr </t>
         </is>
       </c>
-      <c r="B764" t="inlineStr">
+      <c r="B763" t="inlineStr">
         <is>
           <t>images/「珈琲で一番大事な事！誰と飲むか？」_img1.jpg</t>
         </is>
       </c>
-      <c r="C764" t="inlineStr">
+      <c r="C763" t="inlineStr">
         <is>
           <t>コーヒー ,名言</t>
         </is>
       </c>
     </row>
-    <row r="765">
-      <c r="A765" t="inlineStr">
+    <row r="764">
+      <c r="A764" t="inlineStr">
         <is>
           <t xml:space="preserve">「人生は美しい、そう望んだ者には。」
 الحياة جَميلَة .. لمن أراد ذلك
@@ -16527,19 +16506,19 @@
 2109 出典不明 </t>
         </is>
       </c>
-      <c r="B765" t="inlineStr">
+      <c r="B764" t="inlineStr">
         <is>
           <t>images/「人生は美しい、そう望んだ者には。」_img1.jpg</t>
         </is>
       </c>
-      <c r="C765" t="inlineStr">
+      <c r="C764" t="inlineStr">
         <is>
           <t>名言 ,アート</t>
         </is>
       </c>
     </row>
-    <row r="766">
-      <c r="A766" t="inlineStr">
+    <row r="765">
+      <c r="A765" t="inlineStr">
         <is>
           <t xml:space="preserve">「ハム太郎って子を知ってるかい」
 هل تعرفون من هو هامتارو
@@ -16549,19 +16528,19 @@
 2109 </t>
         </is>
       </c>
-      <c r="B766" t="inlineStr">
+      <c r="B765" t="inlineStr">
         <is>
           <t>images/「ハム太郎って子を知ってるかい」_img1.jpg</t>
         </is>
       </c>
-      <c r="C766" t="inlineStr">
+      <c r="C765" t="inlineStr">
         <is>
           <t>オープニング ,ハム太郎</t>
         </is>
       </c>
     </row>
-    <row r="767">
-      <c r="A767" t="inlineStr">
+    <row r="766">
+      <c r="A766" t="inlineStr">
         <is>
           <t xml:space="preserve">「幸せを求める人もいれば、作る人もいる」
 هناك من يبحث عن السعادة وهناك من يصنعها
@@ -16570,19 +16549,19 @@
 2308 hindah tumblr </t>
         </is>
       </c>
-      <c r="B767" t="inlineStr">
+      <c r="B766" t="inlineStr">
         <is>
           <t>images/「幸せを求める人もいれば、作る人もいる_img1.jpg</t>
         </is>
       </c>
-      <c r="C767" t="inlineStr">
+      <c r="C766" t="inlineStr">
         <is>
           <t>幸せ ,名言 ,教訓</t>
         </is>
       </c>
     </row>
-    <row r="768">
-      <c r="A768" t="inlineStr">
+    <row r="767">
+      <c r="A767" t="inlineStr">
         <is>
           <t xml:space="preserve">「明白なるアラブの言葉によって」
 بلسان عربي مبين
@@ -16592,19 +16571,19 @@
 2109 Abdullah Barakat behance </t>
         </is>
       </c>
-      <c r="B768" t="inlineStr">
+      <c r="B767" t="inlineStr">
         <is>
           <t>images/「明白なるアラブの言葉によって」_img1.jpg</t>
         </is>
       </c>
-      <c r="C768" t="inlineStr">
+      <c r="C767" t="inlineStr">
         <is>
           <t>イスラム教 ,神聖</t>
         </is>
       </c>
     </row>
-    <row r="769">
-      <c r="A769" t="inlineStr">
+    <row r="768">
+      <c r="A768" t="inlineStr">
         <is>
           <t xml:space="preserve">「結婚前、結婚後」
 قبل الزواج، بعد الزواج
@@ -16614,19 +16593,19 @@
 2308 出典不明 </t>
         </is>
       </c>
-      <c r="B769" t="inlineStr">
+      <c r="B768" t="inlineStr">
         <is>
           <t>images/「結婚前、結婚後」_img1.jpg</t>
         </is>
       </c>
-      <c r="C769" t="inlineStr">
+      <c r="C768" t="inlineStr">
         <is>
           <t>BeforeAfter ,幸せ太り</t>
         </is>
       </c>
     </row>
-    <row r="770">
-      <c r="A770" t="inlineStr">
+    <row r="769">
+      <c r="A769" t="inlineStr">
         <is>
           <t xml:space="preserve">「驚きの価格で」بسعر رائع
 ビスィアル・ラーイア [bi-si*r raa'i*]
@@ -16635,19 +16614,19 @@
 2109 Jarir Bookstore </t>
         </is>
       </c>
-      <c r="B770" t="inlineStr">
+      <c r="B769" t="inlineStr">
         <is>
           <t>images/「驚きの価格で」_img1.jpg</t>
         </is>
       </c>
-      <c r="C770" t="inlineStr">
+      <c r="C769" t="inlineStr">
         <is>
           <t>広告 ,安値</t>
         </is>
       </c>
     </row>
-    <row r="771">
-      <c r="A771" t="inlineStr">
+    <row r="770">
+      <c r="A770" t="inlineStr">
         <is>
           <t xml:space="preserve">「我が魂と共に」مع نفسي
 マア・ナフスィ [ma*a nafs-iy]
@@ -16656,19 +16635,19 @@
 2110 出典不明 </t>
         </is>
       </c>
-      <c r="B771" t="inlineStr">
+      <c r="B770" t="inlineStr">
         <is>
           <t>images/「我が魂と共に」_img1.jpg</t>
         </is>
       </c>
-      <c r="C771" t="inlineStr">
+      <c r="C770" t="inlineStr">
         <is>
           <t>ソウル ,soul</t>
         </is>
       </c>
     </row>
-    <row r="772">
-      <c r="A772" t="inlineStr">
+    <row r="771">
+      <c r="A771" t="inlineStr">
         <is>
           <t xml:space="preserve">「暗い夜に」في ليلة مظلمة
  [fiy layla(tin) mu_Dhlima(tin)]
@@ -16677,19 +16656,19 @@
 2109 سلسلة الحلزونة </t>
         </is>
       </c>
-      <c r="B772" t="inlineStr">
+      <c r="B771" t="inlineStr">
         <is>
           <t>images/「暗い夜に」_img1.jpg</t>
         </is>
       </c>
-      <c r="C772" t="inlineStr">
+      <c r="C771" t="inlineStr">
         <is>
           <t>絵本</t>
         </is>
       </c>
     </row>
-    <row r="773">
-      <c r="A773" t="inlineStr">
+    <row r="772">
+      <c r="A772" t="inlineStr">
         <is>
           <t xml:space="preserve">「ゆっくりと」بشويش
 ビシワェーシ [bi-ShwySh]
@@ -16697,19 +16676,19 @@
 2109 出典不明 </t>
         </is>
       </c>
-      <c r="B773" t="inlineStr">
+      <c r="B772" t="inlineStr">
         <is>
           <t>images/「ゆっくりと」_img1.jpg</t>
         </is>
       </c>
-      <c r="C773" t="inlineStr">
+      <c r="C772" t="inlineStr">
         <is>
           <t>丸 ,円</t>
         </is>
       </c>
     </row>
-    <row r="774">
-      <c r="A774" t="inlineStr">
+    <row r="773">
+      <c r="A773" t="inlineStr">
         <is>
           <t xml:space="preserve">「この広い宇宙に…」
 في الكون الفسيح
@@ -16718,19 +16697,19 @@
 2308 wattpad </t>
         </is>
       </c>
-      <c r="B774" t="inlineStr">
+      <c r="B773" t="inlineStr">
         <is>
           <t>images/「この広い宇宙に…」_img1.jpg</t>
         </is>
       </c>
-      <c r="C774" t="inlineStr">
+      <c r="C773" t="inlineStr">
         <is>
           <t>アニメ ,宇宙</t>
         </is>
       </c>
     </row>
-    <row r="775">
-      <c r="A775" t="inlineStr">
+    <row r="774">
+      <c r="A774" t="inlineStr">
         <is>
           <t xml:space="preserve">「がんばって！」بالتوفيق
 ビッタウフィーク [bi^tawfiiq]
@@ -16738,19 +16717,19 @@
 2111 https://sites.google.com/site/mathmatic1905/ </t>
         </is>
       </c>
-      <c r="B775" t="inlineStr">
+      <c r="B774" t="inlineStr">
         <is>
           <t>images/「がんばって！」_img1.jpg</t>
         </is>
       </c>
-      <c r="C775" t="inlineStr">
+      <c r="C774" t="inlineStr">
         <is>
           <t>アラビア語</t>
         </is>
       </c>
     </row>
-    <row r="776">
-      <c r="A776" t="inlineStr">
+    <row r="775">
+      <c r="A775" t="inlineStr">
         <is>
           <t xml:space="preserve">「インターステラー」بين النجوم
 バイナ_ンヌジューム [bayna ^nujuum]
@@ -16758,19 +16737,19 @@
 2308 kmrghani </t>
         </is>
       </c>
-      <c r="B776" t="inlineStr">
+      <c r="B775" t="inlineStr">
         <is>
           <t>images/「インターステラー」_img1.jpg</t>
         </is>
       </c>
-      <c r="C776" t="inlineStr">
+      <c r="C775" t="inlineStr">
         <is>
           <t>映画 ,宇宙</t>
         </is>
       </c>
     </row>
-    <row r="777">
-      <c r="A777" t="inlineStr">
+    <row r="776">
+      <c r="A776" t="inlineStr">
         <is>
           <t xml:space="preserve">「アラビア語で」بالعربية
 ビ_ルアラビーヤ [bi-l-*arabiyya]
@@ -16779,19 +16758,19 @@
 1811 </t>
         </is>
       </c>
-      <c r="B777" t="inlineStr">
+      <c r="B776" t="inlineStr">
         <is>
           <t>images/「アラビア語で」_img1.jpg</t>
         </is>
       </c>
-      <c r="C777" t="inlineStr">
+      <c r="C776" t="inlineStr">
         <is>
           <t>ニュース ,CNN</t>
         </is>
       </c>
     </row>
-    <row r="778">
-      <c r="A778" t="inlineStr">
+    <row r="777">
+      <c r="A777" t="inlineStr">
         <is>
           <t xml:space="preserve">「17世紀に発明されて以来…」
 منذ اختراعه بالقرن السابع عشر
@@ -16799,19 +16778,19 @@
 2308 https://twitter.com/SciTalk2U/status/1450888395815854080 </t>
         </is>
       </c>
-      <c r="B778" t="inlineStr">
+      <c r="B777" t="inlineStr">
         <is>
           <t>images/「17世紀に発明されて以来…」_img1.jpg</t>
         </is>
       </c>
-      <c r="C778" t="inlineStr">
+      <c r="C777" t="inlineStr">
         <is>
           <t>手書き語学 ,アラビア語 ,望遠鏡</t>
         </is>
       </c>
     </row>
-    <row r="779">
-      <c r="A779" t="inlineStr">
+    <row r="778">
+      <c r="A778" t="inlineStr">
         <is>
           <t xml:space="preserve">「私できるよ」إنّني أستطيع
 インナニー・アスタティーウ ['inna-niy 'a-sta_tii*u]
@@ -16820,19 +16799,19 @@
 2412 سلسلة الحلزونة </t>
         </is>
       </c>
-      <c r="B779" t="inlineStr">
+      <c r="B778" t="inlineStr">
         <is>
           <t>images/「私できるよ」_img1.jpg</t>
         </is>
       </c>
-      <c r="C779" t="inlineStr">
+      <c r="C778" t="inlineStr">
         <is>
           <t>絵本 ,こども</t>
         </is>
       </c>
     </row>
-    <row r="780">
-      <c r="A780" t="inlineStr">
+    <row r="779">
+      <c r="A779" t="inlineStr">
         <is>
           <t xml:space="preserve">「問題なし」مافيش مشكلة
 マフィーシムシュキラ [ma-fy-Sh muShkila]
@@ -16841,19 +16820,19 @@
 2109 tanzerin.theshop </t>
         </is>
       </c>
-      <c r="B780" t="inlineStr">
+      <c r="B779" t="inlineStr">
         <is>
           <t>images/「問題なし」_img1.jpg</t>
         </is>
       </c>
-      <c r="C780" t="inlineStr">
+      <c r="C779" t="inlineStr">
         <is>
           <t>シャツ ,キッズ</t>
         </is>
       </c>
     </row>
-    <row r="781">
-      <c r="A781" t="inlineStr">
+    <row r="780">
+      <c r="A780" t="inlineStr">
         <is>
           <t xml:space="preserve">「不可能はない」مفيش مستحيل
 マフィーシ・ムスタヒール [ma-fy-Sh mustaHiil]
@@ -16862,19 +16841,19 @@
 2109 أموج </t>
         </is>
       </c>
-      <c r="B781" t="inlineStr">
+      <c r="B780" t="inlineStr">
         <is>
           <t>images/「不可能はない」_img1.jpg</t>
         </is>
       </c>
-      <c r="C781" t="inlineStr">
+      <c r="C780" t="inlineStr">
         <is>
           <t>ポジティブ ,挑戦</t>
         </is>
       </c>
     </row>
-    <row r="782">
-      <c r="A782" t="inlineStr">
+    <row r="781">
+      <c r="A781" t="inlineStr">
         <is>
           <t xml:space="preserve">「等々」إلخ
 イラク ['ilaKh]
@@ -16883,19 +16862,19 @@
 2201 出典不明 </t>
         </is>
       </c>
-      <c r="B782" t="inlineStr">
+      <c r="B781" t="inlineStr">
         <is>
           <t>images/「等々」_img1.jpg</t>
         </is>
       </c>
-      <c r="C782" t="inlineStr">
+      <c r="C781" t="inlineStr">
         <is>
           <t>etc ,とんち</t>
         </is>
       </c>
     </row>
-    <row r="783">
-      <c r="A783" t="inlineStr">
+    <row r="782">
+      <c r="A782" t="inlineStr">
         <is>
           <t xml:space="preserve">⁦「調子どう？」⁩شلونَك؟
 シュローナク？ [Sh-loon-ak?]
@@ -16904,19 +16883,19 @@
 2202 Jozoor Team. </t>
         </is>
       </c>
-      <c r="B783" t="inlineStr">
+      <c r="B782" t="inlineStr">
         <is>
           <t>images/⁦「調子どう？」⁩_img1.jpg</t>
         </is>
       </c>
-      <c r="C783" t="inlineStr">
+      <c r="C782" t="inlineStr">
         <is>
           <t>洒落 ,ルービックキューブ</t>
         </is>
       </c>
     </row>
-    <row r="784">
-      <c r="A784" t="inlineStr">
+    <row r="783">
+      <c r="A783" t="inlineStr">
         <is>
           <t xml:space="preserve">「行くな」ماتروحش
 マトロホシ [ma-troH-Sh]
@@ -16925,19 +16904,19 @@
 2411 triiq tumblr </t>
         </is>
       </c>
-      <c r="B784" t="inlineStr">
+      <c r="B783" t="inlineStr">
         <is>
           <t>images/「行くな」_img1.jpg</t>
         </is>
       </c>
-      <c r="C784" t="inlineStr">
+      <c r="C783" t="inlineStr">
         <is>
           <t>ロゴ ,デザイン ,嵐</t>
         </is>
       </c>
     </row>
-    <row r="785">
-      <c r="A785" t="inlineStr">
+    <row r="784">
+      <c r="A784" t="inlineStr">
         <is>
           <t xml:space="preserve">⁦「元気？」⁩شلونَك؟
 シュローナク？ [Sh-loon-ak?]
@@ -16948,19 +16927,19 @@
 2202 出典不明 </t>
         </is>
       </c>
-      <c r="B785" t="inlineStr">
+      <c r="B784" t="inlineStr">
         <is>
           <t>images/⁦「元気？」⁩_img1.jpg</t>
         </is>
       </c>
-      <c r="C785" t="inlineStr">
+      <c r="C784" t="inlineStr">
         <is>
           <t>洒落 ,挨拶</t>
         </is>
       </c>
     </row>
-    <row r="786">
-      <c r="A786" t="inlineStr">
+    <row r="785">
+      <c r="A785" t="inlineStr">
         <is>
           <t xml:space="preserve">「気分が良いぞう」I فيل GOOD
 アイ・フィール・グッド [ai fiyl gud]
@@ -16969,19 +16948,19 @@
 2308 出典不明 </t>
         </is>
       </c>
-      <c r="B786" t="inlineStr">
+      <c r="B785" t="inlineStr">
         <is>
           <t>images/「気分が良いぞう」_img1.jpg</t>
         </is>
       </c>
-      <c r="C786" t="inlineStr">
+      <c r="C785" t="inlineStr">
         <is>
           <t>洒落 ,和訳</t>
         </is>
       </c>
     </row>
-    <row r="787">
-      <c r="A787" t="inlineStr">
+    <row r="786">
+      <c r="A786" t="inlineStr">
         <is>
           <t xml:space="preserve">「レットイットゴー／let it go」
 ليت اِت غو
@@ -16990,19 +16969,19 @@
 2109 出典不明 </t>
         </is>
       </c>
-      <c r="B787" t="inlineStr">
+      <c r="B786" t="inlineStr">
         <is>
           <t>images/「レットイットゴー／let it go_img1.jpg</t>
         </is>
       </c>
-      <c r="C787" t="inlineStr">
+      <c r="C786" t="inlineStr">
         <is>
           <t>折衷 ,アナ雪</t>
         </is>
       </c>
     </row>
-    <row r="788">
-      <c r="A788" t="inlineStr">
+    <row r="787">
+      <c r="A787" t="inlineStr">
         <is>
           <t xml:space="preserve">「ようこそ」اهلا وسهلا
 アハラン・ワサハラン ['ahlan wa-sahlan]
@@ -17010,19 +16989,19 @@
 2106 behance Anwar Al Eissa </t>
         </is>
       </c>
-      <c r="B788" t="inlineStr">
+      <c r="B787" t="inlineStr">
         <is>
           <t>images/「ようこそ」_img1.jpg</t>
         </is>
       </c>
-      <c r="C788" t="inlineStr">
+      <c r="C787" t="inlineStr">
         <is>
           <t>アラビア語</t>
         </is>
       </c>
     </row>
-    <row r="789">
-      <c r="A789" t="inlineStr">
+    <row r="788">
+      <c r="A788" t="inlineStr">
         <is>
           <t xml:space="preserve">「まぁ何というサプライズでしょう」
 يا لها من مفاجأة
@@ -17033,19 +17012,19 @@
 2108 neelwafurat com </t>
         </is>
       </c>
-      <c r="B789" t="inlineStr">
+      <c r="B788" t="inlineStr">
         <is>
           <t>images/「まぁ何というサプライズでしょう」_img1.jpg</t>
         </is>
       </c>
-      <c r="C789" t="inlineStr">
+      <c r="C788" t="inlineStr">
         <is>
           <t>中国語 ,学習</t>
         </is>
       </c>
     </row>
-    <row r="790">
-      <c r="A790" t="inlineStr">
+    <row r="789">
+      <c r="A789" t="inlineStr">
         <is>
           <t xml:space="preserve">「ハックション」اتشوو
 アチュー！ ['aatShuu]
@@ -17053,19 +17032,19 @@
 1811 </t>
         </is>
       </c>
-      <c r="B790" t="inlineStr">
+      <c r="B789" t="inlineStr">
         <is>
           <t>images/「ハックション」_img1.jpg</t>
         </is>
       </c>
-      <c r="C790" t="inlineStr">
+      <c r="C789" t="inlineStr">
         <is>
           <t>あらびあや</t>
         </is>
       </c>
     </row>
-    <row r="791">
-      <c r="A791" t="inlineStr">
+    <row r="790">
+      <c r="A790" t="inlineStr">
         <is>
           <t xml:space="preserve">「スブハーナッラー」「アルハムドゥリッラー」「アッラーアクバル」
 سبحان الله
@@ -17076,19 +17055,19 @@
 2308 dribbble com </t>
         </is>
       </c>
-      <c r="B791" t="inlineStr">
+      <c r="B790" t="inlineStr">
         <is>
           <t>images/「スブハーナッラー」「アルハムドゥリッ_img1.jpg</t>
         </is>
       </c>
-      <c r="C791" t="inlineStr">
+      <c r="C790" t="inlineStr">
         <is>
           <t>四角 ,コンパクト</t>
         </is>
       </c>
     </row>
-    <row r="792">
-      <c r="A792" t="inlineStr">
+    <row r="791">
+      <c r="A791" t="inlineStr">
         <is>
           <t xml:space="preserve">「すごく美味しい！」لذيذ جدًا
 ラズィーズ・ジッダン [laDhiiDh jiddan]
@@ -17097,19 +17076,19 @@
 2109 goodreads com </t>
         </is>
       </c>
-      <c r="B792" t="inlineStr">
+      <c r="B791" t="inlineStr">
         <is>
           <t>images/「すごく美味しい！」_img1.jpg</t>
         </is>
       </c>
-      <c r="C792" t="inlineStr">
+      <c r="C791" t="inlineStr">
         <is>
           <t>フレーズ ,感想</t>
         </is>
       </c>
     </row>
-    <row r="793">
-      <c r="A793" t="inlineStr">
+    <row r="792">
+      <c r="A792" t="inlineStr">
         <is>
           <t xml:space="preserve">「しとしと、雨」تك تك يا مطر
 ティクティク [tik tik yaa ma_tar]
@@ -17118,19 +17097,19 @@
 2308 出典不明 </t>
         </is>
       </c>
-      <c r="B793" t="inlineStr">
+      <c r="B792" t="inlineStr">
         <is>
           <t>images/「しとしと、雨」_img1.jpg</t>
         </is>
       </c>
-      <c r="C793" t="inlineStr">
+      <c r="C792" t="inlineStr">
         <is>
           <t>天気 ,梅雨</t>
         </is>
       </c>
     </row>
-    <row r="794">
-      <c r="A794" t="inlineStr">
+    <row r="793">
+      <c r="A793" t="inlineStr">
         <is>
           <t xml:space="preserve">「さかさま」رأساً على عقب
 ラッアサン・アラー・アケブ [ra'san *alaa *aqib]
@@ -17138,19 +17117,19 @@
 2109 出典不明 </t>
         </is>
       </c>
-      <c r="B794" t="inlineStr">
+      <c r="B793" t="inlineStr">
         <is>
           <t>images/「さかさま」_img1.jpg</t>
         </is>
       </c>
-      <c r="C794" t="inlineStr">
+      <c r="C793" t="inlineStr">
         <is>
           <t>壁 ,上下</t>
         </is>
       </c>
     </row>
-    <row r="795">
-      <c r="A795" t="inlineStr">
+    <row r="794">
+      <c r="A794" t="inlineStr">
         <is>
           <t xml:space="preserve">「エジプトよどこへ行った」
 فينك يا مصر؟
@@ -17160,19 +17139,19 @@
 1809 shehabfawzy1.tumblr </t>
         </is>
       </c>
-      <c r="B795" t="inlineStr">
+      <c r="B794" t="inlineStr">
         <is>
           <t>images/「エジプトよどこへ行った」_img1.jpg</t>
         </is>
       </c>
-      <c r="C795" t="inlineStr">
+      <c r="C794" t="inlineStr">
         <is>
           <t>ピラミッド ,歴史</t>
         </is>
       </c>
     </row>
-    <row r="796">
-      <c r="A796" t="inlineStr">
+    <row r="795">
+      <c r="A795" t="inlineStr">
         <is>
           <t xml:space="preserve">「ありがとう」شكراً
 シュクラン [Shukran]
@@ -17180,19 +17159,19 @@
 2109 出典不明 </t>
         </is>
       </c>
-      <c r="B796" t="inlineStr">
+      <c r="B795" t="inlineStr">
         <is>
           <t>images/「ありがとう」_img1.jpg</t>
         </is>
       </c>
-      <c r="C796" t="inlineStr">
+      <c r="C795" t="inlineStr">
         <is>
           <t>挨拶 ,文字</t>
         </is>
       </c>
     </row>
-    <row r="797">
-      <c r="A797" t="inlineStr">
+    <row r="796">
+      <c r="A796" t="inlineStr">
         <is>
           <t xml:space="preserve">「昼寝の時間だ」
 إنه وقت القيلولة
@@ -17201,12 +17180,12 @@
 2501 https://x.com/NatGeoMagArab/status/1858049951579910486 </t>
         </is>
       </c>
-      <c r="B797" t="inlineStr">
+      <c r="B796" t="inlineStr">
         <is>
           <t>images/「昼寝の時間だ」_img1.jpg</t>
         </is>
       </c>
-      <c r="C797" t="inlineStr">
+      <c r="C796" t="inlineStr">
         <is>
           <t>手書き語学 ,アラビア語 ,ペンギン</t>
         </is>

--- a/posts.xlsx
+++ b/posts.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C796"/>
+  <dimension ref="A1:C795"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -12687,27 +12687,6 @@
     <row r="584">
       <c r="A584" t="inlineStr">
         <is>
-          <t xml:space="preserve">「あなたの主の栄光を誉め称え、また（御赦しを請え。本当にかれは、度々赦される御方である）」
-فسَبِّح بحمد ربك و
-[fa-sabbiH bi-Hamdi rabbi-ka]
-主（シュ）・栄光（エイコウ）・誉め（ほめ）・称え（たたえ）
-2109 出典不明 </t>
-        </is>
-      </c>
-      <c r="B584" t="inlineStr">
-        <is>
-          <t>images/「あなたの主の栄光を誉め称え、また（御_img1.jpg</t>
-        </is>
-      </c>
-      <c r="C584" t="inlineStr">
-        <is>
-          <t>イスラム教 ,カリグラフィー</t>
-        </is>
-      </c>
-    </row>
-    <row r="585">
-      <c r="A585" t="inlineStr">
-        <is>
           <t xml:space="preserve">「誰かを幸福にしなさい」
 أسْعِد أحدهم
 ['as*id 'aHada-hum]
@@ -12716,19 +12695,19 @@
 1810 in4sser.tumblr </t>
         </is>
       </c>
-      <c r="B585" t="inlineStr">
+      <c r="B584" t="inlineStr">
         <is>
           <t>images/「誰かを幸福にしなさい」_img1.jpg</t>
         </is>
       </c>
-      <c r="C585" t="inlineStr">
+      <c r="C584" t="inlineStr">
         <is>
           <t>人生 ,happy</t>
         </is>
       </c>
     </row>
-    <row r="586">
-      <c r="A586" t="inlineStr">
+    <row r="585">
+      <c r="A585" t="inlineStr">
         <is>
           <t xml:space="preserve">「見よ」أبْصِرْ
 アブスィル ['ab_sir]
@@ -12737,19 +12716,19 @@
 1811 Ruh Al-Alam, via Behance </t>
         </is>
       </c>
-      <c r="B586" t="inlineStr">
+      <c r="B585" t="inlineStr">
         <is>
           <t>images/「見よ」_img1.jpg</t>
         </is>
       </c>
-      <c r="C586" t="inlineStr">
+      <c r="C585" t="inlineStr">
         <is>
           <t>目 ,瞳</t>
         </is>
       </c>
     </row>
-    <row r="587">
-      <c r="A587" t="inlineStr">
+    <row r="586">
+      <c r="A586" t="inlineStr">
         <is>
           <t xml:space="preserve">「言葉は口から出す前に味わいなさい」
 ‪تذوق كلماتك قبل أن تنطقها‬
@@ -12759,19 +12738,19 @@
 2109 Reham-des </t>
         </is>
       </c>
-      <c r="B587" t="inlineStr">
+      <c r="B586" t="inlineStr">
         <is>
           <t>images/「言葉は口から出す前に味わいなさい」_img1.jpg</t>
         </is>
       </c>
-      <c r="C587" t="inlineStr">
+      <c r="C586" t="inlineStr">
         <is>
           <t>言葉</t>
         </is>
       </c>
     </row>
-    <row r="588">
-      <c r="A588" t="inlineStr">
+    <row r="587">
+      <c r="A587" t="inlineStr">
         <is>
           <t xml:space="preserve">「テレビを観るのをやめて下さい」
 توقفي عن مشاهدة التلفاز
@@ -12781,19 +12760,19 @@
 1809 </t>
         </is>
       </c>
-      <c r="B588" t="inlineStr">
+      <c r="B587" t="inlineStr">
         <is>
           <t>images/「テレビを観るのをやめて下さい」_img1.jpg</t>
         </is>
       </c>
-      <c r="C588" t="inlineStr">
+      <c r="C587" t="inlineStr">
         <is>
           <t>あらびあや</t>
         </is>
       </c>
     </row>
-    <row r="589">
-      <c r="A589" t="inlineStr">
+    <row r="588">
+      <c r="A588" t="inlineStr">
         <is>
           <t xml:space="preserve">「言わぬが花」
 انْطِقْ جَمَالاً أو تجَمَّلْ بالسّكُوت
@@ -12803,19 +12782,19 @@
 2411 Ahmed Madyan </t>
         </is>
       </c>
-      <c r="B589" t="inlineStr">
+      <c r="B588" t="inlineStr">
         <is>
           <t>images/「言わぬが花」_img1.jpg</t>
         </is>
       </c>
-      <c r="C589" t="inlineStr">
+      <c r="C588" t="inlineStr">
         <is>
           <t>ことわざ ,デザイン</t>
         </is>
       </c>
     </row>
-    <row r="590">
-      <c r="A590" t="inlineStr">
+    <row r="589">
+      <c r="A589" t="inlineStr">
         <is>
           <t xml:space="preserve">「たくさん考えて、少し話すこと」
 فكّر كثيرا. تكلم قليلا
@@ -12825,19 +12804,19 @@
 2105 In49r </t>
         </is>
       </c>
-      <c r="B590" t="inlineStr">
+      <c r="B589" t="inlineStr">
         <is>
           <t>images/「たくさん考えて、少し話すこと」_img1.jpg</t>
         </is>
       </c>
-      <c r="C590" t="inlineStr">
+      <c r="C589" t="inlineStr">
         <is>
           <t>思慮 ,会話</t>
         </is>
       </c>
     </row>
-    <row r="591">
-      <c r="A591" t="inlineStr">
+    <row r="590">
+      <c r="A590" t="inlineStr">
         <is>
           <t xml:space="preserve">「子供たちよ、いつでも思い出すんだよ」
 تذكروا دوما يا أطفال
@@ -12847,19 +12826,19 @@
 1809 </t>
         </is>
       </c>
-      <c r="B591" t="inlineStr">
+      <c r="B590" t="inlineStr">
         <is>
           <t>images/「子供たちよ、いつでも思い出すんだよ」_img1.jpg</t>
         </is>
       </c>
-      <c r="C591" t="inlineStr">
+      <c r="C590" t="inlineStr">
         <is>
           <t>オープニング ,ハム太郎</t>
         </is>
       </c>
     </row>
-    <row r="592">
-      <c r="A592" t="inlineStr">
+    <row r="591">
+      <c r="A591" t="inlineStr">
         <is>
           <t xml:space="preserve">「分かってから話しなさい」
 تعلَّم ثمَّ تكلَّم
@@ -12869,19 +12848,19 @@
 1903 Hashem Al Shareef, Pinterest </t>
         </is>
       </c>
-      <c r="B592" t="inlineStr">
+      <c r="B591" t="inlineStr">
         <is>
           <t>images/「分かってから話しなさい」_img1.jpg</t>
         </is>
       </c>
-      <c r="C592" t="inlineStr">
+      <c r="C591" t="inlineStr">
         <is>
           <t>教訓 ,トーク</t>
         </is>
       </c>
     </row>
-    <row r="593">
-      <c r="A593" t="inlineStr">
+    <row r="592">
+      <c r="A592" t="inlineStr">
         <is>
           <t xml:space="preserve">「蟻に学べ」تعلم من النملة
 タアッラム・ミナ_ンナムラ [ta*allam mina ^namla]
@@ -12890,19 +12869,19 @@
 2308 fatakat com </t>
         </is>
       </c>
-      <c r="B593" t="inlineStr">
+      <c r="B592" t="inlineStr">
         <is>
           <t>images/「蟻に学べ」_img1.jpg</t>
         </is>
       </c>
-      <c r="C593" t="inlineStr">
+      <c r="C592" t="inlineStr">
         <is>
           <t>教訓 ,問題解決</t>
         </is>
       </c>
     </row>
-    <row r="594">
-      <c r="A594" t="inlineStr">
+    <row r="593">
+      <c r="A593" t="inlineStr">
         <is>
           <t xml:space="preserve">「自分と仲直りしよう、一杯の珈琲で！」
 تصالح مع نفسك بكوب قهوة
@@ -12912,19 +12891,19 @@
 2308 asm95_ </t>
         </is>
       </c>
-      <c r="B594" t="inlineStr">
+      <c r="B593" t="inlineStr">
         <is>
           <t>images/「自分と仲直りしよう、一杯の珈琲で！」_img1.jpg</t>
         </is>
       </c>
-      <c r="C594" t="inlineStr">
+      <c r="C593" t="inlineStr">
         <is>
           <t>一服 ,リラックス</t>
         </is>
       </c>
     </row>
-    <row r="595">
-      <c r="A595" t="inlineStr">
+    <row r="594">
+      <c r="A594" t="inlineStr">
         <is>
           <t xml:space="preserve">「気をつけて　ジュード」
 انتبهي يا جود
@@ -12934,19 +12913,19 @@
 2109 سلسلة الحلزونة </t>
         </is>
       </c>
-      <c r="B595" t="inlineStr">
+      <c r="B594" t="inlineStr">
         <is>
           <t>images/「気をつけて　ジュード」_img1.jpg</t>
         </is>
       </c>
-      <c r="C595" t="inlineStr">
+      <c r="C594" t="inlineStr">
         <is>
           <t>絵本 ,わんぱく</t>
         </is>
       </c>
     </row>
-    <row r="596">
-      <c r="A596" t="inlineStr">
+    <row r="595">
+      <c r="A595" t="inlineStr">
         <is>
           <t xml:space="preserve">「coming soon」
 انتظرونا قريبا
@@ -12955,19 +12934,19 @@
 2307 出典不明 </t>
         </is>
       </c>
-      <c r="B596" t="inlineStr">
+      <c r="B595" t="inlineStr">
         <is>
           <t>images/「coming soon」_img1.jpg</t>
         </is>
       </c>
-      <c r="C596" t="inlineStr">
+      <c r="C595" t="inlineStr">
         <is>
           <t>フレーズ ,カミングスーン</t>
         </is>
       </c>
     </row>
-    <row r="597">
-      <c r="A597" t="inlineStr">
+    <row r="596">
+      <c r="A596" t="inlineStr">
         <is>
           <t xml:space="preserve">「自分の胸に聞きなさい。それが全て知っています」
 استمع لقلبك.. إنه يعرف كل شيء
@@ -12976,19 +12955,19 @@
 1811 </t>
         </is>
       </c>
-      <c r="B597" t="inlineStr">
+      <c r="B596" t="inlineStr">
         <is>
           <t>images/「自分の胸に聞きなさい。それが全て知っ_img1.jpg</t>
         </is>
       </c>
-      <c r="C597" t="inlineStr">
+      <c r="C596" t="inlineStr">
         <is>
           <t>あらびあや</t>
         </is>
       </c>
     </row>
-    <row r="598">
-      <c r="A598" t="inlineStr">
+    <row r="597">
+      <c r="A597" t="inlineStr">
         <is>
           <t xml:space="preserve">「笑ってくれ、絶望を癒すのは君の笑みだから」
 ابتسمي فإن دواء اليأس بسمتك
@@ -12997,19 +12976,19 @@
 2308 arab-quotes tumblr </t>
         </is>
       </c>
-      <c r="B598" t="inlineStr">
+      <c r="B597" t="inlineStr">
         <is>
           <t>images/「笑ってくれ、絶望を癒すのは君の笑みだ_img1.jpg</t>
         </is>
       </c>
-      <c r="C598" t="inlineStr">
+      <c r="C597" t="inlineStr">
         <is>
           <t>癒し ,スマイル</t>
         </is>
       </c>
     </row>
-    <row r="599">
-      <c r="A599" t="inlineStr">
+    <row r="598">
+      <c r="A598" t="inlineStr">
         <is>
           <t xml:space="preserve">「自分を頼りなさい。宇宙で最も確かな物が自分だと思って。」
 استند على نفسك وكأنك أكثر الأشياء ثباتًا بهذا الكون
@@ -13017,19 +12996,19 @@
 2308 x_nourh.15 </t>
         </is>
       </c>
-      <c r="B599" t="inlineStr">
+      <c r="B598" t="inlineStr">
         <is>
           <t>images/「自分を頼りなさい。宇宙で最も確かな物_img1.jpg</t>
         </is>
       </c>
-      <c r="C599" t="inlineStr">
+      <c r="C598" t="inlineStr">
         <is>
           <t>自我 ,宇宙</t>
         </is>
       </c>
     </row>
-    <row r="600">
-      <c r="A600" t="inlineStr">
+    <row r="599">
+      <c r="A599" t="inlineStr">
         <is>
           <t xml:space="preserve">「古いデバイスを交換して新品をゲットしよう」
 استبدل جهازك القديم واحصل على واحد جديد
@@ -13038,19 +13017,19 @@
 2406 stc </t>
         </is>
       </c>
-      <c r="B600" t="inlineStr">
+      <c r="B599" t="inlineStr">
         <is>
           <t>images/「古いデバイスを交換して新品をゲットし_img1.jpg</t>
         </is>
       </c>
-      <c r="C600" t="inlineStr">
+      <c r="C599" t="inlineStr">
         <is>
           <t>キャンペーン ,下取り</t>
         </is>
       </c>
     </row>
-    <row r="601">
-      <c r="A601" t="inlineStr">
+    <row r="600">
+      <c r="A600" t="inlineStr">
         <is>
           <t xml:space="preserve">「あなたの声を聞かせてください。私の心を彩ってください」
 هات صوتك، لوّن قلبي
@@ -13059,19 +13038,19 @@
 2105 3a2esha_ Instagram </t>
         </is>
       </c>
-      <c r="B601" t="inlineStr">
+      <c r="B600" t="inlineStr">
         <is>
           <t>images/「あなたの声を聞かせてください。私の心_img1.jpg</t>
         </is>
       </c>
-      <c r="C601" t="inlineStr">
+      <c r="C600" t="inlineStr">
         <is>
           <t>電話 ,肉声</t>
         </is>
       </c>
     </row>
-    <row r="602">
-      <c r="A602" t="inlineStr">
+    <row r="601">
+      <c r="A601" t="inlineStr">
         <is>
           <t xml:space="preserve">「この子カンガルーは抱っこが好き」
 يُحب صغير الكنغر هذا أن يؤخذ في الأحضان
@@ -13079,19 +13058,19 @@
 2308 NatGeoMagArab </t>
         </is>
       </c>
-      <c r="B602" t="inlineStr">
+      <c r="B601" t="inlineStr">
         <is>
           <t>images/「この子カンガルーは抱っこが好き」.png</t>
         </is>
       </c>
-      <c r="C602" t="inlineStr">
+      <c r="C601" t="inlineStr">
         <is>
           <t>カンガルー ,人肌</t>
         </is>
       </c>
     </row>
-    <row r="603">
-      <c r="A603" t="inlineStr">
+    <row r="602">
+      <c r="A602" t="inlineStr">
         <is>
           <t xml:space="preserve">「カタールが好き」أحب قطر
 ウヒッブ・カタル ['u-Hibb qa_tar]
@@ -13100,19 +13079,19 @@
 1810 出典不明 </t>
         </is>
       </c>
-      <c r="B603" t="inlineStr">
+      <c r="B602" t="inlineStr">
         <is>
           <t>images/「カタールが好き」_img1.jpg</t>
         </is>
       </c>
-      <c r="C603" t="inlineStr">
+      <c r="C602" t="inlineStr">
         <is>
           <t>カタール</t>
         </is>
       </c>
     </row>
-    <row r="604">
-      <c r="A604" t="inlineStr">
+    <row r="603">
+      <c r="A603" t="inlineStr">
         <is>
           <t xml:space="preserve">「一緒に読むのが好き」
 أُحبُّ أن نَقْرَأَ مَعاً
@@ -13122,19 +13101,19 @@
 2509 www.neelwafurat com,  id=lbb212750-185765 </t>
         </is>
       </c>
-      <c r="B604" t="inlineStr">
+      <c r="B603" t="inlineStr">
         <is>
           <t>images/「一緒に読むのが好き」_img1.jpg</t>
         </is>
       </c>
-      <c r="C604" t="inlineStr">
+      <c r="C603" t="inlineStr">
         <is>
           <t>好き ,本</t>
         </is>
       </c>
     </row>
-    <row r="605">
-      <c r="A605" t="inlineStr">
+    <row r="604">
+      <c r="A604" t="inlineStr">
         <is>
           <t xml:space="preserve">「病院に行きたくない」
 لا أريد أن أذهب إلى المشفى
@@ -13144,19 +13123,19 @@
 2508 Tony Ross https://education.hachette-antoine.com/ar/component/%D9%84%D8%A7-%D8%A3%D8%B1%D9%8A%D8%AF-%D8%A3%D9%86-%D8%A3%D8%B0%D9%87%D8%A8-%D8%A5%D9%84%D9%89-%D8%A7%D9%84%D9%85%D8%B4%D9%81%D9%89/ </t>
         </is>
       </c>
-      <c r="B605" t="inlineStr">
+      <c r="B604" t="inlineStr">
         <is>
           <t>images/「病院に行きたくない」_img1.jpg</t>
         </is>
       </c>
-      <c r="C605" t="inlineStr">
+      <c r="C604" t="inlineStr">
         <is>
           <t>絵本 ,子供</t>
         </is>
       </c>
     </row>
-    <row r="606">
-      <c r="A606" t="inlineStr">
+    <row r="605">
+      <c r="A605" t="inlineStr">
         <is>
           <t xml:space="preserve">「男性はいくら？」「女性はいくら？」
 كم يساوى الرجل؟ ..وكم تساوى المرأة؟
@@ -13165,19 +13144,19 @@
 2308 Pinterest, Masr Elmahrousa, Farah Noweir </t>
         </is>
       </c>
-      <c r="B606" t="inlineStr">
+      <c r="B605" t="inlineStr">
         <is>
           <t>images/「男性はいくら？」「女性はいくら？」_img1.jpg,images/「男性はいくら？」「女性はいくら？」_img2.jpg</t>
         </is>
       </c>
-      <c r="C606" t="inlineStr">
+      <c r="C605" t="inlineStr">
         <is>
           <t xml:space="preserve">全身コーデ ,相場 </t>
         </is>
       </c>
     </row>
-    <row r="607">
-      <c r="A607" t="inlineStr">
+    <row r="606">
+      <c r="A606" t="inlineStr">
         <is>
           <t xml:space="preserve">「黙ってもらえます？」
 ممكن تعيرنا سكوتك؟
@@ -13187,19 +13166,19 @@
 2308 Basel26 </t>
         </is>
       </c>
-      <c r="B607" t="inlineStr">
+      <c r="B606" t="inlineStr">
         <is>
           <t>images/「黙ってもらえます？」_img1.jpg</t>
         </is>
       </c>
-      <c r="C607" t="inlineStr">
+      <c r="C606" t="inlineStr">
         <is>
           <t>音量 ,ボリューム</t>
         </is>
       </c>
     </row>
-    <row r="608">
-      <c r="A608" t="inlineStr">
+    <row r="607">
+      <c r="A607" t="inlineStr">
         <is>
           <t xml:space="preserve">「眠りたいです」
 أُريدُ أَن أَنام
@@ -13209,19 +13188,19 @@
 2109 goodreads com </t>
         </is>
       </c>
-      <c r="B608" t="inlineStr">
+      <c r="B607" t="inlineStr">
         <is>
           <t>images/「眠りたいです」_img1.jpg</t>
         </is>
       </c>
-      <c r="C608" t="inlineStr">
+      <c r="C607" t="inlineStr">
         <is>
           <t>絵本</t>
         </is>
       </c>
     </row>
-    <row r="609">
-      <c r="A609" t="inlineStr">
+    <row r="608">
+      <c r="A608" t="inlineStr">
         <is>
           <t xml:space="preserve">「飛びたい！」أُريد أن أطير
 ウリードゥ・アン・アティール ['u-riidu 'an 'a-_tiir]
@@ -13230,19 +13209,19 @@
 2308 出典不明 </t>
         </is>
       </c>
-      <c r="B609" t="inlineStr">
+      <c r="B608" t="inlineStr">
         <is>
           <t>images/「飛びたい！」_img1.jpg</t>
         </is>
       </c>
-      <c r="C609" t="inlineStr">
+      <c r="C608" t="inlineStr">
         <is>
           <t>鳥 ,希望</t>
         </is>
       </c>
     </row>
-    <row r="610">
-      <c r="A610" t="inlineStr">
+    <row r="609">
+      <c r="A609" t="inlineStr">
         <is>
           <t xml:space="preserve">「うちゅうへとびたい」
 أُريدُ أَنْ أَطيرَ إلى الفَضاء
@@ -13251,19 +13230,19 @@
 2308 mybookshelf co </t>
         </is>
       </c>
-      <c r="B610" t="inlineStr">
+      <c r="B609" t="inlineStr">
         <is>
           <t>images/「うちゅうへとびたい」_img1.jpg</t>
         </is>
       </c>
-      <c r="C610" t="inlineStr">
+      <c r="C609" t="inlineStr">
         <is>
           <t>絵本 ,宇宙</t>
         </is>
       </c>
     </row>
-    <row r="611">
-      <c r="A611" t="inlineStr">
+    <row r="610">
+      <c r="A610" t="inlineStr">
         <is>
           <t xml:space="preserve">「とても愛しています」
 أُحِبّك جِدّاً
@@ -13273,19 +13252,19 @@
 2308 hobe cc </t>
         </is>
       </c>
-      <c r="B611" t="inlineStr">
+      <c r="B610" t="inlineStr">
         <is>
           <t>images/「とても愛しています」_img1.jpg</t>
         </is>
       </c>
-      <c r="C611" t="inlineStr">
+      <c r="C610" t="inlineStr">
         <is>
           <t>恋 ,love</t>
         </is>
       </c>
     </row>
-    <row r="612">
-      <c r="A612" t="inlineStr">
+    <row r="611">
+      <c r="A611" t="inlineStr">
         <is>
           <t xml:space="preserve">「あす日が昇るだろう。私は朝が大好きだ」
 غدا ستشرق الشمس وأحب الصباح كثيرا
@@ -13294,19 +13273,19 @@
 2105 warag-3nb.tumblr com </t>
         </is>
       </c>
-      <c r="B612" t="inlineStr">
+      <c r="B611" t="inlineStr">
         <is>
           <t>images/「あす日が昇るだろう。私は朝が大好きだ_img1.jpg,images/ 「あす日が昇るだろう。私は朝が大好きだ_img2.jpg</t>
         </is>
       </c>
-      <c r="C612" t="inlineStr">
+      <c r="C611" t="inlineStr">
         <is>
           <t>おやすみ ,壁</t>
         </is>
       </c>
     </row>
-    <row r="613">
-      <c r="A613" t="inlineStr">
+    <row r="612">
+      <c r="A612" t="inlineStr">
         <is>
           <t xml:space="preserve">「きみは何をえらぶ？」
 ماذا تختار؟
@@ -13316,19 +13295,19 @@
 2109 embadomjp org </t>
         </is>
       </c>
-      <c r="B613" t="inlineStr">
+      <c r="B612" t="inlineStr">
         <is>
           <t>images/「きみは何をえらぶ？」_img1.jpg</t>
         </is>
       </c>
-      <c r="C613" t="inlineStr">
+      <c r="C612" t="inlineStr">
         <is>
           <t>優柔不断 ,絵本</t>
         </is>
       </c>
     </row>
-    <row r="614">
-      <c r="A614" t="inlineStr">
+    <row r="613">
+      <c r="A613" t="inlineStr">
         <is>
           <t xml:space="preserve">「ちょっと静けさが必要な時もある」
 في بعض الأوقات نحتاج لشوية هدوء
@@ -13338,19 +13317,19 @@
 2308 IN49r </t>
         </is>
       </c>
-      <c r="B614" t="inlineStr">
+      <c r="B613" t="inlineStr">
         <is>
           <t>images/「ちょっと静けさが必要な時もある」_img1.jpg</t>
         </is>
       </c>
-      <c r="C614" t="inlineStr">
+      <c r="C613" t="inlineStr">
         <is>
           <t>ミュート ,精神</t>
         </is>
       </c>
     </row>
-    <row r="615">
-      <c r="A615" t="inlineStr">
+    <row r="614">
+      <c r="A614" t="inlineStr">
         <is>
           <t xml:space="preserve">「逃げるな。全力でぶつかれ」
 لا تهرب اصطدم بكل قوتك
@@ -13360,19 +13339,19 @@
 2308 https://risingvibes.tumblr.com/post/189545775129 </t>
         </is>
       </c>
-      <c r="B615" t="inlineStr">
+      <c r="B614" t="inlineStr">
         <is>
           <t>images/「逃げるな。全力でぶつかれ」_img1.jpg</t>
         </is>
       </c>
-      <c r="C615" t="inlineStr">
+      <c r="C614" t="inlineStr">
         <is>
           <t>応援 ,力</t>
         </is>
       </c>
     </row>
-    <row r="616">
-      <c r="A616" t="inlineStr">
+    <row r="615">
+      <c r="A615" t="inlineStr">
         <is>
           <t xml:space="preserve">「着るのだいすき」
 أُحِبُ أَن أَرتَدِيَ
@@ -13382,19 +13361,19 @@
 2308 https://kitab.firmabikes.ru/epub-_hb_n_rtdy_5187.html </t>
         </is>
       </c>
-      <c r="B616" t="inlineStr">
+      <c r="B615" t="inlineStr">
         <is>
           <t>images/「着るのだいすき」_img1.jpg</t>
         </is>
       </c>
-      <c r="C616" t="inlineStr">
+      <c r="C615" t="inlineStr">
         <is>
           <t xml:space="preserve">絵本 ,ファッション </t>
         </is>
       </c>
     </row>
-    <row r="617">
-      <c r="A617" t="inlineStr">
+    <row r="616">
+      <c r="A616" t="inlineStr">
         <is>
           <t xml:space="preserve">「車のバッテリーが要る！」
 نحتاج بطارية سيارة
@@ -13404,19 +13383,19 @@
 2308 instagram roaa_27 </t>
         </is>
       </c>
-      <c r="B617" t="inlineStr">
+      <c r="B616" t="inlineStr">
         <is>
           <t>images/「車のバッテリーが要る！」_img1.jpg</t>
         </is>
       </c>
-      <c r="C617" t="inlineStr">
+      <c r="C616" t="inlineStr">
         <is>
           <t>スマホ ,充電</t>
         </is>
       </c>
     </row>
-    <row r="618">
-      <c r="A618" t="inlineStr">
+    <row r="617">
+      <c r="A617" t="inlineStr">
         <is>
           <t xml:space="preserve">「今日は幸せでいることにしました」
 اخترت أن أكون سعيدا اليوم
@@ -13426,19 +13405,19 @@
 2109 awaasha tumblr </t>
         </is>
       </c>
-      <c r="B618" t="inlineStr">
+      <c r="B617" t="inlineStr">
         <is>
           <t>images/「今日は幸せでいることにしました」_img1.jpg</t>
         </is>
       </c>
-      <c r="C618" t="inlineStr">
+      <c r="C617" t="inlineStr">
         <is>
           <t>心構え ,happy</t>
         </is>
       </c>
     </row>
-    <row r="619">
-      <c r="A619" t="inlineStr">
+    <row r="618">
+      <c r="A618" t="inlineStr">
         <is>
           <t xml:space="preserve">「理想的なスイカの選び方」
 كيف تختار البطيخة المُثلى؟
@@ -13448,19 +13427,19 @@
 2308 bit ly/octmel </t>
         </is>
       </c>
-      <c r="B619" t="inlineStr">
+      <c r="B618" t="inlineStr">
         <is>
           <t>images/「理想的なスイカの選び方」_img1.jpg</t>
         </is>
       </c>
-      <c r="C619" t="inlineStr">
+      <c r="C618" t="inlineStr">
         <is>
           <t>八百屋 ,西瓜</t>
         </is>
       </c>
     </row>
-    <row r="620">
-      <c r="A620" t="inlineStr">
+    <row r="619">
+      <c r="A619" t="inlineStr">
         <is>
           <t xml:space="preserve">「お問い合わせください」
 اتصل بنا
@@ -13470,19 +13449,19 @@
 2308 mtawir.blogspot com </t>
         </is>
       </c>
-      <c r="B620" t="inlineStr">
+      <c r="B619" t="inlineStr">
         <is>
           <t>images/「お問い合わせください」_img1.jpg</t>
         </is>
       </c>
-      <c r="C620" t="inlineStr">
+      <c r="C619" t="inlineStr">
         <is>
           <t>広告 ,電話</t>
         </is>
       </c>
     </row>
-    <row r="621">
-      <c r="A621" t="inlineStr">
+    <row r="620">
+      <c r="A620" t="inlineStr">
         <is>
           <t xml:space="preserve">「両方の動物が海岸の火山岩の亀裂の中に定住している」
 يحتل كلا الحيوانين شقوقًا في صخور الساحل البركانية
@@ -13490,19 +13469,19 @@
 2507 https://x.com/NatGeoMagArab/status/1925167200056521151 </t>
         </is>
       </c>
-      <c r="B621" t="inlineStr">
+      <c r="B620" t="inlineStr">
         <is>
           <t>images/「両方の動物が海岸の火山岩の亀裂の中に_img1.jpg,images/「両方の動物が海岸の火山岩の亀裂の中に_img2.jpg</t>
         </is>
       </c>
-      <c r="C621" t="inlineStr">
+      <c r="C620" t="inlineStr">
         <is>
           <t>手書き語学 ,アラビア語 ,イグアナ</t>
         </is>
       </c>
     </row>
-    <row r="622">
-      <c r="A622" t="inlineStr">
+    <row r="621">
+      <c r="A621" t="inlineStr">
         <is>
           <t xml:space="preserve">「命じられたように正しき道を辿れ」
 واستقم كما أمرت
@@ -13512,19 +13491,19 @@
 2308 Ahmed Madyan </t>
         </is>
       </c>
-      <c r="B622" t="inlineStr">
+      <c r="B621" t="inlineStr">
         <is>
           <t>images/「命じられたように正しき道を辿れ」_img1.jpg</t>
         </is>
       </c>
-      <c r="C622" t="inlineStr">
+      <c r="C621" t="inlineStr">
         <is>
           <t>書道 ,アート</t>
         </is>
       </c>
     </row>
-    <row r="623">
-      <c r="A623" t="inlineStr">
+    <row r="622">
+      <c r="A622" t="inlineStr">
         <is>
           <t xml:space="preserve">「くつろぎなさい」استكن
 イスタキンナ [istakinna]
@@ -13532,19 +13511,19 @@
 2603 m2ff tumblr com </t>
         </is>
       </c>
-      <c r="B623" t="inlineStr">
+      <c r="B622" t="inlineStr">
         <is>
           <t>images/「くつろぎなさい」.jpeg</t>
         </is>
       </c>
-      <c r="C623" t="inlineStr">
+      <c r="C622" t="inlineStr">
         <is>
           <t>relax ,コーヒー</t>
         </is>
       </c>
     </row>
-    <row r="624">
-      <c r="A624" t="inlineStr">
+    <row r="623">
+      <c r="A623" t="inlineStr">
         <is>
           <t xml:space="preserve">「彼は応えるだろう」سيستجيب 
 サヤスタジーブ [sa-ya-stajiibu]
@@ -13553,19 +13532,19 @@
 1811 kareem mrghani </t>
         </is>
       </c>
-      <c r="B624" t="inlineStr">
+      <c r="B623" t="inlineStr">
         <is>
           <t>images/「彼は応えるだろう」_img1.jpg</t>
         </is>
       </c>
-      <c r="C624" t="inlineStr">
+      <c r="C623" t="inlineStr">
         <is>
           <t>縦書き ,現代アート</t>
         </is>
       </c>
     </row>
-    <row r="625">
-      <c r="A625" t="inlineStr">
+    <row r="624">
+      <c r="A624" t="inlineStr">
         <is>
           <t xml:space="preserve">「アラビア語が好き」
 أنا أُحبّ لُغتي
@@ -13575,19 +13554,19 @@
 2308 出典不明 </t>
         </is>
       </c>
-      <c r="B625" t="inlineStr">
+      <c r="B624" t="inlineStr">
         <is>
           <t>images/「アラビア語が好き」_img1.jpg</t>
         </is>
       </c>
-      <c r="C625" t="inlineStr">
+      <c r="C624" t="inlineStr">
         <is>
           <t>和訳 ,こども</t>
         </is>
       </c>
     </row>
-    <row r="626">
-      <c r="A626" t="inlineStr">
+    <row r="625">
+      <c r="A625" t="inlineStr">
         <is>
           <t xml:space="preserve">「私はサッカーが好きです」
 أنا أُحِبُّ كُرةَ القَدَم
@@ -13597,19 +13576,19 @@
 2109 Arabic With Nadia </t>
         </is>
       </c>
-      <c r="B626" t="inlineStr">
+      <c r="B625" t="inlineStr">
         <is>
           <t>images/「私はサッカーが好きです」_img1.jpg</t>
         </is>
       </c>
-      <c r="C626" t="inlineStr">
+      <c r="C625" t="inlineStr">
         <is>
           <t>自由時間 ,例文</t>
         </is>
       </c>
     </row>
-    <row r="627">
-      <c r="A627" t="inlineStr">
+    <row r="626">
+      <c r="A626" t="inlineStr">
         <is>
           <t xml:space="preserve">「これ、私の眼鏡じゃありません」
 هٰذِهِ لَيْسَتْ نَظَّارَاتِي
@@ -13619,19 +13598,19 @@
 2509 </t>
         </is>
       </c>
-      <c r="B627" t="inlineStr">
+      <c r="B626" t="inlineStr">
         <is>
           <t>images/「これ、私の眼鏡じゃありません」_img1.jpg</t>
         </is>
       </c>
-      <c r="C627" t="inlineStr">
+      <c r="C626" t="inlineStr">
         <is>
           <t>あらびあや</t>
         </is>
       </c>
     </row>
-    <row r="628">
-      <c r="A628" t="inlineStr">
+    <row r="627">
+      <c r="A627" t="inlineStr">
         <is>
           <t xml:space="preserve">「我らも米を食います」
 نحن أيضاً نأكل الأرز
@@ -13641,19 +13620,19 @@
 1809 </t>
         </is>
       </c>
-      <c r="B628" t="inlineStr">
+      <c r="B627" t="inlineStr">
         <is>
           <t>images/「我らも米を食います」_img1.jpg</t>
         </is>
       </c>
-      <c r="C628" t="inlineStr">
+      <c r="C627" t="inlineStr">
         <is>
           <t>あらびあや</t>
         </is>
       </c>
     </row>
-    <row r="629">
-      <c r="A629" t="inlineStr">
+    <row r="628">
+      <c r="A628" t="inlineStr">
         <is>
           <t xml:space="preserve">「ひとりでできるもん！」
 أنا أستطيع أن أفعله وحدي
@@ -13662,19 +13641,19 @@
 2105 </t>
         </is>
       </c>
-      <c r="B629" t="inlineStr">
+      <c r="B628" t="inlineStr">
         <is>
           <t>images/「ひとりでできるもん！」_img1.jpg</t>
         </is>
       </c>
-      <c r="C629" t="inlineStr">
+      <c r="C628" t="inlineStr">
         <is>
           <t>あらびあや</t>
         </is>
       </c>
     </row>
-    <row r="630">
-      <c r="A630" t="inlineStr">
+    <row r="629">
+      <c r="A629" t="inlineStr">
         <is>
           <t xml:space="preserve">「恋しくないと言っている時は恋しい」
 أُريدُك حينَ أَقُولُ أَنا لا أُريدُك
@@ -13684,19 +13663,19 @@
 2308 DARWISHISM </t>
         </is>
       </c>
-      <c r="B630" t="inlineStr">
+      <c r="B629" t="inlineStr">
         <is>
           <t>images/「恋しくないと言っている時は恋しい」_img1.jpg</t>
         </is>
       </c>
-      <c r="C630" t="inlineStr">
+      <c r="C629" t="inlineStr">
         <is>
           <t>本音 ,恋愛</t>
         </is>
       </c>
     </row>
-    <row r="631">
-      <c r="A631" t="inlineStr">
+    <row r="630">
+      <c r="A630" t="inlineStr">
         <is>
           <t xml:space="preserve">「私は〜する」
 ⁦「着る」：( أنا ألبس )['ana 'a-lbas]⁩
@@ -13707,19 +13686,19 @@
 2109 RABIE </t>
         </is>
       </c>
-      <c r="B631" t="inlineStr">
+      <c r="B630" t="inlineStr">
         <is>
           <t>images/「私は〜する」_img1.jpg,images/「私は〜する」_img2.jpg,images/「私は〜する」_img3.jpg,images/「私は〜する」_img4.jpg</t>
         </is>
       </c>
-      <c r="C631" t="inlineStr">
+      <c r="C630" t="inlineStr">
         <is>
           <t>動詞 ,絵本</t>
         </is>
       </c>
     </row>
-    <row r="632">
-      <c r="A632" t="inlineStr">
+    <row r="631">
+      <c r="A631" t="inlineStr">
         <is>
           <t xml:space="preserve">「彼は完璧ではない。私は彼の欠点については目をつむった」
 هو ليس كامل. أنا أعميت نفسي عن سيئاته
@@ -13728,19 +13707,19 @@
 2308 _NOHA </t>
         </is>
       </c>
-      <c r="B632" t="inlineStr">
+      <c r="B631" t="inlineStr">
         <is>
           <t>images/「彼は完璧ではない。私は彼の欠点につい_img1.jpg</t>
         </is>
       </c>
-      <c r="C632" t="inlineStr">
+      <c r="C631" t="inlineStr">
         <is>
           <t>愛 ,寛容</t>
         </is>
       </c>
     </row>
-    <row r="633">
-      <c r="A633" t="inlineStr">
+    <row r="632">
+      <c r="A632" t="inlineStr">
         <is>
           <t xml:space="preserve">「この子トラは検疫期間中に生まれた」
 صغير النمر هذا ولد في زمن الحجر الصحي
@@ -13749,19 +13728,19 @@
 2310 https://www.akhbaralaan.net/?p=434924 </t>
         </is>
       </c>
-      <c r="B633" t="inlineStr">
+      <c r="B632" t="inlineStr">
         <is>
           <t>images/「この子トラは検疫期間中に生まれた」_img1.jpg</t>
         </is>
       </c>
-      <c r="C633" t="inlineStr">
+      <c r="C632" t="inlineStr">
         <is>
           <t>Covid ,メキシコ</t>
         </is>
       </c>
     </row>
-    <row r="634">
-      <c r="A634" t="inlineStr">
+    <row r="633">
+      <c r="A633" t="inlineStr">
         <is>
           <t xml:space="preserve">「睡眠の素晴らしさに匹敵するものは無い！」
 وجمال النوم ليس له مثيل
@@ -13770,19 +13749,19 @@
 2308 arabzy tumblr </t>
         </is>
       </c>
-      <c r="B634" t="inlineStr">
+      <c r="B633" t="inlineStr">
         <is>
           <t>images/「睡眠の素晴らしさに匹敵するものは無い_img1.jpg</t>
         </is>
       </c>
-      <c r="C634" t="inlineStr">
+      <c r="C633" t="inlineStr">
         <is>
           <t>オフトゥン ,おやすみ</t>
         </is>
       </c>
     </row>
-    <row r="635">
-      <c r="A635" t="inlineStr">
+    <row r="634">
+      <c r="A634" t="inlineStr">
         <is>
           <t xml:space="preserve">「大器晩成」
 الأشياء العظيمة تأخذ وقت
@@ -13792,19 +13771,19 @@
 2109 出典不明 </t>
         </is>
       </c>
-      <c r="B635" t="inlineStr">
+      <c r="B634" t="inlineStr">
         <is>
           <t>images/「大器晩成」_img1.jpg</t>
         </is>
       </c>
-      <c r="C635" t="inlineStr">
+      <c r="C634" t="inlineStr">
         <is>
           <t>ことわざ ,和訳</t>
         </is>
       </c>
     </row>
-    <row r="636">
-      <c r="A636" t="inlineStr">
+    <row r="635">
+      <c r="A635" t="inlineStr">
         <is>
           <t xml:space="preserve">「コーヒーは急には飲まれない」
 القهْوة لا تشرَب عَلى عَجلْ
@@ -13815,19 +13794,19 @@
 2012 Ahmed Madyan </t>
         </is>
       </c>
-      <c r="B636" t="inlineStr">
+      <c r="B635" t="inlineStr">
         <is>
           <t>images/「コーヒーは急には飲まれない」_img1.jpg</t>
         </is>
       </c>
-      <c r="C636" t="inlineStr">
+      <c r="C635" t="inlineStr">
         <is>
           <t>名言</t>
         </is>
       </c>
     </row>
-    <row r="637">
-      <c r="A637" t="inlineStr">
+    <row r="636">
+      <c r="A636" t="inlineStr">
         <is>
           <t xml:space="preserve">「成功者は情報共有している」
 الناجحون يشاركون المعلومة
@@ -13837,19 +13816,19 @@
 2109 出典不明 </t>
         </is>
       </c>
-      <c r="B637" t="inlineStr">
+      <c r="B636" t="inlineStr">
         <is>
           <t>images/「成功者は情報共有している」_img1.jpg</t>
         </is>
       </c>
-      <c r="C637" t="inlineStr">
+      <c r="C636" t="inlineStr">
         <is>
           <t>鳥 ,シェア</t>
         </is>
       </c>
     </row>
-    <row r="638">
-      <c r="A638" t="inlineStr">
+    <row r="637">
+      <c r="A637" t="inlineStr">
         <is>
           <t xml:space="preserve">「間違いで賢くなる、痛みで強くなる」
 الأخطاء تجعلك حكيمًا، والألم يجعلك قويًا
@@ -13858,19 +13837,19 @@
 2111 https://alaminin.blogspot.com/2020/03/blog-post_6.html </t>
         </is>
       </c>
-      <c r="B638" t="inlineStr">
+      <c r="B637" t="inlineStr">
         <is>
           <t>images/「間違いで賢くなる、痛みで強くなる」_img1.jpg</t>
         </is>
       </c>
-      <c r="C638" t="inlineStr">
+      <c r="C637" t="inlineStr">
         <is>
           <t>名言</t>
         </is>
       </c>
     </row>
-    <row r="639">
-      <c r="A639" t="inlineStr">
+    <row r="638">
+      <c r="A638" t="inlineStr">
         <is>
           <t xml:space="preserve">「何事も永遠には続かない」
 لا شيء يبقى للأبد
@@ -13880,19 +13859,19 @@
 2308 KiTeLetZ </t>
         </is>
       </c>
-      <c r="B639" t="inlineStr">
+      <c r="B638" t="inlineStr">
         <is>
           <t>images/「何事も永遠には続かない」_img1.jpg</t>
         </is>
       </c>
-      <c r="C639" t="inlineStr">
+      <c r="C638" t="inlineStr">
         <is>
           <t>変化 ,名言</t>
         </is>
       </c>
     </row>
-    <row r="640">
-      <c r="A640" t="inlineStr">
+    <row r="639">
+      <c r="A639" t="inlineStr">
         <is>
           <t xml:space="preserve">「惑星地球はあなた方を歓迎します」
 كوكب الارض يرحّب بكم
@@ -13902,19 +13881,19 @@
 1811 iN49R </t>
         </is>
       </c>
-      <c r="B640" t="inlineStr">
+      <c r="B639" t="inlineStr">
         <is>
           <t>images/「惑星地球はあなた方を歓迎します」_img1.jpg</t>
         </is>
       </c>
-      <c r="C640" t="inlineStr">
+      <c r="C639" t="inlineStr">
         <is>
           <t>宇宙 ,人類</t>
         </is>
       </c>
     </row>
-    <row r="641">
-      <c r="A641" t="inlineStr">
+    <row r="640">
+      <c r="A640" t="inlineStr">
         <is>
           <t xml:space="preserve">「自分を信じなさい。人の言うことは尽きないのだから」
 ثق بنفسك فكلام الناس لا ينتهي
@@ -13923,19 +13902,19 @@
 2105 出典不明 </t>
         </is>
       </c>
-      <c r="B641" t="inlineStr">
+      <c r="B640" t="inlineStr">
         <is>
           <t>images/「自分を信じなさい。人の言うことは尽き_img1.jpg</t>
         </is>
       </c>
-      <c r="C641" t="inlineStr">
+      <c r="C640" t="inlineStr">
         <is>
           <t>自信 ,無視</t>
         </is>
       </c>
     </row>
-    <row r="642">
-      <c r="A642" t="inlineStr">
+    <row r="641">
+      <c r="A641" t="inlineStr">
         <is>
           <t xml:space="preserve">「弟が歩くぞ」أخي الصغير يمشي
 アキ_ッサギール・ヤムシー ['aKh-i ^_saGhiiru ya-mShii]
@@ -13944,19 +13923,19 @@
 2308 gulfkids com http://www.gulfkids.com/ar/book48-1909.htm </t>
         </is>
       </c>
-      <c r="B642" t="inlineStr">
+      <c r="B641" t="inlineStr">
         <is>
           <t>images/「弟が歩くぞ」_img1.jpg</t>
         </is>
       </c>
-      <c r="C642" t="inlineStr">
+      <c r="C641" t="inlineStr">
         <is>
           <t>兄弟 ,絵本</t>
         </is>
       </c>
     </row>
-    <row r="643">
-      <c r="A643" t="inlineStr">
+    <row r="642">
+      <c r="A642" t="inlineStr">
         <is>
           <t xml:space="preserve">花より団子おおお（違う）
 「誰もふさわしくない」[laa 'aHada ya-staHiqqu]
@@ -13964,19 +13943,19 @@
 2308 https://twitter.com/NatGeoMagArab/status/1370041991317233664 </t>
         </is>
       </c>
-      <c r="B643" t="inlineStr">
+      <c r="B642" t="inlineStr">
         <is>
           <t>images/花より団子おおお（違う）_img1.jpg</t>
         </is>
       </c>
-      <c r="C643" t="inlineStr">
+      <c r="C642" t="inlineStr">
         <is>
           <t>手書き語学 ,アラビア語 ,キノボリカンガルー</t>
         </is>
       </c>
     </row>
-    <row r="644">
-      <c r="A644" t="inlineStr">
+    <row r="643">
+      <c r="A643" t="inlineStr">
         <is>
           <t xml:space="preserve">「幸せな人生には弱い記憶力が必要」
 الحياة السعيدة تتطلب ذاكرة ضعيفة
@@ -13985,19 +13964,19 @@
 2012 出典不明 </t>
         </is>
       </c>
-      <c r="B644" t="inlineStr">
+      <c r="B643" t="inlineStr">
         <is>
           <t>images/「幸せな人生には弱い記憶力が必要」_img1.jpg</t>
         </is>
       </c>
-      <c r="C644" t="inlineStr">
+      <c r="C643" t="inlineStr">
         <is>
           <t>前向き</t>
         </is>
       </c>
     </row>
-    <row r="645">
-      <c r="A645" t="inlineStr">
+    <row r="644">
+      <c r="A644" t="inlineStr">
         <is>
           <t xml:space="preserve">「このパンダは私たちに、幸せは単純なことの中に隠れているのだと教えている」
 دب "الباندا" هذا يؤكد لنا أن السعادة تكمن في أبسط الأشياء
@@ -14005,19 +13984,19 @@
 2308 https://twitter.com/NatGeoMagArab/status/1309938472065486848 </t>
         </is>
       </c>
-      <c r="B645" t="inlineStr">
+      <c r="B644" t="inlineStr">
         <is>
           <t>images/「このパンダは私たちに、幸せは単純なこ.png</t>
         </is>
       </c>
-      <c r="C645" t="inlineStr">
+      <c r="C644" t="inlineStr">
         <is>
           <t>パンダ ,雪</t>
         </is>
       </c>
     </row>
-    <row r="646">
-      <c r="A646" t="inlineStr">
+    <row r="645">
+      <c r="A645" t="inlineStr">
         <is>
           <t xml:space="preserve">「良い時間は速く過ぎる」
 الأوقات الجميلة تمر بسرعة
@@ -14027,19 +14006,19 @@
 1810 Nasser.Tumblr </t>
         </is>
       </c>
-      <c r="B646" t="inlineStr">
+      <c r="B645" t="inlineStr">
         <is>
           <t>images/「良い時間は速く過ぎる」_img1.jpg</t>
         </is>
       </c>
-      <c r="C646" t="inlineStr">
+      <c r="C645" t="inlineStr">
         <is>
           <t>相対論 ,心理学</t>
         </is>
       </c>
     </row>
-    <row r="647">
-      <c r="A647" t="inlineStr">
+    <row r="646">
+      <c r="A646" t="inlineStr">
         <is>
           <t xml:space="preserve">「今日が始まりかもしれない」
 كل يوم ممكن يكون بداية
@@ -14049,19 +14028,19 @@
 2308 Ahmed Madyan </t>
         </is>
       </c>
-      <c r="B647" t="inlineStr">
+      <c r="B646" t="inlineStr">
         <is>
           <t>images/「今日が始まりかもしれない」_img1.jpg</t>
         </is>
       </c>
-      <c r="C647" t="inlineStr">
+      <c r="C646" t="inlineStr">
         <is>
           <t>吉日 ,開始</t>
         </is>
       </c>
     </row>
-    <row r="648">
-      <c r="A648" t="inlineStr">
+    <row r="647">
+      <c r="A647" t="inlineStr">
         <is>
           <t xml:space="preserve">「ヌール、歯医者さんに行く」
 نور تذهب إلى طبيب الأسنان
@@ -14071,19 +14050,19 @@
 2109 RABIE </t>
         </is>
       </c>
-      <c r="B648" t="inlineStr">
+      <c r="B647" t="inlineStr">
         <is>
           <t>images/「ヌール、歯医者さんに行く」_img1.jpg</t>
         </is>
       </c>
-      <c r="C648" t="inlineStr">
+      <c r="C647" t="inlineStr">
         <is>
           <t>絵本 ,歯科</t>
         </is>
       </c>
     </row>
-    <row r="649">
-      <c r="A649" t="inlineStr">
+    <row r="648">
+      <c r="A648" t="inlineStr">
         <is>
           <t xml:space="preserve">「ラヤンはねむれない」
 لَيان لا تَسْتَطيعُ أَنْ تَنام
@@ -14092,19 +14071,19 @@
 2308 出典不明 </t>
         </is>
       </c>
-      <c r="B649" t="inlineStr">
+      <c r="B648" t="inlineStr">
         <is>
           <t>images/「ラヤンはねむれない」_img1.jpg</t>
         </is>
       </c>
-      <c r="C649" t="inlineStr">
+      <c r="C648" t="inlineStr">
         <is>
           <t>絵本 ,不眠症</t>
         </is>
       </c>
     </row>
-    <row r="650">
-      <c r="A650" t="inlineStr">
+    <row r="649">
+      <c r="A649" t="inlineStr">
         <is>
           <t xml:space="preserve">「クネイトラ県、蜂の巣を約60%失う」
 القنيطرة تفقد حوالي 60 % من خلايا نحلها
@@ -14112,19 +14091,19 @@
 2403 nabd com/t/101679025-fb119f </t>
         </is>
       </c>
-      <c r="B650" t="inlineStr">
+      <c r="B649" t="inlineStr">
         <is>
           <t>images/「クネイトラ県、蜂の巣を約60%失う」_img1.jpg</t>
         </is>
       </c>
-      <c r="C650" t="inlineStr">
+      <c r="C649" t="inlineStr">
         <is>
           <t>蜂の巣 ,パーセント</t>
         </is>
       </c>
     </row>
-    <row r="651">
-      <c r="A651" t="inlineStr">
+    <row r="650">
+      <c r="A650" t="inlineStr">
         <is>
           <t xml:space="preserve">「結ばれしター」ة
 ⁦( تاء مربوطة )[taa' marbuu_ta]：ت「ター」( تاء )[taa']・「結ばれている」( مربوط )[marbuu_t]：( ربط )【結】⁩
@@ -14132,19 +14111,19 @@
 2308 出典不明 </t>
         </is>
       </c>
-      <c r="B651" t="inlineStr">
+      <c r="B650" t="inlineStr">
         <is>
           <t>images/「結ばれしター」_img1.jpg</t>
         </is>
       </c>
-      <c r="C651" t="inlineStr">
+      <c r="C650" t="inlineStr">
         <is>
           <t>アラビア文字 ,顔</t>
         </is>
       </c>
     </row>
-    <row r="652">
-      <c r="A652" t="inlineStr">
+    <row r="651">
+      <c r="A651" t="inlineStr">
         <is>
           <t xml:space="preserve">「忙しい」مشغول
 マシュグール [maShGhuul]
@@ -14153,19 +14132,19 @@
 1811 skyshinichi.instagram </t>
         </is>
       </c>
-      <c r="B652" t="inlineStr">
+      <c r="B651" t="inlineStr">
         <is>
           <t>images/「忙しい」_img1.jpg</t>
         </is>
       </c>
-      <c r="C652" t="inlineStr">
+      <c r="C651" t="inlineStr">
         <is>
           <t>スティッチ ,残業</t>
         </is>
       </c>
     </row>
-    <row r="653">
-      <c r="A653" t="inlineStr">
+    <row r="652">
+      <c r="A652" t="inlineStr">
         <is>
           <t xml:space="preserve">「駐車禁止」ممنوع الوقوف
 マムヌーア・アルウクーフ [mamnuu* al-wuquuf]
@@ -14174,19 +14153,19 @@
 2106 出典不明 </t>
         </is>
       </c>
-      <c r="B653" t="inlineStr">
+      <c r="B652" t="inlineStr">
         <is>
           <t>images/「駐車禁止」_img1.jpg</t>
         </is>
       </c>
-      <c r="C653" t="inlineStr">
+      <c r="C652" t="inlineStr">
         <is>
           <t>標識 ,ジョーク</t>
         </is>
       </c>
     </row>
-    <row r="654">
-      <c r="A654" t="inlineStr">
+    <row r="653">
+      <c r="A653" t="inlineStr">
         <is>
           <t xml:space="preserve">「一人ひとりが責任を」
 كُلنا مسؤول
@@ -14196,19 +14175,19 @@
 2308 covid19awareness sa </t>
         </is>
       </c>
-      <c r="B654" t="inlineStr">
+      <c r="B653" t="inlineStr">
         <is>
           <t>images/「一人ひとりが責任を」_img1.jpg</t>
         </is>
       </c>
-      <c r="C654" t="inlineStr">
+      <c r="C653" t="inlineStr">
         <is>
           <t>Covid ,感染拡大防止</t>
         </is>
       </c>
     </row>
-    <row r="655">
-      <c r="A655" t="inlineStr">
+    <row r="654">
+      <c r="A654" t="inlineStr">
         <is>
           <t xml:space="preserve">「おめでとうございます」مبروك
 マブルーク [mabruuk]
@@ -14217,19 +14196,19 @@
 2308 </t>
         </is>
       </c>
-      <c r="B655" t="inlineStr">
+      <c r="B654" t="inlineStr">
         <is>
           <t>images/「おめでとうございます」_img1.jpg</t>
         </is>
       </c>
-      <c r="C655" t="inlineStr">
+      <c r="C654" t="inlineStr">
         <is>
           <t>詐欺 ,広告</t>
         </is>
       </c>
     </row>
-    <row r="656">
-      <c r="A656" t="inlineStr">
+    <row r="655">
+      <c r="A655" t="inlineStr">
         <is>
           <t xml:space="preserve">「手書きフォント」
 خط مكتوب باليد
@@ -14239,19 +14218,19 @@
 1809 FahdAlFraikh Behance </t>
         </is>
       </c>
-      <c r="B656" t="inlineStr">
+      <c r="B655" t="inlineStr">
         <is>
           <t>images/「手書きフォント」_img1.jpg</t>
         </is>
       </c>
-      <c r="C656" t="inlineStr">
+      <c r="C655" t="inlineStr">
         <is>
           <t>可愛いフォント ,筆跡</t>
         </is>
       </c>
     </row>
-    <row r="657">
-      <c r="A657" t="inlineStr">
+    <row r="656">
+      <c r="A656" t="inlineStr">
         <is>
           <t xml:space="preserve">「開かれたターと結ばれたター」
 التاء المفتوحة والمربوطة
@@ -14261,19 +14240,19 @@
 2109 slideshare.net </t>
         </is>
       </c>
-      <c r="B657" t="inlineStr">
+      <c r="B656" t="inlineStr">
         <is>
           <t>images/「開かれたターと結ばれたター」_img1.jpg</t>
         </is>
       </c>
-      <c r="C657" t="inlineStr">
+      <c r="C656" t="inlineStr">
         <is>
           <t>アラビア文字 ,スマイリー</t>
         </is>
       </c>
     </row>
-    <row r="658">
-      <c r="A658" t="inlineStr">
+    <row r="657">
+      <c r="A657" t="inlineStr">
         <is>
           <t xml:space="preserve">「このラマは誇らしげにして立っている」
 تقف هذه اللاما مزهوة بنفسها
@@ -14281,19 +14260,19 @@
 2410 https://twitter.com/NatGeoMagArab/status/1597485552965935104 </t>
         </is>
       </c>
-      <c r="B658" t="inlineStr">
+      <c r="B657" t="inlineStr">
         <is>
           <t>images/「このラマは誇らしげにして立っている」_img1.jpg</t>
         </is>
       </c>
-      <c r="C658" t="inlineStr">
+      <c r="C657" t="inlineStr">
         <is>
           <t>手書き語学 ,アラビア語 ,マチュピチュ遺跡</t>
         </is>
       </c>
     </row>
-    <row r="659">
-      <c r="A659" t="inlineStr">
+    <row r="658">
+      <c r="A658" t="inlineStr">
         <is>
           <t xml:space="preserve">「小さな生き物にしては危険な名前だ」
 اسم خطير لمخلوق صغير
@@ -14302,19 +14281,19 @@
 2308 https://twitter.com/NatGeoMagArab/status/1495035772071669760 </t>
         </is>
       </c>
-      <c r="B659" t="inlineStr">
+      <c r="B658" t="inlineStr">
         <is>
           <t>images/「小さな生き物にしては危険な名前だ」_img1.jpg</t>
         </is>
       </c>
-      <c r="C659" t="inlineStr">
+      <c r="C658" t="inlineStr">
         <is>
           <t>有袋類 ,タスマニアデビル</t>
         </is>
       </c>
     </row>
-    <row r="660">
-      <c r="A660" t="inlineStr">
+    <row r="659">
+      <c r="A659" t="inlineStr">
         <is>
           <t xml:space="preserve">「こわれている」مكسر
 ムカッサル [mukassar]
@@ -14322,19 +14301,19 @@
 2105 behance Written-Visuals </t>
         </is>
       </c>
-      <c r="B660" t="inlineStr">
+      <c r="B659" t="inlineStr">
         <is>
           <t>images/「こわれている」_img1.jpg</t>
         </is>
       </c>
-      <c r="C660" t="inlineStr">
+      <c r="C659" t="inlineStr">
         <is>
           <t>バラバラ ,デザイン</t>
         </is>
       </c>
     </row>
-    <row r="661">
-      <c r="A661" t="inlineStr">
+    <row r="660">
+      <c r="A660" t="inlineStr">
         <is>
           <t xml:space="preserve">「早起きする方法」
 كيف تنهض مُبكّرًا
@@ -14344,19 +14323,19 @@
 2308 Funders and Founders </t>
         </is>
       </c>
-      <c r="B661" t="inlineStr">
+      <c r="B660" t="inlineStr">
         <is>
           <t>images/「早起きする方法」_img1.jpg</t>
         </is>
       </c>
-      <c r="C661" t="inlineStr">
+      <c r="C660" t="inlineStr">
         <is>
           <t>オフトゥン ,寝起き</t>
         </is>
       </c>
     </row>
-    <row r="662">
-      <c r="A662" t="inlineStr">
+    <row r="661">
+      <c r="A661" t="inlineStr">
         <is>
           <t xml:space="preserve">「アラブ・デザイン文字展覧会」
 معرض لتخطيط الحرف العربي
@@ -14366,19 +14345,19 @@
 2109 arabic lettering exhibition </t>
         </is>
       </c>
-      <c r="B662" t="inlineStr">
+      <c r="B661" t="inlineStr">
         <is>
           <t>images/「アラブ・デザイン文字展覧会」_img1.jpg</t>
         </is>
       </c>
-      <c r="C662" t="inlineStr">
+      <c r="C661" t="inlineStr">
         <is>
           <t>ポスター</t>
         </is>
       </c>
     </row>
-    <row r="663">
-      <c r="A663" t="inlineStr">
+    <row r="662">
+      <c r="A662" t="inlineStr">
         <is>
           <t xml:space="preserve">「名探偵コナン」المحقق كونان
 アルムハッキク・コナン [al-muHaqqiq Conan]
@@ -14387,19 +14366,19 @@
 1809 wikipedia </t>
         </is>
       </c>
-      <c r="B663" t="inlineStr">
+      <c r="B662" t="inlineStr">
         <is>
           <t>images/「名探偵コナン」_img1.jpg</t>
         </is>
       </c>
-      <c r="C663" t="inlineStr">
+      <c r="C662" t="inlineStr">
         <is>
           <t>江戸川コナン ,ロゴ</t>
         </is>
       </c>
     </row>
-    <row r="664">
-      <c r="A664" t="inlineStr">
+    <row r="663">
+      <c r="A663" t="inlineStr">
         <is>
           <t xml:space="preserve">「イードおめでとう」عيد مبارك
 イード・ムバーラク [*iid mubaarak]
@@ -14407,19 +14386,19 @@
 2308 出典不明 </t>
         </is>
       </c>
-      <c r="B664" t="inlineStr">
+      <c r="B663" t="inlineStr">
         <is>
           <t>images/「イードおめでとう」_img1.jpg</t>
         </is>
       </c>
-      <c r="C664" t="inlineStr">
+      <c r="C663" t="inlineStr">
         <is>
           <t>عيد ,アラビア語</t>
         </is>
       </c>
     </row>
-    <row r="665">
-      <c r="A665" t="inlineStr">
+    <row r="664">
+      <c r="A664" t="inlineStr">
         <is>
           <t xml:space="preserve">「戦士」محارب
 ムハーリブ [muHaarib]
@@ -14428,19 +14407,19 @@
 1809 abudinges.tumblr </t>
         </is>
       </c>
-      <c r="B665" t="inlineStr">
+      <c r="B664" t="inlineStr">
         <is>
           <t>images/「戦士」_img1.jpg</t>
         </is>
       </c>
-      <c r="C665" t="inlineStr">
+      <c r="C664" t="inlineStr">
         <is>
           <t>ロゴ ,赤</t>
         </is>
       </c>
     </row>
-    <row r="666">
-      <c r="A666" t="inlineStr">
+    <row r="665">
+      <c r="A665" t="inlineStr">
         <is>
           <t xml:space="preserve">「ライブ」بث مباشر
 バッス・ムバーシル [ba^Th(un) mubaaShir(un)]
@@ -14449,19 +14428,19 @@
 2308 beIN SPORTS </t>
         </is>
       </c>
-      <c r="B666" t="inlineStr">
+      <c r="B665" t="inlineStr">
         <is>
           <t>images/「ライブ」_img1.jpg</t>
         </is>
       </c>
-      <c r="C666" t="inlineStr">
+      <c r="C665" t="inlineStr">
         <is>
           <t xml:space="preserve">生放送 ,試合 </t>
         </is>
       </c>
     </row>
-    <row r="667">
-      <c r="A667" t="inlineStr">
+    <row r="666">
+      <c r="A666" t="inlineStr">
         <is>
           <t xml:space="preserve">「信者」مُؤْمِنٌ
 ムッミン [mu'min(un)]
@@ -14470,19 +14449,19 @@
 2106 出典不明 </t>
         </is>
       </c>
-      <c r="B667" t="inlineStr">
+      <c r="B666" t="inlineStr">
         <is>
           <t>images/「信者」_img1.jpg</t>
         </is>
       </c>
-      <c r="C667" t="inlineStr">
+      <c r="C666" t="inlineStr">
         <is>
           <t>明暗 ,信仰</t>
         </is>
       </c>
     </row>
-    <row r="668">
-      <c r="A668" t="inlineStr">
+    <row r="667">
+      <c r="A667" t="inlineStr">
         <is>
           <t xml:space="preserve">「開⇔閉」
 مفتوح
@@ -14493,19 +14472,19 @@
 2312 Hussein Safina, behance </t>
         </is>
       </c>
-      <c r="B668" t="inlineStr">
+      <c r="B667" t="inlineStr">
         <is>
           <t>images/「開⇔閉」_img1.jpg</t>
         </is>
       </c>
-      <c r="C668" t="inlineStr">
+      <c r="C667" t="inlineStr">
         <is>
           <t>オープンマインド ,トグル</t>
         </is>
       </c>
     </row>
-    <row r="669">
-      <c r="A669" t="inlineStr">
+    <row r="668">
+      <c r="A668" t="inlineStr">
         <is>
           <t xml:space="preserve">「予想外な結末！」
 نهاية غير متوقعة
@@ -14513,19 +14492,19 @@
 2308 https://twitter.com/NatGeoMagArab/status/1159011433444593665 </t>
         </is>
       </c>
-      <c r="B669" t="inlineStr">
+      <c r="B668" t="inlineStr">
         <is>
           <t>images/「予想外な結末！」_img1.jpg</t>
         </is>
       </c>
-      <c r="C669" t="inlineStr">
+      <c r="C668" t="inlineStr">
         <is>
           <t>手書き語学 ,アラビア語 ,ウサギ</t>
         </is>
       </c>
     </row>
-    <row r="670">
-      <c r="A670" t="inlineStr">
+    <row r="669">
+      <c r="A669" t="inlineStr">
         <is>
           <t xml:space="preserve">「ベイルート・アニメイテッド」
 بیروت متحرّکة
@@ -14535,19 +14514,19 @@
 2308 arabic_script Instagram </t>
         </is>
       </c>
-      <c r="B670" t="inlineStr">
+      <c r="B669" t="inlineStr">
         <is>
           <t>images/「ベイルート・アニメイテッド」_img1.jpg</t>
         </is>
       </c>
-      <c r="C670" t="inlineStr">
+      <c r="C669" t="inlineStr">
         <is>
           <t>アニメ ,レバノン</t>
         </is>
       </c>
     </row>
-    <row r="671">
-      <c r="A671" t="inlineStr">
+    <row r="670">
+      <c r="A670" t="inlineStr">
         <is>
           <t xml:space="preserve">「夢みれば叶う」
 كُلُّ مُتَوَقَّعٍ آتٍ
@@ -14557,19 +14536,19 @@
 2108 Ahmed Madyan </t>
         </is>
       </c>
-      <c r="B671" t="inlineStr">
+      <c r="B670" t="inlineStr">
         <is>
           <t>images/「夢みれば叶う」_img1.jpg</t>
         </is>
       </c>
-      <c r="C671" t="inlineStr">
+      <c r="C670" t="inlineStr">
         <is>
           <t>希望 ,ドリカム</t>
         </is>
       </c>
     </row>
-    <row r="672">
-      <c r="A672" t="inlineStr">
+    <row r="671">
+      <c r="A671" t="inlineStr">
         <is>
           <t xml:space="preserve">「もし両者が人間のように鎧で武装して戦いに突入したら」
 لو خاضا معاركهما متسلحين بالدروع على غرار البش
@@ -14577,19 +14556,19 @@
 2404 https://x.com/NatGeoMagArab/status/1759284149456945464 </t>
         </is>
       </c>
-      <c r="B672" t="inlineStr">
+      <c r="B671" t="inlineStr">
         <is>
           <t>images/「もし両者が人間のように鎧で武装して戦_img1.jpg,images/「もし両者が人間のように鎧で武装して戦_img2.jpg</t>
         </is>
       </c>
-      <c r="C672" t="inlineStr">
+      <c r="C671" t="inlineStr">
         <is>
           <t>手書き語学 ,アラビア語 ,猫</t>
         </is>
       </c>
     </row>
-    <row r="673">
-      <c r="A673" t="inlineStr">
+    <row r="672">
+      <c r="A672" t="inlineStr">
         <is>
           <t xml:space="preserve">「全ては結びついている」
 كل شيء مترابط
@@ -14599,19 +14578,19 @@
 2308 Ahmed Madyan https://twitter.com/madyco22/status/1451990828298166273 </t>
         </is>
       </c>
-      <c r="B673" t="inlineStr">
+      <c r="B672" t="inlineStr">
         <is>
           <t>images/「全ては結びついている」_img1.jpg</t>
         </is>
       </c>
-      <c r="C673" t="inlineStr">
+      <c r="C672" t="inlineStr">
         <is>
           <t>一筆書き ,デザイン</t>
         </is>
       </c>
     </row>
-    <row r="674">
-      <c r="A674" t="inlineStr">
+    <row r="673">
+      <c r="A673" t="inlineStr">
         <is>
           <t xml:space="preserve">「初心者のためのスケッチトレーニング」
 تعليم الرسم للمبتدئين
@@ -14621,19 +14600,19 @@
 2308 free-bookspdf com </t>
         </is>
       </c>
-      <c r="B674" t="inlineStr">
+      <c r="B673" t="inlineStr">
         <is>
           <t>images/「初心者のためのスケッチトレーニング」_img1.jpg</t>
         </is>
       </c>
-      <c r="C674" t="inlineStr">
+      <c r="C673" t="inlineStr">
         <is>
           <t>イラスト ,絵</t>
         </is>
       </c>
     </row>
-    <row r="675">
-      <c r="A675" t="inlineStr">
+    <row r="674">
+      <c r="A674" t="inlineStr">
         <is>
           <t xml:space="preserve">「初心者のためのスルス体書道トレーニング」
 تعليم خط الثلث للمبتدئين
@@ -14643,19 +14622,19 @@
 2308 出典不明 </t>
         </is>
       </c>
-      <c r="B675" t="inlineStr">
+      <c r="B674" t="inlineStr">
         <is>
           <t>images/「初心者のためのスルス体書道トレーニン_img1.jpg</t>
         </is>
       </c>
-      <c r="C675" t="inlineStr">
+      <c r="C674" t="inlineStr">
         <is>
           <t>書道</t>
         </is>
       </c>
     </row>
-    <row r="676">
-      <c r="A676" t="inlineStr">
+    <row r="675">
+      <c r="A675" t="inlineStr">
         <is>
           <t xml:space="preserve">「笑顔でいなさい」خليك مبتسم
 カッリーク・ムブタスィム [Khallii-k mubtasim]
@@ -14664,19 +14643,19 @@
 2308 https://tmblr.co/Zj9tguYLXBvC </t>
         </is>
       </c>
-      <c r="B676" t="inlineStr">
+      <c r="B675" t="inlineStr">
         <is>
           <t>images/「笑顔でいなさい」_img1.jpg</t>
         </is>
       </c>
-      <c r="C676" t="inlineStr">
+      <c r="C675" t="inlineStr">
         <is>
           <t>スマイル ,名言</t>
         </is>
       </c>
     </row>
-    <row r="677">
-      <c r="A677" t="inlineStr">
+    <row r="676">
+      <c r="A676" t="inlineStr">
         <is>
           <t xml:space="preserve">自動車メーカー
 ⁦・「TOYOTA」( تويوتا )⁩
@@ -14688,19 +14667,19 @@
 2308 syarah com </t>
         </is>
       </c>
-      <c r="B677" t="inlineStr">
+      <c r="B676" t="inlineStr">
         <is>
           <t>images/自動車メーカー_img1.jpg,images/自動車メーカー_img2.jpg,images/自動車メーカー_img3.jpg,images/自動車メーカー_img4.jpg</t>
         </is>
       </c>
-      <c r="C677" t="inlineStr">
+      <c r="C676" t="inlineStr">
         <is>
           <t>日本車 ,韓国車</t>
         </is>
       </c>
     </row>
-    <row r="678">
-      <c r="A678" t="inlineStr">
+    <row r="677">
+      <c r="A677" t="inlineStr">
         <is>
           <t xml:space="preserve">「僕たちは協力して不可能を達成するよ」
 بالتعاون نحقق المحال
@@ -14710,19 +14689,19 @@
 2109 </t>
         </is>
       </c>
-      <c r="B678" t="inlineStr">
+      <c r="B677" t="inlineStr">
         <is>
           <t>images/「僕たちは協力して不可能を達成するよ」_img1.jpg</t>
         </is>
       </c>
-      <c r="C678" t="inlineStr">
+      <c r="C677" t="inlineStr">
         <is>
           <t>無理 ,ハム太郎</t>
         </is>
       </c>
     </row>
-    <row r="679">
-      <c r="A679" t="inlineStr">
+    <row r="678">
+      <c r="A678" t="inlineStr">
         <is>
           <t xml:space="preserve">「幸せは伝染性。喜びを広めよう」
 السعادة معدية فأشع الفرح
@@ -14732,19 +14711,19 @@
 2511 instagram　com/p/fVEfxEo7Va/ </t>
         </is>
       </c>
-      <c r="B679" t="inlineStr">
+      <c r="B678" t="inlineStr">
         <is>
           <t>images/「幸せは伝染性。喜びを広めよう」_img1.jpg</t>
         </is>
       </c>
-      <c r="C679" t="inlineStr">
+      <c r="C678" t="inlineStr">
         <is>
           <t>拡散希望</t>
         </is>
       </c>
     </row>
-    <row r="680">
-      <c r="A680" t="inlineStr">
+    <row r="679">
+      <c r="A679" t="inlineStr">
         <is>
           <t xml:space="preserve">「ストレスは人間だけのものではない」
 الشعور بالتوتر ليس حكرًا على البشر
@@ -14752,19 +14731,19 @@
 2408 https://x.com/NatGeoMagArab/status/1736755816911487420 </t>
         </is>
       </c>
-      <c r="B680" t="inlineStr">
+      <c r="B679" t="inlineStr">
         <is>
           <t>images/「ストレスは人間だけのものではない」_img1.jpg</t>
         </is>
       </c>
-      <c r="C680" t="inlineStr">
+      <c r="C679" t="inlineStr">
         <is>
           <t>手書き語学 ,アラビア語 ,ストレス</t>
         </is>
       </c>
     </row>
-    <row r="681">
-      <c r="A681" t="inlineStr">
+    <row r="680">
+      <c r="A680" t="inlineStr">
         <is>
           <t xml:space="preserve">「私達は出来ます！」
 نستطيع فعلها
@@ -14774,19 +14753,19 @@
 2308 NAHARBAHIJ com </t>
         </is>
       </c>
-      <c r="B681" t="inlineStr">
+      <c r="B680" t="inlineStr">
         <is>
           <t>images/「私達は出来ます！」_img1.jpg</t>
         </is>
       </c>
-      <c r="C681" t="inlineStr">
+      <c r="C680" t="inlineStr">
         <is>
           <t>女性 ,パロディ</t>
         </is>
       </c>
     </row>
-    <row r="682">
-      <c r="A682" t="inlineStr">
+    <row r="681">
+      <c r="A681" t="inlineStr">
         <is>
           <t xml:space="preserve">「全然分からん」ولا فاهم إشي
 ウラー・ファーヒム・イシ [w-laa faahim 'iShy]
@@ -14796,19 +14775,19 @@
 2209 出典不明 </t>
         </is>
       </c>
-      <c r="B682" t="inlineStr">
+      <c r="B681" t="inlineStr">
         <is>
           <t>images/「全然分からん」_img1.jpg</t>
         </is>
       </c>
-      <c r="C682" t="inlineStr">
+      <c r="C681" t="inlineStr">
         <is>
           <t>アラビア語</t>
         </is>
       </c>
     </row>
-    <row r="683">
-      <c r="A683" t="inlineStr">
+    <row r="682">
+      <c r="A682" t="inlineStr">
         <is>
           <t xml:space="preserve">「人間は一人ひとり、特別な才がある。だから自分を他人と比べるのはやめよう」
 لكل إنسان مواهبه الخاصة 
@@ -14817,19 +14796,19 @@
 1812 Gwid3 </t>
         </is>
       </c>
-      <c r="B683" t="inlineStr">
+      <c r="B682" t="inlineStr">
         <is>
           <t>images/「人間は一人ひとり、特別な才がある。だ_img1.jpg</t>
         </is>
       </c>
-      <c r="C683" t="inlineStr">
+      <c r="C682" t="inlineStr">
         <is>
           <t>自尊 ,プライド</t>
         </is>
       </c>
     </row>
-    <row r="684">
-      <c r="A684" t="inlineStr">
+    <row r="683">
+      <c r="A683" t="inlineStr">
         <is>
           <t xml:space="preserve">「この猫は食事をシェアするのが嫌い！」
 هذه القطة لا تحب مشاركة الطعام
@@ -14838,19 +14817,19 @@
 2605 facebook com/alahram/videos/2154923608133231/ </t>
         </is>
       </c>
-      <c r="B684" t="inlineStr">
+      <c r="B683" t="inlineStr">
         <is>
           <t>images/「この猫は食事をシェアするのが嫌い！」_img1.jpg</t>
         </is>
       </c>
-      <c r="C684" t="inlineStr">
+      <c r="C683" t="inlineStr">
         <is>
           <t>猫 ,ネコ</t>
         </is>
       </c>
     </row>
-    <row r="685">
-      <c r="A685" t="inlineStr">
+    <row r="684">
+      <c r="A684" t="inlineStr">
         <is>
           <t xml:space="preserve">「怪獣との戦いでは自分が怪獣化せぬよう警戒しなさい」
 احذر عند محاربة الوحوش ألا تصبح واحدا منهم
@@ -14860,19 +14839,19 @@
 2108 warag-3nb.tumblr </t>
         </is>
       </c>
-      <c r="B685" t="inlineStr">
+      <c r="B684" t="inlineStr">
         <is>
           <t>images/「怪獣との戦いでは自分が怪獣化せぬよう_img1.jpg,images/ 「怪獣との戦いでは自分が怪獣化せぬよう_img2.jpg</t>
         </is>
       </c>
-      <c r="C685" t="inlineStr">
+      <c r="C684" t="inlineStr">
         <is>
           <t>正気 ,モンスター</t>
         </is>
       </c>
     </row>
-    <row r="686">
-      <c r="A686" t="inlineStr">
+    <row r="685">
+      <c r="A685" t="inlineStr">
         <is>
           <t xml:space="preserve">「錯視アート」فن الخداع البصري
 ファンヌ_ルヒダーイ_ルバサリーイ [fannu l-Khidaa*i l-ba_sariyy]
@@ -14881,19 +14860,19 @@
 2409 https://online.pubhtml5.com/idtb/neft/ </t>
         </is>
       </c>
-      <c r="B686" t="inlineStr">
+      <c r="B685" t="inlineStr">
         <is>
           <t>images/「錯視アート」_img1.jpg</t>
         </is>
       </c>
-      <c r="C686" t="inlineStr">
+      <c r="C685" t="inlineStr">
         <is>
           <t>トリックアート</t>
         </is>
       </c>
     </row>
-    <row r="687">
-      <c r="A687" t="inlineStr">
+    <row r="686">
+      <c r="A686" t="inlineStr">
         <is>
           <t xml:space="preserve">「自然界の消防士の訓練」
 تدريبات رجال الإطفاء في الطبيعة
@@ -14901,19 +14880,19 @@
 2308 https://twitter.com/NatGeoMagArab/status/1462420543890608129 </t>
         </is>
       </c>
-      <c r="B687" t="inlineStr">
+      <c r="B686" t="inlineStr">
         <is>
           <t>images/「自然界の消防士の訓練」_img1.jpg,images/ 「自然界の消防士の訓練」_img2.jpg</t>
         </is>
       </c>
-      <c r="C687" t="inlineStr">
+      <c r="C686" t="inlineStr">
         <is>
           <t>手書き語学 ,アラビア語 ,ヒグマ</t>
         </is>
       </c>
     </row>
-    <row r="688">
-      <c r="A688" t="inlineStr">
+    <row r="687">
+      <c r="A687" t="inlineStr">
         <is>
           <t xml:space="preserve">「救助」إسعاف
 イスアーフ ['is*aaf]
@@ -14922,19 +14901,19 @@
 2109 ambulance gov ae </t>
         </is>
       </c>
-      <c r="B688" t="inlineStr">
+      <c r="B687" t="inlineStr">
         <is>
           <t>images/「救助」_img1.jpg</t>
         </is>
       </c>
-      <c r="C688" t="inlineStr">
+      <c r="C687" t="inlineStr">
         <is>
           <t>救急車 ,はたらくくるま</t>
         </is>
       </c>
     </row>
-    <row r="689">
-      <c r="A689" t="inlineStr">
+    <row r="688">
+      <c r="A688" t="inlineStr">
         <is>
           <t xml:space="preserve">「感情／感覚」الإحْسَاسْ
 アルイヒサース [al-'iHsaas]
@@ -14943,19 +14922,19 @@
 2308 iN49R </t>
         </is>
       </c>
-      <c r="B689" t="inlineStr">
+      <c r="B688" t="inlineStr">
         <is>
           <t>images/「感情／感覚」_img1.jpg</t>
         </is>
       </c>
-      <c r="C689" t="inlineStr">
+      <c r="C688" t="inlineStr">
         <is>
           <t>オフ ,一休み</t>
         </is>
       </c>
     </row>
-    <row r="690">
-      <c r="A690" t="inlineStr">
+    <row r="689">
+      <c r="A689" t="inlineStr">
         <is>
           <t xml:space="preserve">「ひらめき」إلهام
 イルハーム ['lhaam]
@@ -14967,19 +14946,19 @@
 2103 出典不明 </t>
         </is>
       </c>
-      <c r="B690" t="inlineStr">
+      <c r="B689" t="inlineStr">
         <is>
           <t>images/「ひらめき」_img1.jpg</t>
         </is>
       </c>
-      <c r="C690" t="inlineStr">
+      <c r="C689" t="inlineStr">
         <is>
           <t>アラビア語</t>
         </is>
       </c>
     </row>
-    <row r="691">
-      <c r="A691" t="inlineStr">
+    <row r="690">
+      <c r="A690" t="inlineStr">
         <is>
           <t xml:space="preserve">「Ibdaa／クリエイティビティ」
 إبداع
@@ -14988,19 +14967,19 @@
 2308 Ibdaa Design &amp; Decoration Office </t>
         </is>
       </c>
-      <c r="B691" t="inlineStr">
+      <c r="B690" t="inlineStr">
         <is>
           <t>images/「Ibdaa／クリエイティビティ」_img1.jpg</t>
         </is>
       </c>
-      <c r="C691" t="inlineStr">
+      <c r="C690" t="inlineStr">
         <is>
           <t>創造性 ,独自性</t>
         </is>
       </c>
     </row>
-    <row r="692">
-      <c r="A692" t="inlineStr">
+    <row r="691">
+      <c r="A691" t="inlineStr">
         <is>
           <t xml:space="preserve">「奮闘なくして進歩なし」
 بدون كفاح لايوجد تقدم
@@ -15010,19 +14989,19 @@
 2105 ROUYMS TUMBLR COM </t>
         </is>
       </c>
-      <c r="B692" t="inlineStr">
+      <c r="B691" t="inlineStr">
         <is>
           <t>images/「奮闘なくして進歩なし」_img1.jpg</t>
         </is>
       </c>
-      <c r="C692" t="inlineStr">
+      <c r="C691" t="inlineStr">
         <is>
           <t>努力 ,三角形</t>
         </is>
       </c>
     </row>
-    <row r="693">
-      <c r="A693" t="inlineStr">
+    <row r="692">
+      <c r="A692" t="inlineStr">
         <is>
           <t xml:space="preserve">「木に登れば熊の危険を避けられるとお考えなら、考え直しましょう！」 
 إن اعتقدت أنك بمنأى عن خطر الدب عند تسلق الأشجار.. راجع حساباتك
@@ -15030,19 +15009,19 @@
 2202 NatGeoMagArab </t>
         </is>
       </c>
-      <c r="B693" t="inlineStr">
+      <c r="B692" t="inlineStr">
         <is>
           <t>images/「木に登れば熊の危険を避けられるとお考.jpeg</t>
         </is>
       </c>
-      <c r="C693" t="inlineStr">
+      <c r="C692" t="inlineStr">
         <is>
           <t>クマ</t>
         </is>
       </c>
     </row>
-    <row r="694">
-      <c r="A694" t="inlineStr">
+    <row r="693">
+      <c r="A693" t="inlineStr">
         <is>
           <t xml:space="preserve">「卒業おめでとう」مبروك التخرج
 マブルーク・タカッルジ [mabruuk a^taKharruj]
@@ -15051,19 +15030,19 @@
 2308 https://instagram.com/fatoomworld </t>
         </is>
       </c>
-      <c r="B694" t="inlineStr">
+      <c r="B693" t="inlineStr">
         <is>
           <t>images/「卒業おめでとう」_img1.jpg</t>
         </is>
       </c>
-      <c r="C694" t="inlineStr">
+      <c r="C693" t="inlineStr">
         <is>
           <t>卒業 ,イラスト</t>
         </is>
       </c>
     </row>
-    <row r="695">
-      <c r="A695" t="inlineStr">
+    <row r="694">
+      <c r="A694" t="inlineStr">
         <is>
           <t xml:space="preserve">「停止距離の計算」
 حساب مسافة التوقف
@@ -15073,19 +15052,19 @@
 2109 assurance-auto-info </t>
         </is>
       </c>
-      <c r="B695" t="inlineStr">
+      <c r="B694" t="inlineStr">
         <is>
           <t>images/「停止距離の計算」_img1.jpg</t>
         </is>
       </c>
-      <c r="C695" t="inlineStr">
+      <c r="C694" t="inlineStr">
         <is>
           <t>保険 ,自動車</t>
         </is>
       </c>
     </row>
-    <row r="696">
-      <c r="A696" t="inlineStr">
+    <row r="695">
+      <c r="A695" t="inlineStr">
         <is>
           <t xml:space="preserve">「教師要らず：10日でフランス語会話」
 بدون معلم
@@ -15095,19 +15074,19 @@
 2308 englais-best com </t>
         </is>
       </c>
-      <c r="B696" t="inlineStr">
+      <c r="B695" t="inlineStr">
         <is>
           <t>images/「教師要らず：10日でフランス語会話」_img1.jpg</t>
         </is>
       </c>
-      <c r="C696" t="inlineStr">
+      <c r="C695" t="inlineStr">
         <is>
           <t>教師なし学習</t>
         </is>
       </c>
     </row>
-    <row r="697">
-      <c r="A697" t="inlineStr">
+    <row r="696">
+      <c r="A696" t="inlineStr">
         <is>
           <t xml:space="preserve">「衝突」تصادم
 タサードゥム [ta_saadum]
@@ -15116,19 +15095,19 @@
 1810 </t>
         </is>
       </c>
-      <c r="B697" t="inlineStr">
+      <c r="B696" t="inlineStr">
         <is>
           <t>images/「衝突」_img1.jpg</t>
         </is>
       </c>
-      <c r="C697" t="inlineStr">
+      <c r="C696" t="inlineStr">
         <is>
           <t>あらびあや</t>
         </is>
       </c>
     </row>
-    <row r="698">
-      <c r="A698" t="inlineStr">
+    <row r="697">
+      <c r="A697" t="inlineStr">
         <is>
           <t xml:space="preserve">「楽観主義」تَفَاؤُلٌ
 タファーウル [tafaa'ul(un)]
@@ -15137,19 +15116,19 @@
 1904 arabictypography com </t>
         </is>
       </c>
-      <c r="B698" t="inlineStr">
+      <c r="B697" t="inlineStr">
         <is>
           <t>images/「楽観主義」_img1.jpg</t>
         </is>
       </c>
-      <c r="C698" t="inlineStr">
+      <c r="C697" t="inlineStr">
         <is>
           <t>やわらか ,緑</t>
         </is>
       </c>
     </row>
-    <row r="699">
-      <c r="A699" t="inlineStr">
+    <row r="698">
+      <c r="A698" t="inlineStr">
         <is>
           <t xml:space="preserve">「シベリアジャコウジカは、絶滅の危機にあると見なされている」
 يعد "أيل المسك السيبيري" مهددًا بالانقراض
@@ -15157,19 +15136,19 @@
 2308 https://twitter.com/NatGeoMagArab/status/1320666649045790720 </t>
         </is>
       </c>
-      <c r="B699" t="inlineStr">
+      <c r="B698" t="inlineStr">
         <is>
           <t>images/「シベリアジャコウジカは、絶滅の危機に_img1.jpg,images/「シベリアジャコウジカは、絶滅の危機に_img2.jpg</t>
         </is>
       </c>
-      <c r="C699" t="inlineStr">
+      <c r="C698" t="inlineStr">
         <is>
           <t>手書き語学 ,シベリア</t>
         </is>
       </c>
     </row>
-    <row r="700">
-      <c r="A700" t="inlineStr">
+    <row r="699">
+      <c r="A699" t="inlineStr">
         <is>
           <t xml:space="preserve">「融合／折衷／フュージョン」
 انصهار
@@ -15178,38 +15157,38 @@
 1811 elmahdyart Instagram </t>
         </is>
       </c>
-      <c r="B700" t="inlineStr">
+      <c r="B699" t="inlineStr">
         <is>
           <t>images/「融合／折衷／フュージョン」_img1.jpg</t>
         </is>
       </c>
-      <c r="C700" t="inlineStr">
+      <c r="C699" t="inlineStr">
         <is>
           <t>カリグラフィー ,書道</t>
         </is>
       </c>
     </row>
-    <row r="701">
-      <c r="A701" t="inlineStr">
+    <row r="700">
+      <c r="A700" t="inlineStr">
         <is>
           <t xml:space="preserve">「この子供は、昼寝をしようとする母親を邪魔しているようだ」
 「場所はインドのトラ保護区、バンダウガル公園。トラは生態ピラミッドのトップの捕食動物だが、最もリスクの高い絶滅危惧種のひとつである」
 2308 https://twitter.com/natgeomagarab/status/1553681890665586689 </t>
         </is>
       </c>
-      <c r="B701" t="inlineStr">
+      <c r="B700" t="inlineStr">
         <is>
           <t>images/「この子供は、昼寝をしようとする母親を_img1.jpg,images/「この子供は、昼寝をしようとする母親を_img2.jpg</t>
         </is>
       </c>
-      <c r="C701" t="inlineStr">
+      <c r="C700" t="inlineStr">
         <is>
           <t>手書き語学 ,アラビア語 ,トラ</t>
         </is>
       </c>
     </row>
-    <row r="702">
-      <c r="A702" t="inlineStr">
+    <row r="701">
+      <c r="A701" t="inlineStr">
         <is>
           <t xml:space="preserve">「もし敬意が落ちたら、それと一緒に全部落ちるのだ」
 إن سقط الإحترام سقط معه كل شيء
@@ -15218,19 +15197,19 @@
 2109 出典不明 </t>
         </is>
       </c>
-      <c r="B702" t="inlineStr">
+      <c r="B701" t="inlineStr">
         <is>
           <t>images/「もし敬意が落ちたら、それと一緒に全部_img1.jpg</t>
         </is>
       </c>
-      <c r="C702" t="inlineStr">
+      <c r="C701" t="inlineStr">
         <is>
           <t>リスペクト ,落書き</t>
         </is>
       </c>
     </row>
-    <row r="703">
-      <c r="A703" t="inlineStr">
+    <row r="702">
+      <c r="A702" t="inlineStr">
         <is>
           <t xml:space="preserve">「エジプト特許庁」
 مكتب براءات الاختراع المصرى
@@ -15240,19 +15219,19 @@
 2312 </t>
         </is>
       </c>
-      <c r="B703" t="inlineStr">
+      <c r="B702" t="inlineStr">
         <is>
           <t>images/「エジプト特許庁」_img1.jpg</t>
         </is>
       </c>
-      <c r="C703" t="inlineStr">
+      <c r="C702" t="inlineStr">
         <is>
           <t>patent</t>
         </is>
       </c>
     </row>
-    <row r="704">
-      <c r="A704" t="inlineStr">
+    <row r="703">
+      <c r="A703" t="inlineStr">
         <is>
           <t xml:space="preserve">「選挙」إنتخابات
 インティカーバート [intiKhaabaat]
@@ -15261,19 +15240,19 @@
 2311 nna-leb gov lb </t>
         </is>
       </c>
-      <c r="B704" t="inlineStr">
+      <c r="B703" t="inlineStr">
         <is>
           <t>images/「選挙」_img1.jpg</t>
         </is>
       </c>
-      <c r="C704" t="inlineStr">
+      <c r="C703" t="inlineStr">
         <is>
           <t>選挙 ,投票</t>
         </is>
       </c>
     </row>
-    <row r="705">
-      <c r="A705" t="inlineStr">
+    <row r="704">
+      <c r="A704" t="inlineStr">
         <is>
           <t xml:space="preserve">「待ちぼうけ」إنتظار
 インティザール [inti_Dhaar]
@@ -15282,19 +15261,19 @@
 1809 in4sser.tumblr </t>
         </is>
       </c>
-      <c r="B705" t="inlineStr">
+      <c r="B704" t="inlineStr">
         <is>
           <t>images/「待ちぼうけ」_img1.jpg</t>
         </is>
       </c>
-      <c r="C705" t="inlineStr">
+      <c r="C704" t="inlineStr">
         <is>
           <t>遅すぎ ,辛抱</t>
         </is>
       </c>
     </row>
-    <row r="706">
-      <c r="A706" t="inlineStr">
+    <row r="705">
+      <c r="A705" t="inlineStr">
         <is>
           <t xml:space="preserve">「試験」إختبار
 イクティバール [iKhtibaar]
@@ -15303,19 +15282,19 @@
 2109 出典不明 </t>
         </is>
       </c>
-      <c r="B706" t="inlineStr">
+      <c r="B705" t="inlineStr">
         <is>
           <t>images/「試験」_img1.jpg</t>
         </is>
       </c>
-      <c r="C706" t="inlineStr">
+      <c r="C705" t="inlineStr">
         <is>
           <t>テスト ,考査</t>
         </is>
       </c>
     </row>
-    <row r="707">
-      <c r="A707" t="inlineStr">
+    <row r="706">
+      <c r="A706" t="inlineStr">
         <is>
           <t xml:space="preserve">「チャンネル登録」اشتراك
 イシティラーク [iShtiraak]
@@ -15324,19 +15303,19 @@
 2308 </t>
         </is>
       </c>
-      <c r="B707" t="inlineStr">
+      <c r="B706" t="inlineStr">
         <is>
           <t>images/「チャンネル登録」_img1.jpg</t>
         </is>
       </c>
-      <c r="C707" t="inlineStr">
+      <c r="C706" t="inlineStr">
         <is>
           <t>Subscribe ,YouTube</t>
         </is>
       </c>
     </row>
-    <row r="708">
-      <c r="A708" t="inlineStr">
+    <row r="707">
+      <c r="A707" t="inlineStr">
         <is>
           <t xml:space="preserve">「スマイル」ابتسام
 イブティサーム [ibtisaam]
@@ -15344,37 +15323,37 @@
 1903 behance Written-Visuals </t>
         </is>
       </c>
+      <c r="B707" t="inlineStr">
+        <is>
+          <t>images/「スマイル」_img1.jpg</t>
+        </is>
+      </c>
+      <c r="C707" t="inlineStr">
+        <is>
+          <t>スマイリー ,ツ</t>
+        </is>
+      </c>
+    </row>
+    <row r="708">
+      <c r="A708" t="inlineStr">
+        <is>
+          <t xml:space="preserve">「身体の一部として…」
+2308 https://twitter.com/NatGeoMagArab/status/1528292080337813504 </t>
+        </is>
+      </c>
       <c r="B708" t="inlineStr">
         <is>
-          <t>images/「スマイル」_img1.jpg</t>
+          <t>images/「身体の一部として…」_img1.jpg</t>
         </is>
       </c>
       <c r="C708" t="inlineStr">
         <is>
-          <t>スマイリー ,ツ</t>
+          <t>手書き語学 ,カンガルー</t>
         </is>
       </c>
     </row>
     <row r="709">
       <c r="A709" t="inlineStr">
-        <is>
-          <t xml:space="preserve">「身体の一部として…」
-2308 https://twitter.com/NatGeoMagArab/status/1528292080337813504 </t>
-        </is>
-      </c>
-      <c r="B709" t="inlineStr">
-        <is>
-          <t>images/「身体の一部として…」_img1.jpg</t>
-        </is>
-      </c>
-      <c r="C709" t="inlineStr">
-        <is>
-          <t>手書き語学 ,カンガルー</t>
-        </is>
-      </c>
-    </row>
-    <row r="710">
-      <c r="A710" t="inlineStr">
         <is>
           <t xml:space="preserve">「ディスカバリー」إكتشاف
 イクティシャーフ [iktiShaaf]
@@ -15382,19 +15361,19 @@
 2308 tephanegabrielli com </t>
         </is>
       </c>
-      <c r="B710" t="inlineStr">
+      <c r="B709" t="inlineStr">
         <is>
           <t>images/「ディスカバリー」_img1.jpg</t>
         </is>
       </c>
-      <c r="C710" t="inlineStr">
+      <c r="C709" t="inlineStr">
         <is>
           <t>discovery ,デザイン</t>
         </is>
       </c>
     </row>
-    <row r="711">
-      <c r="A711" t="inlineStr">
+    <row r="710">
+      <c r="A710" t="inlineStr">
         <is>
           <t xml:space="preserve">「重力波の発見は新しい窓を開いた」
 فتَح اكتشاف موجات الجاذبية نافذة جديدة
@@ -15402,19 +15381,19 @@
 2308 https://twitter.com/SciTalk2U/status/1454891943440289793 </t>
         </is>
       </c>
-      <c r="B711" t="inlineStr">
+      <c r="B710" t="inlineStr">
         <is>
           <t>images/「重力波の発見は新しい窓を開いた」_img1.jpg</t>
         </is>
       </c>
-      <c r="C711" t="inlineStr">
+      <c r="C710" t="inlineStr">
         <is>
           <t>手書き語学 ,アラビア語 ,重力波</t>
         </is>
       </c>
     </row>
-    <row r="712">
-      <c r="A712" t="inlineStr">
+    <row r="711">
+      <c r="A711" t="inlineStr">
         <is>
           <t xml:space="preserve">「微笑みに微笑み。先にした人の方が美しい」
 الإبتسامة بالإبتسامة والبادئ أجمل
@@ -15423,19 +15402,19 @@
 2104 出典不明 </t>
         </is>
       </c>
-      <c r="B712" t="inlineStr">
+      <c r="B711" t="inlineStr">
         <is>
           <t>images/「微笑みに微笑み。先にした人の方が美し_img1.jpg,images/「微笑みに微笑み。先にした人の方が美し_img2.jpg</t>
         </is>
       </c>
-      <c r="C712" t="inlineStr">
+      <c r="C711" t="inlineStr">
         <is>
           <t>スマイル ,名言</t>
         </is>
       </c>
     </row>
-    <row r="713">
-      <c r="A713" t="inlineStr">
+    <row r="712">
+      <c r="A712" t="inlineStr">
         <is>
           <t xml:space="preserve">「笑顔」ابتسامة
 イブティサーマ [ibtisaama(tun)]
@@ -15444,19 +15423,19 @@
 2308 satokomatsu, minne </t>
         </is>
       </c>
-      <c r="B713" t="inlineStr">
+      <c r="B712" t="inlineStr">
         <is>
           <t>images/「笑顔」_img1.jpg</t>
         </is>
       </c>
-      <c r="C713" t="inlineStr">
+      <c r="C712" t="inlineStr">
         <is>
           <t>スマイル ,ツ</t>
         </is>
       </c>
     </row>
-    <row r="714">
-      <c r="A714" t="inlineStr">
+    <row r="713">
+      <c r="A713" t="inlineStr">
         <is>
           <t xml:space="preserve">「信仰」ايمان
 イーマーン ['iimaan]
@@ -15465,19 +15444,19 @@
 2506 instagram com/p/6ST-WHOOkJ/ </t>
         </is>
       </c>
-      <c r="B714" t="inlineStr">
+      <c r="B713" t="inlineStr">
         <is>
           <t>images/「信仰」_img1.jpg</t>
         </is>
       </c>
-      <c r="C714" t="inlineStr">
+      <c r="C713" t="inlineStr">
         <is>
           <t>宗教 ,信念</t>
         </is>
       </c>
     </row>
-    <row r="715">
-      <c r="A715" t="inlineStr">
+    <row r="714">
+      <c r="A714" t="inlineStr">
         <is>
           <t xml:space="preserve">「放送」إذاعة
 イザーア ['iDhaa*a]
@@ -15486,19 +15465,19 @@
 2404 heemades, Instagram </t>
         </is>
       </c>
-      <c r="B715" t="inlineStr">
+      <c r="B714" t="inlineStr">
         <is>
           <t>images/「放送」_img1.jpg</t>
         </is>
       </c>
-      <c r="C715" t="inlineStr">
+      <c r="C714" t="inlineStr">
         <is>
           <t>デザイン ,ラジオ</t>
         </is>
       </c>
     </row>
-    <row r="716">
-      <c r="A716" t="inlineStr">
+    <row r="715">
+      <c r="A715" t="inlineStr">
         <is>
           <t xml:space="preserve">「かきとりのちから」
 مهاراتي الإملائية
@@ -15507,19 +15486,19 @@
 2308 iqrawaoktoub.wordpress com </t>
         </is>
       </c>
-      <c r="B716" t="inlineStr">
+      <c r="B715" t="inlineStr">
         <is>
           <t>images/「かきとりのちから」_img1.jpg</t>
         </is>
       </c>
-      <c r="C716" t="inlineStr">
+      <c r="C715" t="inlineStr">
         <is>
           <t>国語 ,教材</t>
         </is>
       </c>
     </row>
-    <row r="717">
-      <c r="A717" t="inlineStr">
+    <row r="716">
+      <c r="A716" t="inlineStr">
         <is>
           <t xml:space="preserve">「歴史を作った男たち」
 رجال صنعوا التاريخ
@@ -15529,38 +15508,38 @@
 2410 https://x.gd/Wl5rJ </t>
         </is>
       </c>
-      <c r="B717" t="inlineStr">
+      <c r="B716" t="inlineStr">
         <is>
           <t>images/「歴史を作った男たち」_img1.jpg</t>
         </is>
       </c>
-      <c r="C717" t="inlineStr">
+      <c r="C716" t="inlineStr">
         <is>
           <t>偉人</t>
         </is>
       </c>
     </row>
-    <row r="718">
-      <c r="A718" t="inlineStr">
+    <row r="717">
+      <c r="A717" t="inlineStr">
         <is>
           <t xml:space="preserve">「無限の宇宙を旅した光」
 「何百年もの末にジェイムズ・ウェッブ望遠鏡のレンズの上に落ち、我々に遠い宇宙の美しさを見せてくれる。最も純粋な形と最も素晴らしい姿で」
 2308 https://twitter.com/NatGeoMagArab/status/1557811592636485632 </t>
         </is>
       </c>
-      <c r="B718" t="inlineStr">
+      <c r="B717" t="inlineStr">
         <is>
           <t>images/「無限の宇宙を旅した光」_img1.jpg</t>
         </is>
       </c>
-      <c r="C718" t="inlineStr">
+      <c r="C717" t="inlineStr">
         <is>
           <t>手書き語学 ,宇宙</t>
         </is>
       </c>
     </row>
-    <row r="719">
-      <c r="A719" t="inlineStr">
+    <row r="718">
+      <c r="A718" t="inlineStr">
         <is>
           <t xml:space="preserve">「日本好きになり行きたくなる20項」
 عشرون شيئا يجعلك تحب اليابان وترغب في زيارتها
@@ -15569,19 +15548,19 @@
 2308 wattpad </t>
         </is>
       </c>
-      <c r="B719" t="inlineStr">
+      <c r="B718" t="inlineStr">
         <is>
           <t>images/「日本好きになり行きたくなる20項」_img1.jpg</t>
         </is>
       </c>
-      <c r="C719" t="inlineStr">
+      <c r="C718" t="inlineStr">
         <is>
           <t>اليابان ,Japan</t>
         </is>
       </c>
     </row>
-    <row r="720">
-      <c r="A720" t="inlineStr">
+    <row r="719">
+      <c r="A719" t="inlineStr">
         <is>
           <t xml:space="preserve">「ピッタリの瞬間に撮影され、ドラゴンが火を噴いているように見える」
 التُقطت في اللحظة المناسبة لتبدو مثل تنين ينفث اللهب
@@ -15589,19 +15568,19 @@
 2509 https://twitter.com/NatGeoMagArab/status/1588780660269150208 </t>
         </is>
       </c>
-      <c r="B720" t="inlineStr">
+      <c r="B719" t="inlineStr">
         <is>
           <t>images/「ピッタリの瞬間に撮影され、ドラゴンが_img1.jpg,images/ 「ピッタリの瞬間に撮影され、ドラゴンが_img2.jpg</t>
         </is>
       </c>
-      <c r="C720" t="inlineStr">
+      <c r="C719" t="inlineStr">
         <is>
           <t xml:space="preserve">ドラゴン </t>
         </is>
       </c>
     </row>
-    <row r="721">
-      <c r="A721" t="inlineStr">
+    <row r="720">
+      <c r="A720" t="inlineStr">
         <is>
           <t xml:space="preserve">「満足は不滅の宝である」
 القَناعَةُ كنز لا يَفنَى
@@ -15611,55 +15590,55 @@
 2308 kareem mrghani </t>
         </is>
       </c>
+      <c r="B720" t="inlineStr">
+        <is>
+          <t>images/「満足は不滅の宝である」_img1.jpg</t>
+        </is>
+      </c>
+      <c r="C720" t="inlineStr">
+        <is>
+          <t>幸福度</t>
+        </is>
+      </c>
+    </row>
+    <row r="721">
+      <c r="A721" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ゴシキセイガイインコ。
+2409 https://twitter.com/NatGeoMagArab/status/1600022262014676992 </t>
+        </is>
+      </c>
       <c r="B721" t="inlineStr">
         <is>
-          <t>images/「満足は不滅の宝である」_img1.jpg</t>
+          <t>images/ゴシキセイガイインコ。_img1.jpg</t>
         </is>
       </c>
       <c r="C721" t="inlineStr">
         <is>
-          <t>幸福度</t>
+          <t>手書き語学 ,アラビア語,オウム</t>
         </is>
       </c>
     </row>
     <row r="722">
       <c r="A722" t="inlineStr">
         <is>
-          <t xml:space="preserve">ゴシキセイガイインコ。
-2409 https://twitter.com/NatGeoMagArab/status/1600022262014676992 </t>
+          <t xml:space="preserve">モモンガ。
+2403 https://twitter.com/NatGeoMagArab/status/1552541872966344704 </t>
         </is>
       </c>
       <c r="B722" t="inlineStr">
         <is>
-          <t>images/ゴシキセイガイインコ。_img1.jpg</t>
+          <t>images/モモンガ。_img1.jpg,images/ モモンガ。_img2.jpg</t>
         </is>
       </c>
       <c r="C722" t="inlineStr">
         <is>
-          <t>手書き語学 ,アラビア語,オウム</t>
+          <t>手書き語学 ,アラビア語 ,モモンガ</t>
         </is>
       </c>
     </row>
     <row r="723">
       <c r="A723" t="inlineStr">
-        <is>
-          <t xml:space="preserve">モモンガ。
-2403 https://twitter.com/NatGeoMagArab/status/1552541872966344704 </t>
-        </is>
-      </c>
-      <c r="B723" t="inlineStr">
-        <is>
-          <t>images/モモンガ。_img1.jpg,images/ モモンガ。_img2.jpg</t>
-        </is>
-      </c>
-      <c r="C723" t="inlineStr">
-        <is>
-          <t>手書き語学 ,アラビア語 ,モモンガ</t>
-        </is>
-      </c>
-    </row>
-    <row r="724">
-      <c r="A724" t="inlineStr">
         <is>
           <t xml:space="preserve">「象の群れ。ドローンの音から逃げている」
 قطيع من الفيلة يفر هاربًا من صوت الدرون
@@ -15671,56 +15650,56 @@
 2009 https://twitter.com/NatGeoMagArab/status/1302970033627258881 </t>
         </is>
       </c>
+      <c r="B723" t="inlineStr">
+        <is>
+          <t>images/「象の群れ。ドローンの音から逃げている.jpg</t>
+        </is>
+      </c>
+      <c r="C723" t="inlineStr">
+        <is>
+          <t>ゾウ ,ドローン</t>
+        </is>
+      </c>
+    </row>
+    <row r="724">
+      <c r="A724" t="inlineStr">
+        <is>
+          <t xml:space="preserve">カルマン線。
+2308 https://twitter.com/NatGeoMagArab/status/1536436999522881536 </t>
+        </is>
+      </c>
       <c r="B724" t="inlineStr">
         <is>
-          <t>images/「象の群れ。ドローンの音から逃げている.jpg</t>
+          <t>images/カルマン線。_img1.jpg</t>
         </is>
       </c>
       <c r="C724" t="inlineStr">
         <is>
-          <t>ゾウ ,ドローン</t>
+          <t xml:space="preserve">手書き語学 ,アラビア語 ,宇宙 </t>
         </is>
       </c>
     </row>
     <row r="725">
       <c r="A725" t="inlineStr">
-        <is>
-          <t xml:space="preserve">カルマン線。
-2308 https://twitter.com/NatGeoMagArab/status/1536436999522881536 </t>
-        </is>
-      </c>
-      <c r="B725" t="inlineStr">
-        <is>
-          <t>images/カルマン線。_img1.jpg</t>
-        </is>
-      </c>
-      <c r="C725" t="inlineStr">
-        <is>
-          <t xml:space="preserve">手書き語学 ,アラビア語 ,宇宙 </t>
-        </is>
-      </c>
-    </row>
-    <row r="726">
-      <c r="A726" t="inlineStr">
         <is>
           <t xml:space="preserve">「恥ずかしがり屋のマヌルネコと暖かい朝の太陽光線」
 ⁦「二つの美しいもの」[Shay'-ayni jamiil-ayni] 属格：「物」( شيء )[Shay']・「美しい」( جميل )[jamiil]⁩
 2309 https://twitter.com/NatGeoMagArab/status/1697512148820504912 </t>
         </is>
       </c>
-      <c r="B726" t="inlineStr">
+      <c r="B725" t="inlineStr">
         <is>
           <t>images/「恥ずかしがり屋のマヌルネコと暖かい朝_img1.jpg</t>
         </is>
       </c>
-      <c r="C726" t="inlineStr">
+      <c r="C725" t="inlineStr">
         <is>
           <t>手書き語学 ,アラビア語 ,マヌルネコ</t>
         </is>
       </c>
     </row>
-    <row r="727">
-      <c r="A727" t="inlineStr">
+    <row r="726">
+      <c r="A726" t="inlineStr">
         <is>
           <t xml:space="preserve">「二回失敗しているペンギン」
 بطريق يفشل مرتين
@@ -15730,19 +15709,19 @@
 2308 https://twitter.com/NatGeoMagArab/status/1479483133766426626 </t>
         </is>
       </c>
-      <c r="B727" t="inlineStr">
+      <c r="B726" t="inlineStr">
         <is>
           <t>images/「二回失敗しているペンギン」_img1.jpg</t>
         </is>
       </c>
-      <c r="C727" t="inlineStr">
+      <c r="C726" t="inlineStr">
         <is>
           <t>ペンギン ,動物</t>
         </is>
       </c>
     </row>
-    <row r="728">
-      <c r="A728" t="inlineStr">
+    <row r="727">
+      <c r="A727" t="inlineStr">
         <is>
           <t xml:space="preserve">「2億光年の彼方できらめく炎と光」
 وهج ووميض يتلألأ على بعد 200 مليون سنة ضوئية
@@ -15753,15 +15732,15 @@
 2010 https://twitter.com/NatGeoMagArab/status/1303415502673342464 </t>
         </is>
       </c>
-      <c r="B728" t="inlineStr"/>
-      <c r="C728" t="inlineStr">
+      <c r="B727" t="inlineStr"/>
+      <c r="C727" t="inlineStr">
         <is>
           <t>宇宙 ,銀河</t>
         </is>
       </c>
     </row>
-    <row r="729">
-      <c r="A729" t="inlineStr">
+    <row r="728">
+      <c r="A728" t="inlineStr">
         <is>
           <t xml:space="preserve">「さまよう黒猫」قطة سوداء تجوب
 キッタトゥン・サウダーウ・タジューブ [qi^_tatun sawdaa'u ta-juub]
@@ -15770,19 +15749,19 @@
 2308 https://twitter.com/NatGeoMagArab/status/1532973177453760512 </t>
         </is>
       </c>
-      <c r="B729" t="inlineStr">
+      <c r="B728" t="inlineStr">
         <is>
           <t>images/「さまよう黒猫」_img1.jpg,images/ 「さまよう黒猫」_img2.jpg</t>
         </is>
       </c>
-      <c r="C729" t="inlineStr">
+      <c r="C728" t="inlineStr">
         <is>
           <t xml:space="preserve">手書き語学 ,モロッコ </t>
         </is>
       </c>
     </row>
-    <row r="730">
-      <c r="A730" t="inlineStr">
+    <row r="729">
+      <c r="A729" t="inlineStr">
         <is>
           <t xml:space="preserve">「サイのざらざらした皮を利用して自分の体を掻くネコ」
 قطة تستغل جلد الكركدن الخشن لحك جسدها
@@ -15791,19 +15770,19 @@
 2308 https://twitter.com/NatGeoMagArab/status/1476855740929216517 </t>
         </is>
       </c>
-      <c r="B730" t="inlineStr">
+      <c r="B729" t="inlineStr">
         <is>
           <t>images/「サイのざらざらした皮を利用して自分の_img1.jpg</t>
         </is>
       </c>
-      <c r="C730" t="inlineStr">
+      <c r="C729" t="inlineStr">
         <is>
           <t>サイ ,チェコ</t>
         </is>
       </c>
     </row>
-    <row r="731">
-      <c r="A731" t="inlineStr">
+    <row r="730">
+      <c r="A730" t="inlineStr">
         <is>
           <t xml:space="preserve">「沈まぬ太陽」شمس لا تغيب
 シャムス・ラー・タギーブ [Shams laa ta-Ghiib]
@@ -15812,19 +15791,19 @@
 2308 AHMED ELASSAL </t>
         </is>
       </c>
-      <c r="B731" t="inlineStr">
+      <c r="B730" t="inlineStr">
         <is>
           <t>images/「沈まぬ太陽」_img1.jpg</t>
         </is>
       </c>
-      <c r="C731" t="inlineStr">
+      <c r="C730" t="inlineStr">
         <is>
           <t>帝国 ,白夜</t>
         </is>
       </c>
     </row>
-    <row r="732">
-      <c r="A732" t="inlineStr">
+    <row r="731">
+      <c r="A731" t="inlineStr">
         <is>
           <t xml:space="preserve">「子供に食べさせている忍耐強い母親」
 أم صبورة تطعم صغيرها
@@ -15833,19 +15812,19 @@
 2308 https://twitter.com/natgeomagarab/status/1585572054509957120 </t>
         </is>
       </c>
-      <c r="B732" t="inlineStr">
+      <c r="B731" t="inlineStr">
         <is>
           <t>images/「子供に食べさせている忍耐強い母親」_img1.jpg</t>
         </is>
       </c>
-      <c r="C732" t="inlineStr">
+      <c r="C731" t="inlineStr">
         <is>
           <t>手書き語学 ,アラビア語 ,ミヤコドリ</t>
         </is>
       </c>
     </row>
-    <row r="733">
-      <c r="A733" t="inlineStr">
+    <row r="732">
+      <c r="A732" t="inlineStr">
         <is>
           <t xml:space="preserve">「コーヒーは繰り返さない恋物語」
 القهوة قصة عشق لن تتكرر
@@ -15855,19 +15834,19 @@
 2403 pin it/7tvd8Wc </t>
         </is>
       </c>
-      <c r="B733" t="inlineStr">
+      <c r="B732" t="inlineStr">
         <is>
           <t>images/「コーヒーは繰り返さない恋物語」_img1.jpg</t>
         </is>
       </c>
-      <c r="C733" t="inlineStr">
+      <c r="C732" t="inlineStr">
         <is>
           <t>コーヒー ,名言</t>
         </is>
       </c>
     </row>
-    <row r="734">
-      <c r="A734" t="inlineStr">
+    <row r="733">
+      <c r="A733" t="inlineStr">
         <is>
           <t xml:space="preserve">「星々で飾られた空。魅惑的な色合いで黄昏の美を満たしている」
 سماء مرصعة بالنجوم تضفي لمسة سحرية على جمال الشفق
@@ -15875,19 +15854,19 @@
 2010 https://twitter.com/NatGeoMagArab/status/1303777701975584768 </t>
         </is>
       </c>
-      <c r="B734" t="inlineStr">
+      <c r="B733" t="inlineStr">
         <is>
           <t>images/「星々で飾られた空。魅惑的な色合いで黄.png</t>
         </is>
       </c>
-      <c r="C734" t="inlineStr">
+      <c r="C733" t="inlineStr">
         <is>
           <t>星空 ,宇宙</t>
         </is>
       </c>
     </row>
-    <row r="735">
-      <c r="A735" t="inlineStr">
+    <row r="734">
+      <c r="A734" t="inlineStr">
         <is>
           <t xml:space="preserve">「国際宇宙ステーションからの写真。巨大な台風『ハイシェン（海神）』を映している」
 لقطات من محطة الفضاء الدولية تظهر إعصار "هايشن" الهائل
@@ -15895,19 +15874,19 @@
 2403 https://twitter.com/NatGeoMagArab/status/1302871968522235904 </t>
         </is>
       </c>
-      <c r="B735" t="inlineStr">
+      <c r="B734" t="inlineStr">
         <is>
           <t>images/「国際宇宙ステーションからの写真。巨大.png</t>
         </is>
       </c>
-      <c r="C735" t="inlineStr">
+      <c r="C734" t="inlineStr">
         <is>
           <t>台風</t>
         </is>
       </c>
     </row>
-    <row r="736">
-      <c r="A736" t="inlineStr">
+    <row r="735">
+      <c r="A735" t="inlineStr">
         <is>
           <t xml:space="preserve">「草を食む幸運な子羊たち」
 خراف محظوظة ترعى
@@ -15917,19 +15896,19 @@
 2308 https://twitter.com/NatGeoMagArab/status/1490211393554972676 </t>
         </is>
       </c>
-      <c r="B736" t="inlineStr">
+      <c r="B735" t="inlineStr">
         <is>
           <t>images/「草を食む幸運な子羊たち」_img1.jpg,images/ 「草を食む幸運な子羊たち」_img2.jpg</t>
         </is>
       </c>
-      <c r="C736" t="inlineStr">
+      <c r="C735" t="inlineStr">
         <is>
           <t>羊 ,アイルランド</t>
         </is>
       </c>
     </row>
-    <row r="737">
-      <c r="A737" t="inlineStr">
+    <row r="736">
+      <c r="A736" t="inlineStr">
         <is>
           <t xml:space="preserve">「お金で買えぬ10のもの」
 ١٠ أشياء لا تشترى بالمال
@@ -15939,19 +15918,19 @@
 2308 ayb124 </t>
         </is>
       </c>
-      <c r="B737" t="inlineStr">
+      <c r="B736" t="inlineStr">
         <is>
           <t>images/「お金で買えぬ10のもの」_img1.jpg</t>
         </is>
       </c>
-      <c r="C737" t="inlineStr">
+      <c r="C736" t="inlineStr">
         <is>
           <t>価値 ,購買</t>
         </is>
       </c>
     </row>
-    <row r="738">
-      <c r="A738" t="inlineStr">
+    <row r="737">
+      <c r="A737" t="inlineStr">
         <is>
           <t xml:space="preserve">「お金では買えないよ」
 هي أشْيَاءٌ لا تُشْتَرَى
@@ -15961,19 +15940,19 @@
 1906 mardy_zaawely, Instagram </t>
         </is>
       </c>
-      <c r="B738" t="inlineStr">
+      <c r="B737" t="inlineStr">
         <is>
           <t>images/「お金では買えないよ」_img1.jpg</t>
         </is>
       </c>
-      <c r="C738" t="inlineStr">
+      <c r="C737" t="inlineStr">
         <is>
           <t>マスターカード ,価値</t>
         </is>
       </c>
     </row>
-    <row r="739">
-      <c r="A739" t="inlineStr">
+    <row r="738">
+      <c r="A738" t="inlineStr">
         <is>
           <t xml:space="preserve">「好奇心旺盛なホッキョクギツネ」
 ثعلب قطبي يملؤه الفضول
@@ -15983,15 +15962,15 @@
 2308 https://twitter.com/natgeomagarab/status/1157592172968808449 </t>
         </is>
       </c>
-      <c r="B739" t="inlineStr"/>
-      <c r="C739" t="inlineStr">
+      <c r="B738" t="inlineStr"/>
+      <c r="C738" t="inlineStr">
         <is>
           <t>ファーストコンタクト ,キツネ</t>
         </is>
       </c>
     </row>
-    <row r="740">
-      <c r="A740" t="inlineStr">
+    <row r="739">
+      <c r="A739" t="inlineStr">
         <is>
           <t xml:space="preserve">「グレンダイザーのいる国は死にません」
 لنْ يَموتَ شَعبٌ لدَيهِ غرندايزر
@@ -16000,56 +15979,56 @@
 2308 https://www.aljarida.com/articles/1462241741574732100/ </t>
         </is>
       </c>
+      <c r="B739" t="inlineStr">
+        <is>
+          <t>images/「グレンダイザーのいる国は死にません」_img1.jpg</t>
+        </is>
+      </c>
+      <c r="C739" t="inlineStr">
+        <is>
+          <t>UFOロボ ,アニメ</t>
+        </is>
+      </c>
+    </row>
+    <row r="740">
+      <c r="A740" t="inlineStr">
+        <is>
+          <t xml:space="preserve">「凍結路面を運転中、彼女は嫌な場面に居合わせた」
+2408 https://twitter.com/NatGeoMagArab/status/1610305209657626625 </t>
+        </is>
+      </c>
       <c r="B740" t="inlineStr">
         <is>
-          <t>images/「グレンダイザーのいる国は死にません」_img1.jpg</t>
+          <t>images/「凍結路面を運転中、彼女は嫌な場面に居_img1.jpg</t>
         </is>
       </c>
       <c r="C740" t="inlineStr">
         <is>
-          <t>UFOロボ ,アニメ</t>
+          <t>手書き語学 ,アラビア語 ,路面凍結</t>
         </is>
       </c>
     </row>
     <row r="741">
       <c r="A741" t="inlineStr">
-        <is>
-          <t xml:space="preserve">「凍結路面を運転中、彼女は嫌な場面に居合わせた」
-2408 https://twitter.com/NatGeoMagArab/status/1610305209657626625 </t>
-        </is>
-      </c>
-      <c r="B741" t="inlineStr">
-        <is>
-          <t>images/「凍結路面を運転中、彼女は嫌な場面に居_img1.jpg</t>
-        </is>
-      </c>
-      <c r="C741" t="inlineStr">
-        <is>
-          <t>手書き語学 ,アラビア語 ,路面凍結</t>
-        </is>
-      </c>
-    </row>
-    <row r="742">
-      <c r="A742" t="inlineStr">
         <is>
           <t xml:space="preserve">「虹が美しさを加えている、アルパカという動物の美しいショット」
 ⁦「美しいショット」[laq_tatun jamiilatun]：「ショット」( لقطة )[laq_ta]：( ـلٌ )[-lun]・( ـقٌ )[-qun]・( ـطٌ )[-_tun]・( ـةٌ )[-tun]⁩
 2308 https://twitter.com/natgeomagarab/status/1155115655928004608 </t>
         </is>
       </c>
-      <c r="B742" t="inlineStr">
+      <c r="B741" t="inlineStr">
         <is>
           <t>images/「虹が美しさを加えている、アルパカとい_img1.jpg</t>
         </is>
       </c>
-      <c r="C742" t="inlineStr">
+      <c r="C741" t="inlineStr">
         <is>
           <t>モフモフ ,アルパカ</t>
         </is>
       </c>
     </row>
-    <row r="743">
-      <c r="A743" t="inlineStr">
+    <row r="742">
+      <c r="A742" t="inlineStr">
         <is>
           <t xml:space="preserve">「幸せは…全然思いもよらない所からやって来る」
 السعادة تأتينا من أماكن لم نكن نتوقعها أبداً
@@ -16058,19 +16037,19 @@
 2109 出典不明 </t>
         </is>
       </c>
-      <c r="B743" t="inlineStr">
+      <c r="B742" t="inlineStr">
         <is>
           <t>images/「幸せは…全然思いもよらない所からやっ_img1.jpg,images/ 「幸せは…全然思いもよらない所からやっ_img2.jpg</t>
         </is>
       </c>
-      <c r="C743" t="inlineStr">
+      <c r="C742" t="inlineStr">
         <is>
           <t>訪れ ,予想</t>
         </is>
       </c>
     </row>
-    <row r="744">
-      <c r="A744" t="inlineStr">
+    <row r="743">
+      <c r="A743" t="inlineStr">
         <is>
           <t xml:space="preserve">「あらゆる問題は、食べ物が解決してくれる」
 كل مشكلة ولها أكلة تحلها
@@ -16079,19 +16058,19 @@
 1909 ALQA AN 878 </t>
         </is>
       </c>
-      <c r="B744" t="inlineStr">
+      <c r="B743" t="inlineStr">
         <is>
           <t>images/「あらゆる問題は、食べ物が解決してくれ_img1.jpg</t>
         </is>
       </c>
-      <c r="C744" t="inlineStr">
+      <c r="C743" t="inlineStr">
         <is>
           <t>ストレス ,精神</t>
         </is>
       </c>
     </row>
-    <row r="745">
-      <c r="A745" t="inlineStr">
+    <row r="744">
+      <c r="A744" t="inlineStr">
         <is>
           <t xml:space="preserve">「冬で私が好きな物」
 أشياء أحبها بالشتاء
@@ -16101,19 +16080,19 @@
 2109 出典不明 </t>
         </is>
       </c>
-      <c r="B745" t="inlineStr">
+      <c r="B744" t="inlineStr">
         <is>
           <t>images/「冬で私が好きな物」_img1.jpg</t>
         </is>
       </c>
-      <c r="C745" t="inlineStr">
+      <c r="C744" t="inlineStr">
         <is>
           <t>季節 ,冬</t>
         </is>
       </c>
     </row>
-    <row r="746">
-      <c r="A746" t="inlineStr">
+    <row r="745">
+      <c r="A745" t="inlineStr">
         <is>
           <t xml:space="preserve">「お金で買うことの出来ない物」
 أشياء لا تستطيع شراءها بالمال
@@ -16123,19 +16102,19 @@
 2409 https://x.com/akhbarak/status/1038402708414373888 </t>
         </is>
       </c>
-      <c r="B746" t="inlineStr">
+      <c r="B745" t="inlineStr">
         <is>
           <t>images/「お金で買うことの出来ない物」_img1.jpg,images/ 「お金で買うことの出来ない物」_img2.jpg</t>
         </is>
       </c>
-      <c r="C746" t="inlineStr">
+      <c r="C745" t="inlineStr">
         <is>
           <t>ショッピング ,価値</t>
         </is>
       </c>
     </row>
-    <row r="747">
-      <c r="A747" t="inlineStr">
+    <row r="746">
+      <c r="A746" t="inlineStr">
         <is>
           <t xml:space="preserve">「私たちが愛する言葉」
 كلماتٌ نُحبّها
@@ -16145,19 +16124,19 @@
 2109 جليل خزعل </t>
         </is>
       </c>
-      <c r="B747" t="inlineStr">
+      <c r="B746" t="inlineStr">
         <is>
           <t>images/「私たちが愛する言葉」_img1.jpg</t>
         </is>
       </c>
-      <c r="C747" t="inlineStr">
+      <c r="C746" t="inlineStr">
         <is>
           <t>花 ,贈り物</t>
         </is>
       </c>
     </row>
-    <row r="748">
-      <c r="A748" t="inlineStr">
+    <row r="747">
+      <c r="A747" t="inlineStr">
         <is>
           <t xml:space="preserve">「お茶についてあなたが知らない10の事実」
 عشر معلومات لا تعرفها عن الشاي
@@ -16166,19 +16145,19 @@
 2012 http://ara.tv/6syq2 </t>
         </is>
       </c>
-      <c r="B748" t="inlineStr">
+      <c r="B747" t="inlineStr">
         <is>
           <t>images/「お茶についてあなたが知らない10の事_img1.jpg</t>
         </is>
       </c>
-      <c r="C748" t="inlineStr">
+      <c r="C747" t="inlineStr">
         <is>
           <t>神農</t>
         </is>
       </c>
     </row>
-    <row r="749">
-      <c r="A749" t="inlineStr">
+    <row r="748">
+      <c r="A748" t="inlineStr">
         <is>
           <t xml:space="preserve">「大きくなったウソ」
 الكذبة الّتي كبرت
@@ -16188,19 +16167,19 @@
 2509 سلسلة الحلزونة </t>
         </is>
       </c>
-      <c r="B749" t="inlineStr">
+      <c r="B748" t="inlineStr">
         <is>
           <t>images/「大きくなったウソ」_img1.jpg</t>
         </is>
       </c>
-      <c r="C749" t="inlineStr">
+      <c r="C748" t="inlineStr">
         <is>
           <t>絵本</t>
         </is>
       </c>
     </row>
-    <row r="750">
-      <c r="A750" t="inlineStr">
+    <row r="749">
+      <c r="A749" t="inlineStr">
         <is>
           <t xml:space="preserve">「自分に合った掃除機を買うには？」
 كيف تشتري المكنسة الكهربائية التي تناسبك؟
@@ -16209,19 +16188,19 @@
 2106 ts3a com </t>
         </is>
       </c>
-      <c r="B750" t="inlineStr">
+      <c r="B749" t="inlineStr">
         <is>
           <t>images/「自分に合った掃除機を買うには？」_img1.jpg</t>
         </is>
       </c>
-      <c r="C750" t="inlineStr">
+      <c r="C749" t="inlineStr">
         <is>
           <t>家電 ,掃除</t>
         </is>
       </c>
     </row>
-    <row r="751">
-      <c r="A751" t="inlineStr">
+    <row r="750">
+      <c r="A750" t="inlineStr">
         <is>
           <t xml:space="preserve">「仮にこれが批判の数としよう」
 لنفرض ان عدد الذين ينتقدونك
@@ -16232,19 +16211,19 @@
 2504 出典不明 </t>
         </is>
       </c>
-      <c r="B751" t="inlineStr">
+      <c r="B750" t="inlineStr">
         <is>
           <t>images/「仮にこれが批判の数としよう」_img1.jpg</t>
         </is>
       </c>
-      <c r="C751" t="inlineStr">
+      <c r="C750" t="inlineStr">
         <is>
           <t>アンチ</t>
         </is>
       </c>
     </row>
-    <row r="752">
-      <c r="A752" t="inlineStr">
+    <row r="751">
+      <c r="A751" t="inlineStr">
         <is>
           <t xml:space="preserve">「ここに見えるのは何？」
 ما الذي تراه هنا؟
@@ -16254,15 +16233,15 @@
 2204 https://twitter.com/NatGeoMagArab/status/1506933850617700352 </t>
         </is>
       </c>
-      <c r="B752" t="inlineStr"/>
-      <c r="C752" t="inlineStr">
+      <c r="B751" t="inlineStr"/>
+      <c r="C751" t="inlineStr">
         <is>
           <t xml:space="preserve">ペンギン </t>
         </is>
       </c>
     </row>
-    <row r="753">
-      <c r="A753" t="inlineStr">
+    <row r="752">
+      <c r="A752" t="inlineStr">
         <is>
           <t xml:space="preserve">「今日辛いこと、明日は平気だろう」
 ما يؤلم اليوم سيهون غدًا
@@ -16272,19 +16251,19 @@
 2308 basmahjeff </t>
         </is>
       </c>
-      <c r="B753" t="inlineStr">
+      <c r="B752" t="inlineStr">
         <is>
           <t>images/「今日辛いこと、明日は平気だろう」_img1.jpg</t>
         </is>
       </c>
-      <c r="C753" t="inlineStr">
+      <c r="C752" t="inlineStr">
         <is>
           <t>悩み ,達観</t>
         </is>
       </c>
     </row>
-    <row r="754">
-      <c r="A754" t="inlineStr">
+    <row r="753">
+      <c r="A753" t="inlineStr">
         <is>
           <t xml:space="preserve">「自分のすることを好きでなきゃ」
 عليك أن تحب ما تفعل
@@ -16293,19 +16272,19 @@
 1810 Ahmed Elhakeem </t>
         </is>
       </c>
-      <c r="B754" t="inlineStr">
+      <c r="B753" t="inlineStr">
         <is>
           <t>images/「自分のすることを好きでなきゃ」_img1.jpg</t>
         </is>
       </c>
-      <c r="C754" t="inlineStr">
+      <c r="C753" t="inlineStr">
         <is>
           <t>転職 ,かわいい</t>
         </is>
       </c>
     </row>
-    <row r="755">
-      <c r="A755" t="inlineStr">
+    <row r="754">
+      <c r="A754" t="inlineStr">
         <is>
           <t xml:space="preserve">「この地上に生き甲斐あり」
 على هذه الأرض ما يستحق الحياة
@@ -16315,19 +16294,19 @@
 2308 Mahmoud Gafar </t>
         </is>
       </c>
-      <c r="B755" t="inlineStr">
+      <c r="B754" t="inlineStr">
         <is>
           <t>images/「この地上に生き甲斐あり」_img1.jpg</t>
         </is>
       </c>
-      <c r="C755" t="inlineStr">
+      <c r="C754" t="inlineStr">
         <is>
           <t>詩</t>
         </is>
       </c>
     </row>
-    <row r="756">
-      <c r="A756" t="inlineStr">
+    <row r="755">
+      <c r="A755" t="inlineStr">
         <is>
           <t xml:space="preserve">「おそらく、あなたの求めるものはあるだろう」
 لعلَّ ما تَرجوهُ سيَكونُ
@@ -16337,19 +16316,19 @@
 2308 PIXEL Instagram </t>
         </is>
       </c>
-      <c r="B756" t="inlineStr">
+      <c r="B755" t="inlineStr">
         <is>
           <t>images/「おそらく、あなたの求めるものはあるだ_img1.jpg</t>
         </is>
       </c>
-      <c r="C756" t="inlineStr">
+      <c r="C755" t="inlineStr">
         <is>
           <t>願い ,信仰</t>
         </is>
       </c>
     </row>
-    <row r="757">
-      <c r="A757" t="inlineStr">
+    <row r="756">
+      <c r="A756" t="inlineStr">
         <is>
           <t xml:space="preserve">「オレンジの効能が何か知っていますか？」
 هل تعرف ما هي فوائد البرتقال؟
@@ -16359,19 +16338,19 @@
 2308 sadahadhramowt com </t>
         </is>
       </c>
-      <c r="B757" t="inlineStr">
+      <c r="B756" t="inlineStr">
         <is>
           <t>images/「オレンジの効能が何か知っていますか？_img1.jpg</t>
         </is>
       </c>
-      <c r="C757" t="inlineStr">
+      <c r="C756" t="inlineStr">
         <is>
           <t>オレンジ ,フルーツ</t>
         </is>
       </c>
     </row>
-    <row r="758">
-      <c r="A758" t="inlineStr">
+    <row r="757">
+      <c r="A757" t="inlineStr">
         <is>
           <t xml:space="preserve">「遊ぶパンダの光景より可愛いものがありますか？」
 هل هناك ما هو ألطف من مشاهدة الباندا وهي تلعب؟
@@ -16379,19 +16358,19 @@
 2308 https://twitter.com/NatGeoMagArab/status/1494612797858074626 </t>
         </is>
       </c>
-      <c r="B758" t="inlineStr">
+      <c r="B757" t="inlineStr">
         <is>
           <t>images/「遊ぶパンダの光景より可愛いものがあり_img1.jpg</t>
         </is>
       </c>
-      <c r="C758" t="inlineStr">
+      <c r="C757" t="inlineStr">
         <is>
           <t>パンダ ,モコモコ</t>
         </is>
       </c>
     </row>
-    <row r="759">
-      <c r="A759" t="inlineStr">
+    <row r="758">
+      <c r="A758" t="inlineStr">
         <is>
           <t xml:space="preserve">「大事なのは何者だったかじゃない。何者になるかだ」
 ليسَ المُهم ما كُنتَ بل مَا ستكون
@@ -16400,19 +16379,19 @@
 2308 出典不明 </t>
         </is>
       </c>
-      <c r="B759" t="inlineStr">
+      <c r="B758" t="inlineStr">
         <is>
           <t>images/「大事なのは何者だったかじゃない。何者_img1.jpg</t>
         </is>
       </c>
-      <c r="C759" t="inlineStr">
+      <c r="C758" t="inlineStr">
         <is>
           <t>自己実現 ,存在価値</t>
         </is>
       </c>
     </row>
-    <row r="760">
-      <c r="A760" t="inlineStr">
+    <row r="759">
+      <c r="A759" t="inlineStr">
         <is>
           <t xml:space="preserve">「あなたであれ。ありのままが美しいから」
 كُنْ أَنْتَ لأنك جميل كما أنت
@@ -16421,19 +16400,19 @@
 2308 IDREES DESIGN </t>
         </is>
       </c>
-      <c r="B760" t="inlineStr">
+      <c r="B759" t="inlineStr">
         <is>
           <t>images/「あなたであれ。ありのままが美しいから_img1.jpg</t>
         </is>
       </c>
-      <c r="C760" t="inlineStr">
+      <c r="C759" t="inlineStr">
         <is>
           <t>自己肯定 ,BeYourself</t>
         </is>
       </c>
     </row>
-    <row r="761">
-      <c r="A761" t="inlineStr">
+    <row r="760">
+      <c r="A760" t="inlineStr">
         <is>
           <t xml:space="preserve">「恐れの中に生きる者は決して自由になれない」
 من يعش في خوف لن يكون حرا أبدا
@@ -16442,19 +16421,19 @@
 2111 rjeem com </t>
         </is>
       </c>
-      <c r="B761" t="inlineStr">
+      <c r="B760" t="inlineStr">
         <is>
           <t>images/「恐れの中に生きる者は決して自由になれ_img1.jpg,images/ 「恐れの中に生きる者は決して自由になれ_img2.jpg</t>
         </is>
       </c>
-      <c r="C761" t="inlineStr">
+      <c r="C760" t="inlineStr">
         <is>
           <t>勇気 ,壁</t>
         </is>
       </c>
     </row>
-    <row r="762">
-      <c r="A762" t="inlineStr">
+    <row r="761">
+      <c r="A761" t="inlineStr">
         <is>
           <t xml:space="preserve">「己の翼を信じる者は己の重さを案じない」
 من يثق في جناحيه لن يهتم لوزنه
@@ -16463,19 +16442,19 @@
 2308 kmrghani </t>
         </is>
       </c>
-      <c r="B762" t="inlineStr">
+      <c r="B761" t="inlineStr">
         <is>
           <t>images/「己の翼を信じる者は己の重さを案じない_img1.jpg</t>
         </is>
       </c>
-      <c r="C762" t="inlineStr">
+      <c r="C761" t="inlineStr">
         <is>
           <t>自信</t>
         </is>
       </c>
     </row>
-    <row r="763">
-      <c r="A763" t="inlineStr">
+    <row r="762">
+      <c r="A762" t="inlineStr">
         <is>
           <t xml:space="preserve">「珈琲で一番大事な事！誰と飲むか？」
 الأهم من القهوة!! من ستشربها معه؟
@@ -16484,19 +16463,19 @@
 1812 gwid3.tumblr </t>
         </is>
       </c>
-      <c r="B763" t="inlineStr">
+      <c r="B762" t="inlineStr">
         <is>
           <t>images/「珈琲で一番大事な事！誰と飲むか？」_img1.jpg</t>
         </is>
       </c>
-      <c r="C763" t="inlineStr">
+      <c r="C762" t="inlineStr">
         <is>
           <t>コーヒー ,名言</t>
         </is>
       </c>
     </row>
-    <row r="764">
-      <c r="A764" t="inlineStr">
+    <row r="763">
+      <c r="A763" t="inlineStr">
         <is>
           <t xml:space="preserve">「人生は美しい、そう望んだ者には。」
 الحياة جَميلَة .. لمن أراد ذلك
@@ -16506,19 +16485,19 @@
 2109 出典不明 </t>
         </is>
       </c>
-      <c r="B764" t="inlineStr">
+      <c r="B763" t="inlineStr">
         <is>
           <t>images/「人生は美しい、そう望んだ者には。」_img1.jpg</t>
         </is>
       </c>
-      <c r="C764" t="inlineStr">
+      <c r="C763" t="inlineStr">
         <is>
           <t>名言 ,アート</t>
         </is>
       </c>
     </row>
-    <row r="765">
-      <c r="A765" t="inlineStr">
+    <row r="764">
+      <c r="A764" t="inlineStr">
         <is>
           <t xml:space="preserve">「ハム太郎って子を知ってるかい」
 هل تعرفون من هو هامتارو
@@ -16528,19 +16507,19 @@
 2109 </t>
         </is>
       </c>
-      <c r="B765" t="inlineStr">
+      <c r="B764" t="inlineStr">
         <is>
           <t>images/「ハム太郎って子を知ってるかい」_img1.jpg</t>
         </is>
       </c>
-      <c r="C765" t="inlineStr">
+      <c r="C764" t="inlineStr">
         <is>
           <t>オープニング ,ハム太郎</t>
         </is>
       </c>
     </row>
-    <row r="766">
-      <c r="A766" t="inlineStr">
+    <row r="765">
+      <c r="A765" t="inlineStr">
         <is>
           <t xml:space="preserve">「幸せを求める人もいれば、作る人もいる」
 هناك من يبحث عن السعادة وهناك من يصنعها
@@ -16549,19 +16528,19 @@
 2308 hindah tumblr </t>
         </is>
       </c>
-      <c r="B766" t="inlineStr">
+      <c r="B765" t="inlineStr">
         <is>
           <t>images/「幸せを求める人もいれば、作る人もいる_img1.jpg</t>
         </is>
       </c>
-      <c r="C766" t="inlineStr">
+      <c r="C765" t="inlineStr">
         <is>
           <t>幸せ ,名言 ,教訓</t>
         </is>
       </c>
     </row>
-    <row r="767">
-      <c r="A767" t="inlineStr">
+    <row r="766">
+      <c r="A766" t="inlineStr">
         <is>
           <t xml:space="preserve">「明白なるアラブの言葉によって」
 بلسان عربي مبين
@@ -16571,19 +16550,19 @@
 2109 Abdullah Barakat behance </t>
         </is>
       </c>
-      <c r="B767" t="inlineStr">
+      <c r="B766" t="inlineStr">
         <is>
           <t>images/「明白なるアラブの言葉によって」_img1.jpg</t>
         </is>
       </c>
-      <c r="C767" t="inlineStr">
+      <c r="C766" t="inlineStr">
         <is>
           <t>イスラム教 ,神聖</t>
         </is>
       </c>
     </row>
-    <row r="768">
-      <c r="A768" t="inlineStr">
+    <row r="767">
+      <c r="A767" t="inlineStr">
         <is>
           <t xml:space="preserve">「結婚前、結婚後」
 قبل الزواج، بعد الزواج
@@ -16593,19 +16572,19 @@
 2308 出典不明 </t>
         </is>
       </c>
-      <c r="B768" t="inlineStr">
+      <c r="B767" t="inlineStr">
         <is>
           <t>images/「結婚前、結婚後」_img1.jpg</t>
         </is>
       </c>
-      <c r="C768" t="inlineStr">
+      <c r="C767" t="inlineStr">
         <is>
           <t>BeforeAfter ,幸せ太り</t>
         </is>
       </c>
     </row>
-    <row r="769">
-      <c r="A769" t="inlineStr">
+    <row r="768">
+      <c r="A768" t="inlineStr">
         <is>
           <t xml:space="preserve">「驚きの価格で」بسعر رائع
 ビスィアル・ラーイア [bi-si*r raa'i*]
@@ -16614,19 +16593,19 @@
 2109 Jarir Bookstore </t>
         </is>
       </c>
-      <c r="B769" t="inlineStr">
+      <c r="B768" t="inlineStr">
         <is>
           <t>images/「驚きの価格で」_img1.jpg</t>
         </is>
       </c>
-      <c r="C769" t="inlineStr">
+      <c r="C768" t="inlineStr">
         <is>
           <t>広告 ,安値</t>
         </is>
       </c>
     </row>
-    <row r="770">
-      <c r="A770" t="inlineStr">
+    <row r="769">
+      <c r="A769" t="inlineStr">
         <is>
           <t xml:space="preserve">「我が魂と共に」مع نفسي
 マア・ナフスィ [ma*a nafs-iy]
@@ -16635,19 +16614,19 @@
 2110 出典不明 </t>
         </is>
       </c>
-      <c r="B770" t="inlineStr">
+      <c r="B769" t="inlineStr">
         <is>
           <t>images/「我が魂と共に」_img1.jpg</t>
         </is>
       </c>
-      <c r="C770" t="inlineStr">
+      <c r="C769" t="inlineStr">
         <is>
           <t>ソウル ,soul</t>
         </is>
       </c>
     </row>
-    <row r="771">
-      <c r="A771" t="inlineStr">
+    <row r="770">
+      <c r="A770" t="inlineStr">
         <is>
           <t xml:space="preserve">「暗い夜に」في ليلة مظلمة
  [fiy layla(tin) mu_Dhlima(tin)]
@@ -16656,19 +16635,19 @@
 2109 سلسلة الحلزونة </t>
         </is>
       </c>
-      <c r="B771" t="inlineStr">
+      <c r="B770" t="inlineStr">
         <is>
           <t>images/「暗い夜に」_img1.jpg</t>
         </is>
       </c>
-      <c r="C771" t="inlineStr">
+      <c r="C770" t="inlineStr">
         <is>
           <t>絵本</t>
         </is>
       </c>
     </row>
-    <row r="772">
-      <c r="A772" t="inlineStr">
+    <row r="771">
+      <c r="A771" t="inlineStr">
         <is>
           <t xml:space="preserve">「ゆっくりと」بشويش
 ビシワェーシ [bi-ShwySh]
@@ -16676,19 +16655,19 @@
 2109 出典不明 </t>
         </is>
       </c>
-      <c r="B772" t="inlineStr">
+      <c r="B771" t="inlineStr">
         <is>
           <t>images/「ゆっくりと」_img1.jpg</t>
         </is>
       </c>
-      <c r="C772" t="inlineStr">
+      <c r="C771" t="inlineStr">
         <is>
           <t>丸 ,円</t>
         </is>
       </c>
     </row>
-    <row r="773">
-      <c r="A773" t="inlineStr">
+    <row r="772">
+      <c r="A772" t="inlineStr">
         <is>
           <t xml:space="preserve">「この広い宇宙に…」
 في الكون الفسيح
@@ -16697,19 +16676,19 @@
 2308 wattpad </t>
         </is>
       </c>
-      <c r="B773" t="inlineStr">
+      <c r="B772" t="inlineStr">
         <is>
           <t>images/「この広い宇宙に…」_img1.jpg</t>
         </is>
       </c>
-      <c r="C773" t="inlineStr">
+      <c r="C772" t="inlineStr">
         <is>
           <t>アニメ ,宇宙</t>
         </is>
       </c>
     </row>
-    <row r="774">
-      <c r="A774" t="inlineStr">
+    <row r="773">
+      <c r="A773" t="inlineStr">
         <is>
           <t xml:space="preserve">「がんばって！」بالتوفيق
 ビッタウフィーク [bi^tawfiiq]
@@ -16717,19 +16696,19 @@
 2111 https://sites.google.com/site/mathmatic1905/ </t>
         </is>
       </c>
-      <c r="B774" t="inlineStr">
+      <c r="B773" t="inlineStr">
         <is>
           <t>images/「がんばって！」_img1.jpg</t>
         </is>
       </c>
-      <c r="C774" t="inlineStr">
+      <c r="C773" t="inlineStr">
         <is>
           <t>アラビア語</t>
         </is>
       </c>
     </row>
-    <row r="775">
-      <c r="A775" t="inlineStr">
+    <row r="774">
+      <c r="A774" t="inlineStr">
         <is>
           <t xml:space="preserve">「インターステラー」بين النجوم
 バイナ_ンヌジューム [bayna ^nujuum]
@@ -16737,19 +16716,19 @@
 2308 kmrghani </t>
         </is>
       </c>
-      <c r="B775" t="inlineStr">
+      <c r="B774" t="inlineStr">
         <is>
           <t>images/「インターステラー」_img1.jpg</t>
         </is>
       </c>
-      <c r="C775" t="inlineStr">
+      <c r="C774" t="inlineStr">
         <is>
           <t>映画 ,宇宙</t>
         </is>
       </c>
     </row>
-    <row r="776">
-      <c r="A776" t="inlineStr">
+    <row r="775">
+      <c r="A775" t="inlineStr">
         <is>
           <t xml:space="preserve">「アラビア語で」بالعربية
 ビ_ルアラビーヤ [bi-l-*arabiyya]
@@ -16758,19 +16737,19 @@
 1811 </t>
         </is>
       </c>
-      <c r="B776" t="inlineStr">
+      <c r="B775" t="inlineStr">
         <is>
           <t>images/「アラビア語で」_img1.jpg</t>
         </is>
       </c>
-      <c r="C776" t="inlineStr">
+      <c r="C775" t="inlineStr">
         <is>
           <t>ニュース ,CNN</t>
         </is>
       </c>
     </row>
-    <row r="777">
-      <c r="A777" t="inlineStr">
+    <row r="776">
+      <c r="A776" t="inlineStr">
         <is>
           <t xml:space="preserve">「17世紀に発明されて以来…」
 منذ اختراعه بالقرن السابع عشر
@@ -16778,19 +16757,19 @@
 2308 https://twitter.com/SciTalk2U/status/1450888395815854080 </t>
         </is>
       </c>
-      <c r="B777" t="inlineStr">
+      <c r="B776" t="inlineStr">
         <is>
           <t>images/「17世紀に発明されて以来…」_img1.jpg</t>
         </is>
       </c>
-      <c r="C777" t="inlineStr">
+      <c r="C776" t="inlineStr">
         <is>
           <t>手書き語学 ,アラビア語 ,望遠鏡</t>
         </is>
       </c>
     </row>
-    <row r="778">
-      <c r="A778" t="inlineStr">
+    <row r="777">
+      <c r="A777" t="inlineStr">
         <is>
           <t xml:space="preserve">「私できるよ」إنّني أستطيع
 インナニー・アスタティーウ ['inna-niy 'a-sta_tii*u]
@@ -16799,19 +16778,19 @@
 2412 سلسلة الحلزونة </t>
         </is>
       </c>
-      <c r="B778" t="inlineStr">
+      <c r="B777" t="inlineStr">
         <is>
           <t>images/「私できるよ」_img1.jpg</t>
         </is>
       </c>
-      <c r="C778" t="inlineStr">
+      <c r="C777" t="inlineStr">
         <is>
           <t>絵本 ,こども</t>
         </is>
       </c>
     </row>
-    <row r="779">
-      <c r="A779" t="inlineStr">
+    <row r="778">
+      <c r="A778" t="inlineStr">
         <is>
           <t xml:space="preserve">「問題なし」مافيش مشكلة
 マフィーシムシュキラ [ma-fy-Sh muShkila]
@@ -16820,19 +16799,19 @@
 2109 tanzerin.theshop </t>
         </is>
       </c>
-      <c r="B779" t="inlineStr">
+      <c r="B778" t="inlineStr">
         <is>
           <t>images/「問題なし」_img1.jpg</t>
         </is>
       </c>
-      <c r="C779" t="inlineStr">
+      <c r="C778" t="inlineStr">
         <is>
           <t>シャツ ,キッズ</t>
         </is>
       </c>
     </row>
-    <row r="780">
-      <c r="A780" t="inlineStr">
+    <row r="779">
+      <c r="A779" t="inlineStr">
         <is>
           <t xml:space="preserve">「不可能はない」مفيش مستحيل
 マフィーシ・ムスタヒール [ma-fy-Sh mustaHiil]
@@ -16841,19 +16820,19 @@
 2109 أموج </t>
         </is>
       </c>
-      <c r="B780" t="inlineStr">
+      <c r="B779" t="inlineStr">
         <is>
           <t>images/「不可能はない」_img1.jpg</t>
         </is>
       </c>
-      <c r="C780" t="inlineStr">
+      <c r="C779" t="inlineStr">
         <is>
           <t>ポジティブ ,挑戦</t>
         </is>
       </c>
     </row>
-    <row r="781">
-      <c r="A781" t="inlineStr">
+    <row r="780">
+      <c r="A780" t="inlineStr">
         <is>
           <t xml:space="preserve">「等々」إلخ
 イラク ['ilaKh]
@@ -16862,19 +16841,19 @@
 2201 出典不明 </t>
         </is>
       </c>
-      <c r="B781" t="inlineStr">
+      <c r="B780" t="inlineStr">
         <is>
           <t>images/「等々」_img1.jpg</t>
         </is>
       </c>
-      <c r="C781" t="inlineStr">
+      <c r="C780" t="inlineStr">
         <is>
           <t>etc ,とんち</t>
         </is>
       </c>
     </row>
-    <row r="782">
-      <c r="A782" t="inlineStr">
+    <row r="781">
+      <c r="A781" t="inlineStr">
         <is>
           <t xml:space="preserve">⁦「調子どう？」⁩شلونَك؟
 シュローナク？ [Sh-loon-ak?]
@@ -16883,19 +16862,19 @@
 2202 Jozoor Team. </t>
         </is>
       </c>
-      <c r="B782" t="inlineStr">
+      <c r="B781" t="inlineStr">
         <is>
           <t>images/⁦「調子どう？」⁩_img1.jpg</t>
         </is>
       </c>
-      <c r="C782" t="inlineStr">
+      <c r="C781" t="inlineStr">
         <is>
           <t>洒落 ,ルービックキューブ</t>
         </is>
       </c>
     </row>
-    <row r="783">
-      <c r="A783" t="inlineStr">
+    <row r="782">
+      <c r="A782" t="inlineStr">
         <is>
           <t xml:space="preserve">「行くな」ماتروحش
 マトロホシ [ma-troH-Sh]
@@ -16904,19 +16883,19 @@
 2411 triiq tumblr </t>
         </is>
       </c>
-      <c r="B783" t="inlineStr">
+      <c r="B782" t="inlineStr">
         <is>
           <t>images/「行くな」_img1.jpg</t>
         </is>
       </c>
-      <c r="C783" t="inlineStr">
+      <c r="C782" t="inlineStr">
         <is>
           <t>ロゴ ,デザイン ,嵐</t>
         </is>
       </c>
     </row>
-    <row r="784">
-      <c r="A784" t="inlineStr">
+    <row r="783">
+      <c r="A783" t="inlineStr">
         <is>
           <t xml:space="preserve">⁦「元気？」⁩شلونَك؟
 シュローナク？ [Sh-loon-ak?]
@@ -16927,19 +16906,19 @@
 2202 出典不明 </t>
         </is>
       </c>
-      <c r="B784" t="inlineStr">
+      <c r="B783" t="inlineStr">
         <is>
           <t>images/⁦「元気？」⁩_img1.jpg</t>
         </is>
       </c>
-      <c r="C784" t="inlineStr">
+      <c r="C783" t="inlineStr">
         <is>
           <t>洒落 ,挨拶</t>
         </is>
       </c>
     </row>
-    <row r="785">
-      <c r="A785" t="inlineStr">
+    <row r="784">
+      <c r="A784" t="inlineStr">
         <is>
           <t xml:space="preserve">「気分が良いぞう」I فيل GOOD
 アイ・フィール・グッド [ai fiyl gud]
@@ -16948,19 +16927,19 @@
 2308 出典不明 </t>
         </is>
       </c>
-      <c r="B785" t="inlineStr">
+      <c r="B784" t="inlineStr">
         <is>
           <t>images/「気分が良いぞう」_img1.jpg</t>
         </is>
       </c>
-      <c r="C785" t="inlineStr">
+      <c r="C784" t="inlineStr">
         <is>
           <t>洒落 ,和訳</t>
         </is>
       </c>
     </row>
-    <row r="786">
-      <c r="A786" t="inlineStr">
+    <row r="785">
+      <c r="A785" t="inlineStr">
         <is>
           <t xml:space="preserve">「レットイットゴー／let it go」
 ليت اِت غو
@@ -16969,19 +16948,19 @@
 2109 出典不明 </t>
         </is>
       </c>
-      <c r="B786" t="inlineStr">
+      <c r="B785" t="inlineStr">
         <is>
           <t>images/「レットイットゴー／let it go_img1.jpg</t>
         </is>
       </c>
-      <c r="C786" t="inlineStr">
+      <c r="C785" t="inlineStr">
         <is>
           <t>折衷 ,アナ雪</t>
         </is>
       </c>
     </row>
-    <row r="787">
-      <c r="A787" t="inlineStr">
+    <row r="786">
+      <c r="A786" t="inlineStr">
         <is>
           <t xml:space="preserve">「ようこそ」اهلا وسهلا
 アハラン・ワサハラン ['ahlan wa-sahlan]
@@ -16989,19 +16968,19 @@
 2106 behance Anwar Al Eissa </t>
         </is>
       </c>
-      <c r="B787" t="inlineStr">
+      <c r="B786" t="inlineStr">
         <is>
           <t>images/「ようこそ」_img1.jpg</t>
         </is>
       </c>
-      <c r="C787" t="inlineStr">
+      <c r="C786" t="inlineStr">
         <is>
           <t>アラビア語</t>
         </is>
       </c>
     </row>
-    <row r="788">
-      <c r="A788" t="inlineStr">
+    <row r="787">
+      <c r="A787" t="inlineStr">
         <is>
           <t xml:space="preserve">「まぁ何というサプライズでしょう」
 يا لها من مفاجأة
@@ -17012,19 +16991,19 @@
 2108 neelwafurat com </t>
         </is>
       </c>
-      <c r="B788" t="inlineStr">
+      <c r="B787" t="inlineStr">
         <is>
           <t>images/「まぁ何というサプライズでしょう」_img1.jpg</t>
         </is>
       </c>
-      <c r="C788" t="inlineStr">
+      <c r="C787" t="inlineStr">
         <is>
           <t>中国語 ,学習</t>
         </is>
       </c>
     </row>
-    <row r="789">
-      <c r="A789" t="inlineStr">
+    <row r="788">
+      <c r="A788" t="inlineStr">
         <is>
           <t xml:space="preserve">「ハックション」اتشوو
 アチュー！ ['aatShuu]
@@ -17032,19 +17011,19 @@
 1811 </t>
         </is>
       </c>
-      <c r="B789" t="inlineStr">
+      <c r="B788" t="inlineStr">
         <is>
           <t>images/「ハックション」_img1.jpg</t>
         </is>
       </c>
-      <c r="C789" t="inlineStr">
+      <c r="C788" t="inlineStr">
         <is>
           <t>あらびあや</t>
         </is>
       </c>
     </row>
-    <row r="790">
-      <c r="A790" t="inlineStr">
+    <row r="789">
+      <c r="A789" t="inlineStr">
         <is>
           <t xml:space="preserve">「スブハーナッラー」「アルハムドゥリッラー」「アッラーアクバル」
 سبحان الله
@@ -17055,19 +17034,19 @@
 2308 dribbble com </t>
         </is>
       </c>
-      <c r="B790" t="inlineStr">
+      <c r="B789" t="inlineStr">
         <is>
           <t>images/「スブハーナッラー」「アルハムドゥリッ_img1.jpg</t>
         </is>
       </c>
-      <c r="C790" t="inlineStr">
+      <c r="C789" t="inlineStr">
         <is>
           <t>四角 ,コンパクト</t>
         </is>
       </c>
     </row>
-    <row r="791">
-      <c r="A791" t="inlineStr">
+    <row r="790">
+      <c r="A790" t="inlineStr">
         <is>
           <t xml:space="preserve">「すごく美味しい！」لذيذ جدًا
 ラズィーズ・ジッダン [laDhiiDh jiddan]
@@ -17076,19 +17055,19 @@
 2109 goodreads com </t>
         </is>
       </c>
-      <c r="B791" t="inlineStr">
+      <c r="B790" t="inlineStr">
         <is>
           <t>images/「すごく美味しい！」_img1.jpg</t>
         </is>
       </c>
-      <c r="C791" t="inlineStr">
+      <c r="C790" t="inlineStr">
         <is>
           <t>フレーズ ,感想</t>
         </is>
       </c>
     </row>
-    <row r="792">
-      <c r="A792" t="inlineStr">
+    <row r="791">
+      <c r="A791" t="inlineStr">
         <is>
           <t xml:space="preserve">「しとしと、雨」تك تك يا مطر
 ティクティク [tik tik yaa ma_tar]
@@ -17097,19 +17076,19 @@
 2308 出典不明 </t>
         </is>
       </c>
-      <c r="B792" t="inlineStr">
+      <c r="B791" t="inlineStr">
         <is>
           <t>images/「しとしと、雨」_img1.jpg</t>
         </is>
       </c>
-      <c r="C792" t="inlineStr">
+      <c r="C791" t="inlineStr">
         <is>
           <t>天気 ,梅雨</t>
         </is>
       </c>
     </row>
-    <row r="793">
-      <c r="A793" t="inlineStr">
+    <row r="792">
+      <c r="A792" t="inlineStr">
         <is>
           <t xml:space="preserve">「さかさま」رأساً على عقب
 ラッアサン・アラー・アケブ [ra'san *alaa *aqib]
@@ -17117,19 +17096,19 @@
 2109 出典不明 </t>
         </is>
       </c>
-      <c r="B793" t="inlineStr">
+      <c r="B792" t="inlineStr">
         <is>
           <t>images/「さかさま」_img1.jpg</t>
         </is>
       </c>
-      <c r="C793" t="inlineStr">
+      <c r="C792" t="inlineStr">
         <is>
           <t>壁 ,上下</t>
         </is>
       </c>
     </row>
-    <row r="794">
-      <c r="A794" t="inlineStr">
+    <row r="793">
+      <c r="A793" t="inlineStr">
         <is>
           <t xml:space="preserve">「エジプトよどこへ行った」
 فينك يا مصر؟
@@ -17139,19 +17118,19 @@
 1809 shehabfawzy1.tumblr </t>
         </is>
       </c>
-      <c r="B794" t="inlineStr">
+      <c r="B793" t="inlineStr">
         <is>
           <t>images/「エジプトよどこへ行った」_img1.jpg</t>
         </is>
       </c>
-      <c r="C794" t="inlineStr">
+      <c r="C793" t="inlineStr">
         <is>
           <t>ピラミッド ,歴史</t>
         </is>
       </c>
     </row>
-    <row r="795">
-      <c r="A795" t="inlineStr">
+    <row r="794">
+      <c r="A794" t="inlineStr">
         <is>
           <t xml:space="preserve">「ありがとう」شكراً
 シュクラン [Shukran]
@@ -17159,19 +17138,19 @@
 2109 出典不明 </t>
         </is>
       </c>
-      <c r="B795" t="inlineStr">
+      <c r="B794" t="inlineStr">
         <is>
           <t>images/「ありがとう」_img1.jpg</t>
         </is>
       </c>
-      <c r="C795" t="inlineStr">
+      <c r="C794" t="inlineStr">
         <is>
           <t>挨拶 ,文字</t>
         </is>
       </c>
     </row>
-    <row r="796">
-      <c r="A796" t="inlineStr">
+    <row r="795">
+      <c r="A795" t="inlineStr">
         <is>
           <t xml:space="preserve">「昼寝の時間だ」
 إنه وقت القيلولة
@@ -17180,12 +17159,12 @@
 2501 https://x.com/NatGeoMagArab/status/1858049951579910486 </t>
         </is>
       </c>
-      <c r="B796" t="inlineStr">
+      <c r="B795" t="inlineStr">
         <is>
           <t>images/「昼寝の時間だ」_img1.jpg</t>
         </is>
       </c>
-      <c r="C796" t="inlineStr">
+      <c r="C795" t="inlineStr">
         <is>
           <t>手書き語学 ,アラビア語 ,ペンギン</t>
         </is>

--- a/posts.xlsx
+++ b/posts.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C793"/>
+  <dimension ref="A1:C792"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -16264,28 +16264,6 @@
     <row r="753">
       <c r="A753" t="inlineStr">
         <is>
-          <t xml:space="preserve">「おそらく、あなたの求めるものはあるだろう」
-لعلَّ ما تَرجوهُ سيَكونُ
-[la*alla maa ta-rjuu-hu sa-ya-kuun(u)]
-「恐らく」[la*alla]・「あなたは望む」[ta-rjuu]・「それは存在する」[ya-kuun(u)]
-求める（もとめる）
-2308 PIXEL Instagram </t>
-        </is>
-      </c>
-      <c r="B753" t="inlineStr">
-        <is>
-          <t>images/「おそらく、あなたの求めるものはあるだ_img1.jpg</t>
-        </is>
-      </c>
-      <c r="C753" t="inlineStr">
-        <is>
-          <t>願い ,信仰</t>
-        </is>
-      </c>
-    </row>
-    <row r="754">
-      <c r="A754" t="inlineStr">
-        <is>
           <t xml:space="preserve">「オレンジの効能が何か知っていますか？」
 هل تعرف ما هي فوائد البرتقال؟
 [hal ta-*rifu maa hiya fawaa'idu l-burtuqaal?]
@@ -16294,19 +16272,19 @@
 2308 sadahadhramowt com </t>
         </is>
       </c>
-      <c r="B754" t="inlineStr">
+      <c r="B753" t="inlineStr">
         <is>
           <t>images/「オレンジの効能が何か知っていますか？_img1.jpg</t>
         </is>
       </c>
-      <c r="C754" t="inlineStr">
+      <c r="C753" t="inlineStr">
         <is>
           <t>オレンジ ,フルーツ</t>
         </is>
       </c>
     </row>
-    <row r="755">
-      <c r="A755" t="inlineStr">
+    <row r="754">
+      <c r="A754" t="inlineStr">
         <is>
           <t xml:space="preserve">「遊ぶパンダの光景より可愛いものがありますか？」
 هل هناك ما هو ألطف من مشاهدة الباندا وهي تلعب؟
@@ -16314,19 +16292,19 @@
 2308 https://twitter.com/NatGeoMagArab/status/1494612797858074626 </t>
         </is>
       </c>
-      <c r="B755" t="inlineStr">
+      <c r="B754" t="inlineStr">
         <is>
           <t>images/「遊ぶパンダの光景より可愛いものがあり_img1.jpg</t>
         </is>
       </c>
-      <c r="C755" t="inlineStr">
+      <c r="C754" t="inlineStr">
         <is>
           <t>パンダ ,モコモコ</t>
         </is>
       </c>
     </row>
-    <row r="756">
-      <c r="A756" t="inlineStr">
+    <row r="755">
+      <c r="A755" t="inlineStr">
         <is>
           <t xml:space="preserve">「大事なのは何者だったかじゃない。何者になるかだ」
 ليسَ المُهم ما كُنتَ بل مَا ستكون
@@ -16335,19 +16313,19 @@
 2308 出典不明 </t>
         </is>
       </c>
-      <c r="B756" t="inlineStr">
+      <c r="B755" t="inlineStr">
         <is>
           <t>images/「大事なのは何者だったかじゃない。何者_img1.jpg</t>
         </is>
       </c>
-      <c r="C756" t="inlineStr">
+      <c r="C755" t="inlineStr">
         <is>
           <t>自己実現 ,存在価値</t>
         </is>
       </c>
     </row>
-    <row r="757">
-      <c r="A757" t="inlineStr">
+    <row r="756">
+      <c r="A756" t="inlineStr">
         <is>
           <t xml:space="preserve">「あなたであれ。ありのままが美しいから」
 كُنْ أَنْتَ لأنك جميل كما أنت
@@ -16356,19 +16334,19 @@
 2308 IDREES DESIGN </t>
         </is>
       </c>
-      <c r="B757" t="inlineStr">
+      <c r="B756" t="inlineStr">
         <is>
           <t>images/「あなたであれ。ありのままが美しいから_img1.jpg</t>
         </is>
       </c>
-      <c r="C757" t="inlineStr">
+      <c r="C756" t="inlineStr">
         <is>
           <t>自己肯定 ,BeYourself</t>
         </is>
       </c>
     </row>
-    <row r="758">
-      <c r="A758" t="inlineStr">
+    <row r="757">
+      <c r="A757" t="inlineStr">
         <is>
           <t xml:space="preserve">「恐れの中に生きる者は決して自由になれない」
 من يعش في خوف لن يكون حرا أبدا
@@ -16377,19 +16355,19 @@
 2111 rjeem com </t>
         </is>
       </c>
-      <c r="B758" t="inlineStr">
+      <c r="B757" t="inlineStr">
         <is>
           <t>images/「恐れの中に生きる者は決して自由になれ_img1.jpg,images/ 「恐れの中に生きる者は決して自由になれ_img2.jpg</t>
         </is>
       </c>
-      <c r="C758" t="inlineStr">
+      <c r="C757" t="inlineStr">
         <is>
           <t>勇気 ,壁</t>
         </is>
       </c>
     </row>
-    <row r="759">
-      <c r="A759" t="inlineStr">
+    <row r="758">
+      <c r="A758" t="inlineStr">
         <is>
           <t xml:space="preserve">「己の翼を信じる者は己の重さを案じない」
 من يثق في جناحيه لن يهتم لوزنه
@@ -16398,19 +16376,19 @@
 2308 kmrghani </t>
         </is>
       </c>
-      <c r="B759" t="inlineStr">
+      <c r="B758" t="inlineStr">
         <is>
           <t>images/「己の翼を信じる者は己の重さを案じない_img1.jpg</t>
         </is>
       </c>
-      <c r="C759" t="inlineStr">
+      <c r="C758" t="inlineStr">
         <is>
           <t>自信</t>
         </is>
       </c>
     </row>
-    <row r="760">
-      <c r="A760" t="inlineStr">
+    <row r="759">
+      <c r="A759" t="inlineStr">
         <is>
           <t xml:space="preserve">「珈琲で一番大事な事！誰と飲むか？」
 الأهم من القهوة!! من ستشربها معه؟
@@ -16419,19 +16397,19 @@
 1812 gwid3.tumblr </t>
         </is>
       </c>
-      <c r="B760" t="inlineStr">
+      <c r="B759" t="inlineStr">
         <is>
           <t>images/「珈琲で一番大事な事！誰と飲むか？」_img1.jpg</t>
         </is>
       </c>
-      <c r="C760" t="inlineStr">
+      <c r="C759" t="inlineStr">
         <is>
           <t>コーヒー ,名言</t>
         </is>
       </c>
     </row>
-    <row r="761">
-      <c r="A761" t="inlineStr">
+    <row r="760">
+      <c r="A760" t="inlineStr">
         <is>
           <t xml:space="preserve">「人生は美しい、そう望んだ者には。」
 الحياة جَميلَة .. لمن أراد ذلك
@@ -16441,19 +16419,19 @@
 2109 出典不明 </t>
         </is>
       </c>
-      <c r="B761" t="inlineStr">
+      <c r="B760" t="inlineStr">
         <is>
           <t>images/「人生は美しい、そう望んだ者には。」_img1.jpg</t>
         </is>
       </c>
-      <c r="C761" t="inlineStr">
+      <c r="C760" t="inlineStr">
         <is>
           <t>名言 ,アート</t>
         </is>
       </c>
     </row>
-    <row r="762">
-      <c r="A762" t="inlineStr">
+    <row r="761">
+      <c r="A761" t="inlineStr">
         <is>
           <t xml:space="preserve">「ハム太郎って子を知ってるかい」
 هل تعرفون من هو هامتارو
@@ -16463,19 +16441,19 @@
 2109 </t>
         </is>
       </c>
-      <c r="B762" t="inlineStr">
+      <c r="B761" t="inlineStr">
         <is>
           <t>images/「ハム太郎って子を知ってるかい」_img1.jpg</t>
         </is>
       </c>
-      <c r="C762" t="inlineStr">
+      <c r="C761" t="inlineStr">
         <is>
           <t>オープニング ,ハム太郎</t>
         </is>
       </c>
     </row>
-    <row r="763">
-      <c r="A763" t="inlineStr">
+    <row r="762">
+      <c r="A762" t="inlineStr">
         <is>
           <t xml:space="preserve">「幸せを求める人もいれば、作る人もいる」
 هناك من يبحث عن السعادة وهناك من يصنعها
@@ -16484,19 +16462,19 @@
 2308 hindah tumblr </t>
         </is>
       </c>
-      <c r="B763" t="inlineStr">
+      <c r="B762" t="inlineStr">
         <is>
           <t>images/「幸せを求める人もいれば、作る人もいる_img1.jpg</t>
         </is>
       </c>
-      <c r="C763" t="inlineStr">
+      <c r="C762" t="inlineStr">
         <is>
           <t>幸せ ,名言 ,教訓</t>
         </is>
       </c>
     </row>
-    <row r="764">
-      <c r="A764" t="inlineStr">
+    <row r="763">
+      <c r="A763" t="inlineStr">
         <is>
           <t xml:space="preserve">「明白なるアラブの言葉によって」
 بلسان عربي مبين
@@ -16506,19 +16484,19 @@
 2109 Abdullah Barakat behance </t>
         </is>
       </c>
-      <c r="B764" t="inlineStr">
+      <c r="B763" t="inlineStr">
         <is>
           <t>images/「明白なるアラブの言葉によって」_img1.jpg</t>
         </is>
       </c>
-      <c r="C764" t="inlineStr">
+      <c r="C763" t="inlineStr">
         <is>
           <t>イスラム教 ,神聖</t>
         </is>
       </c>
     </row>
-    <row r="765">
-      <c r="A765" t="inlineStr">
+    <row r="764">
+      <c r="A764" t="inlineStr">
         <is>
           <t xml:space="preserve">「結婚前、結婚後」
 قبل الزواج، بعد الزواج
@@ -16528,19 +16506,19 @@
 2308 出典不明 </t>
         </is>
       </c>
-      <c r="B765" t="inlineStr">
+      <c r="B764" t="inlineStr">
         <is>
           <t>images/「結婚前、結婚後」_img1.jpg</t>
         </is>
       </c>
-      <c r="C765" t="inlineStr">
+      <c r="C764" t="inlineStr">
         <is>
           <t>BeforeAfter ,幸せ太り</t>
         </is>
       </c>
     </row>
-    <row r="766">
-      <c r="A766" t="inlineStr">
+    <row r="765">
+      <c r="A765" t="inlineStr">
         <is>
           <t xml:space="preserve">「驚きの価格で」بسعر رائع
 ビスィアル・ラーイア [bi-si*r raa'i*]
@@ -16549,19 +16527,19 @@
 2109 Jarir Bookstore </t>
         </is>
       </c>
-      <c r="B766" t="inlineStr">
+      <c r="B765" t="inlineStr">
         <is>
           <t>images/「驚きの価格で」_img1.jpg</t>
         </is>
       </c>
-      <c r="C766" t="inlineStr">
+      <c r="C765" t="inlineStr">
         <is>
           <t>広告 ,安値</t>
         </is>
       </c>
     </row>
-    <row r="767">
-      <c r="A767" t="inlineStr">
+    <row r="766">
+      <c r="A766" t="inlineStr">
         <is>
           <t xml:space="preserve">「我が魂と共に」مع نفسي
 マア・ナフスィ [ma*a nafs-iy]
@@ -16570,19 +16548,19 @@
 2110 出典不明 </t>
         </is>
       </c>
-      <c r="B767" t="inlineStr">
+      <c r="B766" t="inlineStr">
         <is>
           <t>images/「我が魂と共に」_img1.jpg</t>
         </is>
       </c>
-      <c r="C767" t="inlineStr">
+      <c r="C766" t="inlineStr">
         <is>
           <t>ソウル ,soul</t>
         </is>
       </c>
     </row>
-    <row r="768">
-      <c r="A768" t="inlineStr">
+    <row r="767">
+      <c r="A767" t="inlineStr">
         <is>
           <t xml:space="preserve">「暗い夜に」في ليلة مظلمة
  [fiy layla(tin) mu_Dhlima(tin)]
@@ -16591,19 +16569,19 @@
 2109 سلسلة الحلزونة </t>
         </is>
       </c>
-      <c r="B768" t="inlineStr">
+      <c r="B767" t="inlineStr">
         <is>
           <t>images/「暗い夜に」_img1.jpg</t>
         </is>
       </c>
-      <c r="C768" t="inlineStr">
+      <c r="C767" t="inlineStr">
         <is>
           <t>絵本</t>
         </is>
       </c>
     </row>
-    <row r="769">
-      <c r="A769" t="inlineStr">
+    <row r="768">
+      <c r="A768" t="inlineStr">
         <is>
           <t xml:space="preserve">「ゆっくりと」بشويش
 ビシワェーシ [bi-ShwySh]
@@ -16611,19 +16589,19 @@
 2109 出典不明 </t>
         </is>
       </c>
-      <c r="B769" t="inlineStr">
+      <c r="B768" t="inlineStr">
         <is>
           <t>images/「ゆっくりと」_img1.jpg</t>
         </is>
       </c>
-      <c r="C769" t="inlineStr">
+      <c r="C768" t="inlineStr">
         <is>
           <t>丸 ,円</t>
         </is>
       </c>
     </row>
-    <row r="770">
-      <c r="A770" t="inlineStr">
+    <row r="769">
+      <c r="A769" t="inlineStr">
         <is>
           <t xml:space="preserve">「この広い宇宙に…」
 في الكون الفسيح
@@ -16632,19 +16610,19 @@
 2308 wattpad </t>
         </is>
       </c>
-      <c r="B770" t="inlineStr">
+      <c r="B769" t="inlineStr">
         <is>
           <t>images/「この広い宇宙に…」_img1.jpg</t>
         </is>
       </c>
-      <c r="C770" t="inlineStr">
+      <c r="C769" t="inlineStr">
         <is>
           <t>アニメ ,宇宙</t>
         </is>
       </c>
     </row>
-    <row r="771">
-      <c r="A771" t="inlineStr">
+    <row r="770">
+      <c r="A770" t="inlineStr">
         <is>
           <t xml:space="preserve">「がんばって！」بالتوفيق
 ビッタウフィーク [bi^tawfiiq]
@@ -16652,19 +16630,19 @@
 2111 https://sites.google.com/site/mathmatic1905/ </t>
         </is>
       </c>
-      <c r="B771" t="inlineStr">
+      <c r="B770" t="inlineStr">
         <is>
           <t>images/「がんばって！」_img1.jpg</t>
         </is>
       </c>
-      <c r="C771" t="inlineStr">
+      <c r="C770" t="inlineStr">
         <is>
           <t>アラビア語</t>
         </is>
       </c>
     </row>
-    <row r="772">
-      <c r="A772" t="inlineStr">
+    <row r="771">
+      <c r="A771" t="inlineStr">
         <is>
           <t xml:space="preserve">「インターステラー」بين النجوم
 バイナ_ンヌジューム [bayna ^nujuum]
@@ -16672,19 +16650,19 @@
 2308 kmrghani </t>
         </is>
       </c>
-      <c r="B772" t="inlineStr">
+      <c r="B771" t="inlineStr">
         <is>
           <t>images/「インターステラー」_img1.jpg</t>
         </is>
       </c>
-      <c r="C772" t="inlineStr">
+      <c r="C771" t="inlineStr">
         <is>
           <t>映画 ,宇宙</t>
         </is>
       </c>
     </row>
-    <row r="773">
-      <c r="A773" t="inlineStr">
+    <row r="772">
+      <c r="A772" t="inlineStr">
         <is>
           <t xml:space="preserve">「アラビア語で」بالعربية
 ビ_ルアラビーヤ [bi-l-*arabiyya]
@@ -16693,19 +16671,19 @@
 1811 </t>
         </is>
       </c>
-      <c r="B773" t="inlineStr">
+      <c r="B772" t="inlineStr">
         <is>
           <t>images/「アラビア語で」_img1.jpg</t>
         </is>
       </c>
-      <c r="C773" t="inlineStr">
+      <c r="C772" t="inlineStr">
         <is>
           <t>ニュース ,CNN</t>
         </is>
       </c>
     </row>
-    <row r="774">
-      <c r="A774" t="inlineStr">
+    <row r="773">
+      <c r="A773" t="inlineStr">
         <is>
           <t xml:space="preserve">「17世紀に発明されて以来…」
 منذ اختراعه بالقرن السابع عشر
@@ -16713,19 +16691,19 @@
 2308 https://twitter.com/SciTalk2U/status/1450888395815854080 </t>
         </is>
       </c>
-      <c r="B774" t="inlineStr">
+      <c r="B773" t="inlineStr">
         <is>
           <t>images/「17世紀に発明されて以来…」_img1.jpg</t>
         </is>
       </c>
-      <c r="C774" t="inlineStr">
+      <c r="C773" t="inlineStr">
         <is>
           <t>手書き語学 ,アラビア語 ,望遠鏡</t>
         </is>
       </c>
     </row>
-    <row r="775">
-      <c r="A775" t="inlineStr">
+    <row r="774">
+      <c r="A774" t="inlineStr">
         <is>
           <t xml:space="preserve">「私できるよ」إنّني أستطيع
 インナニー・アスタティーウ ['inna-niy 'a-sta_tii*u]
@@ -16734,19 +16712,19 @@
 2412 سلسلة الحلزونة </t>
         </is>
       </c>
-      <c r="B775" t="inlineStr">
+      <c r="B774" t="inlineStr">
         <is>
           <t>images/「私できるよ」_img1.jpg</t>
         </is>
       </c>
-      <c r="C775" t="inlineStr">
+      <c r="C774" t="inlineStr">
         <is>
           <t>絵本 ,こども</t>
         </is>
       </c>
     </row>
-    <row r="776">
-      <c r="A776" t="inlineStr">
+    <row r="775">
+      <c r="A775" t="inlineStr">
         <is>
           <t xml:space="preserve">「問題なし」مافيش مشكلة
 マフィーシムシュキラ [ma-fy-Sh muShkila]
@@ -16755,19 +16733,19 @@
 2109 tanzerin.theshop </t>
         </is>
       </c>
-      <c r="B776" t="inlineStr">
+      <c r="B775" t="inlineStr">
         <is>
           <t>images/「問題なし」_img1.jpg</t>
         </is>
       </c>
-      <c r="C776" t="inlineStr">
+      <c r="C775" t="inlineStr">
         <is>
           <t>シャツ ,キッズ</t>
         </is>
       </c>
     </row>
-    <row r="777">
-      <c r="A777" t="inlineStr">
+    <row r="776">
+      <c r="A776" t="inlineStr">
         <is>
           <t xml:space="preserve">「不可能はない」مفيش مستحيل
 マフィーシ・ムスタヒール [ma-fy-Sh mustaHiil]
@@ -16776,19 +16754,19 @@
 2109 أموج </t>
         </is>
       </c>
-      <c r="B777" t="inlineStr">
+      <c r="B776" t="inlineStr">
         <is>
           <t>images/「不可能はない」_img1.jpg</t>
         </is>
       </c>
-      <c r="C777" t="inlineStr">
+      <c r="C776" t="inlineStr">
         <is>
           <t>ポジティブ ,挑戦</t>
         </is>
       </c>
     </row>
-    <row r="778">
-      <c r="A778" t="inlineStr">
+    <row r="777">
+      <c r="A777" t="inlineStr">
         <is>
           <t xml:space="preserve">「等々」إلخ
 イラク ['ilaKh]
@@ -16797,19 +16775,19 @@
 2201 出典不明 </t>
         </is>
       </c>
-      <c r="B778" t="inlineStr">
+      <c r="B777" t="inlineStr">
         <is>
           <t>images/「等々」_img1.jpg</t>
         </is>
       </c>
-      <c r="C778" t="inlineStr">
+      <c r="C777" t="inlineStr">
         <is>
           <t>etc ,とんち</t>
         </is>
       </c>
     </row>
-    <row r="779">
-      <c r="A779" t="inlineStr">
+    <row r="778">
+      <c r="A778" t="inlineStr">
         <is>
           <t xml:space="preserve">⁦「調子どう？」⁩شلونَك؟
 シュローナク？ [Sh-loon-ak?]
@@ -16818,19 +16796,19 @@
 2202 Jozoor Team. </t>
         </is>
       </c>
-      <c r="B779" t="inlineStr">
+      <c r="B778" t="inlineStr">
         <is>
           <t>images/⁦「調子どう？」⁩_img1.jpg</t>
         </is>
       </c>
-      <c r="C779" t="inlineStr">
+      <c r="C778" t="inlineStr">
         <is>
           <t>洒落 ,ルービックキューブ</t>
         </is>
       </c>
     </row>
-    <row r="780">
-      <c r="A780" t="inlineStr">
+    <row r="779">
+      <c r="A779" t="inlineStr">
         <is>
           <t xml:space="preserve">「行くな」ماتروحش
 マトロホシ [ma-troH-Sh]
@@ -16839,19 +16817,19 @@
 2411 triiq tumblr </t>
         </is>
       </c>
-      <c r="B780" t="inlineStr">
+      <c r="B779" t="inlineStr">
         <is>
           <t>images/「行くな」_img1.jpg</t>
         </is>
       </c>
-      <c r="C780" t="inlineStr">
+      <c r="C779" t="inlineStr">
         <is>
           <t>ロゴ ,デザイン ,嵐</t>
         </is>
       </c>
     </row>
-    <row r="781">
-      <c r="A781" t="inlineStr">
+    <row r="780">
+      <c r="A780" t="inlineStr">
         <is>
           <t xml:space="preserve">⁦「元気？」⁩شلونَك؟
 シュローナク？ [Sh-loon-ak?]
@@ -16862,19 +16840,19 @@
 2202 出典不明 </t>
         </is>
       </c>
-      <c r="B781" t="inlineStr">
+      <c r="B780" t="inlineStr">
         <is>
           <t>images/⁦「元気？」⁩_img1.jpg</t>
         </is>
       </c>
-      <c r="C781" t="inlineStr">
+      <c r="C780" t="inlineStr">
         <is>
           <t>洒落 ,挨拶</t>
         </is>
       </c>
     </row>
-    <row r="782">
-      <c r="A782" t="inlineStr">
+    <row r="781">
+      <c r="A781" t="inlineStr">
         <is>
           <t xml:space="preserve">「気分が良いぞう」I فيل GOOD
 アイ・フィール・グッド [ai fiyl gud]
@@ -16883,19 +16861,19 @@
 2308 出典不明 </t>
         </is>
       </c>
-      <c r="B782" t="inlineStr">
+      <c r="B781" t="inlineStr">
         <is>
           <t>images/「気分が良いぞう」_img1.jpg</t>
         </is>
       </c>
-      <c r="C782" t="inlineStr">
+      <c r="C781" t="inlineStr">
         <is>
           <t>洒落 ,和訳</t>
         </is>
       </c>
     </row>
-    <row r="783">
-      <c r="A783" t="inlineStr">
+    <row r="782">
+      <c r="A782" t="inlineStr">
         <is>
           <t xml:space="preserve">「レットイットゴー／let it go」
 ليت اِت غو
@@ -16904,19 +16882,19 @@
 2109 出典不明 </t>
         </is>
       </c>
-      <c r="B783" t="inlineStr">
+      <c r="B782" t="inlineStr">
         <is>
           <t>images/「レットイットゴー／let it go_img1.jpg</t>
         </is>
       </c>
-      <c r="C783" t="inlineStr">
+      <c r="C782" t="inlineStr">
         <is>
           <t>折衷 ,アナ雪</t>
         </is>
       </c>
     </row>
-    <row r="784">
-      <c r="A784" t="inlineStr">
+    <row r="783">
+      <c r="A783" t="inlineStr">
         <is>
           <t xml:space="preserve">「ようこそ」اهلا وسهلا
 アハラン・ワサハラン ['ahlan wa-sahlan]
@@ -16924,19 +16902,19 @@
 2106 behance Anwar Al Eissa </t>
         </is>
       </c>
-      <c r="B784" t="inlineStr">
+      <c r="B783" t="inlineStr">
         <is>
           <t>images/「ようこそ」_img1.jpg</t>
         </is>
       </c>
-      <c r="C784" t="inlineStr">
+      <c r="C783" t="inlineStr">
         <is>
           <t>アラビア語</t>
         </is>
       </c>
     </row>
-    <row r="785">
-      <c r="A785" t="inlineStr">
+    <row r="784">
+      <c r="A784" t="inlineStr">
         <is>
           <t xml:space="preserve">「まぁ何というサプライズでしょう」
 يا لها من مفاجأة
@@ -16947,19 +16925,19 @@
 2108 neelwafurat com </t>
         </is>
       </c>
-      <c r="B785" t="inlineStr">
+      <c r="B784" t="inlineStr">
         <is>
           <t>images/「まぁ何というサプライズでしょう」_img1.jpg</t>
         </is>
       </c>
-      <c r="C785" t="inlineStr">
+      <c r="C784" t="inlineStr">
         <is>
           <t>中国語 ,学習</t>
         </is>
       </c>
     </row>
-    <row r="786">
-      <c r="A786" t="inlineStr">
+    <row r="785">
+      <c r="A785" t="inlineStr">
         <is>
           <t xml:space="preserve">「ハックション」اتشوو
 アチュー！ ['aatShuu]
@@ -16967,19 +16945,19 @@
 1811 </t>
         </is>
       </c>
-      <c r="B786" t="inlineStr">
+      <c r="B785" t="inlineStr">
         <is>
           <t>images/「ハックション」_img1.jpg</t>
         </is>
       </c>
-      <c r="C786" t="inlineStr">
+      <c r="C785" t="inlineStr">
         <is>
           <t>あらびあや</t>
         </is>
       </c>
     </row>
-    <row r="787">
-      <c r="A787" t="inlineStr">
+    <row r="786">
+      <c r="A786" t="inlineStr">
         <is>
           <t xml:space="preserve">「スブハーナッラー」「アルハムドゥリッラー」「アッラーアクバル」
 سبحان الله
@@ -16990,19 +16968,19 @@
 2308 dribbble com </t>
         </is>
       </c>
-      <c r="B787" t="inlineStr">
+      <c r="B786" t="inlineStr">
         <is>
           <t>images/「スブハーナッラー」「アルハムドゥリッ_img1.jpg</t>
         </is>
       </c>
-      <c r="C787" t="inlineStr">
+      <c r="C786" t="inlineStr">
         <is>
           <t>四角 ,コンパクト</t>
         </is>
       </c>
     </row>
-    <row r="788">
-      <c r="A788" t="inlineStr">
+    <row r="787">
+      <c r="A787" t="inlineStr">
         <is>
           <t xml:space="preserve">「すごく美味しい！」لذيذ جدًا
 ラズィーズ・ジッダン [laDhiiDh jiddan]
@@ -17011,19 +16989,19 @@
 2109 goodreads com </t>
         </is>
       </c>
-      <c r="B788" t="inlineStr">
+      <c r="B787" t="inlineStr">
         <is>
           <t>images/「すごく美味しい！」_img1.jpg</t>
         </is>
       </c>
-      <c r="C788" t="inlineStr">
+      <c r="C787" t="inlineStr">
         <is>
           <t>フレーズ ,感想</t>
         </is>
       </c>
     </row>
-    <row r="789">
-      <c r="A789" t="inlineStr">
+    <row r="788">
+      <c r="A788" t="inlineStr">
         <is>
           <t xml:space="preserve">「しとしと、雨」تك تك يا مطر
 ティクティク [tik tik yaa ma_tar]
@@ -17032,19 +17010,19 @@
 2308 出典不明 </t>
         </is>
       </c>
-      <c r="B789" t="inlineStr">
+      <c r="B788" t="inlineStr">
         <is>
           <t>images/「しとしと、雨」_img1.jpg</t>
         </is>
       </c>
-      <c r="C789" t="inlineStr">
+      <c r="C788" t="inlineStr">
         <is>
           <t>天気 ,梅雨</t>
         </is>
       </c>
     </row>
-    <row r="790">
-      <c r="A790" t="inlineStr">
+    <row r="789">
+      <c r="A789" t="inlineStr">
         <is>
           <t xml:space="preserve">「さかさま」رأساً على عقب
 ラッアサン・アラー・アケブ [ra'san *alaa *aqib]
@@ -17052,19 +17030,19 @@
 2109 出典不明 </t>
         </is>
       </c>
-      <c r="B790" t="inlineStr">
+      <c r="B789" t="inlineStr">
         <is>
           <t>images/「さかさま」_img1.jpg</t>
         </is>
       </c>
-      <c r="C790" t="inlineStr">
+      <c r="C789" t="inlineStr">
         <is>
           <t>壁 ,上下</t>
         </is>
       </c>
     </row>
-    <row r="791">
-      <c r="A791" t="inlineStr">
+    <row r="790">
+      <c r="A790" t="inlineStr">
         <is>
           <t xml:space="preserve">「エジプトよどこへ行った」
 فينك يا مصر؟
@@ -17074,19 +17052,19 @@
 1809 shehabfawzy1.tumblr </t>
         </is>
       </c>
-      <c r="B791" t="inlineStr">
+      <c r="B790" t="inlineStr">
         <is>
           <t>images/「エジプトよどこへ行った」_img1.jpg</t>
         </is>
       </c>
-      <c r="C791" t="inlineStr">
+      <c r="C790" t="inlineStr">
         <is>
           <t>ピラミッド ,歴史</t>
         </is>
       </c>
     </row>
-    <row r="792">
-      <c r="A792" t="inlineStr">
+    <row r="791">
+      <c r="A791" t="inlineStr">
         <is>
           <t xml:space="preserve">「ありがとう」شكراً
 シュクラン [Shukran]
@@ -17094,19 +17072,19 @@
 2109 出典不明 </t>
         </is>
       </c>
-      <c r="B792" t="inlineStr">
+      <c r="B791" t="inlineStr">
         <is>
           <t>images/「ありがとう」_img1.jpg</t>
         </is>
       </c>
-      <c r="C792" t="inlineStr">
+      <c r="C791" t="inlineStr">
         <is>
           <t>挨拶 ,文字</t>
         </is>
       </c>
     </row>
-    <row r="793">
-      <c r="A793" t="inlineStr">
+    <row r="792">
+      <c r="A792" t="inlineStr">
         <is>
           <t xml:space="preserve">「昼寝の時間だ」
 إنه وقت القيلولة
@@ -17115,12 +17093,12 @@
 2501 https://x.com/NatGeoMagArab/status/1858049951579910486 </t>
         </is>
       </c>
-      <c r="B793" t="inlineStr">
+      <c r="B792" t="inlineStr">
         <is>
           <t>images/「昼寝の時間だ」_img1.jpg</t>
         </is>
       </c>
-      <c r="C793" t="inlineStr">
+      <c r="C792" t="inlineStr">
         <is>
           <t>手書き語学 ,アラビア語 ,ペンギン</t>
         </is>

--- a/posts.xlsx
+++ b/posts.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C791"/>
+  <dimension ref="A1:C790"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -13093,28 +13093,6 @@
     <row r="603">
       <c r="A603" t="inlineStr">
         <is>
-          <t xml:space="preserve">「黙ってもらえます？」
-ممكن تعيرنا سكوتك؟
-[mumkin tu-*iiru-naa sukuuta-k?]
-⁦「〜出来る」( ممكن )[mumkin …]・「あなたは貸す」( تعير )[tu-*iir]・「沈黙」( سكوت )[sukuut]・「あなたの」[-k]⁩ 
-黙って（だまって）
-2308 Basel26 </t>
-        </is>
-      </c>
-      <c r="B603" t="inlineStr">
-        <is>
-          <t>images/「黙ってもらえます？」_img1.jpg</t>
-        </is>
-      </c>
-      <c r="C603" t="inlineStr">
-        <is>
-          <t>音量 ,ボリューム</t>
-        </is>
-      </c>
-    </row>
-    <row r="604">
-      <c r="A604" t="inlineStr">
-        <is>
           <t xml:space="preserve">「眠りたいです」
 أُريدُ أَن أَنام
 ['u-riidu 'an 'a-naam]
@@ -13123,19 +13101,19 @@
 2109 goodreads com </t>
         </is>
       </c>
-      <c r="B604" t="inlineStr">
+      <c r="B603" t="inlineStr">
         <is>
           <t>images/「眠りたいです」_img1.jpg</t>
         </is>
       </c>
-      <c r="C604" t="inlineStr">
+      <c r="C603" t="inlineStr">
         <is>
           <t>絵本</t>
         </is>
       </c>
     </row>
-    <row r="605">
-      <c r="A605" t="inlineStr">
+    <row r="604">
+      <c r="A604" t="inlineStr">
         <is>
           <t xml:space="preserve">「飛びたい！」أُريد أن أطير
 ウリードゥ・アン・アティール ['u-riidu 'an 'a-_tiir]
@@ -13144,19 +13122,19 @@
 2308 出典不明 </t>
         </is>
       </c>
-      <c r="B605" t="inlineStr">
+      <c r="B604" t="inlineStr">
         <is>
           <t>images/「飛びたい！」_img1.jpg</t>
         </is>
       </c>
-      <c r="C605" t="inlineStr">
+      <c r="C604" t="inlineStr">
         <is>
           <t>鳥 ,希望</t>
         </is>
       </c>
     </row>
-    <row r="606">
-      <c r="A606" t="inlineStr">
+    <row r="605">
+      <c r="A605" t="inlineStr">
         <is>
           <t xml:space="preserve">「うちゅうへとびたい」
 أُريدُ أَنْ أَطيرَ إلى الفَضاء
@@ -13165,19 +13143,19 @@
 2308 mybookshelf co </t>
         </is>
       </c>
-      <c r="B606" t="inlineStr">
+      <c r="B605" t="inlineStr">
         <is>
           <t>images/「うちゅうへとびたい」_img1.jpg</t>
         </is>
       </c>
-      <c r="C606" t="inlineStr">
+      <c r="C605" t="inlineStr">
         <is>
           <t>絵本 ,宇宙</t>
         </is>
       </c>
     </row>
-    <row r="607">
-      <c r="A607" t="inlineStr">
+    <row r="606">
+      <c r="A606" t="inlineStr">
         <is>
           <t xml:space="preserve">「とても愛しています」
 أُحِبّك جِدّاً
@@ -13187,19 +13165,19 @@
 2308 hobe cc </t>
         </is>
       </c>
-      <c r="B607" t="inlineStr">
+      <c r="B606" t="inlineStr">
         <is>
           <t>images/「とても愛しています」_img1.jpg</t>
         </is>
       </c>
-      <c r="C607" t="inlineStr">
+      <c r="C606" t="inlineStr">
         <is>
           <t>恋 ,love</t>
         </is>
       </c>
     </row>
-    <row r="608">
-      <c r="A608" t="inlineStr">
+    <row r="607">
+      <c r="A607" t="inlineStr">
         <is>
           <t xml:space="preserve">「あす日が昇るだろう。私は朝が大好きだ」
 غدا ستشرق الشمس وأحب الصباح كثيرا
@@ -13208,19 +13186,19 @@
 2105 warag-3nb.tumblr com </t>
         </is>
       </c>
-      <c r="B608" t="inlineStr">
+      <c r="B607" t="inlineStr">
         <is>
           <t>images/「あす日が昇るだろう。私は朝が大好きだ_img1.jpg,images/ 「あす日が昇るだろう。私は朝が大好きだ_img2.jpg</t>
         </is>
       </c>
-      <c r="C608" t="inlineStr">
+      <c r="C607" t="inlineStr">
         <is>
           <t>おやすみ ,壁</t>
         </is>
       </c>
     </row>
-    <row r="609">
-      <c r="A609" t="inlineStr">
+    <row r="608">
+      <c r="A608" t="inlineStr">
         <is>
           <t xml:space="preserve">「きみは何をえらぶ？」
 ماذا تختار؟
@@ -13230,19 +13208,19 @@
 2109 embadomjp org </t>
         </is>
       </c>
-      <c r="B609" t="inlineStr">
+      <c r="B608" t="inlineStr">
         <is>
           <t>images/「きみは何をえらぶ？」_img1.jpg</t>
         </is>
       </c>
-      <c r="C609" t="inlineStr">
+      <c r="C608" t="inlineStr">
         <is>
           <t>優柔不断 ,絵本</t>
         </is>
       </c>
     </row>
-    <row r="610">
-      <c r="A610" t="inlineStr">
+    <row r="609">
+      <c r="A609" t="inlineStr">
         <is>
           <t xml:space="preserve">「ちょっと静けさが必要な時もある」
 في بعض الأوقات نحتاج لشوية هدوء
@@ -13252,19 +13230,19 @@
 2308 IN49r </t>
         </is>
       </c>
-      <c r="B610" t="inlineStr">
+      <c r="B609" t="inlineStr">
         <is>
           <t>images/「ちょっと静けさが必要な時もある」_img1.jpg</t>
         </is>
       </c>
-      <c r="C610" t="inlineStr">
+      <c r="C609" t="inlineStr">
         <is>
           <t>ミュート ,精神</t>
         </is>
       </c>
     </row>
-    <row r="611">
-      <c r="A611" t="inlineStr">
+    <row r="610">
+      <c r="A610" t="inlineStr">
         <is>
           <t xml:space="preserve">「逃げるな。全力でぶつかれ」
 لا تهرب اصطدم بكل قوتك
@@ -13274,19 +13252,19 @@
 2308 https://risingvibes.tumblr.com/post/189545775129 </t>
         </is>
       </c>
-      <c r="B611" t="inlineStr">
+      <c r="B610" t="inlineStr">
         <is>
           <t>images/「逃げるな。全力でぶつかれ」_img1.jpg</t>
         </is>
       </c>
-      <c r="C611" t="inlineStr">
+      <c r="C610" t="inlineStr">
         <is>
           <t>応援 ,力</t>
         </is>
       </c>
     </row>
-    <row r="612">
-      <c r="A612" t="inlineStr">
+    <row r="611">
+      <c r="A611" t="inlineStr">
         <is>
           <t xml:space="preserve">「着るのだいすき」
 أُحِبُ أَن أَرتَدِيَ
@@ -13296,19 +13274,19 @@
 2308 https://kitab.firmabikes.ru/epub-_hb_n_rtdy_5187.html </t>
         </is>
       </c>
-      <c r="B612" t="inlineStr">
+      <c r="B611" t="inlineStr">
         <is>
           <t>images/「着るのだいすき」_img1.jpg</t>
         </is>
       </c>
-      <c r="C612" t="inlineStr">
+      <c r="C611" t="inlineStr">
         <is>
           <t xml:space="preserve">絵本 ,ファッション </t>
         </is>
       </c>
     </row>
-    <row r="613">
-      <c r="A613" t="inlineStr">
+    <row r="612">
+      <c r="A612" t="inlineStr">
         <is>
           <t xml:space="preserve">「車のバッテリーが要る！」
 نحتاج بطارية سيارة
@@ -13318,19 +13296,19 @@
 2308 instagram roaa_27 </t>
         </is>
       </c>
-      <c r="B613" t="inlineStr">
+      <c r="B612" t="inlineStr">
         <is>
           <t>images/「車のバッテリーが要る！」_img1.jpg</t>
         </is>
       </c>
-      <c r="C613" t="inlineStr">
+      <c r="C612" t="inlineStr">
         <is>
           <t>スマホ ,充電</t>
         </is>
       </c>
     </row>
-    <row r="614">
-      <c r="A614" t="inlineStr">
+    <row r="613">
+      <c r="A613" t="inlineStr">
         <is>
           <t xml:space="preserve">「今日は幸せでいることにしました」
 اخترت أن أكون سعيدا اليوم
@@ -13340,19 +13318,19 @@
 2109 awaasha tumblr </t>
         </is>
       </c>
-      <c r="B614" t="inlineStr">
+      <c r="B613" t="inlineStr">
         <is>
           <t>images/「今日は幸せでいることにしました」_img1.jpg</t>
         </is>
       </c>
-      <c r="C614" t="inlineStr">
+      <c r="C613" t="inlineStr">
         <is>
           <t>心構え ,happy</t>
         </is>
       </c>
     </row>
-    <row r="615">
-      <c r="A615" t="inlineStr">
+    <row r="614">
+      <c r="A614" t="inlineStr">
         <is>
           <t xml:space="preserve">「理想的なスイカの選び方」
 كيف تختار البطيخة المُثلى؟
@@ -13362,19 +13340,19 @@
 2308 bit ly/octmel </t>
         </is>
       </c>
-      <c r="B615" t="inlineStr">
+      <c r="B614" t="inlineStr">
         <is>
           <t>images/「理想的なスイカの選び方」_img1.jpg</t>
         </is>
       </c>
-      <c r="C615" t="inlineStr">
+      <c r="C614" t="inlineStr">
         <is>
           <t>八百屋 ,西瓜</t>
         </is>
       </c>
     </row>
-    <row r="616">
-      <c r="A616" t="inlineStr">
+    <row r="615">
+      <c r="A615" t="inlineStr">
         <is>
           <t xml:space="preserve">「お問い合わせください」
 اتصل بنا
@@ -13384,19 +13362,19 @@
 2308 mtawir.blogspot com </t>
         </is>
       </c>
-      <c r="B616" t="inlineStr">
+      <c r="B615" t="inlineStr">
         <is>
           <t>images/「お問い合わせください」_img1.jpg</t>
         </is>
       </c>
-      <c r="C616" t="inlineStr">
+      <c r="C615" t="inlineStr">
         <is>
           <t>広告 ,電話</t>
         </is>
       </c>
     </row>
-    <row r="617">
-      <c r="A617" t="inlineStr">
+    <row r="616">
+      <c r="A616" t="inlineStr">
         <is>
           <t xml:space="preserve">「両方の動物が海岸の火山岩の亀裂の中に定住している」
 يحتل كلا الحيوانين شقوقًا في صخور الساحل البركانية
@@ -13404,19 +13382,19 @@
 2507 https://x.com/NatGeoMagArab/status/1925167200056521151 </t>
         </is>
       </c>
-      <c r="B617" t="inlineStr">
+      <c r="B616" t="inlineStr">
         <is>
           <t>images/「両方の動物が海岸の火山岩の亀裂の中に_img1.jpg,images/「両方の動物が海岸の火山岩の亀裂の中に_img2.jpg</t>
         </is>
       </c>
-      <c r="C617" t="inlineStr">
+      <c r="C616" t="inlineStr">
         <is>
           <t>手書き語学 ,アラビア語 ,イグアナ</t>
         </is>
       </c>
     </row>
-    <row r="618">
-      <c r="A618" t="inlineStr">
+    <row r="617">
+      <c r="A617" t="inlineStr">
         <is>
           <t xml:space="preserve">「命じられたように正しき道を辿れ」
 واستقم كما أمرت
@@ -13426,19 +13404,19 @@
 2308 Ahmed Madyan </t>
         </is>
       </c>
-      <c r="B618" t="inlineStr">
+      <c r="B617" t="inlineStr">
         <is>
           <t>images/「命じられたように正しき道を辿れ」_img1.jpg</t>
         </is>
       </c>
-      <c r="C618" t="inlineStr">
+      <c r="C617" t="inlineStr">
         <is>
           <t>書道 ,アート</t>
         </is>
       </c>
     </row>
-    <row r="619">
-      <c r="A619" t="inlineStr">
+    <row r="618">
+      <c r="A618" t="inlineStr">
         <is>
           <t xml:space="preserve">「くつろぎなさい」استكن
 イスタキンナ [istakinna]
@@ -13446,19 +13424,19 @@
 2603 m2ff tumblr com </t>
         </is>
       </c>
-      <c r="B619" t="inlineStr">
+      <c r="B618" t="inlineStr">
         <is>
           <t>images/「くつろぎなさい」.jpeg</t>
         </is>
       </c>
-      <c r="C619" t="inlineStr">
+      <c r="C618" t="inlineStr">
         <is>
           <t>relax ,コーヒー</t>
         </is>
       </c>
     </row>
-    <row r="620">
-      <c r="A620" t="inlineStr">
+    <row r="619">
+      <c r="A619" t="inlineStr">
         <is>
           <t xml:space="preserve">「彼は応えるだろう」سيستجيب 
 サヤスタジーブ [sa-ya-stajiibu]
@@ -13467,19 +13445,19 @@
 1811 kareem mrghani </t>
         </is>
       </c>
-      <c r="B620" t="inlineStr">
+      <c r="B619" t="inlineStr">
         <is>
           <t>images/「彼は応えるだろう」_img1.jpg</t>
         </is>
       </c>
-      <c r="C620" t="inlineStr">
+      <c r="C619" t="inlineStr">
         <is>
           <t>縦書き ,現代アート</t>
         </is>
       </c>
     </row>
-    <row r="621">
-      <c r="A621" t="inlineStr">
+    <row r="620">
+      <c r="A620" t="inlineStr">
         <is>
           <t xml:space="preserve">「アラビア語が好き」
 أنا أُحبّ لُغتي
@@ -13489,19 +13467,19 @@
 2308 出典不明 </t>
         </is>
       </c>
-      <c r="B621" t="inlineStr">
+      <c r="B620" t="inlineStr">
         <is>
           <t>images/「アラビア語が好き」_img1.jpg</t>
         </is>
       </c>
-      <c r="C621" t="inlineStr">
+      <c r="C620" t="inlineStr">
         <is>
           <t>和訳 ,こども</t>
         </is>
       </c>
     </row>
-    <row r="622">
-      <c r="A622" t="inlineStr">
+    <row r="621">
+      <c r="A621" t="inlineStr">
         <is>
           <t xml:space="preserve">「私はサッカーが好きです」
 أنا أُحِبُّ كُرةَ القَدَم
@@ -13511,19 +13489,19 @@
 2109 Arabic With Nadia </t>
         </is>
       </c>
-      <c r="B622" t="inlineStr">
+      <c r="B621" t="inlineStr">
         <is>
           <t>images/「私はサッカーが好きです」_img1.jpg</t>
         </is>
       </c>
-      <c r="C622" t="inlineStr">
+      <c r="C621" t="inlineStr">
         <is>
           <t>自由時間 ,例文</t>
         </is>
       </c>
     </row>
-    <row r="623">
-      <c r="A623" t="inlineStr">
+    <row r="622">
+      <c r="A622" t="inlineStr">
         <is>
           <t xml:space="preserve">「これ、私の眼鏡じゃありません」
 هٰذِهِ لَيْسَتْ نَظَّارَاتِي
@@ -13533,19 +13511,19 @@
 2509 </t>
         </is>
       </c>
-      <c r="B623" t="inlineStr">
+      <c r="B622" t="inlineStr">
         <is>
           <t>images/「これ、私の眼鏡じゃありません」_img1.jpg</t>
         </is>
       </c>
-      <c r="C623" t="inlineStr">
+      <c r="C622" t="inlineStr">
         <is>
           <t>あらびあや</t>
         </is>
       </c>
     </row>
-    <row r="624">
-      <c r="A624" t="inlineStr">
+    <row r="623">
+      <c r="A623" t="inlineStr">
         <is>
           <t xml:space="preserve">「我らも米を食います」
 نحن أيضاً نأكل الأرز
@@ -13555,19 +13533,19 @@
 1809 </t>
         </is>
       </c>
-      <c r="B624" t="inlineStr">
+      <c r="B623" t="inlineStr">
         <is>
           <t>images/「我らも米を食います」_img1.jpg</t>
         </is>
       </c>
-      <c r="C624" t="inlineStr">
+      <c r="C623" t="inlineStr">
         <is>
           <t>あらびあや</t>
         </is>
       </c>
     </row>
-    <row r="625">
-      <c r="A625" t="inlineStr">
+    <row r="624">
+      <c r="A624" t="inlineStr">
         <is>
           <t xml:space="preserve">「ひとりでできるもん！」
 أنا أستطيع أن أفعله وحدي
@@ -13576,19 +13554,19 @@
 2105 </t>
         </is>
       </c>
-      <c r="B625" t="inlineStr">
+      <c r="B624" t="inlineStr">
         <is>
           <t>images/「ひとりでできるもん！」_img1.jpg</t>
         </is>
       </c>
-      <c r="C625" t="inlineStr">
+      <c r="C624" t="inlineStr">
         <is>
           <t>あらびあや</t>
         </is>
       </c>
     </row>
-    <row r="626">
-      <c r="A626" t="inlineStr">
+    <row r="625">
+      <c r="A625" t="inlineStr">
         <is>
           <t xml:space="preserve">「恋しくないと言っている時は恋しい」
 أُريدُك حينَ أَقُولُ أَنا لا أُريدُك
@@ -13598,19 +13576,19 @@
 2308 DARWISHISM </t>
         </is>
       </c>
-      <c r="B626" t="inlineStr">
+      <c r="B625" t="inlineStr">
         <is>
           <t>images/「恋しくないと言っている時は恋しい」_img1.jpg</t>
         </is>
       </c>
-      <c r="C626" t="inlineStr">
+      <c r="C625" t="inlineStr">
         <is>
           <t>本音 ,恋愛</t>
         </is>
       </c>
     </row>
-    <row r="627">
-      <c r="A627" t="inlineStr">
+    <row r="626">
+      <c r="A626" t="inlineStr">
         <is>
           <t xml:space="preserve">「私は〜する」
 ⁦「着る」：( أنا ألبس )['ana 'a-lbas]⁩
@@ -13621,19 +13599,19 @@
 2109 RABIE </t>
         </is>
       </c>
-      <c r="B627" t="inlineStr">
+      <c r="B626" t="inlineStr">
         <is>
           <t>images/「私は〜する」_img1.jpg,images/「私は〜する」_img2.jpg,images/「私は〜する」_img3.jpg,images/「私は〜する」_img4.jpg</t>
         </is>
       </c>
-      <c r="C627" t="inlineStr">
+      <c r="C626" t="inlineStr">
         <is>
           <t>動詞 ,絵本</t>
         </is>
       </c>
     </row>
-    <row r="628">
-      <c r="A628" t="inlineStr">
+    <row r="627">
+      <c r="A627" t="inlineStr">
         <is>
           <t xml:space="preserve">「彼は完璧ではない。私は彼の欠点については目をつむった」
 هو ليس كامل. أنا أعميت نفسي عن سيئاته
@@ -13642,19 +13620,19 @@
 2308 _NOHA </t>
         </is>
       </c>
-      <c r="B628" t="inlineStr">
+      <c r="B627" t="inlineStr">
         <is>
           <t>images/「彼は完璧ではない。私は彼の欠点につい_img1.jpg</t>
         </is>
       </c>
-      <c r="C628" t="inlineStr">
+      <c r="C627" t="inlineStr">
         <is>
           <t>愛 ,寛容</t>
         </is>
       </c>
     </row>
-    <row r="629">
-      <c r="A629" t="inlineStr">
+    <row r="628">
+      <c r="A628" t="inlineStr">
         <is>
           <t xml:space="preserve">「この子トラは検疫期間中に生まれた」
 صغير النمر هذا ولد في زمن الحجر الصحي
@@ -13663,19 +13641,19 @@
 2310 https://www.akhbaralaan.net/?p=434924 </t>
         </is>
       </c>
-      <c r="B629" t="inlineStr">
+      <c r="B628" t="inlineStr">
         <is>
           <t>images/「この子トラは検疫期間中に生まれた」_img1.jpg</t>
         </is>
       </c>
-      <c r="C629" t="inlineStr">
+      <c r="C628" t="inlineStr">
         <is>
           <t>Covid ,メキシコ</t>
         </is>
       </c>
     </row>
-    <row r="630">
-      <c r="A630" t="inlineStr">
+    <row r="629">
+      <c r="A629" t="inlineStr">
         <is>
           <t xml:space="preserve">「睡眠の素晴らしさに匹敵するものは無い！」
 وجمال النوم ليس له مثيل
@@ -13684,19 +13662,19 @@
 2308 arabzy tumblr </t>
         </is>
       </c>
-      <c r="B630" t="inlineStr">
+      <c r="B629" t="inlineStr">
         <is>
           <t>images/「睡眠の素晴らしさに匹敵するものは無い_img1.jpg</t>
         </is>
       </c>
-      <c r="C630" t="inlineStr">
+      <c r="C629" t="inlineStr">
         <is>
           <t>オフトゥン ,おやすみ</t>
         </is>
       </c>
     </row>
-    <row r="631">
-      <c r="A631" t="inlineStr">
+    <row r="630">
+      <c r="A630" t="inlineStr">
         <is>
           <t xml:space="preserve">「大器晩成」
 الأشياء العظيمة تأخذ وقت
@@ -13706,19 +13684,19 @@
 2109 出典不明 </t>
         </is>
       </c>
-      <c r="B631" t="inlineStr">
+      <c r="B630" t="inlineStr">
         <is>
           <t>images/「大器晩成」_img1.jpg</t>
         </is>
       </c>
-      <c r="C631" t="inlineStr">
+      <c r="C630" t="inlineStr">
         <is>
           <t>ことわざ ,和訳</t>
         </is>
       </c>
     </row>
-    <row r="632">
-      <c r="A632" t="inlineStr">
+    <row r="631">
+      <c r="A631" t="inlineStr">
         <is>
           <t xml:space="preserve">「コーヒーは急には飲まれない」
 القهْوة لا تشرَب عَلى عَجلْ
@@ -13729,19 +13707,19 @@
 2012 Ahmed Madyan </t>
         </is>
       </c>
-      <c r="B632" t="inlineStr">
+      <c r="B631" t="inlineStr">
         <is>
           <t>images/「コーヒーは急には飲まれない」_img1.jpg</t>
         </is>
       </c>
-      <c r="C632" t="inlineStr">
+      <c r="C631" t="inlineStr">
         <is>
           <t>名言</t>
         </is>
       </c>
     </row>
-    <row r="633">
-      <c r="A633" t="inlineStr">
+    <row r="632">
+      <c r="A632" t="inlineStr">
         <is>
           <t xml:space="preserve">「成功者は情報共有している」
 الناجحون يشاركون المعلومة
@@ -13751,19 +13729,19 @@
 2109 出典不明 </t>
         </is>
       </c>
-      <c r="B633" t="inlineStr">
+      <c r="B632" t="inlineStr">
         <is>
           <t>images/「成功者は情報共有している」_img1.jpg</t>
         </is>
       </c>
-      <c r="C633" t="inlineStr">
+      <c r="C632" t="inlineStr">
         <is>
           <t>鳥 ,シェア</t>
         </is>
       </c>
     </row>
-    <row r="634">
-      <c r="A634" t="inlineStr">
+    <row r="633">
+      <c r="A633" t="inlineStr">
         <is>
           <t xml:space="preserve">「間違いで賢くなる、痛みで強くなる」
 الأخطاء تجعلك حكيمًا، والألم يجعلك قويًا
@@ -13772,19 +13750,19 @@
 2111 https://alaminin.blogspot.com/2020/03/blog-post_6.html </t>
         </is>
       </c>
-      <c r="B634" t="inlineStr">
+      <c r="B633" t="inlineStr">
         <is>
           <t>images/「間違いで賢くなる、痛みで強くなる」_img1.jpg</t>
         </is>
       </c>
-      <c r="C634" t="inlineStr">
+      <c r="C633" t="inlineStr">
         <is>
           <t>名言</t>
         </is>
       </c>
     </row>
-    <row r="635">
-      <c r="A635" t="inlineStr">
+    <row r="634">
+      <c r="A634" t="inlineStr">
         <is>
           <t xml:space="preserve">「何事も永遠には続かない」
 لا شيء يبقى للأبد
@@ -13794,19 +13772,19 @@
 2308 KiTeLetZ </t>
         </is>
       </c>
-      <c r="B635" t="inlineStr">
+      <c r="B634" t="inlineStr">
         <is>
           <t>images/「何事も永遠には続かない」_img1.jpg</t>
         </is>
       </c>
-      <c r="C635" t="inlineStr">
+      <c r="C634" t="inlineStr">
         <is>
           <t>変化 ,名言</t>
         </is>
       </c>
     </row>
-    <row r="636">
-      <c r="A636" t="inlineStr">
+    <row r="635">
+      <c r="A635" t="inlineStr">
         <is>
           <t xml:space="preserve">「惑星地球はあなた方を歓迎します」
 كوكب الارض يرحّب بكم
@@ -13816,19 +13794,19 @@
 1811 iN49R </t>
         </is>
       </c>
-      <c r="B636" t="inlineStr">
+      <c r="B635" t="inlineStr">
         <is>
           <t>images/「惑星地球はあなた方を歓迎します」_img1.jpg</t>
         </is>
       </c>
-      <c r="C636" t="inlineStr">
+      <c r="C635" t="inlineStr">
         <is>
           <t>宇宙 ,人類</t>
         </is>
       </c>
     </row>
-    <row r="637">
-      <c r="A637" t="inlineStr">
+    <row r="636">
+      <c r="A636" t="inlineStr">
         <is>
           <t xml:space="preserve">「自分を信じなさい。人の言うことは尽きないのだから」
 ثق بنفسك فكلام الناس لا ينتهي
@@ -13837,19 +13815,19 @@
 2105 出典不明 </t>
         </is>
       </c>
-      <c r="B637" t="inlineStr">
+      <c r="B636" t="inlineStr">
         <is>
           <t>images/「自分を信じなさい。人の言うことは尽き_img1.jpg</t>
         </is>
       </c>
-      <c r="C637" t="inlineStr">
+      <c r="C636" t="inlineStr">
         <is>
           <t>自信 ,無視</t>
         </is>
       </c>
     </row>
-    <row r="638">
-      <c r="A638" t="inlineStr">
+    <row r="637">
+      <c r="A637" t="inlineStr">
         <is>
           <t xml:space="preserve">「弟が歩くぞ」أخي الصغير يمشي
 アキ_ッサギール・ヤムシー ['aKh-i ^_saGhiiru ya-mShii]
@@ -13858,19 +13836,19 @@
 2308 gulfkids com http://www.gulfkids.com/ar/book48-1909.htm </t>
         </is>
       </c>
-      <c r="B638" t="inlineStr">
+      <c r="B637" t="inlineStr">
         <is>
           <t>images/「弟が歩くぞ」_img1.jpg</t>
         </is>
       </c>
-      <c r="C638" t="inlineStr">
+      <c r="C637" t="inlineStr">
         <is>
           <t>兄弟 ,絵本</t>
         </is>
       </c>
     </row>
-    <row r="639">
-      <c r="A639" t="inlineStr">
+    <row r="638">
+      <c r="A638" t="inlineStr">
         <is>
           <t xml:space="preserve">花より団子おおお（違う）
 「誰もふさわしくない」[laa 'aHada ya-staHiqqu]
@@ -13878,19 +13856,19 @@
 2308 https://twitter.com/NatGeoMagArab/status/1370041991317233664 </t>
         </is>
       </c>
-      <c r="B639" t="inlineStr">
+      <c r="B638" t="inlineStr">
         <is>
           <t>images/花より団子おおお（違う）_img1.jpg</t>
         </is>
       </c>
-      <c r="C639" t="inlineStr">
+      <c r="C638" t="inlineStr">
         <is>
           <t>手書き語学 ,アラビア語 ,キノボリカンガルー</t>
         </is>
       </c>
     </row>
-    <row r="640">
-      <c r="A640" t="inlineStr">
+    <row r="639">
+      <c r="A639" t="inlineStr">
         <is>
           <t xml:space="preserve">「幸せな人生には弱い記憶力が必要」
 الحياة السعيدة تتطلب ذاكرة ضعيفة
@@ -13899,19 +13877,19 @@
 2012 出典不明 </t>
         </is>
       </c>
-      <c r="B640" t="inlineStr">
+      <c r="B639" t="inlineStr">
         <is>
           <t>images/「幸せな人生には弱い記憶力が必要」_img1.jpg</t>
         </is>
       </c>
-      <c r="C640" t="inlineStr">
+      <c r="C639" t="inlineStr">
         <is>
           <t>前向き</t>
         </is>
       </c>
     </row>
-    <row r="641">
-      <c r="A641" t="inlineStr">
+    <row r="640">
+      <c r="A640" t="inlineStr">
         <is>
           <t xml:space="preserve">「このパンダは私たちに、幸せは単純なことの中に隠れているのだと教えている」
 دب "الباندا" هذا يؤكد لنا أن السعادة تكمن في أبسط الأشياء
@@ -13919,19 +13897,19 @@
 2308 https://twitter.com/NatGeoMagArab/status/1309938472065486848 </t>
         </is>
       </c>
-      <c r="B641" t="inlineStr">
+      <c r="B640" t="inlineStr">
         <is>
           <t>images/「このパンダは私たちに、幸せは単純なこ.png</t>
         </is>
       </c>
-      <c r="C641" t="inlineStr">
+      <c r="C640" t="inlineStr">
         <is>
           <t>パンダ ,雪</t>
         </is>
       </c>
     </row>
-    <row r="642">
-      <c r="A642" t="inlineStr">
+    <row r="641">
+      <c r="A641" t="inlineStr">
         <is>
           <t xml:space="preserve">「良い時間は速く過ぎる」
 الأوقات الجميلة تمر بسرعة
@@ -13941,19 +13919,19 @@
 1810 Nasser.Tumblr </t>
         </is>
       </c>
-      <c r="B642" t="inlineStr">
+      <c r="B641" t="inlineStr">
         <is>
           <t>images/「良い時間は速く過ぎる」_img1.jpg</t>
         </is>
       </c>
-      <c r="C642" t="inlineStr">
+      <c r="C641" t="inlineStr">
         <is>
           <t>相対論 ,心理学</t>
         </is>
       </c>
     </row>
-    <row r="643">
-      <c r="A643" t="inlineStr">
+    <row r="642">
+      <c r="A642" t="inlineStr">
         <is>
           <t xml:space="preserve">「今日が始まりかもしれない」
 كل يوم ممكن يكون بداية
@@ -13963,19 +13941,19 @@
 2308 Ahmed Madyan </t>
         </is>
       </c>
-      <c r="B643" t="inlineStr">
+      <c r="B642" t="inlineStr">
         <is>
           <t>images/「今日が始まりかもしれない」_img1.jpg</t>
         </is>
       </c>
-      <c r="C643" t="inlineStr">
+      <c r="C642" t="inlineStr">
         <is>
           <t>吉日 ,開始</t>
         </is>
       </c>
     </row>
-    <row r="644">
-      <c r="A644" t="inlineStr">
+    <row r="643">
+      <c r="A643" t="inlineStr">
         <is>
           <t xml:space="preserve">「ヌール、歯医者さんに行く」
 نور تذهب إلى طبيب الأسنان
@@ -13985,19 +13963,19 @@
 2109 RABIE </t>
         </is>
       </c>
-      <c r="B644" t="inlineStr">
+      <c r="B643" t="inlineStr">
         <is>
           <t>images/「ヌール、歯医者さんに行く」_img1.jpg</t>
         </is>
       </c>
-      <c r="C644" t="inlineStr">
+      <c r="C643" t="inlineStr">
         <is>
           <t>絵本 ,歯科</t>
         </is>
       </c>
     </row>
-    <row r="645">
-      <c r="A645" t="inlineStr">
+    <row r="644">
+      <c r="A644" t="inlineStr">
         <is>
           <t xml:space="preserve">「ラヤンはねむれない」
 لَيان لا تَسْتَطيعُ أَنْ تَنام
@@ -14006,19 +13984,19 @@
 2308 出典不明 </t>
         </is>
       </c>
-      <c r="B645" t="inlineStr">
+      <c r="B644" t="inlineStr">
         <is>
           <t>images/「ラヤンはねむれない」_img1.jpg</t>
         </is>
       </c>
-      <c r="C645" t="inlineStr">
+      <c r="C644" t="inlineStr">
         <is>
           <t>絵本 ,不眠症</t>
         </is>
       </c>
     </row>
-    <row r="646">
-      <c r="A646" t="inlineStr">
+    <row r="645">
+      <c r="A645" t="inlineStr">
         <is>
           <t xml:space="preserve">「クネイトラ県、蜂の巣を約60%失う」
 القنيطرة تفقد حوالي 60 % من خلايا نحلها
@@ -14026,19 +14004,19 @@
 2403 nabd com/t/101679025-fb119f </t>
         </is>
       </c>
-      <c r="B646" t="inlineStr">
+      <c r="B645" t="inlineStr">
         <is>
           <t>images/「クネイトラ県、蜂の巣を約60%失う」_img1.jpg</t>
         </is>
       </c>
-      <c r="C646" t="inlineStr">
+      <c r="C645" t="inlineStr">
         <is>
           <t>蜂の巣 ,パーセント</t>
         </is>
       </c>
     </row>
-    <row r="647">
-      <c r="A647" t="inlineStr">
+    <row r="646">
+      <c r="A646" t="inlineStr">
         <is>
           <t xml:space="preserve">「結ばれしター」ة
 ⁦( تاء مربوطة )[taa' marbuu_ta]：ت「ター」( تاء )[taa']・「結ばれている」( مربوط )[marbuu_t]：( ربط )【結】⁩
@@ -14046,19 +14024,19 @@
 2308 出典不明 </t>
         </is>
       </c>
-      <c r="B647" t="inlineStr">
+      <c r="B646" t="inlineStr">
         <is>
           <t>images/「結ばれしター」_img1.jpg</t>
         </is>
       </c>
-      <c r="C647" t="inlineStr">
+      <c r="C646" t="inlineStr">
         <is>
           <t>アラビア文字 ,顔</t>
         </is>
       </c>
     </row>
-    <row r="648">
-      <c r="A648" t="inlineStr">
+    <row r="647">
+      <c r="A647" t="inlineStr">
         <is>
           <t xml:space="preserve">「忙しい」مشغول
 マシュグール [maShGhuul]
@@ -14067,19 +14045,19 @@
 1811 skyshinichi.instagram </t>
         </is>
       </c>
-      <c r="B648" t="inlineStr">
+      <c r="B647" t="inlineStr">
         <is>
           <t>images/「忙しい」_img1.jpg</t>
         </is>
       </c>
-      <c r="C648" t="inlineStr">
+      <c r="C647" t="inlineStr">
         <is>
           <t>スティッチ ,残業</t>
         </is>
       </c>
     </row>
-    <row r="649">
-      <c r="A649" t="inlineStr">
+    <row r="648">
+      <c r="A648" t="inlineStr">
         <is>
           <t xml:space="preserve">「駐車禁止」ممنوع الوقوف
 マムヌーア・アルウクーフ [mamnuu* al-wuquuf]
@@ -14088,19 +14066,19 @@
 2106 出典不明 </t>
         </is>
       </c>
-      <c r="B649" t="inlineStr">
+      <c r="B648" t="inlineStr">
         <is>
           <t>images/「駐車禁止」_img1.jpg</t>
         </is>
       </c>
-      <c r="C649" t="inlineStr">
+      <c r="C648" t="inlineStr">
         <is>
           <t>標識 ,ジョーク</t>
         </is>
       </c>
     </row>
-    <row r="650">
-      <c r="A650" t="inlineStr">
+    <row r="649">
+      <c r="A649" t="inlineStr">
         <is>
           <t xml:space="preserve">「一人ひとりが責任を」
 كُلنا مسؤول
@@ -14110,19 +14088,19 @@
 2308 covid19awareness sa </t>
         </is>
       </c>
-      <c r="B650" t="inlineStr">
+      <c r="B649" t="inlineStr">
         <is>
           <t>images/「一人ひとりが責任を」_img1.jpg</t>
         </is>
       </c>
-      <c r="C650" t="inlineStr">
+      <c r="C649" t="inlineStr">
         <is>
           <t>Covid ,感染拡大防止</t>
         </is>
       </c>
     </row>
-    <row r="651">
-      <c r="A651" t="inlineStr">
+    <row r="650">
+      <c r="A650" t="inlineStr">
         <is>
           <t xml:space="preserve">「おめでとうございます」مبروك
 マブルーク [mabruuk]
@@ -14131,19 +14109,19 @@
 2308 </t>
         </is>
       </c>
-      <c r="B651" t="inlineStr">
+      <c r="B650" t="inlineStr">
         <is>
           <t>images/「おめでとうございます」_img1.jpg</t>
         </is>
       </c>
-      <c r="C651" t="inlineStr">
+      <c r="C650" t="inlineStr">
         <is>
           <t>詐欺 ,広告</t>
         </is>
       </c>
     </row>
-    <row r="652">
-      <c r="A652" t="inlineStr">
+    <row r="651">
+      <c r="A651" t="inlineStr">
         <is>
           <t xml:space="preserve">「手書きフォント」
 خط مكتوب باليد
@@ -14153,19 +14131,19 @@
 1809 FahdAlFraikh Behance </t>
         </is>
       </c>
-      <c r="B652" t="inlineStr">
+      <c r="B651" t="inlineStr">
         <is>
           <t>images/「手書きフォント」_img1.jpg</t>
         </is>
       </c>
-      <c r="C652" t="inlineStr">
+      <c r="C651" t="inlineStr">
         <is>
           <t>可愛いフォント ,筆跡</t>
         </is>
       </c>
     </row>
-    <row r="653">
-      <c r="A653" t="inlineStr">
+    <row r="652">
+      <c r="A652" t="inlineStr">
         <is>
           <t xml:space="preserve">「開かれたターと結ばれたター」
 التاء المفتوحة والمربوطة
@@ -14175,19 +14153,19 @@
 2109 slideshare.net </t>
         </is>
       </c>
-      <c r="B653" t="inlineStr">
+      <c r="B652" t="inlineStr">
         <is>
           <t>images/「開かれたターと結ばれたター」_img1.jpg</t>
         </is>
       </c>
-      <c r="C653" t="inlineStr">
+      <c r="C652" t="inlineStr">
         <is>
           <t>アラビア文字 ,スマイリー</t>
         </is>
       </c>
     </row>
-    <row r="654">
-      <c r="A654" t="inlineStr">
+    <row r="653">
+      <c r="A653" t="inlineStr">
         <is>
           <t xml:space="preserve">「このラマは誇らしげにして立っている」
 تقف هذه اللاما مزهوة بنفسها
@@ -14195,19 +14173,19 @@
 2410 https://twitter.com/NatGeoMagArab/status/1597485552965935104 </t>
         </is>
       </c>
-      <c r="B654" t="inlineStr">
+      <c r="B653" t="inlineStr">
         <is>
           <t>images/「このラマは誇らしげにして立っている」_img1.jpg</t>
         </is>
       </c>
-      <c r="C654" t="inlineStr">
+      <c r="C653" t="inlineStr">
         <is>
           <t>手書き語学 ,アラビア語 ,マチュピチュ遺跡</t>
         </is>
       </c>
     </row>
-    <row r="655">
-      <c r="A655" t="inlineStr">
+    <row r="654">
+      <c r="A654" t="inlineStr">
         <is>
           <t xml:space="preserve">「小さな生き物にしては危険な名前だ」
 اسم خطير لمخلوق صغير
@@ -14216,19 +14194,19 @@
 2308 https://twitter.com/NatGeoMagArab/status/1495035772071669760 </t>
         </is>
       </c>
-      <c r="B655" t="inlineStr">
+      <c r="B654" t="inlineStr">
         <is>
           <t>images/「小さな生き物にしては危険な名前だ」_img1.jpg</t>
         </is>
       </c>
-      <c r="C655" t="inlineStr">
+      <c r="C654" t="inlineStr">
         <is>
           <t>有袋類 ,タスマニアデビル</t>
         </is>
       </c>
     </row>
-    <row r="656">
-      <c r="A656" t="inlineStr">
+    <row r="655">
+      <c r="A655" t="inlineStr">
         <is>
           <t xml:space="preserve">「こわれている」مكسر
 ムカッサル [mukassar]
@@ -14236,19 +14214,19 @@
 2105 behance Written-Visuals </t>
         </is>
       </c>
-      <c r="B656" t="inlineStr">
+      <c r="B655" t="inlineStr">
         <is>
           <t>images/「こわれている」_img1.jpg</t>
         </is>
       </c>
-      <c r="C656" t="inlineStr">
+      <c r="C655" t="inlineStr">
         <is>
           <t>バラバラ ,デザイン</t>
         </is>
       </c>
     </row>
-    <row r="657">
-      <c r="A657" t="inlineStr">
+    <row r="656">
+      <c r="A656" t="inlineStr">
         <is>
           <t xml:space="preserve">「早起きする方法」
 كيف تنهض مُبكّرًا
@@ -14258,19 +14236,19 @@
 2308 Funders and Founders </t>
         </is>
       </c>
-      <c r="B657" t="inlineStr">
+      <c r="B656" t="inlineStr">
         <is>
           <t>images/「早起きする方法」_img1.jpg</t>
         </is>
       </c>
-      <c r="C657" t="inlineStr">
+      <c r="C656" t="inlineStr">
         <is>
           <t>オフトゥン ,寝起き</t>
         </is>
       </c>
     </row>
-    <row r="658">
-      <c r="A658" t="inlineStr">
+    <row r="657">
+      <c r="A657" t="inlineStr">
         <is>
           <t xml:space="preserve">「アラブ・デザイン文字展覧会」
 معرض لتخطيط الحرف العربي
@@ -14280,19 +14258,19 @@
 2109 arabic lettering exhibition </t>
         </is>
       </c>
-      <c r="B658" t="inlineStr">
+      <c r="B657" t="inlineStr">
         <is>
           <t>images/「アラブ・デザイン文字展覧会」_img1.jpg</t>
         </is>
       </c>
-      <c r="C658" t="inlineStr">
+      <c r="C657" t="inlineStr">
         <is>
           <t>ポスター</t>
         </is>
       </c>
     </row>
-    <row r="659">
-      <c r="A659" t="inlineStr">
+    <row r="658">
+      <c r="A658" t="inlineStr">
         <is>
           <t xml:space="preserve">「名探偵コナン」المحقق كونان
 アルムハッキク・コナン [al-muHaqqiq Conan]
@@ -14301,19 +14279,19 @@
 1809 wikipedia </t>
         </is>
       </c>
-      <c r="B659" t="inlineStr">
+      <c r="B658" t="inlineStr">
         <is>
           <t>images/「名探偵コナン」_img1.jpg</t>
         </is>
       </c>
-      <c r="C659" t="inlineStr">
+      <c r="C658" t="inlineStr">
         <is>
           <t>江戸川コナン ,ロゴ</t>
         </is>
       </c>
     </row>
-    <row r="660">
-      <c r="A660" t="inlineStr">
+    <row r="659">
+      <c r="A659" t="inlineStr">
         <is>
           <t xml:space="preserve">「イードおめでとう」عيد مبارك
 イード・ムバーラク [*iid mubaarak]
@@ -14321,19 +14299,19 @@
 2308 出典不明 </t>
         </is>
       </c>
-      <c r="B660" t="inlineStr">
+      <c r="B659" t="inlineStr">
         <is>
           <t>images/「イードおめでとう」_img1.jpg</t>
         </is>
       </c>
-      <c r="C660" t="inlineStr">
+      <c r="C659" t="inlineStr">
         <is>
           <t>عيد ,アラビア語</t>
         </is>
       </c>
     </row>
-    <row r="661">
-      <c r="A661" t="inlineStr">
+    <row r="660">
+      <c r="A660" t="inlineStr">
         <is>
           <t xml:space="preserve">「戦士」محارب
 ムハーリブ [muHaarib]
@@ -14342,19 +14320,19 @@
 1809 abudinges.tumblr </t>
         </is>
       </c>
-      <c r="B661" t="inlineStr">
+      <c r="B660" t="inlineStr">
         <is>
           <t>images/「戦士」_img1.jpg</t>
         </is>
       </c>
-      <c r="C661" t="inlineStr">
+      <c r="C660" t="inlineStr">
         <is>
           <t>ロゴ ,赤</t>
         </is>
       </c>
     </row>
-    <row r="662">
-      <c r="A662" t="inlineStr">
+    <row r="661">
+      <c r="A661" t="inlineStr">
         <is>
           <t xml:space="preserve">「ライブ」بث مباشر
 バッス・ムバーシル [ba^Th(un) mubaaShir(un)]
@@ -14363,19 +14341,19 @@
 2308 beIN SPORTS </t>
         </is>
       </c>
-      <c r="B662" t="inlineStr">
+      <c r="B661" t="inlineStr">
         <is>
           <t>images/「ライブ」_img1.jpg</t>
         </is>
       </c>
-      <c r="C662" t="inlineStr">
+      <c r="C661" t="inlineStr">
         <is>
           <t xml:space="preserve">生放送 ,試合 </t>
         </is>
       </c>
     </row>
-    <row r="663">
-      <c r="A663" t="inlineStr">
+    <row r="662">
+      <c r="A662" t="inlineStr">
         <is>
           <t xml:space="preserve">「信者」مُؤْمِنٌ
 ムッミン [mu'min(un)]
@@ -14384,19 +14362,19 @@
 2106 出典不明 </t>
         </is>
       </c>
-      <c r="B663" t="inlineStr">
+      <c r="B662" t="inlineStr">
         <is>
           <t>images/「信者」_img1.jpg</t>
         </is>
       </c>
-      <c r="C663" t="inlineStr">
+      <c r="C662" t="inlineStr">
         <is>
           <t>明暗 ,信仰</t>
         </is>
       </c>
     </row>
-    <row r="664">
-      <c r="A664" t="inlineStr">
+    <row r="663">
+      <c r="A663" t="inlineStr">
         <is>
           <t xml:space="preserve">「開⇔閉」
 مفتوح
@@ -14407,19 +14385,19 @@
 2312 Hussein Safina, behance </t>
         </is>
       </c>
-      <c r="B664" t="inlineStr">
+      <c r="B663" t="inlineStr">
         <is>
           <t>images/「開⇔閉」_img1.jpg</t>
         </is>
       </c>
-      <c r="C664" t="inlineStr">
+      <c r="C663" t="inlineStr">
         <is>
           <t>オープンマインド ,トグル</t>
         </is>
       </c>
     </row>
-    <row r="665">
-      <c r="A665" t="inlineStr">
+    <row r="664">
+      <c r="A664" t="inlineStr">
         <is>
           <t xml:space="preserve">「予想外な結末！」
 نهاية غير متوقعة
@@ -14427,19 +14405,19 @@
 2308 https://twitter.com/NatGeoMagArab/status/1159011433444593665 </t>
         </is>
       </c>
-      <c r="B665" t="inlineStr">
+      <c r="B664" t="inlineStr">
         <is>
           <t>images/「予想外な結末！」_img1.jpg</t>
         </is>
       </c>
-      <c r="C665" t="inlineStr">
+      <c r="C664" t="inlineStr">
         <is>
           <t>手書き語学 ,アラビア語 ,ウサギ</t>
         </is>
       </c>
     </row>
-    <row r="666">
-      <c r="A666" t="inlineStr">
+    <row r="665">
+      <c r="A665" t="inlineStr">
         <is>
           <t xml:space="preserve">「ベイルート・アニメイテッド」
 بیروت متحرّکة
@@ -14449,19 +14427,19 @@
 2308 arabic_script Instagram </t>
         </is>
       </c>
-      <c r="B666" t="inlineStr">
+      <c r="B665" t="inlineStr">
         <is>
           <t>images/「ベイルート・アニメイテッド」_img1.jpg</t>
         </is>
       </c>
-      <c r="C666" t="inlineStr">
+      <c r="C665" t="inlineStr">
         <is>
           <t>アニメ ,レバノン</t>
         </is>
       </c>
     </row>
-    <row r="667">
-      <c r="A667" t="inlineStr">
+    <row r="666">
+      <c r="A666" t="inlineStr">
         <is>
           <t xml:space="preserve">「夢みれば叶う」
 كُلُّ مُتَوَقَّعٍ آتٍ
@@ -14471,19 +14449,19 @@
 2108 Ahmed Madyan </t>
         </is>
       </c>
-      <c r="B667" t="inlineStr">
+      <c r="B666" t="inlineStr">
         <is>
           <t>images/「夢みれば叶う」_img1.jpg</t>
         </is>
       </c>
-      <c r="C667" t="inlineStr">
+      <c r="C666" t="inlineStr">
         <is>
           <t>希望 ,ドリカム</t>
         </is>
       </c>
     </row>
-    <row r="668">
-      <c r="A668" t="inlineStr">
+    <row r="667">
+      <c r="A667" t="inlineStr">
         <is>
           <t xml:space="preserve">「もし両者が人間のように鎧で武装して戦いに突入したら」
 لو خاضا معاركهما متسلحين بالدروع على غرار البش
@@ -14491,19 +14469,19 @@
 2404 https://x.com/NatGeoMagArab/status/1759284149456945464 </t>
         </is>
       </c>
-      <c r="B668" t="inlineStr">
+      <c r="B667" t="inlineStr">
         <is>
           <t>images/「もし両者が人間のように鎧で武装して戦_img1.jpg,images/「もし両者が人間のように鎧で武装して戦_img2.jpg</t>
         </is>
       </c>
-      <c r="C668" t="inlineStr">
+      <c r="C667" t="inlineStr">
         <is>
           <t>手書き語学 ,アラビア語 ,猫</t>
         </is>
       </c>
     </row>
-    <row r="669">
-      <c r="A669" t="inlineStr">
+    <row r="668">
+      <c r="A668" t="inlineStr">
         <is>
           <t xml:space="preserve">「全ては結びついている」
 كل شيء مترابط
@@ -14513,19 +14491,19 @@
 2308 Ahmed Madyan https://twitter.com/madyco22/status/1451990828298166273 </t>
         </is>
       </c>
-      <c r="B669" t="inlineStr">
+      <c r="B668" t="inlineStr">
         <is>
           <t>images/「全ては結びついている」_img1.jpg</t>
         </is>
       </c>
-      <c r="C669" t="inlineStr">
+      <c r="C668" t="inlineStr">
         <is>
           <t>一筆書き ,デザイン</t>
         </is>
       </c>
     </row>
-    <row r="670">
-      <c r="A670" t="inlineStr">
+    <row r="669">
+      <c r="A669" t="inlineStr">
         <is>
           <t xml:space="preserve">「初心者のためのスケッチトレーニング」
 تعليم الرسم للمبتدئين
@@ -14535,19 +14513,19 @@
 2308 free-bookspdf com </t>
         </is>
       </c>
-      <c r="B670" t="inlineStr">
+      <c r="B669" t="inlineStr">
         <is>
           <t>images/「初心者のためのスケッチトレーニング」_img1.jpg</t>
         </is>
       </c>
-      <c r="C670" t="inlineStr">
+      <c r="C669" t="inlineStr">
         <is>
           <t>イラスト ,絵</t>
         </is>
       </c>
     </row>
-    <row r="671">
-      <c r="A671" t="inlineStr">
+    <row r="670">
+      <c r="A670" t="inlineStr">
         <is>
           <t xml:space="preserve">「初心者のためのスルス体書道トレーニング」
 تعليم خط الثلث للمبتدئين
@@ -14557,19 +14535,19 @@
 2308 出典不明 </t>
         </is>
       </c>
-      <c r="B671" t="inlineStr">
+      <c r="B670" t="inlineStr">
         <is>
           <t>images/「初心者のためのスルス体書道トレーニン_img1.jpg</t>
         </is>
       </c>
-      <c r="C671" t="inlineStr">
+      <c r="C670" t="inlineStr">
         <is>
           <t>書道</t>
         </is>
       </c>
     </row>
-    <row r="672">
-      <c r="A672" t="inlineStr">
+    <row r="671">
+      <c r="A671" t="inlineStr">
         <is>
           <t xml:space="preserve">「笑顔でいなさい」خليك مبتسم
 カッリーク・ムブタスィム [Khallii-k mubtasim]
@@ -14578,19 +14556,19 @@
 2308 https://tmblr.co/Zj9tguYLXBvC </t>
         </is>
       </c>
-      <c r="B672" t="inlineStr">
+      <c r="B671" t="inlineStr">
         <is>
           <t>images/「笑顔でいなさい」_img1.jpg</t>
         </is>
       </c>
-      <c r="C672" t="inlineStr">
+      <c r="C671" t="inlineStr">
         <is>
           <t>スマイル ,名言</t>
         </is>
       </c>
     </row>
-    <row r="673">
-      <c r="A673" t="inlineStr">
+    <row r="672">
+      <c r="A672" t="inlineStr">
         <is>
           <t xml:space="preserve">自動車メーカー
 ⁦・「TOYOTA」( تويوتا )⁩
@@ -14602,19 +14580,19 @@
 2308 syarah com </t>
         </is>
       </c>
-      <c r="B673" t="inlineStr">
+      <c r="B672" t="inlineStr">
         <is>
           <t>images/自動車メーカー_img1.jpg,images/自動車メーカー_img2.jpg,images/自動車メーカー_img3.jpg,images/自動車メーカー_img4.jpg</t>
         </is>
       </c>
-      <c r="C673" t="inlineStr">
+      <c r="C672" t="inlineStr">
         <is>
           <t>日本車 ,韓国車</t>
         </is>
       </c>
     </row>
-    <row r="674">
-      <c r="A674" t="inlineStr">
+    <row r="673">
+      <c r="A673" t="inlineStr">
         <is>
           <t xml:space="preserve">「僕たちは協力して不可能を達成するよ」
 بالتعاون نحقق المحال
@@ -14624,19 +14602,19 @@
 2109 </t>
         </is>
       </c>
-      <c r="B674" t="inlineStr">
+      <c r="B673" t="inlineStr">
         <is>
           <t>images/「僕たちは協力して不可能を達成するよ」_img1.jpg</t>
         </is>
       </c>
-      <c r="C674" t="inlineStr">
+      <c r="C673" t="inlineStr">
         <is>
           <t>無理 ,ハム太郎</t>
         </is>
       </c>
     </row>
-    <row r="675">
-      <c r="A675" t="inlineStr">
+    <row r="674">
+      <c r="A674" t="inlineStr">
         <is>
           <t xml:space="preserve">「幸せは伝染性。喜びを広めよう」
 السعادة معدية فأشع الفرح
@@ -14646,19 +14624,19 @@
 2511 instagram　com/p/fVEfxEo7Va/ </t>
         </is>
       </c>
-      <c r="B675" t="inlineStr">
+      <c r="B674" t="inlineStr">
         <is>
           <t>images/「幸せは伝染性。喜びを広めよう」_img1.jpg</t>
         </is>
       </c>
-      <c r="C675" t="inlineStr">
+      <c r="C674" t="inlineStr">
         <is>
           <t>拡散希望</t>
         </is>
       </c>
     </row>
-    <row r="676">
-      <c r="A676" t="inlineStr">
+    <row r="675">
+      <c r="A675" t="inlineStr">
         <is>
           <t xml:space="preserve">「ストレスは人間だけのものではない」
 الشعور بالتوتر ليس حكرًا على البشر
@@ -14666,19 +14644,19 @@
 2408 https://x.com/NatGeoMagArab/status/1736755816911487420 </t>
         </is>
       </c>
-      <c r="B676" t="inlineStr">
+      <c r="B675" t="inlineStr">
         <is>
           <t>images/「ストレスは人間だけのものではない」_img1.jpg</t>
         </is>
       </c>
-      <c r="C676" t="inlineStr">
+      <c r="C675" t="inlineStr">
         <is>
           <t>手書き語学 ,アラビア語 ,ストレス</t>
         </is>
       </c>
     </row>
-    <row r="677">
-      <c r="A677" t="inlineStr">
+    <row r="676">
+      <c r="A676" t="inlineStr">
         <is>
           <t xml:space="preserve">「私達は出来ます！」
 نستطيع فعلها
@@ -14688,19 +14666,19 @@
 2308 NAHARBAHIJ com </t>
         </is>
       </c>
-      <c r="B677" t="inlineStr">
+      <c r="B676" t="inlineStr">
         <is>
           <t>images/「私達は出来ます！」_img1.jpg</t>
         </is>
       </c>
-      <c r="C677" t="inlineStr">
+      <c r="C676" t="inlineStr">
         <is>
           <t>女性 ,パロディ</t>
         </is>
       </c>
     </row>
-    <row r="678">
-      <c r="A678" t="inlineStr">
+    <row r="677">
+      <c r="A677" t="inlineStr">
         <is>
           <t xml:space="preserve">「全然分からん」ولا فاهم إشي
 ウラー・ファーヒム・イシ [w-laa faahim 'iShy]
@@ -14710,19 +14688,19 @@
 2209 出典不明 </t>
         </is>
       </c>
-      <c r="B678" t="inlineStr">
+      <c r="B677" t="inlineStr">
         <is>
           <t>images/「全然分からん」_img1.jpg</t>
         </is>
       </c>
-      <c r="C678" t="inlineStr">
+      <c r="C677" t="inlineStr">
         <is>
           <t>アラビア語</t>
         </is>
       </c>
     </row>
-    <row r="679">
-      <c r="A679" t="inlineStr">
+    <row r="678">
+      <c r="A678" t="inlineStr">
         <is>
           <t xml:space="preserve">「人間は一人ひとり、特別な才がある。だから自分を他人と比べるのはやめよう」
 لكل إنسان مواهبه الخاصة 
@@ -14731,19 +14709,19 @@
 1812 Gwid3 </t>
         </is>
       </c>
-      <c r="B679" t="inlineStr">
+      <c r="B678" t="inlineStr">
         <is>
           <t>images/「人間は一人ひとり、特別な才がある。だ_img1.jpg</t>
         </is>
       </c>
-      <c r="C679" t="inlineStr">
+      <c r="C678" t="inlineStr">
         <is>
           <t>自尊 ,プライド</t>
         </is>
       </c>
     </row>
-    <row r="680">
-      <c r="A680" t="inlineStr">
+    <row r="679">
+      <c r="A679" t="inlineStr">
         <is>
           <t xml:space="preserve">「この猫は食事をシェアするのが嫌い！」
 هذه القطة لا تحب مشاركة الطعام
@@ -14752,19 +14730,19 @@
 2605 facebook com/alahram/videos/2154923608133231/ </t>
         </is>
       </c>
-      <c r="B680" t="inlineStr">
+      <c r="B679" t="inlineStr">
         <is>
           <t>images/「この猫は食事をシェアするのが嫌い！」_img1.jpg</t>
         </is>
       </c>
-      <c r="C680" t="inlineStr">
+      <c r="C679" t="inlineStr">
         <is>
           <t>猫 ,ネコ</t>
         </is>
       </c>
     </row>
-    <row r="681">
-      <c r="A681" t="inlineStr">
+    <row r="680">
+      <c r="A680" t="inlineStr">
         <is>
           <t xml:space="preserve">「怪獣との戦いでは自分が怪獣化せぬよう警戒しなさい」
 احذر عند محاربة الوحوش ألا تصبح واحدا منهم
@@ -14774,19 +14752,19 @@
 2108 warag-3nb.tumblr </t>
         </is>
       </c>
-      <c r="B681" t="inlineStr">
+      <c r="B680" t="inlineStr">
         <is>
           <t>images/「怪獣との戦いでは自分が怪獣化せぬよう_img1.jpg,images/ 「怪獣との戦いでは自分が怪獣化せぬよう_img2.jpg</t>
         </is>
       </c>
-      <c r="C681" t="inlineStr">
+      <c r="C680" t="inlineStr">
         <is>
           <t>正気 ,モンスター</t>
         </is>
       </c>
     </row>
-    <row r="682">
-      <c r="A682" t="inlineStr">
+    <row r="681">
+      <c r="A681" t="inlineStr">
         <is>
           <t xml:space="preserve">「錯視アート」فن الخداع البصري
 ファンヌ_ルヒダーイ_ルバサリーイ [fannu l-Khidaa*i l-ba_sariyy]
@@ -14795,19 +14773,19 @@
 2409 https://online.pubhtml5.com/idtb/neft/ </t>
         </is>
       </c>
-      <c r="B682" t="inlineStr">
+      <c r="B681" t="inlineStr">
         <is>
           <t>images/「錯視アート」_img1.jpg</t>
         </is>
       </c>
-      <c r="C682" t="inlineStr">
+      <c r="C681" t="inlineStr">
         <is>
           <t>トリックアート</t>
         </is>
       </c>
     </row>
-    <row r="683">
-      <c r="A683" t="inlineStr">
+    <row r="682">
+      <c r="A682" t="inlineStr">
         <is>
           <t xml:space="preserve">「自然界の消防士の訓練」
 تدريبات رجال الإطفاء في الطبيعة
@@ -14815,19 +14793,19 @@
 2308 https://twitter.com/NatGeoMagArab/status/1462420543890608129 </t>
         </is>
       </c>
-      <c r="B683" t="inlineStr">
+      <c r="B682" t="inlineStr">
         <is>
           <t>images/「自然界の消防士の訓練」_img1.jpg,images/ 「自然界の消防士の訓練」_img2.jpg</t>
         </is>
       </c>
-      <c r="C683" t="inlineStr">
+      <c r="C682" t="inlineStr">
         <is>
           <t>手書き語学 ,アラビア語 ,ヒグマ</t>
         </is>
       </c>
     </row>
-    <row r="684">
-      <c r="A684" t="inlineStr">
+    <row r="683">
+      <c r="A683" t="inlineStr">
         <is>
           <t xml:space="preserve">「救助」إسعاف
 イスアーフ ['is*aaf]
@@ -14836,19 +14814,19 @@
 2109 ambulance gov ae </t>
         </is>
       </c>
-      <c r="B684" t="inlineStr">
+      <c r="B683" t="inlineStr">
         <is>
           <t>images/「救助」_img1.jpg</t>
         </is>
       </c>
-      <c r="C684" t="inlineStr">
+      <c r="C683" t="inlineStr">
         <is>
           <t>救急車 ,はたらくくるま</t>
         </is>
       </c>
     </row>
-    <row r="685">
-      <c r="A685" t="inlineStr">
+    <row r="684">
+      <c r="A684" t="inlineStr">
         <is>
           <t xml:space="preserve">「感情／感覚」الإحْسَاسْ
 アルイヒサース [al-'iHsaas]
@@ -14857,19 +14835,19 @@
 2308 iN49R </t>
         </is>
       </c>
-      <c r="B685" t="inlineStr">
+      <c r="B684" t="inlineStr">
         <is>
           <t>images/「感情／感覚」_img1.jpg</t>
         </is>
       </c>
-      <c r="C685" t="inlineStr">
+      <c r="C684" t="inlineStr">
         <is>
           <t>オフ ,一休み</t>
         </is>
       </c>
     </row>
-    <row r="686">
-      <c r="A686" t="inlineStr">
+    <row r="685">
+      <c r="A685" t="inlineStr">
         <is>
           <t xml:space="preserve">「ひらめき」إلهام
 イルハーム ['lhaam]
@@ -14881,19 +14859,19 @@
 2103 出典不明 </t>
         </is>
       </c>
-      <c r="B686" t="inlineStr">
+      <c r="B685" t="inlineStr">
         <is>
           <t>images/「ひらめき」_img1.jpg</t>
         </is>
       </c>
-      <c r="C686" t="inlineStr">
+      <c r="C685" t="inlineStr">
         <is>
           <t>アラビア語</t>
         </is>
       </c>
     </row>
-    <row r="687">
-      <c r="A687" t="inlineStr">
+    <row r="686">
+      <c r="A686" t="inlineStr">
         <is>
           <t xml:space="preserve">「Ibdaa／クリエイティビティ」
 إبداع
@@ -14902,19 +14880,19 @@
 2308 Ibdaa Design &amp; Decoration Office </t>
         </is>
       </c>
-      <c r="B687" t="inlineStr">
+      <c r="B686" t="inlineStr">
         <is>
           <t>images/「Ibdaa／クリエイティビティ」_img1.jpg</t>
         </is>
       </c>
-      <c r="C687" t="inlineStr">
+      <c r="C686" t="inlineStr">
         <is>
           <t>創造性 ,独自性</t>
         </is>
       </c>
     </row>
-    <row r="688">
-      <c r="A688" t="inlineStr">
+    <row r="687">
+      <c r="A687" t="inlineStr">
         <is>
           <t xml:space="preserve">「奮闘なくして進歩なし」
 بدون كفاح لايوجد تقدم
@@ -14924,19 +14902,19 @@
 2105 ROUYMS TUMBLR COM </t>
         </is>
       </c>
-      <c r="B688" t="inlineStr">
+      <c r="B687" t="inlineStr">
         <is>
           <t>images/「奮闘なくして進歩なし」_img1.jpg</t>
         </is>
       </c>
-      <c r="C688" t="inlineStr">
+      <c r="C687" t="inlineStr">
         <is>
           <t>努力 ,三角形</t>
         </is>
       </c>
     </row>
-    <row r="689">
-      <c r="A689" t="inlineStr">
+    <row r="688">
+      <c r="A688" t="inlineStr">
         <is>
           <t xml:space="preserve">「木に登れば熊の危険を避けられるとお考えなら、考え直しましょう！」 
 إن اعتقدت أنك بمنأى عن خطر الدب عند تسلق الأشجار.. راجع حساباتك
@@ -14944,19 +14922,19 @@
 2202 NatGeoMagArab </t>
         </is>
       </c>
-      <c r="B689" t="inlineStr">
+      <c r="B688" t="inlineStr">
         <is>
           <t>images/「木に登れば熊の危険を避けられるとお考.jpeg</t>
         </is>
       </c>
-      <c r="C689" t="inlineStr">
+      <c r="C688" t="inlineStr">
         <is>
           <t>クマ</t>
         </is>
       </c>
     </row>
-    <row r="690">
-      <c r="A690" t="inlineStr">
+    <row r="689">
+      <c r="A689" t="inlineStr">
         <is>
           <t xml:space="preserve">「卒業おめでとう」مبروك التخرج
 マブルーク・タカッルジ [mabruuk a^taKharruj]
@@ -14965,19 +14943,19 @@
 2308 https://instagram.com/fatoomworld </t>
         </is>
       </c>
-      <c r="B690" t="inlineStr">
+      <c r="B689" t="inlineStr">
         <is>
           <t>images/「卒業おめでとう」_img1.jpg</t>
         </is>
       </c>
-      <c r="C690" t="inlineStr">
+      <c r="C689" t="inlineStr">
         <is>
           <t>卒業 ,イラスト</t>
         </is>
       </c>
     </row>
-    <row r="691">
-      <c r="A691" t="inlineStr">
+    <row r="690">
+      <c r="A690" t="inlineStr">
         <is>
           <t xml:space="preserve">「停止距離の計算」
 حساب مسافة التوقف
@@ -14987,19 +14965,19 @@
 2109 assurance-auto-info </t>
         </is>
       </c>
-      <c r="B691" t="inlineStr">
+      <c r="B690" t="inlineStr">
         <is>
           <t>images/「停止距離の計算」_img1.jpg</t>
         </is>
       </c>
-      <c r="C691" t="inlineStr">
+      <c r="C690" t="inlineStr">
         <is>
           <t>保険 ,自動車</t>
         </is>
       </c>
     </row>
-    <row r="692">
-      <c r="A692" t="inlineStr">
+    <row r="691">
+      <c r="A691" t="inlineStr">
         <is>
           <t xml:space="preserve">「教師要らず：10日でフランス語会話」
 بدون معلم
@@ -15009,19 +14987,19 @@
 2308 englais-best com </t>
         </is>
       </c>
-      <c r="B692" t="inlineStr">
+      <c r="B691" t="inlineStr">
         <is>
           <t>images/「教師要らず：10日でフランス語会話」_img1.jpg</t>
         </is>
       </c>
-      <c r="C692" t="inlineStr">
+      <c r="C691" t="inlineStr">
         <is>
           <t>教師なし学習</t>
         </is>
       </c>
     </row>
-    <row r="693">
-      <c r="A693" t="inlineStr">
+    <row r="692">
+      <c r="A692" t="inlineStr">
         <is>
           <t xml:space="preserve">「衝突」تصادم
 タサードゥム [ta_saadum]
@@ -15030,19 +15008,19 @@
 1810 </t>
         </is>
       </c>
-      <c r="B693" t="inlineStr">
+      <c r="B692" t="inlineStr">
         <is>
           <t>images/「衝突」_img1.jpg</t>
         </is>
       </c>
-      <c r="C693" t="inlineStr">
+      <c r="C692" t="inlineStr">
         <is>
           <t>あらびあや</t>
         </is>
       </c>
     </row>
-    <row r="694">
-      <c r="A694" t="inlineStr">
+    <row r="693">
+      <c r="A693" t="inlineStr">
         <is>
           <t xml:space="preserve">「楽観主義」تَفَاؤُلٌ
 タファーウル [tafaa'ul(un)]
@@ -15051,19 +15029,19 @@
 1904 arabictypography com </t>
         </is>
       </c>
-      <c r="B694" t="inlineStr">
+      <c r="B693" t="inlineStr">
         <is>
           <t>images/「楽観主義」_img1.jpg</t>
         </is>
       </c>
-      <c r="C694" t="inlineStr">
+      <c r="C693" t="inlineStr">
         <is>
           <t>やわらか ,緑</t>
         </is>
       </c>
     </row>
-    <row r="695">
-      <c r="A695" t="inlineStr">
+    <row r="694">
+      <c r="A694" t="inlineStr">
         <is>
           <t xml:space="preserve">「シベリアジャコウジカは、絶滅の危機にあると見なされている」
 يعد "أيل المسك السيبيري" مهددًا بالانقراض
@@ -15071,19 +15049,19 @@
 2308 https://twitter.com/NatGeoMagArab/status/1320666649045790720 </t>
         </is>
       </c>
-      <c r="B695" t="inlineStr">
+      <c r="B694" t="inlineStr">
         <is>
           <t>images/「シベリアジャコウジカは、絶滅の危機に_img1.jpg,images/「シベリアジャコウジカは、絶滅の危機に_img2.jpg</t>
         </is>
       </c>
-      <c r="C695" t="inlineStr">
+      <c r="C694" t="inlineStr">
         <is>
           <t>手書き語学 ,シベリア</t>
         </is>
       </c>
     </row>
-    <row r="696">
-      <c r="A696" t="inlineStr">
+    <row r="695">
+      <c r="A695" t="inlineStr">
         <is>
           <t xml:space="preserve">「融合／折衷／フュージョン」
 انصهار
@@ -15092,38 +15070,38 @@
 1811 elmahdyart Instagram </t>
         </is>
       </c>
-      <c r="B696" t="inlineStr">
+      <c r="B695" t="inlineStr">
         <is>
           <t>images/「融合／折衷／フュージョン」_img1.jpg</t>
         </is>
       </c>
-      <c r="C696" t="inlineStr">
+      <c r="C695" t="inlineStr">
         <is>
           <t>カリグラフィー ,書道</t>
         </is>
       </c>
     </row>
-    <row r="697">
-      <c r="A697" t="inlineStr">
+    <row r="696">
+      <c r="A696" t="inlineStr">
         <is>
           <t xml:space="preserve">「この子供は、昼寝をしようとする母親を邪魔しているようだ」
 「場所はインドのトラ保護区、バンダウガル公園。トラは生態ピラミッドのトップの捕食動物だが、最もリスクの高い絶滅危惧種のひとつである」
 2308 https://twitter.com/natgeomagarab/status/1553681890665586689 </t>
         </is>
       </c>
-      <c r="B697" t="inlineStr">
+      <c r="B696" t="inlineStr">
         <is>
           <t>images/「この子供は、昼寝をしようとする母親を_img1.jpg,images/「この子供は、昼寝をしようとする母親を_img2.jpg</t>
         </is>
       </c>
-      <c r="C697" t="inlineStr">
+      <c r="C696" t="inlineStr">
         <is>
           <t>手書き語学 ,アラビア語 ,トラ</t>
         </is>
       </c>
     </row>
-    <row r="698">
-      <c r="A698" t="inlineStr">
+    <row r="697">
+      <c r="A697" t="inlineStr">
         <is>
           <t xml:space="preserve">「もし敬意が落ちたら、それと一緒に全部落ちるのだ」
 إن سقط الإحترام سقط معه كل شيء
@@ -15132,19 +15110,19 @@
 2109 出典不明 </t>
         </is>
       </c>
-      <c r="B698" t="inlineStr">
+      <c r="B697" t="inlineStr">
         <is>
           <t>images/「もし敬意が落ちたら、それと一緒に全部_img1.jpg</t>
         </is>
       </c>
-      <c r="C698" t="inlineStr">
+      <c r="C697" t="inlineStr">
         <is>
           <t>リスペクト ,落書き</t>
         </is>
       </c>
     </row>
-    <row r="699">
-      <c r="A699" t="inlineStr">
+    <row r="698">
+      <c r="A698" t="inlineStr">
         <is>
           <t xml:space="preserve">「エジプト特許庁」
 مكتب براءات الاختراع المصرى
@@ -15154,19 +15132,19 @@
 2312 </t>
         </is>
       </c>
-      <c r="B699" t="inlineStr">
+      <c r="B698" t="inlineStr">
         <is>
           <t>images/「エジプト特許庁」_img1.jpg</t>
         </is>
       </c>
-      <c r="C699" t="inlineStr">
+      <c r="C698" t="inlineStr">
         <is>
           <t>patent</t>
         </is>
       </c>
     </row>
-    <row r="700">
-      <c r="A700" t="inlineStr">
+    <row r="699">
+      <c r="A699" t="inlineStr">
         <is>
           <t xml:space="preserve">「選挙」إنتخابات
 インティカーバート [intiKhaabaat]
@@ -15175,19 +15153,19 @@
 2311 nna-leb gov lb </t>
         </is>
       </c>
-      <c r="B700" t="inlineStr">
+      <c r="B699" t="inlineStr">
         <is>
           <t>images/「選挙」_img1.jpg</t>
         </is>
       </c>
-      <c r="C700" t="inlineStr">
+      <c r="C699" t="inlineStr">
         <is>
           <t>選挙 ,投票</t>
         </is>
       </c>
     </row>
-    <row r="701">
-      <c r="A701" t="inlineStr">
+    <row r="700">
+      <c r="A700" t="inlineStr">
         <is>
           <t xml:space="preserve">「待ちぼうけ」إنتظار
 インティザール [inti_Dhaar]
@@ -15196,19 +15174,19 @@
 1809 in4sser.tumblr </t>
         </is>
       </c>
-      <c r="B701" t="inlineStr">
+      <c r="B700" t="inlineStr">
         <is>
           <t>images/「待ちぼうけ」_img1.jpg</t>
         </is>
       </c>
-      <c r="C701" t="inlineStr">
+      <c r="C700" t="inlineStr">
         <is>
           <t>遅すぎ ,辛抱</t>
         </is>
       </c>
     </row>
-    <row r="702">
-      <c r="A702" t="inlineStr">
+    <row r="701">
+      <c r="A701" t="inlineStr">
         <is>
           <t xml:space="preserve">「試験」إختبار
 イクティバール [iKhtibaar]
@@ -15217,19 +15195,19 @@
 2109 出典不明 </t>
         </is>
       </c>
-      <c r="B702" t="inlineStr">
+      <c r="B701" t="inlineStr">
         <is>
           <t>images/「試験」_img1.jpg</t>
         </is>
       </c>
-      <c r="C702" t="inlineStr">
+      <c r="C701" t="inlineStr">
         <is>
           <t>テスト ,考査</t>
         </is>
       </c>
     </row>
-    <row r="703">
-      <c r="A703" t="inlineStr">
+    <row r="702">
+      <c r="A702" t="inlineStr">
         <is>
           <t xml:space="preserve">「チャンネル登録」اشتراك
 イシティラーク [iShtiraak]
@@ -15238,19 +15216,19 @@
 2308 </t>
         </is>
       </c>
-      <c r="B703" t="inlineStr">
+      <c r="B702" t="inlineStr">
         <is>
           <t>images/「チャンネル登録」_img1.jpg</t>
         </is>
       </c>
-      <c r="C703" t="inlineStr">
+      <c r="C702" t="inlineStr">
         <is>
           <t>Subscribe ,YouTube</t>
         </is>
       </c>
     </row>
-    <row r="704">
-      <c r="A704" t="inlineStr">
+    <row r="703">
+      <c r="A703" t="inlineStr">
         <is>
           <t xml:space="preserve">「スマイル」ابتسام
 イブティサーム [ibtisaam]
@@ -15258,37 +15236,37 @@
 1903 behance Written-Visuals </t>
         </is>
       </c>
+      <c r="B703" t="inlineStr">
+        <is>
+          <t>images/「スマイル」_img1.jpg</t>
+        </is>
+      </c>
+      <c r="C703" t="inlineStr">
+        <is>
+          <t>スマイリー ,ツ</t>
+        </is>
+      </c>
+    </row>
+    <row r="704">
+      <c r="A704" t="inlineStr">
+        <is>
+          <t xml:space="preserve">「身体の一部として…」
+2308 https://twitter.com/NatGeoMagArab/status/1528292080337813504 </t>
+        </is>
+      </c>
       <c r="B704" t="inlineStr">
         <is>
-          <t>images/「スマイル」_img1.jpg</t>
+          <t>images/「身体の一部として…」_img1.jpg</t>
         </is>
       </c>
       <c r="C704" t="inlineStr">
         <is>
-          <t>スマイリー ,ツ</t>
+          <t>手書き語学 ,カンガルー</t>
         </is>
       </c>
     </row>
     <row r="705">
       <c r="A705" t="inlineStr">
-        <is>
-          <t xml:space="preserve">「身体の一部として…」
-2308 https://twitter.com/NatGeoMagArab/status/1528292080337813504 </t>
-        </is>
-      </c>
-      <c r="B705" t="inlineStr">
-        <is>
-          <t>images/「身体の一部として…」_img1.jpg</t>
-        </is>
-      </c>
-      <c r="C705" t="inlineStr">
-        <is>
-          <t>手書き語学 ,カンガルー</t>
-        </is>
-      </c>
-    </row>
-    <row r="706">
-      <c r="A706" t="inlineStr">
         <is>
           <t xml:space="preserve">「ディスカバリー」إكتشاف
 イクティシャーフ [iktiShaaf]
@@ -15296,19 +15274,19 @@
 2308 tephanegabrielli com </t>
         </is>
       </c>
-      <c r="B706" t="inlineStr">
+      <c r="B705" t="inlineStr">
         <is>
           <t>images/「ディスカバリー」_img1.jpg</t>
         </is>
       </c>
-      <c r="C706" t="inlineStr">
+      <c r="C705" t="inlineStr">
         <is>
           <t>discovery ,デザイン</t>
         </is>
       </c>
     </row>
-    <row r="707">
-      <c r="A707" t="inlineStr">
+    <row r="706">
+      <c r="A706" t="inlineStr">
         <is>
           <t xml:space="preserve">「重力波の発見は新しい窓を開いた」
 فتَح اكتشاف موجات الجاذبية نافذة جديدة
@@ -15316,19 +15294,19 @@
 2308 https://twitter.com/SciTalk2U/status/1454891943440289793 </t>
         </is>
       </c>
-      <c r="B707" t="inlineStr">
+      <c r="B706" t="inlineStr">
         <is>
           <t>images/「重力波の発見は新しい窓を開いた」_img1.jpg</t>
         </is>
       </c>
-      <c r="C707" t="inlineStr">
+      <c r="C706" t="inlineStr">
         <is>
           <t>手書き語学 ,アラビア語 ,重力波</t>
         </is>
       </c>
     </row>
-    <row r="708">
-      <c r="A708" t="inlineStr">
+    <row r="707">
+      <c r="A707" t="inlineStr">
         <is>
           <t xml:space="preserve">「微笑みに微笑み。先にした人の方が美しい」
 الإبتسامة بالإبتسامة والبادئ أجمل
@@ -15337,19 +15315,19 @@
 2104 出典不明 </t>
         </is>
       </c>
-      <c r="B708" t="inlineStr">
+      <c r="B707" t="inlineStr">
         <is>
           <t>images/「微笑みに微笑み。先にした人の方が美し_img1.jpg,images/「微笑みに微笑み。先にした人の方が美し_img2.jpg</t>
         </is>
       </c>
-      <c r="C708" t="inlineStr">
+      <c r="C707" t="inlineStr">
         <is>
           <t>スマイル ,名言</t>
         </is>
       </c>
     </row>
-    <row r="709">
-      <c r="A709" t="inlineStr">
+    <row r="708">
+      <c r="A708" t="inlineStr">
         <is>
           <t xml:space="preserve">「笑顔」ابتسامة
 イブティサーマ [ibtisaama(tun)]
@@ -15358,19 +15336,19 @@
 2308 satokomatsu, minne </t>
         </is>
       </c>
-      <c r="B709" t="inlineStr">
+      <c r="B708" t="inlineStr">
         <is>
           <t>images/「笑顔」_img1.jpg</t>
         </is>
       </c>
-      <c r="C709" t="inlineStr">
+      <c r="C708" t="inlineStr">
         <is>
           <t>スマイル ,ツ</t>
         </is>
       </c>
     </row>
-    <row r="710">
-      <c r="A710" t="inlineStr">
+    <row r="709">
+      <c r="A709" t="inlineStr">
         <is>
           <t xml:space="preserve">「信仰」ايمان
 イーマーン ['iimaan]
@@ -15379,19 +15357,19 @@
 2506 instagram com/p/6ST-WHOOkJ/ </t>
         </is>
       </c>
-      <c r="B710" t="inlineStr">
+      <c r="B709" t="inlineStr">
         <is>
           <t>images/「信仰」_img1.jpg</t>
         </is>
       </c>
-      <c r="C710" t="inlineStr">
+      <c r="C709" t="inlineStr">
         <is>
           <t>宗教 ,信念</t>
         </is>
       </c>
     </row>
-    <row r="711">
-      <c r="A711" t="inlineStr">
+    <row r="710">
+      <c r="A710" t="inlineStr">
         <is>
           <t xml:space="preserve">「放送」إذاعة
 イザーア ['iDhaa*a]
@@ -15400,19 +15378,19 @@
 2404 heemades, Instagram </t>
         </is>
       </c>
-      <c r="B711" t="inlineStr">
+      <c r="B710" t="inlineStr">
         <is>
           <t>images/「放送」_img1.jpg</t>
         </is>
       </c>
-      <c r="C711" t="inlineStr">
+      <c r="C710" t="inlineStr">
         <is>
           <t>デザイン ,ラジオ</t>
         </is>
       </c>
     </row>
-    <row r="712">
-      <c r="A712" t="inlineStr">
+    <row r="711">
+      <c r="A711" t="inlineStr">
         <is>
           <t xml:space="preserve">「かきとりのちから」
 مهاراتي الإملائية
@@ -15421,19 +15399,19 @@
 2308 iqrawaoktoub.wordpress com </t>
         </is>
       </c>
-      <c r="B712" t="inlineStr">
+      <c r="B711" t="inlineStr">
         <is>
           <t>images/「かきとりのちから」_img1.jpg</t>
         </is>
       </c>
-      <c r="C712" t="inlineStr">
+      <c r="C711" t="inlineStr">
         <is>
           <t>国語 ,教材</t>
         </is>
       </c>
     </row>
-    <row r="713">
-      <c r="A713" t="inlineStr">
+    <row r="712">
+      <c r="A712" t="inlineStr">
         <is>
           <t xml:space="preserve">「歴史を作った男たち」
 رجال صنعوا التاريخ
@@ -15443,38 +15421,38 @@
 2410 https://x.gd/Wl5rJ </t>
         </is>
       </c>
-      <c r="B713" t="inlineStr">
+      <c r="B712" t="inlineStr">
         <is>
           <t>images/「歴史を作った男たち」_img1.jpg</t>
         </is>
       </c>
-      <c r="C713" t="inlineStr">
+      <c r="C712" t="inlineStr">
         <is>
           <t>偉人</t>
         </is>
       </c>
     </row>
-    <row r="714">
-      <c r="A714" t="inlineStr">
+    <row r="713">
+      <c r="A713" t="inlineStr">
         <is>
           <t xml:space="preserve">「無限の宇宙を旅した光」
 「何百年もの末にジェイムズ・ウェッブ望遠鏡のレンズの上に落ち、我々に遠い宇宙の美しさを見せてくれる。最も純粋な形と最も素晴らしい姿で」
 2308 https://twitter.com/NatGeoMagArab/status/1557811592636485632 </t>
         </is>
       </c>
-      <c r="B714" t="inlineStr">
+      <c r="B713" t="inlineStr">
         <is>
           <t>images/「無限の宇宙を旅した光」_img1.jpg</t>
         </is>
       </c>
-      <c r="C714" t="inlineStr">
+      <c r="C713" t="inlineStr">
         <is>
           <t>手書き語学 ,宇宙</t>
         </is>
       </c>
     </row>
-    <row r="715">
-      <c r="A715" t="inlineStr">
+    <row r="714">
+      <c r="A714" t="inlineStr">
         <is>
           <t xml:space="preserve">「日本好きになり行きたくなる20項」
 عشرون شيئا يجعلك تحب اليابان وترغب في زيارتها
@@ -15483,19 +15461,19 @@
 2308 wattpad </t>
         </is>
       </c>
-      <c r="B715" t="inlineStr">
+      <c r="B714" t="inlineStr">
         <is>
           <t>images/「日本好きになり行きたくなる20項」_img1.jpg</t>
         </is>
       </c>
-      <c r="C715" t="inlineStr">
+      <c r="C714" t="inlineStr">
         <is>
           <t>اليابان ,Japan</t>
         </is>
       </c>
     </row>
-    <row r="716">
-      <c r="A716" t="inlineStr">
+    <row r="715">
+      <c r="A715" t="inlineStr">
         <is>
           <t xml:space="preserve">「ピッタリの瞬間に撮影され、ドラゴンが火を噴いているように見える」
 التُقطت في اللحظة المناسبة لتبدو مثل تنين ينفث اللهب
@@ -15503,19 +15481,19 @@
 2509 https://twitter.com/NatGeoMagArab/status/1588780660269150208 </t>
         </is>
       </c>
-      <c r="B716" t="inlineStr">
+      <c r="B715" t="inlineStr">
         <is>
           <t>images/「ピッタリの瞬間に撮影され、ドラゴンが_img1.jpg,images/ 「ピッタリの瞬間に撮影され、ドラゴンが_img2.jpg</t>
         </is>
       </c>
-      <c r="C716" t="inlineStr">
+      <c r="C715" t="inlineStr">
         <is>
           <t xml:space="preserve">ドラゴン </t>
         </is>
       </c>
     </row>
-    <row r="717">
-      <c r="A717" t="inlineStr">
+    <row r="716">
+      <c r="A716" t="inlineStr">
         <is>
           <t xml:space="preserve">「満足は不滅の宝である」
 القَناعَةُ كنز لا يَفنَى
@@ -15525,55 +15503,55 @@
 2308 kareem mrghani </t>
         </is>
       </c>
+      <c r="B716" t="inlineStr">
+        <is>
+          <t>images/「満足は不滅の宝である」_img1.jpg</t>
+        </is>
+      </c>
+      <c r="C716" t="inlineStr">
+        <is>
+          <t>幸福度</t>
+        </is>
+      </c>
+    </row>
+    <row r="717">
+      <c r="A717" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ゴシキセイガイインコ。
+2409 https://twitter.com/NatGeoMagArab/status/1600022262014676992 </t>
+        </is>
+      </c>
       <c r="B717" t="inlineStr">
         <is>
-          <t>images/「満足は不滅の宝である」_img1.jpg</t>
+          <t>images/ゴシキセイガイインコ。_img1.jpg</t>
         </is>
       </c>
       <c r="C717" t="inlineStr">
         <is>
-          <t>幸福度</t>
+          <t>手書き語学 ,アラビア語,オウム</t>
         </is>
       </c>
     </row>
     <row r="718">
       <c r="A718" t="inlineStr">
         <is>
-          <t xml:space="preserve">ゴシキセイガイインコ。
-2409 https://twitter.com/NatGeoMagArab/status/1600022262014676992 </t>
+          <t xml:space="preserve">モモンガ。
+2403 https://twitter.com/NatGeoMagArab/status/1552541872966344704 </t>
         </is>
       </c>
       <c r="B718" t="inlineStr">
         <is>
-          <t>images/ゴシキセイガイインコ。_img1.jpg</t>
+          <t>images/モモンガ。_img1.jpg,images/ モモンガ。_img2.jpg</t>
         </is>
       </c>
       <c r="C718" t="inlineStr">
         <is>
-          <t>手書き語学 ,アラビア語,オウム</t>
+          <t>手書き語学 ,アラビア語 ,モモンガ</t>
         </is>
       </c>
     </row>
     <row r="719">
       <c r="A719" t="inlineStr">
-        <is>
-          <t xml:space="preserve">モモンガ。
-2403 https://twitter.com/NatGeoMagArab/status/1552541872966344704 </t>
-        </is>
-      </c>
-      <c r="B719" t="inlineStr">
-        <is>
-          <t>images/モモンガ。_img1.jpg,images/ モモンガ。_img2.jpg</t>
-        </is>
-      </c>
-      <c r="C719" t="inlineStr">
-        <is>
-          <t>手書き語学 ,アラビア語 ,モモンガ</t>
-        </is>
-      </c>
-    </row>
-    <row r="720">
-      <c r="A720" t="inlineStr">
         <is>
           <t xml:space="preserve">「象の群れ。ドローンの音から逃げている」
 قطيع من الفيلة يفر هاربًا من صوت الدرون
@@ -15585,56 +15563,56 @@
 2009 https://twitter.com/NatGeoMagArab/status/1302970033627258881 </t>
         </is>
       </c>
+      <c r="B719" t="inlineStr">
+        <is>
+          <t>images/「象の群れ。ドローンの音から逃げている.jpg</t>
+        </is>
+      </c>
+      <c r="C719" t="inlineStr">
+        <is>
+          <t>ゾウ ,ドローン</t>
+        </is>
+      </c>
+    </row>
+    <row r="720">
+      <c r="A720" t="inlineStr">
+        <is>
+          <t xml:space="preserve">カルマン線。
+2308 https://twitter.com/NatGeoMagArab/status/1536436999522881536 </t>
+        </is>
+      </c>
       <c r="B720" t="inlineStr">
         <is>
-          <t>images/「象の群れ。ドローンの音から逃げている.jpg</t>
+          <t>images/カルマン線。_img1.jpg</t>
         </is>
       </c>
       <c r="C720" t="inlineStr">
         <is>
-          <t>ゾウ ,ドローン</t>
+          <t xml:space="preserve">手書き語学 ,アラビア語 ,宇宙 </t>
         </is>
       </c>
     </row>
     <row r="721">
       <c r="A721" t="inlineStr">
-        <is>
-          <t xml:space="preserve">カルマン線。
-2308 https://twitter.com/NatGeoMagArab/status/1536436999522881536 </t>
-        </is>
-      </c>
-      <c r="B721" t="inlineStr">
-        <is>
-          <t>images/カルマン線。_img1.jpg</t>
-        </is>
-      </c>
-      <c r="C721" t="inlineStr">
-        <is>
-          <t xml:space="preserve">手書き語学 ,アラビア語 ,宇宙 </t>
-        </is>
-      </c>
-    </row>
-    <row r="722">
-      <c r="A722" t="inlineStr">
         <is>
           <t xml:space="preserve">「恥ずかしがり屋のマヌルネコと暖かい朝の太陽光線」
 ⁦「二つの美しいもの」[Shay'-ayni jamiil-ayni] 属格：「物」( شيء )[Shay']・「美しい」( جميل )[jamiil]⁩
 2309 https://twitter.com/NatGeoMagArab/status/1697512148820504912 </t>
         </is>
       </c>
-      <c r="B722" t="inlineStr">
+      <c r="B721" t="inlineStr">
         <is>
           <t>images/「恥ずかしがり屋のマヌルネコと暖かい朝_img1.jpg</t>
         </is>
       </c>
-      <c r="C722" t="inlineStr">
+      <c r="C721" t="inlineStr">
         <is>
           <t>手書き語学 ,アラビア語 ,マヌルネコ</t>
         </is>
       </c>
     </row>
-    <row r="723">
-      <c r="A723" t="inlineStr">
+    <row r="722">
+      <c r="A722" t="inlineStr">
         <is>
           <t xml:space="preserve">「二回失敗しているペンギン」
 بطريق يفشل مرتين
@@ -15644,19 +15622,19 @@
 2308 https://twitter.com/NatGeoMagArab/status/1479483133766426626 </t>
         </is>
       </c>
-      <c r="B723" t="inlineStr">
+      <c r="B722" t="inlineStr">
         <is>
           <t>images/「二回失敗しているペンギン」_img1.jpg</t>
         </is>
       </c>
-      <c r="C723" t="inlineStr">
+      <c r="C722" t="inlineStr">
         <is>
           <t>ペンギン ,動物</t>
         </is>
       </c>
     </row>
-    <row r="724">
-      <c r="A724" t="inlineStr">
+    <row r="723">
+      <c r="A723" t="inlineStr">
         <is>
           <t xml:space="preserve">「2億光年の彼方できらめく炎と光」
 وهج ووميض يتلألأ على بعد 200 مليون سنة ضوئية
@@ -15667,15 +15645,15 @@
 2010 https://twitter.com/NatGeoMagArab/status/1303415502673342464 </t>
         </is>
       </c>
-      <c r="B724" t="inlineStr"/>
-      <c r="C724" t="inlineStr">
+      <c r="B723" t="inlineStr"/>
+      <c r="C723" t="inlineStr">
         <is>
           <t>宇宙 ,銀河</t>
         </is>
       </c>
     </row>
-    <row r="725">
-      <c r="A725" t="inlineStr">
+    <row r="724">
+      <c r="A724" t="inlineStr">
         <is>
           <t xml:space="preserve">「さまよう黒猫」قطة سوداء تجوب
 キッタトゥン・サウダーウ・タジューブ [qi^_tatun sawdaa'u ta-juub]
@@ -15684,19 +15662,19 @@
 2308 https://twitter.com/NatGeoMagArab/status/1532973177453760512 </t>
         </is>
       </c>
-      <c r="B725" t="inlineStr">
+      <c r="B724" t="inlineStr">
         <is>
           <t>images/「さまよう黒猫」_img1.jpg,images/ 「さまよう黒猫」_img2.jpg</t>
         </is>
       </c>
-      <c r="C725" t="inlineStr">
+      <c r="C724" t="inlineStr">
         <is>
           <t xml:space="preserve">手書き語学 ,モロッコ </t>
         </is>
       </c>
     </row>
-    <row r="726">
-      <c r="A726" t="inlineStr">
+    <row r="725">
+      <c r="A725" t="inlineStr">
         <is>
           <t xml:space="preserve">「サイのざらざらした皮を利用して自分の体を掻くネコ」
 قطة تستغل جلد الكركدن الخشن لحك جسدها
@@ -15705,19 +15683,19 @@
 2308 https://twitter.com/NatGeoMagArab/status/1476855740929216517 </t>
         </is>
       </c>
-      <c r="B726" t="inlineStr">
+      <c r="B725" t="inlineStr">
         <is>
           <t>images/「サイのざらざらした皮を利用して自分の_img1.jpg</t>
         </is>
       </c>
-      <c r="C726" t="inlineStr">
+      <c r="C725" t="inlineStr">
         <is>
           <t>サイ ,チェコ</t>
         </is>
       </c>
     </row>
-    <row r="727">
-      <c r="A727" t="inlineStr">
+    <row r="726">
+      <c r="A726" t="inlineStr">
         <is>
           <t xml:space="preserve">「沈まぬ太陽」شمس لا تغيب
 シャムス・ラー・タギーブ [Shams laa ta-Ghiib]
@@ -15726,19 +15704,19 @@
 2308 AHMED ELASSAL </t>
         </is>
       </c>
-      <c r="B727" t="inlineStr">
+      <c r="B726" t="inlineStr">
         <is>
           <t>images/「沈まぬ太陽」_img1.jpg</t>
         </is>
       </c>
-      <c r="C727" t="inlineStr">
+      <c r="C726" t="inlineStr">
         <is>
           <t>帝国 ,白夜</t>
         </is>
       </c>
     </row>
-    <row r="728">
-      <c r="A728" t="inlineStr">
+    <row r="727">
+      <c r="A727" t="inlineStr">
         <is>
           <t xml:space="preserve">「子供に食べさせている忍耐強い母親」
 أم صبورة تطعم صغيرها
@@ -15747,19 +15725,19 @@
 2308 https://twitter.com/natgeomagarab/status/1585572054509957120 </t>
         </is>
       </c>
-      <c r="B728" t="inlineStr">
+      <c r="B727" t="inlineStr">
         <is>
           <t>images/「子供に食べさせている忍耐強い母親」_img1.jpg</t>
         </is>
       </c>
-      <c r="C728" t="inlineStr">
+      <c r="C727" t="inlineStr">
         <is>
           <t>手書き語学 ,アラビア語 ,ミヤコドリ</t>
         </is>
       </c>
     </row>
-    <row r="729">
-      <c r="A729" t="inlineStr">
+    <row r="728">
+      <c r="A728" t="inlineStr">
         <is>
           <t xml:space="preserve">「コーヒーは繰り返さない恋物語」
 القهوة قصة عشق لن تتكرر
@@ -15769,19 +15747,19 @@
 2403 pin it/7tvd8Wc </t>
         </is>
       </c>
-      <c r="B729" t="inlineStr">
+      <c r="B728" t="inlineStr">
         <is>
           <t>images/「コーヒーは繰り返さない恋物語」_img1.jpg</t>
         </is>
       </c>
-      <c r="C729" t="inlineStr">
+      <c r="C728" t="inlineStr">
         <is>
           <t>コーヒー ,名言</t>
         </is>
       </c>
     </row>
-    <row r="730">
-      <c r="A730" t="inlineStr">
+    <row r="729">
+      <c r="A729" t="inlineStr">
         <is>
           <t xml:space="preserve">「星々で飾られた空。魅惑的な色合いで黄昏の美を満たしている」
 سماء مرصعة بالنجوم تضفي لمسة سحرية على جمال الشفق
@@ -15789,19 +15767,19 @@
 2010 https://twitter.com/NatGeoMagArab/status/1303777701975584768 </t>
         </is>
       </c>
-      <c r="B730" t="inlineStr">
+      <c r="B729" t="inlineStr">
         <is>
           <t>images/「星々で飾られた空。魅惑的な色合いで黄.png</t>
         </is>
       </c>
-      <c r="C730" t="inlineStr">
+      <c r="C729" t="inlineStr">
         <is>
           <t>星空 ,宇宙</t>
         </is>
       </c>
     </row>
-    <row r="731">
-      <c r="A731" t="inlineStr">
+    <row r="730">
+      <c r="A730" t="inlineStr">
         <is>
           <t xml:space="preserve">「国際宇宙ステーションからの写真。巨大な台風『ハイシェン（海神）』を映している」
 لقطات من محطة الفضاء الدولية تظهر إعصار "هايشن" الهائل
@@ -15809,19 +15787,19 @@
 2403 https://twitter.com/NatGeoMagArab/status/1302871968522235904 </t>
         </is>
       </c>
-      <c r="B731" t="inlineStr">
+      <c r="B730" t="inlineStr">
         <is>
           <t>images/「国際宇宙ステーションからの写真。巨大.png</t>
         </is>
       </c>
-      <c r="C731" t="inlineStr">
+      <c r="C730" t="inlineStr">
         <is>
           <t>台風</t>
         </is>
       </c>
     </row>
-    <row r="732">
-      <c r="A732" t="inlineStr">
+    <row r="731">
+      <c r="A731" t="inlineStr">
         <is>
           <t xml:space="preserve">「草を食む幸運な子羊たち」
 خراف محظوظة ترعى
@@ -15831,19 +15809,19 @@
 2308 https://twitter.com/NatGeoMagArab/status/1490211393554972676 </t>
         </is>
       </c>
-      <c r="B732" t="inlineStr">
+      <c r="B731" t="inlineStr">
         <is>
           <t>images/「草を食む幸運な子羊たち」_img1.jpg,images/ 「草を食む幸運な子羊たち」_img2.jpg</t>
         </is>
       </c>
-      <c r="C732" t="inlineStr">
+      <c r="C731" t="inlineStr">
         <is>
           <t>羊 ,アイルランド</t>
         </is>
       </c>
     </row>
-    <row r="733">
-      <c r="A733" t="inlineStr">
+    <row r="732">
+      <c r="A732" t="inlineStr">
         <is>
           <t xml:space="preserve">「お金で買えぬ10のもの」
 ١٠ أشياء لا تشترى بالمال
@@ -15853,19 +15831,19 @@
 2308 ayb124 </t>
         </is>
       </c>
-      <c r="B733" t="inlineStr">
+      <c r="B732" t="inlineStr">
         <is>
           <t>images/「お金で買えぬ10のもの」_img1.jpg</t>
         </is>
       </c>
-      <c r="C733" t="inlineStr">
+      <c r="C732" t="inlineStr">
         <is>
           <t>価値 ,購買</t>
         </is>
       </c>
     </row>
-    <row r="734">
-      <c r="A734" t="inlineStr">
+    <row r="733">
+      <c r="A733" t="inlineStr">
         <is>
           <t xml:space="preserve">「お金では買えないよ」
 هي أشْيَاءٌ لا تُشْتَرَى
@@ -15875,19 +15853,19 @@
 1906 mardy_zaawely, Instagram </t>
         </is>
       </c>
-      <c r="B734" t="inlineStr">
+      <c r="B733" t="inlineStr">
         <is>
           <t>images/「お金では買えないよ」_img1.jpg</t>
         </is>
       </c>
-      <c r="C734" t="inlineStr">
+      <c r="C733" t="inlineStr">
         <is>
           <t>マスターカード ,価値</t>
         </is>
       </c>
     </row>
-    <row r="735">
-      <c r="A735" t="inlineStr">
+    <row r="734">
+      <c r="A734" t="inlineStr">
         <is>
           <t xml:space="preserve">「好奇心旺盛なホッキョクギツネ」
 ثعلب قطبي يملؤه الفضول
@@ -15897,15 +15875,15 @@
 2308 https://twitter.com/natgeomagarab/status/1157592172968808449 </t>
         </is>
       </c>
-      <c r="B735" t="inlineStr"/>
-      <c r="C735" t="inlineStr">
+      <c r="B734" t="inlineStr"/>
+      <c r="C734" t="inlineStr">
         <is>
           <t>ファーストコンタクト ,キツネ</t>
         </is>
       </c>
     </row>
-    <row r="736">
-      <c r="A736" t="inlineStr">
+    <row r="735">
+      <c r="A735" t="inlineStr">
         <is>
           <t xml:space="preserve">「グレンダイザーのいる国は死にません」
 لنْ يَموتَ شَعبٌ لدَيهِ غرندايزر
@@ -15914,56 +15892,56 @@
 2308 https://www.aljarida.com/articles/1462241741574732100/ </t>
         </is>
       </c>
+      <c r="B735" t="inlineStr">
+        <is>
+          <t>images/「グレンダイザーのいる国は死にません」_img1.jpg</t>
+        </is>
+      </c>
+      <c r="C735" t="inlineStr">
+        <is>
+          <t>UFOロボ ,アニメ</t>
+        </is>
+      </c>
+    </row>
+    <row r="736">
+      <c r="A736" t="inlineStr">
+        <is>
+          <t xml:space="preserve">「凍結路面を運転中、彼女は嫌な場面に居合わせた」
+2408 https://twitter.com/NatGeoMagArab/status/1610305209657626625 </t>
+        </is>
+      </c>
       <c r="B736" t="inlineStr">
         <is>
-          <t>images/「グレンダイザーのいる国は死にません」_img1.jpg</t>
+          <t>images/「凍結路面を運転中、彼女は嫌な場面に居_img1.jpg</t>
         </is>
       </c>
       <c r="C736" t="inlineStr">
         <is>
-          <t>UFOロボ ,アニメ</t>
+          <t>手書き語学 ,アラビア語 ,路面凍結</t>
         </is>
       </c>
     </row>
     <row r="737">
       <c r="A737" t="inlineStr">
-        <is>
-          <t xml:space="preserve">「凍結路面を運転中、彼女は嫌な場面に居合わせた」
-2408 https://twitter.com/NatGeoMagArab/status/1610305209657626625 </t>
-        </is>
-      </c>
-      <c r="B737" t="inlineStr">
-        <is>
-          <t>images/「凍結路面を運転中、彼女は嫌な場面に居_img1.jpg</t>
-        </is>
-      </c>
-      <c r="C737" t="inlineStr">
-        <is>
-          <t>手書き語学 ,アラビア語 ,路面凍結</t>
-        </is>
-      </c>
-    </row>
-    <row r="738">
-      <c r="A738" t="inlineStr">
         <is>
           <t xml:space="preserve">「虹が美しさを加えている、アルパカという動物の美しいショット」
 ⁦「美しいショット」[laq_tatun jamiilatun]：「ショット」( لقطة )[laq_ta]：( ـلٌ )[-lun]・( ـقٌ )[-qun]・( ـطٌ )[-_tun]・( ـةٌ )[-tun]⁩
 2308 https://twitter.com/natgeomagarab/status/1155115655928004608 </t>
         </is>
       </c>
-      <c r="B738" t="inlineStr">
+      <c r="B737" t="inlineStr">
         <is>
           <t>images/「虹が美しさを加えている、アルパカとい_img1.jpg</t>
         </is>
       </c>
-      <c r="C738" t="inlineStr">
+      <c r="C737" t="inlineStr">
         <is>
           <t>モフモフ ,アルパカ</t>
         </is>
       </c>
     </row>
-    <row r="739">
-      <c r="A739" t="inlineStr">
+    <row r="738">
+      <c r="A738" t="inlineStr">
         <is>
           <t xml:space="preserve">「幸せは…全然思いもよらない所からやって来る」
 السعادة تأتينا من أماكن لم نكن نتوقعها أبداً
@@ -15972,19 +15950,19 @@
 2109 出典不明 </t>
         </is>
       </c>
-      <c r="B739" t="inlineStr">
+      <c r="B738" t="inlineStr">
         <is>
           <t>images/「幸せは…全然思いもよらない所からやっ_img1.jpg,images/ 「幸せは…全然思いもよらない所からやっ_img2.jpg</t>
         </is>
       </c>
-      <c r="C739" t="inlineStr">
+      <c r="C738" t="inlineStr">
         <is>
           <t>訪れ ,予想</t>
         </is>
       </c>
     </row>
-    <row r="740">
-      <c r="A740" t="inlineStr">
+    <row r="739">
+      <c r="A739" t="inlineStr">
         <is>
           <t xml:space="preserve">「あらゆる問題は、食べ物が解決してくれる」
 كل مشكلة ولها أكلة تحلها
@@ -15993,19 +15971,19 @@
 1909 ALQA AN 878 </t>
         </is>
       </c>
-      <c r="B740" t="inlineStr">
+      <c r="B739" t="inlineStr">
         <is>
           <t>images/「あらゆる問題は、食べ物が解決してくれ_img1.jpg</t>
         </is>
       </c>
-      <c r="C740" t="inlineStr">
+      <c r="C739" t="inlineStr">
         <is>
           <t>ストレス ,精神</t>
         </is>
       </c>
     </row>
-    <row r="741">
-      <c r="A741" t="inlineStr">
+    <row r="740">
+      <c r="A740" t="inlineStr">
         <is>
           <t xml:space="preserve">「冬で私が好きな物」
 أشياء أحبها بالشتاء
@@ -16015,19 +15993,19 @@
 2109 出典不明 </t>
         </is>
       </c>
-      <c r="B741" t="inlineStr">
+      <c r="B740" t="inlineStr">
         <is>
           <t>images/「冬で私が好きな物」_img1.jpg</t>
         </is>
       </c>
-      <c r="C741" t="inlineStr">
+      <c r="C740" t="inlineStr">
         <is>
           <t>季節 ,冬</t>
         </is>
       </c>
     </row>
-    <row r="742">
-      <c r="A742" t="inlineStr">
+    <row r="741">
+      <c r="A741" t="inlineStr">
         <is>
           <t xml:space="preserve">「お金で買うことの出来ない物」
 أشياء لا تستطيع شراءها بالمال
@@ -16037,19 +16015,19 @@
 2409 https://x.com/akhbarak/status/1038402708414373888 </t>
         </is>
       </c>
-      <c r="B742" t="inlineStr">
+      <c r="B741" t="inlineStr">
         <is>
           <t>images/「お金で買うことの出来ない物」_img1.jpg,images/ 「お金で買うことの出来ない物」_img2.jpg</t>
         </is>
       </c>
-      <c r="C742" t="inlineStr">
+      <c r="C741" t="inlineStr">
         <is>
           <t>ショッピング ,価値</t>
         </is>
       </c>
     </row>
-    <row r="743">
-      <c r="A743" t="inlineStr">
+    <row r="742">
+      <c r="A742" t="inlineStr">
         <is>
           <t xml:space="preserve">「私たちが愛する言葉」
 كلماتٌ نُحبّها
@@ -16059,19 +16037,19 @@
 2109 جليل خزعل </t>
         </is>
       </c>
-      <c r="B743" t="inlineStr">
+      <c r="B742" t="inlineStr">
         <is>
           <t>images/「私たちが愛する言葉」_img1.jpg</t>
         </is>
       </c>
-      <c r="C743" t="inlineStr">
+      <c r="C742" t="inlineStr">
         <is>
           <t>花 ,贈り物</t>
         </is>
       </c>
     </row>
-    <row r="744">
-      <c r="A744" t="inlineStr">
+    <row r="743">
+      <c r="A743" t="inlineStr">
         <is>
           <t xml:space="preserve">「お茶についてあなたが知らない10の事実」
 عشر معلومات لا تعرفها عن الشاي
@@ -16080,19 +16058,19 @@
 2012 http://ara.tv/6syq2 </t>
         </is>
       </c>
-      <c r="B744" t="inlineStr">
+      <c r="B743" t="inlineStr">
         <is>
           <t>images/「お茶についてあなたが知らない10の事_img1.jpg</t>
         </is>
       </c>
-      <c r="C744" t="inlineStr">
+      <c r="C743" t="inlineStr">
         <is>
           <t>神農</t>
         </is>
       </c>
     </row>
-    <row r="745">
-      <c r="A745" t="inlineStr">
+    <row r="744">
+      <c r="A744" t="inlineStr">
         <is>
           <t xml:space="preserve">「大きくなったウソ」
 الكذبة الّتي كبرت
@@ -16102,19 +16080,19 @@
 2509 سلسلة الحلزونة </t>
         </is>
       </c>
-      <c r="B745" t="inlineStr">
+      <c r="B744" t="inlineStr">
         <is>
           <t>images/「大きくなったウソ」_img1.jpg</t>
         </is>
       </c>
-      <c r="C745" t="inlineStr">
+      <c r="C744" t="inlineStr">
         <is>
           <t>絵本</t>
         </is>
       </c>
     </row>
-    <row r="746">
-      <c r="A746" t="inlineStr">
+    <row r="745">
+      <c r="A745" t="inlineStr">
         <is>
           <t xml:space="preserve">「自分に合った掃除機を買うには？」
 كيف تشتري المكنسة الكهربائية التي تناسبك؟
@@ -16123,19 +16101,19 @@
 2106 ts3a com </t>
         </is>
       </c>
-      <c r="B746" t="inlineStr">
+      <c r="B745" t="inlineStr">
         <is>
           <t>images/「自分に合った掃除機を買うには？」_img1.jpg</t>
         </is>
       </c>
-      <c r="C746" t="inlineStr">
+      <c r="C745" t="inlineStr">
         <is>
           <t>家電 ,掃除</t>
         </is>
       </c>
     </row>
-    <row r="747">
-      <c r="A747" t="inlineStr">
+    <row r="746">
+      <c r="A746" t="inlineStr">
         <is>
           <t xml:space="preserve">「仮にこれが批判の数としよう」
 لنفرض ان عدد الذين ينتقدونك
@@ -16146,19 +16124,19 @@
 2504 出典不明 </t>
         </is>
       </c>
-      <c r="B747" t="inlineStr">
+      <c r="B746" t="inlineStr">
         <is>
           <t>images/「仮にこれが批判の数としよう」_img1.jpg</t>
         </is>
       </c>
-      <c r="C747" t="inlineStr">
+      <c r="C746" t="inlineStr">
         <is>
           <t>アンチ</t>
         </is>
       </c>
     </row>
-    <row r="748">
-      <c r="A748" t="inlineStr">
+    <row r="747">
+      <c r="A747" t="inlineStr">
         <is>
           <t xml:space="preserve">「ここに見えるのは何？」
 ما الذي تراه هنا؟
@@ -16168,15 +16146,15 @@
 2204 https://twitter.com/NatGeoMagArab/status/1506933850617700352 </t>
         </is>
       </c>
-      <c r="B748" t="inlineStr"/>
-      <c r="C748" t="inlineStr">
+      <c r="B747" t="inlineStr"/>
+      <c r="C747" t="inlineStr">
         <is>
           <t xml:space="preserve">ペンギン </t>
         </is>
       </c>
     </row>
-    <row r="749">
-      <c r="A749" t="inlineStr">
+    <row r="748">
+      <c r="A748" t="inlineStr">
         <is>
           <t xml:space="preserve">「今日辛いこと、明日は平気だろう」
 ما يؤلم اليوم سيهون غدًا
@@ -16186,19 +16164,19 @@
 2308 basmahjeff </t>
         </is>
       </c>
-      <c r="B749" t="inlineStr">
+      <c r="B748" t="inlineStr">
         <is>
           <t>images/「今日辛いこと、明日は平気だろう」_img1.jpg</t>
         </is>
       </c>
-      <c r="C749" t="inlineStr">
+      <c r="C748" t="inlineStr">
         <is>
           <t>悩み ,達観</t>
         </is>
       </c>
     </row>
-    <row r="750">
-      <c r="A750" t="inlineStr">
+    <row r="749">
+      <c r="A749" t="inlineStr">
         <is>
           <t xml:space="preserve">「自分のすることを好きでなきゃ」
 عليك أن تحب ما تفعل
@@ -16207,19 +16185,19 @@
 1810 Ahmed Elhakeem </t>
         </is>
       </c>
-      <c r="B750" t="inlineStr">
+      <c r="B749" t="inlineStr">
         <is>
           <t>images/「自分のすることを好きでなきゃ」_img1.jpg</t>
         </is>
       </c>
-      <c r="C750" t="inlineStr">
+      <c r="C749" t="inlineStr">
         <is>
           <t>転職 ,かわいい</t>
         </is>
       </c>
     </row>
-    <row r="751">
-      <c r="A751" t="inlineStr">
+    <row r="750">
+      <c r="A750" t="inlineStr">
         <is>
           <t xml:space="preserve">「この地上に生き甲斐あり」
 على هذه الأرض ما يستحق الحياة
@@ -16229,19 +16207,19 @@
 2308 Mahmoud Gafar </t>
         </is>
       </c>
-      <c r="B751" t="inlineStr">
+      <c r="B750" t="inlineStr">
         <is>
           <t>images/「この地上に生き甲斐あり」_img1.jpg</t>
         </is>
       </c>
-      <c r="C751" t="inlineStr">
+      <c r="C750" t="inlineStr">
         <is>
           <t>詩</t>
         </is>
       </c>
     </row>
-    <row r="752">
-      <c r="A752" t="inlineStr">
+    <row r="751">
+      <c r="A751" t="inlineStr">
         <is>
           <t xml:space="preserve">「オレンジの効能が何か知っていますか？」
 هل تعرف ما هي فوائد البرتقال؟
@@ -16251,19 +16229,19 @@
 2308 sadahadhramowt com </t>
         </is>
       </c>
-      <c r="B752" t="inlineStr">
+      <c r="B751" t="inlineStr">
         <is>
           <t>images/「オレンジの効能が何か知っていますか？_img1.jpg</t>
         </is>
       </c>
-      <c r="C752" t="inlineStr">
+      <c r="C751" t="inlineStr">
         <is>
           <t>オレンジ ,フルーツ</t>
         </is>
       </c>
     </row>
-    <row r="753">
-      <c r="A753" t="inlineStr">
+    <row r="752">
+      <c r="A752" t="inlineStr">
         <is>
           <t xml:space="preserve">「遊ぶパンダの光景より可愛いものがありますか？」
 هل هناك ما هو ألطف من مشاهدة الباندا وهي تلعب؟
@@ -16271,19 +16249,19 @@
 2308 https://twitter.com/NatGeoMagArab/status/1494612797858074626 </t>
         </is>
       </c>
-      <c r="B753" t="inlineStr">
+      <c r="B752" t="inlineStr">
         <is>
           <t>images/「遊ぶパンダの光景より可愛いものがあり_img1.jpg</t>
         </is>
       </c>
-      <c r="C753" t="inlineStr">
+      <c r="C752" t="inlineStr">
         <is>
           <t>パンダ ,モコモコ</t>
         </is>
       </c>
     </row>
-    <row r="754">
-      <c r="A754" t="inlineStr">
+    <row r="753">
+      <c r="A753" t="inlineStr">
         <is>
           <t xml:space="preserve">「大事なのは何者だったかじゃない。何者になるかだ」
 ليسَ المُهم ما كُنتَ بل مَا ستكون
@@ -16292,19 +16270,19 @@
 2308 出典不明 </t>
         </is>
       </c>
-      <c r="B754" t="inlineStr">
+      <c r="B753" t="inlineStr">
         <is>
           <t>images/「大事なのは何者だったかじゃない。何者_img1.jpg</t>
         </is>
       </c>
-      <c r="C754" t="inlineStr">
+      <c r="C753" t="inlineStr">
         <is>
           <t>自己実現 ,存在価値</t>
         </is>
       </c>
     </row>
-    <row r="755">
-      <c r="A755" t="inlineStr">
+    <row r="754">
+      <c r="A754" t="inlineStr">
         <is>
           <t xml:space="preserve">「あなたであれ。ありのままが美しいから」
 كُنْ أَنْتَ لأنك جميل كما أنت
@@ -16313,19 +16291,19 @@
 2308 IDREES DESIGN </t>
         </is>
       </c>
-      <c r="B755" t="inlineStr">
+      <c r="B754" t="inlineStr">
         <is>
           <t>images/「あなたであれ。ありのままが美しいから_img1.jpg</t>
         </is>
       </c>
-      <c r="C755" t="inlineStr">
+      <c r="C754" t="inlineStr">
         <is>
           <t>自己肯定 ,BeYourself</t>
         </is>
       </c>
     </row>
-    <row r="756">
-      <c r="A756" t="inlineStr">
+    <row r="755">
+      <c r="A755" t="inlineStr">
         <is>
           <t xml:space="preserve">「恐れの中に生きる者は決して自由になれない」
 من يعش في خوف لن يكون حرا أبدا
@@ -16334,19 +16312,19 @@
 2111 rjeem com </t>
         </is>
       </c>
-      <c r="B756" t="inlineStr">
+      <c r="B755" t="inlineStr">
         <is>
           <t>images/「恐れの中に生きる者は決して自由になれ_img1.jpg,images/ 「恐れの中に生きる者は決して自由になれ_img2.jpg</t>
         </is>
       </c>
-      <c r="C756" t="inlineStr">
+      <c r="C755" t="inlineStr">
         <is>
           <t>勇気 ,壁</t>
         </is>
       </c>
     </row>
-    <row r="757">
-      <c r="A757" t="inlineStr">
+    <row r="756">
+      <c r="A756" t="inlineStr">
         <is>
           <t xml:space="preserve">「己の翼を信じる者は己の重さを案じない」
 من يثق في جناحيه لن يهتم لوزنه
@@ -16355,19 +16333,19 @@
 2308 kmrghani </t>
         </is>
       </c>
-      <c r="B757" t="inlineStr">
+      <c r="B756" t="inlineStr">
         <is>
           <t>images/「己の翼を信じる者は己の重さを案じない_img1.jpg</t>
         </is>
       </c>
-      <c r="C757" t="inlineStr">
+      <c r="C756" t="inlineStr">
         <is>
           <t>自信</t>
         </is>
       </c>
     </row>
-    <row r="758">
-      <c r="A758" t="inlineStr">
+    <row r="757">
+      <c r="A757" t="inlineStr">
         <is>
           <t xml:space="preserve">「珈琲で一番大事な事！誰と飲むか？」
 الأهم من القهوة!! من ستشربها معه؟
@@ -16376,19 +16354,19 @@
 1812 gwid3.tumblr </t>
         </is>
       </c>
-      <c r="B758" t="inlineStr">
+      <c r="B757" t="inlineStr">
         <is>
           <t>images/「珈琲で一番大事な事！誰と飲むか？」_img1.jpg</t>
         </is>
       </c>
-      <c r="C758" t="inlineStr">
+      <c r="C757" t="inlineStr">
         <is>
           <t>コーヒー ,名言</t>
         </is>
       </c>
     </row>
-    <row r="759">
-      <c r="A759" t="inlineStr">
+    <row r="758">
+      <c r="A758" t="inlineStr">
         <is>
           <t xml:space="preserve">「人生は美しい、そう望んだ者には。」
 الحياة جَميلَة .. لمن أراد ذلك
@@ -16398,19 +16376,19 @@
 2109 出典不明 </t>
         </is>
       </c>
-      <c r="B759" t="inlineStr">
+      <c r="B758" t="inlineStr">
         <is>
           <t>images/「人生は美しい、そう望んだ者には。」_img1.jpg</t>
         </is>
       </c>
-      <c r="C759" t="inlineStr">
+      <c r="C758" t="inlineStr">
         <is>
           <t>名言 ,アート</t>
         </is>
       </c>
     </row>
-    <row r="760">
-      <c r="A760" t="inlineStr">
+    <row r="759">
+      <c r="A759" t="inlineStr">
         <is>
           <t xml:space="preserve">「ハム太郎って子を知ってるかい」
 هل تعرفون من هو هامتارو
@@ -16420,19 +16398,19 @@
 2109 </t>
         </is>
       </c>
-      <c r="B760" t="inlineStr">
+      <c r="B759" t="inlineStr">
         <is>
           <t>images/「ハム太郎って子を知ってるかい」_img1.jpg</t>
         </is>
       </c>
-      <c r="C760" t="inlineStr">
+      <c r="C759" t="inlineStr">
         <is>
           <t>オープニング ,ハム太郎</t>
         </is>
       </c>
     </row>
-    <row r="761">
-      <c r="A761" t="inlineStr">
+    <row r="760">
+      <c r="A760" t="inlineStr">
         <is>
           <t xml:space="preserve">「幸せを求める人もいれば、作る人もいる」
 هناك من يبحث عن السعادة وهناك من يصنعها
@@ -16441,19 +16419,19 @@
 2308 hindah tumblr </t>
         </is>
       </c>
-      <c r="B761" t="inlineStr">
+      <c r="B760" t="inlineStr">
         <is>
           <t>images/「幸せを求める人もいれば、作る人もいる_img1.jpg</t>
         </is>
       </c>
-      <c r="C761" t="inlineStr">
+      <c r="C760" t="inlineStr">
         <is>
           <t>幸せ ,名言 ,教訓</t>
         </is>
       </c>
     </row>
-    <row r="762">
-      <c r="A762" t="inlineStr">
+    <row r="761">
+      <c r="A761" t="inlineStr">
         <is>
           <t xml:space="preserve">「明白なるアラブの言葉によって」
 بلسان عربي مبين
@@ -16463,19 +16441,19 @@
 2109 Abdullah Barakat behance </t>
         </is>
       </c>
-      <c r="B762" t="inlineStr">
+      <c r="B761" t="inlineStr">
         <is>
           <t>images/「明白なるアラブの言葉によって」_img1.jpg</t>
         </is>
       </c>
-      <c r="C762" t="inlineStr">
+      <c r="C761" t="inlineStr">
         <is>
           <t>イスラム教 ,神聖</t>
         </is>
       </c>
     </row>
-    <row r="763">
-      <c r="A763" t="inlineStr">
+    <row r="762">
+      <c r="A762" t="inlineStr">
         <is>
           <t xml:space="preserve">「結婚前、結婚後」
 قبل الزواج، بعد الزواج
@@ -16485,19 +16463,19 @@
 2308 出典不明 </t>
         </is>
       </c>
-      <c r="B763" t="inlineStr">
+      <c r="B762" t="inlineStr">
         <is>
           <t>images/「結婚前、結婚後」_img1.jpg</t>
         </is>
       </c>
-      <c r="C763" t="inlineStr">
+      <c r="C762" t="inlineStr">
         <is>
           <t>BeforeAfter ,幸せ太り</t>
         </is>
       </c>
     </row>
-    <row r="764">
-      <c r="A764" t="inlineStr">
+    <row r="763">
+      <c r="A763" t="inlineStr">
         <is>
           <t xml:space="preserve">「驚きの価格で」بسعر رائع
 ビスィアル・ラーイア [bi-si*r raa'i*]
@@ -16506,19 +16484,19 @@
 2109 Jarir Bookstore </t>
         </is>
       </c>
-      <c r="B764" t="inlineStr">
+      <c r="B763" t="inlineStr">
         <is>
           <t>images/「驚きの価格で」_img1.jpg</t>
         </is>
       </c>
-      <c r="C764" t="inlineStr">
+      <c r="C763" t="inlineStr">
         <is>
           <t>広告 ,安値</t>
         </is>
       </c>
     </row>
-    <row r="765">
-      <c r="A765" t="inlineStr">
+    <row r="764">
+      <c r="A764" t="inlineStr">
         <is>
           <t xml:space="preserve">「我が魂と共に」مع نفسي
 マア・ナフスィ [ma*a nafs-iy]
@@ -16527,19 +16505,19 @@
 2110 出典不明 </t>
         </is>
       </c>
-      <c r="B765" t="inlineStr">
+      <c r="B764" t="inlineStr">
         <is>
           <t>images/「我が魂と共に」_img1.jpg</t>
         </is>
       </c>
-      <c r="C765" t="inlineStr">
+      <c r="C764" t="inlineStr">
         <is>
           <t>ソウル ,soul</t>
         </is>
       </c>
     </row>
-    <row r="766">
-      <c r="A766" t="inlineStr">
+    <row r="765">
+      <c r="A765" t="inlineStr">
         <is>
           <t xml:space="preserve">「暗い夜に」في ليلة مظلمة
  [fiy layla(tin) mu_Dhlima(tin)]
@@ -16548,19 +16526,19 @@
 2109 سلسلة الحلزونة </t>
         </is>
       </c>
-      <c r="B766" t="inlineStr">
+      <c r="B765" t="inlineStr">
         <is>
           <t>images/「暗い夜に」_img1.jpg</t>
         </is>
       </c>
-      <c r="C766" t="inlineStr">
+      <c r="C765" t="inlineStr">
         <is>
           <t>絵本</t>
         </is>
       </c>
     </row>
-    <row r="767">
-      <c r="A767" t="inlineStr">
+    <row r="766">
+      <c r="A766" t="inlineStr">
         <is>
           <t xml:space="preserve">「ゆっくりと」بشويش
 ビシワェーシ [bi-ShwySh]
@@ -16568,19 +16546,19 @@
 2109 出典不明 </t>
         </is>
       </c>
-      <c r="B767" t="inlineStr">
+      <c r="B766" t="inlineStr">
         <is>
           <t>images/「ゆっくりと」_img1.jpg</t>
         </is>
       </c>
-      <c r="C767" t="inlineStr">
+      <c r="C766" t="inlineStr">
         <is>
           <t>丸 ,円</t>
         </is>
       </c>
     </row>
-    <row r="768">
-      <c r="A768" t="inlineStr">
+    <row r="767">
+      <c r="A767" t="inlineStr">
         <is>
           <t xml:space="preserve">「この広い宇宙に…」
 في الكون الفسيح
@@ -16589,19 +16567,19 @@
 2308 wattpad </t>
         </is>
       </c>
-      <c r="B768" t="inlineStr">
+      <c r="B767" t="inlineStr">
         <is>
           <t>images/「この広い宇宙に…」_img1.jpg</t>
         </is>
       </c>
-      <c r="C768" t="inlineStr">
+      <c r="C767" t="inlineStr">
         <is>
           <t>アニメ ,宇宙</t>
         </is>
       </c>
     </row>
-    <row r="769">
-      <c r="A769" t="inlineStr">
+    <row r="768">
+      <c r="A768" t="inlineStr">
         <is>
           <t xml:space="preserve">「がんばって！」بالتوفيق
 ビッタウフィーク [bi^tawfiiq]
@@ -16609,19 +16587,19 @@
 2111 https://sites.google.com/site/mathmatic1905/ </t>
         </is>
       </c>
-      <c r="B769" t="inlineStr">
+      <c r="B768" t="inlineStr">
         <is>
           <t>images/「がんばって！」_img1.jpg</t>
         </is>
       </c>
-      <c r="C769" t="inlineStr">
+      <c r="C768" t="inlineStr">
         <is>
           <t>アラビア語</t>
         </is>
       </c>
     </row>
-    <row r="770">
-      <c r="A770" t="inlineStr">
+    <row r="769">
+      <c r="A769" t="inlineStr">
         <is>
           <t xml:space="preserve">「インターステラー」بين النجوم
 バイナ_ンヌジューム [bayna ^nujuum]
@@ -16629,19 +16607,19 @@
 2308 kmrghani </t>
         </is>
       </c>
-      <c r="B770" t="inlineStr">
+      <c r="B769" t="inlineStr">
         <is>
           <t>images/「インターステラー」_img1.jpg</t>
         </is>
       </c>
-      <c r="C770" t="inlineStr">
+      <c r="C769" t="inlineStr">
         <is>
           <t>映画 ,宇宙</t>
         </is>
       </c>
     </row>
-    <row r="771">
-      <c r="A771" t="inlineStr">
+    <row r="770">
+      <c r="A770" t="inlineStr">
         <is>
           <t xml:space="preserve">「アラビア語で」بالعربية
 ビ_ルアラビーヤ [bi-l-*arabiyya]
@@ -16650,19 +16628,19 @@
 1811 </t>
         </is>
       </c>
-      <c r="B771" t="inlineStr">
+      <c r="B770" t="inlineStr">
         <is>
           <t>images/「アラビア語で」_img1.jpg</t>
         </is>
       </c>
-      <c r="C771" t="inlineStr">
+      <c r="C770" t="inlineStr">
         <is>
           <t>ニュース ,CNN</t>
         </is>
       </c>
     </row>
-    <row r="772">
-      <c r="A772" t="inlineStr">
+    <row r="771">
+      <c r="A771" t="inlineStr">
         <is>
           <t xml:space="preserve">「17世紀に発明されて以来…」
 منذ اختراعه بالقرن السابع عشر
@@ -16670,19 +16648,19 @@
 2308 https://twitter.com/SciTalk2U/status/1450888395815854080 </t>
         </is>
       </c>
-      <c r="B772" t="inlineStr">
+      <c r="B771" t="inlineStr">
         <is>
           <t>images/「17世紀に発明されて以来…」_img1.jpg</t>
         </is>
       </c>
-      <c r="C772" t="inlineStr">
+      <c r="C771" t="inlineStr">
         <is>
           <t>手書き語学 ,アラビア語 ,望遠鏡</t>
         </is>
       </c>
     </row>
-    <row r="773">
-      <c r="A773" t="inlineStr">
+    <row r="772">
+      <c r="A772" t="inlineStr">
         <is>
           <t xml:space="preserve">「私できるよ」إنّني أستطيع
 インナニー・アスタティーウ ['inna-niy 'a-sta_tii*u]
@@ -16691,19 +16669,19 @@
 2412 سلسلة الحلزونة </t>
         </is>
       </c>
-      <c r="B773" t="inlineStr">
+      <c r="B772" t="inlineStr">
         <is>
           <t>images/「私できるよ」_img1.jpg</t>
         </is>
       </c>
-      <c r="C773" t="inlineStr">
+      <c r="C772" t="inlineStr">
         <is>
           <t>絵本 ,こども</t>
         </is>
       </c>
     </row>
-    <row r="774">
-      <c r="A774" t="inlineStr">
+    <row r="773">
+      <c r="A773" t="inlineStr">
         <is>
           <t xml:space="preserve">「問題なし」مافيش مشكلة
 マフィーシムシュキラ [ma-fy-Sh muShkila]
@@ -16712,19 +16690,19 @@
 2109 tanzerin.theshop </t>
         </is>
       </c>
-      <c r="B774" t="inlineStr">
+      <c r="B773" t="inlineStr">
         <is>
           <t>images/「問題なし」_img1.jpg</t>
         </is>
       </c>
-      <c r="C774" t="inlineStr">
+      <c r="C773" t="inlineStr">
         <is>
           <t>シャツ ,キッズ</t>
         </is>
       </c>
     </row>
-    <row r="775">
-      <c r="A775" t="inlineStr">
+    <row r="774">
+      <c r="A774" t="inlineStr">
         <is>
           <t xml:space="preserve">「不可能はない」مفيش مستحيل
 マフィーシ・ムスタヒール [ma-fy-Sh mustaHiil]
@@ -16733,19 +16711,19 @@
 2109 أموج </t>
         </is>
       </c>
-      <c r="B775" t="inlineStr">
+      <c r="B774" t="inlineStr">
         <is>
           <t>images/「不可能はない」_img1.jpg</t>
         </is>
       </c>
-      <c r="C775" t="inlineStr">
+      <c r="C774" t="inlineStr">
         <is>
           <t>ポジティブ ,挑戦</t>
         </is>
       </c>
     </row>
-    <row r="776">
-      <c r="A776" t="inlineStr">
+    <row r="775">
+      <c r="A775" t="inlineStr">
         <is>
           <t xml:space="preserve">「等々」إلخ
 イラク ['ilaKh]
@@ -16754,19 +16732,19 @@
 2201 出典不明 </t>
         </is>
       </c>
-      <c r="B776" t="inlineStr">
+      <c r="B775" t="inlineStr">
         <is>
           <t>images/「等々」_img1.jpg</t>
         </is>
       </c>
-      <c r="C776" t="inlineStr">
+      <c r="C775" t="inlineStr">
         <is>
           <t>etc ,とんち</t>
         </is>
       </c>
     </row>
-    <row r="777">
-      <c r="A777" t="inlineStr">
+    <row r="776">
+      <c r="A776" t="inlineStr">
         <is>
           <t xml:space="preserve">⁦「調子どう？」⁩شلونَك؟
 シュローナク？ [Sh-loon-ak?]
@@ -16775,19 +16753,19 @@
 2202 Jozoor Team. </t>
         </is>
       </c>
-      <c r="B777" t="inlineStr">
+      <c r="B776" t="inlineStr">
         <is>
           <t>images/⁦「調子どう？」⁩_img1.jpg</t>
         </is>
       </c>
-      <c r="C777" t="inlineStr">
+      <c r="C776" t="inlineStr">
         <is>
           <t>洒落 ,ルービックキューブ</t>
         </is>
       </c>
     </row>
-    <row r="778">
-      <c r="A778" t="inlineStr">
+    <row r="777">
+      <c r="A777" t="inlineStr">
         <is>
           <t xml:space="preserve">「行くな」ماتروحش
 マトロホシ [ma-troH-Sh]
@@ -16796,19 +16774,19 @@
 2411 triiq tumblr </t>
         </is>
       </c>
-      <c r="B778" t="inlineStr">
+      <c r="B777" t="inlineStr">
         <is>
           <t>images/「行くな」_img1.jpg</t>
         </is>
       </c>
-      <c r="C778" t="inlineStr">
+      <c r="C777" t="inlineStr">
         <is>
           <t>ロゴ ,デザイン ,嵐</t>
         </is>
       </c>
     </row>
-    <row r="779">
-      <c r="A779" t="inlineStr">
+    <row r="778">
+      <c r="A778" t="inlineStr">
         <is>
           <t xml:space="preserve">⁦「元気？」⁩شلونَك؟
 シュローナク？ [Sh-loon-ak?]
@@ -16819,19 +16797,19 @@
 2202 出典不明 </t>
         </is>
       </c>
-      <c r="B779" t="inlineStr">
+      <c r="B778" t="inlineStr">
         <is>
           <t>images/⁦「元気？」⁩_img1.jpg</t>
         </is>
       </c>
-      <c r="C779" t="inlineStr">
+      <c r="C778" t="inlineStr">
         <is>
           <t>洒落 ,挨拶</t>
         </is>
       </c>
     </row>
-    <row r="780">
-      <c r="A780" t="inlineStr">
+    <row r="779">
+      <c r="A779" t="inlineStr">
         <is>
           <t xml:space="preserve">「気分が良いぞう」I فيل GOOD
 アイ・フィール・グッド [ai fiyl gud]
@@ -16840,19 +16818,19 @@
 2308 出典不明 </t>
         </is>
       </c>
-      <c r="B780" t="inlineStr">
+      <c r="B779" t="inlineStr">
         <is>
           <t>images/「気分が良いぞう」_img1.jpg</t>
         </is>
       </c>
-      <c r="C780" t="inlineStr">
+      <c r="C779" t="inlineStr">
         <is>
           <t>洒落 ,和訳</t>
         </is>
       </c>
     </row>
-    <row r="781">
-      <c r="A781" t="inlineStr">
+    <row r="780">
+      <c r="A780" t="inlineStr">
         <is>
           <t xml:space="preserve">「レットイットゴー／let it go」
 ليت اِت غو
@@ -16861,19 +16839,19 @@
 2109 出典不明 </t>
         </is>
       </c>
-      <c r="B781" t="inlineStr">
+      <c r="B780" t="inlineStr">
         <is>
           <t>images/「レットイットゴー／let it go_img1.jpg</t>
         </is>
       </c>
-      <c r="C781" t="inlineStr">
+      <c r="C780" t="inlineStr">
         <is>
           <t>折衷 ,アナ雪</t>
         </is>
       </c>
     </row>
-    <row r="782">
-      <c r="A782" t="inlineStr">
+    <row r="781">
+      <c r="A781" t="inlineStr">
         <is>
           <t xml:space="preserve">「ようこそ」اهلا وسهلا
 アハラン・ワサハラン ['ahlan wa-sahlan]
@@ -16881,19 +16859,19 @@
 2106 behance Anwar Al Eissa </t>
         </is>
       </c>
-      <c r="B782" t="inlineStr">
+      <c r="B781" t="inlineStr">
         <is>
           <t>images/「ようこそ」_img1.jpg</t>
         </is>
       </c>
-      <c r="C782" t="inlineStr">
+      <c r="C781" t="inlineStr">
         <is>
           <t>アラビア語</t>
         </is>
       </c>
     </row>
-    <row r="783">
-      <c r="A783" t="inlineStr">
+    <row r="782">
+      <c r="A782" t="inlineStr">
         <is>
           <t xml:space="preserve">「まぁ何というサプライズでしょう」
 يا لها من مفاجأة
@@ -16904,19 +16882,19 @@
 2108 neelwafurat com </t>
         </is>
       </c>
-      <c r="B783" t="inlineStr">
+      <c r="B782" t="inlineStr">
         <is>
           <t>images/「まぁ何というサプライズでしょう」_img1.jpg</t>
         </is>
       </c>
-      <c r="C783" t="inlineStr">
+      <c r="C782" t="inlineStr">
         <is>
           <t>中国語 ,学習</t>
         </is>
       </c>
     </row>
-    <row r="784">
-      <c r="A784" t="inlineStr">
+    <row r="783">
+      <c r="A783" t="inlineStr">
         <is>
           <t xml:space="preserve">「ハックション」اتشوو
 アチュー！ ['aatShuu]
@@ -16924,19 +16902,19 @@
 1811 </t>
         </is>
       </c>
-      <c r="B784" t="inlineStr">
+      <c r="B783" t="inlineStr">
         <is>
           <t>images/「ハックション」_img1.jpg</t>
         </is>
       </c>
-      <c r="C784" t="inlineStr">
+      <c r="C783" t="inlineStr">
         <is>
           <t>あらびあや</t>
         </is>
       </c>
     </row>
-    <row r="785">
-      <c r="A785" t="inlineStr">
+    <row r="784">
+      <c r="A784" t="inlineStr">
         <is>
           <t xml:space="preserve">「スブハーナッラー」「アルハムドゥリッラー」「アッラーアクバル」
 سبحان الله
@@ -16947,19 +16925,19 @@
 2308 dribbble com </t>
         </is>
       </c>
-      <c r="B785" t="inlineStr">
+      <c r="B784" t="inlineStr">
         <is>
           <t>images/「スブハーナッラー」「アルハムドゥリッ_img1.jpg</t>
         </is>
       </c>
-      <c r="C785" t="inlineStr">
+      <c r="C784" t="inlineStr">
         <is>
           <t>四角 ,コンパクト</t>
         </is>
       </c>
     </row>
-    <row r="786">
-      <c r="A786" t="inlineStr">
+    <row r="785">
+      <c r="A785" t="inlineStr">
         <is>
           <t xml:space="preserve">「すごく美味しい！」لذيذ جدًا
 ラズィーズ・ジッダン [laDhiiDh jiddan]
@@ -16968,19 +16946,19 @@
 2109 goodreads com </t>
         </is>
       </c>
-      <c r="B786" t="inlineStr">
+      <c r="B785" t="inlineStr">
         <is>
           <t>images/「すごく美味しい！」_img1.jpg</t>
         </is>
       </c>
-      <c r="C786" t="inlineStr">
+      <c r="C785" t="inlineStr">
         <is>
           <t>フレーズ ,感想</t>
         </is>
       </c>
     </row>
-    <row r="787">
-      <c r="A787" t="inlineStr">
+    <row r="786">
+      <c r="A786" t="inlineStr">
         <is>
           <t xml:space="preserve">「しとしと、雨」تك تك يا مطر
 ティクティク [tik tik yaa ma_tar]
@@ -16989,19 +16967,19 @@
 2308 出典不明 </t>
         </is>
       </c>
-      <c r="B787" t="inlineStr">
+      <c r="B786" t="inlineStr">
         <is>
           <t>images/「しとしと、雨」_img1.jpg</t>
         </is>
       </c>
-      <c r="C787" t="inlineStr">
+      <c r="C786" t="inlineStr">
         <is>
           <t>天気 ,梅雨</t>
         </is>
       </c>
     </row>
-    <row r="788">
-      <c r="A788" t="inlineStr">
+    <row r="787">
+      <c r="A787" t="inlineStr">
         <is>
           <t xml:space="preserve">「さかさま」رأساً على عقب
 ラッアサン・アラー・アケブ [ra'san *alaa *aqib]
@@ -17009,19 +16987,19 @@
 2109 出典不明 </t>
         </is>
       </c>
-      <c r="B788" t="inlineStr">
+      <c r="B787" t="inlineStr">
         <is>
           <t>images/「さかさま」_img1.jpg</t>
         </is>
       </c>
-      <c r="C788" t="inlineStr">
+      <c r="C787" t="inlineStr">
         <is>
           <t>壁 ,上下</t>
         </is>
       </c>
     </row>
-    <row r="789">
-      <c r="A789" t="inlineStr">
+    <row r="788">
+      <c r="A788" t="inlineStr">
         <is>
           <t xml:space="preserve">「エジプトよどこへ行った」
 فينك يا مصر؟
@@ -17031,19 +17009,19 @@
 1809 shehabfawzy1.tumblr </t>
         </is>
       </c>
-      <c r="B789" t="inlineStr">
+      <c r="B788" t="inlineStr">
         <is>
           <t>images/「エジプトよどこへ行った」_img1.jpg</t>
         </is>
       </c>
-      <c r="C789" t="inlineStr">
+      <c r="C788" t="inlineStr">
         <is>
           <t>ピラミッド ,歴史</t>
         </is>
       </c>
     </row>
-    <row r="790">
-      <c r="A790" t="inlineStr">
+    <row r="789">
+      <c r="A789" t="inlineStr">
         <is>
           <t xml:space="preserve">「ありがとう」شكراً
 シュクラン [Shukran]
@@ -17051,19 +17029,19 @@
 2109 出典不明 </t>
         </is>
       </c>
-      <c r="B790" t="inlineStr">
+      <c r="B789" t="inlineStr">
         <is>
           <t>images/「ありがとう」_img1.jpg</t>
         </is>
       </c>
-      <c r="C790" t="inlineStr">
+      <c r="C789" t="inlineStr">
         <is>
           <t>挨拶 ,文字</t>
         </is>
       </c>
     </row>
-    <row r="791">
-      <c r="A791" t="inlineStr">
+    <row r="790">
+      <c r="A790" t="inlineStr">
         <is>
           <t xml:space="preserve">「昼寝の時間だ」
 إنه وقت القيلولة
@@ -17072,12 +17050,12 @@
 2501 https://x.com/NatGeoMagArab/status/1858049951579910486 </t>
         </is>
       </c>
-      <c r="B791" t="inlineStr">
+      <c r="B790" t="inlineStr">
         <is>
           <t>images/「昼寝の時間だ」_img1.jpg</t>
         </is>
       </c>
-      <c r="C791" t="inlineStr">
+      <c r="C790" t="inlineStr">
         <is>
           <t>手書き語学 ,アラビア語 ,ペンギン</t>
         </is>

--- a/posts.xlsx
+++ b/posts.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C790"/>
+  <dimension ref="A1:C789"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -11922,26 +11922,6 @@
     <row r="548">
       <c r="A548" t="inlineStr">
         <is>
-          <t xml:space="preserve">「この世界で君も何かを持っている。だから立ち上がれ！」
-لَكْ شيءٌ في هَذَا العَالَم… فَقُمْ
-[la-k Shay'un fiy haaDha l-*aalam… fa-qum]
-2511 mjdal7arbi tumblr, Ghassan Kanafani </t>
-        </is>
-      </c>
-      <c r="B548" t="inlineStr">
-        <is>
-          <t>images/「この世界で君も何かを持っている。だか.jpg</t>
-        </is>
-      </c>
-      <c r="C548" t="inlineStr">
-        <is>
-          <t>鼓舞 ,ハンカチ王子</t>
-        </is>
-      </c>
-    </row>
-    <row r="549">
-      <c r="A549" t="inlineStr">
-        <is>
           <t xml:space="preserve">「かぞえてかずをかきましょう」
 عد واكتب العدد
 [*udda wa-ktubi l-*adad]
@@ -11949,19 +11929,19 @@
 2604 facebook Qsre alawani </t>
         </is>
       </c>
-      <c r="B549" t="inlineStr">
+      <c r="B548" t="inlineStr">
         <is>
           <t>images/「かぞえてかずをかきましょう」.JPG</t>
         </is>
       </c>
-      <c r="C549" t="inlineStr">
+      <c r="C548" t="inlineStr">
         <is>
           <t>算数 ,さんすう</t>
         </is>
       </c>
     </row>
-    <row r="550">
-      <c r="A550" t="inlineStr">
+    <row r="549">
+      <c r="A549" t="inlineStr">
         <is>
           <t xml:space="preserve">「いつも人助けしなさい」
 كن عونا للناس دوما
@@ -11971,19 +11951,19 @@
 2109 Muhammad ElMahdy </t>
         </is>
       </c>
-      <c r="B550" t="inlineStr">
+      <c r="B549" t="inlineStr">
         <is>
           <t>images/「いつも人助けしなさい」_img1.jpg</t>
         </is>
       </c>
-      <c r="C550" t="inlineStr">
+      <c r="C549" t="inlineStr">
         <is>
           <t>教訓 ,助っ人</t>
         </is>
       </c>
     </row>
-    <row r="551">
-      <c r="A551" t="inlineStr">
+    <row r="550">
+      <c r="A550" t="inlineStr">
         <is>
           <t xml:space="preserve">「毎年、ノーベル賞が授けられる」
 في كل عام تُمنح جوائز نوبل
@@ -11991,19 +11971,19 @@
 2404 https://twitter.com/SciTalk2U/status/1462482447627661319 </t>
         </is>
       </c>
-      <c r="B551" t="inlineStr">
+      <c r="B550" t="inlineStr">
         <is>
           <t>images/「毎年、ノーベル賞が授けられる」_img1.jpg</t>
         </is>
       </c>
-      <c r="C551" t="inlineStr">
+      <c r="C550" t="inlineStr">
         <is>
           <t>手書き語学 ,アラビア語 ,ノーベル賞</t>
         </is>
       </c>
     </row>
-    <row r="552">
-      <c r="A552" t="inlineStr">
+    <row r="551">
+      <c r="A551" t="inlineStr">
         <is>
           <t xml:space="preserve">「あなたはアラビア語を話しますか」
 هل تتكلم العربية؟
@@ -12013,19 +11993,19 @@
 2109 al3arabiya com </t>
         </is>
       </c>
-      <c r="B552" t="inlineStr">
+      <c r="B551" t="inlineStr">
         <is>
           <t>images/「あなたはアラビア語を話しますか」_img1.jpg</t>
         </is>
       </c>
-      <c r="C552" t="inlineStr">
+      <c r="C551" t="inlineStr">
         <is>
           <t>教科書 ,テキスト</t>
         </is>
       </c>
     </row>
-    <row r="553">
-      <c r="A553" t="inlineStr">
+    <row r="552">
+      <c r="A552" t="inlineStr">
         <is>
           <t xml:space="preserve">「このインコは亜熱帯が起源である」
 يتحدر هذا الباراكيت من المناطق شبه الاستوائية
@@ -12033,19 +12013,19 @@
 2402 https://x.com/NatGeoMagArab/status/1690626751578439680 </t>
         </is>
       </c>
-      <c r="B553" t="inlineStr">
+      <c r="B552" t="inlineStr">
         <is>
           <t>images/「このインコは亜熱帯が起源である」_img1.jpg,images/「このインコは亜熱帯が起源である」_img2.jpg</t>
         </is>
       </c>
-      <c r="C553" t="inlineStr">
+      <c r="C552" t="inlineStr">
         <is>
           <t>手書き語学 ,アラビア語 ,オナガミドリインコ</t>
         </is>
       </c>
     </row>
-    <row r="554">
-      <c r="A554" t="inlineStr">
+    <row r="553">
+      <c r="A553" t="inlineStr">
         <is>
           <t xml:space="preserve">「彼を覚えていますか」
 هل تتذكرونه؟
@@ -12055,19 +12035,19 @@
 2308 http://newsfacetruth.blogspot.com/2017/07/blog-post_11.html </t>
         </is>
       </c>
-      <c r="B554" t="inlineStr">
+      <c r="B553" t="inlineStr">
         <is>
           <t>images/「彼を覚えていますか」_img1.jpg</t>
         </is>
       </c>
-      <c r="C554" t="inlineStr">
+      <c r="C553" t="inlineStr">
         <is>
           <t>グレンダイザー ,UFOロボ</t>
         </is>
       </c>
     </row>
-    <row r="555">
-      <c r="A555" t="inlineStr">
+    <row r="554">
+      <c r="A554" t="inlineStr">
         <is>
           <t xml:space="preserve">「内面が変われば周りが変わる」
 عندما تتغير الأشياء داخلك، تتغير الأشياء من حولك
@@ -12076,19 +12056,19 @@
 2501 Facebook, Cairo Mockingbird </t>
         </is>
       </c>
-      <c r="B555" t="inlineStr">
+      <c r="B554" t="inlineStr">
         <is>
           <t>images/「内面が変われば周りが変わる」_img1.jpg</t>
         </is>
       </c>
-      <c r="C555" t="inlineStr">
+      <c r="C554" t="inlineStr">
         <is>
           <t>ポジティブ</t>
         </is>
       </c>
     </row>
-    <row r="556">
-      <c r="A556" t="inlineStr">
+    <row r="555">
+      <c r="A555" t="inlineStr">
         <is>
           <t xml:space="preserve">「天才になるには？」
 كيف تصبح عبقريا؟
@@ -12097,19 +12077,19 @@
 2109 Infographics Samah Faris </t>
         </is>
       </c>
-      <c r="B556" t="inlineStr">
+      <c r="B555" t="inlineStr">
         <is>
           <t>images/「天才になるには？」_img1.jpg</t>
         </is>
       </c>
-      <c r="C556" t="inlineStr">
+      <c r="C555" t="inlineStr">
         <is>
           <t>秘訣 ,コツ</t>
         </is>
       </c>
     </row>
-    <row r="557">
-      <c r="A557" t="inlineStr">
+    <row r="556">
+      <c r="A556" t="inlineStr">
         <is>
           <t xml:space="preserve">「彼らと友情を交わすよハム太郎」
 وبالإخاء يبادلهم هامتارو
@@ -12119,19 +12099,19 @@
 2109 </t>
         </is>
       </c>
-      <c r="B557" t="inlineStr">
+      <c r="B556" t="inlineStr">
         <is>
           <t>images/「彼らと友情を交わすよハム太郎」_img1.jpg</t>
         </is>
       </c>
-      <c r="C557" t="inlineStr">
+      <c r="C556" t="inlineStr">
         <is>
           <t>アニメ ,ハム太郎</t>
         </is>
       </c>
     </row>
-    <row r="558">
-      <c r="A558" t="inlineStr">
+    <row r="557">
+      <c r="A557" t="inlineStr">
         <is>
           <t xml:space="preserve">「誰がニワトリを助ける？」
 من يساعد الدّجاجة؟
@@ -12141,19 +12121,19 @@
 2109 alnqsh com </t>
         </is>
       </c>
-      <c r="B558" t="inlineStr">
+      <c r="B557" t="inlineStr">
         <is>
           <t>images/「誰がニワトリを助ける？」_img1.jpg</t>
         </is>
       </c>
-      <c r="C558" t="inlineStr">
+      <c r="C557" t="inlineStr">
         <is>
           <t>絵本 ,チキン</t>
         </is>
       </c>
     </row>
-    <row r="559">
-      <c r="A559" t="inlineStr">
+    <row r="558">
+      <c r="A558" t="inlineStr">
         <is>
           <t xml:space="preserve">「心臓病を避けるには？」
 كيف تتجنب أمراض القلب؟
@@ -12163,37 +12143,37 @@
 2608 lanamedical_sa </t>
         </is>
       </c>
+      <c r="B558" t="inlineStr">
+        <is>
+          <t>images/「心臓病を避けるには？」.jpg</t>
+        </is>
+      </c>
+      <c r="C558" t="inlineStr">
+        <is>
+          <t>生活習慣病 ,心臓</t>
+        </is>
+      </c>
+    </row>
+    <row r="559">
+      <c r="A559" t="inlineStr">
+        <is>
+          <t xml:space="preserve">「どうやらこの好奇心旺盛なペンギンは…」
+2308 https://twitter.com/NatGeoMagArab/status/1591460860207443968 </t>
+        </is>
+      </c>
       <c r="B559" t="inlineStr">
         <is>
-          <t>images/「心臓病を避けるには？」.jpg</t>
+          <t>images/「どうやらこの好奇心旺盛なペンギンは…_img1.jpg,images/ 「どうやらこの好奇心旺盛なペンギンは…_img2.jpg</t>
         </is>
       </c>
       <c r="C559" t="inlineStr">
         <is>
-          <t>生活習慣病 ,心臓</t>
+          <t>手書き語学 ,アラビア語 ,オウサマペンギン</t>
         </is>
       </c>
     </row>
     <row r="560">
       <c r="A560" t="inlineStr">
-        <is>
-          <t xml:space="preserve">「どうやらこの好奇心旺盛なペンギンは…」
-2308 https://twitter.com/NatGeoMagArab/status/1591460860207443968 </t>
-        </is>
-      </c>
-      <c r="B560" t="inlineStr">
-        <is>
-          <t>images/「どうやらこの好奇心旺盛なペンギンは…_img1.jpg,images/ 「どうやらこの好奇心旺盛なペンギンは…_img2.jpg</t>
-        </is>
-      </c>
-      <c r="C560" t="inlineStr">
-        <is>
-          <t>手書き語学 ,アラビア語 ,オウサマペンギン</t>
-        </is>
-      </c>
-    </row>
-    <row r="561">
-      <c r="A561" t="inlineStr">
         <is>
           <t xml:space="preserve">「ひとを幸せにするには？」
 كيف تسعد غيرك؟
@@ -12203,19 +12183,19 @@
 2308 Gwid3 </t>
         </is>
       </c>
-      <c r="B561" t="inlineStr">
+      <c r="B560" t="inlineStr">
         <is>
           <t>images/「ひとを幸せにするには？」_img1.jpg</t>
         </is>
       </c>
-      <c r="C561" t="inlineStr">
+      <c r="C560" t="inlineStr">
         <is>
           <t>思いやり ,心</t>
         </is>
       </c>
     </row>
-    <row r="562">
-      <c r="A562" t="inlineStr">
+    <row r="561">
+      <c r="A561" t="inlineStr">
         <is>
           <t xml:space="preserve">「ラマダン月に口臭をおさえる方法は？」
 كيف تتجنب رائحة الفم في رمضان
@@ -12224,19 +12204,19 @@
 2109 AlArabiya </t>
         </is>
       </c>
-      <c r="B562" t="inlineStr">
+      <c r="B561" t="inlineStr">
         <is>
           <t>images/「ラマダン月に口臭をおさえる方法は？」_img1.jpg</t>
         </is>
       </c>
-      <c r="C562" t="inlineStr">
+      <c r="C561" t="inlineStr">
         <is>
           <t>イスラム教 ,ブレスケア</t>
         </is>
       </c>
     </row>
-    <row r="563">
-      <c r="A563" t="inlineStr">
+    <row r="562">
+      <c r="A562" t="inlineStr">
         <is>
           <t xml:space="preserve">「ヨユウなきユウヨ」
 يمهل ولا يهمل
@@ -12246,19 +12226,19 @@
 2512 instagram com/p/CK4CLqeJ3dy/ </t>
         </is>
       </c>
-      <c r="B563" t="inlineStr">
+      <c r="B562" t="inlineStr">
         <is>
           <t>images/「ヨユウなきユウヨ」_img1.jpg</t>
         </is>
       </c>
-      <c r="C563" t="inlineStr">
+      <c r="C562" t="inlineStr">
         <is>
           <t>時計 ,からくり</t>
         </is>
       </c>
     </row>
-    <row r="564">
-      <c r="A564" t="inlineStr">
+    <row r="563">
+      <c r="A563" t="inlineStr">
         <is>
           <t xml:space="preserve">「どうして？　動物は絶滅する」
 لماذا؟ تنقرض الحيوانات
@@ -12268,19 +12248,19 @@
 2308 goodreads com </t>
         </is>
       </c>
-      <c r="B564" t="inlineStr">
+      <c r="B563" t="inlineStr">
         <is>
           <t>images/「どうして？　動物は絶滅する」_img1.jpg</t>
         </is>
       </c>
-      <c r="C564" t="inlineStr">
+      <c r="C563" t="inlineStr">
         <is>
           <t>動物 ,子供用</t>
         </is>
       </c>
     </row>
-    <row r="565">
-      <c r="A565" t="inlineStr">
+    <row r="564">
+      <c r="A564" t="inlineStr">
         <is>
           <t xml:space="preserve">「私たちは異なる。だから調和する」
 نختلف.. لنأتلف
@@ -12290,19 +12270,19 @@
 2103 Nawal Saed </t>
         </is>
       </c>
-      <c r="B565" t="inlineStr">
+      <c r="B564" t="inlineStr">
         <is>
           <t>images/「私たちは異なる。だから調和する」_img1.jpg</t>
         </is>
       </c>
-      <c r="C565" t="inlineStr">
+      <c r="C564" t="inlineStr">
         <is>
           <t>異符号 ,ハーモニー</t>
         </is>
       </c>
     </row>
-    <row r="566">
-      <c r="A566" t="inlineStr">
+    <row r="565">
+      <c r="A565" t="inlineStr">
         <is>
           <t xml:space="preserve">「私の肺には蝶々が住んでいて、呼吸の度に羽ばたく」
 تسكن رئتيّ فراشة ترفرف كلما أتنفس
@@ -12311,19 +12291,19 @@
 2109 出典不明 </t>
         </is>
       </c>
-      <c r="B566" t="inlineStr">
+      <c r="B565" t="inlineStr">
         <is>
           <t>images/「私の肺には蝶々が住んでいて、呼吸の度_img1.jpg</t>
         </is>
       </c>
-      <c r="C566" t="inlineStr">
+      <c r="C565" t="inlineStr">
         <is>
           <t>人体 ,昆虫</t>
         </is>
       </c>
     </row>
-    <row r="567">
-      <c r="A567" t="inlineStr">
+    <row r="566">
+      <c r="A566" t="inlineStr">
         <is>
           <t xml:space="preserve">「安らぎを感じますか？」
 هل تستشعر السكينة؟
@@ -12332,19 +12312,19 @@
 2404 https://twitter.com/NatGeoMagArab/status/1541421154950209536 </t>
         </is>
       </c>
-      <c r="B567" t="inlineStr">
+      <c r="B566" t="inlineStr">
         <is>
           <t>images/「安らぎを感じますか？」_img1.jpg</t>
         </is>
       </c>
-      <c r="C567" t="inlineStr">
+      <c r="C566" t="inlineStr">
         <is>
           <t>手書き語学 ,アラビア語 ,エイ</t>
         </is>
       </c>
     </row>
-    <row r="568">
-      <c r="A568" t="inlineStr">
+    <row r="567">
+      <c r="A567" t="inlineStr">
         <is>
           <t xml:space="preserve">「たとえあなたの使うブラウザがChromeだろうとSafariだろうと」
 سواء كنت تستخدم متصفح كروم أو سفاري
@@ -12352,19 +12332,19 @@
 2308 https://twitter.com/ShaayTech/status/1536235333972635649 </t>
         </is>
       </c>
-      <c r="B568" t="inlineStr">
+      <c r="B567" t="inlineStr">
         <is>
           <t>images/「たとえあなたの使うブラウザがChro_img1.jpg</t>
         </is>
       </c>
-      <c r="C568" t="inlineStr">
+      <c r="C567" t="inlineStr">
         <is>
           <t xml:space="preserve">手書き語学 ,アラビア語 ,iPhone </t>
         </is>
       </c>
     </row>
-    <row r="569">
-      <c r="A569" t="inlineStr">
+    <row r="568">
+      <c r="A568" t="inlineStr">
         <is>
           <t xml:space="preserve">「このミドリモリヤツガシラは気づいて欲しい」
 يحرص "هدهد الخشب الأخضر" هذا على أن يدرك
@@ -12373,19 +12353,19 @@
 2308 https://twitter.com/NatGeoMagArab/status/1531161022928539648 </t>
         </is>
       </c>
-      <c r="B569" t="inlineStr">
+      <c r="B568" t="inlineStr">
         <is>
           <t>images/「このミドリモリヤツガシラは気づいて欲_img1.jpg</t>
         </is>
       </c>
-      <c r="C569" t="inlineStr">
+      <c r="C568" t="inlineStr">
         <is>
           <t xml:space="preserve">手書き語学 ,アラビア語 ,鳥 </t>
         </is>
       </c>
     </row>
-    <row r="570">
-      <c r="A570" t="inlineStr">
+    <row r="569">
+      <c r="A569" t="inlineStr">
         <is>
           <t xml:space="preserve">「あなたの怖いものは何ですか」
 ماهي مخاوفك؟
@@ -12397,15 +12377,15 @@
 2308 1112kok </t>
         </is>
       </c>
-      <c r="B570" t="inlineStr">
+      <c r="B569" t="inlineStr">
         <is>
           <t>images/「あなたの怖いものは何ですか」_img1.jpg</t>
         </is>
       </c>
-      <c r="C570" t="inlineStr"/>
-    </row>
-    <row r="571">
-      <c r="A571" t="inlineStr">
+      <c r="C569" t="inlineStr"/>
+    </row>
+    <row r="570">
+      <c r="A570" t="inlineStr">
         <is>
           <t xml:space="preserve">「美しい時は作るもの。待つものではない」
 اصنع اللحظات الجميلة. لا تنتظرها
@@ -12414,19 +12394,19 @@
 2308 abojamal.tumblr com </t>
         </is>
       </c>
-      <c r="B571" t="inlineStr">
+      <c r="B570" t="inlineStr">
         <is>
           <t>images/「美しい時は作るもの。待つものではない_img1.jpg</t>
         </is>
       </c>
-      <c r="C571" t="inlineStr">
+      <c r="C570" t="inlineStr">
         <is>
           <t>おうち時間</t>
         </is>
       </c>
     </row>
-    <row r="572">
-      <c r="A572" t="inlineStr">
+    <row r="571">
+      <c r="A571" t="inlineStr">
         <is>
           <t xml:space="preserve">「大切な時間を大切じゃないことに使わないこと」
 لا تضيع الوقت المهم في شيء غير مهم
@@ -12435,19 +12415,19 @@
 2308 Anwar_122_ </t>
         </is>
       </c>
-      <c r="B572" t="inlineStr">
+      <c r="B571" t="inlineStr">
         <is>
           <t>images/「大切な時間を大切じゃないことに使わな_img1.jpg</t>
         </is>
       </c>
-      <c r="C572" t="inlineStr">
+      <c r="C571" t="inlineStr">
         <is>
           <t>時間 ,貴重</t>
         </is>
       </c>
     </row>
-    <row r="573">
-      <c r="A573" t="inlineStr">
+    <row r="572">
+      <c r="A572" t="inlineStr">
         <is>
           <t xml:space="preserve">「このイノセントな目に騙されるな…」
 لا تنخدع بهذه العيون البريئة
@@ -12457,19 +12437,19 @@
 2201 https://twitter.com/NatGeoMagArab/status/1475715760202797056 </t>
         </is>
       </c>
-      <c r="B573" t="inlineStr">
+      <c r="B572" t="inlineStr">
         <is>
           <t>images/「このイノセントな目に騙されるな…」.png</t>
         </is>
       </c>
-      <c r="C573" t="inlineStr">
+      <c r="C572" t="inlineStr">
         <is>
           <t>がうがう ,カワイイ</t>
         </is>
       </c>
     </row>
-    <row r="574">
-      <c r="A574" t="inlineStr">
+    <row r="573">
+      <c r="A573" t="inlineStr">
         <is>
           <t xml:space="preserve">⁦「カメラを止めろ！」⁩
 أوقفوا التّصوير
@@ -12479,19 +12459,19 @@
 2509 alsalwabooks com </t>
         </is>
       </c>
-      <c r="B574" t="inlineStr">
+      <c r="B573" t="inlineStr">
         <is>
           <t>images/⁦「カメラを止めろ！」⁩_img1.jpg</t>
         </is>
       </c>
-      <c r="C574" t="inlineStr">
+      <c r="C573" t="inlineStr">
         <is>
           <t>絵本 ,撮影</t>
         </is>
       </c>
     </row>
-    <row r="575">
-      <c r="A575" t="inlineStr">
+    <row r="574">
+      <c r="A574" t="inlineStr">
         <is>
           <t xml:space="preserve">「話す前に考えなさい」
 فكر قبل ان تتكلم
@@ -12501,19 +12481,19 @@
 2308 Islamuna YouTube </t>
         </is>
       </c>
-      <c r="B575" t="inlineStr">
+      <c r="B574" t="inlineStr">
         <is>
           <t>images/「話す前に考えなさい」_img1.jpg</t>
         </is>
       </c>
-      <c r="C575" t="inlineStr">
+      <c r="C574" t="inlineStr">
         <is>
           <t>失言 ,発言</t>
         </is>
       </c>
     </row>
-    <row r="576">
-      <c r="A576" t="inlineStr">
+    <row r="575">
+      <c r="A575" t="inlineStr">
         <is>
           <t xml:space="preserve">「ツイッターでフォローして下さい」
 تابعونا على تويتر
@@ -12523,19 +12503,19 @@
 2109 出典不明 </t>
         </is>
       </c>
-      <c r="B576" t="inlineStr">
+      <c r="B575" t="inlineStr">
         <is>
           <t>images/「ツイッターでフォローして下さい」_img1.jpg</t>
         </is>
       </c>
-      <c r="C576" t="inlineStr">
+      <c r="C575" t="inlineStr">
         <is>
           <t>FollowUs ,バナー</t>
         </is>
       </c>
     </row>
-    <row r="577">
-      <c r="A577" t="inlineStr">
+    <row r="576">
+      <c r="A576" t="inlineStr">
         <is>
           <t xml:space="preserve">「敵を倒せ」دمّر العدو
 ダンミリ_ルアドゥーウ [dammiri l-*aduuw]
@@ -12544,19 +12524,19 @@
 2308 apkpure com </t>
         </is>
       </c>
-      <c r="B577" t="inlineStr">
+      <c r="B576" t="inlineStr">
         <is>
           <t>images/「敵を倒せ」_img1.jpg</t>
         </is>
       </c>
-      <c r="C577" t="inlineStr">
+      <c r="C576" t="inlineStr">
         <is>
           <t>ゲーム ,パンダ</t>
         </is>
       </c>
     </row>
-    <row r="578">
-      <c r="A578" t="inlineStr">
+    <row r="577">
+      <c r="A577" t="inlineStr">
         <is>
           <t xml:space="preserve">「咲け。蒔かれたらどこであろうと」
 أزهر أيْنمَا زرعت
@@ -12565,19 +12545,19 @@
 2407 Ahmed Madyan </t>
         </is>
       </c>
-      <c r="B578" t="inlineStr">
+      <c r="B577" t="inlineStr">
         <is>
           <t>images/「咲け。蒔かれたらどこであろうと」_img1.jpg</t>
         </is>
       </c>
-      <c r="C578" t="inlineStr">
+      <c r="C577" t="inlineStr">
         <is>
           <t>環境のせいにしない ,花</t>
         </is>
       </c>
     </row>
-    <row r="579">
-      <c r="A579" t="inlineStr">
+    <row r="578">
+      <c r="A578" t="inlineStr">
         <is>
           <t xml:space="preserve">「頭を働かせろ」شغل مخك
 シャッギル・ムッハク [Sha^Ghil mu^Kha-k]
@@ -12586,19 +12566,19 @@
 2103 facebook elpage </t>
         </is>
       </c>
-      <c r="B579" t="inlineStr">
+      <c r="B578" t="inlineStr">
         <is>
           <t>images/「頭を働かせろ」_img1.jpg</t>
         </is>
       </c>
-      <c r="C579" t="inlineStr">
+      <c r="C578" t="inlineStr">
         <is>
           <t>電源 ,頭脳</t>
         </is>
       </c>
     </row>
-    <row r="580">
-      <c r="A580" t="inlineStr">
+    <row r="579">
+      <c r="A579" t="inlineStr">
         <is>
           <t xml:space="preserve">「傷跡は星にかえなさい」
 حوّل نُدوبكَ إلى نُجومْ
@@ -12608,19 +12588,19 @@
 2107 saramj1992 Instagram </t>
         </is>
       </c>
-      <c r="B580" t="inlineStr">
+      <c r="B579" t="inlineStr">
         <is>
           <t>images/「傷跡は星にかえなさい」_img1.jpg</t>
         </is>
       </c>
-      <c r="C580" t="inlineStr">
+      <c r="C579" t="inlineStr">
         <is>
           <t>勲章 ,証</t>
         </is>
       </c>
     </row>
-    <row r="581">
-      <c r="A581" t="inlineStr">
+    <row r="580">
+      <c r="A580" t="inlineStr">
         <is>
           <t xml:space="preserve">「誰かを幸福にしなさい」
 أسْعِد أحدهم
@@ -12630,19 +12610,19 @@
 1810 in4sser.tumblr </t>
         </is>
       </c>
-      <c r="B581" t="inlineStr">
+      <c r="B580" t="inlineStr">
         <is>
           <t>images/「誰かを幸福にしなさい」_img1.jpg</t>
         </is>
       </c>
-      <c r="C581" t="inlineStr">
+      <c r="C580" t="inlineStr">
         <is>
           <t>人生 ,happy</t>
         </is>
       </c>
     </row>
-    <row r="582">
-      <c r="A582" t="inlineStr">
+    <row r="581">
+      <c r="A581" t="inlineStr">
         <is>
           <t xml:space="preserve">「見よ」أبْصِرْ
 アブスィル ['ab_sir]
@@ -12651,19 +12631,19 @@
 1811 Ruh Al-Alam, via Behance </t>
         </is>
       </c>
-      <c r="B582" t="inlineStr">
+      <c r="B581" t="inlineStr">
         <is>
           <t>images/「見よ」_img1.jpg</t>
         </is>
       </c>
-      <c r="C582" t="inlineStr">
+      <c r="C581" t="inlineStr">
         <is>
           <t>目 ,瞳</t>
         </is>
       </c>
     </row>
-    <row r="583">
-      <c r="A583" t="inlineStr">
+    <row r="582">
+      <c r="A582" t="inlineStr">
         <is>
           <t xml:space="preserve">「言葉は口から出す前に味わいなさい」
 ‪تذوق كلماتك قبل أن تنطقها‬
@@ -12673,19 +12653,19 @@
 2109 Reham-des </t>
         </is>
       </c>
-      <c r="B583" t="inlineStr">
+      <c r="B582" t="inlineStr">
         <is>
           <t>images/「言葉は口から出す前に味わいなさい」_img1.jpg</t>
         </is>
       </c>
-      <c r="C583" t="inlineStr">
+      <c r="C582" t="inlineStr">
         <is>
           <t>言葉</t>
         </is>
       </c>
     </row>
-    <row r="584">
-      <c r="A584" t="inlineStr">
+    <row r="583">
+      <c r="A583" t="inlineStr">
         <is>
           <t xml:space="preserve">「テレビを観るのをやめて下さい」
 توقفي عن مشاهدة التلفاز
@@ -12695,19 +12675,19 @@
 1809 </t>
         </is>
       </c>
-      <c r="B584" t="inlineStr">
+      <c r="B583" t="inlineStr">
         <is>
           <t>images/「テレビを観るのをやめて下さい」_img1.jpg</t>
         </is>
       </c>
-      <c r="C584" t="inlineStr">
+      <c r="C583" t="inlineStr">
         <is>
           <t>あらびあや</t>
         </is>
       </c>
     </row>
-    <row r="585">
-      <c r="A585" t="inlineStr">
+    <row r="584">
+      <c r="A584" t="inlineStr">
         <is>
           <t xml:space="preserve">「言わぬが花」
 انْطِقْ جَمَالاً أو تجَمَّلْ بالسّكُوت
@@ -12717,19 +12697,19 @@
 2411 Ahmed Madyan </t>
         </is>
       </c>
-      <c r="B585" t="inlineStr">
+      <c r="B584" t="inlineStr">
         <is>
           <t>images/「言わぬが花」_img1.jpg</t>
         </is>
       </c>
-      <c r="C585" t="inlineStr">
+      <c r="C584" t="inlineStr">
         <is>
           <t>ことわざ ,デザイン</t>
         </is>
       </c>
     </row>
-    <row r="586">
-      <c r="A586" t="inlineStr">
+    <row r="585">
+      <c r="A585" t="inlineStr">
         <is>
           <t xml:space="preserve">「たくさん考えて、少し話すこと」
 فكّر كثيرا. تكلم قليلا
@@ -12739,19 +12719,19 @@
 2105 In49r </t>
         </is>
       </c>
-      <c r="B586" t="inlineStr">
+      <c r="B585" t="inlineStr">
         <is>
           <t>images/「たくさん考えて、少し話すこと」_img1.jpg</t>
         </is>
       </c>
-      <c r="C586" t="inlineStr">
+      <c r="C585" t="inlineStr">
         <is>
           <t>思慮 ,会話</t>
         </is>
       </c>
     </row>
-    <row r="587">
-      <c r="A587" t="inlineStr">
+    <row r="586">
+      <c r="A586" t="inlineStr">
         <is>
           <t xml:space="preserve">「子供たちよ、いつでも思い出すんだよ」
 تذكروا دوما يا أطفال
@@ -12761,19 +12741,19 @@
 1809 </t>
         </is>
       </c>
-      <c r="B587" t="inlineStr">
+      <c r="B586" t="inlineStr">
         <is>
           <t>images/「子供たちよ、いつでも思い出すんだよ」_img1.jpg</t>
         </is>
       </c>
-      <c r="C587" t="inlineStr">
+      <c r="C586" t="inlineStr">
         <is>
           <t>オープニング ,ハム太郎</t>
         </is>
       </c>
     </row>
-    <row r="588">
-      <c r="A588" t="inlineStr">
+    <row r="587">
+      <c r="A587" t="inlineStr">
         <is>
           <t xml:space="preserve">「分かってから話しなさい」
 تعلَّم ثمَّ تكلَّم
@@ -12783,19 +12763,19 @@
 1903 Hashem Al Shareef, Pinterest </t>
         </is>
       </c>
-      <c r="B588" t="inlineStr">
+      <c r="B587" t="inlineStr">
         <is>
           <t>images/「分かってから話しなさい」_img1.jpg</t>
         </is>
       </c>
-      <c r="C588" t="inlineStr">
+      <c r="C587" t="inlineStr">
         <is>
           <t>教訓 ,トーク</t>
         </is>
       </c>
     </row>
-    <row r="589">
-      <c r="A589" t="inlineStr">
+    <row r="588">
+      <c r="A588" t="inlineStr">
         <is>
           <t xml:space="preserve">「蟻に学べ」تعلم من النملة
 タアッラム・ミナ_ンナムラ [ta*allam mina ^namla]
@@ -12804,19 +12784,19 @@
 2308 fatakat com </t>
         </is>
       </c>
-      <c r="B589" t="inlineStr">
+      <c r="B588" t="inlineStr">
         <is>
           <t>images/「蟻に学べ」_img1.jpg</t>
         </is>
       </c>
-      <c r="C589" t="inlineStr">
+      <c r="C588" t="inlineStr">
         <is>
           <t>教訓 ,問題解決</t>
         </is>
       </c>
     </row>
-    <row r="590">
-      <c r="A590" t="inlineStr">
+    <row r="589">
+      <c r="A589" t="inlineStr">
         <is>
           <t xml:space="preserve">「自分と仲直りしよう、一杯の珈琲で！」
 تصالح مع نفسك بكوب قهوة
@@ -12826,19 +12806,19 @@
 2308 asm95_ </t>
         </is>
       </c>
-      <c r="B590" t="inlineStr">
+      <c r="B589" t="inlineStr">
         <is>
           <t>images/「自分と仲直りしよう、一杯の珈琲で！」_img1.jpg</t>
         </is>
       </c>
-      <c r="C590" t="inlineStr">
+      <c r="C589" t="inlineStr">
         <is>
           <t>一服 ,リラックス</t>
         </is>
       </c>
     </row>
-    <row r="591">
-      <c r="A591" t="inlineStr">
+    <row r="590">
+      <c r="A590" t="inlineStr">
         <is>
           <t xml:space="preserve">「気をつけて　ジュード」
 انتبهي يا جود
@@ -12848,19 +12828,19 @@
 2109 سلسلة الحلزونة </t>
         </is>
       </c>
-      <c r="B591" t="inlineStr">
+      <c r="B590" t="inlineStr">
         <is>
           <t>images/「気をつけて　ジュード」_img1.jpg</t>
         </is>
       </c>
-      <c r="C591" t="inlineStr">
+      <c r="C590" t="inlineStr">
         <is>
           <t>絵本 ,わんぱく</t>
         </is>
       </c>
     </row>
-    <row r="592">
-      <c r="A592" t="inlineStr">
+    <row r="591">
+      <c r="A591" t="inlineStr">
         <is>
           <t xml:space="preserve">「coming soon」
 انتظرونا قريبا
@@ -12869,19 +12849,19 @@
 2307 出典不明 </t>
         </is>
       </c>
-      <c r="B592" t="inlineStr">
+      <c r="B591" t="inlineStr">
         <is>
           <t>images/「coming soon」_img1.jpg</t>
         </is>
       </c>
-      <c r="C592" t="inlineStr">
+      <c r="C591" t="inlineStr">
         <is>
           <t>フレーズ ,カミングスーン</t>
         </is>
       </c>
     </row>
-    <row r="593">
-      <c r="A593" t="inlineStr">
+    <row r="592">
+      <c r="A592" t="inlineStr">
         <is>
           <t xml:space="preserve">「自分の胸に聞きなさい。それが全て知っています」
 استمع لقلبك.. إنه يعرف كل شيء
@@ -12890,19 +12870,19 @@
 1811 </t>
         </is>
       </c>
-      <c r="B593" t="inlineStr">
+      <c r="B592" t="inlineStr">
         <is>
           <t>images/「自分の胸に聞きなさい。それが全て知っ_img1.jpg</t>
         </is>
       </c>
-      <c r="C593" t="inlineStr">
+      <c r="C592" t="inlineStr">
         <is>
           <t>あらびあや</t>
         </is>
       </c>
     </row>
-    <row r="594">
-      <c r="A594" t="inlineStr">
+    <row r="593">
+      <c r="A593" t="inlineStr">
         <is>
           <t xml:space="preserve">「笑ってくれ、絶望を癒すのは君の笑みだから」
 ابتسمي فإن دواء اليأس بسمتك
@@ -12911,19 +12891,19 @@
 2308 arab-quotes tumblr </t>
         </is>
       </c>
-      <c r="B594" t="inlineStr">
+      <c r="B593" t="inlineStr">
         <is>
           <t>images/「笑ってくれ、絶望を癒すのは君の笑みだ_img1.jpg</t>
         </is>
       </c>
-      <c r="C594" t="inlineStr">
+      <c r="C593" t="inlineStr">
         <is>
           <t>癒し ,スマイル</t>
         </is>
       </c>
     </row>
-    <row r="595">
-      <c r="A595" t="inlineStr">
+    <row r="594">
+      <c r="A594" t="inlineStr">
         <is>
           <t xml:space="preserve">「自分を頼りなさい。宇宙で最も確かな物が自分だと思って。」
 استند على نفسك وكأنك أكثر الأشياء ثباتًا بهذا الكون
@@ -12931,19 +12911,19 @@
 2308 x_nourh.15 </t>
         </is>
       </c>
-      <c r="B595" t="inlineStr">
+      <c r="B594" t="inlineStr">
         <is>
           <t>images/「自分を頼りなさい。宇宙で最も確かな物_img1.jpg</t>
         </is>
       </c>
-      <c r="C595" t="inlineStr">
+      <c r="C594" t="inlineStr">
         <is>
           <t>自我 ,宇宙</t>
         </is>
       </c>
     </row>
-    <row r="596">
-      <c r="A596" t="inlineStr">
+    <row r="595">
+      <c r="A595" t="inlineStr">
         <is>
           <t xml:space="preserve">「古いデバイスを交換して新品をゲットしよう」
 استبدل جهازك القديم واحصل على واحد جديد
@@ -12952,19 +12932,19 @@
 2406 stc </t>
         </is>
       </c>
-      <c r="B596" t="inlineStr">
+      <c r="B595" t="inlineStr">
         <is>
           <t>images/「古いデバイスを交換して新品をゲットし_img1.jpg</t>
         </is>
       </c>
-      <c r="C596" t="inlineStr">
+      <c r="C595" t="inlineStr">
         <is>
           <t>キャンペーン ,下取り</t>
         </is>
       </c>
     </row>
-    <row r="597">
-      <c r="A597" t="inlineStr">
+    <row r="596">
+      <c r="A596" t="inlineStr">
         <is>
           <t xml:space="preserve">「あなたの声を聞かせてください。私の心を彩ってください」
 هات صوتك، لوّن قلبي
@@ -12973,19 +12953,19 @@
 2105 3a2esha_ Instagram </t>
         </is>
       </c>
-      <c r="B597" t="inlineStr">
+      <c r="B596" t="inlineStr">
         <is>
           <t>images/「あなたの声を聞かせてください。私の心_img1.jpg</t>
         </is>
       </c>
-      <c r="C597" t="inlineStr">
+      <c r="C596" t="inlineStr">
         <is>
           <t>電話 ,肉声</t>
         </is>
       </c>
     </row>
-    <row r="598">
-      <c r="A598" t="inlineStr">
+    <row r="597">
+      <c r="A597" t="inlineStr">
         <is>
           <t xml:space="preserve">「この子カンガルーは抱っこが好き」
 يُحب صغير الكنغر هذا أن يؤخذ في الأحضان
@@ -12993,19 +12973,19 @@
 2308 NatGeoMagArab </t>
         </is>
       </c>
-      <c r="B598" t="inlineStr">
+      <c r="B597" t="inlineStr">
         <is>
           <t>images/「この子カンガルーは抱っこが好き」.png</t>
         </is>
       </c>
-      <c r="C598" t="inlineStr">
+      <c r="C597" t="inlineStr">
         <is>
           <t>カンガルー ,人肌</t>
         </is>
       </c>
     </row>
-    <row r="599">
-      <c r="A599" t="inlineStr">
+    <row r="598">
+      <c r="A598" t="inlineStr">
         <is>
           <t xml:space="preserve">「カタールが好き」أحب قطر
 ウヒッブ・カタル ['u-Hibb qa_tar]
@@ -13014,19 +12994,19 @@
 1810 出典不明 </t>
         </is>
       </c>
-      <c r="B599" t="inlineStr">
+      <c r="B598" t="inlineStr">
         <is>
           <t>images/「カタールが好き」_img1.jpg</t>
         </is>
       </c>
-      <c r="C599" t="inlineStr">
+      <c r="C598" t="inlineStr">
         <is>
           <t>カタール</t>
         </is>
       </c>
     </row>
-    <row r="600">
-      <c r="A600" t="inlineStr">
+    <row r="599">
+      <c r="A599" t="inlineStr">
         <is>
           <t xml:space="preserve">「一緒に読むのが好き」
 أُحبُّ أن نَقْرَأَ مَعاً
@@ -13036,19 +13016,19 @@
 2509 www.neelwafurat com,  id=lbb212750-185765 </t>
         </is>
       </c>
-      <c r="B600" t="inlineStr">
+      <c r="B599" t="inlineStr">
         <is>
           <t>images/「一緒に読むのが好き」_img1.jpg</t>
         </is>
       </c>
-      <c r="C600" t="inlineStr">
+      <c r="C599" t="inlineStr">
         <is>
           <t>好き ,本</t>
         </is>
       </c>
     </row>
-    <row r="601">
-      <c r="A601" t="inlineStr">
+    <row r="600">
+      <c r="A600" t="inlineStr">
         <is>
           <t xml:space="preserve">「病院に行きたくない」
 لا أريد أن أذهب إلى المشفى
@@ -13058,19 +13038,19 @@
 2508 Tony Ross https://education.hachette-antoine.com/ar/component/%D9%84%D8%A7-%D8%A3%D8%B1%D9%8A%D8%AF-%D8%A3%D9%86-%D8%A3%D8%B0%D9%87%D8%A8-%D8%A5%D9%84%D9%89-%D8%A7%D9%84%D9%85%D8%B4%D9%81%D9%89/ </t>
         </is>
       </c>
-      <c r="B601" t="inlineStr">
+      <c r="B600" t="inlineStr">
         <is>
           <t>images/「病院に行きたくない」_img1.jpg</t>
         </is>
       </c>
-      <c r="C601" t="inlineStr">
+      <c r="C600" t="inlineStr">
         <is>
           <t>絵本 ,子供</t>
         </is>
       </c>
     </row>
-    <row r="602">
-      <c r="A602" t="inlineStr">
+    <row r="601">
+      <c r="A601" t="inlineStr">
         <is>
           <t xml:space="preserve">「男性はいくら？」「女性はいくら？」
 كم يساوى الرجل؟ ..وكم تساوى المرأة؟
@@ -13079,19 +13059,19 @@
 2308 Pinterest, Masr Elmahrousa, Farah Noweir </t>
         </is>
       </c>
-      <c r="B602" t="inlineStr">
+      <c r="B601" t="inlineStr">
         <is>
           <t>images/「男性はいくら？」「女性はいくら？」_img1.jpg,images/「男性はいくら？」「女性はいくら？」_img2.jpg</t>
         </is>
       </c>
-      <c r="C602" t="inlineStr">
+      <c r="C601" t="inlineStr">
         <is>
           <t xml:space="preserve">全身コーデ ,相場 </t>
         </is>
       </c>
     </row>
-    <row r="603">
-      <c r="A603" t="inlineStr">
+    <row r="602">
+      <c r="A602" t="inlineStr">
         <is>
           <t xml:space="preserve">「眠りたいです」
 أُريدُ أَن أَنام
@@ -13101,19 +13081,19 @@
 2109 goodreads com </t>
         </is>
       </c>
-      <c r="B603" t="inlineStr">
+      <c r="B602" t="inlineStr">
         <is>
           <t>images/「眠りたいです」_img1.jpg</t>
         </is>
       </c>
-      <c r="C603" t="inlineStr">
+      <c r="C602" t="inlineStr">
         <is>
           <t>絵本</t>
         </is>
       </c>
     </row>
-    <row r="604">
-      <c r="A604" t="inlineStr">
+    <row r="603">
+      <c r="A603" t="inlineStr">
         <is>
           <t xml:space="preserve">「飛びたい！」أُريد أن أطير
 ウリードゥ・アン・アティール ['u-riidu 'an 'a-_tiir]
@@ -13122,19 +13102,19 @@
 2308 出典不明 </t>
         </is>
       </c>
-      <c r="B604" t="inlineStr">
+      <c r="B603" t="inlineStr">
         <is>
           <t>images/「飛びたい！」_img1.jpg</t>
         </is>
       </c>
-      <c r="C604" t="inlineStr">
+      <c r="C603" t="inlineStr">
         <is>
           <t>鳥 ,希望</t>
         </is>
       </c>
     </row>
-    <row r="605">
-      <c r="A605" t="inlineStr">
+    <row r="604">
+      <c r="A604" t="inlineStr">
         <is>
           <t xml:space="preserve">「うちゅうへとびたい」
 أُريدُ أَنْ أَطيرَ إلى الفَضاء
@@ -13143,19 +13123,19 @@
 2308 mybookshelf co </t>
         </is>
       </c>
-      <c r="B605" t="inlineStr">
+      <c r="B604" t="inlineStr">
         <is>
           <t>images/「うちゅうへとびたい」_img1.jpg</t>
         </is>
       </c>
-      <c r="C605" t="inlineStr">
+      <c r="C604" t="inlineStr">
         <is>
           <t>絵本 ,宇宙</t>
         </is>
       </c>
     </row>
-    <row r="606">
-      <c r="A606" t="inlineStr">
+    <row r="605">
+      <c r="A605" t="inlineStr">
         <is>
           <t xml:space="preserve">「とても愛しています」
 أُحِبّك جِدّاً
@@ -13165,19 +13145,19 @@
 2308 hobe cc </t>
         </is>
       </c>
-      <c r="B606" t="inlineStr">
+      <c r="B605" t="inlineStr">
         <is>
           <t>images/「とても愛しています」_img1.jpg</t>
         </is>
       </c>
-      <c r="C606" t="inlineStr">
+      <c r="C605" t="inlineStr">
         <is>
           <t>恋 ,love</t>
         </is>
       </c>
     </row>
-    <row r="607">
-      <c r="A607" t="inlineStr">
+    <row r="606">
+      <c r="A606" t="inlineStr">
         <is>
           <t xml:space="preserve">「あす日が昇るだろう。私は朝が大好きだ」
 غدا ستشرق الشمس وأحب الصباح كثيرا
@@ -13186,19 +13166,19 @@
 2105 warag-3nb.tumblr com </t>
         </is>
       </c>
-      <c r="B607" t="inlineStr">
+      <c r="B606" t="inlineStr">
         <is>
           <t>images/「あす日が昇るだろう。私は朝が大好きだ_img1.jpg,images/ 「あす日が昇るだろう。私は朝が大好きだ_img2.jpg</t>
         </is>
       </c>
-      <c r="C607" t="inlineStr">
+      <c r="C606" t="inlineStr">
         <is>
           <t>おやすみ ,壁</t>
         </is>
       </c>
     </row>
-    <row r="608">
-      <c r="A608" t="inlineStr">
+    <row r="607">
+      <c r="A607" t="inlineStr">
         <is>
           <t xml:space="preserve">「きみは何をえらぶ？」
 ماذا تختار؟
@@ -13208,19 +13188,19 @@
 2109 embadomjp org </t>
         </is>
       </c>
-      <c r="B608" t="inlineStr">
+      <c r="B607" t="inlineStr">
         <is>
           <t>images/「きみは何をえらぶ？」_img1.jpg</t>
         </is>
       </c>
-      <c r="C608" t="inlineStr">
+      <c r="C607" t="inlineStr">
         <is>
           <t>優柔不断 ,絵本</t>
         </is>
       </c>
     </row>
-    <row r="609">
-      <c r="A609" t="inlineStr">
+    <row r="608">
+      <c r="A608" t="inlineStr">
         <is>
           <t xml:space="preserve">「ちょっと静けさが必要な時もある」
 في بعض الأوقات نحتاج لشوية هدوء
@@ -13230,19 +13210,19 @@
 2308 IN49r </t>
         </is>
       </c>
-      <c r="B609" t="inlineStr">
+      <c r="B608" t="inlineStr">
         <is>
           <t>images/「ちょっと静けさが必要な時もある」_img1.jpg</t>
         </is>
       </c>
-      <c r="C609" t="inlineStr">
+      <c r="C608" t="inlineStr">
         <is>
           <t>ミュート ,精神</t>
         </is>
       </c>
     </row>
-    <row r="610">
-      <c r="A610" t="inlineStr">
+    <row r="609">
+      <c r="A609" t="inlineStr">
         <is>
           <t xml:space="preserve">「逃げるな。全力でぶつかれ」
 لا تهرب اصطدم بكل قوتك
@@ -13252,19 +13232,19 @@
 2308 https://risingvibes.tumblr.com/post/189545775129 </t>
         </is>
       </c>
-      <c r="B610" t="inlineStr">
+      <c r="B609" t="inlineStr">
         <is>
           <t>images/「逃げるな。全力でぶつかれ」_img1.jpg</t>
         </is>
       </c>
-      <c r="C610" t="inlineStr">
+      <c r="C609" t="inlineStr">
         <is>
           <t>応援 ,力</t>
         </is>
       </c>
     </row>
-    <row r="611">
-      <c r="A611" t="inlineStr">
+    <row r="610">
+      <c r="A610" t="inlineStr">
         <is>
           <t xml:space="preserve">「着るのだいすき」
 أُحِبُ أَن أَرتَدِيَ
@@ -13274,19 +13254,19 @@
 2308 https://kitab.firmabikes.ru/epub-_hb_n_rtdy_5187.html </t>
         </is>
       </c>
-      <c r="B611" t="inlineStr">
+      <c r="B610" t="inlineStr">
         <is>
           <t>images/「着るのだいすき」_img1.jpg</t>
         </is>
       </c>
-      <c r="C611" t="inlineStr">
+      <c r="C610" t="inlineStr">
         <is>
           <t xml:space="preserve">絵本 ,ファッション </t>
         </is>
       </c>
     </row>
-    <row r="612">
-      <c r="A612" t="inlineStr">
+    <row r="611">
+      <c r="A611" t="inlineStr">
         <is>
           <t xml:space="preserve">「車のバッテリーが要る！」
 نحتاج بطارية سيارة
@@ -13296,19 +13276,19 @@
 2308 instagram roaa_27 </t>
         </is>
       </c>
-      <c r="B612" t="inlineStr">
+      <c r="B611" t="inlineStr">
         <is>
           <t>images/「車のバッテリーが要る！」_img1.jpg</t>
         </is>
       </c>
-      <c r="C612" t="inlineStr">
+      <c r="C611" t="inlineStr">
         <is>
           <t>スマホ ,充電</t>
         </is>
       </c>
     </row>
-    <row r="613">
-      <c r="A613" t="inlineStr">
+    <row r="612">
+      <c r="A612" t="inlineStr">
         <is>
           <t xml:space="preserve">「今日は幸せでいることにしました」
 اخترت أن أكون سعيدا اليوم
@@ -13318,19 +13298,19 @@
 2109 awaasha tumblr </t>
         </is>
       </c>
-      <c r="B613" t="inlineStr">
+      <c r="B612" t="inlineStr">
         <is>
           <t>images/「今日は幸せでいることにしました」_img1.jpg</t>
         </is>
       </c>
-      <c r="C613" t="inlineStr">
+      <c r="C612" t="inlineStr">
         <is>
           <t>心構え ,happy</t>
         </is>
       </c>
     </row>
-    <row r="614">
-      <c r="A614" t="inlineStr">
+    <row r="613">
+      <c r="A613" t="inlineStr">
         <is>
           <t xml:space="preserve">「理想的なスイカの選び方」
 كيف تختار البطيخة المُثلى؟
@@ -13340,19 +13320,19 @@
 2308 bit ly/octmel </t>
         </is>
       </c>
-      <c r="B614" t="inlineStr">
+      <c r="B613" t="inlineStr">
         <is>
           <t>images/「理想的なスイカの選び方」_img1.jpg</t>
         </is>
       </c>
-      <c r="C614" t="inlineStr">
+      <c r="C613" t="inlineStr">
         <is>
           <t>八百屋 ,西瓜</t>
         </is>
       </c>
     </row>
-    <row r="615">
-      <c r="A615" t="inlineStr">
+    <row r="614">
+      <c r="A614" t="inlineStr">
         <is>
           <t xml:space="preserve">「お問い合わせください」
 اتصل بنا
@@ -13362,19 +13342,19 @@
 2308 mtawir.blogspot com </t>
         </is>
       </c>
-      <c r="B615" t="inlineStr">
+      <c r="B614" t="inlineStr">
         <is>
           <t>images/「お問い合わせください」_img1.jpg</t>
         </is>
       </c>
-      <c r="C615" t="inlineStr">
+      <c r="C614" t="inlineStr">
         <is>
           <t>広告 ,電話</t>
         </is>
       </c>
     </row>
-    <row r="616">
-      <c r="A616" t="inlineStr">
+    <row r="615">
+      <c r="A615" t="inlineStr">
         <is>
           <t xml:space="preserve">「両方の動物が海岸の火山岩の亀裂の中に定住している」
 يحتل كلا الحيوانين شقوقًا في صخور الساحل البركانية
@@ -13382,19 +13362,19 @@
 2507 https://x.com/NatGeoMagArab/status/1925167200056521151 </t>
         </is>
       </c>
-      <c r="B616" t="inlineStr">
+      <c r="B615" t="inlineStr">
         <is>
           <t>images/「両方の動物が海岸の火山岩の亀裂の中に_img1.jpg,images/「両方の動物が海岸の火山岩の亀裂の中に_img2.jpg</t>
         </is>
       </c>
-      <c r="C616" t="inlineStr">
+      <c r="C615" t="inlineStr">
         <is>
           <t>手書き語学 ,アラビア語 ,イグアナ</t>
         </is>
       </c>
     </row>
-    <row r="617">
-      <c r="A617" t="inlineStr">
+    <row r="616">
+      <c r="A616" t="inlineStr">
         <is>
           <t xml:space="preserve">「命じられたように正しき道を辿れ」
 واستقم كما أمرت
@@ -13404,19 +13384,19 @@
 2308 Ahmed Madyan </t>
         </is>
       </c>
-      <c r="B617" t="inlineStr">
+      <c r="B616" t="inlineStr">
         <is>
           <t>images/「命じられたように正しき道を辿れ」_img1.jpg</t>
         </is>
       </c>
-      <c r="C617" t="inlineStr">
+      <c r="C616" t="inlineStr">
         <is>
           <t>書道 ,アート</t>
         </is>
       </c>
     </row>
-    <row r="618">
-      <c r="A618" t="inlineStr">
+    <row r="617">
+      <c r="A617" t="inlineStr">
         <is>
           <t xml:space="preserve">「くつろぎなさい」استكن
 イスタキンナ [istakinna]
@@ -13424,19 +13404,19 @@
 2603 m2ff tumblr com </t>
         </is>
       </c>
-      <c r="B618" t="inlineStr">
+      <c r="B617" t="inlineStr">
         <is>
           <t>images/「くつろぎなさい」.jpeg</t>
         </is>
       </c>
-      <c r="C618" t="inlineStr">
+      <c r="C617" t="inlineStr">
         <is>
           <t>relax ,コーヒー</t>
         </is>
       </c>
     </row>
-    <row r="619">
-      <c r="A619" t="inlineStr">
+    <row r="618">
+      <c r="A618" t="inlineStr">
         <is>
           <t xml:space="preserve">「彼は応えるだろう」سيستجيب 
 サヤスタジーブ [sa-ya-stajiibu]
@@ -13445,19 +13425,19 @@
 1811 kareem mrghani </t>
         </is>
       </c>
-      <c r="B619" t="inlineStr">
+      <c r="B618" t="inlineStr">
         <is>
           <t>images/「彼は応えるだろう」_img1.jpg</t>
         </is>
       </c>
-      <c r="C619" t="inlineStr">
+      <c r="C618" t="inlineStr">
         <is>
           <t>縦書き ,現代アート</t>
         </is>
       </c>
     </row>
-    <row r="620">
-      <c r="A620" t="inlineStr">
+    <row r="619">
+      <c r="A619" t="inlineStr">
         <is>
           <t xml:space="preserve">「アラビア語が好き」
 أنا أُحبّ لُغتي
@@ -13467,19 +13447,19 @@
 2308 出典不明 </t>
         </is>
       </c>
-      <c r="B620" t="inlineStr">
+      <c r="B619" t="inlineStr">
         <is>
           <t>images/「アラビア語が好き」_img1.jpg</t>
         </is>
       </c>
-      <c r="C620" t="inlineStr">
+      <c r="C619" t="inlineStr">
         <is>
           <t>和訳 ,こども</t>
         </is>
       </c>
     </row>
-    <row r="621">
-      <c r="A621" t="inlineStr">
+    <row r="620">
+      <c r="A620" t="inlineStr">
         <is>
           <t xml:space="preserve">「私はサッカーが好きです」
 أنا أُحِبُّ كُرةَ القَدَم
@@ -13489,19 +13469,19 @@
 2109 Arabic With Nadia </t>
         </is>
       </c>
-      <c r="B621" t="inlineStr">
+      <c r="B620" t="inlineStr">
         <is>
           <t>images/「私はサッカーが好きです」_img1.jpg</t>
         </is>
       </c>
-      <c r="C621" t="inlineStr">
+      <c r="C620" t="inlineStr">
         <is>
           <t>自由時間 ,例文</t>
         </is>
       </c>
     </row>
-    <row r="622">
-      <c r="A622" t="inlineStr">
+    <row r="621">
+      <c r="A621" t="inlineStr">
         <is>
           <t xml:space="preserve">「これ、私の眼鏡じゃありません」
 هٰذِهِ لَيْسَتْ نَظَّارَاتِي
@@ -13511,19 +13491,19 @@
 2509 </t>
         </is>
       </c>
-      <c r="B622" t="inlineStr">
+      <c r="B621" t="inlineStr">
         <is>
           <t>images/「これ、私の眼鏡じゃありません」_img1.jpg</t>
         </is>
       </c>
-      <c r="C622" t="inlineStr">
+      <c r="C621" t="inlineStr">
         <is>
           <t>あらびあや</t>
         </is>
       </c>
     </row>
-    <row r="623">
-      <c r="A623" t="inlineStr">
+    <row r="622">
+      <c r="A622" t="inlineStr">
         <is>
           <t xml:space="preserve">「我らも米を食います」
 نحن أيضاً نأكل الأرز
@@ -13533,19 +13513,19 @@
 1809 </t>
         </is>
       </c>
-      <c r="B623" t="inlineStr">
+      <c r="B622" t="inlineStr">
         <is>
           <t>images/「我らも米を食います」_img1.jpg</t>
         </is>
       </c>
-      <c r="C623" t="inlineStr">
+      <c r="C622" t="inlineStr">
         <is>
           <t>あらびあや</t>
         </is>
       </c>
     </row>
-    <row r="624">
-      <c r="A624" t="inlineStr">
+    <row r="623">
+      <c r="A623" t="inlineStr">
         <is>
           <t xml:space="preserve">「ひとりでできるもん！」
 أنا أستطيع أن أفعله وحدي
@@ -13554,19 +13534,19 @@
 2105 </t>
         </is>
       </c>
-      <c r="B624" t="inlineStr">
+      <c r="B623" t="inlineStr">
         <is>
           <t>images/「ひとりでできるもん！」_img1.jpg</t>
         </is>
       </c>
-      <c r="C624" t="inlineStr">
+      <c r="C623" t="inlineStr">
         <is>
           <t>あらびあや</t>
         </is>
       </c>
     </row>
-    <row r="625">
-      <c r="A625" t="inlineStr">
+    <row r="624">
+      <c r="A624" t="inlineStr">
         <is>
           <t xml:space="preserve">「恋しくないと言っている時は恋しい」
 أُريدُك حينَ أَقُولُ أَنا لا أُريدُك
@@ -13576,19 +13556,19 @@
 2308 DARWISHISM </t>
         </is>
       </c>
-      <c r="B625" t="inlineStr">
+      <c r="B624" t="inlineStr">
         <is>
           <t>images/「恋しくないと言っている時は恋しい」_img1.jpg</t>
         </is>
       </c>
-      <c r="C625" t="inlineStr">
+      <c r="C624" t="inlineStr">
         <is>
           <t>本音 ,恋愛</t>
         </is>
       </c>
     </row>
-    <row r="626">
-      <c r="A626" t="inlineStr">
+    <row r="625">
+      <c r="A625" t="inlineStr">
         <is>
           <t xml:space="preserve">「私は〜する」
 ⁦「着る」：( أنا ألبس )['ana 'a-lbas]⁩
@@ -13599,19 +13579,19 @@
 2109 RABIE </t>
         </is>
       </c>
-      <c r="B626" t="inlineStr">
+      <c r="B625" t="inlineStr">
         <is>
           <t>images/「私は〜する」_img1.jpg,images/「私は〜する」_img2.jpg,images/「私は〜する」_img3.jpg,images/「私は〜する」_img4.jpg</t>
         </is>
       </c>
-      <c r="C626" t="inlineStr">
+      <c r="C625" t="inlineStr">
         <is>
           <t>動詞 ,絵本</t>
         </is>
       </c>
     </row>
-    <row r="627">
-      <c r="A627" t="inlineStr">
+    <row r="626">
+      <c r="A626" t="inlineStr">
         <is>
           <t xml:space="preserve">「彼は完璧ではない。私は彼の欠点については目をつむった」
 هو ليس كامل. أنا أعميت نفسي عن سيئاته
@@ -13620,19 +13600,19 @@
 2308 _NOHA </t>
         </is>
       </c>
-      <c r="B627" t="inlineStr">
+      <c r="B626" t="inlineStr">
         <is>
           <t>images/「彼は完璧ではない。私は彼の欠点につい_img1.jpg</t>
         </is>
       </c>
-      <c r="C627" t="inlineStr">
+      <c r="C626" t="inlineStr">
         <is>
           <t>愛 ,寛容</t>
         </is>
       </c>
     </row>
-    <row r="628">
-      <c r="A628" t="inlineStr">
+    <row r="627">
+      <c r="A627" t="inlineStr">
         <is>
           <t xml:space="preserve">「この子トラは検疫期間中に生まれた」
 صغير النمر هذا ولد في زمن الحجر الصحي
@@ -13641,19 +13621,19 @@
 2310 https://www.akhbaralaan.net/?p=434924 </t>
         </is>
       </c>
-      <c r="B628" t="inlineStr">
+      <c r="B627" t="inlineStr">
         <is>
           <t>images/「この子トラは検疫期間中に生まれた」_img1.jpg</t>
         </is>
       </c>
-      <c r="C628" t="inlineStr">
+      <c r="C627" t="inlineStr">
         <is>
           <t>Covid ,メキシコ</t>
         </is>
       </c>
     </row>
-    <row r="629">
-      <c r="A629" t="inlineStr">
+    <row r="628">
+      <c r="A628" t="inlineStr">
         <is>
           <t xml:space="preserve">「睡眠の素晴らしさに匹敵するものは無い！」
 وجمال النوم ليس له مثيل
@@ -13662,19 +13642,19 @@
 2308 arabzy tumblr </t>
         </is>
       </c>
-      <c r="B629" t="inlineStr">
+      <c r="B628" t="inlineStr">
         <is>
           <t>images/「睡眠の素晴らしさに匹敵するものは無い_img1.jpg</t>
         </is>
       </c>
-      <c r="C629" t="inlineStr">
+      <c r="C628" t="inlineStr">
         <is>
           <t>オフトゥン ,おやすみ</t>
         </is>
       </c>
     </row>
-    <row r="630">
-      <c r="A630" t="inlineStr">
+    <row r="629">
+      <c r="A629" t="inlineStr">
         <is>
           <t xml:space="preserve">「大器晩成」
 الأشياء العظيمة تأخذ وقت
@@ -13684,19 +13664,19 @@
 2109 出典不明 </t>
         </is>
       </c>
-      <c r="B630" t="inlineStr">
+      <c r="B629" t="inlineStr">
         <is>
           <t>images/「大器晩成」_img1.jpg</t>
         </is>
       </c>
-      <c r="C630" t="inlineStr">
+      <c r="C629" t="inlineStr">
         <is>
           <t>ことわざ ,和訳</t>
         </is>
       </c>
     </row>
-    <row r="631">
-      <c r="A631" t="inlineStr">
+    <row r="630">
+      <c r="A630" t="inlineStr">
         <is>
           <t xml:space="preserve">「コーヒーは急には飲まれない」
 القهْوة لا تشرَب عَلى عَجلْ
@@ -13707,19 +13687,19 @@
 2012 Ahmed Madyan </t>
         </is>
       </c>
-      <c r="B631" t="inlineStr">
+      <c r="B630" t="inlineStr">
         <is>
           <t>images/「コーヒーは急には飲まれない」_img1.jpg</t>
         </is>
       </c>
-      <c r="C631" t="inlineStr">
+      <c r="C630" t="inlineStr">
         <is>
           <t>名言</t>
         </is>
       </c>
     </row>
-    <row r="632">
-      <c r="A632" t="inlineStr">
+    <row r="631">
+      <c r="A631" t="inlineStr">
         <is>
           <t xml:space="preserve">「成功者は情報共有している」
 الناجحون يشاركون المعلومة
@@ -13729,19 +13709,19 @@
 2109 出典不明 </t>
         </is>
       </c>
-      <c r="B632" t="inlineStr">
+      <c r="B631" t="inlineStr">
         <is>
           <t>images/「成功者は情報共有している」_img1.jpg</t>
         </is>
       </c>
-      <c r="C632" t="inlineStr">
+      <c r="C631" t="inlineStr">
         <is>
           <t>鳥 ,シェア</t>
         </is>
       </c>
     </row>
-    <row r="633">
-      <c r="A633" t="inlineStr">
+    <row r="632">
+      <c r="A632" t="inlineStr">
         <is>
           <t xml:space="preserve">「間違いで賢くなる、痛みで強くなる」
 الأخطاء تجعلك حكيمًا، والألم يجعلك قويًا
@@ -13750,19 +13730,19 @@
 2111 https://alaminin.blogspot.com/2020/03/blog-post_6.html </t>
         </is>
       </c>
-      <c r="B633" t="inlineStr">
+      <c r="B632" t="inlineStr">
         <is>
           <t>images/「間違いで賢くなる、痛みで強くなる」_img1.jpg</t>
         </is>
       </c>
-      <c r="C633" t="inlineStr">
+      <c r="C632" t="inlineStr">
         <is>
           <t>名言</t>
         </is>
       </c>
     </row>
-    <row r="634">
-      <c r="A634" t="inlineStr">
+    <row r="633">
+      <c r="A633" t="inlineStr">
         <is>
           <t xml:space="preserve">「何事も永遠には続かない」
 لا شيء يبقى للأبد
@@ -13772,19 +13752,19 @@
 2308 KiTeLetZ </t>
         </is>
       </c>
-      <c r="B634" t="inlineStr">
+      <c r="B633" t="inlineStr">
         <is>
           <t>images/「何事も永遠には続かない」_img1.jpg</t>
         </is>
       </c>
-      <c r="C634" t="inlineStr">
+      <c r="C633" t="inlineStr">
         <is>
           <t>変化 ,名言</t>
         </is>
       </c>
     </row>
-    <row r="635">
-      <c r="A635" t="inlineStr">
+    <row r="634">
+      <c r="A634" t="inlineStr">
         <is>
           <t xml:space="preserve">「惑星地球はあなた方を歓迎します」
 كوكب الارض يرحّب بكم
@@ -13794,19 +13774,19 @@
 1811 iN49R </t>
         </is>
       </c>
-      <c r="B635" t="inlineStr">
+      <c r="B634" t="inlineStr">
         <is>
           <t>images/「惑星地球はあなた方を歓迎します」_img1.jpg</t>
         </is>
       </c>
-      <c r="C635" t="inlineStr">
+      <c r="C634" t="inlineStr">
         <is>
           <t>宇宙 ,人類</t>
         </is>
       </c>
     </row>
-    <row r="636">
-      <c r="A636" t="inlineStr">
+    <row r="635">
+      <c r="A635" t="inlineStr">
         <is>
           <t xml:space="preserve">「自分を信じなさい。人の言うことは尽きないのだから」
 ثق بنفسك فكلام الناس لا ينتهي
@@ -13815,19 +13795,19 @@
 2105 出典不明 </t>
         </is>
       </c>
-      <c r="B636" t="inlineStr">
+      <c r="B635" t="inlineStr">
         <is>
           <t>images/「自分を信じなさい。人の言うことは尽き_img1.jpg</t>
         </is>
       </c>
-      <c r="C636" t="inlineStr">
+      <c r="C635" t="inlineStr">
         <is>
           <t>自信 ,無視</t>
         </is>
       </c>
     </row>
-    <row r="637">
-      <c r="A637" t="inlineStr">
+    <row r="636">
+      <c r="A636" t="inlineStr">
         <is>
           <t xml:space="preserve">「弟が歩くぞ」أخي الصغير يمشي
 アキ_ッサギール・ヤムシー ['aKh-i ^_saGhiiru ya-mShii]
@@ -13836,19 +13816,19 @@
 2308 gulfkids com http://www.gulfkids.com/ar/book48-1909.htm </t>
         </is>
       </c>
-      <c r="B637" t="inlineStr">
+      <c r="B636" t="inlineStr">
         <is>
           <t>images/「弟が歩くぞ」_img1.jpg</t>
         </is>
       </c>
-      <c r="C637" t="inlineStr">
+      <c r="C636" t="inlineStr">
         <is>
           <t>兄弟 ,絵本</t>
         </is>
       </c>
     </row>
-    <row r="638">
-      <c r="A638" t="inlineStr">
+    <row r="637">
+      <c r="A637" t="inlineStr">
         <is>
           <t xml:space="preserve">花より団子おおお（違う）
 「誰もふさわしくない」[laa 'aHada ya-staHiqqu]
@@ -13856,19 +13836,19 @@
 2308 https://twitter.com/NatGeoMagArab/status/1370041991317233664 </t>
         </is>
       </c>
-      <c r="B638" t="inlineStr">
+      <c r="B637" t="inlineStr">
         <is>
           <t>images/花より団子おおお（違う）_img1.jpg</t>
         </is>
       </c>
-      <c r="C638" t="inlineStr">
+      <c r="C637" t="inlineStr">
         <is>
           <t>手書き語学 ,アラビア語 ,キノボリカンガルー</t>
         </is>
       </c>
     </row>
-    <row r="639">
-      <c r="A639" t="inlineStr">
+    <row r="638">
+      <c r="A638" t="inlineStr">
         <is>
           <t xml:space="preserve">「幸せな人生には弱い記憶力が必要」
 الحياة السعيدة تتطلب ذاكرة ضعيفة
@@ -13877,19 +13857,19 @@
 2012 出典不明 </t>
         </is>
       </c>
-      <c r="B639" t="inlineStr">
+      <c r="B638" t="inlineStr">
         <is>
           <t>images/「幸せな人生には弱い記憶力が必要」_img1.jpg</t>
         </is>
       </c>
-      <c r="C639" t="inlineStr">
+      <c r="C638" t="inlineStr">
         <is>
           <t>前向き</t>
         </is>
       </c>
     </row>
-    <row r="640">
-      <c r="A640" t="inlineStr">
+    <row r="639">
+      <c r="A639" t="inlineStr">
         <is>
           <t xml:space="preserve">「このパンダは私たちに、幸せは単純なことの中に隠れているのだと教えている」
 دب "الباندا" هذا يؤكد لنا أن السعادة تكمن في أبسط الأشياء
@@ -13897,19 +13877,19 @@
 2308 https://twitter.com/NatGeoMagArab/status/1309938472065486848 </t>
         </is>
       </c>
-      <c r="B640" t="inlineStr">
+      <c r="B639" t="inlineStr">
         <is>
           <t>images/「このパンダは私たちに、幸せは単純なこ.png</t>
         </is>
       </c>
-      <c r="C640" t="inlineStr">
+      <c r="C639" t="inlineStr">
         <is>
           <t>パンダ ,雪</t>
         </is>
       </c>
     </row>
-    <row r="641">
-      <c r="A641" t="inlineStr">
+    <row r="640">
+      <c r="A640" t="inlineStr">
         <is>
           <t xml:space="preserve">「良い時間は速く過ぎる」
 الأوقات الجميلة تمر بسرعة
@@ -13919,19 +13899,19 @@
 1810 Nasser.Tumblr </t>
         </is>
       </c>
-      <c r="B641" t="inlineStr">
+      <c r="B640" t="inlineStr">
         <is>
           <t>images/「良い時間は速く過ぎる」_img1.jpg</t>
         </is>
       </c>
-      <c r="C641" t="inlineStr">
+      <c r="C640" t="inlineStr">
         <is>
           <t>相対論 ,心理学</t>
         </is>
       </c>
     </row>
-    <row r="642">
-      <c r="A642" t="inlineStr">
+    <row r="641">
+      <c r="A641" t="inlineStr">
         <is>
           <t xml:space="preserve">「今日が始まりかもしれない」
 كل يوم ممكن يكون بداية
@@ -13941,19 +13921,19 @@
 2308 Ahmed Madyan </t>
         </is>
       </c>
-      <c r="B642" t="inlineStr">
+      <c r="B641" t="inlineStr">
         <is>
           <t>images/「今日が始まりかもしれない」_img1.jpg</t>
         </is>
       </c>
-      <c r="C642" t="inlineStr">
+      <c r="C641" t="inlineStr">
         <is>
           <t>吉日 ,開始</t>
         </is>
       </c>
     </row>
-    <row r="643">
-      <c r="A643" t="inlineStr">
+    <row r="642">
+      <c r="A642" t="inlineStr">
         <is>
           <t xml:space="preserve">「ヌール、歯医者さんに行く」
 نور تذهب إلى طبيب الأسنان
@@ -13963,19 +13943,19 @@
 2109 RABIE </t>
         </is>
       </c>
-      <c r="B643" t="inlineStr">
+      <c r="B642" t="inlineStr">
         <is>
           <t>images/「ヌール、歯医者さんに行く」_img1.jpg</t>
         </is>
       </c>
-      <c r="C643" t="inlineStr">
+      <c r="C642" t="inlineStr">
         <is>
           <t>絵本 ,歯科</t>
         </is>
       </c>
     </row>
-    <row r="644">
-      <c r="A644" t="inlineStr">
+    <row r="643">
+      <c r="A643" t="inlineStr">
         <is>
           <t xml:space="preserve">「ラヤンはねむれない」
 لَيان لا تَسْتَطيعُ أَنْ تَنام
@@ -13984,19 +13964,19 @@
 2308 出典不明 </t>
         </is>
       </c>
-      <c r="B644" t="inlineStr">
+      <c r="B643" t="inlineStr">
         <is>
           <t>images/「ラヤンはねむれない」_img1.jpg</t>
         </is>
       </c>
-      <c r="C644" t="inlineStr">
+      <c r="C643" t="inlineStr">
         <is>
           <t>絵本 ,不眠症</t>
         </is>
       </c>
     </row>
-    <row r="645">
-      <c r="A645" t="inlineStr">
+    <row r="644">
+      <c r="A644" t="inlineStr">
         <is>
           <t xml:space="preserve">「クネイトラ県、蜂の巣を約60%失う」
 القنيطرة تفقد حوالي 60 % من خلايا نحلها
@@ -14004,19 +13984,19 @@
 2403 nabd com/t/101679025-fb119f </t>
         </is>
       </c>
-      <c r="B645" t="inlineStr">
+      <c r="B644" t="inlineStr">
         <is>
           <t>images/「クネイトラ県、蜂の巣を約60%失う」_img1.jpg</t>
         </is>
       </c>
-      <c r="C645" t="inlineStr">
+      <c r="C644" t="inlineStr">
         <is>
           <t>蜂の巣 ,パーセント</t>
         </is>
       </c>
     </row>
-    <row r="646">
-      <c r="A646" t="inlineStr">
+    <row r="645">
+      <c r="A645" t="inlineStr">
         <is>
           <t xml:space="preserve">「結ばれしター」ة
 ⁦( تاء مربوطة )[taa' marbuu_ta]：ت「ター」( تاء )[taa']・「結ばれている」( مربوط )[marbuu_t]：( ربط )【結】⁩
@@ -14024,19 +14004,19 @@
 2308 出典不明 </t>
         </is>
       </c>
-      <c r="B646" t="inlineStr">
+      <c r="B645" t="inlineStr">
         <is>
           <t>images/「結ばれしター」_img1.jpg</t>
         </is>
       </c>
-      <c r="C646" t="inlineStr">
+      <c r="C645" t="inlineStr">
         <is>
           <t>アラビア文字 ,顔</t>
         </is>
       </c>
     </row>
-    <row r="647">
-      <c r="A647" t="inlineStr">
+    <row r="646">
+      <c r="A646" t="inlineStr">
         <is>
           <t xml:space="preserve">「忙しい」مشغول
 マシュグール [maShGhuul]
@@ -14045,19 +14025,19 @@
 1811 skyshinichi.instagram </t>
         </is>
       </c>
-      <c r="B647" t="inlineStr">
+      <c r="B646" t="inlineStr">
         <is>
           <t>images/「忙しい」_img1.jpg</t>
         </is>
       </c>
-      <c r="C647" t="inlineStr">
+      <c r="C646" t="inlineStr">
         <is>
           <t>スティッチ ,残業</t>
         </is>
       </c>
     </row>
-    <row r="648">
-      <c r="A648" t="inlineStr">
+    <row r="647">
+      <c r="A647" t="inlineStr">
         <is>
           <t xml:space="preserve">「駐車禁止」ممنوع الوقوف
 マムヌーア・アルウクーフ [mamnuu* al-wuquuf]
@@ -14066,19 +14046,19 @@
 2106 出典不明 </t>
         </is>
       </c>
-      <c r="B648" t="inlineStr">
+      <c r="B647" t="inlineStr">
         <is>
           <t>images/「駐車禁止」_img1.jpg</t>
         </is>
       </c>
-      <c r="C648" t="inlineStr">
+      <c r="C647" t="inlineStr">
         <is>
           <t>標識 ,ジョーク</t>
         </is>
       </c>
     </row>
-    <row r="649">
-      <c r="A649" t="inlineStr">
+    <row r="648">
+      <c r="A648" t="inlineStr">
         <is>
           <t xml:space="preserve">「一人ひとりが責任を」
 كُلنا مسؤول
@@ -14088,19 +14068,19 @@
 2308 covid19awareness sa </t>
         </is>
       </c>
-      <c r="B649" t="inlineStr">
+      <c r="B648" t="inlineStr">
         <is>
           <t>images/「一人ひとりが責任を」_img1.jpg</t>
         </is>
       </c>
-      <c r="C649" t="inlineStr">
+      <c r="C648" t="inlineStr">
         <is>
           <t>Covid ,感染拡大防止</t>
         </is>
       </c>
     </row>
-    <row r="650">
-      <c r="A650" t="inlineStr">
+    <row r="649">
+      <c r="A649" t="inlineStr">
         <is>
           <t xml:space="preserve">「おめでとうございます」مبروك
 マブルーク [mabruuk]
@@ -14109,19 +14089,19 @@
 2308 </t>
         </is>
       </c>
-      <c r="B650" t="inlineStr">
+      <c r="B649" t="inlineStr">
         <is>
           <t>images/「おめでとうございます」_img1.jpg</t>
         </is>
       </c>
-      <c r="C650" t="inlineStr">
+      <c r="C649" t="inlineStr">
         <is>
           <t>詐欺 ,広告</t>
         </is>
       </c>
     </row>
-    <row r="651">
-      <c r="A651" t="inlineStr">
+    <row r="650">
+      <c r="A650" t="inlineStr">
         <is>
           <t xml:space="preserve">「手書きフォント」
 خط مكتوب باليد
@@ -14131,19 +14111,19 @@
 1809 FahdAlFraikh Behance </t>
         </is>
       </c>
-      <c r="B651" t="inlineStr">
+      <c r="B650" t="inlineStr">
         <is>
           <t>images/「手書きフォント」_img1.jpg</t>
         </is>
       </c>
-      <c r="C651" t="inlineStr">
+      <c r="C650" t="inlineStr">
         <is>
           <t>可愛いフォント ,筆跡</t>
         </is>
       </c>
     </row>
-    <row r="652">
-      <c r="A652" t="inlineStr">
+    <row r="651">
+      <c r="A651" t="inlineStr">
         <is>
           <t xml:space="preserve">「開かれたターと結ばれたター」
 التاء المفتوحة والمربوطة
@@ -14153,19 +14133,19 @@
 2109 slideshare.net </t>
         </is>
       </c>
-      <c r="B652" t="inlineStr">
+      <c r="B651" t="inlineStr">
         <is>
           <t>images/「開かれたターと結ばれたター」_img1.jpg</t>
         </is>
       </c>
-      <c r="C652" t="inlineStr">
+      <c r="C651" t="inlineStr">
         <is>
           <t>アラビア文字 ,スマイリー</t>
         </is>
       </c>
     </row>
-    <row r="653">
-      <c r="A653" t="inlineStr">
+    <row r="652">
+      <c r="A652" t="inlineStr">
         <is>
           <t xml:space="preserve">「このラマは誇らしげにして立っている」
 تقف هذه اللاما مزهوة بنفسها
@@ -14173,19 +14153,19 @@
 2410 https://twitter.com/NatGeoMagArab/status/1597485552965935104 </t>
         </is>
       </c>
-      <c r="B653" t="inlineStr">
+      <c r="B652" t="inlineStr">
         <is>
           <t>images/「このラマは誇らしげにして立っている」_img1.jpg</t>
         </is>
       </c>
-      <c r="C653" t="inlineStr">
+      <c r="C652" t="inlineStr">
         <is>
           <t>手書き語学 ,アラビア語 ,マチュピチュ遺跡</t>
         </is>
       </c>
     </row>
-    <row r="654">
-      <c r="A654" t="inlineStr">
+    <row r="653">
+      <c r="A653" t="inlineStr">
         <is>
           <t xml:space="preserve">「小さな生き物にしては危険な名前だ」
 اسم خطير لمخلوق صغير
@@ -14194,19 +14174,19 @@
 2308 https://twitter.com/NatGeoMagArab/status/1495035772071669760 </t>
         </is>
       </c>
-      <c r="B654" t="inlineStr">
+      <c r="B653" t="inlineStr">
         <is>
           <t>images/「小さな生き物にしては危険な名前だ」_img1.jpg</t>
         </is>
       </c>
-      <c r="C654" t="inlineStr">
+      <c r="C653" t="inlineStr">
         <is>
           <t>有袋類 ,タスマニアデビル</t>
         </is>
       </c>
     </row>
-    <row r="655">
-      <c r="A655" t="inlineStr">
+    <row r="654">
+      <c r="A654" t="inlineStr">
         <is>
           <t xml:space="preserve">「こわれている」مكسر
 ムカッサル [mukassar]
@@ -14214,19 +14194,19 @@
 2105 behance Written-Visuals </t>
         </is>
       </c>
-      <c r="B655" t="inlineStr">
+      <c r="B654" t="inlineStr">
         <is>
           <t>images/「こわれている」_img1.jpg</t>
         </is>
       </c>
-      <c r="C655" t="inlineStr">
+      <c r="C654" t="inlineStr">
         <is>
           <t>バラバラ ,デザイン</t>
         </is>
       </c>
     </row>
-    <row r="656">
-      <c r="A656" t="inlineStr">
+    <row r="655">
+      <c r="A655" t="inlineStr">
         <is>
           <t xml:space="preserve">「早起きする方法」
 كيف تنهض مُبكّرًا
@@ -14236,19 +14216,19 @@
 2308 Funders and Founders </t>
         </is>
       </c>
-      <c r="B656" t="inlineStr">
+      <c r="B655" t="inlineStr">
         <is>
           <t>images/「早起きする方法」_img1.jpg</t>
         </is>
       </c>
-      <c r="C656" t="inlineStr">
+      <c r="C655" t="inlineStr">
         <is>
           <t>オフトゥン ,寝起き</t>
         </is>
       </c>
     </row>
-    <row r="657">
-      <c r="A657" t="inlineStr">
+    <row r="656">
+      <c r="A656" t="inlineStr">
         <is>
           <t xml:space="preserve">「アラブ・デザイン文字展覧会」
 معرض لتخطيط الحرف العربي
@@ -14258,19 +14238,19 @@
 2109 arabic lettering exhibition </t>
         </is>
       </c>
-      <c r="B657" t="inlineStr">
+      <c r="B656" t="inlineStr">
         <is>
           <t>images/「アラブ・デザイン文字展覧会」_img1.jpg</t>
         </is>
       </c>
-      <c r="C657" t="inlineStr">
+      <c r="C656" t="inlineStr">
         <is>
           <t>ポスター</t>
         </is>
       </c>
     </row>
-    <row r="658">
-      <c r="A658" t="inlineStr">
+    <row r="657">
+      <c r="A657" t="inlineStr">
         <is>
           <t xml:space="preserve">「名探偵コナン」المحقق كونان
 アルムハッキク・コナン [al-muHaqqiq Conan]
@@ -14279,19 +14259,19 @@
 1809 wikipedia </t>
         </is>
       </c>
-      <c r="B658" t="inlineStr">
+      <c r="B657" t="inlineStr">
         <is>
           <t>images/「名探偵コナン」_img1.jpg</t>
         </is>
       </c>
-      <c r="C658" t="inlineStr">
+      <c r="C657" t="inlineStr">
         <is>
           <t>江戸川コナン ,ロゴ</t>
         </is>
       </c>
     </row>
-    <row r="659">
-      <c r="A659" t="inlineStr">
+    <row r="658">
+      <c r="A658" t="inlineStr">
         <is>
           <t xml:space="preserve">「イードおめでとう」عيد مبارك
 イード・ムバーラク [*iid mubaarak]
@@ -14299,19 +14279,19 @@
 2308 出典不明 </t>
         </is>
       </c>
-      <c r="B659" t="inlineStr">
+      <c r="B658" t="inlineStr">
         <is>
           <t>images/「イードおめでとう」_img1.jpg</t>
         </is>
       </c>
-      <c r="C659" t="inlineStr">
+      <c r="C658" t="inlineStr">
         <is>
           <t>عيد ,アラビア語</t>
         </is>
       </c>
     </row>
-    <row r="660">
-      <c r="A660" t="inlineStr">
+    <row r="659">
+      <c r="A659" t="inlineStr">
         <is>
           <t xml:space="preserve">「戦士」محارب
 ムハーリブ [muHaarib]
@@ -14320,19 +14300,19 @@
 1809 abudinges.tumblr </t>
         </is>
       </c>
-      <c r="B660" t="inlineStr">
+      <c r="B659" t="inlineStr">
         <is>
           <t>images/「戦士」_img1.jpg</t>
         </is>
       </c>
-      <c r="C660" t="inlineStr">
+      <c r="C659" t="inlineStr">
         <is>
           <t>ロゴ ,赤</t>
         </is>
       </c>
     </row>
-    <row r="661">
-      <c r="A661" t="inlineStr">
+    <row r="660">
+      <c r="A660" t="inlineStr">
         <is>
           <t xml:space="preserve">「ライブ」بث مباشر
 バッス・ムバーシル [ba^Th(un) mubaaShir(un)]
@@ -14341,19 +14321,19 @@
 2308 beIN SPORTS </t>
         </is>
       </c>
-      <c r="B661" t="inlineStr">
+      <c r="B660" t="inlineStr">
         <is>
           <t>images/「ライブ」_img1.jpg</t>
         </is>
       </c>
-      <c r="C661" t="inlineStr">
+      <c r="C660" t="inlineStr">
         <is>
           <t xml:space="preserve">生放送 ,試合 </t>
         </is>
       </c>
     </row>
-    <row r="662">
-      <c r="A662" t="inlineStr">
+    <row r="661">
+      <c r="A661" t="inlineStr">
         <is>
           <t xml:space="preserve">「信者」مُؤْمِنٌ
 ムッミン [mu'min(un)]
@@ -14362,19 +14342,19 @@
 2106 出典不明 </t>
         </is>
       </c>
-      <c r="B662" t="inlineStr">
+      <c r="B661" t="inlineStr">
         <is>
           <t>images/「信者」_img1.jpg</t>
         </is>
       </c>
-      <c r="C662" t="inlineStr">
+      <c r="C661" t="inlineStr">
         <is>
           <t>明暗 ,信仰</t>
         </is>
       </c>
     </row>
-    <row r="663">
-      <c r="A663" t="inlineStr">
+    <row r="662">
+      <c r="A662" t="inlineStr">
         <is>
           <t xml:space="preserve">「開⇔閉」
 مفتوح
@@ -14385,19 +14365,19 @@
 2312 Hussein Safina, behance </t>
         </is>
       </c>
-      <c r="B663" t="inlineStr">
+      <c r="B662" t="inlineStr">
         <is>
           <t>images/「開⇔閉」_img1.jpg</t>
         </is>
       </c>
-      <c r="C663" t="inlineStr">
+      <c r="C662" t="inlineStr">
         <is>
           <t>オープンマインド ,トグル</t>
         </is>
       </c>
     </row>
-    <row r="664">
-      <c r="A664" t="inlineStr">
+    <row r="663">
+      <c r="A663" t="inlineStr">
         <is>
           <t xml:space="preserve">「予想外な結末！」
 نهاية غير متوقعة
@@ -14405,19 +14385,19 @@
 2308 https://twitter.com/NatGeoMagArab/status/1159011433444593665 </t>
         </is>
       </c>
-      <c r="B664" t="inlineStr">
+      <c r="B663" t="inlineStr">
         <is>
           <t>images/「予想外な結末！」_img1.jpg</t>
         </is>
       </c>
-      <c r="C664" t="inlineStr">
+      <c r="C663" t="inlineStr">
         <is>
           <t>手書き語学 ,アラビア語 ,ウサギ</t>
         </is>
       </c>
     </row>
-    <row r="665">
-      <c r="A665" t="inlineStr">
+    <row r="664">
+      <c r="A664" t="inlineStr">
         <is>
           <t xml:space="preserve">「ベイルート・アニメイテッド」
 بیروت متحرّکة
@@ -14427,19 +14407,19 @@
 2308 arabic_script Instagram </t>
         </is>
       </c>
-      <c r="B665" t="inlineStr">
+      <c r="B664" t="inlineStr">
         <is>
           <t>images/「ベイルート・アニメイテッド」_img1.jpg</t>
         </is>
       </c>
-      <c r="C665" t="inlineStr">
+      <c r="C664" t="inlineStr">
         <is>
           <t>アニメ ,レバノン</t>
         </is>
       </c>
     </row>
-    <row r="666">
-      <c r="A666" t="inlineStr">
+    <row r="665">
+      <c r="A665" t="inlineStr">
         <is>
           <t xml:space="preserve">「夢みれば叶う」
 كُلُّ مُتَوَقَّعٍ آتٍ
@@ -14449,19 +14429,19 @@
 2108 Ahmed Madyan </t>
         </is>
       </c>
-      <c r="B666" t="inlineStr">
+      <c r="B665" t="inlineStr">
         <is>
           <t>images/「夢みれば叶う」_img1.jpg</t>
         </is>
       </c>
-      <c r="C666" t="inlineStr">
+      <c r="C665" t="inlineStr">
         <is>
           <t>希望 ,ドリカム</t>
         </is>
       </c>
     </row>
-    <row r="667">
-      <c r="A667" t="inlineStr">
+    <row r="666">
+      <c r="A666" t="inlineStr">
         <is>
           <t xml:space="preserve">「もし両者が人間のように鎧で武装して戦いに突入したら」
 لو خاضا معاركهما متسلحين بالدروع على غرار البش
@@ -14469,19 +14449,19 @@
 2404 https://x.com/NatGeoMagArab/status/1759284149456945464 </t>
         </is>
       </c>
-      <c r="B667" t="inlineStr">
+      <c r="B666" t="inlineStr">
         <is>
           <t>images/「もし両者が人間のように鎧で武装して戦_img1.jpg,images/「もし両者が人間のように鎧で武装して戦_img2.jpg</t>
         </is>
       </c>
-      <c r="C667" t="inlineStr">
+      <c r="C666" t="inlineStr">
         <is>
           <t>手書き語学 ,アラビア語 ,猫</t>
         </is>
       </c>
     </row>
-    <row r="668">
-      <c r="A668" t="inlineStr">
+    <row r="667">
+      <c r="A667" t="inlineStr">
         <is>
           <t xml:space="preserve">「全ては結びついている」
 كل شيء مترابط
@@ -14491,19 +14471,19 @@
 2308 Ahmed Madyan https://twitter.com/madyco22/status/1451990828298166273 </t>
         </is>
       </c>
-      <c r="B668" t="inlineStr">
+      <c r="B667" t="inlineStr">
         <is>
           <t>images/「全ては結びついている」_img1.jpg</t>
         </is>
       </c>
-      <c r="C668" t="inlineStr">
+      <c r="C667" t="inlineStr">
         <is>
           <t>一筆書き ,デザイン</t>
         </is>
       </c>
     </row>
-    <row r="669">
-      <c r="A669" t="inlineStr">
+    <row r="668">
+      <c r="A668" t="inlineStr">
         <is>
           <t xml:space="preserve">「初心者のためのスケッチトレーニング」
 تعليم الرسم للمبتدئين
@@ -14513,19 +14493,19 @@
 2308 free-bookspdf com </t>
         </is>
       </c>
-      <c r="B669" t="inlineStr">
+      <c r="B668" t="inlineStr">
         <is>
           <t>images/「初心者のためのスケッチトレーニング」_img1.jpg</t>
         </is>
       </c>
-      <c r="C669" t="inlineStr">
+      <c r="C668" t="inlineStr">
         <is>
           <t>イラスト ,絵</t>
         </is>
       </c>
     </row>
-    <row r="670">
-      <c r="A670" t="inlineStr">
+    <row r="669">
+      <c r="A669" t="inlineStr">
         <is>
           <t xml:space="preserve">「初心者のためのスルス体書道トレーニング」
 تعليم خط الثلث للمبتدئين
@@ -14535,19 +14515,19 @@
 2308 出典不明 </t>
         </is>
       </c>
-      <c r="B670" t="inlineStr">
+      <c r="B669" t="inlineStr">
         <is>
           <t>images/「初心者のためのスルス体書道トレーニン_img1.jpg</t>
         </is>
       </c>
-      <c r="C670" t="inlineStr">
+      <c r="C669" t="inlineStr">
         <is>
           <t>書道</t>
         </is>
       </c>
     </row>
-    <row r="671">
-      <c r="A671" t="inlineStr">
+    <row r="670">
+      <c r="A670" t="inlineStr">
         <is>
           <t xml:space="preserve">「笑顔でいなさい」خليك مبتسم
 カッリーク・ムブタスィム [Khallii-k mubtasim]
@@ -14556,19 +14536,19 @@
 2308 https://tmblr.co/Zj9tguYLXBvC </t>
         </is>
       </c>
-      <c r="B671" t="inlineStr">
+      <c r="B670" t="inlineStr">
         <is>
           <t>images/「笑顔でいなさい」_img1.jpg</t>
         </is>
       </c>
-      <c r="C671" t="inlineStr">
+      <c r="C670" t="inlineStr">
         <is>
           <t>スマイル ,名言</t>
         </is>
       </c>
     </row>
-    <row r="672">
-      <c r="A672" t="inlineStr">
+    <row r="671">
+      <c r="A671" t="inlineStr">
         <is>
           <t xml:space="preserve">自動車メーカー
 ⁦・「TOYOTA」( تويوتا )⁩
@@ -14580,19 +14560,19 @@
 2308 syarah com </t>
         </is>
       </c>
-      <c r="B672" t="inlineStr">
+      <c r="B671" t="inlineStr">
         <is>
           <t>images/自動車メーカー_img1.jpg,images/自動車メーカー_img2.jpg,images/自動車メーカー_img3.jpg,images/自動車メーカー_img4.jpg</t>
         </is>
       </c>
-      <c r="C672" t="inlineStr">
+      <c r="C671" t="inlineStr">
         <is>
           <t>日本車 ,韓国車</t>
         </is>
       </c>
     </row>
-    <row r="673">
-      <c r="A673" t="inlineStr">
+    <row r="672">
+      <c r="A672" t="inlineStr">
         <is>
           <t xml:space="preserve">「僕たちは協力して不可能を達成するよ」
 بالتعاون نحقق المحال
@@ -14602,19 +14582,19 @@
 2109 </t>
         </is>
       </c>
-      <c r="B673" t="inlineStr">
+      <c r="B672" t="inlineStr">
         <is>
           <t>images/「僕たちは協力して不可能を達成するよ」_img1.jpg</t>
         </is>
       </c>
-      <c r="C673" t="inlineStr">
+      <c r="C672" t="inlineStr">
         <is>
           <t>無理 ,ハム太郎</t>
         </is>
       </c>
     </row>
-    <row r="674">
-      <c r="A674" t="inlineStr">
+    <row r="673">
+      <c r="A673" t="inlineStr">
         <is>
           <t xml:space="preserve">「幸せは伝染性。喜びを広めよう」
 السعادة معدية فأشع الفرح
@@ -14624,19 +14604,19 @@
 2511 instagram　com/p/fVEfxEo7Va/ </t>
         </is>
       </c>
-      <c r="B674" t="inlineStr">
+      <c r="B673" t="inlineStr">
         <is>
           <t>images/「幸せは伝染性。喜びを広めよう」_img1.jpg</t>
         </is>
       </c>
-      <c r="C674" t="inlineStr">
+      <c r="C673" t="inlineStr">
         <is>
           <t>拡散希望</t>
         </is>
       </c>
     </row>
-    <row r="675">
-      <c r="A675" t="inlineStr">
+    <row r="674">
+      <c r="A674" t="inlineStr">
         <is>
           <t xml:space="preserve">「ストレスは人間だけのものではない」
 الشعور بالتوتر ليس حكرًا على البشر
@@ -14644,19 +14624,19 @@
 2408 https://x.com/NatGeoMagArab/status/1736755816911487420 </t>
         </is>
       </c>
-      <c r="B675" t="inlineStr">
+      <c r="B674" t="inlineStr">
         <is>
           <t>images/「ストレスは人間だけのものではない」_img1.jpg</t>
         </is>
       </c>
-      <c r="C675" t="inlineStr">
+      <c r="C674" t="inlineStr">
         <is>
           <t>手書き語学 ,アラビア語 ,ストレス</t>
         </is>
       </c>
     </row>
-    <row r="676">
-      <c r="A676" t="inlineStr">
+    <row r="675">
+      <c r="A675" t="inlineStr">
         <is>
           <t xml:space="preserve">「私達は出来ます！」
 نستطيع فعلها
@@ -14666,19 +14646,19 @@
 2308 NAHARBAHIJ com </t>
         </is>
       </c>
-      <c r="B676" t="inlineStr">
+      <c r="B675" t="inlineStr">
         <is>
           <t>images/「私達は出来ます！」_img1.jpg</t>
         </is>
       </c>
-      <c r="C676" t="inlineStr">
+      <c r="C675" t="inlineStr">
         <is>
           <t>女性 ,パロディ</t>
         </is>
       </c>
     </row>
-    <row r="677">
-      <c r="A677" t="inlineStr">
+    <row r="676">
+      <c r="A676" t="inlineStr">
         <is>
           <t xml:space="preserve">「全然分からん」ولا فاهم إشي
 ウラー・ファーヒム・イシ [w-laa faahim 'iShy]
@@ -14688,19 +14668,19 @@
 2209 出典不明 </t>
         </is>
       </c>
-      <c r="B677" t="inlineStr">
+      <c r="B676" t="inlineStr">
         <is>
           <t>images/「全然分からん」_img1.jpg</t>
         </is>
       </c>
-      <c r="C677" t="inlineStr">
+      <c r="C676" t="inlineStr">
         <is>
           <t>アラビア語</t>
         </is>
       </c>
     </row>
-    <row r="678">
-      <c r="A678" t="inlineStr">
+    <row r="677">
+      <c r="A677" t="inlineStr">
         <is>
           <t xml:space="preserve">「人間は一人ひとり、特別な才がある。だから自分を他人と比べるのはやめよう」
 لكل إنسان مواهبه الخاصة 
@@ -14709,19 +14689,19 @@
 1812 Gwid3 </t>
         </is>
       </c>
-      <c r="B678" t="inlineStr">
+      <c r="B677" t="inlineStr">
         <is>
           <t>images/「人間は一人ひとり、特別な才がある。だ_img1.jpg</t>
         </is>
       </c>
-      <c r="C678" t="inlineStr">
+      <c r="C677" t="inlineStr">
         <is>
           <t>自尊 ,プライド</t>
         </is>
       </c>
     </row>
-    <row r="679">
-      <c r="A679" t="inlineStr">
+    <row r="678">
+      <c r="A678" t="inlineStr">
         <is>
           <t xml:space="preserve">「この猫は食事をシェアするのが嫌い！」
 هذه القطة لا تحب مشاركة الطعام
@@ -14730,19 +14710,19 @@
 2605 facebook com/alahram/videos/2154923608133231/ </t>
         </is>
       </c>
-      <c r="B679" t="inlineStr">
+      <c r="B678" t="inlineStr">
         <is>
           <t>images/「この猫は食事をシェアするのが嫌い！」_img1.jpg</t>
         </is>
       </c>
-      <c r="C679" t="inlineStr">
+      <c r="C678" t="inlineStr">
         <is>
           <t>猫 ,ネコ</t>
         </is>
       </c>
     </row>
-    <row r="680">
-      <c r="A680" t="inlineStr">
+    <row r="679">
+      <c r="A679" t="inlineStr">
         <is>
           <t xml:space="preserve">「怪獣との戦いでは自分が怪獣化せぬよう警戒しなさい」
 احذر عند محاربة الوحوش ألا تصبح واحدا منهم
@@ -14752,19 +14732,19 @@
 2108 warag-3nb.tumblr </t>
         </is>
       </c>
-      <c r="B680" t="inlineStr">
+      <c r="B679" t="inlineStr">
         <is>
           <t>images/「怪獣との戦いでは自分が怪獣化せぬよう_img1.jpg,images/ 「怪獣との戦いでは自分が怪獣化せぬよう_img2.jpg</t>
         </is>
       </c>
-      <c r="C680" t="inlineStr">
+      <c r="C679" t="inlineStr">
         <is>
           <t>正気 ,モンスター</t>
         </is>
       </c>
     </row>
-    <row r="681">
-      <c r="A681" t="inlineStr">
+    <row r="680">
+      <c r="A680" t="inlineStr">
         <is>
           <t xml:space="preserve">「錯視アート」فن الخداع البصري
 ファンヌ_ルヒダーイ_ルバサリーイ [fannu l-Khidaa*i l-ba_sariyy]
@@ -14773,19 +14753,19 @@
 2409 https://online.pubhtml5.com/idtb/neft/ </t>
         </is>
       </c>
-      <c r="B681" t="inlineStr">
+      <c r="B680" t="inlineStr">
         <is>
           <t>images/「錯視アート」_img1.jpg</t>
         </is>
       </c>
-      <c r="C681" t="inlineStr">
+      <c r="C680" t="inlineStr">
         <is>
           <t>トリックアート</t>
         </is>
       </c>
     </row>
-    <row r="682">
-      <c r="A682" t="inlineStr">
+    <row r="681">
+      <c r="A681" t="inlineStr">
         <is>
           <t xml:space="preserve">「自然界の消防士の訓練」
 تدريبات رجال الإطفاء في الطبيعة
@@ -14793,19 +14773,19 @@
 2308 https://twitter.com/NatGeoMagArab/status/1462420543890608129 </t>
         </is>
       </c>
-      <c r="B682" t="inlineStr">
+      <c r="B681" t="inlineStr">
         <is>
           <t>images/「自然界の消防士の訓練」_img1.jpg,images/ 「自然界の消防士の訓練」_img2.jpg</t>
         </is>
       </c>
-      <c r="C682" t="inlineStr">
+      <c r="C681" t="inlineStr">
         <is>
           <t>手書き語学 ,アラビア語 ,ヒグマ</t>
         </is>
       </c>
     </row>
-    <row r="683">
-      <c r="A683" t="inlineStr">
+    <row r="682">
+      <c r="A682" t="inlineStr">
         <is>
           <t xml:space="preserve">「救助」إسعاف
 イスアーフ ['is*aaf]
@@ -14814,19 +14794,19 @@
 2109 ambulance gov ae </t>
         </is>
       </c>
-      <c r="B683" t="inlineStr">
+      <c r="B682" t="inlineStr">
         <is>
           <t>images/「救助」_img1.jpg</t>
         </is>
       </c>
-      <c r="C683" t="inlineStr">
+      <c r="C682" t="inlineStr">
         <is>
           <t>救急車 ,はたらくくるま</t>
         </is>
       </c>
     </row>
-    <row r="684">
-      <c r="A684" t="inlineStr">
+    <row r="683">
+      <c r="A683" t="inlineStr">
         <is>
           <t xml:space="preserve">「感情／感覚」الإحْسَاسْ
 アルイヒサース [al-'iHsaas]
@@ -14835,19 +14815,19 @@
 2308 iN49R </t>
         </is>
       </c>
-      <c r="B684" t="inlineStr">
+      <c r="B683" t="inlineStr">
         <is>
           <t>images/「感情／感覚」_img1.jpg</t>
         </is>
       </c>
-      <c r="C684" t="inlineStr">
+      <c r="C683" t="inlineStr">
         <is>
           <t>オフ ,一休み</t>
         </is>
       </c>
     </row>
-    <row r="685">
-      <c r="A685" t="inlineStr">
+    <row r="684">
+      <c r="A684" t="inlineStr">
         <is>
           <t xml:space="preserve">「ひらめき」إلهام
 イルハーム ['lhaam]
@@ -14859,19 +14839,19 @@
 2103 出典不明 </t>
         </is>
       </c>
-      <c r="B685" t="inlineStr">
+      <c r="B684" t="inlineStr">
         <is>
           <t>images/「ひらめき」_img1.jpg</t>
         </is>
       </c>
-      <c r="C685" t="inlineStr">
+      <c r="C684" t="inlineStr">
         <is>
           <t>アラビア語</t>
         </is>
       </c>
     </row>
-    <row r="686">
-      <c r="A686" t="inlineStr">
+    <row r="685">
+      <c r="A685" t="inlineStr">
         <is>
           <t xml:space="preserve">「Ibdaa／クリエイティビティ」
 إبداع
@@ -14880,19 +14860,19 @@
 2308 Ibdaa Design &amp; Decoration Office </t>
         </is>
       </c>
-      <c r="B686" t="inlineStr">
+      <c r="B685" t="inlineStr">
         <is>
           <t>images/「Ibdaa／クリエイティビティ」_img1.jpg</t>
         </is>
       </c>
-      <c r="C686" t="inlineStr">
+      <c r="C685" t="inlineStr">
         <is>
           <t>創造性 ,独自性</t>
         </is>
       </c>
     </row>
-    <row r="687">
-      <c r="A687" t="inlineStr">
+    <row r="686">
+      <c r="A686" t="inlineStr">
         <is>
           <t xml:space="preserve">「奮闘なくして進歩なし」
 بدون كفاح لايوجد تقدم
@@ -14902,19 +14882,19 @@
 2105 ROUYMS TUMBLR COM </t>
         </is>
       </c>
-      <c r="B687" t="inlineStr">
+      <c r="B686" t="inlineStr">
         <is>
           <t>images/「奮闘なくして進歩なし」_img1.jpg</t>
         </is>
       </c>
-      <c r="C687" t="inlineStr">
+      <c r="C686" t="inlineStr">
         <is>
           <t>努力 ,三角形</t>
         </is>
       </c>
     </row>
-    <row r="688">
-      <c r="A688" t="inlineStr">
+    <row r="687">
+      <c r="A687" t="inlineStr">
         <is>
           <t xml:space="preserve">「木に登れば熊の危険を避けられるとお考えなら、考え直しましょう！」 
 إن اعتقدت أنك بمنأى عن خطر الدب عند تسلق الأشجار.. راجع حساباتك
@@ -14922,19 +14902,19 @@
 2202 NatGeoMagArab </t>
         </is>
       </c>
-      <c r="B688" t="inlineStr">
+      <c r="B687" t="inlineStr">
         <is>
           <t>images/「木に登れば熊の危険を避けられるとお考.jpeg</t>
         </is>
       </c>
-      <c r="C688" t="inlineStr">
+      <c r="C687" t="inlineStr">
         <is>
           <t>クマ</t>
         </is>
       </c>
     </row>
-    <row r="689">
-      <c r="A689" t="inlineStr">
+    <row r="688">
+      <c r="A688" t="inlineStr">
         <is>
           <t xml:space="preserve">「卒業おめでとう」مبروك التخرج
 マブルーク・タカッルジ [mabruuk a^taKharruj]
@@ -14943,19 +14923,19 @@
 2308 https://instagram.com/fatoomworld </t>
         </is>
       </c>
-      <c r="B689" t="inlineStr">
+      <c r="B688" t="inlineStr">
         <is>
           <t>images/「卒業おめでとう」_img1.jpg</t>
         </is>
       </c>
-      <c r="C689" t="inlineStr">
+      <c r="C688" t="inlineStr">
         <is>
           <t>卒業 ,イラスト</t>
         </is>
       </c>
     </row>
-    <row r="690">
-      <c r="A690" t="inlineStr">
+    <row r="689">
+      <c r="A689" t="inlineStr">
         <is>
           <t xml:space="preserve">「停止距離の計算」
 حساب مسافة التوقف
@@ -14965,19 +14945,19 @@
 2109 assurance-auto-info </t>
         </is>
       </c>
-      <c r="B690" t="inlineStr">
+      <c r="B689" t="inlineStr">
         <is>
           <t>images/「停止距離の計算」_img1.jpg</t>
         </is>
       </c>
-      <c r="C690" t="inlineStr">
+      <c r="C689" t="inlineStr">
         <is>
           <t>保険 ,自動車</t>
         </is>
       </c>
     </row>
-    <row r="691">
-      <c r="A691" t="inlineStr">
+    <row r="690">
+      <c r="A690" t="inlineStr">
         <is>
           <t xml:space="preserve">「教師要らず：10日でフランス語会話」
 بدون معلم
@@ -14987,19 +14967,19 @@
 2308 englais-best com </t>
         </is>
       </c>
-      <c r="B691" t="inlineStr">
+      <c r="B690" t="inlineStr">
         <is>
           <t>images/「教師要らず：10日でフランス語会話」_img1.jpg</t>
         </is>
       </c>
-      <c r="C691" t="inlineStr">
+      <c r="C690" t="inlineStr">
         <is>
           <t>教師なし学習</t>
         </is>
       </c>
     </row>
-    <row r="692">
-      <c r="A692" t="inlineStr">
+    <row r="691">
+      <c r="A691" t="inlineStr">
         <is>
           <t xml:space="preserve">「衝突」تصادم
 タサードゥム [ta_saadum]
@@ -15008,19 +14988,19 @@
 1810 </t>
         </is>
       </c>
-      <c r="B692" t="inlineStr">
+      <c r="B691" t="inlineStr">
         <is>
           <t>images/「衝突」_img1.jpg</t>
         </is>
       </c>
-      <c r="C692" t="inlineStr">
+      <c r="C691" t="inlineStr">
         <is>
           <t>あらびあや</t>
         </is>
       </c>
     </row>
-    <row r="693">
-      <c r="A693" t="inlineStr">
+    <row r="692">
+      <c r="A692" t="inlineStr">
         <is>
           <t xml:space="preserve">「楽観主義」تَفَاؤُلٌ
 タファーウル [tafaa'ul(un)]
@@ -15029,19 +15009,19 @@
 1904 arabictypography com </t>
         </is>
       </c>
-      <c r="B693" t="inlineStr">
+      <c r="B692" t="inlineStr">
         <is>
           <t>images/「楽観主義」_img1.jpg</t>
         </is>
       </c>
-      <c r="C693" t="inlineStr">
+      <c r="C692" t="inlineStr">
         <is>
           <t>やわらか ,緑</t>
         </is>
       </c>
     </row>
-    <row r="694">
-      <c r="A694" t="inlineStr">
+    <row r="693">
+      <c r="A693" t="inlineStr">
         <is>
           <t xml:space="preserve">「シベリアジャコウジカは、絶滅の危機にあると見なされている」
 يعد "أيل المسك السيبيري" مهددًا بالانقراض
@@ -15049,19 +15029,19 @@
 2308 https://twitter.com/NatGeoMagArab/status/1320666649045790720 </t>
         </is>
       </c>
-      <c r="B694" t="inlineStr">
+      <c r="B693" t="inlineStr">
         <is>
           <t>images/「シベリアジャコウジカは、絶滅の危機に_img1.jpg,images/「シベリアジャコウジカは、絶滅の危機に_img2.jpg</t>
         </is>
       </c>
-      <c r="C694" t="inlineStr">
+      <c r="C693" t="inlineStr">
         <is>
           <t>手書き語学 ,シベリア</t>
         </is>
       </c>
     </row>
-    <row r="695">
-      <c r="A695" t="inlineStr">
+    <row r="694">
+      <c r="A694" t="inlineStr">
         <is>
           <t xml:space="preserve">「融合／折衷／フュージョン」
 انصهار
@@ -15070,38 +15050,38 @@
 1811 elmahdyart Instagram </t>
         </is>
       </c>
-      <c r="B695" t="inlineStr">
+      <c r="B694" t="inlineStr">
         <is>
           <t>images/「融合／折衷／フュージョン」_img1.jpg</t>
         </is>
       </c>
-      <c r="C695" t="inlineStr">
+      <c r="C694" t="inlineStr">
         <is>
           <t>カリグラフィー ,書道</t>
         </is>
       </c>
     </row>
-    <row r="696">
-      <c r="A696" t="inlineStr">
+    <row r="695">
+      <c r="A695" t="inlineStr">
         <is>
           <t xml:space="preserve">「この子供は、昼寝をしようとする母親を邪魔しているようだ」
 「場所はインドのトラ保護区、バンダウガル公園。トラは生態ピラミッドのトップの捕食動物だが、最もリスクの高い絶滅危惧種のひとつである」
 2308 https://twitter.com/natgeomagarab/status/1553681890665586689 </t>
         </is>
       </c>
-      <c r="B696" t="inlineStr">
+      <c r="B695" t="inlineStr">
         <is>
           <t>images/「この子供は、昼寝をしようとする母親を_img1.jpg,images/「この子供は、昼寝をしようとする母親を_img2.jpg</t>
         </is>
       </c>
-      <c r="C696" t="inlineStr">
+      <c r="C695" t="inlineStr">
         <is>
           <t>手書き語学 ,アラビア語 ,トラ</t>
         </is>
       </c>
     </row>
-    <row r="697">
-      <c r="A697" t="inlineStr">
+    <row r="696">
+      <c r="A696" t="inlineStr">
         <is>
           <t xml:space="preserve">「もし敬意が落ちたら、それと一緒に全部落ちるのだ」
 إن سقط الإحترام سقط معه كل شيء
@@ -15110,19 +15090,19 @@
 2109 出典不明 </t>
         </is>
       </c>
-      <c r="B697" t="inlineStr">
+      <c r="B696" t="inlineStr">
         <is>
           <t>images/「もし敬意が落ちたら、それと一緒に全部_img1.jpg</t>
         </is>
       </c>
-      <c r="C697" t="inlineStr">
+      <c r="C696" t="inlineStr">
         <is>
           <t>リスペクト ,落書き</t>
         </is>
       </c>
     </row>
-    <row r="698">
-      <c r="A698" t="inlineStr">
+    <row r="697">
+      <c r="A697" t="inlineStr">
         <is>
           <t xml:space="preserve">「エジプト特許庁」
 مكتب براءات الاختراع المصرى
@@ -15132,19 +15112,19 @@
 2312 </t>
         </is>
       </c>
-      <c r="B698" t="inlineStr">
+      <c r="B697" t="inlineStr">
         <is>
           <t>images/「エジプト特許庁」_img1.jpg</t>
         </is>
       </c>
-      <c r="C698" t="inlineStr">
+      <c r="C697" t="inlineStr">
         <is>
           <t>patent</t>
         </is>
       </c>
     </row>
-    <row r="699">
-      <c r="A699" t="inlineStr">
+    <row r="698">
+      <c r="A698" t="inlineStr">
         <is>
           <t xml:space="preserve">「選挙」إنتخابات
 インティカーバート [intiKhaabaat]
@@ -15153,19 +15133,19 @@
 2311 nna-leb gov lb </t>
         </is>
       </c>
-      <c r="B699" t="inlineStr">
+      <c r="B698" t="inlineStr">
         <is>
           <t>images/「選挙」_img1.jpg</t>
         </is>
       </c>
-      <c r="C699" t="inlineStr">
+      <c r="C698" t="inlineStr">
         <is>
           <t>選挙 ,投票</t>
         </is>
       </c>
     </row>
-    <row r="700">
-      <c r="A700" t="inlineStr">
+    <row r="699">
+      <c r="A699" t="inlineStr">
         <is>
           <t xml:space="preserve">「待ちぼうけ」إنتظار
 インティザール [inti_Dhaar]
@@ -15174,19 +15154,19 @@
 1809 in4sser.tumblr </t>
         </is>
       </c>
-      <c r="B700" t="inlineStr">
+      <c r="B699" t="inlineStr">
         <is>
           <t>images/「待ちぼうけ」_img1.jpg</t>
         </is>
       </c>
-      <c r="C700" t="inlineStr">
+      <c r="C699" t="inlineStr">
         <is>
           <t>遅すぎ ,辛抱</t>
         </is>
       </c>
     </row>
-    <row r="701">
-      <c r="A701" t="inlineStr">
+    <row r="700">
+      <c r="A700" t="inlineStr">
         <is>
           <t xml:space="preserve">「試験」إختبار
 イクティバール [iKhtibaar]
@@ -15195,19 +15175,19 @@
 2109 出典不明 </t>
         </is>
       </c>
-      <c r="B701" t="inlineStr">
+      <c r="B700" t="inlineStr">
         <is>
           <t>images/「試験」_img1.jpg</t>
         </is>
       </c>
-      <c r="C701" t="inlineStr">
+      <c r="C700" t="inlineStr">
         <is>
           <t>テスト ,考査</t>
         </is>
       </c>
     </row>
-    <row r="702">
-      <c r="A702" t="inlineStr">
+    <row r="701">
+      <c r="A701" t="inlineStr">
         <is>
           <t xml:space="preserve">「チャンネル登録」اشتراك
 イシティラーク [iShtiraak]
@@ -15216,19 +15196,19 @@
 2308 </t>
         </is>
       </c>
-      <c r="B702" t="inlineStr">
+      <c r="B701" t="inlineStr">
         <is>
           <t>images/「チャンネル登録」_img1.jpg</t>
         </is>
       </c>
-      <c r="C702" t="inlineStr">
+      <c r="C701" t="inlineStr">
         <is>
           <t>Subscribe ,YouTube</t>
         </is>
       </c>
     </row>
-    <row r="703">
-      <c r="A703" t="inlineStr">
+    <row r="702">
+      <c r="A702" t="inlineStr">
         <is>
           <t xml:space="preserve">「スマイル」ابتسام
 イブティサーム [ibtisaam]
@@ -15236,37 +15216,37 @@
 1903 behance Written-Visuals </t>
         </is>
       </c>
+      <c r="B702" t="inlineStr">
+        <is>
+          <t>images/「スマイル」_img1.jpg</t>
+        </is>
+      </c>
+      <c r="C702" t="inlineStr">
+        <is>
+          <t>スマイリー ,ツ</t>
+        </is>
+      </c>
+    </row>
+    <row r="703">
+      <c r="A703" t="inlineStr">
+        <is>
+          <t xml:space="preserve">「身体の一部として…」
+2308 https://twitter.com/NatGeoMagArab/status/1528292080337813504 </t>
+        </is>
+      </c>
       <c r="B703" t="inlineStr">
         <is>
-          <t>images/「スマイル」_img1.jpg</t>
+          <t>images/「身体の一部として…」_img1.jpg</t>
         </is>
       </c>
       <c r="C703" t="inlineStr">
         <is>
-          <t>スマイリー ,ツ</t>
+          <t>手書き語学 ,カンガルー</t>
         </is>
       </c>
     </row>
     <row r="704">
       <c r="A704" t="inlineStr">
-        <is>
-          <t xml:space="preserve">「身体の一部として…」
-2308 https://twitter.com/NatGeoMagArab/status/1528292080337813504 </t>
-        </is>
-      </c>
-      <c r="B704" t="inlineStr">
-        <is>
-          <t>images/「身体の一部として…」_img1.jpg</t>
-        </is>
-      </c>
-      <c r="C704" t="inlineStr">
-        <is>
-          <t>手書き語学 ,カンガルー</t>
-        </is>
-      </c>
-    </row>
-    <row r="705">
-      <c r="A705" t="inlineStr">
         <is>
           <t xml:space="preserve">「ディスカバリー」إكتشاف
 イクティシャーフ [iktiShaaf]
@@ -15274,19 +15254,19 @@
 2308 tephanegabrielli com </t>
         </is>
       </c>
-      <c r="B705" t="inlineStr">
+      <c r="B704" t="inlineStr">
         <is>
           <t>images/「ディスカバリー」_img1.jpg</t>
         </is>
       </c>
-      <c r="C705" t="inlineStr">
+      <c r="C704" t="inlineStr">
         <is>
           <t>discovery ,デザイン</t>
         </is>
       </c>
     </row>
-    <row r="706">
-      <c r="A706" t="inlineStr">
+    <row r="705">
+      <c r="A705" t="inlineStr">
         <is>
           <t xml:space="preserve">「重力波の発見は新しい窓を開いた」
 فتَح اكتشاف موجات الجاذبية نافذة جديدة
@@ -15294,19 +15274,19 @@
 2308 https://twitter.com/SciTalk2U/status/1454891943440289793 </t>
         </is>
       </c>
-      <c r="B706" t="inlineStr">
+      <c r="B705" t="inlineStr">
         <is>
           <t>images/「重力波の発見は新しい窓を開いた」_img1.jpg</t>
         </is>
       </c>
-      <c r="C706" t="inlineStr">
+      <c r="C705" t="inlineStr">
         <is>
           <t>手書き語学 ,アラビア語 ,重力波</t>
         </is>
       </c>
     </row>
-    <row r="707">
-      <c r="A707" t="inlineStr">
+    <row r="706">
+      <c r="A706" t="inlineStr">
         <is>
           <t xml:space="preserve">「微笑みに微笑み。先にした人の方が美しい」
 الإبتسامة بالإبتسامة والبادئ أجمل
@@ -15315,19 +15295,19 @@
 2104 出典不明 </t>
         </is>
       </c>
-      <c r="B707" t="inlineStr">
+      <c r="B706" t="inlineStr">
         <is>
           <t>images/「微笑みに微笑み。先にした人の方が美し_img1.jpg,images/「微笑みに微笑み。先にした人の方が美し_img2.jpg</t>
         </is>
       </c>
-      <c r="C707" t="inlineStr">
+      <c r="C706" t="inlineStr">
         <is>
           <t>スマイル ,名言</t>
         </is>
       </c>
     </row>
-    <row r="708">
-      <c r="A708" t="inlineStr">
+    <row r="707">
+      <c r="A707" t="inlineStr">
         <is>
           <t xml:space="preserve">「笑顔」ابتسامة
 イブティサーマ [ibtisaama(tun)]
@@ -15336,19 +15316,19 @@
 2308 satokomatsu, minne </t>
         </is>
       </c>
-      <c r="B708" t="inlineStr">
+      <c r="B707" t="inlineStr">
         <is>
           <t>images/「笑顔」_img1.jpg</t>
         </is>
       </c>
-      <c r="C708" t="inlineStr">
+      <c r="C707" t="inlineStr">
         <is>
           <t>スマイル ,ツ</t>
         </is>
       </c>
     </row>
-    <row r="709">
-      <c r="A709" t="inlineStr">
+    <row r="708">
+      <c r="A708" t="inlineStr">
         <is>
           <t xml:space="preserve">「信仰」ايمان
 イーマーン ['iimaan]
@@ -15357,19 +15337,19 @@
 2506 instagram com/p/6ST-WHOOkJ/ </t>
         </is>
       </c>
-      <c r="B709" t="inlineStr">
+      <c r="B708" t="inlineStr">
         <is>
           <t>images/「信仰」_img1.jpg</t>
         </is>
       </c>
-      <c r="C709" t="inlineStr">
+      <c r="C708" t="inlineStr">
         <is>
           <t>宗教 ,信念</t>
         </is>
       </c>
     </row>
-    <row r="710">
-      <c r="A710" t="inlineStr">
+    <row r="709">
+      <c r="A709" t="inlineStr">
         <is>
           <t xml:space="preserve">「放送」إذاعة
 イザーア ['iDhaa*a]
@@ -15378,19 +15358,19 @@
 2404 heemades, Instagram </t>
         </is>
       </c>
-      <c r="B710" t="inlineStr">
+      <c r="B709" t="inlineStr">
         <is>
           <t>images/「放送」_img1.jpg</t>
         </is>
       </c>
-      <c r="C710" t="inlineStr">
+      <c r="C709" t="inlineStr">
         <is>
           <t>デザイン ,ラジオ</t>
         </is>
       </c>
     </row>
-    <row r="711">
-      <c r="A711" t="inlineStr">
+    <row r="710">
+      <c r="A710" t="inlineStr">
         <is>
           <t xml:space="preserve">「かきとりのちから」
 مهاراتي الإملائية
@@ -15399,19 +15379,19 @@
 2308 iqrawaoktoub.wordpress com </t>
         </is>
       </c>
-      <c r="B711" t="inlineStr">
+      <c r="B710" t="inlineStr">
         <is>
           <t>images/「かきとりのちから」_img1.jpg</t>
         </is>
       </c>
-      <c r="C711" t="inlineStr">
+      <c r="C710" t="inlineStr">
         <is>
           <t>国語 ,教材</t>
         </is>
       </c>
     </row>
-    <row r="712">
-      <c r="A712" t="inlineStr">
+    <row r="711">
+      <c r="A711" t="inlineStr">
         <is>
           <t xml:space="preserve">「歴史を作った男たち」
 رجال صنعوا التاريخ
@@ -15421,38 +15401,38 @@
 2410 https://x.gd/Wl5rJ </t>
         </is>
       </c>
-      <c r="B712" t="inlineStr">
+      <c r="B711" t="inlineStr">
         <is>
           <t>images/「歴史を作った男たち」_img1.jpg</t>
         </is>
       </c>
-      <c r="C712" t="inlineStr">
+      <c r="C711" t="inlineStr">
         <is>
           <t>偉人</t>
         </is>
       </c>
     </row>
-    <row r="713">
-      <c r="A713" t="inlineStr">
+    <row r="712">
+      <c r="A712" t="inlineStr">
         <is>
           <t xml:space="preserve">「無限の宇宙を旅した光」
 「何百年もの末にジェイムズ・ウェッブ望遠鏡のレンズの上に落ち、我々に遠い宇宙の美しさを見せてくれる。最も純粋な形と最も素晴らしい姿で」
 2308 https://twitter.com/NatGeoMagArab/status/1557811592636485632 </t>
         </is>
       </c>
-      <c r="B713" t="inlineStr">
+      <c r="B712" t="inlineStr">
         <is>
           <t>images/「無限の宇宙を旅した光」_img1.jpg</t>
         </is>
       </c>
-      <c r="C713" t="inlineStr">
+      <c r="C712" t="inlineStr">
         <is>
           <t>手書き語学 ,宇宙</t>
         </is>
       </c>
     </row>
-    <row r="714">
-      <c r="A714" t="inlineStr">
+    <row r="713">
+      <c r="A713" t="inlineStr">
         <is>
           <t xml:space="preserve">「日本好きになり行きたくなる20項」
 عشرون شيئا يجعلك تحب اليابان وترغب في زيارتها
@@ -15461,19 +15441,19 @@
 2308 wattpad </t>
         </is>
       </c>
-      <c r="B714" t="inlineStr">
+      <c r="B713" t="inlineStr">
         <is>
           <t>images/「日本好きになり行きたくなる20項」_img1.jpg</t>
         </is>
       </c>
-      <c r="C714" t="inlineStr">
+      <c r="C713" t="inlineStr">
         <is>
           <t>اليابان ,Japan</t>
         </is>
       </c>
     </row>
-    <row r="715">
-      <c r="A715" t="inlineStr">
+    <row r="714">
+      <c r="A714" t="inlineStr">
         <is>
           <t xml:space="preserve">「ピッタリの瞬間に撮影され、ドラゴンが火を噴いているように見える」
 التُقطت في اللحظة المناسبة لتبدو مثل تنين ينفث اللهب
@@ -15481,19 +15461,19 @@
 2509 https://twitter.com/NatGeoMagArab/status/1588780660269150208 </t>
         </is>
       </c>
-      <c r="B715" t="inlineStr">
+      <c r="B714" t="inlineStr">
         <is>
           <t>images/「ピッタリの瞬間に撮影され、ドラゴンが_img1.jpg,images/ 「ピッタリの瞬間に撮影され、ドラゴンが_img2.jpg</t>
         </is>
       </c>
-      <c r="C715" t="inlineStr">
+      <c r="C714" t="inlineStr">
         <is>
           <t xml:space="preserve">ドラゴン </t>
         </is>
       </c>
     </row>
-    <row r="716">
-      <c r="A716" t="inlineStr">
+    <row r="715">
+      <c r="A715" t="inlineStr">
         <is>
           <t xml:space="preserve">「満足は不滅の宝である」
 القَناعَةُ كنز لا يَفنَى
@@ -15503,55 +15483,55 @@
 2308 kareem mrghani </t>
         </is>
       </c>
+      <c r="B715" t="inlineStr">
+        <is>
+          <t>images/「満足は不滅の宝である」_img1.jpg</t>
+        </is>
+      </c>
+      <c r="C715" t="inlineStr">
+        <is>
+          <t>幸福度</t>
+        </is>
+      </c>
+    </row>
+    <row r="716">
+      <c r="A716" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ゴシキセイガイインコ。
+2409 https://twitter.com/NatGeoMagArab/status/1600022262014676992 </t>
+        </is>
+      </c>
       <c r="B716" t="inlineStr">
         <is>
-          <t>images/「満足は不滅の宝である」_img1.jpg</t>
+          <t>images/ゴシキセイガイインコ。_img1.jpg</t>
         </is>
       </c>
       <c r="C716" t="inlineStr">
         <is>
-          <t>幸福度</t>
+          <t>手書き語学 ,アラビア語,オウム</t>
         </is>
       </c>
     </row>
     <row r="717">
       <c r="A717" t="inlineStr">
         <is>
-          <t xml:space="preserve">ゴシキセイガイインコ。
-2409 https://twitter.com/NatGeoMagArab/status/1600022262014676992 </t>
+          <t xml:space="preserve">モモンガ。
+2403 https://twitter.com/NatGeoMagArab/status/1552541872966344704 </t>
         </is>
       </c>
       <c r="B717" t="inlineStr">
         <is>
-          <t>images/ゴシキセイガイインコ。_img1.jpg</t>
+          <t>images/モモンガ。_img1.jpg,images/ モモンガ。_img2.jpg</t>
         </is>
       </c>
       <c r="C717" t="inlineStr">
         <is>
-          <t>手書き語学 ,アラビア語,オウム</t>
+          <t>手書き語学 ,アラビア語 ,モモンガ</t>
         </is>
       </c>
     </row>
     <row r="718">
       <c r="A718" t="inlineStr">
-        <is>
-          <t xml:space="preserve">モモンガ。
-2403 https://twitter.com/NatGeoMagArab/status/1552541872966344704 </t>
-        </is>
-      </c>
-      <c r="B718" t="inlineStr">
-        <is>
-          <t>images/モモンガ。_img1.jpg,images/ モモンガ。_img2.jpg</t>
-        </is>
-      </c>
-      <c r="C718" t="inlineStr">
-        <is>
-          <t>手書き語学 ,アラビア語 ,モモンガ</t>
-        </is>
-      </c>
-    </row>
-    <row r="719">
-      <c r="A719" t="inlineStr">
         <is>
           <t xml:space="preserve">「象の群れ。ドローンの音から逃げている」
 قطيع من الفيلة يفر هاربًا من صوت الدرون
@@ -15563,56 +15543,56 @@
 2009 https://twitter.com/NatGeoMagArab/status/1302970033627258881 </t>
         </is>
       </c>
+      <c r="B718" t="inlineStr">
+        <is>
+          <t>images/「象の群れ。ドローンの音から逃げている.jpg</t>
+        </is>
+      </c>
+      <c r="C718" t="inlineStr">
+        <is>
+          <t>ゾウ ,ドローン</t>
+        </is>
+      </c>
+    </row>
+    <row r="719">
+      <c r="A719" t="inlineStr">
+        <is>
+          <t xml:space="preserve">カルマン線。
+2308 https://twitter.com/NatGeoMagArab/status/1536436999522881536 </t>
+        </is>
+      </c>
       <c r="B719" t="inlineStr">
         <is>
-          <t>images/「象の群れ。ドローンの音から逃げている.jpg</t>
+          <t>images/カルマン線。_img1.jpg</t>
         </is>
       </c>
       <c r="C719" t="inlineStr">
         <is>
-          <t>ゾウ ,ドローン</t>
+          <t xml:space="preserve">手書き語学 ,アラビア語 ,宇宙 </t>
         </is>
       </c>
     </row>
     <row r="720">
       <c r="A720" t="inlineStr">
-        <is>
-          <t xml:space="preserve">カルマン線。
-2308 https://twitter.com/NatGeoMagArab/status/1536436999522881536 </t>
-        </is>
-      </c>
-      <c r="B720" t="inlineStr">
-        <is>
-          <t>images/カルマン線。_img1.jpg</t>
-        </is>
-      </c>
-      <c r="C720" t="inlineStr">
-        <is>
-          <t xml:space="preserve">手書き語学 ,アラビア語 ,宇宙 </t>
-        </is>
-      </c>
-    </row>
-    <row r="721">
-      <c r="A721" t="inlineStr">
         <is>
           <t xml:space="preserve">「恥ずかしがり屋のマヌルネコと暖かい朝の太陽光線」
 ⁦「二つの美しいもの」[Shay'-ayni jamiil-ayni] 属格：「物」( شيء )[Shay']・「美しい」( جميل )[jamiil]⁩
 2309 https://twitter.com/NatGeoMagArab/status/1697512148820504912 </t>
         </is>
       </c>
-      <c r="B721" t="inlineStr">
+      <c r="B720" t="inlineStr">
         <is>
           <t>images/「恥ずかしがり屋のマヌルネコと暖かい朝_img1.jpg</t>
         </is>
       </c>
-      <c r="C721" t="inlineStr">
+      <c r="C720" t="inlineStr">
         <is>
           <t>手書き語学 ,アラビア語 ,マヌルネコ</t>
         </is>
       </c>
     </row>
-    <row r="722">
-      <c r="A722" t="inlineStr">
+    <row r="721">
+      <c r="A721" t="inlineStr">
         <is>
           <t xml:space="preserve">「二回失敗しているペンギン」
 بطريق يفشل مرتين
@@ -15622,19 +15602,19 @@
 2308 https://twitter.com/NatGeoMagArab/status/1479483133766426626 </t>
         </is>
       </c>
-      <c r="B722" t="inlineStr">
+      <c r="B721" t="inlineStr">
         <is>
           <t>images/「二回失敗しているペンギン」_img1.jpg</t>
         </is>
       </c>
-      <c r="C722" t="inlineStr">
+      <c r="C721" t="inlineStr">
         <is>
           <t>ペンギン ,動物</t>
         </is>
       </c>
     </row>
-    <row r="723">
-      <c r="A723" t="inlineStr">
+    <row r="722">
+      <c r="A722" t="inlineStr">
         <is>
           <t xml:space="preserve">「2億光年の彼方できらめく炎と光」
 وهج ووميض يتلألأ على بعد 200 مليون سنة ضوئية
@@ -15645,15 +15625,15 @@
 2010 https://twitter.com/NatGeoMagArab/status/1303415502673342464 </t>
         </is>
       </c>
-      <c r="B723" t="inlineStr"/>
-      <c r="C723" t="inlineStr">
+      <c r="B722" t="inlineStr"/>
+      <c r="C722" t="inlineStr">
         <is>
           <t>宇宙 ,銀河</t>
         </is>
       </c>
     </row>
-    <row r="724">
-      <c r="A724" t="inlineStr">
+    <row r="723">
+      <c r="A723" t="inlineStr">
         <is>
           <t xml:space="preserve">「さまよう黒猫」قطة سوداء تجوب
 キッタトゥン・サウダーウ・タジューブ [qi^_tatun sawdaa'u ta-juub]
@@ -15662,19 +15642,19 @@
 2308 https://twitter.com/NatGeoMagArab/status/1532973177453760512 </t>
         </is>
       </c>
-      <c r="B724" t="inlineStr">
+      <c r="B723" t="inlineStr">
         <is>
           <t>images/「さまよう黒猫」_img1.jpg,images/ 「さまよう黒猫」_img2.jpg</t>
         </is>
       </c>
-      <c r="C724" t="inlineStr">
+      <c r="C723" t="inlineStr">
         <is>
           <t xml:space="preserve">手書き語学 ,モロッコ </t>
         </is>
       </c>
     </row>
-    <row r="725">
-      <c r="A725" t="inlineStr">
+    <row r="724">
+      <c r="A724" t="inlineStr">
         <is>
           <t xml:space="preserve">「サイのざらざらした皮を利用して自分の体を掻くネコ」
 قطة تستغل جلد الكركدن الخشن لحك جسدها
@@ -15683,19 +15663,19 @@
 2308 https://twitter.com/NatGeoMagArab/status/1476855740929216517 </t>
         </is>
       </c>
-      <c r="B725" t="inlineStr">
+      <c r="B724" t="inlineStr">
         <is>
           <t>images/「サイのざらざらした皮を利用して自分の_img1.jpg</t>
         </is>
       </c>
-      <c r="C725" t="inlineStr">
+      <c r="C724" t="inlineStr">
         <is>
           <t>サイ ,チェコ</t>
         </is>
       </c>
     </row>
-    <row r="726">
-      <c r="A726" t="inlineStr">
+    <row r="725">
+      <c r="A725" t="inlineStr">
         <is>
           <t xml:space="preserve">「沈まぬ太陽」شمس لا تغيب
 シャムス・ラー・タギーブ [Shams laa ta-Ghiib]
@@ -15704,19 +15684,19 @@
 2308 AHMED ELASSAL </t>
         </is>
       </c>
-      <c r="B726" t="inlineStr">
+      <c r="B725" t="inlineStr">
         <is>
           <t>images/「沈まぬ太陽」_img1.jpg</t>
         </is>
       </c>
-      <c r="C726" t="inlineStr">
+      <c r="C725" t="inlineStr">
         <is>
           <t>帝国 ,白夜</t>
         </is>
       </c>
     </row>
-    <row r="727">
-      <c r="A727" t="inlineStr">
+    <row r="726">
+      <c r="A726" t="inlineStr">
         <is>
           <t xml:space="preserve">「子供に食べさせている忍耐強い母親」
 أم صبورة تطعم صغيرها
@@ -15725,19 +15705,19 @@
 2308 https://twitter.com/natgeomagarab/status/1585572054509957120 </t>
         </is>
       </c>
-      <c r="B727" t="inlineStr">
+      <c r="B726" t="inlineStr">
         <is>
           <t>images/「子供に食べさせている忍耐強い母親」_img1.jpg</t>
         </is>
       </c>
-      <c r="C727" t="inlineStr">
+      <c r="C726" t="inlineStr">
         <is>
           <t>手書き語学 ,アラビア語 ,ミヤコドリ</t>
         </is>
       </c>
     </row>
-    <row r="728">
-      <c r="A728" t="inlineStr">
+    <row r="727">
+      <c r="A727" t="inlineStr">
         <is>
           <t xml:space="preserve">「コーヒーは繰り返さない恋物語」
 القهوة قصة عشق لن تتكرر
@@ -15747,19 +15727,19 @@
 2403 pin it/7tvd8Wc </t>
         </is>
       </c>
-      <c r="B728" t="inlineStr">
+      <c r="B727" t="inlineStr">
         <is>
           <t>images/「コーヒーは繰り返さない恋物語」_img1.jpg</t>
         </is>
       </c>
-      <c r="C728" t="inlineStr">
+      <c r="C727" t="inlineStr">
         <is>
           <t>コーヒー ,名言</t>
         </is>
       </c>
     </row>
-    <row r="729">
-      <c r="A729" t="inlineStr">
+    <row r="728">
+      <c r="A728" t="inlineStr">
         <is>
           <t xml:space="preserve">「星々で飾られた空。魅惑的な色合いで黄昏の美を満たしている」
 سماء مرصعة بالنجوم تضفي لمسة سحرية على جمال الشفق
@@ -15767,19 +15747,19 @@
 2010 https://twitter.com/NatGeoMagArab/status/1303777701975584768 </t>
         </is>
       </c>
-      <c r="B729" t="inlineStr">
+      <c r="B728" t="inlineStr">
         <is>
           <t>images/「星々で飾られた空。魅惑的な色合いで黄.png</t>
         </is>
       </c>
-      <c r="C729" t="inlineStr">
+      <c r="C728" t="inlineStr">
         <is>
           <t>星空 ,宇宙</t>
         </is>
       </c>
     </row>
-    <row r="730">
-      <c r="A730" t="inlineStr">
+    <row r="729">
+      <c r="A729" t="inlineStr">
         <is>
           <t xml:space="preserve">「国際宇宙ステーションからの写真。巨大な台風『ハイシェン（海神）』を映している」
 لقطات من محطة الفضاء الدولية تظهر إعصار "هايشن" الهائل
@@ -15787,19 +15767,19 @@
 2403 https://twitter.com/NatGeoMagArab/status/1302871968522235904 </t>
         </is>
       </c>
-      <c r="B730" t="inlineStr">
+      <c r="B729" t="inlineStr">
         <is>
           <t>images/「国際宇宙ステーションからの写真。巨大.png</t>
         </is>
       </c>
-      <c r="C730" t="inlineStr">
+      <c r="C729" t="inlineStr">
         <is>
           <t>台風</t>
         </is>
       </c>
     </row>
-    <row r="731">
-      <c r="A731" t="inlineStr">
+    <row r="730">
+      <c r="A730" t="inlineStr">
         <is>
           <t xml:space="preserve">「草を食む幸運な子羊たち」
 خراف محظوظة ترعى
@@ -15809,19 +15789,19 @@
 2308 https://twitter.com/NatGeoMagArab/status/1490211393554972676 </t>
         </is>
       </c>
-      <c r="B731" t="inlineStr">
+      <c r="B730" t="inlineStr">
         <is>
           <t>images/「草を食む幸運な子羊たち」_img1.jpg,images/ 「草を食む幸運な子羊たち」_img2.jpg</t>
         </is>
       </c>
-      <c r="C731" t="inlineStr">
+      <c r="C730" t="inlineStr">
         <is>
           <t>羊 ,アイルランド</t>
         </is>
       </c>
     </row>
-    <row r="732">
-      <c r="A732" t="inlineStr">
+    <row r="731">
+      <c r="A731" t="inlineStr">
         <is>
           <t xml:space="preserve">「お金で買えぬ10のもの」
 ١٠ أشياء لا تشترى بالمال
@@ -15831,19 +15811,19 @@
 2308 ayb124 </t>
         </is>
       </c>
-      <c r="B732" t="inlineStr">
+      <c r="B731" t="inlineStr">
         <is>
           <t>images/「お金で買えぬ10のもの」_img1.jpg</t>
         </is>
       </c>
-      <c r="C732" t="inlineStr">
+      <c r="C731" t="inlineStr">
         <is>
           <t>価値 ,購買</t>
         </is>
       </c>
     </row>
-    <row r="733">
-      <c r="A733" t="inlineStr">
+    <row r="732">
+      <c r="A732" t="inlineStr">
         <is>
           <t xml:space="preserve">「お金では買えないよ」
 هي أشْيَاءٌ لا تُشْتَرَى
@@ -15853,19 +15833,19 @@
 1906 mardy_zaawely, Instagram </t>
         </is>
       </c>
-      <c r="B733" t="inlineStr">
+      <c r="B732" t="inlineStr">
         <is>
           <t>images/「お金では買えないよ」_img1.jpg</t>
         </is>
       </c>
-      <c r="C733" t="inlineStr">
+      <c r="C732" t="inlineStr">
         <is>
           <t>マスターカード ,価値</t>
         </is>
       </c>
     </row>
-    <row r="734">
-      <c r="A734" t="inlineStr">
+    <row r="733">
+      <c r="A733" t="inlineStr">
         <is>
           <t xml:space="preserve">「好奇心旺盛なホッキョクギツネ」
 ثعلب قطبي يملؤه الفضول
@@ -15875,15 +15855,15 @@
 2308 https://twitter.com/natgeomagarab/status/1157592172968808449 </t>
         </is>
       </c>
-      <c r="B734" t="inlineStr"/>
-      <c r="C734" t="inlineStr">
+      <c r="B733" t="inlineStr"/>
+      <c r="C733" t="inlineStr">
         <is>
           <t>ファーストコンタクト ,キツネ</t>
         </is>
       </c>
     </row>
-    <row r="735">
-      <c r="A735" t="inlineStr">
+    <row r="734">
+      <c r="A734" t="inlineStr">
         <is>
           <t xml:space="preserve">「グレンダイザーのいる国は死にません」
 لنْ يَموتَ شَعبٌ لدَيهِ غرندايزر
@@ -15892,56 +15872,56 @@
 2308 https://www.aljarida.com/articles/1462241741574732100/ </t>
         </is>
       </c>
+      <c r="B734" t="inlineStr">
+        <is>
+          <t>images/「グレンダイザーのいる国は死にません」_img1.jpg</t>
+        </is>
+      </c>
+      <c r="C734" t="inlineStr">
+        <is>
+          <t>UFOロボ ,アニメ</t>
+        </is>
+      </c>
+    </row>
+    <row r="735">
+      <c r="A735" t="inlineStr">
+        <is>
+          <t xml:space="preserve">「凍結路面を運転中、彼女は嫌な場面に居合わせた」
+2408 https://twitter.com/NatGeoMagArab/status/1610305209657626625 </t>
+        </is>
+      </c>
       <c r="B735" t="inlineStr">
         <is>
-          <t>images/「グレンダイザーのいる国は死にません」_img1.jpg</t>
+          <t>images/「凍結路面を運転中、彼女は嫌な場面に居_img1.jpg</t>
         </is>
       </c>
       <c r="C735" t="inlineStr">
         <is>
-          <t>UFOロボ ,アニメ</t>
+          <t>手書き語学 ,アラビア語 ,路面凍結</t>
         </is>
       </c>
     </row>
     <row r="736">
       <c r="A736" t="inlineStr">
-        <is>
-          <t xml:space="preserve">「凍結路面を運転中、彼女は嫌な場面に居合わせた」
-2408 https://twitter.com/NatGeoMagArab/status/1610305209657626625 </t>
-        </is>
-      </c>
-      <c r="B736" t="inlineStr">
-        <is>
-          <t>images/「凍結路面を運転中、彼女は嫌な場面に居_img1.jpg</t>
-        </is>
-      </c>
-      <c r="C736" t="inlineStr">
-        <is>
-          <t>手書き語学 ,アラビア語 ,路面凍結</t>
-        </is>
-      </c>
-    </row>
-    <row r="737">
-      <c r="A737" t="inlineStr">
         <is>
           <t xml:space="preserve">「虹が美しさを加えている、アルパカという動物の美しいショット」
 ⁦「美しいショット」[laq_tatun jamiilatun]：「ショット」( لقطة )[laq_ta]：( ـلٌ )[-lun]・( ـقٌ )[-qun]・( ـطٌ )[-_tun]・( ـةٌ )[-tun]⁩
 2308 https://twitter.com/natgeomagarab/status/1155115655928004608 </t>
         </is>
       </c>
-      <c r="B737" t="inlineStr">
+      <c r="B736" t="inlineStr">
         <is>
           <t>images/「虹が美しさを加えている、アルパカとい_img1.jpg</t>
         </is>
       </c>
-      <c r="C737" t="inlineStr">
+      <c r="C736" t="inlineStr">
         <is>
           <t>モフモフ ,アルパカ</t>
         </is>
       </c>
     </row>
-    <row r="738">
-      <c r="A738" t="inlineStr">
+    <row r="737">
+      <c r="A737" t="inlineStr">
         <is>
           <t xml:space="preserve">「幸せは…全然思いもよらない所からやって来る」
 السعادة تأتينا من أماكن لم نكن نتوقعها أبداً
@@ -15950,19 +15930,19 @@
 2109 出典不明 </t>
         </is>
       </c>
-      <c r="B738" t="inlineStr">
+      <c r="B737" t="inlineStr">
         <is>
           <t>images/「幸せは…全然思いもよらない所からやっ_img1.jpg,images/ 「幸せは…全然思いもよらない所からやっ_img2.jpg</t>
         </is>
       </c>
-      <c r="C738" t="inlineStr">
+      <c r="C737" t="inlineStr">
         <is>
           <t>訪れ ,予想</t>
         </is>
       </c>
     </row>
-    <row r="739">
-      <c r="A739" t="inlineStr">
+    <row r="738">
+      <c r="A738" t="inlineStr">
         <is>
           <t xml:space="preserve">「あらゆる問題は、食べ物が解決してくれる」
 كل مشكلة ولها أكلة تحلها
@@ -15971,19 +15951,19 @@
 1909 ALQA AN 878 </t>
         </is>
       </c>
-      <c r="B739" t="inlineStr">
+      <c r="B738" t="inlineStr">
         <is>
           <t>images/「あらゆる問題は、食べ物が解決してくれ_img1.jpg</t>
         </is>
       </c>
-      <c r="C739" t="inlineStr">
+      <c r="C738" t="inlineStr">
         <is>
           <t>ストレス ,精神</t>
         </is>
       </c>
     </row>
-    <row r="740">
-      <c r="A740" t="inlineStr">
+    <row r="739">
+      <c r="A739" t="inlineStr">
         <is>
           <t xml:space="preserve">「冬で私が好きな物」
 أشياء أحبها بالشتاء
@@ -15993,19 +15973,19 @@
 2109 出典不明 </t>
         </is>
       </c>
-      <c r="B740" t="inlineStr">
+      <c r="B739" t="inlineStr">
         <is>
           <t>images/「冬で私が好きな物」_img1.jpg</t>
         </is>
       </c>
-      <c r="C740" t="inlineStr">
+      <c r="C739" t="inlineStr">
         <is>
           <t>季節 ,冬</t>
         </is>
       </c>
     </row>
-    <row r="741">
-      <c r="A741" t="inlineStr">
+    <row r="740">
+      <c r="A740" t="inlineStr">
         <is>
           <t xml:space="preserve">「お金で買うことの出来ない物」
 أشياء لا تستطيع شراءها بالمال
@@ -16015,19 +15995,19 @@
 2409 https://x.com/akhbarak/status/1038402708414373888 </t>
         </is>
       </c>
-      <c r="B741" t="inlineStr">
+      <c r="B740" t="inlineStr">
         <is>
           <t>images/「お金で買うことの出来ない物」_img1.jpg,images/ 「お金で買うことの出来ない物」_img2.jpg</t>
         </is>
       </c>
-      <c r="C741" t="inlineStr">
+      <c r="C740" t="inlineStr">
         <is>
           <t>ショッピング ,価値</t>
         </is>
       </c>
     </row>
-    <row r="742">
-      <c r="A742" t="inlineStr">
+    <row r="741">
+      <c r="A741" t="inlineStr">
         <is>
           <t xml:space="preserve">「私たちが愛する言葉」
 كلماتٌ نُحبّها
@@ -16037,19 +16017,19 @@
 2109 جليل خزعل </t>
         </is>
       </c>
-      <c r="B742" t="inlineStr">
+      <c r="B741" t="inlineStr">
         <is>
           <t>images/「私たちが愛する言葉」_img1.jpg</t>
         </is>
       </c>
-      <c r="C742" t="inlineStr">
+      <c r="C741" t="inlineStr">
         <is>
           <t>花 ,贈り物</t>
         </is>
       </c>
     </row>
-    <row r="743">
-      <c r="A743" t="inlineStr">
+    <row r="742">
+      <c r="A742" t="inlineStr">
         <is>
           <t xml:space="preserve">「お茶についてあなたが知らない10の事実」
 عشر معلومات لا تعرفها عن الشاي
@@ -16058,19 +16038,19 @@
 2012 http://ara.tv/6syq2 </t>
         </is>
       </c>
-      <c r="B743" t="inlineStr">
+      <c r="B742" t="inlineStr">
         <is>
           <t>images/「お茶についてあなたが知らない10の事_img1.jpg</t>
         </is>
       </c>
-      <c r="C743" t="inlineStr">
+      <c r="C742" t="inlineStr">
         <is>
           <t>神農</t>
         </is>
       </c>
     </row>
-    <row r="744">
-      <c r="A744" t="inlineStr">
+    <row r="743">
+      <c r="A743" t="inlineStr">
         <is>
           <t xml:space="preserve">「大きくなったウソ」
 الكذبة الّتي كبرت
@@ -16080,19 +16060,19 @@
 2509 سلسلة الحلزونة </t>
         </is>
       </c>
-      <c r="B744" t="inlineStr">
+      <c r="B743" t="inlineStr">
         <is>
           <t>images/「大きくなったウソ」_img1.jpg</t>
         </is>
       </c>
-      <c r="C744" t="inlineStr">
+      <c r="C743" t="inlineStr">
         <is>
           <t>絵本</t>
         </is>
       </c>
     </row>
-    <row r="745">
-      <c r="A745" t="inlineStr">
+    <row r="744">
+      <c r="A744" t="inlineStr">
         <is>
           <t xml:space="preserve">「自分に合った掃除機を買うには？」
 كيف تشتري المكنسة الكهربائية التي تناسبك؟
@@ -16101,19 +16081,19 @@
 2106 ts3a com </t>
         </is>
       </c>
-      <c r="B745" t="inlineStr">
+      <c r="B744" t="inlineStr">
         <is>
           <t>images/「自分に合った掃除機を買うには？」_img1.jpg</t>
         </is>
       </c>
-      <c r="C745" t="inlineStr">
+      <c r="C744" t="inlineStr">
         <is>
           <t>家電 ,掃除</t>
         </is>
       </c>
     </row>
-    <row r="746">
-      <c r="A746" t="inlineStr">
+    <row r="745">
+      <c r="A745" t="inlineStr">
         <is>
           <t xml:space="preserve">「仮にこれが批判の数としよう」
 لنفرض ان عدد الذين ينتقدونك
@@ -16124,19 +16104,19 @@
 2504 出典不明 </t>
         </is>
       </c>
-      <c r="B746" t="inlineStr">
+      <c r="B745" t="inlineStr">
         <is>
           <t>images/「仮にこれが批判の数としよう」_img1.jpg</t>
         </is>
       </c>
-      <c r="C746" t="inlineStr">
+      <c r="C745" t="inlineStr">
         <is>
           <t>アンチ</t>
         </is>
       </c>
     </row>
-    <row r="747">
-      <c r="A747" t="inlineStr">
+    <row r="746">
+      <c r="A746" t="inlineStr">
         <is>
           <t xml:space="preserve">「ここに見えるのは何？」
 ما الذي تراه هنا؟
@@ -16146,15 +16126,15 @@
 2204 https://twitter.com/NatGeoMagArab/status/1506933850617700352 </t>
         </is>
       </c>
-      <c r="B747" t="inlineStr"/>
-      <c r="C747" t="inlineStr">
+      <c r="B746" t="inlineStr"/>
+      <c r="C746" t="inlineStr">
         <is>
           <t xml:space="preserve">ペンギン </t>
         </is>
       </c>
     </row>
-    <row r="748">
-      <c r="A748" t="inlineStr">
+    <row r="747">
+      <c r="A747" t="inlineStr">
         <is>
           <t xml:space="preserve">「今日辛いこと、明日は平気だろう」
 ما يؤلم اليوم سيهون غدًا
@@ -16164,19 +16144,19 @@
 2308 basmahjeff </t>
         </is>
       </c>
-      <c r="B748" t="inlineStr">
+      <c r="B747" t="inlineStr">
         <is>
           <t>images/「今日辛いこと、明日は平気だろう」_img1.jpg</t>
         </is>
       </c>
-      <c r="C748" t="inlineStr">
+      <c r="C747" t="inlineStr">
         <is>
           <t>悩み ,達観</t>
         </is>
       </c>
     </row>
-    <row r="749">
-      <c r="A749" t="inlineStr">
+    <row r="748">
+      <c r="A748" t="inlineStr">
         <is>
           <t xml:space="preserve">「自分のすることを好きでなきゃ」
 عليك أن تحب ما تفعل
@@ -16185,19 +16165,19 @@
 1810 Ahmed Elhakeem </t>
         </is>
       </c>
-      <c r="B749" t="inlineStr">
+      <c r="B748" t="inlineStr">
         <is>
           <t>images/「自分のすることを好きでなきゃ」_img1.jpg</t>
         </is>
       </c>
-      <c r="C749" t="inlineStr">
+      <c r="C748" t="inlineStr">
         <is>
           <t>転職 ,かわいい</t>
         </is>
       </c>
     </row>
-    <row r="750">
-      <c r="A750" t="inlineStr">
+    <row r="749">
+      <c r="A749" t="inlineStr">
         <is>
           <t xml:space="preserve">「この地上に生き甲斐あり」
 على هذه الأرض ما يستحق الحياة
@@ -16207,19 +16187,19 @@
 2308 Mahmoud Gafar </t>
         </is>
       </c>
-      <c r="B750" t="inlineStr">
+      <c r="B749" t="inlineStr">
         <is>
           <t>images/「この地上に生き甲斐あり」_img1.jpg</t>
         </is>
       </c>
-      <c r="C750" t="inlineStr">
+      <c r="C749" t="inlineStr">
         <is>
           <t>詩</t>
         </is>
       </c>
     </row>
-    <row r="751">
-      <c r="A751" t="inlineStr">
+    <row r="750">
+      <c r="A750" t="inlineStr">
         <is>
           <t xml:space="preserve">「オレンジの効能が何か知っていますか？」
 هل تعرف ما هي فوائد البرتقال؟
@@ -16229,19 +16209,19 @@
 2308 sadahadhramowt com </t>
         </is>
       </c>
-      <c r="B751" t="inlineStr">
+      <c r="B750" t="inlineStr">
         <is>
           <t>images/「オレンジの効能が何か知っていますか？_img1.jpg</t>
         </is>
       </c>
-      <c r="C751" t="inlineStr">
+      <c r="C750" t="inlineStr">
         <is>
           <t>オレンジ ,フルーツ</t>
         </is>
       </c>
     </row>
-    <row r="752">
-      <c r="A752" t="inlineStr">
+    <row r="751">
+      <c r="A751" t="inlineStr">
         <is>
           <t xml:space="preserve">「遊ぶパンダの光景より可愛いものがありますか？」
 هل هناك ما هو ألطف من مشاهدة الباندا وهي تلعب؟
@@ -16249,19 +16229,19 @@
 2308 https://twitter.com/NatGeoMagArab/status/1494612797858074626 </t>
         </is>
       </c>
-      <c r="B752" t="inlineStr">
+      <c r="B751" t="inlineStr">
         <is>
           <t>images/「遊ぶパンダの光景より可愛いものがあり_img1.jpg</t>
         </is>
       </c>
-      <c r="C752" t="inlineStr">
+      <c r="C751" t="inlineStr">
         <is>
           <t>パンダ ,モコモコ</t>
         </is>
       </c>
     </row>
-    <row r="753">
-      <c r="A753" t="inlineStr">
+    <row r="752">
+      <c r="A752" t="inlineStr">
         <is>
           <t xml:space="preserve">「大事なのは何者だったかじゃない。何者になるかだ」
 ليسَ المُهم ما كُنتَ بل مَا ستكون
@@ -16270,19 +16250,19 @@
 2308 出典不明 </t>
         </is>
       </c>
-      <c r="B753" t="inlineStr">
+      <c r="B752" t="inlineStr">
         <is>
           <t>images/「大事なのは何者だったかじゃない。何者_img1.jpg</t>
         </is>
       </c>
-      <c r="C753" t="inlineStr">
+      <c r="C752" t="inlineStr">
         <is>
           <t>自己実現 ,存在価値</t>
         </is>
       </c>
     </row>
-    <row r="754">
-      <c r="A754" t="inlineStr">
+    <row r="753">
+      <c r="A753" t="inlineStr">
         <is>
           <t xml:space="preserve">「あなたであれ。ありのままが美しいから」
 كُنْ أَنْتَ لأنك جميل كما أنت
@@ -16291,19 +16271,19 @@
 2308 IDREES DESIGN </t>
         </is>
       </c>
-      <c r="B754" t="inlineStr">
+      <c r="B753" t="inlineStr">
         <is>
           <t>images/「あなたであれ。ありのままが美しいから_img1.jpg</t>
         </is>
       </c>
-      <c r="C754" t="inlineStr">
+      <c r="C753" t="inlineStr">
         <is>
           <t>自己肯定 ,BeYourself</t>
         </is>
       </c>
     </row>
-    <row r="755">
-      <c r="A755" t="inlineStr">
+    <row r="754">
+      <c r="A754" t="inlineStr">
         <is>
           <t xml:space="preserve">「恐れの中に生きる者は決して自由になれない」
 من يعش في خوف لن يكون حرا أبدا
@@ -16312,19 +16292,19 @@
 2111 rjeem com </t>
         </is>
       </c>
-      <c r="B755" t="inlineStr">
+      <c r="B754" t="inlineStr">
         <is>
           <t>images/「恐れの中に生きる者は決して自由になれ_img1.jpg,images/ 「恐れの中に生きる者は決して自由になれ_img2.jpg</t>
         </is>
       </c>
-      <c r="C755" t="inlineStr">
+      <c r="C754" t="inlineStr">
         <is>
           <t>勇気 ,壁</t>
         </is>
       </c>
     </row>
-    <row r="756">
-      <c r="A756" t="inlineStr">
+    <row r="755">
+      <c r="A755" t="inlineStr">
         <is>
           <t xml:space="preserve">「己の翼を信じる者は己の重さを案じない」
 من يثق في جناحيه لن يهتم لوزنه
@@ -16333,19 +16313,19 @@
 2308 kmrghani </t>
         </is>
       </c>
-      <c r="B756" t="inlineStr">
+      <c r="B755" t="inlineStr">
         <is>
           <t>images/「己の翼を信じる者は己の重さを案じない_img1.jpg</t>
         </is>
       </c>
-      <c r="C756" t="inlineStr">
+      <c r="C755" t="inlineStr">
         <is>
           <t>自信</t>
         </is>
       </c>
     </row>
-    <row r="757">
-      <c r="A757" t="inlineStr">
+    <row r="756">
+      <c r="A756" t="inlineStr">
         <is>
           <t xml:space="preserve">「珈琲で一番大事な事！誰と飲むか？」
 الأهم من القهوة!! من ستشربها معه؟
@@ -16354,19 +16334,19 @@
 1812 gwid3.tumblr </t>
         </is>
       </c>
-      <c r="B757" t="inlineStr">
+      <c r="B756" t="inlineStr">
         <is>
           <t>images/「珈琲で一番大事な事！誰と飲むか？」_img1.jpg</t>
         </is>
       </c>
-      <c r="C757" t="inlineStr">
+      <c r="C756" t="inlineStr">
         <is>
           <t>コーヒー ,名言</t>
         </is>
       </c>
     </row>
-    <row r="758">
-      <c r="A758" t="inlineStr">
+    <row r="757">
+      <c r="A757" t="inlineStr">
         <is>
           <t xml:space="preserve">「人生は美しい、そう望んだ者には。」
 الحياة جَميلَة .. لمن أراد ذلك
@@ -16376,19 +16356,19 @@
 2109 出典不明 </t>
         </is>
       </c>
-      <c r="B758" t="inlineStr">
+      <c r="B757" t="inlineStr">
         <is>
           <t>images/「人生は美しい、そう望んだ者には。」_img1.jpg</t>
         </is>
       </c>
-      <c r="C758" t="inlineStr">
+      <c r="C757" t="inlineStr">
         <is>
           <t>名言 ,アート</t>
         </is>
       </c>
     </row>
-    <row r="759">
-      <c r="A759" t="inlineStr">
+    <row r="758">
+      <c r="A758" t="inlineStr">
         <is>
           <t xml:space="preserve">「ハム太郎って子を知ってるかい」
 هل تعرفون من هو هامتارو
@@ -16398,19 +16378,19 @@
 2109 </t>
         </is>
       </c>
-      <c r="B759" t="inlineStr">
+      <c r="B758" t="inlineStr">
         <is>
           <t>images/「ハム太郎って子を知ってるかい」_img1.jpg</t>
         </is>
       </c>
-      <c r="C759" t="inlineStr">
+      <c r="C758" t="inlineStr">
         <is>
           <t>オープニング ,ハム太郎</t>
         </is>
       </c>
     </row>
-    <row r="760">
-      <c r="A760" t="inlineStr">
+    <row r="759">
+      <c r="A759" t="inlineStr">
         <is>
           <t xml:space="preserve">「幸せを求める人もいれば、作る人もいる」
 هناك من يبحث عن السعادة وهناك من يصنعها
@@ -16419,19 +16399,19 @@
 2308 hindah tumblr </t>
         </is>
       </c>
-      <c r="B760" t="inlineStr">
+      <c r="B759" t="inlineStr">
         <is>
           <t>images/「幸せを求める人もいれば、作る人もいる_img1.jpg</t>
         </is>
       </c>
-      <c r="C760" t="inlineStr">
+      <c r="C759" t="inlineStr">
         <is>
           <t>幸せ ,名言 ,教訓</t>
         </is>
       </c>
     </row>
-    <row r="761">
-      <c r="A761" t="inlineStr">
+    <row r="760">
+      <c r="A760" t="inlineStr">
         <is>
           <t xml:space="preserve">「明白なるアラブの言葉によって」
 بلسان عربي مبين
@@ -16441,19 +16421,19 @@
 2109 Abdullah Barakat behance </t>
         </is>
       </c>
-      <c r="B761" t="inlineStr">
+      <c r="B760" t="inlineStr">
         <is>
           <t>images/「明白なるアラブの言葉によって」_img1.jpg</t>
         </is>
       </c>
-      <c r="C761" t="inlineStr">
+      <c r="C760" t="inlineStr">
         <is>
           <t>イスラム教 ,神聖</t>
         </is>
       </c>
     </row>
-    <row r="762">
-      <c r="A762" t="inlineStr">
+    <row r="761">
+      <c r="A761" t="inlineStr">
         <is>
           <t xml:space="preserve">「結婚前、結婚後」
 قبل الزواج، بعد الزواج
@@ -16463,19 +16443,19 @@
 2308 出典不明 </t>
         </is>
       </c>
-      <c r="B762" t="inlineStr">
+      <c r="B761" t="inlineStr">
         <is>
           <t>images/「結婚前、結婚後」_img1.jpg</t>
         </is>
       </c>
-      <c r="C762" t="inlineStr">
+      <c r="C761" t="inlineStr">
         <is>
           <t>BeforeAfter ,幸せ太り</t>
         </is>
       </c>
     </row>
-    <row r="763">
-      <c r="A763" t="inlineStr">
+    <row r="762">
+      <c r="A762" t="inlineStr">
         <is>
           <t xml:space="preserve">「驚きの価格で」بسعر رائع
 ビスィアル・ラーイア [bi-si*r raa'i*]
@@ -16484,19 +16464,19 @@
 2109 Jarir Bookstore </t>
         </is>
       </c>
-      <c r="B763" t="inlineStr">
+      <c r="B762" t="inlineStr">
         <is>
           <t>images/「驚きの価格で」_img1.jpg</t>
         </is>
       </c>
-      <c r="C763" t="inlineStr">
+      <c r="C762" t="inlineStr">
         <is>
           <t>広告 ,安値</t>
         </is>
       </c>
     </row>
-    <row r="764">
-      <c r="A764" t="inlineStr">
+    <row r="763">
+      <c r="A763" t="inlineStr">
         <is>
           <t xml:space="preserve">「我が魂と共に」مع نفسي
 マア・ナフスィ [ma*a nafs-iy]
@@ -16505,19 +16485,19 @@
 2110 出典不明 </t>
         </is>
       </c>
-      <c r="B764" t="inlineStr">
+      <c r="B763" t="inlineStr">
         <is>
           <t>images/「我が魂と共に」_img1.jpg</t>
         </is>
       </c>
-      <c r="C764" t="inlineStr">
+      <c r="C763" t="inlineStr">
         <is>
           <t>ソウル ,soul</t>
         </is>
       </c>
     </row>
-    <row r="765">
-      <c r="A765" t="inlineStr">
+    <row r="764">
+      <c r="A764" t="inlineStr">
         <is>
           <t xml:space="preserve">「暗い夜に」في ليلة مظلمة
  [fiy layla(tin) mu_Dhlima(tin)]
@@ -16526,19 +16506,19 @@
 2109 سلسلة الحلزونة </t>
         </is>
